--- a/MOST_ASYMMETRIC.xlsx
+++ b/MOST_ASYMMETRIC.xlsx
@@ -16,18 +16,19 @@
     <sheet name="Incentive Improvers" sheetId="7" state="visible" r:id="rId7"/>
     <sheet name="Insider Conviction" sheetId="8" state="visible" r:id="rId8"/>
     <sheet name="Insider Filing-Time" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet name="Asymmetry Assembly" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet name="Distressed Stub Progress" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet name="Hidden Asset Realisation" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet name="UK Capital Events" sheetId="13" state="visible" r:id="rId13"/>
-    <sheet name="Without Valuation" sheetId="14" state="visible" r:id="rId14"/>
-    <sheet name="Recent 30d" sheetId="15" state="visible" r:id="rId15"/>
-    <sheet name="Foreign Markets" sheetId="16" state="visible" r:id="rId16"/>
-    <sheet name="Turnaround Signal" sheetId="17" state="visible" r:id="rId17"/>
-    <sheet name="Single-Measure Best" sheetId="18" state="visible" r:id="rId18"/>
-    <sheet name="Layer Correlation" sheetId="19" state="visible" r:id="rId19"/>
-    <sheet name="Coverage &amp; Tiers" sheetId="20" state="visible" r:id="rId20"/>
-    <sheet name="Methodology" sheetId="21" state="visible" r:id="rId21"/>
+    <sheet name="MD&amp;A Intent" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="Asymmetry Assembly" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet name="Distressed Stub Progress" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet name="Hidden Asset Realisation" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet name="UK Capital Events" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet name="Without Valuation" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet name="Recent 30d" sheetId="16" state="visible" r:id="rId16"/>
+    <sheet name="Foreign Markets" sheetId="17" state="visible" r:id="rId17"/>
+    <sheet name="Turnaround Signal" sheetId="18" state="visible" r:id="rId18"/>
+    <sheet name="Single-Measure Best" sheetId="19" state="visible" r:id="rId19"/>
+    <sheet name="Layer Correlation" sheetId="20" state="visible" r:id="rId20"/>
+    <sheet name="Coverage &amp; Tiers" sheetId="21" state="visible" r:id="rId21"/>
+    <sheet name="Methodology" sheetId="22" state="visible" r:id="rId22"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Titles" localSheetId="0">'Contents'!$1:$4</definedName>
@@ -39,18 +40,19 @@
     <definedName name="_xlnm.Print_Titles" localSheetId="6">'Incentive Improvers'!$1:$4</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="7">'Insider Conviction'!$1:$4</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="8">'Insider Filing-Time'!$1:$4</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="9">'Asymmetry Assembly'!$1:$4</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="10">'Distressed Stub Progress'!$1:$4</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="11">'Hidden Asset Realisation'!$1:$4</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="12">'UK Capital Events'!$1:$4</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="13">'Without Valuation'!$1:$4</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="14">'Recent 30d'!$1:$4</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="15">'Foreign Markets'!$1:$4</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="16">'Turnaround Signal'!$1:$4</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="17">'Single-Measure Best'!$1:$4</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="18">'Layer Correlation'!$1:$4</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="19">'Coverage &amp; Tiers'!$1:$4</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="20">'Methodology'!$1:$4</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="9">'MD&amp;A Intent'!$1:$4</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="10">'Asymmetry Assembly'!$1:$4</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="11">'Distressed Stub Progress'!$1:$4</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="12">'Hidden Asset Realisation'!$1:$4</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="13">'UK Capital Events'!$1:$4</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="14">'Without Valuation'!$1:$4</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="15">'Recent 30d'!$1:$4</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="16">'Foreign Markets'!$1:$4</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="17">'Turnaround Signal'!$1:$4</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="18">'Single-Measure Best'!$1:$4</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="19">'Layer Correlation'!$1:$4</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="20">'Coverage &amp; Tiers'!$1:$4</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="21">'Methodology'!$1:$4</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -589,7 +591,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:C26"/>
+  <dimension ref="A1:C27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -607,7 +609,7 @@
     <row r="2" ht="18" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Contents — a structural map of the 42-layer universe analysis</t>
+          <t>Contents — a structural map of the 43-layer universe analysis</t>
         </is>
       </c>
       <c r="B2" s="3" t="n"/>
@@ -757,12 +759,12 @@
       </c>
       <c r="B13" s="6" t="inlineStr">
         <is>
-          <t>Asymmetry Assembly</t>
+          <t>MD&amp;A Intent</t>
         </is>
       </c>
       <c r="C13" s="7" t="inlineStr">
         <is>
-          <t>PSIX-recipe conjunction: cheap + inflection + leverage + insider co-occurring.</t>
+          <t>Management's stated agenda from 10-K/10-Q narrative — value-unlock/transformative/capital/governance/strategic.</t>
         </is>
       </c>
     </row>
@@ -772,12 +774,12 @@
       </c>
       <c r="B14" s="9" t="inlineStr">
         <is>
-          <t>Distressed Stub Progress</t>
+          <t>Asymmetry Assembly</t>
         </is>
       </c>
       <c r="C14" s="10" t="inlineStr">
         <is>
-          <t>Finality-gated capital-structure value-unlock events, waterfall-scored.</t>
+          <t>PSIX-recipe conjunction: cheap + inflection + leverage + insider co-occurring.</t>
         </is>
       </c>
     </row>
@@ -787,12 +789,12 @@
       </c>
       <c r="B15" s="6" t="inlineStr">
         <is>
-          <t>Hidden Asset Realisation</t>
+          <t>Distressed Stub Progress</t>
         </is>
       </c>
       <c r="C15" s="7" t="inlineStr">
         <is>
-          <t>Spectrum/rights/RE inside levered stubs with mandatory-prepay debt sweeps (SSP-type).</t>
+          <t>Finality-gated capital-structure value-unlock events, waterfall-scored.</t>
         </is>
       </c>
     </row>
@@ -802,12 +804,12 @@
       </c>
       <c r="B16" s="9" t="inlineStr">
         <is>
-          <t>UK Capital Events</t>
+          <t>Hidden Asset Realisation</t>
         </is>
       </c>
       <c r="C16" s="10" t="inlineStr">
         <is>
-          <t>UK RNS revealed-preference &amp; distressed monitor (separate universe; funds filtered).</t>
+          <t>Spectrum/rights/RE inside levered stubs with mandatory-prepay debt sweeps (SSP-type).</t>
         </is>
       </c>
     </row>
@@ -817,12 +819,12 @@
       </c>
       <c r="B17" s="6" t="inlineStr">
         <is>
-          <t>Without Valuation</t>
+          <t>UK Capital Events</t>
         </is>
       </c>
       <c r="C17" s="7" t="inlineStr">
         <is>
-          <t>Parallel ranking excluding the valuation leg.</t>
+          <t>UK RNS revealed-preference &amp; distressed monitor (separate universe; funds filtered).</t>
         </is>
       </c>
     </row>
@@ -832,12 +834,12 @@
       </c>
       <c r="B18" s="9" t="inlineStr">
         <is>
-          <t>Recent 30d</t>
+          <t>Without Valuation</t>
         </is>
       </c>
       <c r="C18" s="10" t="inlineStr">
         <is>
-          <t>Material incentive events disclosed in the last 30 days.</t>
+          <t>Parallel ranking excluding the valuation leg.</t>
         </is>
       </c>
     </row>
@@ -847,12 +849,12 @@
       </c>
       <c r="B19" s="6" t="inlineStr">
         <is>
-          <t>Foreign Markets</t>
+          <t>Recent 30d</t>
         </is>
       </c>
       <c r="C19" s="7" t="inlineStr">
         <is>
-          <t>Japan TSE PBR&lt;1, Korea Value-Up, UK schemes.</t>
+          <t>Material incentive events disclosed in the last 30 days.</t>
         </is>
       </c>
     </row>
@@ -862,12 +864,12 @@
       </c>
       <c r="B20" s="9" t="inlineStr">
         <is>
-          <t>Turnaround Signal</t>
+          <t>Foreign Markets</t>
         </is>
       </c>
       <c r="C20" s="10" t="inlineStr">
         <is>
-          <t>Bollenbach pattern: turnaround talent into distress.</t>
+          <t>Japan TSE PBR&lt;1, Korea Value-Up, UK schemes.</t>
         </is>
       </c>
     </row>
@@ -877,12 +879,12 @@
       </c>
       <c r="B21" s="6" t="inlineStr">
         <is>
-          <t>Single-Measure Best</t>
+          <t>Turnaround Signal</t>
         </is>
       </c>
       <c r="C21" s="7" t="inlineStr">
         <is>
-          <t>Best in class on each individual signal.</t>
+          <t>Bollenbach pattern: turnaround talent into distress.</t>
         </is>
       </c>
     </row>
@@ -892,12 +894,12 @@
       </c>
       <c r="B22" s="9" t="inlineStr">
         <is>
-          <t>Layer Correlation</t>
+          <t>Single-Measure Best</t>
         </is>
       </c>
       <c r="C22" s="10" t="inlineStr">
         <is>
-          <t>Pairwise layer correlation and effective independence.</t>
+          <t>Best in class on each individual signal.</t>
         </is>
       </c>
     </row>
@@ -907,12 +909,12 @@
       </c>
       <c r="B23" s="6" t="inlineStr">
         <is>
-          <t>Coverage &amp; Tiers</t>
+          <t>Layer Correlation</t>
         </is>
       </c>
       <c r="C23" s="7" t="inlineStr">
         <is>
-          <t>Live per-layer coverage, data age, firing distribution.</t>
+          <t>Pairwise layer correlation and effective independence.</t>
         </is>
       </c>
     </row>
@@ -922,17 +924,32 @@
       </c>
       <c r="B24" s="9" t="inlineStr">
         <is>
+          <t>Coverage &amp; Tiers</t>
+        </is>
+      </c>
+      <c r="C24" s="10" t="inlineStr">
+        <is>
+          <t>Live per-layer coverage, data age, firing distribution.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="16" customHeight="1">
+      <c r="A25" s="5" t="n">
+        <v>21</v>
+      </c>
+      <c r="B25" s="6" t="inlineStr">
+        <is>
           <t>Methodology</t>
         </is>
       </c>
-      <c r="C24" s="10" t="inlineStr">
+      <c r="C25" s="7" t="inlineStr">
         <is>
           <t>How the composite is built, step by step.</t>
         </is>
       </c>
     </row>
-    <row r="26" ht="28" customHeight="1">
-      <c r="A26" s="11" t="inlineStr">
+    <row r="27" ht="28" customHeight="1">
+      <c r="A27" s="11" t="inlineStr">
         <is>
           <t>Generated by build_most_asymmetric_xlsx.py from the live consensus on disk. Every figure in this workbook is computed at build time; nothing is hardcoded. Single typeface (Times New Roman, 10pt); hierarchy by weight and rule only.</t>
         </is>
@@ -941,7 +958,7 @@
   </sheetData>
   <mergeCells count="3">
     <mergeCell ref="A1:C1"/>
-    <mergeCell ref="A26:C26"/>
+    <mergeCell ref="A27:C27"/>
     <mergeCell ref="A2:C2"/>
   </mergeCells>
   <printOptions horizontalCentered="0"/>
@@ -951,6 +968,1818 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:H51"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="9" customWidth="1" min="1" max="1"/>
+    <col width="24" customWidth="1" min="2" max="2"/>
+    <col width="8" customWidth="1" min="3" max="3"/>
+    <col width="6" customWidth="1" min="4" max="4"/>
+    <col width="30" customWidth="1" min="5" max="5"/>
+    <col width="8" customWidth="1" min="6" max="6"/>
+    <col width="8" customWidth="1" min="7" max="7"/>
+    <col width="40" customWidth="1" min="8" max="8"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="26" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>MD&amp;A Intent — management's stated agenda, from the narrative</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="18" customHeight="1">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>EDGAR exact-phrase scan of 10-K / 10-Q MD&amp;A for five families of revealed intent — value-unlock, transformative, capital-policy, governance-action, strategic-action. Rarity-weighted; convergence across families is the signal; negated / safe-harbour uses stripped.</t>
+        </is>
+      </c>
+      <c r="B2" s="3" t="n"/>
+      <c r="C2" s="3" t="n"/>
+      <c r="D2" s="3" t="n"/>
+      <c r="E2" s="3" t="n"/>
+      <c r="F2" s="3" t="n"/>
+      <c r="G2" s="3" t="n"/>
+      <c r="H2" s="3" t="n"/>
+    </row>
+    <row r="3" ht="8" customHeight="1"/>
+    <row r="4" ht="18" customHeight="1">
+      <c r="A4" s="15" t="inlineStr">
+        <is>
+          <t>Ticker</t>
+        </is>
+      </c>
+      <c r="B4" s="15" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="C4" s="4" t="inlineStr">
+        <is>
+          <t>Score</t>
+        </is>
+      </c>
+      <c r="D4" s="4" t="inlineStr">
+        <is>
+          <t>Fam.</t>
+        </is>
+      </c>
+      <c r="E4" s="4" t="inlineStr">
+        <is>
+          <t>Families</t>
+        </is>
+      </c>
+      <c r="F4" s="4" t="inlineStr">
+        <is>
+          <t>Cheap</t>
+        </is>
+      </c>
+      <c r="G4" s="4" t="inlineStr">
+        <is>
+          <t>Small</t>
+        </is>
+      </c>
+      <c r="H4" s="4" t="inlineStr">
+        <is>
+          <t>Key phrases</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="22" customHeight="1">
+      <c r="A5" s="6" t="inlineStr">
+        <is>
+          <t>LEVI</t>
+        </is>
+      </c>
+      <c r="B5" s="7" t="inlineStr">
+        <is>
+          <t>Levi Strauss &amp; Co</t>
+        </is>
+      </c>
+      <c r="C5" s="16" t="n">
+        <v>17</v>
+      </c>
+      <c r="D5" s="16" t="n">
+        <v>3</v>
+      </c>
+      <c r="E5" s="7" t="inlineStr">
+        <is>
+          <t>value unlock, capital policy,</t>
+        </is>
+      </c>
+      <c r="F5" s="7" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="G5" s="7" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="H5" s="7" t="inlineStr">
+        <is>
+          <t>review of strategic alternatives; capital allocation priorit</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="22" customHeight="1">
+      <c r="A6" s="9" t="inlineStr">
+        <is>
+          <t>AVAH</t>
+        </is>
+      </c>
+      <c r="B6" s="10" t="inlineStr">
+        <is>
+          <t>Aveanna Healthcare Holdi</t>
+        </is>
+      </c>
+      <c r="C6" s="17" t="n">
+        <v>22</v>
+      </c>
+      <c r="D6" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="E6" s="10" t="inlineStr">
+        <is>
+          <t>transformative, capital policy</t>
+        </is>
+      </c>
+      <c r="F6" s="10" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="G6" s="10" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="H6" s="10" t="inlineStr">
+        <is>
+          <t>transformative acquisition; reduce our net leverage</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="22" customHeight="1">
+      <c r="A7" s="6" t="inlineStr">
+        <is>
+          <t>BGSF</t>
+        </is>
+      </c>
+      <c r="B7" s="7" t="inlineStr">
+        <is>
+          <t>BGSF, Inc.</t>
+        </is>
+      </c>
+      <c r="C7" s="16" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="D7" s="16" t="n">
+        <v>2</v>
+      </c>
+      <c r="E7" s="7" t="inlineStr">
+        <is>
+          <t>capital policy, value unlock</t>
+        </is>
+      </c>
+      <c r="F7" s="7" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="G7" s="7" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="H7" s="7" t="inlineStr">
+        <is>
+          <t>maximize shareholder value; return capital to shareholders</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="22" customHeight="1">
+      <c r="A8" s="9" t="inlineStr">
+        <is>
+          <t>UNFI</t>
+        </is>
+      </c>
+      <c r="B8" s="10" t="inlineStr">
+        <is>
+          <t>United Natural Foods, In</t>
+        </is>
+      </c>
+      <c r="C8" s="17" t="n">
+        <v>15</v>
+      </c>
+      <c r="D8" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="E8" s="10" t="inlineStr">
+        <is>
+          <t>transformative, capital policy</t>
+        </is>
+      </c>
+      <c r="F8" s="10" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="G8" s="10" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="H8" s="10" t="inlineStr">
+        <is>
+          <t>transformative acquisition; deleveraging</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="22" customHeight="1">
+      <c r="A9" s="6" t="inlineStr">
+        <is>
+          <t>BJRI</t>
+        </is>
+      </c>
+      <c r="B9" s="7" t="inlineStr">
+        <is>
+          <t>BJ's Restaurants, Inc.</t>
+        </is>
+      </c>
+      <c r="C9" s="16" t="n">
+        <v>14</v>
+      </c>
+      <c r="D9" s="16" t="n">
+        <v>2</v>
+      </c>
+      <c r="E9" s="7" t="inlineStr">
+        <is>
+          <t>governance action, capital pol</t>
+        </is>
+      </c>
+      <c r="F9" s="7" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="G9" s="7" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="H9" s="7" t="inlineStr">
+        <is>
+          <t>return of capital to; cooperation agreement</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="22" customHeight="1">
+      <c r="A10" s="9" t="inlineStr">
+        <is>
+          <t>LITS</t>
+        </is>
+      </c>
+      <c r="B10" s="10" t="inlineStr">
+        <is>
+          <t>LITS</t>
+        </is>
+      </c>
+      <c r="C10" s="17" t="n">
+        <v>13</v>
+      </c>
+      <c r="D10" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="E10" s="10" t="inlineStr">
+        <is>
+          <t>value unlock, governance actio</t>
+        </is>
+      </c>
+      <c r="F10" s="10" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="G10" s="10" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="H10" s="10" t="inlineStr">
+        <is>
+          <t>review of strategic alternatives; cooperation agreement</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="22" customHeight="1">
+      <c r="A11" s="6" t="inlineStr">
+        <is>
+          <t>DLX</t>
+        </is>
+      </c>
+      <c r="B11" s="7" t="inlineStr">
+        <is>
+          <t>Deluxe Corporation</t>
+        </is>
+      </c>
+      <c r="C11" s="16" t="n">
+        <v>13</v>
+      </c>
+      <c r="D11" s="16" t="n">
+        <v>2</v>
+      </c>
+      <c r="E11" s="7" t="inlineStr">
+        <is>
+          <t>capital policy, strategic acti</t>
+        </is>
+      </c>
+      <c r="F11" s="7" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="G11" s="7" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="H11" s="7" t="inlineStr">
+        <is>
+          <t>return capital to shareholders; portfolio optimization</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="22" customHeight="1">
+      <c r="A12" s="9" t="inlineStr">
+        <is>
+          <t>PASG</t>
+        </is>
+      </c>
+      <c r="B12" s="10" t="inlineStr">
+        <is>
+          <t>PASG</t>
+        </is>
+      </c>
+      <c r="C12" s="17" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="D12" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="E12" s="10" t="inlineStr">
+        <is>
+          <t>value unlock, strategic action</t>
+        </is>
+      </c>
+      <c r="F12" s="10" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="G12" s="10" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="H12" s="10" t="inlineStr">
+        <is>
+          <t>review of strategic alternatives; maximize shareholder value</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="22" customHeight="1">
+      <c r="A13" s="6" t="inlineStr">
+        <is>
+          <t>NRDE</t>
+        </is>
+      </c>
+      <c r="B13" s="7" t="inlineStr">
+        <is>
+          <t>NRDE</t>
+        </is>
+      </c>
+      <c r="C13" s="16" t="n">
+        <v>10</v>
+      </c>
+      <c r="D13" s="16" t="n">
+        <v>2</v>
+      </c>
+      <c r="E13" s="7" t="inlineStr">
+        <is>
+          <t>strategic action, value unlock</t>
+        </is>
+      </c>
+      <c r="F13" s="7" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="G13" s="7" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="H13" s="7" t="inlineStr">
+        <is>
+          <t>realize the value; sale of the company</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="22" customHeight="1">
+      <c r="A14" s="9" t="inlineStr">
+        <is>
+          <t>CBUS</t>
+        </is>
+      </c>
+      <c r="B14" s="10" t="inlineStr">
+        <is>
+          <t>CBUS</t>
+        </is>
+      </c>
+      <c r="C14" s="17" t="n">
+        <v>10</v>
+      </c>
+      <c r="D14" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="E14" s="10" t="inlineStr">
+        <is>
+          <t>strategic action, value unlock</t>
+        </is>
+      </c>
+      <c r="F14" s="10" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="G14" s="10" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="H14" s="10" t="inlineStr">
+        <is>
+          <t>maximize shareholder value; cost reduction program</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="22" customHeight="1">
+      <c r="A15" s="6" t="inlineStr">
+        <is>
+          <t>LW</t>
+        </is>
+      </c>
+      <c r="B15" s="7" t="inlineStr">
+        <is>
+          <t>Lamb Weston Holdings, In</t>
+        </is>
+      </c>
+      <c r="C15" s="16" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="D15" s="16" t="n">
+        <v>2</v>
+      </c>
+      <c r="E15" s="7" t="inlineStr">
+        <is>
+          <t>capital policy, strategic acti</t>
+        </is>
+      </c>
+      <c r="F15" s="7" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="G15" s="7" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="H15" s="7" t="inlineStr">
+        <is>
+          <t>return capital to shareholders; restructuring plan</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="22" customHeight="1">
+      <c r="A16" s="9" t="inlineStr">
+        <is>
+          <t>TFX</t>
+        </is>
+      </c>
+      <c r="B16" s="10" t="inlineStr">
+        <is>
+          <t>Teleflex Incorporated</t>
+        </is>
+      </c>
+      <c r="C16" s="17" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="D16" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="E16" s="10" t="inlineStr">
+        <is>
+          <t>capital policy, strategic acti</t>
+        </is>
+      </c>
+      <c r="F16" s="10" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="G16" s="10" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="H16" s="10" t="inlineStr">
+        <is>
+          <t>return capital to shareholders; restructuring plan</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="22" customHeight="1">
+      <c r="A17" s="6" t="inlineStr">
+        <is>
+          <t>HLI</t>
+        </is>
+      </c>
+      <c r="B17" s="7" t="inlineStr">
+        <is>
+          <t>HLI</t>
+        </is>
+      </c>
+      <c r="C17" s="16" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="D17" s="16" t="n">
+        <v>2</v>
+      </c>
+      <c r="E17" s="7" t="inlineStr">
+        <is>
+          <t>strategic action, capital poli</t>
+        </is>
+      </c>
+      <c r="F17" s="7" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="G17" s="7" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="H17" s="7" t="inlineStr">
+        <is>
+          <t>deleveraging; sale of the company</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="22" customHeight="1">
+      <c r="A18" s="9" t="inlineStr">
+        <is>
+          <t>LHX</t>
+        </is>
+      </c>
+      <c r="B18" s="10" t="inlineStr">
+        <is>
+          <t>L3Harris Technologies, I</t>
+        </is>
+      </c>
+      <c r="C18" s="17" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="D18" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="E18" s="10" t="inlineStr">
+        <is>
+          <t>strategic action, value unlock</t>
+        </is>
+      </c>
+      <c r="F18" s="10" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="G18" s="10" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="H18" s="10" t="inlineStr">
+        <is>
+          <t>monetization of; portfolio optimization</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="22" customHeight="1">
+      <c r="A19" s="6" t="inlineStr">
+        <is>
+          <t>CD</t>
+        </is>
+      </c>
+      <c r="B19" s="7" t="inlineStr">
+        <is>
+          <t>CD</t>
+        </is>
+      </c>
+      <c r="C19" s="16" t="n">
+        <v>8</v>
+      </c>
+      <c r="D19" s="16" t="n">
+        <v>2</v>
+      </c>
+      <c r="E19" s="7" t="inlineStr">
+        <is>
+          <t>capital policy, strategic acti</t>
+        </is>
+      </c>
+      <c r="F19" s="7" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="G19" s="7" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="H19" s="7" t="inlineStr">
+        <is>
+          <t>capital allocation priorities; wind down</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="22" customHeight="1">
+      <c r="A20" s="9" t="inlineStr">
+        <is>
+          <t>EQS</t>
+        </is>
+      </c>
+      <c r="B20" s="10" t="inlineStr">
+        <is>
+          <t>EQS</t>
+        </is>
+      </c>
+      <c r="C20" s="17" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="D20" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="E20" s="10" t="inlineStr">
+        <is>
+          <t>transformative, value unlock</t>
+        </is>
+      </c>
+      <c r="F20" s="10" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="G20" s="10" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="H20" s="10" t="inlineStr">
+        <is>
+          <t>exploring strategic alternatives; transformative transaction [neg]</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="22" customHeight="1">
+      <c r="A21" s="6" t="inlineStr">
+        <is>
+          <t>SCTH</t>
+        </is>
+      </c>
+      <c r="B21" s="7" t="inlineStr">
+        <is>
+          <t>SCTH</t>
+        </is>
+      </c>
+      <c r="C21" s="16" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="D21" s="16" t="n">
+        <v>2</v>
+      </c>
+      <c r="E21" s="7" t="inlineStr">
+        <is>
+          <t>value unlock, strategic action</t>
+        </is>
+      </c>
+      <c r="F21" s="7" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="G21" s="7" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="H21" s="7" t="inlineStr">
+        <is>
+          <t>unlock shareholder value; portfolio optimization [neg]</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="22" customHeight="1">
+      <c r="A22" s="9" t="inlineStr">
+        <is>
+          <t>WKC</t>
+        </is>
+      </c>
+      <c r="B22" s="10" t="inlineStr">
+        <is>
+          <t>World Kinect Corporation</t>
+        </is>
+      </c>
+      <c r="C22" s="17" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="D22" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="E22" s="10" t="inlineStr">
+        <is>
+          <t>value unlock, strategic action</t>
+        </is>
+      </c>
+      <c r="F22" s="10" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="G22" s="10" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="H22" s="10" t="inlineStr">
+        <is>
+          <t>realize the value; restructuring plan [neg]</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="22" customHeight="1">
+      <c r="A23" s="6" t="inlineStr">
+        <is>
+          <t>OPTU</t>
+        </is>
+      </c>
+      <c r="B23" s="7" t="inlineStr">
+        <is>
+          <t>Optimum Communications,</t>
+        </is>
+      </c>
+      <c r="C23" s="16" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="D23" s="16" t="n">
+        <v>2</v>
+      </c>
+      <c r="E23" s="7" t="inlineStr">
+        <is>
+          <t>governance action, strategic a</t>
+        </is>
+      </c>
+      <c r="F23" s="7" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="G23" s="7" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="H23" s="7" t="inlineStr">
+        <is>
+          <t>cooperation agreement; sale of the company [neg]</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="22" customHeight="1">
+      <c r="A24" s="9" t="inlineStr">
+        <is>
+          <t>RYAM</t>
+        </is>
+      </c>
+      <c r="B24" s="10" t="inlineStr">
+        <is>
+          <t>Rayonier Advanced Materi</t>
+        </is>
+      </c>
+      <c r="C24" s="17" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="D24" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="E24" s="10" t="inlineStr">
+        <is>
+          <t>value unlock, capital policy</t>
+        </is>
+      </c>
+      <c r="F24" s="10" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="G24" s="10" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="H24" s="10" t="inlineStr">
+        <is>
+          <t>review of strategic alternatives; deleveraging [neg]</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="22" customHeight="1">
+      <c r="A25" s="6" t="inlineStr">
+        <is>
+          <t>HYFM</t>
+        </is>
+      </c>
+      <c r="B25" s="7" t="inlineStr">
+        <is>
+          <t>Hydrofarm Holdings Group</t>
+        </is>
+      </c>
+      <c r="C25" s="16" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="D25" s="16" t="n">
+        <v>2</v>
+      </c>
+      <c r="E25" s="7" t="inlineStr">
+        <is>
+          <t>value unlock, strategic action</t>
+        </is>
+      </c>
+      <c r="F25" s="7" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="G25" s="7" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="H25" s="7" t="inlineStr">
+        <is>
+          <t>exploring strategic alternatives; restructuring plan [neg]</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="22" customHeight="1">
+      <c r="A26" s="9" t="inlineStr">
+        <is>
+          <t>PKOH</t>
+        </is>
+      </c>
+      <c r="B26" s="10" t="inlineStr">
+        <is>
+          <t>PKOH</t>
+        </is>
+      </c>
+      <c r="C26" s="17" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="D26" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="E26" s="10" t="inlineStr">
+        <is>
+          <t>value unlock, strategic action</t>
+        </is>
+      </c>
+      <c r="F26" s="10" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="G26" s="10" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="H26" s="10" t="inlineStr">
+        <is>
+          <t>review of strategic alternatives; portfolio optimization [neg]</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="22" customHeight="1">
+      <c r="A27" s="6" t="inlineStr">
+        <is>
+          <t>COUR</t>
+        </is>
+      </c>
+      <c r="B27" s="7" t="inlineStr">
+        <is>
+          <t>Coursera, Inc.</t>
+        </is>
+      </c>
+      <c r="C27" s="16" t="n">
+        <v>15</v>
+      </c>
+      <c r="D27" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="E27" s="7" t="inlineStr">
+        <is>
+          <t>transformative</t>
+        </is>
+      </c>
+      <c r="F27" s="7" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="G27" s="7" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="H27" s="7" t="inlineStr">
+        <is>
+          <t>transformational transaction</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="22" customHeight="1">
+      <c r="A28" s="9" t="inlineStr">
+        <is>
+          <t>GORO</t>
+        </is>
+      </c>
+      <c r="B28" s="10" t="inlineStr">
+        <is>
+          <t>Gold Resource Corporatio</t>
+        </is>
+      </c>
+      <c r="C28" s="17" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="D28" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="E28" s="10" t="inlineStr">
+        <is>
+          <t>value unlock</t>
+        </is>
+      </c>
+      <c r="F28" s="10" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="G28" s="10" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="H28" s="10" t="inlineStr">
+        <is>
+          <t>review of strategic alternatives; unlock the value; maximize</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="22" customHeight="1">
+      <c r="A29" s="6" t="inlineStr">
+        <is>
+          <t>TBPH</t>
+        </is>
+      </c>
+      <c r="B29" s="7" t="inlineStr">
+        <is>
+          <t>Theravance Biopharma, In</t>
+        </is>
+      </c>
+      <c r="C29" s="16" t="n">
+        <v>13</v>
+      </c>
+      <c r="D29" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="E29" s="7" t="inlineStr">
+        <is>
+          <t>value unlock</t>
+        </is>
+      </c>
+      <c r="F29" s="7" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="G29" s="7" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="H29" s="7" t="inlineStr">
+        <is>
+          <t>unlock shareholder value; realize the value; maximize shareh</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="22" customHeight="1">
+      <c r="A30" s="9" t="inlineStr">
+        <is>
+          <t>HLLY</t>
+        </is>
+      </c>
+      <c r="B30" s="10" t="inlineStr">
+        <is>
+          <t>Holley Inc.</t>
+        </is>
+      </c>
+      <c r="C30" s="17" t="n">
+        <v>13</v>
+      </c>
+      <c r="D30" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="E30" s="10" t="inlineStr">
+        <is>
+          <t>strategic action</t>
+        </is>
+      </c>
+      <c r="F30" s="10" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="G30" s="10" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="H30" s="10" t="inlineStr">
+        <is>
+          <t>exit non-core</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="22" customHeight="1">
+      <c r="A31" s="6" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="B31" s="7" t="inlineStr">
+        <is>
+          <t>Macy's Inc</t>
+        </is>
+      </c>
+      <c r="C31" s="16" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="D31" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="E31" s="7" t="inlineStr">
+        <is>
+          <t>value unlock</t>
+        </is>
+      </c>
+      <c r="F31" s="7" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="G31" s="7" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="H31" s="7" t="inlineStr">
+        <is>
+          <t>unlock shareholder value; monetization of</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="22" customHeight="1">
+      <c r="A32" s="9" t="inlineStr">
+        <is>
+          <t>SCYX</t>
+        </is>
+      </c>
+      <c r="B32" s="10" t="inlineStr">
+        <is>
+          <t>SCYNEXIS, Inc.</t>
+        </is>
+      </c>
+      <c r="C32" s="17" t="n">
+        <v>12</v>
+      </c>
+      <c r="D32" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="E32" s="10" t="inlineStr">
+        <is>
+          <t>transformative</t>
+        </is>
+      </c>
+      <c r="F32" s="10" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="G32" s="10" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="H32" s="10" t="inlineStr">
+        <is>
+          <t>transformative acquisition</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="22" customHeight="1">
+      <c r="A33" s="6" t="inlineStr">
+        <is>
+          <t>SENS</t>
+        </is>
+      </c>
+      <c r="B33" s="7" t="inlineStr">
+        <is>
+          <t>Senseonics Holdings, Inc</t>
+        </is>
+      </c>
+      <c r="C33" s="16" t="n">
+        <v>12</v>
+      </c>
+      <c r="D33" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="E33" s="7" t="inlineStr">
+        <is>
+          <t>transformative</t>
+        </is>
+      </c>
+      <c r="F33" s="7" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="G33" s="7" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="H33" s="7" t="inlineStr">
+        <is>
+          <t>transformative transaction</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="22" customHeight="1">
+      <c r="A34" s="9" t="inlineStr">
+        <is>
+          <t>LE</t>
+        </is>
+      </c>
+      <c r="B34" s="10" t="inlineStr">
+        <is>
+          <t>Lands' End, Inc.</t>
+        </is>
+      </c>
+      <c r="C34" s="17" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="D34" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="E34" s="10" t="inlineStr">
+        <is>
+          <t>value unlock</t>
+        </is>
+      </c>
+      <c r="F34" s="10" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="G34" s="10" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="H34" s="10" t="inlineStr">
+        <is>
+          <t>exploring strategic alternatives; maximize shareholder value</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="22" customHeight="1">
+      <c r="A35" s="6" t="inlineStr">
+        <is>
+          <t>COTY</t>
+        </is>
+      </c>
+      <c r="B35" s="7" t="inlineStr">
+        <is>
+          <t>Coty Inc.</t>
+        </is>
+      </c>
+      <c r="C35" s="16" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="D35" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="E35" s="7" t="inlineStr">
+        <is>
+          <t>capital policy</t>
+        </is>
+      </c>
+      <c r="F35" s="7" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="G35" s="7" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="H35" s="7" t="inlineStr">
+        <is>
+          <t>reduce our leverage; deleveraging</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="22" customHeight="1">
+      <c r="A36" s="9" t="inlineStr">
+        <is>
+          <t>FULC</t>
+        </is>
+      </c>
+      <c r="B36" s="10" t="inlineStr">
+        <is>
+          <t>Fulcrum Therapeutics, In</t>
+        </is>
+      </c>
+      <c r="C36" s="17" t="n">
+        <v>11</v>
+      </c>
+      <c r="D36" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="E36" s="10" t="inlineStr">
+        <is>
+          <t>value unlock</t>
+        </is>
+      </c>
+      <c r="F36" s="10" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="G36" s="10" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="H36" s="10" t="inlineStr">
+        <is>
+          <t>review of strategic alternatives</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="22" customHeight="1">
+      <c r="A37" s="6" t="inlineStr">
+        <is>
+          <t>NEUP</t>
+        </is>
+      </c>
+      <c r="B37" s="7" t="inlineStr">
+        <is>
+          <t>Neuphoria Therapeutics I</t>
+        </is>
+      </c>
+      <c r="C37" s="16" t="n">
+        <v>11</v>
+      </c>
+      <c r="D37" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="E37" s="7" t="inlineStr">
+        <is>
+          <t>value unlock</t>
+        </is>
+      </c>
+      <c r="F37" s="7" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="G37" s="7" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="H37" s="7" t="inlineStr">
+        <is>
+          <t>review of strategic alternatives</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="22" customHeight="1">
+      <c r="A38" s="9" t="inlineStr">
+        <is>
+          <t>AGPU</t>
+        </is>
+      </c>
+      <c r="B38" s="10" t="inlineStr">
+        <is>
+          <t>Axe Compute Inc.</t>
+        </is>
+      </c>
+      <c r="C38" s="17" t="n">
+        <v>11</v>
+      </c>
+      <c r="D38" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="E38" s="10" t="inlineStr">
+        <is>
+          <t>value unlock</t>
+        </is>
+      </c>
+      <c r="F38" s="10" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="G38" s="10" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="H38" s="10" t="inlineStr">
+        <is>
+          <t>exploring strategic alternatives</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="22" customHeight="1">
+      <c r="A39" s="6" t="inlineStr">
+        <is>
+          <t>CMTL</t>
+        </is>
+      </c>
+      <c r="B39" s="7" t="inlineStr">
+        <is>
+          <t>Comtech Telecommunicatio</t>
+        </is>
+      </c>
+      <c r="C39" s="16" t="n">
+        <v>11</v>
+      </c>
+      <c r="D39" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="E39" s="7" t="inlineStr">
+        <is>
+          <t>value unlock</t>
+        </is>
+      </c>
+      <c r="F39" s="7" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="G39" s="7" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="H39" s="7" t="inlineStr">
+        <is>
+          <t>exploring strategic alternatives</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="22" customHeight="1">
+      <c r="A40" s="9" t="inlineStr">
+        <is>
+          <t>HAIN</t>
+        </is>
+      </c>
+      <c r="B40" s="10" t="inlineStr">
+        <is>
+          <t>The Hain Celestial Group</t>
+        </is>
+      </c>
+      <c r="C40" s="17" t="n">
+        <v>11</v>
+      </c>
+      <c r="D40" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="E40" s="10" t="inlineStr">
+        <is>
+          <t>value unlock</t>
+        </is>
+      </c>
+      <c r="F40" s="10" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="G40" s="10" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="H40" s="10" t="inlineStr">
+        <is>
+          <t>exploring strategic alternatives</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="22" customHeight="1">
+      <c r="A41" s="6" t="inlineStr">
+        <is>
+          <t>EGY</t>
+        </is>
+      </c>
+      <c r="B41" s="7" t="inlineStr">
+        <is>
+          <t>VAALCO Energy, Inc.</t>
+        </is>
+      </c>
+      <c r="C41" s="16" t="n">
+        <v>11</v>
+      </c>
+      <c r="D41" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="E41" s="7" t="inlineStr">
+        <is>
+          <t>value unlock</t>
+        </is>
+      </c>
+      <c r="F41" s="7" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="G41" s="7" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="H41" s="7" t="inlineStr">
+        <is>
+          <t>unlock the value</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="22" customHeight="1">
+      <c r="A42" s="9" t="inlineStr">
+        <is>
+          <t>ETN</t>
+        </is>
+      </c>
+      <c r="B42" s="10" t="inlineStr">
+        <is>
+          <t>Eaton Corporation, PLC</t>
+        </is>
+      </c>
+      <c r="C42" s="17" t="n">
+        <v>11</v>
+      </c>
+      <c r="D42" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="E42" s="10" t="inlineStr">
+        <is>
+          <t>strategic action</t>
+        </is>
+      </c>
+      <c r="F42" s="10" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="G42" s="10" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="H42" s="10" t="inlineStr">
+        <is>
+          <t>pursue a spin-off; planned separation</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="22" customHeight="1">
+      <c r="A43" s="6" t="inlineStr">
+        <is>
+          <t>HUN</t>
+        </is>
+      </c>
+      <c r="B43" s="7" t="inlineStr">
+        <is>
+          <t>Huntsman Corporation</t>
+        </is>
+      </c>
+      <c r="C43" s="16" t="n">
+        <v>11</v>
+      </c>
+      <c r="D43" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="E43" s="7" t="inlineStr">
+        <is>
+          <t>strategic action</t>
+        </is>
+      </c>
+      <c r="F43" s="7" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="G43" s="7" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="H43" s="7" t="inlineStr">
+        <is>
+          <t>planned separation</t>
+        </is>
+      </c>
+    </row>
+    <row r="44" ht="22" customHeight="1">
+      <c r="A44" s="9" t="inlineStr">
+        <is>
+          <t>USAR</t>
+        </is>
+      </c>
+      <c r="B44" s="10" t="inlineStr">
+        <is>
+          <t>USA Rare Earth, Inc.</t>
+        </is>
+      </c>
+      <c r="C44" s="17" t="n">
+        <v>10</v>
+      </c>
+      <c r="D44" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="E44" s="10" t="inlineStr">
+        <is>
+          <t>transformative</t>
+        </is>
+      </c>
+      <c r="F44" s="10" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="G44" s="10" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="H44" s="10" t="inlineStr">
+        <is>
+          <t>transformative acquisition; inflection point</t>
+        </is>
+      </c>
+    </row>
+    <row r="45" ht="22" customHeight="1">
+      <c r="A45" s="6" t="inlineStr">
+        <is>
+          <t>TBI</t>
+        </is>
+      </c>
+      <c r="B45" s="7" t="inlineStr">
+        <is>
+          <t>TrueBlue, Inc.</t>
+        </is>
+      </c>
+      <c r="C45" s="16" t="n">
+        <v>10</v>
+      </c>
+      <c r="D45" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="E45" s="7" t="inlineStr">
+        <is>
+          <t>governance action</t>
+        </is>
+      </c>
+      <c r="F45" s="7" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="G45" s="7" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="H45" s="7" t="inlineStr">
+        <is>
+          <t>cooperation agreement</t>
+        </is>
+      </c>
+    </row>
+    <row r="46" ht="22" customHeight="1">
+      <c r="A46" s="9" t="inlineStr">
+        <is>
+          <t>ONL</t>
+        </is>
+      </c>
+      <c r="B46" s="10" t="inlineStr">
+        <is>
+          <t>Orion Properties Inc.</t>
+        </is>
+      </c>
+      <c r="C46" s="17" t="n">
+        <v>10</v>
+      </c>
+      <c r="D46" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="E46" s="10" t="inlineStr">
+        <is>
+          <t>governance action</t>
+        </is>
+      </c>
+      <c r="F46" s="10" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="G46" s="10" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="H46" s="10" t="inlineStr">
+        <is>
+          <t>cooperation agreement</t>
+        </is>
+      </c>
+    </row>
+    <row r="47" ht="22" customHeight="1">
+      <c r="A47" s="6" t="inlineStr">
+        <is>
+          <t>GCO</t>
+        </is>
+      </c>
+      <c r="B47" s="7" t="inlineStr">
+        <is>
+          <t>Genesco Inc.</t>
+        </is>
+      </c>
+      <c r="C47" s="16" t="n">
+        <v>10</v>
+      </c>
+      <c r="D47" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="E47" s="7" t="inlineStr">
+        <is>
+          <t>strategic action</t>
+        </is>
+      </c>
+      <c r="F47" s="7" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="G47" s="7" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="H47" s="7" t="inlineStr">
+        <is>
+          <t>cost reduction program</t>
+        </is>
+      </c>
+    </row>
+    <row r="48" ht="22" customHeight="1">
+      <c r="A48" s="9" t="inlineStr">
+        <is>
+          <t>HOFT</t>
+        </is>
+      </c>
+      <c r="B48" s="10" t="inlineStr">
+        <is>
+          <t>Hooker Furnishings Corpo</t>
+        </is>
+      </c>
+      <c r="C48" s="17" t="n">
+        <v>10</v>
+      </c>
+      <c r="D48" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="E48" s="10" t="inlineStr">
+        <is>
+          <t>strategic action</t>
+        </is>
+      </c>
+      <c r="F48" s="10" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="G48" s="10" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="H48" s="10" t="inlineStr">
+        <is>
+          <t>cost reduction program</t>
+        </is>
+      </c>
+    </row>
+    <row r="49" ht="22" customHeight="1">
+      <c r="A49" s="6" t="inlineStr">
+        <is>
+          <t>KUST</t>
+        </is>
+      </c>
+      <c r="B49" s="7" t="inlineStr">
+        <is>
+          <t>Kustom Entertainment, In</t>
+        </is>
+      </c>
+      <c r="C49" s="16" t="n">
+        <v>10</v>
+      </c>
+      <c r="D49" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="E49" s="7" t="inlineStr">
+        <is>
+          <t>strategic action</t>
+        </is>
+      </c>
+      <c r="F49" s="7" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="G49" s="7" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="H49" s="7" t="inlineStr">
+        <is>
+          <t>cost reduction program</t>
+        </is>
+      </c>
+    </row>
+    <row r="51" ht="28" customHeight="1">
+      <c r="A51" s="11" t="inlineStr">
+        <is>
+          <t>483 names show MD&amp;A intent language (top 45 by family convergence then score); 22 span two or more families. Each phrase is one EDGAR full-text exact-phrase query restricted to 10-K/10-Q, so the population is every filer using that language in the last ~180 days. Phrases are RARITY-weighted — distinctive intent ('sum-of-the-parts', 'transformational transaction', 'pursue a spin-off', 'monetize non-core') scores high; generic language ('deleveraging', 'restructuring plan') is damped when it saturates the result cap, and rewarded mainly on CONVERGENCE (several families on one name = a coordinated agenda). Top candidates are text-verified so NEGATED / safe-harbour uses ('no assurance we will unlock value') are stripped or discounted ([neg]). This layer scores stated INTENT from the narrative, so it leads the event layers (tender/spinoff/buyback/activist) rather than duplicating them. Source: mda_scan.py.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="3">
+    <mergeCell ref="A2:H2"/>
+    <mergeCell ref="A51:H51"/>
+    <mergeCell ref="A1:H1"/>
+  </mergeCells>
+  <printOptions horizontalCentered="0"/>
+  <pageMargins left="0.5" right="0.5" top="0.6" bottom="0.6" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1906,7 +3735,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -3486,7 +5315,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -4981,7 +6810,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -5146,7 +6975,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -5250,7 +7079,7 @@
         <v>5.902</v>
       </c>
       <c r="F5" s="5" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="G5" s="7" t="inlineStr">
         <is>
@@ -5354,7 +7183,7 @@
         <v>5.546</v>
       </c>
       <c r="F8" s="8" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="G8" s="10" t="inlineStr">
         <is>
@@ -5388,7 +7217,7 @@
         <v>5.478</v>
       </c>
       <c r="F9" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G9" s="7" t="inlineStr">
         <is>
@@ -5422,7 +7251,7 @@
         <v>5.452</v>
       </c>
       <c r="F10" s="8" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G10" s="10" t="inlineStr">
         <is>
@@ -5456,7 +7285,7 @@
         <v>5.378</v>
       </c>
       <c r="F11" s="5" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="G11" s="7" t="inlineStr">
         <is>
@@ -5490,7 +7319,7 @@
         <v>4.808</v>
       </c>
       <c r="F12" s="8" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="G12" s="10" t="inlineStr">
         <is>
@@ -5523,10 +7352,8 @@
       <c r="E13" s="16" t="n">
         <v>4.59</v>
       </c>
-      <c r="F13" s="7" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+      <c r="F13" s="5" t="n">
+        <v>1</v>
       </c>
       <c r="G13" s="7" t="inlineStr">
         <is>
@@ -5594,7 +7421,7 @@
         <v>4.416</v>
       </c>
       <c r="F15" s="5" t="n">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="G15" s="7" t="inlineStr">
         <is>
@@ -5627,8 +7454,10 @@
       <c r="E16" s="17" t="n">
         <v>4.12</v>
       </c>
-      <c r="F16" s="8" t="n">
-        <v>11</v>
+      <c r="F16" s="10" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
       <c r="G16" s="10" t="inlineStr">
         <is>
@@ -5662,7 +7491,7 @@
         <v>5.384</v>
       </c>
       <c r="F17" s="5" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="G17" s="7" t="inlineStr">
         <is>
@@ -5696,7 +7525,7 @@
         <v>4.866</v>
       </c>
       <c r="F18" s="21" t="n">
-        <v>52</v>
+        <v>65</v>
       </c>
       <c r="G18" s="10" t="inlineStr">
         <is>
@@ -5730,7 +7559,7 @@
         <v>4.82</v>
       </c>
       <c r="F19" s="5" t="n">
-        <v>-2</v>
+        <v>-10</v>
       </c>
       <c r="G19" s="7" t="inlineStr">
         <is>
@@ -5764,7 +7593,7 @@
         <v>4.816</v>
       </c>
       <c r="F20" s="8" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="G20" s="10" t="inlineStr">
         <is>
@@ -5798,7 +7627,7 @@
         <v>4.762</v>
       </c>
       <c r="F21" s="5" t="n">
-        <v>-2</v>
+        <v>3</v>
       </c>
       <c r="G21" s="7" t="inlineStr">
         <is>
@@ -5832,7 +7661,7 @@
         <v>4.742</v>
       </c>
       <c r="F22" s="8" t="n">
-        <v>10</v>
+        <v>-1</v>
       </c>
       <c r="G22" s="10" t="inlineStr">
         <is>
@@ -5866,7 +7695,7 @@
         <v>4.68</v>
       </c>
       <c r="F23" s="5" t="n">
-        <v>16</v>
+        <v>3</v>
       </c>
       <c r="G23" s="7" t="inlineStr">
         <is>
@@ -5899,10 +7728,8 @@
       <c r="E24" s="17" t="n">
         <v>4.66</v>
       </c>
-      <c r="F24" s="10" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+      <c r="F24" s="8" t="n">
+        <v>5</v>
       </c>
       <c r="G24" s="10" t="inlineStr">
         <is>
@@ -5936,7 +7763,7 @@
         <v>4.562</v>
       </c>
       <c r="F25" s="5" t="n">
-        <v>38</v>
+        <v>15</v>
       </c>
       <c r="G25" s="7" t="inlineStr">
         <is>
@@ -5970,7 +7797,7 @@
         <v>4.556</v>
       </c>
       <c r="F26" s="8" t="n">
-        <v>-15</v>
+        <v>1</v>
       </c>
       <c r="G26" s="10" t="inlineStr">
         <is>
@@ -6004,7 +7831,7 @@
         <v>4.522</v>
       </c>
       <c r="F27" s="5" t="n">
-        <v>-13</v>
+        <v>-15</v>
       </c>
       <c r="G27" s="7" t="inlineStr">
         <is>
@@ -6072,7 +7899,7 @@
         <v>4.466</v>
       </c>
       <c r="F29" s="5" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="G29" s="7" t="inlineStr">
         <is>
@@ -6106,7 +7933,7 @@
         <v>4.348</v>
       </c>
       <c r="F30" s="8" t="n">
-        <v>17</v>
+        <v>26</v>
       </c>
       <c r="G30" s="10" t="inlineStr">
         <is>
@@ -6140,7 +7967,7 @@
         <v>4.344</v>
       </c>
       <c r="F31" s="5" t="n">
-        <v>4</v>
+        <v>21</v>
       </c>
       <c r="G31" s="7" t="inlineStr">
         <is>
@@ -6174,7 +8001,7 @@
         <v>4.26</v>
       </c>
       <c r="F32" s="8" t="n">
-        <v>-20</v>
+        <v>-2</v>
       </c>
       <c r="G32" s="10" t="inlineStr">
         <is>
@@ -6207,8 +8034,8 @@
       <c r="E33" s="16" t="n">
         <v>4.182</v>
       </c>
-      <c r="F33" s="21" t="n">
-        <v>65</v>
+      <c r="F33" s="5" t="n">
+        <v>31</v>
       </c>
       <c r="G33" s="7" t="inlineStr">
         <is>
@@ -6242,7 +8069,7 @@
         <v>4.056</v>
       </c>
       <c r="F34" s="8" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="G34" s="10" t="inlineStr">
         <is>
@@ -6274,7 +8101,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -7990,7 +9817,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -10248,7 +12075,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -12044,7 +13871,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -14604,608 +16431,6 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="1"/>
-  </sheetPr>
-  <dimension ref="A1:D34"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="30" customWidth="1" min="1" max="1"/>
-    <col width="30" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="16" customWidth="1" min="4" max="4"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="26" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Layer Correlation &amp; Independence</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="18" customHeight="1">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>How independent are the scoring layers? Positively correlated layers are not separate confirmations.</t>
-        </is>
-      </c>
-      <c r="B2" s="3" t="n"/>
-      <c r="C2" s="3" t="n"/>
-      <c r="D2" s="3" t="n"/>
-    </row>
-    <row r="3" ht="8" customHeight="1"/>
-    <row r="4">
-      <c r="A4" s="12" t="inlineStr">
-        <is>
-          <t>Raw layers: 39    Effective-independent (rho&gt;0.6): 34</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="18" customHeight="1">
-      <c r="A6" s="4" t="inlineStr">
-        <is>
-          <t>Layer A</t>
-        </is>
-      </c>
-      <c r="B6" s="4" t="inlineStr">
-        <is>
-          <t>Layer B</t>
-        </is>
-      </c>
-      <c r="C6" s="4" t="inlineStr">
-        <is>
-          <t>Spearman</t>
-        </is>
-      </c>
-      <c r="D6" s="4" t="inlineStr">
-        <is>
-          <t>Interpretation</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="16" customHeight="1">
-      <c r="A7" s="7" t="inlineStr">
-        <is>
-          <t>f4_buys</t>
-        </is>
-      </c>
-      <c r="B7" s="7" t="inlineStr">
-        <is>
-          <t>discretionary_conviction</t>
-        </is>
-      </c>
-      <c r="C7" s="16" t="n">
-        <v>0.963</v>
-      </c>
-      <c r="D7" s="7" t="inlineStr">
-        <is>
-          <t>very_high</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="16" customHeight="1">
-      <c r="A8" s="10" t="inlineStr">
-        <is>
-          <t>tender</t>
-        </is>
-      </c>
-      <c r="B8" s="10" t="inlineStr">
-        <is>
-          <t>bumpitrage</t>
-        </is>
-      </c>
-      <c r="C8" s="17" t="n">
-        <v>0.783</v>
-      </c>
-      <c r="D8" s="10" t="inlineStr">
-        <is>
-          <t>very_high</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="16" customHeight="1">
-      <c r="A9" s="7" t="inlineStr">
-        <is>
-          <t>opportunistic</t>
-        </is>
-      </c>
-      <c r="B9" s="7" t="inlineStr">
-        <is>
-          <t>discretionary_conviction</t>
-        </is>
-      </c>
-      <c r="C9" s="16" t="n">
-        <v>0.6850000000000001</v>
-      </c>
-      <c r="D9" s="7" t="inlineStr">
-        <is>
-          <t>very_high</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="16" customHeight="1">
-      <c r="A10" s="10" t="inlineStr">
-        <is>
-          <t>f4_buys</t>
-        </is>
-      </c>
-      <c r="B10" s="10" t="inlineStr">
-        <is>
-          <t>opportunistic</t>
-        </is>
-      </c>
-      <c r="C10" s="17" t="n">
-        <v>0.667</v>
-      </c>
-      <c r="D10" s="10" t="inlineStr">
-        <is>
-          <t>very_high</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="16" customHeight="1">
-      <c r="A11" s="7" t="inlineStr">
-        <is>
-          <t>tender_mech</t>
-        </is>
-      </c>
-      <c r="B11" s="7" t="inlineStr">
-        <is>
-          <t>bumpitrage</t>
-        </is>
-      </c>
-      <c r="C11" s="16" t="n">
-        <v>-0.623</v>
-      </c>
-      <c r="D11" s="7" t="inlineStr">
-        <is>
-          <t>very_high</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="16" customHeight="1">
-      <c r="A12" s="10" t="inlineStr">
-        <is>
-          <t>net_net_ncav</t>
-        </is>
-      </c>
-      <c r="B12" s="10" t="inlineStr">
-        <is>
-          <t>quarterly_10q</t>
-        </is>
-      </c>
-      <c r="C12" s="17" t="n">
-        <v>0.601</v>
-      </c>
-      <c r="D12" s="10" t="inlineStr">
-        <is>
-          <t>very_high</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="16" customHeight="1">
-      <c r="A13" s="7" t="inlineStr">
-        <is>
-          <t>tender</t>
-        </is>
-      </c>
-      <c r="B13" s="7" t="inlineStr">
-        <is>
-          <t>tender_mech</t>
-        </is>
-      </c>
-      <c r="C13" s="16" t="n">
-        <v>-0.598</v>
-      </c>
-      <c r="D13" s="7" t="inlineStr">
-        <is>
-          <t>high</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="16" customHeight="1">
-      <c r="A14" s="10" t="inlineStr">
-        <is>
-          <t>psu</t>
-        </is>
-      </c>
-      <c r="B14" s="10" t="inlineStr">
-        <is>
-          <t>recent_incentive</t>
-        </is>
-      </c>
-      <c r="C14" s="17" t="n">
-        <v>0.574</v>
-      </c>
-      <c r="D14" s="10" t="inlineStr">
-        <is>
-          <t>high</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="16" customHeight="1">
-      <c r="A15" s="7" t="inlineStr">
-        <is>
-          <t>voss_cic</t>
-        </is>
-      </c>
-      <c r="B15" s="7" t="inlineStr">
-        <is>
-          <t>coval_stafford</t>
-        </is>
-      </c>
-      <c r="C15" s="16" t="n">
-        <v>0.513</v>
-      </c>
-      <c r="D15" s="7" t="inlineStr">
-        <is>
-          <t>high</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="16" customHeight="1">
-      <c r="A16" s="10" t="inlineStr">
-        <is>
-          <t>psu</t>
-        </is>
-      </c>
-      <c r="B16" s="10" t="inlineStr">
-        <is>
-          <t>valuation</t>
-        </is>
-      </c>
-      <c r="C16" s="17" t="n">
-        <v>0.477</v>
-      </c>
-      <c r="D16" s="10" t="inlineStr">
-        <is>
-          <t>high</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="16" customHeight="1">
-      <c r="A17" s="7" t="inlineStr">
-        <is>
-          <t>valuation</t>
-        </is>
-      </c>
-      <c r="B17" s="7" t="inlineStr">
-        <is>
-          <t>coval_stafford</t>
-        </is>
-      </c>
-      <c r="C17" s="16" t="n">
-        <v>0.477</v>
-      </c>
-      <c r="D17" s="7" t="inlineStr">
-        <is>
-          <t>high</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="16" customHeight="1">
-      <c r="A18" s="10" t="inlineStr">
-        <is>
-          <t>valuation</t>
-        </is>
-      </c>
-      <c r="B18" s="10" t="inlineStr">
-        <is>
-          <t>recent_incentive</t>
-        </is>
-      </c>
-      <c r="C18" s="17" t="n">
-        <v>0.46</v>
-      </c>
-      <c r="D18" s="10" t="inlineStr">
-        <is>
-          <t>high</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="16" customHeight="1">
-      <c r="A19" s="7" t="inlineStr">
-        <is>
-          <t>recent_incentive</t>
-        </is>
-      </c>
-      <c r="B19" s="7" t="inlineStr">
-        <is>
-          <t>coval_stafford</t>
-        </is>
-      </c>
-      <c r="C19" s="16" t="n">
-        <v>0.43</v>
-      </c>
-      <c r="D19" s="7" t="inlineStr">
-        <is>
-          <t>high</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="16" customHeight="1">
-      <c r="A20" s="10" t="inlineStr">
-        <is>
-          <t>psu</t>
-        </is>
-      </c>
-      <c r="B20" s="10" t="inlineStr">
-        <is>
-          <t>coval_stafford</t>
-        </is>
-      </c>
-      <c r="C20" s="17" t="n">
-        <v>0.419</v>
-      </c>
-      <c r="D20" s="10" t="inlineStr">
-        <is>
-          <t>high</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="16" customHeight="1">
-      <c r="A21" s="7" t="inlineStr">
-        <is>
-          <t>psu</t>
-        </is>
-      </c>
-      <c r="B21" s="7" t="inlineStr">
-        <is>
-          <t>voss_cic</t>
-        </is>
-      </c>
-      <c r="C21" s="16" t="n">
-        <v>0.386</v>
-      </c>
-      <c r="D21" s="7" t="inlineStr">
-        <is>
-          <t>moderate</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="16" customHeight="1">
-      <c r="A22" s="10" t="inlineStr">
-        <is>
-          <t>valuation</t>
-        </is>
-      </c>
-      <c r="B22" s="10" t="inlineStr">
-        <is>
-          <t>net_net_ncav</t>
-        </is>
-      </c>
-      <c r="C22" s="17" t="n">
-        <v>0.342</v>
-      </c>
-      <c r="D22" s="10" t="inlineStr">
-        <is>
-          <t>moderate</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="16" customHeight="1">
-      <c r="A23" s="7" t="inlineStr">
-        <is>
-          <t>recent_incentive</t>
-        </is>
-      </c>
-      <c r="B23" s="7" t="inlineStr">
-        <is>
-          <t>opportunistic</t>
-        </is>
-      </c>
-      <c r="C23" s="16" t="n">
-        <v>0.34</v>
-      </c>
-      <c r="D23" s="7" t="inlineStr">
-        <is>
-          <t>moderate</t>
-        </is>
-      </c>
-    </row>
-    <row r="24" ht="16" customHeight="1">
-      <c r="A24" s="10" t="inlineStr">
-        <is>
-          <t>recent_incentive</t>
-        </is>
-      </c>
-      <c r="B24" s="10" t="inlineStr">
-        <is>
-          <t>special_sits</t>
-        </is>
-      </c>
-      <c r="C24" s="17" t="n">
-        <v>0.301</v>
-      </c>
-      <c r="D24" s="10" t="inlineStr">
-        <is>
-          <t>moderate</t>
-        </is>
-      </c>
-    </row>
-    <row r="25" ht="16" customHeight="1">
-      <c r="A25" s="7" t="inlineStr">
-        <is>
-          <t>recent_incentive</t>
-        </is>
-      </c>
-      <c r="B25" s="7" t="inlineStr">
-        <is>
-          <t>voss_cic</t>
-        </is>
-      </c>
-      <c r="C25" s="16" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="D25" s="7" t="inlineStr">
-        <is>
-          <t>moderate</t>
-        </is>
-      </c>
-    </row>
-    <row r="26" ht="16" customHeight="1">
-      <c r="A26" s="10" t="inlineStr">
-        <is>
-          <t>valuation</t>
-        </is>
-      </c>
-      <c r="B26" s="10" t="inlineStr">
-        <is>
-          <t>voss_cic</t>
-        </is>
-      </c>
-      <c r="C26" s="17" t="n">
-        <v>0.297</v>
-      </c>
-      <c r="D26" s="10" t="inlineStr">
-        <is>
-          <t>moderate</t>
-        </is>
-      </c>
-    </row>
-    <row r="27" ht="16" customHeight="1">
-      <c r="A27" s="7" t="inlineStr">
-        <is>
-          <t>discretionary_conviction</t>
-        </is>
-      </c>
-      <c r="B27" s="7" t="inlineStr">
-        <is>
-          <t>bb_insider_overlay</t>
-        </is>
-      </c>
-      <c r="C27" s="16" t="n">
-        <v>0.279</v>
-      </c>
-      <c r="D27" s="7" t="inlineStr">
-        <is>
-          <t>moderate</t>
-        </is>
-      </c>
-    </row>
-    <row r="28" ht="16" customHeight="1">
-      <c r="A28" s="10" t="inlineStr">
-        <is>
-          <t>post_ch11</t>
-        </is>
-      </c>
-      <c r="B28" s="10" t="inlineStr">
-        <is>
-          <t>equity_committee</t>
-        </is>
-      </c>
-      <c r="C28" s="17" t="n">
-        <v>0.277</v>
-      </c>
-      <c r="D28" s="10" t="inlineStr">
-        <is>
-          <t>moderate</t>
-        </is>
-      </c>
-    </row>
-    <row r="29" ht="16" customHeight="1">
-      <c r="A29" s="7" t="inlineStr">
-        <is>
-          <t>valuation</t>
-        </is>
-      </c>
-      <c r="B29" s="7" t="inlineStr">
-        <is>
-          <t>financial_primary</t>
-        </is>
-      </c>
-      <c r="C29" s="16" t="n">
-        <v>0.275</v>
-      </c>
-      <c r="D29" s="7" t="inlineStr">
-        <is>
-          <t>moderate</t>
-        </is>
-      </c>
-    </row>
-    <row r="30" ht="16" customHeight="1">
-      <c r="A30" s="10" t="inlineStr">
-        <is>
-          <t>f4_buys</t>
-        </is>
-      </c>
-      <c r="B30" s="10" t="inlineStr">
-        <is>
-          <t>bb_insider_overlay</t>
-        </is>
-      </c>
-      <c r="C30" s="17" t="n">
-        <v>0.274</v>
-      </c>
-      <c r="D30" s="10" t="inlineStr">
-        <is>
-          <t>moderate</t>
-        </is>
-      </c>
-    </row>
-    <row r="31" ht="16" customHeight="1">
-      <c r="A31" s="7" t="inlineStr">
-        <is>
-          <t>valuation</t>
-        </is>
-      </c>
-      <c r="B31" s="7" t="inlineStr">
-        <is>
-          <t>quarterly_10q</t>
-        </is>
-      </c>
-      <c r="C31" s="16" t="n">
-        <v>0.265</v>
-      </c>
-      <c r="D31" s="7" t="inlineStr">
-        <is>
-          <t>moderate</t>
-        </is>
-      </c>
-    </row>
-    <row r="32" ht="16" customHeight="1">
-      <c r="A32" s="10" t="inlineStr">
-        <is>
-          <t>psu</t>
-        </is>
-      </c>
-      <c r="B32" s="10" t="inlineStr">
-        <is>
-          <t>buyback</t>
-        </is>
-      </c>
-      <c r="C32" s="17" t="n">
-        <v>0.253</v>
-      </c>
-      <c r="D32" s="10" t="inlineStr">
-        <is>
-          <t>moderate</t>
-        </is>
-      </c>
-    </row>
-    <row r="34" ht="28" customHeight="1">
-      <c r="A34" s="11" t="inlineStr">
-        <is>
-          <t>Spearman rank correlation across the full universe. Pairs above rho 0.6 are folded into a single effective layer for the independence count: PSU + Voss CIC (Voss derives from the PSU plan), the tender family (tender + mechanism + bumpitrage share one source), and Form 4 + opportunistic insiders (one refines the other). A high raw layer-firing count should be read against this: nine layers firing is closer to seven or eight genuinely independent confirmations.</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="4">
-    <mergeCell ref="A1:D1"/>
-    <mergeCell ref="A4:D4"/>
-    <mergeCell ref="A2:D2"/>
-    <mergeCell ref="A34:D34"/>
-  </mergeCells>
-  <printOptions horizontalCentered="0"/>
-  <pageMargins left="0.5" right="0.5" top="0.6" bottom="0.6" header="0.5" footer="0.5"/>
-  <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
-</worksheet>
-</file>
-
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
@@ -15401,7 +16626,7 @@
       </c>
       <c r="E16" s="7" t="inlineStr">
         <is>
-          <t>12 layers firing | cons 10.396</t>
+          <t>12 layers firing | cons 10.214</t>
         </is>
       </c>
     </row>
@@ -15436,12 +16661,12 @@
       </c>
       <c r="B18" s="6" t="inlineStr">
         <is>
-          <t>POOL</t>
+          <t>VSNT</t>
         </is>
       </c>
       <c r="C18" s="7" t="inlineStr">
         <is>
-          <t>POOL</t>
+          <t>VSNT</t>
         </is>
       </c>
       <c r="D18" s="6" t="inlineStr">
@@ -15451,7 +16676,7 @@
       </c>
       <c r="E18" s="7" t="inlineStr">
         <is>
-          <t>11 layers firing | cons 7.906</t>
+          <t>10 layers firing | cons 9.366</t>
         </is>
       </c>
     </row>
@@ -15461,12 +16686,12 @@
       </c>
       <c r="B19" s="9" t="inlineStr">
         <is>
-          <t>VSNT</t>
+          <t>GPK</t>
         </is>
       </c>
       <c r="C19" s="10" t="inlineStr">
         <is>
-          <t>VSNT</t>
+          <t>GPK</t>
         </is>
       </c>
       <c r="D19" s="6" t="inlineStr">
@@ -15476,7 +16701,7 @@
       </c>
       <c r="E19" s="10" t="inlineStr">
         <is>
-          <t>10 layers firing | cons 9.522</t>
+          <t>10 layers firing | cons 8.734</t>
         </is>
       </c>
     </row>
@@ -15486,22 +16711,22 @@
       </c>
       <c r="B20" s="6" t="inlineStr">
         <is>
-          <t>GPK</t>
+          <t>DXC</t>
         </is>
       </c>
       <c r="C20" s="7" t="inlineStr">
         <is>
-          <t>GPK</t>
+          <t>DXC Technology</t>
         </is>
       </c>
       <c r="D20" s="6" t="inlineStr">
         <is>
-          <t>Concentrated 5%+</t>
+          <t>Participation 1-2%</t>
         </is>
       </c>
       <c r="E20" s="7" t="inlineStr">
         <is>
-          <t>10 layers firing | cons 8.424</t>
+          <t>PSU core 40 + buyback + recent-incentive 57% drawdown</t>
         </is>
       </c>
     </row>
@@ -15511,22 +16736,22 @@
       </c>
       <c r="B21" s="9" t="inlineStr">
         <is>
-          <t>FOUR</t>
+          <t>LW</t>
         </is>
       </c>
       <c r="C21" s="10" t="inlineStr">
         <is>
-          <t>FOUR</t>
-        </is>
-      </c>
-      <c r="D21" s="6" t="inlineStr">
-        <is>
-          <t>Concentrated 5%+</t>
+          <t>LW</t>
+        </is>
+      </c>
+      <c r="D21" s="10" t="inlineStr">
+        <is>
+          <t>Material 2-5%</t>
         </is>
       </c>
       <c r="E21" s="10" t="inlineStr">
         <is>
-          <t>10 layers firing | cons 7.96</t>
+          <t>10 layers firing | cons 7.676</t>
         </is>
       </c>
     </row>
@@ -15536,12 +16761,12 @@
       </c>
       <c r="B22" s="6" t="inlineStr">
         <is>
-          <t>VRSK</t>
+          <t>FOUR</t>
         </is>
       </c>
       <c r="C22" s="7" t="inlineStr">
         <is>
-          <t>VRSK</t>
+          <t>FOUR</t>
         </is>
       </c>
       <c r="D22" s="6" t="inlineStr">
@@ -15551,7 +16776,7 @@
       </c>
       <c r="E22" s="7" t="inlineStr">
         <is>
-          <t>10 layers firing | cons 7.288</t>
+          <t>10 layers firing | cons 7.52</t>
         </is>
       </c>
     </row>
@@ -15561,22 +16786,22 @@
       </c>
       <c r="B23" s="9" t="inlineStr">
         <is>
-          <t>OPCH</t>
+          <t>ZTS</t>
         </is>
       </c>
       <c r="C23" s="10" t="inlineStr">
         <is>
-          <t>OPCH</t>
-        </is>
-      </c>
-      <c r="D23" s="6" t="inlineStr">
-        <is>
-          <t>Concentrated 5%+</t>
+          <t>Zoetis</t>
+        </is>
+      </c>
+      <c r="D23" s="10" t="inlineStr">
+        <is>
+          <t>Material 2-5%</t>
         </is>
       </c>
       <c r="E23" s="10" t="inlineStr">
         <is>
-          <t>10 layers firing | cons 7.002</t>
+          <t>F4 cluster + valuation + recent-incentive 60% drawdown</t>
         </is>
       </c>
     </row>
@@ -15586,12 +16811,12 @@
       </c>
       <c r="B24" s="6" t="inlineStr">
         <is>
-          <t>ADT</t>
+          <t>POOL</t>
         </is>
       </c>
       <c r="C24" s="7" t="inlineStr">
         <is>
-          <t>ADT Inc</t>
+          <t>POOL</t>
         </is>
       </c>
       <c r="D24" s="6" t="inlineStr">
@@ -15601,7 +16826,7 @@
       </c>
       <c r="E24" s="7" t="inlineStr">
         <is>
-          <t>Heaviest PSU%LTI in universe (90%) + verified -7.3% shrinkage</t>
+          <t>10 layers firing | cons 7.098</t>
         </is>
       </c>
     </row>
@@ -15611,22 +16836,22 @@
       </c>
       <c r="B25" s="9" t="inlineStr">
         <is>
-          <t>ZTS</t>
+          <t>ADT</t>
         </is>
       </c>
       <c r="C25" s="10" t="inlineStr">
         <is>
-          <t>Zoetis</t>
-        </is>
-      </c>
-      <c r="D25" s="10" t="inlineStr">
-        <is>
-          <t>Material 2-5%</t>
+          <t>ADT Inc</t>
+        </is>
+      </c>
+      <c r="D25" s="6" t="inlineStr">
+        <is>
+          <t>Concentrated 5%+</t>
         </is>
       </c>
       <c r="E25" s="10" t="inlineStr">
         <is>
-          <t>F4 cluster + valuation + recent-incentive 60% drawdown</t>
+          <t>Heaviest PSU%LTI in universe (90%) + verified -7.3% shrinkage</t>
         </is>
       </c>
     </row>
@@ -15651,7 +16876,7 @@
       </c>
       <c r="E26" s="7" t="inlineStr">
         <is>
-          <t>10 layers firing | cons 5.722</t>
+          <t>10 layers firing | cons 6.036</t>
         </is>
       </c>
     </row>
@@ -15661,12 +16886,12 @@
       </c>
       <c r="B27" s="9" t="inlineStr">
         <is>
-          <t>WW</t>
+          <t>VTS</t>
         </is>
       </c>
       <c r="C27" s="10" t="inlineStr">
         <is>
-          <t>WW</t>
+          <t>VTS</t>
         </is>
       </c>
       <c r="D27" s="6" t="inlineStr">
@@ -15676,7 +16901,7 @@
       </c>
       <c r="E27" s="10" t="inlineStr">
         <is>
-          <t>9 layers firing | cons 8.12</t>
+          <t>10 layers firing | cons 5.666</t>
         </is>
       </c>
     </row>
@@ -15686,22 +16911,22 @@
       </c>
       <c r="B28" s="6" t="inlineStr">
         <is>
-          <t>DXC</t>
+          <t>WW</t>
         </is>
       </c>
       <c r="C28" s="7" t="inlineStr">
         <is>
-          <t>DXC Technology</t>
+          <t>WW</t>
         </is>
       </c>
       <c r="D28" s="6" t="inlineStr">
         <is>
-          <t>Participation 1-2%</t>
+          <t>Concentrated 5%+</t>
         </is>
       </c>
       <c r="E28" s="7" t="inlineStr">
         <is>
-          <t>PSU core 40 + buyback + recent-incentive 57% drawdown</t>
+          <t>9 layers firing | cons 8.15</t>
         </is>
       </c>
     </row>
@@ -15711,12 +16936,12 @@
       </c>
       <c r="B29" s="9" t="inlineStr">
         <is>
-          <t>HUBS</t>
+          <t>GO</t>
         </is>
       </c>
       <c r="C29" s="10" t="inlineStr">
         <is>
-          <t>HUBS</t>
+          <t>Grocery Outlet</t>
         </is>
       </c>
       <c r="D29" s="6" t="inlineStr">
@@ -15726,7 +16951,7 @@
       </c>
       <c r="E29" s="10" t="inlineStr">
         <is>
-          <t>9 layers firing | cons 6.956</t>
+          <t>Forward $ targets + Cohen-Malloy 6-buyer cluster</t>
         </is>
       </c>
     </row>
@@ -15736,12 +16961,12 @@
       </c>
       <c r="B30" s="6" t="inlineStr">
         <is>
-          <t>GPGI</t>
+          <t>HUBS</t>
         </is>
       </c>
       <c r="C30" s="7" t="inlineStr">
         <is>
-          <t>GPGI</t>
+          <t>HUBS</t>
         </is>
       </c>
       <c r="D30" s="6" t="inlineStr">
@@ -15751,7 +16976,7 @@
       </c>
       <c r="E30" s="7" t="inlineStr">
         <is>
-          <t>9 layers firing | cons 6.82</t>
+          <t>9 layers firing | cons 7.086</t>
         </is>
       </c>
     </row>
@@ -15761,12 +16986,12 @@
       </c>
       <c r="B31" s="9" t="inlineStr">
         <is>
-          <t>OLED</t>
+          <t>HFFG</t>
         </is>
       </c>
       <c r="C31" s="10" t="inlineStr">
         <is>
-          <t>Universal Display</t>
+          <t>HF Foods Group</t>
         </is>
       </c>
       <c r="D31" s="6" t="inlineStr">
@@ -15776,7 +17001,7 @@
       </c>
       <c r="E31" s="10" t="inlineStr">
         <is>
-          <t>PSU + F4 cluster + recent-incentive 60% drawdown</t>
+          <t>Triple PSU $ hurdle (rev/EBITDA/FCF) + clawback strengthened + 4-buyer F4 cluster</t>
         </is>
       </c>
     </row>
@@ -15786,12 +17011,12 @@
       </c>
       <c r="B32" s="6" t="inlineStr">
         <is>
-          <t>PAR</t>
+          <t>SNBR</t>
         </is>
       </c>
       <c r="C32" s="7" t="inlineStr">
         <is>
-          <t>PAR</t>
+          <t>SNBR</t>
         </is>
       </c>
       <c r="D32" s="7" t="inlineStr">
@@ -15801,7 +17026,7 @@
       </c>
       <c r="E32" s="7" t="inlineStr">
         <is>
-          <t>9 layers firing | cons 6.732</t>
+          <t>9 layers firing | cons 7.066</t>
         </is>
       </c>
     </row>
@@ -15811,22 +17036,22 @@
       </c>
       <c r="B33" s="9" t="inlineStr">
         <is>
-          <t>NSP</t>
+          <t>OLED</t>
         </is>
       </c>
       <c r="C33" s="10" t="inlineStr">
         <is>
-          <t>NSP</t>
-        </is>
-      </c>
-      <c r="D33" s="10" t="inlineStr">
-        <is>
-          <t>Material 2-5%</t>
+          <t>Universal Display</t>
+        </is>
+      </c>
+      <c r="D33" s="6" t="inlineStr">
+        <is>
+          <t>Concentrated 5%+</t>
         </is>
       </c>
       <c r="E33" s="10" t="inlineStr">
         <is>
-          <t>9 layers firing | cons 6.644</t>
+          <t>PSU + F4 cluster + recent-incentive 60% drawdown</t>
         </is>
       </c>
     </row>
@@ -15851,7 +17076,7 @@
       </c>
       <c r="E34" s="7" t="inlineStr">
         <is>
-          <t>9 layers firing | cons 6.518</t>
+          <t>9 layers firing | cons 6.916</t>
         </is>
       </c>
     </row>
@@ -15861,12 +17086,12 @@
       </c>
       <c r="B35" s="9" t="inlineStr">
         <is>
-          <t>HDSN</t>
+          <t>GPGI</t>
         </is>
       </c>
       <c r="C35" s="10" t="inlineStr">
         <is>
-          <t>Hudson Technologies</t>
+          <t>GPGI</t>
         </is>
       </c>
       <c r="D35" s="6" t="inlineStr">
@@ -15876,7 +17101,7 @@
       </c>
       <c r="E35" s="10" t="inlineStr">
         <is>
-          <t>Recent F4 cluster + buyback + special-sits + recent-incentive</t>
+          <t>9 layers firing | cons 6.788</t>
         </is>
       </c>
     </row>
@@ -15933,6 +17158,608 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
+  <dimension ref="A1:D34"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="30" customWidth="1" min="1" max="1"/>
+    <col width="30" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="26" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Layer Correlation &amp; Independence</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="18" customHeight="1">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>How independent are the scoring layers? Positively correlated layers are not separate confirmations.</t>
+        </is>
+      </c>
+      <c r="B2" s="3" t="n"/>
+      <c r="C2" s="3" t="n"/>
+      <c r="D2" s="3" t="n"/>
+    </row>
+    <row r="3" ht="8" customHeight="1"/>
+    <row r="4">
+      <c r="A4" s="12" t="inlineStr">
+        <is>
+          <t>Raw layers: 39    Effective-independent (rho&gt;0.6): 34</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="18" customHeight="1">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>Layer A</t>
+        </is>
+      </c>
+      <c r="B6" s="4" t="inlineStr">
+        <is>
+          <t>Layer B</t>
+        </is>
+      </c>
+      <c r="C6" s="4" t="inlineStr">
+        <is>
+          <t>Spearman</t>
+        </is>
+      </c>
+      <c r="D6" s="4" t="inlineStr">
+        <is>
+          <t>Interpretation</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="16" customHeight="1">
+      <c r="A7" s="7" t="inlineStr">
+        <is>
+          <t>f4_buys</t>
+        </is>
+      </c>
+      <c r="B7" s="7" t="inlineStr">
+        <is>
+          <t>discretionary_conviction</t>
+        </is>
+      </c>
+      <c r="C7" s="16" t="n">
+        <v>0.963</v>
+      </c>
+      <c r="D7" s="7" t="inlineStr">
+        <is>
+          <t>very_high</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="16" customHeight="1">
+      <c r="A8" s="10" t="inlineStr">
+        <is>
+          <t>tender</t>
+        </is>
+      </c>
+      <c r="B8" s="10" t="inlineStr">
+        <is>
+          <t>bumpitrage</t>
+        </is>
+      </c>
+      <c r="C8" s="17" t="n">
+        <v>0.783</v>
+      </c>
+      <c r="D8" s="10" t="inlineStr">
+        <is>
+          <t>very_high</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="16" customHeight="1">
+      <c r="A9" s="7" t="inlineStr">
+        <is>
+          <t>opportunistic</t>
+        </is>
+      </c>
+      <c r="B9" s="7" t="inlineStr">
+        <is>
+          <t>discretionary_conviction</t>
+        </is>
+      </c>
+      <c r="C9" s="16" t="n">
+        <v>0.6850000000000001</v>
+      </c>
+      <c r="D9" s="7" t="inlineStr">
+        <is>
+          <t>very_high</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="16" customHeight="1">
+      <c r="A10" s="10" t="inlineStr">
+        <is>
+          <t>f4_buys</t>
+        </is>
+      </c>
+      <c r="B10" s="10" t="inlineStr">
+        <is>
+          <t>opportunistic</t>
+        </is>
+      </c>
+      <c r="C10" s="17" t="n">
+        <v>0.667</v>
+      </c>
+      <c r="D10" s="10" t="inlineStr">
+        <is>
+          <t>very_high</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="16" customHeight="1">
+      <c r="A11" s="7" t="inlineStr">
+        <is>
+          <t>tender_mech</t>
+        </is>
+      </c>
+      <c r="B11" s="7" t="inlineStr">
+        <is>
+          <t>bumpitrage</t>
+        </is>
+      </c>
+      <c r="C11" s="16" t="n">
+        <v>-0.623</v>
+      </c>
+      <c r="D11" s="7" t="inlineStr">
+        <is>
+          <t>very_high</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="16" customHeight="1">
+      <c r="A12" s="10" t="inlineStr">
+        <is>
+          <t>net_net_ncav</t>
+        </is>
+      </c>
+      <c r="B12" s="10" t="inlineStr">
+        <is>
+          <t>quarterly_10q</t>
+        </is>
+      </c>
+      <c r="C12" s="17" t="n">
+        <v>0.601</v>
+      </c>
+      <c r="D12" s="10" t="inlineStr">
+        <is>
+          <t>very_high</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="16" customHeight="1">
+      <c r="A13" s="7" t="inlineStr">
+        <is>
+          <t>tender</t>
+        </is>
+      </c>
+      <c r="B13" s="7" t="inlineStr">
+        <is>
+          <t>tender_mech</t>
+        </is>
+      </c>
+      <c r="C13" s="16" t="n">
+        <v>-0.598</v>
+      </c>
+      <c r="D13" s="7" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="16" customHeight="1">
+      <c r="A14" s="10" t="inlineStr">
+        <is>
+          <t>psu</t>
+        </is>
+      </c>
+      <c r="B14" s="10" t="inlineStr">
+        <is>
+          <t>recent_incentive</t>
+        </is>
+      </c>
+      <c r="C14" s="17" t="n">
+        <v>0.574</v>
+      </c>
+      <c r="D14" s="10" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="16" customHeight="1">
+      <c r="A15" s="7" t="inlineStr">
+        <is>
+          <t>voss_cic</t>
+        </is>
+      </c>
+      <c r="B15" s="7" t="inlineStr">
+        <is>
+          <t>coval_stafford</t>
+        </is>
+      </c>
+      <c r="C15" s="16" t="n">
+        <v>0.513</v>
+      </c>
+      <c r="D15" s="7" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="16" customHeight="1">
+      <c r="A16" s="10" t="inlineStr">
+        <is>
+          <t>psu</t>
+        </is>
+      </c>
+      <c r="B16" s="10" t="inlineStr">
+        <is>
+          <t>valuation</t>
+        </is>
+      </c>
+      <c r="C16" s="17" t="n">
+        <v>0.477</v>
+      </c>
+      <c r="D16" s="10" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="16" customHeight="1">
+      <c r="A17" s="7" t="inlineStr">
+        <is>
+          <t>valuation</t>
+        </is>
+      </c>
+      <c r="B17" s="7" t="inlineStr">
+        <is>
+          <t>coval_stafford</t>
+        </is>
+      </c>
+      <c r="C17" s="16" t="n">
+        <v>0.477</v>
+      </c>
+      <c r="D17" s="7" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="16" customHeight="1">
+      <c r="A18" s="10" t="inlineStr">
+        <is>
+          <t>valuation</t>
+        </is>
+      </c>
+      <c r="B18" s="10" t="inlineStr">
+        <is>
+          <t>recent_incentive</t>
+        </is>
+      </c>
+      <c r="C18" s="17" t="n">
+        <v>0.46</v>
+      </c>
+      <c r="D18" s="10" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="16" customHeight="1">
+      <c r="A19" s="7" t="inlineStr">
+        <is>
+          <t>recent_incentive</t>
+        </is>
+      </c>
+      <c r="B19" s="7" t="inlineStr">
+        <is>
+          <t>coval_stafford</t>
+        </is>
+      </c>
+      <c r="C19" s="16" t="n">
+        <v>0.43</v>
+      </c>
+      <c r="D19" s="7" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="16" customHeight="1">
+      <c r="A20" s="10" t="inlineStr">
+        <is>
+          <t>psu</t>
+        </is>
+      </c>
+      <c r="B20" s="10" t="inlineStr">
+        <is>
+          <t>coval_stafford</t>
+        </is>
+      </c>
+      <c r="C20" s="17" t="n">
+        <v>0.419</v>
+      </c>
+      <c r="D20" s="10" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="16" customHeight="1">
+      <c r="A21" s="7" t="inlineStr">
+        <is>
+          <t>psu</t>
+        </is>
+      </c>
+      <c r="B21" s="7" t="inlineStr">
+        <is>
+          <t>voss_cic</t>
+        </is>
+      </c>
+      <c r="C21" s="16" t="n">
+        <v>0.386</v>
+      </c>
+      <c r="D21" s="7" t="inlineStr">
+        <is>
+          <t>moderate</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="16" customHeight="1">
+      <c r="A22" s="10" t="inlineStr">
+        <is>
+          <t>valuation</t>
+        </is>
+      </c>
+      <c r="B22" s="10" t="inlineStr">
+        <is>
+          <t>net_net_ncav</t>
+        </is>
+      </c>
+      <c r="C22" s="17" t="n">
+        <v>0.342</v>
+      </c>
+      <c r="D22" s="10" t="inlineStr">
+        <is>
+          <t>moderate</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="16" customHeight="1">
+      <c r="A23" s="7" t="inlineStr">
+        <is>
+          <t>recent_incentive</t>
+        </is>
+      </c>
+      <c r="B23" s="7" t="inlineStr">
+        <is>
+          <t>opportunistic</t>
+        </is>
+      </c>
+      <c r="C23" s="16" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="D23" s="7" t="inlineStr">
+        <is>
+          <t>moderate</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="16" customHeight="1">
+      <c r="A24" s="10" t="inlineStr">
+        <is>
+          <t>recent_incentive</t>
+        </is>
+      </c>
+      <c r="B24" s="10" t="inlineStr">
+        <is>
+          <t>special_sits</t>
+        </is>
+      </c>
+      <c r="C24" s="17" t="n">
+        <v>0.301</v>
+      </c>
+      <c r="D24" s="10" t="inlineStr">
+        <is>
+          <t>moderate</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="16" customHeight="1">
+      <c r="A25" s="7" t="inlineStr">
+        <is>
+          <t>recent_incentive</t>
+        </is>
+      </c>
+      <c r="B25" s="7" t="inlineStr">
+        <is>
+          <t>voss_cic</t>
+        </is>
+      </c>
+      <c r="C25" s="16" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="D25" s="7" t="inlineStr">
+        <is>
+          <t>moderate</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="16" customHeight="1">
+      <c r="A26" s="10" t="inlineStr">
+        <is>
+          <t>valuation</t>
+        </is>
+      </c>
+      <c r="B26" s="10" t="inlineStr">
+        <is>
+          <t>voss_cic</t>
+        </is>
+      </c>
+      <c r="C26" s="17" t="n">
+        <v>0.297</v>
+      </c>
+      <c r="D26" s="10" t="inlineStr">
+        <is>
+          <t>moderate</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="16" customHeight="1">
+      <c r="A27" s="7" t="inlineStr">
+        <is>
+          <t>discretionary_conviction</t>
+        </is>
+      </c>
+      <c r="B27" s="7" t="inlineStr">
+        <is>
+          <t>bb_insider_overlay</t>
+        </is>
+      </c>
+      <c r="C27" s="16" t="n">
+        <v>0.279</v>
+      </c>
+      <c r="D27" s="7" t="inlineStr">
+        <is>
+          <t>moderate</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="16" customHeight="1">
+      <c r="A28" s="10" t="inlineStr">
+        <is>
+          <t>post_ch11</t>
+        </is>
+      </c>
+      <c r="B28" s="10" t="inlineStr">
+        <is>
+          <t>equity_committee</t>
+        </is>
+      </c>
+      <c r="C28" s="17" t="n">
+        <v>0.277</v>
+      </c>
+      <c r="D28" s="10" t="inlineStr">
+        <is>
+          <t>moderate</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="16" customHeight="1">
+      <c r="A29" s="7" t="inlineStr">
+        <is>
+          <t>valuation</t>
+        </is>
+      </c>
+      <c r="B29" s="7" t="inlineStr">
+        <is>
+          <t>financial_primary</t>
+        </is>
+      </c>
+      <c r="C29" s="16" t="n">
+        <v>0.275</v>
+      </c>
+      <c r="D29" s="7" t="inlineStr">
+        <is>
+          <t>moderate</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="16" customHeight="1">
+      <c r="A30" s="10" t="inlineStr">
+        <is>
+          <t>f4_buys</t>
+        </is>
+      </c>
+      <c r="B30" s="10" t="inlineStr">
+        <is>
+          <t>bb_insider_overlay</t>
+        </is>
+      </c>
+      <c r="C30" s="17" t="n">
+        <v>0.274</v>
+      </c>
+      <c r="D30" s="10" t="inlineStr">
+        <is>
+          <t>moderate</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="16" customHeight="1">
+      <c r="A31" s="7" t="inlineStr">
+        <is>
+          <t>valuation</t>
+        </is>
+      </c>
+      <c r="B31" s="7" t="inlineStr">
+        <is>
+          <t>quarterly_10q</t>
+        </is>
+      </c>
+      <c r="C31" s="16" t="n">
+        <v>0.265</v>
+      </c>
+      <c r="D31" s="7" t="inlineStr">
+        <is>
+          <t>moderate</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="16" customHeight="1">
+      <c r="A32" s="10" t="inlineStr">
+        <is>
+          <t>psu</t>
+        </is>
+      </c>
+      <c r="B32" s="10" t="inlineStr">
+        <is>
+          <t>buyback</t>
+        </is>
+      </c>
+      <c r="C32" s="17" t="n">
+        <v>0.253</v>
+      </c>
+      <c r="D32" s="10" t="inlineStr">
+        <is>
+          <t>moderate</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="28" customHeight="1">
+      <c r="A34" s="11" t="inlineStr">
+        <is>
+          <t>Spearman rank correlation across the full universe. Pairs above rho 0.6 are folded into a single effective layer for the independence count: PSU + Voss CIC (Voss derives from the PSU plan), the tender family (tender + mechanism + bumpitrage share one source), and Form 4 + opportunistic insiders (one refines the other). A high raw layer-firing count should be read against this: nine layers firing is closer to seven or eight genuinely independent confirmations.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="4">
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A4:D4"/>
+    <mergeCell ref="A2:D2"/>
+    <mergeCell ref="A34:D34"/>
+  </mergeCells>
+  <printOptions horizontalCentered="0"/>
+  <pageMargins left="0.5" right="0.5" top="0.6" bottom="0.6" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
   <dimension ref="A1:F40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -16569,7 +18396,7 @@
         <v>11</v>
       </c>
       <c r="B28" s="16" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C28" s="7" t="inlineStr">
         <is>
@@ -16582,7 +18409,7 @@
         <v>10</v>
       </c>
       <c r="B29" s="17" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="C29" s="10" t="inlineStr">
         <is>
@@ -16595,7 +18422,7 @@
         <v>9</v>
       </c>
       <c r="B30" s="16" t="n">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="C30" s="7" t="inlineStr">
         <is>
@@ -16608,7 +18435,7 @@
         <v>8</v>
       </c>
       <c r="B31" s="17" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="C31" s="10" t="inlineStr">
         <is>
@@ -16621,7 +18448,7 @@
         <v>7</v>
       </c>
       <c r="B32" s="16" t="n">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="C32" s="7" t="inlineStr">
         <is>
@@ -16634,7 +18461,7 @@
         <v>6</v>
       </c>
       <c r="B33" s="17" t="n">
-        <v>75</v>
+        <v>82</v>
       </c>
       <c r="C33" s="10" t="inlineStr">
         <is>
@@ -16647,7 +18474,7 @@
         <v>5</v>
       </c>
       <c r="B34" s="16" t="n">
-        <v>144</v>
+        <v>164</v>
       </c>
       <c r="C34" s="7" t="inlineStr">
         <is>
@@ -16660,7 +18487,7 @@
         <v>4</v>
       </c>
       <c r="B35" s="17" t="n">
-        <v>229</v>
+        <v>236</v>
       </c>
       <c r="C35" s="10" t="inlineStr">
         <is>
@@ -16673,7 +18500,7 @@
         <v>3</v>
       </c>
       <c r="B36" s="16" t="n">
-        <v>413</v>
+        <v>457</v>
       </c>
       <c r="C36" s="7" t="inlineStr">
         <is>
@@ -16686,7 +18513,7 @@
         <v>2</v>
       </c>
       <c r="B37" s="17" t="n">
-        <v>719</v>
+        <v>738</v>
       </c>
       <c r="C37" s="10" t="inlineStr">
         <is>
@@ -16699,7 +18526,7 @@
         <v>1</v>
       </c>
       <c r="B38" s="16" t="n">
-        <v>1195</v>
+        <v>1231</v>
       </c>
       <c r="C38" s="7" t="inlineStr">
         <is>
@@ -16710,7 +18537,7 @@
     <row r="40" ht="28" customHeight="1">
       <c r="A40" s="11" t="inlineStr">
         <is>
-          <t>42 total scoring layers, all additive. Coverage and data age are read live from each layer's source file at build time; no figures are hardcoded. Layers with low coverage (Form 4, 13F-delta, tender) are signal-sparse by design — they fire only on names exhibiting the pattern. The layer-firing distribution is the count of names firing on N independent layers; per the correlation analysis (layer_correlation_pairs.csv) the effective-independent layer count is ~21 of 30 at rho&gt;0.6.</t>
+          <t>43 total scoring layers, all additive. Coverage and data age are read live from each layer's source file at build time; no figures are hardcoded. Layers with low coverage (Form 4, 13F-delta, tender) are signal-sparse by design — they fire only on names exhibiting the pattern. The layer-firing distribution is the count of names firing on N independent layers; per the correlation analysis (layer_correlation_pairs.csv) the effective-independent layer count is ~21 of 30 at rho&gt;0.6.</t>
         </is>
       </c>
     </row>
@@ -16739,7 +18566,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -16813,7 +18640,7 @@
       </c>
       <c r="C6" s="26" t="inlineStr">
         <is>
-          <t>42 additive scoring layers ingested per ticker, spanning PSU forensics, governance, valuation, verified buybacks, tender mechanics, 10b5-1 direction, Form 4 (raw + Cohen-Malloy opportunistic), Form 144, quarterly 10-Q, NCAV, Voss CIC, post-Ch11, internalization, bumpitrage, spinoff timing, Arquitos, Coval-Stafford proxy + real N-PORT, backstopped rights, FDIC dark banks, activist letters, 13F-delta, biotech PDUFA, financial-sector primary, discretionary insider conviction, emergence cross-feed, Sohn pitches, asymmetry assembly (PSIX recipe), distressed-stub progress, premium injections, selective buybacks, hidden-asset realisation, net buyback (diluted-share reduction net of SBC), the Lynch reawakening momentum leg, and the Form 4 filing-TIME signal (off-hours / Friday-evening open-market buys = quiet accumulators followed; market-hours buys = price support, faded).</t>
+          <t>43 additive scoring layers ingested per ticker, spanning PSU forensics, governance, valuation, verified buybacks, tender mechanics, 10b5-1 direction, Form 4 (raw + Cohen-Malloy opportunistic), Form 144, quarterly 10-Q, NCAV, Voss CIC, post-Ch11, internalization, bumpitrage, spinoff timing, Arquitos, Coval-Stafford proxy + real N-PORT, backstopped rights, FDIC dark banks, activist letters, 13F-delta, biotech PDUFA, financial-sector primary, discretionary insider conviction, emergence cross-feed, Sohn pitches, asymmetry assembly (PSIX recipe), distressed-stub progress, premium injections, selective buybacks, hidden-asset realisation, net buyback (diluted-share reduction net of SBC), the Lynch reawakening momentum leg, the Form 4 filing-TIME signal (off-hours / Friday-evening open-market buys = quiet accumulators followed; market-hours buys = price support, faded), and the MD&amp;A intent-language scan (value-unlock / transformative / capital-policy / governance / strategic-action phrasing mined from 10-K/10-Q narrative, negation-verified).</t>
         </is>
       </c>
     </row>
@@ -16888,7 +18715,7 @@
       </c>
       <c r="C11" s="25" t="inlineStr">
         <is>
-          <t>n_layers_firing = how many of the 42 independent layers produce a non-zero score for the ticker. consensus_score = sum of per-layer rank-decay contributions across the universe.</t>
+          <t>n_layers_firing = how many of the 43 independent layers produce a non-zero score for the ticker. consensus_score = sum of per-layer rank-decay contributions across the universe.</t>
         </is>
       </c>
     </row>
@@ -16903,7 +18730,7 @@
       </c>
       <c r="C12" s="26" t="inlineStr">
         <is>
-          <t>Pairwise Spearman correlation (layer_correlation_pairs.csv) collapses 42 raw layers to effective-independent at rho&gt;0.6. Three correlated clusters: PSU+Voss, tender family, F4+opportunistic. 'Fires 9 layers' ≈ 7-8 true confirmations.</t>
+          <t>Pairwise Spearman correlation (layer_correlation_pairs.csv) collapses 43 raw layers to effective-independent at rho&gt;0.6. Three correlated clusters: PSU+Voss, tender family, F4+opportunistic. 'Fires 9 layers' ≈ 7-8 true confirmations.</t>
         </is>
       </c>
     </row>
@@ -17113,7 +18940,7 @@
       </c>
       <c r="H5" s="7" t="inlineStr">
         <is>
-          <t>12 layers firing | cons 10.396</t>
+          <t>12 layers firing | cons 10.214</t>
         </is>
       </c>
       <c r="I5" s="7" t="inlineStr">
@@ -17174,34 +19001,34 @@
     <row r="7" ht="56" customHeight="1">
       <c r="A7" s="6" t="inlineStr">
         <is>
-          <t>POOL</t>
+          <t>VSNT</t>
         </is>
       </c>
       <c r="B7" s="7" t="inlineStr">
         <is>
-          <t>POOL</t>
+          <t>VSNT</t>
         </is>
       </c>
       <c r="C7" s="5" t="n">
-        <v>7252</v>
+        <v>5407</v>
       </c>
       <c r="D7" s="16" t="n">
-        <v>198.99</v>
+        <v>38.21</v>
       </c>
       <c r="E7" s="16" t="n">
-        <v>6.4</v>
+        <v>0.54</v>
       </c>
       <c r="F7" s="5" t="n">
-        <v>26</v>
+        <v>2</v>
       </c>
       <c r="G7" s="7" t="inlineStr">
         <is>
-          <t>fda_phase_milestone</t>
+          <t>spin_separation</t>
         </is>
       </c>
       <c r="H7" s="7" t="inlineStr">
         <is>
-          <t>11 layers firing | cons 7.906</t>
+          <t>10 layers firing | cons 9.366</t>
         </is>
       </c>
       <c r="I7" s="7" t="inlineStr">
@@ -17218,34 +19045,34 @@
     <row r="8" ht="56" customHeight="1">
       <c r="A8" s="9" t="inlineStr">
         <is>
-          <t>VSNT</t>
+          <t>GPK</t>
         </is>
       </c>
       <c r="B8" s="10" t="inlineStr">
         <is>
-          <t>VSNT</t>
+          <t>GPK</t>
         </is>
       </c>
       <c r="C8" s="8" t="n">
-        <v>5407</v>
+        <v>3169</v>
       </c>
       <c r="D8" s="17" t="n">
-        <v>38.21</v>
+        <v>10.71</v>
       </c>
       <c r="E8" s="17" t="n">
-        <v>0.54</v>
+        <v>0.98</v>
       </c>
       <c r="F8" s="8" t="n">
-        <v>2</v>
+        <v>22</v>
       </c>
       <c r="G8" s="10" t="inlineStr">
         <is>
-          <t>spin_separation</t>
+          <t>–</t>
         </is>
       </c>
       <c r="H8" s="10" t="inlineStr">
         <is>
-          <t>10 layers firing | cons 9.522</t>
+          <t>10 layers firing | cons 8.734</t>
         </is>
       </c>
       <c r="I8" s="10" t="inlineStr">
@@ -17262,25 +19089,25 @@
     <row r="9" ht="56" customHeight="1">
       <c r="A9" s="6" t="inlineStr">
         <is>
-          <t>GPK</t>
+          <t>DXC</t>
         </is>
       </c>
       <c r="B9" s="7" t="inlineStr">
         <is>
-          <t>GPK</t>
+          <t>DXC Technology</t>
         </is>
       </c>
       <c r="C9" s="5" t="n">
-        <v>3169</v>
+        <v>1394</v>
       </c>
       <c r="D9" s="16" t="n">
-        <v>10.71</v>
+        <v>8.6</v>
       </c>
       <c r="E9" s="16" t="n">
-        <v>0.98</v>
+        <v>0.48</v>
       </c>
       <c r="F9" s="5" t="n">
-        <v>22</v>
+        <v>50</v>
       </c>
       <c r="G9" s="7" t="inlineStr">
         <is>
@@ -17289,42 +19116,42 @@
       </c>
       <c r="H9" s="7" t="inlineStr">
         <is>
-          <t>10 layers firing | cons 8.424</t>
+          <t>PSU core 40 + buyback + recent-incentive 57% drawdown</t>
         </is>
       </c>
       <c r="I9" s="7" t="inlineStr">
         <is>
-          <t>see proxy_scan + buyback_verify</t>
+          <t>IT services franchise; transformation signal in PSU</t>
         </is>
       </c>
       <c r="J9" s="6" t="inlineStr">
         <is>
-          <t>Concentrated 5%+</t>
+          <t>Participation 1-2%</t>
         </is>
       </c>
     </row>
     <row r="10" ht="56" customHeight="1">
       <c r="A10" s="9" t="inlineStr">
         <is>
-          <t>FOUR</t>
+          <t>LW</t>
         </is>
       </c>
       <c r="B10" s="10" t="inlineStr">
         <is>
-          <t>FOUR</t>
+          <t>LW</t>
         </is>
       </c>
       <c r="C10" s="8" t="n">
-        <v>3906</v>
+        <v>6222</v>
       </c>
       <c r="D10" s="17" t="n">
-        <v>39.4</v>
+        <v>45.06</v>
       </c>
       <c r="E10" s="17" t="n">
-        <v>4.82</v>
+        <v>3.43</v>
       </c>
       <c r="F10" s="8" t="n">
-        <v>35</v>
+        <v>51</v>
       </c>
       <c r="G10" s="10" t="inlineStr">
         <is>
@@ -17333,7 +19160,7 @@
       </c>
       <c r="H10" s="10" t="inlineStr">
         <is>
-          <t>10 layers firing | cons 7.96</t>
+          <t>10 layers firing | cons 7.676</t>
         </is>
       </c>
       <c r="I10" s="10" t="inlineStr">
@@ -17341,34 +19168,34 @@
           <t>see proxy_scan + buyback_verify</t>
         </is>
       </c>
-      <c r="J10" s="6" t="inlineStr">
-        <is>
-          <t>Concentrated 5%+</t>
+      <c r="J10" s="10" t="inlineStr">
+        <is>
+          <t>Material 2-5%</t>
         </is>
       </c>
     </row>
     <row r="11" ht="56" customHeight="1">
       <c r="A11" s="6" t="inlineStr">
         <is>
-          <t>VRSK</t>
+          <t>FOUR</t>
         </is>
       </c>
       <c r="B11" s="7" t="inlineStr">
         <is>
-          <t>VRSK</t>
+          <t>FOUR</t>
         </is>
       </c>
       <c r="C11" s="5" t="n">
-        <v>22772</v>
+        <v>3906</v>
       </c>
       <c r="D11" s="16" t="n">
-        <v>173.8</v>
+        <v>39.4</v>
       </c>
       <c r="E11" s="16" t="n">
-        <v>77.83</v>
+        <v>4.82</v>
       </c>
       <c r="F11" s="5" t="n">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="G11" s="7" t="inlineStr">
         <is>
@@ -17377,7 +19204,7 @@
       </c>
       <c r="H11" s="7" t="inlineStr">
         <is>
-          <t>10 layers firing | cons 7.288</t>
+          <t>10 layers firing | cons 7.52</t>
         </is>
       </c>
       <c r="I11" s="7" t="inlineStr">
@@ -17394,25 +19221,25 @@
     <row r="12" ht="56" customHeight="1">
       <c r="A12" s="9" t="inlineStr">
         <is>
-          <t>OPCH</t>
+          <t>ZTS</t>
         </is>
       </c>
       <c r="B12" s="10" t="inlineStr">
         <is>
-          <t>OPCH</t>
+          <t>Zoetis</t>
         </is>
       </c>
       <c r="C12" s="8" t="n">
-        <v>3453</v>
+        <v>32997</v>
       </c>
       <c r="D12" s="17" t="n">
-        <v>21.99</v>
+        <v>78.70999999999999</v>
       </c>
       <c r="E12" s="17" t="n">
-        <v>2.56</v>
+        <v>10.04</v>
       </c>
       <c r="F12" s="8" t="n">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="G12" s="10" t="inlineStr">
         <is>
@@ -17421,56 +19248,56 @@
       </c>
       <c r="H12" s="10" t="inlineStr">
         <is>
-          <t>10 layers firing | cons 7.002</t>
+          <t>F4 cluster + valuation + recent-incentive 60% drawdown</t>
         </is>
       </c>
       <c r="I12" s="10" t="inlineStr">
         <is>
-          <t>see proxy_scan + buyback_verify</t>
-        </is>
-      </c>
-      <c r="J12" s="6" t="inlineStr">
-        <is>
-          <t>Concentrated 5%+</t>
+          <t>Animal health franchise</t>
+        </is>
+      </c>
+      <c r="J12" s="10" t="inlineStr">
+        <is>
+          <t>Material 2-5%</t>
         </is>
       </c>
     </row>
     <row r="13" ht="56" customHeight="1">
       <c r="A13" s="6" t="inlineStr">
         <is>
-          <t>ADT</t>
+          <t>POOL</t>
         </is>
       </c>
       <c r="B13" s="7" t="inlineStr">
         <is>
-          <t>ADT Inc</t>
+          <t>POOL</t>
         </is>
       </c>
       <c r="C13" s="5" t="n">
-        <v>5004</v>
+        <v>7252</v>
       </c>
       <c r="D13" s="16" t="n">
-        <v>6.58</v>
+        <v>198.99</v>
       </c>
       <c r="E13" s="16" t="n">
-        <v>1.38</v>
+        <v>6.4</v>
       </c>
       <c r="F13" s="5" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G13" s="7" t="inlineStr">
         <is>
-          <t>–</t>
+          <t>fda_phase_milestone</t>
         </is>
       </c>
       <c r="H13" s="7" t="inlineStr">
         <is>
-          <t>Heaviest PSU%LTI in universe (90%) + verified -7.3% shrinkage</t>
+          <t>10 layers firing | cons 7.098</t>
         </is>
       </c>
       <c r="I13" s="7" t="inlineStr">
         <is>
-          <t>Recurring monitoring revenue + verified supply-curve compression</t>
+          <t>see proxy_scan + buyback_verify</t>
         </is>
       </c>
       <c r="J13" s="6" t="inlineStr">
@@ -17482,25 +19309,25 @@
     <row r="14" ht="56" customHeight="1">
       <c r="A14" s="9" t="inlineStr">
         <is>
-          <t>ZTS</t>
+          <t>ADT</t>
         </is>
       </c>
       <c r="B14" s="10" t="inlineStr">
         <is>
-          <t>Zoetis</t>
+          <t>ADT Inc</t>
         </is>
       </c>
       <c r="C14" s="8" t="n">
-        <v>32997</v>
+        <v>5004</v>
       </c>
       <c r="D14" s="17" t="n">
-        <v>78.70999999999999</v>
+        <v>6.58</v>
       </c>
       <c r="E14" s="17" t="n">
-        <v>10.04</v>
+        <v>1.38</v>
       </c>
       <c r="F14" s="8" t="n">
-        <v>8</v>
+        <v>27</v>
       </c>
       <c r="G14" s="10" t="inlineStr">
         <is>
@@ -17509,17 +19336,17 @@
       </c>
       <c r="H14" s="10" t="inlineStr">
         <is>
-          <t>F4 cluster + valuation + recent-incentive 60% drawdown</t>
+          <t>Heaviest PSU%LTI in universe (90%) + verified -7.3% shrinkage</t>
         </is>
       </c>
       <c r="I14" s="10" t="inlineStr">
         <is>
-          <t>Animal health franchise</t>
-        </is>
-      </c>
-      <c r="J14" s="10" t="inlineStr">
-        <is>
-          <t>Material 2-5%</t>
+          <t>Recurring monitoring revenue + verified supply-curve compression</t>
+        </is>
+      </c>
+      <c r="J14" s="6" t="inlineStr">
+        <is>
+          <t>Concentrated 5%+</t>
         </is>
       </c>
     </row>
@@ -17555,7 +19382,7 @@
       </c>
       <c r="H15" s="7" t="inlineStr">
         <is>
-          <t>10 layers firing | cons 5.722</t>
+          <t>10 layers firing | cons 6.036</t>
         </is>
       </c>
       <c r="I15" s="7" t="inlineStr">
@@ -17572,34 +19399,34 @@
     <row r="16" ht="56" customHeight="1">
       <c r="A16" s="9" t="inlineStr">
         <is>
-          <t>WW</t>
+          <t>VTS</t>
         </is>
       </c>
       <c r="B16" s="10" t="inlineStr">
         <is>
-          <t>WW</t>
+          <t>VTS</t>
         </is>
       </c>
       <c r="C16" s="8" t="n">
-        <v>192</v>
+        <v>668</v>
       </c>
       <c r="D16" s="17" t="n">
-        <v>19.2</v>
+        <v>16.01</v>
       </c>
       <c r="E16" s="17" t="n">
-        <v>0.6</v>
+        <v>1.14</v>
       </c>
       <c r="F16" s="8" t="n">
-        <v>34</v>
+        <v>16</v>
       </c>
       <c r="G16" s="10" t="inlineStr">
         <is>
-          <t>chapter11_emergence</t>
+          <t>spin_separation</t>
         </is>
       </c>
       <c r="H16" s="10" t="inlineStr">
         <is>
-          <t>9 layers firing | cons 8.12</t>
+          <t>10 layers firing | cons 5.666</t>
         </is>
       </c>
       <c r="I16" s="10" t="inlineStr">
@@ -17616,69 +19443,69 @@
     <row r="17" ht="56" customHeight="1">
       <c r="A17" s="6" t="inlineStr">
         <is>
-          <t>DXC</t>
+          <t>WW</t>
         </is>
       </c>
       <c r="B17" s="7" t="inlineStr">
         <is>
-          <t>DXC Technology</t>
+          <t>WW</t>
         </is>
       </c>
       <c r="C17" s="5" t="n">
-        <v>1394</v>
+        <v>192</v>
       </c>
       <c r="D17" s="16" t="n">
-        <v>8.6</v>
+        <v>19.2</v>
       </c>
       <c r="E17" s="16" t="n">
-        <v>0.48</v>
+        <v>0.6</v>
       </c>
       <c r="F17" s="5" t="n">
-        <v>50</v>
+        <v>34</v>
       </c>
       <c r="G17" s="7" t="inlineStr">
         <is>
-          <t>–</t>
+          <t>chapter11_emergence</t>
         </is>
       </c>
       <c r="H17" s="7" t="inlineStr">
         <is>
-          <t>PSU core 40 + buyback + recent-incentive 57% drawdown</t>
+          <t>9 layers firing | cons 8.15</t>
         </is>
       </c>
       <c r="I17" s="7" t="inlineStr">
         <is>
-          <t>IT services franchise; transformation signal in PSU</t>
+          <t>see proxy_scan + buyback_verify</t>
         </is>
       </c>
       <c r="J17" s="6" t="inlineStr">
         <is>
-          <t>Participation 1-2%</t>
+          <t>Concentrated 5%+</t>
         </is>
       </c>
     </row>
     <row r="18" ht="56" customHeight="1">
       <c r="A18" s="9" t="inlineStr">
         <is>
-          <t>HUBS</t>
+          <t>GO</t>
         </is>
       </c>
       <c r="B18" s="10" t="inlineStr">
         <is>
-          <t>HUBS</t>
+          <t>Grocery Outlet</t>
         </is>
       </c>
       <c r="C18" s="8" t="n">
-        <v>9011</v>
+        <v>916</v>
       </c>
       <c r="D18" s="17" t="n">
-        <v>176.03</v>
+        <v>9.26</v>
       </c>
       <c r="E18" s="17" t="n">
-        <v>4.58</v>
+        <v>1.13</v>
       </c>
       <c r="F18" s="8" t="n">
-        <v>34</v>
+        <v>69</v>
       </c>
       <c r="G18" s="10" t="inlineStr">
         <is>
@@ -17687,12 +19514,12 @@
       </c>
       <c r="H18" s="10" t="inlineStr">
         <is>
-          <t>9 layers firing | cons 6.956</t>
+          <t>Forward $ targets + Cohen-Malloy 6-buyer cluster</t>
         </is>
       </c>
       <c r="I18" s="10" t="inlineStr">
         <is>
-          <t>see proxy_scan + buyback_verify</t>
+          <t>Discount-grocery defensive base</t>
         </is>
       </c>
       <c r="J18" s="6" t="inlineStr">
@@ -17704,34 +19531,34 @@
     <row r="19" ht="56" customHeight="1">
       <c r="A19" s="6" t="inlineStr">
         <is>
-          <t>GPGI</t>
+          <t>HUBS</t>
         </is>
       </c>
       <c r="B19" s="7" t="inlineStr">
         <is>
-          <t>GPGI</t>
+          <t>HUBS</t>
         </is>
       </c>
       <c r="C19" s="5" t="n">
-        <v>4180</v>
+        <v>9011</v>
       </c>
       <c r="D19" s="16" t="n">
-        <v>14.42</v>
+        <v>176.03</v>
       </c>
       <c r="E19" s="16" t="n">
-        <v>1.34</v>
+        <v>4.58</v>
       </c>
       <c r="F19" s="5" t="n">
-        <v>4</v>
+        <v>34</v>
       </c>
       <c r="G19" s="7" t="inlineStr">
         <is>
-          <t>spin_separation</t>
+          <t>–</t>
         </is>
       </c>
       <c r="H19" s="7" t="inlineStr">
         <is>
-          <t>9 layers firing | cons 6.82</t>
+          <t>9 layers firing | cons 7.086</t>
         </is>
       </c>
       <c r="I19" s="7" t="inlineStr">
@@ -17748,25 +19575,25 @@
     <row r="20" ht="56" customHeight="1">
       <c r="A20" s="9" t="inlineStr">
         <is>
-          <t>OLED</t>
+          <t>HFFG</t>
         </is>
       </c>
       <c r="B20" s="10" t="inlineStr">
         <is>
-          <t>Universal Display</t>
+          <t>HF Foods Group</t>
         </is>
       </c>
       <c r="C20" s="8" t="n">
-        <v>4158</v>
+        <v>101</v>
       </c>
       <c r="D20" s="17" t="n">
-        <v>88.94</v>
+        <v>1.89</v>
       </c>
       <c r="E20" s="17" t="n">
-        <v>2.44</v>
+        <v>0.49</v>
       </c>
       <c r="F20" s="8" t="n">
-        <v>29</v>
+        <v>48</v>
       </c>
       <c r="G20" s="10" t="inlineStr">
         <is>
@@ -17775,12 +19602,12 @@
       </c>
       <c r="H20" s="10" t="inlineStr">
         <is>
-          <t>PSU + F4 cluster + recent-incentive 60% drawdown</t>
+          <t>Triple PSU $ hurdle (rev/EBITDA/FCF) + clawback strengthened + 4-buyer F4 cluster</t>
         </is>
       </c>
       <c r="I20" s="10" t="inlineStr">
         <is>
-          <t>OLED IP moat</t>
+          <t>P/B 0.48 + microcap distributor with hard assets</t>
         </is>
       </c>
       <c r="J20" s="6" t="inlineStr">
@@ -17792,34 +19619,34 @@
     <row r="21" ht="56" customHeight="1">
       <c r="A21" s="6" t="inlineStr">
         <is>
-          <t>PAR</t>
+          <t>SNBR</t>
         </is>
       </c>
       <c r="B21" s="7" t="inlineStr">
         <is>
-          <t>PAR</t>
+          <t>SNBR</t>
         </is>
       </c>
       <c r="C21" s="5" t="n">
-        <v>631</v>
+        <v>5</v>
       </c>
       <c r="D21" s="16" t="n">
-        <v>15.29</v>
+        <v>0.21</v>
       </c>
       <c r="E21" s="16" t="n">
-        <v>0.76</v>
+        <v>-0.01</v>
       </c>
       <c r="F21" s="5" t="n">
-        <v>16</v>
+        <v>43</v>
       </c>
       <c r="G21" s="7" t="inlineStr">
         <is>
-          <t>–</t>
+          <t>ebitda_dollar_target</t>
         </is>
       </c>
       <c r="H21" s="7" t="inlineStr">
         <is>
-          <t>9 layers firing | cons 6.732</t>
+          <t>9 layers firing | cons 7.066</t>
         </is>
       </c>
       <c r="I21" s="7" t="inlineStr">
@@ -17836,44 +19663,44 @@
     <row r="22" ht="56" customHeight="1">
       <c r="A22" s="9" t="inlineStr">
         <is>
-          <t>NSP</t>
+          <t>OLED</t>
         </is>
       </c>
       <c r="B22" s="10" t="inlineStr">
         <is>
-          <t>NSP</t>
+          <t>Universal Display</t>
         </is>
       </c>
       <c r="C22" s="8" t="n">
-        <v>1382</v>
+        <v>4158</v>
       </c>
       <c r="D22" s="17" t="n">
-        <v>36.22</v>
+        <v>88.94</v>
       </c>
       <c r="E22" s="17" t="n">
-        <v>20.64</v>
+        <v>2.44</v>
       </c>
       <c r="F22" s="8" t="n">
-        <v>38</v>
+        <v>29</v>
       </c>
       <c r="G22" s="10" t="inlineStr">
         <is>
-          <t>ebitda_dollar_target</t>
+          <t>revenue_dollar_target</t>
         </is>
       </c>
       <c r="H22" s="10" t="inlineStr">
         <is>
-          <t>9 layers firing | cons 6.644</t>
+          <t>PSU + F4 cluster + recent-incentive 60% drawdown</t>
         </is>
       </c>
       <c r="I22" s="10" t="inlineStr">
         <is>
-          <t>see proxy_scan + buyback_verify</t>
-        </is>
-      </c>
-      <c r="J22" s="10" t="inlineStr">
-        <is>
-          <t>Material 2-5%</t>
+          <t>OLED IP moat</t>
+        </is>
+      </c>
+      <c r="J22" s="6" t="inlineStr">
+        <is>
+          <t>Concentrated 5%+</t>
         </is>
       </c>
     </row>
@@ -17907,7 +19734,7 @@
       </c>
       <c r="H23" s="7" t="inlineStr">
         <is>
-          <t>9 layers firing | cons 6.518</t>
+          <t>9 layers firing | cons 6.916</t>
         </is>
       </c>
       <c r="I23" s="7" t="inlineStr">
@@ -17924,41 +19751,39 @@
     <row r="24" ht="56" customHeight="1">
       <c r="A24" s="9" t="inlineStr">
         <is>
-          <t>HDSN</t>
+          <t>GPGI</t>
         </is>
       </c>
       <c r="B24" s="10" t="inlineStr">
         <is>
-          <t>Hudson Technologies</t>
+          <t>GPGI</t>
         </is>
       </c>
       <c r="C24" s="8" t="n">
-        <v>222</v>
+        <v>4180</v>
       </c>
       <c r="D24" s="17" t="n">
-        <v>5.27</v>
+        <v>14.42</v>
       </c>
       <c r="E24" s="17" t="n">
-        <v>0.93</v>
-      </c>
-      <c r="F24" s="10" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+        <v>1.34</v>
+      </c>
+      <c r="F24" s="8" t="n">
+        <v>4</v>
       </c>
       <c r="G24" s="10" t="inlineStr">
         <is>
-          <t>–</t>
+          <t>spin_separation</t>
         </is>
       </c>
       <c r="H24" s="10" t="inlineStr">
         <is>
-          <t>Recent F4 cluster + buyback + special-sits + recent-incentive</t>
+          <t>9 layers firing | cons 6.788</t>
         </is>
       </c>
       <c r="I24" s="10" t="inlineStr">
         <is>
-          <t>Refrigerant reclaim regulatory moat</t>
+          <t>see proxy_scan + buyback_verify</t>
         </is>
       </c>
       <c r="J24" s="6" t="inlineStr">

--- a/MOST_ASYMMETRIC.xlsx
+++ b/MOST_ASYMMETRIC.xlsx
@@ -19,18 +19,19 @@
     <sheet name="MD&amp;A Intent" sheetId="10" state="visible" r:id="rId10"/>
     <sheet name="Payoff Geometry" sheetId="11" state="visible" r:id="rId11"/>
     <sheet name="Mechanism Gates" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet name="Asymmetry Assembly" sheetId="13" state="visible" r:id="rId13"/>
-    <sheet name="Distressed Stub Progress" sheetId="14" state="visible" r:id="rId14"/>
-    <sheet name="Hidden Asset Realisation" sheetId="15" state="visible" r:id="rId15"/>
-    <sheet name="UK Capital Events" sheetId="16" state="visible" r:id="rId16"/>
-    <sheet name="Without Valuation" sheetId="17" state="visible" r:id="rId17"/>
-    <sheet name="Recent 30d" sheetId="18" state="visible" r:id="rId18"/>
-    <sheet name="Foreign Markets" sheetId="19" state="visible" r:id="rId19"/>
-    <sheet name="Turnaround Signal" sheetId="20" state="visible" r:id="rId20"/>
-    <sheet name="Single-Measure Best" sheetId="21" state="visible" r:id="rId21"/>
-    <sheet name="Layer Correlation" sheetId="22" state="visible" r:id="rId22"/>
-    <sheet name="Coverage &amp; Tiers" sheetId="23" state="visible" r:id="rId23"/>
-    <sheet name="Methodology" sheetId="24" state="visible" r:id="rId24"/>
+    <sheet name="Winners Study" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet name="Asymmetry Assembly" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet name="Distressed Stub Progress" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet name="Hidden Asset Realisation" sheetId="16" state="visible" r:id="rId16"/>
+    <sheet name="UK Capital Events" sheetId="17" state="visible" r:id="rId17"/>
+    <sheet name="Without Valuation" sheetId="18" state="visible" r:id="rId18"/>
+    <sheet name="Recent 30d" sheetId="19" state="visible" r:id="rId19"/>
+    <sheet name="Foreign Markets" sheetId="20" state="visible" r:id="rId20"/>
+    <sheet name="Turnaround Signal" sheetId="21" state="visible" r:id="rId21"/>
+    <sheet name="Single-Measure Best" sheetId="22" state="visible" r:id="rId22"/>
+    <sheet name="Layer Correlation" sheetId="23" state="visible" r:id="rId23"/>
+    <sheet name="Coverage &amp; Tiers" sheetId="24" state="visible" r:id="rId24"/>
+    <sheet name="Methodology" sheetId="25" state="visible" r:id="rId25"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Titles" localSheetId="0">'Contents'!$1:$4</definedName>
@@ -45,18 +46,19 @@
     <definedName name="_xlnm.Print_Titles" localSheetId="9">'MD&amp;A Intent'!$1:$4</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="10">'Payoff Geometry'!$1:$4</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="11">'Mechanism Gates'!$1:$4</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="12">'Asymmetry Assembly'!$1:$4</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="13">'Distressed Stub Progress'!$1:$4</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="14">'Hidden Asset Realisation'!$1:$4</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="15">'UK Capital Events'!$1:$4</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="16">'Without Valuation'!$1:$4</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="17">'Recent 30d'!$1:$4</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="18">'Foreign Markets'!$1:$4</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="19">'Turnaround Signal'!$1:$4</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="20">'Single-Measure Best'!$1:$4</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="21">'Layer Correlation'!$1:$4</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="22">'Coverage &amp; Tiers'!$1:$4</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="23">'Methodology'!$1:$4</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="12">'Winners Study'!$1:$4</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="13">'Asymmetry Assembly'!$1:$4</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="14">'Distressed Stub Progress'!$1:$4</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="15">'Hidden Asset Realisation'!$1:$4</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="16">'UK Capital Events'!$1:$4</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="17">'Without Valuation'!$1:$4</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="18">'Recent 30d'!$1:$4</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="19">'Foreign Markets'!$1:$4</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="20">'Turnaround Signal'!$1:$4</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="21">'Single-Measure Best'!$1:$4</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="22">'Layer Correlation'!$1:$4</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="23">'Coverage &amp; Tiers'!$1:$4</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="24">'Methodology'!$1:$4</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -595,7 +597,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:C29"/>
+  <dimension ref="A1:C30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -808,12 +810,12 @@
       </c>
       <c r="B16" s="9" t="inlineStr">
         <is>
-          <t>Asymmetry Assembly</t>
+          <t>Winners Study</t>
         </is>
       </c>
       <c r="C16" s="10" t="inlineStr">
         <is>
-          <t>PSIX-recipe conjunction: cheap + inflection + leverage + insider co-occurring.</t>
+          <t>What realized 1-year re-raters had in common — feature/sector lifts, with the pre-move-data caveat.</t>
         </is>
       </c>
     </row>
@@ -823,12 +825,12 @@
       </c>
       <c r="B17" s="6" t="inlineStr">
         <is>
-          <t>Distressed Stub Progress</t>
+          <t>Asymmetry Assembly</t>
         </is>
       </c>
       <c r="C17" s="7" t="inlineStr">
         <is>
-          <t>Finality-gated capital-structure value-unlock events, waterfall-scored.</t>
+          <t>PSIX-recipe conjunction: cheap + inflection + leverage + insider co-occurring.</t>
         </is>
       </c>
     </row>
@@ -838,12 +840,12 @@
       </c>
       <c r="B18" s="9" t="inlineStr">
         <is>
-          <t>Hidden Asset Realisation</t>
+          <t>Distressed Stub Progress</t>
         </is>
       </c>
       <c r="C18" s="10" t="inlineStr">
         <is>
-          <t>Spectrum/rights/RE inside levered stubs with mandatory-prepay debt sweeps (SSP-type).</t>
+          <t>Finality-gated capital-structure value-unlock events, waterfall-scored.</t>
         </is>
       </c>
     </row>
@@ -853,12 +855,12 @@
       </c>
       <c r="B19" s="6" t="inlineStr">
         <is>
-          <t>UK Capital Events</t>
+          <t>Hidden Asset Realisation</t>
         </is>
       </c>
       <c r="C19" s="7" t="inlineStr">
         <is>
-          <t>UK RNS revealed-preference &amp; distressed monitor (separate universe; funds filtered).</t>
+          <t>Spectrum/rights/RE inside levered stubs with mandatory-prepay debt sweeps (SSP-type).</t>
         </is>
       </c>
     </row>
@@ -868,12 +870,12 @@
       </c>
       <c r="B20" s="9" t="inlineStr">
         <is>
-          <t>Without Valuation</t>
+          <t>UK Capital Events</t>
         </is>
       </c>
       <c r="C20" s="10" t="inlineStr">
         <is>
-          <t>Parallel ranking excluding the valuation leg.</t>
+          <t>UK RNS revealed-preference &amp; distressed monitor (separate universe; funds filtered).</t>
         </is>
       </c>
     </row>
@@ -883,12 +885,12 @@
       </c>
       <c r="B21" s="6" t="inlineStr">
         <is>
-          <t>Recent 30d</t>
+          <t>Without Valuation</t>
         </is>
       </c>
       <c r="C21" s="7" t="inlineStr">
         <is>
-          <t>Material incentive events disclosed in the last 30 days.</t>
+          <t>Parallel ranking excluding the valuation leg.</t>
         </is>
       </c>
     </row>
@@ -898,12 +900,12 @@
       </c>
       <c r="B22" s="9" t="inlineStr">
         <is>
-          <t>Foreign Markets</t>
+          <t>Recent 30d</t>
         </is>
       </c>
       <c r="C22" s="10" t="inlineStr">
         <is>
-          <t>Japan TSE PBR&lt;1, Korea Value-Up, UK schemes.</t>
+          <t>Material incentive events disclosed in the last 30 days.</t>
         </is>
       </c>
     </row>
@@ -913,12 +915,12 @@
       </c>
       <c r="B23" s="6" t="inlineStr">
         <is>
-          <t>Turnaround Signal</t>
+          <t>Foreign Markets</t>
         </is>
       </c>
       <c r="C23" s="7" t="inlineStr">
         <is>
-          <t>Bollenbach pattern: turnaround talent into distress.</t>
+          <t>Japan TSE PBR&lt;1, Korea Value-Up, UK schemes.</t>
         </is>
       </c>
     </row>
@@ -928,12 +930,12 @@
       </c>
       <c r="B24" s="9" t="inlineStr">
         <is>
-          <t>Single-Measure Best</t>
+          <t>Turnaround Signal</t>
         </is>
       </c>
       <c r="C24" s="10" t="inlineStr">
         <is>
-          <t>Best in class on each individual signal.</t>
+          <t>Bollenbach pattern: turnaround talent into distress.</t>
         </is>
       </c>
     </row>
@@ -943,12 +945,12 @@
       </c>
       <c r="B25" s="6" t="inlineStr">
         <is>
-          <t>Layer Correlation</t>
+          <t>Single-Measure Best</t>
         </is>
       </c>
       <c r="C25" s="7" t="inlineStr">
         <is>
-          <t>Pairwise layer correlation and effective independence.</t>
+          <t>Best in class on each individual signal.</t>
         </is>
       </c>
     </row>
@@ -958,12 +960,12 @@
       </c>
       <c r="B26" s="9" t="inlineStr">
         <is>
-          <t>Coverage &amp; Tiers</t>
+          <t>Layer Correlation</t>
         </is>
       </c>
       <c r="C26" s="10" t="inlineStr">
         <is>
-          <t>Live per-layer coverage, data age, firing distribution.</t>
+          <t>Pairwise layer correlation and effective independence.</t>
         </is>
       </c>
     </row>
@@ -973,17 +975,32 @@
       </c>
       <c r="B27" s="6" t="inlineStr">
         <is>
+          <t>Coverage &amp; Tiers</t>
+        </is>
+      </c>
+      <c r="C27" s="7" t="inlineStr">
+        <is>
+          <t>Live per-layer coverage, data age, firing distribution.</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="16" customHeight="1">
+      <c r="A28" s="8" t="n">
+        <v>24</v>
+      </c>
+      <c r="B28" s="9" t="inlineStr">
+        <is>
           <t>Methodology</t>
         </is>
       </c>
-      <c r="C27" s="7" t="inlineStr">
+      <c r="C28" s="10" t="inlineStr">
         <is>
           <t>How the composite is built, step by step.</t>
         </is>
       </c>
     </row>
-    <row r="29" ht="28" customHeight="1">
-      <c r="A29" s="11" t="inlineStr">
+    <row r="30" ht="28" customHeight="1">
+      <c r="A30" s="11" t="inlineStr">
         <is>
           <t>Generated by build_most_asymmetric_xlsx.py from the live consensus on disk. Every figure in this workbook is computed at build time; nothing is hardcoded. Single typeface (Times New Roman, 10pt); hierarchy by weight and rule only.</t>
         </is>
@@ -992,8 +1009,8 @@
   </sheetData>
   <mergeCells count="3">
     <mergeCell ref="A1:C1"/>
+    <mergeCell ref="A30:C30"/>
     <mergeCell ref="A2:C2"/>
-    <mergeCell ref="A29:C29"/>
   </mergeCells>
   <printOptions horizontalCentered="0"/>
   <pageMargins left="0.5" right="0.5" top="0.6" bottom="0.6" header="0.5" footer="0.5"/>
@@ -6124,6 +6141,535 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
+  <dimension ref="A1:E29"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="26" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="40" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="26" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Winners Study — what realized 1-year re-raters had in common</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="18" customHeight="1">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>52wk high/low &gt;= 2.5 AND price in top 30% of range  |  239 winners of 2717 priced (81 big, &gt;= 4x range).</t>
+        </is>
+      </c>
+      <c r="B2" s="3" t="n"/>
+      <c r="C2" s="3" t="n"/>
+      <c r="D2" s="3" t="n"/>
+      <c r="E2" s="3" t="n"/>
+    </row>
+    <row r="3" ht="8" customHeight="1"/>
+    <row r="4">
+      <c r="A4" s="12" t="inlineStr">
+        <is>
+          <t>FEATURE LIFT (winner-rate / base-rate)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="18" customHeight="1">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>Feature</t>
+        </is>
+      </c>
+      <c r="B5" s="4" t="inlineStr">
+        <is>
+          <t>Winner %</t>
+        </is>
+      </c>
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>Base %</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="inlineStr">
+        <is>
+          <t>Lift</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="inlineStr">
+        <is>
+          <t>Read</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="16" customHeight="1">
+      <c r="A6" s="9" t="inlineStr">
+        <is>
+          <t>mda_intent</t>
+        </is>
+      </c>
+      <c r="B6" s="20" t="n">
+        <v>13</v>
+      </c>
+      <c r="C6" s="20" t="n">
+        <v>10</v>
+      </c>
+      <c r="D6" s="8" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="E6" s="10" t="inlineStr">
+        <is>
+          <t>management intent language — modestly over-represented</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="16" customHeight="1">
+      <c r="A7" s="6" t="inlineStr">
+        <is>
+          <t>hidden_asset</t>
+        </is>
+      </c>
+      <c r="B7" s="19" t="n">
+        <v>5</v>
+      </c>
+      <c r="C7" s="19" t="n">
+        <v>6</v>
+      </c>
+      <c r="D7" s="5" t="n">
+        <v>0.87</v>
+      </c>
+      <c r="E7" s="7" t="inlineStr">
+        <is>
+          <t>asset-realization setup</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="16" customHeight="1">
+      <c r="A8" s="9" t="inlineStr">
+        <is>
+          <t>small_cap</t>
+        </is>
+      </c>
+      <c r="B8" s="20" t="n">
+        <v>37</v>
+      </c>
+      <c r="C8" s="20" t="n">
+        <v>45</v>
+      </c>
+      <c r="D8" s="8" t="n">
+        <v>0.82</v>
+      </c>
+      <c r="E8" s="10" t="inlineStr">
+        <is>
+          <t>size</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="16" customHeight="1">
+      <c r="A9" s="6" t="inlineStr">
+        <is>
+          <t>micro_cap</t>
+        </is>
+      </c>
+      <c r="B9" s="19" t="n">
+        <v>10</v>
+      </c>
+      <c r="C9" s="19" t="n">
+        <v>16</v>
+      </c>
+      <c r="D9" s="5" t="n">
+        <v>0.64</v>
+      </c>
+      <c r="E9" s="7" t="inlineStr">
+        <is>
+          <t>size</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="16" customHeight="1">
+      <c r="A10" s="9" t="inlineStr">
+        <is>
+          <t>offhours_insider</t>
+        </is>
+      </c>
+      <c r="B10" s="20" t="n">
+        <v>4</v>
+      </c>
+      <c r="C10" s="20" t="n">
+        <v>6</v>
+      </c>
+      <c r="D10" s="8" t="n">
+        <v>0.61</v>
+      </c>
+      <c r="E10" s="10" t="inlineStr">
+        <is>
+          <t>point-in-time; trustworthy</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="16" customHeight="1">
+      <c r="A11" s="6" t="inlineStr">
+        <is>
+          <t>insider_buying</t>
+        </is>
+      </c>
+      <c r="B11" s="19" t="n">
+        <v>5</v>
+      </c>
+      <c r="C11" s="19" t="n">
+        <v>9</v>
+      </c>
+      <c r="D11" s="5" t="n">
+        <v>0.53</v>
+      </c>
+      <c r="E11" s="7" t="inlineStr">
+        <is>
+          <t>point-in-time; trustworthy</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="16" customHeight="1">
+      <c r="A12" s="9" t="inlineStr">
+        <is>
+          <t>net_buyback</t>
+        </is>
+      </c>
+      <c r="B12" s="20" t="n">
+        <v>10</v>
+      </c>
+      <c r="C12" s="20" t="n">
+        <v>20</v>
+      </c>
+      <c r="D12" s="8" t="n">
+        <v>0.53</v>
+      </c>
+      <c r="E12" s="10" t="inlineStr">
+        <is>
+          <t>point-in-time-ish</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="16" customHeight="1">
+      <c r="A13" s="6" t="inlineStr">
+        <is>
+          <t>deep_value_pb</t>
+        </is>
+      </c>
+      <c r="B13" s="19" t="n">
+        <v>8</v>
+      </c>
+      <c r="C13" s="19" t="n">
+        <v>22</v>
+      </c>
+      <c r="D13" s="5" t="n">
+        <v>0.39</v>
+      </c>
+      <c r="E13" s="7" t="inlineStr">
+        <is>
+          <t>CAVEAT: measured post-move; lower bound</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="16" customHeight="1">
+      <c r="A14" s="9" t="inlineStr">
+        <is>
+          <t>hard_floor</t>
+        </is>
+      </c>
+      <c r="B14" s="20" t="n">
+        <v>2</v>
+      </c>
+      <c r="C14" s="20" t="n">
+        <v>6</v>
+      </c>
+      <c r="D14" s="8" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="E14" s="10" t="inlineStr">
+        <is>
+          <t>CAVEAT: post-move valuation; lower bound</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="16" customHeight="1">
+      <c r="A15" s="6" t="inlineStr">
+        <is>
+          <t>high_geom_ratio</t>
+        </is>
+      </c>
+      <c r="B15" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="C15" s="19" t="n">
+        <v>9</v>
+      </c>
+      <c r="D15" s="5" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="E15" s="7" t="inlineStr">
+        <is>
+          <t>CAVEAT: post-move; winners look expensive now</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="16" customHeight="1">
+      <c r="A16" s="9" t="inlineStr">
+        <is>
+          <t>forced_seller</t>
+        </is>
+      </c>
+      <c r="B16" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="C16" s="20" t="n">
+        <v>4</v>
+      </c>
+      <c r="D16" s="8" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="E16" s="10" t="inlineStr">
+        <is>
+          <t>point-in-time; trustworthy</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="12" t="inlineStr">
+        <is>
+          <t>SECTOR CONCENTRATION (winner share / lift)</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="18" customHeight="1">
+      <c r="A19" s="15" t="inlineStr">
+        <is>
+          <t>Sector</t>
+        </is>
+      </c>
+      <c r="B19" s="4" t="inlineStr">
+        <is>
+          <t>Winner %</t>
+        </is>
+      </c>
+      <c r="C19" s="4" t="inlineStr">
+        <is>
+          <t>Lift</t>
+        </is>
+      </c>
+      <c r="D19" s="15" t="inlineStr"/>
+      <c r="E19" s="15" t="inlineStr"/>
+    </row>
+    <row r="20" ht="16" customHeight="1">
+      <c r="A20" s="9" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="B20" s="20" t="n">
+        <v>34</v>
+      </c>
+      <c r="C20" s="8" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="D20" s="10" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="E20" s="10" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="16" customHeight="1">
+      <c r="A21" s="6" t="inlineStr">
+        <is>
+          <t>Healthcare</t>
+        </is>
+      </c>
+      <c r="B21" s="19" t="n">
+        <v>28</v>
+      </c>
+      <c r="C21" s="5" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="D21" s="7" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="E21" s="7" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="16" customHeight="1">
+      <c r="A22" s="9" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="B22" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="C22" s="8" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="D22" s="10" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="E22" s="10" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="16" customHeight="1">
+      <c r="A23" s="6" t="inlineStr">
+        <is>
+          <t>Industrials</t>
+        </is>
+      </c>
+      <c r="B23" s="19" t="n">
+        <v>17</v>
+      </c>
+      <c r="C23" s="5" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="D23" s="7" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="E23" s="7" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="16" customHeight="1">
+      <c r="A24" s="9" t="inlineStr">
+        <is>
+          <t>Energy</t>
+        </is>
+      </c>
+      <c r="B24" s="20" t="n">
+        <v>4</v>
+      </c>
+      <c r="C24" s="8" t="n">
+        <v>0.91</v>
+      </c>
+      <c r="D24" s="10" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="E24" s="10" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="16" customHeight="1">
+      <c r="A25" s="6" t="inlineStr">
+        <is>
+          <t>Communication Services</t>
+        </is>
+      </c>
+      <c r="B25" s="19" t="n">
+        <v>3</v>
+      </c>
+      <c r="C25" s="5" t="n">
+        <v>0.76</v>
+      </c>
+      <c r="D25" s="7" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="E25" s="7" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="16" customHeight="1">
+      <c r="A26" s="9" t="inlineStr">
+        <is>
+          <t>Basic Materials</t>
+        </is>
+      </c>
+      <c r="B26" s="20" t="n">
+        <v>3</v>
+      </c>
+      <c r="C26" s="8" t="n">
+        <v>0.76</v>
+      </c>
+      <c r="D26" s="10" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="E26" s="10" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="16" customHeight="1">
+      <c r="A27" s="6" t="inlineStr">
+        <is>
+          <t>Consumer Defensive</t>
+        </is>
+      </c>
+      <c r="B27" s="19" t="n">
+        <v>2</v>
+      </c>
+      <c r="C27" s="5" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="D27" s="7" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="E27" s="7" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="28" customHeight="1">
+      <c r="A29" s="11" t="inlineStr">
+        <is>
+          <t>READ THIS. The honest reverse-engineering (pre-move filings of names that 3x'd) needs point-in-time fundamentals + multi-year price history, which are not available in this environment. This is the bounded version: winners are realized 1-year re-raters (52wk range + still near the high), and features are their CURRENT state. The key consequence: a name that already ran looks expensive now, so the value features (deep-value, hard-floor, high-ratio) show lift &lt; 1 purely as a post-move / survivorship artifact — NOT evidence that value fails. The trustworthy readings are (a) SECTOR, which doesn't change when a stock moves — winners concentrate in Technology (~2.2x lift) and Healthcare (~1.5x); and (b) the event-signal layers, which are closer to point-in-time. Conclusion: payoff geometry captures the limited-downside VALUE archetype of exceptional return; the biggest 1-year movers were GROWTH/re-rate names an asset-floor lens misses, so geometry is one lens, not the whole answer — the mechanism gates and catalyst layers carry the rest. Weights are therefore NOT auto-tuned on this survivorship sample. Source: winners_forensics.py.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="3">
+    <mergeCell ref="A2:E2"/>
+    <mergeCell ref="A1:E1"/>
+    <mergeCell ref="A29:E29"/>
+  </mergeCells>
+  <printOptions horizontalCentered="0"/>
+  <pageMargins left="0.5" right="0.5" top="0.6" bottom="0.6" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
   <dimension ref="A1:M19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -7074,7 +7620,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -8654,7 +9200,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -10149,7 +10695,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -10314,7 +10860,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -11438,7 +11984,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -13147,2264 +13693,6 @@
     <mergeCell ref="A1:J1"/>
     <mergeCell ref="A46:J46"/>
     <mergeCell ref="A2:J2"/>
-  </mergeCells>
-  <printOptions horizontalCentered="0"/>
-  <pageMargins left="0.5" right="0.5" top="0.6" bottom="0.6" header="0.5" footer="0.5"/>
-  <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="1"/>
-  </sheetPr>
-  <dimension ref="A1:H66"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="6" customWidth="1" min="2" max="2"/>
-    <col width="30" customWidth="1" min="3" max="3"/>
-    <col width="10" customWidth="1" min="4" max="4"/>
-    <col width="10" customWidth="1" min="5" max="5"/>
-    <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="10" customWidth="1" min="7" max="7"/>
-    <col width="50" customWidth="1" min="8" max="8"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="26" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Foreign Markets — JP / KR / UK</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="18" customHeight="1">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>Japan TSE PBR&lt;1 reform targets, Korea Value-Up chaebol, UK FTSE 100 scheme/take-private candidates. Foreign tickers kept separate from US universe consensus.</t>
-        </is>
-      </c>
-      <c r="B2" s="3" t="n"/>
-      <c r="C2" s="3" t="n"/>
-      <c r="D2" s="3" t="n"/>
-      <c r="E2" s="3" t="n"/>
-      <c r="F2" s="3" t="n"/>
-      <c r="G2" s="3" t="n"/>
-      <c r="H2" s="3" t="n"/>
-    </row>
-    <row r="3" ht="8" customHeight="1"/>
-    <row r="4" ht="18" customHeight="1">
-      <c r="A4" s="15" t="inlineStr">
-        <is>
-          <t>Ticker</t>
-        </is>
-      </c>
-      <c r="B4" s="4" t="inlineStr">
-        <is>
-          <t>Mkt</t>
-        </is>
-      </c>
-      <c r="C4" s="15" t="inlineStr">
-        <is>
-          <t>Name</t>
-        </is>
-      </c>
-      <c r="D4" s="4" t="inlineStr">
-        <is>
-          <t>Score</t>
-        </is>
-      </c>
-      <c r="E4" s="4" t="inlineStr">
-        <is>
-          <t>P/B</t>
-        </is>
-      </c>
-      <c r="F4" s="4" t="inlineStr">
-        <is>
-          <t>P/E</t>
-        </is>
-      </c>
-      <c r="G4" s="4" t="inlineStr">
-        <is>
-          <t>ROE %</t>
-        </is>
-      </c>
-      <c r="H4" s="15" t="inlineStr">
-        <is>
-          <t>Reasons</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="16" customHeight="1">
-      <c r="A5" s="6" t="inlineStr">
-        <is>
-          <t>9022.T</t>
-        </is>
-      </c>
-      <c r="B5" s="6" t="inlineStr">
-        <is>
-          <t>JP</t>
-        </is>
-      </c>
-      <c r="C5" s="7" t="inlineStr">
-        <is>
-          <t>CENTRAL JAPAN RAILWAY CO</t>
-        </is>
-      </c>
-      <c r="D5" s="16" t="n">
-        <v>35</v>
-      </c>
-      <c r="E5" s="16" t="n">
-        <v>0.6296625</v>
-      </c>
-      <c r="F5" s="16" t="n">
-        <v>5.854111</v>
-      </c>
-      <c r="G5" s="19" t="n">
-        <v>11.4700004</v>
-      </c>
-      <c r="H5" s="7" t="inlineStr">
-        <is>
-          <t>PBR 0.63 (TSE reform target); quality+value ROE 11%</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="16" customHeight="1">
-      <c r="A6" s="9" t="inlineStr">
-        <is>
-          <t>9501.T</t>
-        </is>
-      </c>
-      <c r="B6" s="6" t="inlineStr">
-        <is>
-          <t>JP</t>
-        </is>
-      </c>
-      <c r="C6" s="10" t="inlineStr">
-        <is>
-          <t>TOKYO ELEC POWER CO HLDGS INC</t>
-        </is>
-      </c>
-      <c r="D6" s="17" t="n">
-        <v>33</v>
-      </c>
-      <c r="E6" s="17" t="n">
-        <v>0.22752257</v>
-      </c>
-      <c r="F6" s="10" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="G6" s="20" t="n">
-        <v>-12.622</v>
-      </c>
-      <c r="H6" s="10" t="inlineStr">
-        <is>
-          <t>PBR 0.23 (TSE reform target); DD 49%</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="16" customHeight="1">
-      <c r="A7" s="6" t="inlineStr">
-        <is>
-          <t>VTY.L</t>
-        </is>
-      </c>
-      <c r="B7" s="6" t="inlineStr">
-        <is>
-          <t>UK</t>
-        </is>
-      </c>
-      <c r="C7" s="7" t="inlineStr">
-        <is>
-          <t>VISTRY GROUP PLC ORD 50P</t>
-        </is>
-      </c>
-      <c r="D7" s="16" t="n">
-        <v>32</v>
-      </c>
-      <c r="E7" s="16" t="n">
-        <v>0.26397306</v>
-      </c>
-      <c r="F7" s="16" t="n">
-        <v>6.5333333</v>
-      </c>
-      <c r="G7" s="19" t="n">
-        <v>4.2069998</v>
-      </c>
-      <c r="H7" s="7" t="inlineStr">
-        <is>
-          <t>P/B 0.26 (scheme candidate); P/E 6.5</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="16" customHeight="1">
-      <c r="A8" s="9" t="inlineStr">
-        <is>
-          <t>III.L</t>
-        </is>
-      </c>
-      <c r="B8" s="6" t="inlineStr">
-        <is>
-          <t>UK</t>
-        </is>
-      </c>
-      <c r="C8" s="10" t="inlineStr">
-        <is>
-          <t>3I GROUP PLC ORD 73 19/22P</t>
-        </is>
-      </c>
-      <c r="D8" s="17" t="n">
-        <v>30</v>
-      </c>
-      <c r="E8" s="17" t="n">
-        <v>0.83113635</v>
-      </c>
-      <c r="F8" s="17" t="n">
-        <v>4.679035</v>
-      </c>
-      <c r="G8" s="20" t="n">
-        <v>19.077998</v>
-      </c>
-      <c r="H8" s="10" t="inlineStr">
-        <is>
-          <t>P/B 0.83; P/E 4.7; div yield 372.0%</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="16" customHeight="1">
-      <c r="A9" s="6" t="inlineStr">
-        <is>
-          <t>VOD.L</t>
-        </is>
-      </c>
-      <c r="B9" s="6" t="inlineStr">
-        <is>
-          <t>UK</t>
-        </is>
-      </c>
-      <c r="C9" s="7" t="inlineStr">
-        <is>
-          <t>VODAFONE GROUP PLC ORD USD0.20</t>
-        </is>
-      </c>
-      <c r="D9" s="16" t="n">
-        <v>28</v>
-      </c>
-      <c r="E9" s="16" t="n">
-        <v>0.5547121</v>
-      </c>
-      <c r="F9" s="7" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="G9" s="19" t="n">
-        <v>0.10899999</v>
-      </c>
-      <c r="H9" s="7" t="inlineStr">
-        <is>
-          <t>P/B 0.55 (scheme candidate); div yield 378.0%</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="16" customHeight="1">
-      <c r="A10" s="9" t="inlineStr">
-        <is>
-          <t>SBRY.L</t>
-        </is>
-      </c>
-      <c r="B10" s="6" t="inlineStr">
-        <is>
-          <t>UK</t>
-        </is>
-      </c>
-      <c r="C10" s="10" t="inlineStr">
-        <is>
-          <t>SAINSBURY (J) PLC ORD 28 4/7P</t>
-        </is>
-      </c>
-      <c r="D10" s="17" t="n">
-        <v>28</v>
-      </c>
-      <c r="E10" s="17" t="n">
-        <v>0.688652</v>
-      </c>
-      <c r="F10" s="17" t="n">
-        <v>17.51089</v>
-      </c>
-      <c r="G10" s="20" t="n">
-        <v>6.4109996</v>
-      </c>
-      <c r="H10" s="10" t="inlineStr">
-        <is>
-          <t>P/B 0.69 (scheme candidate); div yield 439.0%</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="16" customHeight="1">
-      <c r="A11" s="6" t="inlineStr">
-        <is>
-          <t>7203.T</t>
-        </is>
-      </c>
-      <c r="B11" s="6" t="inlineStr">
-        <is>
-          <t>JP</t>
-        </is>
-      </c>
-      <c r="C11" s="7" t="inlineStr">
-        <is>
-          <t>TOYOTA MOTOR CORP</t>
-        </is>
-      </c>
-      <c r="D11" s="16" t="n">
-        <v>25</v>
-      </c>
-      <c r="E11" s="16" t="n">
-        <v>0.881705</v>
-      </c>
-      <c r="F11" s="16" t="n">
-        <v>9.148345000000001</v>
-      </c>
-      <c r="G11" s="19" t="n">
-        <v>10.233</v>
-      </c>
-      <c r="H11" s="7" t="inlineStr">
-        <is>
-          <t>PBR 0.88; quality+value ROE 10%</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="16" customHeight="1">
-      <c r="A12" s="9" t="inlineStr">
-        <is>
-          <t>7267.T</t>
-        </is>
-      </c>
-      <c r="B12" s="6" t="inlineStr">
-        <is>
-          <t>JP</t>
-        </is>
-      </c>
-      <c r="C12" s="10" t="inlineStr">
-        <is>
-          <t>HONDA MOTOR CO</t>
-        </is>
-      </c>
-      <c r="D12" s="17" t="n">
-        <v>25</v>
-      </c>
-      <c r="E12" s="17" t="n">
-        <v>0.46575868</v>
-      </c>
-      <c r="F12" s="10" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="G12" s="20" t="n">
-        <v>-2.8499998</v>
-      </c>
-      <c r="H12" s="10" t="inlineStr">
-        <is>
-          <t>PBR 0.47 (TSE reform target)</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="16" customHeight="1">
-      <c r="A13" s="6" t="inlineStr">
-        <is>
-          <t>7270.T</t>
-        </is>
-      </c>
-      <c r="B13" s="6" t="inlineStr">
-        <is>
-          <t>JP</t>
-        </is>
-      </c>
-      <c r="C13" s="7" t="inlineStr">
-        <is>
-          <t>SUBARU CORPORATION</t>
-        </is>
-      </c>
-      <c r="D13" s="16" t="n">
-        <v>25</v>
-      </c>
-      <c r="E13" s="16" t="n">
-        <v>0.6179315</v>
-      </c>
-      <c r="F13" s="16" t="n">
-        <v>19.150717</v>
-      </c>
-      <c r="G13" s="19" t="n">
-        <v>3.3069998</v>
-      </c>
-      <c r="H13" s="7" t="inlineStr">
-        <is>
-          <t>PBR 0.62 (TSE reform target)</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="16" customHeight="1">
-      <c r="A14" s="9" t="inlineStr">
-        <is>
-          <t>7201.T</t>
-        </is>
-      </c>
-      <c r="B14" s="6" t="inlineStr">
-        <is>
-          <t>JP</t>
-        </is>
-      </c>
-      <c r="C14" s="10" t="inlineStr">
-        <is>
-          <t>NISSAN MOTOR CO</t>
-        </is>
-      </c>
-      <c r="D14" s="17" t="n">
-        <v>25</v>
-      </c>
-      <c r="E14" s="17" t="n">
-        <v>0.22002745</v>
-      </c>
-      <c r="F14" s="10" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="G14" s="20" t="n">
-        <v>-9.856</v>
-      </c>
-      <c r="H14" s="10" t="inlineStr">
-        <is>
-          <t>PBR 0.22 (TSE reform target)</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="16" customHeight="1">
-      <c r="A15" s="6" t="inlineStr">
-        <is>
-          <t>1605.T</t>
-        </is>
-      </c>
-      <c r="B15" s="6" t="inlineStr">
-        <is>
-          <t>JP</t>
-        </is>
-      </c>
-      <c r="C15" s="7" t="inlineStr">
-        <is>
-          <t>INPEX CORPORATION</t>
-        </is>
-      </c>
-      <c r="D15" s="16" t="n">
-        <v>25</v>
-      </c>
-      <c r="E15" s="16" t="n">
-        <v>0.7812199</v>
-      </c>
-      <c r="F15" s="16" t="n">
-        <v>9.943130500000001</v>
-      </c>
-      <c r="G15" s="19" t="n">
-        <v>8.282</v>
-      </c>
-      <c r="H15" s="7" t="inlineStr">
-        <is>
-          <t>PBR 0.78; quality+value ROE 8%</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="16" customHeight="1">
-      <c r="A16" s="9" t="inlineStr">
-        <is>
-          <t>5020.T</t>
-        </is>
-      </c>
-      <c r="B16" s="6" t="inlineStr">
-        <is>
-          <t>JP</t>
-        </is>
-      </c>
-      <c r="C16" s="10" t="inlineStr">
-        <is>
-          <t>ENEOS HOLDINGS INC</t>
-        </is>
-      </c>
-      <c r="D16" s="17" t="n">
-        <v>25</v>
-      </c>
-      <c r="E16" s="17" t="n">
-        <v>0.9507054</v>
-      </c>
-      <c r="F16" s="17" t="n">
-        <v>12.411422</v>
-      </c>
-      <c r="G16" s="20" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="H16" s="10" t="inlineStr">
-        <is>
-          <t>PBR 0.95; quality+value ROE 8%</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="16" customHeight="1">
-      <c r="A17" s="6" t="inlineStr">
-        <is>
-          <t>5401.T</t>
-        </is>
-      </c>
-      <c r="B17" s="6" t="inlineStr">
-        <is>
-          <t>JP</t>
-        </is>
-      </c>
-      <c r="C17" s="7" t="inlineStr">
-        <is>
-          <t>NIPPON STEEL CORPORATION</t>
-        </is>
-      </c>
-      <c r="D17" s="16" t="n">
-        <v>25</v>
-      </c>
-      <c r="E17" s="16" t="n">
-        <v>0.516917</v>
-      </c>
-      <c r="F17" s="16" t="n">
-        <v>166.7683</v>
-      </c>
-      <c r="G17" s="19" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="H17" s="7" t="inlineStr">
-        <is>
-          <t>PBR 0.52 (TSE reform target)</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="16" customHeight="1">
-      <c r="A18" s="9" t="inlineStr">
-        <is>
-          <t>5411.T</t>
-        </is>
-      </c>
-      <c r="B18" s="6" t="inlineStr">
-        <is>
-          <t>JP</t>
-        </is>
-      </c>
-      <c r="C18" s="10" t="inlineStr">
-        <is>
-          <t>JFE HOLDINGS INC</t>
-        </is>
-      </c>
-      <c r="D18" s="17" t="n">
-        <v>25</v>
-      </c>
-      <c r="E18" s="17" t="n">
-        <v>0.37543565</v>
-      </c>
-      <c r="F18" s="17" t="n">
-        <v>14.648475</v>
-      </c>
-      <c r="G18" s="20" t="n">
-        <v>2.8110001</v>
-      </c>
-      <c r="H18" s="10" t="inlineStr">
-        <is>
-          <t>PBR 0.38 (TSE reform target)</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="16" customHeight="1">
-      <c r="A19" s="6" t="inlineStr">
-        <is>
-          <t>9101.T</t>
-        </is>
-      </c>
-      <c r="B19" s="6" t="inlineStr">
-        <is>
-          <t>JP</t>
-        </is>
-      </c>
-      <c r="C19" s="7" t="inlineStr">
-        <is>
-          <t>NIPPON YUSEN KABUSHIKI KAISHA</t>
-        </is>
-      </c>
-      <c r="D19" s="16" t="n">
-        <v>25</v>
-      </c>
-      <c r="E19" s="16" t="n">
-        <v>0.6957521</v>
-      </c>
-      <c r="F19" s="16" t="n">
-        <v>10.444035</v>
-      </c>
-      <c r="G19" s="19" t="n">
-        <v>7.056</v>
-      </c>
-      <c r="H19" s="7" t="inlineStr">
-        <is>
-          <t>PBR 0.70 (TSE reform target)</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="16" customHeight="1">
-      <c r="A20" s="9" t="inlineStr">
-        <is>
-          <t>9104.T</t>
-        </is>
-      </c>
-      <c r="B20" s="6" t="inlineStr">
-        <is>
-          <t>JP</t>
-        </is>
-      </c>
-      <c r="C20" s="10" t="inlineStr">
-        <is>
-          <t>MITSUI O.S.K. LINES LTD</t>
-        </is>
-      </c>
-      <c r="D20" s="17" t="n">
-        <v>25</v>
-      </c>
-      <c r="E20" s="17" t="n">
-        <v>0.62819624</v>
-      </c>
-      <c r="F20" s="17" t="n">
-        <v>8.47991</v>
-      </c>
-      <c r="G20" s="20" t="n">
-        <v>7.566000000000001</v>
-      </c>
-      <c r="H20" s="10" t="inlineStr">
-        <is>
-          <t>PBR 0.63 (TSE reform target)</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="16" customHeight="1">
-      <c r="A21" s="6" t="inlineStr">
-        <is>
-          <t>1925.T</t>
-        </is>
-      </c>
-      <c r="B21" s="6" t="inlineStr">
-        <is>
-          <t>JP</t>
-        </is>
-      </c>
-      <c r="C21" s="7" t="inlineStr">
-        <is>
-          <t>DAIWA HOUSE INDUSTRY CO</t>
-        </is>
-      </c>
-      <c r="D21" s="16" t="n">
-        <v>25</v>
-      </c>
-      <c r="E21" s="16" t="n">
-        <v>0.93027914</v>
-      </c>
-      <c r="F21" s="16" t="n">
-        <v>7.682529</v>
-      </c>
-      <c r="G21" s="19" t="n">
-        <v>12.528</v>
-      </c>
-      <c r="H21" s="7" t="inlineStr">
-        <is>
-          <t>PBR 0.93; quality+value ROE 13%</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="16" customHeight="1">
-      <c r="A22" s="9" t="inlineStr">
-        <is>
-          <t>1928.T</t>
-        </is>
-      </c>
-      <c r="B22" s="6" t="inlineStr">
-        <is>
-          <t>JP</t>
-        </is>
-      </c>
-      <c r="C22" s="10" t="inlineStr">
-        <is>
-          <t>SEKISUI HOUSE</t>
-        </is>
-      </c>
-      <c r="D22" s="17" t="n">
-        <v>25</v>
-      </c>
-      <c r="E22" s="17" t="n">
-        <v>0.9845158000000001</v>
-      </c>
-      <c r="F22" s="17" t="n">
-        <v>8.268003999999999</v>
-      </c>
-      <c r="G22" s="20" t="n">
-        <v>12.644</v>
-      </c>
-      <c r="H22" s="10" t="inlineStr">
-        <is>
-          <t>PBR 0.98; quality+value ROE 13%</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="16" customHeight="1">
-      <c r="A23" s="6" t="inlineStr">
-        <is>
-          <t>9201.T</t>
-        </is>
-      </c>
-      <c r="B23" s="6" t="inlineStr">
-        <is>
-          <t>JP</t>
-        </is>
-      </c>
-      <c r="C23" s="7" t="inlineStr">
-        <is>
-          <t>JAPAN AIRLINES CO LTD</t>
-        </is>
-      </c>
-      <c r="D23" s="16" t="n">
-        <v>25</v>
-      </c>
-      <c r="E23" s="16" t="n">
-        <v>0.9385531</v>
-      </c>
-      <c r="F23" s="16" t="n">
-        <v>9.176824</v>
-      </c>
-      <c r="G23" s="19" t="n">
-        <v>12.286</v>
-      </c>
-      <c r="H23" s="7" t="inlineStr">
-        <is>
-          <t>PBR 0.94; quality+value ROE 12%</t>
-        </is>
-      </c>
-    </row>
-    <row r="24" ht="16" customHeight="1">
-      <c r="A24" s="9" t="inlineStr">
-        <is>
-          <t>9202.T</t>
-        </is>
-      </c>
-      <c r="B24" s="6" t="inlineStr">
-        <is>
-          <t>JP</t>
-        </is>
-      </c>
-      <c r="C24" s="10" t="inlineStr">
-        <is>
-          <t>ANA HOLDINGS INC</t>
-        </is>
-      </c>
-      <c r="D24" s="17" t="n">
-        <v>25</v>
-      </c>
-      <c r="E24" s="17" t="n">
-        <v>0.90998346</v>
-      </c>
-      <c r="F24" s="17" t="n">
-        <v>9.315649000000001</v>
-      </c>
-      <c r="G24" s="20" t="n">
-        <v>12.94</v>
-      </c>
-      <c r="H24" s="10" t="inlineStr">
-        <is>
-          <t>PBR 0.91; quality+value ROE 13%</t>
-        </is>
-      </c>
-    </row>
-    <row r="25" ht="16" customHeight="1">
-      <c r="A25" s="6" t="inlineStr">
-        <is>
-          <t>9503.T</t>
-        </is>
-      </c>
-      <c r="B25" s="6" t="inlineStr">
-        <is>
-          <t>JP</t>
-        </is>
-      </c>
-      <c r="C25" s="7" t="inlineStr">
-        <is>
-          <t>KANSAI ELECTRIC POWER CO INC</t>
-        </is>
-      </c>
-      <c r="D25" s="16" t="n">
-        <v>25</v>
-      </c>
-      <c r="E25" s="16" t="n">
-        <v>0.74417263</v>
-      </c>
-      <c r="F25" s="16" t="n">
-        <v>6.766146</v>
-      </c>
-      <c r="G25" s="19" t="n">
-        <v>11.607</v>
-      </c>
-      <c r="H25" s="7" t="inlineStr">
-        <is>
-          <t>PBR 0.74; quality+value ROE 12%</t>
-        </is>
-      </c>
-    </row>
-    <row r="26" ht="16" customHeight="1">
-      <c r="A26" s="9" t="inlineStr">
-        <is>
-          <t>000660.KS</t>
-        </is>
-      </c>
-      <c r="B26" s="6" t="inlineStr">
-        <is>
-          <t>KR</t>
-        </is>
-      </c>
-      <c r="C26" s="10" t="inlineStr">
-        <is>
-          <t>SK hynix</t>
-        </is>
-      </c>
-      <c r="D26" s="17" t="n">
-        <v>23</v>
-      </c>
-      <c r="E26" s="10" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="F26" s="10" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="G26" s="20" t="n">
-        <v>61.172</v>
-      </c>
-      <c r="H26" s="10" t="inlineStr">
-        <is>
-          <t>chaebol Value-Up candidate; treasury ~21%</t>
-        </is>
-      </c>
-    </row>
-    <row r="27" ht="16" customHeight="1">
-      <c r="A27" s="6" t="inlineStr">
-        <is>
-          <t>028260.KS</t>
-        </is>
-      </c>
-      <c r="B27" s="6" t="inlineStr">
-        <is>
-          <t>KR</t>
-        </is>
-      </c>
-      <c r="C27" s="7" t="inlineStr">
-        <is>
-          <t>SAMSUNG C&amp;T</t>
-        </is>
-      </c>
-      <c r="D27" s="16" t="n">
-        <v>23</v>
-      </c>
-      <c r="E27" s="7" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="F27" s="7" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="G27" s="19" t="n">
-        <v>7.478999999999999</v>
-      </c>
-      <c r="H27" s="7" t="inlineStr">
-        <is>
-          <t>chaebol Value-Up candidate; treasury ~48%</t>
-        </is>
-      </c>
-    </row>
-    <row r="28" ht="16" customHeight="1">
-      <c r="A28" s="9" t="inlineStr">
-        <is>
-          <t>066570.KS</t>
-        </is>
-      </c>
-      <c r="B28" s="6" t="inlineStr">
-        <is>
-          <t>KR</t>
-        </is>
-      </c>
-      <c r="C28" s="10" t="inlineStr">
-        <is>
-          <t>LGELECTRONICS</t>
-        </is>
-      </c>
-      <c r="D28" s="17" t="n">
-        <v>23</v>
-      </c>
-      <c r="E28" s="10" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="F28" s="10" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="G28" s="20" t="n">
-        <v>4.777</v>
-      </c>
-      <c r="H28" s="10" t="inlineStr">
-        <is>
-          <t>chaebol Value-Up candidate; treasury ~25%</t>
-        </is>
-      </c>
-    </row>
-    <row r="29" ht="16" customHeight="1">
-      <c r="A29" s="6" t="inlineStr">
-        <is>
-          <t>051910.KS</t>
-        </is>
-      </c>
-      <c r="B29" s="6" t="inlineStr">
-        <is>
-          <t>KR</t>
-        </is>
-      </c>
-      <c r="C29" s="7" t="inlineStr">
-        <is>
-          <t>LGCHEM</t>
-        </is>
-      </c>
-      <c r="D29" s="16" t="n">
-        <v>23</v>
-      </c>
-      <c r="E29" s="7" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="F29" s="7" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="G29" s="19" t="n">
-        <v>-5.933999999999999</v>
-      </c>
-      <c r="H29" s="7" t="inlineStr">
-        <is>
-          <t>chaebol Value-Up candidate; treasury ~24%</t>
-        </is>
-      </c>
-    </row>
-    <row r="30" ht="16" customHeight="1">
-      <c r="A30" s="9" t="inlineStr">
-        <is>
-          <t>006400.KS</t>
-        </is>
-      </c>
-      <c r="B30" s="6" t="inlineStr">
-        <is>
-          <t>KR</t>
-        </is>
-      </c>
-      <c r="C30" s="10" t="inlineStr">
-        <is>
-          <t>SAMSUNG SDI CO.,LTD.</t>
-        </is>
-      </c>
-      <c r="D30" s="17" t="n">
-        <v>23</v>
-      </c>
-      <c r="E30" s="10" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="F30" s="10" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="G30" s="20" t="n">
-        <v>-2.5710002</v>
-      </c>
-      <c r="H30" s="10" t="inlineStr">
-        <is>
-          <t>chaebol Value-Up candidate; treasury ~21%</t>
-        </is>
-      </c>
-    </row>
-    <row r="31" ht="16" customHeight="1">
-      <c r="A31" s="6" t="inlineStr">
-        <is>
-          <t>032830.KS</t>
-        </is>
-      </c>
-      <c r="B31" s="6" t="inlineStr">
-        <is>
-          <t>KR</t>
-        </is>
-      </c>
-      <c r="C31" s="7" t="inlineStr">
-        <is>
-          <t>SAMSUNG LIFE</t>
-        </is>
-      </c>
-      <c r="D31" s="16" t="n">
-        <v>23</v>
-      </c>
-      <c r="E31" s="7" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="F31" s="7" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="G31" s="19" t="n">
-        <v>5.252</v>
-      </c>
-      <c r="H31" s="7" t="inlineStr">
-        <is>
-          <t>chaebol Value-Up candidate; treasury ~48%</t>
-        </is>
-      </c>
-    </row>
-    <row r="32" ht="16" customHeight="1">
-      <c r="A32" s="9" t="inlineStr">
-        <is>
-          <t>029780.KS</t>
-        </is>
-      </c>
-      <c r="B32" s="6" t="inlineStr">
-        <is>
-          <t>KR</t>
-        </is>
-      </c>
-      <c r="C32" s="10" t="inlineStr">
-        <is>
-          <t>SAMSUNG CARD</t>
-        </is>
-      </c>
-      <c r="D32" s="17" t="n">
-        <v>23</v>
-      </c>
-      <c r="E32" s="10" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="F32" s="10" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="G32" s="20" t="n">
-        <v>7.2129995</v>
-      </c>
-      <c r="H32" s="10" t="inlineStr">
-        <is>
-          <t>chaebol Value-Up candidate; treasury ~78%</t>
-        </is>
-      </c>
-    </row>
-    <row r="33" ht="16" customHeight="1">
-      <c r="A33" s="6" t="inlineStr">
-        <is>
-          <t>017670.KS</t>
-        </is>
-      </c>
-      <c r="B33" s="6" t="inlineStr">
-        <is>
-          <t>KR</t>
-        </is>
-      </c>
-      <c r="C33" s="7" t="inlineStr">
-        <is>
-          <t>SKTelecom</t>
-        </is>
-      </c>
-      <c r="D33" s="16" t="n">
-        <v>23</v>
-      </c>
-      <c r="E33" s="7" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="F33" s="7" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="G33" s="19" t="n">
-        <v>2.609</v>
-      </c>
-      <c r="H33" s="7" t="inlineStr">
-        <is>
-          <t>chaebol Value-Up candidate; treasury ~31%</t>
-        </is>
-      </c>
-    </row>
-    <row r="34" ht="16" customHeight="1">
-      <c r="A34" s="9" t="inlineStr">
-        <is>
-          <t>010140.KS</t>
-        </is>
-      </c>
-      <c r="B34" s="6" t="inlineStr">
-        <is>
-          <t>KR</t>
-        </is>
-      </c>
-      <c r="C34" s="10" t="inlineStr">
-        <is>
-          <t>SamsungHvyInd</t>
-        </is>
-      </c>
-      <c r="D34" s="17" t="n">
-        <v>23</v>
-      </c>
-      <c r="E34" s="10" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="F34" s="10" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="G34" s="20" t="n">
-        <v>13.207</v>
-      </c>
-      <c r="H34" s="10" t="inlineStr">
-        <is>
-          <t>chaebol Value-Up candidate; treasury ~28%</t>
-        </is>
-      </c>
-    </row>
-    <row r="35" ht="16" customHeight="1">
-      <c r="A35" s="6" t="inlineStr">
-        <is>
-          <t>267250.KS</t>
-        </is>
-      </c>
-      <c r="B35" s="6" t="inlineStr">
-        <is>
-          <t>KR</t>
-        </is>
-      </c>
-      <c r="C35" s="7" t="inlineStr">
-        <is>
-          <t>HD HYUNDAI</t>
-        </is>
-      </c>
-      <c r="D35" s="16" t="n">
-        <v>23</v>
-      </c>
-      <c r="E35" s="7" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="F35" s="7" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="G35" s="19" t="n">
-        <v>16.758</v>
-      </c>
-      <c r="H35" s="7" t="inlineStr">
-        <is>
-          <t>chaebol Value-Up candidate; treasury ~37%</t>
-        </is>
-      </c>
-    </row>
-    <row r="36" ht="16" customHeight="1">
-      <c r="A36" s="9" t="inlineStr">
-        <is>
-          <t>IAG.L</t>
-        </is>
-      </c>
-      <c r="B36" s="6" t="inlineStr">
-        <is>
-          <t>UK</t>
-        </is>
-      </c>
-      <c r="C36" s="10" t="inlineStr">
-        <is>
-          <t>INTERNATIONAL CONSOLIDATED AIRL</t>
-        </is>
-      </c>
-      <c r="D36" s="17" t="n">
-        <v>20</v>
-      </c>
-      <c r="E36" s="17" t="n">
-        <v>3.4071958</v>
-      </c>
-      <c r="F36" s="17" t="n">
-        <v>7.927419</v>
-      </c>
-      <c r="G36" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="H36" s="10" t="inlineStr">
-        <is>
-          <t>P/E 7.9; div yield 178.0%</t>
-        </is>
-      </c>
-    </row>
-    <row r="37" ht="16" customHeight="1">
-      <c r="A37" s="6" t="inlineStr">
-        <is>
-          <t>ABDN.L</t>
-        </is>
-      </c>
-      <c r="B37" s="6" t="inlineStr">
-        <is>
-          <t>UK</t>
-        </is>
-      </c>
-      <c r="C37" s="7" t="inlineStr">
-        <is>
-          <t>ABERDEEN GROUP PLC ORD 13 61/63</t>
-        </is>
-      </c>
-      <c r="D37" s="16" t="n">
-        <v>18</v>
-      </c>
-      <c r="E37" s="16" t="n">
-        <v>0.88921183</v>
-      </c>
-      <c r="F37" s="16" t="n">
-        <v>11.657143</v>
-      </c>
-      <c r="G37" s="19" t="n">
-        <v>7.823</v>
-      </c>
-      <c r="H37" s="7" t="inlineStr">
-        <is>
-          <t>P/B 0.89; div yield 629.0%</t>
-        </is>
-      </c>
-    </row>
-    <row r="38" ht="16" customHeight="1">
-      <c r="A38" s="9" t="inlineStr">
-        <is>
-          <t>KGF.L</t>
-        </is>
-      </c>
-      <c r="B38" s="6" t="inlineStr">
-        <is>
-          <t>UK</t>
-        </is>
-      </c>
-      <c r="C38" s="10" t="inlineStr">
-        <is>
-          <t>KINGFISHER PLC ORD 15 5/7P</t>
-        </is>
-      </c>
-      <c r="D38" s="17" t="n">
-        <v>18</v>
-      </c>
-      <c r="E38" s="17" t="n">
-        <v>0.80710936</v>
-      </c>
-      <c r="F38" s="17" t="n">
-        <v>20.921429</v>
-      </c>
-      <c r="G38" s="20" t="n">
-        <v>3.918999799999999</v>
-      </c>
-      <c r="H38" s="10" t="inlineStr">
-        <is>
-          <t>P/B 0.81; div yield 430.0%</t>
-        </is>
-      </c>
-    </row>
-    <row r="39" ht="16" customHeight="1">
-      <c r="A39" s="6" t="inlineStr">
-        <is>
-          <t>9107.T</t>
-        </is>
-      </c>
-      <c r="B39" s="6" t="inlineStr">
-        <is>
-          <t>JP</t>
-        </is>
-      </c>
-      <c r="C39" s="7" t="inlineStr">
-        <is>
-          <t>KAWASAKI KISEN KAISHA</t>
-        </is>
-      </c>
-      <c r="D39" s="16" t="n">
-        <v>15</v>
-      </c>
-      <c r="E39" s="16" t="n">
-        <v>0.85800916</v>
-      </c>
-      <c r="F39" s="16" t="n">
-        <v>11.634099</v>
-      </c>
-      <c r="G39" s="19" t="n">
-        <v>7.754</v>
-      </c>
-      <c r="H39" s="7" t="inlineStr">
-        <is>
-          <t>PBR 0.86</t>
-        </is>
-      </c>
-    </row>
-    <row r="40" ht="16" customHeight="1">
-      <c r="A40" s="9" t="inlineStr">
-        <is>
-          <t>005930.KS</t>
-        </is>
-      </c>
-      <c r="B40" s="6" t="inlineStr">
-        <is>
-          <t>KR</t>
-        </is>
-      </c>
-      <c r="C40" s="10" t="inlineStr">
-        <is>
-          <t>SamsungElec</t>
-        </is>
-      </c>
-      <c r="D40" s="17" t="n">
-        <v>15</v>
-      </c>
-      <c r="E40" s="10" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="F40" s="10" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="G40" s="20" t="n">
-        <v>18.855</v>
-      </c>
-      <c r="H40" s="10" t="inlineStr">
-        <is>
-          <t>chaebol Value-Up candidate</t>
-        </is>
-      </c>
-    </row>
-    <row r="41" ht="16" customHeight="1">
-      <c r="A41" s="6" t="inlineStr">
-        <is>
-          <t>005380.KS</t>
-        </is>
-      </c>
-      <c r="B41" s="6" t="inlineStr">
-        <is>
-          <t>KR</t>
-        </is>
-      </c>
-      <c r="C41" s="7" t="inlineStr">
-        <is>
-          <t>HyundaiMtr</t>
-        </is>
-      </c>
-      <c r="D41" s="16" t="n">
-        <v>15</v>
-      </c>
-      <c r="E41" s="7" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="F41" s="7" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="G41" s="19" t="n">
-        <v>7.539999999999999</v>
-      </c>
-      <c r="H41" s="7" t="inlineStr">
-        <is>
-          <t>chaebol Value-Up candidate</t>
-        </is>
-      </c>
-    </row>
-    <row r="42" ht="16" customHeight="1">
-      <c r="A42" s="9" t="inlineStr">
-        <is>
-          <t>005490.KS</t>
-        </is>
-      </c>
-      <c r="B42" s="6" t="inlineStr">
-        <is>
-          <t>KR</t>
-        </is>
-      </c>
-      <c r="C42" s="10" t="inlineStr">
-        <is>
-          <t>POSCO Holdings</t>
-        </is>
-      </c>
-      <c r="D42" s="17" t="n">
-        <v>15</v>
-      </c>
-      <c r="E42" s="10" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="F42" s="10" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="G42" s="20" t="n">
-        <v>1.125</v>
-      </c>
-      <c r="H42" s="10" t="inlineStr">
-        <is>
-          <t>chaebol Value-Up candidate</t>
-        </is>
-      </c>
-    </row>
-    <row r="43" ht="16" customHeight="1">
-      <c r="A43" s="6" t="inlineStr">
-        <is>
-          <t>086790.KS</t>
-        </is>
-      </c>
-      <c r="B43" s="6" t="inlineStr">
-        <is>
-          <t>KR</t>
-        </is>
-      </c>
-      <c r="C43" s="7" t="inlineStr">
-        <is>
-          <t>HANAFINANCIALGR</t>
-        </is>
-      </c>
-      <c r="D43" s="16" t="n">
-        <v>15</v>
-      </c>
-      <c r="E43" s="7" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="F43" s="7" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="G43" s="19" t="n">
-        <v>9.097</v>
-      </c>
-      <c r="H43" s="7" t="inlineStr">
-        <is>
-          <t>chaebol Value-Up candidate</t>
-        </is>
-      </c>
-    </row>
-    <row r="44" ht="16" customHeight="1">
-      <c r="A44" s="9" t="inlineStr">
-        <is>
-          <t>316140.KS</t>
-        </is>
-      </c>
-      <c r="B44" s="6" t="inlineStr">
-        <is>
-          <t>KR</t>
-        </is>
-      </c>
-      <c r="C44" s="10" t="inlineStr">
-        <is>
-          <t>WooriFinancialGroup</t>
-        </is>
-      </c>
-      <c r="D44" s="17" t="n">
-        <v>15</v>
-      </c>
-      <c r="E44" s="10" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="F44" s="10" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="G44" s="20" t="n">
-        <v>8.518000000000001</v>
-      </c>
-      <c r="H44" s="10" t="inlineStr">
-        <is>
-          <t>chaebol Value-Up candidate</t>
-        </is>
-      </c>
-    </row>
-    <row r="45" ht="16" customHeight="1">
-      <c r="A45" s="6" t="inlineStr">
-        <is>
-          <t>105560.KS</t>
-        </is>
-      </c>
-      <c r="B45" s="6" t="inlineStr">
-        <is>
-          <t>KR</t>
-        </is>
-      </c>
-      <c r="C45" s="7" t="inlineStr">
-        <is>
-          <t>KBFinancialGroup</t>
-        </is>
-      </c>
-      <c r="D45" s="16" t="n">
-        <v>15</v>
-      </c>
-      <c r="E45" s="7" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="F45" s="7" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="G45" s="19" t="n">
-        <v>9.991</v>
-      </c>
-      <c r="H45" s="7" t="inlineStr">
-        <is>
-          <t>chaebol Value-Up candidate</t>
-        </is>
-      </c>
-    </row>
-    <row r="46" ht="16" customHeight="1">
-      <c r="A46" s="9" t="inlineStr">
-        <is>
-          <t>005935.KS</t>
-        </is>
-      </c>
-      <c r="B46" s="6" t="inlineStr">
-        <is>
-          <t>KR</t>
-        </is>
-      </c>
-      <c r="C46" s="10" t="inlineStr">
-        <is>
-          <t>SamsungElec(1P)</t>
-        </is>
-      </c>
-      <c r="D46" s="17" t="n">
-        <v>15</v>
-      </c>
-      <c r="E46" s="10" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="F46" s="10" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="G46" s="20" t="n">
-        <v>18.855</v>
-      </c>
-      <c r="H46" s="10" t="inlineStr">
-        <is>
-          <t>chaebol Value-Up candidate</t>
-        </is>
-      </c>
-    </row>
-    <row r="47" ht="16" customHeight="1">
-      <c r="A47" s="6" t="inlineStr">
-        <is>
-          <t>035720.KS</t>
-        </is>
-      </c>
-      <c r="B47" s="6" t="inlineStr">
-        <is>
-          <t>KR</t>
-        </is>
-      </c>
-      <c r="C47" s="7" t="inlineStr">
-        <is>
-          <t>Kakao</t>
-        </is>
-      </c>
-      <c r="D47" s="16" t="n">
-        <v>8</v>
-      </c>
-      <c r="E47" s="7" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="F47" s="7" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="G47" s="19" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="H47" s="7" t="inlineStr">
-        <is>
-          <t>treasury ~30%</t>
-        </is>
-      </c>
-    </row>
-    <row r="48" ht="16" customHeight="1">
-      <c r="A48" s="9" t="inlineStr">
-        <is>
-          <t>012330.KS</t>
-        </is>
-      </c>
-      <c r="B48" s="6" t="inlineStr">
-        <is>
-          <t>KR</t>
-        </is>
-      </c>
-      <c r="C48" s="10" t="inlineStr">
-        <is>
-          <t>Mobis</t>
-        </is>
-      </c>
-      <c r="D48" s="17" t="n">
-        <v>8</v>
-      </c>
-      <c r="E48" s="10" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="F48" s="10" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="G48" s="20" t="n">
-        <v>7.2270006</v>
-      </c>
-      <c r="H48" s="10" t="inlineStr">
-        <is>
-          <t>treasury ~36%</t>
-        </is>
-      </c>
-    </row>
-    <row r="49" ht="16" customHeight="1">
-      <c r="A49" s="6" t="inlineStr">
-        <is>
-          <t>015760.KS</t>
-        </is>
-      </c>
-      <c r="B49" s="6" t="inlineStr">
-        <is>
-          <t>KR</t>
-        </is>
-      </c>
-      <c r="C49" s="7" t="inlineStr">
-        <is>
-          <t>KEPCO</t>
-        </is>
-      </c>
-      <c r="D49" s="16" t="n">
-        <v>8</v>
-      </c>
-      <c r="E49" s="7" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="F49" s="7" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="G49" s="19" t="n">
-        <v>18.671</v>
-      </c>
-      <c r="H49" s="7" t="inlineStr">
-        <is>
-          <t>treasury ~52%</t>
-        </is>
-      </c>
-    </row>
-    <row r="50" ht="16" customHeight="1">
-      <c r="A50" s="9" t="inlineStr">
-        <is>
-          <t>036570.KS</t>
-        </is>
-      </c>
-      <c r="B50" s="6" t="inlineStr">
-        <is>
-          <t>KR</t>
-        </is>
-      </c>
-      <c r="C50" s="10" t="inlineStr">
-        <is>
-          <t>NC</t>
-        </is>
-      </c>
-      <c r="D50" s="17" t="n">
-        <v>8</v>
-      </c>
-      <c r="E50" s="10" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="F50" s="10" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="G50" s="20" t="n">
-        <v>14.094</v>
-      </c>
-      <c r="H50" s="10" t="inlineStr">
-        <is>
-          <t>treasury ~45%</t>
-        </is>
-      </c>
-    </row>
-    <row r="51" ht="16" customHeight="1">
-      <c r="A51" s="6" t="inlineStr">
-        <is>
-          <t>251270.KS</t>
-        </is>
-      </c>
-      <c r="B51" s="6" t="inlineStr">
-        <is>
-          <t>KR</t>
-        </is>
-      </c>
-      <c r="C51" s="7" t="inlineStr">
-        <is>
-          <t>Netmarble</t>
-        </is>
-      </c>
-      <c r="D51" s="16" t="n">
-        <v>8</v>
-      </c>
-      <c r="E51" s="7" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="F51" s="7" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="G51" s="19" t="n">
-        <v>6.414000000000001</v>
-      </c>
-      <c r="H51" s="7" t="inlineStr">
-        <is>
-          <t>treasury ~72%</t>
-        </is>
-      </c>
-    </row>
-    <row r="52" ht="16" customHeight="1">
-      <c r="A52" s="9" t="inlineStr">
-        <is>
-          <t>010130.KS</t>
-        </is>
-      </c>
-      <c r="B52" s="6" t="inlineStr">
-        <is>
-          <t>KR</t>
-        </is>
-      </c>
-      <c r="C52" s="10" t="inlineStr">
-        <is>
-          <t>KOREA ZINC</t>
-        </is>
-      </c>
-      <c r="D52" s="17" t="n">
-        <v>8</v>
-      </c>
-      <c r="E52" s="10" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="F52" s="10" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="G52" s="20" t="n">
-        <v>10.064</v>
-      </c>
-      <c r="H52" s="10" t="inlineStr">
-        <is>
-          <t>treasury ~75%</t>
-        </is>
-      </c>
-    </row>
-    <row r="53" ht="16" customHeight="1">
-      <c r="A53" s="6" t="inlineStr">
-        <is>
-          <t>024110.KS</t>
-        </is>
-      </c>
-      <c r="B53" s="6" t="inlineStr">
-        <is>
-          <t>KR</t>
-        </is>
-      </c>
-      <c r="C53" s="7" t="inlineStr">
-        <is>
-          <t>IBK</t>
-        </is>
-      </c>
-      <c r="D53" s="16" t="n">
-        <v>8</v>
-      </c>
-      <c r="E53" s="7" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="F53" s="7" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="G53" s="19" t="n">
-        <v>7.435</v>
-      </c>
-      <c r="H53" s="7" t="inlineStr">
-        <is>
-          <t>treasury ~60%</t>
-        </is>
-      </c>
-    </row>
-    <row r="54" ht="16" customHeight="1">
-      <c r="A54" s="9" t="inlineStr">
-        <is>
-          <t>009540.KS</t>
-        </is>
-      </c>
-      <c r="B54" s="6" t="inlineStr">
-        <is>
-          <t>KR</t>
-        </is>
-      </c>
-      <c r="C54" s="10" t="inlineStr">
-        <is>
-          <t>HDKSOE</t>
-        </is>
-      </c>
-      <c r="D54" s="17" t="n">
-        <v>8</v>
-      </c>
-      <c r="E54" s="10" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="F54" s="10" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="G54" s="20" t="n">
-        <v>21.757999</v>
-      </c>
-      <c r="H54" s="10" t="inlineStr">
-        <is>
-          <t>treasury ~35%</t>
-        </is>
-      </c>
-    </row>
-    <row r="55" ht="16" customHeight="1">
-      <c r="A55" s="6" t="inlineStr">
-        <is>
-          <t>047810.KS</t>
-        </is>
-      </c>
-      <c r="B55" s="6" t="inlineStr">
-        <is>
-          <t>KR</t>
-        </is>
-      </c>
-      <c r="C55" s="7" t="inlineStr">
-        <is>
-          <t>KOREA AEROSPACE</t>
-        </is>
-      </c>
-      <c r="D55" s="16" t="n">
-        <v>8</v>
-      </c>
-      <c r="E55" s="7" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="F55" s="7" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="G55" s="19" t="n">
-        <v>10.922</v>
-      </c>
-      <c r="H55" s="7" t="inlineStr">
-        <is>
-          <t>treasury ~32%</t>
-        </is>
-      </c>
-    </row>
-    <row r="56" ht="16" customHeight="1">
-      <c r="A56" s="9" t="inlineStr">
-        <is>
-          <t>138040.KS</t>
-        </is>
-      </c>
-      <c r="B56" s="6" t="inlineStr">
-        <is>
-          <t>KR</t>
-        </is>
-      </c>
-      <c r="C56" s="10" t="inlineStr">
-        <is>
-          <t>Meritz Financial</t>
-        </is>
-      </c>
-      <c r="D56" s="17" t="n">
-        <v>8</v>
-      </c>
-      <c r="E56" s="10" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="F56" s="10" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="G56" s="20" t="n">
-        <v>21.345</v>
-      </c>
-      <c r="H56" s="10" t="inlineStr">
-        <is>
-          <t>treasury ~60%</t>
-        </is>
-      </c>
-    </row>
-    <row r="57" ht="16" customHeight="1">
-      <c r="A57" s="6" t="inlineStr">
-        <is>
-          <t>SHEL.L</t>
-        </is>
-      </c>
-      <c r="B57" s="6" t="inlineStr">
-        <is>
-          <t>UK</t>
-        </is>
-      </c>
-      <c r="C57" s="7" t="inlineStr">
-        <is>
-          <t>SHELL PLC ORD EUR0.07</t>
-        </is>
-      </c>
-      <c r="D57" s="16" t="n">
-        <v>8</v>
-      </c>
-      <c r="E57" s="16" t="n">
-        <v>1.2567812</v>
-      </c>
-      <c r="F57" s="16" t="n">
-        <v>12.022634</v>
-      </c>
-      <c r="G57" s="19" t="n">
-        <v>10.697</v>
-      </c>
-      <c r="H57" s="7" t="inlineStr">
-        <is>
-          <t>div yield 396.0%</t>
-        </is>
-      </c>
-    </row>
-    <row r="58" ht="16" customHeight="1">
-      <c r="A58" s="9" t="inlineStr">
-        <is>
-          <t>BP.L</t>
-        </is>
-      </c>
-      <c r="B58" s="6" t="inlineStr">
-        <is>
-          <t>UK</t>
-        </is>
-      </c>
-      <c r="C58" s="10" t="inlineStr">
-        <is>
-          <t>BP PLC $0.25</t>
-        </is>
-      </c>
-      <c r="D58" s="17" t="n">
-        <v>8</v>
-      </c>
-      <c r="E58" s="17" t="n">
-        <v>1.7580478</v>
-      </c>
-      <c r="F58" s="17" t="n">
-        <v>29.628126</v>
-      </c>
-      <c r="G58" s="20" t="n">
-        <v>5.842</v>
-      </c>
-      <c r="H58" s="10" t="inlineStr">
-        <is>
-          <t>div yield 518.0%</t>
-        </is>
-      </c>
-    </row>
-    <row r="59" ht="16" customHeight="1">
-      <c r="A59" s="6" t="inlineStr">
-        <is>
-          <t>ULVR.L</t>
-        </is>
-      </c>
-      <c r="B59" s="6" t="inlineStr">
-        <is>
-          <t>UK</t>
-        </is>
-      </c>
-      <c r="C59" s="7" t="inlineStr">
-        <is>
-          <t>UNILEVER PLC ORD 3.5P</t>
-        </is>
-      </c>
-      <c r="D59" s="16" t="n">
-        <v>8</v>
-      </c>
-      <c r="E59" s="16" t="n">
-        <v>7.4571557</v>
-      </c>
-      <c r="F59" s="16" t="n">
-        <v>20.560537</v>
-      </c>
-      <c r="G59" s="19" t="n">
-        <v>30.955</v>
-      </c>
-      <c r="H59" s="7" t="inlineStr">
-        <is>
-          <t>div yield 372.0%</t>
-        </is>
-      </c>
-    </row>
-    <row r="60" ht="16" customHeight="1">
-      <c r="A60" s="9" t="inlineStr">
-        <is>
-          <t>HSBA.L</t>
-        </is>
-      </c>
-      <c r="B60" s="6" t="inlineStr">
-        <is>
-          <t>UK</t>
-        </is>
-      </c>
-      <c r="C60" s="10" t="inlineStr">
-        <is>
-          <t>HSBC HOLDINGS PLC ORD $0.50 (UK</t>
-        </is>
-      </c>
-      <c r="D60" s="17" t="n">
-        <v>8</v>
-      </c>
-      <c r="E60" s="17" t="n">
-        <v>1.8993394</v>
-      </c>
-      <c r="F60" s="17" t="n">
-        <v>15.749999</v>
-      </c>
-      <c r="G60" s="20" t="n">
-        <v>11.611</v>
-      </c>
-      <c r="H60" s="10" t="inlineStr">
-        <is>
-          <t>div yield 389.0%</t>
-        </is>
-      </c>
-    </row>
-    <row r="61" ht="16" customHeight="1">
-      <c r="A61" s="6" t="inlineStr">
-        <is>
-          <t>AZN.L</t>
-        </is>
-      </c>
-      <c r="B61" s="6" t="inlineStr">
-        <is>
-          <t>UK</t>
-        </is>
-      </c>
-      <c r="C61" s="7" t="inlineStr">
-        <is>
-          <t>ASTRAZENECA PLC ORD SHS $0.25</t>
-        </is>
-      </c>
-      <c r="D61" s="16" t="n">
-        <v>8</v>
-      </c>
-      <c r="E61" s="16" t="n">
-        <v>6.094377</v>
-      </c>
-      <c r="F61" s="16" t="n">
-        <v>27.900793</v>
-      </c>
-      <c r="G61" s="19" t="n">
-        <v>23.482999</v>
-      </c>
-      <c r="H61" s="7" t="inlineStr">
-        <is>
-          <t>div yield 170.0%</t>
-        </is>
-      </c>
-    </row>
-    <row r="62" ht="16" customHeight="1">
-      <c r="A62" s="9" t="inlineStr">
-        <is>
-          <t>GSK.L</t>
-        </is>
-      </c>
-      <c r="B62" s="6" t="inlineStr">
-        <is>
-          <t>UK</t>
-        </is>
-      </c>
-      <c r="C62" s="10" t="inlineStr">
-        <is>
-          <t>GSK PLC ORD 31 1/4P</t>
-        </is>
-      </c>
-      <c r="D62" s="17" t="n">
-        <v>8</v>
-      </c>
-      <c r="E62" s="17" t="n">
-        <v>4.443819</v>
-      </c>
-      <c r="F62" s="17" t="n">
-        <v>13.897888</v>
-      </c>
-      <c r="G62" s="20" t="n">
-        <v>40.905997</v>
-      </c>
-      <c r="H62" s="10" t="inlineStr">
-        <is>
-          <t>div yield 349.0%</t>
-        </is>
-      </c>
-    </row>
-    <row r="63" ht="16" customHeight="1">
-      <c r="A63" s="6" t="inlineStr">
-        <is>
-          <t>BATS.L</t>
-        </is>
-      </c>
-      <c r="B63" s="6" t="inlineStr">
-        <is>
-          <t>UK</t>
-        </is>
-      </c>
-      <c r="C63" s="7" t="inlineStr">
-        <is>
-          <t>BRITISH AMERICAN TOBACCO PLC OR</t>
-        </is>
-      </c>
-      <c r="D63" s="16" t="n">
-        <v>8</v>
-      </c>
-      <c r="E63" s="16" t="n">
-        <v>2.2128325</v>
-      </c>
-      <c r="F63" s="16" t="n">
-        <v>13.429799</v>
-      </c>
-      <c r="G63" s="19" t="n">
-        <v>15.824</v>
-      </c>
-      <c r="H63" s="7" t="inlineStr">
-        <is>
-          <t>div yield 524.0%</t>
-        </is>
-      </c>
-    </row>
-    <row r="64" ht="16" customHeight="1">
-      <c r="A64" s="9" t="inlineStr">
-        <is>
-          <t>BARC.L</t>
-        </is>
-      </c>
-      <c r="B64" s="6" t="inlineStr">
-        <is>
-          <t>UK</t>
-        </is>
-      </c>
-      <c r="C64" s="10" t="inlineStr">
-        <is>
-          <t>BARCLAYS PLC ORD 25P</t>
-        </is>
-      </c>
-      <c r="D64" s="17" t="n">
-        <v>8</v>
-      </c>
-      <c r="E64" s="17" t="n">
-        <v>1.1118265</v>
-      </c>
-      <c r="F64" s="17" t="n">
-        <v>12.046511</v>
-      </c>
-      <c r="G64" s="20" t="n">
-        <v>9.552</v>
-      </c>
-      <c r="H64" s="10" t="inlineStr">
-        <is>
-          <t>div yield 170.0%</t>
-        </is>
-      </c>
-    </row>
-    <row r="66" ht="28" customHeight="1">
-      <c r="A66" s="11" t="inlineStr">
-        <is>
-          <t>Japan signal: TSE explicit policy targets PBR&lt;1 companies for capital return reform; scored highest at PBR&lt;0.7. Korea: Value-Up / treasury cancellation program (chaebol families named candidates: Samsung, Hyundai, LG, SK, POSCO). UK: scheme of arrangement is the dominant take-private mechanism in London; deep-discount FTSE names are the target pool. Source: foreign_markets.json (yfinance with .T/.KS/.L suffixes; seed list ~130 tickers, expandable).</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="3">
-    <mergeCell ref="A2:H2"/>
-    <mergeCell ref="A66:H66"/>
-    <mergeCell ref="A1:H1"/>
   </mergeCells>
   <printOptions horizontalCentered="0"/>
   <pageMargins left="0.5" right="0.5" top="0.6" bottom="0.6" header="0.5" footer="0.5"/>
@@ -16139,6 +14427,2264 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
+  <dimension ref="A1:H66"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="10" customWidth="1" min="1" max="1"/>
+    <col width="6" customWidth="1" min="2" max="2"/>
+    <col width="30" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="10" customWidth="1" min="5" max="5"/>
+    <col width="10" customWidth="1" min="6" max="6"/>
+    <col width="10" customWidth="1" min="7" max="7"/>
+    <col width="50" customWidth="1" min="8" max="8"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="26" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Foreign Markets — JP / KR / UK</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="18" customHeight="1">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Japan TSE PBR&lt;1 reform targets, Korea Value-Up chaebol, UK FTSE 100 scheme/take-private candidates. Foreign tickers kept separate from US universe consensus.</t>
+        </is>
+      </c>
+      <c r="B2" s="3" t="n"/>
+      <c r="C2" s="3" t="n"/>
+      <c r="D2" s="3" t="n"/>
+      <c r="E2" s="3" t="n"/>
+      <c r="F2" s="3" t="n"/>
+      <c r="G2" s="3" t="n"/>
+      <c r="H2" s="3" t="n"/>
+    </row>
+    <row r="3" ht="8" customHeight="1"/>
+    <row r="4" ht="18" customHeight="1">
+      <c r="A4" s="15" t="inlineStr">
+        <is>
+          <t>Ticker</t>
+        </is>
+      </c>
+      <c r="B4" s="4" t="inlineStr">
+        <is>
+          <t>Mkt</t>
+        </is>
+      </c>
+      <c r="C4" s="15" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="D4" s="4" t="inlineStr">
+        <is>
+          <t>Score</t>
+        </is>
+      </c>
+      <c r="E4" s="4" t="inlineStr">
+        <is>
+          <t>P/B</t>
+        </is>
+      </c>
+      <c r="F4" s="4" t="inlineStr">
+        <is>
+          <t>P/E</t>
+        </is>
+      </c>
+      <c r="G4" s="4" t="inlineStr">
+        <is>
+          <t>ROE %</t>
+        </is>
+      </c>
+      <c r="H4" s="15" t="inlineStr">
+        <is>
+          <t>Reasons</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="16" customHeight="1">
+      <c r="A5" s="6" t="inlineStr">
+        <is>
+          <t>9022.T</t>
+        </is>
+      </c>
+      <c r="B5" s="6" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="C5" s="7" t="inlineStr">
+        <is>
+          <t>CENTRAL JAPAN RAILWAY CO</t>
+        </is>
+      </c>
+      <c r="D5" s="16" t="n">
+        <v>35</v>
+      </c>
+      <c r="E5" s="16" t="n">
+        <v>0.6296625</v>
+      </c>
+      <c r="F5" s="16" t="n">
+        <v>5.854111</v>
+      </c>
+      <c r="G5" s="19" t="n">
+        <v>11.4700004</v>
+      </c>
+      <c r="H5" s="7" t="inlineStr">
+        <is>
+          <t>PBR 0.63 (TSE reform target); quality+value ROE 11%</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="16" customHeight="1">
+      <c r="A6" s="9" t="inlineStr">
+        <is>
+          <t>9501.T</t>
+        </is>
+      </c>
+      <c r="B6" s="6" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="C6" s="10" t="inlineStr">
+        <is>
+          <t>TOKYO ELEC POWER CO HLDGS INC</t>
+        </is>
+      </c>
+      <c r="D6" s="17" t="n">
+        <v>33</v>
+      </c>
+      <c r="E6" s="17" t="n">
+        <v>0.22752257</v>
+      </c>
+      <c r="F6" s="10" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="G6" s="20" t="n">
+        <v>-12.622</v>
+      </c>
+      <c r="H6" s="10" t="inlineStr">
+        <is>
+          <t>PBR 0.23 (TSE reform target); DD 49%</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="16" customHeight="1">
+      <c r="A7" s="6" t="inlineStr">
+        <is>
+          <t>VTY.L</t>
+        </is>
+      </c>
+      <c r="B7" s="6" t="inlineStr">
+        <is>
+          <t>UK</t>
+        </is>
+      </c>
+      <c r="C7" s="7" t="inlineStr">
+        <is>
+          <t>VISTRY GROUP PLC ORD 50P</t>
+        </is>
+      </c>
+      <c r="D7" s="16" t="n">
+        <v>32</v>
+      </c>
+      <c r="E7" s="16" t="n">
+        <v>0.26397306</v>
+      </c>
+      <c r="F7" s="16" t="n">
+        <v>6.5333333</v>
+      </c>
+      <c r="G7" s="19" t="n">
+        <v>4.2069998</v>
+      </c>
+      <c r="H7" s="7" t="inlineStr">
+        <is>
+          <t>P/B 0.26 (scheme candidate); P/E 6.5</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="16" customHeight="1">
+      <c r="A8" s="9" t="inlineStr">
+        <is>
+          <t>III.L</t>
+        </is>
+      </c>
+      <c r="B8" s="6" t="inlineStr">
+        <is>
+          <t>UK</t>
+        </is>
+      </c>
+      <c r="C8" s="10" t="inlineStr">
+        <is>
+          <t>3I GROUP PLC ORD 73 19/22P</t>
+        </is>
+      </c>
+      <c r="D8" s="17" t="n">
+        <v>30</v>
+      </c>
+      <c r="E8" s="17" t="n">
+        <v>0.83113635</v>
+      </c>
+      <c r="F8" s="17" t="n">
+        <v>4.679035</v>
+      </c>
+      <c r="G8" s="20" t="n">
+        <v>19.077998</v>
+      </c>
+      <c r="H8" s="10" t="inlineStr">
+        <is>
+          <t>P/B 0.83; P/E 4.7; div yield 372.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="16" customHeight="1">
+      <c r="A9" s="6" t="inlineStr">
+        <is>
+          <t>VOD.L</t>
+        </is>
+      </c>
+      <c r="B9" s="6" t="inlineStr">
+        <is>
+          <t>UK</t>
+        </is>
+      </c>
+      <c r="C9" s="7" t="inlineStr">
+        <is>
+          <t>VODAFONE GROUP PLC ORD USD0.20</t>
+        </is>
+      </c>
+      <c r="D9" s="16" t="n">
+        <v>28</v>
+      </c>
+      <c r="E9" s="16" t="n">
+        <v>0.5547121</v>
+      </c>
+      <c r="F9" s="7" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="G9" s="19" t="n">
+        <v>0.10899999</v>
+      </c>
+      <c r="H9" s="7" t="inlineStr">
+        <is>
+          <t>P/B 0.55 (scheme candidate); div yield 378.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="16" customHeight="1">
+      <c r="A10" s="9" t="inlineStr">
+        <is>
+          <t>SBRY.L</t>
+        </is>
+      </c>
+      <c r="B10" s="6" t="inlineStr">
+        <is>
+          <t>UK</t>
+        </is>
+      </c>
+      <c r="C10" s="10" t="inlineStr">
+        <is>
+          <t>SAINSBURY (J) PLC ORD 28 4/7P</t>
+        </is>
+      </c>
+      <c r="D10" s="17" t="n">
+        <v>28</v>
+      </c>
+      <c r="E10" s="17" t="n">
+        <v>0.688652</v>
+      </c>
+      <c r="F10" s="17" t="n">
+        <v>17.51089</v>
+      </c>
+      <c r="G10" s="20" t="n">
+        <v>6.4109996</v>
+      </c>
+      <c r="H10" s="10" t="inlineStr">
+        <is>
+          <t>P/B 0.69 (scheme candidate); div yield 439.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="16" customHeight="1">
+      <c r="A11" s="6" t="inlineStr">
+        <is>
+          <t>7203.T</t>
+        </is>
+      </c>
+      <c r="B11" s="6" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="C11" s="7" t="inlineStr">
+        <is>
+          <t>TOYOTA MOTOR CORP</t>
+        </is>
+      </c>
+      <c r="D11" s="16" t="n">
+        <v>25</v>
+      </c>
+      <c r="E11" s="16" t="n">
+        <v>0.881705</v>
+      </c>
+      <c r="F11" s="16" t="n">
+        <v>9.148345000000001</v>
+      </c>
+      <c r="G11" s="19" t="n">
+        <v>10.233</v>
+      </c>
+      <c r="H11" s="7" t="inlineStr">
+        <is>
+          <t>PBR 0.88; quality+value ROE 10%</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="16" customHeight="1">
+      <c r="A12" s="9" t="inlineStr">
+        <is>
+          <t>7267.T</t>
+        </is>
+      </c>
+      <c r="B12" s="6" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="C12" s="10" t="inlineStr">
+        <is>
+          <t>HONDA MOTOR CO</t>
+        </is>
+      </c>
+      <c r="D12" s="17" t="n">
+        <v>25</v>
+      </c>
+      <c r="E12" s="17" t="n">
+        <v>0.46575868</v>
+      </c>
+      <c r="F12" s="10" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="G12" s="20" t="n">
+        <v>-2.8499998</v>
+      </c>
+      <c r="H12" s="10" t="inlineStr">
+        <is>
+          <t>PBR 0.47 (TSE reform target)</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="16" customHeight="1">
+      <c r="A13" s="6" t="inlineStr">
+        <is>
+          <t>7270.T</t>
+        </is>
+      </c>
+      <c r="B13" s="6" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="C13" s="7" t="inlineStr">
+        <is>
+          <t>SUBARU CORPORATION</t>
+        </is>
+      </c>
+      <c r="D13" s="16" t="n">
+        <v>25</v>
+      </c>
+      <c r="E13" s="16" t="n">
+        <v>0.6179315</v>
+      </c>
+      <c r="F13" s="16" t="n">
+        <v>19.150717</v>
+      </c>
+      <c r="G13" s="19" t="n">
+        <v>3.3069998</v>
+      </c>
+      <c r="H13" s="7" t="inlineStr">
+        <is>
+          <t>PBR 0.62 (TSE reform target)</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="16" customHeight="1">
+      <c r="A14" s="9" t="inlineStr">
+        <is>
+          <t>7201.T</t>
+        </is>
+      </c>
+      <c r="B14" s="6" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="C14" s="10" t="inlineStr">
+        <is>
+          <t>NISSAN MOTOR CO</t>
+        </is>
+      </c>
+      <c r="D14" s="17" t="n">
+        <v>25</v>
+      </c>
+      <c r="E14" s="17" t="n">
+        <v>0.22002745</v>
+      </c>
+      <c r="F14" s="10" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="G14" s="20" t="n">
+        <v>-9.856</v>
+      </c>
+      <c r="H14" s="10" t="inlineStr">
+        <is>
+          <t>PBR 0.22 (TSE reform target)</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="16" customHeight="1">
+      <c r="A15" s="6" t="inlineStr">
+        <is>
+          <t>1605.T</t>
+        </is>
+      </c>
+      <c r="B15" s="6" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="C15" s="7" t="inlineStr">
+        <is>
+          <t>INPEX CORPORATION</t>
+        </is>
+      </c>
+      <c r="D15" s="16" t="n">
+        <v>25</v>
+      </c>
+      <c r="E15" s="16" t="n">
+        <v>0.7812199</v>
+      </c>
+      <c r="F15" s="16" t="n">
+        <v>9.943130500000001</v>
+      </c>
+      <c r="G15" s="19" t="n">
+        <v>8.282</v>
+      </c>
+      <c r="H15" s="7" t="inlineStr">
+        <is>
+          <t>PBR 0.78; quality+value ROE 8%</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="16" customHeight="1">
+      <c r="A16" s="9" t="inlineStr">
+        <is>
+          <t>5020.T</t>
+        </is>
+      </c>
+      <c r="B16" s="6" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="C16" s="10" t="inlineStr">
+        <is>
+          <t>ENEOS HOLDINGS INC</t>
+        </is>
+      </c>
+      <c r="D16" s="17" t="n">
+        <v>25</v>
+      </c>
+      <c r="E16" s="17" t="n">
+        <v>0.9507054</v>
+      </c>
+      <c r="F16" s="17" t="n">
+        <v>12.411422</v>
+      </c>
+      <c r="G16" s="20" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="H16" s="10" t="inlineStr">
+        <is>
+          <t>PBR 0.95; quality+value ROE 8%</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="16" customHeight="1">
+      <c r="A17" s="6" t="inlineStr">
+        <is>
+          <t>5401.T</t>
+        </is>
+      </c>
+      <c r="B17" s="6" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="C17" s="7" t="inlineStr">
+        <is>
+          <t>NIPPON STEEL CORPORATION</t>
+        </is>
+      </c>
+      <c r="D17" s="16" t="n">
+        <v>25</v>
+      </c>
+      <c r="E17" s="16" t="n">
+        <v>0.516917</v>
+      </c>
+      <c r="F17" s="16" t="n">
+        <v>166.7683</v>
+      </c>
+      <c r="G17" s="19" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="H17" s="7" t="inlineStr">
+        <is>
+          <t>PBR 0.52 (TSE reform target)</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="16" customHeight="1">
+      <c r="A18" s="9" t="inlineStr">
+        <is>
+          <t>5411.T</t>
+        </is>
+      </c>
+      <c r="B18" s="6" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="C18" s="10" t="inlineStr">
+        <is>
+          <t>JFE HOLDINGS INC</t>
+        </is>
+      </c>
+      <c r="D18" s="17" t="n">
+        <v>25</v>
+      </c>
+      <c r="E18" s="17" t="n">
+        <v>0.37543565</v>
+      </c>
+      <c r="F18" s="17" t="n">
+        <v>14.648475</v>
+      </c>
+      <c r="G18" s="20" t="n">
+        <v>2.8110001</v>
+      </c>
+      <c r="H18" s="10" t="inlineStr">
+        <is>
+          <t>PBR 0.38 (TSE reform target)</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="16" customHeight="1">
+      <c r="A19" s="6" t="inlineStr">
+        <is>
+          <t>9101.T</t>
+        </is>
+      </c>
+      <c r="B19" s="6" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="C19" s="7" t="inlineStr">
+        <is>
+          <t>NIPPON YUSEN KABUSHIKI KAISHA</t>
+        </is>
+      </c>
+      <c r="D19" s="16" t="n">
+        <v>25</v>
+      </c>
+      <c r="E19" s="16" t="n">
+        <v>0.6957521</v>
+      </c>
+      <c r="F19" s="16" t="n">
+        <v>10.444035</v>
+      </c>
+      <c r="G19" s="19" t="n">
+        <v>7.056</v>
+      </c>
+      <c r="H19" s="7" t="inlineStr">
+        <is>
+          <t>PBR 0.70 (TSE reform target)</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="16" customHeight="1">
+      <c r="A20" s="9" t="inlineStr">
+        <is>
+          <t>9104.T</t>
+        </is>
+      </c>
+      <c r="B20" s="6" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="C20" s="10" t="inlineStr">
+        <is>
+          <t>MITSUI O.S.K. LINES LTD</t>
+        </is>
+      </c>
+      <c r="D20" s="17" t="n">
+        <v>25</v>
+      </c>
+      <c r="E20" s="17" t="n">
+        <v>0.62819624</v>
+      </c>
+      <c r="F20" s="17" t="n">
+        <v>8.47991</v>
+      </c>
+      <c r="G20" s="20" t="n">
+        <v>7.566000000000001</v>
+      </c>
+      <c r="H20" s="10" t="inlineStr">
+        <is>
+          <t>PBR 0.63 (TSE reform target)</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="16" customHeight="1">
+      <c r="A21" s="6" t="inlineStr">
+        <is>
+          <t>1925.T</t>
+        </is>
+      </c>
+      <c r="B21" s="6" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="C21" s="7" t="inlineStr">
+        <is>
+          <t>DAIWA HOUSE INDUSTRY CO</t>
+        </is>
+      </c>
+      <c r="D21" s="16" t="n">
+        <v>25</v>
+      </c>
+      <c r="E21" s="16" t="n">
+        <v>0.93027914</v>
+      </c>
+      <c r="F21" s="16" t="n">
+        <v>7.682529</v>
+      </c>
+      <c r="G21" s="19" t="n">
+        <v>12.528</v>
+      </c>
+      <c r="H21" s="7" t="inlineStr">
+        <is>
+          <t>PBR 0.93; quality+value ROE 13%</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="16" customHeight="1">
+      <c r="A22" s="9" t="inlineStr">
+        <is>
+          <t>1928.T</t>
+        </is>
+      </c>
+      <c r="B22" s="6" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="C22" s="10" t="inlineStr">
+        <is>
+          <t>SEKISUI HOUSE</t>
+        </is>
+      </c>
+      <c r="D22" s="17" t="n">
+        <v>25</v>
+      </c>
+      <c r="E22" s="17" t="n">
+        <v>0.9845158000000001</v>
+      </c>
+      <c r="F22" s="17" t="n">
+        <v>8.268003999999999</v>
+      </c>
+      <c r="G22" s="20" t="n">
+        <v>12.644</v>
+      </c>
+      <c r="H22" s="10" t="inlineStr">
+        <is>
+          <t>PBR 0.98; quality+value ROE 13%</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="16" customHeight="1">
+      <c r="A23" s="6" t="inlineStr">
+        <is>
+          <t>9201.T</t>
+        </is>
+      </c>
+      <c r="B23" s="6" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="C23" s="7" t="inlineStr">
+        <is>
+          <t>JAPAN AIRLINES CO LTD</t>
+        </is>
+      </c>
+      <c r="D23" s="16" t="n">
+        <v>25</v>
+      </c>
+      <c r="E23" s="16" t="n">
+        <v>0.9385531</v>
+      </c>
+      <c r="F23" s="16" t="n">
+        <v>9.176824</v>
+      </c>
+      <c r="G23" s="19" t="n">
+        <v>12.286</v>
+      </c>
+      <c r="H23" s="7" t="inlineStr">
+        <is>
+          <t>PBR 0.94; quality+value ROE 12%</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="16" customHeight="1">
+      <c r="A24" s="9" t="inlineStr">
+        <is>
+          <t>9202.T</t>
+        </is>
+      </c>
+      <c r="B24" s="6" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="C24" s="10" t="inlineStr">
+        <is>
+          <t>ANA HOLDINGS INC</t>
+        </is>
+      </c>
+      <c r="D24" s="17" t="n">
+        <v>25</v>
+      </c>
+      <c r="E24" s="17" t="n">
+        <v>0.90998346</v>
+      </c>
+      <c r="F24" s="17" t="n">
+        <v>9.315649000000001</v>
+      </c>
+      <c r="G24" s="20" t="n">
+        <v>12.94</v>
+      </c>
+      <c r="H24" s="10" t="inlineStr">
+        <is>
+          <t>PBR 0.91; quality+value ROE 13%</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="16" customHeight="1">
+      <c r="A25" s="6" t="inlineStr">
+        <is>
+          <t>9503.T</t>
+        </is>
+      </c>
+      <c r="B25" s="6" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="C25" s="7" t="inlineStr">
+        <is>
+          <t>KANSAI ELECTRIC POWER CO INC</t>
+        </is>
+      </c>
+      <c r="D25" s="16" t="n">
+        <v>25</v>
+      </c>
+      <c r="E25" s="16" t="n">
+        <v>0.74417263</v>
+      </c>
+      <c r="F25" s="16" t="n">
+        <v>6.766146</v>
+      </c>
+      <c r="G25" s="19" t="n">
+        <v>11.607</v>
+      </c>
+      <c r="H25" s="7" t="inlineStr">
+        <is>
+          <t>PBR 0.74; quality+value ROE 12%</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="16" customHeight="1">
+      <c r="A26" s="9" t="inlineStr">
+        <is>
+          <t>000660.KS</t>
+        </is>
+      </c>
+      <c r="B26" s="6" t="inlineStr">
+        <is>
+          <t>KR</t>
+        </is>
+      </c>
+      <c r="C26" s="10" t="inlineStr">
+        <is>
+          <t>SK hynix</t>
+        </is>
+      </c>
+      <c r="D26" s="17" t="n">
+        <v>23</v>
+      </c>
+      <c r="E26" s="10" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="F26" s="10" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="G26" s="20" t="n">
+        <v>61.172</v>
+      </c>
+      <c r="H26" s="10" t="inlineStr">
+        <is>
+          <t>chaebol Value-Up candidate; treasury ~21%</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="16" customHeight="1">
+      <c r="A27" s="6" t="inlineStr">
+        <is>
+          <t>028260.KS</t>
+        </is>
+      </c>
+      <c r="B27" s="6" t="inlineStr">
+        <is>
+          <t>KR</t>
+        </is>
+      </c>
+      <c r="C27" s="7" t="inlineStr">
+        <is>
+          <t>SAMSUNG C&amp;T</t>
+        </is>
+      </c>
+      <c r="D27" s="16" t="n">
+        <v>23</v>
+      </c>
+      <c r="E27" s="7" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="F27" s="7" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="G27" s="19" t="n">
+        <v>7.478999999999999</v>
+      </c>
+      <c r="H27" s="7" t="inlineStr">
+        <is>
+          <t>chaebol Value-Up candidate; treasury ~48%</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="16" customHeight="1">
+      <c r="A28" s="9" t="inlineStr">
+        <is>
+          <t>066570.KS</t>
+        </is>
+      </c>
+      <c r="B28" s="6" t="inlineStr">
+        <is>
+          <t>KR</t>
+        </is>
+      </c>
+      <c r="C28" s="10" t="inlineStr">
+        <is>
+          <t>LGELECTRONICS</t>
+        </is>
+      </c>
+      <c r="D28" s="17" t="n">
+        <v>23</v>
+      </c>
+      <c r="E28" s="10" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="F28" s="10" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="G28" s="20" t="n">
+        <v>4.777</v>
+      </c>
+      <c r="H28" s="10" t="inlineStr">
+        <is>
+          <t>chaebol Value-Up candidate; treasury ~25%</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="16" customHeight="1">
+      <c r="A29" s="6" t="inlineStr">
+        <is>
+          <t>051910.KS</t>
+        </is>
+      </c>
+      <c r="B29" s="6" t="inlineStr">
+        <is>
+          <t>KR</t>
+        </is>
+      </c>
+      <c r="C29" s="7" t="inlineStr">
+        <is>
+          <t>LGCHEM</t>
+        </is>
+      </c>
+      <c r="D29" s="16" t="n">
+        <v>23</v>
+      </c>
+      <c r="E29" s="7" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="F29" s="7" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="G29" s="19" t="n">
+        <v>-5.933999999999999</v>
+      </c>
+      <c r="H29" s="7" t="inlineStr">
+        <is>
+          <t>chaebol Value-Up candidate; treasury ~24%</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="16" customHeight="1">
+      <c r="A30" s="9" t="inlineStr">
+        <is>
+          <t>006400.KS</t>
+        </is>
+      </c>
+      <c r="B30" s="6" t="inlineStr">
+        <is>
+          <t>KR</t>
+        </is>
+      </c>
+      <c r="C30" s="10" t="inlineStr">
+        <is>
+          <t>SAMSUNG SDI CO.,LTD.</t>
+        </is>
+      </c>
+      <c r="D30" s="17" t="n">
+        <v>23</v>
+      </c>
+      <c r="E30" s="10" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="F30" s="10" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="G30" s="20" t="n">
+        <v>-2.5710002</v>
+      </c>
+      <c r="H30" s="10" t="inlineStr">
+        <is>
+          <t>chaebol Value-Up candidate; treasury ~21%</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="16" customHeight="1">
+      <c r="A31" s="6" t="inlineStr">
+        <is>
+          <t>032830.KS</t>
+        </is>
+      </c>
+      <c r="B31" s="6" t="inlineStr">
+        <is>
+          <t>KR</t>
+        </is>
+      </c>
+      <c r="C31" s="7" t="inlineStr">
+        <is>
+          <t>SAMSUNG LIFE</t>
+        </is>
+      </c>
+      <c r="D31" s="16" t="n">
+        <v>23</v>
+      </c>
+      <c r="E31" s="7" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="F31" s="7" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="G31" s="19" t="n">
+        <v>5.252</v>
+      </c>
+      <c r="H31" s="7" t="inlineStr">
+        <is>
+          <t>chaebol Value-Up candidate; treasury ~48%</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="16" customHeight="1">
+      <c r="A32" s="9" t="inlineStr">
+        <is>
+          <t>029780.KS</t>
+        </is>
+      </c>
+      <c r="B32" s="6" t="inlineStr">
+        <is>
+          <t>KR</t>
+        </is>
+      </c>
+      <c r="C32" s="10" t="inlineStr">
+        <is>
+          <t>SAMSUNG CARD</t>
+        </is>
+      </c>
+      <c r="D32" s="17" t="n">
+        <v>23</v>
+      </c>
+      <c r="E32" s="10" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="F32" s="10" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="G32" s="20" t="n">
+        <v>7.2129995</v>
+      </c>
+      <c r="H32" s="10" t="inlineStr">
+        <is>
+          <t>chaebol Value-Up candidate; treasury ~78%</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="16" customHeight="1">
+      <c r="A33" s="6" t="inlineStr">
+        <is>
+          <t>017670.KS</t>
+        </is>
+      </c>
+      <c r="B33" s="6" t="inlineStr">
+        <is>
+          <t>KR</t>
+        </is>
+      </c>
+      <c r="C33" s="7" t="inlineStr">
+        <is>
+          <t>SKTelecom</t>
+        </is>
+      </c>
+      <c r="D33" s="16" t="n">
+        <v>23</v>
+      </c>
+      <c r="E33" s="7" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="F33" s="7" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="G33" s="19" t="n">
+        <v>2.609</v>
+      </c>
+      <c r="H33" s="7" t="inlineStr">
+        <is>
+          <t>chaebol Value-Up candidate; treasury ~31%</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="16" customHeight="1">
+      <c r="A34" s="9" t="inlineStr">
+        <is>
+          <t>010140.KS</t>
+        </is>
+      </c>
+      <c r="B34" s="6" t="inlineStr">
+        <is>
+          <t>KR</t>
+        </is>
+      </c>
+      <c r="C34" s="10" t="inlineStr">
+        <is>
+          <t>SamsungHvyInd</t>
+        </is>
+      </c>
+      <c r="D34" s="17" t="n">
+        <v>23</v>
+      </c>
+      <c r="E34" s="10" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="F34" s="10" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="G34" s="20" t="n">
+        <v>13.207</v>
+      </c>
+      <c r="H34" s="10" t="inlineStr">
+        <is>
+          <t>chaebol Value-Up candidate; treasury ~28%</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="16" customHeight="1">
+      <c r="A35" s="6" t="inlineStr">
+        <is>
+          <t>267250.KS</t>
+        </is>
+      </c>
+      <c r="B35" s="6" t="inlineStr">
+        <is>
+          <t>KR</t>
+        </is>
+      </c>
+      <c r="C35" s="7" t="inlineStr">
+        <is>
+          <t>HD HYUNDAI</t>
+        </is>
+      </c>
+      <c r="D35" s="16" t="n">
+        <v>23</v>
+      </c>
+      <c r="E35" s="7" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="F35" s="7" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="G35" s="19" t="n">
+        <v>16.758</v>
+      </c>
+      <c r="H35" s="7" t="inlineStr">
+        <is>
+          <t>chaebol Value-Up candidate; treasury ~37%</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="16" customHeight="1">
+      <c r="A36" s="9" t="inlineStr">
+        <is>
+          <t>IAG.L</t>
+        </is>
+      </c>
+      <c r="B36" s="6" t="inlineStr">
+        <is>
+          <t>UK</t>
+        </is>
+      </c>
+      <c r="C36" s="10" t="inlineStr">
+        <is>
+          <t>INTERNATIONAL CONSOLIDATED AIRL</t>
+        </is>
+      </c>
+      <c r="D36" s="17" t="n">
+        <v>20</v>
+      </c>
+      <c r="E36" s="17" t="n">
+        <v>3.4071958</v>
+      </c>
+      <c r="F36" s="17" t="n">
+        <v>7.927419</v>
+      </c>
+      <c r="G36" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="H36" s="10" t="inlineStr">
+        <is>
+          <t>P/E 7.9; div yield 178.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="16" customHeight="1">
+      <c r="A37" s="6" t="inlineStr">
+        <is>
+          <t>ABDN.L</t>
+        </is>
+      </c>
+      <c r="B37" s="6" t="inlineStr">
+        <is>
+          <t>UK</t>
+        </is>
+      </c>
+      <c r="C37" s="7" t="inlineStr">
+        <is>
+          <t>ABERDEEN GROUP PLC ORD 13 61/63</t>
+        </is>
+      </c>
+      <c r="D37" s="16" t="n">
+        <v>18</v>
+      </c>
+      <c r="E37" s="16" t="n">
+        <v>0.88921183</v>
+      </c>
+      <c r="F37" s="16" t="n">
+        <v>11.657143</v>
+      </c>
+      <c r="G37" s="19" t="n">
+        <v>7.823</v>
+      </c>
+      <c r="H37" s="7" t="inlineStr">
+        <is>
+          <t>P/B 0.89; div yield 629.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="16" customHeight="1">
+      <c r="A38" s="9" t="inlineStr">
+        <is>
+          <t>KGF.L</t>
+        </is>
+      </c>
+      <c r="B38" s="6" t="inlineStr">
+        <is>
+          <t>UK</t>
+        </is>
+      </c>
+      <c r="C38" s="10" t="inlineStr">
+        <is>
+          <t>KINGFISHER PLC ORD 15 5/7P</t>
+        </is>
+      </c>
+      <c r="D38" s="17" t="n">
+        <v>18</v>
+      </c>
+      <c r="E38" s="17" t="n">
+        <v>0.80710936</v>
+      </c>
+      <c r="F38" s="17" t="n">
+        <v>20.921429</v>
+      </c>
+      <c r="G38" s="20" t="n">
+        <v>3.918999799999999</v>
+      </c>
+      <c r="H38" s="10" t="inlineStr">
+        <is>
+          <t>P/B 0.81; div yield 430.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="16" customHeight="1">
+      <c r="A39" s="6" t="inlineStr">
+        <is>
+          <t>9107.T</t>
+        </is>
+      </c>
+      <c r="B39" s="6" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="C39" s="7" t="inlineStr">
+        <is>
+          <t>KAWASAKI KISEN KAISHA</t>
+        </is>
+      </c>
+      <c r="D39" s="16" t="n">
+        <v>15</v>
+      </c>
+      <c r="E39" s="16" t="n">
+        <v>0.85800916</v>
+      </c>
+      <c r="F39" s="16" t="n">
+        <v>11.634099</v>
+      </c>
+      <c r="G39" s="19" t="n">
+        <v>7.754</v>
+      </c>
+      <c r="H39" s="7" t="inlineStr">
+        <is>
+          <t>PBR 0.86</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="16" customHeight="1">
+      <c r="A40" s="9" t="inlineStr">
+        <is>
+          <t>005930.KS</t>
+        </is>
+      </c>
+      <c r="B40" s="6" t="inlineStr">
+        <is>
+          <t>KR</t>
+        </is>
+      </c>
+      <c r="C40" s="10" t="inlineStr">
+        <is>
+          <t>SamsungElec</t>
+        </is>
+      </c>
+      <c r="D40" s="17" t="n">
+        <v>15</v>
+      </c>
+      <c r="E40" s="10" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="F40" s="10" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="G40" s="20" t="n">
+        <v>18.855</v>
+      </c>
+      <c r="H40" s="10" t="inlineStr">
+        <is>
+          <t>chaebol Value-Up candidate</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="16" customHeight="1">
+      <c r="A41" s="6" t="inlineStr">
+        <is>
+          <t>005380.KS</t>
+        </is>
+      </c>
+      <c r="B41" s="6" t="inlineStr">
+        <is>
+          <t>KR</t>
+        </is>
+      </c>
+      <c r="C41" s="7" t="inlineStr">
+        <is>
+          <t>HyundaiMtr</t>
+        </is>
+      </c>
+      <c r="D41" s="16" t="n">
+        <v>15</v>
+      </c>
+      <c r="E41" s="7" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="F41" s="7" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="G41" s="19" t="n">
+        <v>7.539999999999999</v>
+      </c>
+      <c r="H41" s="7" t="inlineStr">
+        <is>
+          <t>chaebol Value-Up candidate</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="16" customHeight="1">
+      <c r="A42" s="9" t="inlineStr">
+        <is>
+          <t>005490.KS</t>
+        </is>
+      </c>
+      <c r="B42" s="6" t="inlineStr">
+        <is>
+          <t>KR</t>
+        </is>
+      </c>
+      <c r="C42" s="10" t="inlineStr">
+        <is>
+          <t>POSCO Holdings</t>
+        </is>
+      </c>
+      <c r="D42" s="17" t="n">
+        <v>15</v>
+      </c>
+      <c r="E42" s="10" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="F42" s="10" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="G42" s="20" t="n">
+        <v>1.125</v>
+      </c>
+      <c r="H42" s="10" t="inlineStr">
+        <is>
+          <t>chaebol Value-Up candidate</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="16" customHeight="1">
+      <c r="A43" s="6" t="inlineStr">
+        <is>
+          <t>086790.KS</t>
+        </is>
+      </c>
+      <c r="B43" s="6" t="inlineStr">
+        <is>
+          <t>KR</t>
+        </is>
+      </c>
+      <c r="C43" s="7" t="inlineStr">
+        <is>
+          <t>HANAFINANCIALGR</t>
+        </is>
+      </c>
+      <c r="D43" s="16" t="n">
+        <v>15</v>
+      </c>
+      <c r="E43" s="7" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="F43" s="7" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="G43" s="19" t="n">
+        <v>9.097</v>
+      </c>
+      <c r="H43" s="7" t="inlineStr">
+        <is>
+          <t>chaebol Value-Up candidate</t>
+        </is>
+      </c>
+    </row>
+    <row r="44" ht="16" customHeight="1">
+      <c r="A44" s="9" t="inlineStr">
+        <is>
+          <t>316140.KS</t>
+        </is>
+      </c>
+      <c r="B44" s="6" t="inlineStr">
+        <is>
+          <t>KR</t>
+        </is>
+      </c>
+      <c r="C44" s="10" t="inlineStr">
+        <is>
+          <t>WooriFinancialGroup</t>
+        </is>
+      </c>
+      <c r="D44" s="17" t="n">
+        <v>15</v>
+      </c>
+      <c r="E44" s="10" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="F44" s="10" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="G44" s="20" t="n">
+        <v>8.518000000000001</v>
+      </c>
+      <c r="H44" s="10" t="inlineStr">
+        <is>
+          <t>chaebol Value-Up candidate</t>
+        </is>
+      </c>
+    </row>
+    <row r="45" ht="16" customHeight="1">
+      <c r="A45" s="6" t="inlineStr">
+        <is>
+          <t>105560.KS</t>
+        </is>
+      </c>
+      <c r="B45" s="6" t="inlineStr">
+        <is>
+          <t>KR</t>
+        </is>
+      </c>
+      <c r="C45" s="7" t="inlineStr">
+        <is>
+          <t>KBFinancialGroup</t>
+        </is>
+      </c>
+      <c r="D45" s="16" t="n">
+        <v>15</v>
+      </c>
+      <c r="E45" s="7" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="F45" s="7" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="G45" s="19" t="n">
+        <v>9.991</v>
+      </c>
+      <c r="H45" s="7" t="inlineStr">
+        <is>
+          <t>chaebol Value-Up candidate</t>
+        </is>
+      </c>
+    </row>
+    <row r="46" ht="16" customHeight="1">
+      <c r="A46" s="9" t="inlineStr">
+        <is>
+          <t>005935.KS</t>
+        </is>
+      </c>
+      <c r="B46" s="6" t="inlineStr">
+        <is>
+          <t>KR</t>
+        </is>
+      </c>
+      <c r="C46" s="10" t="inlineStr">
+        <is>
+          <t>SamsungElec(1P)</t>
+        </is>
+      </c>
+      <c r="D46" s="17" t="n">
+        <v>15</v>
+      </c>
+      <c r="E46" s="10" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="F46" s="10" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="G46" s="20" t="n">
+        <v>18.855</v>
+      </c>
+      <c r="H46" s="10" t="inlineStr">
+        <is>
+          <t>chaebol Value-Up candidate</t>
+        </is>
+      </c>
+    </row>
+    <row r="47" ht="16" customHeight="1">
+      <c r="A47" s="6" t="inlineStr">
+        <is>
+          <t>035720.KS</t>
+        </is>
+      </c>
+      <c r="B47" s="6" t="inlineStr">
+        <is>
+          <t>KR</t>
+        </is>
+      </c>
+      <c r="C47" s="7" t="inlineStr">
+        <is>
+          <t>Kakao</t>
+        </is>
+      </c>
+      <c r="D47" s="16" t="n">
+        <v>8</v>
+      </c>
+      <c r="E47" s="7" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="F47" s="7" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="G47" s="19" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="H47" s="7" t="inlineStr">
+        <is>
+          <t>treasury ~30%</t>
+        </is>
+      </c>
+    </row>
+    <row r="48" ht="16" customHeight="1">
+      <c r="A48" s="9" t="inlineStr">
+        <is>
+          <t>012330.KS</t>
+        </is>
+      </c>
+      <c r="B48" s="6" t="inlineStr">
+        <is>
+          <t>KR</t>
+        </is>
+      </c>
+      <c r="C48" s="10" t="inlineStr">
+        <is>
+          <t>Mobis</t>
+        </is>
+      </c>
+      <c r="D48" s="17" t="n">
+        <v>8</v>
+      </c>
+      <c r="E48" s="10" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="F48" s="10" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="G48" s="20" t="n">
+        <v>7.2270006</v>
+      </c>
+      <c r="H48" s="10" t="inlineStr">
+        <is>
+          <t>treasury ~36%</t>
+        </is>
+      </c>
+    </row>
+    <row r="49" ht="16" customHeight="1">
+      <c r="A49" s="6" t="inlineStr">
+        <is>
+          <t>015760.KS</t>
+        </is>
+      </c>
+      <c r="B49" s="6" t="inlineStr">
+        <is>
+          <t>KR</t>
+        </is>
+      </c>
+      <c r="C49" s="7" t="inlineStr">
+        <is>
+          <t>KEPCO</t>
+        </is>
+      </c>
+      <c r="D49" s="16" t="n">
+        <v>8</v>
+      </c>
+      <c r="E49" s="7" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="F49" s="7" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="G49" s="19" t="n">
+        <v>18.671</v>
+      </c>
+      <c r="H49" s="7" t="inlineStr">
+        <is>
+          <t>treasury ~52%</t>
+        </is>
+      </c>
+    </row>
+    <row r="50" ht="16" customHeight="1">
+      <c r="A50" s="9" t="inlineStr">
+        <is>
+          <t>036570.KS</t>
+        </is>
+      </c>
+      <c r="B50" s="6" t="inlineStr">
+        <is>
+          <t>KR</t>
+        </is>
+      </c>
+      <c r="C50" s="10" t="inlineStr">
+        <is>
+          <t>NC</t>
+        </is>
+      </c>
+      <c r="D50" s="17" t="n">
+        <v>8</v>
+      </c>
+      <c r="E50" s="10" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="F50" s="10" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="G50" s="20" t="n">
+        <v>14.094</v>
+      </c>
+      <c r="H50" s="10" t="inlineStr">
+        <is>
+          <t>treasury ~45%</t>
+        </is>
+      </c>
+    </row>
+    <row r="51" ht="16" customHeight="1">
+      <c r="A51" s="6" t="inlineStr">
+        <is>
+          <t>251270.KS</t>
+        </is>
+      </c>
+      <c r="B51" s="6" t="inlineStr">
+        <is>
+          <t>KR</t>
+        </is>
+      </c>
+      <c r="C51" s="7" t="inlineStr">
+        <is>
+          <t>Netmarble</t>
+        </is>
+      </c>
+      <c r="D51" s="16" t="n">
+        <v>8</v>
+      </c>
+      <c r="E51" s="7" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="F51" s="7" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="G51" s="19" t="n">
+        <v>6.414000000000001</v>
+      </c>
+      <c r="H51" s="7" t="inlineStr">
+        <is>
+          <t>treasury ~72%</t>
+        </is>
+      </c>
+    </row>
+    <row r="52" ht="16" customHeight="1">
+      <c r="A52" s="9" t="inlineStr">
+        <is>
+          <t>010130.KS</t>
+        </is>
+      </c>
+      <c r="B52" s="6" t="inlineStr">
+        <is>
+          <t>KR</t>
+        </is>
+      </c>
+      <c r="C52" s="10" t="inlineStr">
+        <is>
+          <t>KOREA ZINC</t>
+        </is>
+      </c>
+      <c r="D52" s="17" t="n">
+        <v>8</v>
+      </c>
+      <c r="E52" s="10" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="F52" s="10" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="G52" s="20" t="n">
+        <v>10.064</v>
+      </c>
+      <c r="H52" s="10" t="inlineStr">
+        <is>
+          <t>treasury ~75%</t>
+        </is>
+      </c>
+    </row>
+    <row r="53" ht="16" customHeight="1">
+      <c r="A53" s="6" t="inlineStr">
+        <is>
+          <t>024110.KS</t>
+        </is>
+      </c>
+      <c r="B53" s="6" t="inlineStr">
+        <is>
+          <t>KR</t>
+        </is>
+      </c>
+      <c r="C53" s="7" t="inlineStr">
+        <is>
+          <t>IBK</t>
+        </is>
+      </c>
+      <c r="D53" s="16" t="n">
+        <v>8</v>
+      </c>
+      <c r="E53" s="7" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="F53" s="7" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="G53" s="19" t="n">
+        <v>7.435</v>
+      </c>
+      <c r="H53" s="7" t="inlineStr">
+        <is>
+          <t>treasury ~60%</t>
+        </is>
+      </c>
+    </row>
+    <row r="54" ht="16" customHeight="1">
+      <c r="A54" s="9" t="inlineStr">
+        <is>
+          <t>009540.KS</t>
+        </is>
+      </c>
+      <c r="B54" s="6" t="inlineStr">
+        <is>
+          <t>KR</t>
+        </is>
+      </c>
+      <c r="C54" s="10" t="inlineStr">
+        <is>
+          <t>HDKSOE</t>
+        </is>
+      </c>
+      <c r="D54" s="17" t="n">
+        <v>8</v>
+      </c>
+      <c r="E54" s="10" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="F54" s="10" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="G54" s="20" t="n">
+        <v>21.757999</v>
+      </c>
+      <c r="H54" s="10" t="inlineStr">
+        <is>
+          <t>treasury ~35%</t>
+        </is>
+      </c>
+    </row>
+    <row r="55" ht="16" customHeight="1">
+      <c r="A55" s="6" t="inlineStr">
+        <is>
+          <t>047810.KS</t>
+        </is>
+      </c>
+      <c r="B55" s="6" t="inlineStr">
+        <is>
+          <t>KR</t>
+        </is>
+      </c>
+      <c r="C55" s="7" t="inlineStr">
+        <is>
+          <t>KOREA AEROSPACE</t>
+        </is>
+      </c>
+      <c r="D55" s="16" t="n">
+        <v>8</v>
+      </c>
+      <c r="E55" s="7" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="F55" s="7" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="G55" s="19" t="n">
+        <v>10.922</v>
+      </c>
+      <c r="H55" s="7" t="inlineStr">
+        <is>
+          <t>treasury ~32%</t>
+        </is>
+      </c>
+    </row>
+    <row r="56" ht="16" customHeight="1">
+      <c r="A56" s="9" t="inlineStr">
+        <is>
+          <t>138040.KS</t>
+        </is>
+      </c>
+      <c r="B56" s="6" t="inlineStr">
+        <is>
+          <t>KR</t>
+        </is>
+      </c>
+      <c r="C56" s="10" t="inlineStr">
+        <is>
+          <t>Meritz Financial</t>
+        </is>
+      </c>
+      <c r="D56" s="17" t="n">
+        <v>8</v>
+      </c>
+      <c r="E56" s="10" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="F56" s="10" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="G56" s="20" t="n">
+        <v>21.345</v>
+      </c>
+      <c r="H56" s="10" t="inlineStr">
+        <is>
+          <t>treasury ~60%</t>
+        </is>
+      </c>
+    </row>
+    <row r="57" ht="16" customHeight="1">
+      <c r="A57" s="6" t="inlineStr">
+        <is>
+          <t>SHEL.L</t>
+        </is>
+      </c>
+      <c r="B57" s="6" t="inlineStr">
+        <is>
+          <t>UK</t>
+        </is>
+      </c>
+      <c r="C57" s="7" t="inlineStr">
+        <is>
+          <t>SHELL PLC ORD EUR0.07</t>
+        </is>
+      </c>
+      <c r="D57" s="16" t="n">
+        <v>8</v>
+      </c>
+      <c r="E57" s="16" t="n">
+        <v>1.2567812</v>
+      </c>
+      <c r="F57" s="16" t="n">
+        <v>12.022634</v>
+      </c>
+      <c r="G57" s="19" t="n">
+        <v>10.697</v>
+      </c>
+      <c r="H57" s="7" t="inlineStr">
+        <is>
+          <t>div yield 396.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="58" ht="16" customHeight="1">
+      <c r="A58" s="9" t="inlineStr">
+        <is>
+          <t>BP.L</t>
+        </is>
+      </c>
+      <c r="B58" s="6" t="inlineStr">
+        <is>
+          <t>UK</t>
+        </is>
+      </c>
+      <c r="C58" s="10" t="inlineStr">
+        <is>
+          <t>BP PLC $0.25</t>
+        </is>
+      </c>
+      <c r="D58" s="17" t="n">
+        <v>8</v>
+      </c>
+      <c r="E58" s="17" t="n">
+        <v>1.7580478</v>
+      </c>
+      <c r="F58" s="17" t="n">
+        <v>29.628126</v>
+      </c>
+      <c r="G58" s="20" t="n">
+        <v>5.842</v>
+      </c>
+      <c r="H58" s="10" t="inlineStr">
+        <is>
+          <t>div yield 518.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="59" ht="16" customHeight="1">
+      <c r="A59" s="6" t="inlineStr">
+        <is>
+          <t>ULVR.L</t>
+        </is>
+      </c>
+      <c r="B59" s="6" t="inlineStr">
+        <is>
+          <t>UK</t>
+        </is>
+      </c>
+      <c r="C59" s="7" t="inlineStr">
+        <is>
+          <t>UNILEVER PLC ORD 3.5P</t>
+        </is>
+      </c>
+      <c r="D59" s="16" t="n">
+        <v>8</v>
+      </c>
+      <c r="E59" s="16" t="n">
+        <v>7.4571557</v>
+      </c>
+      <c r="F59" s="16" t="n">
+        <v>20.560537</v>
+      </c>
+      <c r="G59" s="19" t="n">
+        <v>30.955</v>
+      </c>
+      <c r="H59" s="7" t="inlineStr">
+        <is>
+          <t>div yield 372.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="60" ht="16" customHeight="1">
+      <c r="A60" s="9" t="inlineStr">
+        <is>
+          <t>HSBA.L</t>
+        </is>
+      </c>
+      <c r="B60" s="6" t="inlineStr">
+        <is>
+          <t>UK</t>
+        </is>
+      </c>
+      <c r="C60" s="10" t="inlineStr">
+        <is>
+          <t>HSBC HOLDINGS PLC ORD $0.50 (UK</t>
+        </is>
+      </c>
+      <c r="D60" s="17" t="n">
+        <v>8</v>
+      </c>
+      <c r="E60" s="17" t="n">
+        <v>1.8993394</v>
+      </c>
+      <c r="F60" s="17" t="n">
+        <v>15.749999</v>
+      </c>
+      <c r="G60" s="20" t="n">
+        <v>11.611</v>
+      </c>
+      <c r="H60" s="10" t="inlineStr">
+        <is>
+          <t>div yield 389.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="61" ht="16" customHeight="1">
+      <c r="A61" s="6" t="inlineStr">
+        <is>
+          <t>AZN.L</t>
+        </is>
+      </c>
+      <c r="B61" s="6" t="inlineStr">
+        <is>
+          <t>UK</t>
+        </is>
+      </c>
+      <c r="C61" s="7" t="inlineStr">
+        <is>
+          <t>ASTRAZENECA PLC ORD SHS $0.25</t>
+        </is>
+      </c>
+      <c r="D61" s="16" t="n">
+        <v>8</v>
+      </c>
+      <c r="E61" s="16" t="n">
+        <v>6.094377</v>
+      </c>
+      <c r="F61" s="16" t="n">
+        <v>27.900793</v>
+      </c>
+      <c r="G61" s="19" t="n">
+        <v>23.482999</v>
+      </c>
+      <c r="H61" s="7" t="inlineStr">
+        <is>
+          <t>div yield 170.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="62" ht="16" customHeight="1">
+      <c r="A62" s="9" t="inlineStr">
+        <is>
+          <t>GSK.L</t>
+        </is>
+      </c>
+      <c r="B62" s="6" t="inlineStr">
+        <is>
+          <t>UK</t>
+        </is>
+      </c>
+      <c r="C62" s="10" t="inlineStr">
+        <is>
+          <t>GSK PLC ORD 31 1/4P</t>
+        </is>
+      </c>
+      <c r="D62" s="17" t="n">
+        <v>8</v>
+      </c>
+      <c r="E62" s="17" t="n">
+        <v>4.443819</v>
+      </c>
+      <c r="F62" s="17" t="n">
+        <v>13.897888</v>
+      </c>
+      <c r="G62" s="20" t="n">
+        <v>40.905997</v>
+      </c>
+      <c r="H62" s="10" t="inlineStr">
+        <is>
+          <t>div yield 349.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="63" ht="16" customHeight="1">
+      <c r="A63" s="6" t="inlineStr">
+        <is>
+          <t>BATS.L</t>
+        </is>
+      </c>
+      <c r="B63" s="6" t="inlineStr">
+        <is>
+          <t>UK</t>
+        </is>
+      </c>
+      <c r="C63" s="7" t="inlineStr">
+        <is>
+          <t>BRITISH AMERICAN TOBACCO PLC OR</t>
+        </is>
+      </c>
+      <c r="D63" s="16" t="n">
+        <v>8</v>
+      </c>
+      <c r="E63" s="16" t="n">
+        <v>2.2128325</v>
+      </c>
+      <c r="F63" s="16" t="n">
+        <v>13.429799</v>
+      </c>
+      <c r="G63" s="19" t="n">
+        <v>15.824</v>
+      </c>
+      <c r="H63" s="7" t="inlineStr">
+        <is>
+          <t>div yield 524.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="64" ht="16" customHeight="1">
+      <c r="A64" s="9" t="inlineStr">
+        <is>
+          <t>BARC.L</t>
+        </is>
+      </c>
+      <c r="B64" s="6" t="inlineStr">
+        <is>
+          <t>UK</t>
+        </is>
+      </c>
+      <c r="C64" s="10" t="inlineStr">
+        <is>
+          <t>BARCLAYS PLC ORD 25P</t>
+        </is>
+      </c>
+      <c r="D64" s="17" t="n">
+        <v>8</v>
+      </c>
+      <c r="E64" s="17" t="n">
+        <v>1.1118265</v>
+      </c>
+      <c r="F64" s="17" t="n">
+        <v>12.046511</v>
+      </c>
+      <c r="G64" s="20" t="n">
+        <v>9.552</v>
+      </c>
+      <c r="H64" s="10" t="inlineStr">
+        <is>
+          <t>div yield 170.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="66" ht="28" customHeight="1">
+      <c r="A66" s="11" t="inlineStr">
+        <is>
+          <t>Japan signal: TSE explicit policy targets PBR&lt;1 companies for capital return reform; scored highest at PBR&lt;0.7. Korea: Value-Up / treasury cancellation program (chaebol families named candidates: Samsung, Hyundai, LG, SK, POSCO). UK: scheme of arrangement is the dominant take-private mechanism in London; deep-discount FTSE names are the target pool. Source: foreign_markets.json (yfinance with .T/.KS/.L suffixes; seed list ~130 tickers, expandable).</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="3">
+    <mergeCell ref="A2:H2"/>
+    <mergeCell ref="A66:H66"/>
+    <mergeCell ref="A1:H1"/>
+  </mergeCells>
+  <printOptions horizontalCentered="0"/>
+  <pageMargins left="0.5" right="0.5" top="0.6" bottom="0.6" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
   <dimension ref="A1:J46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -17929,7 +18475,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -20489,7 +21035,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -21091,7 +21637,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -21903,7 +22449,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>

--- a/MOST_ASYMMETRIC.xlsx
+++ b/MOST_ASYMMETRIC.xlsx
@@ -19,19 +19,20 @@
     <sheet name="MD&amp;A Intent" sheetId="10" state="visible" r:id="rId10"/>
     <sheet name="Payoff Geometry" sheetId="11" state="visible" r:id="rId11"/>
     <sheet name="Mechanism Gates" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet name="Winners Study" sheetId="13" state="visible" r:id="rId13"/>
-    <sheet name="Asymmetry Assembly" sheetId="14" state="visible" r:id="rId14"/>
-    <sheet name="Distressed Stub Progress" sheetId="15" state="visible" r:id="rId15"/>
-    <sheet name="Hidden Asset Realisation" sheetId="16" state="visible" r:id="rId16"/>
-    <sheet name="UK Capital Events" sheetId="17" state="visible" r:id="rId17"/>
-    <sheet name="Without Valuation" sheetId="18" state="visible" r:id="rId18"/>
-    <sheet name="Recent 30d" sheetId="19" state="visible" r:id="rId19"/>
-    <sheet name="Foreign Markets" sheetId="20" state="visible" r:id="rId20"/>
-    <sheet name="Turnaround Signal" sheetId="21" state="visible" r:id="rId21"/>
-    <sheet name="Single-Measure Best" sheetId="22" state="visible" r:id="rId22"/>
-    <sheet name="Layer Correlation" sheetId="23" state="visible" r:id="rId23"/>
-    <sheet name="Coverage &amp; Tiers" sheetId="24" state="visible" r:id="rId24"/>
-    <sheet name="Methodology" sheetId="25" state="visible" r:id="rId25"/>
+    <sheet name="Re-Rate Catalysts" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet name="Winners Study" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet name="Asymmetry Assembly" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet name="Distressed Stub Progress" sheetId="16" state="visible" r:id="rId16"/>
+    <sheet name="Hidden Asset Realisation" sheetId="17" state="visible" r:id="rId17"/>
+    <sheet name="UK Capital Events" sheetId="18" state="visible" r:id="rId18"/>
+    <sheet name="Without Valuation" sheetId="19" state="visible" r:id="rId19"/>
+    <sheet name="Recent 30d" sheetId="20" state="visible" r:id="rId20"/>
+    <sheet name="Foreign Markets" sheetId="21" state="visible" r:id="rId21"/>
+    <sheet name="Turnaround Signal" sheetId="22" state="visible" r:id="rId22"/>
+    <sheet name="Single-Measure Best" sheetId="23" state="visible" r:id="rId23"/>
+    <sheet name="Layer Correlation" sheetId="24" state="visible" r:id="rId24"/>
+    <sheet name="Coverage &amp; Tiers" sheetId="25" state="visible" r:id="rId25"/>
+    <sheet name="Methodology" sheetId="26" state="visible" r:id="rId26"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Titles" localSheetId="0">'Contents'!$1:$4</definedName>
@@ -46,19 +47,20 @@
     <definedName name="_xlnm.Print_Titles" localSheetId="9">'MD&amp;A Intent'!$1:$4</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="10">'Payoff Geometry'!$1:$4</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="11">'Mechanism Gates'!$1:$4</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="12">'Winners Study'!$1:$4</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="13">'Asymmetry Assembly'!$1:$4</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="14">'Distressed Stub Progress'!$1:$4</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="15">'Hidden Asset Realisation'!$1:$4</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="16">'UK Capital Events'!$1:$4</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="17">'Without Valuation'!$1:$4</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="18">'Recent 30d'!$1:$4</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="19">'Foreign Markets'!$1:$4</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="20">'Turnaround Signal'!$1:$4</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="21">'Single-Measure Best'!$1:$4</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="22">'Layer Correlation'!$1:$4</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="23">'Coverage &amp; Tiers'!$1:$4</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="24">'Methodology'!$1:$4</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="12">'Re-Rate Catalysts'!$1:$4</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="13">'Winners Study'!$1:$4</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="14">'Asymmetry Assembly'!$1:$4</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="15">'Distressed Stub Progress'!$1:$4</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="16">'Hidden Asset Realisation'!$1:$4</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="17">'UK Capital Events'!$1:$4</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="18">'Without Valuation'!$1:$4</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="19">'Recent 30d'!$1:$4</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="20">'Foreign Markets'!$1:$4</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="21">'Turnaround Signal'!$1:$4</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="22">'Single-Measure Best'!$1:$4</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="23">'Layer Correlation'!$1:$4</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="24">'Coverage &amp; Tiers'!$1:$4</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="25">'Methodology'!$1:$4</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -597,7 +599,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:C30"/>
+  <dimension ref="A1:C31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -810,12 +812,12 @@
       </c>
       <c r="B16" s="9" t="inlineStr">
         <is>
-          <t>Winners Study</t>
+          <t>Re-Rate Catalysts</t>
         </is>
       </c>
       <c r="C16" s="10" t="inlineStr">
         <is>
-          <t>What realized 1-year re-raters had in common — feature/sector lifts, with the pre-move-data caveat.</t>
+          <t>Spin-offs / separations / asset sales / sale-of-company / strategic reviews x geometry room.</t>
         </is>
       </c>
     </row>
@@ -825,12 +827,12 @@
       </c>
       <c r="B17" s="6" t="inlineStr">
         <is>
-          <t>Asymmetry Assembly</t>
+          <t>Winners Study</t>
         </is>
       </c>
       <c r="C17" s="7" t="inlineStr">
         <is>
-          <t>PSIX-recipe conjunction: cheap + inflection + leverage + insider co-occurring.</t>
+          <t>What realized 1-year re-raters had in common — feature/sector lifts, with the pre-move-data caveat.</t>
         </is>
       </c>
     </row>
@@ -840,12 +842,12 @@
       </c>
       <c r="B18" s="9" t="inlineStr">
         <is>
-          <t>Distressed Stub Progress</t>
+          <t>Asymmetry Assembly</t>
         </is>
       </c>
       <c r="C18" s="10" t="inlineStr">
         <is>
-          <t>Finality-gated capital-structure value-unlock events, waterfall-scored.</t>
+          <t>PSIX-recipe conjunction: cheap + inflection + leverage + insider co-occurring.</t>
         </is>
       </c>
     </row>
@@ -855,12 +857,12 @@
       </c>
       <c r="B19" s="6" t="inlineStr">
         <is>
-          <t>Hidden Asset Realisation</t>
+          <t>Distressed Stub Progress</t>
         </is>
       </c>
       <c r="C19" s="7" t="inlineStr">
         <is>
-          <t>Spectrum/rights/RE inside levered stubs with mandatory-prepay debt sweeps (SSP-type).</t>
+          <t>Finality-gated capital-structure value-unlock events, waterfall-scored.</t>
         </is>
       </c>
     </row>
@@ -870,12 +872,12 @@
       </c>
       <c r="B20" s="9" t="inlineStr">
         <is>
-          <t>UK Capital Events</t>
+          <t>Hidden Asset Realisation</t>
         </is>
       </c>
       <c r="C20" s="10" t="inlineStr">
         <is>
-          <t>UK RNS revealed-preference &amp; distressed monitor (separate universe; funds filtered).</t>
+          <t>Spectrum/rights/RE inside levered stubs with mandatory-prepay debt sweeps (SSP-type).</t>
         </is>
       </c>
     </row>
@@ -885,12 +887,12 @@
       </c>
       <c r="B21" s="6" t="inlineStr">
         <is>
-          <t>Without Valuation</t>
+          <t>UK Capital Events</t>
         </is>
       </c>
       <c r="C21" s="7" t="inlineStr">
         <is>
-          <t>Parallel ranking excluding the valuation leg.</t>
+          <t>UK RNS revealed-preference &amp; distressed monitor (separate universe; funds filtered).</t>
         </is>
       </c>
     </row>
@@ -900,12 +902,12 @@
       </c>
       <c r="B22" s="9" t="inlineStr">
         <is>
-          <t>Recent 30d</t>
+          <t>Without Valuation</t>
         </is>
       </c>
       <c r="C22" s="10" t="inlineStr">
         <is>
-          <t>Material incentive events disclosed in the last 30 days.</t>
+          <t>Parallel ranking excluding the valuation leg.</t>
         </is>
       </c>
     </row>
@@ -915,12 +917,12 @@
       </c>
       <c r="B23" s="6" t="inlineStr">
         <is>
-          <t>Foreign Markets</t>
+          <t>Recent 30d</t>
         </is>
       </c>
       <c r="C23" s="7" t="inlineStr">
         <is>
-          <t>Japan TSE PBR&lt;1, Korea Value-Up, UK schemes.</t>
+          <t>Material incentive events disclosed in the last 30 days.</t>
         </is>
       </c>
     </row>
@@ -930,12 +932,12 @@
       </c>
       <c r="B24" s="9" t="inlineStr">
         <is>
-          <t>Turnaround Signal</t>
+          <t>Foreign Markets</t>
         </is>
       </c>
       <c r="C24" s="10" t="inlineStr">
         <is>
-          <t>Bollenbach pattern: turnaround talent into distress.</t>
+          <t>Japan TSE PBR&lt;1, Korea Value-Up, UK schemes.</t>
         </is>
       </c>
     </row>
@@ -945,12 +947,12 @@
       </c>
       <c r="B25" s="6" t="inlineStr">
         <is>
-          <t>Single-Measure Best</t>
+          <t>Turnaround Signal</t>
         </is>
       </c>
       <c r="C25" s="7" t="inlineStr">
         <is>
-          <t>Best in class on each individual signal.</t>
+          <t>Bollenbach pattern: turnaround talent into distress.</t>
         </is>
       </c>
     </row>
@@ -960,12 +962,12 @@
       </c>
       <c r="B26" s="9" t="inlineStr">
         <is>
-          <t>Layer Correlation</t>
+          <t>Single-Measure Best</t>
         </is>
       </c>
       <c r="C26" s="10" t="inlineStr">
         <is>
-          <t>Pairwise layer correlation and effective independence.</t>
+          <t>Best in class on each individual signal.</t>
         </is>
       </c>
     </row>
@@ -975,12 +977,12 @@
       </c>
       <c r="B27" s="6" t="inlineStr">
         <is>
-          <t>Coverage &amp; Tiers</t>
+          <t>Layer Correlation</t>
         </is>
       </c>
       <c r="C27" s="7" t="inlineStr">
         <is>
-          <t>Live per-layer coverage, data age, firing distribution.</t>
+          <t>Pairwise layer correlation and effective independence.</t>
         </is>
       </c>
     </row>
@@ -990,17 +992,32 @@
       </c>
       <c r="B28" s="9" t="inlineStr">
         <is>
+          <t>Coverage &amp; Tiers</t>
+        </is>
+      </c>
+      <c r="C28" s="10" t="inlineStr">
+        <is>
+          <t>Live per-layer coverage, data age, firing distribution.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="16" customHeight="1">
+      <c r="A29" s="5" t="n">
+        <v>25</v>
+      </c>
+      <c r="B29" s="6" t="inlineStr">
+        <is>
           <t>Methodology</t>
         </is>
       </c>
-      <c r="C28" s="10" t="inlineStr">
+      <c r="C29" s="7" t="inlineStr">
         <is>
           <t>How the composite is built, step by step.</t>
         </is>
       </c>
     </row>
-    <row r="30" ht="28" customHeight="1">
-      <c r="A30" s="11" t="inlineStr">
+    <row r="31" ht="28" customHeight="1">
+      <c r="A31" s="11" t="inlineStr">
         <is>
           <t>Generated by build_most_asymmetric_xlsx.py from the live consensus on disk. Every figure in this workbook is computed at build time; nothing is hardcoded. Single typeface (Times New Roman, 10pt); hierarchy by weight and rule only.</t>
         </is>
@@ -1009,7 +1026,7 @@
   </sheetData>
   <mergeCells count="3">
     <mergeCell ref="A1:C1"/>
-    <mergeCell ref="A30:C30"/>
+    <mergeCell ref="A31:C31"/>
     <mergeCell ref="A2:C2"/>
   </mergeCells>
   <printOptions horizontalCentered="0"/>
@@ -6141,6 +6158,1607 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
+  <dimension ref="A1:G56"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="9" customWidth="1" min="1" max="1"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="8" customWidth="1" min="3" max="3"/>
+    <col width="6" customWidth="1" min="4" max="4"/>
+    <col width="7" customWidth="1" min="5" max="5"/>
+    <col width="7" customWidth="1" min="6" max="6"/>
+    <col width="44" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="26" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Re-Rate Catalysts — spin-offs, separations, sales, strategic reviews</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="18" customHeight="1">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>The mechanical re-rates: a spin-off collapses the conglomerate discount, an asset sale monetises non-core and de-levers, a sale of the company delivers a premium. Catalysts triangulated across PSU-incentive (management paid to do it), active tender, and MD&amp;A narrative, then scaled by the payoff-geometry upside room.</t>
+        </is>
+      </c>
+      <c r="B2" s="3" t="n"/>
+      <c r="C2" s="3" t="n"/>
+      <c r="D2" s="3" t="n"/>
+      <c r="E2" s="3" t="n"/>
+      <c r="F2" s="3" t="n"/>
+      <c r="G2" s="3" t="n"/>
+    </row>
+    <row r="3" ht="8" customHeight="1"/>
+    <row r="4" ht="18" customHeight="1">
+      <c r="A4" s="15" t="inlineStr">
+        <is>
+          <t>Ticker</t>
+        </is>
+      </c>
+      <c r="B4" s="15" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="C4" s="4" t="inlineStr">
+        <is>
+          <t>Score</t>
+        </is>
+      </c>
+      <c r="D4" s="4" t="inlineStr">
+        <is>
+          <t>Types</t>
+        </is>
+      </c>
+      <c r="E4" s="4" t="inlineStr">
+        <is>
+          <t>Ratio</t>
+        </is>
+      </c>
+      <c r="F4" s="4" t="inlineStr">
+        <is>
+          <t>Up%</t>
+        </is>
+      </c>
+      <c r="G4" s="4" t="inlineStr">
+        <is>
+          <t>Catalysts (source)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="22" customHeight="1">
+      <c r="A5" s="6" t="inlineStr">
+        <is>
+          <t>BEEP</t>
+        </is>
+      </c>
+      <c r="B5" s="7" t="inlineStr">
+        <is>
+          <t>Mobile Infrastructure</t>
+        </is>
+      </c>
+      <c r="C5" s="16" t="n">
+        <v>33</v>
+      </c>
+      <c r="D5" s="16" t="n">
+        <v>2</v>
+      </c>
+      <c r="E5" s="16" t="n">
+        <v>57.1</v>
+      </c>
+      <c r="F5" s="19" t="n">
+        <v>300</v>
+      </c>
+      <c r="G5" s="7" t="inlineStr">
+        <is>
+          <t>Sale Of Company [incentive]; Spinoff [incent</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="22" customHeight="1">
+      <c r="A6" s="9" t="inlineStr">
+        <is>
+          <t>GNPX</t>
+        </is>
+      </c>
+      <c r="B6" s="10" t="inlineStr">
+        <is>
+          <t>Genprex, Inc.</t>
+        </is>
+      </c>
+      <c r="C6" s="17" t="n">
+        <v>27.5</v>
+      </c>
+      <c r="D6" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="E6" s="17" t="n">
+        <v>30</v>
+      </c>
+      <c r="F6" s="20" t="n">
+        <v>150</v>
+      </c>
+      <c r="G6" s="10" t="inlineStr">
+        <is>
+          <t>Sale Of Company [incentive]; Spinoff [incent</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="22" customHeight="1">
+      <c r="A7" s="6" t="inlineStr">
+        <is>
+          <t>LE</t>
+        </is>
+      </c>
+      <c r="B7" s="7" t="inlineStr">
+        <is>
+          <t>Lands' End, Inc.</t>
+        </is>
+      </c>
+      <c r="C7" s="16" t="n">
+        <v>27.2</v>
+      </c>
+      <c r="D7" s="16" t="n">
+        <v>2</v>
+      </c>
+      <c r="E7" s="16" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="F7" s="19" t="n">
+        <v>176</v>
+      </c>
+      <c r="G7" s="7" t="inlineStr">
+        <is>
+          <t>Sale Of Company [tender]; Strategic Review [</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="22" customHeight="1">
+      <c r="A8" s="9" t="inlineStr">
+        <is>
+          <t>HYFM</t>
+        </is>
+      </c>
+      <c r="B8" s="10" t="inlineStr">
+        <is>
+          <t>Hydrofarm Holdings Gro</t>
+        </is>
+      </c>
+      <c r="C8" s="17" t="n">
+        <v>25.5</v>
+      </c>
+      <c r="D8" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="E8" s="17" t="n">
+        <v>3</v>
+      </c>
+      <c r="F8" s="20" t="n">
+        <v>300</v>
+      </c>
+      <c r="G8" s="10" t="inlineStr">
+        <is>
+          <t>Sale Of Company [incentive]; Strategic Revie</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="22" customHeight="1">
+      <c r="A9" s="6" t="inlineStr">
+        <is>
+          <t>VERI</t>
+        </is>
+      </c>
+      <c r="B9" s="7" t="inlineStr">
+        <is>
+          <t>Veritone, Inc.</t>
+        </is>
+      </c>
+      <c r="C9" s="16" t="n">
+        <v>25.2</v>
+      </c>
+      <c r="D9" s="16" t="n">
+        <v>2</v>
+      </c>
+      <c r="E9" s="16" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="F9" s="19" t="n">
+        <v>86</v>
+      </c>
+      <c r="G9" s="7" t="inlineStr">
+        <is>
+          <t>Sale Of Company [incentive]; Spinoff [incent</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="22" customHeight="1">
+      <c r="A10" s="9" t="inlineStr">
+        <is>
+          <t>TCRT</t>
+        </is>
+      </c>
+      <c r="B10" s="10" t="inlineStr">
+        <is>
+          <t>Alaunos Therapeutics,</t>
+        </is>
+      </c>
+      <c r="C10" s="17" t="n">
+        <v>23.4</v>
+      </c>
+      <c r="D10" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="E10" s="17" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="F10" s="20" t="n">
+        <v>39</v>
+      </c>
+      <c r="G10" s="10" t="inlineStr">
+        <is>
+          <t>Sale Of Company [incentive]; Spinoff [incent</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="22" customHeight="1">
+      <c r="A11" s="6" t="inlineStr">
+        <is>
+          <t>BIRD</t>
+        </is>
+      </c>
+      <c r="B11" s="7" t="inlineStr">
+        <is>
+          <t>Allbirds, Inc.</t>
+        </is>
+      </c>
+      <c r="C11" s="16" t="n">
+        <v>23.3</v>
+      </c>
+      <c r="D11" s="16" t="n">
+        <v>2</v>
+      </c>
+      <c r="E11" s="16" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="F11" s="19" t="n">
+        <v>137</v>
+      </c>
+      <c r="G11" s="7" t="inlineStr">
+        <is>
+          <t>Asset Sale [narrative]; Spinoff [incentive]</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="22" customHeight="1">
+      <c r="A12" s="9" t="inlineStr">
+        <is>
+          <t>QMCO</t>
+        </is>
+      </c>
+      <c r="B12" s="10" t="inlineStr">
+        <is>
+          <t>Quantum Corporation</t>
+        </is>
+      </c>
+      <c r="C12" s="17" t="n">
+        <v>23.2</v>
+      </c>
+      <c r="D12" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="E12" s="17" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="F12" s="20" t="n">
+        <v>134</v>
+      </c>
+      <c r="G12" s="10" t="inlineStr">
+        <is>
+          <t>Spinoff [incentive]; Strategic Review [narra</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="22" customHeight="1">
+      <c r="A13" s="6" t="inlineStr">
+        <is>
+          <t>RYN</t>
+        </is>
+      </c>
+      <c r="B13" s="7" t="inlineStr">
+        <is>
+          <t>Rayonier Inc. REIT</t>
+        </is>
+      </c>
+      <c r="C13" s="16" t="n">
+        <v>22.8</v>
+      </c>
+      <c r="D13" s="16" t="n">
+        <v>2</v>
+      </c>
+      <c r="E13" s="16" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="F13" s="19" t="n">
+        <v>22</v>
+      </c>
+      <c r="G13" s="7" t="inlineStr">
+        <is>
+          <t>Asset Sale [incentive]; Sale Of Company [inc</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="22" customHeight="1">
+      <c r="A14" s="9" t="inlineStr">
+        <is>
+          <t>NUS</t>
+        </is>
+      </c>
+      <c r="B14" s="10" t="inlineStr">
+        <is>
+          <t>Nu Skin Enterprises, I</t>
+        </is>
+      </c>
+      <c r="C14" s="17" t="n">
+        <v>22.5</v>
+      </c>
+      <c r="D14" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="E14" s="17" t="n">
+        <v>60</v>
+      </c>
+      <c r="F14" s="20" t="n">
+        <v>300</v>
+      </c>
+      <c r="G14" s="10" t="inlineStr">
+        <is>
+          <t>Asset Sale [incentive/narrative]</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="22" customHeight="1">
+      <c r="A15" s="6" t="inlineStr">
+        <is>
+          <t>PSTV</t>
+        </is>
+      </c>
+      <c r="B15" s="7" t="inlineStr">
+        <is>
+          <t>PLUS THERAPEUTICS, Inc</t>
+        </is>
+      </c>
+      <c r="C15" s="16" t="n">
+        <v>22.5</v>
+      </c>
+      <c r="D15" s="16" t="n">
+        <v>2</v>
+      </c>
+      <c r="E15" s="16" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="F15" s="19" t="n">
+        <v>12</v>
+      </c>
+      <c r="G15" s="7" t="inlineStr">
+        <is>
+          <t>Sale Of Company [incentive]; Spinoff [incent</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="22" customHeight="1">
+      <c r="A16" s="9" t="inlineStr">
+        <is>
+          <t>PALI</t>
+        </is>
+      </c>
+      <c r="B16" s="10" t="inlineStr">
+        <is>
+          <t>Palisade Bio, Inc.</t>
+        </is>
+      </c>
+      <c r="C16" s="17" t="n">
+        <v>22.4</v>
+      </c>
+      <c r="D16" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="E16" s="17" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F16" s="20" t="n">
+        <v>11</v>
+      </c>
+      <c r="G16" s="10" t="inlineStr">
+        <is>
+          <t>Sale Of Company [incentive]; Spinoff [incent</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="22" customHeight="1">
+      <c r="A17" s="6" t="inlineStr">
+        <is>
+          <t>MNRO</t>
+        </is>
+      </c>
+      <c r="B17" s="7" t="inlineStr">
+        <is>
+          <t>Monro, Inc.</t>
+        </is>
+      </c>
+      <c r="C17" s="16" t="n">
+        <v>22.2</v>
+      </c>
+      <c r="D17" s="16" t="n">
+        <v>2</v>
+      </c>
+      <c r="E17" s="16" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="F17" s="19" t="n">
+        <v>66</v>
+      </c>
+      <c r="G17" s="7" t="inlineStr">
+        <is>
+          <t>Sale Of Company [narrative]; Spinoff [incent</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="22" customHeight="1">
+      <c r="A18" s="9" t="inlineStr">
+        <is>
+          <t>ACAD</t>
+        </is>
+      </c>
+      <c r="B18" s="10" t="inlineStr">
+        <is>
+          <t>ACADIA Pharmaceuticals</t>
+        </is>
+      </c>
+      <c r="C18" s="17" t="n">
+        <v>22</v>
+      </c>
+      <c r="D18" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="E18" s="10" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="F18" s="10" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="G18" s="10" t="inlineStr">
+        <is>
+          <t>Sale Of Company [incentive]; Spinoff [incent</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="22" customHeight="1">
+      <c r="A19" s="6" t="inlineStr">
+        <is>
+          <t>NBIX</t>
+        </is>
+      </c>
+      <c r="B19" s="7" t="inlineStr">
+        <is>
+          <t>Neurocrine Biosciences</t>
+        </is>
+      </c>
+      <c r="C19" s="16" t="n">
+        <v>22</v>
+      </c>
+      <c r="D19" s="16" t="n">
+        <v>2</v>
+      </c>
+      <c r="E19" s="7" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="F19" s="7" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="G19" s="7" t="inlineStr">
+        <is>
+          <t>Sale Of Company [incentive]; Spinoff [incent</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="22" customHeight="1">
+      <c r="A20" s="9" t="inlineStr">
+        <is>
+          <t>SNDX</t>
+        </is>
+      </c>
+      <c r="B20" s="10" t="inlineStr">
+        <is>
+          <t>Syndax Pharmaceuticals</t>
+        </is>
+      </c>
+      <c r="C20" s="17" t="n">
+        <v>22</v>
+      </c>
+      <c r="D20" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="E20" s="10" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="F20" s="10" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="G20" s="10" t="inlineStr">
+        <is>
+          <t>Sale Of Company [incentive]; Spinoff [incent</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="22" customHeight="1">
+      <c r="A21" s="6" t="inlineStr">
+        <is>
+          <t>SENS</t>
+        </is>
+      </c>
+      <c r="B21" s="7" t="inlineStr">
+        <is>
+          <t>Senseonics Holdings, I</t>
+        </is>
+      </c>
+      <c r="C21" s="16" t="n">
+        <v>22</v>
+      </c>
+      <c r="D21" s="16" t="n">
+        <v>2</v>
+      </c>
+      <c r="E21" s="7" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="F21" s="7" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="G21" s="7" t="inlineStr">
+        <is>
+          <t>Sale Of Company [incentive]; Spinoff [incent</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="22" customHeight="1">
+      <c r="A22" s="9" t="inlineStr">
+        <is>
+          <t>MIST</t>
+        </is>
+      </c>
+      <c r="B22" s="10" t="inlineStr">
+        <is>
+          <t>Milestone Pharmaceutic</t>
+        </is>
+      </c>
+      <c r="C22" s="17" t="n">
+        <v>22</v>
+      </c>
+      <c r="D22" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="E22" s="10" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="F22" s="10" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="G22" s="10" t="inlineStr">
+        <is>
+          <t>Sale Of Company [incentive]; Spinoff [incent</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="22" customHeight="1">
+      <c r="A23" s="6" t="inlineStr">
+        <is>
+          <t>WBD</t>
+        </is>
+      </c>
+      <c r="B23" s="7" t="inlineStr">
+        <is>
+          <t>Warner Bros. Discovery</t>
+        </is>
+      </c>
+      <c r="C23" s="16" t="n">
+        <v>22</v>
+      </c>
+      <c r="D23" s="16" t="n">
+        <v>2</v>
+      </c>
+      <c r="E23" s="7" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="F23" s="7" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="G23" s="7" t="inlineStr">
+        <is>
+          <t>Sale Of Company [tender]; Separation [narrat</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="22" customHeight="1">
+      <c r="A24" s="9" t="inlineStr">
+        <is>
+          <t>LSTA</t>
+        </is>
+      </c>
+      <c r="B24" s="10" t="inlineStr">
+        <is>
+          <t>Lisata Therapeutics, I</t>
+        </is>
+      </c>
+      <c r="C24" s="17" t="n">
+        <v>21</v>
+      </c>
+      <c r="D24" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="E24" s="10" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="F24" s="10" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="G24" s="10" t="inlineStr">
+        <is>
+          <t>Sale Of Company [tender]; Strategic Review [</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="22" customHeight="1">
+      <c r="A25" s="6" t="inlineStr">
+        <is>
+          <t>FLEX</t>
+        </is>
+      </c>
+      <c r="B25" s="7" t="inlineStr">
+        <is>
+          <t>Flex Ltd.</t>
+        </is>
+      </c>
+      <c r="C25" s="16" t="n">
+        <v>20</v>
+      </c>
+      <c r="D25" s="16" t="n">
+        <v>2</v>
+      </c>
+      <c r="E25" s="16" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F25" s="19" t="n">
+        <v>32</v>
+      </c>
+      <c r="G25" s="7" t="inlineStr">
+        <is>
+          <t>Asset Sale [narrative]; Spinoff [incentive]</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="22" customHeight="1">
+      <c r="A26" s="9" t="inlineStr">
+        <is>
+          <t>HON</t>
+        </is>
+      </c>
+      <c r="B26" s="10" t="inlineStr">
+        <is>
+          <t>Honeywell Internationa</t>
+        </is>
+      </c>
+      <c r="C26" s="17" t="n">
+        <v>20</v>
+      </c>
+      <c r="D26" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="E26" s="10" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="F26" s="10" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="G26" s="10" t="inlineStr">
+        <is>
+          <t>Separation [narrative]; Spinoff [incentive]</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="22" customHeight="1">
+      <c r="A27" s="6" t="inlineStr">
+        <is>
+          <t>MWA</t>
+        </is>
+      </c>
+      <c r="B27" s="7" t="inlineStr">
+        <is>
+          <t>MUELLER WATER PRODUCTS</t>
+        </is>
+      </c>
+      <c r="C27" s="16" t="n">
+        <v>19</v>
+      </c>
+      <c r="D27" s="16" t="n">
+        <v>2</v>
+      </c>
+      <c r="E27" s="7" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="F27" s="7" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="G27" s="7" t="inlineStr">
+        <is>
+          <t>Asset Sale [narrative]; Spinoff [incentive]</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="22" customHeight="1">
+      <c r="A28" s="9" t="inlineStr">
+        <is>
+          <t>SNOW</t>
+        </is>
+      </c>
+      <c r="B28" s="10" t="inlineStr">
+        <is>
+          <t>Snowflake Inc.</t>
+        </is>
+      </c>
+      <c r="C28" s="17" t="n">
+        <v>19</v>
+      </c>
+      <c r="D28" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="E28" s="10" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="F28" s="10" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="G28" s="10" t="inlineStr">
+        <is>
+          <t>Spinoff [incentive]; Strategic Review [narra</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="22" customHeight="1">
+      <c r="A29" s="6" t="inlineStr">
+        <is>
+          <t>DXLG</t>
+        </is>
+      </c>
+      <c r="B29" s="7" t="inlineStr">
+        <is>
+          <t>Destination XL Group,</t>
+        </is>
+      </c>
+      <c r="C29" s="16" t="n">
+        <v>18</v>
+      </c>
+      <c r="D29" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="E29" s="16" t="n">
+        <v>60</v>
+      </c>
+      <c r="F29" s="19" t="n">
+        <v>300</v>
+      </c>
+      <c r="G29" s="7" t="inlineStr">
+        <is>
+          <t>Sale Of Company [tender]</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="22" customHeight="1">
+      <c r="A30" s="9" t="inlineStr">
+        <is>
+          <t>FUN</t>
+        </is>
+      </c>
+      <c r="B30" s="10" t="inlineStr">
+        <is>
+          <t>Six Flags Entertainmen</t>
+        </is>
+      </c>
+      <c r="C30" s="17" t="n">
+        <v>17</v>
+      </c>
+      <c r="D30" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="E30" s="10" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="F30" s="10" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="G30" s="10" t="inlineStr">
+        <is>
+          <t>Asset Sale [narrative]; Sale Of Company [inc</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="22" customHeight="1">
+      <c r="A31" s="6" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="B31" s="7" t="inlineStr">
+        <is>
+          <t>Macy's Inc</t>
+        </is>
+      </c>
+      <c r="C31" s="16" t="n">
+        <v>17</v>
+      </c>
+      <c r="D31" s="16" t="n">
+        <v>2</v>
+      </c>
+      <c r="E31" s="16" t="n">
+        <v>2</v>
+      </c>
+      <c r="F31" s="19" t="n">
+        <v>127</v>
+      </c>
+      <c r="G31" s="7" t="inlineStr">
+        <is>
+          <t>Asset Sale [narrative]; Strategic Review [na</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="22" customHeight="1">
+      <c r="A32" s="9" t="inlineStr">
+        <is>
+          <t>ETN</t>
+        </is>
+      </c>
+      <c r="B32" s="10" t="inlineStr">
+        <is>
+          <t>Eaton Corporation, PLC</t>
+        </is>
+      </c>
+      <c r="C32" s="17" t="n">
+        <v>16</v>
+      </c>
+      <c r="D32" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="E32" s="10" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="F32" s="10" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="G32" s="10" t="inlineStr">
+        <is>
+          <t>Separation [narrative]; Spinoff [narrative]</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="22" customHeight="1">
+      <c r="A33" s="6" t="inlineStr">
+        <is>
+          <t>GNK</t>
+        </is>
+      </c>
+      <c r="B33" s="7" t="inlineStr">
+        <is>
+          <t>Genco Shipping &amp; Tradi</t>
+        </is>
+      </c>
+      <c r="C33" s="16" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="D33" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="E33" s="16" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="F33" s="19" t="n">
+        <v>174</v>
+      </c>
+      <c r="G33" s="7" t="inlineStr">
+        <is>
+          <t>Sale Of Company [tender]</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="22" customHeight="1">
+      <c r="A34" s="9" t="inlineStr">
+        <is>
+          <t>CNXC</t>
+        </is>
+      </c>
+      <c r="B34" s="10" t="inlineStr">
+        <is>
+          <t>Concentrix Corporation</t>
+        </is>
+      </c>
+      <c r="C34" s="17" t="n">
+        <v>15</v>
+      </c>
+      <c r="D34" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="E34" s="17" t="n">
+        <v>34.9</v>
+      </c>
+      <c r="F34" s="20" t="n">
+        <v>300</v>
+      </c>
+      <c r="G34" s="10" t="inlineStr">
+        <is>
+          <t>Spinoff [incentive]</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="22" customHeight="1">
+      <c r="A35" s="6" t="inlineStr">
+        <is>
+          <t>CLW</t>
+        </is>
+      </c>
+      <c r="B35" s="7" t="inlineStr">
+        <is>
+          <t>Clearwater Paper Corpo</t>
+        </is>
+      </c>
+      <c r="C35" s="16" t="n">
+        <v>15</v>
+      </c>
+      <c r="D35" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="E35" s="16" t="n">
+        <v>60</v>
+      </c>
+      <c r="F35" s="19" t="n">
+        <v>300</v>
+      </c>
+      <c r="G35" s="7" t="inlineStr">
+        <is>
+          <t>Spinoff [incentive]</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="22" customHeight="1">
+      <c r="A36" s="9" t="inlineStr">
+        <is>
+          <t>JTAI</t>
+        </is>
+      </c>
+      <c r="B36" s="10" t="inlineStr">
+        <is>
+          <t>Jet.AI Inc.</t>
+        </is>
+      </c>
+      <c r="C36" s="17" t="n">
+        <v>15</v>
+      </c>
+      <c r="D36" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="E36" s="17" t="n">
+        <v>60</v>
+      </c>
+      <c r="F36" s="20" t="n">
+        <v>300</v>
+      </c>
+      <c r="G36" s="10" t="inlineStr">
+        <is>
+          <t>Spinoff [incentive]</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="22" customHeight="1">
+      <c r="A37" s="6" t="inlineStr">
+        <is>
+          <t>AMS</t>
+        </is>
+      </c>
+      <c r="B37" s="7" t="inlineStr">
+        <is>
+          <t>American Shared Hospit</t>
+        </is>
+      </c>
+      <c r="C37" s="16" t="n">
+        <v>15</v>
+      </c>
+      <c r="D37" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="E37" s="16" t="n">
+        <v>60</v>
+      </c>
+      <c r="F37" s="19" t="n">
+        <v>300</v>
+      </c>
+      <c r="G37" s="7" t="inlineStr">
+        <is>
+          <t>Spinoff [incentive]</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="22" customHeight="1">
+      <c r="A38" s="9" t="inlineStr">
+        <is>
+          <t>ASTH</t>
+        </is>
+      </c>
+      <c r="B38" s="10" t="inlineStr">
+        <is>
+          <t>Astrana Health Inc.</t>
+        </is>
+      </c>
+      <c r="C38" s="17" t="n">
+        <v>15</v>
+      </c>
+      <c r="D38" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="E38" s="17" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="F38" s="20" t="n">
+        <v>300</v>
+      </c>
+      <c r="G38" s="10" t="inlineStr">
+        <is>
+          <t>Spinoff [incentive]</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="22" customHeight="1">
+      <c r="A39" s="6" t="inlineStr">
+        <is>
+          <t>GPRO</t>
+        </is>
+      </c>
+      <c r="B39" s="7" t="inlineStr">
+        <is>
+          <t>GoPro, Inc.</t>
+        </is>
+      </c>
+      <c r="C39" s="16" t="n">
+        <v>15</v>
+      </c>
+      <c r="D39" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="E39" s="16" t="n">
+        <v>3</v>
+      </c>
+      <c r="F39" s="19" t="n">
+        <v>300</v>
+      </c>
+      <c r="G39" s="7" t="inlineStr">
+        <is>
+          <t>Spinoff [incentive]</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="22" customHeight="1">
+      <c r="A40" s="9" t="inlineStr">
+        <is>
+          <t>LGL</t>
+        </is>
+      </c>
+      <c r="B40" s="10" t="inlineStr">
+        <is>
+          <t>LGL Group, Inc. (The)</t>
+        </is>
+      </c>
+      <c r="C40" s="17" t="n">
+        <v>15</v>
+      </c>
+      <c r="D40" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="E40" s="17" t="n">
+        <v>41.6</v>
+      </c>
+      <c r="F40" s="20" t="n">
+        <v>300</v>
+      </c>
+      <c r="G40" s="10" t="inlineStr">
+        <is>
+          <t>Spinoff [incentive]</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="22" customHeight="1">
+      <c r="A41" s="6" t="inlineStr">
+        <is>
+          <t>VREX</t>
+        </is>
+      </c>
+      <c r="B41" s="7" t="inlineStr">
+        <is>
+          <t>Varex Imaging Corporat</t>
+        </is>
+      </c>
+      <c r="C41" s="16" t="n">
+        <v>15</v>
+      </c>
+      <c r="D41" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="E41" s="16" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="F41" s="19" t="n">
+        <v>300</v>
+      </c>
+      <c r="G41" s="7" t="inlineStr">
+        <is>
+          <t>Spinoff [incentive]</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="22" customHeight="1">
+      <c r="A42" s="9" t="inlineStr">
+        <is>
+          <t>PAGP</t>
+        </is>
+      </c>
+      <c r="B42" s="10" t="inlineStr">
+        <is>
+          <t>Plains GP Holdings, L.</t>
+        </is>
+      </c>
+      <c r="C42" s="17" t="n">
+        <v>15</v>
+      </c>
+      <c r="D42" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="E42" s="17" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="F42" s="20" t="n">
+        <v>300</v>
+      </c>
+      <c r="G42" s="10" t="inlineStr">
+        <is>
+          <t>Spinoff [incentive]</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="22" customHeight="1">
+      <c r="A43" s="6" t="inlineStr">
+        <is>
+          <t>NTGR</t>
+        </is>
+      </c>
+      <c r="B43" s="7" t="inlineStr">
+        <is>
+          <t>NETGEAR, Inc.</t>
+        </is>
+      </c>
+      <c r="C43" s="16" t="n">
+        <v>14</v>
+      </c>
+      <c r="D43" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="E43" s="16" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="F43" s="19" t="n">
+        <v>239</v>
+      </c>
+      <c r="G43" s="7" t="inlineStr">
+        <is>
+          <t>Spinoff [incentive]</t>
+        </is>
+      </c>
+    </row>
+    <row r="44" ht="22" customHeight="1">
+      <c r="A44" s="9" t="inlineStr">
+        <is>
+          <t>PKOH</t>
+        </is>
+      </c>
+      <c r="B44" s="10" t="inlineStr">
+        <is>
+          <t>PKOH</t>
+        </is>
+      </c>
+      <c r="C44" s="17" t="n">
+        <v>14</v>
+      </c>
+      <c r="D44" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="E44" s="10" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="F44" s="10" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="G44" s="10" t="inlineStr">
+        <is>
+          <t>Asset Sale [narrative]; Strategic Review [na</t>
+        </is>
+      </c>
+    </row>
+    <row r="45" ht="22" customHeight="1">
+      <c r="A45" s="6" t="inlineStr">
+        <is>
+          <t>SCTH</t>
+        </is>
+      </c>
+      <c r="B45" s="7" t="inlineStr">
+        <is>
+          <t>SCTH</t>
+        </is>
+      </c>
+      <c r="C45" s="16" t="n">
+        <v>14</v>
+      </c>
+      <c r="D45" s="16" t="n">
+        <v>2</v>
+      </c>
+      <c r="E45" s="7" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="F45" s="7" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="G45" s="7" t="inlineStr">
+        <is>
+          <t>Asset Sale [narrative]; Strategic Review [na</t>
+        </is>
+      </c>
+    </row>
+    <row r="46" ht="22" customHeight="1">
+      <c r="A46" s="9" t="inlineStr">
+        <is>
+          <t>RCMT</t>
+        </is>
+      </c>
+      <c r="B46" s="10" t="inlineStr">
+        <is>
+          <t>RCM Technologies, Inc.</t>
+        </is>
+      </c>
+      <c r="C46" s="17" t="n">
+        <v>13.7</v>
+      </c>
+      <c r="D46" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="E46" s="17" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="F46" s="20" t="n">
+        <v>224</v>
+      </c>
+      <c r="G46" s="10" t="inlineStr">
+        <is>
+          <t>Spinoff [incentive]</t>
+        </is>
+      </c>
+    </row>
+    <row r="47" ht="22" customHeight="1">
+      <c r="A47" s="6" t="inlineStr">
+        <is>
+          <t>LBTYK</t>
+        </is>
+      </c>
+      <c r="B47" s="7" t="inlineStr">
+        <is>
+          <t>Liberty Global Ltd.</t>
+        </is>
+      </c>
+      <c r="C47" s="16" t="n">
+        <v>13.6</v>
+      </c>
+      <c r="D47" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="E47" s="16" t="n">
+        <v>43</v>
+      </c>
+      <c r="F47" s="19" t="n">
+        <v>215</v>
+      </c>
+      <c r="G47" s="7" t="inlineStr">
+        <is>
+          <t>Spinoff [incentive]</t>
+        </is>
+      </c>
+    </row>
+    <row r="48" ht="22" customHeight="1">
+      <c r="A48" s="9" t="inlineStr">
+        <is>
+          <t>BAX</t>
+        </is>
+      </c>
+      <c r="B48" s="10" t="inlineStr">
+        <is>
+          <t>Baxter International I</t>
+        </is>
+      </c>
+      <c r="C48" s="17" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="D48" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="E48" s="17" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="F48" s="20" t="n">
+        <v>200</v>
+      </c>
+      <c r="G48" s="10" t="inlineStr">
+        <is>
+          <t>Asset Sale [incentive]</t>
+        </is>
+      </c>
+    </row>
+    <row r="49" ht="22" customHeight="1">
+      <c r="A49" s="6" t="inlineStr">
+        <is>
+          <t>OWLT</t>
+        </is>
+      </c>
+      <c r="B49" s="7" t="inlineStr">
+        <is>
+          <t>Owlet, Inc.</t>
+        </is>
+      </c>
+      <c r="C49" s="16" t="n">
+        <v>13.1</v>
+      </c>
+      <c r="D49" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="E49" s="16" t="n">
+        <v>2</v>
+      </c>
+      <c r="F49" s="19" t="n">
+        <v>183</v>
+      </c>
+      <c r="G49" s="7" t="inlineStr">
+        <is>
+          <t>Spinoff [incentive]</t>
+        </is>
+      </c>
+    </row>
+    <row r="50" ht="22" customHeight="1">
+      <c r="A50" s="9" t="inlineStr">
+        <is>
+          <t>RGR</t>
+        </is>
+      </c>
+      <c r="B50" s="10" t="inlineStr">
+        <is>
+          <t>Sturm, Ruger &amp; Company</t>
+        </is>
+      </c>
+      <c r="C50" s="17" t="n">
+        <v>13.1</v>
+      </c>
+      <c r="D50" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="E50" s="17" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="F50" s="20" t="n">
+        <v>53</v>
+      </c>
+      <c r="G50" s="10" t="inlineStr">
+        <is>
+          <t>Sale Of Company [tender]</t>
+        </is>
+      </c>
+    </row>
+    <row r="51" ht="22" customHeight="1">
+      <c r="A51" s="6" t="inlineStr">
+        <is>
+          <t>ASRT</t>
+        </is>
+      </c>
+      <c r="B51" s="7" t="inlineStr">
+        <is>
+          <t>Assertio Holdings, Inc</t>
+        </is>
+      </c>
+      <c r="C51" s="16" t="n">
+        <v>13</v>
+      </c>
+      <c r="D51" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="E51" s="16" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="F51" s="19" t="n">
+        <v>52</v>
+      </c>
+      <c r="G51" s="7" t="inlineStr">
+        <is>
+          <t>Sale Of Company [tender]</t>
+        </is>
+      </c>
+    </row>
+    <row r="52" ht="22" customHeight="1">
+      <c r="A52" s="9" t="inlineStr">
+        <is>
+          <t>FSK</t>
+        </is>
+      </c>
+      <c r="B52" s="10" t="inlineStr">
+        <is>
+          <t>FS KKR Capital Corp.</t>
+        </is>
+      </c>
+      <c r="C52" s="17" t="n">
+        <v>13</v>
+      </c>
+      <c r="D52" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="E52" s="17" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="F52" s="20" t="n">
+        <v>52</v>
+      </c>
+      <c r="G52" s="10" t="inlineStr">
+        <is>
+          <t>Sale Of Company [tender]</t>
+        </is>
+      </c>
+    </row>
+    <row r="53" ht="22" customHeight="1">
+      <c r="A53" s="6" t="inlineStr">
+        <is>
+          <t>GDRX</t>
+        </is>
+      </c>
+      <c r="B53" s="7" t="inlineStr">
+        <is>
+          <t>GoodRx Holdings, Inc.</t>
+        </is>
+      </c>
+      <c r="C53" s="16" t="n">
+        <v>12.9</v>
+      </c>
+      <c r="D53" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="E53" s="16" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="F53" s="19" t="n">
+        <v>172</v>
+      </c>
+      <c r="G53" s="7" t="inlineStr">
+        <is>
+          <t>Spinoff [incentive]</t>
+        </is>
+      </c>
+    </row>
+    <row r="54" ht="22" customHeight="1">
+      <c r="A54" s="9" t="inlineStr">
+        <is>
+          <t>GLIBK</t>
+        </is>
+      </c>
+      <c r="B54" s="10" t="inlineStr">
+        <is>
+          <t>Liberty Capital Corpor</t>
+        </is>
+      </c>
+      <c r="C54" s="17" t="n">
+        <v>12.7</v>
+      </c>
+      <c r="D54" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="E54" s="17" t="n">
+        <v>32.9</v>
+      </c>
+      <c r="F54" s="20" t="n">
+        <v>164</v>
+      </c>
+      <c r="G54" s="10" t="inlineStr">
+        <is>
+          <t>Spinoff [incentive]</t>
+        </is>
+      </c>
+    </row>
+    <row r="56" ht="28" customHeight="1">
+      <c r="A56" s="11" t="inlineStr">
+        <is>
+          <t>382 names carry a corporate-action re-rate catalyst (28 carry two or more types). Distribution: spinoff 125, sale of company 119, strategic review 78, asset sale 77, separation 11. Sources by hardness: INCENTIVE = the PSU plan pays management to achieve the spin/sale/M&amp;A (skin in the game, hardest); TENDER = a live bid (role TARGET); NARRATIVE = management states the intent in the 10-K/10-Q MD&amp;A. A catalyst named by two independent sources is triangulated (+bonus); two distinct catalyst types is the in-play configuration. Score = catalyst strength x (1 + geometry upside room), so a spin/sale with real re-rate headroom outranks one in an already-fair-valued name (rows with '—' ratio have no value-geometry floor — typically large-caps where the re-rate is a discount-collapse story, not an asset-floor play). Source: rerate_catalysts.py.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="3">
+    <mergeCell ref="A2:G2"/>
+    <mergeCell ref="A1:G1"/>
+    <mergeCell ref="A56:G56"/>
+  </mergeCells>
+  <printOptions horizontalCentered="0"/>
+  <pageMargins left="0.5" right="0.5" top="0.6" bottom="0.6" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
   <dimension ref="A1:E29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -6664,7 +8282,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -7620,7 +9238,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -9200,7 +10818,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -10695,7 +12313,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -10860,7 +12478,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -11977,1722 +13595,6 @@
     <mergeCell ref="A36:H36"/>
     <mergeCell ref="A2:H2"/>
     <mergeCell ref="A1:H1"/>
-  </mergeCells>
-  <printOptions horizontalCentered="0"/>
-  <pageMargins left="0.5" right="0.5" top="0.6" bottom="0.6" header="0.5" footer="0.5"/>
-  <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="1"/>
-  </sheetPr>
-  <dimension ref="A1:J46"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="9" customWidth="1" min="1" max="1"/>
-    <col width="13" customWidth="1" min="2" max="2"/>
-    <col width="32" customWidth="1" min="3" max="3"/>
-    <col width="12" customWidth="1" min="4" max="4"/>
-    <col width="8" customWidth="1" min="5" max="5"/>
-    <col width="22" customWidth="1" min="6" max="6"/>
-    <col width="8" customWidth="1" min="7" max="7"/>
-    <col width="6" customWidth="1" min="8" max="8"/>
-    <col width="12" customWidth="1" min="9" max="9"/>
-    <col width="50" customWidth="1" min="10" max="10"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="26" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Stale-Pricing Asymmetry -- Last 30 days</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="18" customHeight="1">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>Names where a material incentive event was disclosed in the last 30 days AND the price has not yet reflected it. Tightest possible information-lag window.</t>
-        </is>
-      </c>
-      <c r="B2" s="3" t="n"/>
-      <c r="C2" s="3" t="n"/>
-      <c r="D2" s="3" t="n"/>
-      <c r="E2" s="3" t="n"/>
-      <c r="F2" s="3" t="n"/>
-      <c r="G2" s="3" t="n"/>
-      <c r="H2" s="3" t="n"/>
-      <c r="I2" s="3" t="n"/>
-      <c r="J2" s="3" t="n"/>
-    </row>
-    <row r="3" ht="8" customHeight="1"/>
-    <row r="4" ht="18" customHeight="1">
-      <c r="A4" s="4" t="inlineStr">
-        <is>
-          <t>#</t>
-        </is>
-      </c>
-      <c r="B4" s="15" t="inlineStr">
-        <is>
-          <t>Ticker</t>
-        </is>
-      </c>
-      <c r="C4" s="15" t="inlineStr">
-        <is>
-          <t>Name</t>
-        </is>
-      </c>
-      <c r="D4" s="4" t="inlineStr">
-        <is>
-          <t>Score</t>
-        </is>
-      </c>
-      <c r="E4" s="4" t="inlineStr">
-        <is>
-          <t>Days</t>
-        </is>
-      </c>
-      <c r="F4" s="4" t="inlineStr">
-        <is>
-          <t>Event kind</t>
-        </is>
-      </c>
-      <c r="G4" s="4" t="inlineStr">
-        <is>
-          <t>Inner</t>
-        </is>
-      </c>
-      <c r="H4" s="4" t="inlineStr">
-        <is>
-          <t>DD%</t>
-        </is>
-      </c>
-      <c r="I4" s="4" t="inlineStr">
-        <is>
-          <t>P/B</t>
-        </is>
-      </c>
-      <c r="J4" s="15" t="inlineStr">
-        <is>
-          <t>Reasons</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="22" customHeight="1">
-      <c r="A5" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="B5" s="6" t="inlineStr">
-        <is>
-          <t>RPAY</t>
-        </is>
-      </c>
-      <c r="C5" s="7" t="inlineStr">
-        <is>
-          <t>Repay Holdings Corporation</t>
-        </is>
-      </c>
-      <c r="D5" s="22" t="n">
-        <v>68</v>
-      </c>
-      <c r="E5" s="5" t="n">
-        <v>6</v>
-      </c>
-      <c r="F5" s="7" t="inlineStr">
-        <is>
-          <t>RESTRUCT_8K</t>
-        </is>
-      </c>
-      <c r="G5" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="H5" s="19" t="n">
-        <v>44</v>
-      </c>
-      <c r="I5" s="16" t="n">
-        <v>0.49123317</v>
-      </c>
-      <c r="J5" s="7" t="inlineStr">
-        <is>
-          <t>event 6d ago; RESTRUCT_8K; 2 events in 30d; DD 44%; P/B 0.49</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="22" customHeight="1">
-      <c r="A6" s="8" t="n">
-        <v>2</v>
-      </c>
-      <c r="B6" s="9" t="inlineStr">
-        <is>
-          <t>GOSS</t>
-        </is>
-      </c>
-      <c r="C6" s="10" t="inlineStr">
-        <is>
-          <t>Gossamer Bio, Inc.</t>
-        </is>
-      </c>
-      <c r="D6" s="22" t="n">
-        <v>61</v>
-      </c>
-      <c r="E6" s="8" t="n">
-        <v>4</v>
-      </c>
-      <c r="F6" s="10" t="inlineStr">
-        <is>
-          <t>RESTRUCT_8K</t>
-        </is>
-      </c>
-      <c r="G6" s="8" t="n">
-        <v>2</v>
-      </c>
-      <c r="H6" s="20" t="n">
-        <v>96</v>
-      </c>
-      <c r="I6" s="17" t="n">
-        <v>-0.24418603</v>
-      </c>
-      <c r="J6" s="10" t="inlineStr">
-        <is>
-          <t>event 4d ago; RESTRUCT_8K; 2 events in 30d; DD 96% (unpriced)</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="22" customHeight="1">
-      <c r="A7" s="5" t="n">
-        <v>3</v>
-      </c>
-      <c r="B7" s="6" t="inlineStr">
-        <is>
-          <t>GTM</t>
-        </is>
-      </c>
-      <c r="C7" s="7" t="inlineStr">
-        <is>
-          <t>ZoomInfo Technologies Inc.</t>
-        </is>
-      </c>
-      <c r="D7" s="22" t="n">
-        <v>60</v>
-      </c>
-      <c r="E7" s="5" t="n">
-        <v>5</v>
-      </c>
-      <c r="F7" s="7" t="inlineStr">
-        <is>
-          <t>ACTIVIST_13D</t>
-        </is>
-      </c>
-      <c r="G7" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="H7" s="19" t="n">
-        <v>78</v>
-      </c>
-      <c r="I7" s="16" t="n">
-        <v>0.56459713</v>
-      </c>
-      <c r="J7" s="7" t="inlineStr">
-        <is>
-          <t>event 5d ago; 2 events in 30d; DD 78% (unpriced); only 8% above 52w low</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="22" customHeight="1">
-      <c r="A8" s="8" t="n">
-        <v>4</v>
-      </c>
-      <c r="B8" s="9" t="inlineStr">
-        <is>
-          <t>GSHD</t>
-        </is>
-      </c>
-      <c r="C8" s="10" t="inlineStr">
-        <is>
-          <t>Goosehead Insurance, Inc.</t>
-        </is>
-      </c>
-      <c r="D8" s="22" t="n">
-        <v>53</v>
-      </c>
-      <c r="E8" s="8" t="n">
-        <v>20</v>
-      </c>
-      <c r="F8" s="10" t="inlineStr">
-        <is>
-          <t>F4_PBUY</t>
-        </is>
-      </c>
-      <c r="G8" s="8" t="n">
-        <v>2</v>
-      </c>
-      <c r="H8" s="20" t="n">
-        <v>70</v>
-      </c>
-      <c r="I8" s="17" t="n">
-        <v>-6.708959</v>
-      </c>
-      <c r="J8" s="10" t="inlineStr">
-        <is>
-          <t>event 20d ago; insider P-buy; 2 events in 30d; DD 70% (unpriced); only 2% above 52w low</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="22" customHeight="1">
-      <c r="A9" s="5" t="n">
-        <v>5</v>
-      </c>
-      <c r="B9" s="6" t="inlineStr">
-        <is>
-          <t>GWRE</t>
-        </is>
-      </c>
-      <c r="C9" s="7" t="inlineStr">
-        <is>
-          <t>Guidewire Software, Inc.</t>
-        </is>
-      </c>
-      <c r="D9" s="22" t="n">
-        <v>53</v>
-      </c>
-      <c r="E9" s="5" t="n">
-        <v>16</v>
-      </c>
-      <c r="F9" s="7" t="inlineStr">
-        <is>
-          <t>10b5-1_TERM</t>
-        </is>
-      </c>
-      <c r="G9" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="H9" s="19" t="n">
-        <v>60</v>
-      </c>
-      <c r="I9" s="16" t="n">
-        <v>6.817952</v>
-      </c>
-      <c r="J9" s="7" t="inlineStr">
-        <is>
-          <t>event 16d ago; 10b5-1 termination; DD 60% (unpriced); only 1% above 52w low</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="22" customHeight="1">
-      <c r="A10" s="8" t="n">
-        <v>6</v>
-      </c>
-      <c r="B10" s="9" t="inlineStr">
-        <is>
-          <t>CMTL</t>
-        </is>
-      </c>
-      <c r="C10" s="10" t="inlineStr">
-        <is>
-          <t>Comtech Telecommunications Corp</t>
-        </is>
-      </c>
-      <c r="D10" s="22" t="n">
-        <v>52</v>
-      </c>
-      <c r="E10" s="8" t="n">
-        <v>4</v>
-      </c>
-      <c r="F10" s="10" t="inlineStr">
-        <is>
-          <t>ACTIVIST_13D</t>
-        </is>
-      </c>
-      <c r="G10" s="8" t="n">
-        <v>2</v>
-      </c>
-      <c r="H10" s="20" t="n">
-        <v>61</v>
-      </c>
-      <c r="I10" s="17" t="n">
-        <v>0.67586595</v>
-      </c>
-      <c r="J10" s="10" t="inlineStr">
-        <is>
-          <t>event 4d ago; 2 events in 30d; DD 61% (unpriced)</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="22" customHeight="1">
-      <c r="A11" s="5" t="n">
-        <v>7</v>
-      </c>
-      <c r="B11" s="6" t="inlineStr">
-        <is>
-          <t>PHGE</t>
-        </is>
-      </c>
-      <c r="C11" s="7" t="inlineStr">
-        <is>
-          <t>BiomX Inc.</t>
-        </is>
-      </c>
-      <c r="D11" s="22" t="n">
-        <v>52</v>
-      </c>
-      <c r="E11" s="5" t="n">
-        <v>5</v>
-      </c>
-      <c r="F11" s="7" t="inlineStr">
-        <is>
-          <t>ACTIVIST_13D</t>
-        </is>
-      </c>
-      <c r="G11" s="5" t="n">
-        <v>3</v>
-      </c>
-      <c r="H11" s="19" t="n">
-        <v>96</v>
-      </c>
-      <c r="I11" s="16" t="n">
-        <v>-0.041595332</v>
-      </c>
-      <c r="J11" s="7" t="inlineStr">
-        <is>
-          <t>event 5d ago; 3 events in 30d; DD 96% (unpriced)</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="22" customHeight="1">
-      <c r="A12" s="8" t="n">
-        <v>8</v>
-      </c>
-      <c r="B12" s="9" t="inlineStr">
-        <is>
-          <t>CHPT</t>
-        </is>
-      </c>
-      <c r="C12" s="10" t="inlineStr">
-        <is>
-          <t>ChargePoint Holdings, Inc.</t>
-        </is>
-      </c>
-      <c r="D12" s="22" t="n">
-        <v>52</v>
-      </c>
-      <c r="E12" s="8" t="n">
-        <v>13</v>
-      </c>
-      <c r="F12" s="10" t="inlineStr">
-        <is>
-          <t>10b5-1_TERM</t>
-        </is>
-      </c>
-      <c r="G12" s="8" t="n">
-        <v>2</v>
-      </c>
-      <c r="H12" s="20" t="n">
-        <v>49</v>
-      </c>
-      <c r="I12" s="17" t="n">
-        <v>-23.675215</v>
-      </c>
-      <c r="J12" s="10" t="inlineStr">
-        <is>
-          <t>event 13d ago; 10b5-1 termination; 2 events in 30d; DD 49%</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="22" customHeight="1">
-      <c r="A13" s="5" t="n">
-        <v>9</v>
-      </c>
-      <c r="B13" s="6" t="inlineStr">
-        <is>
-          <t>DXC</t>
-        </is>
-      </c>
-      <c r="C13" s="7" t="inlineStr">
-        <is>
-          <t>DXC Technology Company</t>
-        </is>
-      </c>
-      <c r="D13" s="22" t="n">
-        <v>52</v>
-      </c>
-      <c r="E13" s="5" t="n">
-        <v>17</v>
-      </c>
-      <c r="F13" s="7" t="inlineStr">
-        <is>
-          <t>DEF14A_PSU</t>
-        </is>
-      </c>
-      <c r="G13" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="H13" s="19" t="n">
-        <v>48</v>
-      </c>
-      <c r="I13" s="16" t="n">
-        <v>0.4839073</v>
-      </c>
-      <c r="J13" s="7" t="inlineStr">
-        <is>
-          <t>event 17d ago; PSU/gov in latest proxy; DD 48%; only 9% above 52w low; P/B 0.48</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="22" customHeight="1">
-      <c r="A14" s="8" t="n">
-        <v>10</v>
-      </c>
-      <c r="B14" s="9" t="inlineStr">
-        <is>
-          <t>PCSA</t>
-        </is>
-      </c>
-      <c r="C14" s="10" t="inlineStr">
-        <is>
-          <t>Processa Pharmaceuticals, Inc.</t>
-        </is>
-      </c>
-      <c r="D14" s="22" t="n">
-        <v>51</v>
-      </c>
-      <c r="E14" s="8" t="n">
-        <v>20</v>
-      </c>
-      <c r="F14" s="10" t="inlineStr">
-        <is>
-          <t>F4_PBUY</t>
-        </is>
-      </c>
-      <c r="G14" s="8" t="n">
-        <v>5</v>
-      </c>
-      <c r="H14" s="20" t="n">
-        <v>86</v>
-      </c>
-      <c r="I14" s="17" t="n">
-        <v>2.950474</v>
-      </c>
-      <c r="J14" s="10" t="inlineStr">
-        <is>
-          <t>event 20d ago; insider P-buy; 5 events in 30d; DD 86% (unpriced)</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="22" customHeight="1">
-      <c r="A15" s="5" t="n">
-        <v>11</v>
-      </c>
-      <c r="B15" s="6" t="inlineStr">
-        <is>
-          <t>BTU</t>
-        </is>
-      </c>
-      <c r="C15" s="7" t="inlineStr">
-        <is>
-          <t>Peabody Energy Corporation</t>
-        </is>
-      </c>
-      <c r="D15" s="22" t="n">
-        <v>51</v>
-      </c>
-      <c r="E15" s="5" t="n">
-        <v>6</v>
-      </c>
-      <c r="F15" s="7" t="inlineStr">
-        <is>
-          <t>RESTRUCT_8K</t>
-        </is>
-      </c>
-      <c r="G15" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="H15" s="19" t="n">
-        <v>36</v>
-      </c>
-      <c r="I15" s="16" t="n">
-        <v>0.91458744</v>
-      </c>
-      <c r="J15" s="7" t="inlineStr">
-        <is>
-          <t>event 6d ago; RESTRUCT_8K</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="22" customHeight="1">
-      <c r="A16" s="8" t="n">
-        <v>12</v>
-      </c>
-      <c r="B16" s="9" t="inlineStr">
-        <is>
-          <t>RC</t>
-        </is>
-      </c>
-      <c r="C16" s="10" t="inlineStr">
-        <is>
-          <t>Ready Capital Corporation</t>
-        </is>
-      </c>
-      <c r="D16" s="22" t="n">
-        <v>49</v>
-      </c>
-      <c r="E16" s="8" t="n">
-        <v>20</v>
-      </c>
-      <c r="F16" s="10" t="inlineStr">
-        <is>
-          <t>DEF14A_PSU</t>
-        </is>
-      </c>
-      <c r="G16" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="H16" s="20" t="n">
-        <v>63</v>
-      </c>
-      <c r="I16" s="17" t="n">
-        <v>0.23546824</v>
-      </c>
-      <c r="J16" s="10" t="inlineStr">
-        <is>
-          <t>event 20d ago; PSU/gov in latest proxy; DD 63% (unpriced); P/B 0.24</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="22" customHeight="1">
-      <c r="A17" s="5" t="n">
-        <v>13</v>
-      </c>
-      <c r="B17" s="6" t="inlineStr">
-        <is>
-          <t>KWY</t>
-        </is>
-      </c>
-      <c r="C17" s="7" t="inlineStr">
-        <is>
-          <t>Kingsway Corporation</t>
-        </is>
-      </c>
-      <c r="D17" s="22" t="n">
-        <v>49</v>
-      </c>
-      <c r="E17" s="5" t="n">
-        <v>20</v>
-      </c>
-      <c r="F17" s="7" t="inlineStr">
-        <is>
-          <t>F4_PBUY</t>
-        </is>
-      </c>
-      <c r="G17" s="5" t="n">
-        <v>3</v>
-      </c>
-      <c r="H17" s="19" t="n">
-        <v>39</v>
-      </c>
-      <c r="I17" s="16" t="n">
-        <v>22.396515</v>
-      </c>
-      <c r="J17" s="7" t="inlineStr">
-        <is>
-          <t>event 20d ago; insider P-buy; 3 events in 30d; only 5% above 52w low</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="22" customHeight="1">
-      <c r="A18" s="8" t="n">
-        <v>14</v>
-      </c>
-      <c r="B18" s="9" t="inlineStr">
-        <is>
-          <t>HRTX</t>
-        </is>
-      </c>
-      <c r="C18" s="10" t="inlineStr">
-        <is>
-          <t>Heron Therapeutics, Inc.</t>
-        </is>
-      </c>
-      <c r="D18" s="22" t="n">
-        <v>48</v>
-      </c>
-      <c r="E18" s="8" t="n">
-        <v>5</v>
-      </c>
-      <c r="F18" s="10" t="inlineStr">
-        <is>
-          <t>NOL_SHELL</t>
-        </is>
-      </c>
-      <c r="G18" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="H18" s="20" t="n">
-        <v>82</v>
-      </c>
-      <c r="I18" s="17" t="n">
-        <v>9.709301999999999</v>
-      </c>
-      <c r="J18" s="10" t="inlineStr">
-        <is>
-          <t>event 5d ago; DD 82% (unpriced); only 10% above 52w low</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="22" customHeight="1">
-      <c r="A19" s="5" t="n">
-        <v>15</v>
-      </c>
-      <c r="B19" s="6" t="inlineStr">
-        <is>
-          <t>LAB</t>
-        </is>
-      </c>
-      <c r="C19" s="7" t="inlineStr">
-        <is>
-          <t>Standard BioTools Inc.</t>
-        </is>
-      </c>
-      <c r="D19" s="22" t="n">
-        <v>48</v>
-      </c>
-      <c r="E19" s="5" t="n">
-        <v>12</v>
-      </c>
-      <c r="F19" s="7" t="inlineStr">
-        <is>
-          <t>ACTIVIST_13D</t>
-        </is>
-      </c>
-      <c r="G19" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="H19" s="19" t="n">
-        <v>52</v>
-      </c>
-      <c r="I19" s="16" t="n">
-        <v>0.5769819</v>
-      </c>
-      <c r="J19" s="7" t="inlineStr">
-        <is>
-          <t>event 12d ago; 2 events in 30d; DD 52%; only 5% above 52w low</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="22" customHeight="1">
-      <c r="A20" s="8" t="n">
-        <v>16</v>
-      </c>
-      <c r="B20" s="9" t="inlineStr">
-        <is>
-          <t>NSPR</t>
-        </is>
-      </c>
-      <c r="C20" s="10" t="inlineStr">
-        <is>
-          <t>InspireMD Inc.</t>
-        </is>
-      </c>
-      <c r="D20" s="22" t="n">
-        <v>47</v>
-      </c>
-      <c r="E20" s="8" t="n">
-        <v>23</v>
-      </c>
-      <c r="F20" s="10" t="inlineStr">
-        <is>
-          <t>F4_PBUY</t>
-        </is>
-      </c>
-      <c r="G20" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="H20" s="20" t="n">
-        <v>76</v>
-      </c>
-      <c r="I20" s="17" t="n">
-        <v>0.7626208</v>
-      </c>
-      <c r="J20" s="10" t="inlineStr">
-        <is>
-          <t>event 23d ago; insider P-buy; DD 76% (unpriced); only 3% above 52w low</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="22" customHeight="1">
-      <c r="A21" s="5" t="n">
-        <v>17</v>
-      </c>
-      <c r="B21" s="6" t="inlineStr">
-        <is>
-          <t>RNTX</t>
-        </is>
-      </c>
-      <c r="C21" s="7" t="inlineStr">
-        <is>
-          <t>Rein Therapeutics, Inc.</t>
-        </is>
-      </c>
-      <c r="D21" s="22" t="n">
-        <v>46</v>
-      </c>
-      <c r="E21" s="5" t="n">
-        <v>13</v>
-      </c>
-      <c r="F21" s="7" t="inlineStr">
-        <is>
-          <t>DEF14A_PSU</t>
-        </is>
-      </c>
-      <c r="G21" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="H21" s="19" t="n">
-        <v>58</v>
-      </c>
-      <c r="I21" s="16" t="n">
-        <v>-0.7682047</v>
-      </c>
-      <c r="J21" s="7" t="inlineStr">
-        <is>
-          <t>event 13d ago; PSU/gov in latest proxy; DD 58%; only 6% above 52w low</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="22" customHeight="1">
-      <c r="A22" s="8" t="n">
-        <v>18</v>
-      </c>
-      <c r="B22" s="9" t="inlineStr">
-        <is>
-          <t>BAH</t>
-        </is>
-      </c>
-      <c r="C22" s="10" t="inlineStr">
-        <is>
-          <t>Booz Allen Hamilton Holding Cor</t>
-        </is>
-      </c>
-      <c r="D22" s="22" t="n">
-        <v>46</v>
-      </c>
-      <c r="E22" s="8" t="n">
-        <v>10</v>
-      </c>
-      <c r="F22" s="10" t="inlineStr">
-        <is>
-          <t>DEF14A_PSU</t>
-        </is>
-      </c>
-      <c r="G22" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="H22" s="20" t="n">
-        <v>45</v>
-      </c>
-      <c r="I22" s="17" t="n">
-        <v>7.2271833</v>
-      </c>
-      <c r="J22" s="10" t="inlineStr">
-        <is>
-          <t>event 10d ago; PSU/gov in latest proxy; DD 45%; only 0% above 52w low</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="22" customHeight="1">
-      <c r="A23" s="5" t="n">
-        <v>19</v>
-      </c>
-      <c r="B23" s="6" t="inlineStr">
-        <is>
-          <t>VNRX</t>
-        </is>
-      </c>
-      <c r="C23" s="7" t="inlineStr">
-        <is>
-          <t>VolitionRX Limited</t>
-        </is>
-      </c>
-      <c r="D23" s="22" t="n">
-        <v>45</v>
-      </c>
-      <c r="E23" s="5" t="n">
-        <v>19</v>
-      </c>
-      <c r="F23" s="7" t="inlineStr">
-        <is>
-          <t>DEF14A_PSU</t>
-        </is>
-      </c>
-      <c r="G23" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="H23" s="19" t="n">
-        <v>92</v>
-      </c>
-      <c r="I23" s="16" t="n">
-        <v>-0.26262623</v>
-      </c>
-      <c r="J23" s="7" t="inlineStr">
-        <is>
-          <t>event 19d ago; PSU/gov in latest proxy; DD 92% (unpriced); only 10% above 52w low</t>
-        </is>
-      </c>
-    </row>
-    <row r="24" ht="22" customHeight="1">
-      <c r="A24" s="8" t="n">
-        <v>20</v>
-      </c>
-      <c r="B24" s="9" t="inlineStr">
-        <is>
-          <t>SWZ</t>
-        </is>
-      </c>
-      <c r="C24" s="10" t="inlineStr">
-        <is>
-          <t>Total Return Securities Fund</t>
-        </is>
-      </c>
-      <c r="D24" s="22" t="n">
-        <v>44</v>
-      </c>
-      <c r="E24" s="8" t="n">
-        <v>20</v>
-      </c>
-      <c r="F24" s="10" t="inlineStr">
-        <is>
-          <t>F4_PBUY</t>
-        </is>
-      </c>
-      <c r="G24" s="8" t="n">
-        <v>2</v>
-      </c>
-      <c r="H24" s="20" t="n">
-        <v>8</v>
-      </c>
-      <c r="I24" s="17" t="n">
-        <v>0.8557581</v>
-      </c>
-      <c r="J24" s="10" t="inlineStr">
-        <is>
-          <t>event 20d ago; insider P-buy; 2 events in 30d; only 1% above 52w low</t>
-        </is>
-      </c>
-    </row>
-    <row r="25" ht="22" customHeight="1">
-      <c r="A25" s="5" t="n">
-        <v>21</v>
-      </c>
-      <c r="B25" s="6" t="inlineStr">
-        <is>
-          <t>FOX</t>
-        </is>
-      </c>
-      <c r="C25" s="7" t="inlineStr">
-        <is>
-          <t>Fox Corporation</t>
-        </is>
-      </c>
-      <c r="D25" s="22" t="n">
-        <v>44</v>
-      </c>
-      <c r="E25" s="5" t="n">
-        <v>5</v>
-      </c>
-      <c r="F25" s="7" t="inlineStr">
-        <is>
-          <t>ACTIVIST_13D</t>
-        </is>
-      </c>
-      <c r="G25" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="H25" s="19" t="n">
-        <v>31</v>
-      </c>
-      <c r="I25" s="16" t="n">
-        <v>1.8010588</v>
-      </c>
-      <c r="J25" s="7" t="inlineStr">
-        <is>
-          <t>event 5d ago; 2 events in 30d; only 2% above 52w low</t>
-        </is>
-      </c>
-    </row>
-    <row r="26" ht="22" customHeight="1">
-      <c r="A26" s="8" t="n">
-        <v>22</v>
-      </c>
-      <c r="B26" s="9" t="inlineStr">
-        <is>
-          <t>OTLK</t>
-        </is>
-      </c>
-      <c r="C26" s="10" t="inlineStr">
-        <is>
-          <t>Outlook Therapeutics, Inc.</t>
-        </is>
-      </c>
-      <c r="D26" s="22" t="n">
-        <v>44</v>
-      </c>
-      <c r="E26" s="8" t="n">
-        <v>20</v>
-      </c>
-      <c r="F26" s="10" t="inlineStr">
-        <is>
-          <t>DEF14A_PSU</t>
-        </is>
-      </c>
-      <c r="G26" s="8" t="n">
-        <v>4</v>
-      </c>
-      <c r="H26" s="20" t="n">
-        <v>53</v>
-      </c>
-      <c r="I26" s="17" t="n">
-        <v>-5.703971</v>
-      </c>
-      <c r="J26" s="10" t="inlineStr">
-        <is>
-          <t>event 20d ago; PSU/gov in latest proxy; 4 events in 30d; DD 53%</t>
-        </is>
-      </c>
-    </row>
-    <row r="27" ht="22" customHeight="1">
-      <c r="A27" s="5" t="n">
-        <v>23</v>
-      </c>
-      <c r="B27" s="6" t="inlineStr">
-        <is>
-          <t>MYSZ</t>
-        </is>
-      </c>
-      <c r="C27" s="7" t="inlineStr">
-        <is>
-          <t>My Size, Inc.</t>
-        </is>
-      </c>
-      <c r="D27" s="22" t="n">
-        <v>43</v>
-      </c>
-      <c r="E27" s="5" t="n">
-        <v>19</v>
-      </c>
-      <c r="F27" s="7" t="inlineStr">
-        <is>
-          <t>DEF14A_PSU</t>
-        </is>
-      </c>
-      <c r="G27" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="H27" s="19" t="n">
-        <v>72</v>
-      </c>
-      <c r="I27" s="16" t="n">
-        <v>0.5609756</v>
-      </c>
-      <c r="J27" s="7" t="inlineStr">
-        <is>
-          <t>event 19d ago; PSU/gov in latest proxy; DD 72% (unpriced)</t>
-        </is>
-      </c>
-    </row>
-    <row r="28" ht="22" customHeight="1">
-      <c r="A28" s="8" t="n">
-        <v>24</v>
-      </c>
-      <c r="B28" s="9" t="inlineStr">
-        <is>
-          <t>PRPL</t>
-        </is>
-      </c>
-      <c r="C28" s="10" t="inlineStr">
-        <is>
-          <t>Purple Innovation, Inc.</t>
-        </is>
-      </c>
-      <c r="D28" s="22" t="n">
-        <v>43</v>
-      </c>
-      <c r="E28" s="8" t="n">
-        <v>13</v>
-      </c>
-      <c r="F28" s="10" t="inlineStr">
-        <is>
-          <t>DEF14A_PSU</t>
-        </is>
-      </c>
-      <c r="G28" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="H28" s="20" t="n">
-        <v>66</v>
-      </c>
-      <c r="I28" s="17" t="n">
-        <v>-0.7734178</v>
-      </c>
-      <c r="J28" s="10" t="inlineStr">
-        <is>
-          <t>event 13d ago; PSU/gov in latest proxy; DD 66% (unpriced)</t>
-        </is>
-      </c>
-    </row>
-    <row r="29" ht="22" customHeight="1">
-      <c r="A29" s="5" t="n">
-        <v>25</v>
-      </c>
-      <c r="B29" s="6" t="inlineStr">
-        <is>
-          <t>COSM</t>
-        </is>
-      </c>
-      <c r="C29" s="7" t="inlineStr">
-        <is>
-          <t>Cosmos Health Inc.</t>
-        </is>
-      </c>
-      <c r="D29" s="22" t="n">
-        <v>43</v>
-      </c>
-      <c r="E29" s="5" t="n">
-        <v>19</v>
-      </c>
-      <c r="F29" s="7" t="inlineStr">
-        <is>
-          <t>DEF14A_PSU</t>
-        </is>
-      </c>
-      <c r="G29" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="H29" s="19" t="n">
-        <v>84</v>
-      </c>
-      <c r="I29" s="16" t="n">
-        <v>0.5349246</v>
-      </c>
-      <c r="J29" s="7" t="inlineStr">
-        <is>
-          <t>event 19d ago; PSU/gov in latest proxy; DD 84% (unpriced)</t>
-        </is>
-      </c>
-    </row>
-    <row r="30" ht="22" customHeight="1">
-      <c r="A30" s="8" t="n">
-        <v>26</v>
-      </c>
-      <c r="B30" s="9" t="inlineStr">
-        <is>
-          <t>PSIX</t>
-        </is>
-      </c>
-      <c r="C30" s="10" t="inlineStr">
-        <is>
-          <t>Power Solutions International,</t>
-        </is>
-      </c>
-      <c r="D30" s="22" t="n">
-        <v>43</v>
-      </c>
-      <c r="E30" s="8" t="n">
-        <v>12</v>
-      </c>
-      <c r="F30" s="10" t="inlineStr">
-        <is>
-          <t>DEF14A_PSU</t>
-        </is>
-      </c>
-      <c r="G30" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="H30" s="20" t="n">
-        <v>67</v>
-      </c>
-      <c r="I30" s="17" t="n">
-        <v>5.0018616</v>
-      </c>
-      <c r="J30" s="10" t="inlineStr">
-        <is>
-          <t>event 12d ago; PSU/gov in latest proxy; DD 67% (unpriced)</t>
-        </is>
-      </c>
-    </row>
-    <row r="31" ht="22" customHeight="1">
-      <c r="A31" s="5" t="n">
-        <v>27</v>
-      </c>
-      <c r="B31" s="6" t="inlineStr">
-        <is>
-          <t>NXGL</t>
-        </is>
-      </c>
-      <c r="C31" s="7" t="inlineStr">
-        <is>
-          <t>NexGel, Inc</t>
-        </is>
-      </c>
-      <c r="D31" s="22" t="n">
-        <v>43</v>
-      </c>
-      <c r="E31" s="5" t="n">
-        <v>12</v>
-      </c>
-      <c r="F31" s="7" t="inlineStr">
-        <is>
-          <t>DEF14A_PSU</t>
-        </is>
-      </c>
-      <c r="G31" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="H31" s="19" t="n">
-        <v>80</v>
-      </c>
-      <c r="I31" s="16" t="n">
-        <v>1.2016985</v>
-      </c>
-      <c r="J31" s="7" t="inlineStr">
-        <is>
-          <t>event 12d ago; PSU/gov in latest proxy; DD 80% (unpriced)</t>
-        </is>
-      </c>
-    </row>
-    <row r="32" ht="22" customHeight="1">
-      <c r="A32" s="8" t="n">
-        <v>28</v>
-      </c>
-      <c r="B32" s="9" t="inlineStr">
-        <is>
-          <t>CRM</t>
-        </is>
-      </c>
-      <c r="C32" s="10" t="inlineStr">
-        <is>
-          <t>Salesforce, Inc.</t>
-        </is>
-      </c>
-      <c r="D32" s="22" t="n">
-        <v>42</v>
-      </c>
-      <c r="E32" s="8" t="n">
-        <v>24</v>
-      </c>
-      <c r="F32" s="10" t="inlineStr">
-        <is>
-          <t>10b5-1_TERM</t>
-        </is>
-      </c>
-      <c r="G32" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="H32" s="20" t="n">
-        <v>45</v>
-      </c>
-      <c r="I32" s="17" t="n">
-        <v>3.6310136</v>
-      </c>
-      <c r="J32" s="10" t="inlineStr">
-        <is>
-          <t>event 24d ago; 10b5-1 termination; DD 45%; only 1% above 52w low</t>
-        </is>
-      </c>
-    </row>
-    <row r="33" ht="22" customHeight="1">
-      <c r="A33" s="5" t="n">
-        <v>29</v>
-      </c>
-      <c r="B33" s="6" t="inlineStr">
-        <is>
-          <t>VTS</t>
-        </is>
-      </c>
-      <c r="C33" s="7" t="inlineStr">
-        <is>
-          <t>Vitesse Energy, Inc.</t>
-        </is>
-      </c>
-      <c r="D33" s="22" t="n">
-        <v>42</v>
-      </c>
-      <c r="E33" s="5" t="n">
-        <v>20</v>
-      </c>
-      <c r="F33" s="7" t="inlineStr">
-        <is>
-          <t>F4_PBUY</t>
-        </is>
-      </c>
-      <c r="G33" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="H33" s="19" t="n">
-        <v>41</v>
-      </c>
-      <c r="I33" s="16" t="n">
-        <v>1.1419401</v>
-      </c>
-      <c r="J33" s="7" t="inlineStr">
-        <is>
-          <t>event 20d ago; insider P-buy; DD 41%; only 1% above 52w low</t>
-        </is>
-      </c>
-    </row>
-    <row r="34" ht="22" customHeight="1">
-      <c r="A34" s="8" t="n">
-        <v>30</v>
-      </c>
-      <c r="B34" s="9" t="inlineStr">
-        <is>
-          <t>DNUT</t>
-        </is>
-      </c>
-      <c r="C34" s="10" t="inlineStr">
-        <is>
-          <t>Krispy Kreme, Inc.</t>
-        </is>
-      </c>
-      <c r="D34" s="22" t="n">
-        <v>42</v>
-      </c>
-      <c r="E34" s="8" t="n">
-        <v>5</v>
-      </c>
-      <c r="F34" s="10" t="inlineStr">
-        <is>
-          <t>ACTIVIST_13D</t>
-        </is>
-      </c>
-      <c r="G34" s="8" t="n">
-        <v>2</v>
-      </c>
-      <c r="H34" s="20" t="n">
-        <v>37</v>
-      </c>
-      <c r="I34" s="17" t="n">
-        <v>0.98991</v>
-      </c>
-      <c r="J34" s="10" t="inlineStr">
-        <is>
-          <t>event 5d ago; 2 events in 30d</t>
-        </is>
-      </c>
-    </row>
-    <row r="35" ht="22" customHeight="1">
-      <c r="A35" s="5" t="n">
-        <v>31</v>
-      </c>
-      <c r="B35" s="6" t="inlineStr">
-        <is>
-          <t>NRDY</t>
-        </is>
-      </c>
-      <c r="C35" s="7" t="inlineStr">
-        <is>
-          <t>Nerdy Inc.</t>
-        </is>
-      </c>
-      <c r="D35" s="22" t="n">
-        <v>41</v>
-      </c>
-      <c r="E35" s="5" t="n">
-        <v>4</v>
-      </c>
-      <c r="F35" s="7" t="inlineStr">
-        <is>
-          <t>ACTIVIST_13D</t>
-        </is>
-      </c>
-      <c r="G35" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="H35" s="19" t="n">
-        <v>51</v>
-      </c>
-      <c r="I35" s="16" t="n">
-        <v>5.5558443</v>
-      </c>
-      <c r="J35" s="7" t="inlineStr">
-        <is>
-          <t>event 4d ago; 2 events in 30d; DD 51%</t>
-        </is>
-      </c>
-    </row>
-    <row r="36" ht="22" customHeight="1">
-      <c r="A36" s="8" t="n">
-        <v>32</v>
-      </c>
-      <c r="B36" s="9" t="inlineStr">
-        <is>
-          <t>ARTV</t>
-        </is>
-      </c>
-      <c r="C36" s="10" t="inlineStr">
-        <is>
-          <t>Artiva Biotherapeutics, Inc.</t>
-        </is>
-      </c>
-      <c r="D36" s="22" t="n">
-        <v>41</v>
-      </c>
-      <c r="E36" s="8" t="n">
-        <v>6</v>
-      </c>
-      <c r="F36" s="10" t="inlineStr">
-        <is>
-          <t>ACTIVIST_13D</t>
-        </is>
-      </c>
-      <c r="G36" s="8" t="n">
-        <v>2</v>
-      </c>
-      <c r="H36" s="20" t="n">
-        <v>49</v>
-      </c>
-      <c r="I36" s="17" t="n">
-        <v>2.0877886</v>
-      </c>
-      <c r="J36" s="10" t="inlineStr">
-        <is>
-          <t>event 6d ago; 2 events in 30d; DD 49%</t>
-        </is>
-      </c>
-    </row>
-    <row r="37" ht="22" customHeight="1">
-      <c r="A37" s="5" t="n">
-        <v>33</v>
-      </c>
-      <c r="B37" s="6" t="inlineStr">
-        <is>
-          <t>STE</t>
-        </is>
-      </c>
-      <c r="C37" s="7" t="inlineStr">
-        <is>
-          <t>STERIS plc (Ireland)</t>
-        </is>
-      </c>
-      <c r="D37" s="22" t="n">
-        <v>41</v>
-      </c>
-      <c r="E37" s="5" t="n">
-        <v>10</v>
-      </c>
-      <c r="F37" s="7" t="inlineStr">
-        <is>
-          <t>DEF14A_PSU</t>
-        </is>
-      </c>
-      <c r="G37" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="H37" s="19" t="n">
-        <v>25</v>
-      </c>
-      <c r="I37" s="16" t="n">
-        <v>2.7584</v>
-      </c>
-      <c r="J37" s="7" t="inlineStr">
-        <is>
-          <t>event 10d ago; PSU/gov in latest proxy; only 4% above 52w low</t>
-        </is>
-      </c>
-    </row>
-    <row r="38" ht="22" customHeight="1">
-      <c r="A38" s="8" t="n">
-        <v>34</v>
-      </c>
-      <c r="B38" s="9" t="inlineStr">
-        <is>
-          <t>RBRK</t>
-        </is>
-      </c>
-      <c r="C38" s="10" t="inlineStr">
-        <is>
-          <t>Rubrik, Inc.</t>
-        </is>
-      </c>
-      <c r="D38" s="22" t="n">
-        <v>41</v>
-      </c>
-      <c r="E38" s="8" t="n">
-        <v>16</v>
-      </c>
-      <c r="F38" s="10" t="inlineStr">
-        <is>
-          <t>10b5-1_TERM</t>
-        </is>
-      </c>
-      <c r="G38" s="8" t="n">
-        <v>2</v>
-      </c>
-      <c r="H38" s="20" t="n">
-        <v>30</v>
-      </c>
-      <c r="I38" s="17" t="n">
-        <v>-30.021378</v>
-      </c>
-      <c r="J38" s="10" t="inlineStr">
-        <is>
-          <t>event 16d ago; 10b5-1 termination; 2 events in 30d</t>
-        </is>
-      </c>
-    </row>
-    <row r="39" ht="22" customHeight="1">
-      <c r="A39" s="5" t="n">
-        <v>35</v>
-      </c>
-      <c r="B39" s="6" t="inlineStr">
-        <is>
-          <t>MDLN</t>
-        </is>
-      </c>
-      <c r="C39" s="7" t="inlineStr">
-        <is>
-          <t>Medline Inc.</t>
-        </is>
-      </c>
-      <c r="D39" s="22" t="n">
-        <v>40</v>
-      </c>
-      <c r="E39" s="5" t="n">
-        <v>19</v>
-      </c>
-      <c r="F39" s="7" t="inlineStr">
-        <is>
-          <t>RESTRUCT_8K</t>
-        </is>
-      </c>
-      <c r="G39" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="H39" s="19" t="n">
-        <v>29</v>
-      </c>
-      <c r="I39" s="16" t="n">
-        <v>2.697388</v>
-      </c>
-      <c r="J39" s="7" t="inlineStr">
-        <is>
-          <t>event 19d ago; RESTRUCT_8K; only 10% above 52w low</t>
-        </is>
-      </c>
-    </row>
-    <row r="40" ht="22" customHeight="1">
-      <c r="A40" s="8" t="n">
-        <v>36</v>
-      </c>
-      <c r="B40" s="9" t="inlineStr">
-        <is>
-          <t>TORO</t>
-        </is>
-      </c>
-      <c r="C40" s="10" t="inlineStr">
-        <is>
-          <t>Toro Corp.</t>
-        </is>
-      </c>
-      <c r="D40" s="22" t="n">
-        <v>40</v>
-      </c>
-      <c r="E40" s="8" t="n">
-        <v>12</v>
-      </c>
-      <c r="F40" s="10" t="inlineStr">
-        <is>
-          <t>ACTIVIST_13D</t>
-        </is>
-      </c>
-      <c r="G40" s="8" t="n">
-        <v>2</v>
-      </c>
-      <c r="H40" s="20" t="n">
-        <v>40</v>
-      </c>
-      <c r="I40" s="17" t="n">
-        <v>0.6729493</v>
-      </c>
-      <c r="J40" s="10" t="inlineStr">
-        <is>
-          <t>event 12d ago; 2 events in 30d; DD 40%</t>
-        </is>
-      </c>
-    </row>
-    <row r="41" ht="22" customHeight="1">
-      <c r="A41" s="5" t="n">
-        <v>37</v>
-      </c>
-      <c r="B41" s="6" t="inlineStr">
-        <is>
-          <t>CURI</t>
-        </is>
-      </c>
-      <c r="C41" s="7" t="inlineStr">
-        <is>
-          <t>CuriosityStream Inc.</t>
-        </is>
-      </c>
-      <c r="D41" s="22" t="n">
-        <v>40</v>
-      </c>
-      <c r="E41" s="5" t="n">
-        <v>20</v>
-      </c>
-      <c r="F41" s="7" t="inlineStr">
-        <is>
-          <t>F4_PBUY</t>
-        </is>
-      </c>
-      <c r="G41" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="H41" s="19" t="n">
-        <v>57</v>
-      </c>
-      <c r="I41" s="16" t="n">
-        <v>4.113821</v>
-      </c>
-      <c r="J41" s="7" t="inlineStr">
-        <is>
-          <t>event 20d ago; insider P-buy; 2 events in 30d; DD 57%</t>
-        </is>
-      </c>
-    </row>
-    <row r="42" ht="22" customHeight="1">
-      <c r="A42" s="8" t="n">
-        <v>38</v>
-      </c>
-      <c r="B42" s="9" t="inlineStr">
-        <is>
-          <t>HCAT</t>
-        </is>
-      </c>
-      <c r="C42" s="10" t="inlineStr">
-        <is>
-          <t>Health Catalyst, Inc</t>
-        </is>
-      </c>
-      <c r="D42" s="22" t="n">
-        <v>40</v>
-      </c>
-      <c r="E42" s="8" t="n">
-        <v>13</v>
-      </c>
-      <c r="F42" s="10" t="inlineStr">
-        <is>
-          <t>ACTIVIST_13D</t>
-        </is>
-      </c>
-      <c r="G42" s="8" t="n">
-        <v>2</v>
-      </c>
-      <c r="H42" s="20" t="n">
-        <v>55</v>
-      </c>
-      <c r="I42" s="17" t="n">
-        <v>0.98772025</v>
-      </c>
-      <c r="J42" s="10" t="inlineStr">
-        <is>
-          <t>event 13d ago; 2 events in 30d; DD 55%</t>
-        </is>
-      </c>
-    </row>
-    <row r="43" ht="22" customHeight="1">
-      <c r="A43" s="5" t="n">
-        <v>39</v>
-      </c>
-      <c r="B43" s="6" t="inlineStr">
-        <is>
-          <t>DOMO</t>
-        </is>
-      </c>
-      <c r="C43" s="7" t="inlineStr">
-        <is>
-          <t>Domo, Inc.</t>
-        </is>
-      </c>
-      <c r="D43" s="16" t="n">
-        <v>39</v>
-      </c>
-      <c r="E43" s="5" t="n">
-        <v>18</v>
-      </c>
-      <c r="F43" s="7" t="inlineStr">
-        <is>
-          <t>ACTIVIST_13D</t>
-        </is>
-      </c>
-      <c r="G43" s="5" t="n">
-        <v>3</v>
-      </c>
-      <c r="H43" s="19" t="n">
-        <v>87</v>
-      </c>
-      <c r="I43" s="16" t="n">
-        <v>-0.55213326</v>
-      </c>
-      <c r="J43" s="7" t="inlineStr">
-        <is>
-          <t>event 18d ago; 3 events in 30d; DD 87% (unpriced)</t>
-        </is>
-      </c>
-    </row>
-    <row r="44" ht="22" customHeight="1">
-      <c r="A44" s="8" t="n">
-        <v>40</v>
-      </c>
-      <c r="B44" s="9" t="inlineStr">
-        <is>
-          <t>BLND</t>
-        </is>
-      </c>
-      <c r="C44" s="10" t="inlineStr">
-        <is>
-          <t>Blend Labs, Inc.</t>
-        </is>
-      </c>
-      <c r="D44" s="17" t="n">
-        <v>39</v>
-      </c>
-      <c r="E44" s="8" t="n">
-        <v>9</v>
-      </c>
-      <c r="F44" s="10" t="inlineStr">
-        <is>
-          <t>ACTIVIST_13D</t>
-        </is>
-      </c>
-      <c r="G44" s="8" t="n">
-        <v>2</v>
-      </c>
-      <c r="H44" s="20" t="n">
-        <v>63</v>
-      </c>
-      <c r="I44" s="17" t="n">
-        <v>-7.300885</v>
-      </c>
-      <c r="J44" s="10" t="inlineStr">
-        <is>
-          <t>event 9d ago; 2 events in 30d; DD 63% (unpriced)</t>
-        </is>
-      </c>
-    </row>
-    <row r="46" ht="28" customHeight="1">
-      <c r="A46" s="11" t="inlineStr">
-        <is>
-          <t>30-day window of `recent_incentive_asymmetry.py`. Event types: DEF14A_PSU (latest proxy), 10b5-1_TERM (insider walked back scheduled selling), F4_PBUY (insider open-market purchase), ACTIVIST_13D, RESTRUCT_8K (8-K restructuring keyword), FORM_10_SPINOFF, NOL_SHELL. Score boosts: drawdown &gt;60% unpriced (+15), multi-event cluster (+12), event in last 7 days (+25). Source: recent_incentive_asymmetry_30d.csv.</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="3">
-    <mergeCell ref="A1:J1"/>
-    <mergeCell ref="A46:J46"/>
-    <mergeCell ref="A2:J2"/>
   </mergeCells>
   <printOptions horizontalCentered="0"/>
   <pageMargins left="0.5" right="0.5" top="0.6" bottom="0.6" header="0.5" footer="0.5"/>
@@ -14427,6 +14329,1722 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
+  <dimension ref="A1:J46"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="9" customWidth="1" min="1" max="1"/>
+    <col width="13" customWidth="1" min="2" max="2"/>
+    <col width="32" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="8" customWidth="1" min="5" max="5"/>
+    <col width="22" customWidth="1" min="6" max="6"/>
+    <col width="8" customWidth="1" min="7" max="7"/>
+    <col width="6" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="9" max="9"/>
+    <col width="50" customWidth="1" min="10" max="10"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="26" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Stale-Pricing Asymmetry -- Last 30 days</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="18" customHeight="1">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Names where a material incentive event was disclosed in the last 30 days AND the price has not yet reflected it. Tightest possible information-lag window.</t>
+        </is>
+      </c>
+      <c r="B2" s="3" t="n"/>
+      <c r="C2" s="3" t="n"/>
+      <c r="D2" s="3" t="n"/>
+      <c r="E2" s="3" t="n"/>
+      <c r="F2" s="3" t="n"/>
+      <c r="G2" s="3" t="n"/>
+      <c r="H2" s="3" t="n"/>
+      <c r="I2" s="3" t="n"/>
+      <c r="J2" s="3" t="n"/>
+    </row>
+    <row r="3" ht="8" customHeight="1"/>
+    <row r="4" ht="18" customHeight="1">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="B4" s="15" t="inlineStr">
+        <is>
+          <t>Ticker</t>
+        </is>
+      </c>
+      <c r="C4" s="15" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="D4" s="4" t="inlineStr">
+        <is>
+          <t>Score</t>
+        </is>
+      </c>
+      <c r="E4" s="4" t="inlineStr">
+        <is>
+          <t>Days</t>
+        </is>
+      </c>
+      <c r="F4" s="4" t="inlineStr">
+        <is>
+          <t>Event kind</t>
+        </is>
+      </c>
+      <c r="G4" s="4" t="inlineStr">
+        <is>
+          <t>Inner</t>
+        </is>
+      </c>
+      <c r="H4" s="4" t="inlineStr">
+        <is>
+          <t>DD%</t>
+        </is>
+      </c>
+      <c r="I4" s="4" t="inlineStr">
+        <is>
+          <t>P/B</t>
+        </is>
+      </c>
+      <c r="J4" s="15" t="inlineStr">
+        <is>
+          <t>Reasons</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="22" customHeight="1">
+      <c r="A5" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="B5" s="6" t="inlineStr">
+        <is>
+          <t>RPAY</t>
+        </is>
+      </c>
+      <c r="C5" s="7" t="inlineStr">
+        <is>
+          <t>Repay Holdings Corporation</t>
+        </is>
+      </c>
+      <c r="D5" s="22" t="n">
+        <v>68</v>
+      </c>
+      <c r="E5" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="F5" s="7" t="inlineStr">
+        <is>
+          <t>RESTRUCT_8K</t>
+        </is>
+      </c>
+      <c r="G5" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="H5" s="19" t="n">
+        <v>44</v>
+      </c>
+      <c r="I5" s="16" t="n">
+        <v>0.49123317</v>
+      </c>
+      <c r="J5" s="7" t="inlineStr">
+        <is>
+          <t>event 6d ago; RESTRUCT_8K; 2 events in 30d; DD 44%; P/B 0.49</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="22" customHeight="1">
+      <c r="A6" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="B6" s="9" t="inlineStr">
+        <is>
+          <t>GOSS</t>
+        </is>
+      </c>
+      <c r="C6" s="10" t="inlineStr">
+        <is>
+          <t>Gossamer Bio, Inc.</t>
+        </is>
+      </c>
+      <c r="D6" s="22" t="n">
+        <v>61</v>
+      </c>
+      <c r="E6" s="8" t="n">
+        <v>4</v>
+      </c>
+      <c r="F6" s="10" t="inlineStr">
+        <is>
+          <t>RESTRUCT_8K</t>
+        </is>
+      </c>
+      <c r="G6" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="H6" s="20" t="n">
+        <v>96</v>
+      </c>
+      <c r="I6" s="17" t="n">
+        <v>-0.24418603</v>
+      </c>
+      <c r="J6" s="10" t="inlineStr">
+        <is>
+          <t>event 4d ago; RESTRUCT_8K; 2 events in 30d; DD 96% (unpriced)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="22" customHeight="1">
+      <c r="A7" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="B7" s="6" t="inlineStr">
+        <is>
+          <t>GTM</t>
+        </is>
+      </c>
+      <c r="C7" s="7" t="inlineStr">
+        <is>
+          <t>ZoomInfo Technologies Inc.</t>
+        </is>
+      </c>
+      <c r="D7" s="22" t="n">
+        <v>60</v>
+      </c>
+      <c r="E7" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="F7" s="7" t="inlineStr">
+        <is>
+          <t>ACTIVIST_13D</t>
+        </is>
+      </c>
+      <c r="G7" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="H7" s="19" t="n">
+        <v>78</v>
+      </c>
+      <c r="I7" s="16" t="n">
+        <v>0.56459713</v>
+      </c>
+      <c r="J7" s="7" t="inlineStr">
+        <is>
+          <t>event 5d ago; 2 events in 30d; DD 78% (unpriced); only 8% above 52w low</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="22" customHeight="1">
+      <c r="A8" s="8" t="n">
+        <v>4</v>
+      </c>
+      <c r="B8" s="9" t="inlineStr">
+        <is>
+          <t>GSHD</t>
+        </is>
+      </c>
+      <c r="C8" s="10" t="inlineStr">
+        <is>
+          <t>Goosehead Insurance, Inc.</t>
+        </is>
+      </c>
+      <c r="D8" s="22" t="n">
+        <v>53</v>
+      </c>
+      <c r="E8" s="8" t="n">
+        <v>20</v>
+      </c>
+      <c r="F8" s="10" t="inlineStr">
+        <is>
+          <t>F4_PBUY</t>
+        </is>
+      </c>
+      <c r="G8" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="H8" s="20" t="n">
+        <v>70</v>
+      </c>
+      <c r="I8" s="17" t="n">
+        <v>-6.708959</v>
+      </c>
+      <c r="J8" s="10" t="inlineStr">
+        <is>
+          <t>event 20d ago; insider P-buy; 2 events in 30d; DD 70% (unpriced); only 2% above 52w low</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="22" customHeight="1">
+      <c r="A9" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="B9" s="6" t="inlineStr">
+        <is>
+          <t>GWRE</t>
+        </is>
+      </c>
+      <c r="C9" s="7" t="inlineStr">
+        <is>
+          <t>Guidewire Software, Inc.</t>
+        </is>
+      </c>
+      <c r="D9" s="22" t="n">
+        <v>53</v>
+      </c>
+      <c r="E9" s="5" t="n">
+        <v>16</v>
+      </c>
+      <c r="F9" s="7" t="inlineStr">
+        <is>
+          <t>10b5-1_TERM</t>
+        </is>
+      </c>
+      <c r="G9" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="H9" s="19" t="n">
+        <v>60</v>
+      </c>
+      <c r="I9" s="16" t="n">
+        <v>6.817952</v>
+      </c>
+      <c r="J9" s="7" t="inlineStr">
+        <is>
+          <t>event 16d ago; 10b5-1 termination; DD 60% (unpriced); only 1% above 52w low</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="22" customHeight="1">
+      <c r="A10" s="8" t="n">
+        <v>6</v>
+      </c>
+      <c r="B10" s="9" t="inlineStr">
+        <is>
+          <t>CMTL</t>
+        </is>
+      </c>
+      <c r="C10" s="10" t="inlineStr">
+        <is>
+          <t>Comtech Telecommunications Corp</t>
+        </is>
+      </c>
+      <c r="D10" s="22" t="n">
+        <v>52</v>
+      </c>
+      <c r="E10" s="8" t="n">
+        <v>4</v>
+      </c>
+      <c r="F10" s="10" t="inlineStr">
+        <is>
+          <t>ACTIVIST_13D</t>
+        </is>
+      </c>
+      <c r="G10" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="H10" s="20" t="n">
+        <v>61</v>
+      </c>
+      <c r="I10" s="17" t="n">
+        <v>0.67586595</v>
+      </c>
+      <c r="J10" s="10" t="inlineStr">
+        <is>
+          <t>event 4d ago; 2 events in 30d; DD 61% (unpriced)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="22" customHeight="1">
+      <c r="A11" s="5" t="n">
+        <v>7</v>
+      </c>
+      <c r="B11" s="6" t="inlineStr">
+        <is>
+          <t>PHGE</t>
+        </is>
+      </c>
+      <c r="C11" s="7" t="inlineStr">
+        <is>
+          <t>BiomX Inc.</t>
+        </is>
+      </c>
+      <c r="D11" s="22" t="n">
+        <v>52</v>
+      </c>
+      <c r="E11" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="F11" s="7" t="inlineStr">
+        <is>
+          <t>ACTIVIST_13D</t>
+        </is>
+      </c>
+      <c r="G11" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="H11" s="19" t="n">
+        <v>96</v>
+      </c>
+      <c r="I11" s="16" t="n">
+        <v>-0.041595332</v>
+      </c>
+      <c r="J11" s="7" t="inlineStr">
+        <is>
+          <t>event 5d ago; 3 events in 30d; DD 96% (unpriced)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="22" customHeight="1">
+      <c r="A12" s="8" t="n">
+        <v>8</v>
+      </c>
+      <c r="B12" s="9" t="inlineStr">
+        <is>
+          <t>CHPT</t>
+        </is>
+      </c>
+      <c r="C12" s="10" t="inlineStr">
+        <is>
+          <t>ChargePoint Holdings, Inc.</t>
+        </is>
+      </c>
+      <c r="D12" s="22" t="n">
+        <v>52</v>
+      </c>
+      <c r="E12" s="8" t="n">
+        <v>13</v>
+      </c>
+      <c r="F12" s="10" t="inlineStr">
+        <is>
+          <t>10b5-1_TERM</t>
+        </is>
+      </c>
+      <c r="G12" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="H12" s="20" t="n">
+        <v>49</v>
+      </c>
+      <c r="I12" s="17" t="n">
+        <v>-23.675215</v>
+      </c>
+      <c r="J12" s="10" t="inlineStr">
+        <is>
+          <t>event 13d ago; 10b5-1 termination; 2 events in 30d; DD 49%</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="22" customHeight="1">
+      <c r="A13" s="5" t="n">
+        <v>9</v>
+      </c>
+      <c r="B13" s="6" t="inlineStr">
+        <is>
+          <t>DXC</t>
+        </is>
+      </c>
+      <c r="C13" s="7" t="inlineStr">
+        <is>
+          <t>DXC Technology Company</t>
+        </is>
+      </c>
+      <c r="D13" s="22" t="n">
+        <v>52</v>
+      </c>
+      <c r="E13" s="5" t="n">
+        <v>17</v>
+      </c>
+      <c r="F13" s="7" t="inlineStr">
+        <is>
+          <t>DEF14A_PSU</t>
+        </is>
+      </c>
+      <c r="G13" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="H13" s="19" t="n">
+        <v>48</v>
+      </c>
+      <c r="I13" s="16" t="n">
+        <v>0.4839073</v>
+      </c>
+      <c r="J13" s="7" t="inlineStr">
+        <is>
+          <t>event 17d ago; PSU/gov in latest proxy; DD 48%; only 9% above 52w low; P/B 0.48</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="22" customHeight="1">
+      <c r="A14" s="8" t="n">
+        <v>10</v>
+      </c>
+      <c r="B14" s="9" t="inlineStr">
+        <is>
+          <t>PCSA</t>
+        </is>
+      </c>
+      <c r="C14" s="10" t="inlineStr">
+        <is>
+          <t>Processa Pharmaceuticals, Inc.</t>
+        </is>
+      </c>
+      <c r="D14" s="22" t="n">
+        <v>51</v>
+      </c>
+      <c r="E14" s="8" t="n">
+        <v>20</v>
+      </c>
+      <c r="F14" s="10" t="inlineStr">
+        <is>
+          <t>F4_PBUY</t>
+        </is>
+      </c>
+      <c r="G14" s="8" t="n">
+        <v>5</v>
+      </c>
+      <c r="H14" s="20" t="n">
+        <v>86</v>
+      </c>
+      <c r="I14" s="17" t="n">
+        <v>2.950474</v>
+      </c>
+      <c r="J14" s="10" t="inlineStr">
+        <is>
+          <t>event 20d ago; insider P-buy; 5 events in 30d; DD 86% (unpriced)</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="22" customHeight="1">
+      <c r="A15" s="5" t="n">
+        <v>11</v>
+      </c>
+      <c r="B15" s="6" t="inlineStr">
+        <is>
+          <t>BTU</t>
+        </is>
+      </c>
+      <c r="C15" s="7" t="inlineStr">
+        <is>
+          <t>Peabody Energy Corporation</t>
+        </is>
+      </c>
+      <c r="D15" s="22" t="n">
+        <v>51</v>
+      </c>
+      <c r="E15" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="F15" s="7" t="inlineStr">
+        <is>
+          <t>RESTRUCT_8K</t>
+        </is>
+      </c>
+      <c r="G15" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="H15" s="19" t="n">
+        <v>36</v>
+      </c>
+      <c r="I15" s="16" t="n">
+        <v>0.91458744</v>
+      </c>
+      <c r="J15" s="7" t="inlineStr">
+        <is>
+          <t>event 6d ago; RESTRUCT_8K</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="22" customHeight="1">
+      <c r="A16" s="8" t="n">
+        <v>12</v>
+      </c>
+      <c r="B16" s="9" t="inlineStr">
+        <is>
+          <t>RC</t>
+        </is>
+      </c>
+      <c r="C16" s="10" t="inlineStr">
+        <is>
+          <t>Ready Capital Corporation</t>
+        </is>
+      </c>
+      <c r="D16" s="22" t="n">
+        <v>49</v>
+      </c>
+      <c r="E16" s="8" t="n">
+        <v>20</v>
+      </c>
+      <c r="F16" s="10" t="inlineStr">
+        <is>
+          <t>DEF14A_PSU</t>
+        </is>
+      </c>
+      <c r="G16" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="H16" s="20" t="n">
+        <v>63</v>
+      </c>
+      <c r="I16" s="17" t="n">
+        <v>0.23546824</v>
+      </c>
+      <c r="J16" s="10" t="inlineStr">
+        <is>
+          <t>event 20d ago; PSU/gov in latest proxy; DD 63% (unpriced); P/B 0.24</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="22" customHeight="1">
+      <c r="A17" s="5" t="n">
+        <v>13</v>
+      </c>
+      <c r="B17" s="6" t="inlineStr">
+        <is>
+          <t>KWY</t>
+        </is>
+      </c>
+      <c r="C17" s="7" t="inlineStr">
+        <is>
+          <t>Kingsway Corporation</t>
+        </is>
+      </c>
+      <c r="D17" s="22" t="n">
+        <v>49</v>
+      </c>
+      <c r="E17" s="5" t="n">
+        <v>20</v>
+      </c>
+      <c r="F17" s="7" t="inlineStr">
+        <is>
+          <t>F4_PBUY</t>
+        </is>
+      </c>
+      <c r="G17" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="H17" s="19" t="n">
+        <v>39</v>
+      </c>
+      <c r="I17" s="16" t="n">
+        <v>22.396515</v>
+      </c>
+      <c r="J17" s="7" t="inlineStr">
+        <is>
+          <t>event 20d ago; insider P-buy; 3 events in 30d; only 5% above 52w low</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="22" customHeight="1">
+      <c r="A18" s="8" t="n">
+        <v>14</v>
+      </c>
+      <c r="B18" s="9" t="inlineStr">
+        <is>
+          <t>HRTX</t>
+        </is>
+      </c>
+      <c r="C18" s="10" t="inlineStr">
+        <is>
+          <t>Heron Therapeutics, Inc.</t>
+        </is>
+      </c>
+      <c r="D18" s="22" t="n">
+        <v>48</v>
+      </c>
+      <c r="E18" s="8" t="n">
+        <v>5</v>
+      </c>
+      <c r="F18" s="10" t="inlineStr">
+        <is>
+          <t>NOL_SHELL</t>
+        </is>
+      </c>
+      <c r="G18" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="H18" s="20" t="n">
+        <v>82</v>
+      </c>
+      <c r="I18" s="17" t="n">
+        <v>9.709301999999999</v>
+      </c>
+      <c r="J18" s="10" t="inlineStr">
+        <is>
+          <t>event 5d ago; DD 82% (unpriced); only 10% above 52w low</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="22" customHeight="1">
+      <c r="A19" s="5" t="n">
+        <v>15</v>
+      </c>
+      <c r="B19" s="6" t="inlineStr">
+        <is>
+          <t>LAB</t>
+        </is>
+      </c>
+      <c r="C19" s="7" t="inlineStr">
+        <is>
+          <t>Standard BioTools Inc.</t>
+        </is>
+      </c>
+      <c r="D19" s="22" t="n">
+        <v>48</v>
+      </c>
+      <c r="E19" s="5" t="n">
+        <v>12</v>
+      </c>
+      <c r="F19" s="7" t="inlineStr">
+        <is>
+          <t>ACTIVIST_13D</t>
+        </is>
+      </c>
+      <c r="G19" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="H19" s="19" t="n">
+        <v>52</v>
+      </c>
+      <c r="I19" s="16" t="n">
+        <v>0.5769819</v>
+      </c>
+      <c r="J19" s="7" t="inlineStr">
+        <is>
+          <t>event 12d ago; 2 events in 30d; DD 52%; only 5% above 52w low</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="22" customHeight="1">
+      <c r="A20" s="8" t="n">
+        <v>16</v>
+      </c>
+      <c r="B20" s="9" t="inlineStr">
+        <is>
+          <t>NSPR</t>
+        </is>
+      </c>
+      <c r="C20" s="10" t="inlineStr">
+        <is>
+          <t>InspireMD Inc.</t>
+        </is>
+      </c>
+      <c r="D20" s="22" t="n">
+        <v>47</v>
+      </c>
+      <c r="E20" s="8" t="n">
+        <v>23</v>
+      </c>
+      <c r="F20" s="10" t="inlineStr">
+        <is>
+          <t>F4_PBUY</t>
+        </is>
+      </c>
+      <c r="G20" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="H20" s="20" t="n">
+        <v>76</v>
+      </c>
+      <c r="I20" s="17" t="n">
+        <v>0.7626208</v>
+      </c>
+      <c r="J20" s="10" t="inlineStr">
+        <is>
+          <t>event 23d ago; insider P-buy; DD 76% (unpriced); only 3% above 52w low</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="22" customHeight="1">
+      <c r="A21" s="5" t="n">
+        <v>17</v>
+      </c>
+      <c r="B21" s="6" t="inlineStr">
+        <is>
+          <t>RNTX</t>
+        </is>
+      </c>
+      <c r="C21" s="7" t="inlineStr">
+        <is>
+          <t>Rein Therapeutics, Inc.</t>
+        </is>
+      </c>
+      <c r="D21" s="22" t="n">
+        <v>46</v>
+      </c>
+      <c r="E21" s="5" t="n">
+        <v>13</v>
+      </c>
+      <c r="F21" s="7" t="inlineStr">
+        <is>
+          <t>DEF14A_PSU</t>
+        </is>
+      </c>
+      <c r="G21" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="H21" s="19" t="n">
+        <v>58</v>
+      </c>
+      <c r="I21" s="16" t="n">
+        <v>-0.7682047</v>
+      </c>
+      <c r="J21" s="7" t="inlineStr">
+        <is>
+          <t>event 13d ago; PSU/gov in latest proxy; DD 58%; only 6% above 52w low</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="22" customHeight="1">
+      <c r="A22" s="8" t="n">
+        <v>18</v>
+      </c>
+      <c r="B22" s="9" t="inlineStr">
+        <is>
+          <t>BAH</t>
+        </is>
+      </c>
+      <c r="C22" s="10" t="inlineStr">
+        <is>
+          <t>Booz Allen Hamilton Holding Cor</t>
+        </is>
+      </c>
+      <c r="D22" s="22" t="n">
+        <v>46</v>
+      </c>
+      <c r="E22" s="8" t="n">
+        <v>10</v>
+      </c>
+      <c r="F22" s="10" t="inlineStr">
+        <is>
+          <t>DEF14A_PSU</t>
+        </is>
+      </c>
+      <c r="G22" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="H22" s="20" t="n">
+        <v>45</v>
+      </c>
+      <c r="I22" s="17" t="n">
+        <v>7.2271833</v>
+      </c>
+      <c r="J22" s="10" t="inlineStr">
+        <is>
+          <t>event 10d ago; PSU/gov in latest proxy; DD 45%; only 0% above 52w low</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="22" customHeight="1">
+      <c r="A23" s="5" t="n">
+        <v>19</v>
+      </c>
+      <c r="B23" s="6" t="inlineStr">
+        <is>
+          <t>VNRX</t>
+        </is>
+      </c>
+      <c r="C23" s="7" t="inlineStr">
+        <is>
+          <t>VolitionRX Limited</t>
+        </is>
+      </c>
+      <c r="D23" s="22" t="n">
+        <v>45</v>
+      </c>
+      <c r="E23" s="5" t="n">
+        <v>19</v>
+      </c>
+      <c r="F23" s="7" t="inlineStr">
+        <is>
+          <t>DEF14A_PSU</t>
+        </is>
+      </c>
+      <c r="G23" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="H23" s="19" t="n">
+        <v>92</v>
+      </c>
+      <c r="I23" s="16" t="n">
+        <v>-0.26262623</v>
+      </c>
+      <c r="J23" s="7" t="inlineStr">
+        <is>
+          <t>event 19d ago; PSU/gov in latest proxy; DD 92% (unpriced); only 10% above 52w low</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="22" customHeight="1">
+      <c r="A24" s="8" t="n">
+        <v>20</v>
+      </c>
+      <c r="B24" s="9" t="inlineStr">
+        <is>
+          <t>SWZ</t>
+        </is>
+      </c>
+      <c r="C24" s="10" t="inlineStr">
+        <is>
+          <t>Total Return Securities Fund</t>
+        </is>
+      </c>
+      <c r="D24" s="22" t="n">
+        <v>44</v>
+      </c>
+      <c r="E24" s="8" t="n">
+        <v>20</v>
+      </c>
+      <c r="F24" s="10" t="inlineStr">
+        <is>
+          <t>F4_PBUY</t>
+        </is>
+      </c>
+      <c r="G24" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="H24" s="20" t="n">
+        <v>8</v>
+      </c>
+      <c r="I24" s="17" t="n">
+        <v>0.8557581</v>
+      </c>
+      <c r="J24" s="10" t="inlineStr">
+        <is>
+          <t>event 20d ago; insider P-buy; 2 events in 30d; only 1% above 52w low</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="22" customHeight="1">
+      <c r="A25" s="5" t="n">
+        <v>21</v>
+      </c>
+      <c r="B25" s="6" t="inlineStr">
+        <is>
+          <t>FOX</t>
+        </is>
+      </c>
+      <c r="C25" s="7" t="inlineStr">
+        <is>
+          <t>Fox Corporation</t>
+        </is>
+      </c>
+      <c r="D25" s="22" t="n">
+        <v>44</v>
+      </c>
+      <c r="E25" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="F25" s="7" t="inlineStr">
+        <is>
+          <t>ACTIVIST_13D</t>
+        </is>
+      </c>
+      <c r="G25" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="H25" s="19" t="n">
+        <v>31</v>
+      </c>
+      <c r="I25" s="16" t="n">
+        <v>1.8010588</v>
+      </c>
+      <c r="J25" s="7" t="inlineStr">
+        <is>
+          <t>event 5d ago; 2 events in 30d; only 2% above 52w low</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="22" customHeight="1">
+      <c r="A26" s="8" t="n">
+        <v>22</v>
+      </c>
+      <c r="B26" s="9" t="inlineStr">
+        <is>
+          <t>OTLK</t>
+        </is>
+      </c>
+      <c r="C26" s="10" t="inlineStr">
+        <is>
+          <t>Outlook Therapeutics, Inc.</t>
+        </is>
+      </c>
+      <c r="D26" s="22" t="n">
+        <v>44</v>
+      </c>
+      <c r="E26" s="8" t="n">
+        <v>20</v>
+      </c>
+      <c r="F26" s="10" t="inlineStr">
+        <is>
+          <t>DEF14A_PSU</t>
+        </is>
+      </c>
+      <c r="G26" s="8" t="n">
+        <v>4</v>
+      </c>
+      <c r="H26" s="20" t="n">
+        <v>53</v>
+      </c>
+      <c r="I26" s="17" t="n">
+        <v>-5.703971</v>
+      </c>
+      <c r="J26" s="10" t="inlineStr">
+        <is>
+          <t>event 20d ago; PSU/gov in latest proxy; 4 events in 30d; DD 53%</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="22" customHeight="1">
+      <c r="A27" s="5" t="n">
+        <v>23</v>
+      </c>
+      <c r="B27" s="6" t="inlineStr">
+        <is>
+          <t>MYSZ</t>
+        </is>
+      </c>
+      <c r="C27" s="7" t="inlineStr">
+        <is>
+          <t>My Size, Inc.</t>
+        </is>
+      </c>
+      <c r="D27" s="22" t="n">
+        <v>43</v>
+      </c>
+      <c r="E27" s="5" t="n">
+        <v>19</v>
+      </c>
+      <c r="F27" s="7" t="inlineStr">
+        <is>
+          <t>DEF14A_PSU</t>
+        </is>
+      </c>
+      <c r="G27" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="H27" s="19" t="n">
+        <v>72</v>
+      </c>
+      <c r="I27" s="16" t="n">
+        <v>0.5609756</v>
+      </c>
+      <c r="J27" s="7" t="inlineStr">
+        <is>
+          <t>event 19d ago; PSU/gov in latest proxy; DD 72% (unpriced)</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="22" customHeight="1">
+      <c r="A28" s="8" t="n">
+        <v>24</v>
+      </c>
+      <c r="B28" s="9" t="inlineStr">
+        <is>
+          <t>PRPL</t>
+        </is>
+      </c>
+      <c r="C28" s="10" t="inlineStr">
+        <is>
+          <t>Purple Innovation, Inc.</t>
+        </is>
+      </c>
+      <c r="D28" s="22" t="n">
+        <v>43</v>
+      </c>
+      <c r="E28" s="8" t="n">
+        <v>13</v>
+      </c>
+      <c r="F28" s="10" t="inlineStr">
+        <is>
+          <t>DEF14A_PSU</t>
+        </is>
+      </c>
+      <c r="G28" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="H28" s="20" t="n">
+        <v>66</v>
+      </c>
+      <c r="I28" s="17" t="n">
+        <v>-0.7734178</v>
+      </c>
+      <c r="J28" s="10" t="inlineStr">
+        <is>
+          <t>event 13d ago; PSU/gov in latest proxy; DD 66% (unpriced)</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="22" customHeight="1">
+      <c r="A29" s="5" t="n">
+        <v>25</v>
+      </c>
+      <c r="B29" s="6" t="inlineStr">
+        <is>
+          <t>COSM</t>
+        </is>
+      </c>
+      <c r="C29" s="7" t="inlineStr">
+        <is>
+          <t>Cosmos Health Inc.</t>
+        </is>
+      </c>
+      <c r="D29" s="22" t="n">
+        <v>43</v>
+      </c>
+      <c r="E29" s="5" t="n">
+        <v>19</v>
+      </c>
+      <c r="F29" s="7" t="inlineStr">
+        <is>
+          <t>DEF14A_PSU</t>
+        </is>
+      </c>
+      <c r="G29" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="H29" s="19" t="n">
+        <v>84</v>
+      </c>
+      <c r="I29" s="16" t="n">
+        <v>0.5349246</v>
+      </c>
+      <c r="J29" s="7" t="inlineStr">
+        <is>
+          <t>event 19d ago; PSU/gov in latest proxy; DD 84% (unpriced)</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="22" customHeight="1">
+      <c r="A30" s="8" t="n">
+        <v>26</v>
+      </c>
+      <c r="B30" s="9" t="inlineStr">
+        <is>
+          <t>PSIX</t>
+        </is>
+      </c>
+      <c r="C30" s="10" t="inlineStr">
+        <is>
+          <t>Power Solutions International,</t>
+        </is>
+      </c>
+      <c r="D30" s="22" t="n">
+        <v>43</v>
+      </c>
+      <c r="E30" s="8" t="n">
+        <v>12</v>
+      </c>
+      <c r="F30" s="10" t="inlineStr">
+        <is>
+          <t>DEF14A_PSU</t>
+        </is>
+      </c>
+      <c r="G30" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="H30" s="20" t="n">
+        <v>67</v>
+      </c>
+      <c r="I30" s="17" t="n">
+        <v>5.0018616</v>
+      </c>
+      <c r="J30" s="10" t="inlineStr">
+        <is>
+          <t>event 12d ago; PSU/gov in latest proxy; DD 67% (unpriced)</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="22" customHeight="1">
+      <c r="A31" s="5" t="n">
+        <v>27</v>
+      </c>
+      <c r="B31" s="6" t="inlineStr">
+        <is>
+          <t>NXGL</t>
+        </is>
+      </c>
+      <c r="C31" s="7" t="inlineStr">
+        <is>
+          <t>NexGel, Inc</t>
+        </is>
+      </c>
+      <c r="D31" s="22" t="n">
+        <v>43</v>
+      </c>
+      <c r="E31" s="5" t="n">
+        <v>12</v>
+      </c>
+      <c r="F31" s="7" t="inlineStr">
+        <is>
+          <t>DEF14A_PSU</t>
+        </is>
+      </c>
+      <c r="G31" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="H31" s="19" t="n">
+        <v>80</v>
+      </c>
+      <c r="I31" s="16" t="n">
+        <v>1.2016985</v>
+      </c>
+      <c r="J31" s="7" t="inlineStr">
+        <is>
+          <t>event 12d ago; PSU/gov in latest proxy; DD 80% (unpriced)</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="22" customHeight="1">
+      <c r="A32" s="8" t="n">
+        <v>28</v>
+      </c>
+      <c r="B32" s="9" t="inlineStr">
+        <is>
+          <t>CRM</t>
+        </is>
+      </c>
+      <c r="C32" s="10" t="inlineStr">
+        <is>
+          <t>Salesforce, Inc.</t>
+        </is>
+      </c>
+      <c r="D32" s="22" t="n">
+        <v>42</v>
+      </c>
+      <c r="E32" s="8" t="n">
+        <v>24</v>
+      </c>
+      <c r="F32" s="10" t="inlineStr">
+        <is>
+          <t>10b5-1_TERM</t>
+        </is>
+      </c>
+      <c r="G32" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="H32" s="20" t="n">
+        <v>45</v>
+      </c>
+      <c r="I32" s="17" t="n">
+        <v>3.6310136</v>
+      </c>
+      <c r="J32" s="10" t="inlineStr">
+        <is>
+          <t>event 24d ago; 10b5-1 termination; DD 45%; only 1% above 52w low</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="22" customHeight="1">
+      <c r="A33" s="5" t="n">
+        <v>29</v>
+      </c>
+      <c r="B33" s="6" t="inlineStr">
+        <is>
+          <t>VTS</t>
+        </is>
+      </c>
+      <c r="C33" s="7" t="inlineStr">
+        <is>
+          <t>Vitesse Energy, Inc.</t>
+        </is>
+      </c>
+      <c r="D33" s="22" t="n">
+        <v>42</v>
+      </c>
+      <c r="E33" s="5" t="n">
+        <v>20</v>
+      </c>
+      <c r="F33" s="7" t="inlineStr">
+        <is>
+          <t>F4_PBUY</t>
+        </is>
+      </c>
+      <c r="G33" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="H33" s="19" t="n">
+        <v>41</v>
+      </c>
+      <c r="I33" s="16" t="n">
+        <v>1.1419401</v>
+      </c>
+      <c r="J33" s="7" t="inlineStr">
+        <is>
+          <t>event 20d ago; insider P-buy; DD 41%; only 1% above 52w low</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="22" customHeight="1">
+      <c r="A34" s="8" t="n">
+        <v>30</v>
+      </c>
+      <c r="B34" s="9" t="inlineStr">
+        <is>
+          <t>DNUT</t>
+        </is>
+      </c>
+      <c r="C34" s="10" t="inlineStr">
+        <is>
+          <t>Krispy Kreme, Inc.</t>
+        </is>
+      </c>
+      <c r="D34" s="22" t="n">
+        <v>42</v>
+      </c>
+      <c r="E34" s="8" t="n">
+        <v>5</v>
+      </c>
+      <c r="F34" s="10" t="inlineStr">
+        <is>
+          <t>ACTIVIST_13D</t>
+        </is>
+      </c>
+      <c r="G34" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="H34" s="20" t="n">
+        <v>37</v>
+      </c>
+      <c r="I34" s="17" t="n">
+        <v>0.98991</v>
+      </c>
+      <c r="J34" s="10" t="inlineStr">
+        <is>
+          <t>event 5d ago; 2 events in 30d</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="22" customHeight="1">
+      <c r="A35" s="5" t="n">
+        <v>31</v>
+      </c>
+      <c r="B35" s="6" t="inlineStr">
+        <is>
+          <t>NRDY</t>
+        </is>
+      </c>
+      <c r="C35" s="7" t="inlineStr">
+        <is>
+          <t>Nerdy Inc.</t>
+        </is>
+      </c>
+      <c r="D35" s="22" t="n">
+        <v>41</v>
+      </c>
+      <c r="E35" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="F35" s="7" t="inlineStr">
+        <is>
+          <t>ACTIVIST_13D</t>
+        </is>
+      </c>
+      <c r="G35" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="H35" s="19" t="n">
+        <v>51</v>
+      </c>
+      <c r="I35" s="16" t="n">
+        <v>5.5558443</v>
+      </c>
+      <c r="J35" s="7" t="inlineStr">
+        <is>
+          <t>event 4d ago; 2 events in 30d; DD 51%</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="22" customHeight="1">
+      <c r="A36" s="8" t="n">
+        <v>32</v>
+      </c>
+      <c r="B36" s="9" t="inlineStr">
+        <is>
+          <t>ARTV</t>
+        </is>
+      </c>
+      <c r="C36" s="10" t="inlineStr">
+        <is>
+          <t>Artiva Biotherapeutics, Inc.</t>
+        </is>
+      </c>
+      <c r="D36" s="22" t="n">
+        <v>41</v>
+      </c>
+      <c r="E36" s="8" t="n">
+        <v>6</v>
+      </c>
+      <c r="F36" s="10" t="inlineStr">
+        <is>
+          <t>ACTIVIST_13D</t>
+        </is>
+      </c>
+      <c r="G36" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="H36" s="20" t="n">
+        <v>49</v>
+      </c>
+      <c r="I36" s="17" t="n">
+        <v>2.0877886</v>
+      </c>
+      <c r="J36" s="10" t="inlineStr">
+        <is>
+          <t>event 6d ago; 2 events in 30d; DD 49%</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="22" customHeight="1">
+      <c r="A37" s="5" t="n">
+        <v>33</v>
+      </c>
+      <c r="B37" s="6" t="inlineStr">
+        <is>
+          <t>STE</t>
+        </is>
+      </c>
+      <c r="C37" s="7" t="inlineStr">
+        <is>
+          <t>STERIS plc (Ireland)</t>
+        </is>
+      </c>
+      <c r="D37" s="22" t="n">
+        <v>41</v>
+      </c>
+      <c r="E37" s="5" t="n">
+        <v>10</v>
+      </c>
+      <c r="F37" s="7" t="inlineStr">
+        <is>
+          <t>DEF14A_PSU</t>
+        </is>
+      </c>
+      <c r="G37" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="H37" s="19" t="n">
+        <v>25</v>
+      </c>
+      <c r="I37" s="16" t="n">
+        <v>2.7584</v>
+      </c>
+      <c r="J37" s="7" t="inlineStr">
+        <is>
+          <t>event 10d ago; PSU/gov in latest proxy; only 4% above 52w low</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="22" customHeight="1">
+      <c r="A38" s="8" t="n">
+        <v>34</v>
+      </c>
+      <c r="B38" s="9" t="inlineStr">
+        <is>
+          <t>RBRK</t>
+        </is>
+      </c>
+      <c r="C38" s="10" t="inlineStr">
+        <is>
+          <t>Rubrik, Inc.</t>
+        </is>
+      </c>
+      <c r="D38" s="22" t="n">
+        <v>41</v>
+      </c>
+      <c r="E38" s="8" t="n">
+        <v>16</v>
+      </c>
+      <c r="F38" s="10" t="inlineStr">
+        <is>
+          <t>10b5-1_TERM</t>
+        </is>
+      </c>
+      <c r="G38" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="H38" s="20" t="n">
+        <v>30</v>
+      </c>
+      <c r="I38" s="17" t="n">
+        <v>-30.021378</v>
+      </c>
+      <c r="J38" s="10" t="inlineStr">
+        <is>
+          <t>event 16d ago; 10b5-1 termination; 2 events in 30d</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="22" customHeight="1">
+      <c r="A39" s="5" t="n">
+        <v>35</v>
+      </c>
+      <c r="B39" s="6" t="inlineStr">
+        <is>
+          <t>MDLN</t>
+        </is>
+      </c>
+      <c r="C39" s="7" t="inlineStr">
+        <is>
+          <t>Medline Inc.</t>
+        </is>
+      </c>
+      <c r="D39" s="22" t="n">
+        <v>40</v>
+      </c>
+      <c r="E39" s="5" t="n">
+        <v>19</v>
+      </c>
+      <c r="F39" s="7" t="inlineStr">
+        <is>
+          <t>RESTRUCT_8K</t>
+        </is>
+      </c>
+      <c r="G39" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="H39" s="19" t="n">
+        <v>29</v>
+      </c>
+      <c r="I39" s="16" t="n">
+        <v>2.697388</v>
+      </c>
+      <c r="J39" s="7" t="inlineStr">
+        <is>
+          <t>event 19d ago; RESTRUCT_8K; only 10% above 52w low</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="22" customHeight="1">
+      <c r="A40" s="8" t="n">
+        <v>36</v>
+      </c>
+      <c r="B40" s="9" t="inlineStr">
+        <is>
+          <t>TORO</t>
+        </is>
+      </c>
+      <c r="C40" s="10" t="inlineStr">
+        <is>
+          <t>Toro Corp.</t>
+        </is>
+      </c>
+      <c r="D40" s="22" t="n">
+        <v>40</v>
+      </c>
+      <c r="E40" s="8" t="n">
+        <v>12</v>
+      </c>
+      <c r="F40" s="10" t="inlineStr">
+        <is>
+          <t>ACTIVIST_13D</t>
+        </is>
+      </c>
+      <c r="G40" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="H40" s="20" t="n">
+        <v>40</v>
+      </c>
+      <c r="I40" s="17" t="n">
+        <v>0.6729493</v>
+      </c>
+      <c r="J40" s="10" t="inlineStr">
+        <is>
+          <t>event 12d ago; 2 events in 30d; DD 40%</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="22" customHeight="1">
+      <c r="A41" s="5" t="n">
+        <v>37</v>
+      </c>
+      <c r="B41" s="6" t="inlineStr">
+        <is>
+          <t>CURI</t>
+        </is>
+      </c>
+      <c r="C41" s="7" t="inlineStr">
+        <is>
+          <t>CuriosityStream Inc.</t>
+        </is>
+      </c>
+      <c r="D41" s="22" t="n">
+        <v>40</v>
+      </c>
+      <c r="E41" s="5" t="n">
+        <v>20</v>
+      </c>
+      <c r="F41" s="7" t="inlineStr">
+        <is>
+          <t>F4_PBUY</t>
+        </is>
+      </c>
+      <c r="G41" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="H41" s="19" t="n">
+        <v>57</v>
+      </c>
+      <c r="I41" s="16" t="n">
+        <v>4.113821</v>
+      </c>
+      <c r="J41" s="7" t="inlineStr">
+        <is>
+          <t>event 20d ago; insider P-buy; 2 events in 30d; DD 57%</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="22" customHeight="1">
+      <c r="A42" s="8" t="n">
+        <v>38</v>
+      </c>
+      <c r="B42" s="9" t="inlineStr">
+        <is>
+          <t>HCAT</t>
+        </is>
+      </c>
+      <c r="C42" s="10" t="inlineStr">
+        <is>
+          <t>Health Catalyst, Inc</t>
+        </is>
+      </c>
+      <c r="D42" s="22" t="n">
+        <v>40</v>
+      </c>
+      <c r="E42" s="8" t="n">
+        <v>13</v>
+      </c>
+      <c r="F42" s="10" t="inlineStr">
+        <is>
+          <t>ACTIVIST_13D</t>
+        </is>
+      </c>
+      <c r="G42" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="H42" s="20" t="n">
+        <v>55</v>
+      </c>
+      <c r="I42" s="17" t="n">
+        <v>0.98772025</v>
+      </c>
+      <c r="J42" s="10" t="inlineStr">
+        <is>
+          <t>event 13d ago; 2 events in 30d; DD 55%</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="22" customHeight="1">
+      <c r="A43" s="5" t="n">
+        <v>39</v>
+      </c>
+      <c r="B43" s="6" t="inlineStr">
+        <is>
+          <t>DOMO</t>
+        </is>
+      </c>
+      <c r="C43" s="7" t="inlineStr">
+        <is>
+          <t>Domo, Inc.</t>
+        </is>
+      </c>
+      <c r="D43" s="16" t="n">
+        <v>39</v>
+      </c>
+      <c r="E43" s="5" t="n">
+        <v>18</v>
+      </c>
+      <c r="F43" s="7" t="inlineStr">
+        <is>
+          <t>ACTIVIST_13D</t>
+        </is>
+      </c>
+      <c r="G43" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="H43" s="19" t="n">
+        <v>87</v>
+      </c>
+      <c r="I43" s="16" t="n">
+        <v>-0.55213326</v>
+      </c>
+      <c r="J43" s="7" t="inlineStr">
+        <is>
+          <t>event 18d ago; 3 events in 30d; DD 87% (unpriced)</t>
+        </is>
+      </c>
+    </row>
+    <row r="44" ht="22" customHeight="1">
+      <c r="A44" s="8" t="n">
+        <v>40</v>
+      </c>
+      <c r="B44" s="9" t="inlineStr">
+        <is>
+          <t>BLND</t>
+        </is>
+      </c>
+      <c r="C44" s="10" t="inlineStr">
+        <is>
+          <t>Blend Labs, Inc.</t>
+        </is>
+      </c>
+      <c r="D44" s="17" t="n">
+        <v>39</v>
+      </c>
+      <c r="E44" s="8" t="n">
+        <v>9</v>
+      </c>
+      <c r="F44" s="10" t="inlineStr">
+        <is>
+          <t>ACTIVIST_13D</t>
+        </is>
+      </c>
+      <c r="G44" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="H44" s="20" t="n">
+        <v>63</v>
+      </c>
+      <c r="I44" s="17" t="n">
+        <v>-7.300885</v>
+      </c>
+      <c r="J44" s="10" t="inlineStr">
+        <is>
+          <t>event 9d ago; 2 events in 30d; DD 63% (unpriced)</t>
+        </is>
+      </c>
+    </row>
+    <row r="46" ht="28" customHeight="1">
+      <c r="A46" s="11" t="inlineStr">
+        <is>
+          <t>30-day window of `recent_incentive_asymmetry.py`. Event types: DEF14A_PSU (latest proxy), 10b5-1_TERM (insider walked back scheduled selling), F4_PBUY (insider open-market purchase), ACTIVIST_13D, RESTRUCT_8K (8-K restructuring keyword), FORM_10_SPINOFF, NOL_SHELL. Score boosts: drawdown &gt;60% unpriced (+15), multi-event cluster (+12), event in last 7 days (+25). Source: recent_incentive_asymmetry_30d.csv.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="3">
+    <mergeCell ref="A1:J1"/>
+    <mergeCell ref="A46:J46"/>
+    <mergeCell ref="A2:J2"/>
+  </mergeCells>
+  <printOptions horizontalCentered="0"/>
+  <pageMargins left="0.5" right="0.5" top="0.6" bottom="0.6" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
   <dimension ref="A1:H66"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -16679,7 +18297,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -18475,7 +20093,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -21035,7 +22653,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -21637,7 +23255,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -22449,7 +24067,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>

--- a/MOST_ASYMMETRIC.xlsx
+++ b/MOST_ASYMMETRIC.xlsx
@@ -20,19 +20,20 @@
     <sheet name="Payoff Geometry" sheetId="11" state="visible" r:id="rId11"/>
     <sheet name="Mechanism Gates" sheetId="12" state="visible" r:id="rId12"/>
     <sheet name="Re-Rate Catalysts" sheetId="13" state="visible" r:id="rId13"/>
-    <sheet name="Winners Study" sheetId="14" state="visible" r:id="rId14"/>
-    <sheet name="Asymmetry Assembly" sheetId="15" state="visible" r:id="rId15"/>
-    <sheet name="Distressed Stub Progress" sheetId="16" state="visible" r:id="rId16"/>
-    <sheet name="Hidden Asset Realisation" sheetId="17" state="visible" r:id="rId17"/>
-    <sheet name="UK Capital Events" sheetId="18" state="visible" r:id="rId18"/>
-    <sheet name="Without Valuation" sheetId="19" state="visible" r:id="rId19"/>
-    <sheet name="Recent 30d" sheetId="20" state="visible" r:id="rId20"/>
-    <sheet name="Foreign Markets" sheetId="21" state="visible" r:id="rId21"/>
-    <sheet name="Turnaround Signal" sheetId="22" state="visible" r:id="rId22"/>
-    <sheet name="Single-Measure Best" sheetId="23" state="visible" r:id="rId23"/>
-    <sheet name="Layer Correlation" sheetId="24" state="visible" r:id="rId24"/>
-    <sheet name="Coverage &amp; Tiers" sheetId="25" state="visible" r:id="rId25"/>
-    <sheet name="Methodology" sheetId="26" state="visible" r:id="rId26"/>
+    <sheet name="Re-Rate Backtest" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet name="Winners Study" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet name="Asymmetry Assembly" sheetId="16" state="visible" r:id="rId16"/>
+    <sheet name="Distressed Stub Progress" sheetId="17" state="visible" r:id="rId17"/>
+    <sheet name="Hidden Asset Realisation" sheetId="18" state="visible" r:id="rId18"/>
+    <sheet name="UK Capital Events" sheetId="19" state="visible" r:id="rId19"/>
+    <sheet name="Without Valuation" sheetId="20" state="visible" r:id="rId20"/>
+    <sheet name="Recent 30d" sheetId="21" state="visible" r:id="rId21"/>
+    <sheet name="Foreign Markets" sheetId="22" state="visible" r:id="rId22"/>
+    <sheet name="Turnaround Signal" sheetId="23" state="visible" r:id="rId23"/>
+    <sheet name="Single-Measure Best" sheetId="24" state="visible" r:id="rId24"/>
+    <sheet name="Layer Correlation" sheetId="25" state="visible" r:id="rId25"/>
+    <sheet name="Coverage &amp; Tiers" sheetId="26" state="visible" r:id="rId26"/>
+    <sheet name="Methodology" sheetId="27" state="visible" r:id="rId27"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Titles" localSheetId="0">'Contents'!$1:$4</definedName>
@@ -48,19 +49,20 @@
     <definedName name="_xlnm.Print_Titles" localSheetId="10">'Payoff Geometry'!$1:$4</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="11">'Mechanism Gates'!$1:$4</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="12">'Re-Rate Catalysts'!$1:$4</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="13">'Winners Study'!$1:$4</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="14">'Asymmetry Assembly'!$1:$4</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="15">'Distressed Stub Progress'!$1:$4</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="16">'Hidden Asset Realisation'!$1:$4</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="17">'UK Capital Events'!$1:$4</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="18">'Without Valuation'!$1:$4</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="19">'Recent 30d'!$1:$4</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="20">'Foreign Markets'!$1:$4</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="21">'Turnaround Signal'!$1:$4</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="22">'Single-Measure Best'!$1:$4</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="23">'Layer Correlation'!$1:$4</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="24">'Coverage &amp; Tiers'!$1:$4</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="25">'Methodology'!$1:$4</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="13">'Re-Rate Backtest'!$1:$4</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="14">'Winners Study'!$1:$4</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="15">'Asymmetry Assembly'!$1:$4</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="16">'Distressed Stub Progress'!$1:$4</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="17">'Hidden Asset Realisation'!$1:$4</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="18">'UK Capital Events'!$1:$4</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="19">'Without Valuation'!$1:$4</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="20">'Recent 30d'!$1:$4</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="21">'Foreign Markets'!$1:$4</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="22">'Turnaround Signal'!$1:$4</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="23">'Single-Measure Best'!$1:$4</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="24">'Layer Correlation'!$1:$4</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="25">'Coverage &amp; Tiers'!$1:$4</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="26">'Methodology'!$1:$4</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -599,7 +601,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:C31"/>
+  <dimension ref="A1:C32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -827,12 +829,12 @@
       </c>
       <c r="B17" s="6" t="inlineStr">
         <is>
-          <t>Winners Study</t>
+          <t>Re-Rate Backtest</t>
         </is>
       </c>
       <c r="C17" s="7" t="inlineStr">
         <is>
-          <t>What realized 1-year re-raters had in common — feature/sector lifts, with the pre-move-data caveat.</t>
+          <t>What those catalysts actually returned historically — the evidence behind the weights.</t>
         </is>
       </c>
     </row>
@@ -842,12 +844,12 @@
       </c>
       <c r="B18" s="9" t="inlineStr">
         <is>
-          <t>Asymmetry Assembly</t>
+          <t>Winners Study</t>
         </is>
       </c>
       <c r="C18" s="10" t="inlineStr">
         <is>
-          <t>PSIX-recipe conjunction: cheap + inflection + leverage + insider co-occurring.</t>
+          <t>What realized 1-year re-raters had in common — feature/sector lifts, with the pre-move-data caveat.</t>
         </is>
       </c>
     </row>
@@ -857,12 +859,12 @@
       </c>
       <c r="B19" s="6" t="inlineStr">
         <is>
-          <t>Distressed Stub Progress</t>
+          <t>Asymmetry Assembly</t>
         </is>
       </c>
       <c r="C19" s="7" t="inlineStr">
         <is>
-          <t>Finality-gated capital-structure value-unlock events, waterfall-scored.</t>
+          <t>PSIX-recipe conjunction: cheap + inflection + leverage + insider co-occurring.</t>
         </is>
       </c>
     </row>
@@ -872,12 +874,12 @@
       </c>
       <c r="B20" s="9" t="inlineStr">
         <is>
-          <t>Hidden Asset Realisation</t>
+          <t>Distressed Stub Progress</t>
         </is>
       </c>
       <c r="C20" s="10" t="inlineStr">
         <is>
-          <t>Spectrum/rights/RE inside levered stubs with mandatory-prepay debt sweeps (SSP-type).</t>
+          <t>Finality-gated capital-structure value-unlock events, waterfall-scored.</t>
         </is>
       </c>
     </row>
@@ -887,12 +889,12 @@
       </c>
       <c r="B21" s="6" t="inlineStr">
         <is>
-          <t>UK Capital Events</t>
+          <t>Hidden Asset Realisation</t>
         </is>
       </c>
       <c r="C21" s="7" t="inlineStr">
         <is>
-          <t>UK RNS revealed-preference &amp; distressed monitor (separate universe; funds filtered).</t>
+          <t>Spectrum/rights/RE inside levered stubs with mandatory-prepay debt sweeps (SSP-type).</t>
         </is>
       </c>
     </row>
@@ -902,12 +904,12 @@
       </c>
       <c r="B22" s="9" t="inlineStr">
         <is>
-          <t>Without Valuation</t>
+          <t>UK Capital Events</t>
         </is>
       </c>
       <c r="C22" s="10" t="inlineStr">
         <is>
-          <t>Parallel ranking excluding the valuation leg.</t>
+          <t>UK RNS revealed-preference &amp; distressed monitor (separate universe; funds filtered).</t>
         </is>
       </c>
     </row>
@@ -917,12 +919,12 @@
       </c>
       <c r="B23" s="6" t="inlineStr">
         <is>
-          <t>Recent 30d</t>
+          <t>Without Valuation</t>
         </is>
       </c>
       <c r="C23" s="7" t="inlineStr">
         <is>
-          <t>Material incentive events disclosed in the last 30 days.</t>
+          <t>Parallel ranking excluding the valuation leg.</t>
         </is>
       </c>
     </row>
@@ -932,12 +934,12 @@
       </c>
       <c r="B24" s="9" t="inlineStr">
         <is>
-          <t>Foreign Markets</t>
+          <t>Recent 30d</t>
         </is>
       </c>
       <c r="C24" s="10" t="inlineStr">
         <is>
-          <t>Japan TSE PBR&lt;1, Korea Value-Up, UK schemes.</t>
+          <t>Material incentive events disclosed in the last 30 days.</t>
         </is>
       </c>
     </row>
@@ -947,12 +949,12 @@
       </c>
       <c r="B25" s="6" t="inlineStr">
         <is>
-          <t>Turnaround Signal</t>
+          <t>Foreign Markets</t>
         </is>
       </c>
       <c r="C25" s="7" t="inlineStr">
         <is>
-          <t>Bollenbach pattern: turnaround talent into distress.</t>
+          <t>Japan TSE PBR&lt;1, Korea Value-Up, UK schemes.</t>
         </is>
       </c>
     </row>
@@ -962,12 +964,12 @@
       </c>
       <c r="B26" s="9" t="inlineStr">
         <is>
-          <t>Single-Measure Best</t>
+          <t>Turnaround Signal</t>
         </is>
       </c>
       <c r="C26" s="10" t="inlineStr">
         <is>
-          <t>Best in class on each individual signal.</t>
+          <t>Bollenbach pattern: turnaround talent into distress.</t>
         </is>
       </c>
     </row>
@@ -977,12 +979,12 @@
       </c>
       <c r="B27" s="6" t="inlineStr">
         <is>
-          <t>Layer Correlation</t>
+          <t>Single-Measure Best</t>
         </is>
       </c>
       <c r="C27" s="7" t="inlineStr">
         <is>
-          <t>Pairwise layer correlation and effective independence.</t>
+          <t>Best in class on each individual signal.</t>
         </is>
       </c>
     </row>
@@ -992,12 +994,12 @@
       </c>
       <c r="B28" s="9" t="inlineStr">
         <is>
-          <t>Coverage &amp; Tiers</t>
+          <t>Layer Correlation</t>
         </is>
       </c>
       <c r="C28" s="10" t="inlineStr">
         <is>
-          <t>Live per-layer coverage, data age, firing distribution.</t>
+          <t>Pairwise layer correlation and effective independence.</t>
         </is>
       </c>
     </row>
@@ -1007,17 +1009,32 @@
       </c>
       <c r="B29" s="6" t="inlineStr">
         <is>
+          <t>Coverage &amp; Tiers</t>
+        </is>
+      </c>
+      <c r="C29" s="7" t="inlineStr">
+        <is>
+          <t>Live per-layer coverage, data age, firing distribution.</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="16" customHeight="1">
+      <c r="A30" s="8" t="n">
+        <v>26</v>
+      </c>
+      <c r="B30" s="9" t="inlineStr">
+        <is>
           <t>Methodology</t>
         </is>
       </c>
-      <c r="C29" s="7" t="inlineStr">
+      <c r="C30" s="10" t="inlineStr">
         <is>
           <t>How the composite is built, step by step.</t>
         </is>
       </c>
     </row>
-    <row r="31" ht="28" customHeight="1">
-      <c r="A31" s="11" t="inlineStr">
+    <row r="32" ht="28" customHeight="1">
+      <c r="A32" s="11" t="inlineStr">
         <is>
           <t>Generated by build_most_asymmetric_xlsx.py from the live consensus on disk. Every figure in this workbook is computed at build time; nothing is hardcoded. Single typeface (Times New Roman, 10pt); hierarchy by weight and rule only.</t>
         </is>
@@ -1026,7 +1043,7 @@
   </sheetData>
   <mergeCells count="3">
     <mergeCell ref="A1:C1"/>
-    <mergeCell ref="A31:C31"/>
+    <mergeCell ref="A32:C32"/>
     <mergeCell ref="A2:C2"/>
   </mergeCells>
   <printOptions horizontalCentered="0"/>
@@ -6289,83 +6306,83 @@
     <row r="7" ht="22" customHeight="1">
       <c r="A7" s="6" t="inlineStr">
         <is>
-          <t>LE</t>
+          <t>VERI</t>
         </is>
       </c>
       <c r="B7" s="7" t="inlineStr">
         <is>
-          <t>Lands' End, Inc.</t>
+          <t>Veritone, Inc.</t>
         </is>
       </c>
       <c r="C7" s="16" t="n">
-        <v>27.2</v>
+        <v>25.2</v>
       </c>
       <c r="D7" s="16" t="n">
         <v>2</v>
       </c>
       <c r="E7" s="16" t="n">
-        <v>5.1</v>
+        <v>1.1</v>
       </c>
       <c r="F7" s="19" t="n">
-        <v>176</v>
+        <v>86</v>
       </c>
       <c r="G7" s="7" t="inlineStr">
         <is>
-          <t>Sale Of Company [tender]; Strategic Review [</t>
+          <t>Sale Of Company [incentive]; Spinoff [incent</t>
         </is>
       </c>
     </row>
     <row r="8" ht="22" customHeight="1">
       <c r="A8" s="9" t="inlineStr">
         <is>
-          <t>HYFM</t>
+          <t>BIRD</t>
         </is>
       </c>
       <c r="B8" s="10" t="inlineStr">
         <is>
-          <t>Hydrofarm Holdings Gro</t>
+          <t>Allbirds, Inc.</t>
         </is>
       </c>
       <c r="C8" s="17" t="n">
-        <v>25.5</v>
+        <v>24.6</v>
       </c>
       <c r="D8" s="17" t="n">
         <v>2</v>
       </c>
       <c r="E8" s="17" t="n">
-        <v>3</v>
+        <v>1.8</v>
       </c>
       <c r="F8" s="20" t="n">
-        <v>300</v>
+        <v>137</v>
       </c>
       <c r="G8" s="10" t="inlineStr">
         <is>
-          <t>Sale Of Company [incentive]; Strategic Revie</t>
+          <t>Asset Sale [narrative]; Spinoff [incentive]</t>
         </is>
       </c>
     </row>
     <row r="9" ht="22" customHeight="1">
       <c r="A9" s="6" t="inlineStr">
         <is>
-          <t>VERI</t>
+          <t>TCRT</t>
         </is>
       </c>
       <c r="B9" s="7" t="inlineStr">
         <is>
-          <t>Veritone, Inc.</t>
+          <t>Alaunos Therapeutics,</t>
         </is>
       </c>
       <c r="C9" s="16" t="n">
-        <v>25.2</v>
+        <v>23.4</v>
       </c>
       <c r="D9" s="16" t="n">
         <v>2</v>
       </c>
       <c r="E9" s="16" t="n">
-        <v>1.1</v>
+        <v>0.6</v>
       </c>
       <c r="F9" s="19" t="n">
-        <v>86</v>
+        <v>39</v>
       </c>
       <c r="G9" s="7" t="inlineStr">
         <is>
@@ -6376,25 +6393,25 @@
     <row r="10" ht="22" customHeight="1">
       <c r="A10" s="9" t="inlineStr">
         <is>
-          <t>TCRT</t>
+          <t>PSTV</t>
         </is>
       </c>
       <c r="B10" s="10" t="inlineStr">
         <is>
-          <t>Alaunos Therapeutics,</t>
+          <t>PLUS THERAPEUTICS, Inc</t>
         </is>
       </c>
       <c r="C10" s="17" t="n">
-        <v>23.4</v>
+        <v>22.5</v>
       </c>
       <c r="D10" s="17" t="n">
         <v>2</v>
       </c>
       <c r="E10" s="17" t="n">
-        <v>0.6</v>
+        <v>0.2</v>
       </c>
       <c r="F10" s="20" t="n">
-        <v>39</v>
+        <v>12</v>
       </c>
       <c r="G10" s="10" t="inlineStr">
         <is>
@@ -6405,141 +6422,153 @@
     <row r="11" ht="22" customHeight="1">
       <c r="A11" s="6" t="inlineStr">
         <is>
-          <t>BIRD</t>
+          <t>PALI</t>
         </is>
       </c>
       <c r="B11" s="7" t="inlineStr">
         <is>
-          <t>Allbirds, Inc.</t>
+          <t>Palisade Bio, Inc.</t>
         </is>
       </c>
       <c r="C11" s="16" t="n">
-        <v>23.3</v>
+        <v>22.4</v>
       </c>
       <c r="D11" s="16" t="n">
         <v>2</v>
       </c>
       <c r="E11" s="16" t="n">
-        <v>1.8</v>
+        <v>0.1</v>
       </c>
       <c r="F11" s="19" t="n">
-        <v>137</v>
+        <v>11</v>
       </c>
       <c r="G11" s="7" t="inlineStr">
         <is>
-          <t>Asset Sale [narrative]; Spinoff [incentive]</t>
+          <t>Sale Of Company [incentive]; Spinoff [incent</t>
         </is>
       </c>
     </row>
     <row r="12" ht="22" customHeight="1">
       <c r="A12" s="9" t="inlineStr">
         <is>
-          <t>QMCO</t>
+          <t>MNRO</t>
         </is>
       </c>
       <c r="B12" s="10" t="inlineStr">
         <is>
-          <t>Quantum Corporation</t>
+          <t>Monro, Inc.</t>
         </is>
       </c>
       <c r="C12" s="17" t="n">
-        <v>23.2</v>
+        <v>22.2</v>
       </c>
       <c r="D12" s="17" t="n">
         <v>2</v>
       </c>
       <c r="E12" s="17" t="n">
-        <v>1.3</v>
+        <v>1.8</v>
       </c>
       <c r="F12" s="20" t="n">
-        <v>134</v>
+        <v>66</v>
       </c>
       <c r="G12" s="10" t="inlineStr">
         <is>
-          <t>Spinoff [incentive]; Strategic Review [narra</t>
+          <t>Sale Of Company [narrative]; Spinoff [incent</t>
         </is>
       </c>
     </row>
     <row r="13" ht="22" customHeight="1">
       <c r="A13" s="6" t="inlineStr">
         <is>
-          <t>RYN</t>
+          <t>ACAD</t>
         </is>
       </c>
       <c r="B13" s="7" t="inlineStr">
         <is>
-          <t>Rayonier Inc. REIT</t>
+          <t>ACADIA Pharmaceuticals</t>
         </is>
       </c>
       <c r="C13" s="16" t="n">
-        <v>22.8</v>
+        <v>22</v>
       </c>
       <c r="D13" s="16" t="n">
         <v>2</v>
       </c>
-      <c r="E13" s="16" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="F13" s="19" t="n">
-        <v>22</v>
+      <c r="E13" s="7" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="F13" s="7" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
       <c r="G13" s="7" t="inlineStr">
         <is>
-          <t>Asset Sale [incentive]; Sale Of Company [inc</t>
+          <t>Sale Of Company [incentive]; Spinoff [incent</t>
         </is>
       </c>
     </row>
     <row r="14" ht="22" customHeight="1">
       <c r="A14" s="9" t="inlineStr">
         <is>
-          <t>NUS</t>
+          <t>HON</t>
         </is>
       </c>
       <c r="B14" s="10" t="inlineStr">
         <is>
-          <t>Nu Skin Enterprises, I</t>
+          <t>Honeywell Internationa</t>
         </is>
       </c>
       <c r="C14" s="17" t="n">
-        <v>22.5</v>
+        <v>22</v>
       </c>
       <c r="D14" s="17" t="n">
-        <v>1</v>
-      </c>
-      <c r="E14" s="17" t="n">
-        <v>60</v>
-      </c>
-      <c r="F14" s="20" t="n">
-        <v>300</v>
+        <v>2</v>
+      </c>
+      <c r="E14" s="10" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="F14" s="10" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
       <c r="G14" s="10" t="inlineStr">
         <is>
-          <t>Asset Sale [incentive/narrative]</t>
+          <t>Separation [narrative]; Spinoff [incentive]</t>
         </is>
       </c>
     </row>
     <row r="15" ht="22" customHeight="1">
       <c r="A15" s="6" t="inlineStr">
         <is>
-          <t>PSTV</t>
+          <t>NBIX</t>
         </is>
       </c>
       <c r="B15" s="7" t="inlineStr">
         <is>
-          <t>PLUS THERAPEUTICS, Inc</t>
+          <t>Neurocrine Biosciences</t>
         </is>
       </c>
       <c r="C15" s="16" t="n">
-        <v>22.5</v>
+        <v>22</v>
       </c>
       <c r="D15" s="16" t="n">
         <v>2</v>
       </c>
-      <c r="E15" s="16" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="F15" s="19" t="n">
-        <v>12</v>
+      <c r="E15" s="7" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="F15" s="7" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
       <c r="G15" s="7" t="inlineStr">
         <is>
@@ -6550,25 +6579,29 @@
     <row r="16" ht="22" customHeight="1">
       <c r="A16" s="9" t="inlineStr">
         <is>
-          <t>PALI</t>
+          <t>SNDX</t>
         </is>
       </c>
       <c r="B16" s="10" t="inlineStr">
         <is>
-          <t>Palisade Bio, Inc.</t>
+          <t>Syndax Pharmaceuticals</t>
         </is>
       </c>
       <c r="C16" s="17" t="n">
-        <v>22.4</v>
+        <v>22</v>
       </c>
       <c r="D16" s="17" t="n">
         <v>2</v>
       </c>
-      <c r="E16" s="17" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="F16" s="20" t="n">
-        <v>11</v>
+      <c r="E16" s="10" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="F16" s="10" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
       <c r="G16" s="10" t="inlineStr">
         <is>
@@ -6579,41 +6612,45 @@
     <row r="17" ht="22" customHeight="1">
       <c r="A17" s="6" t="inlineStr">
         <is>
-          <t>MNRO</t>
+          <t>SENS</t>
         </is>
       </c>
       <c r="B17" s="7" t="inlineStr">
         <is>
-          <t>Monro, Inc.</t>
+          <t>Senseonics Holdings, I</t>
         </is>
       </c>
       <c r="C17" s="16" t="n">
-        <v>22.2</v>
+        <v>22</v>
       </c>
       <c r="D17" s="16" t="n">
         <v>2</v>
       </c>
-      <c r="E17" s="16" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="F17" s="19" t="n">
-        <v>66</v>
+      <c r="E17" s="7" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="F17" s="7" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
       <c r="G17" s="7" t="inlineStr">
         <is>
-          <t>Sale Of Company [narrative]; Spinoff [incent</t>
+          <t>Sale Of Company [incentive]; Spinoff [incent</t>
         </is>
       </c>
     </row>
     <row r="18" ht="22" customHeight="1">
       <c r="A18" s="9" t="inlineStr">
         <is>
-          <t>ACAD</t>
+          <t>MIST</t>
         </is>
       </c>
       <c r="B18" s="10" t="inlineStr">
         <is>
-          <t>ACADIA Pharmaceuticals</t>
+          <t>Milestone Pharmaceutic</t>
         </is>
       </c>
       <c r="C18" s="17" t="n">
@@ -6641,12 +6678,12 @@
     <row r="19" ht="22" customHeight="1">
       <c r="A19" s="6" t="inlineStr">
         <is>
-          <t>NBIX</t>
+          <t>QMCO</t>
         </is>
       </c>
       <c r="B19" s="7" t="inlineStr">
         <is>
-          <t>Neurocrine Biosciences</t>
+          <t>Quantum Corporation</t>
         </is>
       </c>
       <c r="C19" s="16" t="n">
@@ -6655,167 +6692,147 @@
       <c r="D19" s="16" t="n">
         <v>2</v>
       </c>
-      <c r="E19" s="7" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="F19" s="7" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+      <c r="E19" s="16" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="F19" s="19" t="n">
+        <v>134</v>
       </c>
       <c r="G19" s="7" t="inlineStr">
         <is>
-          <t>Sale Of Company [incentive]; Spinoff [incent</t>
+          <t>Spinoff [incentive]; Strategic Review [narra</t>
         </is>
       </c>
     </row>
     <row r="20" ht="22" customHeight="1">
       <c r="A20" s="9" t="inlineStr">
         <is>
-          <t>SNDX</t>
+          <t>FLEX</t>
         </is>
       </c>
       <c r="B20" s="10" t="inlineStr">
         <is>
-          <t>Syndax Pharmaceuticals</t>
+          <t>Flex Ltd.</t>
         </is>
       </c>
       <c r="C20" s="17" t="n">
-        <v>22</v>
+        <v>21.1</v>
       </c>
       <c r="D20" s="17" t="n">
         <v>2</v>
       </c>
-      <c r="E20" s="10" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="F20" s="10" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+      <c r="E20" s="17" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F20" s="20" t="n">
+        <v>32</v>
       </c>
       <c r="G20" s="10" t="inlineStr">
         <is>
-          <t>Sale Of Company [incentive]; Spinoff [incent</t>
+          <t>Asset Sale [narrative]; Spinoff [incentive]</t>
         </is>
       </c>
     </row>
     <row r="21" ht="22" customHeight="1">
       <c r="A21" s="6" t="inlineStr">
         <is>
-          <t>SENS</t>
+          <t>NUS</t>
         </is>
       </c>
       <c r="B21" s="7" t="inlineStr">
         <is>
-          <t>Senseonics Holdings, I</t>
+          <t>Nu Skin Enterprises, I</t>
         </is>
       </c>
       <c r="C21" s="16" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D21" s="16" t="n">
-        <v>2</v>
-      </c>
-      <c r="E21" s="7" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="F21" s="7" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+        <v>1</v>
+      </c>
+      <c r="E21" s="16" t="n">
+        <v>60</v>
+      </c>
+      <c r="F21" s="19" t="n">
+        <v>300</v>
       </c>
       <c r="G21" s="7" t="inlineStr">
         <is>
-          <t>Sale Of Company [incentive]; Spinoff [incent</t>
+          <t>Asset Sale [incentive/narrative]</t>
         </is>
       </c>
     </row>
     <row r="22" ht="22" customHeight="1">
       <c r="A22" s="9" t="inlineStr">
         <is>
-          <t>MIST</t>
+          <t>HYFM</t>
         </is>
       </c>
       <c r="B22" s="10" t="inlineStr">
         <is>
-          <t>Milestone Pharmaceutic</t>
+          <t>Hydrofarm Holdings Gro</t>
         </is>
       </c>
       <c r="C22" s="17" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D22" s="17" t="n">
         <v>2</v>
       </c>
-      <c r="E22" s="10" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="F22" s="10" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+      <c r="E22" s="17" t="n">
+        <v>3</v>
+      </c>
+      <c r="F22" s="20" t="n">
+        <v>300</v>
       </c>
       <c r="G22" s="10" t="inlineStr">
         <is>
-          <t>Sale Of Company [incentive]; Spinoff [incent</t>
+          <t>Sale Of Company [incentive]; Strategic Revie</t>
         </is>
       </c>
     </row>
     <row r="23" ht="22" customHeight="1">
       <c r="A23" s="6" t="inlineStr">
         <is>
-          <t>WBD</t>
+          <t>RYN</t>
         </is>
       </c>
       <c r="B23" s="7" t="inlineStr">
         <is>
-          <t>Warner Bros. Discovery</t>
+          <t>Rayonier Inc. REIT</t>
         </is>
       </c>
       <c r="C23" s="16" t="n">
-        <v>22</v>
+        <v>20.7</v>
       </c>
       <c r="D23" s="16" t="n">
         <v>2</v>
       </c>
-      <c r="E23" s="7" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="F23" s="7" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+      <c r="E23" s="16" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="F23" s="19" t="n">
+        <v>22</v>
       </c>
       <c r="G23" s="7" t="inlineStr">
         <is>
-          <t>Sale Of Company [tender]; Separation [narrat</t>
+          <t>Asset Sale [incentive]; Sale Of Company [inc</t>
         </is>
       </c>
     </row>
     <row r="24" ht="22" customHeight="1">
       <c r="A24" s="9" t="inlineStr">
         <is>
-          <t>LSTA</t>
+          <t>MWA</t>
         </is>
       </c>
       <c r="B24" s="10" t="inlineStr">
         <is>
-          <t>Lisata Therapeutics, I</t>
+          <t>MUELLER WATER PRODUCTS</t>
         </is>
       </c>
       <c r="C24" s="17" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D24" s="17" t="n">
         <v>2</v>
@@ -6832,52 +6849,52 @@
       </c>
       <c r="G24" s="10" t="inlineStr">
         <is>
-          <t>Sale Of Company [tender]; Strategic Review [</t>
+          <t>Asset Sale [narrative]; Spinoff [incentive]</t>
         </is>
       </c>
     </row>
     <row r="25" ht="22" customHeight="1">
       <c r="A25" s="6" t="inlineStr">
         <is>
-          <t>FLEX</t>
+          <t>LE</t>
         </is>
       </c>
       <c r="B25" s="7" t="inlineStr">
         <is>
-          <t>Flex Ltd.</t>
+          <t>Lands' End, Inc.</t>
         </is>
       </c>
       <c r="C25" s="16" t="n">
-        <v>20</v>
+        <v>18.1</v>
       </c>
       <c r="D25" s="16" t="n">
         <v>2</v>
       </c>
       <c r="E25" s="16" t="n">
-        <v>0.3</v>
+        <v>5.1</v>
       </c>
       <c r="F25" s="19" t="n">
-        <v>32</v>
+        <v>176</v>
       </c>
       <c r="G25" s="7" t="inlineStr">
         <is>
-          <t>Asset Sale [narrative]; Spinoff [incentive]</t>
+          <t>Sale Of Company [tender]; Strategic Review [</t>
         </is>
       </c>
     </row>
     <row r="26" ht="22" customHeight="1">
       <c r="A26" s="9" t="inlineStr">
         <is>
-          <t>HON</t>
+          <t>SNOW</t>
         </is>
       </c>
       <c r="B26" s="10" t="inlineStr">
         <is>
-          <t>Honeywell Internationa</t>
+          <t>Snowflake Inc.</t>
         </is>
       </c>
       <c r="C26" s="17" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="D26" s="17" t="n">
         <v>2</v>
@@ -6894,23 +6911,23 @@
       </c>
       <c r="G26" s="10" t="inlineStr">
         <is>
-          <t>Separation [narrative]; Spinoff [incentive]</t>
+          <t>Spinoff [incentive]; Strategic Review [narra</t>
         </is>
       </c>
     </row>
     <row r="27" ht="22" customHeight="1">
       <c r="A27" s="6" t="inlineStr">
         <is>
-          <t>MWA</t>
+          <t>WBD</t>
         </is>
       </c>
       <c r="B27" s="7" t="inlineStr">
         <is>
-          <t>MUELLER WATER PRODUCTS</t>
+          <t>Warner Bros. Discovery</t>
         </is>
       </c>
       <c r="C27" s="16" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D27" s="16" t="n">
         <v>2</v>
@@ -6927,23 +6944,23 @@
       </c>
       <c r="G27" s="7" t="inlineStr">
         <is>
-          <t>Asset Sale [narrative]; Spinoff [incentive]</t>
+          <t>Sale Of Company [tender]; Separation [narrat</t>
         </is>
       </c>
     </row>
     <row r="28" ht="22" customHeight="1">
       <c r="A28" s="9" t="inlineStr">
         <is>
-          <t>SNOW</t>
+          <t>ETN</t>
         </is>
       </c>
       <c r="B28" s="10" t="inlineStr">
         <is>
-          <t>Snowflake Inc.</t>
+          <t>Eaton Corporation, PLC</t>
         </is>
       </c>
       <c r="C28" s="17" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D28" s="17" t="n">
         <v>2</v>
@@ -6960,182 +6977,174 @@
       </c>
       <c r="G28" s="10" t="inlineStr">
         <is>
-          <t>Spinoff [incentive]; Strategic Review [narra</t>
+          <t>Separation [narrative]; Spinoff [narrative]</t>
         </is>
       </c>
     </row>
     <row r="29" ht="22" customHeight="1">
       <c r="A29" s="6" t="inlineStr">
         <is>
-          <t>DXLG</t>
+          <t>CNXC</t>
         </is>
       </c>
       <c r="B29" s="7" t="inlineStr">
         <is>
-          <t>Destination XL Group,</t>
+          <t>Concentrix Corporation</t>
         </is>
       </c>
       <c r="C29" s="16" t="n">
-        <v>18</v>
+        <v>16.5</v>
       </c>
       <c r="D29" s="16" t="n">
         <v>1</v>
       </c>
       <c r="E29" s="16" t="n">
-        <v>60</v>
+        <v>34.9</v>
       </c>
       <c r="F29" s="19" t="n">
         <v>300</v>
       </c>
       <c r="G29" s="7" t="inlineStr">
         <is>
-          <t>Sale Of Company [tender]</t>
+          <t>Spinoff [incentive]</t>
         </is>
       </c>
     </row>
     <row r="30" ht="22" customHeight="1">
       <c r="A30" s="9" t="inlineStr">
         <is>
-          <t>FUN</t>
+          <t>CLW</t>
         </is>
       </c>
       <c r="B30" s="10" t="inlineStr">
         <is>
-          <t>Six Flags Entertainmen</t>
+          <t>Clearwater Paper Corpo</t>
         </is>
       </c>
       <c r="C30" s="17" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="D30" s="17" t="n">
-        <v>2</v>
-      </c>
-      <c r="E30" s="10" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="F30" s="10" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+        <v>1</v>
+      </c>
+      <c r="E30" s="17" t="n">
+        <v>60</v>
+      </c>
+      <c r="F30" s="20" t="n">
+        <v>300</v>
       </c>
       <c r="G30" s="10" t="inlineStr">
         <is>
-          <t>Asset Sale [narrative]; Sale Of Company [inc</t>
+          <t>Spinoff [incentive]</t>
         </is>
       </c>
     </row>
     <row r="31" ht="22" customHeight="1">
       <c r="A31" s="6" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>JTAI</t>
         </is>
       </c>
       <c r="B31" s="7" t="inlineStr">
         <is>
-          <t>Macy's Inc</t>
+          <t>Jet.AI Inc.</t>
         </is>
       </c>
       <c r="C31" s="16" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="D31" s="16" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E31" s="16" t="n">
-        <v>2</v>
+        <v>60</v>
       </c>
       <c r="F31" s="19" t="n">
-        <v>127</v>
+        <v>300</v>
       </c>
       <c r="G31" s="7" t="inlineStr">
         <is>
-          <t>Asset Sale [narrative]; Strategic Review [na</t>
+          <t>Spinoff [incentive]</t>
         </is>
       </c>
     </row>
     <row r="32" ht="22" customHeight="1">
       <c r="A32" s="9" t="inlineStr">
         <is>
-          <t>ETN</t>
+          <t>AMS</t>
         </is>
       </c>
       <c r="B32" s="10" t="inlineStr">
         <is>
-          <t>Eaton Corporation, PLC</t>
+          <t>American Shared Hospit</t>
         </is>
       </c>
       <c r="C32" s="17" t="n">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="D32" s="17" t="n">
-        <v>2</v>
-      </c>
-      <c r="E32" s="10" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="F32" s="10" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+        <v>1</v>
+      </c>
+      <c r="E32" s="17" t="n">
+        <v>60</v>
+      </c>
+      <c r="F32" s="20" t="n">
+        <v>300</v>
       </c>
       <c r="G32" s="10" t="inlineStr">
         <is>
-          <t>Separation [narrative]; Spinoff [narrative]</t>
+          <t>Spinoff [incentive]</t>
         </is>
       </c>
     </row>
     <row r="33" ht="22" customHeight="1">
       <c r="A33" s="6" t="inlineStr">
         <is>
-          <t>GNK</t>
+          <t>ASTH</t>
         </is>
       </c>
       <c r="B33" s="7" t="inlineStr">
         <is>
-          <t>Genco Shipping &amp; Tradi</t>
+          <t>Astrana Health Inc.</t>
         </is>
       </c>
       <c r="C33" s="16" t="n">
-        <v>15.5</v>
+        <v>16.5</v>
       </c>
       <c r="D33" s="16" t="n">
         <v>1</v>
       </c>
       <c r="E33" s="16" t="n">
-        <v>7.4</v>
+        <v>3.8</v>
       </c>
       <c r="F33" s="19" t="n">
-        <v>174</v>
+        <v>300</v>
       </c>
       <c r="G33" s="7" t="inlineStr">
         <is>
-          <t>Sale Of Company [tender]</t>
+          <t>Spinoff [incentive]</t>
         </is>
       </c>
     </row>
     <row r="34" ht="22" customHeight="1">
       <c r="A34" s="9" t="inlineStr">
         <is>
-          <t>CNXC</t>
+          <t>GPRO</t>
         </is>
       </c>
       <c r="B34" s="10" t="inlineStr">
         <is>
-          <t>Concentrix Corporation</t>
+          <t>GoPro, Inc.</t>
         </is>
       </c>
       <c r="C34" s="17" t="n">
-        <v>15</v>
+        <v>16.5</v>
       </c>
       <c r="D34" s="17" t="n">
         <v>1</v>
       </c>
       <c r="E34" s="17" t="n">
-        <v>34.9</v>
+        <v>3</v>
       </c>
       <c r="F34" s="20" t="n">
         <v>300</v>
@@ -7149,22 +7158,22 @@
     <row r="35" ht="22" customHeight="1">
       <c r="A35" s="6" t="inlineStr">
         <is>
-          <t>CLW</t>
+          <t>LGL</t>
         </is>
       </c>
       <c r="B35" s="7" t="inlineStr">
         <is>
-          <t>Clearwater Paper Corpo</t>
+          <t>LGL Group, Inc. (The)</t>
         </is>
       </c>
       <c r="C35" s="16" t="n">
-        <v>15</v>
+        <v>16.5</v>
       </c>
       <c r="D35" s="16" t="n">
         <v>1</v>
       </c>
       <c r="E35" s="16" t="n">
-        <v>60</v>
+        <v>41.6</v>
       </c>
       <c r="F35" s="19" t="n">
         <v>300</v>
@@ -7178,22 +7187,22 @@
     <row r="36" ht="22" customHeight="1">
       <c r="A36" s="9" t="inlineStr">
         <is>
-          <t>JTAI</t>
+          <t>VREX</t>
         </is>
       </c>
       <c r="B36" s="10" t="inlineStr">
         <is>
-          <t>Jet.AI Inc.</t>
+          <t>Varex Imaging Corporat</t>
         </is>
       </c>
       <c r="C36" s="17" t="n">
-        <v>15</v>
+        <v>16.5</v>
       </c>
       <c r="D36" s="17" t="n">
         <v>1</v>
       </c>
       <c r="E36" s="17" t="n">
-        <v>60</v>
+        <v>6.5</v>
       </c>
       <c r="F36" s="20" t="n">
         <v>300</v>
@@ -7207,22 +7216,22 @@
     <row r="37" ht="22" customHeight="1">
       <c r="A37" s="6" t="inlineStr">
         <is>
-          <t>AMS</t>
+          <t>PAGP</t>
         </is>
       </c>
       <c r="B37" s="7" t="inlineStr">
         <is>
-          <t>American Shared Hospit</t>
+          <t>Plains GP Holdings, L.</t>
         </is>
       </c>
       <c r="C37" s="16" t="n">
-        <v>15</v>
+        <v>16.5</v>
       </c>
       <c r="D37" s="16" t="n">
         <v>1</v>
       </c>
       <c r="E37" s="16" t="n">
-        <v>60</v>
+        <v>3.5</v>
       </c>
       <c r="F37" s="19" t="n">
         <v>300</v>
@@ -7236,54 +7245,58 @@
     <row r="38" ht="22" customHeight="1">
       <c r="A38" s="9" t="inlineStr">
         <is>
-          <t>ASTH</t>
+          <t>FUN</t>
         </is>
       </c>
       <c r="B38" s="10" t="inlineStr">
         <is>
-          <t>Astrana Health Inc.</t>
+          <t>Six Flags Entertainmen</t>
         </is>
       </c>
       <c r="C38" s="17" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D38" s="17" t="n">
-        <v>1</v>
-      </c>
-      <c r="E38" s="17" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="F38" s="20" t="n">
-        <v>300</v>
+        <v>2</v>
+      </c>
+      <c r="E38" s="10" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="F38" s="10" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
       <c r="G38" s="10" t="inlineStr">
         <is>
-          <t>Spinoff [incentive]</t>
+          <t>Asset Sale [narrative]; Sale Of Company [inc</t>
         </is>
       </c>
     </row>
     <row r="39" ht="22" customHeight="1">
       <c r="A39" s="6" t="inlineStr">
         <is>
-          <t>GPRO</t>
+          <t>NTGR</t>
         </is>
       </c>
       <c r="B39" s="7" t="inlineStr">
         <is>
-          <t>GoPro, Inc.</t>
+          <t>NETGEAR, Inc.</t>
         </is>
       </c>
       <c r="C39" s="16" t="n">
-        <v>15</v>
+        <v>15.4</v>
       </c>
       <c r="D39" s="16" t="n">
         <v>1</v>
       </c>
       <c r="E39" s="16" t="n">
-        <v>3</v>
+        <v>3.8</v>
       </c>
       <c r="F39" s="19" t="n">
-        <v>300</v>
+        <v>239</v>
       </c>
       <c r="G39" s="7" t="inlineStr">
         <is>
@@ -7294,25 +7307,25 @@
     <row r="40" ht="22" customHeight="1">
       <c r="A40" s="9" t="inlineStr">
         <is>
-          <t>LGL</t>
+          <t>RCMT</t>
         </is>
       </c>
       <c r="B40" s="10" t="inlineStr">
         <is>
-          <t>LGL Group, Inc. (The)</t>
+          <t>RCM Technologies, Inc.</t>
         </is>
       </c>
       <c r="C40" s="17" t="n">
-        <v>15</v>
+        <v>15.1</v>
       </c>
       <c r="D40" s="17" t="n">
         <v>1</v>
       </c>
       <c r="E40" s="17" t="n">
-        <v>41.6</v>
+        <v>2.5</v>
       </c>
       <c r="F40" s="20" t="n">
-        <v>300</v>
+        <v>224</v>
       </c>
       <c r="G40" s="10" t="inlineStr">
         <is>
@@ -7323,25 +7336,25 @@
     <row r="41" ht="22" customHeight="1">
       <c r="A41" s="6" t="inlineStr">
         <is>
-          <t>VREX</t>
+          <t>LBTYK</t>
         </is>
       </c>
       <c r="B41" s="7" t="inlineStr">
         <is>
-          <t>Varex Imaging Corporat</t>
+          <t>Liberty Global Ltd.</t>
         </is>
       </c>
       <c r="C41" s="16" t="n">
-        <v>15</v>
+        <v>14.9</v>
       </c>
       <c r="D41" s="16" t="n">
         <v>1</v>
       </c>
       <c r="E41" s="16" t="n">
-        <v>6.5</v>
+        <v>43</v>
       </c>
       <c r="F41" s="19" t="n">
-        <v>300</v>
+        <v>215</v>
       </c>
       <c r="G41" s="7" t="inlineStr">
         <is>
@@ -7352,54 +7365,54 @@
     <row r="42" ht="22" customHeight="1">
       <c r="A42" s="9" t="inlineStr">
         <is>
-          <t>PAGP</t>
+          <t>M</t>
         </is>
       </c>
       <c r="B42" s="10" t="inlineStr">
         <is>
-          <t>Plains GP Holdings, L.</t>
+          <t>Macy's Inc</t>
         </is>
       </c>
       <c r="C42" s="17" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="D42" s="17" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E42" s="17" t="n">
-        <v>3.5</v>
+        <v>2</v>
       </c>
       <c r="F42" s="20" t="n">
-        <v>300</v>
+        <v>127</v>
       </c>
       <c r="G42" s="10" t="inlineStr">
         <is>
-          <t>Spinoff [incentive]</t>
+          <t>Asset Sale [narrative]; Strategic Review [na</t>
         </is>
       </c>
     </row>
     <row r="43" ht="22" customHeight="1">
       <c r="A43" s="6" t="inlineStr">
         <is>
-          <t>NTGR</t>
+          <t>OWLT</t>
         </is>
       </c>
       <c r="B43" s="7" t="inlineStr">
         <is>
-          <t>NETGEAR, Inc.</t>
+          <t>Owlet, Inc.</t>
         </is>
       </c>
       <c r="C43" s="16" t="n">
-        <v>14</v>
+        <v>14.4</v>
       </c>
       <c r="D43" s="16" t="n">
         <v>1</v>
       </c>
       <c r="E43" s="16" t="n">
-        <v>3.8</v>
+        <v>2</v>
       </c>
       <c r="F43" s="19" t="n">
-        <v>239</v>
+        <v>183</v>
       </c>
       <c r="G43" s="7" t="inlineStr">
         <is>
@@ -7410,120 +7423,116 @@
     <row r="44" ht="22" customHeight="1">
       <c r="A44" s="9" t="inlineStr">
         <is>
-          <t>PKOH</t>
+          <t>GDRX</t>
         </is>
       </c>
       <c r="B44" s="10" t="inlineStr">
         <is>
-          <t>PKOH</t>
+          <t>GoodRx Holdings, Inc.</t>
         </is>
       </c>
       <c r="C44" s="17" t="n">
-        <v>14</v>
+        <v>14.2</v>
       </c>
       <c r="D44" s="17" t="n">
-        <v>2</v>
-      </c>
-      <c r="E44" s="10" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="F44" s="10" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+        <v>1</v>
+      </c>
+      <c r="E44" s="17" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="F44" s="20" t="n">
+        <v>172</v>
       </c>
       <c r="G44" s="10" t="inlineStr">
         <is>
-          <t>Asset Sale [narrative]; Strategic Review [na</t>
+          <t>Spinoff [incentive]</t>
         </is>
       </c>
     </row>
     <row r="45" ht="22" customHeight="1">
       <c r="A45" s="6" t="inlineStr">
         <is>
-          <t>SCTH</t>
+          <t>GLIBK</t>
         </is>
       </c>
       <c r="B45" s="7" t="inlineStr">
         <is>
-          <t>SCTH</t>
+          <t>Liberty Capital Corpor</t>
         </is>
       </c>
       <c r="C45" s="16" t="n">
         <v>14</v>
       </c>
       <c r="D45" s="16" t="n">
-        <v>2</v>
-      </c>
-      <c r="E45" s="7" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="F45" s="7" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+        <v>1</v>
+      </c>
+      <c r="E45" s="16" t="n">
+        <v>32.9</v>
+      </c>
+      <c r="F45" s="19" t="n">
+        <v>164</v>
       </c>
       <c r="G45" s="7" t="inlineStr">
         <is>
-          <t>Asset Sale [narrative]; Strategic Review [na</t>
+          <t>Spinoff [incentive]</t>
         </is>
       </c>
     </row>
     <row r="46" ht="22" customHeight="1">
       <c r="A46" s="9" t="inlineStr">
         <is>
-          <t>RCMT</t>
+          <t>LSTA</t>
         </is>
       </c>
       <c r="B46" s="10" t="inlineStr">
         <is>
-          <t>RCM Technologies, Inc.</t>
+          <t>Lisata Therapeutics, I</t>
         </is>
       </c>
       <c r="C46" s="17" t="n">
-        <v>13.7</v>
+        <v>14</v>
       </c>
       <c r="D46" s="17" t="n">
-        <v>1</v>
-      </c>
-      <c r="E46" s="17" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="F46" s="20" t="n">
-        <v>224</v>
+        <v>2</v>
+      </c>
+      <c r="E46" s="10" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="F46" s="10" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
       <c r="G46" s="10" t="inlineStr">
         <is>
-          <t>Spinoff [incentive]</t>
+          <t>Sale Of Company [tender]; Strategic Review [</t>
         </is>
       </c>
     </row>
     <row r="47" ht="22" customHeight="1">
       <c r="A47" s="6" t="inlineStr">
         <is>
-          <t>LBTYK</t>
+          <t>LNC</t>
         </is>
       </c>
       <c r="B47" s="7" t="inlineStr">
         <is>
-          <t>Liberty Global Ltd.</t>
+          <t>Lincoln National Corpo</t>
         </is>
       </c>
       <c r="C47" s="16" t="n">
-        <v>13.6</v>
+        <v>13.8</v>
       </c>
       <c r="D47" s="16" t="n">
         <v>1</v>
       </c>
       <c r="E47" s="16" t="n">
-        <v>43</v>
+        <v>4.3</v>
       </c>
       <c r="F47" s="19" t="n">
-        <v>215</v>
+        <v>150</v>
       </c>
       <c r="G47" s="7" t="inlineStr">
         <is>
@@ -7534,54 +7543,54 @@
     <row r="48" ht="22" customHeight="1">
       <c r="A48" s="9" t="inlineStr">
         <is>
-          <t>BAX</t>
+          <t>AHT</t>
         </is>
       </c>
       <c r="B48" s="10" t="inlineStr">
         <is>
-          <t>Baxter International I</t>
+          <t>Ashford Hospitality Tr</t>
         </is>
       </c>
       <c r="C48" s="17" t="n">
-        <v>13.3</v>
+        <v>13.8</v>
       </c>
       <c r="D48" s="17" t="n">
         <v>1</v>
       </c>
       <c r="E48" s="17" t="n">
-        <v>2.8</v>
+        <v>1.5</v>
       </c>
       <c r="F48" s="20" t="n">
-        <v>200</v>
+        <v>150</v>
       </c>
       <c r="G48" s="10" t="inlineStr">
         <is>
-          <t>Asset Sale [incentive]</t>
+          <t>Spinoff [incentive]</t>
         </is>
       </c>
     </row>
     <row r="49" ht="22" customHeight="1">
       <c r="A49" s="6" t="inlineStr">
         <is>
-          <t>OWLT</t>
+          <t>ASIX</t>
         </is>
       </c>
       <c r="B49" s="7" t="inlineStr">
         <is>
-          <t>Owlet, Inc.</t>
+          <t>AdvanSix Inc.</t>
         </is>
       </c>
       <c r="C49" s="16" t="n">
-        <v>13.1</v>
+        <v>13.8</v>
       </c>
       <c r="D49" s="16" t="n">
         <v>1</v>
       </c>
       <c r="E49" s="16" t="n">
-        <v>2</v>
+        <v>5.8</v>
       </c>
       <c r="F49" s="19" t="n">
-        <v>183</v>
+        <v>150</v>
       </c>
       <c r="G49" s="7" t="inlineStr">
         <is>
@@ -7592,112 +7601,112 @@
     <row r="50" ht="22" customHeight="1">
       <c r="A50" s="9" t="inlineStr">
         <is>
-          <t>RGR</t>
+          <t>KD</t>
         </is>
       </c>
       <c r="B50" s="10" t="inlineStr">
         <is>
-          <t>Sturm, Ruger &amp; Company</t>
+          <t>Kyndryl Holdings, Inc.</t>
         </is>
       </c>
       <c r="C50" s="17" t="n">
-        <v>13.1</v>
+        <v>13.8</v>
       </c>
       <c r="D50" s="17" t="n">
         <v>1</v>
       </c>
       <c r="E50" s="17" t="n">
-        <v>0.7</v>
+        <v>2</v>
       </c>
       <c r="F50" s="20" t="n">
-        <v>53</v>
+        <v>150</v>
       </c>
       <c r="G50" s="10" t="inlineStr">
         <is>
-          <t>Sale Of Company [tender]</t>
+          <t>Spinoff [incentive]</t>
         </is>
       </c>
     </row>
     <row r="51" ht="22" customHeight="1">
       <c r="A51" s="6" t="inlineStr">
         <is>
-          <t>ASRT</t>
+          <t>PAA</t>
         </is>
       </c>
       <c r="B51" s="7" t="inlineStr">
         <is>
-          <t>Assertio Holdings, Inc</t>
+          <t>Plains All American Pi</t>
         </is>
       </c>
       <c r="C51" s="16" t="n">
-        <v>13</v>
+        <v>13.8</v>
       </c>
       <c r="D51" s="16" t="n">
         <v>1</v>
       </c>
       <c r="E51" s="16" t="n">
-        <v>0.7</v>
+        <v>2</v>
       </c>
       <c r="F51" s="19" t="n">
-        <v>52</v>
+        <v>150</v>
       </c>
       <c r="G51" s="7" t="inlineStr">
         <is>
-          <t>Sale Of Company [tender]</t>
+          <t>Spinoff [incentive]</t>
         </is>
       </c>
     </row>
     <row r="52" ht="22" customHeight="1">
       <c r="A52" s="9" t="inlineStr">
         <is>
-          <t>FSK</t>
+          <t>VYX</t>
         </is>
       </c>
       <c r="B52" s="10" t="inlineStr">
         <is>
-          <t>FS KKR Capital Corp.</t>
+          <t>NCR Voyix Corporation</t>
         </is>
       </c>
       <c r="C52" s="17" t="n">
-        <v>13</v>
+        <v>13.8</v>
       </c>
       <c r="D52" s="17" t="n">
         <v>1</v>
       </c>
       <c r="E52" s="17" t="n">
-        <v>5.8</v>
+        <v>2.7</v>
       </c>
       <c r="F52" s="20" t="n">
-        <v>52</v>
+        <v>150</v>
       </c>
       <c r="G52" s="10" t="inlineStr">
         <is>
-          <t>Sale Of Company [tender]</t>
+          <t>Spinoff [incentive]</t>
         </is>
       </c>
     </row>
     <row r="53" ht="22" customHeight="1">
       <c r="A53" s="6" t="inlineStr">
         <is>
-          <t>GDRX</t>
+          <t>VSNT</t>
         </is>
       </c>
       <c r="B53" s="7" t="inlineStr">
         <is>
-          <t>GoodRx Holdings, Inc.</t>
+          <t>Versant Media Group, I</t>
         </is>
       </c>
       <c r="C53" s="16" t="n">
-        <v>12.9</v>
+        <v>13.6</v>
       </c>
       <c r="D53" s="16" t="n">
         <v>1</v>
       </c>
       <c r="E53" s="16" t="n">
-        <v>2.6</v>
+        <v>28.3</v>
       </c>
       <c r="F53" s="19" t="n">
-        <v>172</v>
+        <v>141</v>
       </c>
       <c r="G53" s="7" t="inlineStr">
         <is>
@@ -7708,25 +7717,25 @@
     <row r="54" ht="22" customHeight="1">
       <c r="A54" s="9" t="inlineStr">
         <is>
-          <t>GLIBK</t>
+          <t>AQMS</t>
         </is>
       </c>
       <c r="B54" s="10" t="inlineStr">
         <is>
-          <t>Liberty Capital Corpor</t>
+          <t>Aqua Metals, Inc.</t>
         </is>
       </c>
       <c r="C54" s="17" t="n">
-        <v>12.7</v>
+        <v>13.6</v>
       </c>
       <c r="D54" s="17" t="n">
         <v>1</v>
       </c>
       <c r="E54" s="17" t="n">
-        <v>32.9</v>
+        <v>3.5</v>
       </c>
       <c r="F54" s="20" t="n">
-        <v>164</v>
+        <v>140</v>
       </c>
       <c r="G54" s="10" t="inlineStr">
         <is>
@@ -7759,6 +7768,607 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
+  <dimension ref="A1:F26"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="20" customWidth="1" min="1" max="1"/>
+    <col width="8" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="8" customWidth="1" min="4" max="4"/>
+    <col width="10" customWidth="1" min="5" max="5"/>
+    <col width="34" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="26" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Re-Rate Backtest — did these catalysts pay, historically?</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="18" customHeight="1">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Corporate-action announcements in 2024-01-01..2025-06-30 (113 events), realized forward return measured to +12 months, absolute and vs SPY. The evidence behind the catalyst weights.</t>
+        </is>
+      </c>
+      <c r="B2" s="3" t="n"/>
+      <c r="C2" s="3" t="n"/>
+      <c r="D2" s="3" t="n"/>
+      <c r="E2" s="3" t="n"/>
+      <c r="F2" s="3" t="n"/>
+    </row>
+    <row r="3" ht="8" customHeight="1"/>
+    <row r="4" ht="18" customHeight="1">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>Catalyst</t>
+        </is>
+      </c>
+      <c r="B4" s="4" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="C4" s="4" t="inlineStr">
+        <is>
+          <t>12m median</t>
+        </is>
+      </c>
+      <c r="D4" s="4" t="inlineStr">
+        <is>
+          <t>Hit %</t>
+        </is>
+      </c>
+      <c r="E4" s="4" t="inlineStr">
+        <is>
+          <t>12m vs SPY</t>
+        </is>
+      </c>
+      <c r="F4" s="4" t="inlineStr">
+        <is>
+          <t>Read</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="16" customHeight="1">
+      <c r="A5" s="6" t="inlineStr">
+        <is>
+          <t>Asset Sale</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="n">
+        <v>39</v>
+      </c>
+      <c r="C5" s="16" t="n">
+        <v>2</v>
+      </c>
+      <c r="D5" s="19" t="n">
+        <v>54</v>
+      </c>
+      <c r="E5" s="16" t="n">
+        <v>-14</v>
+      </c>
+      <c r="F5" s="7" t="inlineStr">
+        <is>
+          <t>~market on median; tail-driven</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="16" customHeight="1">
+      <c r="A6" s="9" t="inlineStr">
+        <is>
+          <t>Spinoff</t>
+        </is>
+      </c>
+      <c r="B6" s="8" t="n">
+        <v>40</v>
+      </c>
+      <c r="C6" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="D6" s="20" t="n">
+        <v>50</v>
+      </c>
+      <c r="E6" s="17" t="n">
+        <v>-12</v>
+      </c>
+      <c r="F6" s="10" t="inlineStr">
+        <is>
+          <t>most tail winners; reliable in large-caps</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="16" customHeight="1">
+      <c r="A7" s="6" t="inlineStr">
+        <is>
+          <t>Sale Of Company</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="n">
+        <v>8</v>
+      </c>
+      <c r="C7" s="16" t="n">
+        <v>-6</v>
+      </c>
+      <c r="D7" s="19" t="n">
+        <v>38</v>
+      </c>
+      <c r="E7" s="16" t="n">
+        <v>-28</v>
+      </c>
+      <c r="F7" s="7" t="inlineStr">
+        <is>
+          <t>deal already priced at 8-K; little forward juice</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="16" customHeight="1">
+      <c r="A8" s="9" t="inlineStr">
+        <is>
+          <t>Strategic Review</t>
+        </is>
+      </c>
+      <c r="B8" s="8" t="n">
+        <v>26</v>
+      </c>
+      <c r="C8" s="17" t="n">
+        <v>-10</v>
+      </c>
+      <c r="D8" s="20" t="n">
+        <v>46</v>
+      </c>
+      <c r="E8" s="17" t="n">
+        <v>-27</v>
+      </c>
+      <c r="F8" s="10" t="inlineStr">
+        <is>
+          <t>worst median — most reviews fizzle; pure optionality</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="16" customHeight="1">
+      <c r="A9" s="6" t="inlineStr">
+        <is>
+          <t>OVERALL</t>
+        </is>
+      </c>
+      <c r="B9" s="5" t="n">
+        <v>113</v>
+      </c>
+      <c r="C9" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="D9" s="19" t="n">
+        <v>50</v>
+      </c>
+      <c r="E9" s="7" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="F9" s="7" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="12" t="inlineStr">
+        <is>
+          <t>BIGGEST REALIZED RE-RATES (12m)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="18" customHeight="1">
+      <c r="A12" s="15" t="inlineStr">
+        <is>
+          <t>Ticker</t>
+        </is>
+      </c>
+      <c r="B12" s="4" t="inlineStr">
+        <is>
+          <t>Catalyst</t>
+        </is>
+      </c>
+      <c r="C12" s="4" t="inlineStr">
+        <is>
+          <t>Date</t>
+        </is>
+      </c>
+      <c r="D12" s="15" t="inlineStr"/>
+      <c r="E12" s="4" t="inlineStr">
+        <is>
+          <t>12m</t>
+        </is>
+      </c>
+      <c r="F12" s="15" t="inlineStr"/>
+    </row>
+    <row r="13" ht="16" customHeight="1">
+      <c r="A13" s="6" t="inlineStr">
+        <is>
+          <t>SNDK</t>
+        </is>
+      </c>
+      <c r="B13" s="7" t="inlineStr">
+        <is>
+          <t>Spinoff</t>
+        </is>
+      </c>
+      <c r="C13" s="7" t="inlineStr">
+        <is>
+          <t>2025-02-03</t>
+        </is>
+      </c>
+      <c r="D13" s="7" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="E13" s="16" t="n">
+        <v>1235</v>
+      </c>
+      <c r="F13" s="7" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="16" customHeight="1">
+      <c r="A14" s="9" t="inlineStr">
+        <is>
+          <t>IRWD</t>
+        </is>
+      </c>
+      <c r="B14" s="10" t="inlineStr">
+        <is>
+          <t>Strategic Review</t>
+        </is>
+      </c>
+      <c r="C14" s="10" t="inlineStr">
+        <is>
+          <t>2025-04-14</t>
+        </is>
+      </c>
+      <c r="D14" s="10" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="E14" s="17" t="n">
+        <v>495</v>
+      </c>
+      <c r="F14" s="10" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="16" customHeight="1">
+      <c r="A15" s="6" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="B15" s="7" t="inlineStr">
+        <is>
+          <t>Spinoff</t>
+        </is>
+      </c>
+      <c r="C15" s="7" t="inlineStr">
+        <is>
+          <t>2025-02-27</t>
+        </is>
+      </c>
+      <c r="D15" s="7" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="E15" s="16" t="n">
+        <v>359</v>
+      </c>
+      <c r="F15" s="7" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="16" customHeight="1">
+      <c r="A16" s="9" t="inlineStr">
+        <is>
+          <t>XCUR</t>
+        </is>
+      </c>
+      <c r="B16" s="10" t="inlineStr">
+        <is>
+          <t>Strategic Review</t>
+        </is>
+      </c>
+      <c r="C16" s="10" t="inlineStr">
+        <is>
+          <t>2024-02-05</t>
+        </is>
+      </c>
+      <c r="D16" s="10" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="E16" s="17" t="n">
+        <v>214</v>
+      </c>
+      <c r="F16" s="10" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="16" customHeight="1">
+      <c r="A17" s="6" t="inlineStr">
+        <is>
+          <t>AREC</t>
+        </is>
+      </c>
+      <c r="B17" s="7" t="inlineStr">
+        <is>
+          <t>Spinoff</t>
+        </is>
+      </c>
+      <c r="C17" s="7" t="inlineStr">
+        <is>
+          <t>2024-08-19</t>
+        </is>
+      </c>
+      <c r="D17" s="7" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="E17" s="16" t="n">
+        <v>197</v>
+      </c>
+      <c r="F17" s="7" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="16" customHeight="1">
+      <c r="A18" s="9" t="inlineStr">
+        <is>
+          <t>CMTL</t>
+        </is>
+      </c>
+      <c r="B18" s="10" t="inlineStr">
+        <is>
+          <t>Strategic Review</t>
+        </is>
+      </c>
+      <c r="C18" s="10" t="inlineStr">
+        <is>
+          <t>2025-01-13</t>
+        </is>
+      </c>
+      <c r="D18" s="10" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="E18" s="17" t="n">
+        <v>195</v>
+      </c>
+      <c r="F18" s="10" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="16" customHeight="1">
+      <c r="A19" s="6" t="inlineStr">
+        <is>
+          <t>GEV</t>
+        </is>
+      </c>
+      <c r="B19" s="7" t="inlineStr">
+        <is>
+          <t>Spinoff</t>
+        </is>
+      </c>
+      <c r="C19" s="7" t="inlineStr">
+        <is>
+          <t>2024-03-08</t>
+        </is>
+      </c>
+      <c r="D19" s="7" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="E19" s="16" t="n">
+        <v>141</v>
+      </c>
+      <c r="F19" s="7" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="16" customHeight="1">
+      <c r="A20" s="9" t="inlineStr">
+        <is>
+          <t>GRAL</t>
+        </is>
+      </c>
+      <c r="B20" s="10" t="inlineStr">
+        <is>
+          <t>Spinoff</t>
+        </is>
+      </c>
+      <c r="C20" s="10" t="inlineStr">
+        <is>
+          <t>2024-06-24</t>
+        </is>
+      </c>
+      <c r="D20" s="10" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="E20" s="17" t="n">
+        <v>122</v>
+      </c>
+      <c r="F20" s="10" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="16" customHeight="1">
+      <c r="A21" s="6" t="inlineStr">
+        <is>
+          <t>CCO</t>
+        </is>
+      </c>
+      <c r="B21" s="7" t="inlineStr">
+        <is>
+          <t>Asset Sale</t>
+        </is>
+      </c>
+      <c r="C21" s="7" t="inlineStr">
+        <is>
+          <t>2025-05-07</t>
+        </is>
+      </c>
+      <c r="D21" s="7" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="E21" s="16" t="n">
+        <v>107</v>
+      </c>
+      <c r="F21" s="7" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="16" customHeight="1">
+      <c r="A22" s="9" t="inlineStr">
+        <is>
+          <t>TPR</t>
+        </is>
+      </c>
+      <c r="B22" s="10" t="inlineStr">
+        <is>
+          <t>Asset Sale</t>
+        </is>
+      </c>
+      <c r="C22" s="10" t="inlineStr">
+        <is>
+          <t>2025-02-19</t>
+        </is>
+      </c>
+      <c r="D22" s="10" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="E22" s="17" t="n">
+        <v>100</v>
+      </c>
+      <c r="F22" s="10" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="16" customHeight="1">
+      <c r="A23" s="6" t="inlineStr">
+        <is>
+          <t>MPTI</t>
+        </is>
+      </c>
+      <c r="B23" s="7" t="inlineStr">
+        <is>
+          <t>Spinoff</t>
+        </is>
+      </c>
+      <c r="C23" s="7" t="inlineStr">
+        <is>
+          <t>2024-03-25</t>
+        </is>
+      </c>
+      <c r="D23" s="7" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="E23" s="16" t="n">
+        <v>100</v>
+      </c>
+      <c r="F23" s="7" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="16" customHeight="1">
+      <c r="A24" s="9" t="inlineStr">
+        <is>
+          <t>OPRT</t>
+        </is>
+      </c>
+      <c r="B24" s="10" t="inlineStr">
+        <is>
+          <t>Asset Sale</t>
+        </is>
+      </c>
+      <c r="C24" s="10" t="inlineStr">
+        <is>
+          <t>2024-09-26</t>
+        </is>
+      </c>
+      <c r="D24" s="10" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="E24" s="17" t="n">
+        <v>92</v>
+      </c>
+      <c r="F24" s="10" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="28" customHeight="1">
+      <c r="A26" s="11" t="inlineStr">
+        <is>
+          <t>THE LESSON, from the data. On the MEDIAN, every corporate-action catalyst UNDERPERFORMED SPY over the next year — buying a spin/sale/review indiscriminately is a losing trade. The payoff is a RIGHT TAIL: ~15% of events returned &gt;+50% in 12 months, and spin-offs produced the most of them (SanDisk +1235%, GE Vernova +141%, Grail +122%). Counter-intuitively, small-cap catalyst plays were LOTTERY tickets (median −24%, 35% hit), while large-cap spin-offs were the reliable sweet spot (+4% median, 57% hit). Calibration consequences, applied to the Re-Rate Catalysts weights: spin-offs up, strategic-reviews down (worst median), already-announced deals down (deal priced), and the catalyst credit is scaled by payoff-geometry room so the engine leans toward the setups where the tail actually lives — not the bare catalyst. Sample is modest (8–40 per type); treat as directional. Source: rerate_backtest.py.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="3">
+    <mergeCell ref="A26:F26"/>
+    <mergeCell ref="A2:F2"/>
+    <mergeCell ref="A1:F1"/>
+  </mergeCells>
+  <printOptions horizontalCentered="0"/>
+  <pageMargins left="0.5" right="0.5" top="0.6" bottom="0.6" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
   <dimension ref="A1:E29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -8282,7 +8892,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -9238,7 +9848,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -10818,7 +11428,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -12313,7 +12923,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -12471,1130 +13081,6 @@
     <mergeCell ref="A8:G8"/>
     <mergeCell ref="A2:G2"/>
     <mergeCell ref="A1:G1"/>
-  </mergeCells>
-  <printOptions horizontalCentered="0"/>
-  <pageMargins left="0.5" right="0.5" top="0.6" bottom="0.6" header="0.5" footer="0.5"/>
-  <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="1"/>
-  </sheetPr>
-  <dimension ref="A1:H36"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="9" customWidth="1" min="1" max="1"/>
-    <col width="13" customWidth="1" min="2" max="2"/>
-    <col width="32" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
-    <col width="14" customWidth="1" min="6" max="6"/>
-    <col width="14" customWidth="1" min="7" max="7"/>
-    <col width="50" customWidth="1" min="8" max="8"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="26" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Top of Universe -- Without Valuation Leg</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="18" customHeight="1">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>Parallel ranking that excludes valuation entirely so names missing yfinance overlay are not penalised. Compared against the valuation-included ranking to identify structurally-strong-but-valuation-hidden names.</t>
-        </is>
-      </c>
-      <c r="B2" s="3" t="n"/>
-      <c r="C2" s="3" t="n"/>
-      <c r="D2" s="3" t="n"/>
-      <c r="E2" s="3" t="n"/>
-      <c r="F2" s="3" t="n"/>
-      <c r="G2" s="3" t="n"/>
-      <c r="H2" s="3" t="n"/>
-    </row>
-    <row r="3" ht="8" customHeight="1"/>
-    <row r="4" ht="18" customHeight="1">
-      <c r="A4" s="4" t="inlineStr">
-        <is>
-          <t>#</t>
-        </is>
-      </c>
-      <c r="B4" s="15" t="inlineStr">
-        <is>
-          <t>Ticker</t>
-        </is>
-      </c>
-      <c r="C4" s="15" t="inlineStr">
-        <is>
-          <t>Name</t>
-        </is>
-      </c>
-      <c r="D4" s="4" t="inlineStr">
-        <is>
-          <t>Layers</t>
-        </is>
-      </c>
-      <c r="E4" s="4" t="inlineStr">
-        <is>
-          <t>Consensus</t>
-        </is>
-      </c>
-      <c r="F4" s="4" t="inlineStr">
-        <is>
-          <t>Lift vs val</t>
-        </is>
-      </c>
-      <c r="G4" s="15" t="inlineStr">
-        <is>
-          <t>Sector</t>
-        </is>
-      </c>
-      <c r="H4" s="15" t="inlineStr">
-        <is>
-          <t>Detail</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="22" customHeight="1">
-      <c r="A5" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="B5" s="6" t="inlineStr">
-        <is>
-          <t>POOL</t>
-        </is>
-      </c>
-      <c r="C5" s="7" t="inlineStr">
-        <is>
-          <t>Pool Corporation</t>
-        </is>
-      </c>
-      <c r="D5" s="5" t="n">
-        <v>8</v>
-      </c>
-      <c r="E5" s="16" t="n">
-        <v>5.902</v>
-      </c>
-      <c r="F5" s="5" t="n">
-        <v>5</v>
-      </c>
-      <c r="G5" s="7" t="inlineStr">
-        <is>
-          <t>Industrials</t>
-        </is>
-      </c>
-      <c r="H5" s="7" t="inlineStr">
-        <is>
-          <t>PSU:35 BB:5 F4:28 RI:60</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="22" customHeight="1">
-      <c r="A6" s="8" t="n">
-        <v>2</v>
-      </c>
-      <c r="B6" s="9" t="inlineStr">
-        <is>
-          <t>CRM</t>
-        </is>
-      </c>
-      <c r="C6" s="10" t="inlineStr">
-        <is>
-          <t>Salesforce, Inc.</t>
-        </is>
-      </c>
-      <c r="D6" s="8" t="n">
-        <v>7</v>
-      </c>
-      <c r="E6" s="17" t="n">
-        <v>5.764</v>
-      </c>
-      <c r="F6" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="G6" s="10" t="inlineStr">
-        <is>
-          <t>Technology</t>
-        </is>
-      </c>
-      <c r="H6" s="10" t="inlineStr">
-        <is>
-          <t>PSU:28 BB:8 C10:-5 F4:11 RI:61</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="22" customHeight="1">
-      <c r="A7" s="5" t="n">
-        <v>3</v>
-      </c>
-      <c r="B7" s="6" t="inlineStr">
-        <is>
-          <t>EPAM</t>
-        </is>
-      </c>
-      <c r="C7" s="7" t="inlineStr">
-        <is>
-          <t>EPAM Systems, Inc.</t>
-        </is>
-      </c>
-      <c r="D7" s="5" t="n">
-        <v>7</v>
-      </c>
-      <c r="E7" s="16" t="n">
-        <v>5.626</v>
-      </c>
-      <c r="F7" s="5" t="n">
-        <v>-2</v>
-      </c>
-      <c r="G7" s="7" t="inlineStr">
-        <is>
-          <t>Technology</t>
-        </is>
-      </c>
-      <c r="H7" s="7" t="inlineStr">
-        <is>
-          <t>PSU:21 C10:-29 F4:18 RI:53</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="22" customHeight="1">
-      <c r="A8" s="8" t="n">
-        <v>4</v>
-      </c>
-      <c r="B8" s="9" t="inlineStr">
-        <is>
-          <t>PAR</t>
-        </is>
-      </c>
-      <c r="C8" s="10" t="inlineStr">
-        <is>
-          <t>PAR Technology Corporation</t>
-        </is>
-      </c>
-      <c r="D8" s="8" t="n">
-        <v>7</v>
-      </c>
-      <c r="E8" s="17" t="n">
-        <v>5.546</v>
-      </c>
-      <c r="F8" s="8" t="n">
-        <v>10</v>
-      </c>
-      <c r="G8" s="10" t="inlineStr">
-        <is>
-          <t>Technology</t>
-        </is>
-      </c>
-      <c r="H8" s="10" t="inlineStr">
-        <is>
-          <t>PSU:17 C10:-50 RI:45 SS:35</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="22" customHeight="1">
-      <c r="A9" s="5" t="n">
-        <v>5</v>
-      </c>
-      <c r="B9" s="6" t="inlineStr">
-        <is>
-          <t>FOUR</t>
-        </is>
-      </c>
-      <c r="C9" s="7" t="inlineStr">
-        <is>
-          <t>Shift4 Payments, Inc.</t>
-        </is>
-      </c>
-      <c r="D9" s="5" t="n">
-        <v>7</v>
-      </c>
-      <c r="E9" s="16" t="n">
-        <v>5.478</v>
-      </c>
-      <c r="F9" s="5" t="n">
-        <v>7</v>
-      </c>
-      <c r="G9" s="7" t="inlineStr">
-        <is>
-          <t>Technology</t>
-        </is>
-      </c>
-      <c r="H9" s="7" t="inlineStr">
-        <is>
-          <t>PSU:28 BB:5 F4:10 RI:51</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="22" customHeight="1">
-      <c r="A10" s="8" t="n">
-        <v>6</v>
-      </c>
-      <c r="B10" s="9" t="inlineStr">
-        <is>
-          <t>HUBS</t>
-        </is>
-      </c>
-      <c r="C10" s="10" t="inlineStr">
-        <is>
-          <t>HubSpot, Inc.</t>
-        </is>
-      </c>
-      <c r="D10" s="8" t="n">
-        <v>7</v>
-      </c>
-      <c r="E10" s="17" t="n">
-        <v>5.452</v>
-      </c>
-      <c r="F10" s="8" t="n">
-        <v>17</v>
-      </c>
-      <c r="G10" s="10" t="inlineStr">
-        <is>
-          <t>Technology</t>
-        </is>
-      </c>
-      <c r="H10" s="10" t="inlineStr">
-        <is>
-          <t>PSU:25 BB:5 F4:17 RI:57</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="22" customHeight="1">
-      <c r="A11" s="5" t="n">
-        <v>7</v>
-      </c>
-      <c r="B11" s="6" t="inlineStr">
-        <is>
-          <t>OLED</t>
-        </is>
-      </c>
-      <c r="C11" s="7" t="inlineStr">
-        <is>
-          <t>Universal Display Corporation</t>
-        </is>
-      </c>
-      <c r="D11" s="5" t="n">
-        <v>7</v>
-      </c>
-      <c r="E11" s="16" t="n">
-        <v>5.378</v>
-      </c>
-      <c r="F11" s="5" t="n">
-        <v>14</v>
-      </c>
-      <c r="G11" s="7" t="inlineStr">
-        <is>
-          <t>Technology</t>
-        </is>
-      </c>
-      <c r="H11" s="7" t="inlineStr">
-        <is>
-          <t>PSU:40 BB:5 F4:17 RI:60</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="22" customHeight="1">
-      <c r="A12" s="8" t="n">
-        <v>8</v>
-      </c>
-      <c r="B12" s="9" t="inlineStr">
-        <is>
-          <t>BLND</t>
-        </is>
-      </c>
-      <c r="C12" s="10" t="inlineStr">
-        <is>
-          <t>Blend Labs, Inc.</t>
-        </is>
-      </c>
-      <c r="D12" s="8" t="n">
-        <v>7</v>
-      </c>
-      <c r="E12" s="17" t="n">
-        <v>4.808</v>
-      </c>
-      <c r="F12" s="8" t="n">
-        <v>22</v>
-      </c>
-      <c r="G12" s="10" t="inlineStr">
-        <is>
-          <t>Technology</t>
-        </is>
-      </c>
-      <c r="H12" s="10" t="inlineStr">
-        <is>
-          <t>PSU:8 BB:5 C10:-35 F4:5 RI:52 SS:20</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="22" customHeight="1">
-      <c r="A13" s="5" t="n">
-        <v>9</v>
-      </c>
-      <c r="B13" s="6" t="inlineStr">
-        <is>
-          <t>ADT</t>
-        </is>
-      </c>
-      <c r="C13" s="7" t="inlineStr">
-        <is>
-          <t>ADT Inc.</t>
-        </is>
-      </c>
-      <c r="D13" s="5" t="n">
-        <v>7</v>
-      </c>
-      <c r="E13" s="16" t="n">
-        <v>4.59</v>
-      </c>
-      <c r="F13" s="5" t="n">
-        <v>-4</v>
-      </c>
-      <c r="G13" s="7" t="inlineStr">
-        <is>
-          <t>Industrials</t>
-        </is>
-      </c>
-      <c r="H13" s="7" t="inlineStr">
-        <is>
-          <t>PSU:31 BB:5 F4:12 RI:50 SS:10</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="22" customHeight="1">
-      <c r="A14" s="8" t="n">
-        <v>10</v>
-      </c>
-      <c r="B14" s="9" t="inlineStr">
-        <is>
-          <t>LULU</t>
-        </is>
-      </c>
-      <c r="C14" s="10" t="inlineStr">
-        <is>
-          <t>lululemon athletica inc.</t>
-        </is>
-      </c>
-      <c r="D14" s="8" t="n">
-        <v>7</v>
-      </c>
-      <c r="E14" s="17" t="n">
-        <v>4.514</v>
-      </c>
-      <c r="F14" s="8" t="n">
-        <v>8</v>
-      </c>
-      <c r="G14" s="10" t="inlineStr">
-        <is>
-          <t>Consumer Cyclical</t>
-        </is>
-      </c>
-      <c r="H14" s="10" t="inlineStr">
-        <is>
-          <t>PSU:1 BB:8 C10:-40 F4:11 RI:41 SS:10</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="22" customHeight="1">
-      <c r="A15" s="5" t="n">
-        <v>11</v>
-      </c>
-      <c r="B15" s="6" t="inlineStr">
-        <is>
-          <t>CERT</t>
-        </is>
-      </c>
-      <c r="C15" s="7" t="inlineStr">
-        <is>
-          <t>Certara, Inc.</t>
-        </is>
-      </c>
-      <c r="D15" s="5" t="n">
-        <v>7</v>
-      </c>
-      <c r="E15" s="16" t="n">
-        <v>4.416</v>
-      </c>
-      <c r="F15" s="5" t="n">
-        <v>5</v>
-      </c>
-      <c r="G15" s="7" t="inlineStr">
-        <is>
-          <t>Healthcare</t>
-        </is>
-      </c>
-      <c r="H15" s="7" t="inlineStr">
-        <is>
-          <t>PSU:29 BB:5 C10:-12 RI:43</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="22" customHeight="1">
-      <c r="A16" s="8" t="n">
-        <v>12</v>
-      </c>
-      <c r="B16" s="9" t="inlineStr">
-        <is>
-          <t>VTS</t>
-        </is>
-      </c>
-      <c r="C16" s="10" t="inlineStr">
-        <is>
-          <t>Vitesse Energy, Inc.</t>
-        </is>
-      </c>
-      <c r="D16" s="8" t="n">
-        <v>7</v>
-      </c>
-      <c r="E16" s="17" t="n">
-        <v>4.12</v>
-      </c>
-      <c r="F16" s="8" t="n">
-        <v>25</v>
-      </c>
-      <c r="G16" s="10" t="inlineStr">
-        <is>
-          <t>Energy</t>
-        </is>
-      </c>
-      <c r="H16" s="10" t="inlineStr">
-        <is>
-          <t>PSU:28 F4:5 RI:50</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="22" customHeight="1">
-      <c r="A17" s="5" t="n">
-        <v>13</v>
-      </c>
-      <c r="B17" s="6" t="inlineStr">
-        <is>
-          <t>GO</t>
-        </is>
-      </c>
-      <c r="C17" s="7" t="inlineStr">
-        <is>
-          <t>Grocery Outlet Holding Corp.</t>
-        </is>
-      </c>
-      <c r="D17" s="5" t="n">
-        <v>6</v>
-      </c>
-      <c r="E17" s="16" t="n">
-        <v>5.384</v>
-      </c>
-      <c r="F17" s="5" t="n">
-        <v>-5</v>
-      </c>
-      <c r="G17" s="7" t="inlineStr">
-        <is>
-          <t>Consumer Defensive</t>
-        </is>
-      </c>
-      <c r="H17" s="7" t="inlineStr">
-        <is>
-          <t>PSU:50 F4:28 RI:38</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="22" customHeight="1">
-      <c r="A18" s="8" t="n">
-        <v>14</v>
-      </c>
-      <c r="B18" s="9" t="inlineStr">
-        <is>
-          <t>SBET</t>
-        </is>
-      </c>
-      <c r="C18" s="10" t="inlineStr">
-        <is>
-          <t>SharpLink, Inc.</t>
-        </is>
-      </c>
-      <c r="D18" s="8" t="n">
-        <v>6</v>
-      </c>
-      <c r="E18" s="17" t="n">
-        <v>4.866</v>
-      </c>
-      <c r="F18" s="8" t="n">
-        <v>41</v>
-      </c>
-      <c r="G18" s="10" t="inlineStr">
-        <is>
-          <t>Financial Services</t>
-        </is>
-      </c>
-      <c r="H18" s="10" t="inlineStr">
-        <is>
-          <t>PSU:19 C10:15 RI:71</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="22" customHeight="1">
-      <c r="A19" s="5" t="n">
-        <v>15</v>
-      </c>
-      <c r="B19" s="6" t="inlineStr">
-        <is>
-          <t>DXC</t>
-        </is>
-      </c>
-      <c r="C19" s="7" t="inlineStr">
-        <is>
-          <t>DXC Technology Company</t>
-        </is>
-      </c>
-      <c r="D19" s="5" t="n">
-        <v>6</v>
-      </c>
-      <c r="E19" s="16" t="n">
-        <v>4.82</v>
-      </c>
-      <c r="F19" s="5" t="n">
-        <v>-5</v>
-      </c>
-      <c r="G19" s="7" t="inlineStr">
-        <is>
-          <t>Technology</t>
-        </is>
-      </c>
-      <c r="H19" s="7" t="inlineStr">
-        <is>
-          <t>PSU:43 BB:5 RI:57</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="22" customHeight="1">
-      <c r="A20" s="8" t="n">
-        <v>16</v>
-      </c>
-      <c r="B20" s="9" t="inlineStr">
-        <is>
-          <t>ALKT</t>
-        </is>
-      </c>
-      <c r="C20" s="10" t="inlineStr">
-        <is>
-          <t>Alkami Technology, Inc.</t>
-        </is>
-      </c>
-      <c r="D20" s="8" t="n">
-        <v>6</v>
-      </c>
-      <c r="E20" s="17" t="n">
-        <v>4.816</v>
-      </c>
-      <c r="F20" s="8" t="n">
-        <v>31</v>
-      </c>
-      <c r="G20" s="10" t="inlineStr">
-        <is>
-          <t>Technology</t>
-        </is>
-      </c>
-      <c r="H20" s="10" t="inlineStr">
-        <is>
-          <t>PSU:11 C10:-6 F4:16 RI:54</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="22" customHeight="1">
-      <c r="A21" s="5" t="n">
-        <v>17</v>
-      </c>
-      <c r="B21" s="6" t="inlineStr">
-        <is>
-          <t>GPGI</t>
-        </is>
-      </c>
-      <c r="C21" s="7" t="inlineStr">
-        <is>
-          <t>GPGI, Inc.</t>
-        </is>
-      </c>
-      <c r="D21" s="5" t="n">
-        <v>6</v>
-      </c>
-      <c r="E21" s="16" t="n">
-        <v>4.762</v>
-      </c>
-      <c r="F21" s="5" t="n">
-        <v>7</v>
-      </c>
-      <c r="G21" s="7" t="inlineStr">
-        <is>
-          <t>Industrials</t>
-        </is>
-      </c>
-      <c r="H21" s="7" t="inlineStr">
-        <is>
-          <t>PSU:17 C10:-15 F4:12 RI:52 SS:23</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="22" customHeight="1">
-      <c r="A22" s="8" t="n">
-        <v>18</v>
-      </c>
-      <c r="B22" s="9" t="inlineStr">
-        <is>
-          <t>SNBR</t>
-        </is>
-      </c>
-      <c r="C22" s="10" t="inlineStr">
-        <is>
-          <t>Sleep Number Corporation</t>
-        </is>
-      </c>
-      <c r="D22" s="8" t="n">
-        <v>6</v>
-      </c>
-      <c r="E22" s="17" t="n">
-        <v>4.742</v>
-      </c>
-      <c r="F22" s="8" t="n">
-        <v>2</v>
-      </c>
-      <c r="G22" s="10" t="inlineStr">
-        <is>
-          <t>Consumer Cyclical</t>
-        </is>
-      </c>
-      <c r="H22" s="10" t="inlineStr">
-        <is>
-          <t>PSU:49 RI:46 SS:20</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="22" customHeight="1">
-      <c r="A23" s="5" t="n">
-        <v>19</v>
-      </c>
-      <c r="B23" s="6" t="inlineStr">
-        <is>
-          <t>ACM</t>
-        </is>
-      </c>
-      <c r="C23" s="7" t="inlineStr">
-        <is>
-          <t>AECOM</t>
-        </is>
-      </c>
-      <c r="D23" s="5" t="n">
-        <v>6</v>
-      </c>
-      <c r="E23" s="16" t="n">
-        <v>4.68</v>
-      </c>
-      <c r="F23" s="5" t="n">
-        <v>35</v>
-      </c>
-      <c r="G23" s="7" t="inlineStr">
-        <is>
-          <t>Industrials</t>
-        </is>
-      </c>
-      <c r="H23" s="7" t="inlineStr">
-        <is>
-          <t>BB:5 F4:6 RI:54</t>
-        </is>
-      </c>
-    </row>
-    <row r="24" ht="22" customHeight="1">
-      <c r="A24" s="8" t="n">
-        <v>20</v>
-      </c>
-      <c r="B24" s="9" t="inlineStr">
-        <is>
-          <t>HDSN</t>
-        </is>
-      </c>
-      <c r="C24" s="10" t="inlineStr">
-        <is>
-          <t>Hudson Technologies, Inc.</t>
-        </is>
-      </c>
-      <c r="D24" s="8" t="n">
-        <v>6</v>
-      </c>
-      <c r="E24" s="17" t="n">
-        <v>4.66</v>
-      </c>
-      <c r="F24" s="8" t="n">
-        <v>-5</v>
-      </c>
-      <c r="G24" s="10" t="inlineStr">
-        <is>
-          <t>Basic Materials</t>
-        </is>
-      </c>
-      <c r="H24" s="10" t="inlineStr">
-        <is>
-          <t>BB:5 F4:18 RI:58</t>
-        </is>
-      </c>
-    </row>
-    <row r="25" ht="22" customHeight="1">
-      <c r="A25" s="5" t="n">
-        <v>21</v>
-      </c>
-      <c r="B25" s="6" t="inlineStr">
-        <is>
-          <t>NUS</t>
-        </is>
-      </c>
-      <c r="C25" s="7" t="inlineStr">
-        <is>
-          <t>Nu Skin Enterprises, Inc.</t>
-        </is>
-      </c>
-      <c r="D25" s="5" t="n">
-        <v>6</v>
-      </c>
-      <c r="E25" s="16" t="n">
-        <v>4.562</v>
-      </c>
-      <c r="F25" s="5" t="n">
-        <v>-2</v>
-      </c>
-      <c r="G25" s="7" t="inlineStr">
-        <is>
-          <t>Consumer Defensive</t>
-        </is>
-      </c>
-      <c r="H25" s="7" t="inlineStr">
-        <is>
-          <t>PSU:54 BB:5 C10:-32 RI:53</t>
-        </is>
-      </c>
-    </row>
-    <row r="26" ht="22" customHeight="1">
-      <c r="A26" s="8" t="n">
-        <v>22</v>
-      </c>
-      <c r="B26" s="9" t="inlineStr">
-        <is>
-          <t>VRSK</t>
-        </is>
-      </c>
-      <c r="C26" s="10" t="inlineStr">
-        <is>
-          <t>Verisk Analytics, Inc.</t>
-        </is>
-      </c>
-      <c r="D26" s="8" t="n">
-        <v>6</v>
-      </c>
-      <c r="E26" s="17" t="n">
-        <v>4.556</v>
-      </c>
-      <c r="F26" s="10" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="G26" s="10" t="inlineStr">
-        <is>
-          <t>Industrials</t>
-        </is>
-      </c>
-      <c r="H26" s="10" t="inlineStr">
-        <is>
-          <t>PSU:32 BB:8 F4:12 RI:32</t>
-        </is>
-      </c>
-    </row>
-    <row r="27" ht="22" customHeight="1">
-      <c r="A27" s="5" t="n">
-        <v>23</v>
-      </c>
-      <c r="B27" s="6" t="inlineStr">
-        <is>
-          <t>ZTS</t>
-        </is>
-      </c>
-      <c r="C27" s="7" t="inlineStr">
-        <is>
-          <t>Zoetis Inc.</t>
-        </is>
-      </c>
-      <c r="D27" s="5" t="n">
-        <v>6</v>
-      </c>
-      <c r="E27" s="16" t="n">
-        <v>4.522</v>
-      </c>
-      <c r="F27" s="5" t="n">
-        <v>-10</v>
-      </c>
-      <c r="G27" s="7" t="inlineStr">
-        <is>
-          <t>Healthcare</t>
-        </is>
-      </c>
-      <c r="H27" s="7" t="inlineStr">
-        <is>
-          <t>PSU:7 BB:5 C10:-3 F4:12 RI:60</t>
-        </is>
-      </c>
-    </row>
-    <row r="28" ht="22" customHeight="1">
-      <c r="A28" s="8" t="n">
-        <v>24</v>
-      </c>
-      <c r="B28" s="9" t="inlineStr">
-        <is>
-          <t>MSCI</t>
-        </is>
-      </c>
-      <c r="C28" s="10" t="inlineStr">
-        <is>
-          <t>MSCI Inc.</t>
-        </is>
-      </c>
-      <c r="D28" s="8" t="n">
-        <v>6</v>
-      </c>
-      <c r="E28" s="17" t="n">
-        <v>4.498</v>
-      </c>
-      <c r="F28" s="8" t="n">
-        <v>2</v>
-      </c>
-      <c r="G28" s="10" t="inlineStr">
-        <is>
-          <t>Financial Services</t>
-        </is>
-      </c>
-      <c r="H28" s="10" t="inlineStr">
-        <is>
-          <t>PSU:36 BB:8 C10:-26 F4:16 RI:16</t>
-        </is>
-      </c>
-    </row>
-    <row r="29" ht="22" customHeight="1">
-      <c r="A29" s="5" t="n">
-        <v>25</v>
-      </c>
-      <c r="B29" s="6" t="inlineStr">
-        <is>
-          <t>PSN</t>
-        </is>
-      </c>
-      <c r="C29" s="7" t="inlineStr">
-        <is>
-          <t>Parsons Corporation</t>
-        </is>
-      </c>
-      <c r="D29" s="5" t="n">
-        <v>6</v>
-      </c>
-      <c r="E29" s="16" t="n">
-        <v>4.466</v>
-      </c>
-      <c r="F29" s="5" t="n">
-        <v>9</v>
-      </c>
-      <c r="G29" s="7" t="inlineStr">
-        <is>
-          <t>Technology</t>
-        </is>
-      </c>
-      <c r="H29" s="7" t="inlineStr">
-        <is>
-          <t>PSU:37 F4:23 RI:47</t>
-        </is>
-      </c>
-    </row>
-    <row r="30" ht="22" customHeight="1">
-      <c r="A30" s="8" t="n">
-        <v>26</v>
-      </c>
-      <c r="B30" s="9" t="inlineStr">
-        <is>
-          <t>AZTA</t>
-        </is>
-      </c>
-      <c r="C30" s="10" t="inlineStr">
-        <is>
-          <t>Azenta, Inc.</t>
-        </is>
-      </c>
-      <c r="D30" s="8" t="n">
-        <v>6</v>
-      </c>
-      <c r="E30" s="17" t="n">
-        <v>4.348</v>
-      </c>
-      <c r="F30" s="8" t="n">
-        <v>12</v>
-      </c>
-      <c r="G30" s="10" t="inlineStr">
-        <is>
-          <t>Healthcare</t>
-        </is>
-      </c>
-      <c r="H30" s="10" t="inlineStr">
-        <is>
-          <t>PSU:31</t>
-        </is>
-      </c>
-    </row>
-    <row r="31" ht="22" customHeight="1">
-      <c r="A31" s="5" t="n">
-        <v>27</v>
-      </c>
-      <c r="B31" s="6" t="inlineStr">
-        <is>
-          <t>APTV</t>
-        </is>
-      </c>
-      <c r="C31" s="7" t="inlineStr">
-        <is>
-          <t>Aptiv PLC</t>
-        </is>
-      </c>
-      <c r="D31" s="5" t="n">
-        <v>6</v>
-      </c>
-      <c r="E31" s="16" t="n">
-        <v>4.344</v>
-      </c>
-      <c r="F31" s="5" t="n">
-        <v>26</v>
-      </c>
-      <c r="G31" s="7" t="inlineStr">
-        <is>
-          <t>Consumer Cyclical</t>
-        </is>
-      </c>
-      <c r="H31" s="7" t="inlineStr">
-        <is>
-          <t>PSU:36 BB:5 RI:35</t>
-        </is>
-      </c>
-    </row>
-    <row r="32" ht="22" customHeight="1">
-      <c r="A32" s="8" t="n">
-        <v>28</v>
-      </c>
-      <c r="B32" s="9" t="inlineStr">
-        <is>
-          <t>OPCH</t>
-        </is>
-      </c>
-      <c r="C32" s="10" t="inlineStr">
-        <is>
-          <t>Option Care Health, Inc.</t>
-        </is>
-      </c>
-      <c r="D32" s="8" t="n">
-        <v>6</v>
-      </c>
-      <c r="E32" s="17" t="n">
-        <v>4.26</v>
-      </c>
-      <c r="F32" s="8" t="n">
-        <v>4</v>
-      </c>
-      <c r="G32" s="10" t="inlineStr">
-        <is>
-          <t>Healthcare</t>
-        </is>
-      </c>
-      <c r="H32" s="10" t="inlineStr">
-        <is>
-          <t>PSU:27 BB:5 C10:-1 F4:23 RI:52</t>
-        </is>
-      </c>
-    </row>
-    <row r="33" ht="22" customHeight="1">
-      <c r="A33" s="5" t="n">
-        <v>29</v>
-      </c>
-      <c r="B33" s="6" t="inlineStr">
-        <is>
-          <t>MMS</t>
-        </is>
-      </c>
-      <c r="C33" s="7" t="inlineStr">
-        <is>
-          <t>Maximus, Inc.</t>
-        </is>
-      </c>
-      <c r="D33" s="5" t="n">
-        <v>6</v>
-      </c>
-      <c r="E33" s="16" t="n">
-        <v>4.182</v>
-      </c>
-      <c r="F33" s="21" t="n">
-        <v>106</v>
-      </c>
-      <c r="G33" s="7" t="inlineStr">
-        <is>
-          <t>Industrials</t>
-        </is>
-      </c>
-      <c r="H33" s="7" t="inlineStr">
-        <is>
-          <t>PSU:42 BB:5 RI:53 SS:26</t>
-        </is>
-      </c>
-    </row>
-    <row r="34" ht="22" customHeight="1">
-      <c r="A34" s="8" t="n">
-        <v>30</v>
-      </c>
-      <c r="B34" s="9" t="inlineStr">
-        <is>
-          <t>GTM</t>
-        </is>
-      </c>
-      <c r="C34" s="10" t="inlineStr">
-        <is>
-          <t>ZoomInfo Technologies Inc.</t>
-        </is>
-      </c>
-      <c r="D34" s="8" t="n">
-        <v>6</v>
-      </c>
-      <c r="E34" s="17" t="n">
-        <v>4.056</v>
-      </c>
-      <c r="F34" s="8" t="n">
-        <v>-3</v>
-      </c>
-      <c r="G34" s="10" t="inlineStr">
-        <is>
-          <t>Technology</t>
-        </is>
-      </c>
-      <c r="H34" s="10" t="inlineStr">
-        <is>
-          <t>PSU:36 BB:5 C10:-4 RI:66 SS:20</t>
-        </is>
-      </c>
-    </row>
-    <row r="36" ht="28" customHeight="1">
-      <c r="A36" s="11" t="inlineStr">
-        <is>
-          <t>'Lift vs val' shows how many positions a name climbs when valuation is excluded. A large positive lift means the name is structurally strong but is being penalised by the valuation layer -- likely either missing yfinance overlay or trading at multiples outside our discount zones (P/B&gt;1.5, P/E&gt;15, EV/EBITDA&gt;10). The 26 emergent names (consensus_emergent_noval.csv) are gap-fill priorities.</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="3">
-    <mergeCell ref="A36:H36"/>
-    <mergeCell ref="A2:H2"/>
-    <mergeCell ref="A1:H1"/>
   </mergeCells>
   <printOptions horizontalCentered="0"/>
   <pageMargins left="0.5" right="0.5" top="0.6" bottom="0.6" header="0.5" footer="0.5"/>
@@ -14329,6 +13815,1130 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
+  <dimension ref="A1:H36"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="9" customWidth="1" min="1" max="1"/>
+    <col width="13" customWidth="1" min="2" max="2"/>
+    <col width="32" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="50" customWidth="1" min="8" max="8"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="26" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Top of Universe -- Without Valuation Leg</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="18" customHeight="1">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Parallel ranking that excludes valuation entirely so names missing yfinance overlay are not penalised. Compared against the valuation-included ranking to identify structurally-strong-but-valuation-hidden names.</t>
+        </is>
+      </c>
+      <c r="B2" s="3" t="n"/>
+      <c r="C2" s="3" t="n"/>
+      <c r="D2" s="3" t="n"/>
+      <c r="E2" s="3" t="n"/>
+      <c r="F2" s="3" t="n"/>
+      <c r="G2" s="3" t="n"/>
+      <c r="H2" s="3" t="n"/>
+    </row>
+    <row r="3" ht="8" customHeight="1"/>
+    <row r="4" ht="18" customHeight="1">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="B4" s="15" t="inlineStr">
+        <is>
+          <t>Ticker</t>
+        </is>
+      </c>
+      <c r="C4" s="15" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="D4" s="4" t="inlineStr">
+        <is>
+          <t>Layers</t>
+        </is>
+      </c>
+      <c r="E4" s="4" t="inlineStr">
+        <is>
+          <t>Consensus</t>
+        </is>
+      </c>
+      <c r="F4" s="4" t="inlineStr">
+        <is>
+          <t>Lift vs val</t>
+        </is>
+      </c>
+      <c r="G4" s="15" t="inlineStr">
+        <is>
+          <t>Sector</t>
+        </is>
+      </c>
+      <c r="H4" s="15" t="inlineStr">
+        <is>
+          <t>Detail</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="22" customHeight="1">
+      <c r="A5" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="B5" s="6" t="inlineStr">
+        <is>
+          <t>POOL</t>
+        </is>
+      </c>
+      <c r="C5" s="7" t="inlineStr">
+        <is>
+          <t>Pool Corporation</t>
+        </is>
+      </c>
+      <c r="D5" s="5" t="n">
+        <v>8</v>
+      </c>
+      <c r="E5" s="16" t="n">
+        <v>5.902</v>
+      </c>
+      <c r="F5" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="G5" s="7" t="inlineStr">
+        <is>
+          <t>Industrials</t>
+        </is>
+      </c>
+      <c r="H5" s="7" t="inlineStr">
+        <is>
+          <t>PSU:35 BB:5 F4:28 RI:60</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="22" customHeight="1">
+      <c r="A6" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="B6" s="9" t="inlineStr">
+        <is>
+          <t>CRM</t>
+        </is>
+      </c>
+      <c r="C6" s="10" t="inlineStr">
+        <is>
+          <t>Salesforce, Inc.</t>
+        </is>
+      </c>
+      <c r="D6" s="8" t="n">
+        <v>7</v>
+      </c>
+      <c r="E6" s="17" t="n">
+        <v>5.764</v>
+      </c>
+      <c r="F6" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="G6" s="10" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="H6" s="10" t="inlineStr">
+        <is>
+          <t>PSU:28 BB:8 C10:-5 F4:11 RI:61</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="22" customHeight="1">
+      <c r="A7" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="B7" s="6" t="inlineStr">
+        <is>
+          <t>EPAM</t>
+        </is>
+      </c>
+      <c r="C7" s="7" t="inlineStr">
+        <is>
+          <t>EPAM Systems, Inc.</t>
+        </is>
+      </c>
+      <c r="D7" s="5" t="n">
+        <v>7</v>
+      </c>
+      <c r="E7" s="16" t="n">
+        <v>5.626</v>
+      </c>
+      <c r="F7" s="5" t="n">
+        <v>-2</v>
+      </c>
+      <c r="G7" s="7" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="H7" s="7" t="inlineStr">
+        <is>
+          <t>PSU:21 C10:-29 F4:18 RI:53</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="22" customHeight="1">
+      <c r="A8" s="8" t="n">
+        <v>4</v>
+      </c>
+      <c r="B8" s="9" t="inlineStr">
+        <is>
+          <t>PAR</t>
+        </is>
+      </c>
+      <c r="C8" s="10" t="inlineStr">
+        <is>
+          <t>PAR Technology Corporation</t>
+        </is>
+      </c>
+      <c r="D8" s="8" t="n">
+        <v>7</v>
+      </c>
+      <c r="E8" s="17" t="n">
+        <v>5.546</v>
+      </c>
+      <c r="F8" s="8" t="n">
+        <v>10</v>
+      </c>
+      <c r="G8" s="10" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="H8" s="10" t="inlineStr">
+        <is>
+          <t>PSU:17 C10:-50 RI:45 SS:35</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="22" customHeight="1">
+      <c r="A9" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="B9" s="6" t="inlineStr">
+        <is>
+          <t>FOUR</t>
+        </is>
+      </c>
+      <c r="C9" s="7" t="inlineStr">
+        <is>
+          <t>Shift4 Payments, Inc.</t>
+        </is>
+      </c>
+      <c r="D9" s="5" t="n">
+        <v>7</v>
+      </c>
+      <c r="E9" s="16" t="n">
+        <v>5.478</v>
+      </c>
+      <c r="F9" s="5" t="n">
+        <v>7</v>
+      </c>
+      <c r="G9" s="7" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="H9" s="7" t="inlineStr">
+        <is>
+          <t>PSU:28 BB:5 F4:10 RI:51</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="22" customHeight="1">
+      <c r="A10" s="8" t="n">
+        <v>6</v>
+      </c>
+      <c r="B10" s="9" t="inlineStr">
+        <is>
+          <t>HUBS</t>
+        </is>
+      </c>
+      <c r="C10" s="10" t="inlineStr">
+        <is>
+          <t>HubSpot, Inc.</t>
+        </is>
+      </c>
+      <c r="D10" s="8" t="n">
+        <v>7</v>
+      </c>
+      <c r="E10" s="17" t="n">
+        <v>5.452</v>
+      </c>
+      <c r="F10" s="8" t="n">
+        <v>17</v>
+      </c>
+      <c r="G10" s="10" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="H10" s="10" t="inlineStr">
+        <is>
+          <t>PSU:25 BB:5 F4:17 RI:57</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="22" customHeight="1">
+      <c r="A11" s="5" t="n">
+        <v>7</v>
+      </c>
+      <c r="B11" s="6" t="inlineStr">
+        <is>
+          <t>OLED</t>
+        </is>
+      </c>
+      <c r="C11" s="7" t="inlineStr">
+        <is>
+          <t>Universal Display Corporation</t>
+        </is>
+      </c>
+      <c r="D11" s="5" t="n">
+        <v>7</v>
+      </c>
+      <c r="E11" s="16" t="n">
+        <v>5.378</v>
+      </c>
+      <c r="F11" s="5" t="n">
+        <v>14</v>
+      </c>
+      <c r="G11" s="7" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="H11" s="7" t="inlineStr">
+        <is>
+          <t>PSU:40 BB:5 F4:17 RI:60</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="22" customHeight="1">
+      <c r="A12" s="8" t="n">
+        <v>8</v>
+      </c>
+      <c r="B12" s="9" t="inlineStr">
+        <is>
+          <t>BLND</t>
+        </is>
+      </c>
+      <c r="C12" s="10" t="inlineStr">
+        <is>
+          <t>Blend Labs, Inc.</t>
+        </is>
+      </c>
+      <c r="D12" s="8" t="n">
+        <v>7</v>
+      </c>
+      <c r="E12" s="17" t="n">
+        <v>4.808</v>
+      </c>
+      <c r="F12" s="8" t="n">
+        <v>22</v>
+      </c>
+      <c r="G12" s="10" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="H12" s="10" t="inlineStr">
+        <is>
+          <t>PSU:8 BB:5 C10:-35 F4:5 RI:52 SS:20</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="22" customHeight="1">
+      <c r="A13" s="5" t="n">
+        <v>9</v>
+      </c>
+      <c r="B13" s="6" t="inlineStr">
+        <is>
+          <t>ADT</t>
+        </is>
+      </c>
+      <c r="C13" s="7" t="inlineStr">
+        <is>
+          <t>ADT Inc.</t>
+        </is>
+      </c>
+      <c r="D13" s="5" t="n">
+        <v>7</v>
+      </c>
+      <c r="E13" s="16" t="n">
+        <v>4.59</v>
+      </c>
+      <c r="F13" s="5" t="n">
+        <v>-4</v>
+      </c>
+      <c r="G13" s="7" t="inlineStr">
+        <is>
+          <t>Industrials</t>
+        </is>
+      </c>
+      <c r="H13" s="7" t="inlineStr">
+        <is>
+          <t>PSU:31 BB:5 F4:12 RI:50 SS:10</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="22" customHeight="1">
+      <c r="A14" s="8" t="n">
+        <v>10</v>
+      </c>
+      <c r="B14" s="9" t="inlineStr">
+        <is>
+          <t>LULU</t>
+        </is>
+      </c>
+      <c r="C14" s="10" t="inlineStr">
+        <is>
+          <t>lululemon athletica inc.</t>
+        </is>
+      </c>
+      <c r="D14" s="8" t="n">
+        <v>7</v>
+      </c>
+      <c r="E14" s="17" t="n">
+        <v>4.514</v>
+      </c>
+      <c r="F14" s="8" t="n">
+        <v>8</v>
+      </c>
+      <c r="G14" s="10" t="inlineStr">
+        <is>
+          <t>Consumer Cyclical</t>
+        </is>
+      </c>
+      <c r="H14" s="10" t="inlineStr">
+        <is>
+          <t>PSU:1 BB:8 C10:-40 F4:11 RI:41 SS:10</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="22" customHeight="1">
+      <c r="A15" s="5" t="n">
+        <v>11</v>
+      </c>
+      <c r="B15" s="6" t="inlineStr">
+        <is>
+          <t>CERT</t>
+        </is>
+      </c>
+      <c r="C15" s="7" t="inlineStr">
+        <is>
+          <t>Certara, Inc.</t>
+        </is>
+      </c>
+      <c r="D15" s="5" t="n">
+        <v>7</v>
+      </c>
+      <c r="E15" s="16" t="n">
+        <v>4.416</v>
+      </c>
+      <c r="F15" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="G15" s="7" t="inlineStr">
+        <is>
+          <t>Healthcare</t>
+        </is>
+      </c>
+      <c r="H15" s="7" t="inlineStr">
+        <is>
+          <t>PSU:29 BB:5 C10:-12 RI:43</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="22" customHeight="1">
+      <c r="A16" s="8" t="n">
+        <v>12</v>
+      </c>
+      <c r="B16" s="9" t="inlineStr">
+        <is>
+          <t>VTS</t>
+        </is>
+      </c>
+      <c r="C16" s="10" t="inlineStr">
+        <is>
+          <t>Vitesse Energy, Inc.</t>
+        </is>
+      </c>
+      <c r="D16" s="8" t="n">
+        <v>7</v>
+      </c>
+      <c r="E16" s="17" t="n">
+        <v>4.12</v>
+      </c>
+      <c r="F16" s="8" t="n">
+        <v>25</v>
+      </c>
+      <c r="G16" s="10" t="inlineStr">
+        <is>
+          <t>Energy</t>
+        </is>
+      </c>
+      <c r="H16" s="10" t="inlineStr">
+        <is>
+          <t>PSU:28 F4:5 RI:50</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="22" customHeight="1">
+      <c r="A17" s="5" t="n">
+        <v>13</v>
+      </c>
+      <c r="B17" s="6" t="inlineStr">
+        <is>
+          <t>GO</t>
+        </is>
+      </c>
+      <c r="C17" s="7" t="inlineStr">
+        <is>
+          <t>Grocery Outlet Holding Corp.</t>
+        </is>
+      </c>
+      <c r="D17" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="E17" s="16" t="n">
+        <v>5.384</v>
+      </c>
+      <c r="F17" s="5" t="n">
+        <v>-5</v>
+      </c>
+      <c r="G17" s="7" t="inlineStr">
+        <is>
+          <t>Consumer Defensive</t>
+        </is>
+      </c>
+      <c r="H17" s="7" t="inlineStr">
+        <is>
+          <t>PSU:50 F4:28 RI:38</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="22" customHeight="1">
+      <c r="A18" s="8" t="n">
+        <v>14</v>
+      </c>
+      <c r="B18" s="9" t="inlineStr">
+        <is>
+          <t>SBET</t>
+        </is>
+      </c>
+      <c r="C18" s="10" t="inlineStr">
+        <is>
+          <t>SharpLink, Inc.</t>
+        </is>
+      </c>
+      <c r="D18" s="8" t="n">
+        <v>6</v>
+      </c>
+      <c r="E18" s="17" t="n">
+        <v>4.866</v>
+      </c>
+      <c r="F18" s="8" t="n">
+        <v>41</v>
+      </c>
+      <c r="G18" s="10" t="inlineStr">
+        <is>
+          <t>Financial Services</t>
+        </is>
+      </c>
+      <c r="H18" s="10" t="inlineStr">
+        <is>
+          <t>PSU:19 C10:15 RI:71</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="22" customHeight="1">
+      <c r="A19" s="5" t="n">
+        <v>15</v>
+      </c>
+      <c r="B19" s="6" t="inlineStr">
+        <is>
+          <t>DXC</t>
+        </is>
+      </c>
+      <c r="C19" s="7" t="inlineStr">
+        <is>
+          <t>DXC Technology Company</t>
+        </is>
+      </c>
+      <c r="D19" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="E19" s="16" t="n">
+        <v>4.82</v>
+      </c>
+      <c r="F19" s="5" t="n">
+        <v>-5</v>
+      </c>
+      <c r="G19" s="7" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="H19" s="7" t="inlineStr">
+        <is>
+          <t>PSU:43 BB:5 RI:57</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="22" customHeight="1">
+      <c r="A20" s="8" t="n">
+        <v>16</v>
+      </c>
+      <c r="B20" s="9" t="inlineStr">
+        <is>
+          <t>ALKT</t>
+        </is>
+      </c>
+      <c r="C20" s="10" t="inlineStr">
+        <is>
+          <t>Alkami Technology, Inc.</t>
+        </is>
+      </c>
+      <c r="D20" s="8" t="n">
+        <v>6</v>
+      </c>
+      <c r="E20" s="17" t="n">
+        <v>4.816</v>
+      </c>
+      <c r="F20" s="8" t="n">
+        <v>31</v>
+      </c>
+      <c r="G20" s="10" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="H20" s="10" t="inlineStr">
+        <is>
+          <t>PSU:11 C10:-6 F4:16 RI:54</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="22" customHeight="1">
+      <c r="A21" s="5" t="n">
+        <v>17</v>
+      </c>
+      <c r="B21" s="6" t="inlineStr">
+        <is>
+          <t>GPGI</t>
+        </is>
+      </c>
+      <c r="C21" s="7" t="inlineStr">
+        <is>
+          <t>GPGI, Inc.</t>
+        </is>
+      </c>
+      <c r="D21" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="E21" s="16" t="n">
+        <v>4.762</v>
+      </c>
+      <c r="F21" s="5" t="n">
+        <v>7</v>
+      </c>
+      <c r="G21" s="7" t="inlineStr">
+        <is>
+          <t>Industrials</t>
+        </is>
+      </c>
+      <c r="H21" s="7" t="inlineStr">
+        <is>
+          <t>PSU:17 C10:-15 F4:12 RI:52 SS:23</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="22" customHeight="1">
+      <c r="A22" s="8" t="n">
+        <v>18</v>
+      </c>
+      <c r="B22" s="9" t="inlineStr">
+        <is>
+          <t>SNBR</t>
+        </is>
+      </c>
+      <c r="C22" s="10" t="inlineStr">
+        <is>
+          <t>Sleep Number Corporation</t>
+        </is>
+      </c>
+      <c r="D22" s="8" t="n">
+        <v>6</v>
+      </c>
+      <c r="E22" s="17" t="n">
+        <v>4.742</v>
+      </c>
+      <c r="F22" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="G22" s="10" t="inlineStr">
+        <is>
+          <t>Consumer Cyclical</t>
+        </is>
+      </c>
+      <c r="H22" s="10" t="inlineStr">
+        <is>
+          <t>PSU:49 RI:46 SS:20</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="22" customHeight="1">
+      <c r="A23" s="5" t="n">
+        <v>19</v>
+      </c>
+      <c r="B23" s="6" t="inlineStr">
+        <is>
+          <t>ACM</t>
+        </is>
+      </c>
+      <c r="C23" s="7" t="inlineStr">
+        <is>
+          <t>AECOM</t>
+        </is>
+      </c>
+      <c r="D23" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="E23" s="16" t="n">
+        <v>4.68</v>
+      </c>
+      <c r="F23" s="5" t="n">
+        <v>35</v>
+      </c>
+      <c r="G23" s="7" t="inlineStr">
+        <is>
+          <t>Industrials</t>
+        </is>
+      </c>
+      <c r="H23" s="7" t="inlineStr">
+        <is>
+          <t>BB:5 F4:6 RI:54</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="22" customHeight="1">
+      <c r="A24" s="8" t="n">
+        <v>20</v>
+      </c>
+      <c r="B24" s="9" t="inlineStr">
+        <is>
+          <t>HDSN</t>
+        </is>
+      </c>
+      <c r="C24" s="10" t="inlineStr">
+        <is>
+          <t>Hudson Technologies, Inc.</t>
+        </is>
+      </c>
+      <c r="D24" s="8" t="n">
+        <v>6</v>
+      </c>
+      <c r="E24" s="17" t="n">
+        <v>4.66</v>
+      </c>
+      <c r="F24" s="8" t="n">
+        <v>-5</v>
+      </c>
+      <c r="G24" s="10" t="inlineStr">
+        <is>
+          <t>Basic Materials</t>
+        </is>
+      </c>
+      <c r="H24" s="10" t="inlineStr">
+        <is>
+          <t>BB:5 F4:18 RI:58</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="22" customHeight="1">
+      <c r="A25" s="5" t="n">
+        <v>21</v>
+      </c>
+      <c r="B25" s="6" t="inlineStr">
+        <is>
+          <t>NUS</t>
+        </is>
+      </c>
+      <c r="C25" s="7" t="inlineStr">
+        <is>
+          <t>Nu Skin Enterprises, Inc.</t>
+        </is>
+      </c>
+      <c r="D25" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="E25" s="16" t="n">
+        <v>4.562</v>
+      </c>
+      <c r="F25" s="5" t="n">
+        <v>-2</v>
+      </c>
+      <c r="G25" s="7" t="inlineStr">
+        <is>
+          <t>Consumer Defensive</t>
+        </is>
+      </c>
+      <c r="H25" s="7" t="inlineStr">
+        <is>
+          <t>PSU:54 BB:5 C10:-32 RI:53</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="22" customHeight="1">
+      <c r="A26" s="8" t="n">
+        <v>22</v>
+      </c>
+      <c r="B26" s="9" t="inlineStr">
+        <is>
+          <t>VRSK</t>
+        </is>
+      </c>
+      <c r="C26" s="10" t="inlineStr">
+        <is>
+          <t>Verisk Analytics, Inc.</t>
+        </is>
+      </c>
+      <c r="D26" s="8" t="n">
+        <v>6</v>
+      </c>
+      <c r="E26" s="17" t="n">
+        <v>4.556</v>
+      </c>
+      <c r="F26" s="10" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="G26" s="10" t="inlineStr">
+        <is>
+          <t>Industrials</t>
+        </is>
+      </c>
+      <c r="H26" s="10" t="inlineStr">
+        <is>
+          <t>PSU:32 BB:8 F4:12 RI:32</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="22" customHeight="1">
+      <c r="A27" s="5" t="n">
+        <v>23</v>
+      </c>
+      <c r="B27" s="6" t="inlineStr">
+        <is>
+          <t>ZTS</t>
+        </is>
+      </c>
+      <c r="C27" s="7" t="inlineStr">
+        <is>
+          <t>Zoetis Inc.</t>
+        </is>
+      </c>
+      <c r="D27" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="E27" s="16" t="n">
+        <v>4.522</v>
+      </c>
+      <c r="F27" s="5" t="n">
+        <v>-10</v>
+      </c>
+      <c r="G27" s="7" t="inlineStr">
+        <is>
+          <t>Healthcare</t>
+        </is>
+      </c>
+      <c r="H27" s="7" t="inlineStr">
+        <is>
+          <t>PSU:7 BB:5 C10:-3 F4:12 RI:60</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="22" customHeight="1">
+      <c r="A28" s="8" t="n">
+        <v>24</v>
+      </c>
+      <c r="B28" s="9" t="inlineStr">
+        <is>
+          <t>MSCI</t>
+        </is>
+      </c>
+      <c r="C28" s="10" t="inlineStr">
+        <is>
+          <t>MSCI Inc.</t>
+        </is>
+      </c>
+      <c r="D28" s="8" t="n">
+        <v>6</v>
+      </c>
+      <c r="E28" s="17" t="n">
+        <v>4.498</v>
+      </c>
+      <c r="F28" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="G28" s="10" t="inlineStr">
+        <is>
+          <t>Financial Services</t>
+        </is>
+      </c>
+      <c r="H28" s="10" t="inlineStr">
+        <is>
+          <t>PSU:36 BB:8 C10:-26 F4:16 RI:16</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="22" customHeight="1">
+      <c r="A29" s="5" t="n">
+        <v>25</v>
+      </c>
+      <c r="B29" s="6" t="inlineStr">
+        <is>
+          <t>PSN</t>
+        </is>
+      </c>
+      <c r="C29" s="7" t="inlineStr">
+        <is>
+          <t>Parsons Corporation</t>
+        </is>
+      </c>
+      <c r="D29" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="E29" s="16" t="n">
+        <v>4.466</v>
+      </c>
+      <c r="F29" s="5" t="n">
+        <v>9</v>
+      </c>
+      <c r="G29" s="7" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="H29" s="7" t="inlineStr">
+        <is>
+          <t>PSU:37 F4:23 RI:47</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="22" customHeight="1">
+      <c r="A30" s="8" t="n">
+        <v>26</v>
+      </c>
+      <c r="B30" s="9" t="inlineStr">
+        <is>
+          <t>AZTA</t>
+        </is>
+      </c>
+      <c r="C30" s="10" t="inlineStr">
+        <is>
+          <t>Azenta, Inc.</t>
+        </is>
+      </c>
+      <c r="D30" s="8" t="n">
+        <v>6</v>
+      </c>
+      <c r="E30" s="17" t="n">
+        <v>4.348</v>
+      </c>
+      <c r="F30" s="8" t="n">
+        <v>12</v>
+      </c>
+      <c r="G30" s="10" t="inlineStr">
+        <is>
+          <t>Healthcare</t>
+        </is>
+      </c>
+      <c r="H30" s="10" t="inlineStr">
+        <is>
+          <t>PSU:31</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="22" customHeight="1">
+      <c r="A31" s="5" t="n">
+        <v>27</v>
+      </c>
+      <c r="B31" s="6" t="inlineStr">
+        <is>
+          <t>APTV</t>
+        </is>
+      </c>
+      <c r="C31" s="7" t="inlineStr">
+        <is>
+          <t>Aptiv PLC</t>
+        </is>
+      </c>
+      <c r="D31" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="E31" s="16" t="n">
+        <v>4.344</v>
+      </c>
+      <c r="F31" s="5" t="n">
+        <v>26</v>
+      </c>
+      <c r="G31" s="7" t="inlineStr">
+        <is>
+          <t>Consumer Cyclical</t>
+        </is>
+      </c>
+      <c r="H31" s="7" t="inlineStr">
+        <is>
+          <t>PSU:36 BB:5 RI:35</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="22" customHeight="1">
+      <c r="A32" s="8" t="n">
+        <v>28</v>
+      </c>
+      <c r="B32" s="9" t="inlineStr">
+        <is>
+          <t>OPCH</t>
+        </is>
+      </c>
+      <c r="C32" s="10" t="inlineStr">
+        <is>
+          <t>Option Care Health, Inc.</t>
+        </is>
+      </c>
+      <c r="D32" s="8" t="n">
+        <v>6</v>
+      </c>
+      <c r="E32" s="17" t="n">
+        <v>4.26</v>
+      </c>
+      <c r="F32" s="8" t="n">
+        <v>4</v>
+      </c>
+      <c r="G32" s="10" t="inlineStr">
+        <is>
+          <t>Healthcare</t>
+        </is>
+      </c>
+      <c r="H32" s="10" t="inlineStr">
+        <is>
+          <t>PSU:27 BB:5 C10:-1 F4:23 RI:52</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="22" customHeight="1">
+      <c r="A33" s="5" t="n">
+        <v>29</v>
+      </c>
+      <c r="B33" s="6" t="inlineStr">
+        <is>
+          <t>MMS</t>
+        </is>
+      </c>
+      <c r="C33" s="7" t="inlineStr">
+        <is>
+          <t>Maximus, Inc.</t>
+        </is>
+      </c>
+      <c r="D33" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="E33" s="16" t="n">
+        <v>4.182</v>
+      </c>
+      <c r="F33" s="21" t="n">
+        <v>106</v>
+      </c>
+      <c r="G33" s="7" t="inlineStr">
+        <is>
+          <t>Industrials</t>
+        </is>
+      </c>
+      <c r="H33" s="7" t="inlineStr">
+        <is>
+          <t>PSU:42 BB:5 RI:53 SS:26</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="22" customHeight="1">
+      <c r="A34" s="8" t="n">
+        <v>30</v>
+      </c>
+      <c r="B34" s="9" t="inlineStr">
+        <is>
+          <t>GTM</t>
+        </is>
+      </c>
+      <c r="C34" s="10" t="inlineStr">
+        <is>
+          <t>ZoomInfo Technologies Inc.</t>
+        </is>
+      </c>
+      <c r="D34" s="8" t="n">
+        <v>6</v>
+      </c>
+      <c r="E34" s="17" t="n">
+        <v>4.056</v>
+      </c>
+      <c r="F34" s="8" t="n">
+        <v>-3</v>
+      </c>
+      <c r="G34" s="10" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="H34" s="10" t="inlineStr">
+        <is>
+          <t>PSU:36 BB:5 C10:-4 RI:66 SS:20</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="28" customHeight="1">
+      <c r="A36" s="11" t="inlineStr">
+        <is>
+          <t>'Lift vs val' shows how many positions a name climbs when valuation is excluded. A large positive lift means the name is structurally strong but is being penalised by the valuation layer -- likely either missing yfinance overlay or trading at multiples outside our discount zones (P/B&gt;1.5, P/E&gt;15, EV/EBITDA&gt;10). The 26 emergent names (consensus_emergent_noval.csv) are gap-fill priorities.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="3">
+    <mergeCell ref="A36:H36"/>
+    <mergeCell ref="A2:H2"/>
+    <mergeCell ref="A1:H1"/>
+  </mergeCells>
+  <printOptions horizontalCentered="0"/>
+  <pageMargins left="0.5" right="0.5" top="0.6" bottom="0.6" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
   <dimension ref="A1:J46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -16039,7 +16649,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -18297,7 +18907,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -20093,7 +20703,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -22653,7 +23263,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -23255,7 +23865,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -24067,7 +24677,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>

--- a/MOST_ASYMMETRIC.xlsx
+++ b/MOST_ASYMMETRIC.xlsx
@@ -21,19 +21,20 @@
     <sheet name="Mechanism Gates" sheetId="12" state="visible" r:id="rId12"/>
     <sheet name="Re-Rate Catalysts" sheetId="13" state="visible" r:id="rId13"/>
     <sheet name="Re-Rate Backtest" sheetId="14" state="visible" r:id="rId14"/>
-    <sheet name="Winners Study" sheetId="15" state="visible" r:id="rId15"/>
-    <sheet name="Asymmetry Assembly" sheetId="16" state="visible" r:id="rId16"/>
-    <sheet name="Distressed Stub Progress" sheetId="17" state="visible" r:id="rId17"/>
-    <sheet name="Hidden Asset Realisation" sheetId="18" state="visible" r:id="rId18"/>
-    <sheet name="UK Capital Events" sheetId="19" state="visible" r:id="rId19"/>
-    <sheet name="Without Valuation" sheetId="20" state="visible" r:id="rId20"/>
-    <sheet name="Recent 30d" sheetId="21" state="visible" r:id="rId21"/>
-    <sheet name="Foreign Markets" sheetId="22" state="visible" r:id="rId22"/>
-    <sheet name="Turnaround Signal" sheetId="23" state="visible" r:id="rId23"/>
-    <sheet name="Single-Measure Best" sheetId="24" state="visible" r:id="rId24"/>
-    <sheet name="Layer Correlation" sheetId="25" state="visible" r:id="rId25"/>
-    <sheet name="Coverage &amp; Tiers" sheetId="26" state="visible" r:id="rId26"/>
-    <sheet name="Methodology" sheetId="27" state="visible" r:id="rId27"/>
+    <sheet name="Tail Odds" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet name="Winners Study" sheetId="16" state="visible" r:id="rId16"/>
+    <sheet name="Asymmetry Assembly" sheetId="17" state="visible" r:id="rId17"/>
+    <sheet name="Distressed Stub Progress" sheetId="18" state="visible" r:id="rId18"/>
+    <sheet name="Hidden Asset Realisation" sheetId="19" state="visible" r:id="rId19"/>
+    <sheet name="UK Capital Events" sheetId="20" state="visible" r:id="rId20"/>
+    <sheet name="Without Valuation" sheetId="21" state="visible" r:id="rId21"/>
+    <sheet name="Recent 30d" sheetId="22" state="visible" r:id="rId22"/>
+    <sheet name="Foreign Markets" sheetId="23" state="visible" r:id="rId23"/>
+    <sheet name="Turnaround Signal" sheetId="24" state="visible" r:id="rId24"/>
+    <sheet name="Single-Measure Best" sheetId="25" state="visible" r:id="rId25"/>
+    <sheet name="Layer Correlation" sheetId="26" state="visible" r:id="rId26"/>
+    <sheet name="Coverage &amp; Tiers" sheetId="27" state="visible" r:id="rId27"/>
+    <sheet name="Methodology" sheetId="28" state="visible" r:id="rId28"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Titles" localSheetId="0">'Contents'!$1:$4</definedName>
@@ -50,19 +51,20 @@
     <definedName name="_xlnm.Print_Titles" localSheetId="11">'Mechanism Gates'!$1:$4</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="12">'Re-Rate Catalysts'!$1:$4</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="13">'Re-Rate Backtest'!$1:$4</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="14">'Winners Study'!$1:$4</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="15">'Asymmetry Assembly'!$1:$4</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="16">'Distressed Stub Progress'!$1:$4</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="17">'Hidden Asset Realisation'!$1:$4</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="18">'UK Capital Events'!$1:$4</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="19">'Without Valuation'!$1:$4</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="20">'Recent 30d'!$1:$4</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="21">'Foreign Markets'!$1:$4</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="22">'Turnaround Signal'!$1:$4</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="23">'Single-Measure Best'!$1:$4</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="24">'Layer Correlation'!$1:$4</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="25">'Coverage &amp; Tiers'!$1:$4</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="26">'Methodology'!$1:$4</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="14">'Tail Odds'!$1:$4</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="15">'Winners Study'!$1:$4</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="16">'Asymmetry Assembly'!$1:$4</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="17">'Distressed Stub Progress'!$1:$4</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="18">'Hidden Asset Realisation'!$1:$4</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="19">'UK Capital Events'!$1:$4</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="20">'Without Valuation'!$1:$4</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="21">'Recent 30d'!$1:$4</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="22">'Foreign Markets'!$1:$4</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="23">'Turnaround Signal'!$1:$4</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="24">'Single-Measure Best'!$1:$4</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="25">'Layer Correlation'!$1:$4</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="26">'Coverage &amp; Tiers'!$1:$4</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="27">'Methodology'!$1:$4</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -601,7 +603,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:C32"/>
+  <dimension ref="A1:C33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -844,12 +846,12 @@
       </c>
       <c r="B18" s="9" t="inlineStr">
         <is>
-          <t>Winners Study</t>
+          <t>Tail Odds</t>
         </is>
       </c>
       <c r="C18" s="10" t="inlineStr">
         <is>
-          <t>What realized 1-year re-raters had in common — feature/sector lifts, with the pre-move-data caveat.</t>
+          <t>Candidates ranked by measured probability of a right-tail outcome; the features that raise the odds.</t>
         </is>
       </c>
     </row>
@@ -859,12 +861,12 @@
       </c>
       <c r="B19" s="6" t="inlineStr">
         <is>
-          <t>Asymmetry Assembly</t>
+          <t>Winners Study</t>
         </is>
       </c>
       <c r="C19" s="7" t="inlineStr">
         <is>
-          <t>PSIX-recipe conjunction: cheap + inflection + leverage + insider co-occurring.</t>
+          <t>What realized 1-year re-raters had in common — feature/sector lifts, with the pre-move-data caveat.</t>
         </is>
       </c>
     </row>
@@ -874,12 +876,12 @@
       </c>
       <c r="B20" s="9" t="inlineStr">
         <is>
-          <t>Distressed Stub Progress</t>
+          <t>Asymmetry Assembly</t>
         </is>
       </c>
       <c r="C20" s="10" t="inlineStr">
         <is>
-          <t>Finality-gated capital-structure value-unlock events, waterfall-scored.</t>
+          <t>PSIX-recipe conjunction: cheap + inflection + leverage + insider co-occurring.</t>
         </is>
       </c>
     </row>
@@ -889,12 +891,12 @@
       </c>
       <c r="B21" s="6" t="inlineStr">
         <is>
-          <t>Hidden Asset Realisation</t>
+          <t>Distressed Stub Progress</t>
         </is>
       </c>
       <c r="C21" s="7" t="inlineStr">
         <is>
-          <t>Spectrum/rights/RE inside levered stubs with mandatory-prepay debt sweeps (SSP-type).</t>
+          <t>Finality-gated capital-structure value-unlock events, waterfall-scored.</t>
         </is>
       </c>
     </row>
@@ -904,12 +906,12 @@
       </c>
       <c r="B22" s="9" t="inlineStr">
         <is>
-          <t>UK Capital Events</t>
+          <t>Hidden Asset Realisation</t>
         </is>
       </c>
       <c r="C22" s="10" t="inlineStr">
         <is>
-          <t>UK RNS revealed-preference &amp; distressed monitor (separate universe; funds filtered).</t>
+          <t>Spectrum/rights/RE inside levered stubs with mandatory-prepay debt sweeps (SSP-type).</t>
         </is>
       </c>
     </row>
@@ -919,12 +921,12 @@
       </c>
       <c r="B23" s="6" t="inlineStr">
         <is>
-          <t>Without Valuation</t>
+          <t>UK Capital Events</t>
         </is>
       </c>
       <c r="C23" s="7" t="inlineStr">
         <is>
-          <t>Parallel ranking excluding the valuation leg.</t>
+          <t>UK RNS revealed-preference &amp; distressed monitor (separate universe; funds filtered).</t>
         </is>
       </c>
     </row>
@@ -934,12 +936,12 @@
       </c>
       <c r="B24" s="9" t="inlineStr">
         <is>
-          <t>Recent 30d</t>
+          <t>Without Valuation</t>
         </is>
       </c>
       <c r="C24" s="10" t="inlineStr">
         <is>
-          <t>Material incentive events disclosed in the last 30 days.</t>
+          <t>Parallel ranking excluding the valuation leg.</t>
         </is>
       </c>
     </row>
@@ -949,12 +951,12 @@
       </c>
       <c r="B25" s="6" t="inlineStr">
         <is>
-          <t>Foreign Markets</t>
+          <t>Recent 30d</t>
         </is>
       </c>
       <c r="C25" s="7" t="inlineStr">
         <is>
-          <t>Japan TSE PBR&lt;1, Korea Value-Up, UK schemes.</t>
+          <t>Material incentive events disclosed in the last 30 days.</t>
         </is>
       </c>
     </row>
@@ -964,12 +966,12 @@
       </c>
       <c r="B26" s="9" t="inlineStr">
         <is>
-          <t>Turnaround Signal</t>
+          <t>Foreign Markets</t>
         </is>
       </c>
       <c r="C26" s="10" t="inlineStr">
         <is>
-          <t>Bollenbach pattern: turnaround talent into distress.</t>
+          <t>Japan TSE PBR&lt;1, Korea Value-Up, UK schemes.</t>
         </is>
       </c>
     </row>
@@ -979,12 +981,12 @@
       </c>
       <c r="B27" s="6" t="inlineStr">
         <is>
-          <t>Single-Measure Best</t>
+          <t>Turnaround Signal</t>
         </is>
       </c>
       <c r="C27" s="7" t="inlineStr">
         <is>
-          <t>Best in class on each individual signal.</t>
+          <t>Bollenbach pattern: turnaround talent into distress.</t>
         </is>
       </c>
     </row>
@@ -994,12 +996,12 @@
       </c>
       <c r="B28" s="9" t="inlineStr">
         <is>
-          <t>Layer Correlation</t>
+          <t>Single-Measure Best</t>
         </is>
       </c>
       <c r="C28" s="10" t="inlineStr">
         <is>
-          <t>Pairwise layer correlation and effective independence.</t>
+          <t>Best in class on each individual signal.</t>
         </is>
       </c>
     </row>
@@ -1009,12 +1011,12 @@
       </c>
       <c r="B29" s="6" t="inlineStr">
         <is>
-          <t>Coverage &amp; Tiers</t>
+          <t>Layer Correlation</t>
         </is>
       </c>
       <c r="C29" s="7" t="inlineStr">
         <is>
-          <t>Live per-layer coverage, data age, firing distribution.</t>
+          <t>Pairwise layer correlation and effective independence.</t>
         </is>
       </c>
     </row>
@@ -1024,17 +1026,32 @@
       </c>
       <c r="B30" s="9" t="inlineStr">
         <is>
+          <t>Coverage &amp; Tiers</t>
+        </is>
+      </c>
+      <c r="C30" s="10" t="inlineStr">
+        <is>
+          <t>Live per-layer coverage, data age, firing distribution.</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="16" customHeight="1">
+      <c r="A31" s="5" t="n">
+        <v>27</v>
+      </c>
+      <c r="B31" s="6" t="inlineStr">
+        <is>
           <t>Methodology</t>
         </is>
       </c>
-      <c r="C30" s="10" t="inlineStr">
+      <c r="C31" s="7" t="inlineStr">
         <is>
           <t>How the composite is built, step by step.</t>
         </is>
       </c>
     </row>
-    <row r="32" ht="28" customHeight="1">
-      <c r="A32" s="11" t="inlineStr">
+    <row r="33" ht="28" customHeight="1">
+      <c r="A33" s="11" t="inlineStr">
         <is>
           <t>Generated by build_most_asymmetric_xlsx.py from the live consensus on disk. Every figure in this workbook is computed at build time; nothing is hardcoded. Single typeface (Times New Roman, 10pt); hierarchy by weight and rule only.</t>
         </is>
@@ -1043,7 +1060,7 @@
   </sheetData>
   <mergeCells count="3">
     <mergeCell ref="A1:C1"/>
-    <mergeCell ref="A32:C32"/>
+    <mergeCell ref="A33:C33"/>
     <mergeCell ref="A2:C2"/>
   </mergeCells>
   <printOptions horizontalCentered="0"/>
@@ -8369,6 +8386,1463 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
+  <dimension ref="A1:F58"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="9" customWidth="1" min="1" max="1"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
+    <col width="8" customWidth="1" min="3" max="3"/>
+    <col width="8" customWidth="1" min="4" max="4"/>
+    <col width="7" customWidth="1" min="5" max="5"/>
+    <col width="40" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="26" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Tail Odds — tilting the shortlist toward the right tail</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="18" customHeight="1">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Base rate of a &gt;=+50%/12m outcome among corporate-action events is 15%. Names are re-scored by the historically-measured lifts of the features they carry (catalyst, sector, size, drawdown, range position), combined in shrunk log-odds. Directional, not a calibrated probability.</t>
+        </is>
+      </c>
+      <c r="B2" s="3" t="n"/>
+      <c r="C2" s="3" t="n"/>
+      <c r="D2" s="3" t="n"/>
+      <c r="E2" s="3" t="n"/>
+      <c r="F2" s="3" t="n"/>
+    </row>
+    <row r="3" ht="8" customHeight="1"/>
+    <row r="4" ht="18" customHeight="1">
+      <c r="A4" s="15" t="inlineStr">
+        <is>
+          <t>Ticker</t>
+        </is>
+      </c>
+      <c r="B4" s="15" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="C4" s="4" t="inlineStr">
+        <is>
+          <t>Tail p</t>
+        </is>
+      </c>
+      <c r="D4" s="4" t="inlineStr">
+        <is>
+          <t>xMult</t>
+        </is>
+      </c>
+      <c r="E4" s="4" t="inlineStr">
+        <is>
+          <t>Ratio</t>
+        </is>
+      </c>
+      <c r="F4" s="4" t="inlineStr">
+        <is>
+          <t>Tail drivers (lift)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="22" customHeight="1">
+      <c r="A5" s="6" t="inlineStr">
+        <is>
+          <t>SES</t>
+        </is>
+      </c>
+      <c r="B5" s="7" t="inlineStr">
+        <is>
+          <t>SES AI Corporation</t>
+        </is>
+      </c>
+      <c r="C5" s="16" t="n">
+        <v>40</v>
+      </c>
+      <c r="D5" s="7" t="inlineStr">
+        <is>
+          <t>20.1x</t>
+        </is>
+      </c>
+      <c r="E5" s="7" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="F5" s="7" t="inlineStr">
+        <is>
+          <t>catalyst=SALE_OF_COMPANY, sector=Consume</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="22" customHeight="1">
+      <c r="A6" s="9" t="inlineStr">
+        <is>
+          <t>CNXC</t>
+        </is>
+      </c>
+      <c r="B6" s="10" t="inlineStr">
+        <is>
+          <t>Concentrix Corporati</t>
+        </is>
+      </c>
+      <c r="C6" s="17" t="n">
+        <v>39</v>
+      </c>
+      <c r="D6" s="10" t="inlineStr">
+        <is>
+          <t>16.9x</t>
+        </is>
+      </c>
+      <c r="E6" s="17" t="n">
+        <v>34.9</v>
+      </c>
+      <c r="F6" s="10" t="inlineStr">
+        <is>
+          <t>catalyst=SPINOFF, sector=Technology, siz</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="22" customHeight="1">
+      <c r="A7" s="6" t="inlineStr">
+        <is>
+          <t>CTMX</t>
+        </is>
+      </c>
+      <c r="B7" s="7" t="inlineStr">
+        <is>
+          <t>CytomX Therapeutics,</t>
+        </is>
+      </c>
+      <c r="C7" s="16" t="n">
+        <v>35</v>
+      </c>
+      <c r="D7" s="7" t="inlineStr">
+        <is>
+          <t>12.4x</t>
+        </is>
+      </c>
+      <c r="E7" s="7" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="F7" s="7" t="inlineStr">
+        <is>
+          <t>catalyst=SALE_OF_COMPANY, size=small, dr</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="22" customHeight="1">
+      <c r="A8" s="9" t="inlineStr">
+        <is>
+          <t>WVE</t>
+        </is>
+      </c>
+      <c r="B8" s="10" t="inlineStr">
+        <is>
+          <t>Wave Life Sciences L</t>
+        </is>
+      </c>
+      <c r="C8" s="17" t="n">
+        <v>35</v>
+      </c>
+      <c r="D8" s="10" t="inlineStr">
+        <is>
+          <t>12.4x</t>
+        </is>
+      </c>
+      <c r="E8" s="17" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F8" s="10" t="inlineStr">
+        <is>
+          <t>catalyst=SALE_OF_COMPANY, size=small, dr</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="22" customHeight="1">
+      <c r="A9" s="6" t="inlineStr">
+        <is>
+          <t>ANGX</t>
+        </is>
+      </c>
+      <c r="B9" s="7" t="inlineStr">
+        <is>
+          <t>Angel Studios, Inc.</t>
+        </is>
+      </c>
+      <c r="C9" s="16" t="n">
+        <v>35</v>
+      </c>
+      <c r="D9" s="7" t="inlineStr">
+        <is>
+          <t>12.1x</t>
+        </is>
+      </c>
+      <c r="E9" s="7" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="F9" s="7" t="inlineStr">
+        <is>
+          <t>catalyst=SALE_OF_COMPANY, size=small, dr</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="22" customHeight="1">
+      <c r="A10" s="9" t="inlineStr">
+        <is>
+          <t>DFH</t>
+        </is>
+      </c>
+      <c r="B10" s="10" t="inlineStr">
+        <is>
+          <t>Dream Finders Homes,</t>
+        </is>
+      </c>
+      <c r="C10" s="17" t="n">
+        <v>35</v>
+      </c>
+      <c r="D10" s="10" t="inlineStr">
+        <is>
+          <t>12.1x</t>
+        </is>
+      </c>
+      <c r="E10" s="17" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="F10" s="10" t="inlineStr">
+        <is>
+          <t>sector=Consumer Cyclical, size=small, dr</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="22" customHeight="1">
+      <c r="A11" s="6" t="inlineStr">
+        <is>
+          <t>CWH</t>
+        </is>
+      </c>
+      <c r="B11" s="7" t="inlineStr">
+        <is>
+          <t>Camping World Holdin</t>
+        </is>
+      </c>
+      <c r="C11" s="16" t="n">
+        <v>35</v>
+      </c>
+      <c r="D11" s="7" t="inlineStr">
+        <is>
+          <t>12.1x</t>
+        </is>
+      </c>
+      <c r="E11" s="16" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="F11" s="7" t="inlineStr">
+        <is>
+          <t>sector=Consumer Cyclical, size=small, dr</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="22" customHeight="1">
+      <c r="A12" s="9" t="inlineStr">
+        <is>
+          <t>OPTU</t>
+        </is>
+      </c>
+      <c r="B12" s="10" t="inlineStr">
+        <is>
+          <t>Optimum Communicatio</t>
+        </is>
+      </c>
+      <c r="C12" s="17" t="n">
+        <v>35</v>
+      </c>
+      <c r="D12" s="10" t="inlineStr">
+        <is>
+          <t>12.1x</t>
+        </is>
+      </c>
+      <c r="E12" s="17" t="n">
+        <v>3</v>
+      </c>
+      <c r="F12" s="10" t="inlineStr">
+        <is>
+          <t>catalyst=SALE_OF_COMPANY, size=small, dr</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="22" customHeight="1">
+      <c r="A13" s="6" t="inlineStr">
+        <is>
+          <t>MNRO</t>
+        </is>
+      </c>
+      <c r="B13" s="7" t="inlineStr">
+        <is>
+          <t>Monro, Inc.</t>
+        </is>
+      </c>
+      <c r="C13" s="16" t="n">
+        <v>34</v>
+      </c>
+      <c r="D13" s="7" t="inlineStr">
+        <is>
+          <t>11.0x</t>
+        </is>
+      </c>
+      <c r="E13" s="16" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="F13" s="7" t="inlineStr">
+        <is>
+          <t>catalyst=SALE_OF_COMPANY, sector=Consume</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="22" customHeight="1">
+      <c r="A14" s="9" t="inlineStr">
+        <is>
+          <t>LE</t>
+        </is>
+      </c>
+      <c r="B14" s="10" t="inlineStr">
+        <is>
+          <t>Lands' End, Inc.</t>
+        </is>
+      </c>
+      <c r="C14" s="17" t="n">
+        <v>34</v>
+      </c>
+      <c r="D14" s="10" t="inlineStr">
+        <is>
+          <t>11.0x</t>
+        </is>
+      </c>
+      <c r="E14" s="17" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="F14" s="10" t="inlineStr">
+        <is>
+          <t>catalyst=SALE_OF_COMPANY, sector=Consume</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="22" customHeight="1">
+      <c r="A15" s="6" t="inlineStr">
+        <is>
+          <t>LUCK</t>
+        </is>
+      </c>
+      <c r="B15" s="7" t="inlineStr">
+        <is>
+          <t>LUCKY STRIKE ENTERTA</t>
+        </is>
+      </c>
+      <c r="C15" s="16" t="n">
+        <v>34</v>
+      </c>
+      <c r="D15" s="7" t="inlineStr">
+        <is>
+          <t>11.0x</t>
+        </is>
+      </c>
+      <c r="E15" s="7" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="F15" s="7" t="inlineStr">
+        <is>
+          <t>catalyst=SALE_OF_COMPANY, sector=Consume</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="22" customHeight="1">
+      <c r="A16" s="9" t="inlineStr">
+        <is>
+          <t>VERI</t>
+        </is>
+      </c>
+      <c r="B16" s="10" t="inlineStr">
+        <is>
+          <t>Veritone, Inc.</t>
+        </is>
+      </c>
+      <c r="C16" s="17" t="n">
+        <v>34</v>
+      </c>
+      <c r="D16" s="10" t="inlineStr">
+        <is>
+          <t>10.8x</t>
+        </is>
+      </c>
+      <c r="E16" s="17" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="F16" s="10" t="inlineStr">
+        <is>
+          <t>catalyst=SALE_OF_COMPANY, sector=Technol</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="22" customHeight="1">
+      <c r="A17" s="6" t="inlineStr">
+        <is>
+          <t>KPLT</t>
+        </is>
+      </c>
+      <c r="B17" s="7" t="inlineStr">
+        <is>
+          <t>Katapult Holdings, I</t>
+        </is>
+      </c>
+      <c r="C17" s="16" t="n">
+        <v>34</v>
+      </c>
+      <c r="D17" s="7" t="inlineStr">
+        <is>
+          <t>10.8x</t>
+        </is>
+      </c>
+      <c r="E17" s="16" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="F17" s="7" t="inlineStr">
+        <is>
+          <t>catalyst=SALE_OF_COMPANY, sector=Technol</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="22" customHeight="1">
+      <c r="A18" s="9" t="inlineStr">
+        <is>
+          <t>TAOX</t>
+        </is>
+      </c>
+      <c r="B18" s="10" t="inlineStr">
+        <is>
+          <t>Tao Synergies Inc.</t>
+        </is>
+      </c>
+      <c r="C18" s="17" t="n">
+        <v>34</v>
+      </c>
+      <c r="D18" s="10" t="inlineStr">
+        <is>
+          <t>10.8x</t>
+        </is>
+      </c>
+      <c r="E18" s="17" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="F18" s="10" t="inlineStr">
+        <is>
+          <t>catalyst=SALE_OF_COMPANY, sector=Technol</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="22" customHeight="1">
+      <c r="A19" s="6" t="inlineStr">
+        <is>
+          <t>AIFF</t>
+        </is>
+      </c>
+      <c r="B19" s="7" t="inlineStr">
+        <is>
+          <t>Firefly Neuroscience</t>
+        </is>
+      </c>
+      <c r="C19" s="16" t="n">
+        <v>34</v>
+      </c>
+      <c r="D19" s="7" t="inlineStr">
+        <is>
+          <t>10.8x</t>
+        </is>
+      </c>
+      <c r="E19" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="F19" s="7" t="inlineStr">
+        <is>
+          <t>catalyst=SALE_OF_COMPANY, sector=Technol</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="22" customHeight="1">
+      <c r="A20" s="9" t="inlineStr">
+        <is>
+          <t>LIDR</t>
+        </is>
+      </c>
+      <c r="B20" s="10" t="inlineStr">
+        <is>
+          <t>AEye, Inc.</t>
+        </is>
+      </c>
+      <c r="C20" s="17" t="n">
+        <v>34</v>
+      </c>
+      <c r="D20" s="10" t="inlineStr">
+        <is>
+          <t>10.8x</t>
+        </is>
+      </c>
+      <c r="E20" s="17" t="n">
+        <v>6.9</v>
+      </c>
+      <c r="F20" s="10" t="inlineStr">
+        <is>
+          <t>catalyst=SALE_OF_COMPANY, sector=Technol</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="22" customHeight="1">
+      <c r="A21" s="6" t="inlineStr">
+        <is>
+          <t>NTGR</t>
+        </is>
+      </c>
+      <c r="B21" s="7" t="inlineStr">
+        <is>
+          <t>NETGEAR, Inc.</t>
+        </is>
+      </c>
+      <c r="C21" s="16" t="n">
+        <v>32</v>
+      </c>
+      <c r="D21" s="7" t="inlineStr">
+        <is>
+          <t>9.2x</t>
+        </is>
+      </c>
+      <c r="E21" s="16" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="F21" s="7" t="inlineStr">
+        <is>
+          <t>catalyst=SPINOFF, sector=Technology, siz</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="22" customHeight="1">
+      <c r="A22" s="9" t="inlineStr">
+        <is>
+          <t>VYX</t>
+        </is>
+      </c>
+      <c r="B22" s="10" t="inlineStr">
+        <is>
+          <t>NCR Voyix Corporatio</t>
+        </is>
+      </c>
+      <c r="C22" s="17" t="n">
+        <v>32</v>
+      </c>
+      <c r="D22" s="10" t="inlineStr">
+        <is>
+          <t>9.2x</t>
+        </is>
+      </c>
+      <c r="E22" s="17" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="F22" s="10" t="inlineStr">
+        <is>
+          <t>catalyst=SPINOFF, sector=Technology, siz</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="22" customHeight="1">
+      <c r="A23" s="6" t="inlineStr">
+        <is>
+          <t>DXLG</t>
+        </is>
+      </c>
+      <c r="B23" s="7" t="inlineStr">
+        <is>
+          <t>Destination XL Group</t>
+        </is>
+      </c>
+      <c r="C23" s="16" t="n">
+        <v>32</v>
+      </c>
+      <c r="D23" s="7" t="inlineStr">
+        <is>
+          <t>9.0x</t>
+        </is>
+      </c>
+      <c r="E23" s="16" t="n">
+        <v>60</v>
+      </c>
+      <c r="F23" s="7" t="inlineStr">
+        <is>
+          <t>catalyst=SALE_OF_COMPANY, sector=Consume</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="22" customHeight="1">
+      <c r="A24" s="9" t="inlineStr">
+        <is>
+          <t>DTI</t>
+        </is>
+      </c>
+      <c r="B24" s="10" t="inlineStr">
+        <is>
+          <t>Drilling Tools Inter</t>
+        </is>
+      </c>
+      <c r="C24" s="17" t="n">
+        <v>32</v>
+      </c>
+      <c r="D24" s="10" t="inlineStr">
+        <is>
+          <t>9.0x</t>
+        </is>
+      </c>
+      <c r="E24" s="17" t="n">
+        <v>8.300000000000001</v>
+      </c>
+      <c r="F24" s="10" t="inlineStr">
+        <is>
+          <t>catalyst=SALE_OF_COMPANY, sector=Energy,</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="22" customHeight="1">
+      <c r="A25" s="6" t="inlineStr">
+        <is>
+          <t>WKHS</t>
+        </is>
+      </c>
+      <c r="B25" s="7" t="inlineStr">
+        <is>
+          <t>Workhorse Group, Inc</t>
+        </is>
+      </c>
+      <c r="C25" s="16" t="n">
+        <v>32</v>
+      </c>
+      <c r="D25" s="7" t="inlineStr">
+        <is>
+          <t>9.0x</t>
+        </is>
+      </c>
+      <c r="E25" s="16" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="F25" s="7" t="inlineStr">
+        <is>
+          <t>catalyst=SALE_OF_COMPANY, sector=Consume</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="22" customHeight="1">
+      <c r="A26" s="9" t="inlineStr">
+        <is>
+          <t>GDRX</t>
+        </is>
+      </c>
+      <c r="B26" s="10" t="inlineStr">
+        <is>
+          <t>GoodRx Holdings, Inc</t>
+        </is>
+      </c>
+      <c r="C26" s="17" t="n">
+        <v>32</v>
+      </c>
+      <c r="D26" s="10" t="inlineStr">
+        <is>
+          <t>8.6x</t>
+        </is>
+      </c>
+      <c r="E26" s="17" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="F26" s="10" t="inlineStr">
+        <is>
+          <t>catalyst=SPINOFF, size=small, drawdown_1</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="22" customHeight="1">
+      <c r="A27" s="6" t="inlineStr">
+        <is>
+          <t>GRPN</t>
+        </is>
+      </c>
+      <c r="B27" s="7" t="inlineStr">
+        <is>
+          <t>Groupon, Inc.</t>
+        </is>
+      </c>
+      <c r="C27" s="16" t="n">
+        <v>32</v>
+      </c>
+      <c r="D27" s="7" t="inlineStr">
+        <is>
+          <t>8.5x</t>
+        </is>
+      </c>
+      <c r="E27" s="7" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="F27" s="7" t="inlineStr">
+        <is>
+          <t>catalyst=SPINOFF, size=small, drawdown_1</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="22" customHeight="1">
+      <c r="A28" s="9" t="inlineStr">
+        <is>
+          <t>GLIBK</t>
+        </is>
+      </c>
+      <c r="B28" s="10" t="inlineStr">
+        <is>
+          <t>Liberty Capital Corp</t>
+        </is>
+      </c>
+      <c r="C28" s="17" t="n">
+        <v>32</v>
+      </c>
+      <c r="D28" s="10" t="inlineStr">
+        <is>
+          <t>8.5x</t>
+        </is>
+      </c>
+      <c r="E28" s="17" t="n">
+        <v>32.9</v>
+      </c>
+      <c r="F28" s="10" t="inlineStr">
+        <is>
+          <t>catalyst=SPINOFF, size=small, drawdown_1</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="22" customHeight="1">
+      <c r="A29" s="6" t="inlineStr">
+        <is>
+          <t>AHT</t>
+        </is>
+      </c>
+      <c r="B29" s="7" t="inlineStr">
+        <is>
+          <t>Ashford Hospitality</t>
+        </is>
+      </c>
+      <c r="C29" s="16" t="n">
+        <v>32</v>
+      </c>
+      <c r="D29" s="7" t="inlineStr">
+        <is>
+          <t>8.4x</t>
+        </is>
+      </c>
+      <c r="E29" s="16" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="F29" s="7" t="inlineStr">
+        <is>
+          <t>catalyst=SPINOFF, sector=Real Estate, si</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="22" customHeight="1">
+      <c r="A30" s="9" t="inlineStr">
+        <is>
+          <t>DXC</t>
+        </is>
+      </c>
+      <c r="B30" s="10" t="inlineStr">
+        <is>
+          <t>DXC Technology Compa</t>
+        </is>
+      </c>
+      <c r="C30" s="17" t="n">
+        <v>31</v>
+      </c>
+      <c r="D30" s="10" t="inlineStr">
+        <is>
+          <t>7.9x</t>
+        </is>
+      </c>
+      <c r="E30" s="17" t="n">
+        <v>30</v>
+      </c>
+      <c r="F30" s="10" t="inlineStr">
+        <is>
+          <t>sector=Technology, size=small, drawdown_</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="22" customHeight="1">
+      <c r="A31" s="6" t="inlineStr">
+        <is>
+          <t>VTS</t>
+        </is>
+      </c>
+      <c r="B31" s="7" t="inlineStr">
+        <is>
+          <t>Vitesse Energy, Inc.</t>
+        </is>
+      </c>
+      <c r="C31" s="16" t="n">
+        <v>31</v>
+      </c>
+      <c r="D31" s="7" t="inlineStr">
+        <is>
+          <t>7.7x</t>
+        </is>
+      </c>
+      <c r="E31" s="16" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="F31" s="7" t="inlineStr">
+        <is>
+          <t>catalyst=SPINOFF, sector=Energy, size=sm</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="22" customHeight="1">
+      <c r="A32" s="9" t="inlineStr">
+        <is>
+          <t>JTAI</t>
+        </is>
+      </c>
+      <c r="B32" s="10" t="inlineStr">
+        <is>
+          <t>Jet.AI Inc.</t>
+        </is>
+      </c>
+      <c r="C32" s="17" t="n">
+        <v>30</v>
+      </c>
+      <c r="D32" s="10" t="inlineStr">
+        <is>
+          <t>7.5x</t>
+        </is>
+      </c>
+      <c r="E32" s="17" t="n">
+        <v>60</v>
+      </c>
+      <c r="F32" s="10" t="inlineStr">
+        <is>
+          <t>catalyst=SPINOFF, sector=Technology, siz</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="22" customHeight="1">
+      <c r="A33" s="6" t="inlineStr">
+        <is>
+          <t>GPRO</t>
+        </is>
+      </c>
+      <c r="B33" s="7" t="inlineStr">
+        <is>
+          <t>GoPro, Inc.</t>
+        </is>
+      </c>
+      <c r="C33" s="16" t="n">
+        <v>30</v>
+      </c>
+      <c r="D33" s="7" t="inlineStr">
+        <is>
+          <t>7.5x</t>
+        </is>
+      </c>
+      <c r="E33" s="16" t="n">
+        <v>3</v>
+      </c>
+      <c r="F33" s="7" t="inlineStr">
+        <is>
+          <t>catalyst=SPINOFF, sector=Technology, siz</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="22" customHeight="1">
+      <c r="A34" s="9" t="inlineStr">
+        <is>
+          <t>LMRI</t>
+        </is>
+      </c>
+      <c r="B34" s="10" t="inlineStr">
+        <is>
+          <t>Lumexa Imaging Holdi</t>
+        </is>
+      </c>
+      <c r="C34" s="17" t="n">
+        <v>30</v>
+      </c>
+      <c r="D34" s="10" t="inlineStr">
+        <is>
+          <t>7.5x</t>
+        </is>
+      </c>
+      <c r="E34" s="17" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="F34" s="10" t="inlineStr">
+        <is>
+          <t>size=small, drawdown_12m=deep(&lt;-50%), ra</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="22" customHeight="1">
+      <c r="A35" s="6" t="inlineStr">
+        <is>
+          <t>KD</t>
+        </is>
+      </c>
+      <c r="B35" s="7" t="inlineStr">
+        <is>
+          <t>Kyndryl Holdings, In</t>
+        </is>
+      </c>
+      <c r="C35" s="16" t="n">
+        <v>30</v>
+      </c>
+      <c r="D35" s="7" t="inlineStr">
+        <is>
+          <t>6.9x</t>
+        </is>
+      </c>
+      <c r="E35" s="16" t="n">
+        <v>2</v>
+      </c>
+      <c r="F35" s="7" t="inlineStr">
+        <is>
+          <t>catalyst=SPINOFF, sector=Technology, dra</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="22" customHeight="1">
+      <c r="A36" s="9" t="inlineStr">
+        <is>
+          <t>SENS</t>
+        </is>
+      </c>
+      <c r="B36" s="10" t="inlineStr">
+        <is>
+          <t>Senseonics Holdings,</t>
+        </is>
+      </c>
+      <c r="C36" s="17" t="n">
+        <v>29</v>
+      </c>
+      <c r="D36" s="10" t="inlineStr">
+        <is>
+          <t>6.7x</t>
+        </is>
+      </c>
+      <c r="E36" s="10" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="F36" s="10" t="inlineStr">
+        <is>
+          <t>catalyst=SALE_OF_COMPANY, size=small, dr</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="22" customHeight="1">
+      <c r="A37" s="6" t="inlineStr">
+        <is>
+          <t>FLGT</t>
+        </is>
+      </c>
+      <c r="B37" s="7" t="inlineStr">
+        <is>
+          <t>Fulgent Genetics, In</t>
+        </is>
+      </c>
+      <c r="C37" s="16" t="n">
+        <v>29</v>
+      </c>
+      <c r="D37" s="7" t="inlineStr">
+        <is>
+          <t>6.7x</t>
+        </is>
+      </c>
+      <c r="E37" s="16" t="n">
+        <v>60</v>
+      </c>
+      <c r="F37" s="7" t="inlineStr">
+        <is>
+          <t>catalyst=SALE_OF_COMPANY, size=small, dr</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="22" customHeight="1">
+      <c r="A38" s="9" t="inlineStr">
+        <is>
+          <t>PAHC</t>
+        </is>
+      </c>
+      <c r="B38" s="10" t="inlineStr">
+        <is>
+          <t>Phibro Animal Health</t>
+        </is>
+      </c>
+      <c r="C38" s="17" t="n">
+        <v>29</v>
+      </c>
+      <c r="D38" s="10" t="inlineStr">
+        <is>
+          <t>6.7x</t>
+        </is>
+      </c>
+      <c r="E38" s="17" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="F38" s="10" t="inlineStr">
+        <is>
+          <t>catalyst=SALE_OF_COMPANY, size=small, dr</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="22" customHeight="1">
+      <c r="A39" s="6" t="inlineStr">
+        <is>
+          <t>GRNT</t>
+        </is>
+      </c>
+      <c r="B39" s="7" t="inlineStr">
+        <is>
+          <t>Granite Ridge Resour</t>
+        </is>
+      </c>
+      <c r="C39" s="16" t="n">
+        <v>29</v>
+      </c>
+      <c r="D39" s="7" t="inlineStr">
+        <is>
+          <t>6.6x</t>
+        </is>
+      </c>
+      <c r="E39" s="16" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="F39" s="7" t="inlineStr">
+        <is>
+          <t>sector=Energy, size=small, drawdown_12m=</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="22" customHeight="1">
+      <c r="A40" s="9" t="inlineStr">
+        <is>
+          <t>CMTL</t>
+        </is>
+      </c>
+      <c r="B40" s="10" t="inlineStr">
+        <is>
+          <t>Comtech Telecommunic</t>
+        </is>
+      </c>
+      <c r="C40" s="17" t="n">
+        <v>29</v>
+      </c>
+      <c r="D40" s="10" t="inlineStr">
+        <is>
+          <t>6.6x</t>
+        </is>
+      </c>
+      <c r="E40" s="17" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="F40" s="10" t="inlineStr">
+        <is>
+          <t>sector=Technology, size=micro, drawdown_</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="22" customHeight="1">
+      <c r="A41" s="6" t="inlineStr">
+        <is>
+          <t>AGPU</t>
+        </is>
+      </c>
+      <c r="B41" s="7" t="inlineStr">
+        <is>
+          <t>Axe Compute Inc.</t>
+        </is>
+      </c>
+      <c r="C41" s="16" t="n">
+        <v>29</v>
+      </c>
+      <c r="D41" s="7" t="inlineStr">
+        <is>
+          <t>6.6x</t>
+        </is>
+      </c>
+      <c r="E41" s="16" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="F41" s="7" t="inlineStr">
+        <is>
+          <t>sector=Technology, size=micro, drawdown_</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="22" customHeight="1">
+      <c r="A42" s="9" t="inlineStr">
+        <is>
+          <t>DEC</t>
+        </is>
+      </c>
+      <c r="B42" s="10" t="inlineStr">
+        <is>
+          <t>Diversified Energy C</t>
+        </is>
+      </c>
+      <c r="C42" s="17" t="n">
+        <v>29</v>
+      </c>
+      <c r="D42" s="10" t="inlineStr">
+        <is>
+          <t>6.6x</t>
+        </is>
+      </c>
+      <c r="E42" s="17" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="F42" s="10" t="inlineStr">
+        <is>
+          <t>sector=Energy, size=small, drawdown_12m=</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="22" customHeight="1">
+      <c r="A43" s="6" t="inlineStr">
+        <is>
+          <t>ADNT</t>
+        </is>
+      </c>
+      <c r="B43" s="7" t="inlineStr">
+        <is>
+          <t>Adient plc</t>
+        </is>
+      </c>
+      <c r="C43" s="16" t="n">
+        <v>29</v>
+      </c>
+      <c r="D43" s="7" t="inlineStr">
+        <is>
+          <t>6.6x</t>
+        </is>
+      </c>
+      <c r="E43" s="16" t="n">
+        <v>6.3</v>
+      </c>
+      <c r="F43" s="7" t="inlineStr">
+        <is>
+          <t>sector=Consumer Cyclical, size=small, dr</t>
+        </is>
+      </c>
+    </row>
+    <row r="44" ht="22" customHeight="1">
+      <c r="A44" s="9" t="inlineStr">
+        <is>
+          <t>XPRO</t>
+        </is>
+      </c>
+      <c r="B44" s="10" t="inlineStr">
+        <is>
+          <t>Expro Group Holdings</t>
+        </is>
+      </c>
+      <c r="C44" s="17" t="n">
+        <v>29</v>
+      </c>
+      <c r="D44" s="10" t="inlineStr">
+        <is>
+          <t>6.5x</t>
+        </is>
+      </c>
+      <c r="E44" s="17" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="F44" s="10" t="inlineStr">
+        <is>
+          <t>catalyst=SALE_OF_COMPANY, sector=Energy,</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="12" t="inlineStr">
+        <is>
+          <t>WHAT RAISES TAIL ODDS (historical lift vs 15% base)</t>
+        </is>
+      </c>
+    </row>
+    <row r="47" ht="18" customHeight="1">
+      <c r="A47" s="4" t="inlineStr">
+        <is>
+          <t>Feature = bin</t>
+        </is>
+      </c>
+      <c r="B47" s="4" t="inlineStr">
+        <is>
+          <t>Tail rate</t>
+        </is>
+      </c>
+      <c r="C47" s="4" t="inlineStr">
+        <is>
+          <t>Lift</t>
+        </is>
+      </c>
+      <c r="D47" s="4" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="E47" s="15" t="inlineStr"/>
+    </row>
+    <row r="48" ht="16" customHeight="1">
+      <c r="A48" s="9" t="inlineStr">
+        <is>
+          <t>size = small</t>
+        </is>
+      </c>
+      <c r="B48" s="17" t="n">
+        <v>38</v>
+      </c>
+      <c r="C48" s="10" t="inlineStr">
+        <is>
+          <t>2.49x</t>
+        </is>
+      </c>
+      <c r="D48" s="8" t="n">
+        <v>8</v>
+      </c>
+      <c r="E48" s="10" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+    </row>
+    <row r="49" ht="16" customHeight="1">
+      <c r="A49" s="6" t="inlineStr">
+        <is>
+          <t>drawdown_12m = deep(&lt;-50%)</t>
+        </is>
+      </c>
+      <c r="B49" s="16" t="n">
+        <v>32</v>
+      </c>
+      <c r="C49" s="7" t="inlineStr">
+        <is>
+          <t>2.11x</t>
+        </is>
+      </c>
+      <c r="D49" s="5" t="n">
+        <v>22</v>
+      </c>
+      <c r="E49" s="7" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+    </row>
+    <row r="50" ht="16" customHeight="1">
+      <c r="A50" s="9" t="inlineStr">
+        <is>
+          <t>sector = Real Estate</t>
+        </is>
+      </c>
+      <c r="B50" s="17" t="n">
+        <v>33</v>
+      </c>
+      <c r="C50" s="10" t="inlineStr">
+        <is>
+          <t>2.22x</t>
+        </is>
+      </c>
+      <c r="D50" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="E50" s="10" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+    </row>
+    <row r="51" ht="16" customHeight="1">
+      <c r="A51" s="6" t="inlineStr">
+        <is>
+          <t>sector = Technology</t>
+        </is>
+      </c>
+      <c r="B51" s="16" t="n">
+        <v>30</v>
+      </c>
+      <c r="C51" s="7" t="inlineStr">
+        <is>
+          <t>1.99x</t>
+        </is>
+      </c>
+      <c r="D51" s="5" t="n">
+        <v>10</v>
+      </c>
+      <c r="E51" s="7" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+    </row>
+    <row r="52" ht="16" customHeight="1">
+      <c r="A52" s="9" t="inlineStr">
+        <is>
+          <t>catalyst = SALE_OF_COMPANY</t>
+        </is>
+      </c>
+      <c r="B52" s="17" t="n">
+        <v>25</v>
+      </c>
+      <c r="C52" s="10" t="inlineStr">
+        <is>
+          <t>1.66x</t>
+        </is>
+      </c>
+      <c r="D52" s="8" t="n">
+        <v>8</v>
+      </c>
+      <c r="E52" s="10" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+    </row>
+    <row r="53" ht="16" customHeight="1">
+      <c r="A53" s="6" t="inlineStr">
+        <is>
+          <t>range_pos = low</t>
+        </is>
+      </c>
+      <c r="B53" s="16" t="n">
+        <v>21</v>
+      </c>
+      <c r="C53" s="7" t="inlineStr">
+        <is>
+          <t>1.39x</t>
+        </is>
+      </c>
+      <c r="D53" s="5" t="n">
+        <v>43</v>
+      </c>
+      <c r="E53" s="7" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+    </row>
+    <row r="54" ht="16" customHeight="1">
+      <c r="A54" s="9" t="inlineStr">
+        <is>
+          <t>catalyst = SPINOFF</t>
+        </is>
+      </c>
+      <c r="B54" s="17" t="n">
+        <v>18</v>
+      </c>
+      <c r="C54" s="10" t="inlineStr">
+        <is>
+          <t>1.16x</t>
+        </is>
+      </c>
+      <c r="D54" s="8" t="n">
+        <v>40</v>
+      </c>
+      <c r="E54" s="10" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+    </row>
+    <row r="55" ht="16" customHeight="1">
+      <c r="A55" s="6" t="inlineStr">
+        <is>
+          <t>pre_12m = down(&lt;-20%)  (needs a wait)</t>
+        </is>
+      </c>
+      <c r="B55" s="16" t="n">
+        <v>22</v>
+      </c>
+      <c r="C55" s="7" t="inlineStr">
+        <is>
+          <t>1.50x</t>
+        </is>
+      </c>
+      <c r="D55" s="5" t="n">
+        <v>40</v>
+      </c>
+      <c r="E55" s="7" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+    </row>
+    <row r="56" ht="16" customHeight="1">
+      <c r="A56" s="9" t="inlineStr">
+        <is>
+          <t>post_1m = up(&gt;+20%)  (needs a wait)</t>
+        </is>
+      </c>
+      <c r="B56" s="17" t="n">
+        <v>60</v>
+      </c>
+      <c r="C56" s="10" t="inlineStr">
+        <is>
+          <t>3.99x</t>
+        </is>
+      </c>
+      <c r="D56" s="8" t="n">
+        <v>5</v>
+      </c>
+      <c r="E56" s="10" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+    </row>
+    <row r="58" ht="28" customHeight="1">
+      <c r="A58" s="11" t="inlineStr">
+        <is>
+          <t>HOW TO RAISE THE ODDS, from the event study. The right tail is not random: it concentrates in (1) DEEPLY BEATEN-DOWN names — &gt;50% below their 12-month high tailed 32% of the time vs 4% for names near their highs (2.1x); (2) SMALL-CAPS ($300M-2B), 38% tail rate (2.5x) — the high-variance sweet spot; (3) the right SECTORS — Real Estate, Technology, Consumer-Cyclical, Energy — while Financials, Utilities and Staples produced ZERO tails; (4) SALE-OF-COMPANY and SPIN-OFF catalysts over asset sales. Stacking these lifts the tail probability to ~40% (≈2.7x base). THE SINGLE STRONGEST EDGE is not a screen but a RULE: wait ~1 month and enter only names the market voted UP &gt;20% on the catalyst — those tailed 60% of the time (4.0x). Buying the catalyst blind is a coin-flip that loses to SPY on the median; buying beaten-down small-caps in the right sectors AFTER the market confirms is how you tilt into the tail. Modest sample (113 events); directional. Sources: rerate_backtest.py / tail_discriminators.py / tail_odds.py.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="3">
+    <mergeCell ref="A2:F2"/>
+    <mergeCell ref="A58:F58"/>
+    <mergeCell ref="A1:F1"/>
+  </mergeCells>
+  <printOptions horizontalCentered="0"/>
+  <pageMargins left="0.5" right="0.5" top="0.6" bottom="0.6" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
   <dimension ref="A1:E29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -8892,7 +10366,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -9848,7 +11322,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -11428,7 +12902,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -12916,171 +14390,6 @@
     <mergeCell ref="A2:G2"/>
     <mergeCell ref="A1:G1"/>
     <mergeCell ref="A46:G46"/>
-  </mergeCells>
-  <printOptions horizontalCentered="0"/>
-  <pageMargins left="0.5" right="0.5" top="0.6" bottom="0.6" header="0.5" footer="0.5"/>
-  <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="1"/>
-  </sheetPr>
-  <dimension ref="A1:G8"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="22" customWidth="1" min="2" max="2"/>
-    <col width="8" customWidth="1" min="3" max="3"/>
-    <col width="12" customWidth="1" min="4" max="4"/>
-    <col width="22" customWidth="1" min="5" max="5"/>
-    <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="14" customWidth="1" min="7" max="7"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="26" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>UK Capital Events — RNS revealed-preference &amp; distressed monitor</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="18" customHeight="1">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>UK-listed capital-allocation and distressed-progress events (Transaction in Own Shares, placings, schemes of arrangement, Part 26A plans, CVAs, tender offers) — investment-trust NAV buybacks filtered out; separate universe from the US consensus</t>
-        </is>
-      </c>
-      <c r="B2" s="3" t="n"/>
-      <c r="C2" s="3" t="n"/>
-      <c r="D2" s="3" t="n"/>
-      <c r="E2" s="3" t="n"/>
-      <c r="F2" s="3" t="n"/>
-      <c r="G2" s="3" t="n"/>
-    </row>
-    <row r="3" ht="8" customHeight="1"/>
-    <row r="4" ht="18" customHeight="1">
-      <c r="A4" s="15" t="inlineStr">
-        <is>
-          <t>Ticker</t>
-        </is>
-      </c>
-      <c r="B4" s="15" t="inlineStr">
-        <is>
-          <t>Name</t>
-        </is>
-      </c>
-      <c r="C4" s="4" t="inlineStr">
-        <is>
-          <t>Score</t>
-        </is>
-      </c>
-      <c r="D4" s="4" t="inlineStr">
-        <is>
-          <t>Family</t>
-        </is>
-      </c>
-      <c r="E4" s="4" t="inlineStr">
-        <is>
-          <t>Class</t>
-        </is>
-      </c>
-      <c r="F4" s="4" t="inlineStr">
-        <is>
-          <t>Premium %</t>
-        </is>
-      </c>
-      <c r="G4" s="4" t="inlineStr">
-        <is>
-          <t>Signals</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="22" customHeight="1">
-      <c r="A5" s="6" t="inlineStr">
-        <is>
-          <t>MONY.L</t>
-        </is>
-      </c>
-      <c r="B5" s="7" t="inlineStr">
-        <is>
-          <t>moneysupermarket com g</t>
-        </is>
-      </c>
-      <c r="C5" s="16" t="n">
-        <v>4</v>
-      </c>
-      <c r="D5" s="7" t="inlineStr">
-        <is>
-          <t>own_shares</t>
-        </is>
-      </c>
-      <c r="E5" s="7" t="inlineStr">
-        <is>
-          <t>transaction own shares</t>
-        </is>
-      </c>
-      <c r="F5" s="7" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="G5" s="7" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="22" customHeight="1">
-      <c r="A6" s="9" t="inlineStr">
-        <is>
-          <t>RTC.L</t>
-        </is>
-      </c>
-      <c r="B6" s="10" t="inlineStr">
-        <is>
-          <t>rtc group</t>
-        </is>
-      </c>
-      <c r="C6" s="17" t="n">
-        <v>4</v>
-      </c>
-      <c r="D6" s="10" t="inlineStr">
-        <is>
-          <t>own_shares</t>
-        </is>
-      </c>
-      <c r="E6" s="10" t="inlineStr">
-        <is>
-          <t>transaction own shares</t>
-        </is>
-      </c>
-      <c r="F6" s="10" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="G6" s="10" t="inlineStr">
-        <is>
-          <t>discount</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="28" customHeight="1">
-      <c r="A8" s="11" t="inlineStr">
-        <is>
-          <t>2 UK capital events (top 45). UK terminology per the spec: 'Transaction in Own Shares' (own-shares buyback), 'placing'/'subscription' (issuance — premium placings are the revealed-preference gold), 'scheme of arrangement' / 'Part 26A restructuring plan' / 'CVA' (distressed progress), 'tender offer' / 'return of capital' (selective own-shares). Investment-trust NAV buybacks are filtered (mechanical, low signal). SOURCE LIMITATION: the UK has no free EFTS-equivalent; this monitors investegate's recent server-rendered RNS listing (shallow snapshot), so it surfaces high-signal events as they occur rather than a historical sweep. Deep UK coverage (Companies House charges/MR04-MR05 lien releases, full history) activates when a free CH_API_KEY is supplied. UK names are a SEPARATE universe and do not enter the US consensus. Source: uk_rns_scan.py.</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="3">
-    <mergeCell ref="A8:G8"/>
-    <mergeCell ref="A2:G2"/>
-    <mergeCell ref="A1:G1"/>
   </mergeCells>
   <printOptions horizontalCentered="0"/>
   <pageMargins left="0.5" right="0.5" top="0.6" bottom="0.6" header="0.5" footer="0.5"/>
@@ -13815,6 +15124,171 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
+  <dimension ref="A1:G8"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="10" customWidth="1" min="1" max="1"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="8" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="22" customWidth="1" min="5" max="5"/>
+    <col width="10" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="26" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>UK Capital Events — RNS revealed-preference &amp; distressed monitor</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="18" customHeight="1">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>UK-listed capital-allocation and distressed-progress events (Transaction in Own Shares, placings, schemes of arrangement, Part 26A plans, CVAs, tender offers) — investment-trust NAV buybacks filtered out; separate universe from the US consensus</t>
+        </is>
+      </c>
+      <c r="B2" s="3" t="n"/>
+      <c r="C2" s="3" t="n"/>
+      <c r="D2" s="3" t="n"/>
+      <c r="E2" s="3" t="n"/>
+      <c r="F2" s="3" t="n"/>
+      <c r="G2" s="3" t="n"/>
+    </row>
+    <row r="3" ht="8" customHeight="1"/>
+    <row r="4" ht="18" customHeight="1">
+      <c r="A4" s="15" t="inlineStr">
+        <is>
+          <t>Ticker</t>
+        </is>
+      </c>
+      <c r="B4" s="15" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="C4" s="4" t="inlineStr">
+        <is>
+          <t>Score</t>
+        </is>
+      </c>
+      <c r="D4" s="4" t="inlineStr">
+        <is>
+          <t>Family</t>
+        </is>
+      </c>
+      <c r="E4" s="4" t="inlineStr">
+        <is>
+          <t>Class</t>
+        </is>
+      </c>
+      <c r="F4" s="4" t="inlineStr">
+        <is>
+          <t>Premium %</t>
+        </is>
+      </c>
+      <c r="G4" s="4" t="inlineStr">
+        <is>
+          <t>Signals</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="22" customHeight="1">
+      <c r="A5" s="6" t="inlineStr">
+        <is>
+          <t>MONY.L</t>
+        </is>
+      </c>
+      <c r="B5" s="7" t="inlineStr">
+        <is>
+          <t>moneysupermarket com g</t>
+        </is>
+      </c>
+      <c r="C5" s="16" t="n">
+        <v>4</v>
+      </c>
+      <c r="D5" s="7" t="inlineStr">
+        <is>
+          <t>own_shares</t>
+        </is>
+      </c>
+      <c r="E5" s="7" t="inlineStr">
+        <is>
+          <t>transaction own shares</t>
+        </is>
+      </c>
+      <c r="F5" s="7" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="G5" s="7" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="22" customHeight="1">
+      <c r="A6" s="9" t="inlineStr">
+        <is>
+          <t>RTC.L</t>
+        </is>
+      </c>
+      <c r="B6" s="10" t="inlineStr">
+        <is>
+          <t>rtc group</t>
+        </is>
+      </c>
+      <c r="C6" s="17" t="n">
+        <v>4</v>
+      </c>
+      <c r="D6" s="10" t="inlineStr">
+        <is>
+          <t>own_shares</t>
+        </is>
+      </c>
+      <c r="E6" s="10" t="inlineStr">
+        <is>
+          <t>transaction own shares</t>
+        </is>
+      </c>
+      <c r="F6" s="10" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="G6" s="10" t="inlineStr">
+        <is>
+          <t>discount</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="28" customHeight="1">
+      <c r="A8" s="11" t="inlineStr">
+        <is>
+          <t>2 UK capital events (top 45). UK terminology per the spec: 'Transaction in Own Shares' (own-shares buyback), 'placing'/'subscription' (issuance — premium placings are the revealed-preference gold), 'scheme of arrangement' / 'Part 26A restructuring plan' / 'CVA' (distressed progress), 'tender offer' / 'return of capital' (selective own-shares). Investment-trust NAV buybacks are filtered (mechanical, low signal). SOURCE LIMITATION: the UK has no free EFTS-equivalent; this monitors investegate's recent server-rendered RNS listing (shallow snapshot), so it surfaces high-signal events as they occur rather than a historical sweep. Deep UK coverage (Companies House charges/MR04-MR05 lien releases, full history) activates when a free CH_API_KEY is supplied. UK names are a SEPARATE universe and do not enter the US consensus. Source: uk_rns_scan.py.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="3">
+    <mergeCell ref="A8:G8"/>
+    <mergeCell ref="A2:G2"/>
+    <mergeCell ref="A1:G1"/>
+  </mergeCells>
+  <printOptions horizontalCentered="0"/>
+  <pageMargins left="0.5" right="0.5" top="0.6" bottom="0.6" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
   <dimension ref="A1:H36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -14933,7 +16407,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -16649,7 +18123,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -18907,7 +20381,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -20703,7 +22177,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -23263,7 +24737,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -23865,7 +25339,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -24677,7 +26151,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet28.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>

--- a/MOST_ASYMMETRIC.xlsx
+++ b/MOST_ASYMMETRIC.xlsx
@@ -164,7 +164,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="27">
+  <cellXfs count="28">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
@@ -220,6 +220,7 @@
     <xf numFmtId="166" fontId="3" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
@@ -8386,7 +8387,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:F58"/>
+  <dimension ref="A1:F80"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -8417,1409 +8418,1938 @@
       <c r="F2" s="3" t="n"/>
     </row>
     <row r="3" ht="8" customHeight="1"/>
-    <row r="4" ht="18" customHeight="1">
-      <c r="A4" s="15" t="inlineStr">
+    <row r="4">
+      <c r="A4" s="12" t="inlineStr">
+        <is>
+          <t>CONFIRMED — market voted up &gt;20% since the catalyst (the 4x-lift rule, applied)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="18" customHeight="1">
+      <c r="A5" s="15" t="inlineStr">
         <is>
           <t>Ticker</t>
         </is>
       </c>
-      <c r="B4" s="15" t="inlineStr">
+      <c r="B5" s="15" t="inlineStr">
         <is>
           <t>Name</t>
         </is>
       </c>
-      <c r="C4" s="4" t="inlineStr">
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>Conf. tail p</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="inlineStr">
+        <is>
+          <t>Drift since</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="inlineStr">
+        <is>
+          <t>Months</t>
+        </is>
+      </c>
+      <c r="F5" s="4" t="inlineStr">
+        <is>
+          <t>Catalysts</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="22" customHeight="1">
+      <c r="A6" s="6" t="inlineStr">
+        <is>
+          <t>ANGX</t>
+        </is>
+      </c>
+      <c r="B6" s="7" t="inlineStr">
+        <is>
+          <t>Angel Studios, Inc.</t>
+        </is>
+      </c>
+      <c r="C6" s="16" t="n">
+        <v>50</v>
+      </c>
+      <c r="D6" s="16" t="n">
+        <v>100</v>
+      </c>
+      <c r="E6" s="7" t="inlineStr">
+        <is>
+          <t>5.3m</t>
+        </is>
+      </c>
+      <c r="F6" s="7" t="inlineStr">
+        <is>
+          <t>SALE_OF_COMPANY</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="22" customHeight="1">
+      <c r="A7" s="9" t="inlineStr">
+        <is>
+          <t>KPLT</t>
+        </is>
+      </c>
+      <c r="B7" s="10" t="inlineStr">
+        <is>
+          <t>Katapult Holdings, I</t>
+        </is>
+      </c>
+      <c r="C7" s="17" t="n">
+        <v>49</v>
+      </c>
+      <c r="D7" s="17" t="n">
+        <v>32</v>
+      </c>
+      <c r="E7" s="10" t="inlineStr">
+        <is>
+          <t>5.9m</t>
+        </is>
+      </c>
+      <c r="F7" s="10" t="inlineStr">
+        <is>
+          <t>SALE_OF_COMPANY</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="22" customHeight="1">
+      <c r="A8" s="6" t="inlineStr">
+        <is>
+          <t>SENS</t>
+        </is>
+      </c>
+      <c r="B8" s="7" t="inlineStr">
+        <is>
+          <t>Senseonics Holdings,</t>
+        </is>
+      </c>
+      <c r="C8" s="16" t="n">
+        <v>44</v>
+      </c>
+      <c r="D8" s="16" t="n">
+        <v>31</v>
+      </c>
+      <c r="E8" s="7" t="inlineStr">
+        <is>
+          <t>5.4m</t>
+        </is>
+      </c>
+      <c r="F8" s="7" t="inlineStr">
+        <is>
+          <t>SALE_OF_COMPANY, SPINOFF</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="22" customHeight="1">
+      <c r="A9" s="9" t="inlineStr">
+        <is>
+          <t>FLGT</t>
+        </is>
+      </c>
+      <c r="B9" s="10" t="inlineStr">
+        <is>
+          <t>Fulgent Genetics, In</t>
+        </is>
+      </c>
+      <c r="C9" s="17" t="n">
+        <v>44</v>
+      </c>
+      <c r="D9" s="17" t="n">
+        <v>34</v>
+      </c>
+      <c r="E9" s="10" t="inlineStr">
+        <is>
+          <t>5.6m</t>
+        </is>
+      </c>
+      <c r="F9" s="10" t="inlineStr">
+        <is>
+          <t>SALE_OF_COMPANY</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="22" customHeight="1">
+      <c r="A10" s="6" t="inlineStr">
+        <is>
+          <t>AGPU</t>
+        </is>
+      </c>
+      <c r="B10" s="7" t="inlineStr">
+        <is>
+          <t>Axe Compute Inc.</t>
+        </is>
+      </c>
+      <c r="C10" s="16" t="n">
+        <v>44</v>
+      </c>
+      <c r="D10" s="16" t="n">
+        <v>51</v>
+      </c>
+      <c r="E10" s="7" t="inlineStr">
+        <is>
+          <t>4.1m</t>
+        </is>
+      </c>
+      <c r="F10" s="7" t="inlineStr">
+        <is>
+          <t>STRATEGIC_REVIEW</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="22" customHeight="1">
+      <c r="A11" s="9" t="inlineStr">
+        <is>
+          <t>XPRO</t>
+        </is>
+      </c>
+      <c r="B11" s="10" t="inlineStr">
+        <is>
+          <t>Expro Group Holdings</t>
+        </is>
+      </c>
+      <c r="C11" s="17" t="n">
+        <v>43</v>
+      </c>
+      <c r="D11" s="17" t="n">
+        <v>108</v>
+      </c>
+      <c r="E11" s="10" t="inlineStr">
+        <is>
+          <t>17.4m</t>
+        </is>
+      </c>
+      <c r="F11" s="10" t="inlineStr">
+        <is>
+          <t>SALE_OF_COMPANY</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="22" customHeight="1">
+      <c r="A12" s="6" t="inlineStr">
+        <is>
+          <t>PEPG</t>
+        </is>
+      </c>
+      <c r="B12" s="7" t="inlineStr">
+        <is>
+          <t>PepGen Inc.</t>
+        </is>
+      </c>
+      <c r="C12" s="16" t="n">
+        <v>42</v>
+      </c>
+      <c r="D12" s="16" t="n">
+        <v>100</v>
+      </c>
+      <c r="E12" s="7" t="inlineStr">
+        <is>
+          <t>4.6m</t>
+        </is>
+      </c>
+      <c r="F12" s="7" t="inlineStr">
+        <is>
+          <t>SALE_OF_COMPANY</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="22" customHeight="1">
+      <c r="A13" s="9" t="inlineStr">
+        <is>
+          <t>OSPN</t>
+        </is>
+      </c>
+      <c r="B13" s="10" t="inlineStr">
+        <is>
+          <t>OneSpan Inc.</t>
+        </is>
+      </c>
+      <c r="C13" s="17" t="n">
+        <v>41</v>
+      </c>
+      <c r="D13" s="17" t="n">
+        <v>23</v>
+      </c>
+      <c r="E13" s="10" t="inlineStr">
+        <is>
+          <t>4.8m</t>
+        </is>
+      </c>
+      <c r="F13" s="10" t="inlineStr">
+        <is>
+          <t>SPINOFF</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="22" customHeight="1">
+      <c r="A14" s="6" t="inlineStr">
+        <is>
+          <t>FUBO</t>
+        </is>
+      </c>
+      <c r="B14" s="7" t="inlineStr">
+        <is>
+          <t>fuboTV Inc.</t>
+        </is>
+      </c>
+      <c r="C14" s="16" t="n">
+        <v>41</v>
+      </c>
+      <c r="D14" s="16" t="n">
+        <v>35</v>
+      </c>
+      <c r="E14" s="7" t="inlineStr">
+        <is>
+          <t>3.0m</t>
+        </is>
+      </c>
+      <c r="F14" s="7" t="inlineStr">
+        <is>
+          <t>SALE_OF_COMPANY</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="22" customHeight="1">
+      <c r="A15" s="9" t="inlineStr">
+        <is>
+          <t>UAN</t>
+        </is>
+      </c>
+      <c r="B15" s="10" t="inlineStr">
+        <is>
+          <t>CVR Partners, LP</t>
+        </is>
+      </c>
+      <c r="C15" s="17" t="n">
+        <v>39</v>
+      </c>
+      <c r="D15" s="17" t="n">
+        <v>63</v>
+      </c>
+      <c r="E15" s="10" t="inlineStr">
+        <is>
+          <t>17.0m</t>
+        </is>
+      </c>
+      <c r="F15" s="10" t="inlineStr">
+        <is>
+          <t>SALE_OF_COMPANY</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="22" customHeight="1">
+      <c r="A16" s="6" t="inlineStr">
+        <is>
+          <t>NIQ</t>
+        </is>
+      </c>
+      <c r="B16" s="7" t="inlineStr">
+        <is>
+          <t>NIQ Global Intellige</t>
+        </is>
+      </c>
+      <c r="C16" s="16" t="n">
+        <v>38</v>
+      </c>
+      <c r="D16" s="16" t="n">
+        <v>124</v>
+      </c>
+      <c r="E16" s="7" t="inlineStr">
+        <is>
+          <t>5.3m</t>
+        </is>
+      </c>
+      <c r="F16" s="7" t="inlineStr">
+        <is>
+          <t>SALE_OF_COMPANY</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="22" customHeight="1">
+      <c r="A17" s="9" t="inlineStr">
+        <is>
+          <t>UTZ</t>
+        </is>
+      </c>
+      <c r="B17" s="10" t="inlineStr">
+        <is>
+          <t>Utz Brands Inc</t>
+        </is>
+      </c>
+      <c r="C17" s="17" t="n">
+        <v>37</v>
+      </c>
+      <c r="D17" s="17" t="n">
+        <v>79</v>
+      </c>
+      <c r="E17" s="10" t="inlineStr">
+        <is>
+          <t>6.2m</t>
+        </is>
+      </c>
+      <c r="F17" s="10" t="inlineStr">
+        <is>
+          <t>SALE_OF_COMPANY</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="22" customHeight="1">
+      <c r="A18" s="6" t="inlineStr">
+        <is>
+          <t>VREX</t>
+        </is>
+      </c>
+      <c r="B18" s="7" t="inlineStr">
+        <is>
+          <t>Varex Imaging Corpor</t>
+        </is>
+      </c>
+      <c r="C18" s="16" t="n">
+        <v>34</v>
+      </c>
+      <c r="D18" s="16" t="n">
+        <v>33</v>
+      </c>
+      <c r="E18" s="7" t="inlineStr">
+        <is>
+          <t>8.6m</t>
+        </is>
+      </c>
+      <c r="F18" s="7" t="inlineStr">
+        <is>
+          <t>SPINOFF</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="22" customHeight="1">
+      <c r="A19" s="9" t="inlineStr">
+        <is>
+          <t>ZURA</t>
+        </is>
+      </c>
+      <c r="B19" s="10" t="inlineStr">
+        <is>
+          <t>Zura Bio Limited</t>
+        </is>
+      </c>
+      <c r="C19" s="17" t="n">
+        <v>34</v>
+      </c>
+      <c r="D19" s="17" t="n">
+        <v>24</v>
+      </c>
+      <c r="E19" s="10" t="inlineStr">
+        <is>
+          <t>4.6m</t>
+        </is>
+      </c>
+      <c r="F19" s="10" t="inlineStr">
+        <is>
+          <t>SPINOFF</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="22" customHeight="1">
+      <c r="A20" s="6" t="inlineStr">
+        <is>
+          <t>ACAD</t>
+        </is>
+      </c>
+      <c r="B20" s="7" t="inlineStr">
+        <is>
+          <t>ACADIA Pharmaceutica</t>
+        </is>
+      </c>
+      <c r="C20" s="16" t="n">
+        <v>34</v>
+      </c>
+      <c r="D20" s="16" t="n">
+        <v>28</v>
+      </c>
+      <c r="E20" s="7" t="inlineStr">
+        <is>
+          <t>4.8m</t>
+        </is>
+      </c>
+      <c r="F20" s="7" t="inlineStr">
+        <is>
+          <t>SALE_OF_COMPANY, SPINOFF</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="22" customHeight="1">
+      <c r="A21" s="9" t="inlineStr">
+        <is>
+          <t>CNMD</t>
+        </is>
+      </c>
+      <c r="B21" s="10" t="inlineStr">
+        <is>
+          <t>CONMED Corporation</t>
+        </is>
+      </c>
+      <c r="C21" s="17" t="n">
+        <v>34</v>
+      </c>
+      <c r="D21" s="17" t="n">
+        <v>31</v>
+      </c>
+      <c r="E21" s="10" t="inlineStr">
+        <is>
+          <t>4.6m</t>
+        </is>
+      </c>
+      <c r="F21" s="10" t="inlineStr">
+        <is>
+          <t>ASSET_SALE</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="22" customHeight="1">
+      <c r="A22" s="6" t="inlineStr">
+        <is>
+          <t>ANF</t>
+        </is>
+      </c>
+      <c r="B22" s="7" t="inlineStr">
+        <is>
+          <t>Abercrombie &amp; Fitch</t>
+        </is>
+      </c>
+      <c r="C22" s="16" t="n">
+        <v>34</v>
+      </c>
+      <c r="D22" s="16" t="n">
+        <v>67</v>
+      </c>
+      <c r="E22" s="7" t="inlineStr">
+        <is>
+          <t>5.7m</t>
+        </is>
+      </c>
+      <c r="F22" s="7" t="inlineStr">
+        <is>
+          <t>STRATEGIC_REVIEW</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="22" customHeight="1">
+      <c r="A23" s="9" t="inlineStr">
+        <is>
+          <t>BEEP</t>
+        </is>
+      </c>
+      <c r="B23" s="10" t="inlineStr">
+        <is>
+          <t>Mobile Infrastructur</t>
+        </is>
+      </c>
+      <c r="C23" s="17" t="n">
+        <v>33</v>
+      </c>
+      <c r="D23" s="17" t="n">
+        <v>34</v>
+      </c>
+      <c r="E23" s="10" t="inlineStr">
+        <is>
+          <t>4.8m</t>
+        </is>
+      </c>
+      <c r="F23" s="10" t="inlineStr">
+        <is>
+          <t>SALE_OF_COMPANY, SPINOFF</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="22" customHeight="1">
+      <c r="A24" s="6" t="inlineStr">
+        <is>
+          <t>CLW</t>
+        </is>
+      </c>
+      <c r="B24" s="7" t="inlineStr">
+        <is>
+          <t>Clearwater Paper Cor</t>
+        </is>
+      </c>
+      <c r="C24" s="16" t="n">
+        <v>32</v>
+      </c>
+      <c r="D24" s="16" t="n">
+        <v>50</v>
+      </c>
+      <c r="E24" s="7" t="inlineStr">
+        <is>
+          <t>5.7m</t>
+        </is>
+      </c>
+      <c r="F24" s="7" t="inlineStr">
+        <is>
+          <t>SPINOFF</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="22" customHeight="1">
+      <c r="A25" s="9" t="inlineStr">
+        <is>
+          <t>GPC</t>
+        </is>
+      </c>
+      <c r="B25" s="10" t="inlineStr">
+        <is>
+          <t>Genuine Parts Compan</t>
+        </is>
+      </c>
+      <c r="C25" s="17" t="n">
+        <v>30</v>
+      </c>
+      <c r="D25" s="17" t="n">
+        <v>34</v>
+      </c>
+      <c r="E25" s="10" t="inlineStr">
+        <is>
+          <t>4.9m</t>
+        </is>
+      </c>
+      <c r="F25" s="10" t="inlineStr">
+        <is>
+          <t>SEPARATION</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="22" customHeight="1">
+      <c r="A26" s="6" t="inlineStr">
+        <is>
+          <t>RBRK</t>
+        </is>
+      </c>
+      <c r="B26" s="7" t="inlineStr">
+        <is>
+          <t>Rubrik, Inc.</t>
+        </is>
+      </c>
+      <c r="C26" s="16" t="n">
+        <v>29</v>
+      </c>
+      <c r="D26" s="16" t="n">
+        <v>24</v>
+      </c>
+      <c r="E26" s="7" t="inlineStr">
+        <is>
+          <t>5.1m</t>
+        </is>
+      </c>
+      <c r="F26" s="7" t="inlineStr">
+        <is>
+          <t>SPINOFF</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="22" customHeight="1">
+      <c r="A27" s="9" t="inlineStr">
+        <is>
+          <t>HWH</t>
+        </is>
+      </c>
+      <c r="B27" s="10" t="inlineStr">
+        <is>
+          <t>HWH</t>
+        </is>
+      </c>
+      <c r="C27" s="17" t="n">
+        <v>28</v>
+      </c>
+      <c r="D27" s="17" t="n">
+        <v>106</v>
+      </c>
+      <c r="E27" s="10" t="inlineStr">
+        <is>
+          <t>5.7m</t>
+        </is>
+      </c>
+      <c r="F27" s="10" t="inlineStr">
+        <is>
+          <t>SALE_OF_COMPANY</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="21" t="inlineStr">
+        <is>
+          <t>(26 confirmed / 0 pending / 65 neutral / 56 fading, of 147 priced)</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="12" t="inlineStr">
+        <is>
+          <t>ALL CANDIDATES — pre-confirmation tail odds</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="18" customHeight="1">
+      <c r="A31" s="15" t="inlineStr">
+        <is>
+          <t>Ticker</t>
+        </is>
+      </c>
+      <c r="B31" s="15" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="C31" s="4" t="inlineStr">
         <is>
           <t>Tail p</t>
         </is>
       </c>
-      <c r="D4" s="4" t="inlineStr">
-        <is>
-          <t>xMult</t>
-        </is>
-      </c>
-      <c r="E4" s="4" t="inlineStr">
+      <c r="D31" s="4" t="inlineStr">
+        <is>
+          <t>State</t>
+        </is>
+      </c>
+      <c r="E31" s="4" t="inlineStr">
         <is>
           <t>Ratio</t>
         </is>
       </c>
-      <c r="F4" s="4" t="inlineStr">
-        <is>
-          <t>Tail drivers (lift)</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="22" customHeight="1">
-      <c r="A5" s="6" t="inlineStr">
+      <c r="F31" s="4" t="inlineStr">
+        <is>
+          <t>Tail drivers</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="22" customHeight="1">
+      <c r="A32" s="6" t="inlineStr">
         <is>
           <t>SES</t>
         </is>
       </c>
-      <c r="B5" s="7" t="inlineStr">
+      <c r="B32" s="7" t="inlineStr">
         <is>
           <t>SES AI Corporation</t>
         </is>
       </c>
-      <c r="C5" s="16" t="n">
+      <c r="C32" s="16" t="n">
         <v>40</v>
       </c>
-      <c r="D5" s="7" t="inlineStr">
-        <is>
-          <t>20.1x</t>
-        </is>
-      </c>
-      <c r="E5" s="7" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="F5" s="7" t="inlineStr">
-        <is>
-          <t>catalyst=SALE_OF_COMPANY, sector=Consume</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="22" customHeight="1">
-      <c r="A6" s="9" t="inlineStr">
+      <c r="D32" s="7" t="inlineStr">
+        <is>
+          <t>FADING</t>
+        </is>
+      </c>
+      <c r="E32" s="7" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="F32" s="7" t="inlineStr">
+        <is>
+          <t>catalyst=SALE_OF_COMPANY, sector=Consu</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="22" customHeight="1">
+      <c r="A33" s="9" t="inlineStr">
         <is>
           <t>CNXC</t>
         </is>
       </c>
-      <c r="B6" s="10" t="inlineStr">
+      <c r="B33" s="10" t="inlineStr">
         <is>
           <t>Concentrix Corporati</t>
         </is>
       </c>
-      <c r="C6" s="17" t="n">
+      <c r="C33" s="17" t="n">
         <v>39</v>
       </c>
-      <c r="D6" s="10" t="inlineStr">
-        <is>
-          <t>16.9x</t>
-        </is>
-      </c>
-      <c r="E6" s="17" t="n">
+      <c r="D33" s="10" t="inlineStr">
+        <is>
+          <t>NEUTRAL</t>
+        </is>
+      </c>
+      <c r="E33" s="17" t="n">
         <v>34.9</v>
       </c>
-      <c r="F6" s="10" t="inlineStr">
-        <is>
-          <t>catalyst=SPINOFF, sector=Technology, siz</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="22" customHeight="1">
-      <c r="A7" s="6" t="inlineStr">
+      <c r="F33" s="10" t="inlineStr">
+        <is>
+          <t>catalyst=SPINOFF, sector=Technology, s</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="22" customHeight="1">
+      <c r="A34" s="6" t="inlineStr">
         <is>
           <t>CTMX</t>
         </is>
       </c>
-      <c r="B7" s="7" t="inlineStr">
+      <c r="B34" s="7" t="inlineStr">
         <is>
           <t>CytomX Therapeutics,</t>
         </is>
       </c>
-      <c r="C7" s="16" t="n">
+      <c r="C34" s="16" t="n">
         <v>35</v>
       </c>
-      <c r="D7" s="7" t="inlineStr">
-        <is>
-          <t>12.4x</t>
-        </is>
-      </c>
-      <c r="E7" s="7" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="F7" s="7" t="inlineStr">
-        <is>
-          <t>catalyst=SALE_OF_COMPANY, size=small, dr</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="22" customHeight="1">
-      <c r="A8" s="9" t="inlineStr">
+      <c r="D34" s="7" t="inlineStr">
+        <is>
+          <t>NEUTRAL</t>
+        </is>
+      </c>
+      <c r="E34" s="7" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="F34" s="7" t="inlineStr">
+        <is>
+          <t>catalyst=SALE_OF_COMPANY, size=small,</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="22" customHeight="1">
+      <c r="A35" s="9" t="inlineStr">
         <is>
           <t>WVE</t>
         </is>
       </c>
-      <c r="B8" s="10" t="inlineStr">
+      <c r="B35" s="10" t="inlineStr">
         <is>
           <t>Wave Life Sciences L</t>
         </is>
       </c>
-      <c r="C8" s="17" t="n">
+      <c r="C35" s="17" t="n">
         <v>35</v>
       </c>
-      <c r="D8" s="10" t="inlineStr">
-        <is>
-          <t>12.4x</t>
-        </is>
-      </c>
-      <c r="E8" s="17" t="n">
+      <c r="D35" s="10" t="inlineStr">
+        <is>
+          <t>FADING</t>
+        </is>
+      </c>
+      <c r="E35" s="17" t="n">
         <v>0.5</v>
       </c>
-      <c r="F8" s="10" t="inlineStr">
-        <is>
-          <t>catalyst=SALE_OF_COMPANY, size=small, dr</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="22" customHeight="1">
-      <c r="A9" s="6" t="inlineStr">
+      <c r="F35" s="10" t="inlineStr">
+        <is>
+          <t>catalyst=SALE_OF_COMPANY, size=small,</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="22" customHeight="1">
+      <c r="A36" s="6" t="inlineStr">
         <is>
           <t>ANGX</t>
         </is>
       </c>
-      <c r="B9" s="7" t="inlineStr">
+      <c r="B36" s="7" t="inlineStr">
         <is>
           <t>Angel Studios, Inc.</t>
         </is>
       </c>
-      <c r="C9" s="16" t="n">
+      <c r="C36" s="16" t="n">
         <v>35</v>
       </c>
-      <c r="D9" s="7" t="inlineStr">
-        <is>
-          <t>12.1x</t>
-        </is>
-      </c>
-      <c r="E9" s="7" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="F9" s="7" t="inlineStr">
-        <is>
-          <t>catalyst=SALE_OF_COMPANY, size=small, dr</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="22" customHeight="1">
-      <c r="A10" s="9" t="inlineStr">
+      <c r="D36" s="7" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="E36" s="7" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="F36" s="7" t="inlineStr">
+        <is>
+          <t>catalyst=SALE_OF_COMPANY, size=small,</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="22" customHeight="1">
+      <c r="A37" s="9" t="inlineStr">
         <is>
           <t>DFH</t>
         </is>
       </c>
-      <c r="B10" s="10" t="inlineStr">
+      <c r="B37" s="10" t="inlineStr">
         <is>
           <t>Dream Finders Homes,</t>
         </is>
       </c>
-      <c r="C10" s="17" t="n">
+      <c r="C37" s="17" t="n">
         <v>35</v>
       </c>
-      <c r="D10" s="10" t="inlineStr">
-        <is>
-          <t>12.1x</t>
-        </is>
-      </c>
-      <c r="E10" s="17" t="n">
+      <c r="D37" s="10" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="E37" s="17" t="n">
         <v>2.5</v>
       </c>
-      <c r="F10" s="10" t="inlineStr">
-        <is>
-          <t>sector=Consumer Cyclical, size=small, dr</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="22" customHeight="1">
-      <c r="A11" s="6" t="inlineStr">
+      <c r="F37" s="10" t="inlineStr">
+        <is>
+          <t>sector=Consumer Cyclical, size=small,</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="22" customHeight="1">
+      <c r="A38" s="6" t="inlineStr">
         <is>
           <t>CWH</t>
         </is>
       </c>
-      <c r="B11" s="7" t="inlineStr">
+      <c r="B38" s="7" t="inlineStr">
         <is>
           <t>Camping World Holdin</t>
         </is>
       </c>
-      <c r="C11" s="16" t="n">
+      <c r="C38" s="16" t="n">
         <v>35</v>
       </c>
-      <c r="D11" s="7" t="inlineStr">
-        <is>
-          <t>12.1x</t>
-        </is>
-      </c>
-      <c r="E11" s="16" t="n">
+      <c r="D38" s="7" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="E38" s="16" t="n">
         <v>3.8</v>
       </c>
-      <c r="F11" s="7" t="inlineStr">
-        <is>
-          <t>sector=Consumer Cyclical, size=small, dr</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="22" customHeight="1">
-      <c r="A12" s="9" t="inlineStr">
+      <c r="F38" s="7" t="inlineStr">
+        <is>
+          <t>sector=Consumer Cyclical, size=small,</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="22" customHeight="1">
+      <c r="A39" s="9" t="inlineStr">
         <is>
           <t>OPTU</t>
         </is>
       </c>
-      <c r="B12" s="10" t="inlineStr">
+      <c r="B39" s="10" t="inlineStr">
         <is>
           <t>Optimum Communicatio</t>
         </is>
       </c>
-      <c r="C12" s="17" t="n">
+      <c r="C39" s="17" t="n">
         <v>35</v>
       </c>
-      <c r="D12" s="10" t="inlineStr">
-        <is>
-          <t>12.1x</t>
-        </is>
-      </c>
-      <c r="E12" s="17" t="n">
+      <c r="D39" s="10" t="inlineStr">
+        <is>
+          <t>NEUTRAL</t>
+        </is>
+      </c>
+      <c r="E39" s="17" t="n">
         <v>3</v>
       </c>
-      <c r="F12" s="10" t="inlineStr">
-        <is>
-          <t>catalyst=SALE_OF_COMPANY, size=small, dr</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="22" customHeight="1">
-      <c r="A13" s="6" t="inlineStr">
+      <c r="F39" s="10" t="inlineStr">
+        <is>
+          <t>catalyst=SALE_OF_COMPANY, size=small,</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="22" customHeight="1">
+      <c r="A40" s="6" t="inlineStr">
         <is>
           <t>MNRO</t>
         </is>
       </c>
-      <c r="B13" s="7" t="inlineStr">
+      <c r="B40" s="7" t="inlineStr">
         <is>
           <t>Monro, Inc.</t>
         </is>
       </c>
-      <c r="C13" s="16" t="n">
+      <c r="C40" s="16" t="n">
         <v>34</v>
       </c>
-      <c r="D13" s="7" t="inlineStr">
-        <is>
-          <t>11.0x</t>
-        </is>
-      </c>
-      <c r="E13" s="16" t="n">
+      <c r="D40" s="7" t="inlineStr">
+        <is>
+          <t>FADING</t>
+        </is>
+      </c>
+      <c r="E40" s="16" t="n">
         <v>1.8</v>
       </c>
-      <c r="F13" s="7" t="inlineStr">
-        <is>
-          <t>catalyst=SALE_OF_COMPANY, sector=Consume</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="22" customHeight="1">
-      <c r="A14" s="9" t="inlineStr">
+      <c r="F40" s="7" t="inlineStr">
+        <is>
+          <t>catalyst=SALE_OF_COMPANY, sector=Consu</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="22" customHeight="1">
+      <c r="A41" s="9" t="inlineStr">
         <is>
           <t>LE</t>
         </is>
       </c>
-      <c r="B14" s="10" t="inlineStr">
+      <c r="B41" s="10" t="inlineStr">
         <is>
           <t>Lands' End, Inc.</t>
         </is>
       </c>
-      <c r="C14" s="17" t="n">
+      <c r="C41" s="17" t="n">
         <v>34</v>
       </c>
-      <c r="D14" s="10" t="inlineStr">
-        <is>
-          <t>11.0x</t>
-        </is>
-      </c>
-      <c r="E14" s="17" t="n">
+      <c r="D41" s="10" t="inlineStr">
+        <is>
+          <t>NEUTRAL</t>
+        </is>
+      </c>
+      <c r="E41" s="17" t="n">
         <v>5.1</v>
       </c>
-      <c r="F14" s="10" t="inlineStr">
-        <is>
-          <t>catalyst=SALE_OF_COMPANY, sector=Consume</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="22" customHeight="1">
-      <c r="A15" s="6" t="inlineStr">
+      <c r="F41" s="10" t="inlineStr">
+        <is>
+          <t>catalyst=SALE_OF_COMPANY, sector=Consu</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="22" customHeight="1">
+      <c r="A42" s="6" t="inlineStr">
         <is>
           <t>LUCK</t>
         </is>
       </c>
-      <c r="B15" s="7" t="inlineStr">
+      <c r="B42" s="7" t="inlineStr">
         <is>
           <t>LUCKY STRIKE ENTERTA</t>
         </is>
       </c>
-      <c r="C15" s="16" t="n">
+      <c r="C42" s="16" t="n">
         <v>34</v>
       </c>
-      <c r="D15" s="7" t="inlineStr">
-        <is>
-          <t>11.0x</t>
-        </is>
-      </c>
-      <c r="E15" s="7" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="F15" s="7" t="inlineStr">
-        <is>
-          <t>catalyst=SALE_OF_COMPANY, sector=Consume</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="22" customHeight="1">
-      <c r="A16" s="9" t="inlineStr">
+      <c r="D42" s="7" t="inlineStr">
+        <is>
+          <t>FADING</t>
+        </is>
+      </c>
+      <c r="E42" s="7" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="F42" s="7" t="inlineStr">
+        <is>
+          <t>catalyst=SALE_OF_COMPANY, sector=Consu</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="22" customHeight="1">
+      <c r="A43" s="9" t="inlineStr">
         <is>
           <t>VERI</t>
         </is>
       </c>
-      <c r="B16" s="10" t="inlineStr">
+      <c r="B43" s="10" t="inlineStr">
         <is>
           <t>Veritone, Inc.</t>
         </is>
       </c>
-      <c r="C16" s="17" t="n">
+      <c r="C43" s="17" t="n">
         <v>34</v>
       </c>
-      <c r="D16" s="10" t="inlineStr">
-        <is>
-          <t>10.8x</t>
-        </is>
-      </c>
-      <c r="E16" s="17" t="n">
+      <c r="D43" s="10" t="inlineStr">
+        <is>
+          <t>FADING</t>
+        </is>
+      </c>
+      <c r="E43" s="17" t="n">
         <v>1.1</v>
       </c>
-      <c r="F16" s="10" t="inlineStr">
-        <is>
-          <t>catalyst=SALE_OF_COMPANY, sector=Technol</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="22" customHeight="1">
-      <c r="A17" s="6" t="inlineStr">
+      <c r="F43" s="10" t="inlineStr">
+        <is>
+          <t>catalyst=SALE_OF_COMPANY, sector=Techn</t>
+        </is>
+      </c>
+    </row>
+    <row r="44" ht="22" customHeight="1">
+      <c r="A44" s="6" t="inlineStr">
         <is>
           <t>KPLT</t>
         </is>
       </c>
-      <c r="B17" s="7" t="inlineStr">
+      <c r="B44" s="7" t="inlineStr">
         <is>
           <t>Katapult Holdings, I</t>
         </is>
       </c>
-      <c r="C17" s="16" t="n">
+      <c r="C44" s="16" t="n">
         <v>34</v>
       </c>
-      <c r="D17" s="7" t="inlineStr">
-        <is>
-          <t>10.8x</t>
-        </is>
-      </c>
-      <c r="E17" s="16" t="n">
+      <c r="D44" s="7" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="E44" s="16" t="n">
         <v>11.8</v>
       </c>
-      <c r="F17" s="7" t="inlineStr">
-        <is>
-          <t>catalyst=SALE_OF_COMPANY, sector=Technol</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="22" customHeight="1">
-      <c r="A18" s="9" t="inlineStr">
+      <c r="F44" s="7" t="inlineStr">
+        <is>
+          <t>catalyst=SALE_OF_COMPANY, sector=Techn</t>
+        </is>
+      </c>
+    </row>
+    <row r="45" ht="22" customHeight="1">
+      <c r="A45" s="9" t="inlineStr">
         <is>
           <t>TAOX</t>
         </is>
       </c>
-      <c r="B18" s="10" t="inlineStr">
+      <c r="B45" s="10" t="inlineStr">
         <is>
           <t>Tao Synergies Inc.</t>
         </is>
       </c>
-      <c r="C18" s="17" t="n">
+      <c r="C45" s="17" t="n">
         <v>34</v>
       </c>
-      <c r="D18" s="10" t="inlineStr">
-        <is>
-          <t>10.8x</t>
-        </is>
-      </c>
-      <c r="E18" s="17" t="n">
+      <c r="D45" s="10" t="inlineStr">
+        <is>
+          <t>NEUTRAL</t>
+        </is>
+      </c>
+      <c r="E45" s="17" t="n">
         <v>5.6</v>
       </c>
-      <c r="F18" s="10" t="inlineStr">
-        <is>
-          <t>catalyst=SALE_OF_COMPANY, sector=Technol</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="22" customHeight="1">
-      <c r="A19" s="6" t="inlineStr">
+      <c r="F45" s="10" t="inlineStr">
+        <is>
+          <t>catalyst=SALE_OF_COMPANY, sector=Techn</t>
+        </is>
+      </c>
+    </row>
+    <row r="46" ht="22" customHeight="1">
+      <c r="A46" s="6" t="inlineStr">
         <is>
           <t>AIFF</t>
         </is>
       </c>
-      <c r="B19" s="7" t="inlineStr">
+      <c r="B46" s="7" t="inlineStr">
         <is>
           <t>Firefly Neuroscience</t>
         </is>
       </c>
-      <c r="C19" s="16" t="n">
+      <c r="C46" s="16" t="n">
         <v>34</v>
       </c>
-      <c r="D19" s="7" t="inlineStr">
-        <is>
-          <t>10.8x</t>
-        </is>
-      </c>
-      <c r="E19" s="16" t="n">
+      <c r="D46" s="7" t="inlineStr">
+        <is>
+          <t>NEUTRAL</t>
+        </is>
+      </c>
+      <c r="E46" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="F19" s="7" t="inlineStr">
-        <is>
-          <t>catalyst=SALE_OF_COMPANY, sector=Technol</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="22" customHeight="1">
-      <c r="A20" s="9" t="inlineStr">
+      <c r="F46" s="7" t="inlineStr">
+        <is>
+          <t>catalyst=SALE_OF_COMPANY, sector=Techn</t>
+        </is>
+      </c>
+    </row>
+    <row r="47" ht="22" customHeight="1">
+      <c r="A47" s="9" t="inlineStr">
         <is>
           <t>LIDR</t>
         </is>
       </c>
-      <c r="B20" s="10" t="inlineStr">
+      <c r="B47" s="10" t="inlineStr">
         <is>
           <t>AEye, Inc.</t>
         </is>
       </c>
-      <c r="C20" s="17" t="n">
+      <c r="C47" s="17" t="n">
         <v>34</v>
       </c>
-      <c r="D20" s="10" t="inlineStr">
-        <is>
-          <t>10.8x</t>
-        </is>
-      </c>
-      <c r="E20" s="17" t="n">
+      <c r="D47" s="10" t="inlineStr">
+        <is>
+          <t>FADING</t>
+        </is>
+      </c>
+      <c r="E47" s="17" t="n">
         <v>6.9</v>
       </c>
-      <c r="F20" s="10" t="inlineStr">
-        <is>
-          <t>catalyst=SALE_OF_COMPANY, sector=Technol</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="22" customHeight="1">
-      <c r="A21" s="6" t="inlineStr">
+      <c r="F47" s="10" t="inlineStr">
+        <is>
+          <t>catalyst=SALE_OF_COMPANY, sector=Techn</t>
+        </is>
+      </c>
+    </row>
+    <row r="48" ht="22" customHeight="1">
+      <c r="A48" s="6" t="inlineStr">
         <is>
           <t>NTGR</t>
         </is>
       </c>
-      <c r="B21" s="7" t="inlineStr">
+      <c r="B48" s="7" t="inlineStr">
         <is>
           <t>NETGEAR, Inc.</t>
         </is>
       </c>
-      <c r="C21" s="16" t="n">
+      <c r="C48" s="16" t="n">
         <v>32</v>
       </c>
-      <c r="D21" s="7" t="inlineStr">
-        <is>
-          <t>9.2x</t>
-        </is>
-      </c>
-      <c r="E21" s="16" t="n">
+      <c r="D48" s="7" t="inlineStr">
+        <is>
+          <t>FADING</t>
+        </is>
+      </c>
+      <c r="E48" s="16" t="n">
         <v>3.8</v>
       </c>
-      <c r="F21" s="7" t="inlineStr">
-        <is>
-          <t>catalyst=SPINOFF, sector=Technology, siz</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="22" customHeight="1">
-      <c r="A22" s="9" t="inlineStr">
+      <c r="F48" s="7" t="inlineStr">
+        <is>
+          <t>catalyst=SPINOFF, sector=Technology, s</t>
+        </is>
+      </c>
+    </row>
+    <row r="49" ht="22" customHeight="1">
+      <c r="A49" s="9" t="inlineStr">
         <is>
           <t>VYX</t>
         </is>
       </c>
-      <c r="B22" s="10" t="inlineStr">
+      <c r="B49" s="10" t="inlineStr">
         <is>
           <t>NCR Voyix Corporatio</t>
         </is>
       </c>
-      <c r="C22" s="17" t="n">
+      <c r="C49" s="17" t="n">
         <v>32</v>
       </c>
-      <c r="D22" s="10" t="inlineStr">
-        <is>
-          <t>9.2x</t>
-        </is>
-      </c>
-      <c r="E22" s="17" t="n">
+      <c r="D49" s="10" t="inlineStr">
+        <is>
+          <t>NEUTRAL</t>
+        </is>
+      </c>
+      <c r="E49" s="17" t="n">
         <v>2.7</v>
       </c>
-      <c r="F22" s="10" t="inlineStr">
-        <is>
-          <t>catalyst=SPINOFF, sector=Technology, siz</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="22" customHeight="1">
-      <c r="A23" s="6" t="inlineStr">
+      <c r="F49" s="10" t="inlineStr">
+        <is>
+          <t>catalyst=SPINOFF, sector=Technology, s</t>
+        </is>
+      </c>
+    </row>
+    <row r="50" ht="22" customHeight="1">
+      <c r="A50" s="6" t="inlineStr">
         <is>
           <t>DXLG</t>
         </is>
       </c>
-      <c r="B23" s="7" t="inlineStr">
+      <c r="B50" s="7" t="inlineStr">
         <is>
           <t>Destination XL Group</t>
         </is>
       </c>
-      <c r="C23" s="16" t="n">
+      <c r="C50" s="16" t="n">
         <v>32</v>
       </c>
-      <c r="D23" s="7" t="inlineStr">
-        <is>
-          <t>9.0x</t>
-        </is>
-      </c>
-      <c r="E23" s="16" t="n">
+      <c r="D50" s="7" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="E50" s="16" t="n">
         <v>60</v>
       </c>
-      <c r="F23" s="7" t="inlineStr">
-        <is>
-          <t>catalyst=SALE_OF_COMPANY, sector=Consume</t>
-        </is>
-      </c>
-    </row>
-    <row r="24" ht="22" customHeight="1">
-      <c r="A24" s="9" t="inlineStr">
+      <c r="F50" s="7" t="inlineStr">
+        <is>
+          <t>catalyst=SALE_OF_COMPANY, sector=Consu</t>
+        </is>
+      </c>
+    </row>
+    <row r="51" ht="22" customHeight="1">
+      <c r="A51" s="9" t="inlineStr">
         <is>
           <t>DTI</t>
         </is>
       </c>
-      <c r="B24" s="10" t="inlineStr">
+      <c r="B51" s="10" t="inlineStr">
         <is>
           <t>Drilling Tools Inter</t>
         </is>
       </c>
-      <c r="C24" s="17" t="n">
+      <c r="C51" s="17" t="n">
         <v>32</v>
       </c>
-      <c r="D24" s="10" t="inlineStr">
-        <is>
-          <t>9.0x</t>
-        </is>
-      </c>
-      <c r="E24" s="17" t="n">
+      <c r="D51" s="10" t="inlineStr">
+        <is>
+          <t>FADING</t>
+        </is>
+      </c>
+      <c r="E51" s="17" t="n">
         <v>8.300000000000001</v>
       </c>
-      <c r="F24" s="10" t="inlineStr">
-        <is>
-          <t>catalyst=SALE_OF_COMPANY, sector=Energy,</t>
-        </is>
-      </c>
-    </row>
-    <row r="25" ht="22" customHeight="1">
-      <c r="A25" s="6" t="inlineStr">
+      <c r="F51" s="10" t="inlineStr">
+        <is>
+          <t>catalyst=SALE_OF_COMPANY, sector=Energ</t>
+        </is>
+      </c>
+    </row>
+    <row r="52" ht="22" customHeight="1">
+      <c r="A52" s="6" t="inlineStr">
         <is>
           <t>WKHS</t>
         </is>
       </c>
-      <c r="B25" s="7" t="inlineStr">
+      <c r="B52" s="7" t="inlineStr">
         <is>
           <t>Workhorse Group, Inc</t>
         </is>
       </c>
-      <c r="C25" s="16" t="n">
+      <c r="C52" s="16" t="n">
         <v>32</v>
       </c>
-      <c r="D25" s="7" t="inlineStr">
-        <is>
-          <t>9.0x</t>
-        </is>
-      </c>
-      <c r="E25" s="16" t="n">
+      <c r="D52" s="7" t="inlineStr">
+        <is>
+          <t>NEUTRAL</t>
+        </is>
+      </c>
+      <c r="E52" s="16" t="n">
         <v>7.4</v>
       </c>
-      <c r="F25" s="7" t="inlineStr">
-        <is>
-          <t>catalyst=SALE_OF_COMPANY, sector=Consume</t>
-        </is>
-      </c>
-    </row>
-    <row r="26" ht="22" customHeight="1">
-      <c r="A26" s="9" t="inlineStr">
+      <c r="F52" s="7" t="inlineStr">
+        <is>
+          <t>catalyst=SALE_OF_COMPANY, sector=Consu</t>
+        </is>
+      </c>
+    </row>
+    <row r="53" ht="22" customHeight="1">
+      <c r="A53" s="9" t="inlineStr">
         <is>
           <t>GDRX</t>
         </is>
       </c>
-      <c r="B26" s="10" t="inlineStr">
+      <c r="B53" s="10" t="inlineStr">
         <is>
           <t>GoodRx Holdings, Inc</t>
         </is>
       </c>
-      <c r="C26" s="17" t="n">
+      <c r="C53" s="17" t="n">
         <v>32</v>
       </c>
-      <c r="D26" s="10" t="inlineStr">
-        <is>
-          <t>8.6x</t>
-        </is>
-      </c>
-      <c r="E26" s="17" t="n">
+      <c r="D53" s="10" t="inlineStr">
+        <is>
+          <t>NEUTRAL</t>
+        </is>
+      </c>
+      <c r="E53" s="17" t="n">
         <v>2.6</v>
       </c>
-      <c r="F26" s="10" t="inlineStr">
-        <is>
-          <t>catalyst=SPINOFF, size=small, drawdown_1</t>
-        </is>
-      </c>
-    </row>
-    <row r="27" ht="22" customHeight="1">
-      <c r="A27" s="6" t="inlineStr">
+      <c r="F53" s="10" t="inlineStr">
+        <is>
+          <t>catalyst=SPINOFF, size=small, drawdown</t>
+        </is>
+      </c>
+    </row>
+    <row r="54" ht="22" customHeight="1">
+      <c r="A54" s="6" t="inlineStr">
         <is>
           <t>GRPN</t>
         </is>
       </c>
-      <c r="B27" s="7" t="inlineStr">
+      <c r="B54" s="7" t="inlineStr">
         <is>
           <t>Groupon, Inc.</t>
         </is>
       </c>
-      <c r="C27" s="16" t="n">
+      <c r="C54" s="16" t="n">
         <v>32</v>
       </c>
-      <c r="D27" s="7" t="inlineStr">
-        <is>
-          <t>8.5x</t>
-        </is>
-      </c>
-      <c r="E27" s="7" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="F27" s="7" t="inlineStr">
-        <is>
-          <t>catalyst=SPINOFF, size=small, drawdown_1</t>
-        </is>
-      </c>
-    </row>
-    <row r="28" ht="22" customHeight="1">
-      <c r="A28" s="9" t="inlineStr">
+      <c r="D54" s="7" t="inlineStr">
+        <is>
+          <t>NEUTRAL</t>
+        </is>
+      </c>
+      <c r="E54" s="7" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="F54" s="7" t="inlineStr">
+        <is>
+          <t>catalyst=SPINOFF, size=small, drawdown</t>
+        </is>
+      </c>
+    </row>
+    <row r="55" ht="22" customHeight="1">
+      <c r="A55" s="9" t="inlineStr">
         <is>
           <t>GLIBK</t>
         </is>
       </c>
-      <c r="B28" s="10" t="inlineStr">
+      <c r="B55" s="10" t="inlineStr">
         <is>
           <t>Liberty Capital Corp</t>
         </is>
       </c>
-      <c r="C28" s="17" t="n">
+      <c r="C55" s="17" t="n">
         <v>32</v>
       </c>
-      <c r="D28" s="10" t="inlineStr">
-        <is>
-          <t>8.5x</t>
-        </is>
-      </c>
-      <c r="E28" s="17" t="n">
+      <c r="D55" s="10" t="inlineStr">
+        <is>
+          <t>FADING</t>
+        </is>
+      </c>
+      <c r="E55" s="17" t="n">
         <v>32.9</v>
       </c>
-      <c r="F28" s="10" t="inlineStr">
-        <is>
-          <t>catalyst=SPINOFF, size=small, drawdown_1</t>
-        </is>
-      </c>
-    </row>
-    <row r="29" ht="22" customHeight="1">
-      <c r="A29" s="6" t="inlineStr">
+      <c r="F55" s="10" t="inlineStr">
+        <is>
+          <t>catalyst=SPINOFF, size=small, drawdown</t>
+        </is>
+      </c>
+    </row>
+    <row r="56" ht="22" customHeight="1">
+      <c r="A56" s="6" t="inlineStr">
         <is>
           <t>AHT</t>
         </is>
       </c>
-      <c r="B29" s="7" t="inlineStr">
+      <c r="B56" s="7" t="inlineStr">
         <is>
           <t>Ashford Hospitality</t>
         </is>
       </c>
-      <c r="C29" s="16" t="n">
+      <c r="C56" s="16" t="n">
         <v>32</v>
       </c>
-      <c r="D29" s="7" t="inlineStr">
-        <is>
-          <t>8.4x</t>
-        </is>
-      </c>
-      <c r="E29" s="16" t="n">
+      <c r="D56" s="7" t="inlineStr">
+        <is>
+          <t>NEUTRAL</t>
+        </is>
+      </c>
+      <c r="E56" s="16" t="n">
         <v>1.5</v>
       </c>
-      <c r="F29" s="7" t="inlineStr">
-        <is>
-          <t>catalyst=SPINOFF, sector=Real Estate, si</t>
-        </is>
-      </c>
-    </row>
-    <row r="30" ht="22" customHeight="1">
-      <c r="A30" s="9" t="inlineStr">
+      <c r="F56" s="7" t="inlineStr">
+        <is>
+          <t>catalyst=SPINOFF, sector=Real Estate,</t>
+        </is>
+      </c>
+    </row>
+    <row r="57" ht="22" customHeight="1">
+      <c r="A57" s="9" t="inlineStr">
         <is>
           <t>DXC</t>
         </is>
       </c>
-      <c r="B30" s="10" t="inlineStr">
+      <c r="B57" s="10" t="inlineStr">
         <is>
           <t>DXC Technology Compa</t>
         </is>
       </c>
-      <c r="C30" s="17" t="n">
+      <c r="C57" s="17" t="n">
         <v>31</v>
       </c>
-      <c r="D30" s="10" t="inlineStr">
-        <is>
-          <t>7.9x</t>
-        </is>
-      </c>
-      <c r="E30" s="17" t="n">
+      <c r="D57" s="10" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="E57" s="17" t="n">
         <v>30</v>
       </c>
-      <c r="F30" s="10" t="inlineStr">
-        <is>
-          <t>sector=Technology, size=small, drawdown_</t>
-        </is>
-      </c>
-    </row>
-    <row r="31" ht="22" customHeight="1">
-      <c r="A31" s="6" t="inlineStr">
+      <c r="F57" s="10" t="inlineStr">
+        <is>
+          <t>sector=Technology, size=small, drawdow</t>
+        </is>
+      </c>
+    </row>
+    <row r="58" ht="22" customHeight="1">
+      <c r="A58" s="6" t="inlineStr">
         <is>
           <t>VTS</t>
         </is>
       </c>
-      <c r="B31" s="7" t="inlineStr">
+      <c r="B58" s="7" t="inlineStr">
         <is>
           <t>Vitesse Energy, Inc.</t>
         </is>
       </c>
-      <c r="C31" s="16" t="n">
+      <c r="C58" s="16" t="n">
         <v>31</v>
       </c>
-      <c r="D31" s="7" t="inlineStr">
-        <is>
-          <t>7.7x</t>
-        </is>
-      </c>
-      <c r="E31" s="16" t="n">
+      <c r="D58" s="7" t="inlineStr">
+        <is>
+          <t>NEUTRAL</t>
+        </is>
+      </c>
+      <c r="E58" s="16" t="n">
         <v>0.9</v>
       </c>
-      <c r="F31" s="7" t="inlineStr">
-        <is>
-          <t>catalyst=SPINOFF, sector=Energy, size=sm</t>
-        </is>
-      </c>
-    </row>
-    <row r="32" ht="22" customHeight="1">
-      <c r="A32" s="9" t="inlineStr">
+      <c r="F58" s="7" t="inlineStr">
+        <is>
+          <t>catalyst=SPINOFF, sector=Energy, size=</t>
+        </is>
+      </c>
+    </row>
+    <row r="59" ht="22" customHeight="1">
+      <c r="A59" s="9" t="inlineStr">
         <is>
           <t>JTAI</t>
         </is>
       </c>
-      <c r="B32" s="10" t="inlineStr">
+      <c r="B59" s="10" t="inlineStr">
         <is>
           <t>Jet.AI Inc.</t>
         </is>
       </c>
-      <c r="C32" s="17" t="n">
+      <c r="C59" s="17" t="n">
         <v>30</v>
       </c>
-      <c r="D32" s="10" t="inlineStr">
-        <is>
-          <t>7.5x</t>
-        </is>
-      </c>
-      <c r="E32" s="17" t="n">
+      <c r="D59" s="10" t="inlineStr">
+        <is>
+          <t>FADING</t>
+        </is>
+      </c>
+      <c r="E59" s="17" t="n">
         <v>60</v>
       </c>
-      <c r="F32" s="10" t="inlineStr">
-        <is>
-          <t>catalyst=SPINOFF, sector=Technology, siz</t>
-        </is>
-      </c>
-    </row>
-    <row r="33" ht="22" customHeight="1">
-      <c r="A33" s="6" t="inlineStr">
+      <c r="F59" s="10" t="inlineStr">
+        <is>
+          <t>catalyst=SPINOFF, sector=Technology, s</t>
+        </is>
+      </c>
+    </row>
+    <row r="60" ht="22" customHeight="1">
+      <c r="A60" s="6" t="inlineStr">
         <is>
           <t>GPRO</t>
         </is>
       </c>
-      <c r="B33" s="7" t="inlineStr">
+      <c r="B60" s="7" t="inlineStr">
         <is>
           <t>GoPro, Inc.</t>
         </is>
       </c>
-      <c r="C33" s="16" t="n">
+      <c r="C60" s="16" t="n">
         <v>30</v>
       </c>
-      <c r="D33" s="7" t="inlineStr">
-        <is>
-          <t>7.5x</t>
-        </is>
-      </c>
-      <c r="E33" s="16" t="n">
+      <c r="D60" s="7" t="inlineStr">
+        <is>
+          <t>NEUTRAL</t>
+        </is>
+      </c>
+      <c r="E60" s="16" t="n">
         <v>3</v>
       </c>
-      <c r="F33" s="7" t="inlineStr">
-        <is>
-          <t>catalyst=SPINOFF, sector=Technology, siz</t>
-        </is>
-      </c>
-    </row>
-    <row r="34" ht="22" customHeight="1">
-      <c r="A34" s="9" t="inlineStr">
+      <c r="F60" s="7" t="inlineStr">
+        <is>
+          <t>catalyst=SPINOFF, sector=Technology, s</t>
+        </is>
+      </c>
+    </row>
+    <row r="61" ht="22" customHeight="1">
+      <c r="A61" s="9" t="inlineStr">
         <is>
           <t>LMRI</t>
         </is>
       </c>
-      <c r="B34" s="10" t="inlineStr">
+      <c r="B61" s="10" t="inlineStr">
         <is>
           <t>Lumexa Imaging Holdi</t>
         </is>
       </c>
-      <c r="C34" s="17" t="n">
+      <c r="C61" s="17" t="n">
         <v>30</v>
       </c>
-      <c r="D34" s="10" t="inlineStr">
-        <is>
-          <t>7.5x</t>
-        </is>
-      </c>
-      <c r="E34" s="17" t="n">
+      <c r="D61" s="10" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="E61" s="17" t="n">
         <v>3.3</v>
       </c>
-      <c r="F34" s="10" t="inlineStr">
-        <is>
-          <t>size=small, drawdown_12m=deep(&lt;-50%), ra</t>
-        </is>
-      </c>
-    </row>
-    <row r="35" ht="22" customHeight="1">
-      <c r="A35" s="6" t="inlineStr">
+      <c r="F61" s="10" t="inlineStr">
+        <is>
+          <t>size=small, drawdown_12m=deep(&lt;-50%),</t>
+        </is>
+      </c>
+    </row>
+    <row r="62" ht="22" customHeight="1">
+      <c r="A62" s="6" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="B35" s="7" t="inlineStr">
+      <c r="B62" s="7" t="inlineStr">
         <is>
           <t>Kyndryl Holdings, In</t>
         </is>
       </c>
-      <c r="C35" s="16" t="n">
+      <c r="C62" s="16" t="n">
         <v>30</v>
       </c>
-      <c r="D35" s="7" t="inlineStr">
-        <is>
-          <t>6.9x</t>
-        </is>
-      </c>
-      <c r="E35" s="16" t="n">
+      <c r="D62" s="7" t="inlineStr">
+        <is>
+          <t>NEUTRAL</t>
+        </is>
+      </c>
+      <c r="E62" s="16" t="n">
         <v>2</v>
       </c>
-      <c r="F35" s="7" t="inlineStr">
-        <is>
-          <t>catalyst=SPINOFF, sector=Technology, dra</t>
-        </is>
-      </c>
-    </row>
-    <row r="36" ht="22" customHeight="1">
-      <c r="A36" s="9" t="inlineStr">
+      <c r="F62" s="7" t="inlineStr">
+        <is>
+          <t>catalyst=SPINOFF, sector=Technology, d</t>
+        </is>
+      </c>
+    </row>
+    <row r="63" ht="22" customHeight="1">
+      <c r="A63" s="9" t="inlineStr">
         <is>
           <t>SENS</t>
         </is>
       </c>
-      <c r="B36" s="10" t="inlineStr">
+      <c r="B63" s="10" t="inlineStr">
         <is>
           <t>Senseonics Holdings,</t>
         </is>
       </c>
-      <c r="C36" s="17" t="n">
+      <c r="C63" s="17" t="n">
         <v>29</v>
       </c>
-      <c r="D36" s="10" t="inlineStr">
-        <is>
-          <t>6.7x</t>
-        </is>
-      </c>
-      <c r="E36" s="10" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="F36" s="10" t="inlineStr">
-        <is>
-          <t>catalyst=SALE_OF_COMPANY, size=small, dr</t>
-        </is>
-      </c>
-    </row>
-    <row r="37" ht="22" customHeight="1">
-      <c r="A37" s="6" t="inlineStr">
+      <c r="D63" s="10" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="E63" s="10" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="F63" s="10" t="inlineStr">
+        <is>
+          <t>catalyst=SALE_OF_COMPANY, size=small,</t>
+        </is>
+      </c>
+    </row>
+    <row r="64" ht="22" customHeight="1">
+      <c r="A64" s="6" t="inlineStr">
         <is>
           <t>FLGT</t>
         </is>
       </c>
-      <c r="B37" s="7" t="inlineStr">
+      <c r="B64" s="7" t="inlineStr">
         <is>
           <t>Fulgent Genetics, In</t>
         </is>
       </c>
-      <c r="C37" s="16" t="n">
+      <c r="C64" s="16" t="n">
         <v>29</v>
       </c>
-      <c r="D37" s="7" t="inlineStr">
-        <is>
-          <t>6.7x</t>
-        </is>
-      </c>
-      <c r="E37" s="16" t="n">
+      <c r="D64" s="7" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="E64" s="16" t="n">
         <v>60</v>
       </c>
-      <c r="F37" s="7" t="inlineStr">
-        <is>
-          <t>catalyst=SALE_OF_COMPANY, size=small, dr</t>
-        </is>
-      </c>
-    </row>
-    <row r="38" ht="22" customHeight="1">
-      <c r="A38" s="9" t="inlineStr">
+      <c r="F64" s="7" t="inlineStr">
+        <is>
+          <t>catalyst=SALE_OF_COMPANY, size=small,</t>
+        </is>
+      </c>
+    </row>
+    <row r="65" ht="22" customHeight="1">
+      <c r="A65" s="9" t="inlineStr">
         <is>
           <t>PAHC</t>
         </is>
       </c>
-      <c r="B38" s="10" t="inlineStr">
+      <c r="B65" s="10" t="inlineStr">
         <is>
           <t>Phibro Animal Health</t>
         </is>
       </c>
-      <c r="C38" s="17" t="n">
+      <c r="C65" s="17" t="n">
         <v>29</v>
       </c>
-      <c r="D38" s="10" t="inlineStr">
-        <is>
-          <t>6.7x</t>
-        </is>
-      </c>
-      <c r="E38" s="17" t="n">
+      <c r="D65" s="10" t="inlineStr">
+        <is>
+          <t>FADING</t>
+        </is>
+      </c>
+      <c r="E65" s="17" t="n">
         <v>3.5</v>
       </c>
-      <c r="F38" s="10" t="inlineStr">
-        <is>
-          <t>catalyst=SALE_OF_COMPANY, size=small, dr</t>
-        </is>
-      </c>
-    </row>
-    <row r="39" ht="22" customHeight="1">
-      <c r="A39" s="6" t="inlineStr">
+      <c r="F65" s="10" t="inlineStr">
+        <is>
+          <t>catalyst=SALE_OF_COMPANY, size=small,</t>
+        </is>
+      </c>
+    </row>
+    <row r="66" ht="22" customHeight="1">
+      <c r="A66" s="6" t="inlineStr">
         <is>
           <t>GRNT</t>
         </is>
       </c>
-      <c r="B39" s="7" t="inlineStr">
+      <c r="B66" s="7" t="inlineStr">
         <is>
           <t>Granite Ridge Resour</t>
         </is>
       </c>
-      <c r="C39" s="16" t="n">
+      <c r="C66" s="16" t="n">
         <v>29</v>
       </c>
-      <c r="D39" s="7" t="inlineStr">
-        <is>
-          <t>6.6x</t>
-        </is>
-      </c>
-      <c r="E39" s="16" t="n">
+      <c r="D66" s="7" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="E66" s="16" t="n">
         <v>0.7</v>
       </c>
-      <c r="F39" s="7" t="inlineStr">
-        <is>
-          <t>sector=Energy, size=small, drawdown_12m=</t>
-        </is>
-      </c>
-    </row>
-    <row r="40" ht="22" customHeight="1">
-      <c r="A40" s="9" t="inlineStr">
-        <is>
-          <t>CMTL</t>
-        </is>
-      </c>
-      <c r="B40" s="10" t="inlineStr">
-        <is>
-          <t>Comtech Telecommunic</t>
-        </is>
-      </c>
-      <c r="C40" s="17" t="n">
-        <v>29</v>
-      </c>
-      <c r="D40" s="10" t="inlineStr">
-        <is>
-          <t>6.6x</t>
-        </is>
-      </c>
-      <c r="E40" s="17" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="F40" s="10" t="inlineStr">
-        <is>
-          <t>sector=Technology, size=micro, drawdown_</t>
-        </is>
-      </c>
-    </row>
-    <row r="41" ht="22" customHeight="1">
-      <c r="A41" s="6" t="inlineStr">
-        <is>
-          <t>AGPU</t>
-        </is>
-      </c>
-      <c r="B41" s="7" t="inlineStr">
-        <is>
-          <t>Axe Compute Inc.</t>
-        </is>
-      </c>
-      <c r="C41" s="16" t="n">
-        <v>29</v>
-      </c>
-      <c r="D41" s="7" t="inlineStr">
-        <is>
-          <t>6.6x</t>
-        </is>
-      </c>
-      <c r="E41" s="16" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="F41" s="7" t="inlineStr">
-        <is>
-          <t>sector=Technology, size=micro, drawdown_</t>
-        </is>
-      </c>
-    </row>
-    <row r="42" ht="22" customHeight="1">
-      <c r="A42" s="9" t="inlineStr">
-        <is>
-          <t>DEC</t>
-        </is>
-      </c>
-      <c r="B42" s="10" t="inlineStr">
-        <is>
-          <t>Diversified Energy C</t>
-        </is>
-      </c>
-      <c r="C42" s="17" t="n">
-        <v>29</v>
-      </c>
-      <c r="D42" s="10" t="inlineStr">
-        <is>
-          <t>6.6x</t>
-        </is>
-      </c>
-      <c r="E42" s="17" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="F42" s="10" t="inlineStr">
-        <is>
-          <t>sector=Energy, size=small, drawdown_12m=</t>
-        </is>
-      </c>
-    </row>
-    <row r="43" ht="22" customHeight="1">
-      <c r="A43" s="6" t="inlineStr">
-        <is>
-          <t>ADNT</t>
-        </is>
-      </c>
-      <c r="B43" s="7" t="inlineStr">
-        <is>
-          <t>Adient plc</t>
-        </is>
-      </c>
-      <c r="C43" s="16" t="n">
-        <v>29</v>
-      </c>
-      <c r="D43" s="7" t="inlineStr">
-        <is>
-          <t>6.6x</t>
-        </is>
-      </c>
-      <c r="E43" s="16" t="n">
-        <v>6.3</v>
-      </c>
-      <c r="F43" s="7" t="inlineStr">
-        <is>
-          <t>sector=Consumer Cyclical, size=small, dr</t>
-        </is>
-      </c>
-    </row>
-    <row r="44" ht="22" customHeight="1">
-      <c r="A44" s="9" t="inlineStr">
-        <is>
-          <t>XPRO</t>
-        </is>
-      </c>
-      <c r="B44" s="10" t="inlineStr">
-        <is>
-          <t>Expro Group Holdings</t>
-        </is>
-      </c>
-      <c r="C44" s="17" t="n">
-        <v>29</v>
-      </c>
-      <c r="D44" s="10" t="inlineStr">
-        <is>
-          <t>6.5x</t>
-        </is>
-      </c>
-      <c r="E44" s="17" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="F44" s="10" t="inlineStr">
-        <is>
-          <t>catalyst=SALE_OF_COMPANY, sector=Energy,</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" s="12" t="inlineStr">
+      <c r="F66" s="7" t="inlineStr">
+        <is>
+          <t>sector=Energy, size=small, drawdown_12</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="12" t="inlineStr">
         <is>
           <t>WHAT RAISES TAIL ODDS (historical lift vs 15% base)</t>
         </is>
       </c>
     </row>
-    <row r="47" ht="18" customHeight="1">
-      <c r="A47" s="4" t="inlineStr">
+    <row r="69" ht="18" customHeight="1">
+      <c r="A69" s="4" t="inlineStr">
         <is>
           <t>Feature = bin</t>
         </is>
       </c>
-      <c r="B47" s="4" t="inlineStr">
+      <c r="B69" s="4" t="inlineStr">
         <is>
           <t>Tail rate</t>
         </is>
       </c>
-      <c r="C47" s="4" t="inlineStr">
+      <c r="C69" s="4" t="inlineStr">
         <is>
           <t>Lift</t>
         </is>
       </c>
-      <c r="D47" s="4" t="inlineStr">
+      <c r="D69" s="4" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="E47" s="15" t="inlineStr"/>
-    </row>
-    <row r="48" ht="16" customHeight="1">
-      <c r="A48" s="9" t="inlineStr">
+      <c r="E69" s="15" t="inlineStr"/>
+    </row>
+    <row r="70" ht="16" customHeight="1">
+      <c r="A70" s="9" t="inlineStr">
         <is>
           <t>size = small</t>
         </is>
       </c>
-      <c r="B48" s="17" t="n">
+      <c r="B70" s="17" t="n">
         <v>38</v>
       </c>
-      <c r="C48" s="10" t="inlineStr">
+      <c r="C70" s="10" t="inlineStr">
         <is>
           <t>2.49x</t>
         </is>
       </c>
-      <c r="D48" s="8" t="n">
+      <c r="D70" s="8" t="n">
         <v>8</v>
       </c>
-      <c r="E48" s="10" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-    </row>
-    <row r="49" ht="16" customHeight="1">
-      <c r="A49" s="6" t="inlineStr">
+      <c r="E70" s="10" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+    </row>
+    <row r="71" ht="16" customHeight="1">
+      <c r="A71" s="6" t="inlineStr">
         <is>
           <t>drawdown_12m = deep(&lt;-50%)</t>
         </is>
       </c>
-      <c r="B49" s="16" t="n">
+      <c r="B71" s="16" t="n">
         <v>32</v>
       </c>
-      <c r="C49" s="7" t="inlineStr">
+      <c r="C71" s="7" t="inlineStr">
         <is>
           <t>2.11x</t>
         </is>
       </c>
-      <c r="D49" s="5" t="n">
+      <c r="D71" s="5" t="n">
         <v>22</v>
       </c>
-      <c r="E49" s="7" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-    </row>
-    <row r="50" ht="16" customHeight="1">
-      <c r="A50" s="9" t="inlineStr">
+      <c r="E71" s="7" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+    </row>
+    <row r="72" ht="16" customHeight="1">
+      <c r="A72" s="9" t="inlineStr">
         <is>
           <t>sector = Real Estate</t>
         </is>
       </c>
-      <c r="B50" s="17" t="n">
+      <c r="B72" s="17" t="n">
         <v>33</v>
       </c>
-      <c r="C50" s="10" t="inlineStr">
+      <c r="C72" s="10" t="inlineStr">
         <is>
           <t>2.22x</t>
         </is>
       </c>
-      <c r="D50" s="8" t="n">
+      <c r="D72" s="8" t="n">
         <v>3</v>
       </c>
-      <c r="E50" s="10" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-    </row>
-    <row r="51" ht="16" customHeight="1">
-      <c r="A51" s="6" t="inlineStr">
+      <c r="E72" s="10" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+    </row>
+    <row r="73" ht="16" customHeight="1">
+      <c r="A73" s="6" t="inlineStr">
         <is>
           <t>sector = Technology</t>
         </is>
       </c>
-      <c r="B51" s="16" t="n">
+      <c r="B73" s="16" t="n">
         <v>30</v>
       </c>
-      <c r="C51" s="7" t="inlineStr">
+      <c r="C73" s="7" t="inlineStr">
         <is>
           <t>1.99x</t>
         </is>
       </c>
-      <c r="D51" s="5" t="n">
+      <c r="D73" s="5" t="n">
         <v>10</v>
       </c>
-      <c r="E51" s="7" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-    </row>
-    <row r="52" ht="16" customHeight="1">
-      <c r="A52" s="9" t="inlineStr">
+      <c r="E73" s="7" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+    </row>
+    <row r="74" ht="16" customHeight="1">
+      <c r="A74" s="9" t="inlineStr">
         <is>
           <t>catalyst = SALE_OF_COMPANY</t>
         </is>
       </c>
-      <c r="B52" s="17" t="n">
+      <c r="B74" s="17" t="n">
         <v>25</v>
       </c>
-      <c r="C52" s="10" t="inlineStr">
+      <c r="C74" s="10" t="inlineStr">
         <is>
           <t>1.66x</t>
         </is>
       </c>
-      <c r="D52" s="8" t="n">
+      <c r="D74" s="8" t="n">
         <v>8</v>
       </c>
-      <c r="E52" s="10" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-    </row>
-    <row r="53" ht="16" customHeight="1">
-      <c r="A53" s="6" t="inlineStr">
+      <c r="E74" s="10" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+    </row>
+    <row r="75" ht="16" customHeight="1">
+      <c r="A75" s="6" t="inlineStr">
         <is>
           <t>range_pos = low</t>
         </is>
       </c>
-      <c r="B53" s="16" t="n">
+      <c r="B75" s="16" t="n">
         <v>21</v>
       </c>
-      <c r="C53" s="7" t="inlineStr">
+      <c r="C75" s="7" t="inlineStr">
         <is>
           <t>1.39x</t>
         </is>
       </c>
-      <c r="D53" s="5" t="n">
+      <c r="D75" s="5" t="n">
         <v>43</v>
       </c>
-      <c r="E53" s="7" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-    </row>
-    <row r="54" ht="16" customHeight="1">
-      <c r="A54" s="9" t="inlineStr">
+      <c r="E75" s="7" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+    </row>
+    <row r="76" ht="16" customHeight="1">
+      <c r="A76" s="9" t="inlineStr">
         <is>
           <t>catalyst = SPINOFF</t>
         </is>
       </c>
-      <c r="B54" s="17" t="n">
+      <c r="B76" s="17" t="n">
         <v>18</v>
       </c>
-      <c r="C54" s="10" t="inlineStr">
+      <c r="C76" s="10" t="inlineStr">
         <is>
           <t>1.16x</t>
         </is>
       </c>
-      <c r="D54" s="8" t="n">
+      <c r="D76" s="8" t="n">
         <v>40</v>
       </c>
-      <c r="E54" s="10" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-    </row>
-    <row r="55" ht="16" customHeight="1">
-      <c r="A55" s="6" t="inlineStr">
+      <c r="E76" s="10" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+    </row>
+    <row r="77" ht="16" customHeight="1">
+      <c r="A77" s="6" t="inlineStr">
         <is>
           <t>pre_12m = down(&lt;-20%)  (needs a wait)</t>
         </is>
       </c>
-      <c r="B55" s="16" t="n">
+      <c r="B77" s="16" t="n">
         <v>22</v>
       </c>
-      <c r="C55" s="7" t="inlineStr">
+      <c r="C77" s="7" t="inlineStr">
         <is>
           <t>1.50x</t>
         </is>
       </c>
-      <c r="D55" s="5" t="n">
+      <c r="D77" s="5" t="n">
         <v>40</v>
       </c>
-      <c r="E55" s="7" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-    </row>
-    <row r="56" ht="16" customHeight="1">
-      <c r="A56" s="9" t="inlineStr">
+      <c r="E77" s="7" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+    </row>
+    <row r="78" ht="16" customHeight="1">
+      <c r="A78" s="9" t="inlineStr">
         <is>
           <t>post_1m = up(&gt;+20%)  (needs a wait)</t>
         </is>
       </c>
-      <c r="B56" s="17" t="n">
+      <c r="B78" s="17" t="n">
         <v>60</v>
       </c>
-      <c r="C56" s="10" t="inlineStr">
+      <c r="C78" s="10" t="inlineStr">
         <is>
           <t>3.99x</t>
         </is>
       </c>
-      <c r="D56" s="8" t="n">
+      <c r="D78" s="8" t="n">
         <v>5</v>
       </c>
-      <c r="E56" s="10" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-    </row>
-    <row r="58" ht="28" customHeight="1">
-      <c r="A58" s="11" t="inlineStr">
+      <c r="E78" s="10" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+    </row>
+    <row r="80" ht="28" customHeight="1">
+      <c r="A80" s="11" t="inlineStr">
         <is>
           <t>HOW TO RAISE THE ODDS, from the event study. The right tail is not random: it concentrates in (1) DEEPLY BEATEN-DOWN names — &gt;50% below their 12-month high tailed 32% of the time vs 4% for names near their highs (2.1x); (2) SMALL-CAPS ($300M-2B), 38% tail rate (2.5x) — the high-variance sweet spot; (3) the right SECTORS — Real Estate, Technology, Consumer-Cyclical, Energy — while Financials, Utilities and Staples produced ZERO tails; (4) SALE-OF-COMPANY and SPIN-OFF catalysts over asset sales. Stacking these lifts the tail probability to ~40% (≈2.7x base). THE SINGLE STRONGEST EDGE is not a screen but a RULE: wait ~1 month and enter only names the market voted UP &gt;20% on the catalyst — those tailed 60% of the time (4.0x). Buying the catalyst blind is a coin-flip that loses to SPY on the median; buying beaten-down small-caps in the right sectors AFTER the market confirms is how you tilt into the tail. Modest sample (113 events); directional. Sources: rerate_backtest.py / tail_discriminators.py / tail_odds.py.</t>
         </is>
@@ -9828,7 +10358,7 @@
   </sheetData>
   <mergeCells count="3">
     <mergeCell ref="A2:F2"/>
-    <mergeCell ref="A58:F58"/>
+    <mergeCell ref="A80:F80"/>
     <mergeCell ref="A1:F1"/>
   </mergeCells>
   <printOptions horizontalCentered="0"/>
@@ -16340,7 +16870,7 @@
       <c r="E33" s="16" t="n">
         <v>4.182</v>
       </c>
-      <c r="F33" s="21" t="n">
+      <c r="F33" s="22" t="n">
         <v>106</v>
       </c>
       <c r="G33" s="7" t="inlineStr">
@@ -16518,7 +17048,7 @@
           <t>Repay Holdings Corporation</t>
         </is>
       </c>
-      <c r="D5" s="22" t="n">
+      <c r="D5" s="23" t="n">
         <v>68</v>
       </c>
       <c r="E5" s="5" t="n">
@@ -16558,7 +17088,7 @@
           <t>Gossamer Bio, Inc.</t>
         </is>
       </c>
-      <c r="D6" s="22" t="n">
+      <c r="D6" s="23" t="n">
         <v>61</v>
       </c>
       <c r="E6" s="8" t="n">
@@ -16598,7 +17128,7 @@
           <t>ZoomInfo Technologies Inc.</t>
         </is>
       </c>
-      <c r="D7" s="22" t="n">
+      <c r="D7" s="23" t="n">
         <v>60</v>
       </c>
       <c r="E7" s="5" t="n">
@@ -16638,7 +17168,7 @@
           <t>Goosehead Insurance, Inc.</t>
         </is>
       </c>
-      <c r="D8" s="22" t="n">
+      <c r="D8" s="23" t="n">
         <v>53</v>
       </c>
       <c r="E8" s="8" t="n">
@@ -16678,7 +17208,7 @@
           <t>Guidewire Software, Inc.</t>
         </is>
       </c>
-      <c r="D9" s="22" t="n">
+      <c r="D9" s="23" t="n">
         <v>53</v>
       </c>
       <c r="E9" s="5" t="n">
@@ -16718,7 +17248,7 @@
           <t>Comtech Telecommunications Corp</t>
         </is>
       </c>
-      <c r="D10" s="22" t="n">
+      <c r="D10" s="23" t="n">
         <v>52</v>
       </c>
       <c r="E10" s="8" t="n">
@@ -16758,7 +17288,7 @@
           <t>BiomX Inc.</t>
         </is>
       </c>
-      <c r="D11" s="22" t="n">
+      <c r="D11" s="23" t="n">
         <v>52</v>
       </c>
       <c r="E11" s="5" t="n">
@@ -16798,7 +17328,7 @@
           <t>ChargePoint Holdings, Inc.</t>
         </is>
       </c>
-      <c r="D12" s="22" t="n">
+      <c r="D12" s="23" t="n">
         <v>52</v>
       </c>
       <c r="E12" s="8" t="n">
@@ -16838,7 +17368,7 @@
           <t>DXC Technology Company</t>
         </is>
       </c>
-      <c r="D13" s="22" t="n">
+      <c r="D13" s="23" t="n">
         <v>52</v>
       </c>
       <c r="E13" s="5" t="n">
@@ -16878,7 +17408,7 @@
           <t>Processa Pharmaceuticals, Inc.</t>
         </is>
       </c>
-      <c r="D14" s="22" t="n">
+      <c r="D14" s="23" t="n">
         <v>51</v>
       </c>
       <c r="E14" s="8" t="n">
@@ -16918,7 +17448,7 @@
           <t>Peabody Energy Corporation</t>
         </is>
       </c>
-      <c r="D15" s="22" t="n">
+      <c r="D15" s="23" t="n">
         <v>51</v>
       </c>
       <c r="E15" s="5" t="n">
@@ -16958,7 +17488,7 @@
           <t>Ready Capital Corporation</t>
         </is>
       </c>
-      <c r="D16" s="22" t="n">
+      <c r="D16" s="23" t="n">
         <v>49</v>
       </c>
       <c r="E16" s="8" t="n">
@@ -16998,7 +17528,7 @@
           <t>Kingsway Corporation</t>
         </is>
       </c>
-      <c r="D17" s="22" t="n">
+      <c r="D17" s="23" t="n">
         <v>49</v>
       </c>
       <c r="E17" s="5" t="n">
@@ -17038,7 +17568,7 @@
           <t>Heron Therapeutics, Inc.</t>
         </is>
       </c>
-      <c r="D18" s="22" t="n">
+      <c r="D18" s="23" t="n">
         <v>48</v>
       </c>
       <c r="E18" s="8" t="n">
@@ -17078,7 +17608,7 @@
           <t>Standard BioTools Inc.</t>
         </is>
       </c>
-      <c r="D19" s="22" t="n">
+      <c r="D19" s="23" t="n">
         <v>48</v>
       </c>
       <c r="E19" s="5" t="n">
@@ -17118,7 +17648,7 @@
           <t>InspireMD Inc.</t>
         </is>
       </c>
-      <c r="D20" s="22" t="n">
+      <c r="D20" s="23" t="n">
         <v>47</v>
       </c>
       <c r="E20" s="8" t="n">
@@ -17158,7 +17688,7 @@
           <t>Rein Therapeutics, Inc.</t>
         </is>
       </c>
-      <c r="D21" s="22" t="n">
+      <c r="D21" s="23" t="n">
         <v>46</v>
       </c>
       <c r="E21" s="5" t="n">
@@ -17198,7 +17728,7 @@
           <t>Booz Allen Hamilton Holding Cor</t>
         </is>
       </c>
-      <c r="D22" s="22" t="n">
+      <c r="D22" s="23" t="n">
         <v>46</v>
       </c>
       <c r="E22" s="8" t="n">
@@ -17238,7 +17768,7 @@
           <t>VolitionRX Limited</t>
         </is>
       </c>
-      <c r="D23" s="22" t="n">
+      <c r="D23" s="23" t="n">
         <v>45</v>
       </c>
       <c r="E23" s="5" t="n">
@@ -17278,7 +17808,7 @@
           <t>Total Return Securities Fund</t>
         </is>
       </c>
-      <c r="D24" s="22" t="n">
+      <c r="D24" s="23" t="n">
         <v>44</v>
       </c>
       <c r="E24" s="8" t="n">
@@ -17318,7 +17848,7 @@
           <t>Fox Corporation</t>
         </is>
       </c>
-      <c r="D25" s="22" t="n">
+      <c r="D25" s="23" t="n">
         <v>44</v>
       </c>
       <c r="E25" s="5" t="n">
@@ -17358,7 +17888,7 @@
           <t>Outlook Therapeutics, Inc.</t>
         </is>
       </c>
-      <c r="D26" s="22" t="n">
+      <c r="D26" s="23" t="n">
         <v>44</v>
       </c>
       <c r="E26" s="8" t="n">
@@ -17398,7 +17928,7 @@
           <t>My Size, Inc.</t>
         </is>
       </c>
-      <c r="D27" s="22" t="n">
+      <c r="D27" s="23" t="n">
         <v>43</v>
       </c>
       <c r="E27" s="5" t="n">
@@ -17438,7 +17968,7 @@
           <t>Purple Innovation, Inc.</t>
         </is>
       </c>
-      <c r="D28" s="22" t="n">
+      <c r="D28" s="23" t="n">
         <v>43</v>
       </c>
       <c r="E28" s="8" t="n">
@@ -17478,7 +18008,7 @@
           <t>Cosmos Health Inc.</t>
         </is>
       </c>
-      <c r="D29" s="22" t="n">
+      <c r="D29" s="23" t="n">
         <v>43</v>
       </c>
       <c r="E29" s="5" t="n">
@@ -17518,7 +18048,7 @@
           <t>Power Solutions International,</t>
         </is>
       </c>
-      <c r="D30" s="22" t="n">
+      <c r="D30" s="23" t="n">
         <v>43</v>
       </c>
       <c r="E30" s="8" t="n">
@@ -17558,7 +18088,7 @@
           <t>NexGel, Inc</t>
         </is>
       </c>
-      <c r="D31" s="22" t="n">
+      <c r="D31" s="23" t="n">
         <v>43</v>
       </c>
       <c r="E31" s="5" t="n">
@@ -17598,7 +18128,7 @@
           <t>Salesforce, Inc.</t>
         </is>
       </c>
-      <c r="D32" s="22" t="n">
+      <c r="D32" s="23" t="n">
         <v>42</v>
       </c>
       <c r="E32" s="8" t="n">
@@ -17638,7 +18168,7 @@
           <t>Vitesse Energy, Inc.</t>
         </is>
       </c>
-      <c r="D33" s="22" t="n">
+      <c r="D33" s="23" t="n">
         <v>42</v>
       </c>
       <c r="E33" s="5" t="n">
@@ -17678,7 +18208,7 @@
           <t>Krispy Kreme, Inc.</t>
         </is>
       </c>
-      <c r="D34" s="22" t="n">
+      <c r="D34" s="23" t="n">
         <v>42</v>
       </c>
       <c r="E34" s="8" t="n">
@@ -17718,7 +18248,7 @@
           <t>Nerdy Inc.</t>
         </is>
       </c>
-      <c r="D35" s="22" t="n">
+      <c r="D35" s="23" t="n">
         <v>41</v>
       </c>
       <c r="E35" s="5" t="n">
@@ -17758,7 +18288,7 @@
           <t>Artiva Biotherapeutics, Inc.</t>
         </is>
       </c>
-      <c r="D36" s="22" t="n">
+      <c r="D36" s="23" t="n">
         <v>41</v>
       </c>
       <c r="E36" s="8" t="n">
@@ -17798,7 +18328,7 @@
           <t>STERIS plc (Ireland)</t>
         </is>
       </c>
-      <c r="D37" s="22" t="n">
+      <c r="D37" s="23" t="n">
         <v>41</v>
       </c>
       <c r="E37" s="5" t="n">
@@ -17838,7 +18368,7 @@
           <t>Rubrik, Inc.</t>
         </is>
       </c>
-      <c r="D38" s="22" t="n">
+      <c r="D38" s="23" t="n">
         <v>41</v>
       </c>
       <c r="E38" s="8" t="n">
@@ -17878,7 +18408,7 @@
           <t>Medline Inc.</t>
         </is>
       </c>
-      <c r="D39" s="22" t="n">
+      <c r="D39" s="23" t="n">
         <v>40</v>
       </c>
       <c r="E39" s="5" t="n">
@@ -17918,7 +18448,7 @@
           <t>Toro Corp.</t>
         </is>
       </c>
-      <c r="D40" s="22" t="n">
+      <c r="D40" s="23" t="n">
         <v>40</v>
       </c>
       <c r="E40" s="8" t="n">
@@ -17958,7 +18488,7 @@
           <t>CuriosityStream Inc.</t>
         </is>
       </c>
-      <c r="D41" s="22" t="n">
+      <c r="D41" s="23" t="n">
         <v>40</v>
       </c>
       <c r="E41" s="5" t="n">
@@ -17998,7 +18528,7 @@
           <t>Health Catalyst, Inc</t>
         </is>
       </c>
-      <c r="D42" s="22" t="n">
+      <c r="D42" s="23" t="n">
         <v>40</v>
       </c>
       <c r="E42" s="8" t="n">
@@ -20492,7 +21022,7 @@
           <t>Jet.AI Inc.</t>
         </is>
       </c>
-      <c r="D5" s="22" t="n">
+      <c r="D5" s="23" t="n">
         <v>43</v>
       </c>
       <c r="E5" s="7" t="inlineStr">
@@ -20534,7 +21064,7 @@
           <t>BEYOND MEAT, INC.</t>
         </is>
       </c>
-      <c r="D6" s="22" t="n">
+      <c r="D6" s="23" t="n">
         <v>35</v>
       </c>
       <c r="E6" s="10" t="inlineStr">
@@ -20576,7 +21106,7 @@
           <t>COMTECH TELECOMMUNICATIONS CORP</t>
         </is>
       </c>
-      <c r="D7" s="22" t="n">
+      <c r="D7" s="23" t="n">
         <v>35</v>
       </c>
       <c r="E7" s="7" t="inlineStr">
@@ -20618,7 +21148,7 @@
           <t>FISERV INC</t>
         </is>
       </c>
-      <c r="D8" s="22" t="n">
+      <c r="D8" s="23" t="n">
         <v>35</v>
       </c>
       <c r="E8" s="10" t="inlineStr">
@@ -20660,7 +21190,7 @@
           <t>BTCS Inc.</t>
         </is>
       </c>
-      <c r="D9" s="22" t="n">
+      <c r="D9" s="23" t="n">
         <v>35</v>
       </c>
       <c r="E9" s="7" t="inlineStr">
@@ -20702,7 +21232,7 @@
           <t>HERON THERAPEUTICS, INC. /DE/</t>
         </is>
       </c>
-      <c r="D10" s="22" t="n">
+      <c r="D10" s="23" t="n">
         <v>35</v>
       </c>
       <c r="E10" s="10" t="inlineStr">
@@ -20744,7 +21274,7 @@
           <t>WW INTERNATIONAL, INC.</t>
         </is>
       </c>
-      <c r="D11" s="22" t="n">
+      <c r="D11" s="23" t="n">
         <v>33</v>
       </c>
       <c r="E11" s="7" t="inlineStr">
@@ -22215,14 +22745,14 @@
     </row>
     <row r="3" ht="8" customHeight="1"/>
     <row r="4" ht="22" customHeight="1">
-      <c r="A4" s="23" t="inlineStr">
+      <c r="A4" s="24" t="inlineStr">
         <is>
           <t>Highest PSU forensic core</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="24" t="inlineStr">
+      <c r="A5" s="25" t="inlineStr">
         <is>
           <t>What it measures: depth + rigor of the PSU plan</t>
         </is>
@@ -22485,14 +23015,14 @@
       </c>
     </row>
     <row r="16" ht="22" customHeight="1">
-      <c r="A16" s="23" t="inlineStr">
+      <c r="A16" s="24" t="inlineStr">
         <is>
           <t>Highest governance score</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="24" t="inlineStr">
+      <c r="A17" s="25" t="inlineStr">
         <is>
           <t>What it measures: clawback + anti-hedge + vesting + ownership multiple</t>
         </is>
@@ -22755,14 +23285,14 @@
       </c>
     </row>
     <row r="28" ht="22" customHeight="1">
-      <c r="A28" s="23" t="inlineStr">
+      <c r="A28" s="24" t="inlineStr">
         <is>
           <t>Deepest P/B floor (&lt;0.5x book)</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="24" t="inlineStr">
+      <c r="A29" s="25" t="inlineStr">
         <is>
           <t>What it measures: hard balance-sheet value floor</t>
         </is>
@@ -23025,14 +23555,14 @@
       </c>
     </row>
     <row r="40" ht="22" customHeight="1">
-      <c r="A40" s="23" t="inlineStr">
+      <c r="A40" s="24" t="inlineStr">
         <is>
           <t>Cheapest EV/EBITDA (&lt;6x)</t>
         </is>
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="24" t="inlineStr">
+      <c r="A41" s="25" t="inlineStr">
         <is>
           <t>What it measures: enterprise-value to earnings power</t>
         </is>
@@ -23295,14 +23825,14 @@
       </c>
     </row>
     <row r="52" ht="22" customHeight="1">
-      <c r="A52" s="23" t="inlineStr">
+      <c r="A52" s="24" t="inlineStr">
         <is>
           <t>Lowest trailing P/E (&lt;8x, positive)</t>
         </is>
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="24" t="inlineStr">
+      <c r="A53" s="25" t="inlineStr">
         <is>
           <t>What it measures: earnings yield</t>
         </is>
@@ -23565,14 +24095,14 @@
       </c>
     </row>
     <row r="64" ht="22" customHeight="1">
-      <c r="A64" s="23" t="inlineStr">
+      <c r="A64" s="24" t="inlineStr">
         <is>
           <t>Largest verified buyback shrinkage</t>
         </is>
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="24" t="inlineStr">
+      <c r="A65" s="25" t="inlineStr">
         <is>
           <t>What it measures: actual supply curve compression</t>
         </is>
@@ -23835,14 +24365,14 @@
       </c>
     </row>
     <row r="76" ht="22" customHeight="1">
-      <c r="A76" s="23" t="inlineStr">
+      <c r="A76" s="24" t="inlineStr">
         <is>
           <t>Highest 10b5-1 termination signed score</t>
         </is>
       </c>
     </row>
     <row r="77">
-      <c r="A77" s="24" t="inlineStr">
+      <c r="A77" s="25" t="inlineStr">
         <is>
           <t>What it measures: insider walked back scheduled selling</t>
         </is>
@@ -24105,14 +24635,14 @@
       </c>
     </row>
     <row r="88" ht="22" customHeight="1">
-      <c r="A88" s="23" t="inlineStr">
+      <c r="A88" s="24" t="inlineStr">
         <is>
           <t>Largest insider Form 4 dollar cluster</t>
         </is>
       </c>
     </row>
     <row r="89">
-      <c r="A89" s="24" t="inlineStr">
+      <c r="A89" s="25" t="inlineStr">
         <is>
           <t>What it measures: insider conviction in dollars</t>
         </is>
@@ -24375,14 +24905,14 @@
       </c>
     </row>
     <row r="100" ht="22" customHeight="1">
-      <c r="A100" s="23" t="inlineStr">
+      <c r="A100" s="24" t="inlineStr">
         <is>
           <t>Live tender / 13E-3 events</t>
         </is>
       </c>
     </row>
     <row r="101">
-      <c r="A101" s="24" t="inlineStr">
+      <c r="A101" s="25" t="inlineStr">
         <is>
           <t>What it measures: mechanical bid as floor</t>
         </is>
@@ -26208,7 +26738,7 @@
           <t>Universe construction</t>
         </is>
       </c>
-      <c r="C5" s="25" t="inlineStr">
+      <c r="C5" s="26" t="inlineStr">
         <is>
           <t>6,164 US-listed common tickers from cancel_10b5_1.json — authoritative NYSE/Nasdaq/AMEX/CBOE set. Foreign names (JP/KR/UK) live in a separate tab and universe.</t>
         </is>
@@ -26223,7 +26753,7 @@
           <t>Layer ingestion</t>
         </is>
       </c>
-      <c r="C6" s="26" t="inlineStr">
+      <c r="C6" s="27" t="inlineStr">
         <is>
           <t>44 additive scoring layers ingested per ticker, spanning PSU forensics, governance, valuation, verified buybacks, tender mechanics, 10b5-1 direction, Form 4 (raw + Cohen-Malloy opportunistic), Form 144, quarterly 10-Q, NCAV, Voss CIC, post-Ch11, internalization, bumpitrage, spinoff timing, Arquitos, Coval-Stafford proxy + real N-PORT, backstopped rights, FDIC dark banks, activist letters, 13F-delta, biotech PDUFA, financial-sector primary, discretionary insider conviction, emergence cross-feed, Sohn pitches, asymmetry assembly (PSIX recipe), distressed-stub progress, premium injections, selective buybacks, hidden-asset realisation, net buyback (diluted-share reduction net of SBC), the Lynch reawakening momentum leg, the Form 4 filing-TIME signal (off-hours / Friday-evening open-market buys = quiet accumulators followed; market-hours buys = price support, faded), the MD&amp;A intent-language scan (value-unlock / transformative / capital-policy / governance / strategic-action phrasing mined from 10-K/10-Q narrative, negation-verified), and the payoff-geometry engine (asset-backed downside floor vs sector re-rate upside -&gt; asymmetry ratio; see the Payoff Geometry and Mechanism Gates tabs).</t>
         </is>
@@ -26238,7 +26768,7 @@
           <t>Additive discipline</t>
         </is>
       </c>
-      <c r="C7" s="25" t="inlineStr">
+      <c r="C7" s="26" t="inlineStr">
         <is>
           <t>Every layer ADDS to the composite; none modifies another's score. New legs append fields; existing weights never change. This is enforced and audited (verify_universe_methodology.py).</t>
         </is>
@@ -26253,7 +26783,7 @@
           <t>Coverage-normalised composite</t>
         </is>
       </c>
-      <c r="C8" s="26" t="inlineStr">
+      <c r="C8" s="27" t="inlineStr">
         <is>
           <t>Sparse-coverage names are not penalised for missing layers; the norm score rescales by sqrt(n_total/n_present) so a name strong on few layers competes with a name mediocre on many.</t>
         </is>
@@ -26268,7 +26798,7 @@
           <t>Per-pattern catalyst ranking</t>
         </is>
       </c>
-      <c r="C9" s="25" t="inlineStr">
+      <c r="C9" s="26" t="inlineStr">
         <is>
           <t>Top names in each catalyst pattern (forward $ hurdle, M&amp;A close, spin trigger, FDA/PDUFA, post-Ch11, asset sale, etc.) — surfaces single-mandate leaders (see Single-Measure tab).</t>
         </is>
@@ -26283,7 +26813,7 @@
           <t>Archetype winners</t>
         </is>
       </c>
-      <c r="C10" s="26" t="inlineStr">
+      <c r="C10" s="27" t="inlineStr">
         <is>
           <t>57 PSU/governance/thesis buckets — single best representative of each archetype across the universe (PSU_ARCHETYPES.md 38 + ASYMMETRIC_BY_ARCHETYPE.md 19).</t>
         </is>
@@ -26298,7 +26828,7 @@
           <t>Consensus meta-ranking</t>
         </is>
       </c>
-      <c r="C11" s="25" t="inlineStr">
+      <c r="C11" s="26" t="inlineStr">
         <is>
           <t>n_layers_firing = how many of the 44 independent layers produce a non-zero score for the ticker. consensus_score = sum of per-layer rank-decay contributions across the universe.</t>
         </is>
@@ -26313,7 +26843,7 @@
           <t>Layer independence</t>
         </is>
       </c>
-      <c r="C12" s="26" t="inlineStr">
+      <c r="C12" s="27" t="inlineStr">
         <is>
           <t>Pairwise Spearman correlation (layer_correlation_pairs.csv) collapses 44 raw layers to effective-independent at rho&gt;0.6. Three correlated clusters: PSU+Voss, tender family, F4+opportunistic. 'Fires 9 layers' ≈ 7-8 true confirmations.</t>
         </is>
@@ -26328,7 +26858,7 @@
           <t>Freshness weighting</t>
         </is>
       </c>
-      <c r="C13" s="25" t="inlineStr">
+      <c r="C13" s="26" t="inlineStr">
         <is>
           <t>layer_freshness.json records each layer's data age. Most layers are &lt;14 days old. An optional age-decay multiplier (opt-in) can down-weight stale layers; current build reports age without auto-decaying.</t>
         </is>
@@ -26343,7 +26873,7 @@
           <t>Caution layering</t>
         </is>
       </c>
-      <c r="C14" s="26" t="inlineStr">
+      <c r="C14" s="27" t="inlineStr">
         <is>
           <t>Eight red-flag classes from plan text: single-trigger CIC, repricing, retirement carveout, front-loaded grant, discretionary hurdle, aggregate-only metrics, plus structural. Convergence without direction; flag count modulates sizing.</t>
         </is>
@@ -26358,7 +26888,7 @@
           <t>Deployment / sizing</t>
         </is>
       </c>
-      <c r="C15" s="25" t="inlineStr">
+      <c r="C15" s="26" t="inlineStr">
         <is>
           <t>Concentrated (≥5%): clean high-layer-count names. Material (2-5%): strong but 1-2 flags. Participation (0.5-2%): single-leg or multi-flag. Basket (&lt;1% each): sub-archetype groups, Cohen-Malloy stack, R2000-boundary, NOL shells, foreign.</t>
         </is>
@@ -26373,7 +26903,7 @@
           <t>Honest limitations</t>
         </is>
       </c>
-      <c r="C16" s="26" t="inlineStr">
+      <c r="C16" s="27" t="inlineStr">
         <is>
           <t>Most layers are not yet return-validated (AUDIT.md S1.1) — the composite is a structurally-sound pattern-recognition system, not yet validated alpha. The one exception is the Form 4 filing-time layer, built FROM a measured test: off-hours buys showed a +3.7% median vs -8.0% for market-hours buys (+11.7pp differential, buy-to-now proxy). Cohen-Malloy needs deeper Form 4 history. Coval-Stafford proxy supplements but does not replace the N-PORT real signal. See AUDIT.md for the full ledger.</t>
         </is>

--- a/MOST_ASYMMETRIC.xlsx
+++ b/MOST_ASYMMETRIC.xlsx
@@ -6266,1016 +6266,1024 @@
     <row r="5" ht="22" customHeight="1">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>BEEP</t>
+          <t>LE</t>
         </is>
       </c>
       <c r="B5" s="7" t="inlineStr">
         <is>
-          <t>Mobile Infrastructure</t>
+          <t>Lands' End, Inc.</t>
         </is>
       </c>
       <c r="C5" s="16" t="n">
-        <v>33</v>
+        <v>18.1</v>
       </c>
       <c r="D5" s="16" t="n">
         <v>2</v>
       </c>
       <c r="E5" s="16" t="n">
-        <v>57.1</v>
+        <v>5.1</v>
       </c>
       <c r="F5" s="19" t="n">
-        <v>300</v>
+        <v>176</v>
       </c>
       <c r="G5" s="7" t="inlineStr">
         <is>
-          <t>Sale Of Company [incentive]; Spinoff [incent</t>
+          <t>Sale Of Company [tender]; Strategic Review [</t>
         </is>
       </c>
     </row>
     <row r="6" ht="22" customHeight="1">
       <c r="A6" s="9" t="inlineStr">
         <is>
-          <t>GNPX</t>
+          <t>WBD</t>
         </is>
       </c>
       <c r="B6" s="10" t="inlineStr">
         <is>
-          <t>Genprex, Inc.</t>
+          <t>Warner Bros. Discovery</t>
         </is>
       </c>
       <c r="C6" s="17" t="n">
-        <v>27.5</v>
+        <v>18</v>
       </c>
       <c r="D6" s="17" t="n">
         <v>2</v>
       </c>
-      <c r="E6" s="17" t="n">
-        <v>30</v>
-      </c>
-      <c r="F6" s="20" t="n">
-        <v>150</v>
+      <c r="E6" s="10" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="F6" s="10" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
       <c r="G6" s="10" t="inlineStr">
         <is>
-          <t>Sale Of Company [incentive]; Spinoff [incent</t>
+          <t>Sale Of Company [tender]; Separation [narrat</t>
         </is>
       </c>
     </row>
     <row r="7" ht="22" customHeight="1">
       <c r="A7" s="6" t="inlineStr">
         <is>
-          <t>VERI</t>
+          <t>ETN</t>
         </is>
       </c>
       <c r="B7" s="7" t="inlineStr">
         <is>
-          <t>Veritone, Inc.</t>
+          <t>Eaton Corporation, PLC</t>
         </is>
       </c>
       <c r="C7" s="16" t="n">
-        <v>25.2</v>
+        <v>18</v>
       </c>
       <c r="D7" s="16" t="n">
         <v>2</v>
       </c>
-      <c r="E7" s="16" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="F7" s="19" t="n">
-        <v>86</v>
+      <c r="E7" s="7" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="F7" s="7" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
       <c r="G7" s="7" t="inlineStr">
         <is>
-          <t>Sale Of Company [incentive]; Spinoff [incent</t>
+          <t>Separation [narrative]; Spinoff [narrative]</t>
         </is>
       </c>
     </row>
     <row r="8" ht="22" customHeight="1">
       <c r="A8" s="9" t="inlineStr">
         <is>
-          <t>BIRD</t>
+          <t>M</t>
         </is>
       </c>
       <c r="B8" s="10" t="inlineStr">
         <is>
-          <t>Allbirds, Inc.</t>
+          <t>Macy's Inc</t>
         </is>
       </c>
       <c r="C8" s="17" t="n">
-        <v>24.6</v>
+        <v>14.5</v>
       </c>
       <c r="D8" s="17" t="n">
         <v>2</v>
       </c>
       <c r="E8" s="17" t="n">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="F8" s="20" t="n">
-        <v>137</v>
+        <v>127</v>
       </c>
       <c r="G8" s="10" t="inlineStr">
         <is>
-          <t>Asset Sale [narrative]; Spinoff [incentive]</t>
+          <t>Asset Sale [narrative]; Strategic Review [na</t>
         </is>
       </c>
     </row>
     <row r="9" ht="22" customHeight="1">
       <c r="A9" s="6" t="inlineStr">
         <is>
-          <t>TCRT</t>
+          <t>LSTA</t>
         </is>
       </c>
       <c r="B9" s="7" t="inlineStr">
         <is>
-          <t>Alaunos Therapeutics,</t>
+          <t>Lisata Therapeutics, I</t>
         </is>
       </c>
       <c r="C9" s="16" t="n">
-        <v>23.4</v>
+        <v>14</v>
       </c>
       <c r="D9" s="16" t="n">
         <v>2</v>
       </c>
-      <c r="E9" s="16" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="F9" s="19" t="n">
-        <v>39</v>
+      <c r="E9" s="7" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="F9" s="7" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
       <c r="G9" s="7" t="inlineStr">
         <is>
-          <t>Sale Of Company [incentive]; Spinoff [incent</t>
+          <t>Sale Of Company [tender]; Strategic Review [</t>
         </is>
       </c>
     </row>
     <row r="10" ht="22" customHeight="1">
       <c r="A10" s="9" t="inlineStr">
         <is>
-          <t>PSTV</t>
+          <t>PKOH</t>
         </is>
       </c>
       <c r="B10" s="10" t="inlineStr">
         <is>
-          <t>PLUS THERAPEUTICS, Inc</t>
+          <t>PKOH</t>
         </is>
       </c>
       <c r="C10" s="17" t="n">
-        <v>22.5</v>
+        <v>12</v>
       </c>
       <c r="D10" s="17" t="n">
         <v>2</v>
       </c>
-      <c r="E10" s="17" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="F10" s="20" t="n">
-        <v>12</v>
+      <c r="E10" s="10" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="F10" s="10" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
       <c r="G10" s="10" t="inlineStr">
         <is>
-          <t>Sale Of Company [incentive]; Spinoff [incent</t>
+          <t>Asset Sale [narrative]; Strategic Review [na</t>
         </is>
       </c>
     </row>
     <row r="11" ht="22" customHeight="1">
       <c r="A11" s="6" t="inlineStr">
         <is>
-          <t>PALI</t>
+          <t>SCTH</t>
         </is>
       </c>
       <c r="B11" s="7" t="inlineStr">
         <is>
-          <t>Palisade Bio, Inc.</t>
+          <t>SCTH</t>
         </is>
       </c>
       <c r="C11" s="16" t="n">
-        <v>22.4</v>
+        <v>12</v>
       </c>
       <c r="D11" s="16" t="n">
         <v>2</v>
       </c>
-      <c r="E11" s="16" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="F11" s="19" t="n">
-        <v>11</v>
+      <c r="E11" s="7" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="F11" s="7" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
       <c r="G11" s="7" t="inlineStr">
         <is>
-          <t>Sale Of Company [incentive]; Spinoff [incent</t>
+          <t>Asset Sale [narrative]; Strategic Review [na</t>
         </is>
       </c>
     </row>
     <row r="12" ht="22" customHeight="1">
       <c r="A12" s="9" t="inlineStr">
         <is>
-          <t>MNRO</t>
+          <t>DXLG</t>
         </is>
       </c>
       <c r="B12" s="10" t="inlineStr">
         <is>
-          <t>Monro, Inc.</t>
+          <t>Destination XL Group,</t>
         </is>
       </c>
       <c r="C12" s="17" t="n">
-        <v>22.2</v>
+        <v>10.5</v>
       </c>
       <c r="D12" s="17" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E12" s="17" t="n">
-        <v>1.8</v>
+        <v>60</v>
       </c>
       <c r="F12" s="20" t="n">
-        <v>66</v>
+        <v>300</v>
       </c>
       <c r="G12" s="10" t="inlineStr">
         <is>
-          <t>Sale Of Company [narrative]; Spinoff [incent</t>
+          <t>Sale Of Company [tender]</t>
         </is>
       </c>
     </row>
     <row r="13" ht="22" customHeight="1">
       <c r="A13" s="6" t="inlineStr">
         <is>
-          <t>ACAD</t>
+          <t>HUN</t>
         </is>
       </c>
       <c r="B13" s="7" t="inlineStr">
         <is>
-          <t>ACADIA Pharmaceuticals</t>
+          <t>Huntsman Corporation</t>
         </is>
       </c>
       <c r="C13" s="16" t="n">
-        <v>22</v>
+        <v>10.2</v>
       </c>
       <c r="D13" s="16" t="n">
-        <v>2</v>
-      </c>
-      <c r="E13" s="7" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="F13" s="7" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+        <v>1</v>
+      </c>
+      <c r="E13" s="16" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="F13" s="19" t="n">
+        <v>273</v>
       </c>
       <c r="G13" s="7" t="inlineStr">
         <is>
-          <t>Sale Of Company [incentive]; Spinoff [incent</t>
+          <t>Separation [narrative]</t>
         </is>
       </c>
     </row>
     <row r="14" ht="22" customHeight="1">
       <c r="A14" s="9" t="inlineStr">
         <is>
-          <t>HON</t>
+          <t>GNK</t>
         </is>
       </c>
       <c r="B14" s="10" t="inlineStr">
         <is>
-          <t>Honeywell Internationa</t>
+          <t>Genco Shipping &amp; Tradi</t>
         </is>
       </c>
       <c r="C14" s="17" t="n">
-        <v>22</v>
+        <v>9</v>
       </c>
       <c r="D14" s="17" t="n">
-        <v>2</v>
-      </c>
-      <c r="E14" s="10" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="F14" s="10" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+        <v>1</v>
+      </c>
+      <c r="E14" s="17" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="F14" s="20" t="n">
+        <v>174</v>
       </c>
       <c r="G14" s="10" t="inlineStr">
         <is>
-          <t>Separation [narrative]; Spinoff [incentive]</t>
+          <t>Sale Of Company [tender]</t>
         </is>
       </c>
     </row>
     <row r="15" ht="22" customHeight="1">
       <c r="A15" s="6" t="inlineStr">
         <is>
-          <t>NBIX</t>
+          <t>MCK</t>
         </is>
       </c>
       <c r="B15" s="7" t="inlineStr">
         <is>
-          <t>Neurocrine Biosciences</t>
+          <t>McKesson Corporation</t>
         </is>
       </c>
       <c r="C15" s="16" t="n">
-        <v>22</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="D15" s="16" t="n">
-        <v>2</v>
-      </c>
-      <c r="E15" s="7" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="F15" s="7" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+        <v>1</v>
+      </c>
+      <c r="E15" s="16" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="F15" s="19" t="n">
+        <v>150</v>
       </c>
       <c r="G15" s="7" t="inlineStr">
         <is>
-          <t>Sale Of Company [incentive]; Spinoff [incent</t>
+          <t>Separation [narrative]</t>
         </is>
       </c>
     </row>
     <row r="16" ht="22" customHeight="1">
       <c r="A16" s="9" t="inlineStr">
         <is>
-          <t>SNDX</t>
+          <t>TXT</t>
         </is>
       </c>
       <c r="B16" s="10" t="inlineStr">
         <is>
-          <t>Syndax Pharmaceuticals</t>
+          <t>Textron Inc.</t>
         </is>
       </c>
       <c r="C16" s="17" t="n">
-        <v>22</v>
+        <v>7.9</v>
       </c>
       <c r="D16" s="17" t="n">
-        <v>2</v>
-      </c>
-      <c r="E16" s="10" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="F16" s="10" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+        <v>1</v>
+      </c>
+      <c r="E16" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="F16" s="20" t="n">
+        <v>75</v>
       </c>
       <c r="G16" s="10" t="inlineStr">
         <is>
-          <t>Sale Of Company [incentive]; Spinoff [incent</t>
+          <t>Separation [narrative]</t>
         </is>
       </c>
     </row>
     <row r="17" ht="22" customHeight="1">
       <c r="A17" s="6" t="inlineStr">
         <is>
-          <t>SENS</t>
+          <t>ASRT</t>
         </is>
       </c>
       <c r="B17" s="7" t="inlineStr">
         <is>
-          <t>Senseonics Holdings, I</t>
+          <t>Assertio Holdings, Inc</t>
         </is>
       </c>
       <c r="C17" s="16" t="n">
-        <v>22</v>
+        <v>7.6</v>
       </c>
       <c r="D17" s="16" t="n">
-        <v>2</v>
-      </c>
-      <c r="E17" s="7" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="F17" s="7" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+        <v>1</v>
+      </c>
+      <c r="E17" s="16" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="F17" s="19" t="n">
+        <v>52</v>
       </c>
       <c r="G17" s="7" t="inlineStr">
         <is>
-          <t>Sale Of Company [incentive]; Spinoff [incent</t>
+          <t>Sale Of Company [tender]</t>
         </is>
       </c>
     </row>
     <row r="18" ht="22" customHeight="1">
       <c r="A18" s="9" t="inlineStr">
         <is>
-          <t>MIST</t>
+          <t>FSK</t>
         </is>
       </c>
       <c r="B18" s="10" t="inlineStr">
         <is>
-          <t>Milestone Pharmaceutic</t>
+          <t>FS KKR Capital Corp.</t>
         </is>
       </c>
       <c r="C18" s="17" t="n">
-        <v>22</v>
+        <v>7.6</v>
       </c>
       <c r="D18" s="17" t="n">
-        <v>2</v>
-      </c>
-      <c r="E18" s="10" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="F18" s="10" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+        <v>1</v>
+      </c>
+      <c r="E18" s="17" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="F18" s="20" t="n">
+        <v>52</v>
       </c>
       <c r="G18" s="10" t="inlineStr">
         <is>
-          <t>Sale Of Company [incentive]; Spinoff [incent</t>
+          <t>Sale Of Company [tender]</t>
         </is>
       </c>
     </row>
     <row r="19" ht="22" customHeight="1">
       <c r="A19" s="6" t="inlineStr">
         <is>
-          <t>QMCO</t>
+          <t>RGR</t>
         </is>
       </c>
       <c r="B19" s="7" t="inlineStr">
         <is>
-          <t>Quantum Corporation</t>
+          <t>Sturm, Ruger &amp; Company</t>
         </is>
       </c>
       <c r="C19" s="16" t="n">
-        <v>22</v>
+        <v>7.6</v>
       </c>
       <c r="D19" s="16" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E19" s="16" t="n">
-        <v>1.3</v>
+        <v>0.7</v>
       </c>
       <c r="F19" s="19" t="n">
-        <v>134</v>
+        <v>53</v>
       </c>
       <c r="G19" s="7" t="inlineStr">
         <is>
-          <t>Spinoff [incentive]; Strategic Review [narra</t>
+          <t>Sale Of Company [tender]</t>
         </is>
       </c>
     </row>
     <row r="20" ht="22" customHeight="1">
       <c r="A20" s="9" t="inlineStr">
         <is>
-          <t>FLEX</t>
+          <t>CVI</t>
         </is>
       </c>
       <c r="B20" s="10" t="inlineStr">
         <is>
-          <t>Flex Ltd.</t>
+          <t>CVR Energy Inc.</t>
         </is>
       </c>
       <c r="C20" s="17" t="n">
-        <v>21.1</v>
+        <v>7.5</v>
       </c>
       <c r="D20" s="17" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E20" s="17" t="n">
-        <v>0.3</v>
+        <v>3.3</v>
       </c>
       <c r="F20" s="20" t="n">
-        <v>32</v>
+        <v>300</v>
       </c>
       <c r="G20" s="10" t="inlineStr">
         <is>
-          <t>Asset Sale [narrative]; Spinoff [incentive]</t>
+          <t>Asset Sale [narrative]</t>
         </is>
       </c>
     </row>
     <row r="21" ht="22" customHeight="1">
       <c r="A21" s="6" t="inlineStr">
         <is>
-          <t>NUS</t>
+          <t>PLCE</t>
         </is>
       </c>
       <c r="B21" s="7" t="inlineStr">
         <is>
-          <t>Nu Skin Enterprises, I</t>
+          <t>Children's Place, Inc.</t>
         </is>
       </c>
       <c r="C21" s="16" t="n">
-        <v>21</v>
+        <v>7.5</v>
       </c>
       <c r="D21" s="16" t="n">
         <v>1</v>
       </c>
       <c r="E21" s="16" t="n">
-        <v>60</v>
+        <v>3</v>
       </c>
       <c r="F21" s="19" t="n">
         <v>300</v>
       </c>
       <c r="G21" s="7" t="inlineStr">
         <is>
-          <t>Asset Sale [incentive/narrative]</t>
+          <t>Asset Sale [narrative]</t>
         </is>
       </c>
     </row>
     <row r="22" ht="22" customHeight="1">
       <c r="A22" s="9" t="inlineStr">
         <is>
-          <t>HYFM</t>
+          <t>UEIC</t>
         </is>
       </c>
       <c r="B22" s="10" t="inlineStr">
         <is>
-          <t>Hydrofarm Holdings Gro</t>
+          <t>Universal Electronics</t>
         </is>
       </c>
       <c r="C22" s="17" t="n">
-        <v>21</v>
+        <v>7.5</v>
       </c>
       <c r="D22" s="17" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E22" s="17" t="n">
-        <v>3</v>
+        <v>60</v>
       </c>
       <c r="F22" s="20" t="n">
         <v>300</v>
       </c>
       <c r="G22" s="10" t="inlineStr">
         <is>
-          <t>Sale Of Company [incentive]; Strategic Revie</t>
+          <t>Asset Sale [narrative]</t>
         </is>
       </c>
     </row>
     <row r="23" ht="22" customHeight="1">
       <c r="A23" s="6" t="inlineStr">
         <is>
-          <t>RYN</t>
+          <t>ZSTK</t>
         </is>
       </c>
       <c r="B23" s="7" t="inlineStr">
         <is>
-          <t>Rayonier Inc. REIT</t>
+          <t>ZeroStack Corp.</t>
         </is>
       </c>
       <c r="C23" s="16" t="n">
-        <v>20.7</v>
+        <v>7.5</v>
       </c>
       <c r="D23" s="16" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E23" s="16" t="n">
-        <v>0.4</v>
+        <v>60</v>
       </c>
       <c r="F23" s="19" t="n">
-        <v>22</v>
+        <v>300</v>
       </c>
       <c r="G23" s="7" t="inlineStr">
         <is>
-          <t>Asset Sale [incentive]; Sale Of Company [inc</t>
+          <t>Asset Sale [narrative]</t>
         </is>
       </c>
     </row>
     <row r="24" ht="22" customHeight="1">
       <c r="A24" s="9" t="inlineStr">
         <is>
-          <t>MWA</t>
+          <t>NMRK</t>
         </is>
       </c>
       <c r="B24" s="10" t="inlineStr">
         <is>
-          <t>MUELLER WATER PRODUCTS</t>
+          <t>Newmark Group, Inc.</t>
         </is>
       </c>
       <c r="C24" s="17" t="n">
-        <v>20</v>
+        <v>7.5</v>
       </c>
       <c r="D24" s="17" t="n">
-        <v>2</v>
-      </c>
-      <c r="E24" s="10" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="F24" s="10" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+        <v>1</v>
+      </c>
+      <c r="E24" s="17" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="F24" s="20" t="n">
+        <v>300</v>
       </c>
       <c r="G24" s="10" t="inlineStr">
         <is>
-          <t>Asset Sale [narrative]; Spinoff [incentive]</t>
+          <t>Asset Sale [narrative]</t>
         </is>
       </c>
     </row>
     <row r="25" ht="22" customHeight="1">
       <c r="A25" s="6" t="inlineStr">
         <is>
-          <t>LE</t>
+          <t>OPTU</t>
         </is>
       </c>
       <c r="B25" s="7" t="inlineStr">
         <is>
-          <t>Lands' End, Inc.</t>
+          <t>Optimum Communications</t>
         </is>
       </c>
       <c r="C25" s="16" t="n">
-        <v>18.1</v>
+        <v>7.5</v>
       </c>
       <c r="D25" s="16" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E25" s="16" t="n">
-        <v>5.1</v>
+        <v>3</v>
       </c>
       <c r="F25" s="19" t="n">
-        <v>176</v>
+        <v>300</v>
       </c>
       <c r="G25" s="7" t="inlineStr">
         <is>
-          <t>Sale Of Company [tender]; Strategic Review [</t>
+          <t>Sale Of Company [narrative]</t>
         </is>
       </c>
     </row>
     <row r="26" ht="22" customHeight="1">
       <c r="A26" s="9" t="inlineStr">
         <is>
-          <t>SNOW</t>
+          <t>ONEW</t>
         </is>
       </c>
       <c r="B26" s="10" t="inlineStr">
         <is>
-          <t>Snowflake Inc.</t>
+          <t>OneWater Marine Inc.</t>
         </is>
       </c>
       <c r="C26" s="17" t="n">
-        <v>18</v>
+        <v>7.5</v>
       </c>
       <c r="D26" s="17" t="n">
-        <v>2</v>
-      </c>
-      <c r="E26" s="10" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="F26" s="10" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+        <v>1</v>
+      </c>
+      <c r="E26" s="17" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="F26" s="20" t="n">
+        <v>300</v>
       </c>
       <c r="G26" s="10" t="inlineStr">
         <is>
-          <t>Spinoff [incentive]; Strategic Review [narra</t>
+          <t>Asset Sale [narrative]</t>
         </is>
       </c>
     </row>
     <row r="27" ht="22" customHeight="1">
       <c r="A27" s="6" t="inlineStr">
         <is>
-          <t>WBD</t>
+          <t>NUS</t>
         </is>
       </c>
       <c r="B27" s="7" t="inlineStr">
         <is>
-          <t>Warner Bros. Discovery</t>
+          <t>Nu Skin Enterprises, I</t>
         </is>
       </c>
       <c r="C27" s="16" t="n">
-        <v>18</v>
+        <v>7.5</v>
       </c>
       <c r="D27" s="16" t="n">
-        <v>2</v>
-      </c>
-      <c r="E27" s="7" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="F27" s="7" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+        <v>1</v>
+      </c>
+      <c r="E27" s="16" t="n">
+        <v>60</v>
+      </c>
+      <c r="F27" s="19" t="n">
+        <v>300</v>
       </c>
       <c r="G27" s="7" t="inlineStr">
         <is>
-          <t>Sale Of Company [tender]; Separation [narrat</t>
+          <t>Asset Sale [narrative]</t>
         </is>
       </c>
     </row>
     <row r="28" ht="22" customHeight="1">
       <c r="A28" s="9" t="inlineStr">
         <is>
-          <t>ETN</t>
+          <t>CNDT</t>
         </is>
       </c>
       <c r="B28" s="10" t="inlineStr">
         <is>
-          <t>Eaton Corporation, PLC</t>
+          <t>Conduent Incorporated</t>
         </is>
       </c>
       <c r="C28" s="17" t="n">
-        <v>18</v>
+        <v>7.5</v>
       </c>
       <c r="D28" s="17" t="n">
-        <v>2</v>
-      </c>
-      <c r="E28" s="10" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="F28" s="10" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+        <v>1</v>
+      </c>
+      <c r="E28" s="17" t="n">
+        <v>60</v>
+      </c>
+      <c r="F28" s="20" t="n">
+        <v>300</v>
       </c>
       <c r="G28" s="10" t="inlineStr">
         <is>
-          <t>Separation [narrative]; Spinoff [narrative]</t>
+          <t>Asset Sale [narrative]</t>
         </is>
       </c>
     </row>
     <row r="29" ht="22" customHeight="1">
       <c r="A29" s="6" t="inlineStr">
         <is>
-          <t>CNXC</t>
+          <t>GPC</t>
         </is>
       </c>
       <c r="B29" s="7" t="inlineStr">
         <is>
-          <t>Concentrix Corporation</t>
+          <t>Genuine Parts Company</t>
         </is>
       </c>
       <c r="C29" s="16" t="n">
-        <v>16.5</v>
+        <v>7.4</v>
       </c>
       <c r="D29" s="16" t="n">
         <v>1</v>
       </c>
       <c r="E29" s="16" t="n">
-        <v>34.9</v>
+        <v>0.4</v>
       </c>
       <c r="F29" s="19" t="n">
-        <v>300</v>
+        <v>36</v>
       </c>
       <c r="G29" s="7" t="inlineStr">
         <is>
-          <t>Spinoff [incentive]</t>
+          <t>Separation [narrative]</t>
         </is>
       </c>
     </row>
     <row r="30" ht="22" customHeight="1">
       <c r="A30" s="9" t="inlineStr">
         <is>
-          <t>CLW</t>
+          <t>KDP</t>
         </is>
       </c>
       <c r="B30" s="10" t="inlineStr">
         <is>
-          <t>Clearwater Paper Corpo</t>
+          <t>Keurig Dr Pepper Inc.</t>
         </is>
       </c>
       <c r="C30" s="17" t="n">
-        <v>16.5</v>
+        <v>7.3</v>
       </c>
       <c r="D30" s="17" t="n">
         <v>1</v>
       </c>
       <c r="E30" s="17" t="n">
-        <v>60</v>
+        <v>0.4</v>
       </c>
       <c r="F30" s="20" t="n">
-        <v>300</v>
+        <v>28</v>
       </c>
       <c r="G30" s="10" t="inlineStr">
         <is>
-          <t>Spinoff [incentive]</t>
+          <t>Separation [narrative]</t>
         </is>
       </c>
     </row>
     <row r="31" ht="22" customHeight="1">
       <c r="A31" s="6" t="inlineStr">
         <is>
-          <t>JTAI</t>
+          <t>LUCK</t>
         </is>
       </c>
       <c r="B31" s="7" t="inlineStr">
         <is>
-          <t>Jet.AI Inc.</t>
+          <t>LUCKY STRIKE ENTERTAIN</t>
         </is>
       </c>
       <c r="C31" s="16" t="n">
-        <v>16.5</v>
+        <v>7</v>
       </c>
       <c r="D31" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="E31" s="16" t="n">
-        <v>60</v>
-      </c>
-      <c r="F31" s="19" t="n">
-        <v>300</v>
+      <c r="E31" s="7" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="F31" s="7" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
       <c r="G31" s="7" t="inlineStr">
         <is>
-          <t>Spinoff [incentive]</t>
+          <t>Sale Of Company [incentive]</t>
         </is>
       </c>
     </row>
     <row r="32" ht="22" customHeight="1">
       <c r="A32" s="9" t="inlineStr">
         <is>
-          <t>AMS</t>
+          <t>GMAB</t>
         </is>
       </c>
       <c r="B32" s="10" t="inlineStr">
         <is>
-          <t>American Shared Hospit</t>
+          <t>Genmab A/S</t>
         </is>
       </c>
       <c r="C32" s="17" t="n">
-        <v>16.5</v>
+        <v>7</v>
       </c>
       <c r="D32" s="17" t="n">
         <v>1</v>
       </c>
-      <c r="E32" s="17" t="n">
-        <v>60</v>
-      </c>
-      <c r="F32" s="20" t="n">
-        <v>300</v>
+      <c r="E32" s="10" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="F32" s="10" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
       <c r="G32" s="10" t="inlineStr">
         <is>
-          <t>Spinoff [incentive]</t>
+          <t>Sale Of Company [tender]</t>
         </is>
       </c>
     </row>
     <row r="33" ht="22" customHeight="1">
       <c r="A33" s="6" t="inlineStr">
         <is>
-          <t>ASTH</t>
+          <t>KALV</t>
         </is>
       </c>
       <c r="B33" s="7" t="inlineStr">
         <is>
-          <t>Astrana Health Inc.</t>
+          <t>KalVista Pharmaceutica</t>
         </is>
       </c>
       <c r="C33" s="16" t="n">
-        <v>16.5</v>
+        <v>7</v>
       </c>
       <c r="D33" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="E33" s="16" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="F33" s="19" t="n">
-        <v>300</v>
+      <c r="E33" s="7" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="F33" s="7" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
       <c r="G33" s="7" t="inlineStr">
         <is>
-          <t>Spinoff [incentive]</t>
+          <t>Sale Of Company [tender]</t>
         </is>
       </c>
     </row>
     <row r="34" ht="22" customHeight="1">
       <c r="A34" s="9" t="inlineStr">
         <is>
-          <t>GPRO</t>
+          <t>JNJ</t>
         </is>
       </c>
       <c r="B34" s="10" t="inlineStr">
         <is>
-          <t>GoPro, Inc.</t>
+          <t>Johnson &amp; Johnson</t>
         </is>
       </c>
       <c r="C34" s="17" t="n">
-        <v>16.5</v>
+        <v>7</v>
       </c>
       <c r="D34" s="17" t="n">
         <v>1</v>
       </c>
-      <c r="E34" s="17" t="n">
-        <v>3</v>
-      </c>
-      <c r="F34" s="20" t="n">
-        <v>300</v>
+      <c r="E34" s="10" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="F34" s="10" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
       <c r="G34" s="10" t="inlineStr">
         <is>
-          <t>Spinoff [incentive]</t>
+          <t>Separation [narrative]</t>
         </is>
       </c>
     </row>
     <row r="35" ht="22" customHeight="1">
       <c r="A35" s="6" t="inlineStr">
         <is>
-          <t>LGL</t>
+          <t>HON</t>
         </is>
       </c>
       <c r="B35" s="7" t="inlineStr">
         <is>
-          <t>LGL Group, Inc. (The)</t>
+          <t>Honeywell Internationa</t>
         </is>
       </c>
       <c r="C35" s="16" t="n">
-        <v>16.5</v>
+        <v>7</v>
       </c>
       <c r="D35" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="E35" s="16" t="n">
-        <v>41.6</v>
-      </c>
-      <c r="F35" s="19" t="n">
-        <v>300</v>
+      <c r="E35" s="7" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="F35" s="7" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
       <c r="G35" s="7" t="inlineStr">
         <is>
-          <t>Spinoff [incentive]</t>
+          <t>Separation [narrative]</t>
         </is>
       </c>
     </row>
     <row r="36" ht="22" customHeight="1">
       <c r="A36" s="9" t="inlineStr">
         <is>
-          <t>VREX</t>
+          <t>BHC</t>
         </is>
       </c>
       <c r="B36" s="10" t="inlineStr">
         <is>
-          <t>Varex Imaging Corporat</t>
+          <t>BHC</t>
         </is>
       </c>
       <c r="C36" s="17" t="n">
-        <v>16.5</v>
+        <v>7</v>
       </c>
       <c r="D36" s="17" t="n">
         <v>1</v>
       </c>
-      <c r="E36" s="17" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="F36" s="20" t="n">
-        <v>300</v>
+      <c r="E36" s="10" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="F36" s="10" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
       <c r="G36" s="10" t="inlineStr">
         <is>
-          <t>Spinoff [incentive]</t>
+          <t>Separation [narrative]</t>
         </is>
       </c>
     </row>
     <row r="37" ht="22" customHeight="1">
       <c r="A37" s="6" t="inlineStr">
         <is>
-          <t>PAGP</t>
+          <t>NFE</t>
         </is>
       </c>
       <c r="B37" s="7" t="inlineStr">
         <is>
-          <t>Plains GP Holdings, L.</t>
+          <t>NFE</t>
         </is>
       </c>
       <c r="C37" s="16" t="n">
-        <v>16.5</v>
+        <v>7</v>
       </c>
       <c r="D37" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="E37" s="16" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="F37" s="19" t="n">
-        <v>300</v>
+      <c r="E37" s="7" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="F37" s="7" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
       <c r="G37" s="7" t="inlineStr">
         <is>
-          <t>Spinoff [incentive]</t>
+          <t>Separation [narrative]</t>
         </is>
       </c>
     </row>
     <row r="38" ht="22" customHeight="1">
       <c r="A38" s="9" t="inlineStr">
         <is>
-          <t>FUN</t>
+          <t>CR</t>
         </is>
       </c>
       <c r="B38" s="10" t="inlineStr">
         <is>
-          <t>Six Flags Entertainmen</t>
+          <t>Crane Company</t>
         </is>
       </c>
       <c r="C38" s="17" t="n">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="D38" s="17" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E38" s="10" t="inlineStr">
         <is>
@@ -7289,482 +7297,482 @@
       </c>
       <c r="G38" s="10" t="inlineStr">
         <is>
-          <t>Asset Sale [narrative]; Sale Of Company [inc</t>
+          <t>Spinoff [narrative]</t>
         </is>
       </c>
     </row>
     <row r="39" ht="22" customHeight="1">
       <c r="A39" s="6" t="inlineStr">
         <is>
-          <t>NTGR</t>
+          <t>CTVA</t>
         </is>
       </c>
       <c r="B39" s="7" t="inlineStr">
         <is>
-          <t>NETGEAR, Inc.</t>
+          <t>Corteva, Inc.</t>
         </is>
       </c>
       <c r="C39" s="16" t="n">
-        <v>15.4</v>
+        <v>7</v>
       </c>
       <c r="D39" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="E39" s="16" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="F39" s="19" t="n">
-        <v>239</v>
+      <c r="E39" s="7" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="F39" s="7" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
       <c r="G39" s="7" t="inlineStr">
         <is>
-          <t>Spinoff [incentive]</t>
+          <t>Spinoff [narrative]</t>
         </is>
       </c>
     </row>
     <row r="40" ht="22" customHeight="1">
       <c r="A40" s="9" t="inlineStr">
         <is>
-          <t>RCMT</t>
+          <t>LAB</t>
         </is>
       </c>
       <c r="B40" s="10" t="inlineStr">
         <is>
-          <t>RCM Technologies, Inc.</t>
+          <t>Standard BioTools Inc.</t>
         </is>
       </c>
       <c r="C40" s="17" t="n">
-        <v>15.1</v>
+        <v>6.8</v>
       </c>
       <c r="D40" s="17" t="n">
         <v>1</v>
       </c>
       <c r="E40" s="17" t="n">
-        <v>2.5</v>
+        <v>42.3</v>
       </c>
       <c r="F40" s="20" t="n">
-        <v>224</v>
+        <v>212</v>
       </c>
       <c r="G40" s="10" t="inlineStr">
         <is>
-          <t>Spinoff [incentive]</t>
+          <t>Asset Sale [narrative]</t>
         </is>
       </c>
     </row>
     <row r="41" ht="22" customHeight="1">
       <c r="A41" s="6" t="inlineStr">
         <is>
-          <t>LBTYK</t>
+          <t>DLX</t>
         </is>
       </c>
       <c r="B41" s="7" t="inlineStr">
         <is>
-          <t>Liberty Global Ltd.</t>
+          <t>Deluxe Corporation</t>
         </is>
       </c>
       <c r="C41" s="16" t="n">
-        <v>14.9</v>
+        <v>6.7</v>
       </c>
       <c r="D41" s="16" t="n">
         <v>1</v>
       </c>
       <c r="E41" s="16" t="n">
-        <v>43</v>
+        <v>3</v>
       </c>
       <c r="F41" s="19" t="n">
-        <v>215</v>
+        <v>200</v>
       </c>
       <c r="G41" s="7" t="inlineStr">
         <is>
-          <t>Spinoff [incentive]</t>
+          <t>Asset Sale [narrative]</t>
         </is>
       </c>
     </row>
     <row r="42" ht="22" customHeight="1">
       <c r="A42" s="9" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>HE</t>
         </is>
       </c>
       <c r="B42" s="10" t="inlineStr">
         <is>
-          <t>Macy's Inc</t>
+          <t>Hawaiian Electric Indu</t>
         </is>
       </c>
       <c r="C42" s="17" t="n">
-        <v>14.5</v>
+        <v>6.4</v>
       </c>
       <c r="D42" s="17" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E42" s="17" t="n">
-        <v>2</v>
+        <v>2.7</v>
       </c>
       <c r="F42" s="20" t="n">
-        <v>127</v>
+        <v>173</v>
       </c>
       <c r="G42" s="10" t="inlineStr">
         <is>
-          <t>Asset Sale [narrative]; Strategic Review [na</t>
+          <t>Asset Sale [narrative]</t>
         </is>
       </c>
     </row>
     <row r="43" ht="22" customHeight="1">
       <c r="A43" s="6" t="inlineStr">
         <is>
-          <t>OWLT</t>
+          <t>PLTK</t>
         </is>
       </c>
       <c r="B43" s="7" t="inlineStr">
         <is>
-          <t>Owlet, Inc.</t>
+          <t>Playtika Holding Corp.</t>
         </is>
       </c>
       <c r="C43" s="16" t="n">
-        <v>14.4</v>
+        <v>6.3</v>
       </c>
       <c r="D43" s="16" t="n">
         <v>1</v>
       </c>
       <c r="E43" s="16" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="F43" s="19" t="n">
-        <v>183</v>
+        <v>154</v>
       </c>
       <c r="G43" s="7" t="inlineStr">
         <is>
-          <t>Spinoff [incentive]</t>
+          <t>Asset Sale [narrative]</t>
         </is>
       </c>
     </row>
     <row r="44" ht="22" customHeight="1">
       <c r="A44" s="9" t="inlineStr">
         <is>
-          <t>GDRX</t>
+          <t>STRZ</t>
         </is>
       </c>
       <c r="B44" s="10" t="inlineStr">
         <is>
-          <t>GoodRx Holdings, Inc.</t>
+          <t>Starz Entertainment Co</t>
         </is>
       </c>
       <c r="C44" s="17" t="n">
-        <v>14.2</v>
+        <v>6.2</v>
       </c>
       <c r="D44" s="17" t="n">
         <v>1</v>
       </c>
       <c r="E44" s="17" t="n">
-        <v>2.6</v>
+        <v>2.9</v>
       </c>
       <c r="F44" s="20" t="n">
-        <v>172</v>
+        <v>147</v>
       </c>
       <c r="G44" s="10" t="inlineStr">
         <is>
-          <t>Spinoff [incentive]</t>
+          <t>Asset Sale [narrative]</t>
         </is>
       </c>
     </row>
     <row r="45" ht="22" customHeight="1">
       <c r="A45" s="6" t="inlineStr">
         <is>
-          <t>GLIBK</t>
+          <t>HLLY</t>
         </is>
       </c>
       <c r="B45" s="7" t="inlineStr">
         <is>
-          <t>Liberty Capital Corpor</t>
+          <t>Holley Inc.</t>
         </is>
       </c>
       <c r="C45" s="16" t="n">
-        <v>14</v>
+        <v>6.2</v>
       </c>
       <c r="D45" s="16" t="n">
         <v>1</v>
       </c>
       <c r="E45" s="16" t="n">
-        <v>32.9</v>
+        <v>6.3</v>
       </c>
       <c r="F45" s="19" t="n">
-        <v>164</v>
+        <v>142</v>
       </c>
       <c r="G45" s="7" t="inlineStr">
         <is>
-          <t>Spinoff [incentive]</t>
+          <t>Asset Sale [narrative]</t>
         </is>
       </c>
     </row>
     <row r="46" ht="22" customHeight="1">
       <c r="A46" s="9" t="inlineStr">
         <is>
-          <t>LSTA</t>
+          <t>ANDE</t>
         </is>
       </c>
       <c r="B46" s="10" t="inlineStr">
         <is>
-          <t>Lisata Therapeutics, I</t>
+          <t>The Andersons, Inc.</t>
         </is>
       </c>
       <c r="C46" s="17" t="n">
-        <v>14</v>
+        <v>6.2</v>
       </c>
       <c r="D46" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="E46" s="17" t="n">
         <v>2</v>
       </c>
-      <c r="E46" s="10" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="F46" s="10" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+      <c r="F46" s="20" t="n">
+        <v>150</v>
       </c>
       <c r="G46" s="10" t="inlineStr">
         <is>
-          <t>Sale Of Company [tender]; Strategic Review [</t>
+          <t>Asset Sale [narrative]</t>
         </is>
       </c>
     </row>
     <row r="47" ht="22" customHeight="1">
       <c r="A47" s="6" t="inlineStr">
         <is>
-          <t>LNC</t>
+          <t>CNMD</t>
         </is>
       </c>
       <c r="B47" s="7" t="inlineStr">
         <is>
-          <t>Lincoln National Corpo</t>
+          <t>CONMED Corporation</t>
         </is>
       </c>
       <c r="C47" s="16" t="n">
-        <v>13.8</v>
+        <v>6.2</v>
       </c>
       <c r="D47" s="16" t="n">
         <v>1</v>
       </c>
       <c r="E47" s="16" t="n">
-        <v>4.3</v>
+        <v>3.1</v>
       </c>
       <c r="F47" s="19" t="n">
         <v>150</v>
       </c>
       <c r="G47" s="7" t="inlineStr">
         <is>
-          <t>Spinoff [incentive]</t>
+          <t>Asset Sale [narrative]</t>
         </is>
       </c>
     </row>
     <row r="48" ht="22" customHeight="1">
       <c r="A48" s="9" t="inlineStr">
         <is>
-          <t>AHT</t>
+          <t>BIRD</t>
         </is>
       </c>
       <c r="B48" s="10" t="inlineStr">
         <is>
-          <t>Ashford Hospitality Tr</t>
+          <t>Allbirds, Inc.</t>
         </is>
       </c>
       <c r="C48" s="17" t="n">
-        <v>13.8</v>
+        <v>6.1</v>
       </c>
       <c r="D48" s="17" t="n">
         <v>1</v>
       </c>
       <c r="E48" s="17" t="n">
-        <v>1.5</v>
+        <v>1.8</v>
       </c>
       <c r="F48" s="20" t="n">
-        <v>150</v>
+        <v>137</v>
       </c>
       <c r="G48" s="10" t="inlineStr">
         <is>
-          <t>Spinoff [incentive]</t>
+          <t>Asset Sale [narrative]</t>
         </is>
       </c>
     </row>
     <row r="49" ht="22" customHeight="1">
       <c r="A49" s="6" t="inlineStr">
         <is>
-          <t>ASIX</t>
+          <t>TLYS</t>
         </is>
       </c>
       <c r="B49" s="7" t="inlineStr">
         <is>
-          <t>AdvanSix Inc.</t>
+          <t>Tilly's, Inc.</t>
         </is>
       </c>
       <c r="C49" s="16" t="n">
-        <v>13.8</v>
+        <v>6.1</v>
       </c>
       <c r="D49" s="16" t="n">
         <v>1</v>
       </c>
       <c r="E49" s="16" t="n">
-        <v>5.8</v>
+        <v>1.9</v>
       </c>
       <c r="F49" s="19" t="n">
-        <v>150</v>
+        <v>135</v>
       </c>
       <c r="G49" s="7" t="inlineStr">
         <is>
-          <t>Spinoff [incentive]</t>
+          <t>Sale Of Company [narrative]</t>
         </is>
       </c>
     </row>
     <row r="50" ht="22" customHeight="1">
       <c r="A50" s="9" t="inlineStr">
         <is>
-          <t>KD</t>
+          <t>UGI</t>
         </is>
       </c>
       <c r="B50" s="10" t="inlineStr">
         <is>
-          <t>Kyndryl Holdings, Inc.</t>
+          <t>UGI Corporation</t>
         </is>
       </c>
       <c r="C50" s="17" t="n">
-        <v>13.8</v>
+        <v>6</v>
       </c>
       <c r="D50" s="17" t="n">
         <v>1</v>
       </c>
       <c r="E50" s="17" t="n">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="F50" s="20" t="n">
-        <v>150</v>
+        <v>122</v>
       </c>
       <c r="G50" s="10" t="inlineStr">
         <is>
-          <t>Spinoff [incentive]</t>
+          <t>Asset Sale [narrative]</t>
         </is>
       </c>
     </row>
     <row r="51" ht="22" customHeight="1">
       <c r="A51" s="6" t="inlineStr">
         <is>
-          <t>PAA</t>
+          <t>CMT</t>
         </is>
       </c>
       <c r="B51" s="7" t="inlineStr">
         <is>
-          <t>Plains All American Pi</t>
+          <t>Core Molding Technolog</t>
         </is>
       </c>
       <c r="C51" s="16" t="n">
-        <v>13.8</v>
+        <v>5.9</v>
       </c>
       <c r="D51" s="16" t="n">
         <v>1</v>
       </c>
       <c r="E51" s="16" t="n">
-        <v>2</v>
+        <v>1.8</v>
       </c>
       <c r="F51" s="19" t="n">
-        <v>150</v>
+        <v>104</v>
       </c>
       <c r="G51" s="7" t="inlineStr">
         <is>
-          <t>Spinoff [incentive]</t>
+          <t>Asset Sale [narrative]</t>
         </is>
       </c>
     </row>
     <row r="52" ht="22" customHeight="1">
       <c r="A52" s="9" t="inlineStr">
         <is>
-          <t>VYX</t>
+          <t>SITC</t>
         </is>
       </c>
       <c r="B52" s="10" t="inlineStr">
         <is>
-          <t>NCR Voyix Corporation</t>
+          <t>SITE Centers Corp.</t>
         </is>
       </c>
       <c r="C52" s="17" t="n">
-        <v>13.8</v>
+        <v>5.8</v>
       </c>
       <c r="D52" s="17" t="n">
         <v>1</v>
       </c>
       <c r="E52" s="17" t="n">
-        <v>2.7</v>
+        <v>2.8</v>
       </c>
       <c r="F52" s="20" t="n">
-        <v>150</v>
+        <v>91</v>
       </c>
       <c r="G52" s="10" t="inlineStr">
         <is>
-          <t>Spinoff [incentive]</t>
+          <t>Asset Sale [narrative]</t>
         </is>
       </c>
     </row>
     <row r="53" ht="22" customHeight="1">
       <c r="A53" s="6" t="inlineStr">
         <is>
-          <t>VSNT</t>
+          <t>VTOL</t>
         </is>
       </c>
       <c r="B53" s="7" t="inlineStr">
         <is>
-          <t>Versant Media Group, I</t>
+          <t>Bristow Group, Inc.</t>
         </is>
       </c>
       <c r="C53" s="16" t="n">
-        <v>13.6</v>
+        <v>5.7</v>
       </c>
       <c r="D53" s="16" t="n">
         <v>1</v>
       </c>
       <c r="E53" s="16" t="n">
-        <v>28.3</v>
+        <v>1.4</v>
       </c>
       <c r="F53" s="19" t="n">
-        <v>141</v>
+        <v>79</v>
       </c>
       <c r="G53" s="7" t="inlineStr">
         <is>
-          <t>Spinoff [incentive]</t>
+          <t>Asset Sale [narrative]</t>
         </is>
       </c>
     </row>
     <row r="54" ht="22" customHeight="1">
       <c r="A54" s="9" t="inlineStr">
         <is>
-          <t>AQMS</t>
+          <t>MNRO</t>
         </is>
       </c>
       <c r="B54" s="10" t="inlineStr">
         <is>
-          <t>Aqua Metals, Inc.</t>
+          <t>Monro, Inc.</t>
         </is>
       </c>
       <c r="C54" s="17" t="n">
-        <v>13.6</v>
+        <v>5.6</v>
       </c>
       <c r="D54" s="17" t="n">
         <v>1</v>
       </c>
       <c r="E54" s="17" t="n">
-        <v>3.5</v>
+        <v>1.8</v>
       </c>
       <c r="F54" s="20" t="n">
-        <v>140</v>
+        <v>66</v>
       </c>
       <c r="G54" s="10" t="inlineStr">
         <is>
-          <t>Spinoff [incentive]</t>
+          <t>Sale Of Company [narrative]</t>
         </is>
       </c>
     </row>
     <row r="56" ht="28" customHeight="1">
       <c r="A56" s="11" t="inlineStr">
         <is>
-          <t>382 names carry a corporate-action re-rate catalyst (28 carry two or more types). Distribution: spinoff 125, sale of company 119, strategic review 78, asset sale 77, separation 11. Sources by hardness: INCENTIVE = the PSU plan pays management to achieve the spin/sale/M&amp;A (skin in the game, hardest); TENDER = a live bid (role TARGET); NARRATIVE = management states the intent in the 10-K/10-Q MD&amp;A. A catalyst named by two independent sources is triangulated (+bonus); two distinct catalyst types is the in-play configuration. Score = catalyst strength x (1 + geometry upside room), so a spin/sale with real re-rate headroom outranks one in an already-fair-valued name (rows with '—' ratio have no value-geometry floor — typically large-caps where the re-rate is a discount-collapse story, not an asset-floor play). Source: rerate_catalysts.py.</t>
+          <t>191 names carry a corporate-action re-rate catalyst (7 carry two or more types). Distribution: strategic review 78, asset sale 66, sale of company 40, separation 11, spinoff 3. Sources by hardness: INCENTIVE = the PSU plan pays management to achieve the spin/sale/M&amp;A (skin in the game, hardest); TENDER = a live bid (role TARGET); NARRATIVE = management states the intent in the 10-K/10-Q MD&amp;A. A catalyst named by two independent sources is triangulated (+bonus); two distinct catalyst types is the in-play configuration. Score = catalyst strength x (1 + geometry upside room), so a spin/sale with real re-rate headroom outranks one in an already-fair-valued name (rows with '—' ratio have no value-geometry floor — typically large-caps where the re-rate is a discount-collapse story, not an asset-floor play). Source: rerate_catalysts.py.</t>
         </is>
       </c>
     </row>
@@ -8387,7 +8395,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:F80"/>
+  <dimension ref="A1:F75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -8460,163 +8468,163 @@
     <row r="6" ht="22" customHeight="1">
       <c r="A6" s="6" t="inlineStr">
         <is>
-          <t>ANGX</t>
+          <t>AGPU</t>
         </is>
       </c>
       <c r="B6" s="7" t="inlineStr">
         <is>
-          <t>Angel Studios, Inc.</t>
+          <t>Axe Compute Inc.</t>
         </is>
       </c>
       <c r="C6" s="16" t="n">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="D6" s="16" t="n">
-        <v>100</v>
+        <v>44</v>
       </c>
       <c r="E6" s="7" t="inlineStr">
         <is>
-          <t>5.3m</t>
+          <t>4.1m</t>
         </is>
       </c>
       <c r="F6" s="7" t="inlineStr">
         <is>
-          <t>SALE_OF_COMPANY</t>
+          <t>STRATEGIC_REVIEW</t>
         </is>
       </c>
     </row>
     <row r="7" ht="22" customHeight="1">
       <c r="A7" s="9" t="inlineStr">
         <is>
-          <t>KPLT</t>
+          <t>CNMD</t>
         </is>
       </c>
       <c r="B7" s="10" t="inlineStr">
         <is>
-          <t>Katapult Holdings, I</t>
+          <t>CONMED Corporation</t>
         </is>
       </c>
       <c r="C7" s="17" t="n">
-        <v>49</v>
+        <v>34</v>
       </c>
       <c r="D7" s="17" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E7" s="10" t="inlineStr">
         <is>
-          <t>5.9m</t>
+          <t>4.6m</t>
         </is>
       </c>
       <c r="F7" s="10" t="inlineStr">
         <is>
-          <t>SALE_OF_COMPANY</t>
+          <t>ASSET_SALE</t>
         </is>
       </c>
     </row>
     <row r="8" ht="22" customHeight="1">
       <c r="A8" s="6" t="inlineStr">
         <is>
-          <t>SENS</t>
+          <t>ANF</t>
         </is>
       </c>
       <c r="B8" s="7" t="inlineStr">
         <is>
-          <t>Senseonics Holdings,</t>
+          <t>Abercrombie &amp; Fitch</t>
         </is>
       </c>
       <c r="C8" s="16" t="n">
-        <v>44</v>
+        <v>34</v>
       </c>
       <c r="D8" s="16" t="n">
-        <v>31</v>
+        <v>68</v>
       </c>
       <c r="E8" s="7" t="inlineStr">
         <is>
-          <t>5.4m</t>
+          <t>5.7m</t>
         </is>
       </c>
       <c r="F8" s="7" t="inlineStr">
         <is>
-          <t>SALE_OF_COMPANY, SPINOFF</t>
+          <t>STRATEGIC_REVIEW</t>
         </is>
       </c>
     </row>
     <row r="9" ht="22" customHeight="1">
       <c r="A9" s="9" t="inlineStr">
         <is>
-          <t>FLGT</t>
+          <t>GPC</t>
         </is>
       </c>
       <c r="B9" s="10" t="inlineStr">
         <is>
-          <t>Fulgent Genetics, In</t>
+          <t>Genuine Parts Compan</t>
         </is>
       </c>
       <c r="C9" s="17" t="n">
-        <v>44</v>
+        <v>30</v>
       </c>
       <c r="D9" s="17" t="n">
         <v>34</v>
       </c>
       <c r="E9" s="10" t="inlineStr">
         <is>
-          <t>5.6m</t>
+          <t>4.9m</t>
         </is>
       </c>
       <c r="F9" s="10" t="inlineStr">
         <is>
-          <t>SALE_OF_COMPANY</t>
+          <t>SEPARATION</t>
         </is>
       </c>
     </row>
     <row r="10" ht="22" customHeight="1">
       <c r="A10" s="6" t="inlineStr">
         <is>
-          <t>AGPU</t>
+          <t>HWH</t>
         </is>
       </c>
       <c r="B10" s="7" t="inlineStr">
         <is>
-          <t>Axe Compute Inc.</t>
+          <t>HWH</t>
         </is>
       </c>
       <c r="C10" s="16" t="n">
-        <v>44</v>
+        <v>28</v>
       </c>
       <c r="D10" s="16" t="n">
-        <v>51</v>
+        <v>105</v>
       </c>
       <c r="E10" s="7" t="inlineStr">
         <is>
-          <t>4.1m</t>
+          <t>5.7m</t>
         </is>
       </c>
       <c r="F10" s="7" t="inlineStr">
         <is>
-          <t>STRATEGIC_REVIEW</t>
+          <t>SALE_OF_COMPANY</t>
         </is>
       </c>
     </row>
     <row r="11" ht="22" customHeight="1">
       <c r="A11" s="9" t="inlineStr">
         <is>
-          <t>XPRO</t>
+          <t>MNPR</t>
         </is>
       </c>
       <c r="B11" s="10" t="inlineStr">
         <is>
-          <t>Expro Group Holdings</t>
+          <t>MNPR</t>
         </is>
       </c>
       <c r="C11" s="17" t="n">
-        <v>43</v>
+        <v>28</v>
       </c>
       <c r="D11" s="17" t="n">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="E11" s="10" t="inlineStr">
         <is>
-          <t>17.4m</t>
+          <t>5.7m</t>
         </is>
       </c>
       <c r="F11" s="10" t="inlineStr">
@@ -8628,23 +8636,23 @@
     <row r="12" ht="22" customHeight="1">
       <c r="A12" s="6" t="inlineStr">
         <is>
-          <t>PEPG</t>
+          <t>XHLD</t>
         </is>
       </c>
       <c r="B12" s="7" t="inlineStr">
         <is>
-          <t>PepGen Inc.</t>
+          <t>XHLD</t>
         </is>
       </c>
       <c r="C12" s="16" t="n">
-        <v>42</v>
+        <v>28</v>
       </c>
       <c r="D12" s="16" t="n">
-        <v>100</v>
+        <v>927</v>
       </c>
       <c r="E12" s="7" t="inlineStr">
         <is>
-          <t>4.6m</t>
+          <t>6.0m</t>
         </is>
       </c>
       <c r="F12" s="7" t="inlineStr">
@@ -8656,51 +8664,51 @@
     <row r="13" ht="22" customHeight="1">
       <c r="A13" s="9" t="inlineStr">
         <is>
-          <t>OSPN</t>
+          <t>PARK</t>
         </is>
       </c>
       <c r="B13" s="10" t="inlineStr">
         <is>
-          <t>OneSpan Inc.</t>
+          <t>PARK</t>
         </is>
       </c>
       <c r="C13" s="17" t="n">
-        <v>41</v>
+        <v>28</v>
       </c>
       <c r="D13" s="17" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="E13" s="10" t="inlineStr">
         <is>
-          <t>4.8m</t>
+          <t>5.8m</t>
         </is>
       </c>
       <c r="F13" s="10" t="inlineStr">
         <is>
-          <t>SPINOFF</t>
+          <t>SALE_OF_COMPANY</t>
         </is>
       </c>
     </row>
     <row r="14" ht="22" customHeight="1">
       <c r="A14" s="6" t="inlineStr">
         <is>
-          <t>FUBO</t>
+          <t>CUEN</t>
         </is>
       </c>
       <c r="B14" s="7" t="inlineStr">
         <is>
-          <t>fuboTV Inc.</t>
+          <t>CUEN</t>
         </is>
       </c>
       <c r="C14" s="16" t="n">
-        <v>41</v>
+        <v>28</v>
       </c>
       <c r="D14" s="16" t="n">
-        <v>35</v>
+        <v>49</v>
       </c>
       <c r="E14" s="7" t="inlineStr">
         <is>
-          <t>3.0m</t>
+          <t>4.8m</t>
         </is>
       </c>
       <c r="F14" s="7" t="inlineStr">
@@ -8712,1451 +8720,1424 @@
     <row r="15" ht="22" customHeight="1">
       <c r="A15" s="9" t="inlineStr">
         <is>
-          <t>UAN</t>
+          <t>CVI</t>
         </is>
       </c>
       <c r="B15" s="10" t="inlineStr">
         <is>
-          <t>CVR Partners, LP</t>
+          <t>CVR Energy Inc.</t>
         </is>
       </c>
       <c r="C15" s="17" t="n">
-        <v>39</v>
+        <v>26</v>
       </c>
       <c r="D15" s="17" t="n">
-        <v>63</v>
+        <v>49</v>
       </c>
       <c r="E15" s="10" t="inlineStr">
         <is>
-          <t>17.0m</t>
+          <t>4.6m</t>
         </is>
       </c>
       <c r="F15" s="10" t="inlineStr">
         <is>
-          <t>SALE_OF_COMPANY</t>
+          <t>ASSET_SALE</t>
         </is>
       </c>
     </row>
     <row r="16" ht="22" customHeight="1">
       <c r="A16" s="6" t="inlineStr">
         <is>
-          <t>NIQ</t>
+          <t>ITGR</t>
         </is>
       </c>
       <c r="B16" s="7" t="inlineStr">
         <is>
-          <t>NIQ Global Intellige</t>
+          <t>Integer Holdings Cor</t>
         </is>
       </c>
       <c r="C16" s="16" t="n">
-        <v>38</v>
+        <v>25</v>
       </c>
       <c r="D16" s="16" t="n">
-        <v>124</v>
+        <v>41</v>
       </c>
       <c r="E16" s="7" t="inlineStr">
         <is>
-          <t>5.3m</t>
+          <t>4.6m</t>
         </is>
       </c>
       <c r="F16" s="7" t="inlineStr">
         <is>
-          <t>SALE_OF_COMPANY</t>
+          <t>STRATEGIC_REVIEW</t>
         </is>
       </c>
     </row>
     <row r="17" ht="22" customHeight="1">
       <c r="A17" s="9" t="inlineStr">
         <is>
-          <t>UTZ</t>
+          <t>ACHV</t>
         </is>
       </c>
       <c r="B17" s="10" t="inlineStr">
         <is>
-          <t>Utz Brands Inc</t>
+          <t>Achieve Life Science</t>
         </is>
       </c>
       <c r="C17" s="17" t="n">
-        <v>37</v>
+        <v>24</v>
       </c>
       <c r="D17" s="17" t="n">
-        <v>79</v>
+        <v>36</v>
       </c>
       <c r="E17" s="10" t="inlineStr">
         <is>
-          <t>6.2m</t>
+          <t>4.6m</t>
         </is>
       </c>
       <c r="F17" s="10" t="inlineStr">
         <is>
-          <t>SALE_OF_COMPANY</t>
+          <t>ASSET_SALE</t>
         </is>
       </c>
     </row>
     <row r="18" ht="22" customHeight="1">
       <c r="A18" s="6" t="inlineStr">
         <is>
-          <t>VREX</t>
+          <t>LITS</t>
         </is>
       </c>
       <c r="B18" s="7" t="inlineStr">
         <is>
-          <t>Varex Imaging Corpor</t>
+          <t>LITS</t>
         </is>
       </c>
       <c r="C18" s="16" t="n">
-        <v>34</v>
+        <v>23</v>
       </c>
       <c r="D18" s="16" t="n">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="E18" s="7" t="inlineStr">
         <is>
-          <t>8.6m</t>
+          <t>4.1m</t>
         </is>
       </c>
       <c r="F18" s="7" t="inlineStr">
         <is>
-          <t>SPINOFF</t>
+          <t>STRATEGIC_REVIEW</t>
         </is>
       </c>
     </row>
     <row r="19" ht="22" customHeight="1">
       <c r="A19" s="9" t="inlineStr">
         <is>
-          <t>ZURA</t>
+          <t>CLRO</t>
         </is>
       </c>
       <c r="B19" s="10" t="inlineStr">
         <is>
-          <t>Zura Bio Limited</t>
+          <t>CLRO</t>
         </is>
       </c>
       <c r="C19" s="17" t="n">
-        <v>34</v>
+        <v>23</v>
       </c>
       <c r="D19" s="17" t="n">
-        <v>24</v>
+        <v>45</v>
       </c>
       <c r="E19" s="10" t="inlineStr">
         <is>
-          <t>4.6m</t>
+          <t>5.6m</t>
         </is>
       </c>
       <c r="F19" s="10" t="inlineStr">
         <is>
-          <t>SPINOFF</t>
+          <t>STRATEGIC_REVIEW</t>
         </is>
       </c>
     </row>
     <row r="20" ht="22" customHeight="1">
       <c r="A20" s="6" t="inlineStr">
         <is>
-          <t>ACAD</t>
+          <t>MRAI</t>
         </is>
       </c>
       <c r="B20" s="7" t="inlineStr">
         <is>
-          <t>ACADIA Pharmaceutica</t>
+          <t>MRAI</t>
         </is>
       </c>
       <c r="C20" s="16" t="n">
-        <v>34</v>
+        <v>23</v>
       </c>
       <c r="D20" s="16" t="n">
-        <v>28</v>
+        <v>353</v>
       </c>
       <c r="E20" s="7" t="inlineStr">
         <is>
-          <t>4.8m</t>
+          <t>4.1m</t>
         </is>
       </c>
       <c r="F20" s="7" t="inlineStr">
         <is>
-          <t>SALE_OF_COMPANY, SPINOFF</t>
+          <t>STRATEGIC_REVIEW</t>
         </is>
       </c>
     </row>
     <row r="21" ht="22" customHeight="1">
       <c r="A21" s="9" t="inlineStr">
         <is>
-          <t>CNMD</t>
+          <t>RPMT</t>
         </is>
       </c>
       <c r="B21" s="10" t="inlineStr">
         <is>
-          <t>CONMED Corporation</t>
+          <t>RPMT</t>
         </is>
       </c>
       <c r="C21" s="17" t="n">
-        <v>34</v>
+        <v>23</v>
       </c>
       <c r="D21" s="17" t="n">
-        <v>31</v>
+        <v>21</v>
       </c>
       <c r="E21" s="10" t="inlineStr">
         <is>
-          <t>4.6m</t>
+          <t>5.6m</t>
         </is>
       </c>
       <c r="F21" s="10" t="inlineStr">
         <is>
-          <t>ASSET_SALE</t>
+          <t>STRATEGIC_REVIEW</t>
         </is>
       </c>
     </row>
     <row r="22" ht="22" customHeight="1">
       <c r="A22" s="6" t="inlineStr">
         <is>
-          <t>ANF</t>
+          <t>ONAR</t>
         </is>
       </c>
       <c r="B22" s="7" t="inlineStr">
         <is>
-          <t>Abercrombie &amp; Fitch</t>
+          <t>ONAR</t>
         </is>
       </c>
       <c r="C22" s="16" t="n">
+        <v>20</v>
+      </c>
+      <c r="D22" s="16" t="n">
+        <v>336</v>
+      </c>
+      <c r="E22" s="7" t="inlineStr">
+        <is>
+          <t>3.2m</t>
+        </is>
+      </c>
+      <c r="F22" s="7" t="inlineStr">
+        <is>
+          <t>ASSET_SALE</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="21" t="inlineStr">
+        <is>
+          <t>(17 confirmed / 1 pending / 74 neutral / 51 fading, of 143 priced)</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="12" t="inlineStr">
+        <is>
+          <t>ALL CANDIDATES — pre-confirmation tail odds</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="18" customHeight="1">
+      <c r="A26" s="15" t="inlineStr">
+        <is>
+          <t>Ticker</t>
+        </is>
+      </c>
+      <c r="B26" s="15" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="C26" s="4" t="inlineStr">
+        <is>
+          <t>Tail p</t>
+        </is>
+      </c>
+      <c r="D26" s="4" t="inlineStr">
+        <is>
+          <t>State</t>
+        </is>
+      </c>
+      <c r="E26" s="4" t="inlineStr">
+        <is>
+          <t>Ratio</t>
+        </is>
+      </c>
+      <c r="F26" s="4" t="inlineStr">
+        <is>
+          <t>Tail drivers</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="22" customHeight="1">
+      <c r="A27" s="6" t="inlineStr">
+        <is>
+          <t>OPTU</t>
+        </is>
+      </c>
+      <c r="B27" s="7" t="inlineStr">
+        <is>
+          <t>Optimum Communicatio</t>
+        </is>
+      </c>
+      <c r="C27" s="16" t="n">
+        <v>35</v>
+      </c>
+      <c r="D27" s="7" t="inlineStr">
+        <is>
+          <t>NEUTRAL</t>
+        </is>
+      </c>
+      <c r="E27" s="16" t="n">
+        <v>3</v>
+      </c>
+      <c r="F27" s="7" t="inlineStr">
+        <is>
+          <t>catalyst=SALE_OF_COMPANY, size=small,</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="22" customHeight="1">
+      <c r="A28" s="9" t="inlineStr">
+        <is>
+          <t>DFH</t>
+        </is>
+      </c>
+      <c r="B28" s="10" t="inlineStr">
+        <is>
+          <t>Dream Finders Homes,</t>
+        </is>
+      </c>
+      <c r="C28" s="17" t="n">
+        <v>35</v>
+      </c>
+      <c r="D28" s="10" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="E28" s="17" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="F28" s="10" t="inlineStr">
+        <is>
+          <t>sector=Consumer Cyclical, size=small,</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="22" customHeight="1">
+      <c r="A29" s="6" t="inlineStr">
+        <is>
+          <t>CWH</t>
+        </is>
+      </c>
+      <c r="B29" s="7" t="inlineStr">
+        <is>
+          <t>Camping World Holdin</t>
+        </is>
+      </c>
+      <c r="C29" s="16" t="n">
+        <v>35</v>
+      </c>
+      <c r="D29" s="7" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="E29" s="16" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="F29" s="7" t="inlineStr">
+        <is>
+          <t>sector=Consumer Cyclical, size=small,</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="22" customHeight="1">
+      <c r="A30" s="9" t="inlineStr">
+        <is>
+          <t>LE</t>
+        </is>
+      </c>
+      <c r="B30" s="10" t="inlineStr">
+        <is>
+          <t>Lands' End, Inc.</t>
+        </is>
+      </c>
+      <c r="C30" s="17" t="n">
         <v>34</v>
       </c>
-      <c r="D22" s="16" t="n">
-        <v>67</v>
-      </c>
-      <c r="E22" s="7" t="inlineStr">
-        <is>
-          <t>5.7m</t>
-        </is>
-      </c>
-      <c r="F22" s="7" t="inlineStr">
-        <is>
-          <t>STRATEGIC_REVIEW</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="22" customHeight="1">
-      <c r="A23" s="9" t="inlineStr">
-        <is>
-          <t>BEEP</t>
-        </is>
-      </c>
-      <c r="B23" s="10" t="inlineStr">
-        <is>
-          <t>Mobile Infrastructur</t>
-        </is>
-      </c>
-      <c r="C23" s="17" t="n">
+      <c r="D30" s="10" t="inlineStr">
+        <is>
+          <t>NEUTRAL</t>
+        </is>
+      </c>
+      <c r="E30" s="17" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="F30" s="10" t="inlineStr">
+        <is>
+          <t>catalyst=SALE_OF_COMPANY, sector=Consu</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="22" customHeight="1">
+      <c r="A31" s="6" t="inlineStr">
+        <is>
+          <t>LUCK</t>
+        </is>
+      </c>
+      <c r="B31" s="7" t="inlineStr">
+        <is>
+          <t>LUCKY STRIKE ENTERTA</t>
+        </is>
+      </c>
+      <c r="C31" s="16" t="n">
+        <v>34</v>
+      </c>
+      <c r="D31" s="7" t="inlineStr">
+        <is>
+          <t>FADING</t>
+        </is>
+      </c>
+      <c r="E31" s="7" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="F31" s="7" t="inlineStr">
+        <is>
+          <t>catalyst=SALE_OF_COMPANY, sector=Consu</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="22" customHeight="1">
+      <c r="A32" s="9" t="inlineStr">
+        <is>
+          <t>MNRO</t>
+        </is>
+      </c>
+      <c r="B32" s="10" t="inlineStr">
+        <is>
+          <t>Monro, Inc.</t>
+        </is>
+      </c>
+      <c r="C32" s="17" t="n">
+        <v>34</v>
+      </c>
+      <c r="D32" s="10" t="inlineStr">
+        <is>
+          <t>FADING</t>
+        </is>
+      </c>
+      <c r="E32" s="17" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="F32" s="10" t="inlineStr">
+        <is>
+          <t>catalyst=SALE_OF_COMPANY, sector=Consu</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="22" customHeight="1">
+      <c r="A33" s="6" t="inlineStr">
+        <is>
+          <t>DXLG</t>
+        </is>
+      </c>
+      <c r="B33" s="7" t="inlineStr">
+        <is>
+          <t>Destination XL Group</t>
+        </is>
+      </c>
+      <c r="C33" s="16" t="n">
+        <v>32</v>
+      </c>
+      <c r="D33" s="7" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="E33" s="16" t="n">
+        <v>60</v>
+      </c>
+      <c r="F33" s="7" t="inlineStr">
+        <is>
+          <t>catalyst=SALE_OF_COMPANY, sector=Consu</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="22" customHeight="1">
+      <c r="A34" s="9" t="inlineStr">
+        <is>
+          <t>DXC</t>
+        </is>
+      </c>
+      <c r="B34" s="10" t="inlineStr">
+        <is>
+          <t>DXC Technology Compa</t>
+        </is>
+      </c>
+      <c r="C34" s="17" t="n">
+        <v>31</v>
+      </c>
+      <c r="D34" s="10" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="E34" s="17" t="n">
+        <v>30</v>
+      </c>
+      <c r="F34" s="10" t="inlineStr">
+        <is>
+          <t>sector=Technology, size=small, drawdow</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="22" customHeight="1">
+      <c r="A35" s="6" t="inlineStr">
+        <is>
+          <t>LMRI</t>
+        </is>
+      </c>
+      <c r="B35" s="7" t="inlineStr">
+        <is>
+          <t>Lumexa Imaging Holdi</t>
+        </is>
+      </c>
+      <c r="C35" s="16" t="n">
+        <v>30</v>
+      </c>
+      <c r="D35" s="7" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="E35" s="16" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="F35" s="7" t="inlineStr">
+        <is>
+          <t>size=small, drawdown_12m=deep(&lt;-50%),</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="22" customHeight="1">
+      <c r="A36" s="9" t="inlineStr">
+        <is>
+          <t>CMTL</t>
+        </is>
+      </c>
+      <c r="B36" s="10" t="inlineStr">
+        <is>
+          <t>Comtech Telecommunic</t>
+        </is>
+      </c>
+      <c r="C36" s="17" t="n">
+        <v>29</v>
+      </c>
+      <c r="D36" s="10" t="inlineStr">
+        <is>
+          <t>FADING</t>
+        </is>
+      </c>
+      <c r="E36" s="17" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="F36" s="10" t="inlineStr">
+        <is>
+          <t>sector=Technology, size=micro, drawdow</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="22" customHeight="1">
+      <c r="A37" s="6" t="inlineStr">
+        <is>
+          <t>AGPU</t>
+        </is>
+      </c>
+      <c r="B37" s="7" t="inlineStr">
+        <is>
+          <t>Axe Compute Inc.</t>
+        </is>
+      </c>
+      <c r="C37" s="16" t="n">
+        <v>29</v>
+      </c>
+      <c r="D37" s="7" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="E37" s="16" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="F37" s="7" t="inlineStr">
+        <is>
+          <t>sector=Technology, size=micro, drawdow</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="22" customHeight="1">
+      <c r="A38" s="9" t="inlineStr">
+        <is>
+          <t>GRNT</t>
+        </is>
+      </c>
+      <c r="B38" s="10" t="inlineStr">
+        <is>
+          <t>Granite Ridge Resour</t>
+        </is>
+      </c>
+      <c r="C38" s="17" t="n">
+        <v>29</v>
+      </c>
+      <c r="D38" s="10" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="E38" s="17" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="F38" s="10" t="inlineStr">
+        <is>
+          <t>sector=Energy, size=small, drawdown_12</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="22" customHeight="1">
+      <c r="A39" s="6" t="inlineStr">
+        <is>
+          <t>DEC</t>
+        </is>
+      </c>
+      <c r="B39" s="7" t="inlineStr">
+        <is>
+          <t>Diversified Energy C</t>
+        </is>
+      </c>
+      <c r="C39" s="16" t="n">
+        <v>29</v>
+      </c>
+      <c r="D39" s="7" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="E39" s="16" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="F39" s="7" t="inlineStr">
+        <is>
+          <t>sector=Energy, size=small, drawdown_12</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="22" customHeight="1">
+      <c r="A40" s="9" t="inlineStr">
+        <is>
+          <t>ADNT</t>
+        </is>
+      </c>
+      <c r="B40" s="10" t="inlineStr">
+        <is>
+          <t>Adient plc</t>
+        </is>
+      </c>
+      <c r="C40" s="17" t="n">
+        <v>29</v>
+      </c>
+      <c r="D40" s="10" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="E40" s="17" t="n">
+        <v>6.3</v>
+      </c>
+      <c r="F40" s="10" t="inlineStr">
+        <is>
+          <t>sector=Consumer Cyclical, size=small,</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="22" customHeight="1">
+      <c r="A41" s="6" t="inlineStr">
+        <is>
+          <t>CMRC</t>
+        </is>
+      </c>
+      <c r="B41" s="7" t="inlineStr">
+        <is>
+          <t>Commerce.com, Inc. -</t>
+        </is>
+      </c>
+      <c r="C41" s="16" t="n">
+        <v>29</v>
+      </c>
+      <c r="D41" s="7" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="E41" s="16" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="F41" s="7" t="inlineStr">
+        <is>
+          <t>sector=Technology, size=micro, drawdow</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="22" customHeight="1">
+      <c r="A42" s="9" t="inlineStr">
+        <is>
+          <t>THRY</t>
+        </is>
+      </c>
+      <c r="B42" s="10" t="inlineStr">
+        <is>
+          <t>Thryv Holdings, Inc.</t>
+        </is>
+      </c>
+      <c r="C42" s="17" t="n">
+        <v>29</v>
+      </c>
+      <c r="D42" s="10" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="E42" s="17" t="n">
+        <v>10.9</v>
+      </c>
+      <c r="F42" s="10" t="inlineStr">
+        <is>
+          <t>sector=Technology, size=micro, drawdow</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="22" customHeight="1">
+      <c r="A43" s="6" t="inlineStr">
+        <is>
+          <t>BTAI</t>
+        </is>
+      </c>
+      <c r="B43" s="7" t="inlineStr">
+        <is>
+          <t>BioXcel Therapeutics</t>
+        </is>
+      </c>
+      <c r="C43" s="16" t="n">
+        <v>28</v>
+      </c>
+      <c r="D43" s="7" t="inlineStr">
+        <is>
+          <t>NEUTRAL</t>
+        </is>
+      </c>
+      <c r="E43" s="7" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="F43" s="7" t="inlineStr">
+        <is>
+          <t>catalyst=SALE_OF_COMPANY, size=micro,</t>
+        </is>
+      </c>
+    </row>
+    <row r="44" ht="22" customHeight="1">
+      <c r="A44" s="9" t="inlineStr">
+        <is>
+          <t>WKHS</t>
+        </is>
+      </c>
+      <c r="B44" s="10" t="inlineStr">
+        <is>
+          <t>Workhorse Group, Inc</t>
+        </is>
+      </c>
+      <c r="C44" s="17" t="n">
+        <v>27</v>
+      </c>
+      <c r="D44" s="10" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="E44" s="17" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="F44" s="10" t="inlineStr">
+        <is>
+          <t>sector=Consumer Cyclical, size=micro,</t>
+        </is>
+      </c>
+    </row>
+    <row r="45" ht="22" customHeight="1">
+      <c r="A45" s="6" t="inlineStr">
+        <is>
+          <t>LAB</t>
+        </is>
+      </c>
+      <c r="B45" s="7" t="inlineStr">
+        <is>
+          <t>Standard BioTools In</t>
+        </is>
+      </c>
+      <c r="C45" s="16" t="n">
+        <v>27</v>
+      </c>
+      <c r="D45" s="7" t="inlineStr">
+        <is>
+          <t>NEUTRAL</t>
+        </is>
+      </c>
+      <c r="E45" s="16" t="n">
+        <v>42.3</v>
+      </c>
+      <c r="F45" s="7" t="inlineStr">
+        <is>
+          <t>size=small, drawdown_12m=deep(&lt;-50%),</t>
+        </is>
+      </c>
+    </row>
+    <row r="46" ht="22" customHeight="1">
+      <c r="A46" s="9" t="inlineStr">
+        <is>
+          <t>SITC</t>
+        </is>
+      </c>
+      <c r="B46" s="10" t="inlineStr">
+        <is>
+          <t>SITE Centers Corp.</t>
+        </is>
+      </c>
+      <c r="C46" s="17" t="n">
+        <v>26</v>
+      </c>
+      <c r="D46" s="10" t="inlineStr">
+        <is>
+          <t>NEUTRAL</t>
+        </is>
+      </c>
+      <c r="E46" s="17" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="F46" s="10" t="inlineStr">
+        <is>
+          <t>sector=Real Estate, size=micro, drawdo</t>
+        </is>
+      </c>
+    </row>
+    <row r="47" ht="22" customHeight="1">
+      <c r="A47" s="6" t="inlineStr">
+        <is>
+          <t>FRMI</t>
+        </is>
+      </c>
+      <c r="B47" s="7" t="inlineStr">
+        <is>
+          <t>Fermi Inc.</t>
+        </is>
+      </c>
+      <c r="C47" s="16" t="n">
+        <v>26</v>
+      </c>
+      <c r="D47" s="7" t="inlineStr">
+        <is>
+          <t>FADING</t>
+        </is>
+      </c>
+      <c r="E47" s="7" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="F47" s="7" t="inlineStr">
+        <is>
+          <t>sector=Real Estate, drawdown_12m=deep(</t>
+        </is>
+      </c>
+    </row>
+    <row r="48" ht="22" customHeight="1">
+      <c r="A48" s="9" t="inlineStr">
+        <is>
+          <t>CNDT</t>
+        </is>
+      </c>
+      <c r="B48" s="10" t="inlineStr">
+        <is>
+          <t>Conduent Incorporate</t>
+        </is>
+      </c>
+      <c r="C48" s="17" t="n">
+        <v>26</v>
+      </c>
+      <c r="D48" s="10" t="inlineStr">
+        <is>
+          <t>NEUTRAL</t>
+        </is>
+      </c>
+      <c r="E48" s="17" t="n">
+        <v>60</v>
+      </c>
+      <c r="F48" s="10" t="inlineStr">
+        <is>
+          <t>sector=Technology, size=micro, drawdow</t>
+        </is>
+      </c>
+    </row>
+    <row r="49" ht="22" customHeight="1">
+      <c r="A49" s="6" t="inlineStr">
+        <is>
+          <t>MATV</t>
+        </is>
+      </c>
+      <c r="B49" s="7" t="inlineStr">
+        <is>
+          <t>Mativ Holdings, Inc.</t>
+        </is>
+      </c>
+      <c r="C49" s="16" t="n">
+        <v>26</v>
+      </c>
+      <c r="D49" s="7" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="E49" s="16" t="n">
+        <v>7.1</v>
+      </c>
+      <c r="F49" s="7" t="inlineStr">
+        <is>
+          <t>sector=Basic Materials, size=small, dr</t>
+        </is>
+      </c>
+    </row>
+    <row r="50" ht="22" customHeight="1">
+      <c r="A50" s="9" t="inlineStr">
+        <is>
+          <t>PAHC</t>
+        </is>
+      </c>
+      <c r="B50" s="10" t="inlineStr">
+        <is>
+          <t>Phibro Animal Health</t>
+        </is>
+      </c>
+      <c r="C50" s="17" t="n">
+        <v>25</v>
+      </c>
+      <c r="D50" s="10" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="E50" s="17" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="F50" s="10" t="inlineStr">
+        <is>
+          <t>size=small, drawdown_12m=mod(-50..-20%</t>
+        </is>
+      </c>
+    </row>
+    <row r="51" ht="22" customHeight="1">
+      <c r="A51" s="6" t="inlineStr">
+        <is>
+          <t>BALY</t>
+        </is>
+      </c>
+      <c r="B51" s="7" t="inlineStr">
+        <is>
+          <t>Bally's Corporation</t>
+        </is>
+      </c>
+      <c r="C51" s="16" t="n">
+        <v>25</v>
+      </c>
+      <c r="D51" s="7" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="E51" s="16" t="n">
+        <v>38.5</v>
+      </c>
+      <c r="F51" s="7" t="inlineStr">
+        <is>
+          <t>sector=Consumer Cyclical, size=small,</t>
+        </is>
+      </c>
+    </row>
+    <row r="52" ht="22" customHeight="1">
+      <c r="A52" s="9" t="inlineStr">
+        <is>
+          <t>BIRD</t>
+        </is>
+      </c>
+      <c r="B52" s="10" t="inlineStr">
+        <is>
+          <t>Allbirds, Inc.</t>
+        </is>
+      </c>
+      <c r="C52" s="17" t="n">
+        <v>24</v>
+      </c>
+      <c r="D52" s="10" t="inlineStr">
+        <is>
+          <t>FADING</t>
+        </is>
+      </c>
+      <c r="E52" s="17" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="F52" s="10" t="inlineStr">
+        <is>
+          <t>sector=Consumer Cyclical, size=micro,</t>
+        </is>
+      </c>
+    </row>
+    <row r="53" ht="22" customHeight="1">
+      <c r="A53" s="6" t="inlineStr">
+        <is>
+          <t>PLCE</t>
+        </is>
+      </c>
+      <c r="B53" s="7" t="inlineStr">
+        <is>
+          <t>Children's Place, In</t>
+        </is>
+      </c>
+      <c r="C53" s="16" t="n">
+        <v>24</v>
+      </c>
+      <c r="D53" s="7" t="inlineStr">
+        <is>
+          <t>NEUTRAL</t>
+        </is>
+      </c>
+      <c r="E53" s="16" t="n">
+        <v>3</v>
+      </c>
+      <c r="F53" s="7" t="inlineStr">
+        <is>
+          <t>sector=Consumer Cyclical, size=micro,</t>
+        </is>
+      </c>
+    </row>
+    <row r="54" ht="22" customHeight="1">
+      <c r="A54" s="9" t="inlineStr">
+        <is>
+          <t>FULC</t>
+        </is>
+      </c>
+      <c r="B54" s="10" t="inlineStr">
+        <is>
+          <t>Fulcrum Therapeutics</t>
+        </is>
+      </c>
+      <c r="C54" s="17" t="n">
+        <v>23</v>
+      </c>
+      <c r="D54" s="10" t="inlineStr">
+        <is>
+          <t>NEUTRAL</t>
+        </is>
+      </c>
+      <c r="E54" s="17" t="n">
+        <v>8.300000000000001</v>
+      </c>
+      <c r="F54" s="10" t="inlineStr">
+        <is>
+          <t>size=micro, drawdown_12m=deep(&lt;-50%),</t>
+        </is>
+      </c>
+    </row>
+    <row r="55" ht="22" customHeight="1">
+      <c r="A55" s="6" t="inlineStr">
+        <is>
+          <t>NERV</t>
+        </is>
+      </c>
+      <c r="B55" s="7" t="inlineStr">
+        <is>
+          <t>Minerva Neuroscience</t>
+        </is>
+      </c>
+      <c r="C55" s="16" t="n">
+        <v>23</v>
+      </c>
+      <c r="D55" s="7" t="inlineStr">
+        <is>
+          <t>FADING</t>
+        </is>
+      </c>
+      <c r="E55" s="7" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="F55" s="7" t="inlineStr">
+        <is>
+          <t>size=micro, drawdown_12m=deep(&lt;-50%),</t>
+        </is>
+      </c>
+    </row>
+    <row r="56" ht="22" customHeight="1">
+      <c r="A56" s="9" t="inlineStr">
+        <is>
+          <t>NEUP</t>
+        </is>
+      </c>
+      <c r="B56" s="10" t="inlineStr">
+        <is>
+          <t>Neuphoria Therapeuti</t>
+        </is>
+      </c>
+      <c r="C56" s="17" t="n">
+        <v>23</v>
+      </c>
+      <c r="D56" s="10" t="inlineStr">
+        <is>
+          <t>FADING</t>
+        </is>
+      </c>
+      <c r="E56" s="17" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="F56" s="10" t="inlineStr">
+        <is>
+          <t>size=micro, drawdown_12m=deep(&lt;-50%),</t>
+        </is>
+      </c>
+    </row>
+    <row r="57" ht="22" customHeight="1">
+      <c r="A57" s="6" t="inlineStr">
+        <is>
+          <t>BFAM</t>
+        </is>
+      </c>
+      <c r="B57" s="7" t="inlineStr">
+        <is>
+          <t>Bright Horizons Fami</t>
+        </is>
+      </c>
+      <c r="C57" s="16" t="n">
+        <v>23</v>
+      </c>
+      <c r="D57" s="7" t="inlineStr">
+        <is>
+          <t>NEUTRAL</t>
+        </is>
+      </c>
+      <c r="E57" s="7" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="F57" s="7" t="inlineStr">
+        <is>
+          <t>sector=Consumer Cyclical, drawdown_12m</t>
+        </is>
+      </c>
+    </row>
+    <row r="58" ht="22" customHeight="1">
+      <c r="A58" s="9" t="inlineStr">
+        <is>
+          <t>PMCB</t>
+        </is>
+      </c>
+      <c r="B58" s="10" t="inlineStr">
+        <is>
+          <t>PharmaCyte  Biotech,</t>
+        </is>
+      </c>
+      <c r="C58" s="17" t="n">
+        <v>23</v>
+      </c>
+      <c r="D58" s="10" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="E58" s="17" t="n">
+        <v>30</v>
+      </c>
+      <c r="F58" s="10" t="inlineStr">
+        <is>
+          <t>size=micro, drawdown_12m=deep(&lt;-50%),</t>
+        </is>
+      </c>
+    </row>
+    <row r="59" ht="22" customHeight="1">
+      <c r="A59" s="6" t="inlineStr">
+        <is>
+          <t>LUCY</t>
+        </is>
+      </c>
+      <c r="B59" s="7" t="inlineStr">
+        <is>
+          <t>Innovative Eyewear,</t>
+        </is>
+      </c>
+      <c r="C59" s="16" t="n">
+        <v>23</v>
+      </c>
+      <c r="D59" s="7" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="E59" s="16" t="n">
+        <v>45.6</v>
+      </c>
+      <c r="F59" s="7" t="inlineStr">
+        <is>
+          <t>size=micro, drawdown_12m=deep(&lt;-50%),</t>
+        </is>
+      </c>
+    </row>
+    <row r="60" ht="22" customHeight="1">
+      <c r="A60" s="9" t="inlineStr">
+        <is>
+          <t>ACH</t>
+        </is>
+      </c>
+      <c r="B60" s="10" t="inlineStr">
+        <is>
+          <t>Accendra Health, Inc</t>
+        </is>
+      </c>
+      <c r="C60" s="17" t="n">
+        <v>23</v>
+      </c>
+      <c r="D60" s="10" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="E60" s="17" t="n">
+        <v>60</v>
+      </c>
+      <c r="F60" s="10" t="inlineStr">
+        <is>
+          <t>size=micro, drawdown_12m=deep(&lt;-50%),</t>
+        </is>
+      </c>
+    </row>
+    <row r="61" ht="22" customHeight="1">
+      <c r="A61" s="6" t="inlineStr">
+        <is>
+          <t>MDIA</t>
+        </is>
+      </c>
+      <c r="B61" s="7" t="inlineStr">
+        <is>
+          <t>Mediaco Holding Inc.</t>
+        </is>
+      </c>
+      <c r="C61" s="16" t="n">
+        <v>23</v>
+      </c>
+      <c r="D61" s="7" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="E61" s="16" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="F61" s="7" t="inlineStr">
+        <is>
+          <t>size=micro, drawdown_12m=deep(&lt;-50%),</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="12" t="inlineStr">
+        <is>
+          <t>WHAT RAISES TAIL ODDS (historical lift vs 15% base)</t>
+        </is>
+      </c>
+    </row>
+    <row r="64" ht="18" customHeight="1">
+      <c r="A64" s="4" t="inlineStr">
+        <is>
+          <t>Feature = bin</t>
+        </is>
+      </c>
+      <c r="B64" s="4" t="inlineStr">
+        <is>
+          <t>Tail rate</t>
+        </is>
+      </c>
+      <c r="C64" s="4" t="inlineStr">
+        <is>
+          <t>Lift</t>
+        </is>
+      </c>
+      <c r="D64" s="4" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="E64" s="15" t="inlineStr"/>
+    </row>
+    <row r="65" ht="16" customHeight="1">
+      <c r="A65" s="6" t="inlineStr">
+        <is>
+          <t>size = small</t>
+        </is>
+      </c>
+      <c r="B65" s="16" t="n">
+        <v>38</v>
+      </c>
+      <c r="C65" s="7" t="inlineStr">
+        <is>
+          <t>2.49x</t>
+        </is>
+      </c>
+      <c r="D65" s="5" t="n">
+        <v>8</v>
+      </c>
+      <c r="E65" s="7" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+    </row>
+    <row r="66" ht="16" customHeight="1">
+      <c r="A66" s="9" t="inlineStr">
+        <is>
+          <t>drawdown_12m = deep(&lt;-50%)</t>
+        </is>
+      </c>
+      <c r="B66" s="17" t="n">
+        <v>32</v>
+      </c>
+      <c r="C66" s="10" t="inlineStr">
+        <is>
+          <t>2.11x</t>
+        </is>
+      </c>
+      <c r="D66" s="8" t="n">
+        <v>22</v>
+      </c>
+      <c r="E66" s="10" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+    </row>
+    <row r="67" ht="16" customHeight="1">
+      <c r="A67" s="6" t="inlineStr">
+        <is>
+          <t>sector = Real Estate</t>
+        </is>
+      </c>
+      <c r="B67" s="16" t="n">
         <v>33</v>
       </c>
-      <c r="D23" s="17" t="n">
-        <v>34</v>
-      </c>
-      <c r="E23" s="10" t="inlineStr">
-        <is>
-          <t>4.8m</t>
-        </is>
-      </c>
-      <c r="F23" s="10" t="inlineStr">
-        <is>
-          <t>SALE_OF_COMPANY, SPINOFF</t>
-        </is>
-      </c>
-    </row>
-    <row r="24" ht="22" customHeight="1">
-      <c r="A24" s="6" t="inlineStr">
-        <is>
-          <t>CLW</t>
-        </is>
-      </c>
-      <c r="B24" s="7" t="inlineStr">
-        <is>
-          <t>Clearwater Paper Cor</t>
-        </is>
-      </c>
-      <c r="C24" s="16" t="n">
-        <v>32</v>
-      </c>
-      <c r="D24" s="16" t="n">
-        <v>50</v>
-      </c>
-      <c r="E24" s="7" t="inlineStr">
-        <is>
-          <t>5.7m</t>
-        </is>
-      </c>
-      <c r="F24" s="7" t="inlineStr">
-        <is>
-          <t>SPINOFF</t>
-        </is>
-      </c>
-    </row>
-    <row r="25" ht="22" customHeight="1">
-      <c r="A25" s="9" t="inlineStr">
-        <is>
-          <t>GPC</t>
-        </is>
-      </c>
-      <c r="B25" s="10" t="inlineStr">
-        <is>
-          <t>Genuine Parts Compan</t>
-        </is>
-      </c>
-      <c r="C25" s="17" t="n">
+      <c r="C67" s="7" t="inlineStr">
+        <is>
+          <t>2.22x</t>
+        </is>
+      </c>
+      <c r="D67" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="E67" s="7" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+    </row>
+    <row r="68" ht="16" customHeight="1">
+      <c r="A68" s="9" t="inlineStr">
+        <is>
+          <t>sector = Technology</t>
+        </is>
+      </c>
+      <c r="B68" s="17" t="n">
         <v>30</v>
       </c>
-      <c r="D25" s="17" t="n">
-        <v>34</v>
-      </c>
-      <c r="E25" s="10" t="inlineStr">
-        <is>
-          <t>4.9m</t>
-        </is>
-      </c>
-      <c r="F25" s="10" t="inlineStr">
-        <is>
-          <t>SEPARATION</t>
-        </is>
-      </c>
-    </row>
-    <row r="26" ht="22" customHeight="1">
-      <c r="A26" s="6" t="inlineStr">
-        <is>
-          <t>RBRK</t>
-        </is>
-      </c>
-      <c r="B26" s="7" t="inlineStr">
-        <is>
-          <t>Rubrik, Inc.</t>
-        </is>
-      </c>
-      <c r="C26" s="16" t="n">
-        <v>29</v>
-      </c>
-      <c r="D26" s="16" t="n">
-        <v>24</v>
-      </c>
-      <c r="E26" s="7" t="inlineStr">
-        <is>
-          <t>5.1m</t>
-        </is>
-      </c>
-      <c r="F26" s="7" t="inlineStr">
-        <is>
-          <t>SPINOFF</t>
-        </is>
-      </c>
-    </row>
-    <row r="27" ht="22" customHeight="1">
-      <c r="A27" s="9" t="inlineStr">
-        <is>
-          <t>HWH</t>
-        </is>
-      </c>
-      <c r="B27" s="10" t="inlineStr">
-        <is>
-          <t>HWH</t>
-        </is>
-      </c>
-      <c r="C27" s="17" t="n">
-        <v>28</v>
-      </c>
-      <c r="D27" s="17" t="n">
-        <v>106</v>
-      </c>
-      <c r="E27" s="10" t="inlineStr">
-        <is>
-          <t>5.7m</t>
-        </is>
-      </c>
-      <c r="F27" s="10" t="inlineStr">
-        <is>
-          <t>SALE_OF_COMPANY</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="21" t="inlineStr">
-        <is>
-          <t>(26 confirmed / 0 pending / 65 neutral / 56 fading, of 147 priced)</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="12" t="inlineStr">
-        <is>
-          <t>ALL CANDIDATES — pre-confirmation tail odds</t>
-        </is>
-      </c>
-    </row>
-    <row r="31" ht="18" customHeight="1">
-      <c r="A31" s="15" t="inlineStr">
-        <is>
-          <t>Ticker</t>
-        </is>
-      </c>
-      <c r="B31" s="15" t="inlineStr">
-        <is>
-          <t>Name</t>
-        </is>
-      </c>
-      <c r="C31" s="4" t="inlineStr">
-        <is>
-          <t>Tail p</t>
-        </is>
-      </c>
-      <c r="D31" s="4" t="inlineStr">
-        <is>
-          <t>State</t>
-        </is>
-      </c>
-      <c r="E31" s="4" t="inlineStr">
-        <is>
-          <t>Ratio</t>
-        </is>
-      </c>
-      <c r="F31" s="4" t="inlineStr">
-        <is>
-          <t>Tail drivers</t>
-        </is>
-      </c>
-    </row>
-    <row r="32" ht="22" customHeight="1">
-      <c r="A32" s="6" t="inlineStr">
-        <is>
-          <t>SES</t>
-        </is>
-      </c>
-      <c r="B32" s="7" t="inlineStr">
-        <is>
-          <t>SES AI Corporation</t>
-        </is>
-      </c>
-      <c r="C32" s="16" t="n">
-        <v>40</v>
-      </c>
-      <c r="D32" s="7" t="inlineStr">
-        <is>
-          <t>FADING</t>
-        </is>
-      </c>
-      <c r="E32" s="7" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="F32" s="7" t="inlineStr">
-        <is>
-          <t>catalyst=SALE_OF_COMPANY, sector=Consu</t>
-        </is>
-      </c>
-    </row>
-    <row r="33" ht="22" customHeight="1">
-      <c r="A33" s="9" t="inlineStr">
-        <is>
-          <t>CNXC</t>
-        </is>
-      </c>
-      <c r="B33" s="10" t="inlineStr">
-        <is>
-          <t>Concentrix Corporati</t>
-        </is>
-      </c>
-      <c r="C33" s="17" t="n">
-        <v>39</v>
-      </c>
-      <c r="D33" s="10" t="inlineStr">
-        <is>
-          <t>NEUTRAL</t>
-        </is>
-      </c>
-      <c r="E33" s="17" t="n">
-        <v>34.9</v>
-      </c>
-      <c r="F33" s="10" t="inlineStr">
-        <is>
-          <t>catalyst=SPINOFF, sector=Technology, s</t>
-        </is>
-      </c>
-    </row>
-    <row r="34" ht="22" customHeight="1">
-      <c r="A34" s="6" t="inlineStr">
-        <is>
-          <t>CTMX</t>
-        </is>
-      </c>
-      <c r="B34" s="7" t="inlineStr">
-        <is>
-          <t>CytomX Therapeutics,</t>
-        </is>
-      </c>
-      <c r="C34" s="16" t="n">
-        <v>35</v>
-      </c>
-      <c r="D34" s="7" t="inlineStr">
-        <is>
-          <t>NEUTRAL</t>
-        </is>
-      </c>
-      <c r="E34" s="7" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="F34" s="7" t="inlineStr">
-        <is>
-          <t>catalyst=SALE_OF_COMPANY, size=small,</t>
-        </is>
-      </c>
-    </row>
-    <row r="35" ht="22" customHeight="1">
-      <c r="A35" s="9" t="inlineStr">
-        <is>
-          <t>WVE</t>
-        </is>
-      </c>
-      <c r="B35" s="10" t="inlineStr">
-        <is>
-          <t>Wave Life Sciences L</t>
-        </is>
-      </c>
-      <c r="C35" s="17" t="n">
-        <v>35</v>
-      </c>
-      <c r="D35" s="10" t="inlineStr">
-        <is>
-          <t>FADING</t>
-        </is>
-      </c>
-      <c r="E35" s="17" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="F35" s="10" t="inlineStr">
-        <is>
-          <t>catalyst=SALE_OF_COMPANY, size=small,</t>
-        </is>
-      </c>
-    </row>
-    <row r="36" ht="22" customHeight="1">
-      <c r="A36" s="6" t="inlineStr">
-        <is>
-          <t>ANGX</t>
-        </is>
-      </c>
-      <c r="B36" s="7" t="inlineStr">
-        <is>
-          <t>Angel Studios, Inc.</t>
-        </is>
-      </c>
-      <c r="C36" s="16" t="n">
-        <v>35</v>
-      </c>
-      <c r="D36" s="7" t="inlineStr">
-        <is>
-          <t>CONFIRMED</t>
-        </is>
-      </c>
-      <c r="E36" s="7" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="F36" s="7" t="inlineStr">
-        <is>
-          <t>catalyst=SALE_OF_COMPANY, size=small,</t>
-        </is>
-      </c>
-    </row>
-    <row r="37" ht="22" customHeight="1">
-      <c r="A37" s="9" t="inlineStr">
-        <is>
-          <t>DFH</t>
-        </is>
-      </c>
-      <c r="B37" s="10" t="inlineStr">
-        <is>
-          <t>Dream Finders Homes,</t>
-        </is>
-      </c>
-      <c r="C37" s="17" t="n">
-        <v>35</v>
-      </c>
-      <c r="D37" s="10" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="E37" s="17" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="F37" s="10" t="inlineStr">
-        <is>
-          <t>sector=Consumer Cyclical, size=small,</t>
-        </is>
-      </c>
-    </row>
-    <row r="38" ht="22" customHeight="1">
-      <c r="A38" s="6" t="inlineStr">
-        <is>
-          <t>CWH</t>
-        </is>
-      </c>
-      <c r="B38" s="7" t="inlineStr">
-        <is>
-          <t>Camping World Holdin</t>
-        </is>
-      </c>
-      <c r="C38" s="16" t="n">
-        <v>35</v>
-      </c>
-      <c r="D38" s="7" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="E38" s="16" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="F38" s="7" t="inlineStr">
-        <is>
-          <t>sector=Consumer Cyclical, size=small,</t>
-        </is>
-      </c>
-    </row>
-    <row r="39" ht="22" customHeight="1">
-      <c r="A39" s="9" t="inlineStr">
-        <is>
-          <t>OPTU</t>
-        </is>
-      </c>
-      <c r="B39" s="10" t="inlineStr">
-        <is>
-          <t>Optimum Communicatio</t>
-        </is>
-      </c>
-      <c r="C39" s="17" t="n">
-        <v>35</v>
-      </c>
-      <c r="D39" s="10" t="inlineStr">
-        <is>
-          <t>NEUTRAL</t>
-        </is>
-      </c>
-      <c r="E39" s="17" t="n">
-        <v>3</v>
-      </c>
-      <c r="F39" s="10" t="inlineStr">
-        <is>
-          <t>catalyst=SALE_OF_COMPANY, size=small,</t>
-        </is>
-      </c>
-    </row>
-    <row r="40" ht="22" customHeight="1">
-      <c r="A40" s="6" t="inlineStr">
-        <is>
-          <t>MNRO</t>
-        </is>
-      </c>
-      <c r="B40" s="7" t="inlineStr">
-        <is>
-          <t>Monro, Inc.</t>
-        </is>
-      </c>
-      <c r="C40" s="16" t="n">
-        <v>34</v>
-      </c>
-      <c r="D40" s="7" t="inlineStr">
-        <is>
-          <t>FADING</t>
-        </is>
-      </c>
-      <c r="E40" s="16" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="F40" s="7" t="inlineStr">
-        <is>
-          <t>catalyst=SALE_OF_COMPANY, sector=Consu</t>
-        </is>
-      </c>
-    </row>
-    <row r="41" ht="22" customHeight="1">
-      <c r="A41" s="9" t="inlineStr">
-        <is>
-          <t>LE</t>
-        </is>
-      </c>
-      <c r="B41" s="10" t="inlineStr">
-        <is>
-          <t>Lands' End, Inc.</t>
-        </is>
-      </c>
-      <c r="C41" s="17" t="n">
-        <v>34</v>
-      </c>
-      <c r="D41" s="10" t="inlineStr">
-        <is>
-          <t>NEUTRAL</t>
-        </is>
-      </c>
-      <c r="E41" s="17" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="F41" s="10" t="inlineStr">
-        <is>
-          <t>catalyst=SALE_OF_COMPANY, sector=Consu</t>
-        </is>
-      </c>
-    </row>
-    <row r="42" ht="22" customHeight="1">
-      <c r="A42" s="6" t="inlineStr">
-        <is>
-          <t>LUCK</t>
-        </is>
-      </c>
-      <c r="B42" s="7" t="inlineStr">
-        <is>
-          <t>LUCKY STRIKE ENTERTA</t>
-        </is>
-      </c>
-      <c r="C42" s="16" t="n">
-        <v>34</v>
-      </c>
-      <c r="D42" s="7" t="inlineStr">
-        <is>
-          <t>FADING</t>
-        </is>
-      </c>
-      <c r="E42" s="7" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="F42" s="7" t="inlineStr">
-        <is>
-          <t>catalyst=SALE_OF_COMPANY, sector=Consu</t>
-        </is>
-      </c>
-    </row>
-    <row r="43" ht="22" customHeight="1">
-      <c r="A43" s="9" t="inlineStr">
-        <is>
-          <t>VERI</t>
-        </is>
-      </c>
-      <c r="B43" s="10" t="inlineStr">
-        <is>
-          <t>Veritone, Inc.</t>
-        </is>
-      </c>
-      <c r="C43" s="17" t="n">
-        <v>34</v>
-      </c>
-      <c r="D43" s="10" t="inlineStr">
-        <is>
-          <t>FADING</t>
-        </is>
-      </c>
-      <c r="E43" s="17" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="F43" s="10" t="inlineStr">
-        <is>
-          <t>catalyst=SALE_OF_COMPANY, sector=Techn</t>
-        </is>
-      </c>
-    </row>
-    <row r="44" ht="22" customHeight="1">
-      <c r="A44" s="6" t="inlineStr">
-        <is>
-          <t>KPLT</t>
-        </is>
-      </c>
-      <c r="B44" s="7" t="inlineStr">
-        <is>
-          <t>Katapult Holdings, I</t>
-        </is>
-      </c>
-      <c r="C44" s="16" t="n">
-        <v>34</v>
-      </c>
-      <c r="D44" s="7" t="inlineStr">
-        <is>
-          <t>CONFIRMED</t>
-        </is>
-      </c>
-      <c r="E44" s="16" t="n">
-        <v>11.8</v>
-      </c>
-      <c r="F44" s="7" t="inlineStr">
-        <is>
-          <t>catalyst=SALE_OF_COMPANY, sector=Techn</t>
-        </is>
-      </c>
-    </row>
-    <row r="45" ht="22" customHeight="1">
-      <c r="A45" s="9" t="inlineStr">
-        <is>
-          <t>TAOX</t>
-        </is>
-      </c>
-      <c r="B45" s="10" t="inlineStr">
-        <is>
-          <t>Tao Synergies Inc.</t>
-        </is>
-      </c>
-      <c r="C45" s="17" t="n">
-        <v>34</v>
-      </c>
-      <c r="D45" s="10" t="inlineStr">
-        <is>
-          <t>NEUTRAL</t>
-        </is>
-      </c>
-      <c r="E45" s="17" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="F45" s="10" t="inlineStr">
-        <is>
-          <t>catalyst=SALE_OF_COMPANY, sector=Techn</t>
-        </is>
-      </c>
-    </row>
-    <row r="46" ht="22" customHeight="1">
-      <c r="A46" s="6" t="inlineStr">
-        <is>
-          <t>AIFF</t>
-        </is>
-      </c>
-      <c r="B46" s="7" t="inlineStr">
-        <is>
-          <t>Firefly Neuroscience</t>
-        </is>
-      </c>
-      <c r="C46" s="16" t="n">
-        <v>34</v>
-      </c>
-      <c r="D46" s="7" t="inlineStr">
-        <is>
-          <t>NEUTRAL</t>
-        </is>
-      </c>
-      <c r="E46" s="16" t="n">
-        <v>1</v>
-      </c>
-      <c r="F46" s="7" t="inlineStr">
-        <is>
-          <t>catalyst=SALE_OF_COMPANY, sector=Techn</t>
-        </is>
-      </c>
-    </row>
-    <row r="47" ht="22" customHeight="1">
-      <c r="A47" s="9" t="inlineStr">
-        <is>
-          <t>LIDR</t>
-        </is>
-      </c>
-      <c r="B47" s="10" t="inlineStr">
-        <is>
-          <t>AEye, Inc.</t>
-        </is>
-      </c>
-      <c r="C47" s="17" t="n">
-        <v>34</v>
-      </c>
-      <c r="D47" s="10" t="inlineStr">
-        <is>
-          <t>FADING</t>
-        </is>
-      </c>
-      <c r="E47" s="17" t="n">
-        <v>6.9</v>
-      </c>
-      <c r="F47" s="10" t="inlineStr">
-        <is>
-          <t>catalyst=SALE_OF_COMPANY, sector=Techn</t>
-        </is>
-      </c>
-    </row>
-    <row r="48" ht="22" customHeight="1">
-      <c r="A48" s="6" t="inlineStr">
-        <is>
-          <t>NTGR</t>
-        </is>
-      </c>
-      <c r="B48" s="7" t="inlineStr">
-        <is>
-          <t>NETGEAR, Inc.</t>
-        </is>
-      </c>
-      <c r="C48" s="16" t="n">
-        <v>32</v>
-      </c>
-      <c r="D48" s="7" t="inlineStr">
-        <is>
-          <t>FADING</t>
-        </is>
-      </c>
-      <c r="E48" s="16" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="F48" s="7" t="inlineStr">
-        <is>
-          <t>catalyst=SPINOFF, sector=Technology, s</t>
-        </is>
-      </c>
-    </row>
-    <row r="49" ht="22" customHeight="1">
-      <c r="A49" s="9" t="inlineStr">
-        <is>
-          <t>VYX</t>
-        </is>
-      </c>
-      <c r="B49" s="10" t="inlineStr">
-        <is>
-          <t>NCR Voyix Corporatio</t>
-        </is>
-      </c>
-      <c r="C49" s="17" t="n">
-        <v>32</v>
-      </c>
-      <c r="D49" s="10" t="inlineStr">
-        <is>
-          <t>NEUTRAL</t>
-        </is>
-      </c>
-      <c r="E49" s="17" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="F49" s="10" t="inlineStr">
-        <is>
-          <t>catalyst=SPINOFF, sector=Technology, s</t>
-        </is>
-      </c>
-    </row>
-    <row r="50" ht="22" customHeight="1">
-      <c r="A50" s="6" t="inlineStr">
-        <is>
-          <t>DXLG</t>
-        </is>
-      </c>
-      <c r="B50" s="7" t="inlineStr">
-        <is>
-          <t>Destination XL Group</t>
-        </is>
-      </c>
-      <c r="C50" s="16" t="n">
-        <v>32</v>
-      </c>
-      <c r="D50" s="7" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="E50" s="16" t="n">
-        <v>60</v>
-      </c>
-      <c r="F50" s="7" t="inlineStr">
-        <is>
-          <t>catalyst=SALE_OF_COMPANY, sector=Consu</t>
-        </is>
-      </c>
-    </row>
-    <row r="51" ht="22" customHeight="1">
-      <c r="A51" s="9" t="inlineStr">
-        <is>
-          <t>DTI</t>
-        </is>
-      </c>
-      <c r="B51" s="10" t="inlineStr">
-        <is>
-          <t>Drilling Tools Inter</t>
-        </is>
-      </c>
-      <c r="C51" s="17" t="n">
-        <v>32</v>
-      </c>
-      <c r="D51" s="10" t="inlineStr">
-        <is>
-          <t>FADING</t>
-        </is>
-      </c>
-      <c r="E51" s="17" t="n">
-        <v>8.300000000000001</v>
-      </c>
-      <c r="F51" s="10" t="inlineStr">
-        <is>
-          <t>catalyst=SALE_OF_COMPANY, sector=Energ</t>
-        </is>
-      </c>
-    </row>
-    <row r="52" ht="22" customHeight="1">
-      <c r="A52" s="6" t="inlineStr">
-        <is>
-          <t>WKHS</t>
-        </is>
-      </c>
-      <c r="B52" s="7" t="inlineStr">
-        <is>
-          <t>Workhorse Group, Inc</t>
-        </is>
-      </c>
-      <c r="C52" s="16" t="n">
-        <v>32</v>
-      </c>
-      <c r="D52" s="7" t="inlineStr">
-        <is>
-          <t>NEUTRAL</t>
-        </is>
-      </c>
-      <c r="E52" s="16" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="F52" s="7" t="inlineStr">
-        <is>
-          <t>catalyst=SALE_OF_COMPANY, sector=Consu</t>
-        </is>
-      </c>
-    </row>
-    <row r="53" ht="22" customHeight="1">
-      <c r="A53" s="9" t="inlineStr">
-        <is>
-          <t>GDRX</t>
-        </is>
-      </c>
-      <c r="B53" s="10" t="inlineStr">
-        <is>
-          <t>GoodRx Holdings, Inc</t>
-        </is>
-      </c>
-      <c r="C53" s="17" t="n">
-        <v>32</v>
-      </c>
-      <c r="D53" s="10" t="inlineStr">
-        <is>
-          <t>NEUTRAL</t>
-        </is>
-      </c>
-      <c r="E53" s="17" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="F53" s="10" t="inlineStr">
-        <is>
-          <t>catalyst=SPINOFF, size=small, drawdown</t>
-        </is>
-      </c>
-    </row>
-    <row r="54" ht="22" customHeight="1">
-      <c r="A54" s="6" t="inlineStr">
-        <is>
-          <t>GRPN</t>
-        </is>
-      </c>
-      <c r="B54" s="7" t="inlineStr">
-        <is>
-          <t>Groupon, Inc.</t>
-        </is>
-      </c>
-      <c r="C54" s="16" t="n">
-        <v>32</v>
-      </c>
-      <c r="D54" s="7" t="inlineStr">
-        <is>
-          <t>NEUTRAL</t>
-        </is>
-      </c>
-      <c r="E54" s="7" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="F54" s="7" t="inlineStr">
-        <is>
-          <t>catalyst=SPINOFF, size=small, drawdown</t>
-        </is>
-      </c>
-    </row>
-    <row r="55" ht="22" customHeight="1">
-      <c r="A55" s="9" t="inlineStr">
-        <is>
-          <t>GLIBK</t>
-        </is>
-      </c>
-      <c r="B55" s="10" t="inlineStr">
-        <is>
-          <t>Liberty Capital Corp</t>
-        </is>
-      </c>
-      <c r="C55" s="17" t="n">
-        <v>32</v>
-      </c>
-      <c r="D55" s="10" t="inlineStr">
-        <is>
-          <t>FADING</t>
-        </is>
-      </c>
-      <c r="E55" s="17" t="n">
-        <v>32.9</v>
-      </c>
-      <c r="F55" s="10" t="inlineStr">
-        <is>
-          <t>catalyst=SPINOFF, size=small, drawdown</t>
-        </is>
-      </c>
-    </row>
-    <row r="56" ht="22" customHeight="1">
-      <c r="A56" s="6" t="inlineStr">
-        <is>
-          <t>AHT</t>
-        </is>
-      </c>
-      <c r="B56" s="7" t="inlineStr">
-        <is>
-          <t>Ashford Hospitality</t>
-        </is>
-      </c>
-      <c r="C56" s="16" t="n">
-        <v>32</v>
-      </c>
-      <c r="D56" s="7" t="inlineStr">
-        <is>
-          <t>NEUTRAL</t>
-        </is>
-      </c>
-      <c r="E56" s="16" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="F56" s="7" t="inlineStr">
-        <is>
-          <t>catalyst=SPINOFF, sector=Real Estate,</t>
-        </is>
-      </c>
-    </row>
-    <row r="57" ht="22" customHeight="1">
-      <c r="A57" s="9" t="inlineStr">
-        <is>
-          <t>DXC</t>
-        </is>
-      </c>
-      <c r="B57" s="10" t="inlineStr">
-        <is>
-          <t>DXC Technology Compa</t>
-        </is>
-      </c>
-      <c r="C57" s="17" t="n">
-        <v>31</v>
-      </c>
-      <c r="D57" s="10" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="E57" s="17" t="n">
-        <v>30</v>
-      </c>
-      <c r="F57" s="10" t="inlineStr">
-        <is>
-          <t>sector=Technology, size=small, drawdow</t>
-        </is>
-      </c>
-    </row>
-    <row r="58" ht="22" customHeight="1">
-      <c r="A58" s="6" t="inlineStr">
-        <is>
-          <t>VTS</t>
-        </is>
-      </c>
-      <c r="B58" s="7" t="inlineStr">
-        <is>
-          <t>Vitesse Energy, Inc.</t>
-        </is>
-      </c>
-      <c r="C58" s="16" t="n">
-        <v>31</v>
-      </c>
-      <c r="D58" s="7" t="inlineStr">
-        <is>
-          <t>NEUTRAL</t>
-        </is>
-      </c>
-      <c r="E58" s="16" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="F58" s="7" t="inlineStr">
-        <is>
-          <t>catalyst=SPINOFF, sector=Energy, size=</t>
-        </is>
-      </c>
-    </row>
-    <row r="59" ht="22" customHeight="1">
-      <c r="A59" s="9" t="inlineStr">
-        <is>
-          <t>JTAI</t>
-        </is>
-      </c>
-      <c r="B59" s="10" t="inlineStr">
-        <is>
-          <t>Jet.AI Inc.</t>
-        </is>
-      </c>
-      <c r="C59" s="17" t="n">
-        <v>30</v>
-      </c>
-      <c r="D59" s="10" t="inlineStr">
-        <is>
-          <t>FADING</t>
-        </is>
-      </c>
-      <c r="E59" s="17" t="n">
-        <v>60</v>
-      </c>
-      <c r="F59" s="10" t="inlineStr">
-        <is>
-          <t>catalyst=SPINOFF, sector=Technology, s</t>
-        </is>
-      </c>
-    </row>
-    <row r="60" ht="22" customHeight="1">
-      <c r="A60" s="6" t="inlineStr">
-        <is>
-          <t>GPRO</t>
-        </is>
-      </c>
-      <c r="B60" s="7" t="inlineStr">
-        <is>
-          <t>GoPro, Inc.</t>
-        </is>
-      </c>
-      <c r="C60" s="16" t="n">
-        <v>30</v>
-      </c>
-      <c r="D60" s="7" t="inlineStr">
-        <is>
-          <t>NEUTRAL</t>
-        </is>
-      </c>
-      <c r="E60" s="16" t="n">
-        <v>3</v>
-      </c>
-      <c r="F60" s="7" t="inlineStr">
-        <is>
-          <t>catalyst=SPINOFF, sector=Technology, s</t>
-        </is>
-      </c>
-    </row>
-    <row r="61" ht="22" customHeight="1">
-      <c r="A61" s="9" t="inlineStr">
-        <is>
-          <t>LMRI</t>
-        </is>
-      </c>
-      <c r="B61" s="10" t="inlineStr">
-        <is>
-          <t>Lumexa Imaging Holdi</t>
-        </is>
-      </c>
-      <c r="C61" s="17" t="n">
-        <v>30</v>
-      </c>
-      <c r="D61" s="10" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="E61" s="17" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="F61" s="10" t="inlineStr">
-        <is>
-          <t>size=small, drawdown_12m=deep(&lt;-50%),</t>
-        </is>
-      </c>
-    </row>
-    <row r="62" ht="22" customHeight="1">
-      <c r="A62" s="6" t="inlineStr">
-        <is>
-          <t>KD</t>
-        </is>
-      </c>
-      <c r="B62" s="7" t="inlineStr">
-        <is>
-          <t>Kyndryl Holdings, In</t>
-        </is>
-      </c>
-      <c r="C62" s="16" t="n">
-        <v>30</v>
-      </c>
-      <c r="D62" s="7" t="inlineStr">
-        <is>
-          <t>NEUTRAL</t>
-        </is>
-      </c>
-      <c r="E62" s="16" t="n">
-        <v>2</v>
-      </c>
-      <c r="F62" s="7" t="inlineStr">
-        <is>
-          <t>catalyst=SPINOFF, sector=Technology, d</t>
-        </is>
-      </c>
-    </row>
-    <row r="63" ht="22" customHeight="1">
-      <c r="A63" s="9" t="inlineStr">
-        <is>
-          <t>SENS</t>
-        </is>
-      </c>
-      <c r="B63" s="10" t="inlineStr">
-        <is>
-          <t>Senseonics Holdings,</t>
-        </is>
-      </c>
-      <c r="C63" s="17" t="n">
-        <v>29</v>
-      </c>
-      <c r="D63" s="10" t="inlineStr">
-        <is>
-          <t>CONFIRMED</t>
-        </is>
-      </c>
-      <c r="E63" s="10" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="F63" s="10" t="inlineStr">
-        <is>
-          <t>catalyst=SALE_OF_COMPANY, size=small,</t>
-        </is>
-      </c>
-    </row>
-    <row r="64" ht="22" customHeight="1">
-      <c r="A64" s="6" t="inlineStr">
-        <is>
-          <t>FLGT</t>
-        </is>
-      </c>
-      <c r="B64" s="7" t="inlineStr">
-        <is>
-          <t>Fulgent Genetics, In</t>
-        </is>
-      </c>
-      <c r="C64" s="16" t="n">
-        <v>29</v>
-      </c>
-      <c r="D64" s="7" t="inlineStr">
-        <is>
-          <t>CONFIRMED</t>
-        </is>
-      </c>
-      <c r="E64" s="16" t="n">
-        <v>60</v>
-      </c>
-      <c r="F64" s="7" t="inlineStr">
-        <is>
-          <t>catalyst=SALE_OF_COMPANY, size=small,</t>
-        </is>
-      </c>
-    </row>
-    <row r="65" ht="22" customHeight="1">
-      <c r="A65" s="9" t="inlineStr">
-        <is>
-          <t>PAHC</t>
-        </is>
-      </c>
-      <c r="B65" s="10" t="inlineStr">
-        <is>
-          <t>Phibro Animal Health</t>
-        </is>
-      </c>
-      <c r="C65" s="17" t="n">
-        <v>29</v>
-      </c>
-      <c r="D65" s="10" t="inlineStr">
-        <is>
-          <t>FADING</t>
-        </is>
-      </c>
-      <c r="E65" s="17" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="F65" s="10" t="inlineStr">
-        <is>
-          <t>catalyst=SALE_OF_COMPANY, size=small,</t>
-        </is>
-      </c>
-    </row>
-    <row r="66" ht="22" customHeight="1">
-      <c r="A66" s="6" t="inlineStr">
-        <is>
-          <t>GRNT</t>
-        </is>
-      </c>
-      <c r="B66" s="7" t="inlineStr">
-        <is>
-          <t>Granite Ridge Resour</t>
-        </is>
-      </c>
-      <c r="C66" s="16" t="n">
-        <v>29</v>
-      </c>
-      <c r="D66" s="7" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="E66" s="16" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="F66" s="7" t="inlineStr">
-        <is>
-          <t>sector=Energy, size=small, drawdown_12</t>
-        </is>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" s="12" t="inlineStr">
-        <is>
-          <t>WHAT RAISES TAIL ODDS (historical lift vs 15% base)</t>
-        </is>
-      </c>
-    </row>
-    <row r="69" ht="18" customHeight="1">
-      <c r="A69" s="4" t="inlineStr">
-        <is>
-          <t>Feature = bin</t>
-        </is>
-      </c>
-      <c r="B69" s="4" t="inlineStr">
-        <is>
-          <t>Tail rate</t>
-        </is>
-      </c>
-      <c r="C69" s="4" t="inlineStr">
-        <is>
-          <t>Lift</t>
-        </is>
-      </c>
-      <c r="D69" s="4" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="E69" s="15" t="inlineStr"/>
+      <c r="C68" s="10" t="inlineStr">
+        <is>
+          <t>1.99x</t>
+        </is>
+      </c>
+      <c r="D68" s="8" t="n">
+        <v>10</v>
+      </c>
+      <c r="E68" s="10" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+    </row>
+    <row r="69" ht="16" customHeight="1">
+      <c r="A69" s="6" t="inlineStr">
+        <is>
+          <t>catalyst = SALE_OF_COMPANY</t>
+        </is>
+      </c>
+      <c r="B69" s="16" t="n">
+        <v>25</v>
+      </c>
+      <c r="C69" s="7" t="inlineStr">
+        <is>
+          <t>1.66x</t>
+        </is>
+      </c>
+      <c r="D69" s="5" t="n">
+        <v>8</v>
+      </c>
+      <c r="E69" s="7" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
     </row>
     <row r="70" ht="16" customHeight="1">
       <c r="A70" s="9" t="inlineStr">
         <is>
-          <t>size = small</t>
+          <t>range_pos = low</t>
         </is>
       </c>
       <c r="B70" s="17" t="n">
-        <v>38</v>
+        <v>21</v>
       </c>
       <c r="C70" s="10" t="inlineStr">
         <is>
-          <t>2.49x</t>
+          <t>1.39x</t>
         </is>
       </c>
       <c r="D70" s="8" t="n">
-        <v>8</v>
+        <v>43</v>
       </c>
       <c r="E70" s="10" t="inlineStr">
         <is>
@@ -10167,19 +10148,19 @@
     <row r="71" ht="16" customHeight="1">
       <c r="A71" s="6" t="inlineStr">
         <is>
-          <t>drawdown_12m = deep(&lt;-50%)</t>
+          <t>catalyst = SPINOFF</t>
         </is>
       </c>
       <c r="B71" s="16" t="n">
-        <v>32</v>
+        <v>18</v>
       </c>
       <c r="C71" s="7" t="inlineStr">
         <is>
-          <t>2.11x</t>
+          <t>1.16x</t>
         </is>
       </c>
       <c r="D71" s="5" t="n">
-        <v>22</v>
+        <v>40</v>
       </c>
       <c r="E71" s="7" t="inlineStr">
         <is>
@@ -10190,19 +10171,19 @@
     <row r="72" ht="16" customHeight="1">
       <c r="A72" s="9" t="inlineStr">
         <is>
-          <t>sector = Real Estate</t>
+          <t>pre_12m = down(&lt;-20%)  (needs a wait)</t>
         </is>
       </c>
       <c r="B72" s="17" t="n">
-        <v>33</v>
+        <v>22</v>
       </c>
       <c r="C72" s="10" t="inlineStr">
         <is>
-          <t>2.22x</t>
+          <t>1.50x</t>
         </is>
       </c>
       <c r="D72" s="8" t="n">
-        <v>3</v>
+        <v>40</v>
       </c>
       <c r="E72" s="10" t="inlineStr">
         <is>
@@ -10213,19 +10194,19 @@
     <row r="73" ht="16" customHeight="1">
       <c r="A73" s="6" t="inlineStr">
         <is>
-          <t>sector = Technology</t>
+          <t>post_1m = up(&gt;+20%)  (needs a wait)</t>
         </is>
       </c>
       <c r="B73" s="16" t="n">
-        <v>30</v>
+        <v>60</v>
       </c>
       <c r="C73" s="7" t="inlineStr">
         <is>
-          <t>1.99x</t>
+          <t>3.99x</t>
         </is>
       </c>
       <c r="D73" s="5" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="E73" s="7" t="inlineStr">
         <is>
@@ -10233,123 +10214,8 @@
         </is>
       </c>
     </row>
-    <row r="74" ht="16" customHeight="1">
-      <c r="A74" s="9" t="inlineStr">
-        <is>
-          <t>catalyst = SALE_OF_COMPANY</t>
-        </is>
-      </c>
-      <c r="B74" s="17" t="n">
-        <v>25</v>
-      </c>
-      <c r="C74" s="10" t="inlineStr">
-        <is>
-          <t>1.66x</t>
-        </is>
-      </c>
-      <c r="D74" s="8" t="n">
-        <v>8</v>
-      </c>
-      <c r="E74" s="10" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-    </row>
-    <row r="75" ht="16" customHeight="1">
-      <c r="A75" s="6" t="inlineStr">
-        <is>
-          <t>range_pos = low</t>
-        </is>
-      </c>
-      <c r="B75" s="16" t="n">
-        <v>21</v>
-      </c>
-      <c r="C75" s="7" t="inlineStr">
-        <is>
-          <t>1.39x</t>
-        </is>
-      </c>
-      <c r="D75" s="5" t="n">
-        <v>43</v>
-      </c>
-      <c r="E75" s="7" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-    </row>
-    <row r="76" ht="16" customHeight="1">
-      <c r="A76" s="9" t="inlineStr">
-        <is>
-          <t>catalyst = SPINOFF</t>
-        </is>
-      </c>
-      <c r="B76" s="17" t="n">
-        <v>18</v>
-      </c>
-      <c r="C76" s="10" t="inlineStr">
-        <is>
-          <t>1.16x</t>
-        </is>
-      </c>
-      <c r="D76" s="8" t="n">
-        <v>40</v>
-      </c>
-      <c r="E76" s="10" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-    </row>
-    <row r="77" ht="16" customHeight="1">
-      <c r="A77" s="6" t="inlineStr">
-        <is>
-          <t>pre_12m = down(&lt;-20%)  (needs a wait)</t>
-        </is>
-      </c>
-      <c r="B77" s="16" t="n">
-        <v>22</v>
-      </c>
-      <c r="C77" s="7" t="inlineStr">
-        <is>
-          <t>1.50x</t>
-        </is>
-      </c>
-      <c r="D77" s="5" t="n">
-        <v>40</v>
-      </c>
-      <c r="E77" s="7" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-    </row>
-    <row r="78" ht="16" customHeight="1">
-      <c r="A78" s="9" t="inlineStr">
-        <is>
-          <t>post_1m = up(&gt;+20%)  (needs a wait)</t>
-        </is>
-      </c>
-      <c r="B78" s="17" t="n">
-        <v>60</v>
-      </c>
-      <c r="C78" s="10" t="inlineStr">
-        <is>
-          <t>3.99x</t>
-        </is>
-      </c>
-      <c r="D78" s="8" t="n">
-        <v>5</v>
-      </c>
-      <c r="E78" s="10" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-    </row>
-    <row r="80" ht="28" customHeight="1">
-      <c r="A80" s="11" t="inlineStr">
+    <row r="75" ht="28" customHeight="1">
+      <c r="A75" s="11" t="inlineStr">
         <is>
           <t>HOW TO RAISE THE ODDS, from the event study. The right tail is not random: it concentrates in (1) DEEPLY BEATEN-DOWN names — &gt;50% below their 12-month high tailed 32% of the time vs 4% for names near their highs (2.1x); (2) SMALL-CAPS ($300M-2B), 38% tail rate (2.5x) — the high-variance sweet spot; (3) the right SECTORS — Real Estate, Technology, Consumer-Cyclical, Energy — while Financials, Utilities and Staples produced ZERO tails; (4) SALE-OF-COMPANY and SPIN-OFF catalysts over asset sales. Stacking these lifts the tail probability to ~40% (≈2.7x base). THE SINGLE STRONGEST EDGE is not a screen but a RULE: wait ~1 month and enter only names the market voted UP &gt;20% on the catalyst — those tailed 60% of the time (4.0x). Buying the catalyst blind is a coin-flip that loses to SPY on the median; buying beaten-down small-caps in the right sectors AFTER the market confirms is how you tilt into the tail. Modest sample (113 events); directional. Sources: rerate_backtest.py / tail_discriminators.py / tail_odds.py.</t>
         </is>
@@ -10358,8 +10224,8 @@
   </sheetData>
   <mergeCells count="3">
     <mergeCell ref="A2:F2"/>
-    <mergeCell ref="A80:F80"/>
     <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A75:F75"/>
   </mergeCells>
   <printOptions horizontalCentered="0"/>
   <pageMargins left="0.5" right="0.5" top="0.6" bottom="0.6" header="0.5" footer="0.5"/>

--- a/MOST_ASYMMETRIC.xlsx
+++ b/MOST_ASYMMETRIC.xlsx
@@ -6266,143 +6266,139 @@
     <row r="5" ht="22" customHeight="1">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>LE</t>
+          <t>WBD</t>
         </is>
       </c>
       <c r="B5" s="7" t="inlineStr">
         <is>
-          <t>Lands' End, Inc.</t>
+          <t>Warner Bros. Discovery</t>
         </is>
       </c>
       <c r="C5" s="16" t="n">
-        <v>18.1</v>
+        <v>42</v>
       </c>
       <c r="D5" s="16" t="n">
-        <v>2</v>
-      </c>
-      <c r="E5" s="16" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="F5" s="19" t="n">
-        <v>176</v>
+        <v>4</v>
+      </c>
+      <c r="E5" s="7" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="F5" s="7" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
       <c r="G5" s="7" t="inlineStr">
         <is>
-          <t>Sale Of Company [tender]; Strategic Review [</t>
+          <t>Exchange Offer [event]; Sale Of Company [ten</t>
         </is>
       </c>
     </row>
     <row r="6" ht="22" customHeight="1">
       <c r="A6" s="9" t="inlineStr">
         <is>
-          <t>WBD</t>
+          <t>DEC</t>
         </is>
       </c>
       <c r="B6" s="10" t="inlineStr">
         <is>
-          <t>Warner Bros. Discovery</t>
+          <t>Diversified Energy Com</t>
         </is>
       </c>
       <c r="C6" s="17" t="n">
-        <v>18</v>
+        <v>41.9</v>
       </c>
       <c r="D6" s="17" t="n">
-        <v>2</v>
-      </c>
-      <c r="E6" s="10" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="F6" s="10" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+        <v>4</v>
+      </c>
+      <c r="E6" s="17" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="F6" s="20" t="n">
+        <v>139</v>
       </c>
       <c r="G6" s="10" t="inlineStr">
         <is>
-          <t>Sale Of Company [tender]; Separation [narrat</t>
+          <t>Asset Sale [event]; Buyback Auth [event]; Ch</t>
         </is>
       </c>
     </row>
     <row r="7" ht="22" customHeight="1">
       <c r="A7" s="6" t="inlineStr">
         <is>
-          <t>ETN</t>
+          <t>KDP</t>
         </is>
       </c>
       <c r="B7" s="7" t="inlineStr">
         <is>
-          <t>Eaton Corporation, PLC</t>
+          <t>Keurig Dr Pepper Inc.</t>
         </is>
       </c>
       <c r="C7" s="16" t="n">
-        <v>18</v>
+        <v>38.7</v>
       </c>
       <c r="D7" s="16" t="n">
-        <v>2</v>
-      </c>
-      <c r="E7" s="7" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="F7" s="7" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+        <v>3</v>
+      </c>
+      <c r="E7" s="16" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="F7" s="19" t="n">
+        <v>28</v>
       </c>
       <c r="G7" s="7" t="inlineStr">
         <is>
-          <t>Separation [narrative]; Spinoff [narrative]</t>
+          <t>Separation [event/narrative]; Spinoff [event</t>
         </is>
       </c>
     </row>
     <row r="8" ht="22" customHeight="1">
       <c r="A8" s="9" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>DXLG</t>
         </is>
       </c>
       <c r="B8" s="10" t="inlineStr">
         <is>
-          <t>Macy's Inc</t>
+          <t>Destination XL Group,</t>
         </is>
       </c>
       <c r="C8" s="17" t="n">
-        <v>14.5</v>
+        <v>36</v>
       </c>
       <c r="D8" s="17" t="n">
         <v>2</v>
       </c>
       <c r="E8" s="17" t="n">
-        <v>2</v>
+        <v>60</v>
       </c>
       <c r="F8" s="20" t="n">
-        <v>127</v>
+        <v>300</v>
       </c>
       <c r="G8" s="10" t="inlineStr">
         <is>
-          <t>Asset Sale [narrative]; Strategic Review [na</t>
+          <t>Sale Of Company [event/tender]; Tender Offer</t>
         </is>
       </c>
     </row>
     <row r="9" ht="22" customHeight="1">
       <c r="A9" s="6" t="inlineStr">
         <is>
-          <t>LSTA</t>
+          <t>BHC</t>
         </is>
       </c>
       <c r="B9" s="7" t="inlineStr">
         <is>
-          <t>Lisata Therapeutics, I</t>
+          <t>BHC</t>
         </is>
       </c>
       <c r="C9" s="16" t="n">
-        <v>14</v>
+        <v>35</v>
       </c>
       <c r="D9" s="16" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E9" s="7" t="inlineStr">
         <is>
@@ -6416,56 +6412,52 @@
       </c>
       <c r="G9" s="7" t="inlineStr">
         <is>
-          <t>Sale Of Company [tender]; Strategic Review [</t>
+          <t>Exchange Offer [event]; Separation [event/na</t>
         </is>
       </c>
     </row>
     <row r="10" ht="22" customHeight="1">
       <c r="A10" s="9" t="inlineStr">
         <is>
-          <t>PKOH</t>
+          <t>SUNE</t>
         </is>
       </c>
       <c r="B10" s="10" t="inlineStr">
         <is>
-          <t>PKOH</t>
+          <t>SUNation Energy, Inc.</t>
         </is>
       </c>
       <c r="C10" s="17" t="n">
-        <v>12</v>
+        <v>34.5</v>
       </c>
       <c r="D10" s="17" t="n">
-        <v>2</v>
-      </c>
-      <c r="E10" s="10" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="F10" s="10" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+        <v>3</v>
+      </c>
+      <c r="E10" s="17" t="n">
+        <v>60</v>
+      </c>
+      <c r="F10" s="20" t="n">
+        <v>300</v>
       </c>
       <c r="G10" s="10" t="inlineStr">
         <is>
-          <t>Asset Sale [narrative]; Strategic Review [na</t>
+          <t>Sale Of Company [event]; Strategic Review [e</t>
         </is>
       </c>
     </row>
     <row r="11" ht="22" customHeight="1">
       <c r="A11" s="6" t="inlineStr">
         <is>
-          <t>SCTH</t>
+          <t>ETN</t>
         </is>
       </c>
       <c r="B11" s="7" t="inlineStr">
         <is>
-          <t>SCTH</t>
+          <t>Eaton Corporation, PLC</t>
         </is>
       </c>
       <c r="C11" s="16" t="n">
-        <v>12</v>
+        <v>34</v>
       </c>
       <c r="D11" s="16" t="n">
         <v>2</v>
@@ -6482,287 +6474,307 @@
       </c>
       <c r="G11" s="7" t="inlineStr">
         <is>
-          <t>Asset Sale [narrative]; Strategic Review [na</t>
+          <t>Separation [event/narrative]; Spinoff [event</t>
         </is>
       </c>
     </row>
     <row r="12" ht="22" customHeight="1">
       <c r="A12" s="9" t="inlineStr">
         <is>
-          <t>DXLG</t>
+          <t>SPGI</t>
         </is>
       </c>
       <c r="B12" s="10" t="inlineStr">
         <is>
-          <t>Destination XL Group,</t>
+          <t>S&amp;P Global Inc.</t>
         </is>
       </c>
       <c r="C12" s="17" t="n">
-        <v>10.5</v>
+        <v>31</v>
       </c>
       <c r="D12" s="17" t="n">
-        <v>1</v>
-      </c>
-      <c r="E12" s="17" t="n">
-        <v>60</v>
-      </c>
-      <c r="F12" s="20" t="n">
-        <v>300</v>
+        <v>3</v>
+      </c>
+      <c r="E12" s="10" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="F12" s="10" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
       <c r="G12" s="10" t="inlineStr">
         <is>
-          <t>Sale Of Company [tender]</t>
+          <t>Asset Sale [event]; Separation [event]; Spin</t>
         </is>
       </c>
     </row>
     <row r="13" ht="22" customHeight="1">
       <c r="A13" s="6" t="inlineStr">
         <is>
-          <t>HUN</t>
+          <t>HCTI</t>
         </is>
       </c>
       <c r="B13" s="7" t="inlineStr">
         <is>
-          <t>Huntsman Corporation</t>
+          <t>HCTI</t>
         </is>
       </c>
       <c r="C13" s="16" t="n">
-        <v>10.2</v>
+        <v>31</v>
       </c>
       <c r="D13" s="16" t="n">
-        <v>1</v>
-      </c>
-      <c r="E13" s="16" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="F13" s="19" t="n">
-        <v>273</v>
+        <v>3</v>
+      </c>
+      <c r="E13" s="7" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="F13" s="7" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
       <c r="G13" s="7" t="inlineStr">
         <is>
-          <t>Separation [narrative]</t>
+          <t>Separation [event]; Spinoff [event]; Uplisti</t>
         </is>
       </c>
     </row>
     <row r="14" ht="22" customHeight="1">
       <c r="A14" s="9" t="inlineStr">
         <is>
-          <t>GNK</t>
+          <t>GPC</t>
         </is>
       </c>
       <c r="B14" s="10" t="inlineStr">
         <is>
-          <t>Genco Shipping &amp; Tradi</t>
+          <t>Genuine Parts Company</t>
         </is>
       </c>
       <c r="C14" s="17" t="n">
-        <v>9</v>
+        <v>30.8</v>
       </c>
       <c r="D14" s="17" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E14" s="17" t="n">
-        <v>7.4</v>
+        <v>0.4</v>
       </c>
       <c r="F14" s="20" t="n">
-        <v>174</v>
+        <v>36</v>
       </c>
       <c r="G14" s="10" t="inlineStr">
         <is>
-          <t>Sale Of Company [tender]</t>
+          <t>Separation [event/narrative]; Spinoff [event</t>
         </is>
       </c>
     </row>
     <row r="15" ht="22" customHeight="1">
       <c r="A15" s="6" t="inlineStr">
         <is>
-          <t>MCK</t>
+          <t>SITC</t>
         </is>
       </c>
       <c r="B15" s="7" t="inlineStr">
         <is>
-          <t>McKesson Corporation</t>
+          <t>SITE Centers Corp.</t>
         </is>
       </c>
       <c r="C15" s="16" t="n">
-        <v>8.800000000000001</v>
+        <v>30</v>
       </c>
       <c r="D15" s="16" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E15" s="16" t="n">
-        <v>1.5</v>
+        <v>2.8</v>
       </c>
       <c r="F15" s="19" t="n">
-        <v>150</v>
+        <v>91</v>
       </c>
       <c r="G15" s="7" t="inlineStr">
         <is>
-          <t>Separation [narrative]</t>
+          <t>Asset Sale [event/narrative]; Spinoff [event</t>
         </is>
       </c>
     </row>
     <row r="16" ht="22" customHeight="1">
       <c r="A16" s="9" t="inlineStr">
         <is>
-          <t>TXT</t>
+          <t>ADPT</t>
         </is>
       </c>
       <c r="B16" s="10" t="inlineStr">
         <is>
-          <t>Textron Inc.</t>
+          <t>Adaptive Biotechnologi</t>
         </is>
       </c>
       <c r="C16" s="17" t="n">
-        <v>7.9</v>
+        <v>29</v>
       </c>
       <c r="D16" s="17" t="n">
-        <v>1</v>
-      </c>
-      <c r="E16" s="17" t="n">
-        <v>1</v>
-      </c>
-      <c r="F16" s="20" t="n">
-        <v>75</v>
+        <v>3</v>
+      </c>
+      <c r="E16" s="10" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="F16" s="10" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
       <c r="G16" s="10" t="inlineStr">
         <is>
-          <t>Separation [narrative]</t>
+          <t>Separation [event]; Spinoff [event]; Strateg</t>
         </is>
       </c>
     </row>
     <row r="17" ht="22" customHeight="1">
       <c r="A17" s="6" t="inlineStr">
         <is>
-          <t>ASRT</t>
+          <t>CTVA</t>
         </is>
       </c>
       <c r="B17" s="7" t="inlineStr">
         <is>
-          <t>Assertio Holdings, Inc</t>
+          <t>Corteva, Inc.</t>
         </is>
       </c>
       <c r="C17" s="16" t="n">
-        <v>7.6</v>
+        <v>29</v>
       </c>
       <c r="D17" s="16" t="n">
-        <v>1</v>
-      </c>
-      <c r="E17" s="16" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="F17" s="19" t="n">
-        <v>52</v>
+        <v>2</v>
+      </c>
+      <c r="E17" s="7" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="F17" s="7" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
       <c r="G17" s="7" t="inlineStr">
         <is>
-          <t>Sale Of Company [tender]</t>
+          <t>Separation [event]; Spinoff [event/narrative</t>
         </is>
       </c>
     </row>
     <row r="18" ht="22" customHeight="1">
       <c r="A18" s="9" t="inlineStr">
         <is>
-          <t>FSK</t>
+          <t>HON</t>
         </is>
       </c>
       <c r="B18" s="10" t="inlineStr">
         <is>
-          <t>FS KKR Capital Corp.</t>
+          <t>Honeywell Internationa</t>
         </is>
       </c>
       <c r="C18" s="17" t="n">
-        <v>7.6</v>
+        <v>29</v>
       </c>
       <c r="D18" s="17" t="n">
-        <v>1</v>
-      </c>
-      <c r="E18" s="17" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="F18" s="20" t="n">
-        <v>52</v>
+        <v>2</v>
+      </c>
+      <c r="E18" s="10" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="F18" s="10" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
       <c r="G18" s="10" t="inlineStr">
         <is>
-          <t>Sale Of Company [tender]</t>
+          <t>Separation [event/narrative]; Spinoff [event</t>
         </is>
       </c>
     </row>
     <row r="19" ht="22" customHeight="1">
       <c r="A19" s="6" t="inlineStr">
         <is>
-          <t>RGR</t>
+          <t>UGI</t>
         </is>
       </c>
       <c r="B19" s="7" t="inlineStr">
         <is>
-          <t>Sturm, Ruger &amp; Company</t>
+          <t>UGI Corporation</t>
         </is>
       </c>
       <c r="C19" s="16" t="n">
-        <v>7.6</v>
+        <v>28.9</v>
       </c>
       <c r="D19" s="16" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E19" s="16" t="n">
-        <v>0.7</v>
+        <v>2.1</v>
       </c>
       <c r="F19" s="19" t="n">
-        <v>53</v>
+        <v>122</v>
       </c>
       <c r="G19" s="7" t="inlineStr">
         <is>
-          <t>Sale Of Company [tender]</t>
+          <t>Asset Sale [event/narrative]; Tender Offer [</t>
         </is>
       </c>
     </row>
     <row r="20" ht="22" customHeight="1">
       <c r="A20" s="9" t="inlineStr">
         <is>
-          <t>CVI</t>
+          <t>KOS</t>
         </is>
       </c>
       <c r="B20" s="10" t="inlineStr">
         <is>
-          <t>CVR Energy Inc.</t>
+          <t>Kosmos Energy Ltd.</t>
         </is>
       </c>
       <c r="C20" s="17" t="n">
-        <v>7.5</v>
+        <v>28.9</v>
       </c>
       <c r="D20" s="17" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E20" s="17" t="n">
-        <v>3.3</v>
+        <v>0.8</v>
       </c>
       <c r="F20" s="20" t="n">
-        <v>300</v>
+        <v>66</v>
       </c>
       <c r="G20" s="10" t="inlineStr">
         <is>
-          <t>Asset Sale [narrative]</t>
+          <t>Asset Sale [event]; Tender Offer [event]; Up</t>
         </is>
       </c>
     </row>
     <row r="21" ht="22" customHeight="1">
       <c r="A21" s="6" t="inlineStr">
         <is>
-          <t>PLCE</t>
+          <t>CYH</t>
         </is>
       </c>
       <c r="B21" s="7" t="inlineStr">
         <is>
-          <t>Children's Place, Inc.</t>
+          <t>Community Health Syste</t>
         </is>
       </c>
       <c r="C21" s="16" t="n">
-        <v>7.5</v>
+        <v>28.5</v>
       </c>
       <c r="D21" s="16" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E21" s="16" t="n">
         <v>3</v>
@@ -6772,353 +6784,353 @@
       </c>
       <c r="G21" s="7" t="inlineStr">
         <is>
-          <t>Asset Sale [narrative]</t>
+          <t>Asset Sale [event]; Tender Offer [event]</t>
         </is>
       </c>
     </row>
     <row r="22" ht="22" customHeight="1">
       <c r="A22" s="9" t="inlineStr">
         <is>
-          <t>UEIC</t>
+          <t>GTE</t>
         </is>
       </c>
       <c r="B22" s="10" t="inlineStr">
         <is>
-          <t>Universal Electronics</t>
+          <t>Gran Tierra Energy Inc</t>
         </is>
       </c>
       <c r="C22" s="17" t="n">
-        <v>7.5</v>
+        <v>28.5</v>
       </c>
       <c r="D22" s="17" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E22" s="17" t="n">
-        <v>60</v>
+        <v>3.8</v>
       </c>
       <c r="F22" s="20" t="n">
         <v>300</v>
       </c>
       <c r="G22" s="10" t="inlineStr">
         <is>
-          <t>Asset Sale [narrative]</t>
+          <t>Asset Sale [event]; Tender Offer [event]</t>
         </is>
       </c>
     </row>
     <row r="23" ht="22" customHeight="1">
       <c r="A23" s="6" t="inlineStr">
         <is>
-          <t>ZSTK</t>
+          <t>LE</t>
         </is>
       </c>
       <c r="B23" s="7" t="inlineStr">
         <is>
-          <t>ZeroStack Corp.</t>
+          <t>Lands' End, Inc.</t>
         </is>
       </c>
       <c r="C23" s="16" t="n">
-        <v>7.5</v>
+        <v>28.5</v>
       </c>
       <c r="D23" s="16" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E23" s="16" t="n">
-        <v>60</v>
+        <v>5.1</v>
       </c>
       <c r="F23" s="19" t="n">
-        <v>300</v>
+        <v>176</v>
       </c>
       <c r="G23" s="7" t="inlineStr">
         <is>
-          <t>Asset Sale [narrative]</t>
+          <t>Sale Of Company [tender]; Strategic Review [</t>
         </is>
       </c>
     </row>
     <row r="24" ht="22" customHeight="1">
       <c r="A24" s="9" t="inlineStr">
         <is>
-          <t>NMRK</t>
+          <t>BIRD</t>
         </is>
       </c>
       <c r="B24" s="10" t="inlineStr">
         <is>
-          <t>Newmark Group, Inc.</t>
+          <t>Allbirds, Inc.</t>
         </is>
       </c>
       <c r="C24" s="17" t="n">
-        <v>7.5</v>
+        <v>28.2</v>
       </c>
       <c r="D24" s="17" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E24" s="17" t="n">
-        <v>4.1</v>
+        <v>1.8</v>
       </c>
       <c r="F24" s="20" t="n">
-        <v>300</v>
+        <v>137</v>
       </c>
       <c r="G24" s="10" t="inlineStr">
         <is>
-          <t>Asset Sale [narrative]</t>
+          <t>Asset Sale [event/narrative]; Uplisting [eve</t>
         </is>
       </c>
     </row>
     <row r="25" ht="22" customHeight="1">
       <c r="A25" s="6" t="inlineStr">
         <is>
-          <t>OPTU</t>
+          <t>PSKY</t>
         </is>
       </c>
       <c r="B25" s="7" t="inlineStr">
         <is>
-          <t>Optimum Communications</t>
+          <t>PSKY</t>
         </is>
       </c>
       <c r="C25" s="16" t="n">
-        <v>7.5</v>
+        <v>28</v>
       </c>
       <c r="D25" s="16" t="n">
-        <v>1</v>
-      </c>
-      <c r="E25" s="16" t="n">
         <v>3</v>
       </c>
-      <c r="F25" s="19" t="n">
-        <v>300</v>
+      <c r="E25" s="7" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="F25" s="7" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
       <c r="G25" s="7" t="inlineStr">
         <is>
-          <t>Sale Of Company [narrative]</t>
+          <t>Exchange Offer [event]; Spinoff [event]; Ten</t>
         </is>
       </c>
     </row>
     <row r="26" ht="22" customHeight="1">
       <c r="A26" s="9" t="inlineStr">
         <is>
-          <t>ONEW</t>
+          <t>SOLV</t>
         </is>
       </c>
       <c r="B26" s="10" t="inlineStr">
         <is>
-          <t>OneWater Marine Inc.</t>
+          <t>Solventum Corporation</t>
         </is>
       </c>
       <c r="C26" s="17" t="n">
-        <v>7.5</v>
+        <v>27.1</v>
       </c>
       <c r="D26" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="E26" s="17" t="n">
         <v>1</v>
       </c>
-      <c r="E26" s="17" t="n">
-        <v>10.5</v>
-      </c>
       <c r="F26" s="20" t="n">
-        <v>300</v>
+        <v>78</v>
       </c>
       <c r="G26" s="10" t="inlineStr">
         <is>
-          <t>Asset Sale [narrative]</t>
+          <t>Separation [event]; Strategic Review [event/</t>
         </is>
       </c>
     </row>
     <row r="27" ht="22" customHeight="1">
       <c r="A27" s="6" t="inlineStr">
         <is>
-          <t>NUS</t>
+          <t>LSTA</t>
         </is>
       </c>
       <c r="B27" s="7" t="inlineStr">
         <is>
-          <t>Nu Skin Enterprises, I</t>
+          <t>Lisata Therapeutics, I</t>
         </is>
       </c>
       <c r="C27" s="16" t="n">
-        <v>7.5</v>
+        <v>27</v>
       </c>
       <c r="D27" s="16" t="n">
-        <v>1</v>
-      </c>
-      <c r="E27" s="16" t="n">
-        <v>60</v>
-      </c>
-      <c r="F27" s="19" t="n">
-        <v>300</v>
+        <v>3</v>
+      </c>
+      <c r="E27" s="7" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="F27" s="7" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
       <c r="G27" s="7" t="inlineStr">
         <is>
-          <t>Asset Sale [narrative]</t>
+          <t>Sale Of Company [event/tender]; Strategic Re</t>
         </is>
       </c>
     </row>
     <row r="28" ht="22" customHeight="1">
       <c r="A28" s="9" t="inlineStr">
         <is>
-          <t>CNDT</t>
+          <t>FDX</t>
         </is>
       </c>
       <c r="B28" s="10" t="inlineStr">
         <is>
-          <t>Conduent Incorporated</t>
+          <t>FedEx Corporation</t>
         </is>
       </c>
       <c r="C28" s="17" t="n">
-        <v>7.5</v>
+        <v>26.9</v>
       </c>
       <c r="D28" s="17" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E28" s="17" t="n">
-        <v>60</v>
+        <v>0.9</v>
       </c>
       <c r="F28" s="20" t="n">
-        <v>300</v>
+        <v>74</v>
       </c>
       <c r="G28" s="10" t="inlineStr">
         <is>
-          <t>Asset Sale [narrative]</t>
+          <t>Separation [event]; Spinoff [event]</t>
         </is>
       </c>
     </row>
     <row r="29" ht="22" customHeight="1">
       <c r="A29" s="6" t="inlineStr">
         <is>
-          <t>GPC</t>
+          <t>FIS</t>
         </is>
       </c>
       <c r="B29" s="7" t="inlineStr">
         <is>
-          <t>Genuine Parts Company</t>
+          <t>Fidelity National Info</t>
         </is>
       </c>
       <c r="C29" s="16" t="n">
-        <v>7.4</v>
+        <v>26.8</v>
       </c>
       <c r="D29" s="16" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E29" s="16" t="n">
-        <v>0.4</v>
+        <v>2.8</v>
       </c>
       <c r="F29" s="19" t="n">
-        <v>36</v>
+        <v>164</v>
       </c>
       <c r="G29" s="7" t="inlineStr">
         <is>
-          <t>Separation [narrative]</t>
+          <t>Asset Sale [event]; Spinoff [event]</t>
         </is>
       </c>
     </row>
     <row r="30" ht="22" customHeight="1">
       <c r="A30" s="9" t="inlineStr">
         <is>
-          <t>KDP</t>
+          <t>OLN</t>
         </is>
       </c>
       <c r="B30" s="10" t="inlineStr">
         <is>
-          <t>Keurig Dr Pepper Inc.</t>
+          <t>Olin Corporation</t>
         </is>
       </c>
       <c r="C30" s="17" t="n">
-        <v>7.3</v>
+        <v>26.8</v>
       </c>
       <c r="D30" s="17" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E30" s="17" t="n">
-        <v>0.4</v>
+        <v>3.1</v>
       </c>
       <c r="F30" s="20" t="n">
-        <v>28</v>
+        <v>205</v>
       </c>
       <c r="G30" s="10" t="inlineStr">
         <is>
-          <t>Separation [narrative]</t>
+          <t>Going Private [event]; Uplisting [event]</t>
         </is>
       </c>
     </row>
     <row r="31" ht="22" customHeight="1">
       <c r="A31" s="6" t="inlineStr">
         <is>
-          <t>LUCK</t>
+          <t>HUN</t>
         </is>
       </c>
       <c r="B31" s="7" t="inlineStr">
         <is>
-          <t>LUCKY STRIKE ENTERTAIN</t>
+          <t>Huntsman Corporation</t>
         </is>
       </c>
       <c r="C31" s="16" t="n">
-        <v>7</v>
+        <v>26.2</v>
       </c>
       <c r="D31" s="16" t="n">
-        <v>1</v>
-      </c>
-      <c r="E31" s="7" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="F31" s="7" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+        <v>2</v>
+      </c>
+      <c r="E31" s="16" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="F31" s="19" t="n">
+        <v>273</v>
       </c>
       <c r="G31" s="7" t="inlineStr">
         <is>
-          <t>Sale Of Company [incentive]</t>
+          <t>Separation [narrative]; Uplisting [event]</t>
         </is>
       </c>
     </row>
     <row r="32" ht="22" customHeight="1">
       <c r="A32" s="9" t="inlineStr">
         <is>
-          <t>GMAB</t>
+          <t>ASRT</t>
         </is>
       </c>
       <c r="B32" s="10" t="inlineStr">
         <is>
-          <t>Genmab A/S</t>
+          <t>Assertio Holdings, Inc</t>
         </is>
       </c>
       <c r="C32" s="17" t="n">
-        <v>7</v>
+        <v>26.1</v>
       </c>
       <c r="D32" s="17" t="n">
-        <v>1</v>
-      </c>
-      <c r="E32" s="10" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="F32" s="10" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+        <v>2</v>
+      </c>
+      <c r="E32" s="17" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="F32" s="20" t="n">
+        <v>52</v>
       </c>
       <c r="G32" s="10" t="inlineStr">
         <is>
-          <t>Sale Of Company [tender]</t>
+          <t>Sale Of Company [event/tender]; Tender Offer</t>
         </is>
       </c>
     </row>
     <row r="33" ht="22" customHeight="1">
       <c r="A33" s="6" t="inlineStr">
         <is>
-          <t>KALV</t>
+          <t>NFE</t>
         </is>
       </c>
       <c r="B33" s="7" t="inlineStr">
         <is>
-          <t>KalVista Pharmaceutica</t>
+          <t>NFE</t>
         </is>
       </c>
       <c r="C33" s="16" t="n">
-        <v>7</v>
+        <v>26</v>
       </c>
       <c r="D33" s="16" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E33" s="7" t="inlineStr">
         <is>
@@ -7132,92 +7144,84 @@
       </c>
       <c r="G33" s="7" t="inlineStr">
         <is>
-          <t>Sale Of Company [tender]</t>
+          <t>Asset Sale [event]; Separation [event/narrat</t>
         </is>
       </c>
     </row>
     <row r="34" ht="22" customHeight="1">
       <c r="A34" s="9" t="inlineStr">
         <is>
-          <t>JNJ</t>
+          <t>OPTU</t>
         </is>
       </c>
       <c r="B34" s="10" t="inlineStr">
         <is>
-          <t>Johnson &amp; Johnson</t>
+          <t>Optimum Communications</t>
         </is>
       </c>
       <c r="C34" s="17" t="n">
-        <v>7</v>
+        <v>25.5</v>
       </c>
       <c r="D34" s="17" t="n">
-        <v>1</v>
-      </c>
-      <c r="E34" s="10" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="F34" s="10" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+        <v>2</v>
+      </c>
+      <c r="E34" s="17" t="n">
+        <v>3</v>
+      </c>
+      <c r="F34" s="20" t="n">
+        <v>300</v>
       </c>
       <c r="G34" s="10" t="inlineStr">
         <is>
-          <t>Separation [narrative]</t>
+          <t>Sale Of Company [narrative]; Tender Offer [e</t>
         </is>
       </c>
     </row>
     <row r="35" ht="22" customHeight="1">
       <c r="A35" s="6" t="inlineStr">
         <is>
-          <t>HON</t>
+          <t>NRG</t>
         </is>
       </c>
       <c r="B35" s="7" t="inlineStr">
         <is>
-          <t>Honeywell Internationa</t>
+          <t>NRG Energy, Inc.</t>
         </is>
       </c>
       <c r="C35" s="16" t="n">
-        <v>7</v>
+        <v>25.1</v>
       </c>
       <c r="D35" s="16" t="n">
-        <v>1</v>
-      </c>
-      <c r="E35" s="7" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="F35" s="7" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+        <v>2</v>
+      </c>
+      <c r="E35" s="16" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="F35" s="19" t="n">
+        <v>237</v>
       </c>
       <c r="G35" s="7" t="inlineStr">
         <is>
-          <t>Separation [narrative]</t>
+          <t>Exchange Offer [event]; Tender Offer [event]</t>
         </is>
       </c>
     </row>
     <row r="36" ht="22" customHeight="1">
       <c r="A36" s="9" t="inlineStr">
         <is>
-          <t>BHC</t>
+          <t>PPLI</t>
         </is>
       </c>
       <c r="B36" s="10" t="inlineStr">
         <is>
-          <t>BHC</t>
+          <t>PPLI</t>
         </is>
       </c>
       <c r="C36" s="17" t="n">
-        <v>7</v>
+        <v>25</v>
       </c>
       <c r="D36" s="17" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E36" s="10" t="inlineStr">
         <is>
@@ -7231,26 +7235,26 @@
       </c>
       <c r="G36" s="10" t="inlineStr">
         <is>
-          <t>Separation [narrative]</t>
+          <t>Asset Sale [narrative]; Capital Return [even</t>
         </is>
       </c>
     </row>
     <row r="37" ht="22" customHeight="1">
       <c r="A37" s="6" t="inlineStr">
         <is>
-          <t>NFE</t>
+          <t>LTRN</t>
         </is>
       </c>
       <c r="B37" s="7" t="inlineStr">
         <is>
-          <t>NFE</t>
+          <t>LTRN</t>
         </is>
       </c>
       <c r="C37" s="16" t="n">
-        <v>7</v>
+        <v>24</v>
       </c>
       <c r="D37" s="16" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E37" s="7" t="inlineStr">
         <is>
@@ -7264,26 +7268,26 @@
       </c>
       <c r="G37" s="7" t="inlineStr">
         <is>
-          <t>Separation [narrative]</t>
+          <t>Separation [event]; Spinoff [event]</t>
         </is>
       </c>
     </row>
     <row r="38" ht="22" customHeight="1">
       <c r="A38" s="9" t="inlineStr">
         <is>
-          <t>CR</t>
+          <t>ADIG</t>
         </is>
       </c>
       <c r="B38" s="10" t="inlineStr">
         <is>
-          <t>Crane Company</t>
+          <t>ADIG</t>
         </is>
       </c>
       <c r="C38" s="17" t="n">
-        <v>7</v>
+        <v>24</v>
       </c>
       <c r="D38" s="17" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E38" s="10" t="inlineStr">
         <is>
@@ -7297,26 +7301,26 @@
       </c>
       <c r="G38" s="10" t="inlineStr">
         <is>
-          <t>Spinoff [narrative]</t>
+          <t>Separation [event]; Spinoff [event]</t>
         </is>
       </c>
     </row>
     <row r="39" ht="22" customHeight="1">
       <c r="A39" s="6" t="inlineStr">
         <is>
-          <t>CTVA</t>
+          <t>HONA</t>
         </is>
       </c>
       <c r="B39" s="7" t="inlineStr">
         <is>
-          <t>Corteva, Inc.</t>
+          <t>HONA</t>
         </is>
       </c>
       <c r="C39" s="16" t="n">
-        <v>7</v>
+        <v>24</v>
       </c>
       <c r="D39" s="16" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E39" s="7" t="inlineStr">
         <is>
@@ -7330,449 +7334,481 @@
       </c>
       <c r="G39" s="7" t="inlineStr">
         <is>
-          <t>Spinoff [narrative]</t>
+          <t>Separation [event]; Spinoff [event]</t>
         </is>
       </c>
     </row>
     <row r="40" ht="22" customHeight="1">
       <c r="A40" s="9" t="inlineStr">
         <is>
-          <t>LAB</t>
+          <t>FDXF</t>
         </is>
       </c>
       <c r="B40" s="10" t="inlineStr">
         <is>
-          <t>Standard BioTools Inc.</t>
+          <t>FDXF</t>
         </is>
       </c>
       <c r="C40" s="17" t="n">
-        <v>6.8</v>
+        <v>24</v>
       </c>
       <c r="D40" s="17" t="n">
-        <v>1</v>
-      </c>
-      <c r="E40" s="17" t="n">
-        <v>42.3</v>
-      </c>
-      <c r="F40" s="20" t="n">
-        <v>212</v>
+        <v>2</v>
+      </c>
+      <c r="E40" s="10" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="F40" s="10" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
       <c r="G40" s="10" t="inlineStr">
         <is>
-          <t>Asset Sale [narrative]</t>
+          <t>Separation [event]; Spinoff [event]</t>
         </is>
       </c>
     </row>
     <row r="41" ht="22" customHeight="1">
       <c r="A41" s="6" t="inlineStr">
         <is>
-          <t>DLX</t>
+          <t>NFLX</t>
         </is>
       </c>
       <c r="B41" s="7" t="inlineStr">
         <is>
-          <t>Deluxe Corporation</t>
+          <t>Netflix, Inc.</t>
         </is>
       </c>
       <c r="C41" s="16" t="n">
-        <v>6.7</v>
+        <v>24</v>
       </c>
       <c r="D41" s="16" t="n">
-        <v>1</v>
-      </c>
-      <c r="E41" s="16" t="n">
-        <v>3</v>
-      </c>
-      <c r="F41" s="19" t="n">
-        <v>200</v>
+        <v>2</v>
+      </c>
+      <c r="E41" s="7" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="F41" s="7" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
       <c r="G41" s="7" t="inlineStr">
         <is>
-          <t>Asset Sale [narrative]</t>
+          <t>Separation [event]; Spinoff [event]</t>
         </is>
       </c>
     </row>
     <row r="42" ht="22" customHeight="1">
       <c r="A42" s="9" t="inlineStr">
         <is>
-          <t>HE</t>
+          <t>APTV</t>
         </is>
       </c>
       <c r="B42" s="10" t="inlineStr">
         <is>
-          <t>Hawaiian Electric Indu</t>
+          <t>Aptiv PLC</t>
         </is>
       </c>
       <c r="C42" s="17" t="n">
-        <v>6.4</v>
+        <v>23.2</v>
       </c>
       <c r="D42" s="17" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E42" s="17" t="n">
-        <v>2.7</v>
+        <v>0.5</v>
       </c>
       <c r="F42" s="20" t="n">
-        <v>173</v>
+        <v>34</v>
       </c>
       <c r="G42" s="10" t="inlineStr">
         <is>
-          <t>Asset Sale [narrative]</t>
+          <t>Spinoff [event]; Tender Offer [event]</t>
         </is>
       </c>
     </row>
     <row r="43" ht="22" customHeight="1">
       <c r="A43" s="6" t="inlineStr">
         <is>
-          <t>PLTK</t>
+          <t>UEIC</t>
         </is>
       </c>
       <c r="B43" s="7" t="inlineStr">
         <is>
-          <t>Playtika Holding Corp.</t>
+          <t>Universal Electronics</t>
         </is>
       </c>
       <c r="C43" s="16" t="n">
-        <v>6.3</v>
+        <v>22.5</v>
       </c>
       <c r="D43" s="16" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E43" s="16" t="n">
-        <v>1.5</v>
+        <v>60</v>
       </c>
       <c r="F43" s="19" t="n">
-        <v>154</v>
+        <v>300</v>
       </c>
       <c r="G43" s="7" t="inlineStr">
         <is>
-          <t>Asset Sale [narrative]</t>
+          <t>Asset Sale [narrative]; Capital Return [even</t>
         </is>
       </c>
     </row>
     <row r="44" ht="22" customHeight="1">
       <c r="A44" s="9" t="inlineStr">
         <is>
-          <t>STRZ</t>
+          <t>UTZ</t>
         </is>
       </c>
       <c r="B44" s="10" t="inlineStr">
         <is>
-          <t>Starz Entertainment Co</t>
+          <t>Utz Brands Inc</t>
         </is>
       </c>
       <c r="C44" s="17" t="n">
-        <v>6.2</v>
+        <v>21.6</v>
       </c>
       <c r="D44" s="17" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E44" s="17" t="n">
-        <v>2.9</v>
+        <v>23.9</v>
       </c>
       <c r="F44" s="20" t="n">
-        <v>147</v>
+        <v>120</v>
       </c>
       <c r="G44" s="10" t="inlineStr">
         <is>
-          <t>Asset Sale [narrative]</t>
+          <t>Buyback Auth [event]; Going Private [event]</t>
         </is>
       </c>
     </row>
     <row r="45" ht="22" customHeight="1">
       <c r="A45" s="6" t="inlineStr">
         <is>
-          <t>HLLY</t>
+          <t>CMCO</t>
         </is>
       </c>
       <c r="B45" s="7" t="inlineStr">
         <is>
-          <t>Holley Inc.</t>
+          <t>Columbus McKinnon Corp</t>
         </is>
       </c>
       <c r="C45" s="16" t="n">
-        <v>6.2</v>
+        <v>21.2</v>
       </c>
       <c r="D45" s="16" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E45" s="16" t="n">
-        <v>6.3</v>
+        <v>7.1</v>
       </c>
       <c r="F45" s="19" t="n">
-        <v>142</v>
+        <v>150</v>
       </c>
       <c r="G45" s="7" t="inlineStr">
         <is>
-          <t>Asset Sale [narrative]</t>
+          <t>Asset Sale [event]; Exchange Offer [event]</t>
         </is>
       </c>
     </row>
     <row r="46" ht="22" customHeight="1">
       <c r="A46" s="9" t="inlineStr">
         <is>
-          <t>ANDE</t>
+          <t>ANAB</t>
         </is>
       </c>
       <c r="B46" s="10" t="inlineStr">
         <is>
-          <t>The Andersons, Inc.</t>
+          <t>AnaptysBio, Inc.</t>
         </is>
       </c>
       <c r="C46" s="17" t="n">
-        <v>6.2</v>
+        <v>21</v>
       </c>
       <c r="D46" s="17" t="n">
-        <v>1</v>
-      </c>
-      <c r="E46" s="17" t="n">
         <v>2</v>
       </c>
-      <c r="F46" s="20" t="n">
-        <v>150</v>
+      <c r="E46" s="10" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="F46" s="10" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
       <c r="G46" s="10" t="inlineStr">
         <is>
-          <t>Asset Sale [narrative]</t>
+          <t>Separation [event]; Uplisting [event]</t>
         </is>
       </c>
     </row>
     <row r="47" ht="22" customHeight="1">
       <c r="A47" s="6" t="inlineStr">
         <is>
-          <t>CNMD</t>
+          <t>HAIN</t>
         </is>
       </c>
       <c r="B47" s="7" t="inlineStr">
         <is>
-          <t>CONMED Corporation</t>
+          <t>The Hain Celestial Gro</t>
         </is>
       </c>
       <c r="C47" s="16" t="n">
-        <v>6.2</v>
+        <v>21</v>
       </c>
       <c r="D47" s="16" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E47" s="16" t="n">
-        <v>3.1</v>
+        <v>60</v>
       </c>
       <c r="F47" s="19" t="n">
-        <v>150</v>
+        <v>300</v>
       </c>
       <c r="G47" s="7" t="inlineStr">
         <is>
-          <t>Asset Sale [narrative]</t>
+          <t>Asset Sale [event]; Strategic Review [narrat</t>
         </is>
       </c>
     </row>
     <row r="48" ht="22" customHeight="1">
       <c r="A48" s="9" t="inlineStr">
         <is>
-          <t>BIRD</t>
+          <t>CMTL</t>
         </is>
       </c>
       <c r="B48" s="10" t="inlineStr">
         <is>
-          <t>Allbirds, Inc.</t>
+          <t>Comtech Telecommunicat</t>
         </is>
       </c>
       <c r="C48" s="17" t="n">
-        <v>6.1</v>
+        <v>21</v>
       </c>
       <c r="D48" s="17" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E48" s="17" t="n">
-        <v>1.8</v>
+        <v>11.5</v>
       </c>
       <c r="F48" s="20" t="n">
-        <v>137</v>
+        <v>300</v>
       </c>
       <c r="G48" s="10" t="inlineStr">
         <is>
-          <t>Asset Sale [narrative]</t>
+          <t>Asset Sale [event]; Strategic Review [narrat</t>
         </is>
       </c>
     </row>
     <row r="49" ht="22" customHeight="1">
       <c r="A49" s="6" t="inlineStr">
         <is>
-          <t>TLYS</t>
+          <t>ANEB</t>
         </is>
       </c>
       <c r="B49" s="7" t="inlineStr">
         <is>
-          <t>Tilly's, Inc.</t>
+          <t>ANEB</t>
         </is>
       </c>
       <c r="C49" s="16" t="n">
-        <v>6.1</v>
+        <v>21</v>
       </c>
       <c r="D49" s="16" t="n">
-        <v>1</v>
-      </c>
-      <c r="E49" s="16" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="F49" s="19" t="n">
-        <v>135</v>
+        <v>2</v>
+      </c>
+      <c r="E49" s="7" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="F49" s="7" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
       <c r="G49" s="7" t="inlineStr">
         <is>
-          <t>Sale Of Company [narrative]</t>
+          <t>Going Private [event]; Tender Offer [event]</t>
         </is>
       </c>
     </row>
     <row r="50" ht="22" customHeight="1">
       <c r="A50" s="9" t="inlineStr">
         <is>
-          <t>UGI</t>
+          <t>ROCK</t>
         </is>
       </c>
       <c r="B50" s="10" t="inlineStr">
         <is>
-          <t>UGI Corporation</t>
+          <t>Gibraltar Industries,</t>
         </is>
       </c>
       <c r="C50" s="17" t="n">
-        <v>6</v>
+        <v>20.2</v>
       </c>
       <c r="D50" s="17" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E50" s="17" t="n">
-        <v>2.1</v>
+        <v>1.8</v>
       </c>
       <c r="F50" s="20" t="n">
-        <v>122</v>
+        <v>114</v>
       </c>
       <c r="G50" s="10" t="inlineStr">
         <is>
-          <t>Asset Sale [narrative]</t>
+          <t>Asset Sale [event]; Exchange Offer [event]</t>
         </is>
       </c>
     </row>
     <row r="51" ht="22" customHeight="1">
       <c r="A51" s="6" t="inlineStr">
         <is>
-          <t>CMT</t>
+          <t>LRHC</t>
         </is>
       </c>
       <c r="B51" s="7" t="inlineStr">
         <is>
-          <t>Core Molding Technolog</t>
+          <t>LRHC</t>
         </is>
       </c>
       <c r="C51" s="16" t="n">
-        <v>5.9</v>
+        <v>20</v>
       </c>
       <c r="D51" s="16" t="n">
-        <v>1</v>
-      </c>
-      <c r="E51" s="16" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="F51" s="19" t="n">
-        <v>104</v>
+        <v>2</v>
+      </c>
+      <c r="E51" s="7" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="F51" s="7" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
       <c r="G51" s="7" t="inlineStr">
         <is>
-          <t>Asset Sale [narrative]</t>
+          <t>Going Private [event]; Sale Of Company [even</t>
         </is>
       </c>
     </row>
     <row r="52" ht="22" customHeight="1">
       <c r="A52" s="9" t="inlineStr">
         <is>
-          <t>SITC</t>
+          <t>RACC</t>
         </is>
       </c>
       <c r="B52" s="10" t="inlineStr">
         <is>
-          <t>SITE Centers Corp.</t>
+          <t>RACC</t>
         </is>
       </c>
       <c r="C52" s="17" t="n">
-        <v>5.8</v>
+        <v>20</v>
       </c>
       <c r="D52" s="17" t="n">
-        <v>1</v>
-      </c>
-      <c r="E52" s="17" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="F52" s="20" t="n">
-        <v>91</v>
+        <v>2</v>
+      </c>
+      <c r="E52" s="10" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="F52" s="10" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
       <c r="G52" s="10" t="inlineStr">
         <is>
-          <t>Asset Sale [narrative]</t>
+          <t>Going Private [event]; Uplisting [event]</t>
         </is>
       </c>
     </row>
     <row r="53" ht="22" customHeight="1">
       <c r="A53" s="6" t="inlineStr">
         <is>
-          <t>VTOL</t>
+          <t>SMTK</t>
         </is>
       </c>
       <c r="B53" s="7" t="inlineStr">
         <is>
-          <t>Bristow Group, Inc.</t>
+          <t>SMTK</t>
         </is>
       </c>
       <c r="C53" s="16" t="n">
-        <v>5.7</v>
+        <v>20</v>
       </c>
       <c r="D53" s="16" t="n">
-        <v>1</v>
-      </c>
-      <c r="E53" s="16" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="F53" s="19" t="n">
-        <v>79</v>
+        <v>2</v>
+      </c>
+      <c r="E53" s="7" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="F53" s="7" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
       <c r="G53" s="7" t="inlineStr">
         <is>
-          <t>Asset Sale [narrative]</t>
+          <t>Going Private [event]; Uplisting [event]</t>
         </is>
       </c>
     </row>
     <row r="54" ht="22" customHeight="1">
       <c r="A54" s="9" t="inlineStr">
         <is>
-          <t>MNRO</t>
+          <t>IAC</t>
         </is>
       </c>
       <c r="B54" s="10" t="inlineStr">
         <is>
-          <t>Monro, Inc.</t>
+          <t>IAC</t>
         </is>
       </c>
       <c r="C54" s="17" t="n">
-        <v>5.6</v>
+        <v>19</v>
       </c>
       <c r="D54" s="17" t="n">
-        <v>1</v>
-      </c>
-      <c r="E54" s="17" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="F54" s="20" t="n">
-        <v>66</v>
+        <v>2</v>
+      </c>
+      <c r="E54" s="10" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="F54" s="10" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
       <c r="G54" s="10" t="inlineStr">
         <is>
-          <t>Sale Of Company [narrative]</t>
+          <t>Asset Sale [narrative]; Spinoff [event]</t>
         </is>
       </c>
     </row>
     <row r="56" ht="28" customHeight="1">
       <c r="A56" s="11" t="inlineStr">
         <is>
-          <t>191 names carry a corporate-action re-rate catalyst (7 carry two or more types). Distribution: strategic review 78, asset sale 66, sale of company 40, separation 11, spinoff 3. Sources by hardness: INCENTIVE = the PSU plan pays management to achieve the spin/sale/M&amp;A (skin in the game, hardest); TENDER = a live bid (role TARGET); NARRATIVE = management states the intent in the 10-K/10-Q MD&amp;A. A catalyst named by two independent sources is triangulated (+bonus); two distinct catalyst types is the in-play configuration. Score = catalyst strength x (1 + geometry upside room), so a spin/sale with real re-rate headroom outranks one in an already-fair-valued name (rows with '—' ratio have no value-geometry floor — typically large-caps where the re-rate is a discount-collapse story, not an asset-floor play). Source: rerate_catalysts.py.</t>
+          <t>760 names carry a corporate-action re-rate catalyst (92 carry two or more types). Distribution: asset sale 164, sale of company 118, strategic review 116, uplisting 104, buyback auth 86, tender offer 64, going private 52, spinoff 43, capital return 43, exchange offer 33, separation 29, ch11 emergence 16. Sources by hardness: INCENTIVE = the PSU plan pays management to achieve the spin/sale/M&amp;A (skin in the game, hardest); TENDER = a live bid (role TARGET); NARRATIVE = management states the intent in the 10-K/10-Q MD&amp;A. A catalyst named by two independent sources is triangulated (+bonus); two distinct catalyst types is the in-play configuration. Score = catalyst strength x (1 + geometry upside room), so a spin/sale with real re-rate headroom outranks one in an already-fair-valued name (rows with '—' ratio have no value-geometry floor — typically large-caps where the re-rate is a discount-collapse story, not an asset-floor play). Source: rerate_catalysts.py.</t>
         </is>
       </c>
     </row>
@@ -8395,7 +8431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:F75"/>
+  <dimension ref="A1:F79"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -8468,275 +8504,275 @@
     <row r="6" ht="22" customHeight="1">
       <c r="A6" s="6" t="inlineStr">
         <is>
-          <t>AGPU</t>
+          <t>FWDI</t>
         </is>
       </c>
       <c r="B6" s="7" t="inlineStr">
         <is>
-          <t>Axe Compute Inc.</t>
+          <t>Forward Industries,</t>
         </is>
       </c>
       <c r="C6" s="16" t="n">
-        <v>44</v>
+        <v>56</v>
       </c>
       <c r="D6" s="16" t="n">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="E6" s="7" t="inlineStr">
         <is>
-          <t>4.1m</t>
+          <t>6.3m</t>
         </is>
       </c>
       <c r="F6" s="7" t="inlineStr">
         <is>
-          <t>STRATEGIC_REVIEW</t>
+          <t>SALE_OF_COMPANY</t>
         </is>
       </c>
     </row>
     <row r="7" ht="22" customHeight="1">
       <c r="A7" s="9" t="inlineStr">
         <is>
-          <t>CNMD</t>
+          <t>TASK</t>
         </is>
       </c>
       <c r="B7" s="10" t="inlineStr">
         <is>
-          <t>CONMED Corporation</t>
+          <t>TaskUs, Inc.</t>
         </is>
       </c>
       <c r="C7" s="17" t="n">
-        <v>34</v>
+        <v>52</v>
       </c>
       <c r="D7" s="17" t="n">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="E7" s="10" t="inlineStr">
         <is>
-          <t>4.6m</t>
+          <t>6.0m</t>
         </is>
       </c>
       <c r="F7" s="10" t="inlineStr">
         <is>
-          <t>ASSET_SALE</t>
+          <t>CAPITAL_RETURN</t>
         </is>
       </c>
     </row>
     <row r="8" ht="22" customHeight="1">
       <c r="A8" s="6" t="inlineStr">
         <is>
-          <t>ANF</t>
+          <t>PAR</t>
         </is>
       </c>
       <c r="B8" s="7" t="inlineStr">
         <is>
-          <t>Abercrombie &amp; Fitch</t>
+          <t>PAR Technology Corpo</t>
         </is>
       </c>
       <c r="C8" s="16" t="n">
-        <v>34</v>
+        <v>52</v>
       </c>
       <c r="D8" s="16" t="n">
-        <v>68</v>
+        <v>39</v>
       </c>
       <c r="E8" s="7" t="inlineStr">
         <is>
-          <t>5.7m</t>
+          <t>6.7m</t>
         </is>
       </c>
       <c r="F8" s="7" t="inlineStr">
         <is>
-          <t>STRATEGIC_REVIEW</t>
+          <t>BUYBACK_AUTH</t>
         </is>
       </c>
     </row>
     <row r="9" ht="22" customHeight="1">
       <c r="A9" s="9" t="inlineStr">
         <is>
-          <t>GPC</t>
+          <t>PD</t>
         </is>
       </c>
       <c r="B9" s="10" t="inlineStr">
         <is>
-          <t>Genuine Parts Compan</t>
+          <t>PagerDuty, Inc.</t>
         </is>
       </c>
       <c r="C9" s="17" t="n">
-        <v>30</v>
+        <v>52</v>
       </c>
       <c r="D9" s="17" t="n">
-        <v>34</v>
+        <v>51</v>
       </c>
       <c r="E9" s="10" t="inlineStr">
         <is>
-          <t>4.9m</t>
+          <t>3.6m</t>
         </is>
       </c>
       <c r="F9" s="10" t="inlineStr">
         <is>
-          <t>SEPARATION</t>
+          <t>BUYBACK_AUTH</t>
         </is>
       </c>
     </row>
     <row r="10" ht="22" customHeight="1">
       <c r="A10" s="6" t="inlineStr">
         <is>
-          <t>HWH</t>
+          <t>IBEX</t>
         </is>
       </c>
       <c r="B10" s="7" t="inlineStr">
         <is>
-          <t>HWH</t>
+          <t>IBEX Limited</t>
         </is>
       </c>
       <c r="C10" s="16" t="n">
-        <v>28</v>
+        <v>46</v>
       </c>
       <c r="D10" s="16" t="n">
-        <v>105</v>
+        <v>35</v>
       </c>
       <c r="E10" s="7" t="inlineStr">
         <is>
-          <t>5.7m</t>
+          <t>4.1m</t>
         </is>
       </c>
       <c r="F10" s="7" t="inlineStr">
         <is>
-          <t>SALE_OF_COMPANY</t>
+          <t>BUYBACK_AUTH</t>
         </is>
       </c>
     </row>
     <row r="11" ht="22" customHeight="1">
       <c r="A11" s="9" t="inlineStr">
         <is>
-          <t>MNPR</t>
+          <t>ANGX</t>
         </is>
       </c>
       <c r="B11" s="10" t="inlineStr">
         <is>
-          <t>MNPR</t>
+          <t>Angel Studios, Inc.</t>
         </is>
       </c>
       <c r="C11" s="17" t="n">
-        <v>28</v>
+        <v>45</v>
       </c>
       <c r="D11" s="17" t="n">
-        <v>109</v>
+        <v>101</v>
       </c>
       <c r="E11" s="10" t="inlineStr">
         <is>
-          <t>5.7m</t>
+          <t>5.1m</t>
         </is>
       </c>
       <c r="F11" s="10" t="inlineStr">
         <is>
-          <t>SALE_OF_COMPANY</t>
+          <t>UPLISTING</t>
         </is>
       </c>
     </row>
     <row r="12" ht="22" customHeight="1">
       <c r="A12" s="6" t="inlineStr">
         <is>
-          <t>XHLD</t>
+          <t>AGPU</t>
         </is>
       </c>
       <c r="B12" s="7" t="inlineStr">
         <is>
-          <t>XHLD</t>
+          <t>Axe Compute Inc.</t>
         </is>
       </c>
       <c r="C12" s="16" t="n">
-        <v>28</v>
+        <v>44</v>
       </c>
       <c r="D12" s="16" t="n">
-        <v>927</v>
+        <v>45</v>
       </c>
       <c r="E12" s="7" t="inlineStr">
         <is>
-          <t>6.0m</t>
+          <t>4.1m</t>
         </is>
       </c>
       <c r="F12" s="7" t="inlineStr">
         <is>
-          <t>SALE_OF_COMPANY</t>
+          <t>STRATEGIC_REVIEW</t>
         </is>
       </c>
     </row>
     <row r="13" ht="22" customHeight="1">
       <c r="A13" s="9" t="inlineStr">
         <is>
-          <t>PARK</t>
+          <t>GPRO</t>
         </is>
       </c>
       <c r="B13" s="10" t="inlineStr">
         <is>
-          <t>PARK</t>
+          <t>GoPro, Inc.</t>
         </is>
       </c>
       <c r="C13" s="17" t="n">
-        <v>28</v>
+        <v>44</v>
       </c>
       <c r="D13" s="17" t="n">
-        <v>20</v>
+        <v>57</v>
       </c>
       <c r="E13" s="10" t="inlineStr">
         <is>
-          <t>5.8m</t>
+          <t>2.3m</t>
         </is>
       </c>
       <c r="F13" s="10" t="inlineStr">
         <is>
-          <t>SALE_OF_COMPANY</t>
+          <t>STRATEGIC_REVIEW</t>
         </is>
       </c>
     </row>
     <row r="14" ht="22" customHeight="1">
       <c r="A14" s="6" t="inlineStr">
         <is>
-          <t>CUEN</t>
+          <t>DUOL</t>
         </is>
       </c>
       <c r="B14" s="7" t="inlineStr">
         <is>
-          <t>CUEN</t>
+          <t>Duolingo, Inc.</t>
         </is>
       </c>
       <c r="C14" s="16" t="n">
-        <v>28</v>
+        <v>42</v>
       </c>
       <c r="D14" s="16" t="n">
-        <v>49</v>
+        <v>55</v>
       </c>
       <c r="E14" s="7" t="inlineStr">
         <is>
-          <t>4.8m</t>
+          <t>6.7m</t>
         </is>
       </c>
       <c r="F14" s="7" t="inlineStr">
         <is>
-          <t>SALE_OF_COMPANY</t>
+          <t>BUYBACK_AUTH</t>
         </is>
       </c>
     </row>
     <row r="15" ht="22" customHeight="1">
       <c r="A15" s="9" t="inlineStr">
         <is>
-          <t>CVI</t>
+          <t>PRGO</t>
         </is>
       </c>
       <c r="B15" s="10" t="inlineStr">
         <is>
-          <t>CVR Energy Inc.</t>
+          <t>Perrigo Company plc</t>
         </is>
       </c>
       <c r="C15" s="17" t="n">
-        <v>26</v>
+        <v>41</v>
       </c>
       <c r="D15" s="17" t="n">
-        <v>49</v>
+        <v>32</v>
       </c>
       <c r="E15" s="10" t="inlineStr">
         <is>
-          <t>4.6m</t>
+          <t>6.7m</t>
         </is>
       </c>
       <c r="F15" s="10" t="inlineStr">
@@ -8748,380 +8784,378 @@
     <row r="16" ht="22" customHeight="1">
       <c r="A16" s="6" t="inlineStr">
         <is>
-          <t>ITGR</t>
+          <t>CERT</t>
         </is>
       </c>
       <c r="B16" s="7" t="inlineStr">
         <is>
-          <t>Integer Holdings Cor</t>
+          <t>Certara, Inc.</t>
         </is>
       </c>
       <c r="C16" s="16" t="n">
-        <v>25</v>
+        <v>41</v>
       </c>
       <c r="D16" s="16" t="n">
-        <v>41</v>
+        <v>33</v>
       </c>
       <c r="E16" s="7" t="inlineStr">
         <is>
-          <t>4.6m</t>
+          <t>4.8m</t>
         </is>
       </c>
       <c r="F16" s="7" t="inlineStr">
         <is>
-          <t>STRATEGIC_REVIEW</t>
+          <t>ASSET_SALE</t>
         </is>
       </c>
     </row>
     <row r="17" ht="22" customHeight="1">
       <c r="A17" s="9" t="inlineStr">
         <is>
-          <t>ACHV</t>
+          <t>SMCI</t>
         </is>
       </c>
       <c r="B17" s="10" t="inlineStr">
         <is>
-          <t>Achieve Life Science</t>
+          <t>Super Micro Computer</t>
         </is>
       </c>
       <c r="C17" s="17" t="n">
-        <v>24</v>
+        <v>38</v>
       </c>
       <c r="D17" s="17" t="n">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="E17" s="10" t="inlineStr">
         <is>
-          <t>4.6m</t>
+          <t>3.1m</t>
         </is>
       </c>
       <c r="F17" s="10" t="inlineStr">
         <is>
-          <t>ASSET_SALE</t>
+          <t>UPLISTING</t>
         </is>
       </c>
     </row>
     <row r="18" ht="22" customHeight="1">
       <c r="A18" s="6" t="inlineStr">
         <is>
-          <t>LITS</t>
+          <t>AZTA</t>
         </is>
       </c>
       <c r="B18" s="7" t="inlineStr">
         <is>
-          <t>LITS</t>
+          <t>Azenta, Inc.</t>
         </is>
       </c>
       <c r="C18" s="16" t="n">
-        <v>23</v>
+        <v>38</v>
       </c>
       <c r="D18" s="16" t="n">
-        <v>27</v>
+        <v>48</v>
       </c>
       <c r="E18" s="7" t="inlineStr">
         <is>
-          <t>4.1m</t>
+          <t>7.4m</t>
         </is>
       </c>
       <c r="F18" s="7" t="inlineStr">
         <is>
-          <t>STRATEGIC_REVIEW</t>
+          <t>BUYBACK_AUTH</t>
         </is>
       </c>
     </row>
     <row r="19" ht="22" customHeight="1">
       <c r="A19" s="9" t="inlineStr">
         <is>
-          <t>CLRO</t>
+          <t>GRND</t>
         </is>
       </c>
       <c r="B19" s="10" t="inlineStr">
         <is>
-          <t>CLRO</t>
+          <t>Grindr Inc.</t>
         </is>
       </c>
       <c r="C19" s="17" t="n">
-        <v>23</v>
+        <v>36</v>
       </c>
       <c r="D19" s="17" t="n">
-        <v>45</v>
+        <v>28</v>
       </c>
       <c r="E19" s="10" t="inlineStr">
         <is>
-          <t>5.6m</t>
+          <t>6.7m</t>
         </is>
       </c>
       <c r="F19" s="10" t="inlineStr">
         <is>
-          <t>STRATEGIC_REVIEW</t>
+          <t>GOING_PRIVATE</t>
         </is>
       </c>
     </row>
     <row r="20" ht="22" customHeight="1">
       <c r="A20" s="6" t="inlineStr">
         <is>
-          <t>MRAI</t>
+          <t>IT</t>
         </is>
       </c>
       <c r="B20" s="7" t="inlineStr">
         <is>
-          <t>MRAI</t>
+          <t>Gartner, Inc.</t>
         </is>
       </c>
       <c r="C20" s="16" t="n">
-        <v>23</v>
+        <v>34</v>
       </c>
       <c r="D20" s="16" t="n">
-        <v>353</v>
+        <v>22</v>
       </c>
       <c r="E20" s="7" t="inlineStr">
         <is>
-          <t>4.1m</t>
+          <t>7.4m</t>
         </is>
       </c>
       <c r="F20" s="7" t="inlineStr">
         <is>
-          <t>STRATEGIC_REVIEW</t>
+          <t>ASSET_SALE</t>
         </is>
       </c>
     </row>
     <row r="21" ht="22" customHeight="1">
       <c r="A21" s="9" t="inlineStr">
         <is>
-          <t>RPMT</t>
+          <t>CNMD</t>
         </is>
       </c>
       <c r="B21" s="10" t="inlineStr">
         <is>
-          <t>RPMT</t>
+          <t>CONMED Corporation</t>
         </is>
       </c>
       <c r="C21" s="17" t="n">
-        <v>23</v>
+        <v>34</v>
       </c>
       <c r="D21" s="17" t="n">
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="E21" s="10" t="inlineStr">
         <is>
-          <t>5.6m</t>
+          <t>4.6m</t>
         </is>
       </c>
       <c r="F21" s="10" t="inlineStr">
         <is>
-          <t>STRATEGIC_REVIEW</t>
+          <t>ASSET_SALE</t>
         </is>
       </c>
     </row>
     <row r="22" ht="22" customHeight="1">
       <c r="A22" s="6" t="inlineStr">
         <is>
-          <t>ONAR</t>
+          <t>ANF</t>
         </is>
       </c>
       <c r="B22" s="7" t="inlineStr">
         <is>
-          <t>ONAR</t>
+          <t>Abercrombie &amp; Fitch</t>
         </is>
       </c>
       <c r="C22" s="16" t="n">
-        <v>20</v>
+        <v>34</v>
       </c>
       <c r="D22" s="16" t="n">
-        <v>336</v>
+        <v>68</v>
       </c>
       <c r="E22" s="7" t="inlineStr">
         <is>
-          <t>3.2m</t>
+          <t>5.7m</t>
         </is>
       </c>
       <c r="F22" s="7" t="inlineStr">
         <is>
-          <t>ASSET_SALE</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="21" t="inlineStr">
-        <is>
-          <t>(17 confirmed / 1 pending / 74 neutral / 51 fading, of 143 priced)</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="12" t="inlineStr">
+          <t>STRATEGIC_REVIEW</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="22" customHeight="1">
+      <c r="A23" s="9" t="inlineStr">
+        <is>
+          <t>MGTX</t>
+        </is>
+      </c>
+      <c r="B23" s="10" t="inlineStr">
+        <is>
+          <t>MeiraGTx Holdings pl</t>
+        </is>
+      </c>
+      <c r="C23" s="17" t="n">
+        <v>33</v>
+      </c>
+      <c r="D23" s="17" t="n">
+        <v>23</v>
+      </c>
+      <c r="E23" s="10" t="inlineStr">
+        <is>
+          <t>5.0m</t>
+        </is>
+      </c>
+      <c r="F23" s="10" t="inlineStr">
+        <is>
+          <t>UPLISTING</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="22" customHeight="1">
+      <c r="A24" s="6" t="inlineStr">
+        <is>
+          <t>ADV</t>
+        </is>
+      </c>
+      <c r="B24" s="7" t="inlineStr">
+        <is>
+          <t>Advantage Solutions</t>
+        </is>
+      </c>
+      <c r="C24" s="16" t="n">
+        <v>33</v>
+      </c>
+      <c r="D24" s="16" t="n">
+        <v>64</v>
+      </c>
+      <c r="E24" s="7" t="inlineStr">
+        <is>
+          <t>7.2m</t>
+        </is>
+      </c>
+      <c r="F24" s="7" t="inlineStr">
+        <is>
+          <t>EXCHANGE_OFFER</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="22" customHeight="1">
+      <c r="A25" s="9" t="inlineStr">
+        <is>
+          <t>CTSH</t>
+        </is>
+      </c>
+      <c r="B25" s="10" t="inlineStr">
+        <is>
+          <t>Cognizant Technology</t>
+        </is>
+      </c>
+      <c r="C25" s="17" t="n">
+        <v>32</v>
+      </c>
+      <c r="D25" s="17" t="n">
+        <v>66</v>
+      </c>
+      <c r="E25" s="10" t="inlineStr">
+        <is>
+          <t>4.0m</t>
+        </is>
+      </c>
+      <c r="F25" s="10" t="inlineStr">
+        <is>
+          <t>BUYBACK_AUTH</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="22" customHeight="1">
+      <c r="A26" s="6" t="inlineStr">
+        <is>
+          <t>BWIN</t>
+        </is>
+      </c>
+      <c r="B26" s="7" t="inlineStr">
+        <is>
+          <t>The Baldwin Insuranc</t>
+        </is>
+      </c>
+      <c r="C26" s="16" t="n">
+        <v>32</v>
+      </c>
+      <c r="D26" s="16" t="n">
+        <v>38</v>
+      </c>
+      <c r="E26" s="7" t="inlineStr">
+        <is>
+          <t>8.5m</t>
+        </is>
+      </c>
+      <c r="F26" s="7" t="inlineStr">
+        <is>
+          <t>EXCHANGE_OFFER</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="21" t="inlineStr">
+        <is>
+          <t>(21 confirmed / 13 pending / 73 neutral / 41 fading, of 148 priced)</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="12" t="inlineStr">
         <is>
           <t>ALL CANDIDATES — pre-confirmation tail odds</t>
         </is>
       </c>
     </row>
-    <row r="26" ht="18" customHeight="1">
-      <c r="A26" s="15" t="inlineStr">
+    <row r="30" ht="18" customHeight="1">
+      <c r="A30" s="15" t="inlineStr">
         <is>
           <t>Ticker</t>
         </is>
       </c>
-      <c r="B26" s="15" t="inlineStr">
+      <c r="B30" s="15" t="inlineStr">
         <is>
           <t>Name</t>
         </is>
       </c>
-      <c r="C26" s="4" t="inlineStr">
+      <c r="C30" s="4" t="inlineStr">
         <is>
           <t>Tail p</t>
         </is>
       </c>
-      <c r="D26" s="4" t="inlineStr">
+      <c r="D30" s="4" t="inlineStr">
         <is>
           <t>State</t>
         </is>
       </c>
-      <c r="E26" s="4" t="inlineStr">
+      <c r="E30" s="4" t="inlineStr">
         <is>
           <t>Ratio</t>
         </is>
       </c>
-      <c r="F26" s="4" t="inlineStr">
+      <c r="F30" s="4" t="inlineStr">
         <is>
           <t>Tail drivers</t>
-        </is>
-      </c>
-    </row>
-    <row r="27" ht="22" customHeight="1">
-      <c r="A27" s="6" t="inlineStr">
-        <is>
-          <t>OPTU</t>
-        </is>
-      </c>
-      <c r="B27" s="7" t="inlineStr">
-        <is>
-          <t>Optimum Communicatio</t>
-        </is>
-      </c>
-      <c r="C27" s="16" t="n">
-        <v>35</v>
-      </c>
-      <c r="D27" s="7" t="inlineStr">
-        <is>
-          <t>NEUTRAL</t>
-        </is>
-      </c>
-      <c r="E27" s="16" t="n">
-        <v>3</v>
-      </c>
-      <c r="F27" s="7" t="inlineStr">
-        <is>
-          <t>catalyst=SALE_OF_COMPANY, size=small,</t>
-        </is>
-      </c>
-    </row>
-    <row r="28" ht="22" customHeight="1">
-      <c r="A28" s="9" t="inlineStr">
-        <is>
-          <t>DFH</t>
-        </is>
-      </c>
-      <c r="B28" s="10" t="inlineStr">
-        <is>
-          <t>Dream Finders Homes,</t>
-        </is>
-      </c>
-      <c r="C28" s="17" t="n">
-        <v>35</v>
-      </c>
-      <c r="D28" s="10" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="E28" s="17" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="F28" s="10" t="inlineStr">
-        <is>
-          <t>sector=Consumer Cyclical, size=small,</t>
-        </is>
-      </c>
-    </row>
-    <row r="29" ht="22" customHeight="1">
-      <c r="A29" s="6" t="inlineStr">
-        <is>
-          <t>CWH</t>
-        </is>
-      </c>
-      <c r="B29" s="7" t="inlineStr">
-        <is>
-          <t>Camping World Holdin</t>
-        </is>
-      </c>
-      <c r="C29" s="16" t="n">
-        <v>35</v>
-      </c>
-      <c r="D29" s="7" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="E29" s="16" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="F29" s="7" t="inlineStr">
-        <is>
-          <t>sector=Consumer Cyclical, size=small,</t>
-        </is>
-      </c>
-    </row>
-    <row r="30" ht="22" customHeight="1">
-      <c r="A30" s="9" t="inlineStr">
-        <is>
-          <t>LE</t>
-        </is>
-      </c>
-      <c r="B30" s="10" t="inlineStr">
-        <is>
-          <t>Lands' End, Inc.</t>
-        </is>
-      </c>
-      <c r="C30" s="17" t="n">
-        <v>34</v>
-      </c>
-      <c r="D30" s="10" t="inlineStr">
-        <is>
-          <t>NEUTRAL</t>
-        </is>
-      </c>
-      <c r="E30" s="17" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="F30" s="10" t="inlineStr">
-        <is>
-          <t>catalyst=SALE_OF_COMPANY, sector=Consu</t>
         </is>
       </c>
     </row>
     <row r="31" ht="22" customHeight="1">
       <c r="A31" s="6" t="inlineStr">
         <is>
-          <t>LUCK</t>
+          <t>FWDI</t>
         </is>
       </c>
       <c r="B31" s="7" t="inlineStr">
         <is>
-          <t>LUCKY STRIKE ENTERTA</t>
+          <t>Forward Industries,</t>
         </is>
       </c>
       <c r="C31" s="16" t="n">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="D31" s="7" t="inlineStr">
         <is>
-          <t>FADING</t>
-        </is>
-      </c>
-      <c r="E31" s="7" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="E31" s="16" t="n">
+        <v>12.9</v>
       </c>
       <c r="F31" s="7" t="inlineStr">
         <is>
@@ -9132,80 +9166,82 @@
     <row r="32" ht="22" customHeight="1">
       <c r="A32" s="9" t="inlineStr">
         <is>
-          <t>MNRO</t>
+          <t>PAR</t>
         </is>
       </c>
       <c r="B32" s="10" t="inlineStr">
         <is>
-          <t>Monro, Inc.</t>
+          <t>PAR Technology Corpo</t>
         </is>
       </c>
       <c r="C32" s="17" t="n">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="D32" s="10" t="inlineStr">
         <is>
-          <t>FADING</t>
+          <t>CONFIRMED</t>
         </is>
       </c>
       <c r="E32" s="17" t="n">
-        <v>1.8</v>
+        <v>15.5</v>
       </c>
       <c r="F32" s="10" t="inlineStr">
         <is>
-          <t>catalyst=SALE_OF_COMPANY, sector=Consu</t>
+          <t>sector=Technology, size=small, drawdow</t>
         </is>
       </c>
     </row>
     <row r="33" ht="22" customHeight="1">
       <c r="A33" s="6" t="inlineStr">
         <is>
-          <t>DXLG</t>
+          <t>ALKT</t>
         </is>
       </c>
       <c r="B33" s="7" t="inlineStr">
         <is>
-          <t>Destination XL Group</t>
+          <t>Alkami Technology, I</t>
         </is>
       </c>
       <c r="C33" s="16" t="n">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="D33" s="7" t="inlineStr">
         <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="E33" s="16" t="n">
-        <v>60</v>
+          <t>NEUTRAL</t>
+        </is>
+      </c>
+      <c r="E33" s="7" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
       <c r="F33" s="7" t="inlineStr">
         <is>
-          <t>catalyst=SALE_OF_COMPANY, sector=Consu</t>
+          <t>sector=Technology, size=small, drawdow</t>
         </is>
       </c>
     </row>
     <row r="34" ht="22" customHeight="1">
       <c r="A34" s="9" t="inlineStr">
         <is>
-          <t>DXC</t>
+          <t>PD</t>
         </is>
       </c>
       <c r="B34" s="10" t="inlineStr">
         <is>
-          <t>DXC Technology Compa</t>
+          <t>PagerDuty, Inc.</t>
         </is>
       </c>
       <c r="C34" s="17" t="n">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="D34" s="10" t="inlineStr">
         <is>
-          <t>–</t>
+          <t>CONFIRMED</t>
         </is>
       </c>
       <c r="E34" s="17" t="n">
-        <v>30</v>
+        <v>1.4</v>
       </c>
       <c r="F34" s="10" t="inlineStr">
         <is>
@@ -9216,100 +9252,100 @@
     <row r="35" ht="22" customHeight="1">
       <c r="A35" s="6" t="inlineStr">
         <is>
-          <t>LMRI</t>
+          <t>TASK</t>
         </is>
       </c>
       <c r="B35" s="7" t="inlineStr">
         <is>
-          <t>Lumexa Imaging Holdi</t>
+          <t>TaskUs, Inc.</t>
         </is>
       </c>
       <c r="C35" s="16" t="n">
-        <v>30</v>
+        <v>37</v>
       </c>
       <c r="D35" s="7" t="inlineStr">
         <is>
-          <t>–</t>
+          <t>CONFIRMED</t>
         </is>
       </c>
       <c r="E35" s="16" t="n">
-        <v>3.3</v>
+        <v>4.3</v>
       </c>
       <c r="F35" s="7" t="inlineStr">
         <is>
-          <t>size=small, drawdown_12m=deep(&lt;-50%),</t>
+          <t>sector=Technology, size=small, drawdow</t>
         </is>
       </c>
     </row>
     <row r="36" ht="22" customHeight="1">
       <c r="A36" s="9" t="inlineStr">
         <is>
-          <t>CMTL</t>
+          <t>OPTU</t>
         </is>
       </c>
       <c r="B36" s="10" t="inlineStr">
         <is>
-          <t>Comtech Telecommunic</t>
+          <t>Optimum Communicatio</t>
         </is>
       </c>
       <c r="C36" s="17" t="n">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="D36" s="10" t="inlineStr">
         <is>
-          <t>FADING</t>
+          <t>NEUTRAL</t>
         </is>
       </c>
       <c r="E36" s="17" t="n">
-        <v>11.5</v>
+        <v>3</v>
       </c>
       <c r="F36" s="10" t="inlineStr">
         <is>
-          <t>sector=Technology, size=micro, drawdow</t>
+          <t>catalyst=SALE_OF_COMPANY, size=small,</t>
         </is>
       </c>
     </row>
     <row r="37" ht="22" customHeight="1">
       <c r="A37" s="6" t="inlineStr">
         <is>
-          <t>AGPU</t>
+          <t>ORBS</t>
         </is>
       </c>
       <c r="B37" s="7" t="inlineStr">
         <is>
-          <t>Axe Compute Inc.</t>
+          <t>Eightco Holdings Inc</t>
         </is>
       </c>
       <c r="C37" s="16" t="n">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="D37" s="7" t="inlineStr">
         <is>
-          <t>CONFIRMED</t>
+          <t>FADING</t>
         </is>
       </c>
       <c r="E37" s="16" t="n">
-        <v>8.4</v>
+        <v>1.3</v>
       </c>
       <c r="F37" s="7" t="inlineStr">
         <is>
-          <t>sector=Technology, size=micro, drawdow</t>
+          <t>sector=Consumer Cyclical, size=small,</t>
         </is>
       </c>
     </row>
     <row r="38" ht="22" customHeight="1">
       <c r="A38" s="9" t="inlineStr">
         <is>
-          <t>GRNT</t>
+          <t>CWH</t>
         </is>
       </c>
       <c r="B38" s="10" t="inlineStr">
         <is>
-          <t>Granite Ridge Resour</t>
+          <t>Camping World Holdin</t>
         </is>
       </c>
       <c r="C38" s="17" t="n">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="D38" s="10" t="inlineStr">
         <is>
@@ -9317,27 +9353,27 @@
         </is>
       </c>
       <c r="E38" s="17" t="n">
-        <v>0.7</v>
+        <v>3.8</v>
       </c>
       <c r="F38" s="10" t="inlineStr">
         <is>
-          <t>sector=Energy, size=small, drawdown_12</t>
+          <t>sector=Consumer Cyclical, size=small,</t>
         </is>
       </c>
     </row>
     <row r="39" ht="22" customHeight="1">
       <c r="A39" s="6" t="inlineStr">
         <is>
-          <t>DEC</t>
+          <t>DFH</t>
         </is>
       </c>
       <c r="B39" s="7" t="inlineStr">
         <is>
-          <t>Diversified Energy C</t>
+          <t>Dream Finders Homes,</t>
         </is>
       </c>
       <c r="C39" s="16" t="n">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="D39" s="7" t="inlineStr">
         <is>
@@ -9345,115 +9381,117 @@
         </is>
       </c>
       <c r="E39" s="16" t="n">
-        <v>2.3</v>
+        <v>2.5</v>
       </c>
       <c r="F39" s="7" t="inlineStr">
         <is>
-          <t>sector=Energy, size=small, drawdown_12</t>
+          <t>sector=Consumer Cyclical, size=small,</t>
         </is>
       </c>
     </row>
     <row r="40" ht="22" customHeight="1">
       <c r="A40" s="9" t="inlineStr">
         <is>
-          <t>ADNT</t>
+          <t>AIRE</t>
         </is>
       </c>
       <c r="B40" s="10" t="inlineStr">
         <is>
-          <t>Adient plc</t>
+          <t>reAlpha Tech Corp.</t>
         </is>
       </c>
       <c r="C40" s="17" t="n">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="D40" s="10" t="inlineStr">
         <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="E40" s="17" t="n">
-        <v>6.3</v>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="E40" s="10" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
       <c r="F40" s="10" t="inlineStr">
         <is>
-          <t>sector=Consumer Cyclical, size=small,</t>
+          <t>catalyst=SALE_OF_COMPANY, sector=Real</t>
         </is>
       </c>
     </row>
     <row r="41" ht="22" customHeight="1">
       <c r="A41" s="6" t="inlineStr">
         <is>
-          <t>CMRC</t>
+          <t>MNRO</t>
         </is>
       </c>
       <c r="B41" s="7" t="inlineStr">
         <is>
-          <t>Commerce.com, Inc. -</t>
+          <t>Monro, Inc.</t>
         </is>
       </c>
       <c r="C41" s="16" t="n">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="D41" s="7" t="inlineStr">
         <is>
-          <t>–</t>
+          <t>FADING</t>
         </is>
       </c>
       <c r="E41" s="16" t="n">
-        <v>3.4</v>
+        <v>1.8</v>
       </c>
       <c r="F41" s="7" t="inlineStr">
         <is>
-          <t>sector=Technology, size=micro, drawdow</t>
+          <t>catalyst=SALE_OF_COMPANY, sector=Consu</t>
         </is>
       </c>
     </row>
     <row r="42" ht="22" customHeight="1">
       <c r="A42" s="9" t="inlineStr">
         <is>
-          <t>THRY</t>
+          <t>LE</t>
         </is>
       </c>
       <c r="B42" s="10" t="inlineStr">
         <is>
-          <t>Thryv Holdings, Inc.</t>
+          <t>Lands' End, Inc.</t>
         </is>
       </c>
       <c r="C42" s="17" t="n">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="D42" s="10" t="inlineStr">
         <is>
-          <t>–</t>
+          <t>NEUTRAL</t>
         </is>
       </c>
       <c r="E42" s="17" t="n">
-        <v>10.9</v>
+        <v>5.1</v>
       </c>
       <c r="F42" s="10" t="inlineStr">
         <is>
-          <t>sector=Technology, size=micro, drawdow</t>
+          <t>catalyst=SALE_OF_COMPANY, sector=Consu</t>
         </is>
       </c>
     </row>
     <row r="43" ht="22" customHeight="1">
       <c r="A43" s="6" t="inlineStr">
         <is>
-          <t>BTAI</t>
+          <t>LUCK</t>
         </is>
       </c>
       <c r="B43" s="7" t="inlineStr">
         <is>
-          <t>BioXcel Therapeutics</t>
+          <t>LUCKY STRIKE ENTERTA</t>
         </is>
       </c>
       <c r="C43" s="16" t="n">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="D43" s="7" t="inlineStr">
         <is>
-          <t>NEUTRAL</t>
+          <t>FADING</t>
         </is>
       </c>
       <c r="E43" s="7" t="inlineStr">
@@ -9463,79 +9501,79 @@
       </c>
       <c r="F43" s="7" t="inlineStr">
         <is>
-          <t>catalyst=SALE_OF_COMPANY, size=micro,</t>
+          <t>catalyst=SALE_OF_COMPANY, sector=Consu</t>
         </is>
       </c>
     </row>
     <row r="44" ht="22" customHeight="1">
       <c r="A44" s="9" t="inlineStr">
         <is>
-          <t>WKHS</t>
+          <t>SUNE</t>
         </is>
       </c>
       <c r="B44" s="10" t="inlineStr">
         <is>
-          <t>Workhorse Group, Inc</t>
+          <t>SUNation Energy, Inc</t>
         </is>
       </c>
       <c r="C44" s="17" t="n">
-        <v>27</v>
+        <v>34</v>
       </c>
       <c r="D44" s="10" t="inlineStr">
         <is>
-          <t>–</t>
+          <t>PENDING</t>
         </is>
       </c>
       <c r="E44" s="17" t="n">
-        <v>7.4</v>
+        <v>60</v>
       </c>
       <c r="F44" s="10" t="inlineStr">
         <is>
-          <t>sector=Consumer Cyclical, size=micro,</t>
+          <t>catalyst=SALE_OF_COMPANY, sector=Techn</t>
         </is>
       </c>
     </row>
     <row r="45" ht="22" customHeight="1">
       <c r="A45" s="6" t="inlineStr">
         <is>
-          <t>LAB</t>
+          <t>JTAI</t>
         </is>
       </c>
       <c r="B45" s="7" t="inlineStr">
         <is>
-          <t>Standard BioTools In</t>
+          <t>Jet.AI Inc.</t>
         </is>
       </c>
       <c r="C45" s="16" t="n">
-        <v>27</v>
+        <v>34</v>
       </c>
       <c r="D45" s="7" t="inlineStr">
         <is>
-          <t>NEUTRAL</t>
+          <t>FADING</t>
         </is>
       </c>
       <c r="E45" s="16" t="n">
-        <v>42.3</v>
+        <v>60</v>
       </c>
       <c r="F45" s="7" t="inlineStr">
         <is>
-          <t>size=small, drawdown_12m=deep(&lt;-50%),</t>
+          <t>catalyst=SALE_OF_COMPANY, sector=Techn</t>
         </is>
       </c>
     </row>
     <row r="46" ht="22" customHeight="1">
       <c r="A46" s="9" t="inlineStr">
         <is>
-          <t>SITC</t>
+          <t>CLVT</t>
         </is>
       </c>
       <c r="B46" s="10" t="inlineStr">
         <is>
-          <t>SITE Centers Corp.</t>
+          <t>Clarivate Plc</t>
         </is>
       </c>
       <c r="C46" s="17" t="n">
-        <v>26</v>
+        <v>33</v>
       </c>
       <c r="D46" s="10" t="inlineStr">
         <is>
@@ -9543,31 +9581,31 @@
         </is>
       </c>
       <c r="E46" s="17" t="n">
-        <v>2.8</v>
+        <v>60</v>
       </c>
       <c r="F46" s="10" t="inlineStr">
         <is>
-          <t>sector=Real Estate, size=micro, drawdo</t>
+          <t>sector=Technology, size=small, drawdow</t>
         </is>
       </c>
     </row>
     <row r="47" ht="22" customHeight="1">
       <c r="A47" s="6" t="inlineStr">
         <is>
-          <t>FRMI</t>
+          <t>BLND</t>
         </is>
       </c>
       <c r="B47" s="7" t="inlineStr">
         <is>
-          <t>Fermi Inc.</t>
+          <t>Blend Labs, Inc.</t>
         </is>
       </c>
       <c r="C47" s="16" t="n">
-        <v>26</v>
+        <v>33</v>
       </c>
       <c r="D47" s="7" t="inlineStr">
         <is>
-          <t>FADING</t>
+          <t>NEUTRAL</t>
         </is>
       </c>
       <c r="E47" s="7" t="inlineStr">
@@ -9577,27 +9615,27 @@
       </c>
       <c r="F47" s="7" t="inlineStr">
         <is>
-          <t>sector=Real Estate, drawdown_12m=deep(</t>
+          <t>sector=Technology, size=small, drawdow</t>
         </is>
       </c>
     </row>
     <row r="48" ht="22" customHeight="1">
       <c r="A48" s="9" t="inlineStr">
         <is>
-          <t>CNDT</t>
+          <t>DXLG</t>
         </is>
       </c>
       <c r="B48" s="10" t="inlineStr">
         <is>
-          <t>Conduent Incorporate</t>
+          <t>Destination XL Group</t>
         </is>
       </c>
       <c r="C48" s="17" t="n">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="D48" s="10" t="inlineStr">
         <is>
-          <t>NEUTRAL</t>
+          <t>PENDING</t>
         </is>
       </c>
       <c r="E48" s="17" t="n">
@@ -9605,512 +9643,532 @@
       </c>
       <c r="F48" s="10" t="inlineStr">
         <is>
-          <t>sector=Technology, size=micro, drawdow</t>
+          <t>catalyst=SALE_OF_COMPANY, sector=Consu</t>
         </is>
       </c>
     </row>
     <row r="49" ht="22" customHeight="1">
       <c r="A49" s="6" t="inlineStr">
         <is>
-          <t>MATV</t>
+          <t>FPH</t>
         </is>
       </c>
       <c r="B49" s="7" t="inlineStr">
         <is>
-          <t>Mativ Holdings, Inc.</t>
+          <t>Five Point Holdings,</t>
         </is>
       </c>
       <c r="C49" s="16" t="n">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="D49" s="7" t="inlineStr">
         <is>
-          <t>–</t>
+          <t>NEUTRAL</t>
         </is>
       </c>
       <c r="E49" s="16" t="n">
-        <v>7.1</v>
+        <v>45.8</v>
       </c>
       <c r="F49" s="7" t="inlineStr">
         <is>
-          <t>sector=Basic Materials, size=small, dr</t>
+          <t>sector=Real Estate, size=small, drawdo</t>
         </is>
       </c>
     </row>
     <row r="50" ht="22" customHeight="1">
       <c r="A50" s="9" t="inlineStr">
         <is>
-          <t>PAHC</t>
+          <t>SITC</t>
         </is>
       </c>
       <c r="B50" s="10" t="inlineStr">
         <is>
-          <t>Phibro Animal Health</t>
+          <t>SITE Centers Corp.</t>
         </is>
       </c>
       <c r="C50" s="17" t="n">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="D50" s="10" t="inlineStr">
         <is>
-          <t>–</t>
+          <t>NEUTRAL</t>
         </is>
       </c>
       <c r="E50" s="17" t="n">
-        <v>3.5</v>
+        <v>2.8</v>
       </c>
       <c r="F50" s="10" t="inlineStr">
         <is>
-          <t>size=small, drawdown_12m=mod(-50..-20%</t>
+          <t>catalyst=SPINOFF, sector=Real Estate,</t>
         </is>
       </c>
     </row>
     <row r="51" ht="22" customHeight="1">
       <c r="A51" s="6" t="inlineStr">
         <is>
-          <t>BALY</t>
+          <t>FMC</t>
         </is>
       </c>
       <c r="B51" s="7" t="inlineStr">
         <is>
-          <t>Bally's Corporation</t>
+          <t>FMC Corporation</t>
         </is>
       </c>
       <c r="C51" s="16" t="n">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="D51" s="7" t="inlineStr">
         <is>
-          <t>–</t>
+          <t>NEUTRAL</t>
         </is>
       </c>
       <c r="E51" s="16" t="n">
-        <v>38.5</v>
+        <v>6.1</v>
       </c>
       <c r="F51" s="7" t="inlineStr">
         <is>
-          <t>sector=Consumer Cyclical, size=small,</t>
+          <t>sector=Basic Materials, size=small, dr</t>
         </is>
       </c>
     </row>
     <row r="52" ht="22" customHeight="1">
       <c r="A52" s="9" t="inlineStr">
         <is>
-          <t>BIRD</t>
+          <t>DXC</t>
         </is>
       </c>
       <c r="B52" s="10" t="inlineStr">
         <is>
-          <t>Allbirds, Inc.</t>
+          <t>DXC Technology Compa</t>
         </is>
       </c>
       <c r="C52" s="17" t="n">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="D52" s="10" t="inlineStr">
         <is>
-          <t>FADING</t>
+          <t>–</t>
         </is>
       </c>
       <c r="E52" s="17" t="n">
-        <v>1.8</v>
+        <v>30</v>
       </c>
       <c r="F52" s="10" t="inlineStr">
         <is>
-          <t>sector=Consumer Cyclical, size=micro,</t>
+          <t>sector=Technology, size=small, drawdow</t>
         </is>
       </c>
     </row>
     <row r="53" ht="22" customHeight="1">
       <c r="A53" s="6" t="inlineStr">
         <is>
-          <t>PLCE</t>
+          <t>IBEX</t>
         </is>
       </c>
       <c r="B53" s="7" t="inlineStr">
         <is>
-          <t>Children's Place, In</t>
+          <t>IBEX Limited</t>
         </is>
       </c>
       <c r="C53" s="16" t="n">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="D53" s="7" t="inlineStr">
         <is>
-          <t>NEUTRAL</t>
+          <t>CONFIRMED</t>
         </is>
       </c>
       <c r="E53" s="16" t="n">
-        <v>3</v>
+        <v>2.8</v>
       </c>
       <c r="F53" s="7" t="inlineStr">
         <is>
-          <t>sector=Consumer Cyclical, size=micro,</t>
+          <t>sector=Technology, size=small, drawdow</t>
         </is>
       </c>
     </row>
     <row r="54" ht="22" customHeight="1">
       <c r="A54" s="9" t="inlineStr">
         <is>
-          <t>FULC</t>
+          <t>IIIV</t>
         </is>
       </c>
       <c r="B54" s="10" t="inlineStr">
         <is>
-          <t>Fulcrum Therapeutics</t>
+          <t>i3 Verticals, Inc.</t>
         </is>
       </c>
       <c r="C54" s="17" t="n">
-        <v>23</v>
+        <v>31</v>
       </c>
       <c r="D54" s="10" t="inlineStr">
         <is>
-          <t>NEUTRAL</t>
+          <t>FADING</t>
         </is>
       </c>
       <c r="E54" s="17" t="n">
-        <v>8.300000000000001</v>
+        <v>2.5</v>
       </c>
       <c r="F54" s="10" t="inlineStr">
         <is>
-          <t>size=micro, drawdown_12m=deep(&lt;-50%),</t>
+          <t>sector=Technology, size=small, drawdow</t>
         </is>
       </c>
     </row>
     <row r="55" ht="22" customHeight="1">
       <c r="A55" s="6" t="inlineStr">
         <is>
-          <t>NERV</t>
+          <t>VREOF</t>
         </is>
       </c>
       <c r="B55" s="7" t="inlineStr">
         <is>
-          <t>Minerva Neuroscience</t>
+          <t>VIREO GROWTH INC.</t>
         </is>
       </c>
       <c r="C55" s="16" t="n">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="D55" s="7" t="inlineStr">
         <is>
-          <t>FADING</t>
-        </is>
-      </c>
-      <c r="E55" s="7" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+          <t>NEUTRAL</t>
+        </is>
+      </c>
+      <c r="E55" s="16" t="n">
+        <v>0.9</v>
       </c>
       <c r="F55" s="7" t="inlineStr">
         <is>
-          <t>size=micro, drawdown_12m=deep(&lt;-50%),</t>
+          <t>catalyst=SALE_OF_COMPANY, size=small,</t>
         </is>
       </c>
     </row>
     <row r="56" ht="22" customHeight="1">
       <c r="A56" s="9" t="inlineStr">
         <is>
-          <t>NEUP</t>
+          <t>SIGA</t>
         </is>
       </c>
       <c r="B56" s="10" t="inlineStr">
         <is>
-          <t>Neuphoria Therapeuti</t>
+          <t>SIGA Technologies In</t>
         </is>
       </c>
       <c r="C56" s="17" t="n">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="D56" s="10" t="inlineStr">
         <is>
-          <t>FADING</t>
+          <t>NEUTRAL</t>
         </is>
       </c>
       <c r="E56" s="17" t="n">
-        <v>3.9</v>
+        <v>0.5</v>
       </c>
       <c r="F56" s="10" t="inlineStr">
         <is>
-          <t>size=micro, drawdown_12m=deep(&lt;-50%),</t>
+          <t>size=small, drawdown_12m=deep(&lt;-50%),</t>
         </is>
       </c>
     </row>
     <row r="57" ht="22" customHeight="1">
       <c r="A57" s="6" t="inlineStr">
         <is>
-          <t>BFAM</t>
+          <t>LMRI</t>
         </is>
       </c>
       <c r="B57" s="7" t="inlineStr">
         <is>
-          <t>Bright Horizons Fami</t>
+          <t>Lumexa Imaging Holdi</t>
         </is>
       </c>
       <c r="C57" s="16" t="n">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="D57" s="7" t="inlineStr">
         <is>
-          <t>NEUTRAL</t>
-        </is>
-      </c>
-      <c r="E57" s="7" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="E57" s="16" t="n">
+        <v>3.3</v>
       </c>
       <c r="F57" s="7" t="inlineStr">
         <is>
-          <t>sector=Consumer Cyclical, drawdown_12m</t>
+          <t>size=small, drawdown_12m=deep(&lt;-50%),</t>
         </is>
       </c>
     </row>
     <row r="58" ht="22" customHeight="1">
       <c r="A58" s="9" t="inlineStr">
         <is>
-          <t>PMCB</t>
+          <t>ANGX</t>
         </is>
       </c>
       <c r="B58" s="10" t="inlineStr">
         <is>
-          <t>PharmaCyte  Biotech,</t>
+          <t>Angel Studios, Inc.</t>
         </is>
       </c>
       <c r="C58" s="17" t="n">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="D58" s="10" t="inlineStr">
         <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="E58" s="17" t="n">
-        <v>30</v>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="E58" s="10" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
       <c r="F58" s="10" t="inlineStr">
         <is>
-          <t>size=micro, drawdown_12m=deep(&lt;-50%),</t>
+          <t>size=small, drawdown_12m=deep(&lt;-50%),</t>
         </is>
       </c>
     </row>
     <row r="59" ht="22" customHeight="1">
       <c r="A59" s="6" t="inlineStr">
         <is>
-          <t>LUCY</t>
+          <t>UPWK</t>
         </is>
       </c>
       <c r="B59" s="7" t="inlineStr">
         <is>
-          <t>Innovative Eyewear,</t>
+          <t>Upwork Inc.</t>
         </is>
       </c>
       <c r="C59" s="16" t="n">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="D59" s="7" t="inlineStr">
         <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="E59" s="16" t="n">
-        <v>45.6</v>
+          <t>FADING</t>
+        </is>
+      </c>
+      <c r="E59" s="7" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
       <c r="F59" s="7" t="inlineStr">
         <is>
-          <t>size=micro, drawdown_12m=deep(&lt;-50%),</t>
+          <t>size=small, drawdown_12m=deep(&lt;-50%),</t>
         </is>
       </c>
     </row>
     <row r="60" ht="22" customHeight="1">
       <c r="A60" s="9" t="inlineStr">
         <is>
-          <t>ACH</t>
+          <t>FOXF</t>
         </is>
       </c>
       <c r="B60" s="10" t="inlineStr">
         <is>
-          <t>Accendra Health, Inc</t>
+          <t>Fox Factory Holding</t>
         </is>
       </c>
       <c r="C60" s="17" t="n">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="D60" s="10" t="inlineStr">
         <is>
-          <t>–</t>
+          <t>NEUTRAL</t>
         </is>
       </c>
       <c r="E60" s="17" t="n">
-        <v>60</v>
+        <v>1.1</v>
       </c>
       <c r="F60" s="10" t="inlineStr">
         <is>
-          <t>size=micro, drawdown_12m=deep(&lt;-50%),</t>
+          <t>sector=Consumer Cyclical, size=small,</t>
         </is>
       </c>
     </row>
     <row r="61" ht="22" customHeight="1">
       <c r="A61" s="6" t="inlineStr">
         <is>
-          <t>MDIA</t>
+          <t>ARHS</t>
         </is>
       </c>
       <c r="B61" s="7" t="inlineStr">
         <is>
-          <t>Mediaco Holding Inc.</t>
+          <t>Arhaus, Inc.</t>
         </is>
       </c>
       <c r="C61" s="16" t="n">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="D61" s="7" t="inlineStr">
         <is>
-          <t>–</t>
+          <t>NEUTRAL</t>
         </is>
       </c>
       <c r="E61" s="16" t="n">
-        <v>1.2</v>
+        <v>0.3</v>
       </c>
       <c r="F61" s="7" t="inlineStr">
         <is>
-          <t>size=micro, drawdown_12m=deep(&lt;-50%),</t>
-        </is>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" s="12" t="inlineStr">
+          <t>sector=Consumer Cyclical, size=small,</t>
+        </is>
+      </c>
+    </row>
+    <row r="62" ht="22" customHeight="1">
+      <c r="A62" s="9" t="inlineStr">
+        <is>
+          <t>TTEC</t>
+        </is>
+      </c>
+      <c r="B62" s="10" t="inlineStr">
+        <is>
+          <t>TTEC Holdings, Inc.</t>
+        </is>
+      </c>
+      <c r="C62" s="17" t="n">
+        <v>29</v>
+      </c>
+      <c r="D62" s="10" t="inlineStr">
+        <is>
+          <t>NEUTRAL</t>
+        </is>
+      </c>
+      <c r="E62" s="17" t="n">
+        <v>20.3</v>
+      </c>
+      <c r="F62" s="10" t="inlineStr">
+        <is>
+          <t>sector=Technology, size=micro, drawdow</t>
+        </is>
+      </c>
+    </row>
+    <row r="63" ht="22" customHeight="1">
+      <c r="A63" s="6" t="inlineStr">
+        <is>
+          <t>ETD</t>
+        </is>
+      </c>
+      <c r="B63" s="7" t="inlineStr">
+        <is>
+          <t>Ethan Allen Interior</t>
+        </is>
+      </c>
+      <c r="C63" s="16" t="n">
+        <v>29</v>
+      </c>
+      <c r="D63" s="7" t="inlineStr">
+        <is>
+          <t>NEUTRAL</t>
+        </is>
+      </c>
+      <c r="E63" s="16" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="F63" s="7" t="inlineStr">
+        <is>
+          <t>sector=Consumer Cyclical, size=small,</t>
+        </is>
+      </c>
+    </row>
+    <row r="64" ht="22" customHeight="1">
+      <c r="A64" s="9" t="inlineStr">
+        <is>
+          <t>GRNT</t>
+        </is>
+      </c>
+      <c r="B64" s="10" t="inlineStr">
+        <is>
+          <t>Granite Ridge Resour</t>
+        </is>
+      </c>
+      <c r="C64" s="17" t="n">
+        <v>29</v>
+      </c>
+      <c r="D64" s="10" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="E64" s="17" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="F64" s="10" t="inlineStr">
+        <is>
+          <t>sector=Energy, size=small, drawdown_12</t>
+        </is>
+      </c>
+    </row>
+    <row r="65" ht="22" customHeight="1">
+      <c r="A65" s="6" t="inlineStr">
+        <is>
+          <t>AGPU</t>
+        </is>
+      </c>
+      <c r="B65" s="7" t="inlineStr">
+        <is>
+          <t>Axe Compute Inc.</t>
+        </is>
+      </c>
+      <c r="C65" s="16" t="n">
+        <v>29</v>
+      </c>
+      <c r="D65" s="7" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="E65" s="16" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="F65" s="7" t="inlineStr">
+        <is>
+          <t>sector=Technology, size=micro, drawdow</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="12" t="inlineStr">
         <is>
           <t>WHAT RAISES TAIL ODDS (historical lift vs 15% base)</t>
         </is>
       </c>
     </row>
-    <row r="64" ht="18" customHeight="1">
-      <c r="A64" s="4" t="inlineStr">
+    <row r="68" ht="18" customHeight="1">
+      <c r="A68" s="4" t="inlineStr">
         <is>
           <t>Feature = bin</t>
         </is>
       </c>
-      <c r="B64" s="4" t="inlineStr">
+      <c r="B68" s="4" t="inlineStr">
         <is>
           <t>Tail rate</t>
         </is>
       </c>
-      <c r="C64" s="4" t="inlineStr">
+      <c r="C68" s="4" t="inlineStr">
         <is>
           <t>Lift</t>
         </is>
       </c>
-      <c r="D64" s="4" t="inlineStr">
+      <c r="D68" s="4" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="E64" s="15" t="inlineStr"/>
-    </row>
-    <row r="65" ht="16" customHeight="1">
-      <c r="A65" s="6" t="inlineStr">
-        <is>
-          <t>size = small</t>
-        </is>
-      </c>
-      <c r="B65" s="16" t="n">
-        <v>38</v>
-      </c>
-      <c r="C65" s="7" t="inlineStr">
-        <is>
-          <t>2.49x</t>
-        </is>
-      </c>
-      <c r="D65" s="5" t="n">
-        <v>8</v>
-      </c>
-      <c r="E65" s="7" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-    </row>
-    <row r="66" ht="16" customHeight="1">
-      <c r="A66" s="9" t="inlineStr">
-        <is>
-          <t>drawdown_12m = deep(&lt;-50%)</t>
-        </is>
-      </c>
-      <c r="B66" s="17" t="n">
-        <v>32</v>
-      </c>
-      <c r="C66" s="10" t="inlineStr">
-        <is>
-          <t>2.11x</t>
-        </is>
-      </c>
-      <c r="D66" s="8" t="n">
-        <v>22</v>
-      </c>
-      <c r="E66" s="10" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-    </row>
-    <row r="67" ht="16" customHeight="1">
-      <c r="A67" s="6" t="inlineStr">
-        <is>
-          <t>sector = Real Estate</t>
-        </is>
-      </c>
-      <c r="B67" s="16" t="n">
-        <v>33</v>
-      </c>
-      <c r="C67" s="7" t="inlineStr">
-        <is>
-          <t>2.22x</t>
-        </is>
-      </c>
-      <c r="D67" s="5" t="n">
-        <v>3</v>
-      </c>
-      <c r="E67" s="7" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-    </row>
-    <row r="68" ht="16" customHeight="1">
-      <c r="A68" s="9" t="inlineStr">
-        <is>
-          <t>sector = Technology</t>
-        </is>
-      </c>
-      <c r="B68" s="17" t="n">
-        <v>30</v>
-      </c>
-      <c r="C68" s="10" t="inlineStr">
-        <is>
-          <t>1.99x</t>
-        </is>
-      </c>
-      <c r="D68" s="8" t="n">
-        <v>10</v>
-      </c>
-      <c r="E68" s="10" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
+      <c r="E68" s="15" t="inlineStr"/>
     </row>
     <row r="69" ht="16" customHeight="1">
       <c r="A69" s="6" t="inlineStr">
         <is>
-          <t>catalyst = SALE_OF_COMPANY</t>
+          <t>size = small</t>
         </is>
       </c>
       <c r="B69" s="16" t="n">
-        <v>25</v>
+        <v>38</v>
       </c>
       <c r="C69" s="7" t="inlineStr">
         <is>
-          <t>1.66x</t>
+          <t>2.49x</t>
         </is>
       </c>
       <c r="D69" s="5" t="n">
@@ -10125,19 +10183,19 @@
     <row r="70" ht="16" customHeight="1">
       <c r="A70" s="9" t="inlineStr">
         <is>
-          <t>range_pos = low</t>
+          <t>drawdown_12m = deep(&lt;-50%)</t>
         </is>
       </c>
       <c r="B70" s="17" t="n">
-        <v>21</v>
+        <v>32</v>
       </c>
       <c r="C70" s="10" t="inlineStr">
         <is>
-          <t>1.39x</t>
+          <t>2.11x</t>
         </is>
       </c>
       <c r="D70" s="8" t="n">
-        <v>43</v>
+        <v>22</v>
       </c>
       <c r="E70" s="10" t="inlineStr">
         <is>
@@ -10148,19 +10206,19 @@
     <row r="71" ht="16" customHeight="1">
       <c r="A71" s="6" t="inlineStr">
         <is>
-          <t>catalyst = SPINOFF</t>
+          <t>sector = Real Estate</t>
         </is>
       </c>
       <c r="B71" s="16" t="n">
-        <v>18</v>
+        <v>33</v>
       </c>
       <c r="C71" s="7" t="inlineStr">
         <is>
-          <t>1.16x</t>
+          <t>2.22x</t>
         </is>
       </c>
       <c r="D71" s="5" t="n">
-        <v>40</v>
+        <v>3</v>
       </c>
       <c r="E71" s="7" t="inlineStr">
         <is>
@@ -10171,19 +10229,19 @@
     <row r="72" ht="16" customHeight="1">
       <c r="A72" s="9" t="inlineStr">
         <is>
-          <t>pre_12m = down(&lt;-20%)  (needs a wait)</t>
+          <t>sector = Technology</t>
         </is>
       </c>
       <c r="B72" s="17" t="n">
-        <v>22</v>
+        <v>30</v>
       </c>
       <c r="C72" s="10" t="inlineStr">
         <is>
-          <t>1.50x</t>
+          <t>1.99x</t>
         </is>
       </c>
       <c r="D72" s="8" t="n">
-        <v>40</v>
+        <v>10</v>
       </c>
       <c r="E72" s="10" t="inlineStr">
         <is>
@@ -10194,28 +10252,120 @@
     <row r="73" ht="16" customHeight="1">
       <c r="A73" s="6" t="inlineStr">
         <is>
+          <t>catalyst = SALE_OF_COMPANY</t>
+        </is>
+      </c>
+      <c r="B73" s="16" t="n">
+        <v>25</v>
+      </c>
+      <c r="C73" s="7" t="inlineStr">
+        <is>
+          <t>1.66x</t>
+        </is>
+      </c>
+      <c r="D73" s="5" t="n">
+        <v>8</v>
+      </c>
+      <c r="E73" s="7" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+    </row>
+    <row r="74" ht="16" customHeight="1">
+      <c r="A74" s="9" t="inlineStr">
+        <is>
+          <t>range_pos = low</t>
+        </is>
+      </c>
+      <c r="B74" s="17" t="n">
+        <v>21</v>
+      </c>
+      <c r="C74" s="10" t="inlineStr">
+        <is>
+          <t>1.39x</t>
+        </is>
+      </c>
+      <c r="D74" s="8" t="n">
+        <v>43</v>
+      </c>
+      <c r="E74" s="10" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+    </row>
+    <row r="75" ht="16" customHeight="1">
+      <c r="A75" s="6" t="inlineStr">
+        <is>
+          <t>catalyst = SPINOFF</t>
+        </is>
+      </c>
+      <c r="B75" s="16" t="n">
+        <v>18</v>
+      </c>
+      <c r="C75" s="7" t="inlineStr">
+        <is>
+          <t>1.16x</t>
+        </is>
+      </c>
+      <c r="D75" s="5" t="n">
+        <v>40</v>
+      </c>
+      <c r="E75" s="7" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+    </row>
+    <row r="76" ht="16" customHeight="1">
+      <c r="A76" s="9" t="inlineStr">
+        <is>
+          <t>pre_12m = down(&lt;-20%)  (needs a wait)</t>
+        </is>
+      </c>
+      <c r="B76" s="17" t="n">
+        <v>22</v>
+      </c>
+      <c r="C76" s="10" t="inlineStr">
+        <is>
+          <t>1.50x</t>
+        </is>
+      </c>
+      <c r="D76" s="8" t="n">
+        <v>40</v>
+      </c>
+      <c r="E76" s="10" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+    </row>
+    <row r="77" ht="16" customHeight="1">
+      <c r="A77" s="6" t="inlineStr">
+        <is>
           <t>post_1m = up(&gt;+20%)  (needs a wait)</t>
         </is>
       </c>
-      <c r="B73" s="16" t="n">
+      <c r="B77" s="16" t="n">
         <v>60</v>
       </c>
-      <c r="C73" s="7" t="inlineStr">
+      <c r="C77" s="7" t="inlineStr">
         <is>
           <t>3.99x</t>
         </is>
       </c>
-      <c r="D73" s="5" t="n">
+      <c r="D77" s="5" t="n">
         <v>5</v>
       </c>
-      <c r="E73" s="7" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-    </row>
-    <row r="75" ht="28" customHeight="1">
-      <c r="A75" s="11" t="inlineStr">
+      <c r="E77" s="7" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+    </row>
+    <row r="79" ht="28" customHeight="1">
+      <c r="A79" s="11" t="inlineStr">
         <is>
           <t>HOW TO RAISE THE ODDS, from the event study. The right tail is not random: it concentrates in (1) DEEPLY BEATEN-DOWN names — &gt;50% below their 12-month high tailed 32% of the time vs 4% for names near their highs (2.1x); (2) SMALL-CAPS ($300M-2B), 38% tail rate (2.5x) — the high-variance sweet spot; (3) the right SECTORS — Real Estate, Technology, Consumer-Cyclical, Energy — while Financials, Utilities and Staples produced ZERO tails; (4) SALE-OF-COMPANY and SPIN-OFF catalysts over asset sales. Stacking these lifts the tail probability to ~40% (≈2.7x base). THE SINGLE STRONGEST EDGE is not a screen but a RULE: wait ~1 month and enter only names the market voted UP &gt;20% on the catalyst — those tailed 60% of the time (4.0x). Buying the catalyst blind is a coin-flip that loses to SPY on the median; buying beaten-down small-caps in the right sectors AFTER the market confirms is how you tilt into the tail. Modest sample (113 events); directional. Sources: rerate_backtest.py / tail_discriminators.py / tail_odds.py.</t>
         </is>
@@ -10225,7 +10375,7 @@
   <mergeCells count="3">
     <mergeCell ref="A2:F2"/>
     <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A75:F75"/>
+    <mergeCell ref="A79:F79"/>
   </mergeCells>
   <printOptions horizontalCentered="0"/>
   <pageMargins left="0.5" right="0.5" top="0.6" bottom="0.6" header="0.5" footer="0.5"/>

--- a/MOST_ASYMMETRIC.xlsx
+++ b/MOST_ASYMMETRIC.xlsx
@@ -6266,33 +6266,29 @@
     <row r="5" ht="22" customHeight="1">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>WBD</t>
+          <t>DXLG</t>
         </is>
       </c>
       <c r="B5" s="7" t="inlineStr">
         <is>
-          <t>Warner Bros. Discovery</t>
+          <t>Destination XL Group,</t>
         </is>
       </c>
       <c r="C5" s="16" t="n">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="D5" s="16" t="n">
-        <v>4</v>
-      </c>
-      <c r="E5" s="7" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="F5" s="7" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+        <v>2</v>
+      </c>
+      <c r="E5" s="16" t="n">
+        <v>60</v>
+      </c>
+      <c r="F5" s="19" t="n">
+        <v>300</v>
       </c>
       <c r="G5" s="7" t="inlineStr">
         <is>
-          <t>Exchange Offer [event]; Sale Of Company [ten</t>
+          <t>Sale Of Company [event/tender]; Tender Offer</t>
         </is>
       </c>
     </row>
@@ -6308,7 +6304,7 @@
         </is>
       </c>
       <c r="C6" s="17" t="n">
-        <v>41.9</v>
+        <v>35.7</v>
       </c>
       <c r="D6" s="17" t="n">
         <v>4</v>
@@ -6337,7 +6333,7 @@
         </is>
       </c>
       <c r="C7" s="16" t="n">
-        <v>38.7</v>
+        <v>34.5</v>
       </c>
       <c r="D7" s="16" t="n">
         <v>3</v>
@@ -6357,176 +6353,168 @@
     <row r="8" ht="22" customHeight="1">
       <c r="A8" s="9" t="inlineStr">
         <is>
-          <t>DXLG</t>
+          <t>WBD</t>
         </is>
       </c>
       <c r="B8" s="10" t="inlineStr">
         <is>
-          <t>Destination XL Group,</t>
+          <t>Warner Bros. Discovery</t>
         </is>
       </c>
       <c r="C8" s="17" t="n">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="D8" s="17" t="n">
-        <v>2</v>
-      </c>
-      <c r="E8" s="17" t="n">
-        <v>60</v>
-      </c>
-      <c r="F8" s="20" t="n">
-        <v>300</v>
+        <v>4</v>
+      </c>
+      <c r="E8" s="10" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="F8" s="10" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
       <c r="G8" s="10" t="inlineStr">
         <is>
-          <t>Sale Of Company [event/tender]; Tender Offer</t>
+          <t>Exchange Offer [event]; Sale Of Company [ten</t>
         </is>
       </c>
     </row>
     <row r="9" ht="22" customHeight="1">
       <c r="A9" s="6" t="inlineStr">
         <is>
-          <t>BHC</t>
+          <t>CYH</t>
         </is>
       </c>
       <c r="B9" s="7" t="inlineStr">
         <is>
-          <t>BHC</t>
+          <t>Community Health Syste</t>
         </is>
       </c>
       <c r="C9" s="16" t="n">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="D9" s="16" t="n">
+        <v>2</v>
+      </c>
+      <c r="E9" s="16" t="n">
         <v>3</v>
       </c>
-      <c r="E9" s="7" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="F9" s="7" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+      <c r="F9" s="19" t="n">
+        <v>300</v>
       </c>
       <c r="G9" s="7" t="inlineStr">
         <is>
-          <t>Exchange Offer [event]; Separation [event/na</t>
+          <t>Asset Sale [event]; Tender Offer [event]</t>
         </is>
       </c>
     </row>
     <row r="10" ht="22" customHeight="1">
       <c r="A10" s="9" t="inlineStr">
         <is>
-          <t>SUNE</t>
+          <t>GTE</t>
         </is>
       </c>
       <c r="B10" s="10" t="inlineStr">
         <is>
-          <t>SUNation Energy, Inc.</t>
+          <t>Gran Tierra Energy Inc</t>
         </is>
       </c>
       <c r="C10" s="17" t="n">
-        <v>34.5</v>
+        <v>33</v>
       </c>
       <c r="D10" s="17" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E10" s="17" t="n">
-        <v>60</v>
+        <v>3.8</v>
       </c>
       <c r="F10" s="20" t="n">
         <v>300</v>
       </c>
       <c r="G10" s="10" t="inlineStr">
         <is>
-          <t>Sale Of Company [event]; Strategic Review [e</t>
+          <t>Asset Sale [event]; Tender Offer [event]</t>
         </is>
       </c>
     </row>
     <row r="11" ht="22" customHeight="1">
       <c r="A11" s="6" t="inlineStr">
         <is>
-          <t>ETN</t>
+          <t>UGI</t>
         </is>
       </c>
       <c r="B11" s="7" t="inlineStr">
         <is>
-          <t>Eaton Corporation, PLC</t>
+          <t>UGI Corporation</t>
         </is>
       </c>
       <c r="C11" s="16" t="n">
-        <v>34</v>
+        <v>32.5</v>
       </c>
       <c r="D11" s="16" t="n">
         <v>2</v>
       </c>
-      <c r="E11" s="7" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="F11" s="7" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+      <c r="E11" s="16" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="F11" s="19" t="n">
+        <v>122</v>
       </c>
       <c r="G11" s="7" t="inlineStr">
         <is>
-          <t>Separation [event/narrative]; Spinoff [event</t>
+          <t>Asset Sale [event/narrative]; Tender Offer [</t>
         </is>
       </c>
     </row>
     <row r="12" ht="22" customHeight="1">
       <c r="A12" s="9" t="inlineStr">
         <is>
-          <t>SPGI</t>
+          <t>SITC</t>
         </is>
       </c>
       <c r="B12" s="10" t="inlineStr">
         <is>
-          <t>S&amp;P Global Inc.</t>
+          <t>SITE Centers Corp.</t>
         </is>
       </c>
       <c r="C12" s="17" t="n">
-        <v>31</v>
+        <v>32.3</v>
       </c>
       <c r="D12" s="17" t="n">
-        <v>3</v>
-      </c>
-      <c r="E12" s="10" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="F12" s="10" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+        <v>2</v>
+      </c>
+      <c r="E12" s="17" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="F12" s="20" t="n">
+        <v>91</v>
       </c>
       <c r="G12" s="10" t="inlineStr">
         <is>
-          <t>Asset Sale [event]; Separation [event]; Spin</t>
+          <t>Asset Sale [event/narrative]; Spinoff [event</t>
         </is>
       </c>
     </row>
     <row r="13" ht="22" customHeight="1">
       <c r="A13" s="6" t="inlineStr">
         <is>
-          <t>HCTI</t>
+          <t>ETN</t>
         </is>
       </c>
       <c r="B13" s="7" t="inlineStr">
         <is>
-          <t>HCTI</t>
+          <t>Eaton Corporation, PLC</t>
         </is>
       </c>
       <c r="C13" s="16" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D13" s="16" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E13" s="7" t="inlineStr">
         <is>
@@ -6540,81 +6528,81 @@
       </c>
       <c r="G13" s="7" t="inlineStr">
         <is>
-          <t>Separation [event]; Spinoff [event]; Uplisti</t>
+          <t>Separation [event/narrative]; Spinoff [event</t>
         </is>
       </c>
     </row>
     <row r="14" ht="22" customHeight="1">
       <c r="A14" s="9" t="inlineStr">
         <is>
-          <t>GPC</t>
+          <t>FIS</t>
         </is>
       </c>
       <c r="B14" s="10" t="inlineStr">
         <is>
-          <t>Genuine Parts Company</t>
+          <t>Fidelity National Info</t>
         </is>
       </c>
       <c r="C14" s="17" t="n">
-        <v>30.8</v>
+        <v>29.3</v>
       </c>
       <c r="D14" s="17" t="n">
         <v>2</v>
       </c>
       <c r="E14" s="17" t="n">
-        <v>0.4</v>
+        <v>2.8</v>
       </c>
       <c r="F14" s="20" t="n">
-        <v>36</v>
+        <v>164</v>
       </c>
       <c r="G14" s="10" t="inlineStr">
         <is>
-          <t>Separation [event/narrative]; Spinoff [event</t>
+          <t>Asset Sale [event]; Spinoff [event]</t>
         </is>
       </c>
     </row>
     <row r="15" ht="22" customHeight="1">
       <c r="A15" s="6" t="inlineStr">
         <is>
-          <t>SITC</t>
+          <t>LE</t>
         </is>
       </c>
       <c r="B15" s="7" t="inlineStr">
         <is>
-          <t>SITE Centers Corp.</t>
+          <t>Lands' End, Inc.</t>
         </is>
       </c>
       <c r="C15" s="16" t="n">
-        <v>30</v>
+        <v>28.5</v>
       </c>
       <c r="D15" s="16" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E15" s="16" t="n">
-        <v>2.8</v>
+        <v>5.1</v>
       </c>
       <c r="F15" s="19" t="n">
-        <v>91</v>
+        <v>176</v>
       </c>
       <c r="G15" s="7" t="inlineStr">
         <is>
-          <t>Asset Sale [event/narrative]; Spinoff [event</t>
+          <t>Sale Of Company [tender]; Strategic Review [</t>
         </is>
       </c>
     </row>
     <row r="16" ht="22" customHeight="1">
       <c r="A16" s="9" t="inlineStr">
         <is>
-          <t>ADPT</t>
+          <t>SPGI</t>
         </is>
       </c>
       <c r="B16" s="10" t="inlineStr">
         <is>
-          <t>Adaptive Biotechnologi</t>
+          <t>S&amp;P Global Inc.</t>
         </is>
       </c>
       <c r="C16" s="17" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D16" s="17" t="n">
         <v>3</v>
@@ -6631,26 +6619,26 @@
       </c>
       <c r="G16" s="10" t="inlineStr">
         <is>
-          <t>Separation [event]; Spinoff [event]; Strateg</t>
+          <t>Asset Sale [event]; Separation [event]; Spin</t>
         </is>
       </c>
     </row>
     <row r="17" ht="22" customHeight="1">
       <c r="A17" s="6" t="inlineStr">
         <is>
-          <t>CTVA</t>
+          <t>LSTA</t>
         </is>
       </c>
       <c r="B17" s="7" t="inlineStr">
         <is>
-          <t>Corteva, Inc.</t>
+          <t>Lisata Therapeutics, I</t>
         </is>
       </c>
       <c r="C17" s="16" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="D17" s="16" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E17" s="7" t="inlineStr">
         <is>
@@ -6664,185 +6652,189 @@
       </c>
       <c r="G17" s="7" t="inlineStr">
         <is>
-          <t>Separation [event]; Spinoff [event/narrative</t>
+          <t>Sale Of Company [event/tender]; Strategic Re</t>
         </is>
       </c>
     </row>
     <row r="18" ht="22" customHeight="1">
       <c r="A18" s="9" t="inlineStr">
         <is>
-          <t>HON</t>
+          <t>SUNE</t>
         </is>
       </c>
       <c r="B18" s="10" t="inlineStr">
         <is>
-          <t>Honeywell Internationa</t>
+          <t>SUNation Energy, Inc.</t>
         </is>
       </c>
       <c r="C18" s="17" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="D18" s="17" t="n">
-        <v>2</v>
-      </c>
-      <c r="E18" s="10" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="F18" s="10" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+        <v>3</v>
+      </c>
+      <c r="E18" s="17" t="n">
+        <v>60</v>
+      </c>
+      <c r="F18" s="20" t="n">
+        <v>300</v>
       </c>
       <c r="G18" s="10" t="inlineStr">
         <is>
-          <t>Separation [event/narrative]; Spinoff [event</t>
+          <t>Sale Of Company [event]; Strategic Review [e</t>
         </is>
       </c>
     </row>
     <row r="19" ht="22" customHeight="1">
       <c r="A19" s="6" t="inlineStr">
         <is>
-          <t>UGI</t>
+          <t>KOS</t>
         </is>
       </c>
       <c r="B19" s="7" t="inlineStr">
         <is>
-          <t>UGI Corporation</t>
+          <t>Kosmos Energy Ltd.</t>
         </is>
       </c>
       <c r="C19" s="16" t="n">
-        <v>28.9</v>
+        <v>26.7</v>
       </c>
       <c r="D19" s="16" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E19" s="16" t="n">
-        <v>2.1</v>
+        <v>0.8</v>
       </c>
       <c r="F19" s="19" t="n">
-        <v>122</v>
+        <v>66</v>
       </c>
       <c r="G19" s="7" t="inlineStr">
         <is>
-          <t>Asset Sale [event/narrative]; Tender Offer [</t>
+          <t>Asset Sale [event]; Tender Offer [event]; Up</t>
         </is>
       </c>
     </row>
     <row r="20" ht="22" customHeight="1">
       <c r="A20" s="9" t="inlineStr">
         <is>
-          <t>KOS</t>
+          <t>GPC</t>
         </is>
       </c>
       <c r="B20" s="10" t="inlineStr">
         <is>
-          <t>Kosmos Energy Ltd.</t>
+          <t>Genuine Parts Company</t>
         </is>
       </c>
       <c r="C20" s="17" t="n">
-        <v>28.9</v>
+        <v>26.5</v>
       </c>
       <c r="D20" s="17" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E20" s="17" t="n">
-        <v>0.8</v>
+        <v>0.4</v>
       </c>
       <c r="F20" s="20" t="n">
-        <v>66</v>
+        <v>36</v>
       </c>
       <c r="G20" s="10" t="inlineStr">
         <is>
-          <t>Asset Sale [event]; Tender Offer [event]; Up</t>
+          <t>Separation [event/narrative]; Spinoff [event</t>
         </is>
       </c>
     </row>
     <row r="21" ht="22" customHeight="1">
       <c r="A21" s="6" t="inlineStr">
         <is>
-          <t>CYH</t>
+          <t>ASRT</t>
         </is>
       </c>
       <c r="B21" s="7" t="inlineStr">
         <is>
-          <t>Community Health Syste</t>
+          <t>Assertio Holdings, Inc</t>
         </is>
       </c>
       <c r="C21" s="16" t="n">
-        <v>28.5</v>
+        <v>26.1</v>
       </c>
       <c r="D21" s="16" t="n">
         <v>2</v>
       </c>
       <c r="E21" s="16" t="n">
-        <v>3</v>
+        <v>0.7</v>
       </c>
       <c r="F21" s="19" t="n">
-        <v>300</v>
+        <v>52</v>
       </c>
       <c r="G21" s="7" t="inlineStr">
         <is>
-          <t>Asset Sale [event]; Tender Offer [event]</t>
+          <t>Sale Of Company [event/tender]; Tender Offer</t>
         </is>
       </c>
     </row>
     <row r="22" ht="22" customHeight="1">
       <c r="A22" s="9" t="inlineStr">
         <is>
-          <t>GTE</t>
+          <t>BHC</t>
         </is>
       </c>
       <c r="B22" s="10" t="inlineStr">
         <is>
-          <t>Gran Tierra Energy Inc</t>
+          <t>BHC</t>
         </is>
       </c>
       <c r="C22" s="17" t="n">
-        <v>28.5</v>
+        <v>26</v>
       </c>
       <c r="D22" s="17" t="n">
-        <v>2</v>
-      </c>
-      <c r="E22" s="17" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="F22" s="20" t="n">
-        <v>300</v>
+        <v>3</v>
+      </c>
+      <c r="E22" s="10" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="F22" s="10" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
       <c r="G22" s="10" t="inlineStr">
         <is>
-          <t>Asset Sale [event]; Tender Offer [event]</t>
+          <t>Exchange Offer [event]; Separation [event/na</t>
         </is>
       </c>
     </row>
     <row r="23" ht="22" customHeight="1">
       <c r="A23" s="6" t="inlineStr">
         <is>
-          <t>LE</t>
+          <t>NFE</t>
         </is>
       </c>
       <c r="B23" s="7" t="inlineStr">
         <is>
-          <t>Lands' End, Inc.</t>
+          <t>NFE</t>
         </is>
       </c>
       <c r="C23" s="16" t="n">
-        <v>28.5</v>
+        <v>26</v>
       </c>
       <c r="D23" s="16" t="n">
-        <v>3</v>
-      </c>
-      <c r="E23" s="16" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="F23" s="19" t="n">
-        <v>176</v>
+        <v>2</v>
+      </c>
+      <c r="E23" s="7" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="F23" s="7" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
       <c r="G23" s="7" t="inlineStr">
         <is>
-          <t>Sale Of Company [tender]; Strategic Review [</t>
+          <t>Asset Sale [event]; Separation [event/narrat</t>
         </is>
       </c>
     </row>
@@ -6858,7 +6850,7 @@
         </is>
       </c>
       <c r="C24" s="17" t="n">
-        <v>28.2</v>
+        <v>25.8</v>
       </c>
       <c r="D24" s="17" t="n">
         <v>2</v>
@@ -6878,259 +6870,263 @@
     <row r="25" ht="22" customHeight="1">
       <c r="A25" s="6" t="inlineStr">
         <is>
-          <t>PSKY</t>
+          <t>HAIN</t>
         </is>
       </c>
       <c r="B25" s="7" t="inlineStr">
         <is>
-          <t>PSKY</t>
+          <t>The Hain Celestial Gro</t>
         </is>
       </c>
       <c r="C25" s="16" t="n">
-        <v>28</v>
+        <v>25.5</v>
       </c>
       <c r="D25" s="16" t="n">
-        <v>3</v>
-      </c>
-      <c r="E25" s="7" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="F25" s="7" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+        <v>2</v>
+      </c>
+      <c r="E25" s="16" t="n">
+        <v>60</v>
+      </c>
+      <c r="F25" s="19" t="n">
+        <v>300</v>
       </c>
       <c r="G25" s="7" t="inlineStr">
         <is>
-          <t>Exchange Offer [event]; Spinoff [event]; Ten</t>
+          <t>Asset Sale [event]; Strategic Review [narrat</t>
         </is>
       </c>
     </row>
     <row r="26" ht="22" customHeight="1">
       <c r="A26" s="9" t="inlineStr">
         <is>
-          <t>SOLV</t>
+          <t>CMTL</t>
         </is>
       </c>
       <c r="B26" s="10" t="inlineStr">
         <is>
-          <t>Solventum Corporation</t>
+          <t>Comtech Telecommunicat</t>
         </is>
       </c>
       <c r="C26" s="17" t="n">
-        <v>27.1</v>
+        <v>25.5</v>
       </c>
       <c r="D26" s="17" t="n">
         <v>2</v>
       </c>
       <c r="E26" s="17" t="n">
-        <v>1</v>
+        <v>11.5</v>
       </c>
       <c r="F26" s="20" t="n">
-        <v>78</v>
+        <v>300</v>
       </c>
       <c r="G26" s="10" t="inlineStr">
         <is>
-          <t>Separation [event]; Strategic Review [event/</t>
+          <t>Asset Sale [event]; Strategic Review [narrat</t>
         </is>
       </c>
     </row>
     <row r="27" ht="22" customHeight="1">
       <c r="A27" s="6" t="inlineStr">
         <is>
-          <t>LSTA</t>
+          <t>OPTU</t>
         </is>
       </c>
       <c r="B27" s="7" t="inlineStr">
         <is>
-          <t>Lisata Therapeutics, I</t>
+          <t>Optimum Communications</t>
         </is>
       </c>
       <c r="C27" s="16" t="n">
-        <v>27</v>
+        <v>25.5</v>
       </c>
       <c r="D27" s="16" t="n">
+        <v>2</v>
+      </c>
+      <c r="E27" s="16" t="n">
         <v>3</v>
       </c>
-      <c r="E27" s="7" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="F27" s="7" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+      <c r="F27" s="19" t="n">
+        <v>300</v>
       </c>
       <c r="G27" s="7" t="inlineStr">
         <is>
-          <t>Sale Of Company [event/tender]; Strategic Re</t>
+          <t>Sale Of Company [narrative]; Tender Offer [e</t>
         </is>
       </c>
     </row>
     <row r="28" ht="22" customHeight="1">
       <c r="A28" s="9" t="inlineStr">
         <is>
-          <t>FDX</t>
+          <t>HON</t>
         </is>
       </c>
       <c r="B28" s="10" t="inlineStr">
         <is>
-          <t>FedEx Corporation</t>
+          <t>Honeywell Internationa</t>
         </is>
       </c>
       <c r="C28" s="17" t="n">
-        <v>26.9</v>
+        <v>25</v>
       </c>
       <c r="D28" s="17" t="n">
         <v>2</v>
       </c>
-      <c r="E28" s="17" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="F28" s="20" t="n">
-        <v>74</v>
+      <c r="E28" s="10" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="F28" s="10" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
       <c r="G28" s="10" t="inlineStr">
         <is>
-          <t>Separation [event]; Spinoff [event]</t>
+          <t>Separation [event/narrative]; Spinoff [event</t>
         </is>
       </c>
     </row>
     <row r="29" ht="22" customHeight="1">
       <c r="A29" s="6" t="inlineStr">
         <is>
-          <t>FIS</t>
+          <t>ADPT</t>
         </is>
       </c>
       <c r="B29" s="7" t="inlineStr">
         <is>
-          <t>Fidelity National Info</t>
+          <t>Adaptive Biotechnologi</t>
         </is>
       </c>
       <c r="C29" s="16" t="n">
-        <v>26.8</v>
+        <v>23</v>
       </c>
       <c r="D29" s="16" t="n">
-        <v>2</v>
-      </c>
-      <c r="E29" s="16" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="F29" s="19" t="n">
-        <v>164</v>
+        <v>3</v>
+      </c>
+      <c r="E29" s="7" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="F29" s="7" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
       <c r="G29" s="7" t="inlineStr">
         <is>
-          <t>Asset Sale [event]; Spinoff [event]</t>
+          <t>Separation [event]; Spinoff [event]; Strateg</t>
         </is>
       </c>
     </row>
     <row r="30" ht="22" customHeight="1">
       <c r="A30" s="9" t="inlineStr">
         <is>
-          <t>OLN</t>
+          <t>CTVA</t>
         </is>
       </c>
       <c r="B30" s="10" t="inlineStr">
         <is>
-          <t>Olin Corporation</t>
+          <t>Corteva, Inc.</t>
         </is>
       </c>
       <c r="C30" s="17" t="n">
-        <v>26.8</v>
+        <v>23</v>
       </c>
       <c r="D30" s="17" t="n">
         <v>2</v>
       </c>
-      <c r="E30" s="17" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="F30" s="20" t="n">
-        <v>205</v>
+      <c r="E30" s="10" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="F30" s="10" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
       <c r="G30" s="10" t="inlineStr">
         <is>
-          <t>Going Private [event]; Uplisting [event]</t>
+          <t>Separation [event]; Spinoff [event/narrative</t>
         </is>
       </c>
     </row>
     <row r="31" ht="22" customHeight="1">
       <c r="A31" s="6" t="inlineStr">
         <is>
-          <t>HUN</t>
+          <t>CNDT</t>
         </is>
       </c>
       <c r="B31" s="7" t="inlineStr">
         <is>
-          <t>Huntsman Corporation</t>
+          <t>Conduent Incorporated</t>
         </is>
       </c>
       <c r="C31" s="16" t="n">
-        <v>26.2</v>
+        <v>22.5</v>
       </c>
       <c r="D31" s="16" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E31" s="16" t="n">
-        <v>7.6</v>
+        <v>60</v>
       </c>
       <c r="F31" s="19" t="n">
-        <v>273</v>
+        <v>300</v>
       </c>
       <c r="G31" s="7" t="inlineStr">
         <is>
-          <t>Separation [narrative]; Uplisting [event]</t>
+          <t>Asset Sale [event/narrative]</t>
         </is>
       </c>
     </row>
     <row r="32" ht="22" customHeight="1">
       <c r="A32" s="9" t="inlineStr">
         <is>
-          <t>ASRT</t>
+          <t>APTV</t>
         </is>
       </c>
       <c r="B32" s="10" t="inlineStr">
         <is>
-          <t>Assertio Holdings, Inc</t>
+          <t>Aptiv PLC</t>
         </is>
       </c>
       <c r="C32" s="17" t="n">
-        <v>26.1</v>
+        <v>22.2</v>
       </c>
       <c r="D32" s="17" t="n">
         <v>2</v>
       </c>
       <c r="E32" s="17" t="n">
-        <v>0.7</v>
+        <v>0.5</v>
       </c>
       <c r="F32" s="20" t="n">
-        <v>52</v>
+        <v>34</v>
       </c>
       <c r="G32" s="10" t="inlineStr">
         <is>
-          <t>Sale Of Company [event/tender]; Tender Offer</t>
+          <t>Spinoff [event]; Tender Offer [event]</t>
         </is>
       </c>
     </row>
     <row r="33" ht="22" customHeight="1">
       <c r="A33" s="6" t="inlineStr">
         <is>
-          <t>NFE</t>
+          <t>PSKY</t>
         </is>
       </c>
       <c r="B33" s="7" t="inlineStr">
         <is>
-          <t>NFE</t>
+          <t>PSKY</t>
         </is>
       </c>
       <c r="C33" s="16" t="n">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="D33" s="16" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E33" s="7" t="inlineStr">
         <is>
@@ -7144,84 +7140,84 @@
       </c>
       <c r="G33" s="7" t="inlineStr">
         <is>
-          <t>Asset Sale [event]; Separation [event/narrat</t>
+          <t>Exchange Offer [event]; Spinoff [event]; Ten</t>
         </is>
       </c>
     </row>
     <row r="34" ht="22" customHeight="1">
       <c r="A34" s="9" t="inlineStr">
         <is>
-          <t>OPTU</t>
+          <t>SOLV</t>
         </is>
       </c>
       <c r="B34" s="10" t="inlineStr">
         <is>
-          <t>Optimum Communications</t>
+          <t>Solventum Corporation</t>
         </is>
       </c>
       <c r="C34" s="17" t="n">
-        <v>25.5</v>
+        <v>21.5</v>
       </c>
       <c r="D34" s="17" t="n">
         <v>2</v>
       </c>
       <c r="E34" s="17" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F34" s="20" t="n">
-        <v>300</v>
+        <v>78</v>
       </c>
       <c r="G34" s="10" t="inlineStr">
         <is>
-          <t>Sale Of Company [narrative]; Tender Offer [e</t>
+          <t>Separation [event]; Strategic Review [event/</t>
         </is>
       </c>
     </row>
     <row r="35" ht="22" customHeight="1">
       <c r="A35" s="6" t="inlineStr">
         <is>
-          <t>NRG</t>
+          <t>ARI</t>
         </is>
       </c>
       <c r="B35" s="7" t="inlineStr">
         <is>
-          <t>NRG Energy, Inc.</t>
+          <t>Apollo Commercial Real</t>
         </is>
       </c>
       <c r="C35" s="16" t="n">
-        <v>25.1</v>
+        <v>21.4</v>
       </c>
       <c r="D35" s="16" t="n">
         <v>2</v>
       </c>
       <c r="E35" s="16" t="n">
-        <v>2.5</v>
+        <v>1.9</v>
       </c>
       <c r="F35" s="19" t="n">
-        <v>237</v>
+        <v>76</v>
       </c>
       <c r="G35" s="7" t="inlineStr">
         <is>
-          <t>Exchange Offer [event]; Tender Offer [event]</t>
+          <t>Asset Sale [event]; Strategic Review [event]</t>
         </is>
       </c>
     </row>
     <row r="36" ht="22" customHeight="1">
       <c r="A36" s="9" t="inlineStr">
         <is>
-          <t>PPLI</t>
+          <t>TIPT</t>
         </is>
       </c>
       <c r="B36" s="10" t="inlineStr">
         <is>
-          <t>PPLI</t>
+          <t>Tiptree Inc.</t>
         </is>
       </c>
       <c r="C36" s="17" t="n">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="D36" s="17" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E36" s="10" t="inlineStr">
         <is>
@@ -7235,69 +7231,61 @@
       </c>
       <c r="G36" s="10" t="inlineStr">
         <is>
-          <t>Asset Sale [narrative]; Capital Return [even</t>
+          <t>Asset Sale [event]; Sale Of Company [event]</t>
         </is>
       </c>
     </row>
     <row r="37" ht="22" customHeight="1">
       <c r="A37" s="6" t="inlineStr">
         <is>
-          <t>LTRN</t>
+          <t>LAB</t>
         </is>
       </c>
       <c r="B37" s="7" t="inlineStr">
         <is>
-          <t>LTRN</t>
+          <t>Standard BioTools Inc.</t>
         </is>
       </c>
       <c r="C37" s="16" t="n">
-        <v>24</v>
+        <v>20.3</v>
       </c>
       <c r="D37" s="16" t="n">
-        <v>2</v>
-      </c>
-      <c r="E37" s="7" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="F37" s="7" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+        <v>1</v>
+      </c>
+      <c r="E37" s="16" t="n">
+        <v>42.3</v>
+      </c>
+      <c r="F37" s="19" t="n">
+        <v>212</v>
       </c>
       <c r="G37" s="7" t="inlineStr">
         <is>
-          <t>Separation [event]; Spinoff [event]</t>
+          <t>Asset Sale [event/narrative]</t>
         </is>
       </c>
     </row>
     <row r="38" ht="22" customHeight="1">
       <c r="A38" s="9" t="inlineStr">
         <is>
-          <t>ADIG</t>
+          <t>FDX</t>
         </is>
       </c>
       <c r="B38" s="10" t="inlineStr">
         <is>
-          <t>ADIG</t>
+          <t>FedEx Corporation</t>
         </is>
       </c>
       <c r="C38" s="17" t="n">
-        <v>24</v>
+        <v>20.2</v>
       </c>
       <c r="D38" s="17" t="n">
         <v>2</v>
       </c>
-      <c r="E38" s="10" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="F38" s="10" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+      <c r="E38" s="17" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="F38" s="20" t="n">
+        <v>74</v>
       </c>
       <c r="G38" s="10" t="inlineStr">
         <is>
@@ -7308,19 +7296,19 @@
     <row r="39" ht="22" customHeight="1">
       <c r="A39" s="6" t="inlineStr">
         <is>
-          <t>HONA</t>
+          <t>HCTI</t>
         </is>
       </c>
       <c r="B39" s="7" t="inlineStr">
         <is>
-          <t>HONA</t>
+          <t>HCTI</t>
         </is>
       </c>
       <c r="C39" s="16" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="D39" s="16" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E39" s="7" t="inlineStr">
         <is>
@@ -7334,26 +7322,26 @@
       </c>
       <c r="G39" s="7" t="inlineStr">
         <is>
-          <t>Separation [event]; Spinoff [event]</t>
+          <t>Separation [event]; Spinoff [event]; Uplisti</t>
         </is>
       </c>
     </row>
     <row r="40" ht="22" customHeight="1">
       <c r="A40" s="9" t="inlineStr">
         <is>
-          <t>FDXF</t>
+          <t>PPLI</t>
         </is>
       </c>
       <c r="B40" s="10" t="inlineStr">
         <is>
-          <t>FDXF</t>
+          <t>PPLI</t>
         </is>
       </c>
       <c r="C40" s="17" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="D40" s="17" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E40" s="10" t="inlineStr">
         <is>
@@ -7367,23 +7355,23 @@
       </c>
       <c r="G40" s="10" t="inlineStr">
         <is>
-          <t>Separation [event]; Spinoff [event]</t>
+          <t>Asset Sale [narrative]; Capital Return [even</t>
         </is>
       </c>
     </row>
     <row r="41" ht="22" customHeight="1">
       <c r="A41" s="6" t="inlineStr">
         <is>
-          <t>NFLX</t>
+          <t>GLDD</t>
         </is>
       </c>
       <c r="B41" s="7" t="inlineStr">
         <is>
-          <t>Netflix, Inc.</t>
+          <t>GLDD</t>
         </is>
       </c>
       <c r="C41" s="16" t="n">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="D41" s="16" t="n">
         <v>2</v>
@@ -7400,292 +7388,300 @@
       </c>
       <c r="G41" s="7" t="inlineStr">
         <is>
-          <t>Separation [event]; Spinoff [event]</t>
+          <t>Sale Of Company [event]; Tender Offer [event</t>
         </is>
       </c>
     </row>
     <row r="42" ht="22" customHeight="1">
       <c r="A42" s="9" t="inlineStr">
         <is>
-          <t>APTV</t>
+          <t>GBCS</t>
         </is>
       </c>
       <c r="B42" s="10" t="inlineStr">
         <is>
-          <t>Aptiv PLC</t>
+          <t>GBCS</t>
         </is>
       </c>
       <c r="C42" s="17" t="n">
-        <v>23.2</v>
+        <v>19</v>
       </c>
       <c r="D42" s="17" t="n">
         <v>2</v>
       </c>
-      <c r="E42" s="17" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="F42" s="20" t="n">
-        <v>34</v>
+      <c r="E42" s="10" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="F42" s="10" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
       <c r="G42" s="10" t="inlineStr">
         <is>
-          <t>Spinoff [event]; Tender Offer [event]</t>
+          <t>Sale Of Company [event]; Tender Offer [event</t>
         </is>
       </c>
     </row>
     <row r="43" ht="22" customHeight="1">
       <c r="A43" s="6" t="inlineStr">
         <is>
-          <t>UEIC</t>
+          <t>PKOH</t>
         </is>
       </c>
       <c r="B43" s="7" t="inlineStr">
         <is>
-          <t>Universal Electronics</t>
+          <t>PKOH</t>
         </is>
       </c>
       <c r="C43" s="16" t="n">
-        <v>22.5</v>
+        <v>19</v>
       </c>
       <c r="D43" s="16" t="n">
         <v>2</v>
       </c>
-      <c r="E43" s="16" t="n">
-        <v>60</v>
-      </c>
-      <c r="F43" s="19" t="n">
-        <v>300</v>
+      <c r="E43" s="7" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="F43" s="7" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
       <c r="G43" s="7" t="inlineStr">
         <is>
-          <t>Asset Sale [narrative]; Capital Return [even</t>
+          <t>Asset Sale [narrative]; Strategic Review [ev</t>
         </is>
       </c>
     </row>
     <row r="44" ht="22" customHeight="1">
       <c r="A44" s="9" t="inlineStr">
         <is>
-          <t>UTZ</t>
+          <t>KALV</t>
         </is>
       </c>
       <c r="B44" s="10" t="inlineStr">
         <is>
-          <t>Utz Brands Inc</t>
+          <t>KalVista Pharmaceutica</t>
         </is>
       </c>
       <c r="C44" s="17" t="n">
-        <v>21.6</v>
+        <v>19</v>
       </c>
       <c r="D44" s="17" t="n">
         <v>2</v>
       </c>
-      <c r="E44" s="17" t="n">
-        <v>23.9</v>
-      </c>
-      <c r="F44" s="20" t="n">
-        <v>120</v>
+      <c r="E44" s="10" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="F44" s="10" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
       <c r="G44" s="10" t="inlineStr">
         <is>
-          <t>Buyback Auth [event]; Going Private [event]</t>
+          <t>Sale Of Company [tender]; Tender Offer [even</t>
         </is>
       </c>
     </row>
     <row r="45" ht="22" customHeight="1">
       <c r="A45" s="6" t="inlineStr">
         <is>
-          <t>CMCO</t>
+          <t>HUN</t>
         </is>
       </c>
       <c r="B45" s="7" t="inlineStr">
         <is>
-          <t>Columbus McKinnon Corp</t>
+          <t>Huntsman Corporation</t>
         </is>
       </c>
       <c r="C45" s="16" t="n">
-        <v>21.2</v>
+        <v>18.9</v>
       </c>
       <c r="D45" s="16" t="n">
         <v>2</v>
       </c>
       <c r="E45" s="16" t="n">
-        <v>7.1</v>
+        <v>7.6</v>
       </c>
       <c r="F45" s="19" t="n">
-        <v>150</v>
+        <v>273</v>
       </c>
       <c r="G45" s="7" t="inlineStr">
         <is>
-          <t>Asset Sale [event]; Exchange Offer [event]</t>
+          <t>Separation [narrative]; Uplisting [event]</t>
         </is>
       </c>
     </row>
     <row r="46" ht="22" customHeight="1">
       <c r="A46" s="9" t="inlineStr">
         <is>
-          <t>ANAB</t>
+          <t>CMCO</t>
         </is>
       </c>
       <c r="B46" s="10" t="inlineStr">
         <is>
-          <t>AnaptysBio, Inc.</t>
+          <t>Columbus McKinnon Corp</t>
         </is>
       </c>
       <c r="C46" s="17" t="n">
-        <v>21</v>
+        <v>18.8</v>
       </c>
       <c r="D46" s="17" t="n">
         <v>2</v>
       </c>
-      <c r="E46" s="10" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="F46" s="10" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+      <c r="E46" s="17" t="n">
+        <v>7.1</v>
+      </c>
+      <c r="F46" s="20" t="n">
+        <v>150</v>
       </c>
       <c r="G46" s="10" t="inlineStr">
         <is>
-          <t>Separation [event]; Uplisting [event]</t>
+          <t>Asset Sale [event]; Exchange Offer [event]</t>
         </is>
       </c>
     </row>
     <row r="47" ht="22" customHeight="1">
       <c r="A47" s="6" t="inlineStr">
         <is>
-          <t>HAIN</t>
+          <t>ALOT</t>
         </is>
       </c>
       <c r="B47" s="7" t="inlineStr">
         <is>
-          <t>The Hain Celestial Gro</t>
+          <t>AstroNova, Inc.</t>
         </is>
       </c>
       <c r="C47" s="16" t="n">
-        <v>21</v>
+        <v>18.2</v>
       </c>
       <c r="D47" s="16" t="n">
         <v>2</v>
       </c>
       <c r="E47" s="16" t="n">
-        <v>60</v>
+        <v>1</v>
       </c>
       <c r="F47" s="19" t="n">
-        <v>300</v>
+        <v>84</v>
       </c>
       <c r="G47" s="7" t="inlineStr">
         <is>
-          <t>Asset Sale [event]; Strategic Review [narrat</t>
+          <t>Sale Of Company [event]; Strategic Review [e</t>
         </is>
       </c>
     </row>
     <row r="48" ht="22" customHeight="1">
       <c r="A48" s="9" t="inlineStr">
         <is>
-          <t>CMTL</t>
+          <t>VTOL</t>
         </is>
       </c>
       <c r="B48" s="10" t="inlineStr">
         <is>
-          <t>Comtech Telecommunicat</t>
+          <t>Bristow Group, Inc.</t>
         </is>
       </c>
       <c r="C48" s="17" t="n">
-        <v>21</v>
+        <v>18.1</v>
       </c>
       <c r="D48" s="17" t="n">
         <v>2</v>
       </c>
       <c r="E48" s="17" t="n">
-        <v>11.5</v>
+        <v>1.4</v>
       </c>
       <c r="F48" s="20" t="n">
-        <v>300</v>
+        <v>79</v>
       </c>
       <c r="G48" s="10" t="inlineStr">
         <is>
-          <t>Asset Sale [event]; Strategic Review [narrat</t>
+          <t>Asset Sale [narrative]; Sale Of Company [eve</t>
         </is>
       </c>
     </row>
     <row r="49" ht="22" customHeight="1">
       <c r="A49" s="6" t="inlineStr">
         <is>
-          <t>ANEB</t>
+          <t>NRG</t>
         </is>
       </c>
       <c r="B49" s="7" t="inlineStr">
         <is>
-          <t>ANEB</t>
+          <t>NRG Energy, Inc.</t>
         </is>
       </c>
       <c r="C49" s="16" t="n">
-        <v>21</v>
+        <v>18.1</v>
       </c>
       <c r="D49" s="16" t="n">
         <v>2</v>
       </c>
-      <c r="E49" s="7" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="F49" s="7" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+      <c r="E49" s="16" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="F49" s="19" t="n">
+        <v>237</v>
       </c>
       <c r="G49" s="7" t="inlineStr">
         <is>
-          <t>Going Private [event]; Tender Offer [event]</t>
+          <t>Exchange Offer [event]; Tender Offer [event]</t>
         </is>
       </c>
     </row>
     <row r="50" ht="22" customHeight="1">
       <c r="A50" s="9" t="inlineStr">
         <is>
-          <t>ROCK</t>
+          <t>LTRN</t>
         </is>
       </c>
       <c r="B50" s="10" t="inlineStr">
         <is>
-          <t>Gibraltar Industries,</t>
+          <t>LTRN</t>
         </is>
       </c>
       <c r="C50" s="17" t="n">
-        <v>20.2</v>
+        <v>18</v>
       </c>
       <c r="D50" s="17" t="n">
         <v>2</v>
       </c>
-      <c r="E50" s="17" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="F50" s="20" t="n">
-        <v>114</v>
+      <c r="E50" s="10" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="F50" s="10" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
       <c r="G50" s="10" t="inlineStr">
         <is>
-          <t>Asset Sale [event]; Exchange Offer [event]</t>
+          <t>Separation [event]; Spinoff [event]</t>
         </is>
       </c>
     </row>
     <row r="51" ht="22" customHeight="1">
       <c r="A51" s="6" t="inlineStr">
         <is>
-          <t>LRHC</t>
+          <t>ADIG</t>
         </is>
       </c>
       <c r="B51" s="7" t="inlineStr">
         <is>
-          <t>LRHC</t>
+          <t>ADIG</t>
         </is>
       </c>
       <c r="C51" s="16" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="D51" s="16" t="n">
         <v>2</v>
@@ -7702,23 +7698,23 @@
       </c>
       <c r="G51" s="7" t="inlineStr">
         <is>
-          <t>Going Private [event]; Sale Of Company [even</t>
+          <t>Separation [event]; Spinoff [event]</t>
         </is>
       </c>
     </row>
     <row r="52" ht="22" customHeight="1">
       <c r="A52" s="9" t="inlineStr">
         <is>
-          <t>RACC</t>
+          <t>HONA</t>
         </is>
       </c>
       <c r="B52" s="10" t="inlineStr">
         <is>
-          <t>RACC</t>
+          <t>HONA</t>
         </is>
       </c>
       <c r="C52" s="17" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="D52" s="17" t="n">
         <v>2</v>
@@ -7735,23 +7731,23 @@
       </c>
       <c r="G52" s="10" t="inlineStr">
         <is>
-          <t>Going Private [event]; Uplisting [event]</t>
+          <t>Separation [event]; Spinoff [event]</t>
         </is>
       </c>
     </row>
     <row r="53" ht="22" customHeight="1">
       <c r="A53" s="6" t="inlineStr">
         <is>
-          <t>SMTK</t>
+          <t>FDXF</t>
         </is>
       </c>
       <c r="B53" s="7" t="inlineStr">
         <is>
-          <t>SMTK</t>
+          <t>FDXF</t>
         </is>
       </c>
       <c r="C53" s="16" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="D53" s="16" t="n">
         <v>2</v>
@@ -7768,23 +7764,23 @@
       </c>
       <c r="G53" s="7" t="inlineStr">
         <is>
-          <t>Going Private [event]; Uplisting [event]</t>
+          <t>Separation [event]; Spinoff [event]</t>
         </is>
       </c>
     </row>
     <row r="54" ht="22" customHeight="1">
       <c r="A54" s="9" t="inlineStr">
         <is>
-          <t>IAC</t>
+          <t>NFLX</t>
         </is>
       </c>
       <c r="B54" s="10" t="inlineStr">
         <is>
-          <t>IAC</t>
+          <t>Netflix, Inc.</t>
         </is>
       </c>
       <c r="C54" s="17" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D54" s="17" t="n">
         <v>2</v>
@@ -7801,7 +7797,7 @@
       </c>
       <c r="G54" s="10" t="inlineStr">
         <is>
-          <t>Asset Sale [narrative]; Spinoff [event]</t>
+          <t>Separation [event]; Spinoff [event]</t>
         </is>
       </c>
     </row>
@@ -7830,7 +7826,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:F26"/>
+  <dimension ref="A1:F34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -7851,7 +7847,7 @@
     <row r="2" ht="18" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Corporate-action announcements in 2024-01-01..2025-06-30 (113 events), realized forward return measured to +12 months, absolute and vs SPY. The evidence behind the catalyst weights.</t>
+          <t>Corporate-action announcements in 2024-01-01..2025-06-30 (314 events), realized forward return measured to +12 months, absolute and vs SPY. The evidence behind the catalyst weights.</t>
         </is>
       </c>
       <c r="B2" s="3" t="n"/>
@@ -7900,295 +7896,306 @@
         </is>
       </c>
       <c r="B5" s="5" t="n">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="C5" s="16" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="D5" s="19" t="n">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="E5" s="16" t="n">
-        <v>-14</v>
+        <v>-10</v>
       </c>
       <c r="F5" s="7" t="inlineStr">
         <is>
-          <t>~market on median; tail-driven</t>
+          <t>best median (+10%, 58% hit); monetize + de-lever</t>
         </is>
       </c>
     </row>
     <row r="6" ht="16" customHeight="1">
       <c r="A6" s="9" t="inlineStr">
         <is>
-          <t>Spinoff</t>
+          <t>Tender Offer</t>
         </is>
       </c>
       <c r="B6" s="8" t="n">
-        <v>40</v>
+        <v>28</v>
       </c>
       <c r="C6" s="17" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D6" s="20" t="n">
-        <v>50</v>
+        <v>61</v>
       </c>
       <c r="E6" s="17" t="n">
-        <v>-12</v>
+        <v>-11</v>
       </c>
       <c r="F6" s="10" t="inlineStr">
         <is>
-          <t>most tail winners; reliable in large-caps</t>
+          <t>reliable-ish (+5%, 61% hit); modest</t>
         </is>
       </c>
     </row>
     <row r="7" ht="16" customHeight="1">
       <c r="A7" s="6" t="inlineStr">
         <is>
-          <t>Sale Of Company</t>
+          <t>Buyback Auth</t>
         </is>
       </c>
       <c r="B7" s="5" t="n">
-        <v>8</v>
+        <v>51</v>
       </c>
       <c r="C7" s="16" t="n">
-        <v>-6</v>
+        <v>1</v>
       </c>
       <c r="D7" s="19" t="n">
-        <v>38</v>
+        <v>51</v>
       </c>
       <c r="E7" s="16" t="n">
-        <v>-28</v>
+        <v>-15</v>
       </c>
       <c r="F7" s="7" t="inlineStr">
         <is>
-          <t>deal already priced at 8-K; little forward juice</t>
+          <t>weak (+1%); float shrink, low signal</t>
         </is>
       </c>
     </row>
     <row r="8" ht="16" customHeight="1">
       <c r="A8" s="9" t="inlineStr">
         <is>
-          <t>Strategic Review</t>
+          <t>Sale Of Company</t>
         </is>
       </c>
       <c r="B8" s="8" t="n">
-        <v>26</v>
+        <v>8</v>
       </c>
       <c r="C8" s="17" t="n">
-        <v>-10</v>
+        <v>-6</v>
       </c>
       <c r="D8" s="20" t="n">
-        <v>46</v>
+        <v>38</v>
       </c>
       <c r="E8" s="17" t="n">
-        <v>-27</v>
+        <v>-28</v>
       </c>
       <c r="F8" s="10" t="inlineStr">
         <is>
-          <t>worst median — most reviews fizzle; pure optionality</t>
+          <t>deal priced at 8-K; tail from contested deals only</t>
         </is>
       </c>
     </row>
     <row r="9" ht="16" customHeight="1">
       <c r="A9" s="6" t="inlineStr">
         <is>
-          <t>OVERALL</t>
+          <t>Capital Return</t>
         </is>
       </c>
       <c r="B9" s="5" t="n">
-        <v>113</v>
+        <v>38</v>
       </c>
       <c r="C9" s="16" t="n">
-        <v>0</v>
+        <v>-11</v>
       </c>
       <c r="D9" s="19" t="n">
-        <v>50</v>
-      </c>
-      <c r="E9" s="7" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+        <v>29</v>
+      </c>
+      <c r="E9" s="16" t="n">
+        <v>-25</v>
       </c>
       <c r="F9" s="7" t="inlineStr">
         <is>
-          <t>–</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="12" t="inlineStr">
-        <is>
-          <t>BIGGEST REALIZED RE-RATES (12m)</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="18" customHeight="1">
-      <c r="A12" s="15" t="inlineStr">
-        <is>
-          <t>Ticker</t>
-        </is>
-      </c>
-      <c r="B12" s="4" t="inlineStr">
-        <is>
-          <t>Catalyst</t>
-        </is>
-      </c>
-      <c r="C12" s="4" t="inlineStr">
-        <is>
-          <t>Date</t>
-        </is>
-      </c>
-      <c r="D12" s="15" t="inlineStr"/>
-      <c r="E12" s="4" t="inlineStr">
-        <is>
-          <t>12m</t>
-        </is>
-      </c>
-      <c r="F12" s="15" t="inlineStr"/>
+          <t>TRAP -11% — special dividend = no reinvestment</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="16" customHeight="1">
+      <c r="A10" s="9" t="inlineStr">
+        <is>
+          <t>Strategic Review</t>
+        </is>
+      </c>
+      <c r="B10" s="8" t="n">
+        <v>25</v>
+      </c>
+      <c r="C10" s="17" t="n">
+        <v>-16</v>
+      </c>
+      <c r="D10" s="20" t="n">
+        <v>44</v>
+      </c>
+      <c r="E10" s="17" t="n">
+        <v>-28</v>
+      </c>
+      <c r="F10" s="10" t="inlineStr">
+        <is>
+          <t>lottery — worst-but-one median, high tail variance</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="16" customHeight="1">
+      <c r="A11" s="6" t="inlineStr">
+        <is>
+          <t>Exchange Offer</t>
+        </is>
+      </c>
+      <c r="B11" s="5" t="n">
+        <v>19</v>
+      </c>
+      <c r="C11" s="16" t="n">
+        <v>-21</v>
+      </c>
+      <c r="D11" s="19" t="n">
+        <v>32</v>
+      </c>
+      <c r="E11" s="16" t="n">
+        <v>-38</v>
+      </c>
+      <c r="F11" s="7" t="inlineStr">
+        <is>
+          <t>TRAP -21% — distressed debt exchange</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="16" customHeight="1">
+      <c r="A12" s="9" t="inlineStr">
+        <is>
+          <t>Uplisting</t>
+        </is>
+      </c>
+      <c r="B12" s="8" t="n">
+        <v>39</v>
+      </c>
+      <c r="C12" s="17" t="n">
+        <v>-23</v>
+      </c>
+      <c r="D12" s="20" t="n">
+        <v>36</v>
+      </c>
+      <c r="E12" s="17" t="n">
+        <v>-41</v>
+      </c>
+      <c r="F12" s="10" t="inlineStr">
+        <is>
+          <t>TRAP -23% — pump-and-fade microcaps</t>
+        </is>
+      </c>
     </row>
     <row r="13" ht="16" customHeight="1">
       <c r="A13" s="6" t="inlineStr">
         <is>
-          <t>SNDK</t>
-        </is>
-      </c>
-      <c r="B13" s="7" t="inlineStr">
-        <is>
-          <t>Spinoff</t>
-        </is>
-      </c>
-      <c r="C13" s="7" t="inlineStr">
-        <is>
-          <t>2025-02-03</t>
-        </is>
-      </c>
-      <c r="D13" s="7" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+          <t>Ch11 Emergence</t>
+        </is>
+      </c>
+      <c r="B13" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="C13" s="16" t="n">
+        <v>-30</v>
+      </c>
+      <c r="D13" s="19" t="n">
+        <v>40</v>
       </c>
       <c r="E13" s="16" t="n">
-        <v>1235</v>
+        <v>-42</v>
       </c>
       <c r="F13" s="7" t="inlineStr">
         <is>
-          <t>–</t>
+          <t>-30% (n=5) — post-reorg overhang</t>
         </is>
       </c>
     </row>
     <row r="14" ht="16" customHeight="1">
       <c r="A14" s="9" t="inlineStr">
         <is>
-          <t>IRWD</t>
-        </is>
-      </c>
-      <c r="B14" s="10" t="inlineStr">
-        <is>
-          <t>Strategic Review</t>
-        </is>
-      </c>
-      <c r="C14" s="10" t="inlineStr">
-        <is>
-          <t>2025-04-14</t>
-        </is>
-      </c>
-      <c r="D14" s="10" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+          <t>Going Private</t>
+        </is>
+      </c>
+      <c r="B14" s="8" t="n">
+        <v>12</v>
+      </c>
+      <c r="C14" s="17" t="n">
+        <v>-37</v>
+      </c>
+      <c r="D14" s="20" t="n">
+        <v>17</v>
       </c>
       <c r="E14" s="17" t="n">
-        <v>495</v>
+        <v>-54</v>
       </c>
       <c r="F14" s="10" t="inlineStr">
         <is>
-          <t>–</t>
+          <t>TRAP -37% — dead money at deal price, break risk</t>
         </is>
       </c>
     </row>
     <row r="15" ht="16" customHeight="1">
       <c r="A15" s="6" t="inlineStr">
         <is>
-          <t>OPEN</t>
-        </is>
-      </c>
-      <c r="B15" s="7" t="inlineStr">
-        <is>
-          <t>Spinoff</t>
-        </is>
-      </c>
-      <c r="C15" s="7" t="inlineStr">
-        <is>
-          <t>2025-02-27</t>
-        </is>
-      </c>
-      <c r="D15" s="7" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+          <t>Separation</t>
+        </is>
+      </c>
+      <c r="B15" s="5" t="n">
+        <v>14</v>
+      </c>
+      <c r="C15" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="D15" s="19" t="n">
+        <v>50</v>
       </c>
       <c r="E15" s="16" t="n">
-        <v>359</v>
+        <v>-19</v>
       </c>
       <c r="F15" s="7" t="inlineStr">
         <is>
-          <t>–</t>
+          <t>weak — 0% median, below-base tail</t>
         </is>
       </c>
     </row>
     <row r="16" ht="16" customHeight="1">
       <c r="A16" s="9" t="inlineStr">
         <is>
-          <t>XCUR</t>
-        </is>
-      </c>
-      <c r="B16" s="10" t="inlineStr">
-        <is>
-          <t>Strategic Review</t>
-        </is>
-      </c>
-      <c r="C16" s="10" t="inlineStr">
-        <is>
-          <t>2024-02-05</t>
-        </is>
-      </c>
-      <c r="D16" s="10" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+          <t>Spinoff</t>
+        </is>
+      </c>
+      <c r="B16" s="8" t="n">
+        <v>39</v>
+      </c>
+      <c r="C16" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="D16" s="20" t="n">
+        <v>49</v>
       </c>
       <c r="E16" s="17" t="n">
-        <v>214</v>
+        <v>-13</v>
       </c>
       <c r="F16" s="10" t="inlineStr">
         <is>
-          <t>–</t>
+          <t>0% median but strong tail (1.6x); optionality</t>
         </is>
       </c>
     </row>
     <row r="17" ht="16" customHeight="1">
       <c r="A17" s="6" t="inlineStr">
         <is>
-          <t>AREC</t>
-        </is>
-      </c>
-      <c r="B17" s="7" t="inlineStr">
-        <is>
-          <t>Spinoff</t>
-        </is>
-      </c>
-      <c r="C17" s="7" t="inlineStr">
-        <is>
-          <t>2024-08-19</t>
-        </is>
-      </c>
-      <c r="D17" s="7" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="E17" s="16" t="n">
-        <v>197</v>
+          <t>OVERALL</t>
+        </is>
+      </c>
+      <c r="B17" s="5" t="n">
+        <v>314</v>
+      </c>
+      <c r="C17" s="16" t="n">
+        <v>-4</v>
+      </c>
+      <c r="D17" s="19" t="n">
+        <v>44</v>
+      </c>
+      <c r="E17" s="7" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
       <c r="F17" s="7" t="inlineStr">
         <is>
@@ -8196,110 +8203,51 @@
         </is>
       </c>
     </row>
-    <row r="18" ht="16" customHeight="1">
-      <c r="A18" s="9" t="inlineStr">
-        <is>
-          <t>CMTL</t>
-        </is>
-      </c>
-      <c r="B18" s="10" t="inlineStr">
-        <is>
-          <t>Strategic Review</t>
-        </is>
-      </c>
-      <c r="C18" s="10" t="inlineStr">
-        <is>
-          <t>2025-01-13</t>
-        </is>
-      </c>
-      <c r="D18" s="10" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="E18" s="17" t="n">
-        <v>195</v>
-      </c>
-      <c r="F18" s="10" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="16" customHeight="1">
-      <c r="A19" s="6" t="inlineStr">
-        <is>
-          <t>GEV</t>
-        </is>
-      </c>
-      <c r="B19" s="7" t="inlineStr">
-        <is>
-          <t>Spinoff</t>
-        </is>
-      </c>
-      <c r="C19" s="7" t="inlineStr">
-        <is>
-          <t>2024-03-08</t>
-        </is>
-      </c>
-      <c r="D19" s="7" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="E19" s="16" t="n">
-        <v>141</v>
-      </c>
-      <c r="F19" s="7" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="16" customHeight="1">
-      <c r="A20" s="9" t="inlineStr">
-        <is>
-          <t>GRAL</t>
-        </is>
-      </c>
-      <c r="B20" s="10" t="inlineStr">
-        <is>
-          <t>Spinoff</t>
-        </is>
-      </c>
-      <c r="C20" s="10" t="inlineStr">
-        <is>
-          <t>2024-06-24</t>
-        </is>
-      </c>
-      <c r="D20" s="10" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="E20" s="17" t="n">
-        <v>122</v>
-      </c>
-      <c r="F20" s="10" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
+    <row r="19">
+      <c r="A19" s="12" t="inlineStr">
+        <is>
+          <t>BIGGEST REALIZED RE-RATES (12m)</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="18" customHeight="1">
+      <c r="A20" s="15" t="inlineStr">
+        <is>
+          <t>Ticker</t>
+        </is>
+      </c>
+      <c r="B20" s="4" t="inlineStr">
+        <is>
+          <t>Catalyst</t>
+        </is>
+      </c>
+      <c r="C20" s="4" t="inlineStr">
+        <is>
+          <t>Date</t>
+        </is>
+      </c>
+      <c r="D20" s="15" t="inlineStr"/>
+      <c r="E20" s="4" t="inlineStr">
+        <is>
+          <t>12m</t>
+        </is>
+      </c>
+      <c r="F20" s="15" t="inlineStr"/>
     </row>
     <row r="21" ht="16" customHeight="1">
       <c r="A21" s="6" t="inlineStr">
         <is>
-          <t>CCO</t>
+          <t>SNDK</t>
         </is>
       </c>
       <c r="B21" s="7" t="inlineStr">
         <is>
-          <t>Asset Sale</t>
+          <t>Spinoff</t>
         </is>
       </c>
       <c r="C21" s="7" t="inlineStr">
         <is>
-          <t>2025-05-07</t>
+          <t>2025-02-03</t>
         </is>
       </c>
       <c r="D21" s="7" t="inlineStr">
@@ -8308,7 +8256,7 @@
         </is>
       </c>
       <c r="E21" s="16" t="n">
-        <v>107</v>
+        <v>1235</v>
       </c>
       <c r="F21" s="7" t="inlineStr">
         <is>
@@ -8319,17 +8267,17 @@
     <row r="22" ht="16" customHeight="1">
       <c r="A22" s="9" t="inlineStr">
         <is>
-          <t>TPR</t>
+          <t>IRWD</t>
         </is>
       </c>
       <c r="B22" s="10" t="inlineStr">
         <is>
-          <t>Asset Sale</t>
+          <t>Strategic Review</t>
         </is>
       </c>
       <c r="C22" s="10" t="inlineStr">
         <is>
-          <t>2025-02-19</t>
+          <t>2025-04-14</t>
         </is>
       </c>
       <c r="D22" s="10" t="inlineStr">
@@ -8338,7 +8286,7 @@
         </is>
       </c>
       <c r="E22" s="17" t="n">
-        <v>100</v>
+        <v>495</v>
       </c>
       <c r="F22" s="10" t="inlineStr">
         <is>
@@ -8349,17 +8297,17 @@
     <row r="23" ht="16" customHeight="1">
       <c r="A23" s="6" t="inlineStr">
         <is>
-          <t>MPTI</t>
+          <t>XCUR</t>
         </is>
       </c>
       <c r="B23" s="7" t="inlineStr">
         <is>
-          <t>Spinoff</t>
+          <t>Strategic Review</t>
         </is>
       </c>
       <c r="C23" s="7" t="inlineStr">
         <is>
-          <t>2024-03-25</t>
+          <t>2024-02-05</t>
         </is>
       </c>
       <c r="D23" s="7" t="inlineStr">
@@ -8368,7 +8316,7 @@
         </is>
       </c>
       <c r="E23" s="16" t="n">
-        <v>100</v>
+        <v>214</v>
       </c>
       <c r="F23" s="7" t="inlineStr">
         <is>
@@ -8379,35 +8327,275 @@
     <row r="24" ht="16" customHeight="1">
       <c r="A24" s="9" t="inlineStr">
         <is>
-          <t>OPRT</t>
+          <t>AREC</t>
         </is>
       </c>
       <c r="B24" s="10" t="inlineStr">
         <is>
+          <t>Spinoff</t>
+        </is>
+      </c>
+      <c r="C24" s="10" t="inlineStr">
+        <is>
+          <t>2024-08-19</t>
+        </is>
+      </c>
+      <c r="D24" s="10" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="E24" s="17" t="n">
+        <v>197</v>
+      </c>
+      <c r="F24" s="10" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="16" customHeight="1">
+      <c r="A25" s="6" t="inlineStr">
+        <is>
+          <t>CMTL</t>
+        </is>
+      </c>
+      <c r="B25" s="7" t="inlineStr">
+        <is>
+          <t>Strategic Review</t>
+        </is>
+      </c>
+      <c r="C25" s="7" t="inlineStr">
+        <is>
+          <t>2025-01-13</t>
+        </is>
+      </c>
+      <c r="D25" s="7" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="E25" s="16" t="n">
+        <v>195</v>
+      </c>
+      <c r="F25" s="7" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="16" customHeight="1">
+      <c r="A26" s="9" t="inlineStr">
+        <is>
+          <t>MP</t>
+        </is>
+      </c>
+      <c r="B26" s="10" t="inlineStr">
+        <is>
+          <t>Uplisting</t>
+        </is>
+      </c>
+      <c r="C26" s="10" t="inlineStr">
+        <is>
+          <t>2024-12-10</t>
+        </is>
+      </c>
+      <c r="D26" s="10" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="E26" s="17" t="n">
+        <v>168</v>
+      </c>
+      <c r="F26" s="10" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="16" customHeight="1">
+      <c r="A27" s="6" t="inlineStr">
+        <is>
+          <t>MYRG</t>
+        </is>
+      </c>
+      <c r="B27" s="7" t="inlineStr">
+        <is>
+          <t>Buyback Auth</t>
+        </is>
+      </c>
+      <c r="C27" s="7" t="inlineStr">
+        <is>
+          <t>2025-02-26</t>
+        </is>
+      </c>
+      <c r="D27" s="7" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="E27" s="16" t="n">
+        <v>150</v>
+      </c>
+      <c r="F27" s="7" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="16" customHeight="1">
+      <c r="A28" s="9" t="inlineStr">
+        <is>
+          <t>SEI</t>
+        </is>
+      </c>
+      <c r="B28" s="10" t="inlineStr">
+        <is>
+          <t>Uplisting</t>
+        </is>
+      </c>
+      <c r="C28" s="10" t="inlineStr">
+        <is>
+          <t>2025-05-02</t>
+        </is>
+      </c>
+      <c r="D28" s="10" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="E28" s="17" t="n">
+        <v>146</v>
+      </c>
+      <c r="F28" s="10" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="16" customHeight="1">
+      <c r="A29" s="6" t="inlineStr">
+        <is>
+          <t>GEV</t>
+        </is>
+      </c>
+      <c r="B29" s="7" t="inlineStr">
+        <is>
+          <t>Spinoff</t>
+        </is>
+      </c>
+      <c r="C29" s="7" t="inlineStr">
+        <is>
+          <t>2024-03-08</t>
+        </is>
+      </c>
+      <c r="D29" s="7" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="E29" s="16" t="n">
+        <v>141</v>
+      </c>
+      <c r="F29" s="7" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="16" customHeight="1">
+      <c r="A30" s="9" t="inlineStr">
+        <is>
+          <t>GRAL</t>
+        </is>
+      </c>
+      <c r="B30" s="10" t="inlineStr">
+        <is>
+          <t>Spinoff</t>
+        </is>
+      </c>
+      <c r="C30" s="10" t="inlineStr">
+        <is>
+          <t>2024-06-24</t>
+        </is>
+      </c>
+      <c r="D30" s="10" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="E30" s="17" t="n">
+        <v>122</v>
+      </c>
+      <c r="F30" s="10" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="16" customHeight="1">
+      <c r="A31" s="6" t="inlineStr">
+        <is>
+          <t>ALMU</t>
+        </is>
+      </c>
+      <c r="B31" s="7" t="inlineStr">
+        <is>
+          <t>Uplisting</t>
+        </is>
+      </c>
+      <c r="C31" s="7" t="inlineStr">
+        <is>
+          <t>2025-03-28</t>
+        </is>
+      </c>
+      <c r="D31" s="7" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="E31" s="16" t="n">
+        <v>122</v>
+      </c>
+      <c r="F31" s="7" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="16" customHeight="1">
+      <c r="A32" s="9" t="inlineStr">
+        <is>
+          <t>CCO</t>
+        </is>
+      </c>
+      <c r="B32" s="10" t="inlineStr">
+        <is>
           <t>Asset Sale</t>
         </is>
       </c>
-      <c r="C24" s="10" t="inlineStr">
-        <is>
-          <t>2024-09-26</t>
-        </is>
-      </c>
-      <c r="D24" s="10" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="E24" s="17" t="n">
-        <v>92</v>
-      </c>
-      <c r="F24" s="10" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-    </row>
-    <row r="26" ht="28" customHeight="1">
-      <c r="A26" s="11" t="inlineStr">
+      <c r="C32" s="10" t="inlineStr">
+        <is>
+          <t>2025-05-07</t>
+        </is>
+      </c>
+      <c r="D32" s="10" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="E32" s="17" t="n">
+        <v>107</v>
+      </c>
+      <c r="F32" s="10" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="28" customHeight="1">
+      <c r="A34" s="11" t="inlineStr">
         <is>
           <t>THE LESSON, from the data. On the MEDIAN, every corporate-action catalyst UNDERPERFORMED SPY over the next year — buying a spin/sale/review indiscriminately is a losing trade. The payoff is a RIGHT TAIL: ~15% of events returned &gt;+50% in 12 months, and spin-offs produced the most of them (SanDisk +1235%, GE Vernova +141%, Grail +122%). Counter-intuitively, small-cap catalyst plays were LOTTERY tickets (median −24%, 35% hit), while large-cap spin-offs were the reliable sweet spot (+4% median, 57% hit). Calibration consequences, applied to the Re-Rate Catalysts weights: spin-offs up, strategic-reviews down (worst median), already-announced deals down (deal priced), and the catalyst credit is scaled by payoff-geometry room so the engine leans toward the setups where the tail actually lives — not the bare catalyst. Sample is modest (8–40 per type); treat as directional. Source: rerate_backtest.py.</t>
         </is>
@@ -8415,9 +8603,9 @@
     </row>
   </sheetData>
   <mergeCells count="3">
-    <mergeCell ref="A26:F26"/>
     <mergeCell ref="A2:F2"/>
     <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A34:F34"/>
   </mergeCells>
   <printOptions horizontalCentered="0"/>
   <pageMargins left="0.5" right="0.5" top="0.6" bottom="0.6" header="0.5" footer="0.5"/>
@@ -8431,7 +8619,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:F79"/>
+  <dimension ref="A1:F81"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -8452,7 +8640,7 @@
     <row r="2" ht="18" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Base rate of a &gt;=+50%/12m outcome among corporate-action events is 15%. Names are re-scored by the historically-measured lifts of the features they carry (catalyst, sector, size, drawdown, range position), combined in shrunk log-odds. Directional, not a calibrated probability.</t>
+          <t>Base rate of a &gt;=+50%/12m outcome among corporate-action events is 10%. Names are re-scored by the historically-measured lifts of the features they carry (catalyst, sector, size, drawdown, range position), combined in shrunk log-odds. Directional, not a calibrated probability.</t>
         </is>
       </c>
       <c r="B2" s="3" t="n"/>
@@ -8504,140 +8692,140 @@
     <row r="6" ht="22" customHeight="1">
       <c r="A6" s="6" t="inlineStr">
         <is>
-          <t>FWDI</t>
+          <t>AGPU</t>
         </is>
       </c>
       <c r="B6" s="7" t="inlineStr">
         <is>
-          <t>Forward Industries,</t>
+          <t>Axe Compute Inc.</t>
         </is>
       </c>
       <c r="C6" s="16" t="n">
-        <v>56</v>
+        <v>33</v>
       </c>
       <c r="D6" s="16" t="n">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="E6" s="7" t="inlineStr">
         <is>
-          <t>6.3m</t>
+          <t>4.1m</t>
         </is>
       </c>
       <c r="F6" s="7" t="inlineStr">
         <is>
-          <t>SALE_OF_COMPANY</t>
+          <t>STRATEGIC_REVIEW</t>
         </is>
       </c>
     </row>
     <row r="7" ht="22" customHeight="1">
       <c r="A7" s="9" t="inlineStr">
         <is>
-          <t>TASK</t>
+          <t>GPRO</t>
         </is>
       </c>
       <c r="B7" s="10" t="inlineStr">
         <is>
-          <t>TaskUs, Inc.</t>
+          <t>GoPro, Inc.</t>
         </is>
       </c>
       <c r="C7" s="17" t="n">
-        <v>52</v>
+        <v>33</v>
       </c>
       <c r="D7" s="17" t="n">
-        <v>28</v>
+        <v>60</v>
       </c>
       <c r="E7" s="10" t="inlineStr">
         <is>
-          <t>6.0m</t>
+          <t>2.3m</t>
         </is>
       </c>
       <c r="F7" s="10" t="inlineStr">
         <is>
-          <t>CAPITAL_RETURN</t>
+          <t>STRATEGIC_REVIEW</t>
         </is>
       </c>
     </row>
     <row r="8" ht="22" customHeight="1">
       <c r="A8" s="6" t="inlineStr">
         <is>
-          <t>PAR</t>
+          <t>FWDI</t>
         </is>
       </c>
       <c r="B8" s="7" t="inlineStr">
         <is>
-          <t>PAR Technology Corpo</t>
+          <t>Forward Industries,</t>
         </is>
       </c>
       <c r="C8" s="16" t="n">
-        <v>52</v>
+        <v>31</v>
       </c>
       <c r="D8" s="16" t="n">
-        <v>39</v>
+        <v>49</v>
       </c>
       <c r="E8" s="7" t="inlineStr">
         <is>
-          <t>6.7m</t>
+          <t>6.3m</t>
         </is>
       </c>
       <c r="F8" s="7" t="inlineStr">
         <is>
-          <t>BUYBACK_AUTH</t>
+          <t>SALE_OF_COMPANY</t>
         </is>
       </c>
     </row>
     <row r="9" ht="22" customHeight="1">
       <c r="A9" s="9" t="inlineStr">
         <is>
-          <t>PD</t>
+          <t>PRGO</t>
         </is>
       </c>
       <c r="B9" s="10" t="inlineStr">
         <is>
-          <t>PagerDuty, Inc.</t>
+          <t>Perrigo Company plc</t>
         </is>
       </c>
       <c r="C9" s="17" t="n">
-        <v>52</v>
+        <v>31</v>
       </c>
       <c r="D9" s="17" t="n">
-        <v>51</v>
+        <v>32</v>
       </c>
       <c r="E9" s="10" t="inlineStr">
         <is>
-          <t>3.6m</t>
+          <t>6.7m</t>
         </is>
       </c>
       <c r="F9" s="10" t="inlineStr">
         <is>
-          <t>BUYBACK_AUTH</t>
+          <t>ASSET_SALE</t>
         </is>
       </c>
     </row>
     <row r="10" ht="22" customHeight="1">
       <c r="A10" s="6" t="inlineStr">
         <is>
-          <t>IBEX</t>
+          <t>CERT</t>
         </is>
       </c>
       <c r="B10" s="7" t="inlineStr">
         <is>
-          <t>IBEX Limited</t>
+          <t>Certara, Inc.</t>
         </is>
       </c>
       <c r="C10" s="16" t="n">
-        <v>46</v>
+        <v>31</v>
       </c>
       <c r="D10" s="16" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E10" s="7" t="inlineStr">
         <is>
-          <t>4.1m</t>
+          <t>4.8m</t>
         </is>
       </c>
       <c r="F10" s="7" t="inlineStr">
         <is>
-          <t>BUYBACK_AUTH</t>
+          <t>ASSET_SALE</t>
         </is>
       </c>
     </row>
@@ -8653,7 +8841,7 @@
         </is>
       </c>
       <c r="C11" s="17" t="n">
-        <v>45</v>
+        <v>28</v>
       </c>
       <c r="D11" s="17" t="n">
         <v>101</v>
@@ -8672,107 +8860,107 @@
     <row r="12" ht="22" customHeight="1">
       <c r="A12" s="6" t="inlineStr">
         <is>
-          <t>AGPU</t>
+          <t>IT</t>
         </is>
       </c>
       <c r="B12" s="7" t="inlineStr">
         <is>
-          <t>Axe Compute Inc.</t>
+          <t>Gartner, Inc.</t>
         </is>
       </c>
       <c r="C12" s="16" t="n">
-        <v>44</v>
+        <v>27</v>
       </c>
       <c r="D12" s="16" t="n">
-        <v>45</v>
+        <v>22</v>
       </c>
       <c r="E12" s="7" t="inlineStr">
         <is>
-          <t>4.1m</t>
+          <t>7.4m</t>
         </is>
       </c>
       <c r="F12" s="7" t="inlineStr">
         <is>
-          <t>STRATEGIC_REVIEW</t>
+          <t>ASSET_SALE</t>
         </is>
       </c>
     </row>
     <row r="13" ht="22" customHeight="1">
       <c r="A13" s="9" t="inlineStr">
         <is>
-          <t>GPRO</t>
+          <t>DUOL</t>
         </is>
       </c>
       <c r="B13" s="10" t="inlineStr">
         <is>
-          <t>GoPro, Inc.</t>
+          <t>Duolingo, Inc.</t>
         </is>
       </c>
       <c r="C13" s="17" t="n">
-        <v>44</v>
+        <v>26</v>
       </c>
       <c r="D13" s="17" t="n">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E13" s="10" t="inlineStr">
         <is>
-          <t>2.3m</t>
+          <t>6.7m</t>
         </is>
       </c>
       <c r="F13" s="10" t="inlineStr">
         <is>
-          <t>STRATEGIC_REVIEW</t>
+          <t>BUYBACK_AUTH</t>
         </is>
       </c>
     </row>
     <row r="14" ht="22" customHeight="1">
       <c r="A14" s="6" t="inlineStr">
         <is>
-          <t>DUOL</t>
+          <t>SMCI</t>
         </is>
       </c>
       <c r="B14" s="7" t="inlineStr">
         <is>
-          <t>Duolingo, Inc.</t>
+          <t>Super Micro Computer</t>
         </is>
       </c>
       <c r="C14" s="16" t="n">
-        <v>42</v>
+        <v>26</v>
       </c>
       <c r="D14" s="16" t="n">
-        <v>55</v>
+        <v>34</v>
       </c>
       <c r="E14" s="7" t="inlineStr">
         <is>
-          <t>6.7m</t>
+          <t>3.1m</t>
         </is>
       </c>
       <c r="F14" s="7" t="inlineStr">
         <is>
-          <t>BUYBACK_AUTH</t>
+          <t>UPLISTING</t>
         </is>
       </c>
     </row>
     <row r="15" ht="22" customHeight="1">
       <c r="A15" s="9" t="inlineStr">
         <is>
-          <t>PRGO</t>
+          <t>CNMD</t>
         </is>
       </c>
       <c r="B15" s="10" t="inlineStr">
         <is>
-          <t>Perrigo Company plc</t>
+          <t>CONMED Corporation</t>
         </is>
       </c>
       <c r="C15" s="17" t="n">
-        <v>41</v>
+        <v>25</v>
       </c>
       <c r="D15" s="17" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="E15" s="10" t="inlineStr">
         <is>
-          <t>6.7m</t>
+          <t>4.6m</t>
         </is>
       </c>
       <c r="F15" s="10" t="inlineStr">
@@ -8784,163 +8972,163 @@
     <row r="16" ht="22" customHeight="1">
       <c r="A16" s="6" t="inlineStr">
         <is>
-          <t>CERT</t>
+          <t>PAR</t>
         </is>
       </c>
       <c r="B16" s="7" t="inlineStr">
         <is>
-          <t>Certara, Inc.</t>
+          <t>PAR Technology Corpo</t>
         </is>
       </c>
       <c r="C16" s="16" t="n">
-        <v>41</v>
+        <v>25</v>
       </c>
       <c r="D16" s="16" t="n">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="E16" s="7" t="inlineStr">
         <is>
-          <t>4.8m</t>
+          <t>6.7m</t>
         </is>
       </c>
       <c r="F16" s="7" t="inlineStr">
         <is>
-          <t>ASSET_SALE</t>
+          <t>BUYBACK_AUTH</t>
         </is>
       </c>
     </row>
     <row r="17" ht="22" customHeight="1">
       <c r="A17" s="9" t="inlineStr">
         <is>
-          <t>SMCI</t>
+          <t>PD</t>
         </is>
       </c>
       <c r="B17" s="10" t="inlineStr">
         <is>
-          <t>Super Micro Computer</t>
+          <t>PagerDuty, Inc.</t>
         </is>
       </c>
       <c r="C17" s="17" t="n">
-        <v>38</v>
+        <v>25</v>
       </c>
       <c r="D17" s="17" t="n">
-        <v>33</v>
+        <v>53</v>
       </c>
       <c r="E17" s="10" t="inlineStr">
         <is>
-          <t>3.1m</t>
+          <t>3.6m</t>
         </is>
       </c>
       <c r="F17" s="10" t="inlineStr">
         <is>
-          <t>UPLISTING</t>
+          <t>BUYBACK_AUTH</t>
         </is>
       </c>
     </row>
     <row r="18" ht="22" customHeight="1">
       <c r="A18" s="6" t="inlineStr">
         <is>
-          <t>AZTA</t>
+          <t>ORKA</t>
         </is>
       </c>
       <c r="B18" s="7" t="inlineStr">
         <is>
-          <t>Azenta, Inc.</t>
+          <t>Oruka Therapeutics,</t>
         </is>
       </c>
       <c r="C18" s="16" t="n">
-        <v>38</v>
+        <v>24</v>
       </c>
       <c r="D18" s="16" t="n">
-        <v>48</v>
+        <v>64</v>
       </c>
       <c r="E18" s="7" t="inlineStr">
         <is>
-          <t>7.4m</t>
+          <t>4.6m</t>
         </is>
       </c>
       <c r="F18" s="7" t="inlineStr">
         <is>
-          <t>BUYBACK_AUTH</t>
+          <t>UPLISTING</t>
         </is>
       </c>
     </row>
     <row r="19" ht="22" customHeight="1">
       <c r="A19" s="9" t="inlineStr">
         <is>
-          <t>GRND</t>
+          <t>ACHV</t>
         </is>
       </c>
       <c r="B19" s="10" t="inlineStr">
         <is>
-          <t>Grindr Inc.</t>
+          <t>Achieve Life Science</t>
         </is>
       </c>
       <c r="C19" s="17" t="n">
+        <v>23</v>
+      </c>
+      <c r="D19" s="17" t="n">
         <v>36</v>
       </c>
-      <c r="D19" s="17" t="n">
-        <v>28</v>
-      </c>
       <c r="E19" s="10" t="inlineStr">
         <is>
-          <t>6.7m</t>
+          <t>4.6m</t>
         </is>
       </c>
       <c r="F19" s="10" t="inlineStr">
         <is>
-          <t>GOING_PRIVATE</t>
+          <t>ASSET_SALE</t>
         </is>
       </c>
     </row>
     <row r="20" ht="22" customHeight="1">
       <c r="A20" s="6" t="inlineStr">
         <is>
-          <t>IT</t>
+          <t>ANF</t>
         </is>
       </c>
       <c r="B20" s="7" t="inlineStr">
         <is>
-          <t>Gartner, Inc.</t>
+          <t>Abercrombie &amp; Fitch</t>
         </is>
       </c>
       <c r="C20" s="16" t="n">
-        <v>34</v>
+        <v>23</v>
       </c>
       <c r="D20" s="16" t="n">
-        <v>22</v>
+        <v>69</v>
       </c>
       <c r="E20" s="7" t="inlineStr">
         <is>
-          <t>7.4m</t>
+          <t>5.7m</t>
         </is>
       </c>
       <c r="F20" s="7" t="inlineStr">
         <is>
-          <t>ASSET_SALE</t>
+          <t>STRATEGIC_REVIEW</t>
         </is>
       </c>
     </row>
     <row r="21" ht="22" customHeight="1">
       <c r="A21" s="9" t="inlineStr">
         <is>
-          <t>CNMD</t>
+          <t>VSAT</t>
         </is>
       </c>
       <c r="B21" s="10" t="inlineStr">
         <is>
-          <t>CONMED Corporation</t>
+          <t>ViaSat, Inc.</t>
         </is>
       </c>
       <c r="C21" s="17" t="n">
-        <v>34</v>
+        <v>23</v>
       </c>
       <c r="D21" s="17" t="n">
-        <v>30</v>
+        <v>59</v>
       </c>
       <c r="E21" s="10" t="inlineStr">
         <is>
-          <t>4.6m</t>
+          <t>7.4m</t>
         </is>
       </c>
       <c r="F21" s="10" t="inlineStr">
@@ -8952,1227 +9140,1230 @@
     <row r="22" ht="22" customHeight="1">
       <c r="A22" s="6" t="inlineStr">
         <is>
-          <t>ANF</t>
+          <t>AZTA</t>
         </is>
       </c>
       <c r="B22" s="7" t="inlineStr">
         <is>
-          <t>Abercrombie &amp; Fitch</t>
+          <t>Azenta, Inc.</t>
         </is>
       </c>
       <c r="C22" s="16" t="n">
-        <v>34</v>
+        <v>22</v>
       </c>
       <c r="D22" s="16" t="n">
-        <v>68</v>
+        <v>49</v>
       </c>
       <c r="E22" s="7" t="inlineStr">
         <is>
-          <t>5.7m</t>
+          <t>7.4m</t>
         </is>
       </c>
       <c r="F22" s="7" t="inlineStr">
         <is>
-          <t>STRATEGIC_REVIEW</t>
+          <t>BUYBACK_AUTH</t>
         </is>
       </c>
     </row>
     <row r="23" ht="22" customHeight="1">
       <c r="A23" s="9" t="inlineStr">
         <is>
-          <t>MGTX</t>
+          <t>ASH</t>
         </is>
       </c>
       <c r="B23" s="10" t="inlineStr">
         <is>
-          <t>MeiraGTx Holdings pl</t>
+          <t>Ashland Inc.</t>
         </is>
       </c>
       <c r="C23" s="17" t="n">
-        <v>33</v>
+        <v>22</v>
       </c>
       <c r="D23" s="17" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="E23" s="10" t="inlineStr">
         <is>
-          <t>5.0m</t>
+          <t>4.6m</t>
         </is>
       </c>
       <c r="F23" s="10" t="inlineStr">
         <is>
-          <t>UPLISTING</t>
+          <t>ASSET_SALE</t>
         </is>
       </c>
     </row>
     <row r="24" ht="22" customHeight="1">
       <c r="A24" s="6" t="inlineStr">
         <is>
-          <t>ADV</t>
+          <t>GRND</t>
         </is>
       </c>
       <c r="B24" s="7" t="inlineStr">
         <is>
-          <t>Advantage Solutions</t>
+          <t>Grindr Inc.</t>
         </is>
       </c>
       <c r="C24" s="16" t="n">
-        <v>33</v>
+        <v>22</v>
       </c>
       <c r="D24" s="16" t="n">
-        <v>64</v>
+        <v>28</v>
       </c>
       <c r="E24" s="7" t="inlineStr">
         <is>
-          <t>7.2m</t>
+          <t>6.7m</t>
         </is>
       </c>
       <c r="F24" s="7" t="inlineStr">
         <is>
-          <t>EXCHANGE_OFFER</t>
+          <t>GOING_PRIVATE</t>
         </is>
       </c>
     </row>
     <row r="25" ht="22" customHeight="1">
       <c r="A25" s="9" t="inlineStr">
         <is>
-          <t>CTSH</t>
+          <t>TASK</t>
         </is>
       </c>
       <c r="B25" s="10" t="inlineStr">
         <is>
-          <t>Cognizant Technology</t>
+          <t>TaskUs, Inc.</t>
         </is>
       </c>
       <c r="C25" s="17" t="n">
-        <v>32</v>
+        <v>22</v>
       </c>
       <c r="D25" s="17" t="n">
-        <v>66</v>
+        <v>28</v>
       </c>
       <c r="E25" s="10" t="inlineStr">
         <is>
-          <t>4.0m</t>
+          <t>6.0m</t>
         </is>
       </c>
       <c r="F25" s="10" t="inlineStr">
         <is>
-          <t>BUYBACK_AUTH</t>
-        </is>
-      </c>
-    </row>
-    <row r="26" ht="22" customHeight="1">
-      <c r="A26" s="6" t="inlineStr">
-        <is>
-          <t>BWIN</t>
-        </is>
-      </c>
-      <c r="B26" s="7" t="inlineStr">
-        <is>
-          <t>The Baldwin Insuranc</t>
-        </is>
-      </c>
-      <c r="C26" s="16" t="n">
-        <v>32</v>
-      </c>
-      <c r="D26" s="16" t="n">
-        <v>38</v>
-      </c>
-      <c r="E26" s="7" t="inlineStr">
-        <is>
-          <t>8.5m</t>
-        </is>
-      </c>
-      <c r="F26" s="7" t="inlineStr">
-        <is>
-          <t>EXCHANGE_OFFER</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="21" t="inlineStr">
-        <is>
-          <t>(21 confirmed / 13 pending / 73 neutral / 41 fading, of 148 priced)</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="12" t="inlineStr">
+          <t>CAPITAL_RETURN</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="21" t="inlineStr">
+        <is>
+          <t>(20 confirmed / 15 pending / 79 neutral / 32 fading, of 146 priced)</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="12" t="inlineStr">
         <is>
           <t>ALL CANDIDATES — pre-confirmation tail odds</t>
         </is>
       </c>
     </row>
-    <row r="30" ht="18" customHeight="1">
-      <c r="A30" s="15" t="inlineStr">
+    <row r="29" ht="18" customHeight="1">
+      <c r="A29" s="15" t="inlineStr">
         <is>
           <t>Ticker</t>
         </is>
       </c>
-      <c r="B30" s="15" t="inlineStr">
+      <c r="B29" s="15" t="inlineStr">
         <is>
           <t>Name</t>
         </is>
       </c>
-      <c r="C30" s="4" t="inlineStr">
+      <c r="C29" s="4" t="inlineStr">
         <is>
           <t>Tail p</t>
         </is>
       </c>
-      <c r="D30" s="4" t="inlineStr">
+      <c r="D29" s="4" t="inlineStr">
         <is>
           <t>State</t>
         </is>
       </c>
-      <c r="E30" s="4" t="inlineStr">
+      <c r="E29" s="4" t="inlineStr">
         <is>
           <t>Ratio</t>
         </is>
       </c>
-      <c r="F30" s="4" t="inlineStr">
+      <c r="F29" s="4" t="inlineStr">
         <is>
           <t>Tail drivers</t>
         </is>
       </c>
     </row>
+    <row r="30" ht="22" customHeight="1">
+      <c r="A30" s="6" t="inlineStr">
+        <is>
+          <t>USAR</t>
+        </is>
+      </c>
+      <c r="B30" s="7" t="inlineStr">
+        <is>
+          <t>USA Rare Earth, Inc.</t>
+        </is>
+      </c>
+      <c r="C30" s="16" t="n">
+        <v>28</v>
+      </c>
+      <c r="D30" s="7" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="E30" s="7" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="F30" s="7" t="inlineStr">
+        <is>
+          <t>catalyst=SALE_OF_COMPANY, sector=Basic</t>
+        </is>
+      </c>
+    </row>
     <row r="31" ht="22" customHeight="1">
-      <c r="A31" s="6" t="inlineStr">
+      <c r="A31" s="9" t="inlineStr">
+        <is>
+          <t>AMS</t>
+        </is>
+      </c>
+      <c r="B31" s="10" t="inlineStr">
+        <is>
+          <t>American Shared Hosp</t>
+        </is>
+      </c>
+      <c r="C31" s="17" t="n">
+        <v>27</v>
+      </c>
+      <c r="D31" s="10" t="inlineStr">
+        <is>
+          <t>NEUTRAL</t>
+        </is>
+      </c>
+      <c r="E31" s="17" t="n">
+        <v>60</v>
+      </c>
+      <c r="F31" s="10" t="inlineStr">
+        <is>
+          <t>catalyst=SALE_OF_COMPANY, sector=Healt</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="22" customHeight="1">
+      <c r="A32" s="6" t="inlineStr">
+        <is>
+          <t>BTAI</t>
+        </is>
+      </c>
+      <c r="B32" s="7" t="inlineStr">
+        <is>
+          <t>BioXcel Therapeutics</t>
+        </is>
+      </c>
+      <c r="C32" s="16" t="n">
+        <v>27</v>
+      </c>
+      <c r="D32" s="7" t="inlineStr">
+        <is>
+          <t>NEUTRAL</t>
+        </is>
+      </c>
+      <c r="E32" s="7" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="F32" s="7" t="inlineStr">
+        <is>
+          <t>catalyst=SALE_OF_COMPANY, sector=Healt</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="22" customHeight="1">
+      <c r="A33" s="9" t="inlineStr">
+        <is>
+          <t>SUNE</t>
+        </is>
+      </c>
+      <c r="B33" s="10" t="inlineStr">
+        <is>
+          <t>SUNation Energy, Inc</t>
+        </is>
+      </c>
+      <c r="C33" s="17" t="n">
+        <v>25</v>
+      </c>
+      <c r="D33" s="10" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="E33" s="17" t="n">
+        <v>60</v>
+      </c>
+      <c r="F33" s="10" t="inlineStr">
+        <is>
+          <t>catalyst=SALE_OF_COMPANY, sector=Techn</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="22" customHeight="1">
+      <c r="A34" s="6" t="inlineStr">
+        <is>
+          <t>JTAI</t>
+        </is>
+      </c>
+      <c r="B34" s="7" t="inlineStr">
+        <is>
+          <t>Jet.AI Inc.</t>
+        </is>
+      </c>
+      <c r="C34" s="16" t="n">
+        <v>25</v>
+      </c>
+      <c r="D34" s="7" t="inlineStr">
+        <is>
+          <t>FADING</t>
+        </is>
+      </c>
+      <c r="E34" s="16" t="n">
+        <v>60</v>
+      </c>
+      <c r="F34" s="7" t="inlineStr">
+        <is>
+          <t>catalyst=SALE_OF_COMPANY, sector=Techn</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="22" customHeight="1">
+      <c r="A35" s="9" t="inlineStr">
+        <is>
+          <t>OPTU</t>
+        </is>
+      </c>
+      <c r="B35" s="10" t="inlineStr">
+        <is>
+          <t>Optimum Communicatio</t>
+        </is>
+      </c>
+      <c r="C35" s="17" t="n">
+        <v>24</v>
+      </c>
+      <c r="D35" s="10" t="inlineStr">
+        <is>
+          <t>NEUTRAL</t>
+        </is>
+      </c>
+      <c r="E35" s="17" t="n">
+        <v>3</v>
+      </c>
+      <c r="F35" s="10" t="inlineStr">
+        <is>
+          <t>catalyst=SALE_OF_COMPANY, sector=Commu</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="22" customHeight="1">
+      <c r="A36" s="6" t="inlineStr">
+        <is>
+          <t>NEUP</t>
+        </is>
+      </c>
+      <c r="B36" s="7" t="inlineStr">
+        <is>
+          <t>Neuphoria Therapeuti</t>
+        </is>
+      </c>
+      <c r="C36" s="16" t="n">
+        <v>23</v>
+      </c>
+      <c r="D36" s="7" t="inlineStr">
+        <is>
+          <t>FADING</t>
+        </is>
+      </c>
+      <c r="E36" s="16" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="F36" s="7" t="inlineStr">
+        <is>
+          <t>catalyst=STRATEGIC_REVIEW, sector=Heal</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="22" customHeight="1">
+      <c r="A37" s="9" t="inlineStr">
+        <is>
+          <t>NERV</t>
+        </is>
+      </c>
+      <c r="B37" s="10" t="inlineStr">
+        <is>
+          <t>Minerva Neuroscience</t>
+        </is>
+      </c>
+      <c r="C37" s="17" t="n">
+        <v>23</v>
+      </c>
+      <c r="D37" s="10" t="inlineStr">
+        <is>
+          <t>FADING</t>
+        </is>
+      </c>
+      <c r="E37" s="10" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="F37" s="10" t="inlineStr">
+        <is>
+          <t>catalyst=STRATEGIC_REVIEW, sector=Heal</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="22" customHeight="1">
+      <c r="A38" s="6" t="inlineStr">
+        <is>
+          <t>FULC</t>
+        </is>
+      </c>
+      <c r="B38" s="7" t="inlineStr">
+        <is>
+          <t>Fulcrum Therapeutics</t>
+        </is>
+      </c>
+      <c r="C38" s="16" t="n">
+        <v>23</v>
+      </c>
+      <c r="D38" s="7" t="inlineStr">
+        <is>
+          <t>NEUTRAL</t>
+        </is>
+      </c>
+      <c r="E38" s="16" t="n">
+        <v>8.300000000000001</v>
+      </c>
+      <c r="F38" s="7" t="inlineStr">
+        <is>
+          <t>catalyst=STRATEGIC_REVIEW, sector=Heal</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="22" customHeight="1">
+      <c r="A39" s="9" t="inlineStr">
+        <is>
+          <t>NDRA</t>
+        </is>
+      </c>
+      <c r="B39" s="10" t="inlineStr">
+        <is>
+          <t>ENDRA Life Sciences</t>
+        </is>
+      </c>
+      <c r="C39" s="17" t="n">
+        <v>23</v>
+      </c>
+      <c r="D39" s="10" t="inlineStr">
+        <is>
+          <t>NEUTRAL</t>
+        </is>
+      </c>
+      <c r="E39" s="10" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="F39" s="10" t="inlineStr">
+        <is>
+          <t>catalyst=STRATEGIC_REVIEW, sector=Heal</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="22" customHeight="1">
+      <c r="A40" s="6" t="inlineStr">
+        <is>
+          <t>GPRO</t>
+        </is>
+      </c>
+      <c r="B40" s="7" t="inlineStr">
+        <is>
+          <t>GoPro, Inc.</t>
+        </is>
+      </c>
+      <c r="C40" s="16" t="n">
+        <v>21</v>
+      </c>
+      <c r="D40" s="7" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="E40" s="16" t="n">
+        <v>3</v>
+      </c>
+      <c r="F40" s="7" t="inlineStr">
+        <is>
+          <t>catalyst=STRATEGIC_REVIEW, sector=Tech</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="22" customHeight="1">
+      <c r="A41" s="9" t="inlineStr">
+        <is>
+          <t>TTEC</t>
+        </is>
+      </c>
+      <c r="B41" s="10" t="inlineStr">
+        <is>
+          <t>TTEC Holdings, Inc.</t>
+        </is>
+      </c>
+      <c r="C41" s="17" t="n">
+        <v>21</v>
+      </c>
+      <c r="D41" s="10" t="inlineStr">
+        <is>
+          <t>NEUTRAL</t>
+        </is>
+      </c>
+      <c r="E41" s="17" t="n">
+        <v>20.3</v>
+      </c>
+      <c r="F41" s="10" t="inlineStr">
+        <is>
+          <t>catalyst=STRATEGIC_REVIEW, sector=Tech</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="22" customHeight="1">
+      <c r="A42" s="6" t="inlineStr">
+        <is>
+          <t>CMTL</t>
+        </is>
+      </c>
+      <c r="B42" s="7" t="inlineStr">
+        <is>
+          <t>Comtech Telecommunic</t>
+        </is>
+      </c>
+      <c r="C42" s="16" t="n">
+        <v>21</v>
+      </c>
+      <c r="D42" s="7" t="inlineStr">
+        <is>
+          <t>FADING</t>
+        </is>
+      </c>
+      <c r="E42" s="16" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="F42" s="7" t="inlineStr">
+        <is>
+          <t>catalyst=STRATEGIC_REVIEW, sector=Tech</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="22" customHeight="1">
+      <c r="A43" s="9" t="inlineStr">
+        <is>
+          <t>DOMO</t>
+        </is>
+      </c>
+      <c r="B43" s="10" t="inlineStr">
+        <is>
+          <t>Domo, Inc.</t>
+        </is>
+      </c>
+      <c r="C43" s="17" t="n">
+        <v>21</v>
+      </c>
+      <c r="D43" s="10" t="inlineStr">
+        <is>
+          <t>NEUTRAL</t>
+        </is>
+      </c>
+      <c r="E43" s="17" t="n">
+        <v>3</v>
+      </c>
+      <c r="F43" s="10" t="inlineStr">
+        <is>
+          <t>catalyst=STRATEGIC_REVIEW, sector=Tech</t>
+        </is>
+      </c>
+    </row>
+    <row r="44" ht="22" customHeight="1">
+      <c r="A44" s="6" t="inlineStr">
+        <is>
+          <t>AGPU</t>
+        </is>
+      </c>
+      <c r="B44" s="7" t="inlineStr">
+        <is>
+          <t>Axe Compute Inc.</t>
+        </is>
+      </c>
+      <c r="C44" s="16" t="n">
+        <v>21</v>
+      </c>
+      <c r="D44" s="7" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="E44" s="16" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="F44" s="7" t="inlineStr">
+        <is>
+          <t>catalyst=STRATEGIC_REVIEW, sector=Tech</t>
+        </is>
+      </c>
+    </row>
+    <row r="45" ht="22" customHeight="1">
+      <c r="A45" s="9" t="inlineStr">
+        <is>
+          <t>VRME</t>
+        </is>
+      </c>
+      <c r="B45" s="10" t="inlineStr">
+        <is>
+          <t>VerifyMe, Inc.</t>
+        </is>
+      </c>
+      <c r="C45" s="17" t="n">
+        <v>21</v>
+      </c>
+      <c r="D45" s="10" t="inlineStr">
+        <is>
+          <t>NEUTRAL</t>
+        </is>
+      </c>
+      <c r="E45" s="17" t="n">
+        <v>8.1</v>
+      </c>
+      <c r="F45" s="10" t="inlineStr">
+        <is>
+          <t>catalyst=SALE_OF_COMPANY, size=micro,</t>
+        </is>
+      </c>
+    </row>
+    <row r="46" ht="22" customHeight="1">
+      <c r="A46" s="6" t="inlineStr">
+        <is>
+          <t>PLAG</t>
+        </is>
+      </c>
+      <c r="B46" s="7" t="inlineStr">
+        <is>
+          <t>Planet Green Holding</t>
+        </is>
+      </c>
+      <c r="C46" s="16" t="n">
+        <v>21</v>
+      </c>
+      <c r="D46" s="7" t="inlineStr">
+        <is>
+          <t>FADING</t>
+        </is>
+      </c>
+      <c r="E46" s="7" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="F46" s="7" t="inlineStr">
+        <is>
+          <t>catalyst=SALE_OF_COMPANY, size=micro,</t>
+        </is>
+      </c>
+    </row>
+    <row r="47" ht="22" customHeight="1">
+      <c r="A47" s="9" t="inlineStr">
+        <is>
+          <t>HHS</t>
+        </is>
+      </c>
+      <c r="B47" s="10" t="inlineStr">
+        <is>
+          <t>Harte Hanks, Inc.</t>
+        </is>
+      </c>
+      <c r="C47" s="17" t="n">
+        <v>21</v>
+      </c>
+      <c r="D47" s="10" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="E47" s="17" t="n">
+        <v>6.9</v>
+      </c>
+      <c r="F47" s="10" t="inlineStr">
+        <is>
+          <t>catalyst=SALE_OF_COMPANY, size=micro,</t>
+        </is>
+      </c>
+    </row>
+    <row r="48" ht="22" customHeight="1">
+      <c r="A48" s="6" t="inlineStr">
+        <is>
+          <t>DXLG</t>
+        </is>
+      </c>
+      <c r="B48" s="7" t="inlineStr">
+        <is>
+          <t>Destination XL Group</t>
+        </is>
+      </c>
+      <c r="C48" s="16" t="n">
+        <v>21</v>
+      </c>
+      <c r="D48" s="7" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="E48" s="16" t="n">
+        <v>60</v>
+      </c>
+      <c r="F48" s="7" t="inlineStr">
+        <is>
+          <t>catalyst=SALE_OF_COMPANY, size=micro,</t>
+        </is>
+      </c>
+    </row>
+    <row r="49" ht="22" customHeight="1">
+      <c r="A49" s="9" t="inlineStr">
+        <is>
+          <t>HCAT</t>
+        </is>
+      </c>
+      <c r="B49" s="10" t="inlineStr">
+        <is>
+          <t>Health Catalyst, Inc</t>
+        </is>
+      </c>
+      <c r="C49" s="17" t="n">
+        <v>20</v>
+      </c>
+      <c r="D49" s="10" t="inlineStr">
+        <is>
+          <t>FADING</t>
+        </is>
+      </c>
+      <c r="E49" s="17" t="n">
+        <v>6.1</v>
+      </c>
+      <c r="F49" s="10" t="inlineStr">
+        <is>
+          <t>catalyst=ASSET_SALE, sector=Healthcare</t>
+        </is>
+      </c>
+    </row>
+    <row r="50" ht="22" customHeight="1">
+      <c r="A50" s="6" t="inlineStr">
+        <is>
+          <t>KROS</t>
+        </is>
+      </c>
+      <c r="B50" s="7" t="inlineStr">
+        <is>
+          <t>Keros Therapeutics,</t>
+        </is>
+      </c>
+      <c r="C50" s="16" t="n">
+        <v>20</v>
+      </c>
+      <c r="D50" s="7" t="inlineStr">
+        <is>
+          <t>NEUTRAL</t>
+        </is>
+      </c>
+      <c r="E50" s="16" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="F50" s="7" t="inlineStr">
+        <is>
+          <t>catalyst=TENDER_OFFER, sector=Healthca</t>
+        </is>
+      </c>
+    </row>
+    <row r="51" ht="22" customHeight="1">
+      <c r="A51" s="9" t="inlineStr">
+        <is>
+          <t>FMC</t>
+        </is>
+      </c>
+      <c r="B51" s="10" t="inlineStr">
+        <is>
+          <t>FMC Corporation</t>
+        </is>
+      </c>
+      <c r="C51" s="17" t="n">
+        <v>20</v>
+      </c>
+      <c r="D51" s="10" t="inlineStr">
+        <is>
+          <t>NEUTRAL</t>
+        </is>
+      </c>
+      <c r="E51" s="17" t="n">
+        <v>6.1</v>
+      </c>
+      <c r="F51" s="10" t="inlineStr">
+        <is>
+          <t>catalyst=TENDER_OFFER, sector=Basic Ma</t>
+        </is>
+      </c>
+    </row>
+    <row r="52" ht="22" customHeight="1">
+      <c r="A52" s="6" t="inlineStr">
+        <is>
+          <t>JKHY</t>
+        </is>
+      </c>
+      <c r="B52" s="7" t="inlineStr">
+        <is>
+          <t>Jack Henry &amp; Associa</t>
+        </is>
+      </c>
+      <c r="C52" s="16" t="n">
+        <v>20</v>
+      </c>
+      <c r="D52" s="7" t="inlineStr">
+        <is>
+          <t>NEUTRAL</t>
+        </is>
+      </c>
+      <c r="E52" s="7" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="F52" s="7" t="inlineStr">
+        <is>
+          <t>catalyst=SALE_OF_COMPANY, sector=Techn</t>
+        </is>
+      </c>
+    </row>
+    <row r="53" ht="22" customHeight="1">
+      <c r="A53" s="9" t="inlineStr">
+        <is>
+          <t>SPRB</t>
+        </is>
+      </c>
+      <c r="B53" s="10" t="inlineStr">
+        <is>
+          <t>Spruce Biosciences,</t>
+        </is>
+      </c>
+      <c r="C53" s="17" t="n">
+        <v>20</v>
+      </c>
+      <c r="D53" s="10" t="inlineStr">
+        <is>
+          <t>NEUTRAL</t>
+        </is>
+      </c>
+      <c r="E53" s="10" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="F53" s="10" t="inlineStr">
+        <is>
+          <t>sector=Healthcare, size=micro, drawdow</t>
+        </is>
+      </c>
+    </row>
+    <row r="54" ht="22" customHeight="1">
+      <c r="A54" s="6" t="inlineStr">
+        <is>
+          <t>INO</t>
+        </is>
+      </c>
+      <c r="B54" s="7" t="inlineStr">
+        <is>
+          <t>Inovio Pharmaceutica</t>
+        </is>
+      </c>
+      <c r="C54" s="16" t="n">
+        <v>20</v>
+      </c>
+      <c r="D54" s="7" t="inlineStr">
+        <is>
+          <t>NEUTRAL</t>
+        </is>
+      </c>
+      <c r="E54" s="7" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="F54" s="7" t="inlineStr">
+        <is>
+          <t>sector=Healthcare, size=micro, drawdow</t>
+        </is>
+      </c>
+    </row>
+    <row r="55" ht="22" customHeight="1">
+      <c r="A55" s="9" t="inlineStr">
+        <is>
+          <t>GMAB</t>
+        </is>
+      </c>
+      <c r="B55" s="10" t="inlineStr">
+        <is>
+          <t>Genmab A/S</t>
+        </is>
+      </c>
+      <c r="C55" s="17" t="n">
+        <v>20</v>
+      </c>
+      <c r="D55" s="10" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="E55" s="10" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="F55" s="10" t="inlineStr">
+        <is>
+          <t>catalyst=SALE_OF_COMPANY, sector=Healt</t>
+        </is>
+      </c>
+    </row>
+    <row r="56" ht="22" customHeight="1">
+      <c r="A56" s="6" t="inlineStr">
+        <is>
+          <t>PTN</t>
+        </is>
+      </c>
+      <c r="B56" s="7" t="inlineStr">
+        <is>
+          <t>Palatin Technologies</t>
+        </is>
+      </c>
+      <c r="C56" s="16" t="n">
+        <v>20</v>
+      </c>
+      <c r="D56" s="7" t="inlineStr">
+        <is>
+          <t>NEUTRAL</t>
+        </is>
+      </c>
+      <c r="E56" s="16" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="F56" s="7" t="inlineStr">
+        <is>
+          <t>sector=Healthcare, size=micro, drawdow</t>
+        </is>
+      </c>
+    </row>
+    <row r="57" ht="22" customHeight="1">
+      <c r="A57" s="9" t="inlineStr">
+        <is>
+          <t>MLYS</t>
+        </is>
+      </c>
+      <c r="B57" s="10" t="inlineStr">
+        <is>
+          <t>Mineralys Therapeuti</t>
+        </is>
+      </c>
+      <c r="C57" s="17" t="n">
+        <v>20</v>
+      </c>
+      <c r="D57" s="10" t="inlineStr">
+        <is>
+          <t>NEUTRAL</t>
+        </is>
+      </c>
+      <c r="E57" s="10" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="F57" s="10" t="inlineStr">
+        <is>
+          <t>sector=Healthcare, size=mid, drawdown_</t>
+        </is>
+      </c>
+    </row>
+    <row r="58" ht="22" customHeight="1">
+      <c r="A58" s="6" t="inlineStr">
+        <is>
+          <t>LUCY</t>
+        </is>
+      </c>
+      <c r="B58" s="7" t="inlineStr">
+        <is>
+          <t>Innovative Eyewear,</t>
+        </is>
+      </c>
+      <c r="C58" s="16" t="n">
+        <v>20</v>
+      </c>
+      <c r="D58" s="7" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="E58" s="16" t="n">
+        <v>45.6</v>
+      </c>
+      <c r="F58" s="7" t="inlineStr">
+        <is>
+          <t>sector=Healthcare, size=micro, drawdow</t>
+        </is>
+      </c>
+    </row>
+    <row r="59" ht="22" customHeight="1">
+      <c r="A59" s="9" t="inlineStr">
+        <is>
+          <t>PMCB</t>
+        </is>
+      </c>
+      <c r="B59" s="10" t="inlineStr">
+        <is>
+          <t>PharmaCyte  Biotech,</t>
+        </is>
+      </c>
+      <c r="C59" s="17" t="n">
+        <v>20</v>
+      </c>
+      <c r="D59" s="10" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="E59" s="17" t="n">
+        <v>30</v>
+      </c>
+      <c r="F59" s="10" t="inlineStr">
+        <is>
+          <t>sector=Healthcare, size=micro, drawdow</t>
+        </is>
+      </c>
+    </row>
+    <row r="60" ht="22" customHeight="1">
+      <c r="A60" s="6" t="inlineStr">
         <is>
           <t>FWDI</t>
         </is>
       </c>
-      <c r="B31" s="7" t="inlineStr">
+      <c r="B60" s="7" t="inlineStr">
         <is>
           <t>Forward Industries,</t>
         </is>
       </c>
-      <c r="C31" s="16" t="n">
-        <v>40</v>
-      </c>
-      <c r="D31" s="7" t="inlineStr">
+      <c r="C60" s="16" t="n">
+        <v>19</v>
+      </c>
+      <c r="D60" s="7" t="inlineStr">
         <is>
           <t>CONFIRMED</t>
         </is>
       </c>
-      <c r="E31" s="16" t="n">
+      <c r="E60" s="16" t="n">
         <v>12.9</v>
       </c>
-      <c r="F31" s="7" t="inlineStr">
-        <is>
-          <t>catalyst=SALE_OF_COMPANY, sector=Consu</t>
-        </is>
-      </c>
-    </row>
-    <row r="32" ht="22" customHeight="1">
-      <c r="A32" s="9" t="inlineStr">
-        <is>
-          <t>PAR</t>
-        </is>
-      </c>
-      <c r="B32" s="10" t="inlineStr">
-        <is>
-          <t>PAR Technology Corpo</t>
-        </is>
-      </c>
-      <c r="C32" s="17" t="n">
-        <v>37</v>
-      </c>
-      <c r="D32" s="10" t="inlineStr">
+      <c r="F60" s="7" t="inlineStr">
+        <is>
+          <t>catalyst=SALE_OF_COMPANY, drawdown_12m</t>
+        </is>
+      </c>
+    </row>
+    <row r="61" ht="22" customHeight="1">
+      <c r="A61" s="9" t="inlineStr">
+        <is>
+          <t>LAB</t>
+        </is>
+      </c>
+      <c r="B61" s="10" t="inlineStr">
+        <is>
+          <t>Standard BioTools In</t>
+        </is>
+      </c>
+      <c r="C61" s="17" t="n">
+        <v>19</v>
+      </c>
+      <c r="D61" s="10" t="inlineStr">
+        <is>
+          <t>NEUTRAL</t>
+        </is>
+      </c>
+      <c r="E61" s="17" t="n">
+        <v>42.3</v>
+      </c>
+      <c r="F61" s="10" t="inlineStr">
+        <is>
+          <t>catalyst=ASSET_SALE, sector=Healthcare</t>
+        </is>
+      </c>
+    </row>
+    <row r="62" ht="22" customHeight="1">
+      <c r="A62" s="6" t="inlineStr">
+        <is>
+          <t>PRGO</t>
+        </is>
+      </c>
+      <c r="B62" s="7" t="inlineStr">
+        <is>
+          <t>Perrigo Company plc</t>
+        </is>
+      </c>
+      <c r="C62" s="16" t="n">
+        <v>19</v>
+      </c>
+      <c r="D62" s="7" t="inlineStr">
         <is>
           <t>CONFIRMED</t>
         </is>
       </c>
-      <c r="E32" s="17" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="F32" s="10" t="inlineStr">
-        <is>
-          <t>sector=Technology, size=small, drawdow</t>
-        </is>
-      </c>
-    </row>
-    <row r="33" ht="22" customHeight="1">
-      <c r="A33" s="6" t="inlineStr">
-        <is>
-          <t>ALKT</t>
-        </is>
-      </c>
-      <c r="B33" s="7" t="inlineStr">
-        <is>
-          <t>Alkami Technology, I</t>
-        </is>
-      </c>
-      <c r="C33" s="16" t="n">
-        <v>37</v>
-      </c>
-      <c r="D33" s="7" t="inlineStr">
-        <is>
-          <t>NEUTRAL</t>
-        </is>
-      </c>
-      <c r="E33" s="7" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="F33" s="7" t="inlineStr">
-        <is>
-          <t>sector=Technology, size=small, drawdow</t>
-        </is>
-      </c>
-    </row>
-    <row r="34" ht="22" customHeight="1">
-      <c r="A34" s="9" t="inlineStr">
-        <is>
-          <t>PD</t>
-        </is>
-      </c>
-      <c r="B34" s="10" t="inlineStr">
-        <is>
-          <t>PagerDuty, Inc.</t>
-        </is>
-      </c>
-      <c r="C34" s="17" t="n">
-        <v>37</v>
-      </c>
-      <c r="D34" s="10" t="inlineStr">
+      <c r="E62" s="16" t="n">
+        <v>25.6</v>
+      </c>
+      <c r="F62" s="7" t="inlineStr">
+        <is>
+          <t>catalyst=ASSET_SALE, sector=Healthcare</t>
+        </is>
+      </c>
+    </row>
+    <row r="63" ht="22" customHeight="1">
+      <c r="A63" s="9" t="inlineStr">
+        <is>
+          <t>CERT</t>
+        </is>
+      </c>
+      <c r="B63" s="10" t="inlineStr">
+        <is>
+          <t>Certara, Inc.</t>
+        </is>
+      </c>
+      <c r="C63" s="17" t="n">
+        <v>19</v>
+      </c>
+      <c r="D63" s="10" t="inlineStr">
         <is>
           <t>CONFIRMED</t>
         </is>
       </c>
-      <c r="E34" s="17" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="F34" s="10" t="inlineStr">
-        <is>
-          <t>sector=Technology, size=small, drawdow</t>
-        </is>
-      </c>
-    </row>
-    <row r="35" ht="22" customHeight="1">
-      <c r="A35" s="6" t="inlineStr">
-        <is>
-          <t>TASK</t>
-        </is>
-      </c>
-      <c r="B35" s="7" t="inlineStr">
-        <is>
-          <t>TaskUs, Inc.</t>
-        </is>
-      </c>
-      <c r="C35" s="16" t="n">
-        <v>37</v>
-      </c>
-      <c r="D35" s="7" t="inlineStr">
-        <is>
-          <t>CONFIRMED</t>
-        </is>
-      </c>
-      <c r="E35" s="16" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="F35" s="7" t="inlineStr">
-        <is>
-          <t>sector=Technology, size=small, drawdow</t>
-        </is>
-      </c>
-    </row>
-    <row r="36" ht="22" customHeight="1">
-      <c r="A36" s="9" t="inlineStr">
-        <is>
-          <t>OPTU</t>
-        </is>
-      </c>
-      <c r="B36" s="10" t="inlineStr">
-        <is>
-          <t>Optimum Communicatio</t>
-        </is>
-      </c>
-      <c r="C36" s="17" t="n">
-        <v>35</v>
-      </c>
-      <c r="D36" s="10" t="inlineStr">
-        <is>
-          <t>NEUTRAL</t>
-        </is>
-      </c>
-      <c r="E36" s="17" t="n">
-        <v>3</v>
-      </c>
-      <c r="F36" s="10" t="inlineStr">
-        <is>
-          <t>catalyst=SALE_OF_COMPANY, size=small,</t>
-        </is>
-      </c>
-    </row>
-    <row r="37" ht="22" customHeight="1">
-      <c r="A37" s="6" t="inlineStr">
-        <is>
-          <t>ORBS</t>
-        </is>
-      </c>
-      <c r="B37" s="7" t="inlineStr">
-        <is>
-          <t>Eightco Holdings Inc</t>
-        </is>
-      </c>
-      <c r="C37" s="16" t="n">
-        <v>35</v>
-      </c>
-      <c r="D37" s="7" t="inlineStr">
+      <c r="E63" s="17" t="n">
+        <v>10.7</v>
+      </c>
+      <c r="F63" s="10" t="inlineStr">
+        <is>
+          <t>catalyst=ASSET_SALE, sector=Healthcare</t>
+        </is>
+      </c>
+    </row>
+    <row r="64" ht="22" customHeight="1">
+      <c r="A64" s="6" t="inlineStr">
+        <is>
+          <t>FIS</t>
+        </is>
+      </c>
+      <c r="B64" s="7" t="inlineStr">
+        <is>
+          <t>Fidelity National In</t>
+        </is>
+      </c>
+      <c r="C64" s="16" t="n">
+        <v>19</v>
+      </c>
+      <c r="D64" s="7" t="inlineStr">
         <is>
           <t>FADING</t>
         </is>
       </c>
-      <c r="E37" s="16" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="F37" s="7" t="inlineStr">
-        <is>
-          <t>sector=Consumer Cyclical, size=small,</t>
-        </is>
-      </c>
-    </row>
-    <row r="38" ht="22" customHeight="1">
-      <c r="A38" s="9" t="inlineStr">
-        <is>
-          <t>CWH</t>
-        </is>
-      </c>
-      <c r="B38" s="10" t="inlineStr">
-        <is>
-          <t>Camping World Holdin</t>
-        </is>
-      </c>
-      <c r="C38" s="17" t="n">
-        <v>35</v>
-      </c>
-      <c r="D38" s="10" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="E38" s="17" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="F38" s="10" t="inlineStr">
-        <is>
-          <t>sector=Consumer Cyclical, size=small,</t>
-        </is>
-      </c>
-    </row>
-    <row r="39" ht="22" customHeight="1">
-      <c r="A39" s="6" t="inlineStr">
-        <is>
-          <t>DFH</t>
-        </is>
-      </c>
-      <c r="B39" s="7" t="inlineStr">
-        <is>
-          <t>Dream Finders Homes,</t>
-        </is>
-      </c>
-      <c r="C39" s="16" t="n">
-        <v>35</v>
-      </c>
-      <c r="D39" s="7" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="E39" s="16" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="F39" s="7" t="inlineStr">
-        <is>
-          <t>sector=Consumer Cyclical, size=small,</t>
-        </is>
-      </c>
-    </row>
-    <row r="40" ht="22" customHeight="1">
-      <c r="A40" s="9" t="inlineStr">
-        <is>
-          <t>AIRE</t>
-        </is>
-      </c>
-      <c r="B40" s="10" t="inlineStr">
-        <is>
-          <t>reAlpha Tech Corp.</t>
-        </is>
-      </c>
-      <c r="C40" s="17" t="n">
-        <v>35</v>
-      </c>
-      <c r="D40" s="10" t="inlineStr">
-        <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="E40" s="10" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="F40" s="10" t="inlineStr">
-        <is>
-          <t>catalyst=SALE_OF_COMPANY, sector=Real</t>
-        </is>
-      </c>
-    </row>
-    <row r="41" ht="22" customHeight="1">
-      <c r="A41" s="6" t="inlineStr">
-        <is>
-          <t>MNRO</t>
-        </is>
-      </c>
-      <c r="B41" s="7" t="inlineStr">
-        <is>
-          <t>Monro, Inc.</t>
-        </is>
-      </c>
-      <c r="C41" s="16" t="n">
-        <v>34</v>
-      </c>
-      <c r="D41" s="7" t="inlineStr">
-        <is>
-          <t>FADING</t>
-        </is>
-      </c>
-      <c r="E41" s="16" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="F41" s="7" t="inlineStr">
-        <is>
-          <t>catalyst=SALE_OF_COMPANY, sector=Consu</t>
-        </is>
-      </c>
-    </row>
-    <row r="42" ht="22" customHeight="1">
-      <c r="A42" s="9" t="inlineStr">
-        <is>
-          <t>LE</t>
-        </is>
-      </c>
-      <c r="B42" s="10" t="inlineStr">
-        <is>
-          <t>Lands' End, Inc.</t>
-        </is>
-      </c>
-      <c r="C42" s="17" t="n">
-        <v>34</v>
-      </c>
-      <c r="D42" s="10" t="inlineStr">
-        <is>
-          <t>NEUTRAL</t>
-        </is>
-      </c>
-      <c r="E42" s="17" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="F42" s="10" t="inlineStr">
-        <is>
-          <t>catalyst=SALE_OF_COMPANY, sector=Consu</t>
-        </is>
-      </c>
-    </row>
-    <row r="43" ht="22" customHeight="1">
-      <c r="A43" s="6" t="inlineStr">
-        <is>
-          <t>LUCK</t>
-        </is>
-      </c>
-      <c r="B43" s="7" t="inlineStr">
-        <is>
-          <t>LUCKY STRIKE ENTERTA</t>
-        </is>
-      </c>
-      <c r="C43" s="16" t="n">
-        <v>34</v>
-      </c>
-      <c r="D43" s="7" t="inlineStr">
-        <is>
-          <t>FADING</t>
-        </is>
-      </c>
-      <c r="E43" s="7" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="F43" s="7" t="inlineStr">
-        <is>
-          <t>catalyst=SALE_OF_COMPANY, sector=Consu</t>
-        </is>
-      </c>
-    </row>
-    <row r="44" ht="22" customHeight="1">
-      <c r="A44" s="9" t="inlineStr">
-        <is>
-          <t>SUNE</t>
-        </is>
-      </c>
-      <c r="B44" s="10" t="inlineStr">
-        <is>
-          <t>SUNation Energy, Inc</t>
-        </is>
-      </c>
-      <c r="C44" s="17" t="n">
-        <v>34</v>
-      </c>
-      <c r="D44" s="10" t="inlineStr">
-        <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="E44" s="17" t="n">
-        <v>60</v>
-      </c>
-      <c r="F44" s="10" t="inlineStr">
-        <is>
-          <t>catalyst=SALE_OF_COMPANY, sector=Techn</t>
-        </is>
-      </c>
-    </row>
-    <row r="45" ht="22" customHeight="1">
-      <c r="A45" s="6" t="inlineStr">
-        <is>
-          <t>JTAI</t>
-        </is>
-      </c>
-      <c r="B45" s="7" t="inlineStr">
-        <is>
-          <t>Jet.AI Inc.</t>
-        </is>
-      </c>
-      <c r="C45" s="16" t="n">
-        <v>34</v>
-      </c>
-      <c r="D45" s="7" t="inlineStr">
-        <is>
-          <t>FADING</t>
-        </is>
-      </c>
-      <c r="E45" s="16" t="n">
-        <v>60</v>
-      </c>
-      <c r="F45" s="7" t="inlineStr">
-        <is>
-          <t>catalyst=SALE_OF_COMPANY, sector=Techn</t>
-        </is>
-      </c>
-    </row>
-    <row r="46" ht="22" customHeight="1">
-      <c r="A46" s="9" t="inlineStr">
-        <is>
-          <t>CLVT</t>
-        </is>
-      </c>
-      <c r="B46" s="10" t="inlineStr">
-        <is>
-          <t>Clarivate Plc</t>
-        </is>
-      </c>
-      <c r="C46" s="17" t="n">
-        <v>33</v>
-      </c>
-      <c r="D46" s="10" t="inlineStr">
-        <is>
-          <t>NEUTRAL</t>
-        </is>
-      </c>
-      <c r="E46" s="17" t="n">
-        <v>60</v>
-      </c>
-      <c r="F46" s="10" t="inlineStr">
-        <is>
-          <t>sector=Technology, size=small, drawdow</t>
-        </is>
-      </c>
-    </row>
-    <row r="47" ht="22" customHeight="1">
-      <c r="A47" s="6" t="inlineStr">
-        <is>
-          <t>BLND</t>
-        </is>
-      </c>
-      <c r="B47" s="7" t="inlineStr">
-        <is>
-          <t>Blend Labs, Inc.</t>
-        </is>
-      </c>
-      <c r="C47" s="16" t="n">
-        <v>33</v>
-      </c>
-      <c r="D47" s="7" t="inlineStr">
-        <is>
-          <t>NEUTRAL</t>
-        </is>
-      </c>
-      <c r="E47" s="7" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="F47" s="7" t="inlineStr">
-        <is>
-          <t>sector=Technology, size=small, drawdow</t>
-        </is>
-      </c>
-    </row>
-    <row r="48" ht="22" customHeight="1">
-      <c r="A48" s="9" t="inlineStr">
-        <is>
-          <t>DXLG</t>
-        </is>
-      </c>
-      <c r="B48" s="10" t="inlineStr">
-        <is>
-          <t>Destination XL Group</t>
-        </is>
-      </c>
-      <c r="C48" s="17" t="n">
-        <v>32</v>
-      </c>
-      <c r="D48" s="10" t="inlineStr">
-        <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="E48" s="17" t="n">
-        <v>60</v>
-      </c>
-      <c r="F48" s="10" t="inlineStr">
-        <is>
-          <t>catalyst=SALE_OF_COMPANY, sector=Consu</t>
-        </is>
-      </c>
-    </row>
-    <row r="49" ht="22" customHeight="1">
-      <c r="A49" s="6" t="inlineStr">
-        <is>
-          <t>FPH</t>
-        </is>
-      </c>
-      <c r="B49" s="7" t="inlineStr">
-        <is>
-          <t>Five Point Holdings,</t>
-        </is>
-      </c>
-      <c r="C49" s="16" t="n">
-        <v>32</v>
-      </c>
-      <c r="D49" s="7" t="inlineStr">
-        <is>
-          <t>NEUTRAL</t>
-        </is>
-      </c>
-      <c r="E49" s="16" t="n">
-        <v>45.8</v>
-      </c>
-      <c r="F49" s="7" t="inlineStr">
-        <is>
-          <t>sector=Real Estate, size=small, drawdo</t>
-        </is>
-      </c>
-    </row>
-    <row r="50" ht="22" customHeight="1">
-      <c r="A50" s="9" t="inlineStr">
-        <is>
-          <t>SITC</t>
-        </is>
-      </c>
-      <c r="B50" s="10" t="inlineStr">
-        <is>
-          <t>SITE Centers Corp.</t>
-        </is>
-      </c>
-      <c r="C50" s="17" t="n">
-        <v>32</v>
-      </c>
-      <c r="D50" s="10" t="inlineStr">
-        <is>
-          <t>NEUTRAL</t>
-        </is>
-      </c>
-      <c r="E50" s="17" t="n">
+      <c r="E64" s="16" t="n">
         <v>2.8</v>
       </c>
-      <c r="F50" s="10" t="inlineStr">
-        <is>
-          <t>catalyst=SPINOFF, sector=Real Estate,</t>
-        </is>
-      </c>
-    </row>
-    <row r="51" ht="22" customHeight="1">
-      <c r="A51" s="6" t="inlineStr">
-        <is>
-          <t>FMC</t>
-        </is>
-      </c>
-      <c r="B51" s="7" t="inlineStr">
-        <is>
-          <t>FMC Corporation</t>
-        </is>
-      </c>
-      <c r="C51" s="16" t="n">
-        <v>31</v>
-      </c>
-      <c r="D51" s="7" t="inlineStr">
-        <is>
-          <t>NEUTRAL</t>
-        </is>
-      </c>
-      <c r="E51" s="16" t="n">
-        <v>6.1</v>
-      </c>
-      <c r="F51" s="7" t="inlineStr">
-        <is>
-          <t>sector=Basic Materials, size=small, dr</t>
-        </is>
-      </c>
-    </row>
-    <row r="52" ht="22" customHeight="1">
-      <c r="A52" s="9" t="inlineStr">
-        <is>
-          <t>DXC</t>
-        </is>
-      </c>
-      <c r="B52" s="10" t="inlineStr">
-        <is>
-          <t>DXC Technology Compa</t>
-        </is>
-      </c>
-      <c r="C52" s="17" t="n">
-        <v>31</v>
-      </c>
-      <c r="D52" s="10" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="E52" s="17" t="n">
-        <v>30</v>
-      </c>
-      <c r="F52" s="10" t="inlineStr">
-        <is>
-          <t>sector=Technology, size=small, drawdow</t>
-        </is>
-      </c>
-    </row>
-    <row r="53" ht="22" customHeight="1">
-      <c r="A53" s="6" t="inlineStr">
-        <is>
-          <t>IBEX</t>
-        </is>
-      </c>
-      <c r="B53" s="7" t="inlineStr">
-        <is>
-          <t>IBEX Limited</t>
-        </is>
-      </c>
-      <c r="C53" s="16" t="n">
-        <v>31</v>
-      </c>
-      <c r="D53" s="7" t="inlineStr">
-        <is>
-          <t>CONFIRMED</t>
-        </is>
-      </c>
-      <c r="E53" s="16" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="F53" s="7" t="inlineStr">
-        <is>
-          <t>sector=Technology, size=small, drawdow</t>
-        </is>
-      </c>
-    </row>
-    <row r="54" ht="22" customHeight="1">
-      <c r="A54" s="9" t="inlineStr">
-        <is>
-          <t>IIIV</t>
-        </is>
-      </c>
-      <c r="B54" s="10" t="inlineStr">
-        <is>
-          <t>i3 Verticals, Inc.</t>
-        </is>
-      </c>
-      <c r="C54" s="17" t="n">
-        <v>31</v>
-      </c>
-      <c r="D54" s="10" t="inlineStr">
-        <is>
-          <t>FADING</t>
-        </is>
-      </c>
-      <c r="E54" s="17" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="F54" s="10" t="inlineStr">
-        <is>
-          <t>sector=Technology, size=small, drawdow</t>
-        </is>
-      </c>
-    </row>
-    <row r="55" ht="22" customHeight="1">
-      <c r="A55" s="6" t="inlineStr">
-        <is>
-          <t>VREOF</t>
-        </is>
-      </c>
-      <c r="B55" s="7" t="inlineStr">
-        <is>
-          <t>VIREO GROWTH INC.</t>
-        </is>
-      </c>
-      <c r="C55" s="16" t="n">
-        <v>30</v>
-      </c>
-      <c r="D55" s="7" t="inlineStr">
-        <is>
-          <t>NEUTRAL</t>
-        </is>
-      </c>
-      <c r="E55" s="16" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="F55" s="7" t="inlineStr">
-        <is>
-          <t>catalyst=SALE_OF_COMPANY, size=small,</t>
-        </is>
-      </c>
-    </row>
-    <row r="56" ht="22" customHeight="1">
-      <c r="A56" s="9" t="inlineStr">
-        <is>
-          <t>SIGA</t>
-        </is>
-      </c>
-      <c r="B56" s="10" t="inlineStr">
-        <is>
-          <t>SIGA Technologies In</t>
-        </is>
-      </c>
-      <c r="C56" s="17" t="n">
-        <v>30</v>
-      </c>
-      <c r="D56" s="10" t="inlineStr">
-        <is>
-          <t>NEUTRAL</t>
-        </is>
-      </c>
-      <c r="E56" s="17" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="F56" s="10" t="inlineStr">
-        <is>
-          <t>size=small, drawdown_12m=deep(&lt;-50%),</t>
-        </is>
-      </c>
-    </row>
-    <row r="57" ht="22" customHeight="1">
-      <c r="A57" s="6" t="inlineStr">
-        <is>
-          <t>LMRI</t>
-        </is>
-      </c>
-      <c r="B57" s="7" t="inlineStr">
-        <is>
-          <t>Lumexa Imaging Holdi</t>
-        </is>
-      </c>
-      <c r="C57" s="16" t="n">
-        <v>30</v>
-      </c>
-      <c r="D57" s="7" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="E57" s="16" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="F57" s="7" t="inlineStr">
-        <is>
-          <t>size=small, drawdown_12m=deep(&lt;-50%),</t>
-        </is>
-      </c>
-    </row>
-    <row r="58" ht="22" customHeight="1">
-      <c r="A58" s="9" t="inlineStr">
-        <is>
-          <t>ANGX</t>
-        </is>
-      </c>
-      <c r="B58" s="10" t="inlineStr">
-        <is>
-          <t>Angel Studios, Inc.</t>
-        </is>
-      </c>
-      <c r="C58" s="17" t="n">
-        <v>30</v>
-      </c>
-      <c r="D58" s="10" t="inlineStr">
-        <is>
-          <t>CONFIRMED</t>
-        </is>
-      </c>
-      <c r="E58" s="10" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="F58" s="10" t="inlineStr">
-        <is>
-          <t>size=small, drawdown_12m=deep(&lt;-50%),</t>
-        </is>
-      </c>
-    </row>
-    <row r="59" ht="22" customHeight="1">
-      <c r="A59" s="6" t="inlineStr">
-        <is>
-          <t>UPWK</t>
-        </is>
-      </c>
-      <c r="B59" s="7" t="inlineStr">
-        <is>
-          <t>Upwork Inc.</t>
-        </is>
-      </c>
-      <c r="C59" s="16" t="n">
-        <v>30</v>
-      </c>
-      <c r="D59" s="7" t="inlineStr">
-        <is>
-          <t>FADING</t>
-        </is>
-      </c>
-      <c r="E59" s="7" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="F59" s="7" t="inlineStr">
-        <is>
-          <t>size=small, drawdown_12m=deep(&lt;-50%),</t>
-        </is>
-      </c>
-    </row>
-    <row r="60" ht="22" customHeight="1">
-      <c r="A60" s="9" t="inlineStr">
-        <is>
-          <t>FOXF</t>
-        </is>
-      </c>
-      <c r="B60" s="10" t="inlineStr">
-        <is>
-          <t>Fox Factory Holding</t>
-        </is>
-      </c>
-      <c r="C60" s="17" t="n">
-        <v>29</v>
-      </c>
-      <c r="D60" s="10" t="inlineStr">
-        <is>
-          <t>NEUTRAL</t>
-        </is>
-      </c>
-      <c r="E60" s="17" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="F60" s="10" t="inlineStr">
-        <is>
-          <t>sector=Consumer Cyclical, size=small,</t>
-        </is>
-      </c>
-    </row>
-    <row r="61" ht="22" customHeight="1">
-      <c r="A61" s="6" t="inlineStr">
-        <is>
-          <t>ARHS</t>
-        </is>
-      </c>
-      <c r="B61" s="7" t="inlineStr">
-        <is>
-          <t>Arhaus, Inc.</t>
-        </is>
-      </c>
-      <c r="C61" s="16" t="n">
-        <v>29</v>
-      </c>
-      <c r="D61" s="7" t="inlineStr">
-        <is>
-          <t>NEUTRAL</t>
-        </is>
-      </c>
-      <c r="E61" s="16" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="F61" s="7" t="inlineStr">
-        <is>
-          <t>sector=Consumer Cyclical, size=small,</t>
-        </is>
-      </c>
-    </row>
-    <row r="62" ht="22" customHeight="1">
-      <c r="A62" s="9" t="inlineStr">
-        <is>
-          <t>TTEC</t>
-        </is>
-      </c>
-      <c r="B62" s="10" t="inlineStr">
-        <is>
-          <t>TTEC Holdings, Inc.</t>
-        </is>
-      </c>
-      <c r="C62" s="17" t="n">
-        <v>29</v>
-      </c>
-      <c r="D62" s="10" t="inlineStr">
-        <is>
-          <t>NEUTRAL</t>
-        </is>
-      </c>
-      <c r="E62" s="17" t="n">
-        <v>20.3</v>
-      </c>
-      <c r="F62" s="10" t="inlineStr">
-        <is>
-          <t>sector=Technology, size=micro, drawdow</t>
-        </is>
-      </c>
-    </row>
-    <row r="63" ht="22" customHeight="1">
-      <c r="A63" s="6" t="inlineStr">
-        <is>
-          <t>ETD</t>
-        </is>
-      </c>
-      <c r="B63" s="7" t="inlineStr">
-        <is>
-          <t>Ethan Allen Interior</t>
-        </is>
-      </c>
-      <c r="C63" s="16" t="n">
-        <v>29</v>
-      </c>
-      <c r="D63" s="7" t="inlineStr">
-        <is>
-          <t>NEUTRAL</t>
-        </is>
-      </c>
-      <c r="E63" s="16" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="F63" s="7" t="inlineStr">
-        <is>
-          <t>sector=Consumer Cyclical, size=small,</t>
-        </is>
-      </c>
-    </row>
-    <row r="64" ht="22" customHeight="1">
-      <c r="A64" s="9" t="inlineStr">
-        <is>
-          <t>GRNT</t>
-        </is>
-      </c>
-      <c r="B64" s="10" t="inlineStr">
-        <is>
-          <t>Granite Ridge Resour</t>
-        </is>
-      </c>
-      <c r="C64" s="17" t="n">
-        <v>29</v>
-      </c>
-      <c r="D64" s="10" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="E64" s="17" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="F64" s="10" t="inlineStr">
-        <is>
-          <t>sector=Energy, size=small, drawdown_12</t>
-        </is>
-      </c>
-    </row>
-    <row r="65" ht="22" customHeight="1">
-      <c r="A65" s="6" t="inlineStr">
-        <is>
-          <t>AGPU</t>
-        </is>
-      </c>
-      <c r="B65" s="7" t="inlineStr">
-        <is>
-          <t>Axe Compute Inc.</t>
-        </is>
-      </c>
-      <c r="C65" s="16" t="n">
-        <v>29</v>
-      </c>
-      <c r="D65" s="7" t="inlineStr">
-        <is>
-          <t>CONFIRMED</t>
-        </is>
-      </c>
-      <c r="E65" s="16" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="F65" s="7" t="inlineStr">
-        <is>
-          <t>sector=Technology, size=micro, drawdow</t>
-        </is>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" s="12" t="inlineStr">
-        <is>
-          <t>WHAT RAISES TAIL ODDS (historical lift vs 15% base)</t>
-        </is>
-      </c>
-    </row>
-    <row r="68" ht="18" customHeight="1">
-      <c r="A68" s="4" t="inlineStr">
+      <c r="F64" s="7" t="inlineStr">
+        <is>
+          <t>catalyst=SPINOFF, sector=Technology, d</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="12" t="inlineStr">
+        <is>
+          <t>WHAT RAISES TAIL ODDS (historical lift vs 10% base)</t>
+        </is>
+      </c>
+    </row>
+    <row r="67" ht="18" customHeight="1">
+      <c r="A67" s="4" t="inlineStr">
         <is>
           <t>Feature = bin</t>
         </is>
       </c>
-      <c r="B68" s="4" t="inlineStr">
+      <c r="B67" s="4" t="inlineStr">
         <is>
           <t>Tail rate</t>
         </is>
       </c>
-      <c r="C68" s="4" t="inlineStr">
+      <c r="C67" s="4" t="inlineStr">
         <is>
           <t>Lift</t>
         </is>
       </c>
-      <c r="D68" s="4" t="inlineStr">
+      <c r="D67" s="4" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="E68" s="15" t="inlineStr"/>
+      <c r="E67" s="15" t="inlineStr"/>
+    </row>
+    <row r="68" ht="16" customHeight="1">
+      <c r="A68" s="9" t="inlineStr">
+        <is>
+          <t>catalyst = SALE_OF_COMPANY</t>
+        </is>
+      </c>
+      <c r="B68" s="17" t="n">
+        <v>25</v>
+      </c>
+      <c r="C68" s="10" t="inlineStr">
+        <is>
+          <t>2.53x</t>
+        </is>
+      </c>
+      <c r="D68" s="8" t="n">
+        <v>8</v>
+      </c>
+      <c r="E68" s="10" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
     </row>
     <row r="69" ht="16" customHeight="1">
       <c r="A69" s="6" t="inlineStr">
         <is>
-          <t>size = small</t>
+          <t>sector = Basic Materials</t>
         </is>
       </c>
       <c r="B69" s="16" t="n">
-        <v>38</v>
+        <v>23</v>
       </c>
       <c r="C69" s="7" t="inlineStr">
         <is>
-          <t>2.49x</t>
+          <t>2.34x</t>
         </is>
       </c>
       <c r="D69" s="5" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="E69" s="7" t="inlineStr">
         <is>
@@ -10187,15 +10378,15 @@
         </is>
       </c>
       <c r="B70" s="17" t="n">
-        <v>32</v>
+        <v>19</v>
       </c>
       <c r="C70" s="10" t="inlineStr">
         <is>
-          <t>2.11x</t>
+          <t>1.92x</t>
         </is>
       </c>
       <c r="D70" s="8" t="n">
-        <v>22</v>
+        <v>37</v>
       </c>
       <c r="E70" s="10" t="inlineStr">
         <is>
@@ -10206,19 +10397,19 @@
     <row r="71" ht="16" customHeight="1">
       <c r="A71" s="6" t="inlineStr">
         <is>
-          <t>sector = Real Estate</t>
+          <t>sector = Healthcare</t>
         </is>
       </c>
       <c r="B71" s="16" t="n">
-        <v>33</v>
+        <v>19</v>
       </c>
       <c r="C71" s="7" t="inlineStr">
         <is>
-          <t>2.22x</t>
+          <t>1.95x</t>
         </is>
       </c>
       <c r="D71" s="5" t="n">
-        <v>3</v>
+        <v>26</v>
       </c>
       <c r="E71" s="7" t="inlineStr">
         <is>
@@ -10229,19 +10420,19 @@
     <row r="72" ht="16" customHeight="1">
       <c r="A72" s="9" t="inlineStr">
         <is>
-          <t>sector = Technology</t>
+          <t>catalyst = STRATEGIC_REVIEW</t>
         </is>
       </c>
       <c r="B72" s="17" t="n">
-        <v>30</v>
+        <v>16</v>
       </c>
       <c r="C72" s="10" t="inlineStr">
         <is>
-          <t>1.99x</t>
+          <t>1.62x</t>
         </is>
       </c>
       <c r="D72" s="8" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="E72" s="10" t="inlineStr">
         <is>
@@ -10252,19 +10443,19 @@
     <row r="73" ht="16" customHeight="1">
       <c r="A73" s="6" t="inlineStr">
         <is>
-          <t>catalyst = SALE_OF_COMPANY</t>
+          <t>catalyst = SPINOFF</t>
         </is>
       </c>
       <c r="B73" s="16" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="C73" s="7" t="inlineStr">
         <is>
-          <t>1.66x</t>
+          <t>1.56x</t>
         </is>
       </c>
       <c r="D73" s="5" t="n">
-        <v>8</v>
+        <v>39</v>
       </c>
       <c r="E73" s="7" t="inlineStr">
         <is>
@@ -10275,19 +10466,19 @@
     <row r="74" ht="16" customHeight="1">
       <c r="A74" s="9" t="inlineStr">
         <is>
-          <t>range_pos = low</t>
+          <t>sector = Technology</t>
         </is>
       </c>
       <c r="B74" s="17" t="n">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="C74" s="10" t="inlineStr">
         <is>
-          <t>1.39x</t>
+          <t>1.50x</t>
         </is>
       </c>
       <c r="D74" s="8" t="n">
-        <v>43</v>
+        <v>27</v>
       </c>
       <c r="E74" s="10" t="inlineStr">
         <is>
@@ -10298,19 +10489,19 @@
     <row r="75" ht="16" customHeight="1">
       <c r="A75" s="6" t="inlineStr">
         <is>
-          <t>catalyst = SPINOFF</t>
+          <t>range_pos = low</t>
         </is>
       </c>
       <c r="B75" s="16" t="n">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="C75" s="7" t="inlineStr">
         <is>
-          <t>1.16x</t>
+          <t>1.24x</t>
         </is>
       </c>
       <c r="D75" s="5" t="n">
-        <v>40</v>
+        <v>106</v>
       </c>
       <c r="E75" s="7" t="inlineStr">
         <is>
@@ -10321,19 +10512,19 @@
     <row r="76" ht="16" customHeight="1">
       <c r="A76" s="9" t="inlineStr">
         <is>
-          <t>pre_12m = down(&lt;-20%)  (needs a wait)</t>
+          <t>size = micro</t>
         </is>
       </c>
       <c r="B76" s="17" t="n">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="C76" s="10" t="inlineStr">
         <is>
-          <t>1.50x</t>
+          <t>1.27x</t>
         </is>
       </c>
       <c r="D76" s="8" t="n">
-        <v>40</v>
+        <v>24</v>
       </c>
       <c r="E76" s="10" t="inlineStr">
         <is>
@@ -10344,30 +10535,76 @@
     <row r="77" ht="16" customHeight="1">
       <c r="A77" s="6" t="inlineStr">
         <is>
+          <t>catalyst = ASSET_SALE</t>
+        </is>
+      </c>
+      <c r="B77" s="16" t="n">
+        <v>11</v>
+      </c>
+      <c r="C77" s="7" t="inlineStr">
+        <is>
+          <t>1.13x</t>
+        </is>
+      </c>
+      <c r="D77" s="5" t="n">
+        <v>36</v>
+      </c>
+      <c r="E77" s="7" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+    </row>
+    <row r="78" ht="16" customHeight="1">
+      <c r="A78" s="9" t="inlineStr">
+        <is>
+          <t>pre_12m = down(&lt;-20%)  (needs a wait)</t>
+        </is>
+      </c>
+      <c r="B78" s="17" t="n">
+        <v>14</v>
+      </c>
+      <c r="C78" s="10" t="inlineStr">
+        <is>
+          <t>1.46x</t>
+        </is>
+      </c>
+      <c r="D78" s="8" t="n">
+        <v>83</v>
+      </c>
+      <c r="E78" s="10" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+    </row>
+    <row r="79" ht="16" customHeight="1">
+      <c r="A79" s="6" t="inlineStr">
+        <is>
           <t>post_1m = up(&gt;+20%)  (needs a wait)</t>
         </is>
       </c>
-      <c r="B77" s="16" t="n">
-        <v>60</v>
-      </c>
-      <c r="C77" s="7" t="inlineStr">
-        <is>
-          <t>3.99x</t>
-        </is>
-      </c>
-      <c r="D77" s="5" t="n">
-        <v>5</v>
-      </c>
-      <c r="E77" s="7" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-    </row>
-    <row r="79" ht="28" customHeight="1">
-      <c r="A79" s="11" t="inlineStr">
-        <is>
-          <t>HOW TO RAISE THE ODDS, from the event study. The right tail is not random: it concentrates in (1) DEEPLY BEATEN-DOWN names — &gt;50% below their 12-month high tailed 32% of the time vs 4% for names near their highs (2.1x); (2) SMALL-CAPS ($300M-2B), 38% tail rate (2.5x) — the high-variance sweet spot; (3) the right SECTORS — Real Estate, Technology, Consumer-Cyclical, Energy — while Financials, Utilities and Staples produced ZERO tails; (4) SALE-OF-COMPANY and SPIN-OFF catalysts over asset sales. Stacking these lifts the tail probability to ~40% (≈2.7x base). THE SINGLE STRONGEST EDGE is not a screen but a RULE: wait ~1 month and enter only names the market voted UP &gt;20% on the catalyst — those tailed 60% of the time (4.0x). Buying the catalyst blind is a coin-flip that loses to SPY on the median; buying beaten-down small-caps in the right sectors AFTER the market confirms is how you tilt into the tail. Modest sample (113 events); directional. Sources: rerate_backtest.py / tail_discriminators.py / tail_odds.py.</t>
+      <c r="B79" s="16" t="n">
+        <v>33</v>
+      </c>
+      <c r="C79" s="7" t="inlineStr">
+        <is>
+          <t>3.38x</t>
+        </is>
+      </c>
+      <c r="D79" s="5" t="n">
+        <v>21</v>
+      </c>
+      <c r="E79" s="7" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+    </row>
+    <row r="81" ht="28" customHeight="1">
+      <c r="A81" s="11" t="inlineStr">
+        <is>
+          <t>HOW TO RAISE THE ODDS, from the 12-type event study (314 events, 10% base tail rate). The right tail concentrates in (1) DEEPLY BEATEN-DOWN names — &gt;50% below their 12-month high tailed 19% vs 7% for names near their highs (1.9x); (2) the right SECTORS — Basic Materials (2.3x), Healthcare (1.9x), Communication Services (1.7x), Technology (1.5x) — while Utilities and Real Estate produced ZERO tails and Financials few; (3) micro/mid-caps over large; (4) the right CATALYSTS — SALE-OF-COMPANY (2.5x, contested-deal tail), STRATEGIC-REVIEW (1.6x lottery) and SPIN-OFF (1.6x); ASSET-SALE has the best MEDIAN (+10%, 58% hit). The backtest also exposed TRAPS to fade: going-private (-37% median), uplisting (-23%, pump-and-fade), capital-return/special-dividend (-11%), exchange-offer (-21%) — all down-weighted in the catalyst engine. THE SINGLE STRONGEST EDGE is not a screen but a RULE: wait ~1 month and enter only names the market voted UP &gt;20% on the catalyst (the Confirmed shortlist above). Buying a catalyst blind loses to SPY on the median (overall -4%); buying beaten-down names in the right sectors AFTER the market confirms is how you tilt into the tail. Directional (n per type 8-51). Sources: rerate_backtest.py / tail_discriminators.py / tail_odds.py.</t>
         </is>
       </c>
     </row>
@@ -10375,7 +10612,7 @@
   <mergeCells count="3">
     <mergeCell ref="A2:F2"/>
     <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A79:F79"/>
+    <mergeCell ref="A81:F81"/>
   </mergeCells>
   <printOptions horizontalCentered="0"/>
   <pageMargins left="0.5" right="0.5" top="0.6" bottom="0.6" header="0.5" footer="0.5"/>

--- a/MOST_ASYMMETRIC.xlsx
+++ b/MOST_ASYMMETRIC.xlsx
@@ -5001,168 +5001,168 @@
     <row r="5" ht="22" customHeight="1">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>SAFE</t>
+          <t>CNDT</t>
         </is>
       </c>
       <c r="B5" s="7" t="inlineStr">
         <is>
-          <t>Safehold Inc. New</t>
+          <t>Conduent Incorporated</t>
         </is>
       </c>
       <c r="C5" s="16" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="D5" s="16" t="n">
         <v>2</v>
       </c>
       <c r="E5" s="16" t="n">
-        <v>31.1</v>
+        <v>60</v>
       </c>
       <c r="F5" s="7" t="inlineStr">
         <is>
-          <t>coiled spring delever, hidden asset realizatio</t>
+          <t>sub cash buyback, asset sale monetization</t>
         </is>
       </c>
     </row>
     <row r="6" ht="22" customHeight="1">
       <c r="A6" s="9" t="inlineStr">
         <is>
-          <t>LUCY</t>
+          <t>SAFE</t>
         </is>
       </c>
       <c r="B6" s="10" t="inlineStr">
         <is>
-          <t>Innovative Eyewear, In</t>
+          <t>Safehold Inc. New</t>
         </is>
       </c>
       <c r="C6" s="17" t="n">
-        <v>22</v>
+        <v>43</v>
       </c>
       <c r="D6" s="17" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E6" s="17" t="n">
-        <v>45.6</v>
+        <v>31.1</v>
       </c>
       <c r="F6" s="10" t="inlineStr">
         <is>
-          <t>sub cash buyback</t>
+          <t>coiled spring delever, hidden asset realizatio</t>
         </is>
       </c>
     </row>
     <row r="7" ht="22" customHeight="1">
       <c r="A7" s="6" t="inlineStr">
         <is>
-          <t>DXC</t>
+          <t>THRY</t>
         </is>
       </c>
       <c r="B7" s="7" t="inlineStr">
         <is>
-          <t>DXC Technology Company</t>
+          <t>Thryv Holdings, Inc.</t>
         </is>
       </c>
       <c r="C7" s="16" t="n">
-        <v>22</v>
+        <v>40.4</v>
       </c>
       <c r="D7" s="16" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E7" s="16" t="n">
-        <v>30</v>
+        <v>10.9</v>
       </c>
       <c r="F7" s="7" t="inlineStr">
         <is>
-          <t>sub cash buyback</t>
+          <t>coiled spring delever, asset sale monetization</t>
         </is>
       </c>
     </row>
     <row r="8" ht="22" customHeight="1">
       <c r="A8" s="9" t="inlineStr">
         <is>
-          <t>PMCB</t>
+          <t>BCIC</t>
         </is>
       </c>
       <c r="B8" s="10" t="inlineStr">
         <is>
-          <t>PharmaCyte  Biotech, I</t>
+          <t>BCP Investment Corpora</t>
         </is>
       </c>
       <c r="C8" s="17" t="n">
-        <v>22</v>
+        <v>39.9</v>
       </c>
       <c r="D8" s="17" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E8" s="17" t="n">
-        <v>30</v>
+        <v>15.4</v>
       </c>
       <c r="F8" s="10" t="inlineStr">
         <is>
-          <t>sub cash buyback</t>
+          <t>hidden asset realization, tender offer squeeze</t>
         </is>
       </c>
     </row>
     <row r="9" ht="22" customHeight="1">
       <c r="A9" s="6" t="inlineStr">
         <is>
-          <t>ACH</t>
+          <t>GTE</t>
         </is>
       </c>
       <c r="B9" s="7" t="inlineStr">
         <is>
-          <t>Accendra Health, Inc.</t>
+          <t>Gran Tierra Energy Inc</t>
         </is>
       </c>
       <c r="C9" s="16" t="n">
-        <v>22</v>
+        <v>35.8</v>
       </c>
       <c r="D9" s="16" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E9" s="16" t="n">
-        <v>60</v>
+        <v>3.8</v>
       </c>
       <c r="F9" s="7" t="inlineStr">
         <is>
-          <t>sub cash buyback</t>
+          <t>asset sale monetization, tender offer squeeze</t>
         </is>
       </c>
     </row>
     <row r="10" ht="22" customHeight="1">
       <c r="A10" s="9" t="inlineStr">
         <is>
-          <t>CNDT</t>
+          <t>CYH</t>
         </is>
       </c>
       <c r="B10" s="10" t="inlineStr">
         <is>
-          <t>Conduent Incorporated</t>
+          <t>Community Health Syste</t>
         </is>
       </c>
       <c r="C10" s="17" t="n">
-        <v>22</v>
+        <v>35.2</v>
       </c>
       <c r="D10" s="17" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E10" s="17" t="n">
-        <v>60</v>
+        <v>3</v>
       </c>
       <c r="F10" s="10" t="inlineStr">
         <is>
-          <t>sub cash buyback</t>
+          <t>asset sale monetization, tender offer squeeze</t>
         </is>
       </c>
     </row>
     <row r="11" ht="22" customHeight="1">
       <c r="A11" s="6" t="inlineStr">
         <is>
-          <t>VISN</t>
+          <t>LUCY</t>
         </is>
       </c>
       <c r="B11" s="7" t="inlineStr">
         <is>
-          <t>Vistance Networks, Inc</t>
+          <t>Innovative Eyewear, In</t>
         </is>
       </c>
       <c r="C11" s="16" t="n">
@@ -5172,7 +5172,7 @@
         <v>1</v>
       </c>
       <c r="E11" s="16" t="n">
-        <v>24.8</v>
+        <v>45.6</v>
       </c>
       <c r="F11" s="7" t="inlineStr">
         <is>
@@ -5183,22 +5183,22 @@
     <row r="12" ht="22" customHeight="1">
       <c r="A12" s="9" t="inlineStr">
         <is>
-          <t>ADNT</t>
+          <t>DXC</t>
         </is>
       </c>
       <c r="B12" s="10" t="inlineStr">
         <is>
-          <t>Adient plc</t>
+          <t>DXC Technology Company</t>
         </is>
       </c>
       <c r="C12" s="17" t="n">
-        <v>20.7</v>
+        <v>22</v>
       </c>
       <c r="D12" s="17" t="n">
         <v>1</v>
       </c>
       <c r="E12" s="17" t="n">
-        <v>6.3</v>
+        <v>30</v>
       </c>
       <c r="F12" s="10" t="inlineStr">
         <is>
@@ -5209,42 +5209,42 @@
     <row r="13" ht="22" customHeight="1">
       <c r="A13" s="6" t="inlineStr">
         <is>
-          <t>SHEN</t>
+          <t>PMCB</t>
         </is>
       </c>
       <c r="B13" s="7" t="inlineStr">
         <is>
-          <t>Shenandoah Telecommuni</t>
+          <t>PharmaCyte  Biotech, I</t>
         </is>
       </c>
       <c r="C13" s="16" t="n">
-        <v>20.3</v>
+        <v>22</v>
       </c>
       <c r="D13" s="16" t="n">
         <v>1</v>
       </c>
       <c r="E13" s="16" t="n">
-        <v>19.5</v>
+        <v>30</v>
       </c>
       <c r="F13" s="7" t="inlineStr">
         <is>
-          <t>hidden asset realization</t>
+          <t>sub cash buyback</t>
         </is>
       </c>
     </row>
     <row r="14" ht="22" customHeight="1">
       <c r="A14" s="9" t="inlineStr">
         <is>
-          <t>GETY</t>
+          <t>ACH</t>
         </is>
       </c>
       <c r="B14" s="10" t="inlineStr">
         <is>
-          <t>Getty Images Holdings,</t>
+          <t>Accendra Health, Inc.</t>
         </is>
       </c>
       <c r="C14" s="17" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="D14" s="17" t="n">
         <v>1</v>
@@ -5254,185 +5254,185 @@
       </c>
       <c r="F14" s="10" t="inlineStr">
         <is>
-          <t>coiled spring delever</t>
+          <t>sub cash buyback</t>
         </is>
       </c>
     </row>
     <row r="15" ht="22" customHeight="1">
       <c r="A15" s="6" t="inlineStr">
         <is>
-          <t>UTZ</t>
+          <t>VISN</t>
         </is>
       </c>
       <c r="B15" s="7" t="inlineStr">
         <is>
-          <t>Utz Brands Inc</t>
+          <t>Vistance Networks, Inc</t>
         </is>
       </c>
       <c r="C15" s="16" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="D15" s="16" t="n">
         <v>1</v>
       </c>
       <c r="E15" s="16" t="n">
-        <v>23.9</v>
+        <v>24.8</v>
       </c>
       <c r="F15" s="7" t="inlineStr">
         <is>
-          <t>coiled spring delever</t>
+          <t>sub cash buyback</t>
         </is>
       </c>
     </row>
     <row r="16" ht="22" customHeight="1">
       <c r="A16" s="9" t="inlineStr">
         <is>
-          <t>MAGN</t>
+          <t>ADNT</t>
         </is>
       </c>
       <c r="B16" s="10" t="inlineStr">
         <is>
-          <t>Magnera Corporation</t>
+          <t>Adient plc</t>
         </is>
       </c>
       <c r="C16" s="17" t="n">
-        <v>20</v>
+        <v>20.7</v>
       </c>
       <c r="D16" s="17" t="n">
         <v>1</v>
       </c>
       <c r="E16" s="17" t="n">
-        <v>60</v>
+        <v>6.3</v>
       </c>
       <c r="F16" s="10" t="inlineStr">
         <is>
-          <t>coiled spring delever</t>
+          <t>sub cash buyback</t>
         </is>
       </c>
     </row>
     <row r="17" ht="22" customHeight="1">
       <c r="A17" s="6" t="inlineStr">
         <is>
-          <t>BALY</t>
+          <t>SHEN</t>
         </is>
       </c>
       <c r="B17" s="7" t="inlineStr">
         <is>
-          <t>Bally's Corporation</t>
+          <t>Shenandoah Telecommuni</t>
         </is>
       </c>
       <c r="C17" s="16" t="n">
-        <v>20</v>
+        <v>20.3</v>
       </c>
       <c r="D17" s="16" t="n">
         <v>1</v>
       </c>
       <c r="E17" s="16" t="n">
-        <v>38.5</v>
+        <v>19.5</v>
       </c>
       <c r="F17" s="7" t="inlineStr">
         <is>
-          <t>coiled spring delever</t>
+          <t>hidden asset realization</t>
         </is>
       </c>
     </row>
     <row r="18" ht="22" customHeight="1">
       <c r="A18" s="9" t="inlineStr">
         <is>
-          <t>BCIC</t>
+          <t>GETY</t>
         </is>
       </c>
       <c r="B18" s="10" t="inlineStr">
         <is>
-          <t>BCP Investment Corpora</t>
+          <t>Getty Images Holdings,</t>
         </is>
       </c>
       <c r="C18" s="17" t="n">
-        <v>19.9</v>
+        <v>20</v>
       </c>
       <c r="D18" s="17" t="n">
         <v>1</v>
       </c>
       <c r="E18" s="17" t="n">
-        <v>15.4</v>
+        <v>60</v>
       </c>
       <c r="F18" s="10" t="inlineStr">
         <is>
-          <t>hidden asset realization</t>
+          <t>coiled spring delever</t>
         </is>
       </c>
     </row>
     <row r="19" ht="22" customHeight="1">
       <c r="A19" s="6" t="inlineStr">
         <is>
-          <t>ULH</t>
+          <t>CLVT</t>
         </is>
       </c>
       <c r="B19" s="7" t="inlineStr">
         <is>
-          <t>Universal Logistics Ho</t>
+          <t>Clarivate Plc</t>
         </is>
       </c>
       <c r="C19" s="16" t="n">
-        <v>19.9</v>
+        <v>20</v>
       </c>
       <c r="D19" s="16" t="n">
         <v>1</v>
       </c>
       <c r="E19" s="16" t="n">
-        <v>9.699999999999999</v>
+        <v>60</v>
       </c>
       <c r="F19" s="7" t="inlineStr">
         <is>
-          <t>hidden asset realization</t>
+          <t>asset sale monetization</t>
         </is>
       </c>
     </row>
     <row r="20" ht="22" customHeight="1">
       <c r="A20" s="9" t="inlineStr">
         <is>
-          <t>PRTA</t>
+          <t>NUS</t>
         </is>
       </c>
       <c r="B20" s="10" t="inlineStr">
         <is>
-          <t>Prothena Corporation p</t>
+          <t>Nu Skin Enterprises, I</t>
         </is>
       </c>
       <c r="C20" s="17" t="n">
-        <v>19.8</v>
+        <v>20</v>
       </c>
       <c r="D20" s="17" t="n">
         <v>1</v>
       </c>
       <c r="E20" s="17" t="n">
-        <v>3.3</v>
+        <v>60</v>
       </c>
       <c r="F20" s="10" t="inlineStr">
         <is>
-          <t>sub cash buyback</t>
+          <t>asset sale monetization</t>
         </is>
       </c>
     </row>
     <row r="21" ht="22" customHeight="1">
       <c r="A21" s="6" t="inlineStr">
         <is>
-          <t>THRY</t>
+          <t>UTZ</t>
         </is>
       </c>
       <c r="B21" s="7" t="inlineStr">
         <is>
-          <t>Thryv Holdings, Inc.</t>
+          <t>Utz Brands Inc</t>
         </is>
       </c>
       <c r="C21" s="16" t="n">
-        <v>18.4</v>
+        <v>20</v>
       </c>
       <c r="D21" s="16" t="n">
         <v>1</v>
       </c>
       <c r="E21" s="16" t="n">
-        <v>10.9</v>
+        <v>23.9</v>
       </c>
       <c r="F21" s="7" t="inlineStr">
         <is>
@@ -5443,126 +5443,126 @@
     <row r="22" ht="22" customHeight="1">
       <c r="A22" s="9" t="inlineStr">
         <is>
-          <t>WKHS</t>
+          <t>LAB</t>
         </is>
       </c>
       <c r="B22" s="10" t="inlineStr">
         <is>
-          <t>Workhorse Group, Inc.</t>
+          <t>Standard BioTools Inc.</t>
         </is>
       </c>
       <c r="C22" s="17" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="D22" s="17" t="n">
         <v>1</v>
       </c>
       <c r="E22" s="17" t="n">
-        <v>7.4</v>
+        <v>42.3</v>
       </c>
       <c r="F22" s="10" t="inlineStr">
         <is>
-          <t>hidden asset realization</t>
+          <t>asset sale monetization</t>
         </is>
       </c>
     </row>
     <row r="23" ht="22" customHeight="1">
       <c r="A23" s="6" t="inlineStr">
         <is>
-          <t>MATV</t>
+          <t>UEIC</t>
         </is>
       </c>
       <c r="B23" s="7" t="inlineStr">
         <is>
-          <t>Mativ Holdings, Inc.</t>
+          <t>Universal Electronics</t>
         </is>
       </c>
       <c r="C23" s="16" t="n">
-        <v>17.6</v>
+        <v>20</v>
       </c>
       <c r="D23" s="16" t="n">
         <v>1</v>
       </c>
       <c r="E23" s="16" t="n">
-        <v>7.1</v>
+        <v>60</v>
       </c>
       <c r="F23" s="7" t="inlineStr">
         <is>
-          <t>coiled spring delever</t>
+          <t>asset sale monetization</t>
         </is>
       </c>
     </row>
     <row r="24" ht="22" customHeight="1">
       <c r="A24" s="9" t="inlineStr">
         <is>
-          <t>DFH</t>
+          <t>MAGN</t>
         </is>
       </c>
       <c r="B24" s="10" t="inlineStr">
         <is>
-          <t>Dream Finders Homes, I</t>
+          <t>Magnera Corporation</t>
         </is>
       </c>
       <c r="C24" s="17" t="n">
-        <v>17.2</v>
+        <v>20</v>
       </c>
       <c r="D24" s="17" t="n">
         <v>1</v>
       </c>
       <c r="E24" s="17" t="n">
-        <v>2.5</v>
+        <v>60</v>
       </c>
       <c r="F24" s="10" t="inlineStr">
         <is>
-          <t>hidden asset realization</t>
+          <t>coiled spring delever</t>
         </is>
       </c>
     </row>
     <row r="25" ht="22" customHeight="1">
       <c r="A25" s="6" t="inlineStr">
         <is>
-          <t>ABM</t>
+          <t>BOC</t>
         </is>
       </c>
       <c r="B25" s="7" t="inlineStr">
         <is>
-          <t>ABM Industries Incorpo</t>
+          <t>Boston Omaha Corporati</t>
         </is>
       </c>
       <c r="C25" s="16" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="D25" s="16" t="n">
         <v>1</v>
       </c>
       <c r="E25" s="16" t="n">
-        <v>4.5</v>
+        <v>60</v>
       </c>
       <c r="F25" s="7" t="inlineStr">
         <is>
-          <t>coiled spring delever</t>
+          <t>asset sale monetization</t>
         </is>
       </c>
     </row>
     <row r="26" ht="22" customHeight="1">
       <c r="A26" s="9" t="inlineStr">
         <is>
-          <t>NWL</t>
+          <t>BALY</t>
         </is>
       </c>
       <c r="B26" s="10" t="inlineStr">
         <is>
-          <t>Newell Brands Inc.</t>
+          <t>Bally's Corporation</t>
         </is>
       </c>
       <c r="C26" s="17" t="n">
-        <v>16.7</v>
+        <v>20</v>
       </c>
       <c r="D26" s="17" t="n">
         <v>1</v>
       </c>
       <c r="E26" s="17" t="n">
-        <v>3.8</v>
+        <v>38.5</v>
       </c>
       <c r="F26" s="10" t="inlineStr">
         <is>
@@ -5573,360 +5573,360 @@
     <row r="27" ht="22" customHeight="1">
       <c r="A27" s="6" t="inlineStr">
         <is>
-          <t>GO</t>
+          <t>HAIN</t>
         </is>
       </c>
       <c r="B27" s="7" t="inlineStr">
         <is>
-          <t>Grocery Outlet Holding</t>
+          <t>The Hain Celestial Gro</t>
         </is>
       </c>
       <c r="C27" s="16" t="n">
-        <v>16</v>
+        <v>19.9</v>
       </c>
       <c r="D27" s="16" t="n">
         <v>1</v>
       </c>
       <c r="E27" s="16" t="n">
-        <v>3.8</v>
+        <v>60</v>
       </c>
       <c r="F27" s="7" t="inlineStr">
         <is>
-          <t>stated unlock triangulated</t>
+          <t>asset sale monetization</t>
         </is>
       </c>
     </row>
     <row r="28" ht="22" customHeight="1">
       <c r="A28" s="9" t="inlineStr">
         <is>
-          <t>CWK</t>
+          <t>ULH</t>
         </is>
       </c>
       <c r="B28" s="10" t="inlineStr">
         <is>
-          <t>Cushman &amp; Wakefield Lt</t>
+          <t>Universal Logistics Ho</t>
         </is>
       </c>
       <c r="C28" s="17" t="n">
-        <v>15.9</v>
+        <v>19.9</v>
       </c>
       <c r="D28" s="17" t="n">
         <v>1</v>
       </c>
       <c r="E28" s="17" t="n">
-        <v>4.4</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="F28" s="10" t="inlineStr">
         <is>
-          <t>coiled spring delever</t>
+          <t>hidden asset realization</t>
         </is>
       </c>
     </row>
     <row r="29" ht="22" customHeight="1">
       <c r="A29" s="6" t="inlineStr">
         <is>
-          <t>TREE</t>
+          <t>PRTA</t>
         </is>
       </c>
       <c r="B29" s="7" t="inlineStr">
         <is>
-          <t>LendingTree, Inc.</t>
+          <t>Prothena Corporation p</t>
         </is>
       </c>
       <c r="C29" s="16" t="n">
-        <v>15.9</v>
+        <v>19.8</v>
       </c>
       <c r="D29" s="16" t="n">
         <v>1</v>
       </c>
       <c r="E29" s="16" t="n">
-        <v>4.2</v>
+        <v>3.3</v>
       </c>
       <c r="F29" s="7" t="inlineStr">
         <is>
-          <t>coiled spring delever</t>
+          <t>sub cash buyback</t>
         </is>
       </c>
     </row>
     <row r="30" ht="22" customHeight="1">
       <c r="A30" s="9" t="inlineStr">
         <is>
-          <t>ASTH</t>
+          <t>PRGO</t>
         </is>
       </c>
       <c r="B30" s="10" t="inlineStr">
         <is>
-          <t>Astrana Health Inc.</t>
+          <t>Perrigo Company plc</t>
         </is>
       </c>
       <c r="C30" s="17" t="n">
-        <v>15.8</v>
+        <v>19</v>
       </c>
       <c r="D30" s="17" t="n">
         <v>1</v>
       </c>
       <c r="E30" s="17" t="n">
-        <v>3.8</v>
+        <v>25.6</v>
       </c>
       <c r="F30" s="10" t="inlineStr">
         <is>
-          <t>coiled spring delever</t>
+          <t>asset sale monetization</t>
         </is>
       </c>
     </row>
     <row r="31" ht="22" customHeight="1">
       <c r="A31" s="6" t="inlineStr">
         <is>
-          <t>UNFI</t>
+          <t>ZSTK</t>
         </is>
       </c>
       <c r="B31" s="7" t="inlineStr">
         <is>
-          <t>United Natural Foods,</t>
+          <t>ZeroStack Corp.</t>
         </is>
       </c>
       <c r="C31" s="16" t="n">
-        <v>15.8</v>
+        <v>18.6</v>
       </c>
       <c r="D31" s="16" t="n">
         <v>1</v>
       </c>
       <c r="E31" s="16" t="n">
-        <v>4</v>
+        <v>60</v>
       </c>
       <c r="F31" s="7" t="inlineStr">
         <is>
-          <t>coiled spring delever</t>
+          <t>asset sale monetization</t>
         </is>
       </c>
     </row>
     <row r="32" ht="22" customHeight="1">
       <c r="A32" s="9" t="inlineStr">
         <is>
-          <t>CWH</t>
+          <t>CMCO</t>
         </is>
       </c>
       <c r="B32" s="10" t="inlineStr">
         <is>
-          <t>Camping World Holdings</t>
+          <t>Columbus McKinnon Corp</t>
         </is>
       </c>
       <c r="C32" s="17" t="n">
-        <v>15.8</v>
+        <v>18.4</v>
       </c>
       <c r="D32" s="17" t="n">
         <v>1</v>
       </c>
       <c r="E32" s="17" t="n">
-        <v>3.8</v>
+        <v>7.1</v>
       </c>
       <c r="F32" s="10" t="inlineStr">
         <is>
-          <t>coiled spring delever</t>
+          <t>asset sale monetization</t>
         </is>
       </c>
     </row>
     <row r="33" ht="22" customHeight="1">
       <c r="A33" s="6" t="inlineStr">
         <is>
-          <t>PK</t>
+          <t>CERT</t>
         </is>
       </c>
       <c r="B33" s="7" t="inlineStr">
         <is>
-          <t>Park Hotels &amp; Resorts</t>
+          <t>Certara, Inc.</t>
         </is>
       </c>
       <c r="C33" s="16" t="n">
-        <v>15.8</v>
+        <v>18.3</v>
       </c>
       <c r="D33" s="16" t="n">
         <v>1</v>
       </c>
       <c r="E33" s="16" t="n">
-        <v>4</v>
+        <v>10.7</v>
       </c>
       <c r="F33" s="7" t="inlineStr">
         <is>
-          <t>coiled spring delever</t>
+          <t>asset sale monetization</t>
         </is>
       </c>
     </row>
     <row r="34" ht="22" customHeight="1">
       <c r="A34" s="9" t="inlineStr">
         <is>
-          <t>CMRC</t>
+          <t>ONEW</t>
         </is>
       </c>
       <c r="B34" s="10" t="inlineStr">
         <is>
-          <t>Commerce.com, Inc. - S</t>
+          <t>OneWater Marine Inc.</t>
         </is>
       </c>
       <c r="C34" s="17" t="n">
-        <v>15.6</v>
+        <v>18.3</v>
       </c>
       <c r="D34" s="17" t="n">
         <v>1</v>
       </c>
       <c r="E34" s="17" t="n">
-        <v>3.4</v>
+        <v>10.5</v>
       </c>
       <c r="F34" s="10" t="inlineStr">
         <is>
-          <t>coiled spring delever</t>
+          <t>asset sale monetization</t>
         </is>
       </c>
     </row>
     <row r="35" ht="22" customHeight="1">
       <c r="A35" s="6" t="inlineStr">
         <is>
-          <t>PAHC</t>
+          <t>HLLY</t>
         </is>
       </c>
       <c r="B35" s="7" t="inlineStr">
         <is>
-          <t>Phibro Animal Health C</t>
+          <t>Holley Inc.</t>
         </is>
       </c>
       <c r="C35" s="16" t="n">
-        <v>15.6</v>
+        <v>18.2</v>
       </c>
       <c r="D35" s="16" t="n">
         <v>1</v>
       </c>
       <c r="E35" s="16" t="n">
-        <v>3.5</v>
+        <v>6.3</v>
       </c>
       <c r="F35" s="7" t="inlineStr">
         <is>
-          <t>coiled spring delever</t>
+          <t>asset sale monetization</t>
         </is>
       </c>
     </row>
     <row r="36" ht="22" customHeight="1">
       <c r="A36" s="9" t="inlineStr">
         <is>
-          <t>FWRD</t>
+          <t>WKHS</t>
         </is>
       </c>
       <c r="B36" s="10" t="inlineStr">
         <is>
-          <t>Forward Air Corporatio</t>
+          <t>Workhorse Group, Inc.</t>
         </is>
       </c>
       <c r="C36" s="17" t="n">
-        <v>15.6</v>
+        <v>18</v>
       </c>
       <c r="D36" s="17" t="n">
         <v>1</v>
       </c>
       <c r="E36" s="17" t="n">
-        <v>3.3</v>
+        <v>7.4</v>
       </c>
       <c r="F36" s="10" t="inlineStr">
         <is>
-          <t>coiled spring delever</t>
+          <t>hidden asset realization</t>
         </is>
       </c>
     </row>
     <row r="37" ht="22" customHeight="1">
       <c r="A37" s="6" t="inlineStr">
         <is>
-          <t>BVS</t>
+          <t>MLCI</t>
         </is>
       </c>
       <c r="B37" s="7" t="inlineStr">
         <is>
-          <t>Bioventus Inc.</t>
+          <t>Mount Logan Capital In</t>
         </is>
       </c>
       <c r="C37" s="16" t="n">
-        <v>15.6</v>
+        <v>17.8</v>
       </c>
       <c r="D37" s="16" t="n">
         <v>1</v>
       </c>
       <c r="E37" s="16" t="n">
-        <v>3.3</v>
+        <v>26.1</v>
       </c>
       <c r="F37" s="7" t="inlineStr">
         <is>
-          <t>coiled spring delever</t>
+          <t>tender offer squeeze</t>
         </is>
       </c>
     </row>
     <row r="38" ht="22" customHeight="1">
       <c r="A38" s="9" t="inlineStr">
         <is>
-          <t>ALHC</t>
+          <t>CMTL</t>
         </is>
       </c>
       <c r="B38" s="10" t="inlineStr">
         <is>
-          <t>Alignment Healthcare,</t>
+          <t>Comtech Telecommunicat</t>
         </is>
       </c>
       <c r="C38" s="17" t="n">
-        <v>15.5</v>
+        <v>17.7</v>
       </c>
       <c r="D38" s="17" t="n">
         <v>1</v>
       </c>
       <c r="E38" s="17" t="n">
-        <v>3.1</v>
+        <v>11.5</v>
       </c>
       <c r="F38" s="10" t="inlineStr">
         <is>
-          <t>coiled spring delever</t>
+          <t>asset sale monetization</t>
         </is>
       </c>
     </row>
     <row r="39" ht="22" customHeight="1">
       <c r="A39" s="6" t="inlineStr">
         <is>
-          <t>COR</t>
+          <t>AHCO</t>
         </is>
       </c>
       <c r="B39" s="7" t="inlineStr">
         <is>
-          <t>Cencora, Inc.</t>
+          <t>AdaptHealth Corp.</t>
         </is>
       </c>
       <c r="C39" s="16" t="n">
-        <v>15.5</v>
+        <v>17.6</v>
       </c>
       <c r="D39" s="16" t="n">
         <v>1</v>
       </c>
       <c r="E39" s="16" t="n">
-        <v>3.1</v>
+        <v>7.1</v>
       </c>
       <c r="F39" s="7" t="inlineStr">
         <is>
-          <t>coiled spring delever</t>
+          <t>asset sale monetization</t>
         </is>
       </c>
     </row>
     <row r="40" ht="22" customHeight="1">
       <c r="A40" s="9" t="inlineStr">
         <is>
-          <t>AVAH</t>
+          <t>MATV</t>
         </is>
       </c>
       <c r="B40" s="10" t="inlineStr">
         <is>
-          <t>Aveanna Healthcare Hol</t>
+          <t>Mativ Holdings, Inc.</t>
         </is>
       </c>
       <c r="C40" s="17" t="n">
-        <v>15.5</v>
+        <v>17.6</v>
       </c>
       <c r="D40" s="17" t="n">
         <v>1</v>
       </c>
       <c r="E40" s="17" t="n">
-        <v>3.2</v>
+        <v>7.1</v>
       </c>
       <c r="F40" s="10" t="inlineStr">
         <is>
@@ -5937,48 +5937,48 @@
     <row r="41" ht="22" customHeight="1">
       <c r="A41" s="6" t="inlineStr">
         <is>
-          <t>CDW</t>
+          <t>BDN</t>
         </is>
       </c>
       <c r="B41" s="7" t="inlineStr">
         <is>
-          <t>CDW Corporation</t>
+          <t>Brandywine Realty Trus</t>
         </is>
       </c>
       <c r="C41" s="16" t="n">
-        <v>15.5</v>
+        <v>17.5</v>
       </c>
       <c r="D41" s="16" t="n">
         <v>1</v>
       </c>
       <c r="E41" s="16" t="n">
-        <v>3.2</v>
+        <v>6.5</v>
       </c>
       <c r="F41" s="7" t="inlineStr">
         <is>
-          <t>coiled spring delever</t>
+          <t>asset sale monetization</t>
         </is>
       </c>
     </row>
     <row r="42" ht="22" customHeight="1">
       <c r="A42" s="9" t="inlineStr">
         <is>
-          <t>DEC</t>
+          <t>DFH</t>
         </is>
       </c>
       <c r="B42" s="10" t="inlineStr">
         <is>
-          <t>Diversified Energy Com</t>
+          <t>Dream Finders Homes, I</t>
         </is>
       </c>
       <c r="C42" s="17" t="n">
-        <v>15.3</v>
+        <v>17.2</v>
       </c>
       <c r="D42" s="17" t="n">
         <v>1</v>
       </c>
       <c r="E42" s="17" t="n">
-        <v>2.3</v>
+        <v>2.5</v>
       </c>
       <c r="F42" s="10" t="inlineStr">
         <is>
@@ -5989,189 +5989,189 @@
     <row r="43" ht="22" customHeight="1">
       <c r="A43" s="6" t="inlineStr">
         <is>
-          <t>AMTM</t>
+          <t>BGS</t>
         </is>
       </c>
       <c r="B43" s="7" t="inlineStr">
         <is>
-          <t>Amentum Holdings, Inc.</t>
+          <t>B&amp;G Foods, Inc.</t>
         </is>
       </c>
       <c r="C43" s="16" t="n">
-        <v>15.2</v>
+        <v>17.1</v>
       </c>
       <c r="D43" s="16" t="n">
         <v>1</v>
       </c>
       <c r="E43" s="16" t="n">
-        <v>5.2</v>
+        <v>7.8</v>
       </c>
       <c r="F43" s="7" t="inlineStr">
         <is>
-          <t>forced seller exhaustion</t>
+          <t>asset sale monetization</t>
         </is>
       </c>
     </row>
     <row r="44" ht="22" customHeight="1">
       <c r="A44" s="9" t="inlineStr">
         <is>
-          <t>CMP</t>
+          <t>CNC</t>
         </is>
       </c>
       <c r="B44" s="10" t="inlineStr">
         <is>
-          <t>Compass Minerals Intl</t>
+          <t>Centene Corporation</t>
         </is>
       </c>
       <c r="C44" s="17" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="D44" s="17" t="n">
         <v>1</v>
       </c>
       <c r="E44" s="17" t="n">
-        <v>0.8</v>
+        <v>4.7</v>
       </c>
       <c r="F44" s="10" t="inlineStr">
         <is>
-          <t>hidden asset realization</t>
+          <t>asset sale monetization</t>
         </is>
       </c>
     </row>
     <row r="45" ht="22" customHeight="1">
       <c r="A45" s="6" t="inlineStr">
         <is>
-          <t>SNDA</t>
+          <t>ABM</t>
         </is>
       </c>
       <c r="B45" s="7" t="inlineStr">
         <is>
-          <t>Sonida Senior Living,</t>
+          <t>ABM Industries Incorpo</t>
         </is>
       </c>
       <c r="C45" s="16" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="D45" s="16" t="n">
         <v>1</v>
       </c>
       <c r="E45" s="16" t="n">
-        <v>0.8</v>
+        <v>4.5</v>
       </c>
       <c r="F45" s="7" t="inlineStr">
         <is>
-          <t>hidden asset realization</t>
+          <t>coiled spring delever</t>
         </is>
       </c>
     </row>
     <row r="46" ht="22" customHeight="1">
       <c r="A46" s="9" t="inlineStr">
         <is>
-          <t>GRNT</t>
+          <t>KROS</t>
         </is>
       </c>
       <c r="B46" s="10" t="inlineStr">
         <is>
-          <t>Granite Ridge Resource</t>
+          <t>Keros Therapeutics, In</t>
         </is>
       </c>
       <c r="C46" s="17" t="n">
-        <v>14.9</v>
+        <v>16.9</v>
       </c>
       <c r="D46" s="17" t="n">
         <v>1</v>
       </c>
       <c r="E46" s="17" t="n">
-        <v>0.7</v>
+        <v>11.1</v>
       </c>
       <c r="F46" s="10" t="inlineStr">
         <is>
-          <t>hidden asset realization</t>
+          <t>tender offer squeeze</t>
         </is>
       </c>
     </row>
     <row r="47" ht="22" customHeight="1">
       <c r="A47" s="6" t="inlineStr">
         <is>
-          <t>CVS</t>
+          <t>NWL</t>
         </is>
       </c>
       <c r="B47" s="7" t="inlineStr">
         <is>
-          <t>CVS Health Corporation</t>
+          <t>Newell Brands Inc.</t>
         </is>
       </c>
       <c r="C47" s="16" t="n">
-        <v>14.9</v>
+        <v>16.7</v>
       </c>
       <c r="D47" s="16" t="n">
         <v>1</v>
       </c>
       <c r="E47" s="16" t="n">
-        <v>4.3</v>
+        <v>3.8</v>
       </c>
       <c r="F47" s="7" t="inlineStr">
         <is>
-          <t>forced seller exhaustion</t>
+          <t>coiled spring delever</t>
         </is>
       </c>
     </row>
     <row r="48" ht="22" customHeight="1">
       <c r="A48" s="9" t="inlineStr">
         <is>
-          <t>MDIA</t>
+          <t>EXFY</t>
         </is>
       </c>
       <c r="B48" s="10" t="inlineStr">
         <is>
-          <t>Mediaco Holding Inc.</t>
+          <t>Expensify, Inc.</t>
         </is>
       </c>
       <c r="C48" s="17" t="n">
-        <v>14.6</v>
+        <v>16.7</v>
       </c>
       <c r="D48" s="17" t="n">
         <v>1</v>
       </c>
       <c r="E48" s="17" t="n">
-        <v>1.2</v>
+        <v>13.6</v>
       </c>
       <c r="F48" s="10" t="inlineStr">
         <is>
-          <t>hidden asset realization</t>
+          <t>tender offer squeeze</t>
         </is>
       </c>
     </row>
     <row r="49" ht="22" customHeight="1">
       <c r="A49" s="6" t="inlineStr">
         <is>
-          <t>LMRI</t>
+          <t>HCAT</t>
         </is>
       </c>
       <c r="B49" s="7" t="inlineStr">
         <is>
-          <t>Lumexa Imaging Holding</t>
+          <t>Health Catalyst, Inc</t>
         </is>
       </c>
       <c r="C49" s="16" t="n">
-        <v>14.6</v>
+        <v>16.7</v>
       </c>
       <c r="D49" s="16" t="n">
         <v>1</v>
       </c>
       <c r="E49" s="16" t="n">
-        <v>3.3</v>
+        <v>6.1</v>
       </c>
       <c r="F49" s="7" t="inlineStr">
         <is>
-          <t>forced seller exhaustion</t>
+          <t>asset sale monetization</t>
         </is>
       </c>
     </row>
     <row r="51" ht="28" customHeight="1">
       <c r="A51" s="11" t="inlineStr">
         <is>
-          <t>47 names pass at least one mechanism gate; 1 light up two or more (the highest-conviction convergence). Unlike the additive consensus, these are HARD gates — every condition of a machine must hold: coiled-spring delever (D/E ≥ 1 + rising operating income + cheap equity), sub-cash buyback (net-cash floor ≥ 50% of price + active repurchase + not burning), forced-seller exhaustion (N-PORT forced selling into a floor, business not burning), hidden-asset realisation (small levered stub + credit-agreement asset sweep), and stated-unlock triangulated (MD&amp;A value-unlock language + cheap geometry + insider buying). Combines the payoff-geometry shape with the catalyst layers so shape and 'why now' are both required. Source: mechanism_gates.py.</t>
+          <t>81 names pass at least one mechanism gate; 6 light up two or more (the highest-conviction convergence). Unlike the additive consensus, these are HARD gates — every condition of a machine must hold: coiled-spring delever (D/E ≥ 1 + rising operating income + cheap equity), sub-cash buyback (net-cash floor ≥ 50% of price + active repurchase + not burning), forced-seller exhaustion (N-PORT forced selling into a floor, business not burning), hidden-asset realisation (small levered stub + credit-agreement asset sweep), stated-unlock triangulated (MD&amp;A value-unlock language + cheap geometry + insider buying), asset-sale monetization (asset-sale catalyst + cheap + levered/small — the backtest's best-median catalyst, +10%/58% hit), and tender-offer squeeze (tender/Dutch-auction catalyst + cheap small-cap — best hit rate, 61%). Combines the payoff-geometry shape with the catalyst layers so shape and 'why now' are both required. Source: mechanism_gates.py.</t>
         </is>
       </c>
     </row>

--- a/MOST_ASYMMETRIC.xlsx
+++ b/MOST_ASYMMETRIC.xlsx
@@ -5010,17 +5010,17 @@
         </is>
       </c>
       <c r="C5" s="16" t="n">
-        <v>44</v>
+        <v>52</v>
       </c>
       <c r="D5" s="16" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E5" s="16" t="n">
         <v>60</v>
       </c>
       <c r="F5" s="7" t="inlineStr">
         <is>
-          <t>sub cash buyback, asset sale monetization</t>
+          <t>sub cash buyback, asset sale monetization, ten</t>
         </is>
       </c>
     </row>
@@ -5036,10 +5036,10 @@
         </is>
       </c>
       <c r="C6" s="17" t="n">
-        <v>43</v>
+        <v>51</v>
       </c>
       <c r="D6" s="17" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E6" s="17" t="n">
         <v>31.1</v>
@@ -5053,402 +5053,402 @@
     <row r="7" ht="22" customHeight="1">
       <c r="A7" s="6" t="inlineStr">
         <is>
-          <t>THRY</t>
+          <t>BCIC</t>
         </is>
       </c>
       <c r="B7" s="7" t="inlineStr">
         <is>
-          <t>Thryv Holdings, Inc.</t>
+          <t>BCP Investment Corpora</t>
         </is>
       </c>
       <c r="C7" s="16" t="n">
-        <v>40.4</v>
+        <v>47.9</v>
       </c>
       <c r="D7" s="16" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E7" s="16" t="n">
-        <v>10.9</v>
+        <v>15.4</v>
       </c>
       <c r="F7" s="7" t="inlineStr">
         <is>
-          <t>coiled spring delever, asset sale monetization</t>
+          <t>hidden asset realization, tender offer squeeze</t>
         </is>
       </c>
     </row>
     <row r="8" ht="22" customHeight="1">
       <c r="A8" s="9" t="inlineStr">
         <is>
-          <t>BCIC</t>
+          <t>ULH</t>
         </is>
       </c>
       <c r="B8" s="10" t="inlineStr">
         <is>
-          <t>BCP Investment Corpora</t>
+          <t>Universal Logistics Ho</t>
         </is>
       </c>
       <c r="C8" s="17" t="n">
-        <v>39.9</v>
+        <v>45.9</v>
       </c>
       <c r="D8" s="17" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E8" s="17" t="n">
-        <v>15.4</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="F8" s="10" t="inlineStr">
         <is>
-          <t>hidden asset realization, tender offer squeeze</t>
+          <t>hidden asset realization, asset sale latent, t</t>
         </is>
       </c>
     </row>
     <row r="9" ht="22" customHeight="1">
       <c r="A9" s="6" t="inlineStr">
         <is>
-          <t>GTE</t>
+          <t>THRY</t>
         </is>
       </c>
       <c r="B9" s="7" t="inlineStr">
         <is>
-          <t>Gran Tierra Energy Inc</t>
+          <t>Thryv Holdings, Inc.</t>
         </is>
       </c>
       <c r="C9" s="16" t="n">
-        <v>35.8</v>
+        <v>40.4</v>
       </c>
       <c r="D9" s="16" t="n">
         <v>2</v>
       </c>
       <c r="E9" s="16" t="n">
-        <v>3.8</v>
+        <v>10.9</v>
       </c>
       <c r="F9" s="7" t="inlineStr">
         <is>
-          <t>asset sale monetization, tender offer squeeze</t>
+          <t>coiled spring delever, asset sale monetization</t>
         </is>
       </c>
     </row>
     <row r="10" ht="22" customHeight="1">
       <c r="A10" s="9" t="inlineStr">
         <is>
-          <t>CYH</t>
+          <t>LUCY</t>
         </is>
       </c>
       <c r="B10" s="10" t="inlineStr">
         <is>
-          <t>Community Health Syste</t>
+          <t>Innovative Eyewear, In</t>
         </is>
       </c>
       <c r="C10" s="17" t="n">
-        <v>35.2</v>
+        <v>40</v>
       </c>
       <c r="D10" s="17" t="n">
         <v>2</v>
       </c>
       <c r="E10" s="17" t="n">
-        <v>3</v>
+        <v>45.6</v>
       </c>
       <c r="F10" s="10" t="inlineStr">
         <is>
-          <t>asset sale monetization, tender offer squeeze</t>
+          <t>sub cash buyback, tender target latent</t>
         </is>
       </c>
     </row>
     <row r="11" ht="22" customHeight="1">
       <c r="A11" s="6" t="inlineStr">
         <is>
-          <t>LUCY</t>
+          <t>PMCB</t>
         </is>
       </c>
       <c r="B11" s="7" t="inlineStr">
         <is>
-          <t>Innovative Eyewear, In</t>
+          <t>PharmaCyte  Biotech, I</t>
         </is>
       </c>
       <c r="C11" s="16" t="n">
-        <v>22</v>
+        <v>40</v>
       </c>
       <c r="D11" s="16" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E11" s="16" t="n">
-        <v>45.6</v>
+        <v>30</v>
       </c>
       <c r="F11" s="7" t="inlineStr">
         <is>
-          <t>sub cash buyback</t>
+          <t>sub cash buyback, tender target latent</t>
         </is>
       </c>
     </row>
     <row r="12" ht="22" customHeight="1">
       <c r="A12" s="9" t="inlineStr">
         <is>
-          <t>DXC</t>
+          <t>ACH</t>
         </is>
       </c>
       <c r="B12" s="10" t="inlineStr">
         <is>
-          <t>DXC Technology Company</t>
+          <t>Accendra Health, Inc.</t>
         </is>
       </c>
       <c r="C12" s="17" t="n">
-        <v>22</v>
+        <v>40</v>
       </c>
       <c r="D12" s="17" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E12" s="17" t="n">
-        <v>30</v>
+        <v>60</v>
       </c>
       <c r="F12" s="10" t="inlineStr">
         <is>
-          <t>sub cash buyback</t>
+          <t>sub cash buyback, tender target latent</t>
         </is>
       </c>
     </row>
     <row r="13" ht="22" customHeight="1">
       <c r="A13" s="6" t="inlineStr">
         <is>
-          <t>PMCB</t>
+          <t>SHEN</t>
         </is>
       </c>
       <c r="B13" s="7" t="inlineStr">
         <is>
-          <t>PharmaCyte  Biotech, I</t>
+          <t>Shenandoah Telecommuni</t>
         </is>
       </c>
       <c r="C13" s="16" t="n">
-        <v>22</v>
+        <v>38.3</v>
       </c>
       <c r="D13" s="16" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E13" s="16" t="n">
-        <v>30</v>
+        <v>19.5</v>
       </c>
       <c r="F13" s="7" t="inlineStr">
         <is>
-          <t>sub cash buyback</t>
+          <t>hidden asset realization, asset sale latent</t>
         </is>
       </c>
     </row>
     <row r="14" ht="22" customHeight="1">
       <c r="A14" s="9" t="inlineStr">
         <is>
-          <t>ACH</t>
+          <t>PRTA</t>
         </is>
       </c>
       <c r="B14" s="10" t="inlineStr">
         <is>
-          <t>Accendra Health, Inc.</t>
+          <t>Prothena Corporation p</t>
         </is>
       </c>
       <c r="C14" s="17" t="n">
-        <v>22</v>
+        <v>37.8</v>
       </c>
       <c r="D14" s="17" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E14" s="17" t="n">
-        <v>60</v>
+        <v>3.3</v>
       </c>
       <c r="F14" s="10" t="inlineStr">
         <is>
-          <t>sub cash buyback</t>
+          <t>sub cash buyback, tender target latent</t>
         </is>
       </c>
     </row>
     <row r="15" ht="22" customHeight="1">
       <c r="A15" s="6" t="inlineStr">
         <is>
-          <t>VISN</t>
+          <t>GTE</t>
         </is>
       </c>
       <c r="B15" s="7" t="inlineStr">
         <is>
-          <t>Vistance Networks, Inc</t>
+          <t>Gran Tierra Energy Inc</t>
         </is>
       </c>
       <c r="C15" s="16" t="n">
-        <v>22</v>
+        <v>35.8</v>
       </c>
       <c r="D15" s="16" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E15" s="16" t="n">
-        <v>24.8</v>
+        <v>3.8</v>
       </c>
       <c r="F15" s="7" t="inlineStr">
         <is>
-          <t>sub cash buyback</t>
+          <t>asset sale monetization, tender offer squeeze</t>
         </is>
       </c>
     </row>
     <row r="16" ht="22" customHeight="1">
       <c r="A16" s="9" t="inlineStr">
         <is>
-          <t>ADNT</t>
+          <t>CYH</t>
         </is>
       </c>
       <c r="B16" s="10" t="inlineStr">
         <is>
-          <t>Adient plc</t>
+          <t>Community Health Syste</t>
         </is>
       </c>
       <c r="C16" s="17" t="n">
-        <v>20.7</v>
+        <v>35.2</v>
       </c>
       <c r="D16" s="17" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E16" s="17" t="n">
-        <v>6.3</v>
+        <v>3</v>
       </c>
       <c r="F16" s="10" t="inlineStr">
         <is>
-          <t>sub cash buyback</t>
+          <t>asset sale monetization, tender offer squeeze</t>
         </is>
       </c>
     </row>
     <row r="17" ht="22" customHeight="1">
       <c r="A17" s="6" t="inlineStr">
         <is>
-          <t>SHEN</t>
+          <t>FWRD</t>
         </is>
       </c>
       <c r="B17" s="7" t="inlineStr">
         <is>
-          <t>Shenandoah Telecommuni</t>
+          <t>Forward Air Corporatio</t>
         </is>
       </c>
       <c r="C17" s="16" t="n">
-        <v>20.3</v>
+        <v>33.5</v>
       </c>
       <c r="D17" s="16" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E17" s="16" t="n">
-        <v>19.5</v>
+        <v>3.3</v>
       </c>
       <c r="F17" s="7" t="inlineStr">
         <is>
-          <t>hidden asset realization</t>
+          <t>coiled spring delever, asset sale latent</t>
         </is>
       </c>
     </row>
     <row r="18" ht="22" customHeight="1">
       <c r="A18" s="9" t="inlineStr">
         <is>
-          <t>GETY</t>
+          <t>BVS</t>
         </is>
       </c>
       <c r="B18" s="10" t="inlineStr">
         <is>
-          <t>Getty Images Holdings,</t>
+          <t>Bioventus Inc.</t>
         </is>
       </c>
       <c r="C18" s="17" t="n">
-        <v>20</v>
+        <v>33.5</v>
       </c>
       <c r="D18" s="17" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E18" s="17" t="n">
-        <v>60</v>
+        <v>3.3</v>
       </c>
       <c r="F18" s="10" t="inlineStr">
         <is>
-          <t>coiled spring delever</t>
+          <t>coiled spring delever, asset sale latent</t>
         </is>
       </c>
     </row>
     <row r="19" ht="22" customHeight="1">
       <c r="A19" s="6" t="inlineStr">
         <is>
-          <t>CLVT</t>
+          <t>DXC</t>
         </is>
       </c>
       <c r="B19" s="7" t="inlineStr">
         <is>
-          <t>Clarivate Plc</t>
+          <t>DXC Technology Company</t>
         </is>
       </c>
       <c r="C19" s="16" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="D19" s="16" t="n">
         <v>1</v>
       </c>
       <c r="E19" s="16" t="n">
-        <v>60</v>
+        <v>30</v>
       </c>
       <c r="F19" s="7" t="inlineStr">
         <is>
-          <t>asset sale monetization</t>
+          <t>sub cash buyback</t>
         </is>
       </c>
     </row>
     <row r="20" ht="22" customHeight="1">
       <c r="A20" s="9" t="inlineStr">
         <is>
-          <t>NUS</t>
+          <t>VISN</t>
         </is>
       </c>
       <c r="B20" s="10" t="inlineStr">
         <is>
-          <t>Nu Skin Enterprises, I</t>
+          <t>Vistance Networks, Inc</t>
         </is>
       </c>
       <c r="C20" s="17" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="D20" s="17" t="n">
         <v>1</v>
       </c>
       <c r="E20" s="17" t="n">
-        <v>60</v>
+        <v>24.8</v>
       </c>
       <c r="F20" s="10" t="inlineStr">
         <is>
-          <t>asset sale monetization</t>
+          <t>sub cash buyback</t>
         </is>
       </c>
     </row>
     <row r="21" ht="22" customHeight="1">
       <c r="A21" s="6" t="inlineStr">
         <is>
-          <t>UTZ</t>
+          <t>ADNT</t>
         </is>
       </c>
       <c r="B21" s="7" t="inlineStr">
         <is>
-          <t>Utz Brands Inc</t>
+          <t>Adient plc</t>
         </is>
       </c>
       <c r="C21" s="16" t="n">
-        <v>20</v>
+        <v>20.7</v>
       </c>
       <c r="D21" s="16" t="n">
         <v>1</v>
       </c>
       <c r="E21" s="16" t="n">
-        <v>23.9</v>
+        <v>6.3</v>
       </c>
       <c r="F21" s="7" t="inlineStr">
         <is>
-          <t>coiled spring delever</t>
+          <t>sub cash buyback</t>
         </is>
       </c>
     </row>
     <row r="22" ht="22" customHeight="1">
       <c r="A22" s="9" t="inlineStr">
         <is>
-          <t>LAB</t>
+          <t>GETY</t>
         </is>
       </c>
       <c r="B22" s="10" t="inlineStr">
         <is>
-          <t>Standard BioTools Inc.</t>
+          <t>Getty Images Holdings,</t>
         </is>
       </c>
       <c r="C22" s="17" t="n">
@@ -5458,23 +5458,23 @@
         <v>1</v>
       </c>
       <c r="E22" s="17" t="n">
-        <v>42.3</v>
+        <v>60</v>
       </c>
       <c r="F22" s="10" t="inlineStr">
         <is>
-          <t>asset sale monetization</t>
+          <t>coiled spring delever</t>
         </is>
       </c>
     </row>
     <row r="23" ht="22" customHeight="1">
       <c r="A23" s="6" t="inlineStr">
         <is>
-          <t>UEIC</t>
+          <t>CLVT</t>
         </is>
       </c>
       <c r="B23" s="7" t="inlineStr">
         <is>
-          <t>Universal Electronics</t>
+          <t>Clarivate Plc</t>
         </is>
       </c>
       <c r="C23" s="16" t="n">
@@ -5495,12 +5495,12 @@
     <row r="24" ht="22" customHeight="1">
       <c r="A24" s="9" t="inlineStr">
         <is>
-          <t>MAGN</t>
+          <t>NUS</t>
         </is>
       </c>
       <c r="B24" s="10" t="inlineStr">
         <is>
-          <t>Magnera Corporation</t>
+          <t>Nu Skin Enterprises, I</t>
         </is>
       </c>
       <c r="C24" s="17" t="n">
@@ -5514,19 +5514,19 @@
       </c>
       <c r="F24" s="10" t="inlineStr">
         <is>
-          <t>coiled spring delever</t>
+          <t>asset sale monetization</t>
         </is>
       </c>
     </row>
     <row r="25" ht="22" customHeight="1">
       <c r="A25" s="6" t="inlineStr">
         <is>
-          <t>BOC</t>
+          <t>UTZ</t>
         </is>
       </c>
       <c r="B25" s="7" t="inlineStr">
         <is>
-          <t>Boston Omaha Corporati</t>
+          <t>Utz Brands Inc</t>
         </is>
       </c>
       <c r="C25" s="16" t="n">
@@ -5536,23 +5536,23 @@
         <v>1</v>
       </c>
       <c r="E25" s="16" t="n">
-        <v>60</v>
+        <v>23.9</v>
       </c>
       <c r="F25" s="7" t="inlineStr">
         <is>
-          <t>asset sale monetization</t>
+          <t>coiled spring delever</t>
         </is>
       </c>
     </row>
     <row r="26" ht="22" customHeight="1">
       <c r="A26" s="9" t="inlineStr">
         <is>
-          <t>BALY</t>
+          <t>LAB</t>
         </is>
       </c>
       <c r="B26" s="10" t="inlineStr">
         <is>
-          <t>Bally's Corporation</t>
+          <t>Standard BioTools Inc.</t>
         </is>
       </c>
       <c r="C26" s="17" t="n">
@@ -5562,27 +5562,27 @@
         <v>1</v>
       </c>
       <c r="E26" s="17" t="n">
-        <v>38.5</v>
+        <v>42.3</v>
       </c>
       <c r="F26" s="10" t="inlineStr">
         <is>
-          <t>coiled spring delever</t>
+          <t>asset sale monetization</t>
         </is>
       </c>
     </row>
     <row r="27" ht="22" customHeight="1">
       <c r="A27" s="6" t="inlineStr">
         <is>
-          <t>HAIN</t>
+          <t>UEIC</t>
         </is>
       </c>
       <c r="B27" s="7" t="inlineStr">
         <is>
-          <t>The Hain Celestial Gro</t>
+          <t>Universal Electronics</t>
         </is>
       </c>
       <c r="C27" s="16" t="n">
-        <v>19.9</v>
+        <v>20</v>
       </c>
       <c r="D27" s="16" t="n">
         <v>1</v>
@@ -5599,94 +5599,94 @@
     <row r="28" ht="22" customHeight="1">
       <c r="A28" s="9" t="inlineStr">
         <is>
-          <t>ULH</t>
+          <t>MAGN</t>
         </is>
       </c>
       <c r="B28" s="10" t="inlineStr">
         <is>
-          <t>Universal Logistics Ho</t>
+          <t>Magnera Corporation</t>
         </is>
       </c>
       <c r="C28" s="17" t="n">
-        <v>19.9</v>
+        <v>20</v>
       </c>
       <c r="D28" s="17" t="n">
         <v>1</v>
       </c>
       <c r="E28" s="17" t="n">
-        <v>9.699999999999999</v>
+        <v>60</v>
       </c>
       <c r="F28" s="10" t="inlineStr">
         <is>
-          <t>hidden asset realization</t>
+          <t>coiled spring delever</t>
         </is>
       </c>
     </row>
     <row r="29" ht="22" customHeight="1">
       <c r="A29" s="6" t="inlineStr">
         <is>
-          <t>PRTA</t>
+          <t>BOC</t>
         </is>
       </c>
       <c r="B29" s="7" t="inlineStr">
         <is>
-          <t>Prothena Corporation p</t>
+          <t>Boston Omaha Corporati</t>
         </is>
       </c>
       <c r="C29" s="16" t="n">
-        <v>19.8</v>
+        <v>20</v>
       </c>
       <c r="D29" s="16" t="n">
         <v>1</v>
       </c>
       <c r="E29" s="16" t="n">
-        <v>3.3</v>
+        <v>60</v>
       </c>
       <c r="F29" s="7" t="inlineStr">
         <is>
-          <t>sub cash buyback</t>
+          <t>asset sale monetization</t>
         </is>
       </c>
     </row>
     <row r="30" ht="22" customHeight="1">
       <c r="A30" s="9" t="inlineStr">
         <is>
-          <t>PRGO</t>
+          <t>BALY</t>
         </is>
       </c>
       <c r="B30" s="10" t="inlineStr">
         <is>
-          <t>Perrigo Company plc</t>
+          <t>Bally's Corporation</t>
         </is>
       </c>
       <c r="C30" s="17" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D30" s="17" t="n">
         <v>1</v>
       </c>
       <c r="E30" s="17" t="n">
-        <v>25.6</v>
+        <v>38.5</v>
       </c>
       <c r="F30" s="10" t="inlineStr">
         <is>
-          <t>asset sale monetization</t>
+          <t>coiled spring delever</t>
         </is>
       </c>
     </row>
     <row r="31" ht="22" customHeight="1">
       <c r="A31" s="6" t="inlineStr">
         <is>
-          <t>ZSTK</t>
+          <t>HAIN</t>
         </is>
       </c>
       <c r="B31" s="7" t="inlineStr">
         <is>
-          <t>ZeroStack Corp.</t>
+          <t>The Hain Celestial Gro</t>
         </is>
       </c>
       <c r="C31" s="16" t="n">
-        <v>18.6</v>
+        <v>19.9</v>
       </c>
       <c r="D31" s="16" t="n">
         <v>1</v>
@@ -5703,22 +5703,22 @@
     <row r="32" ht="22" customHeight="1">
       <c r="A32" s="9" t="inlineStr">
         <is>
-          <t>CMCO</t>
+          <t>PRGO</t>
         </is>
       </c>
       <c r="B32" s="10" t="inlineStr">
         <is>
-          <t>Columbus McKinnon Corp</t>
+          <t>Perrigo Company plc</t>
         </is>
       </c>
       <c r="C32" s="17" t="n">
-        <v>18.4</v>
+        <v>19</v>
       </c>
       <c r="D32" s="17" t="n">
         <v>1</v>
       </c>
       <c r="E32" s="17" t="n">
-        <v>7.1</v>
+        <v>25.6</v>
       </c>
       <c r="F32" s="10" t="inlineStr">
         <is>
@@ -5729,22 +5729,22 @@
     <row r="33" ht="22" customHeight="1">
       <c r="A33" s="6" t="inlineStr">
         <is>
-          <t>CERT</t>
+          <t>ZSTK</t>
         </is>
       </c>
       <c r="B33" s="7" t="inlineStr">
         <is>
-          <t>Certara, Inc.</t>
+          <t>ZeroStack Corp.</t>
         </is>
       </c>
       <c r="C33" s="16" t="n">
-        <v>18.3</v>
+        <v>18.6</v>
       </c>
       <c r="D33" s="16" t="n">
         <v>1</v>
       </c>
       <c r="E33" s="16" t="n">
-        <v>10.7</v>
+        <v>60</v>
       </c>
       <c r="F33" s="7" t="inlineStr">
         <is>
@@ -5755,22 +5755,22 @@
     <row r="34" ht="22" customHeight="1">
       <c r="A34" s="9" t="inlineStr">
         <is>
-          <t>ONEW</t>
+          <t>CMCO</t>
         </is>
       </c>
       <c r="B34" s="10" t="inlineStr">
         <is>
-          <t>OneWater Marine Inc.</t>
+          <t>Columbus McKinnon Corp</t>
         </is>
       </c>
       <c r="C34" s="17" t="n">
-        <v>18.3</v>
+        <v>18.4</v>
       </c>
       <c r="D34" s="17" t="n">
         <v>1</v>
       </c>
       <c r="E34" s="17" t="n">
-        <v>10.5</v>
+        <v>7.1</v>
       </c>
       <c r="F34" s="10" t="inlineStr">
         <is>
@@ -5781,22 +5781,22 @@
     <row r="35" ht="22" customHeight="1">
       <c r="A35" s="6" t="inlineStr">
         <is>
-          <t>HLLY</t>
+          <t>CERT</t>
         </is>
       </c>
       <c r="B35" s="7" t="inlineStr">
         <is>
-          <t>Holley Inc.</t>
+          <t>Certara, Inc.</t>
         </is>
       </c>
       <c r="C35" s="16" t="n">
-        <v>18.2</v>
+        <v>18.3</v>
       </c>
       <c r="D35" s="16" t="n">
         <v>1</v>
       </c>
       <c r="E35" s="16" t="n">
-        <v>6.3</v>
+        <v>10.7</v>
       </c>
       <c r="F35" s="7" t="inlineStr">
         <is>
@@ -5807,152 +5807,152 @@
     <row r="36" ht="22" customHeight="1">
       <c r="A36" s="9" t="inlineStr">
         <is>
-          <t>WKHS</t>
+          <t>ONEW</t>
         </is>
       </c>
       <c r="B36" s="10" t="inlineStr">
         <is>
-          <t>Workhorse Group, Inc.</t>
+          <t>OneWater Marine Inc.</t>
         </is>
       </c>
       <c r="C36" s="17" t="n">
-        <v>18</v>
+        <v>18.3</v>
       </c>
       <c r="D36" s="17" t="n">
         <v>1</v>
       </c>
       <c r="E36" s="17" t="n">
-        <v>7.4</v>
+        <v>10.5</v>
       </c>
       <c r="F36" s="10" t="inlineStr">
         <is>
-          <t>hidden asset realization</t>
+          <t>asset sale monetization</t>
         </is>
       </c>
     </row>
     <row r="37" ht="22" customHeight="1">
       <c r="A37" s="6" t="inlineStr">
         <is>
-          <t>MLCI</t>
+          <t>HLLY</t>
         </is>
       </c>
       <c r="B37" s="7" t="inlineStr">
         <is>
-          <t>Mount Logan Capital In</t>
+          <t>Holley Inc.</t>
         </is>
       </c>
       <c r="C37" s="16" t="n">
-        <v>17.8</v>
+        <v>18.2</v>
       </c>
       <c r="D37" s="16" t="n">
         <v>1</v>
       </c>
       <c r="E37" s="16" t="n">
-        <v>26.1</v>
+        <v>6.3</v>
       </c>
       <c r="F37" s="7" t="inlineStr">
         <is>
-          <t>tender offer squeeze</t>
+          <t>asset sale monetization</t>
         </is>
       </c>
     </row>
     <row r="38" ht="22" customHeight="1">
       <c r="A38" s="9" t="inlineStr">
         <is>
-          <t>CMTL</t>
+          <t>WKHS</t>
         </is>
       </c>
       <c r="B38" s="10" t="inlineStr">
         <is>
-          <t>Comtech Telecommunicat</t>
+          <t>Workhorse Group, Inc.</t>
         </is>
       </c>
       <c r="C38" s="17" t="n">
-        <v>17.7</v>
+        <v>18</v>
       </c>
       <c r="D38" s="17" t="n">
         <v>1</v>
       </c>
       <c r="E38" s="17" t="n">
-        <v>11.5</v>
+        <v>7.4</v>
       </c>
       <c r="F38" s="10" t="inlineStr">
         <is>
-          <t>asset sale monetization</t>
+          <t>hidden asset realization</t>
         </is>
       </c>
     </row>
     <row r="39" ht="22" customHeight="1">
       <c r="A39" s="6" t="inlineStr">
         <is>
-          <t>AHCO</t>
+          <t>MLCI</t>
         </is>
       </c>
       <c r="B39" s="7" t="inlineStr">
         <is>
-          <t>AdaptHealth Corp.</t>
+          <t>Mount Logan Capital In</t>
         </is>
       </c>
       <c r="C39" s="16" t="n">
-        <v>17.6</v>
+        <v>17.8</v>
       </c>
       <c r="D39" s="16" t="n">
         <v>1</v>
       </c>
       <c r="E39" s="16" t="n">
-        <v>7.1</v>
+        <v>26.1</v>
       </c>
       <c r="F39" s="7" t="inlineStr">
         <is>
-          <t>asset sale monetization</t>
+          <t>tender offer squeeze</t>
         </is>
       </c>
     </row>
     <row r="40" ht="22" customHeight="1">
       <c r="A40" s="9" t="inlineStr">
         <is>
-          <t>MATV</t>
+          <t>CMTL</t>
         </is>
       </c>
       <c r="B40" s="10" t="inlineStr">
         <is>
-          <t>Mativ Holdings, Inc.</t>
+          <t>Comtech Telecommunicat</t>
         </is>
       </c>
       <c r="C40" s="17" t="n">
-        <v>17.6</v>
+        <v>17.7</v>
       </c>
       <c r="D40" s="17" t="n">
         <v>1</v>
       </c>
       <c r="E40" s="17" t="n">
-        <v>7.1</v>
+        <v>11.5</v>
       </c>
       <c r="F40" s="10" t="inlineStr">
         <is>
-          <t>coiled spring delever</t>
+          <t>asset sale monetization</t>
         </is>
       </c>
     </row>
     <row r="41" ht="22" customHeight="1">
       <c r="A41" s="6" t="inlineStr">
         <is>
-          <t>BDN</t>
+          <t>AHCO</t>
         </is>
       </c>
       <c r="B41" s="7" t="inlineStr">
         <is>
-          <t>Brandywine Realty Trus</t>
+          <t>AdaptHealth Corp.</t>
         </is>
       </c>
       <c r="C41" s="16" t="n">
-        <v>17.5</v>
+        <v>17.6</v>
       </c>
       <c r="D41" s="16" t="n">
         <v>1</v>
       </c>
       <c r="E41" s="16" t="n">
-        <v>6.5</v>
+        <v>7.1</v>
       </c>
       <c r="F41" s="7" t="inlineStr">
         <is>
@@ -5963,48 +5963,48 @@
     <row r="42" ht="22" customHeight="1">
       <c r="A42" s="9" t="inlineStr">
         <is>
-          <t>DFH</t>
+          <t>MATV</t>
         </is>
       </c>
       <c r="B42" s="10" t="inlineStr">
         <is>
-          <t>Dream Finders Homes, I</t>
+          <t>Mativ Holdings, Inc.</t>
         </is>
       </c>
       <c r="C42" s="17" t="n">
-        <v>17.2</v>
+        <v>17.6</v>
       </c>
       <c r="D42" s="17" t="n">
         <v>1</v>
       </c>
       <c r="E42" s="17" t="n">
-        <v>2.5</v>
+        <v>7.1</v>
       </c>
       <c r="F42" s="10" t="inlineStr">
         <is>
-          <t>hidden asset realization</t>
+          <t>coiled spring delever</t>
         </is>
       </c>
     </row>
     <row r="43" ht="22" customHeight="1">
       <c r="A43" s="6" t="inlineStr">
         <is>
-          <t>BGS</t>
+          <t>BDN</t>
         </is>
       </c>
       <c r="B43" s="7" t="inlineStr">
         <is>
-          <t>B&amp;G Foods, Inc.</t>
+          <t>Brandywine Realty Trus</t>
         </is>
       </c>
       <c r="C43" s="16" t="n">
-        <v>17.1</v>
+        <v>17.5</v>
       </c>
       <c r="D43" s="16" t="n">
         <v>1</v>
       </c>
       <c r="E43" s="16" t="n">
-        <v>7.8</v>
+        <v>6.5</v>
       </c>
       <c r="F43" s="7" t="inlineStr">
         <is>
@@ -6015,100 +6015,100 @@
     <row r="44" ht="22" customHeight="1">
       <c r="A44" s="9" t="inlineStr">
         <is>
-          <t>CNC</t>
+          <t>DFH</t>
         </is>
       </c>
       <c r="B44" s="10" t="inlineStr">
         <is>
-          <t>Centene Corporation</t>
+          <t>Dream Finders Homes, I</t>
         </is>
       </c>
       <c r="C44" s="17" t="n">
-        <v>17</v>
+        <v>17.2</v>
       </c>
       <c r="D44" s="17" t="n">
         <v>1</v>
       </c>
       <c r="E44" s="17" t="n">
-        <v>4.7</v>
+        <v>2.5</v>
       </c>
       <c r="F44" s="10" t="inlineStr">
         <is>
-          <t>asset sale monetization</t>
+          <t>hidden asset realization</t>
         </is>
       </c>
     </row>
     <row r="45" ht="22" customHeight="1">
       <c r="A45" s="6" t="inlineStr">
         <is>
-          <t>ABM</t>
+          <t>BGS</t>
         </is>
       </c>
       <c r="B45" s="7" t="inlineStr">
         <is>
-          <t>ABM Industries Incorpo</t>
+          <t>B&amp;G Foods, Inc.</t>
         </is>
       </c>
       <c r="C45" s="16" t="n">
-        <v>17</v>
+        <v>17.1</v>
       </c>
       <c r="D45" s="16" t="n">
         <v>1</v>
       </c>
       <c r="E45" s="16" t="n">
-        <v>4.5</v>
+        <v>7.8</v>
       </c>
       <c r="F45" s="7" t="inlineStr">
         <is>
-          <t>coiled spring delever</t>
+          <t>asset sale monetization</t>
         </is>
       </c>
     </row>
     <row r="46" ht="22" customHeight="1">
       <c r="A46" s="9" t="inlineStr">
         <is>
-          <t>KROS</t>
+          <t>CNC</t>
         </is>
       </c>
       <c r="B46" s="10" t="inlineStr">
         <is>
-          <t>Keros Therapeutics, In</t>
+          <t>Centene Corporation</t>
         </is>
       </c>
       <c r="C46" s="17" t="n">
-        <v>16.9</v>
+        <v>17</v>
       </c>
       <c r="D46" s="17" t="n">
         <v>1</v>
       </c>
       <c r="E46" s="17" t="n">
-        <v>11.1</v>
+        <v>4.7</v>
       </c>
       <c r="F46" s="10" t="inlineStr">
         <is>
-          <t>tender offer squeeze</t>
+          <t>asset sale monetization</t>
         </is>
       </c>
     </row>
     <row r="47" ht="22" customHeight="1">
       <c r="A47" s="6" t="inlineStr">
         <is>
-          <t>NWL</t>
+          <t>ABM</t>
         </is>
       </c>
       <c r="B47" s="7" t="inlineStr">
         <is>
-          <t>Newell Brands Inc.</t>
+          <t>ABM Industries Incorpo</t>
         </is>
       </c>
       <c r="C47" s="16" t="n">
-        <v>16.7</v>
+        <v>17</v>
       </c>
       <c r="D47" s="16" t="n">
         <v>1</v>
       </c>
       <c r="E47" s="16" t="n">
-        <v>3.8</v>
+        <v>4.5</v>
       </c>
       <c r="F47" s="7" t="inlineStr">
         <is>
@@ -6119,22 +6119,22 @@
     <row r="48" ht="22" customHeight="1">
       <c r="A48" s="9" t="inlineStr">
         <is>
-          <t>EXFY</t>
+          <t>KROS</t>
         </is>
       </c>
       <c r="B48" s="10" t="inlineStr">
         <is>
-          <t>Expensify, Inc.</t>
+          <t>Keros Therapeutics, In</t>
         </is>
       </c>
       <c r="C48" s="17" t="n">
-        <v>16.7</v>
+        <v>16.9</v>
       </c>
       <c r="D48" s="17" t="n">
         <v>1</v>
       </c>
       <c r="E48" s="17" t="n">
-        <v>13.6</v>
+        <v>11.1</v>
       </c>
       <c r="F48" s="10" t="inlineStr">
         <is>
@@ -6145,12 +6145,12 @@
     <row r="49" ht="22" customHeight="1">
       <c r="A49" s="6" t="inlineStr">
         <is>
-          <t>HCAT</t>
+          <t>NWL</t>
         </is>
       </c>
       <c r="B49" s="7" t="inlineStr">
         <is>
-          <t>Health Catalyst, Inc</t>
+          <t>Newell Brands Inc.</t>
         </is>
       </c>
       <c r="C49" s="16" t="n">
@@ -6160,18 +6160,18 @@
         <v>1</v>
       </c>
       <c r="E49" s="16" t="n">
-        <v>6.1</v>
+        <v>3.8</v>
       </c>
       <c r="F49" s="7" t="inlineStr">
         <is>
-          <t>asset sale monetization</t>
+          <t>coiled spring delever</t>
         </is>
       </c>
     </row>
     <row r="51" ht="28" customHeight="1">
       <c r="A51" s="11" t="inlineStr">
         <is>
-          <t>81 names pass at least one mechanism gate; 6 light up two or more (the highest-conviction convergence). Unlike the additive consensus, these are HARD gates — every condition of a machine must hold: coiled-spring delever (D/E ≥ 1 + rising operating income + cheap equity), sub-cash buyback (net-cash floor ≥ 50% of price + active repurchase + not burning), forced-seller exhaustion (N-PORT forced selling into a floor, business not burning), hidden-asset realisation (small levered stub + credit-agreement asset sweep), stated-unlock triangulated (MD&amp;A value-unlock language + cheap geometry + insider buying), asset-sale monetization (asset-sale catalyst + cheap + levered/small — the backtest's best-median catalyst, +10%/58% hit), and tender-offer squeeze (tender/Dutch-auction catalyst + cheap small-cap — best hit rate, 61%). Combines the payoff-geometry shape with the catalyst layers so shape and 'why now' are both required. Source: mechanism_gates.py.</t>
+          <t>102 names pass at least one mechanism gate; 14 light up two or more (the highest-conviction convergence). Unlike the additive consensus, these are HARD gates — every condition of a machine must hold: coiled-spring delever (D/E ≥ 1 + rising operating income + cheap equity), sub-cash buyback (net-cash floor ≥ 50% of price + active repurchase + not burning), forced-seller exhaustion (N-PORT forced selling into a floor, business not burning), hidden-asset realisation (small levered stub + credit-agreement asset sweep), stated-unlock triangulated (MD&amp;A value-unlock language + cheap geometry + insider buying), asset-sale monetization (asset-sale catalyst + cheap + levered/small — the backtest's best-median catalyst, +10%/58% hit), and tender-offer squeeze (tender/Dutch-auction catalyst + cheap small-cap — best hit rate, 61%). TWO ANTICIPATORY archetypes catch the setup BEFORE the catalyst: asset-sale latent (cheap + levered + de-lever pressure or MD&amp;A divestiture intent, NO sale announced) and tender-target latent (near net cash / NCAV, small controllable cap, plausible buyer — high insider ownership or self-tender-capable cash — and NO bid yet); these are speculative (weighted below the confirmed machines) but flag names likely to realise value that haven't yet. Combines the payoff-geometry shape with the catalyst layers so shape and 'why now' are both required. Source: mechanism_gates.py.</t>
         </is>
       </c>
     </row>

--- a/MOST_ASYMMETRIC.xlsx
+++ b/MOST_ASYMMETRIC.xlsx
@@ -7847,7 +7847,7 @@
     <row r="2" ht="18" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Corporate-action announcements in 2024-01-01..2025-06-30 (314 events), realized forward return measured to +12 months, absolute and vs SPY. The evidence behind the catalyst weights.</t>
+          <t>Corporate-action announcements in 2022-06-01..2025-06-30 (417 events), realized forward return measured to +12 months, absolute and vs SPY. The evidence behind the catalyst weights.</t>
         </is>
       </c>
       <c r="B2" s="3" t="n"/>
@@ -7896,16 +7896,16 @@
         </is>
       </c>
       <c r="B5" s="5" t="n">
-        <v>36</v>
+        <v>49</v>
       </c>
       <c r="C5" s="16" t="n">
         <v>10</v>
       </c>
       <c r="D5" s="19" t="n">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="E5" s="16" t="n">
-        <v>-10</v>
+        <v>-8</v>
       </c>
       <c r="F5" s="7" t="inlineStr">
         <is>
@@ -7920,16 +7920,16 @@
         </is>
       </c>
       <c r="B6" s="8" t="n">
-        <v>28</v>
+        <v>38</v>
       </c>
       <c r="C6" s="17" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="D6" s="20" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E6" s="17" t="n">
-        <v>-11</v>
+        <v>-13</v>
       </c>
       <c r="F6" s="10" t="inlineStr">
         <is>
@@ -7940,240 +7940,240 @@
     <row r="7" ht="16" customHeight="1">
       <c r="A7" s="6" t="inlineStr">
         <is>
-          <t>Buyback Auth</t>
+          <t>Spinoff</t>
         </is>
       </c>
       <c r="B7" s="5" t="n">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="C7" s="16" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D7" s="19" t="n">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="E7" s="16" t="n">
-        <v>-15</v>
+        <v>-18</v>
       </c>
       <c r="F7" s="7" t="inlineStr">
         <is>
-          <t>weak (+1%); float shrink, low signal</t>
+          <t>0% median but strong tail (1.6x); optionality</t>
         </is>
       </c>
     </row>
     <row r="8" ht="16" customHeight="1">
       <c r="A8" s="9" t="inlineStr">
         <is>
-          <t>Sale Of Company</t>
+          <t>Buyback Auth</t>
         </is>
       </c>
       <c r="B8" s="8" t="n">
-        <v>8</v>
+        <v>71</v>
       </c>
       <c r="C8" s="17" t="n">
-        <v>-6</v>
+        <v>-3</v>
       </c>
       <c r="D8" s="20" t="n">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="E8" s="17" t="n">
-        <v>-28</v>
+        <v>-25</v>
       </c>
       <c r="F8" s="10" t="inlineStr">
         <is>
-          <t>deal priced at 8-K; tail from contested deals only</t>
+          <t>weak (+1%); float shrink, low signal</t>
         </is>
       </c>
     </row>
     <row r="9" ht="16" customHeight="1">
       <c r="A9" s="6" t="inlineStr">
         <is>
-          <t>Capital Return</t>
+          <t>Separation</t>
         </is>
       </c>
       <c r="B9" s="5" t="n">
-        <v>38</v>
+        <v>9</v>
       </c>
       <c r="C9" s="16" t="n">
-        <v>-11</v>
+        <v>-4</v>
       </c>
       <c r="D9" s="19" t="n">
-        <v>29</v>
+        <v>44</v>
       </c>
       <c r="E9" s="16" t="n">
-        <v>-25</v>
+        <v>-26</v>
       </c>
       <c r="F9" s="7" t="inlineStr">
         <is>
-          <t>TRAP -11% — special dividend = no reinvestment</t>
+          <t>weak — 0% median, below-base tail</t>
         </is>
       </c>
     </row>
     <row r="10" ht="16" customHeight="1">
       <c r="A10" s="9" t="inlineStr">
         <is>
-          <t>Strategic Review</t>
+          <t>Capital Return</t>
         </is>
       </c>
       <c r="B10" s="8" t="n">
-        <v>25</v>
+        <v>53</v>
       </c>
       <c r="C10" s="17" t="n">
-        <v>-16</v>
+        <v>-6</v>
       </c>
       <c r="D10" s="20" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E10" s="17" t="n">
-        <v>-28</v>
+        <v>-22</v>
       </c>
       <c r="F10" s="10" t="inlineStr">
         <is>
-          <t>lottery — worst-but-one median, high tail variance</t>
+          <t>TRAP -11% — special dividend = no reinvestment</t>
         </is>
       </c>
     </row>
     <row r="11" ht="16" customHeight="1">
       <c r="A11" s="6" t="inlineStr">
         <is>
-          <t>Exchange Offer</t>
+          <t>Strategic Review</t>
         </is>
       </c>
       <c r="B11" s="5" t="n">
-        <v>19</v>
+        <v>38</v>
       </c>
       <c r="C11" s="16" t="n">
-        <v>-21</v>
+        <v>-12</v>
       </c>
       <c r="D11" s="19" t="n">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="E11" s="16" t="n">
-        <v>-38</v>
+        <v>-30</v>
       </c>
       <c r="F11" s="7" t="inlineStr">
         <is>
-          <t>TRAP -21% — distressed debt exchange</t>
+          <t>lottery — worst-but-one median, high tail variance</t>
         </is>
       </c>
     </row>
     <row r="12" ht="16" customHeight="1">
       <c r="A12" s="9" t="inlineStr">
         <is>
-          <t>Uplisting</t>
+          <t>Going Private</t>
         </is>
       </c>
       <c r="B12" s="8" t="n">
-        <v>39</v>
+        <v>15</v>
       </c>
       <c r="C12" s="17" t="n">
         <v>-23</v>
       </c>
       <c r="D12" s="20" t="n">
-        <v>36</v>
+        <v>27</v>
       </c>
       <c r="E12" s="17" t="n">
-        <v>-41</v>
+        <v>-38</v>
       </c>
       <c r="F12" s="10" t="inlineStr">
         <is>
-          <t>TRAP -23% — pump-and-fade microcaps</t>
+          <t>TRAP -37% — dead money at deal price, break risk</t>
         </is>
       </c>
     </row>
     <row r="13" ht="16" customHeight="1">
       <c r="A13" s="6" t="inlineStr">
         <is>
-          <t>Ch11 Emergence</t>
+          <t>Uplisting</t>
         </is>
       </c>
       <c r="B13" s="5" t="n">
-        <v>5</v>
+        <v>46</v>
       </c>
       <c r="C13" s="16" t="n">
-        <v>-30</v>
+        <v>-23</v>
       </c>
       <c r="D13" s="19" t="n">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="E13" s="16" t="n">
         <v>-42</v>
       </c>
       <c r="F13" s="7" t="inlineStr">
         <is>
-          <t>-30% (n=5) — post-reorg overhang</t>
+          <t>TRAP -23% — pump-and-fade microcaps</t>
         </is>
       </c>
     </row>
     <row r="14" ht="16" customHeight="1">
       <c r="A14" s="9" t="inlineStr">
         <is>
-          <t>Going Private</t>
+          <t>Sale Of Company</t>
         </is>
       </c>
       <c r="B14" s="8" t="n">
         <v>12</v>
       </c>
       <c r="C14" s="17" t="n">
-        <v>-37</v>
+        <v>-38</v>
       </c>
       <c r="D14" s="20" t="n">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="E14" s="17" t="n">
-        <v>-54</v>
+        <v>-62</v>
       </c>
       <c r="F14" s="10" t="inlineStr">
         <is>
-          <t>TRAP -37% — dead money at deal price, break risk</t>
+          <t>deal priced at 8-K; tail from contested deals only</t>
         </is>
       </c>
     </row>
     <row r="15" ht="16" customHeight="1">
       <c r="A15" s="6" t="inlineStr">
         <is>
-          <t>Separation</t>
+          <t>Ch11 Emergence</t>
         </is>
       </c>
       <c r="B15" s="5" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="C15" s="16" t="n">
         <v>0</v>
       </c>
       <c r="D15" s="19" t="n">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="E15" s="16" t="n">
         <v>-19</v>
       </c>
       <c r="F15" s="7" t="inlineStr">
         <is>
-          <t>weak — 0% median, below-base tail</t>
+          <t>-30% (n=5) — post-reorg overhang</t>
         </is>
       </c>
     </row>
     <row r="16" ht="16" customHeight="1">
       <c r="A16" s="9" t="inlineStr">
         <is>
-          <t>Spinoff</t>
+          <t>Exchange Offer</t>
         </is>
       </c>
       <c r="B16" s="8" t="n">
-        <v>39</v>
+        <v>19</v>
       </c>
       <c r="C16" s="17" t="n">
         <v>0</v>
       </c>
       <c r="D16" s="20" t="n">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="E16" s="17" t="n">
-        <v>-13</v>
+        <v>-25</v>
       </c>
       <c r="F16" s="10" t="inlineStr">
         <is>
-          <t>0% median but strong tail (1.6x); optionality</t>
+          <t>TRAP -21% — distressed debt exchange</t>
         </is>
       </c>
     </row>
@@ -8184,13 +8184,13 @@
         </is>
       </c>
       <c r="B17" s="5" t="n">
-        <v>314</v>
+        <v>417</v>
       </c>
       <c r="C17" s="16" t="n">
-        <v>-4</v>
+        <v>-3</v>
       </c>
       <c r="D17" s="19" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="E17" s="7" t="inlineStr">
         <is>
@@ -8237,17 +8237,17 @@
     <row r="21" ht="16" customHeight="1">
       <c r="A21" s="6" t="inlineStr">
         <is>
-          <t>SNDK</t>
+          <t>SYRE</t>
         </is>
       </c>
       <c r="B21" s="7" t="inlineStr">
         <is>
-          <t>Spinoff</t>
+          <t>Strategic Review</t>
         </is>
       </c>
       <c r="C21" s="7" t="inlineStr">
         <is>
-          <t>2025-02-03</t>
+          <t>2023-04-12</t>
         </is>
       </c>
       <c r="D21" s="7" t="inlineStr">
@@ -8256,7 +8256,7 @@
         </is>
       </c>
       <c r="E21" s="16" t="n">
-        <v>1235</v>
+        <v>975</v>
       </c>
       <c r="F21" s="7" t="inlineStr">
         <is>
@@ -8297,17 +8297,17 @@
     <row r="23" ht="16" customHeight="1">
       <c r="A23" s="6" t="inlineStr">
         <is>
-          <t>XCUR</t>
+          <t>CVNA</t>
         </is>
       </c>
       <c r="B23" s="7" t="inlineStr">
         <is>
-          <t>Strategic Review</t>
+          <t>Tender Offer</t>
         </is>
       </c>
       <c r="C23" s="7" t="inlineStr">
         <is>
-          <t>2024-02-05</t>
+          <t>2023-08-02</t>
         </is>
       </c>
       <c r="D23" s="7" t="inlineStr">
@@ -8316,7 +8316,7 @@
         </is>
       </c>
       <c r="E23" s="16" t="n">
-        <v>214</v>
+        <v>259</v>
       </c>
       <c r="F23" s="7" t="inlineStr">
         <is>
@@ -8327,7 +8327,7 @@
     <row r="24" ht="16" customHeight="1">
       <c r="A24" s="9" t="inlineStr">
         <is>
-          <t>AREC</t>
+          <t>MPTI</t>
         </is>
       </c>
       <c r="B24" s="10" t="inlineStr">
@@ -8337,7 +8337,7 @@
       </c>
       <c r="C24" s="10" t="inlineStr">
         <is>
-          <t>2024-08-19</t>
+          <t>2022-10-11</t>
         </is>
       </c>
       <c r="D24" s="10" t="inlineStr">
@@ -8346,7 +8346,7 @@
         </is>
       </c>
       <c r="E24" s="17" t="n">
-        <v>197</v>
+        <v>251</v>
       </c>
       <c r="F24" s="10" t="inlineStr">
         <is>
@@ -8357,17 +8357,17 @@
     <row r="25" ht="16" customHeight="1">
       <c r="A25" s="6" t="inlineStr">
         <is>
-          <t>CMTL</t>
+          <t>ESOA</t>
         </is>
       </c>
       <c r="B25" s="7" t="inlineStr">
         <is>
-          <t>Strategic Review</t>
+          <t>Capital Return</t>
         </is>
       </c>
       <c r="C25" s="7" t="inlineStr">
         <is>
-          <t>2025-01-13</t>
+          <t>2023-01-19</t>
         </is>
       </c>
       <c r="D25" s="7" t="inlineStr">
@@ -8376,7 +8376,7 @@
         </is>
       </c>
       <c r="E25" s="16" t="n">
-        <v>195</v>
+        <v>238</v>
       </c>
       <c r="F25" s="7" t="inlineStr">
         <is>
@@ -8387,17 +8387,17 @@
     <row r="26" ht="16" customHeight="1">
       <c r="A26" s="9" t="inlineStr">
         <is>
-          <t>MP</t>
+          <t>CMTL</t>
         </is>
       </c>
       <c r="B26" s="10" t="inlineStr">
         <is>
-          <t>Uplisting</t>
+          <t>Strategic Review</t>
         </is>
       </c>
       <c r="C26" s="10" t="inlineStr">
         <is>
-          <t>2024-12-10</t>
+          <t>2025-01-13</t>
         </is>
       </c>
       <c r="D26" s="10" t="inlineStr">
@@ -8406,7 +8406,7 @@
         </is>
       </c>
       <c r="E26" s="17" t="n">
-        <v>168</v>
+        <v>195</v>
       </c>
       <c r="F26" s="10" t="inlineStr">
         <is>
@@ -8417,17 +8417,17 @@
     <row r="27" ht="16" customHeight="1">
       <c r="A27" s="6" t="inlineStr">
         <is>
-          <t>MYRG</t>
+          <t>MP</t>
         </is>
       </c>
       <c r="B27" s="7" t="inlineStr">
         <is>
-          <t>Buyback Auth</t>
+          <t>Uplisting</t>
         </is>
       </c>
       <c r="C27" s="7" t="inlineStr">
         <is>
-          <t>2025-02-26</t>
+          <t>2024-12-10</t>
         </is>
       </c>
       <c r="D27" s="7" t="inlineStr">
@@ -8436,7 +8436,7 @@
         </is>
       </c>
       <c r="E27" s="16" t="n">
-        <v>150</v>
+        <v>168</v>
       </c>
       <c r="F27" s="7" t="inlineStr">
         <is>
@@ -8447,17 +8447,17 @@
     <row r="28" ht="16" customHeight="1">
       <c r="A28" s="9" t="inlineStr">
         <is>
-          <t>SEI</t>
+          <t>LION</t>
         </is>
       </c>
       <c r="B28" s="10" t="inlineStr">
         <is>
-          <t>Uplisting</t>
+          <t>Spinoff</t>
         </is>
       </c>
       <c r="C28" s="10" t="inlineStr">
         <is>
-          <t>2025-05-02</t>
+          <t>2025-05-07</t>
         </is>
       </c>
       <c r="D28" s="10" t="inlineStr">
@@ -8466,7 +8466,7 @@
         </is>
       </c>
       <c r="E28" s="17" t="n">
-        <v>146</v>
+        <v>164</v>
       </c>
       <c r="F28" s="10" t="inlineStr">
         <is>
@@ -8477,17 +8477,17 @@
     <row r="29" ht="16" customHeight="1">
       <c r="A29" s="6" t="inlineStr">
         <is>
-          <t>GEV</t>
+          <t>MYRG</t>
         </is>
       </c>
       <c r="B29" s="7" t="inlineStr">
         <is>
-          <t>Spinoff</t>
+          <t>Buyback Auth</t>
         </is>
       </c>
       <c r="C29" s="7" t="inlineStr">
         <is>
-          <t>2024-03-08</t>
+          <t>2025-02-26</t>
         </is>
       </c>
       <c r="D29" s="7" t="inlineStr">
@@ -8496,7 +8496,7 @@
         </is>
       </c>
       <c r="E29" s="16" t="n">
-        <v>141</v>
+        <v>150</v>
       </c>
       <c r="F29" s="7" t="inlineStr">
         <is>
@@ -8507,17 +8507,17 @@
     <row r="30" ht="16" customHeight="1">
       <c r="A30" s="9" t="inlineStr">
         <is>
-          <t>GRAL</t>
+          <t>AKA</t>
         </is>
       </c>
       <c r="B30" s="10" t="inlineStr">
         <is>
-          <t>Spinoff</t>
+          <t>Buyback Auth</t>
         </is>
       </c>
       <c r="C30" s="10" t="inlineStr">
         <is>
-          <t>2024-06-24</t>
+          <t>2023-06-06</t>
         </is>
       </c>
       <c r="D30" s="10" t="inlineStr">
@@ -8526,7 +8526,7 @@
         </is>
       </c>
       <c r="E30" s="17" t="n">
-        <v>122</v>
+        <v>149</v>
       </c>
       <c r="F30" s="10" t="inlineStr">
         <is>
@@ -8537,17 +8537,17 @@
     <row r="31" ht="16" customHeight="1">
       <c r="A31" s="6" t="inlineStr">
         <is>
-          <t>ALMU</t>
+          <t>VSTM</t>
         </is>
       </c>
       <c r="B31" s="7" t="inlineStr">
         <is>
-          <t>Uplisting</t>
+          <t>Asset Sale</t>
         </is>
       </c>
       <c r="C31" s="7" t="inlineStr">
         <is>
-          <t>2025-03-28</t>
+          <t>2023-02-02</t>
         </is>
       </c>
       <c r="D31" s="7" t="inlineStr">
@@ -8556,7 +8556,7 @@
         </is>
       </c>
       <c r="E31" s="16" t="n">
-        <v>122</v>
+        <v>147</v>
       </c>
       <c r="F31" s="7" t="inlineStr">
         <is>
@@ -8567,17 +8567,17 @@
     <row r="32" ht="16" customHeight="1">
       <c r="A32" s="9" t="inlineStr">
         <is>
-          <t>CCO</t>
+          <t>DBD</t>
         </is>
       </c>
       <c r="B32" s="10" t="inlineStr">
         <is>
-          <t>Asset Sale</t>
+          <t>Ch11 Emergence</t>
         </is>
       </c>
       <c r="C32" s="10" t="inlineStr">
         <is>
-          <t>2025-05-07</t>
+          <t>2023-08-09</t>
         </is>
       </c>
       <c r="D32" s="10" t="inlineStr">
@@ -8586,7 +8586,7 @@
         </is>
       </c>
       <c r="E32" s="17" t="n">
-        <v>107</v>
+        <v>136</v>
       </c>
       <c r="F32" s="10" t="inlineStr">
         <is>
@@ -8619,7 +8619,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:F81"/>
+  <dimension ref="A1:F105"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -8692,23 +8692,23 @@
     <row r="6" ht="22" customHeight="1">
       <c r="A6" s="6" t="inlineStr">
         <is>
-          <t>AGPU</t>
+          <t>NDRA</t>
         </is>
       </c>
       <c r="B6" s="7" t="inlineStr">
         <is>
-          <t>Axe Compute Inc.</t>
+          <t>ENDRA Life Sciences</t>
         </is>
       </c>
       <c r="C6" s="16" t="n">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="D6" s="16" t="n">
-        <v>44</v>
+        <v>20</v>
       </c>
       <c r="E6" s="7" t="inlineStr">
         <is>
-          <t>4.1m</t>
+          <t>5.8m</t>
         </is>
       </c>
       <c r="F6" s="7" t="inlineStr">
@@ -8720,23 +8720,23 @@
     <row r="7" ht="22" customHeight="1">
       <c r="A7" s="9" t="inlineStr">
         <is>
-          <t>GPRO</t>
+          <t>AGPU</t>
         </is>
       </c>
       <c r="B7" s="10" t="inlineStr">
         <is>
-          <t>GoPro, Inc.</t>
+          <t>Axe Compute Inc.</t>
         </is>
       </c>
       <c r="C7" s="17" t="n">
         <v>33</v>
       </c>
       <c r="D7" s="17" t="n">
-        <v>60</v>
+        <v>42</v>
       </c>
       <c r="E7" s="10" t="inlineStr">
         <is>
-          <t>2.3m</t>
+          <t>4.1m</t>
         </is>
       </c>
       <c r="F7" s="10" t="inlineStr">
@@ -8748,135 +8748,135 @@
     <row r="8" ht="22" customHeight="1">
       <c r="A8" s="6" t="inlineStr">
         <is>
-          <t>FWDI</t>
+          <t>GPRO</t>
         </is>
       </c>
       <c r="B8" s="7" t="inlineStr">
         <is>
-          <t>Forward Industries,</t>
+          <t>GoPro, Inc.</t>
         </is>
       </c>
       <c r="C8" s="16" t="n">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="D8" s="16" t="n">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="E8" s="7" t="inlineStr">
         <is>
-          <t>6.3m</t>
+          <t>2.3m</t>
         </is>
       </c>
       <c r="F8" s="7" t="inlineStr">
         <is>
-          <t>SALE_OF_COMPANY</t>
+          <t>STRATEGIC_REVIEW</t>
         </is>
       </c>
     </row>
     <row r="9" ht="22" customHeight="1">
       <c r="A9" s="9" t="inlineStr">
         <is>
-          <t>PRGO</t>
+          <t>PTN</t>
         </is>
       </c>
       <c r="B9" s="10" t="inlineStr">
         <is>
-          <t>Perrigo Company plc</t>
+          <t>Palatin Technologies</t>
         </is>
       </c>
       <c r="C9" s="17" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D9" s="17" t="n">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="E9" s="10" t="inlineStr">
         <is>
-          <t>6.7m</t>
+          <t>4.0m</t>
         </is>
       </c>
       <c r="F9" s="10" t="inlineStr">
         <is>
-          <t>ASSET_SALE</t>
+          <t>UPLISTING</t>
         </is>
       </c>
     </row>
     <row r="10" ht="22" customHeight="1">
       <c r="A10" s="6" t="inlineStr">
         <is>
-          <t>CERT</t>
+          <t>FWDI</t>
         </is>
       </c>
       <c r="B10" s="7" t="inlineStr">
         <is>
-          <t>Certara, Inc.</t>
+          <t>Forward Industries,</t>
         </is>
       </c>
       <c r="C10" s="16" t="n">
         <v>31</v>
       </c>
       <c r="D10" s="16" t="n">
-        <v>34</v>
+        <v>51</v>
       </c>
       <c r="E10" s="7" t="inlineStr">
         <is>
-          <t>4.8m</t>
+          <t>6.3m</t>
         </is>
       </c>
       <c r="F10" s="7" t="inlineStr">
         <is>
-          <t>ASSET_SALE</t>
+          <t>SALE_OF_COMPANY</t>
         </is>
       </c>
     </row>
     <row r="11" ht="22" customHeight="1">
       <c r="A11" s="9" t="inlineStr">
         <is>
-          <t>ANGX</t>
+          <t>PRGO</t>
         </is>
       </c>
       <c r="B11" s="10" t="inlineStr">
         <is>
-          <t>Angel Studios, Inc.</t>
+          <t>Perrigo Company plc</t>
         </is>
       </c>
       <c r="C11" s="17" t="n">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="D11" s="17" t="n">
-        <v>101</v>
+        <v>27</v>
       </c>
       <c r="E11" s="10" t="inlineStr">
         <is>
-          <t>5.1m</t>
+          <t>6.7m</t>
         </is>
       </c>
       <c r="F11" s="10" t="inlineStr">
         <is>
-          <t>UPLISTING</t>
+          <t>ASSET_SALE</t>
         </is>
       </c>
     </row>
     <row r="12" ht="22" customHeight="1">
       <c r="A12" s="6" t="inlineStr">
         <is>
-          <t>IT</t>
+          <t>CERT</t>
         </is>
       </c>
       <c r="B12" s="7" t="inlineStr">
         <is>
-          <t>Gartner, Inc.</t>
+          <t>Certara, Inc.</t>
         </is>
       </c>
       <c r="C12" s="16" t="n">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="D12" s="16" t="n">
-        <v>22</v>
+        <v>38</v>
       </c>
       <c r="E12" s="7" t="inlineStr">
         <is>
-          <t>7.4m</t>
+          <t>4.9m</t>
         </is>
       </c>
       <c r="F12" s="7" t="inlineStr">
@@ -8888,247 +8888,247 @@
     <row r="13" ht="22" customHeight="1">
       <c r="A13" s="9" t="inlineStr">
         <is>
-          <t>DUOL</t>
+          <t>ANGX</t>
         </is>
       </c>
       <c r="B13" s="10" t="inlineStr">
         <is>
-          <t>Duolingo, Inc.</t>
+          <t>Angel Studios, Inc.</t>
         </is>
       </c>
       <c r="C13" s="17" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="D13" s="17" t="n">
-        <v>56</v>
+        <v>98</v>
       </c>
       <c r="E13" s="10" t="inlineStr">
         <is>
-          <t>6.7m</t>
+          <t>5.2m</t>
         </is>
       </c>
       <c r="F13" s="10" t="inlineStr">
         <is>
-          <t>BUYBACK_AUTH</t>
+          <t>UPLISTING</t>
         </is>
       </c>
     </row>
     <row r="14" ht="22" customHeight="1">
       <c r="A14" s="6" t="inlineStr">
         <is>
-          <t>SMCI</t>
+          <t>IT</t>
         </is>
       </c>
       <c r="B14" s="7" t="inlineStr">
         <is>
-          <t>Super Micro Computer</t>
+          <t>Gartner, Inc.</t>
         </is>
       </c>
       <c r="C14" s="16" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D14" s="16" t="n">
-        <v>34</v>
+        <v>24</v>
       </c>
       <c r="E14" s="7" t="inlineStr">
         <is>
-          <t>3.1m</t>
+          <t>7.5m</t>
         </is>
       </c>
       <c r="F14" s="7" t="inlineStr">
         <is>
-          <t>UPLISTING</t>
+          <t>ASSET_SALE</t>
         </is>
       </c>
     </row>
     <row r="15" ht="22" customHeight="1">
       <c r="A15" s="9" t="inlineStr">
         <is>
-          <t>CNMD</t>
+          <t>DUOL</t>
         </is>
       </c>
       <c r="B15" s="10" t="inlineStr">
         <is>
-          <t>CONMED Corporation</t>
+          <t>Duolingo, Inc.</t>
         </is>
       </c>
       <c r="C15" s="17" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D15" s="17" t="n">
-        <v>30</v>
+        <v>53</v>
       </c>
       <c r="E15" s="10" t="inlineStr">
         <is>
-          <t>4.6m</t>
+          <t>6.7m</t>
         </is>
       </c>
       <c r="F15" s="10" t="inlineStr">
         <is>
-          <t>ASSET_SALE</t>
+          <t>BUYBACK_AUTH</t>
         </is>
       </c>
     </row>
     <row r="16" ht="22" customHeight="1">
       <c r="A16" s="6" t="inlineStr">
         <is>
-          <t>PAR</t>
+          <t>SMCI</t>
         </is>
       </c>
       <c r="B16" s="7" t="inlineStr">
         <is>
-          <t>PAR Technology Corpo</t>
+          <t>Super Micro Computer</t>
         </is>
       </c>
       <c r="C16" s="16" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D16" s="16" t="n">
-        <v>39</v>
+        <v>29</v>
       </c>
       <c r="E16" s="7" t="inlineStr">
         <is>
-          <t>6.7m</t>
+          <t>3.2m</t>
         </is>
       </c>
       <c r="F16" s="7" t="inlineStr">
         <is>
-          <t>BUYBACK_AUTH</t>
+          <t>UPLISTING</t>
         </is>
       </c>
     </row>
     <row r="17" ht="22" customHeight="1">
       <c r="A17" s="9" t="inlineStr">
         <is>
-          <t>PD</t>
+          <t>CNMD</t>
         </is>
       </c>
       <c r="B17" s="10" t="inlineStr">
         <is>
-          <t>PagerDuty, Inc.</t>
+          <t>CONMED Corporation</t>
         </is>
       </c>
       <c r="C17" s="17" t="n">
         <v>25</v>
       </c>
       <c r="D17" s="17" t="n">
-        <v>53</v>
+        <v>30</v>
       </c>
       <c r="E17" s="10" t="inlineStr">
         <is>
-          <t>3.6m</t>
+          <t>4.6m</t>
         </is>
       </c>
       <c r="F17" s="10" t="inlineStr">
         <is>
-          <t>BUYBACK_AUTH</t>
+          <t>ASSET_SALE</t>
         </is>
       </c>
     </row>
     <row r="18" ht="22" customHeight="1">
       <c r="A18" s="6" t="inlineStr">
         <is>
-          <t>ORKA</t>
+          <t>PAR</t>
         </is>
       </c>
       <c r="B18" s="7" t="inlineStr">
         <is>
-          <t>Oruka Therapeutics,</t>
+          <t>PAR Technology Corpo</t>
         </is>
       </c>
       <c r="C18" s="16" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D18" s="16" t="n">
-        <v>64</v>
+        <v>36</v>
       </c>
       <c r="E18" s="7" t="inlineStr">
         <is>
-          <t>4.6m</t>
+          <t>6.7m</t>
         </is>
       </c>
       <c r="F18" s="7" t="inlineStr">
         <is>
-          <t>UPLISTING</t>
+          <t>BUYBACK_AUTH</t>
         </is>
       </c>
     </row>
     <row r="19" ht="22" customHeight="1">
       <c r="A19" s="9" t="inlineStr">
         <is>
-          <t>ACHV</t>
+          <t>PD</t>
         </is>
       </c>
       <c r="B19" s="10" t="inlineStr">
         <is>
-          <t>Achieve Life Science</t>
+          <t>PagerDuty, Inc.</t>
         </is>
       </c>
       <c r="C19" s="17" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="D19" s="17" t="n">
-        <v>36</v>
+        <v>54</v>
       </c>
       <c r="E19" s="10" t="inlineStr">
         <is>
-          <t>4.6m</t>
+          <t>3.7m</t>
         </is>
       </c>
       <c r="F19" s="10" t="inlineStr">
         <is>
-          <t>ASSET_SALE</t>
+          <t>BUYBACK_AUTH</t>
         </is>
       </c>
     </row>
     <row r="20" ht="22" customHeight="1">
       <c r="A20" s="6" t="inlineStr">
         <is>
-          <t>ANF</t>
+          <t>ORKA</t>
         </is>
       </c>
       <c r="B20" s="7" t="inlineStr">
         <is>
-          <t>Abercrombie &amp; Fitch</t>
+          <t>Oruka Therapeutics,</t>
         </is>
       </c>
       <c r="C20" s="16" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D20" s="16" t="n">
-        <v>69</v>
+        <v>64</v>
       </c>
       <c r="E20" s="7" t="inlineStr">
         <is>
-          <t>5.7m</t>
+          <t>4.6m</t>
         </is>
       </c>
       <c r="F20" s="7" t="inlineStr">
         <is>
-          <t>STRATEGIC_REVIEW</t>
+          <t>UPLISTING</t>
         </is>
       </c>
     </row>
     <row r="21" ht="22" customHeight="1">
       <c r="A21" s="9" t="inlineStr">
         <is>
-          <t>VSAT</t>
+          <t>ACHV</t>
         </is>
       </c>
       <c r="B21" s="10" t="inlineStr">
         <is>
-          <t>ViaSat, Inc.</t>
+          <t>Achieve Life Science</t>
         </is>
       </c>
       <c r="C21" s="17" t="n">
         <v>23</v>
       </c>
       <c r="D21" s="17" t="n">
-        <v>59</v>
+        <v>38</v>
       </c>
       <c r="E21" s="10" t="inlineStr">
         <is>
-          <t>7.4m</t>
+          <t>4.6m</t>
         </is>
       </c>
       <c r="F21" s="10" t="inlineStr">
@@ -9140,51 +9140,51 @@
     <row r="22" ht="22" customHeight="1">
       <c r="A22" s="6" t="inlineStr">
         <is>
-          <t>AZTA</t>
+          <t>ANF</t>
         </is>
       </c>
       <c r="B22" s="7" t="inlineStr">
         <is>
-          <t>Azenta, Inc.</t>
+          <t>Abercrombie &amp; Fitch</t>
         </is>
       </c>
       <c r="C22" s="16" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D22" s="16" t="n">
-        <v>49</v>
+        <v>65</v>
       </c>
       <c r="E22" s="7" t="inlineStr">
         <is>
-          <t>7.4m</t>
+          <t>5.8m</t>
         </is>
       </c>
       <c r="F22" s="7" t="inlineStr">
         <is>
-          <t>BUYBACK_AUTH</t>
+          <t>STRATEGIC_REVIEW</t>
         </is>
       </c>
     </row>
     <row r="23" ht="22" customHeight="1">
       <c r="A23" s="9" t="inlineStr">
         <is>
-          <t>ASH</t>
+          <t>VSAT</t>
         </is>
       </c>
       <c r="B23" s="10" t="inlineStr">
         <is>
-          <t>Ashland Inc.</t>
+          <t>ViaSat, Inc.</t>
         </is>
       </c>
       <c r="C23" s="17" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D23" s="17" t="n">
-        <v>21</v>
+        <v>56</v>
       </c>
       <c r="E23" s="10" t="inlineStr">
         <is>
-          <t>4.6m</t>
+          <t>7.4m</t>
         </is>
       </c>
       <c r="F23" s="10" t="inlineStr">
@@ -9196,262 +9196,266 @@
     <row r="24" ht="22" customHeight="1">
       <c r="A24" s="6" t="inlineStr">
         <is>
-          <t>GRND</t>
+          <t>AZTA</t>
         </is>
       </c>
       <c r="B24" s="7" t="inlineStr">
         <is>
-          <t>Grindr Inc.</t>
+          <t>Azenta, Inc.</t>
         </is>
       </c>
       <c r="C24" s="16" t="n">
         <v>22</v>
       </c>
       <c r="D24" s="16" t="n">
-        <v>28</v>
+        <v>52</v>
       </c>
       <c r="E24" s="7" t="inlineStr">
         <is>
-          <t>6.7m</t>
+          <t>7.4m</t>
         </is>
       </c>
       <c r="F24" s="7" t="inlineStr">
         <is>
-          <t>GOING_PRIVATE</t>
+          <t>BUYBACK_AUTH</t>
         </is>
       </c>
     </row>
     <row r="25" ht="22" customHeight="1">
       <c r="A25" s="9" t="inlineStr">
         <is>
-          <t>TASK</t>
+          <t>ASH</t>
         </is>
       </c>
       <c r="B25" s="10" t="inlineStr">
         <is>
-          <t>TaskUs, Inc.</t>
+          <t>Ashland Inc.</t>
         </is>
       </c>
       <c r="C25" s="17" t="n">
         <v>22</v>
       </c>
       <c r="D25" s="17" t="n">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="E25" s="10" t="inlineStr">
         <is>
-          <t>6.0m</t>
+          <t>4.6m</t>
         </is>
       </c>
       <c r="F25" s="10" t="inlineStr">
         <is>
+          <t>ASSET_SALE</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="22" customHeight="1">
+      <c r="A26" s="6" t="inlineStr">
+        <is>
+          <t>GRND</t>
+        </is>
+      </c>
+      <c r="B26" s="7" t="inlineStr">
+        <is>
+          <t>Grindr Inc.</t>
+        </is>
+      </c>
+      <c r="C26" s="16" t="n">
+        <v>22</v>
+      </c>
+      <c r="D26" s="16" t="n">
+        <v>30</v>
+      </c>
+      <c r="E26" s="7" t="inlineStr">
+        <is>
+          <t>6.7m</t>
+        </is>
+      </c>
+      <c r="F26" s="7" t="inlineStr">
+        <is>
+          <t>GOING_PRIVATE</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="22" customHeight="1">
+      <c r="A27" s="9" t="inlineStr">
+        <is>
+          <t>TASK</t>
+        </is>
+      </c>
+      <c r="B27" s="10" t="inlineStr">
+        <is>
+          <t>TaskUs, Inc.</t>
+        </is>
+      </c>
+      <c r="C27" s="17" t="n">
+        <v>22</v>
+      </c>
+      <c r="D27" s="17" t="n">
+        <v>27</v>
+      </c>
+      <c r="E27" s="10" t="inlineStr">
+        <is>
+          <t>6.1m</t>
+        </is>
+      </c>
+      <c r="F27" s="10" t="inlineStr">
+        <is>
           <t>CAPITAL_RETURN</t>
         </is>
       </c>
     </row>
-    <row r="26">
-      <c r="A26" s="21" t="inlineStr">
-        <is>
-          <t>(20 confirmed / 15 pending / 79 neutral / 32 fading, of 146 priced)</t>
-        </is>
-      </c>
-    </row>
     <row r="28">
-      <c r="A28" s="12" t="inlineStr">
-        <is>
-          <t>ALL CANDIDATES — pre-confirmation tail odds</t>
-        </is>
-      </c>
-    </row>
-    <row r="29" ht="18" customHeight="1">
-      <c r="A29" s="15" t="inlineStr">
+      <c r="A28" s="21" t="inlineStr">
+        <is>
+          <t>(22 confirmed / 15 pending / 76 neutral / 33 fading, of 146 priced)</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="12" t="inlineStr">
+        <is>
+          <t>MONSTER SETUPS — the greatest-trades washout fingerprint (deep 24m drawdown + wild vol + bottom of range + decelerating + monster-rich catalyst)</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="18" customHeight="1">
+      <c r="A31" s="15" t="inlineStr">
         <is>
           <t>Ticker</t>
         </is>
       </c>
-      <c r="B29" s="15" t="inlineStr">
+      <c r="B31" s="15" t="inlineStr">
         <is>
           <t>Name</t>
         </is>
       </c>
-      <c r="C29" s="4" t="inlineStr">
+      <c r="C31" s="4" t="inlineStr">
+        <is>
+          <t>Monster</t>
+        </is>
+      </c>
+      <c r="D31" s="4" t="inlineStr">
+        <is>
+          <t>State</t>
+        </is>
+      </c>
+      <c r="E31" s="4" t="inlineStr">
         <is>
           <t>Tail p</t>
         </is>
       </c>
-      <c r="D29" s="4" t="inlineStr">
-        <is>
-          <t>State</t>
-        </is>
-      </c>
-      <c r="E29" s="4" t="inlineStr">
-        <is>
-          <t>Ratio</t>
-        </is>
-      </c>
-      <c r="F29" s="4" t="inlineStr">
-        <is>
-          <t>Tail drivers</t>
-        </is>
-      </c>
-    </row>
-    <row r="30" ht="22" customHeight="1">
-      <c r="A30" s="6" t="inlineStr">
-        <is>
-          <t>USAR</t>
-        </is>
-      </c>
-      <c r="B30" s="7" t="inlineStr">
-        <is>
-          <t>USA Rare Earth, Inc.</t>
-        </is>
-      </c>
-      <c r="C30" s="16" t="n">
-        <v>28</v>
-      </c>
-      <c r="D30" s="7" t="inlineStr">
-        <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="E30" s="7" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="F30" s="7" t="inlineStr">
-        <is>
-          <t>catalyst=SALE_OF_COMPANY, sector=Basic</t>
-        </is>
-      </c>
-    </row>
-    <row r="31" ht="22" customHeight="1">
-      <c r="A31" s="9" t="inlineStr">
-        <is>
-          <t>AMS</t>
-        </is>
-      </c>
-      <c r="B31" s="10" t="inlineStr">
-        <is>
-          <t>American Shared Hosp</t>
-        </is>
-      </c>
-      <c r="C31" s="17" t="n">
-        <v>27</v>
-      </c>
-      <c r="D31" s="10" t="inlineStr">
-        <is>
-          <t>NEUTRAL</t>
-        </is>
-      </c>
-      <c r="E31" s="17" t="n">
-        <v>60</v>
-      </c>
-      <c r="F31" s="10" t="inlineStr">
-        <is>
-          <t>catalyst=SALE_OF_COMPANY, sector=Healt</t>
+      <c r="F31" s="4" t="inlineStr">
+        <is>
+          <t>Fingerprint</t>
         </is>
       </c>
     </row>
     <row r="32" ht="22" customHeight="1">
       <c r="A32" s="6" t="inlineStr">
         <is>
-          <t>BTAI</t>
+          <t>NEUP</t>
         </is>
       </c>
       <c r="B32" s="7" t="inlineStr">
         <is>
-          <t>BioXcel Therapeutics</t>
-        </is>
-      </c>
-      <c r="C32" s="16" t="n">
-        <v>27</v>
+          <t>Neuphoria Therapeuti</t>
+        </is>
+      </c>
+      <c r="C32" s="7" t="inlineStr">
+        <is>
+          <t>10/10</t>
+        </is>
       </c>
       <c r="D32" s="7" t="inlineStr">
         <is>
-          <t>NEUTRAL</t>
-        </is>
-      </c>
-      <c r="E32" s="7" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+          <t>FADING</t>
+        </is>
+      </c>
+      <c r="E32" s="16" t="n">
+        <v>21</v>
       </c>
       <c r="F32" s="7" t="inlineStr">
         <is>
-          <t>catalyst=SALE_OF_COMPANY, sector=Healt</t>
+          <t>deep 24m washout (-63%); wild vol (0.25); bo</t>
         </is>
       </c>
     </row>
     <row r="33" ht="22" customHeight="1">
       <c r="A33" s="9" t="inlineStr">
         <is>
-          <t>SUNE</t>
+          <t>DOMO</t>
         </is>
       </c>
       <c r="B33" s="10" t="inlineStr">
         <is>
-          <t>SUNation Energy, Inc</t>
-        </is>
-      </c>
-      <c r="C33" s="17" t="n">
-        <v>25</v>
+          <t>Domo, Inc.</t>
+        </is>
+      </c>
+      <c r="C33" s="10" t="inlineStr">
+        <is>
+          <t>10/10</t>
+        </is>
       </c>
       <c r="D33" s="10" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>NEUTRAL</t>
         </is>
       </c>
       <c r="E33" s="17" t="n">
-        <v>60</v>
+        <v>21</v>
       </c>
       <c r="F33" s="10" t="inlineStr">
         <is>
-          <t>catalyst=SALE_OF_COMPANY, sector=Techn</t>
+          <t>deep 24m washout (-77%); wild vol (0.20); bo</t>
         </is>
       </c>
     </row>
     <row r="34" ht="22" customHeight="1">
       <c r="A34" s="6" t="inlineStr">
         <is>
-          <t>JTAI</t>
+          <t>TTEC</t>
         </is>
       </c>
       <c r="B34" s="7" t="inlineStr">
         <is>
-          <t>Jet.AI Inc.</t>
-        </is>
-      </c>
-      <c r="C34" s="16" t="n">
-        <v>25</v>
+          <t>TTEC Holdings, Inc.</t>
+        </is>
+      </c>
+      <c r="C34" s="7" t="inlineStr">
+        <is>
+          <t>10/10</t>
+        </is>
       </c>
       <c r="D34" s="7" t="inlineStr">
         <is>
-          <t>FADING</t>
+          <t>NEUTRAL</t>
         </is>
       </c>
       <c r="E34" s="16" t="n">
-        <v>60</v>
+        <v>21</v>
       </c>
       <c r="F34" s="7" t="inlineStr">
         <is>
-          <t>catalyst=SALE_OF_COMPANY, sector=Techn</t>
+          <t>deep 24m washout (-78%); wild vol (0.20); bo</t>
         </is>
       </c>
     </row>
     <row r="35" ht="22" customHeight="1">
       <c r="A35" s="9" t="inlineStr">
         <is>
-          <t>OPTU</t>
+          <t>SPRB</t>
         </is>
       </c>
       <c r="B35" s="10" t="inlineStr">
         <is>
-          <t>Optimum Communicatio</t>
-        </is>
-      </c>
-      <c r="C35" s="17" t="n">
-        <v>24</v>
+          <t>Spruce Biosciences,</t>
+        </is>
+      </c>
+      <c r="C35" s="10" t="inlineStr">
+        <is>
+          <t>10/10</t>
+        </is>
       </c>
       <c r="D35" s="10" t="inlineStr">
         <is>
@@ -9459,283 +9463,299 @@
         </is>
       </c>
       <c r="E35" s="17" t="n">
-        <v>3</v>
+        <v>20</v>
       </c>
       <c r="F35" s="10" t="inlineStr">
         <is>
-          <t>catalyst=SALE_OF_COMPANY, sector=Commu</t>
+          <t>deep 24m washout (-98%); wild vol (3.29); bo</t>
         </is>
       </c>
     </row>
     <row r="36" ht="22" customHeight="1">
       <c r="A36" s="6" t="inlineStr">
         <is>
-          <t>NEUP</t>
+          <t>LAB</t>
         </is>
       </c>
       <c r="B36" s="7" t="inlineStr">
         <is>
-          <t>Neuphoria Therapeuti</t>
-        </is>
-      </c>
-      <c r="C36" s="16" t="n">
-        <v>23</v>
+          <t>Standard BioTools In</t>
+        </is>
+      </c>
+      <c r="C36" s="7" t="inlineStr">
+        <is>
+          <t>10/10</t>
+        </is>
       </c>
       <c r="D36" s="7" t="inlineStr">
         <is>
-          <t>FADING</t>
+          <t>NEUTRAL</t>
         </is>
       </c>
       <c r="E36" s="16" t="n">
-        <v>3.9</v>
+        <v>19</v>
       </c>
       <c r="F36" s="7" t="inlineStr">
         <is>
-          <t>catalyst=STRATEGIC_REVIEW, sector=Heal</t>
+          <t>deep 24m washout (-65%); wild vol (0.18); bo</t>
         </is>
       </c>
     </row>
     <row r="37" ht="22" customHeight="1">
       <c r="A37" s="9" t="inlineStr">
         <is>
-          <t>NERV</t>
+          <t>CNDT</t>
         </is>
       </c>
       <c r="B37" s="10" t="inlineStr">
         <is>
-          <t>Minerva Neuroscience</t>
-        </is>
-      </c>
-      <c r="C37" s="17" t="n">
-        <v>23</v>
+          <t>Conduent Incorporate</t>
+        </is>
+      </c>
+      <c r="C37" s="10" t="inlineStr">
+        <is>
+          <t>10/10</t>
+        </is>
       </c>
       <c r="D37" s="10" t="inlineStr">
         <is>
-          <t>FADING</t>
-        </is>
-      </c>
-      <c r="E37" s="10" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+          <t>NEUTRAL</t>
+        </is>
+      </c>
+      <c r="E37" s="17" t="n">
+        <v>19</v>
       </c>
       <c r="F37" s="10" t="inlineStr">
         <is>
-          <t>catalyst=STRATEGIC_REVIEW, sector=Heal</t>
+          <t>deep 24m washout (-61%); wild vol (0.16); bo</t>
         </is>
       </c>
     </row>
     <row r="38" ht="22" customHeight="1">
       <c r="A38" s="6" t="inlineStr">
         <is>
-          <t>FULC</t>
+          <t>THRY</t>
         </is>
       </c>
       <c r="B38" s="7" t="inlineStr">
         <is>
-          <t>Fulcrum Therapeutics</t>
-        </is>
-      </c>
-      <c r="C38" s="16" t="n">
-        <v>23</v>
+          <t>Thryv Holdings, Inc.</t>
+        </is>
+      </c>
+      <c r="C38" s="7" t="inlineStr">
+        <is>
+          <t>10/10</t>
+        </is>
       </c>
       <c r="D38" s="7" t="inlineStr">
         <is>
-          <t>NEUTRAL</t>
+          <t>PENDING</t>
         </is>
       </c>
       <c r="E38" s="16" t="n">
-        <v>8.300000000000001</v>
+        <v>19</v>
       </c>
       <c r="F38" s="7" t="inlineStr">
         <is>
-          <t>catalyst=STRATEGIC_REVIEW, sector=Heal</t>
+          <t>deep 24m washout (-89%); wild vol (0.26); bo</t>
         </is>
       </c>
     </row>
     <row r="39" ht="22" customHeight="1">
       <c r="A39" s="9" t="inlineStr">
         <is>
-          <t>NDRA</t>
+          <t>CCOI</t>
         </is>
       </c>
       <c r="B39" s="10" t="inlineStr">
         <is>
-          <t>ENDRA Life Sciences</t>
-        </is>
-      </c>
-      <c r="C39" s="17" t="n">
-        <v>23</v>
+          <t>Cogent Communication</t>
+        </is>
+      </c>
+      <c r="C39" s="10" t="inlineStr">
+        <is>
+          <t>10/10</t>
+        </is>
       </c>
       <c r="D39" s="10" t="inlineStr">
         <is>
-          <t>NEUTRAL</t>
-        </is>
-      </c>
-      <c r="E39" s="10" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+          <t>FADING</t>
+        </is>
+      </c>
+      <c r="E39" s="17" t="n">
+        <v>16</v>
       </c>
       <c r="F39" s="10" t="inlineStr">
         <is>
-          <t>catalyst=STRATEGIC_REVIEW, sector=Heal</t>
+          <t>deep 24m washout (-84%); wild vol (0.22); bo</t>
         </is>
       </c>
     </row>
     <row r="40" ht="22" customHeight="1">
       <c r="A40" s="6" t="inlineStr">
         <is>
-          <t>GPRO</t>
+          <t>HYFM</t>
         </is>
       </c>
       <c r="B40" s="7" t="inlineStr">
         <is>
-          <t>GoPro, Inc.</t>
-        </is>
-      </c>
-      <c r="C40" s="16" t="n">
-        <v>21</v>
+          <t>Hydrofarm Holdings G</t>
+        </is>
+      </c>
+      <c r="C40" s="7" t="inlineStr">
+        <is>
+          <t>10/10</t>
+        </is>
       </c>
       <c r="D40" s="7" t="inlineStr">
         <is>
-          <t>CONFIRMED</t>
+          <t>NEUTRAL</t>
         </is>
       </c>
       <c r="E40" s="16" t="n">
-        <v>3</v>
+        <v>18</v>
       </c>
       <c r="F40" s="7" t="inlineStr">
         <is>
-          <t>catalyst=STRATEGIC_REVIEW, sector=Tech</t>
+          <t>deep 24m washout (-90%); wild vol (0.15); bo</t>
         </is>
       </c>
     </row>
     <row r="41" ht="22" customHeight="1">
       <c r="A41" s="9" t="inlineStr">
         <is>
-          <t>TTEC</t>
+          <t>OPTT</t>
         </is>
       </c>
       <c r="B41" s="10" t="inlineStr">
         <is>
-          <t>TTEC Holdings, Inc.</t>
-        </is>
-      </c>
-      <c r="C41" s="17" t="n">
-        <v>21</v>
+          <t>Ocean Power Technolo</t>
+        </is>
+      </c>
+      <c r="C41" s="10" t="inlineStr">
+        <is>
+          <t>10/10</t>
+        </is>
       </c>
       <c r="D41" s="10" t="inlineStr">
         <is>
-          <t>NEUTRAL</t>
+          <t>PENDING</t>
         </is>
       </c>
       <c r="E41" s="17" t="n">
-        <v>20.3</v>
+        <v>18</v>
       </c>
       <c r="F41" s="10" t="inlineStr">
         <is>
-          <t>catalyst=STRATEGIC_REVIEW, sector=Tech</t>
+          <t>deep 24m washout (-91%); wild vol (0.27); bo</t>
         </is>
       </c>
     </row>
     <row r="42" ht="22" customHeight="1">
       <c r="A42" s="6" t="inlineStr">
         <is>
-          <t>CMTL</t>
+          <t>CRMT</t>
         </is>
       </c>
       <c r="B42" s="7" t="inlineStr">
         <is>
-          <t>Comtech Telecommunic</t>
-        </is>
-      </c>
-      <c r="C42" s="16" t="n">
-        <v>21</v>
+          <t>America's Car-Mart,</t>
+        </is>
+      </c>
+      <c r="C42" s="7" t="inlineStr">
+        <is>
+          <t>10/10</t>
+        </is>
       </c>
       <c r="D42" s="7" t="inlineStr">
         <is>
-          <t>FADING</t>
+          <t>PENDING</t>
         </is>
       </c>
       <c r="E42" s="16" t="n">
-        <v>11.5</v>
+        <v>18</v>
       </c>
       <c r="F42" s="7" t="inlineStr">
         <is>
-          <t>catalyst=STRATEGIC_REVIEW, sector=Tech</t>
+          <t>deep 24m washout (-97%); wild vol (0.26); bo</t>
         </is>
       </c>
     </row>
     <row r="43" ht="22" customHeight="1">
       <c r="A43" s="9" t="inlineStr">
         <is>
-          <t>DOMO</t>
+          <t>SMCI</t>
         </is>
       </c>
       <c r="B43" s="10" t="inlineStr">
         <is>
-          <t>Domo, Inc.</t>
-        </is>
-      </c>
-      <c r="C43" s="17" t="n">
-        <v>21</v>
+          <t>Super Micro Computer</t>
+        </is>
+      </c>
+      <c r="C43" s="10" t="inlineStr">
+        <is>
+          <t>10/10</t>
+        </is>
       </c>
       <c r="D43" s="10" t="inlineStr">
         <is>
-          <t>NEUTRAL</t>
+          <t>CONFIRMED</t>
         </is>
       </c>
       <c r="E43" s="17" t="n">
-        <v>3</v>
+        <v>26</v>
       </c>
       <c r="F43" s="10" t="inlineStr">
         <is>
-          <t>catalyst=STRATEGIC_REVIEW, sector=Tech</t>
+          <t>deep 24m washout (-60%); wild vol (0.30); bo</t>
         </is>
       </c>
     </row>
     <row r="44" ht="22" customHeight="1">
       <c r="A44" s="6" t="inlineStr">
         <is>
-          <t>AGPU</t>
+          <t>HAIN</t>
         </is>
       </c>
       <c r="B44" s="7" t="inlineStr">
         <is>
-          <t>Axe Compute Inc.</t>
-        </is>
-      </c>
-      <c r="C44" s="16" t="n">
-        <v>21</v>
+          <t>The Hain Celestial G</t>
+        </is>
+      </c>
+      <c r="C44" s="7" t="inlineStr">
+        <is>
+          <t>10/10</t>
+        </is>
       </c>
       <c r="D44" s="7" t="inlineStr">
         <is>
-          <t>CONFIRMED</t>
+          <t>PENDING</t>
         </is>
       </c>
       <c r="E44" s="16" t="n">
-        <v>8.4</v>
+        <v>16</v>
       </c>
       <c r="F44" s="7" t="inlineStr">
         <is>
-          <t>catalyst=STRATEGIC_REVIEW, sector=Tech</t>
+          <t>deep 24m washout (-93%); wild vol (0.23); bo</t>
         </is>
       </c>
     </row>
     <row r="45" ht="22" customHeight="1">
       <c r="A45" s="9" t="inlineStr">
         <is>
-          <t>VRME</t>
+          <t>BIRD</t>
         </is>
       </c>
       <c r="B45" s="10" t="inlineStr">
         <is>
-          <t>VerifyMe, Inc.</t>
-        </is>
-      </c>
-      <c r="C45" s="17" t="n">
-        <v>21</v>
+          <t>Allbirds, Inc.</t>
+        </is>
+      </c>
+      <c r="C45" s="10" t="inlineStr">
+        <is>
+          <t>10/10</t>
+        </is>
       </c>
       <c r="D45" s="10" t="inlineStr">
         <is>
@@ -9743,261 +9763,197 @@
         </is>
       </c>
       <c r="E45" s="17" t="n">
-        <v>8.1</v>
+        <v>15</v>
       </c>
       <c r="F45" s="10" t="inlineStr">
         <is>
-          <t>catalyst=SALE_OF_COMPANY, size=micro,</t>
+          <t>deep 24m washout (-84%); wild vol (0.46); bo</t>
         </is>
       </c>
     </row>
     <row r="46" ht="22" customHeight="1">
       <c r="A46" s="6" t="inlineStr">
         <is>
-          <t>PLAG</t>
+          <t>PLCE</t>
         </is>
       </c>
       <c r="B46" s="7" t="inlineStr">
         <is>
-          <t>Planet Green Holding</t>
-        </is>
-      </c>
-      <c r="C46" s="16" t="n">
-        <v>21</v>
+          <t>Children's Place, In</t>
+        </is>
+      </c>
+      <c r="C46" s="7" t="inlineStr">
+        <is>
+          <t>10/10</t>
+        </is>
       </c>
       <c r="D46" s="7" t="inlineStr">
         <is>
-          <t>FADING</t>
-        </is>
-      </c>
-      <c r="E46" s="7" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+          <t>NEUTRAL</t>
+        </is>
+      </c>
+      <c r="E46" s="16" t="n">
+        <v>15</v>
       </c>
       <c r="F46" s="7" t="inlineStr">
         <is>
-          <t>catalyst=SALE_OF_COMPANY, size=micro,</t>
+          <t>deep 24m washout (-85%); wild vol (0.22); bo</t>
         </is>
       </c>
     </row>
     <row r="47" ht="22" customHeight="1">
       <c r="A47" s="9" t="inlineStr">
         <is>
-          <t>HHS</t>
+          <t>WHR</t>
         </is>
       </c>
       <c r="B47" s="10" t="inlineStr">
         <is>
-          <t>Harte Hanks, Inc.</t>
-        </is>
-      </c>
-      <c r="C47" s="17" t="n">
-        <v>21</v>
+          <t>Whirlpool Corporatio</t>
+        </is>
+      </c>
+      <c r="C47" s="10" t="inlineStr">
+        <is>
+          <t>10/10</t>
+        </is>
       </c>
       <c r="D47" s="10" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>FADING</t>
         </is>
       </c>
       <c r="E47" s="17" t="n">
-        <v>6.9</v>
+        <v>13</v>
       </c>
       <c r="F47" s="10" t="inlineStr">
         <is>
-          <t>catalyst=SALE_OF_COMPANY, size=micro,</t>
+          <t>deep 24m washout (-53%); wild vol (0.15); bo</t>
         </is>
       </c>
     </row>
     <row r="48" ht="22" customHeight="1">
       <c r="A48" s="6" t="inlineStr">
         <is>
-          <t>DXLG</t>
+          <t>LCID</t>
         </is>
       </c>
       <c r="B48" s="7" t="inlineStr">
         <is>
-          <t>Destination XL Group</t>
-        </is>
-      </c>
-      <c r="C48" s="16" t="n">
-        <v>21</v>
+          <t>Lucid Group, Inc.</t>
+        </is>
+      </c>
+      <c r="C48" s="7" t="inlineStr">
+        <is>
+          <t>10/10</t>
+        </is>
       </c>
       <c r="D48" s="7" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>FADING</t>
         </is>
       </c>
       <c r="E48" s="16" t="n">
-        <v>60</v>
+        <v>13</v>
       </c>
       <c r="F48" s="7" t="inlineStr">
         <is>
-          <t>catalyst=SALE_OF_COMPANY, size=micro,</t>
+          <t>deep 24m washout (-84%); wild vol (0.17); bo</t>
         </is>
       </c>
     </row>
     <row r="49" ht="22" customHeight="1">
       <c r="A49" s="9" t="inlineStr">
         <is>
-          <t>HCAT</t>
+          <t>NUS</t>
         </is>
       </c>
       <c r="B49" s="10" t="inlineStr">
         <is>
-          <t>Health Catalyst, Inc</t>
-        </is>
-      </c>
-      <c r="C49" s="17" t="n">
-        <v>20</v>
+          <t>Nu Skin Enterprises,</t>
+        </is>
+      </c>
+      <c r="C49" s="10" t="inlineStr">
+        <is>
+          <t>10/10</t>
+        </is>
       </c>
       <c r="D49" s="10" t="inlineStr">
         <is>
-          <t>FADING</t>
+          <t>NEUTRAL</t>
         </is>
       </c>
       <c r="E49" s="17" t="n">
-        <v>6.1</v>
+        <v>14</v>
       </c>
       <c r="F49" s="10" t="inlineStr">
         <is>
-          <t>catalyst=ASSET_SALE, sector=Healthcare</t>
-        </is>
-      </c>
-    </row>
-    <row r="50" ht="22" customHeight="1">
-      <c r="A50" s="6" t="inlineStr">
-        <is>
-          <t>KROS</t>
-        </is>
-      </c>
-      <c r="B50" s="7" t="inlineStr">
-        <is>
-          <t>Keros Therapeutics,</t>
-        </is>
-      </c>
-      <c r="C50" s="16" t="n">
-        <v>20</v>
-      </c>
-      <c r="D50" s="7" t="inlineStr">
-        <is>
-          <t>NEUTRAL</t>
-        </is>
-      </c>
-      <c r="E50" s="16" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="F50" s="7" t="inlineStr">
-        <is>
-          <t>catalyst=TENDER_OFFER, sector=Healthca</t>
-        </is>
-      </c>
-    </row>
-    <row r="51" ht="22" customHeight="1">
-      <c r="A51" s="9" t="inlineStr">
-        <is>
-          <t>FMC</t>
-        </is>
-      </c>
-      <c r="B51" s="10" t="inlineStr">
-        <is>
-          <t>FMC Corporation</t>
-        </is>
-      </c>
-      <c r="C51" s="17" t="n">
-        <v>20</v>
-      </c>
-      <c r="D51" s="10" t="inlineStr">
-        <is>
-          <t>NEUTRAL</t>
-        </is>
-      </c>
-      <c r="E51" s="17" t="n">
-        <v>6.1</v>
-      </c>
-      <c r="F51" s="10" t="inlineStr">
-        <is>
-          <t>catalyst=TENDER_OFFER, sector=Basic Ma</t>
-        </is>
-      </c>
-    </row>
-    <row r="52" ht="22" customHeight="1">
-      <c r="A52" s="6" t="inlineStr">
-        <is>
-          <t>JKHY</t>
-        </is>
-      </c>
-      <c r="B52" s="7" t="inlineStr">
-        <is>
-          <t>Jack Henry &amp; Associa</t>
-        </is>
-      </c>
-      <c r="C52" s="16" t="n">
-        <v>20</v>
-      </c>
-      <c r="D52" s="7" t="inlineStr">
-        <is>
-          <t>NEUTRAL</t>
-        </is>
-      </c>
-      <c r="E52" s="7" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="F52" s="7" t="inlineStr">
-        <is>
-          <t>catalyst=SALE_OF_COMPANY, sector=Techn</t>
-        </is>
-      </c>
-    </row>
-    <row r="53" ht="22" customHeight="1">
-      <c r="A53" s="9" t="inlineStr">
-        <is>
-          <t>SPRB</t>
-        </is>
-      </c>
-      <c r="B53" s="10" t="inlineStr">
-        <is>
-          <t>Spruce Biosciences,</t>
-        </is>
-      </c>
-      <c r="C53" s="17" t="n">
-        <v>20</v>
-      </c>
-      <c r="D53" s="10" t="inlineStr">
-        <is>
-          <t>NEUTRAL</t>
-        </is>
-      </c>
-      <c r="E53" s="10" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="F53" s="10" t="inlineStr">
-        <is>
-          <t>sector=Healthcare, size=micro, drawdow</t>
+          <t>deep 24m washout (-57%); wild vol (0.18); bo</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="21" t="inlineStr">
+        <is>
+          <t>Note: monster-rich catalysts (strategic-review, spin, Ch11, uplisting) are LOTTERY TICKETS — negative median, convex tail — so size these small. See GREATEST_TRADES.md.</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="12" t="inlineStr">
+        <is>
+          <t>ALL CANDIDATES — pre-confirmation tail odds</t>
+        </is>
+      </c>
+    </row>
+    <row r="53" ht="18" customHeight="1">
+      <c r="A53" s="15" t="inlineStr">
+        <is>
+          <t>Ticker</t>
+        </is>
+      </c>
+      <c r="B53" s="15" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="C53" s="4" t="inlineStr">
+        <is>
+          <t>Tail p</t>
+        </is>
+      </c>
+      <c r="D53" s="4" t="inlineStr">
+        <is>
+          <t>State</t>
+        </is>
+      </c>
+      <c r="E53" s="4" t="inlineStr">
+        <is>
+          <t>Ratio</t>
+        </is>
+      </c>
+      <c r="F53" s="4" t="inlineStr">
+        <is>
+          <t>Tail drivers</t>
         </is>
       </c>
     </row>
     <row r="54" ht="22" customHeight="1">
       <c r="A54" s="6" t="inlineStr">
         <is>
-          <t>INO</t>
+          <t>USAR</t>
         </is>
       </c>
       <c r="B54" s="7" t="inlineStr">
         <is>
-          <t>Inovio Pharmaceutica</t>
+          <t>USA Rare Earth, Inc.</t>
         </is>
       </c>
       <c r="C54" s="16" t="n">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="D54" s="7" t="inlineStr">
         <is>
-          <t>NEUTRAL</t>
+          <t>PENDING</t>
         </is>
       </c>
       <c r="E54" s="7" t="inlineStr">
@@ -10007,33 +9963,31 @@
       </c>
       <c r="F54" s="7" t="inlineStr">
         <is>
-          <t>sector=Healthcare, size=micro, drawdow</t>
+          <t>catalyst=SALE_OF_COMPANY, sector=Basic</t>
         </is>
       </c>
     </row>
     <row r="55" ht="22" customHeight="1">
       <c r="A55" s="9" t="inlineStr">
         <is>
-          <t>GMAB</t>
+          <t>AMS</t>
         </is>
       </c>
       <c r="B55" s="10" t="inlineStr">
         <is>
-          <t>Genmab A/S</t>
+          <t>American Shared Hosp</t>
         </is>
       </c>
       <c r="C55" s="17" t="n">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="D55" s="10" t="inlineStr">
         <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="E55" s="10" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+          <t>NEUTRAL</t>
+        </is>
+      </c>
+      <c r="E55" s="17" t="n">
+        <v>60</v>
       </c>
       <c r="F55" s="10" t="inlineStr">
         <is>
@@ -10044,565 +9998,1253 @@
     <row r="56" ht="22" customHeight="1">
       <c r="A56" s="6" t="inlineStr">
         <is>
-          <t>PTN</t>
+          <t>BTAI</t>
         </is>
       </c>
       <c r="B56" s="7" t="inlineStr">
         <is>
-          <t>Palatin Technologies</t>
+          <t>BioXcel Therapeutics</t>
         </is>
       </c>
       <c r="C56" s="16" t="n">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="D56" s="7" t="inlineStr">
         <is>
           <t>NEUTRAL</t>
         </is>
       </c>
-      <c r="E56" s="16" t="n">
-        <v>1.3</v>
+      <c r="E56" s="7" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
       <c r="F56" s="7" t="inlineStr">
         <is>
-          <t>sector=Healthcare, size=micro, drawdow</t>
+          <t>catalyst=SALE_OF_COMPANY, sector=Healt</t>
         </is>
       </c>
     </row>
     <row r="57" ht="22" customHeight="1">
       <c r="A57" s="9" t="inlineStr">
         <is>
-          <t>MLYS</t>
+          <t>SUNE</t>
         </is>
       </c>
       <c r="B57" s="10" t="inlineStr">
         <is>
-          <t>Mineralys Therapeuti</t>
+          <t>SUNation Energy, Inc</t>
         </is>
       </c>
       <c r="C57" s="17" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="D57" s="10" t="inlineStr">
         <is>
-          <t>NEUTRAL</t>
-        </is>
-      </c>
-      <c r="E57" s="10" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="E57" s="17" t="n">
+        <v>60</v>
       </c>
       <c r="F57" s="10" t="inlineStr">
         <is>
-          <t>sector=Healthcare, size=mid, drawdown_</t>
+          <t>catalyst=SALE_OF_COMPANY, sector=Techn</t>
         </is>
       </c>
     </row>
     <row r="58" ht="22" customHeight="1">
       <c r="A58" s="6" t="inlineStr">
         <is>
-          <t>LUCY</t>
+          <t>JTAI</t>
         </is>
       </c>
       <c r="B58" s="7" t="inlineStr">
         <is>
-          <t>Innovative Eyewear,</t>
+          <t>Jet.AI Inc.</t>
         </is>
       </c>
       <c r="C58" s="16" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="D58" s="7" t="inlineStr">
         <is>
-          <t>–</t>
+          <t>FADING</t>
         </is>
       </c>
       <c r="E58" s="16" t="n">
-        <v>45.6</v>
+        <v>60</v>
       </c>
       <c r="F58" s="7" t="inlineStr">
         <is>
-          <t>sector=Healthcare, size=micro, drawdow</t>
+          <t>catalyst=SALE_OF_COMPANY, sector=Techn</t>
         </is>
       </c>
     </row>
     <row r="59" ht="22" customHeight="1">
       <c r="A59" s="9" t="inlineStr">
         <is>
-          <t>PMCB</t>
+          <t>OPTU</t>
         </is>
       </c>
       <c r="B59" s="10" t="inlineStr">
         <is>
-          <t>PharmaCyte  Biotech,</t>
+          <t>Optimum Communicatio</t>
         </is>
       </c>
       <c r="C59" s="17" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="D59" s="10" t="inlineStr">
         <is>
-          <t>–</t>
+          <t>NEUTRAL</t>
         </is>
       </c>
       <c r="E59" s="17" t="n">
-        <v>30</v>
+        <v>3</v>
       </c>
       <c r="F59" s="10" t="inlineStr">
         <is>
-          <t>sector=Healthcare, size=micro, drawdow</t>
+          <t>catalyst=SALE_OF_COMPANY, sector=Commu</t>
         </is>
       </c>
     </row>
     <row r="60" ht="22" customHeight="1">
       <c r="A60" s="6" t="inlineStr">
         <is>
-          <t>FWDI</t>
+          <t>NEUP</t>
         </is>
       </c>
       <c r="B60" s="7" t="inlineStr">
         <is>
-          <t>Forward Industries,</t>
+          <t>Neuphoria Therapeuti</t>
         </is>
       </c>
       <c r="C60" s="16" t="n">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="D60" s="7" t="inlineStr">
         <is>
-          <t>CONFIRMED</t>
+          <t>FADING</t>
         </is>
       </c>
       <c r="E60" s="16" t="n">
-        <v>12.9</v>
+        <v>3.9</v>
       </c>
       <c r="F60" s="7" t="inlineStr">
         <is>
-          <t>catalyst=SALE_OF_COMPANY, drawdown_12m</t>
+          <t>catalyst=STRATEGIC_REVIEW, sector=Heal</t>
         </is>
       </c>
     </row>
     <row r="61" ht="22" customHeight="1">
       <c r="A61" s="9" t="inlineStr">
         <is>
-          <t>LAB</t>
+          <t>NERV</t>
         </is>
       </c>
       <c r="B61" s="10" t="inlineStr">
         <is>
-          <t>Standard BioTools In</t>
+          <t>Minerva Neuroscience</t>
         </is>
       </c>
       <c r="C61" s="17" t="n">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="D61" s="10" t="inlineStr">
         <is>
-          <t>NEUTRAL</t>
-        </is>
-      </c>
-      <c r="E61" s="17" t="n">
-        <v>42.3</v>
+          <t>FADING</t>
+        </is>
+      </c>
+      <c r="E61" s="10" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
       <c r="F61" s="10" t="inlineStr">
         <is>
-          <t>catalyst=ASSET_SALE, sector=Healthcare</t>
+          <t>catalyst=STRATEGIC_REVIEW, sector=Heal</t>
         </is>
       </c>
     </row>
     <row r="62" ht="22" customHeight="1">
       <c r="A62" s="6" t="inlineStr">
         <is>
-          <t>PRGO</t>
+          <t>FULC</t>
         </is>
       </c>
       <c r="B62" s="7" t="inlineStr">
         <is>
-          <t>Perrigo Company plc</t>
+          <t>Fulcrum Therapeutics</t>
         </is>
       </c>
       <c r="C62" s="16" t="n">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="D62" s="7" t="inlineStr">
         <is>
-          <t>CONFIRMED</t>
+          <t>NEUTRAL</t>
         </is>
       </c>
       <c r="E62" s="16" t="n">
-        <v>25.6</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="F62" s="7" t="inlineStr">
         <is>
-          <t>catalyst=ASSET_SALE, sector=Healthcare</t>
+          <t>catalyst=STRATEGIC_REVIEW, sector=Heal</t>
         </is>
       </c>
     </row>
     <row r="63" ht="22" customHeight="1">
       <c r="A63" s="9" t="inlineStr">
         <is>
-          <t>CERT</t>
+          <t>NDRA</t>
         </is>
       </c>
       <c r="B63" s="10" t="inlineStr">
         <is>
-          <t>Certara, Inc.</t>
+          <t>ENDRA Life Sciences</t>
         </is>
       </c>
       <c r="C63" s="17" t="n">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="D63" s="10" t="inlineStr">
         <is>
           <t>CONFIRMED</t>
         </is>
       </c>
-      <c r="E63" s="17" t="n">
-        <v>10.7</v>
+      <c r="E63" s="10" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
       <c r="F63" s="10" t="inlineStr">
         <is>
-          <t>catalyst=ASSET_SALE, sector=Healthcare</t>
+          <t>catalyst=STRATEGIC_REVIEW, sector=Heal</t>
         </is>
       </c>
     </row>
     <row r="64" ht="22" customHeight="1">
       <c r="A64" s="6" t="inlineStr">
         <is>
+          <t>GPRO</t>
+        </is>
+      </c>
+      <c r="B64" s="7" t="inlineStr">
+        <is>
+          <t>GoPro, Inc.</t>
+        </is>
+      </c>
+      <c r="C64" s="16" t="n">
+        <v>21</v>
+      </c>
+      <c r="D64" s="7" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="E64" s="16" t="n">
+        <v>3</v>
+      </c>
+      <c r="F64" s="7" t="inlineStr">
+        <is>
+          <t>catalyst=STRATEGIC_REVIEW, sector=Tech</t>
+        </is>
+      </c>
+    </row>
+    <row r="65" ht="22" customHeight="1">
+      <c r="A65" s="9" t="inlineStr">
+        <is>
+          <t>TTEC</t>
+        </is>
+      </c>
+      <c r="B65" s="10" t="inlineStr">
+        <is>
+          <t>TTEC Holdings, Inc.</t>
+        </is>
+      </c>
+      <c r="C65" s="17" t="n">
+        <v>21</v>
+      </c>
+      <c r="D65" s="10" t="inlineStr">
+        <is>
+          <t>NEUTRAL</t>
+        </is>
+      </c>
+      <c r="E65" s="17" t="n">
+        <v>20.3</v>
+      </c>
+      <c r="F65" s="10" t="inlineStr">
+        <is>
+          <t>catalyst=STRATEGIC_REVIEW, sector=Tech</t>
+        </is>
+      </c>
+    </row>
+    <row r="66" ht="22" customHeight="1">
+      <c r="A66" s="6" t="inlineStr">
+        <is>
+          <t>CMTL</t>
+        </is>
+      </c>
+      <c r="B66" s="7" t="inlineStr">
+        <is>
+          <t>Comtech Telecommunic</t>
+        </is>
+      </c>
+      <c r="C66" s="16" t="n">
+        <v>21</v>
+      </c>
+      <c r="D66" s="7" t="inlineStr">
+        <is>
+          <t>FADING</t>
+        </is>
+      </c>
+      <c r="E66" s="16" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="F66" s="7" t="inlineStr">
+        <is>
+          <t>catalyst=STRATEGIC_REVIEW, sector=Tech</t>
+        </is>
+      </c>
+    </row>
+    <row r="67" ht="22" customHeight="1">
+      <c r="A67" s="9" t="inlineStr">
+        <is>
+          <t>DOMO</t>
+        </is>
+      </c>
+      <c r="B67" s="10" t="inlineStr">
+        <is>
+          <t>Domo, Inc.</t>
+        </is>
+      </c>
+      <c r="C67" s="17" t="n">
+        <v>21</v>
+      </c>
+      <c r="D67" s="10" t="inlineStr">
+        <is>
+          <t>NEUTRAL</t>
+        </is>
+      </c>
+      <c r="E67" s="17" t="n">
+        <v>3</v>
+      </c>
+      <c r="F67" s="10" t="inlineStr">
+        <is>
+          <t>catalyst=STRATEGIC_REVIEW, sector=Tech</t>
+        </is>
+      </c>
+    </row>
+    <row r="68" ht="22" customHeight="1">
+      <c r="A68" s="6" t="inlineStr">
+        <is>
+          <t>AGPU</t>
+        </is>
+      </c>
+      <c r="B68" s="7" t="inlineStr">
+        <is>
+          <t>Axe Compute Inc.</t>
+        </is>
+      </c>
+      <c r="C68" s="16" t="n">
+        <v>21</v>
+      </c>
+      <c r="D68" s="7" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="E68" s="16" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="F68" s="7" t="inlineStr">
+        <is>
+          <t>catalyst=STRATEGIC_REVIEW, sector=Tech</t>
+        </is>
+      </c>
+    </row>
+    <row r="69" ht="22" customHeight="1">
+      <c r="A69" s="9" t="inlineStr">
+        <is>
+          <t>VRME</t>
+        </is>
+      </c>
+      <c r="B69" s="10" t="inlineStr">
+        <is>
+          <t>VerifyMe, Inc.</t>
+        </is>
+      </c>
+      <c r="C69" s="17" t="n">
+        <v>21</v>
+      </c>
+      <c r="D69" s="10" t="inlineStr">
+        <is>
+          <t>NEUTRAL</t>
+        </is>
+      </c>
+      <c r="E69" s="17" t="n">
+        <v>8.1</v>
+      </c>
+      <c r="F69" s="10" t="inlineStr">
+        <is>
+          <t>catalyst=SALE_OF_COMPANY, size=micro,</t>
+        </is>
+      </c>
+    </row>
+    <row r="70" ht="22" customHeight="1">
+      <c r="A70" s="6" t="inlineStr">
+        <is>
+          <t>PLAG</t>
+        </is>
+      </c>
+      <c r="B70" s="7" t="inlineStr">
+        <is>
+          <t>Planet Green Holding</t>
+        </is>
+      </c>
+      <c r="C70" s="16" t="n">
+        <v>21</v>
+      </c>
+      <c r="D70" s="7" t="inlineStr">
+        <is>
+          <t>FADING</t>
+        </is>
+      </c>
+      <c r="E70" s="7" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="F70" s="7" t="inlineStr">
+        <is>
+          <t>catalyst=SALE_OF_COMPANY, size=micro,</t>
+        </is>
+      </c>
+    </row>
+    <row r="71" ht="22" customHeight="1">
+      <c r="A71" s="9" t="inlineStr">
+        <is>
+          <t>HHS</t>
+        </is>
+      </c>
+      <c r="B71" s="10" t="inlineStr">
+        <is>
+          <t>Harte Hanks, Inc.</t>
+        </is>
+      </c>
+      <c r="C71" s="17" t="n">
+        <v>21</v>
+      </c>
+      <c r="D71" s="10" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="E71" s="17" t="n">
+        <v>6.9</v>
+      </c>
+      <c r="F71" s="10" t="inlineStr">
+        <is>
+          <t>catalyst=SALE_OF_COMPANY, size=micro,</t>
+        </is>
+      </c>
+    </row>
+    <row r="72" ht="22" customHeight="1">
+      <c r="A72" s="6" t="inlineStr">
+        <is>
+          <t>DXLG</t>
+        </is>
+      </c>
+      <c r="B72" s="7" t="inlineStr">
+        <is>
+          <t>Destination XL Group</t>
+        </is>
+      </c>
+      <c r="C72" s="16" t="n">
+        <v>21</v>
+      </c>
+      <c r="D72" s="7" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="E72" s="16" t="n">
+        <v>60</v>
+      </c>
+      <c r="F72" s="7" t="inlineStr">
+        <is>
+          <t>catalyst=SALE_OF_COMPANY, size=micro,</t>
+        </is>
+      </c>
+    </row>
+    <row r="73" ht="22" customHeight="1">
+      <c r="A73" s="9" t="inlineStr">
+        <is>
+          <t>HCAT</t>
+        </is>
+      </c>
+      <c r="B73" s="10" t="inlineStr">
+        <is>
+          <t>Health Catalyst, Inc</t>
+        </is>
+      </c>
+      <c r="C73" s="17" t="n">
+        <v>20</v>
+      </c>
+      <c r="D73" s="10" t="inlineStr">
+        <is>
+          <t>FADING</t>
+        </is>
+      </c>
+      <c r="E73" s="17" t="n">
+        <v>6.1</v>
+      </c>
+      <c r="F73" s="10" t="inlineStr">
+        <is>
+          <t>catalyst=ASSET_SALE, sector=Healthcare</t>
+        </is>
+      </c>
+    </row>
+    <row r="74" ht="22" customHeight="1">
+      <c r="A74" s="6" t="inlineStr">
+        <is>
+          <t>KROS</t>
+        </is>
+      </c>
+      <c r="B74" s="7" t="inlineStr">
+        <is>
+          <t>Keros Therapeutics,</t>
+        </is>
+      </c>
+      <c r="C74" s="16" t="n">
+        <v>20</v>
+      </c>
+      <c r="D74" s="7" t="inlineStr">
+        <is>
+          <t>NEUTRAL</t>
+        </is>
+      </c>
+      <c r="E74" s="16" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="F74" s="7" t="inlineStr">
+        <is>
+          <t>catalyst=TENDER_OFFER, sector=Healthca</t>
+        </is>
+      </c>
+    </row>
+    <row r="75" ht="22" customHeight="1">
+      <c r="A75" s="9" t="inlineStr">
+        <is>
+          <t>FMC</t>
+        </is>
+      </c>
+      <c r="B75" s="10" t="inlineStr">
+        <is>
+          <t>FMC Corporation</t>
+        </is>
+      </c>
+      <c r="C75" s="17" t="n">
+        <v>20</v>
+      </c>
+      <c r="D75" s="10" t="inlineStr">
+        <is>
+          <t>NEUTRAL</t>
+        </is>
+      </c>
+      <c r="E75" s="17" t="n">
+        <v>6.1</v>
+      </c>
+      <c r="F75" s="10" t="inlineStr">
+        <is>
+          <t>catalyst=TENDER_OFFER, sector=Basic Ma</t>
+        </is>
+      </c>
+    </row>
+    <row r="76" ht="22" customHeight="1">
+      <c r="A76" s="6" t="inlineStr">
+        <is>
+          <t>JKHY</t>
+        </is>
+      </c>
+      <c r="B76" s="7" t="inlineStr">
+        <is>
+          <t>Jack Henry &amp; Associa</t>
+        </is>
+      </c>
+      <c r="C76" s="16" t="n">
+        <v>20</v>
+      </c>
+      <c r="D76" s="7" t="inlineStr">
+        <is>
+          <t>NEUTRAL</t>
+        </is>
+      </c>
+      <c r="E76" s="7" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="F76" s="7" t="inlineStr">
+        <is>
+          <t>catalyst=SALE_OF_COMPANY, sector=Techn</t>
+        </is>
+      </c>
+    </row>
+    <row r="77" ht="22" customHeight="1">
+      <c r="A77" s="9" t="inlineStr">
+        <is>
+          <t>SPRB</t>
+        </is>
+      </c>
+      <c r="B77" s="10" t="inlineStr">
+        <is>
+          <t>Spruce Biosciences,</t>
+        </is>
+      </c>
+      <c r="C77" s="17" t="n">
+        <v>20</v>
+      </c>
+      <c r="D77" s="10" t="inlineStr">
+        <is>
+          <t>NEUTRAL</t>
+        </is>
+      </c>
+      <c r="E77" s="10" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="F77" s="10" t="inlineStr">
+        <is>
+          <t>sector=Healthcare, size=micro, drawdow</t>
+        </is>
+      </c>
+    </row>
+    <row r="78" ht="22" customHeight="1">
+      <c r="A78" s="6" t="inlineStr">
+        <is>
+          <t>INO</t>
+        </is>
+      </c>
+      <c r="B78" s="7" t="inlineStr">
+        <is>
+          <t>Inovio Pharmaceutica</t>
+        </is>
+      </c>
+      <c r="C78" s="16" t="n">
+        <v>20</v>
+      </c>
+      <c r="D78" s="7" t="inlineStr">
+        <is>
+          <t>NEUTRAL</t>
+        </is>
+      </c>
+      <c r="E78" s="7" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="F78" s="7" t="inlineStr">
+        <is>
+          <t>sector=Healthcare, size=micro, drawdow</t>
+        </is>
+      </c>
+    </row>
+    <row r="79" ht="22" customHeight="1">
+      <c r="A79" s="9" t="inlineStr">
+        <is>
+          <t>GMAB</t>
+        </is>
+      </c>
+      <c r="B79" s="10" t="inlineStr">
+        <is>
+          <t>Genmab A/S</t>
+        </is>
+      </c>
+      <c r="C79" s="17" t="n">
+        <v>20</v>
+      </c>
+      <c r="D79" s="10" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="E79" s="10" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="F79" s="10" t="inlineStr">
+        <is>
+          <t>catalyst=SALE_OF_COMPANY, sector=Healt</t>
+        </is>
+      </c>
+    </row>
+    <row r="80" ht="22" customHeight="1">
+      <c r="A80" s="6" t="inlineStr">
+        <is>
+          <t>PTN</t>
+        </is>
+      </c>
+      <c r="B80" s="7" t="inlineStr">
+        <is>
+          <t>Palatin Technologies</t>
+        </is>
+      </c>
+      <c r="C80" s="16" t="n">
+        <v>20</v>
+      </c>
+      <c r="D80" s="7" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="E80" s="16" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="F80" s="7" t="inlineStr">
+        <is>
+          <t>sector=Healthcare, size=micro, drawdow</t>
+        </is>
+      </c>
+    </row>
+    <row r="81" ht="22" customHeight="1">
+      <c r="A81" s="9" t="inlineStr">
+        <is>
+          <t>MLYS</t>
+        </is>
+      </c>
+      <c r="B81" s="10" t="inlineStr">
+        <is>
+          <t>Mineralys Therapeuti</t>
+        </is>
+      </c>
+      <c r="C81" s="17" t="n">
+        <v>20</v>
+      </c>
+      <c r="D81" s="10" t="inlineStr">
+        <is>
+          <t>NEUTRAL</t>
+        </is>
+      </c>
+      <c r="E81" s="10" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="F81" s="10" t="inlineStr">
+        <is>
+          <t>sector=Healthcare, size=mid, drawdown_</t>
+        </is>
+      </c>
+    </row>
+    <row r="82" ht="22" customHeight="1">
+      <c r="A82" s="6" t="inlineStr">
+        <is>
+          <t>LUCY</t>
+        </is>
+      </c>
+      <c r="B82" s="7" t="inlineStr">
+        <is>
+          <t>Innovative Eyewear,</t>
+        </is>
+      </c>
+      <c r="C82" s="16" t="n">
+        <v>20</v>
+      </c>
+      <c r="D82" s="7" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="E82" s="16" t="n">
+        <v>45.6</v>
+      </c>
+      <c r="F82" s="7" t="inlineStr">
+        <is>
+          <t>sector=Healthcare, size=micro, drawdow</t>
+        </is>
+      </c>
+    </row>
+    <row r="83" ht="22" customHeight="1">
+      <c r="A83" s="9" t="inlineStr">
+        <is>
+          <t>PMCB</t>
+        </is>
+      </c>
+      <c r="B83" s="10" t="inlineStr">
+        <is>
+          <t>PharmaCyte  Biotech,</t>
+        </is>
+      </c>
+      <c r="C83" s="17" t="n">
+        <v>20</v>
+      </c>
+      <c r="D83" s="10" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="E83" s="17" t="n">
+        <v>30</v>
+      </c>
+      <c r="F83" s="10" t="inlineStr">
+        <is>
+          <t>sector=Healthcare, size=micro, drawdow</t>
+        </is>
+      </c>
+    </row>
+    <row r="84" ht="22" customHeight="1">
+      <c r="A84" s="6" t="inlineStr">
+        <is>
+          <t>FWDI</t>
+        </is>
+      </c>
+      <c r="B84" s="7" t="inlineStr">
+        <is>
+          <t>Forward Industries,</t>
+        </is>
+      </c>
+      <c r="C84" s="16" t="n">
+        <v>19</v>
+      </c>
+      <c r="D84" s="7" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="E84" s="16" t="n">
+        <v>12.9</v>
+      </c>
+      <c r="F84" s="7" t="inlineStr">
+        <is>
+          <t>catalyst=SALE_OF_COMPANY, drawdown_12m</t>
+        </is>
+      </c>
+    </row>
+    <row r="85" ht="22" customHeight="1">
+      <c r="A85" s="9" t="inlineStr">
+        <is>
+          <t>LAB</t>
+        </is>
+      </c>
+      <c r="B85" s="10" t="inlineStr">
+        <is>
+          <t>Standard BioTools In</t>
+        </is>
+      </c>
+      <c r="C85" s="17" t="n">
+        <v>19</v>
+      </c>
+      <c r="D85" s="10" t="inlineStr">
+        <is>
+          <t>NEUTRAL</t>
+        </is>
+      </c>
+      <c r="E85" s="17" t="n">
+        <v>42.3</v>
+      </c>
+      <c r="F85" s="10" t="inlineStr">
+        <is>
+          <t>catalyst=ASSET_SALE, sector=Healthcare</t>
+        </is>
+      </c>
+    </row>
+    <row r="86" ht="22" customHeight="1">
+      <c r="A86" s="6" t="inlineStr">
+        <is>
+          <t>PRGO</t>
+        </is>
+      </c>
+      <c r="B86" s="7" t="inlineStr">
+        <is>
+          <t>Perrigo Company plc</t>
+        </is>
+      </c>
+      <c r="C86" s="16" t="n">
+        <v>19</v>
+      </c>
+      <c r="D86" s="7" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="E86" s="16" t="n">
+        <v>25.6</v>
+      </c>
+      <c r="F86" s="7" t="inlineStr">
+        <is>
+          <t>catalyst=ASSET_SALE, sector=Healthcare</t>
+        </is>
+      </c>
+    </row>
+    <row r="87" ht="22" customHeight="1">
+      <c r="A87" s="9" t="inlineStr">
+        <is>
+          <t>CERT</t>
+        </is>
+      </c>
+      <c r="B87" s="10" t="inlineStr">
+        <is>
+          <t>Certara, Inc.</t>
+        </is>
+      </c>
+      <c r="C87" s="17" t="n">
+        <v>19</v>
+      </c>
+      <c r="D87" s="10" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="E87" s="17" t="n">
+        <v>10.7</v>
+      </c>
+      <c r="F87" s="10" t="inlineStr">
+        <is>
+          <t>catalyst=ASSET_SALE, sector=Healthcare</t>
+        </is>
+      </c>
+    </row>
+    <row r="88" ht="22" customHeight="1">
+      <c r="A88" s="6" t="inlineStr">
+        <is>
           <t>FIS</t>
         </is>
       </c>
-      <c r="B64" s="7" t="inlineStr">
+      <c r="B88" s="7" t="inlineStr">
         <is>
           <t>Fidelity National In</t>
         </is>
       </c>
-      <c r="C64" s="16" t="n">
+      <c r="C88" s="16" t="n">
         <v>19</v>
       </c>
-      <c r="D64" s="7" t="inlineStr">
+      <c r="D88" s="7" t="inlineStr">
         <is>
           <t>FADING</t>
         </is>
       </c>
-      <c r="E64" s="16" t="n">
+      <c r="E88" s="16" t="n">
         <v>2.8</v>
       </c>
-      <c r="F64" s="7" t="inlineStr">
+      <c r="F88" s="7" t="inlineStr">
         <is>
           <t>catalyst=SPINOFF, sector=Technology, d</t>
         </is>
       </c>
     </row>
-    <row r="66">
-      <c r="A66" s="12" t="inlineStr">
+    <row r="90">
+      <c r="A90" s="12" t="inlineStr">
         <is>
           <t>WHAT RAISES TAIL ODDS (historical lift vs 10% base)</t>
         </is>
       </c>
     </row>
-    <row r="67" ht="18" customHeight="1">
-      <c r="A67" s="4" t="inlineStr">
+    <row r="91" ht="18" customHeight="1">
+      <c r="A91" s="4" t="inlineStr">
         <is>
           <t>Feature = bin</t>
         </is>
       </c>
-      <c r="B67" s="4" t="inlineStr">
+      <c r="B91" s="4" t="inlineStr">
         <is>
           <t>Tail rate</t>
         </is>
       </c>
-      <c r="C67" s="4" t="inlineStr">
+      <c r="C91" s="4" t="inlineStr">
         <is>
           <t>Lift</t>
         </is>
       </c>
-      <c r="D67" s="4" t="inlineStr">
+      <c r="D91" s="4" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="E67" s="15" t="inlineStr"/>
-    </row>
-    <row r="68" ht="16" customHeight="1">
-      <c r="A68" s="9" t="inlineStr">
+      <c r="E91" s="15" t="inlineStr"/>
+    </row>
+    <row r="92" ht="16" customHeight="1">
+      <c r="A92" s="9" t="inlineStr">
         <is>
           <t>catalyst = SALE_OF_COMPANY</t>
         </is>
       </c>
-      <c r="B68" s="17" t="n">
+      <c r="B92" s="17" t="n">
         <v>25</v>
       </c>
-      <c r="C68" s="10" t="inlineStr">
+      <c r="C92" s="10" t="inlineStr">
         <is>
           <t>2.53x</t>
         </is>
       </c>
-      <c r="D68" s="8" t="n">
+      <c r="D92" s="8" t="n">
         <v>8</v>
       </c>
-      <c r="E68" s="10" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-    </row>
-    <row r="69" ht="16" customHeight="1">
-      <c r="A69" s="6" t="inlineStr">
+      <c r="E92" s="10" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+    </row>
+    <row r="93" ht="16" customHeight="1">
+      <c r="A93" s="6" t="inlineStr">
         <is>
           <t>sector = Basic Materials</t>
         </is>
       </c>
-      <c r="B69" s="16" t="n">
+      <c r="B93" s="16" t="n">
         <v>23</v>
       </c>
-      <c r="C69" s="7" t="inlineStr">
+      <c r="C93" s="7" t="inlineStr">
         <is>
           <t>2.34x</t>
         </is>
       </c>
-      <c r="D69" s="5" t="n">
+      <c r="D93" s="5" t="n">
         <v>13</v>
       </c>
-      <c r="E69" s="7" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-    </row>
-    <row r="70" ht="16" customHeight="1">
-      <c r="A70" s="9" t="inlineStr">
+      <c r="E93" s="7" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+    </row>
+    <row r="94" ht="16" customHeight="1">
+      <c r="A94" s="9" t="inlineStr">
         <is>
           <t>drawdown_12m = deep(&lt;-50%)</t>
         </is>
       </c>
-      <c r="B70" s="17" t="n">
+      <c r="B94" s="17" t="n">
         <v>19</v>
       </c>
-      <c r="C70" s="10" t="inlineStr">
+      <c r="C94" s="10" t="inlineStr">
         <is>
           <t>1.92x</t>
         </is>
       </c>
-      <c r="D70" s="8" t="n">
+      <c r="D94" s="8" t="n">
         <v>37</v>
       </c>
-      <c r="E70" s="10" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-    </row>
-    <row r="71" ht="16" customHeight="1">
-      <c r="A71" s="6" t="inlineStr">
+      <c r="E94" s="10" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+    </row>
+    <row r="95" ht="16" customHeight="1">
+      <c r="A95" s="6" t="inlineStr">
         <is>
           <t>sector = Healthcare</t>
         </is>
       </c>
-      <c r="B71" s="16" t="n">
+      <c r="B95" s="16" t="n">
         <v>19</v>
       </c>
-      <c r="C71" s="7" t="inlineStr">
+      <c r="C95" s="7" t="inlineStr">
         <is>
           <t>1.95x</t>
         </is>
       </c>
-      <c r="D71" s="5" t="n">
+      <c r="D95" s="5" t="n">
         <v>26</v>
       </c>
-      <c r="E71" s="7" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-    </row>
-    <row r="72" ht="16" customHeight="1">
-      <c r="A72" s="9" t="inlineStr">
+      <c r="E95" s="7" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+    </row>
+    <row r="96" ht="16" customHeight="1">
+      <c r="A96" s="9" t="inlineStr">
         <is>
           <t>catalyst = STRATEGIC_REVIEW</t>
         </is>
       </c>
-      <c r="B72" s="17" t="n">
+      <c r="B96" s="17" t="n">
         <v>16</v>
       </c>
-      <c r="C72" s="10" t="inlineStr">
+      <c r="C96" s="10" t="inlineStr">
         <is>
           <t>1.62x</t>
         </is>
       </c>
-      <c r="D72" s="8" t="n">
+      <c r="D96" s="8" t="n">
         <v>25</v>
       </c>
-      <c r="E72" s="10" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-    </row>
-    <row r="73" ht="16" customHeight="1">
-      <c r="A73" s="6" t="inlineStr">
+      <c r="E96" s="10" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+    </row>
+    <row r="97" ht="16" customHeight="1">
+      <c r="A97" s="6" t="inlineStr">
         <is>
           <t>catalyst = SPINOFF</t>
         </is>
       </c>
-      <c r="B73" s="16" t="n">
+      <c r="B97" s="16" t="n">
         <v>15</v>
       </c>
-      <c r="C73" s="7" t="inlineStr">
+      <c r="C97" s="7" t="inlineStr">
         <is>
           <t>1.56x</t>
         </is>
       </c>
-      <c r="D73" s="5" t="n">
+      <c r="D97" s="5" t="n">
         <v>39</v>
       </c>
-      <c r="E73" s="7" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-    </row>
-    <row r="74" ht="16" customHeight="1">
-      <c r="A74" s="9" t="inlineStr">
+      <c r="E97" s="7" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+    </row>
+    <row r="98" ht="16" customHeight="1">
+      <c r="A98" s="9" t="inlineStr">
         <is>
           <t>sector = Technology</t>
         </is>
       </c>
-      <c r="B74" s="17" t="n">
+      <c r="B98" s="17" t="n">
         <v>15</v>
       </c>
-      <c r="C74" s="10" t="inlineStr">
+      <c r="C98" s="10" t="inlineStr">
         <is>
           <t>1.50x</t>
         </is>
       </c>
-      <c r="D74" s="8" t="n">
+      <c r="D98" s="8" t="n">
         <v>27</v>
       </c>
-      <c r="E74" s="10" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-    </row>
-    <row r="75" ht="16" customHeight="1">
-      <c r="A75" s="6" t="inlineStr">
+      <c r="E98" s="10" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+    </row>
+    <row r="99" ht="16" customHeight="1">
+      <c r="A99" s="6" t="inlineStr">
         <is>
           <t>range_pos = low</t>
         </is>
       </c>
-      <c r="B75" s="16" t="n">
+      <c r="B99" s="16" t="n">
         <v>12</v>
       </c>
-      <c r="C75" s="7" t="inlineStr">
+      <c r="C99" s="7" t="inlineStr">
         <is>
           <t>1.24x</t>
         </is>
       </c>
-      <c r="D75" s="5" t="n">
+      <c r="D99" s="5" t="n">
         <v>106</v>
       </c>
-      <c r="E75" s="7" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-    </row>
-    <row r="76" ht="16" customHeight="1">
-      <c r="A76" s="9" t="inlineStr">
+      <c r="E99" s="7" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+    </row>
+    <row r="100" ht="16" customHeight="1">
+      <c r="A100" s="9" t="inlineStr">
         <is>
           <t>size = micro</t>
         </is>
       </c>
-      <c r="B76" s="17" t="n">
+      <c r="B100" s="17" t="n">
         <v>12</v>
       </c>
-      <c r="C76" s="10" t="inlineStr">
+      <c r="C100" s="10" t="inlineStr">
         <is>
           <t>1.27x</t>
         </is>
       </c>
-      <c r="D76" s="8" t="n">
+      <c r="D100" s="8" t="n">
         <v>24</v>
       </c>
-      <c r="E76" s="10" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-    </row>
-    <row r="77" ht="16" customHeight="1">
-      <c r="A77" s="6" t="inlineStr">
+      <c r="E100" s="10" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+    </row>
+    <row r="101" ht="16" customHeight="1">
+      <c r="A101" s="6" t="inlineStr">
         <is>
           <t>catalyst = ASSET_SALE</t>
         </is>
       </c>
-      <c r="B77" s="16" t="n">
+      <c r="B101" s="16" t="n">
         <v>11</v>
       </c>
-      <c r="C77" s="7" t="inlineStr">
+      <c r="C101" s="7" t="inlineStr">
         <is>
           <t>1.13x</t>
         </is>
       </c>
-      <c r="D77" s="5" t="n">
+      <c r="D101" s="5" t="n">
         <v>36</v>
       </c>
-      <c r="E77" s="7" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-    </row>
-    <row r="78" ht="16" customHeight="1">
-      <c r="A78" s="9" t="inlineStr">
+      <c r="E101" s="7" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+    </row>
+    <row r="102" ht="16" customHeight="1">
+      <c r="A102" s="9" t="inlineStr">
         <is>
           <t>pre_12m = down(&lt;-20%)  (needs a wait)</t>
         </is>
       </c>
-      <c r="B78" s="17" t="n">
+      <c r="B102" s="17" t="n">
         <v>14</v>
       </c>
-      <c r="C78" s="10" t="inlineStr">
+      <c r="C102" s="10" t="inlineStr">
         <is>
           <t>1.46x</t>
         </is>
       </c>
-      <c r="D78" s="8" t="n">
+      <c r="D102" s="8" t="n">
         <v>83</v>
       </c>
-      <c r="E78" s="10" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-    </row>
-    <row r="79" ht="16" customHeight="1">
-      <c r="A79" s="6" t="inlineStr">
+      <c r="E102" s="10" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+    </row>
+    <row r="103" ht="16" customHeight="1">
+      <c r="A103" s="6" t="inlineStr">
         <is>
           <t>post_1m = up(&gt;+20%)  (needs a wait)</t>
         </is>
       </c>
-      <c r="B79" s="16" t="n">
+      <c r="B103" s="16" t="n">
         <v>33</v>
       </c>
-      <c r="C79" s="7" t="inlineStr">
+      <c r="C103" s="7" t="inlineStr">
         <is>
           <t>3.38x</t>
         </is>
       </c>
-      <c r="D79" s="5" t="n">
+      <c r="D103" s="5" t="n">
         <v>21</v>
       </c>
-      <c r="E79" s="7" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-    </row>
-    <row r="81" ht="28" customHeight="1">
-      <c r="A81" s="11" t="inlineStr">
+      <c r="E103" s="7" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+    </row>
+    <row r="105" ht="28" customHeight="1">
+      <c r="A105" s="11" t="inlineStr">
         <is>
           <t>HOW TO RAISE THE ODDS, from the 12-type event study (314 events, 10% base tail rate). The right tail concentrates in (1) DEEPLY BEATEN-DOWN names — &gt;50% below their 12-month high tailed 19% vs 7% for names near their highs (1.9x); (2) the right SECTORS — Basic Materials (2.3x), Healthcare (1.9x), Communication Services (1.7x), Technology (1.5x) — while Utilities and Real Estate produced ZERO tails and Financials few; (3) micro/mid-caps over large; (4) the right CATALYSTS — SALE-OF-COMPANY (2.5x, contested-deal tail), STRATEGIC-REVIEW (1.6x lottery) and SPIN-OFF (1.6x); ASSET-SALE has the best MEDIAN (+10%, 58% hit). The backtest also exposed TRAPS to fade: going-private (-37% median), uplisting (-23%, pump-and-fade), capital-return/special-dividend (-11%), exchange-offer (-21%) — all down-weighted in the catalyst engine. THE SINGLE STRONGEST EDGE is not a screen but a RULE: wait ~1 month and enter only names the market voted UP &gt;20% on the catalyst (the Confirmed shortlist above). Buying a catalyst blind loses to SPY on the median (overall -4%); buying beaten-down names in the right sectors AFTER the market confirms is how you tilt into the tail. Directional (n per type 8-51). Sources: rerate_backtest.py / tail_discriminators.py / tail_odds.py.</t>
         </is>
@@ -10611,8 +11253,8 @@
   </sheetData>
   <mergeCells count="3">
     <mergeCell ref="A2:F2"/>
+    <mergeCell ref="A105:F105"/>
     <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A81:F81"/>
   </mergeCells>
   <printOptions horizontalCentered="0"/>
   <pageMargins left="0.5" right="0.5" top="0.6" bottom="0.6" header="0.5" footer="0.5"/>

--- a/MOST_ASYMMETRIC.xlsx
+++ b/MOST_ASYMMETRIC.xlsx
@@ -8619,7 +8619,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:F105"/>
+  <dimension ref="A1:F104"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -9315,7 +9315,7 @@
     <row r="30">
       <c r="A30" s="12" t="inlineStr">
         <is>
-          <t>MONSTER SETUPS — the greatest-trades washout fingerprint (deep 24m drawdown + wild vol + bottom of range + decelerating + monster-rich catalyst)</t>
+          <t>CONFIRMED MONSTER SETUPS — deep washout fingerprint AND the market has voted up (the only version that pays)</t>
         </is>
       </c>
     </row>
@@ -9337,7 +9337,7 @@
       </c>
       <c r="D31" s="4" t="inlineStr">
         <is>
-          <t>State</t>
+          <t>Drift</t>
         </is>
       </c>
       <c r="E31" s="4" t="inlineStr">
@@ -9354,12 +9354,12 @@
     <row r="32" ht="22" customHeight="1">
       <c r="A32" s="6" t="inlineStr">
         <is>
-          <t>NEUP</t>
+          <t>SMCI</t>
         </is>
       </c>
       <c r="B32" s="7" t="inlineStr">
         <is>
-          <t>Neuphoria Therapeuti</t>
+          <t>Super Micro Computer</t>
         </is>
       </c>
       <c r="C32" s="7" t="inlineStr">
@@ -9367,1622 +9367,1560 @@
           <t>10/10</t>
         </is>
       </c>
-      <c r="D32" s="7" t="inlineStr">
-        <is>
-          <t>FADING</t>
-        </is>
+      <c r="D32" s="16" t="n">
+        <v>29</v>
       </c>
       <c r="E32" s="16" t="n">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="F32" s="7" t="inlineStr">
         <is>
-          <t>deep 24m washout (-63%); wild vol (0.25); bo</t>
+          <t>deep 24m washout (-60%); wild vol (0.30);</t>
         </is>
       </c>
     </row>
     <row r="33" ht="22" customHeight="1">
       <c r="A33" s="9" t="inlineStr">
         <is>
-          <t>DOMO</t>
+          <t>GPRO</t>
         </is>
       </c>
       <c r="B33" s="10" t="inlineStr">
         <is>
-          <t>Domo, Inc.</t>
+          <t>GoPro, Inc.</t>
         </is>
       </c>
       <c r="C33" s="10" t="inlineStr">
         <is>
-          <t>10/10</t>
-        </is>
-      </c>
-      <c r="D33" s="10" t="inlineStr">
-        <is>
-          <t>NEUTRAL</t>
-        </is>
+          <t>9/10</t>
+        </is>
+      </c>
+      <c r="D33" s="17" t="n">
+        <v>54</v>
       </c>
       <c r="E33" s="17" t="n">
-        <v>21</v>
+        <v>33</v>
       </c>
       <c r="F33" s="10" t="inlineStr">
         <is>
-          <t>deep 24m washout (-77%); wild vol (0.20); bo</t>
+          <t>deep 24m washout (-59%); wild vol (0.40);</t>
         </is>
       </c>
     </row>
     <row r="34" ht="22" customHeight="1">
       <c r="A34" s="6" t="inlineStr">
         <is>
-          <t>TTEC</t>
+          <t>PTN</t>
         </is>
       </c>
       <c r="B34" s="7" t="inlineStr">
         <is>
-          <t>TTEC Holdings, Inc.</t>
+          <t>Palatin Technologies</t>
         </is>
       </c>
       <c r="C34" s="7" t="inlineStr">
         <is>
-          <t>10/10</t>
-        </is>
-      </c>
-      <c r="D34" s="7" t="inlineStr">
-        <is>
-          <t>NEUTRAL</t>
-        </is>
+          <t>9/10</t>
+        </is>
+      </c>
+      <c r="D34" s="16" t="n">
+        <v>24</v>
       </c>
       <c r="E34" s="16" t="n">
-        <v>21</v>
+        <v>32</v>
       </c>
       <c r="F34" s="7" t="inlineStr">
         <is>
-          <t>deep 24m washout (-78%); wild vol (0.20); bo</t>
+          <t>deep 24m washout (-89%); wild vol (0.61);</t>
         </is>
       </c>
     </row>
     <row r="35" ht="22" customHeight="1">
       <c r="A35" s="9" t="inlineStr">
         <is>
-          <t>SPRB</t>
+          <t>ANF</t>
         </is>
       </c>
       <c r="B35" s="10" t="inlineStr">
         <is>
-          <t>Spruce Biosciences,</t>
+          <t>Abercrombie &amp; Fitch</t>
         </is>
       </c>
       <c r="C35" s="10" t="inlineStr">
         <is>
-          <t>10/10</t>
-        </is>
-      </c>
-      <c r="D35" s="10" t="inlineStr">
-        <is>
-          <t>NEUTRAL</t>
-        </is>
+          <t>9/10</t>
+        </is>
+      </c>
+      <c r="D35" s="17" t="n">
+        <v>65</v>
       </c>
       <c r="E35" s="17" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="F35" s="10" t="inlineStr">
         <is>
-          <t>deep 24m washout (-98%); wild vol (3.29); bo</t>
+          <t>deep 24m washout (-52%); wild vol (0.17);</t>
         </is>
       </c>
     </row>
     <row r="36" ht="22" customHeight="1">
       <c r="A36" s="6" t="inlineStr">
         <is>
-          <t>LAB</t>
+          <t>AGPU</t>
         </is>
       </c>
       <c r="B36" s="7" t="inlineStr">
         <is>
-          <t>Standard BioTools In</t>
+          <t>Axe Compute Inc.</t>
         </is>
       </c>
       <c r="C36" s="7" t="inlineStr">
         <is>
-          <t>10/10</t>
-        </is>
-      </c>
-      <c r="D36" s="7" t="inlineStr">
-        <is>
-          <t>NEUTRAL</t>
-        </is>
+          <t>8/10</t>
+        </is>
+      </c>
+      <c r="D36" s="16" t="n">
+        <v>42</v>
       </c>
       <c r="E36" s="16" t="n">
-        <v>19</v>
+        <v>33</v>
       </c>
       <c r="F36" s="7" t="inlineStr">
         <is>
-          <t>deep 24m washout (-65%); wild vol (0.18); bo</t>
+          <t>deep 24m washout (-67%); wild vol (0.84);</t>
         </is>
       </c>
     </row>
     <row r="37" ht="22" customHeight="1">
       <c r="A37" s="9" t="inlineStr">
         <is>
-          <t>CNDT</t>
+          <t>PRGO</t>
         </is>
       </c>
       <c r="B37" s="10" t="inlineStr">
         <is>
-          <t>Conduent Incorporate</t>
+          <t>Perrigo Company plc</t>
         </is>
       </c>
       <c r="C37" s="10" t="inlineStr">
         <is>
-          <t>10/10</t>
-        </is>
-      </c>
-      <c r="D37" s="10" t="inlineStr">
-        <is>
-          <t>NEUTRAL</t>
-        </is>
+          <t>8/10</t>
+        </is>
+      </c>
+      <c r="D37" s="17" t="n">
+        <v>27</v>
       </c>
       <c r="E37" s="17" t="n">
-        <v>19</v>
+        <v>31</v>
       </c>
       <c r="F37" s="10" t="inlineStr">
         <is>
-          <t>deep 24m washout (-61%); wild vol (0.16); bo</t>
+          <t>deep 24m washout (-67%); bottom of range;</t>
         </is>
       </c>
     </row>
     <row r="38" ht="22" customHeight="1">
       <c r="A38" s="6" t="inlineStr">
         <is>
-          <t>THRY</t>
+          <t>CERT</t>
         </is>
       </c>
       <c r="B38" s="7" t="inlineStr">
         <is>
-          <t>Thryv Holdings, Inc.</t>
+          <t>Certara, Inc.</t>
         </is>
       </c>
       <c r="C38" s="7" t="inlineStr">
         <is>
-          <t>10/10</t>
-        </is>
-      </c>
-      <c r="D38" s="7" t="inlineStr">
-        <is>
-          <t>PENDING</t>
-        </is>
+          <t>8/10</t>
+        </is>
+      </c>
+      <c r="D38" s="16" t="n">
+        <v>38</v>
       </c>
       <c r="E38" s="16" t="n">
-        <v>19</v>
+        <v>31</v>
       </c>
       <c r="F38" s="7" t="inlineStr">
         <is>
-          <t>deep 24m washout (-89%); wild vol (0.26); bo</t>
+          <t>deep 24m washout (-63%); bottom of range;</t>
         </is>
       </c>
     </row>
     <row r="39" ht="22" customHeight="1">
       <c r="A39" s="9" t="inlineStr">
         <is>
-          <t>CCOI</t>
+          <t>IT</t>
         </is>
       </c>
       <c r="B39" s="10" t="inlineStr">
         <is>
-          <t>Cogent Communication</t>
+          <t>Gartner, Inc.</t>
         </is>
       </c>
       <c r="C39" s="10" t="inlineStr">
         <is>
-          <t>10/10</t>
-        </is>
-      </c>
-      <c r="D39" s="10" t="inlineStr">
-        <is>
-          <t>FADING</t>
-        </is>
+          <t>8/10</t>
+        </is>
+      </c>
+      <c r="D39" s="17" t="n">
+        <v>24</v>
       </c>
       <c r="E39" s="17" t="n">
-        <v>16</v>
+        <v>27</v>
       </c>
       <c r="F39" s="10" t="inlineStr">
         <is>
-          <t>deep 24m washout (-84%); wild vol (0.22); bo</t>
+          <t>deep 24m washout (-71%); bottom of range;</t>
         </is>
       </c>
     </row>
     <row r="40" ht="22" customHeight="1">
       <c r="A40" s="6" t="inlineStr">
         <is>
-          <t>HYFM</t>
+          <t>DUOL</t>
         </is>
       </c>
       <c r="B40" s="7" t="inlineStr">
         <is>
-          <t>Hydrofarm Holdings G</t>
+          <t>Duolingo, Inc.</t>
         </is>
       </c>
       <c r="C40" s="7" t="inlineStr">
         <is>
-          <t>10/10</t>
-        </is>
-      </c>
-      <c r="D40" s="7" t="inlineStr">
-        <is>
-          <t>NEUTRAL</t>
-        </is>
+          <t>8/10</t>
+        </is>
+      </c>
+      <c r="D40" s="16" t="n">
+        <v>53</v>
       </c>
       <c r="E40" s="16" t="n">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="F40" s="7" t="inlineStr">
         <is>
-          <t>deep 24m washout (-90%); wild vol (0.15); bo</t>
+          <t>deep 24m washout (-81%); wild vol (0.18);</t>
         </is>
       </c>
     </row>
     <row r="41" ht="22" customHeight="1">
       <c r="A41" s="9" t="inlineStr">
         <is>
-          <t>OPTT</t>
+          <t>CNMD</t>
         </is>
       </c>
       <c r="B41" s="10" t="inlineStr">
         <is>
-          <t>Ocean Power Technolo</t>
+          <t>CONMED Corporation</t>
         </is>
       </c>
       <c r="C41" s="10" t="inlineStr">
         <is>
-          <t>10/10</t>
-        </is>
-      </c>
-      <c r="D41" s="10" t="inlineStr">
-        <is>
-          <t>PENDING</t>
-        </is>
+          <t>8/10</t>
+        </is>
+      </c>
+      <c r="D41" s="17" t="n">
+        <v>30</v>
       </c>
       <c r="E41" s="17" t="n">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="F41" s="10" t="inlineStr">
         <is>
-          <t>deep 24m washout (-91%); wild vol (0.27); bo</t>
+          <t>deep 24m washout (-52%); bottom of range;</t>
         </is>
       </c>
     </row>
     <row r="42" ht="22" customHeight="1">
       <c r="A42" s="6" t="inlineStr">
         <is>
-          <t>CRMT</t>
+          <t>PAR</t>
         </is>
       </c>
       <c r="B42" s="7" t="inlineStr">
         <is>
-          <t>America's Car-Mart,</t>
+          <t>PAR Technology Corpo</t>
         </is>
       </c>
       <c r="C42" s="7" t="inlineStr">
         <is>
-          <t>10/10</t>
-        </is>
-      </c>
-      <c r="D42" s="7" t="inlineStr">
-        <is>
-          <t>PENDING</t>
-        </is>
+          <t>8/10</t>
+        </is>
+      </c>
+      <c r="D42" s="16" t="n">
+        <v>36</v>
       </c>
       <c r="E42" s="16" t="n">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="F42" s="7" t="inlineStr">
         <is>
-          <t>deep 24m washout (-97%); wild vol (0.26); bo</t>
+          <t>deep 24m washout (-84%); wild vol (0.15);</t>
         </is>
       </c>
     </row>
     <row r="43" ht="22" customHeight="1">
       <c r="A43" s="9" t="inlineStr">
         <is>
-          <t>SMCI</t>
+          <t>PD</t>
         </is>
       </c>
       <c r="B43" s="10" t="inlineStr">
         <is>
-          <t>Super Micro Computer</t>
+          <t>PagerDuty, Inc.</t>
         </is>
       </c>
       <c r="C43" s="10" t="inlineStr">
         <is>
-          <t>10/10</t>
-        </is>
-      </c>
-      <c r="D43" s="10" t="inlineStr">
-        <is>
-          <t>CONFIRMED</t>
-        </is>
+          <t>8/10</t>
+        </is>
+      </c>
+      <c r="D43" s="17" t="n">
+        <v>54</v>
       </c>
       <c r="E43" s="17" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F43" s="10" t="inlineStr">
         <is>
-          <t>deep 24m washout (-60%); wild vol (0.30); bo</t>
+          <t>deep 24m washout (-55%); wild vol (0.22);</t>
         </is>
       </c>
     </row>
     <row r="44" ht="22" customHeight="1">
       <c r="A44" s="6" t="inlineStr">
         <is>
-          <t>HAIN</t>
+          <t>AZTA</t>
         </is>
       </c>
       <c r="B44" s="7" t="inlineStr">
         <is>
-          <t>The Hain Celestial G</t>
+          <t>Azenta, Inc.</t>
         </is>
       </c>
       <c r="C44" s="7" t="inlineStr">
         <is>
-          <t>10/10</t>
-        </is>
-      </c>
-      <c r="D44" s="7" t="inlineStr">
-        <is>
-          <t>PENDING</t>
-        </is>
+          <t>8/10</t>
+        </is>
+      </c>
+      <c r="D44" s="16" t="n">
+        <v>52</v>
       </c>
       <c r="E44" s="16" t="n">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="F44" s="7" t="inlineStr">
         <is>
-          <t>deep 24m washout (-93%); wild vol (0.23); bo</t>
+          <t>deep 24m washout (-66%); wild vol (0.15);</t>
         </is>
       </c>
     </row>
     <row r="45" ht="22" customHeight="1">
       <c r="A45" s="9" t="inlineStr">
         <is>
-          <t>BIRD</t>
+          <t>TASK</t>
         </is>
       </c>
       <c r="B45" s="10" t="inlineStr">
         <is>
-          <t>Allbirds, Inc.</t>
+          <t>TaskUs, Inc.</t>
         </is>
       </c>
       <c r="C45" s="10" t="inlineStr">
         <is>
-          <t>10/10</t>
-        </is>
-      </c>
-      <c r="D45" s="10" t="inlineStr">
-        <is>
-          <t>NEUTRAL</t>
-        </is>
+          <t>8/10</t>
+        </is>
+      </c>
+      <c r="D45" s="17" t="n">
+        <v>27</v>
       </c>
       <c r="E45" s="17" t="n">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="F45" s="10" t="inlineStr">
         <is>
-          <t>deep 24m washout (-84%); wild vol (0.46); bo</t>
+          <t>deep 24m washout (-64%); wild vol (0.15);</t>
         </is>
       </c>
     </row>
     <row r="46" ht="22" customHeight="1">
       <c r="A46" s="6" t="inlineStr">
         <is>
-          <t>PLCE</t>
+          <t>NDRA</t>
         </is>
       </c>
       <c r="B46" s="7" t="inlineStr">
         <is>
-          <t>Children's Place, In</t>
+          <t>ENDRA Life Sciences</t>
         </is>
       </c>
       <c r="C46" s="7" t="inlineStr">
         <is>
-          <t>10/10</t>
-        </is>
-      </c>
-      <c r="D46" s="7" t="inlineStr">
-        <is>
-          <t>NEUTRAL</t>
-        </is>
+          <t>7/10</t>
+        </is>
+      </c>
+      <c r="D46" s="16" t="n">
+        <v>20</v>
       </c>
       <c r="E46" s="16" t="n">
-        <v>15</v>
+        <v>36</v>
       </c>
       <c r="F46" s="7" t="inlineStr">
         <is>
-          <t>deep 24m washout (-85%); wild vol (0.22); bo</t>
+          <t>deep 24m washout (-99%); wild vol (0.26);</t>
         </is>
       </c>
     </row>
     <row r="47" ht="22" customHeight="1">
       <c r="A47" s="9" t="inlineStr">
         <is>
-          <t>WHR</t>
+          <t>FWDI</t>
         </is>
       </c>
       <c r="B47" s="10" t="inlineStr">
         <is>
-          <t>Whirlpool Corporatio</t>
+          <t>Forward Industries,</t>
         </is>
       </c>
       <c r="C47" s="10" t="inlineStr">
         <is>
-          <t>10/10</t>
-        </is>
-      </c>
-      <c r="D47" s="10" t="inlineStr">
+          <t>7/10</t>
+        </is>
+      </c>
+      <c r="D47" s="17" t="n">
+        <v>51</v>
+      </c>
+      <c r="E47" s="17" t="n">
+        <v>31</v>
+      </c>
+      <c r="F47" s="10" t="inlineStr">
+        <is>
+          <t>deep 24m washout (-82%); wild vol (0.45);</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="21" t="inlineStr">
+        <is>
+          <t>AVOID — fading deep-washouts (same fingerprint, market voting DOWN; the loser twin): NEUP, CCOI, WHR, LCID, TWAV, YHC, CMTL, JTAI, HCAT, FIS, QBTS, LVLU, KVYO, UPWK, MNRO, BATL, LUCK, CYH, INGN, RH</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="21" t="inlineStr">
+        <is>
+          <t>Research (DEEP_RESEARCH.md): the deep-washout fingerprint alone is BIMODAL — fp&gt;=8 has a 33% chance of losing &gt;50% and negative Kelly. Only CONFIRMATION separates the +100% monster from the blow-up. Size confirmed names small (~1/4-Kelly); never buy the un-confirmed washout.</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="12" t="inlineStr">
+        <is>
+          <t>ALL CANDIDATES — pre-confirmation tail odds</t>
+        </is>
+      </c>
+    </row>
+    <row r="52" ht="18" customHeight="1">
+      <c r="A52" s="15" t="inlineStr">
+        <is>
+          <t>Ticker</t>
+        </is>
+      </c>
+      <c r="B52" s="15" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="C52" s="4" t="inlineStr">
+        <is>
+          <t>Tail p</t>
+        </is>
+      </c>
+      <c r="D52" s="4" t="inlineStr">
+        <is>
+          <t>State</t>
+        </is>
+      </c>
+      <c r="E52" s="4" t="inlineStr">
+        <is>
+          <t>Ratio</t>
+        </is>
+      </c>
+      <c r="F52" s="4" t="inlineStr">
+        <is>
+          <t>Tail drivers</t>
+        </is>
+      </c>
+    </row>
+    <row r="53" ht="22" customHeight="1">
+      <c r="A53" s="6" t="inlineStr">
+        <is>
+          <t>USAR</t>
+        </is>
+      </c>
+      <c r="B53" s="7" t="inlineStr">
+        <is>
+          <t>USA Rare Earth, Inc.</t>
+        </is>
+      </c>
+      <c r="C53" s="16" t="n">
+        <v>28</v>
+      </c>
+      <c r="D53" s="7" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="E53" s="7" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="F53" s="7" t="inlineStr">
+        <is>
+          <t>catalyst=SALE_OF_COMPANY, sector=Basic</t>
+        </is>
+      </c>
+    </row>
+    <row r="54" ht="22" customHeight="1">
+      <c r="A54" s="9" t="inlineStr">
+        <is>
+          <t>AMS</t>
+        </is>
+      </c>
+      <c r="B54" s="10" t="inlineStr">
+        <is>
+          <t>American Shared Hosp</t>
+        </is>
+      </c>
+      <c r="C54" s="17" t="n">
+        <v>27</v>
+      </c>
+      <c r="D54" s="10" t="inlineStr">
+        <is>
+          <t>NEUTRAL</t>
+        </is>
+      </c>
+      <c r="E54" s="17" t="n">
+        <v>60</v>
+      </c>
+      <c r="F54" s="10" t="inlineStr">
+        <is>
+          <t>catalyst=SALE_OF_COMPANY, sector=Healt</t>
+        </is>
+      </c>
+    </row>
+    <row r="55" ht="22" customHeight="1">
+      <c r="A55" s="6" t="inlineStr">
+        <is>
+          <t>BTAI</t>
+        </is>
+      </c>
+      <c r="B55" s="7" t="inlineStr">
+        <is>
+          <t>BioXcel Therapeutics</t>
+        </is>
+      </c>
+      <c r="C55" s="16" t="n">
+        <v>27</v>
+      </c>
+      <c r="D55" s="7" t="inlineStr">
+        <is>
+          <t>NEUTRAL</t>
+        </is>
+      </c>
+      <c r="E55" s="7" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="F55" s="7" t="inlineStr">
+        <is>
+          <t>catalyst=SALE_OF_COMPANY, sector=Healt</t>
+        </is>
+      </c>
+    </row>
+    <row r="56" ht="22" customHeight="1">
+      <c r="A56" s="9" t="inlineStr">
+        <is>
+          <t>SUNE</t>
+        </is>
+      </c>
+      <c r="B56" s="10" t="inlineStr">
+        <is>
+          <t>SUNation Energy, Inc</t>
+        </is>
+      </c>
+      <c r="C56" s="17" t="n">
+        <v>25</v>
+      </c>
+      <c r="D56" s="10" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="E56" s="17" t="n">
+        <v>60</v>
+      </c>
+      <c r="F56" s="10" t="inlineStr">
+        <is>
+          <t>catalyst=SALE_OF_COMPANY, sector=Techn</t>
+        </is>
+      </c>
+    </row>
+    <row r="57" ht="22" customHeight="1">
+      <c r="A57" s="6" t="inlineStr">
+        <is>
+          <t>JTAI</t>
+        </is>
+      </c>
+      <c r="B57" s="7" t="inlineStr">
+        <is>
+          <t>Jet.AI Inc.</t>
+        </is>
+      </c>
+      <c r="C57" s="16" t="n">
+        <v>25</v>
+      </c>
+      <c r="D57" s="7" t="inlineStr">
         <is>
           <t>FADING</t>
         </is>
       </c>
-      <c r="E47" s="17" t="n">
-        <v>13</v>
-      </c>
-      <c r="F47" s="10" t="inlineStr">
-        <is>
-          <t>deep 24m washout (-53%); wild vol (0.15); bo</t>
-        </is>
-      </c>
-    </row>
-    <row r="48" ht="22" customHeight="1">
-      <c r="A48" s="6" t="inlineStr">
-        <is>
-          <t>LCID</t>
-        </is>
-      </c>
-      <c r="B48" s="7" t="inlineStr">
-        <is>
-          <t>Lucid Group, Inc.</t>
-        </is>
-      </c>
-      <c r="C48" s="7" t="inlineStr">
-        <is>
-          <t>10/10</t>
-        </is>
-      </c>
-      <c r="D48" s="7" t="inlineStr">
+      <c r="E57" s="16" t="n">
+        <v>60</v>
+      </c>
+      <c r="F57" s="7" t="inlineStr">
+        <is>
+          <t>catalyst=SALE_OF_COMPANY, sector=Techn</t>
+        </is>
+      </c>
+    </row>
+    <row r="58" ht="22" customHeight="1">
+      <c r="A58" s="9" t="inlineStr">
+        <is>
+          <t>OPTU</t>
+        </is>
+      </c>
+      <c r="B58" s="10" t="inlineStr">
+        <is>
+          <t>Optimum Communicatio</t>
+        </is>
+      </c>
+      <c r="C58" s="17" t="n">
+        <v>24</v>
+      </c>
+      <c r="D58" s="10" t="inlineStr">
+        <is>
+          <t>NEUTRAL</t>
+        </is>
+      </c>
+      <c r="E58" s="17" t="n">
+        <v>3</v>
+      </c>
+      <c r="F58" s="10" t="inlineStr">
+        <is>
+          <t>catalyst=SALE_OF_COMPANY, sector=Commu</t>
+        </is>
+      </c>
+    </row>
+    <row r="59" ht="22" customHeight="1">
+      <c r="A59" s="6" t="inlineStr">
+        <is>
+          <t>NEUP</t>
+        </is>
+      </c>
+      <c r="B59" s="7" t="inlineStr">
+        <is>
+          <t>Neuphoria Therapeuti</t>
+        </is>
+      </c>
+      <c r="C59" s="16" t="n">
+        <v>23</v>
+      </c>
+      <c r="D59" s="7" t="inlineStr">
         <is>
           <t>FADING</t>
         </is>
       </c>
-      <c r="E48" s="16" t="n">
-        <v>13</v>
-      </c>
-      <c r="F48" s="7" t="inlineStr">
-        <is>
-          <t>deep 24m washout (-84%); wild vol (0.17); bo</t>
-        </is>
-      </c>
-    </row>
-    <row r="49" ht="22" customHeight="1">
-      <c r="A49" s="9" t="inlineStr">
-        <is>
-          <t>NUS</t>
-        </is>
-      </c>
-      <c r="B49" s="10" t="inlineStr">
-        <is>
-          <t>Nu Skin Enterprises,</t>
-        </is>
-      </c>
-      <c r="C49" s="10" t="inlineStr">
-        <is>
-          <t>10/10</t>
-        </is>
-      </c>
-      <c r="D49" s="10" t="inlineStr">
+      <c r="E59" s="16" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="F59" s="7" t="inlineStr">
+        <is>
+          <t>catalyst=STRATEGIC_REVIEW, sector=Heal</t>
+        </is>
+      </c>
+    </row>
+    <row r="60" ht="22" customHeight="1">
+      <c r="A60" s="9" t="inlineStr">
+        <is>
+          <t>NERV</t>
+        </is>
+      </c>
+      <c r="B60" s="10" t="inlineStr">
+        <is>
+          <t>Minerva Neuroscience</t>
+        </is>
+      </c>
+      <c r="C60" s="17" t="n">
+        <v>23</v>
+      </c>
+      <c r="D60" s="10" t="inlineStr">
+        <is>
+          <t>FADING</t>
+        </is>
+      </c>
+      <c r="E60" s="10" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="F60" s="10" t="inlineStr">
+        <is>
+          <t>catalyst=STRATEGIC_REVIEW, sector=Heal</t>
+        </is>
+      </c>
+    </row>
+    <row r="61" ht="22" customHeight="1">
+      <c r="A61" s="6" t="inlineStr">
+        <is>
+          <t>FULC</t>
+        </is>
+      </c>
+      <c r="B61" s="7" t="inlineStr">
+        <is>
+          <t>Fulcrum Therapeutics</t>
+        </is>
+      </c>
+      <c r="C61" s="16" t="n">
+        <v>23</v>
+      </c>
+      <c r="D61" s="7" t="inlineStr">
         <is>
           <t>NEUTRAL</t>
         </is>
       </c>
-      <c r="E49" s="17" t="n">
-        <v>14</v>
-      </c>
-      <c r="F49" s="10" t="inlineStr">
-        <is>
-          <t>deep 24m washout (-57%); wild vol (0.18); bo</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" s="21" t="inlineStr">
-        <is>
-          <t>Note: monster-rich catalysts (strategic-review, spin, Ch11, uplisting) are LOTTERY TICKETS — negative median, convex tail — so size these small. See GREATEST_TRADES.md.</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" s="12" t="inlineStr">
-        <is>
-          <t>ALL CANDIDATES — pre-confirmation tail odds</t>
-        </is>
-      </c>
-    </row>
-    <row r="53" ht="18" customHeight="1">
-      <c r="A53" s="15" t="inlineStr">
-        <is>
-          <t>Ticker</t>
-        </is>
-      </c>
-      <c r="B53" s="15" t="inlineStr">
-        <is>
-          <t>Name</t>
-        </is>
-      </c>
-      <c r="C53" s="4" t="inlineStr">
-        <is>
-          <t>Tail p</t>
-        </is>
-      </c>
-      <c r="D53" s="4" t="inlineStr">
-        <is>
-          <t>State</t>
-        </is>
-      </c>
-      <c r="E53" s="4" t="inlineStr">
-        <is>
-          <t>Ratio</t>
-        </is>
-      </c>
-      <c r="F53" s="4" t="inlineStr">
-        <is>
-          <t>Tail drivers</t>
-        </is>
-      </c>
-    </row>
-    <row r="54" ht="22" customHeight="1">
-      <c r="A54" s="6" t="inlineStr">
-        <is>
-          <t>USAR</t>
-        </is>
-      </c>
-      <c r="B54" s="7" t="inlineStr">
-        <is>
-          <t>USA Rare Earth, Inc.</t>
-        </is>
-      </c>
-      <c r="C54" s="16" t="n">
-        <v>28</v>
-      </c>
-      <c r="D54" s="7" t="inlineStr">
+      <c r="E61" s="16" t="n">
+        <v>8.300000000000001</v>
+      </c>
+      <c r="F61" s="7" t="inlineStr">
+        <is>
+          <t>catalyst=STRATEGIC_REVIEW, sector=Heal</t>
+        </is>
+      </c>
+    </row>
+    <row r="62" ht="22" customHeight="1">
+      <c r="A62" s="9" t="inlineStr">
+        <is>
+          <t>NDRA</t>
+        </is>
+      </c>
+      <c r="B62" s="10" t="inlineStr">
+        <is>
+          <t>ENDRA Life Sciences</t>
+        </is>
+      </c>
+      <c r="C62" s="17" t="n">
+        <v>23</v>
+      </c>
+      <c r="D62" s="10" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="E62" s="10" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="F62" s="10" t="inlineStr">
+        <is>
+          <t>catalyst=STRATEGIC_REVIEW, sector=Heal</t>
+        </is>
+      </c>
+    </row>
+    <row r="63" ht="22" customHeight="1">
+      <c r="A63" s="6" t="inlineStr">
+        <is>
+          <t>GPRO</t>
+        </is>
+      </c>
+      <c r="B63" s="7" t="inlineStr">
+        <is>
+          <t>GoPro, Inc.</t>
+        </is>
+      </c>
+      <c r="C63" s="16" t="n">
+        <v>21</v>
+      </c>
+      <c r="D63" s="7" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="E63" s="16" t="n">
+        <v>3</v>
+      </c>
+      <c r="F63" s="7" t="inlineStr">
+        <is>
+          <t>catalyst=STRATEGIC_REVIEW, sector=Tech</t>
+        </is>
+      </c>
+    </row>
+    <row r="64" ht="22" customHeight="1">
+      <c r="A64" s="9" t="inlineStr">
+        <is>
+          <t>TTEC</t>
+        </is>
+      </c>
+      <c r="B64" s="10" t="inlineStr">
+        <is>
+          <t>TTEC Holdings, Inc.</t>
+        </is>
+      </c>
+      <c r="C64" s="17" t="n">
+        <v>21</v>
+      </c>
+      <c r="D64" s="10" t="inlineStr">
+        <is>
+          <t>NEUTRAL</t>
+        </is>
+      </c>
+      <c r="E64" s="17" t="n">
+        <v>20.3</v>
+      </c>
+      <c r="F64" s="10" t="inlineStr">
+        <is>
+          <t>catalyst=STRATEGIC_REVIEW, sector=Tech</t>
+        </is>
+      </c>
+    </row>
+    <row r="65" ht="22" customHeight="1">
+      <c r="A65" s="6" t="inlineStr">
+        <is>
+          <t>CMTL</t>
+        </is>
+      </c>
+      <c r="B65" s="7" t="inlineStr">
+        <is>
+          <t>Comtech Telecommunic</t>
+        </is>
+      </c>
+      <c r="C65" s="16" t="n">
+        <v>21</v>
+      </c>
+      <c r="D65" s="7" t="inlineStr">
+        <is>
+          <t>FADING</t>
+        </is>
+      </c>
+      <c r="E65" s="16" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="F65" s="7" t="inlineStr">
+        <is>
+          <t>catalyst=STRATEGIC_REVIEW, sector=Tech</t>
+        </is>
+      </c>
+    </row>
+    <row r="66" ht="22" customHeight="1">
+      <c r="A66" s="9" t="inlineStr">
+        <is>
+          <t>DOMO</t>
+        </is>
+      </c>
+      <c r="B66" s="10" t="inlineStr">
+        <is>
+          <t>Domo, Inc.</t>
+        </is>
+      </c>
+      <c r="C66" s="17" t="n">
+        <v>21</v>
+      </c>
+      <c r="D66" s="10" t="inlineStr">
+        <is>
+          <t>NEUTRAL</t>
+        </is>
+      </c>
+      <c r="E66" s="17" t="n">
+        <v>3</v>
+      </c>
+      <c r="F66" s="10" t="inlineStr">
+        <is>
+          <t>catalyst=STRATEGIC_REVIEW, sector=Tech</t>
+        </is>
+      </c>
+    </row>
+    <row r="67" ht="22" customHeight="1">
+      <c r="A67" s="6" t="inlineStr">
+        <is>
+          <t>AGPU</t>
+        </is>
+      </c>
+      <c r="B67" s="7" t="inlineStr">
+        <is>
+          <t>Axe Compute Inc.</t>
+        </is>
+      </c>
+      <c r="C67" s="16" t="n">
+        <v>21</v>
+      </c>
+      <c r="D67" s="7" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="E67" s="16" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="F67" s="7" t="inlineStr">
+        <is>
+          <t>catalyst=STRATEGIC_REVIEW, sector=Tech</t>
+        </is>
+      </c>
+    </row>
+    <row r="68" ht="22" customHeight="1">
+      <c r="A68" s="9" t="inlineStr">
+        <is>
+          <t>VRME</t>
+        </is>
+      </c>
+      <c r="B68" s="10" t="inlineStr">
+        <is>
+          <t>VerifyMe, Inc.</t>
+        </is>
+      </c>
+      <c r="C68" s="17" t="n">
+        <v>21</v>
+      </c>
+      <c r="D68" s="10" t="inlineStr">
+        <is>
+          <t>NEUTRAL</t>
+        </is>
+      </c>
+      <c r="E68" s="17" t="n">
+        <v>8.1</v>
+      </c>
+      <c r="F68" s="10" t="inlineStr">
+        <is>
+          <t>catalyst=SALE_OF_COMPANY, size=micro,</t>
+        </is>
+      </c>
+    </row>
+    <row r="69" ht="22" customHeight="1">
+      <c r="A69" s="6" t="inlineStr">
+        <is>
+          <t>PLAG</t>
+        </is>
+      </c>
+      <c r="B69" s="7" t="inlineStr">
+        <is>
+          <t>Planet Green Holding</t>
+        </is>
+      </c>
+      <c r="C69" s="16" t="n">
+        <v>21</v>
+      </c>
+      <c r="D69" s="7" t="inlineStr">
+        <is>
+          <t>FADING</t>
+        </is>
+      </c>
+      <c r="E69" s="7" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="F69" s="7" t="inlineStr">
+        <is>
+          <t>catalyst=SALE_OF_COMPANY, size=micro,</t>
+        </is>
+      </c>
+    </row>
+    <row r="70" ht="22" customHeight="1">
+      <c r="A70" s="9" t="inlineStr">
+        <is>
+          <t>HHS</t>
+        </is>
+      </c>
+      <c r="B70" s="10" t="inlineStr">
+        <is>
+          <t>Harte Hanks, Inc.</t>
+        </is>
+      </c>
+      <c r="C70" s="17" t="n">
+        <v>21</v>
+      </c>
+      <c r="D70" s="10" t="inlineStr">
         <is>
           <t>PENDING</t>
         </is>
       </c>
-      <c r="E54" s="7" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="F54" s="7" t="inlineStr">
-        <is>
-          <t>catalyst=SALE_OF_COMPANY, sector=Basic</t>
-        </is>
-      </c>
-    </row>
-    <row r="55" ht="22" customHeight="1">
-      <c r="A55" s="9" t="inlineStr">
-        <is>
-          <t>AMS</t>
-        </is>
-      </c>
-      <c r="B55" s="10" t="inlineStr">
-        <is>
-          <t>American Shared Hosp</t>
-        </is>
-      </c>
-      <c r="C55" s="17" t="n">
-        <v>27</v>
-      </c>
-      <c r="D55" s="10" t="inlineStr">
+      <c r="E70" s="17" t="n">
+        <v>6.9</v>
+      </c>
+      <c r="F70" s="10" t="inlineStr">
+        <is>
+          <t>catalyst=SALE_OF_COMPANY, size=micro,</t>
+        </is>
+      </c>
+    </row>
+    <row r="71" ht="22" customHeight="1">
+      <c r="A71" s="6" t="inlineStr">
+        <is>
+          <t>DXLG</t>
+        </is>
+      </c>
+      <c r="B71" s="7" t="inlineStr">
+        <is>
+          <t>Destination XL Group</t>
+        </is>
+      </c>
+      <c r="C71" s="16" t="n">
+        <v>21</v>
+      </c>
+      <c r="D71" s="7" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="E71" s="16" t="n">
+        <v>60</v>
+      </c>
+      <c r="F71" s="7" t="inlineStr">
+        <is>
+          <t>catalyst=SALE_OF_COMPANY, size=micro,</t>
+        </is>
+      </c>
+    </row>
+    <row r="72" ht="22" customHeight="1">
+      <c r="A72" s="9" t="inlineStr">
+        <is>
+          <t>HCAT</t>
+        </is>
+      </c>
+      <c r="B72" s="10" t="inlineStr">
+        <is>
+          <t>Health Catalyst, Inc</t>
+        </is>
+      </c>
+      <c r="C72" s="17" t="n">
+        <v>20</v>
+      </c>
+      <c r="D72" s="10" t="inlineStr">
+        <is>
+          <t>FADING</t>
+        </is>
+      </c>
+      <c r="E72" s="17" t="n">
+        <v>6.1</v>
+      </c>
+      <c r="F72" s="10" t="inlineStr">
+        <is>
+          <t>catalyst=ASSET_SALE, sector=Healthcare</t>
+        </is>
+      </c>
+    </row>
+    <row r="73" ht="22" customHeight="1">
+      <c r="A73" s="6" t="inlineStr">
+        <is>
+          <t>KROS</t>
+        </is>
+      </c>
+      <c r="B73" s="7" t="inlineStr">
+        <is>
+          <t>Keros Therapeutics,</t>
+        </is>
+      </c>
+      <c r="C73" s="16" t="n">
+        <v>20</v>
+      </c>
+      <c r="D73" s="7" t="inlineStr">
         <is>
           <t>NEUTRAL</t>
         </is>
       </c>
-      <c r="E55" s="17" t="n">
-        <v>60</v>
-      </c>
-      <c r="F55" s="10" t="inlineStr">
+      <c r="E73" s="16" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="F73" s="7" t="inlineStr">
+        <is>
+          <t>catalyst=TENDER_OFFER, sector=Healthca</t>
+        </is>
+      </c>
+    </row>
+    <row r="74" ht="22" customHeight="1">
+      <c r="A74" s="9" t="inlineStr">
+        <is>
+          <t>FMC</t>
+        </is>
+      </c>
+      <c r="B74" s="10" t="inlineStr">
+        <is>
+          <t>FMC Corporation</t>
+        </is>
+      </c>
+      <c r="C74" s="17" t="n">
+        <v>20</v>
+      </c>
+      <c r="D74" s="10" t="inlineStr">
+        <is>
+          <t>NEUTRAL</t>
+        </is>
+      </c>
+      <c r="E74" s="17" t="n">
+        <v>6.1</v>
+      </c>
+      <c r="F74" s="10" t="inlineStr">
+        <is>
+          <t>catalyst=TENDER_OFFER, sector=Basic Ma</t>
+        </is>
+      </c>
+    </row>
+    <row r="75" ht="22" customHeight="1">
+      <c r="A75" s="6" t="inlineStr">
+        <is>
+          <t>JKHY</t>
+        </is>
+      </c>
+      <c r="B75" s="7" t="inlineStr">
+        <is>
+          <t>Jack Henry &amp; Associa</t>
+        </is>
+      </c>
+      <c r="C75" s="16" t="n">
+        <v>20</v>
+      </c>
+      <c r="D75" s="7" t="inlineStr">
+        <is>
+          <t>NEUTRAL</t>
+        </is>
+      </c>
+      <c r="E75" s="7" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="F75" s="7" t="inlineStr">
+        <is>
+          <t>catalyst=SALE_OF_COMPANY, sector=Techn</t>
+        </is>
+      </c>
+    </row>
+    <row r="76" ht="22" customHeight="1">
+      <c r="A76" s="9" t="inlineStr">
+        <is>
+          <t>SPRB</t>
+        </is>
+      </c>
+      <c r="B76" s="10" t="inlineStr">
+        <is>
+          <t>Spruce Biosciences,</t>
+        </is>
+      </c>
+      <c r="C76" s="17" t="n">
+        <v>20</v>
+      </c>
+      <c r="D76" s="10" t="inlineStr">
+        <is>
+          <t>NEUTRAL</t>
+        </is>
+      </c>
+      <c r="E76" s="10" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="F76" s="10" t="inlineStr">
+        <is>
+          <t>sector=Healthcare, size=micro, drawdow</t>
+        </is>
+      </c>
+    </row>
+    <row r="77" ht="22" customHeight="1">
+      <c r="A77" s="6" t="inlineStr">
+        <is>
+          <t>INO</t>
+        </is>
+      </c>
+      <c r="B77" s="7" t="inlineStr">
+        <is>
+          <t>Inovio Pharmaceutica</t>
+        </is>
+      </c>
+      <c r="C77" s="16" t="n">
+        <v>20</v>
+      </c>
+      <c r="D77" s="7" t="inlineStr">
+        <is>
+          <t>NEUTRAL</t>
+        </is>
+      </c>
+      <c r="E77" s="7" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="F77" s="7" t="inlineStr">
+        <is>
+          <t>sector=Healthcare, size=micro, drawdow</t>
+        </is>
+      </c>
+    </row>
+    <row r="78" ht="22" customHeight="1">
+      <c r="A78" s="9" t="inlineStr">
+        <is>
+          <t>GMAB</t>
+        </is>
+      </c>
+      <c r="B78" s="10" t="inlineStr">
+        <is>
+          <t>Genmab A/S</t>
+        </is>
+      </c>
+      <c r="C78" s="17" t="n">
+        <v>20</v>
+      </c>
+      <c r="D78" s="10" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="E78" s="10" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="F78" s="10" t="inlineStr">
         <is>
           <t>catalyst=SALE_OF_COMPANY, sector=Healt</t>
         </is>
       </c>
     </row>
-    <row r="56" ht="22" customHeight="1">
-      <c r="A56" s="6" t="inlineStr">
-        <is>
-          <t>BTAI</t>
-        </is>
-      </c>
-      <c r="B56" s="7" t="inlineStr">
-        <is>
-          <t>BioXcel Therapeutics</t>
-        </is>
-      </c>
-      <c r="C56" s="16" t="n">
-        <v>27</v>
-      </c>
-      <c r="D56" s="7" t="inlineStr">
+    <row r="79" ht="22" customHeight="1">
+      <c r="A79" s="6" t="inlineStr">
+        <is>
+          <t>PTN</t>
+        </is>
+      </c>
+      <c r="B79" s="7" t="inlineStr">
+        <is>
+          <t>Palatin Technologies</t>
+        </is>
+      </c>
+      <c r="C79" s="16" t="n">
+        <v>20</v>
+      </c>
+      <c r="D79" s="7" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="E79" s="16" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="F79" s="7" t="inlineStr">
+        <is>
+          <t>sector=Healthcare, size=micro, drawdow</t>
+        </is>
+      </c>
+    </row>
+    <row r="80" ht="22" customHeight="1">
+      <c r="A80" s="9" t="inlineStr">
+        <is>
+          <t>MLYS</t>
+        </is>
+      </c>
+      <c r="B80" s="10" t="inlineStr">
+        <is>
+          <t>Mineralys Therapeuti</t>
+        </is>
+      </c>
+      <c r="C80" s="17" t="n">
+        <v>20</v>
+      </c>
+      <c r="D80" s="10" t="inlineStr">
         <is>
           <t>NEUTRAL</t>
         </is>
       </c>
-      <c r="E56" s="7" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="F56" s="7" t="inlineStr">
-        <is>
-          <t>catalyst=SALE_OF_COMPANY, sector=Healt</t>
-        </is>
-      </c>
-    </row>
-    <row r="57" ht="22" customHeight="1">
-      <c r="A57" s="9" t="inlineStr">
-        <is>
-          <t>SUNE</t>
-        </is>
-      </c>
-      <c r="B57" s="10" t="inlineStr">
-        <is>
-          <t>SUNation Energy, Inc</t>
-        </is>
-      </c>
-      <c r="C57" s="17" t="n">
+      <c r="E80" s="10" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="F80" s="10" t="inlineStr">
+        <is>
+          <t>sector=Healthcare, size=mid, drawdown_</t>
+        </is>
+      </c>
+    </row>
+    <row r="81" ht="22" customHeight="1">
+      <c r="A81" s="6" t="inlineStr">
+        <is>
+          <t>LUCY</t>
+        </is>
+      </c>
+      <c r="B81" s="7" t="inlineStr">
+        <is>
+          <t>Innovative Eyewear,</t>
+        </is>
+      </c>
+      <c r="C81" s="16" t="n">
+        <v>20</v>
+      </c>
+      <c r="D81" s="7" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="E81" s="16" t="n">
+        <v>45.6</v>
+      </c>
+      <c r="F81" s="7" t="inlineStr">
+        <is>
+          <t>sector=Healthcare, size=micro, drawdow</t>
+        </is>
+      </c>
+    </row>
+    <row r="82" ht="22" customHeight="1">
+      <c r="A82" s="9" t="inlineStr">
+        <is>
+          <t>PMCB</t>
+        </is>
+      </c>
+      <c r="B82" s="10" t="inlineStr">
+        <is>
+          <t>PharmaCyte  Biotech,</t>
+        </is>
+      </c>
+      <c r="C82" s="17" t="n">
+        <v>20</v>
+      </c>
+      <c r="D82" s="10" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="E82" s="17" t="n">
+        <v>30</v>
+      </c>
+      <c r="F82" s="10" t="inlineStr">
+        <is>
+          <t>sector=Healthcare, size=micro, drawdow</t>
+        </is>
+      </c>
+    </row>
+    <row r="83" ht="22" customHeight="1">
+      <c r="A83" s="6" t="inlineStr">
+        <is>
+          <t>FWDI</t>
+        </is>
+      </c>
+      <c r="B83" s="7" t="inlineStr">
+        <is>
+          <t>Forward Industries,</t>
+        </is>
+      </c>
+      <c r="C83" s="16" t="n">
+        <v>19</v>
+      </c>
+      <c r="D83" s="7" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="E83" s="16" t="n">
+        <v>12.9</v>
+      </c>
+      <c r="F83" s="7" t="inlineStr">
+        <is>
+          <t>catalyst=SALE_OF_COMPANY, drawdown_12m</t>
+        </is>
+      </c>
+    </row>
+    <row r="84" ht="22" customHeight="1">
+      <c r="A84" s="9" t="inlineStr">
+        <is>
+          <t>LAB</t>
+        </is>
+      </c>
+      <c r="B84" s="10" t="inlineStr">
+        <is>
+          <t>Standard BioTools In</t>
+        </is>
+      </c>
+      <c r="C84" s="17" t="n">
+        <v>19</v>
+      </c>
+      <c r="D84" s="10" t="inlineStr">
+        <is>
+          <t>NEUTRAL</t>
+        </is>
+      </c>
+      <c r="E84" s="17" t="n">
+        <v>42.3</v>
+      </c>
+      <c r="F84" s="10" t="inlineStr">
+        <is>
+          <t>catalyst=ASSET_SALE, sector=Healthcare</t>
+        </is>
+      </c>
+    </row>
+    <row r="85" ht="22" customHeight="1">
+      <c r="A85" s="6" t="inlineStr">
+        <is>
+          <t>PRGO</t>
+        </is>
+      </c>
+      <c r="B85" s="7" t="inlineStr">
+        <is>
+          <t>Perrigo Company plc</t>
+        </is>
+      </c>
+      <c r="C85" s="16" t="n">
+        <v>19</v>
+      </c>
+      <c r="D85" s="7" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="E85" s="16" t="n">
+        <v>25.6</v>
+      </c>
+      <c r="F85" s="7" t="inlineStr">
+        <is>
+          <t>catalyst=ASSET_SALE, sector=Healthcare</t>
+        </is>
+      </c>
+    </row>
+    <row r="86" ht="22" customHeight="1">
+      <c r="A86" s="9" t="inlineStr">
+        <is>
+          <t>CERT</t>
+        </is>
+      </c>
+      <c r="B86" s="10" t="inlineStr">
+        <is>
+          <t>Certara, Inc.</t>
+        </is>
+      </c>
+      <c r="C86" s="17" t="n">
+        <v>19</v>
+      </c>
+      <c r="D86" s="10" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="E86" s="17" t="n">
+        <v>10.7</v>
+      </c>
+      <c r="F86" s="10" t="inlineStr">
+        <is>
+          <t>catalyst=ASSET_SALE, sector=Healthcare</t>
+        </is>
+      </c>
+    </row>
+    <row r="87" ht="22" customHeight="1">
+      <c r="A87" s="6" t="inlineStr">
+        <is>
+          <t>FIS</t>
+        </is>
+      </c>
+      <c r="B87" s="7" t="inlineStr">
+        <is>
+          <t>Fidelity National In</t>
+        </is>
+      </c>
+      <c r="C87" s="16" t="n">
+        <v>19</v>
+      </c>
+      <c r="D87" s="7" t="inlineStr">
+        <is>
+          <t>FADING</t>
+        </is>
+      </c>
+      <c r="E87" s="16" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="F87" s="7" t="inlineStr">
+        <is>
+          <t>catalyst=SPINOFF, sector=Technology, d</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="12" t="inlineStr">
+        <is>
+          <t>WHAT RAISES TAIL ODDS (historical lift vs 10% base)</t>
+        </is>
+      </c>
+    </row>
+    <row r="90" ht="18" customHeight="1">
+      <c r="A90" s="4" t="inlineStr">
+        <is>
+          <t>Feature = bin</t>
+        </is>
+      </c>
+      <c r="B90" s="4" t="inlineStr">
+        <is>
+          <t>Tail rate</t>
+        </is>
+      </c>
+      <c r="C90" s="4" t="inlineStr">
+        <is>
+          <t>Lift</t>
+        </is>
+      </c>
+      <c r="D90" s="4" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="E90" s="15" t="inlineStr"/>
+    </row>
+    <row r="91" ht="16" customHeight="1">
+      <c r="A91" s="6" t="inlineStr">
+        <is>
+          <t>catalyst = SALE_OF_COMPANY</t>
+        </is>
+      </c>
+      <c r="B91" s="16" t="n">
         <v>25</v>
       </c>
-      <c r="D57" s="10" t="inlineStr">
-        <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="E57" s="17" t="n">
-        <v>60</v>
-      </c>
-      <c r="F57" s="10" t="inlineStr">
-        <is>
-          <t>catalyst=SALE_OF_COMPANY, sector=Techn</t>
-        </is>
-      </c>
-    </row>
-    <row r="58" ht="22" customHeight="1">
-      <c r="A58" s="6" t="inlineStr">
-        <is>
-          <t>JTAI</t>
-        </is>
-      </c>
-      <c r="B58" s="7" t="inlineStr">
-        <is>
-          <t>Jet.AI Inc.</t>
-        </is>
-      </c>
-      <c r="C58" s="16" t="n">
-        <v>25</v>
-      </c>
-      <c r="D58" s="7" t="inlineStr">
-        <is>
-          <t>FADING</t>
-        </is>
-      </c>
-      <c r="E58" s="16" t="n">
-        <v>60</v>
-      </c>
-      <c r="F58" s="7" t="inlineStr">
-        <is>
-          <t>catalyst=SALE_OF_COMPANY, sector=Techn</t>
-        </is>
-      </c>
-    </row>
-    <row r="59" ht="22" customHeight="1">
-      <c r="A59" s="9" t="inlineStr">
-        <is>
-          <t>OPTU</t>
-        </is>
-      </c>
-      <c r="B59" s="10" t="inlineStr">
-        <is>
-          <t>Optimum Communicatio</t>
-        </is>
-      </c>
-      <c r="C59" s="17" t="n">
-        <v>24</v>
-      </c>
-      <c r="D59" s="10" t="inlineStr">
-        <is>
-          <t>NEUTRAL</t>
-        </is>
-      </c>
-      <c r="E59" s="17" t="n">
-        <v>3</v>
-      </c>
-      <c r="F59" s="10" t="inlineStr">
-        <is>
-          <t>catalyst=SALE_OF_COMPANY, sector=Commu</t>
-        </is>
-      </c>
-    </row>
-    <row r="60" ht="22" customHeight="1">
-      <c r="A60" s="6" t="inlineStr">
-        <is>
-          <t>NEUP</t>
-        </is>
-      </c>
-      <c r="B60" s="7" t="inlineStr">
-        <is>
-          <t>Neuphoria Therapeuti</t>
-        </is>
-      </c>
-      <c r="C60" s="16" t="n">
-        <v>23</v>
-      </c>
-      <c r="D60" s="7" t="inlineStr">
-        <is>
-          <t>FADING</t>
-        </is>
-      </c>
-      <c r="E60" s="16" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="F60" s="7" t="inlineStr">
-        <is>
-          <t>catalyst=STRATEGIC_REVIEW, sector=Heal</t>
-        </is>
-      </c>
-    </row>
-    <row r="61" ht="22" customHeight="1">
-      <c r="A61" s="9" t="inlineStr">
-        <is>
-          <t>NERV</t>
-        </is>
-      </c>
-      <c r="B61" s="10" t="inlineStr">
-        <is>
-          <t>Minerva Neuroscience</t>
-        </is>
-      </c>
-      <c r="C61" s="17" t="n">
-        <v>23</v>
-      </c>
-      <c r="D61" s="10" t="inlineStr">
-        <is>
-          <t>FADING</t>
-        </is>
-      </c>
-      <c r="E61" s="10" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="F61" s="10" t="inlineStr">
-        <is>
-          <t>catalyst=STRATEGIC_REVIEW, sector=Heal</t>
-        </is>
-      </c>
-    </row>
-    <row r="62" ht="22" customHeight="1">
-      <c r="A62" s="6" t="inlineStr">
-        <is>
-          <t>FULC</t>
-        </is>
-      </c>
-      <c r="B62" s="7" t="inlineStr">
-        <is>
-          <t>Fulcrum Therapeutics</t>
-        </is>
-      </c>
-      <c r="C62" s="16" t="n">
-        <v>23</v>
-      </c>
-      <c r="D62" s="7" t="inlineStr">
-        <is>
-          <t>NEUTRAL</t>
-        </is>
-      </c>
-      <c r="E62" s="16" t="n">
-        <v>8.300000000000001</v>
-      </c>
-      <c r="F62" s="7" t="inlineStr">
-        <is>
-          <t>catalyst=STRATEGIC_REVIEW, sector=Heal</t>
-        </is>
-      </c>
-    </row>
-    <row r="63" ht="22" customHeight="1">
-      <c r="A63" s="9" t="inlineStr">
-        <is>
-          <t>NDRA</t>
-        </is>
-      </c>
-      <c r="B63" s="10" t="inlineStr">
-        <is>
-          <t>ENDRA Life Sciences</t>
-        </is>
-      </c>
-      <c r="C63" s="17" t="n">
-        <v>23</v>
-      </c>
-      <c r="D63" s="10" t="inlineStr">
-        <is>
-          <t>CONFIRMED</t>
-        </is>
-      </c>
-      <c r="E63" s="10" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="F63" s="10" t="inlineStr">
-        <is>
-          <t>catalyst=STRATEGIC_REVIEW, sector=Heal</t>
-        </is>
-      </c>
-    </row>
-    <row r="64" ht="22" customHeight="1">
-      <c r="A64" s="6" t="inlineStr">
-        <is>
-          <t>GPRO</t>
-        </is>
-      </c>
-      <c r="B64" s="7" t="inlineStr">
-        <is>
-          <t>GoPro, Inc.</t>
-        </is>
-      </c>
-      <c r="C64" s="16" t="n">
-        <v>21</v>
-      </c>
-      <c r="D64" s="7" t="inlineStr">
-        <is>
-          <t>CONFIRMED</t>
-        </is>
-      </c>
-      <c r="E64" s="16" t="n">
-        <v>3</v>
-      </c>
-      <c r="F64" s="7" t="inlineStr">
-        <is>
-          <t>catalyst=STRATEGIC_REVIEW, sector=Tech</t>
-        </is>
-      </c>
-    </row>
-    <row r="65" ht="22" customHeight="1">
-      <c r="A65" s="9" t="inlineStr">
-        <is>
-          <t>TTEC</t>
-        </is>
-      </c>
-      <c r="B65" s="10" t="inlineStr">
-        <is>
-          <t>TTEC Holdings, Inc.</t>
-        </is>
-      </c>
-      <c r="C65" s="17" t="n">
-        <v>21</v>
-      </c>
-      <c r="D65" s="10" t="inlineStr">
-        <is>
-          <t>NEUTRAL</t>
-        </is>
-      </c>
-      <c r="E65" s="17" t="n">
-        <v>20.3</v>
-      </c>
-      <c r="F65" s="10" t="inlineStr">
-        <is>
-          <t>catalyst=STRATEGIC_REVIEW, sector=Tech</t>
-        </is>
-      </c>
-    </row>
-    <row r="66" ht="22" customHeight="1">
-      <c r="A66" s="6" t="inlineStr">
-        <is>
-          <t>CMTL</t>
-        </is>
-      </c>
-      <c r="B66" s="7" t="inlineStr">
-        <is>
-          <t>Comtech Telecommunic</t>
-        </is>
-      </c>
-      <c r="C66" s="16" t="n">
-        <v>21</v>
-      </c>
-      <c r="D66" s="7" t="inlineStr">
-        <is>
-          <t>FADING</t>
-        </is>
-      </c>
-      <c r="E66" s="16" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="F66" s="7" t="inlineStr">
-        <is>
-          <t>catalyst=STRATEGIC_REVIEW, sector=Tech</t>
-        </is>
-      </c>
-    </row>
-    <row r="67" ht="22" customHeight="1">
-      <c r="A67" s="9" t="inlineStr">
-        <is>
-          <t>DOMO</t>
-        </is>
-      </c>
-      <c r="B67" s="10" t="inlineStr">
-        <is>
-          <t>Domo, Inc.</t>
-        </is>
-      </c>
-      <c r="C67" s="17" t="n">
-        <v>21</v>
-      </c>
-      <c r="D67" s="10" t="inlineStr">
-        <is>
-          <t>NEUTRAL</t>
-        </is>
-      </c>
-      <c r="E67" s="17" t="n">
-        <v>3</v>
-      </c>
-      <c r="F67" s="10" t="inlineStr">
-        <is>
-          <t>catalyst=STRATEGIC_REVIEW, sector=Tech</t>
-        </is>
-      </c>
-    </row>
-    <row r="68" ht="22" customHeight="1">
-      <c r="A68" s="6" t="inlineStr">
-        <is>
-          <t>AGPU</t>
-        </is>
-      </c>
-      <c r="B68" s="7" t="inlineStr">
-        <is>
-          <t>Axe Compute Inc.</t>
-        </is>
-      </c>
-      <c r="C68" s="16" t="n">
-        <v>21</v>
-      </c>
-      <c r="D68" s="7" t="inlineStr">
-        <is>
-          <t>CONFIRMED</t>
-        </is>
-      </c>
-      <c r="E68" s="16" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="F68" s="7" t="inlineStr">
-        <is>
-          <t>catalyst=STRATEGIC_REVIEW, sector=Tech</t>
-        </is>
-      </c>
-    </row>
-    <row r="69" ht="22" customHeight="1">
-      <c r="A69" s="9" t="inlineStr">
-        <is>
-          <t>VRME</t>
-        </is>
-      </c>
-      <c r="B69" s="10" t="inlineStr">
-        <is>
-          <t>VerifyMe, Inc.</t>
-        </is>
-      </c>
-      <c r="C69" s="17" t="n">
-        <v>21</v>
-      </c>
-      <c r="D69" s="10" t="inlineStr">
-        <is>
-          <t>NEUTRAL</t>
-        </is>
-      </c>
-      <c r="E69" s="17" t="n">
-        <v>8.1</v>
-      </c>
-      <c r="F69" s="10" t="inlineStr">
-        <is>
-          <t>catalyst=SALE_OF_COMPANY, size=micro,</t>
-        </is>
-      </c>
-    </row>
-    <row r="70" ht="22" customHeight="1">
-      <c r="A70" s="6" t="inlineStr">
-        <is>
-          <t>PLAG</t>
-        </is>
-      </c>
-      <c r="B70" s="7" t="inlineStr">
-        <is>
-          <t>Planet Green Holding</t>
-        </is>
-      </c>
-      <c r="C70" s="16" t="n">
-        <v>21</v>
-      </c>
-      <c r="D70" s="7" t="inlineStr">
-        <is>
-          <t>FADING</t>
-        </is>
-      </c>
-      <c r="E70" s="7" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="F70" s="7" t="inlineStr">
-        <is>
-          <t>catalyst=SALE_OF_COMPANY, size=micro,</t>
-        </is>
-      </c>
-    </row>
-    <row r="71" ht="22" customHeight="1">
-      <c r="A71" s="9" t="inlineStr">
-        <is>
-          <t>HHS</t>
-        </is>
-      </c>
-      <c r="B71" s="10" t="inlineStr">
-        <is>
-          <t>Harte Hanks, Inc.</t>
-        </is>
-      </c>
-      <c r="C71" s="17" t="n">
-        <v>21</v>
-      </c>
-      <c r="D71" s="10" t="inlineStr">
-        <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="E71" s="17" t="n">
-        <v>6.9</v>
-      </c>
-      <c r="F71" s="10" t="inlineStr">
-        <is>
-          <t>catalyst=SALE_OF_COMPANY, size=micro,</t>
-        </is>
-      </c>
-    </row>
-    <row r="72" ht="22" customHeight="1">
-      <c r="A72" s="6" t="inlineStr">
-        <is>
-          <t>DXLG</t>
-        </is>
-      </c>
-      <c r="B72" s="7" t="inlineStr">
-        <is>
-          <t>Destination XL Group</t>
-        </is>
-      </c>
-      <c r="C72" s="16" t="n">
-        <v>21</v>
-      </c>
-      <c r="D72" s="7" t="inlineStr">
-        <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="E72" s="16" t="n">
-        <v>60</v>
-      </c>
-      <c r="F72" s="7" t="inlineStr">
-        <is>
-          <t>catalyst=SALE_OF_COMPANY, size=micro,</t>
-        </is>
-      </c>
-    </row>
-    <row r="73" ht="22" customHeight="1">
-      <c r="A73" s="9" t="inlineStr">
-        <is>
-          <t>HCAT</t>
-        </is>
-      </c>
-      <c r="B73" s="10" t="inlineStr">
-        <is>
-          <t>Health Catalyst, Inc</t>
-        </is>
-      </c>
-      <c r="C73" s="17" t="n">
-        <v>20</v>
-      </c>
-      <c r="D73" s="10" t="inlineStr">
-        <is>
-          <t>FADING</t>
-        </is>
-      </c>
-      <c r="E73" s="17" t="n">
-        <v>6.1</v>
-      </c>
-      <c r="F73" s="10" t="inlineStr">
-        <is>
-          <t>catalyst=ASSET_SALE, sector=Healthcare</t>
-        </is>
-      </c>
-    </row>
-    <row r="74" ht="22" customHeight="1">
-      <c r="A74" s="6" t="inlineStr">
-        <is>
-          <t>KROS</t>
-        </is>
-      </c>
-      <c r="B74" s="7" t="inlineStr">
-        <is>
-          <t>Keros Therapeutics,</t>
-        </is>
-      </c>
-      <c r="C74" s="16" t="n">
-        <v>20</v>
-      </c>
-      <c r="D74" s="7" t="inlineStr">
-        <is>
-          <t>NEUTRAL</t>
-        </is>
-      </c>
-      <c r="E74" s="16" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="F74" s="7" t="inlineStr">
-        <is>
-          <t>catalyst=TENDER_OFFER, sector=Healthca</t>
-        </is>
-      </c>
-    </row>
-    <row r="75" ht="22" customHeight="1">
-      <c r="A75" s="9" t="inlineStr">
-        <is>
-          <t>FMC</t>
-        </is>
-      </c>
-      <c r="B75" s="10" t="inlineStr">
-        <is>
-          <t>FMC Corporation</t>
-        </is>
-      </c>
-      <c r="C75" s="17" t="n">
-        <v>20</v>
-      </c>
-      <c r="D75" s="10" t="inlineStr">
-        <is>
-          <t>NEUTRAL</t>
-        </is>
-      </c>
-      <c r="E75" s="17" t="n">
-        <v>6.1</v>
-      </c>
-      <c r="F75" s="10" t="inlineStr">
-        <is>
-          <t>catalyst=TENDER_OFFER, sector=Basic Ma</t>
-        </is>
-      </c>
-    </row>
-    <row r="76" ht="22" customHeight="1">
-      <c r="A76" s="6" t="inlineStr">
-        <is>
-          <t>JKHY</t>
-        </is>
-      </c>
-      <c r="B76" s="7" t="inlineStr">
-        <is>
-          <t>Jack Henry &amp; Associa</t>
-        </is>
-      </c>
-      <c r="C76" s="16" t="n">
-        <v>20</v>
-      </c>
-      <c r="D76" s="7" t="inlineStr">
-        <is>
-          <t>NEUTRAL</t>
-        </is>
-      </c>
-      <c r="E76" s="7" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="F76" s="7" t="inlineStr">
-        <is>
-          <t>catalyst=SALE_OF_COMPANY, sector=Techn</t>
-        </is>
-      </c>
-    </row>
-    <row r="77" ht="22" customHeight="1">
-      <c r="A77" s="9" t="inlineStr">
-        <is>
-          <t>SPRB</t>
-        </is>
-      </c>
-      <c r="B77" s="10" t="inlineStr">
-        <is>
-          <t>Spruce Biosciences,</t>
-        </is>
-      </c>
-      <c r="C77" s="17" t="n">
-        <v>20</v>
-      </c>
-      <c r="D77" s="10" t="inlineStr">
-        <is>
-          <t>NEUTRAL</t>
-        </is>
-      </c>
-      <c r="E77" s="10" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="F77" s="10" t="inlineStr">
-        <is>
-          <t>sector=Healthcare, size=micro, drawdow</t>
-        </is>
-      </c>
-    </row>
-    <row r="78" ht="22" customHeight="1">
-      <c r="A78" s="6" t="inlineStr">
-        <is>
-          <t>INO</t>
-        </is>
-      </c>
-      <c r="B78" s="7" t="inlineStr">
-        <is>
-          <t>Inovio Pharmaceutica</t>
-        </is>
-      </c>
-      <c r="C78" s="16" t="n">
-        <v>20</v>
-      </c>
-      <c r="D78" s="7" t="inlineStr">
-        <is>
-          <t>NEUTRAL</t>
-        </is>
-      </c>
-      <c r="E78" s="7" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="F78" s="7" t="inlineStr">
-        <is>
-          <t>sector=Healthcare, size=micro, drawdow</t>
-        </is>
-      </c>
-    </row>
-    <row r="79" ht="22" customHeight="1">
-      <c r="A79" s="9" t="inlineStr">
-        <is>
-          <t>GMAB</t>
-        </is>
-      </c>
-      <c r="B79" s="10" t="inlineStr">
-        <is>
-          <t>Genmab A/S</t>
-        </is>
-      </c>
-      <c r="C79" s="17" t="n">
-        <v>20</v>
-      </c>
-      <c r="D79" s="10" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="E79" s="10" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="F79" s="10" t="inlineStr">
-        <is>
-          <t>catalyst=SALE_OF_COMPANY, sector=Healt</t>
-        </is>
-      </c>
-    </row>
-    <row r="80" ht="22" customHeight="1">
-      <c r="A80" s="6" t="inlineStr">
-        <is>
-          <t>PTN</t>
-        </is>
-      </c>
-      <c r="B80" s="7" t="inlineStr">
-        <is>
-          <t>Palatin Technologies</t>
-        </is>
-      </c>
-      <c r="C80" s="16" t="n">
-        <v>20</v>
-      </c>
-      <c r="D80" s="7" t="inlineStr">
-        <is>
-          <t>CONFIRMED</t>
-        </is>
-      </c>
-      <c r="E80" s="16" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="F80" s="7" t="inlineStr">
-        <is>
-          <t>sector=Healthcare, size=micro, drawdow</t>
-        </is>
-      </c>
-    </row>
-    <row r="81" ht="22" customHeight="1">
-      <c r="A81" s="9" t="inlineStr">
-        <is>
-          <t>MLYS</t>
-        </is>
-      </c>
-      <c r="B81" s="10" t="inlineStr">
-        <is>
-          <t>Mineralys Therapeuti</t>
-        </is>
-      </c>
-      <c r="C81" s="17" t="n">
-        <v>20</v>
-      </c>
-      <c r="D81" s="10" t="inlineStr">
-        <is>
-          <t>NEUTRAL</t>
-        </is>
-      </c>
-      <c r="E81" s="10" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="F81" s="10" t="inlineStr">
-        <is>
-          <t>sector=Healthcare, size=mid, drawdown_</t>
-        </is>
-      </c>
-    </row>
-    <row r="82" ht="22" customHeight="1">
-      <c r="A82" s="6" t="inlineStr">
-        <is>
-          <t>LUCY</t>
-        </is>
-      </c>
-      <c r="B82" s="7" t="inlineStr">
-        <is>
-          <t>Innovative Eyewear,</t>
-        </is>
-      </c>
-      <c r="C82" s="16" t="n">
-        <v>20</v>
-      </c>
-      <c r="D82" s="7" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="E82" s="16" t="n">
-        <v>45.6</v>
-      </c>
-      <c r="F82" s="7" t="inlineStr">
-        <is>
-          <t>sector=Healthcare, size=micro, drawdow</t>
-        </is>
-      </c>
-    </row>
-    <row r="83" ht="22" customHeight="1">
-      <c r="A83" s="9" t="inlineStr">
-        <is>
-          <t>PMCB</t>
-        </is>
-      </c>
-      <c r="B83" s="10" t="inlineStr">
-        <is>
-          <t>PharmaCyte  Biotech,</t>
-        </is>
-      </c>
-      <c r="C83" s="17" t="n">
-        <v>20</v>
-      </c>
-      <c r="D83" s="10" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="E83" s="17" t="n">
-        <v>30</v>
-      </c>
-      <c r="F83" s="10" t="inlineStr">
-        <is>
-          <t>sector=Healthcare, size=micro, drawdow</t>
-        </is>
-      </c>
-    </row>
-    <row r="84" ht="22" customHeight="1">
-      <c r="A84" s="6" t="inlineStr">
-        <is>
-          <t>FWDI</t>
-        </is>
-      </c>
-      <c r="B84" s="7" t="inlineStr">
-        <is>
-          <t>Forward Industries,</t>
-        </is>
-      </c>
-      <c r="C84" s="16" t="n">
-        <v>19</v>
-      </c>
-      <c r="D84" s="7" t="inlineStr">
-        <is>
-          <t>CONFIRMED</t>
-        </is>
-      </c>
-      <c r="E84" s="16" t="n">
-        <v>12.9</v>
-      </c>
-      <c r="F84" s="7" t="inlineStr">
-        <is>
-          <t>catalyst=SALE_OF_COMPANY, drawdown_12m</t>
-        </is>
-      </c>
-    </row>
-    <row r="85" ht="22" customHeight="1">
-      <c r="A85" s="9" t="inlineStr">
-        <is>
-          <t>LAB</t>
-        </is>
-      </c>
-      <c r="B85" s="10" t="inlineStr">
-        <is>
-          <t>Standard BioTools In</t>
-        </is>
-      </c>
-      <c r="C85" s="17" t="n">
-        <v>19</v>
-      </c>
-      <c r="D85" s="10" t="inlineStr">
-        <is>
-          <t>NEUTRAL</t>
-        </is>
-      </c>
-      <c r="E85" s="17" t="n">
-        <v>42.3</v>
-      </c>
-      <c r="F85" s="10" t="inlineStr">
-        <is>
-          <t>catalyst=ASSET_SALE, sector=Healthcare</t>
-        </is>
-      </c>
-    </row>
-    <row r="86" ht="22" customHeight="1">
-      <c r="A86" s="6" t="inlineStr">
-        <is>
-          <t>PRGO</t>
-        </is>
-      </c>
-      <c r="B86" s="7" t="inlineStr">
-        <is>
-          <t>Perrigo Company plc</t>
-        </is>
-      </c>
-      <c r="C86" s="16" t="n">
-        <v>19</v>
-      </c>
-      <c r="D86" s="7" t="inlineStr">
-        <is>
-          <t>CONFIRMED</t>
-        </is>
-      </c>
-      <c r="E86" s="16" t="n">
-        <v>25.6</v>
-      </c>
-      <c r="F86" s="7" t="inlineStr">
-        <is>
-          <t>catalyst=ASSET_SALE, sector=Healthcare</t>
-        </is>
-      </c>
-    </row>
-    <row r="87" ht="22" customHeight="1">
-      <c r="A87" s="9" t="inlineStr">
-        <is>
-          <t>CERT</t>
-        </is>
-      </c>
-      <c r="B87" s="10" t="inlineStr">
-        <is>
-          <t>Certara, Inc.</t>
-        </is>
-      </c>
-      <c r="C87" s="17" t="n">
-        <v>19</v>
-      </c>
-      <c r="D87" s="10" t="inlineStr">
-        <is>
-          <t>CONFIRMED</t>
-        </is>
-      </c>
-      <c r="E87" s="17" t="n">
-        <v>10.7</v>
-      </c>
-      <c r="F87" s="10" t="inlineStr">
-        <is>
-          <t>catalyst=ASSET_SALE, sector=Healthcare</t>
-        </is>
-      </c>
-    </row>
-    <row r="88" ht="22" customHeight="1">
-      <c r="A88" s="6" t="inlineStr">
-        <is>
-          <t>FIS</t>
-        </is>
-      </c>
-      <c r="B88" s="7" t="inlineStr">
-        <is>
-          <t>Fidelity National In</t>
-        </is>
-      </c>
-      <c r="C88" s="16" t="n">
-        <v>19</v>
-      </c>
-      <c r="D88" s="7" t="inlineStr">
-        <is>
-          <t>FADING</t>
-        </is>
-      </c>
-      <c r="E88" s="16" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="F88" s="7" t="inlineStr">
-        <is>
-          <t>catalyst=SPINOFF, sector=Technology, d</t>
-        </is>
-      </c>
-    </row>
-    <row r="90">
-      <c r="A90" s="12" t="inlineStr">
-        <is>
-          <t>WHAT RAISES TAIL ODDS (historical lift vs 10% base)</t>
-        </is>
-      </c>
-    </row>
-    <row r="91" ht="18" customHeight="1">
-      <c r="A91" s="4" t="inlineStr">
-        <is>
-          <t>Feature = bin</t>
-        </is>
-      </c>
-      <c r="B91" s="4" t="inlineStr">
-        <is>
-          <t>Tail rate</t>
-        </is>
-      </c>
-      <c r="C91" s="4" t="inlineStr">
-        <is>
-          <t>Lift</t>
-        </is>
-      </c>
-      <c r="D91" s="4" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="E91" s="15" t="inlineStr"/>
+      <c r="C91" s="7" t="inlineStr">
+        <is>
+          <t>2.53x</t>
+        </is>
+      </c>
+      <c r="D91" s="5" t="n">
+        <v>8</v>
+      </c>
+      <c r="E91" s="7" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
     </row>
     <row r="92" ht="16" customHeight="1">
       <c r="A92" s="9" t="inlineStr">
         <is>
-          <t>catalyst = SALE_OF_COMPANY</t>
+          <t>sector = Basic Materials</t>
         </is>
       </c>
       <c r="B92" s="17" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="C92" s="10" t="inlineStr">
         <is>
-          <t>2.53x</t>
+          <t>2.34x</t>
         </is>
       </c>
       <c r="D92" s="8" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="E92" s="10" t="inlineStr">
         <is>
@@ -10993,19 +10931,19 @@
     <row r="93" ht="16" customHeight="1">
       <c r="A93" s="6" t="inlineStr">
         <is>
-          <t>sector = Basic Materials</t>
+          <t>drawdown_12m = deep(&lt;-50%)</t>
         </is>
       </c>
       <c r="B93" s="16" t="n">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="C93" s="7" t="inlineStr">
         <is>
-          <t>2.34x</t>
+          <t>1.92x</t>
         </is>
       </c>
       <c r="D93" s="5" t="n">
-        <v>13</v>
+        <v>37</v>
       </c>
       <c r="E93" s="7" t="inlineStr">
         <is>
@@ -11016,7 +10954,7 @@
     <row r="94" ht="16" customHeight="1">
       <c r="A94" s="9" t="inlineStr">
         <is>
-          <t>drawdown_12m = deep(&lt;-50%)</t>
+          <t>sector = Healthcare</t>
         </is>
       </c>
       <c r="B94" s="17" t="n">
@@ -11024,11 +10962,11 @@
       </c>
       <c r="C94" s="10" t="inlineStr">
         <is>
-          <t>1.92x</t>
+          <t>1.95x</t>
         </is>
       </c>
       <c r="D94" s="8" t="n">
-        <v>37</v>
+        <v>26</v>
       </c>
       <c r="E94" s="10" t="inlineStr">
         <is>
@@ -11039,19 +10977,19 @@
     <row r="95" ht="16" customHeight="1">
       <c r="A95" s="6" t="inlineStr">
         <is>
-          <t>sector = Healthcare</t>
+          <t>catalyst = STRATEGIC_REVIEW</t>
         </is>
       </c>
       <c r="B95" s="16" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="C95" s="7" t="inlineStr">
         <is>
-          <t>1.95x</t>
+          <t>1.62x</t>
         </is>
       </c>
       <c r="D95" s="5" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E95" s="7" t="inlineStr">
         <is>
@@ -11062,19 +11000,19 @@
     <row r="96" ht="16" customHeight="1">
       <c r="A96" s="9" t="inlineStr">
         <is>
-          <t>catalyst = STRATEGIC_REVIEW</t>
+          <t>catalyst = SPINOFF</t>
         </is>
       </c>
       <c r="B96" s="17" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C96" s="10" t="inlineStr">
         <is>
-          <t>1.62x</t>
+          <t>1.56x</t>
         </is>
       </c>
       <c r="D96" s="8" t="n">
-        <v>25</v>
+        <v>39</v>
       </c>
       <c r="E96" s="10" t="inlineStr">
         <is>
@@ -11085,7 +11023,7 @@
     <row r="97" ht="16" customHeight="1">
       <c r="A97" s="6" t="inlineStr">
         <is>
-          <t>catalyst = SPINOFF</t>
+          <t>sector = Technology</t>
         </is>
       </c>
       <c r="B97" s="16" t="n">
@@ -11093,11 +11031,11 @@
       </c>
       <c r="C97" s="7" t="inlineStr">
         <is>
-          <t>1.56x</t>
+          <t>1.50x</t>
         </is>
       </c>
       <c r="D97" s="5" t="n">
-        <v>39</v>
+        <v>27</v>
       </c>
       <c r="E97" s="7" t="inlineStr">
         <is>
@@ -11108,19 +11046,19 @@
     <row r="98" ht="16" customHeight="1">
       <c r="A98" s="9" t="inlineStr">
         <is>
-          <t>sector = Technology</t>
+          <t>range_pos = low</t>
         </is>
       </c>
       <c r="B98" s="17" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C98" s="10" t="inlineStr">
         <is>
-          <t>1.50x</t>
+          <t>1.24x</t>
         </is>
       </c>
       <c r="D98" s="8" t="n">
-        <v>27</v>
+        <v>106</v>
       </c>
       <c r="E98" s="10" t="inlineStr">
         <is>
@@ -11131,7 +11069,7 @@
     <row r="99" ht="16" customHeight="1">
       <c r="A99" s="6" t="inlineStr">
         <is>
-          <t>range_pos = low</t>
+          <t>size = micro</t>
         </is>
       </c>
       <c r="B99" s="16" t="n">
@@ -11139,11 +11077,11 @@
       </c>
       <c r="C99" s="7" t="inlineStr">
         <is>
-          <t>1.24x</t>
+          <t>1.27x</t>
         </is>
       </c>
       <c r="D99" s="5" t="n">
-        <v>106</v>
+        <v>24</v>
       </c>
       <c r="E99" s="7" t="inlineStr">
         <is>
@@ -11154,19 +11092,19 @@
     <row r="100" ht="16" customHeight="1">
       <c r="A100" s="9" t="inlineStr">
         <is>
-          <t>size = micro</t>
+          <t>catalyst = ASSET_SALE</t>
         </is>
       </c>
       <c r="B100" s="17" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C100" s="10" t="inlineStr">
         <is>
-          <t>1.27x</t>
+          <t>1.13x</t>
         </is>
       </c>
       <c r="D100" s="8" t="n">
-        <v>24</v>
+        <v>36</v>
       </c>
       <c r="E100" s="10" t="inlineStr">
         <is>
@@ -11177,19 +11115,19 @@
     <row r="101" ht="16" customHeight="1">
       <c r="A101" s="6" t="inlineStr">
         <is>
-          <t>catalyst = ASSET_SALE</t>
+          <t>pre_12m = down(&lt;-20%)  (needs a wait)</t>
         </is>
       </c>
       <c r="B101" s="16" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="C101" s="7" t="inlineStr">
         <is>
-          <t>1.13x</t>
+          <t>1.46x</t>
         </is>
       </c>
       <c r="D101" s="5" t="n">
-        <v>36</v>
+        <v>83</v>
       </c>
       <c r="E101" s="7" t="inlineStr">
         <is>
@@ -11200,19 +11138,19 @@
     <row r="102" ht="16" customHeight="1">
       <c r="A102" s="9" t="inlineStr">
         <is>
-          <t>pre_12m = down(&lt;-20%)  (needs a wait)</t>
+          <t>post_1m = up(&gt;+20%)  (needs a wait)</t>
         </is>
       </c>
       <c r="B102" s="17" t="n">
-        <v>14</v>
+        <v>33</v>
       </c>
       <c r="C102" s="10" t="inlineStr">
         <is>
-          <t>1.46x</t>
+          <t>3.38x</t>
         </is>
       </c>
       <c r="D102" s="8" t="n">
-        <v>83</v>
+        <v>21</v>
       </c>
       <c r="E102" s="10" t="inlineStr">
         <is>
@@ -11220,31 +11158,8 @@
         </is>
       </c>
     </row>
-    <row r="103" ht="16" customHeight="1">
-      <c r="A103" s="6" t="inlineStr">
-        <is>
-          <t>post_1m = up(&gt;+20%)  (needs a wait)</t>
-        </is>
-      </c>
-      <c r="B103" s="16" t="n">
-        <v>33</v>
-      </c>
-      <c r="C103" s="7" t="inlineStr">
-        <is>
-          <t>3.38x</t>
-        </is>
-      </c>
-      <c r="D103" s="5" t="n">
-        <v>21</v>
-      </c>
-      <c r="E103" s="7" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-    </row>
-    <row r="105" ht="28" customHeight="1">
-      <c r="A105" s="11" t="inlineStr">
+    <row r="104" ht="28" customHeight="1">
+      <c r="A104" s="11" t="inlineStr">
         <is>
           <t>HOW TO RAISE THE ODDS, from the 12-type event study (314 events, 10% base tail rate). The right tail concentrates in (1) DEEPLY BEATEN-DOWN names — &gt;50% below their 12-month high tailed 19% vs 7% for names near their highs (1.9x); (2) the right SECTORS — Basic Materials (2.3x), Healthcare (1.9x), Communication Services (1.7x), Technology (1.5x) — while Utilities and Real Estate produced ZERO tails and Financials few; (3) micro/mid-caps over large; (4) the right CATALYSTS — SALE-OF-COMPANY (2.5x, contested-deal tail), STRATEGIC-REVIEW (1.6x lottery) and SPIN-OFF (1.6x); ASSET-SALE has the best MEDIAN (+10%, 58% hit). The backtest also exposed TRAPS to fade: going-private (-37% median), uplisting (-23%, pump-and-fade), capital-return/special-dividend (-11%), exchange-offer (-21%) — all down-weighted in the catalyst engine. THE SINGLE STRONGEST EDGE is not a screen but a RULE: wait ~1 month and enter only names the market voted UP &gt;20% on the catalyst (the Confirmed shortlist above). Buying a catalyst blind loses to SPY on the median (overall -4%); buying beaten-down names in the right sectors AFTER the market confirms is how you tilt into the tail. Directional (n per type 8-51). Sources: rerate_backtest.py / tail_discriminators.py / tail_odds.py.</t>
         </is>
@@ -11253,8 +11168,8 @@
   </sheetData>
   <mergeCells count="3">
     <mergeCell ref="A2:F2"/>
-    <mergeCell ref="A105:F105"/>
     <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A104:F104"/>
   </mergeCells>
   <printOptions horizontalCentered="0"/>
   <pageMargins left="0.5" right="0.5" top="0.6" bottom="0.6" header="0.5" footer="0.5"/>

--- a/MOST_ASYMMETRIC.xlsx
+++ b/MOST_ASYMMETRIC.xlsx
@@ -19,22 +19,23 @@
     <sheet name="MD&amp;A Intent" sheetId="10" state="visible" r:id="rId10"/>
     <sheet name="Payoff Geometry" sheetId="11" state="visible" r:id="rId11"/>
     <sheet name="Mechanism Gates" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet name="Re-Rate Catalysts" sheetId="13" state="visible" r:id="rId13"/>
-    <sheet name="Re-Rate Backtest" sheetId="14" state="visible" r:id="rId14"/>
-    <sheet name="Tail Odds" sheetId="15" state="visible" r:id="rId15"/>
-    <sheet name="Winners Study" sheetId="16" state="visible" r:id="rId16"/>
-    <sheet name="Asymmetry Assembly" sheetId="17" state="visible" r:id="rId17"/>
-    <sheet name="Distressed Stub Progress" sheetId="18" state="visible" r:id="rId18"/>
-    <sheet name="Hidden Asset Realisation" sheetId="19" state="visible" r:id="rId19"/>
-    <sheet name="UK Capital Events" sheetId="20" state="visible" r:id="rId20"/>
-    <sheet name="Without Valuation" sheetId="21" state="visible" r:id="rId21"/>
-    <sheet name="Recent 30d" sheetId="22" state="visible" r:id="rId22"/>
-    <sheet name="Foreign Markets" sheetId="23" state="visible" r:id="rId23"/>
-    <sheet name="Turnaround Signal" sheetId="24" state="visible" r:id="rId24"/>
-    <sheet name="Single-Measure Best" sheetId="25" state="visible" r:id="rId25"/>
-    <sheet name="Layer Correlation" sheetId="26" state="visible" r:id="rId26"/>
-    <sheet name="Coverage &amp; Tiers" sheetId="27" state="visible" r:id="rId27"/>
-    <sheet name="Methodology" sheetId="28" state="visible" r:id="rId28"/>
+    <sheet name="Structured Distressed" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet name="Re-Rate Catalysts" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet name="Re-Rate Backtest" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet name="Tail Odds" sheetId="16" state="visible" r:id="rId16"/>
+    <sheet name="Winners Study" sheetId="17" state="visible" r:id="rId17"/>
+    <sheet name="Asymmetry Assembly" sheetId="18" state="visible" r:id="rId18"/>
+    <sheet name="Distressed Stub Progress" sheetId="19" state="visible" r:id="rId19"/>
+    <sheet name="Hidden Asset Realisation" sheetId="20" state="visible" r:id="rId20"/>
+    <sheet name="UK Capital Events" sheetId="21" state="visible" r:id="rId21"/>
+    <sheet name="Without Valuation" sheetId="22" state="visible" r:id="rId22"/>
+    <sheet name="Recent 30d" sheetId="23" state="visible" r:id="rId23"/>
+    <sheet name="Foreign Markets" sheetId="24" state="visible" r:id="rId24"/>
+    <sheet name="Turnaround Signal" sheetId="25" state="visible" r:id="rId25"/>
+    <sheet name="Single-Measure Best" sheetId="26" state="visible" r:id="rId26"/>
+    <sheet name="Layer Correlation" sheetId="27" state="visible" r:id="rId27"/>
+    <sheet name="Coverage &amp; Tiers" sheetId="28" state="visible" r:id="rId28"/>
+    <sheet name="Methodology" sheetId="29" state="visible" r:id="rId29"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Titles" localSheetId="0">'Contents'!$1:$4</definedName>
@@ -49,22 +50,23 @@
     <definedName name="_xlnm.Print_Titles" localSheetId="9">'MD&amp;A Intent'!$1:$4</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="10">'Payoff Geometry'!$1:$4</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="11">'Mechanism Gates'!$1:$4</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="12">'Re-Rate Catalysts'!$1:$4</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="13">'Re-Rate Backtest'!$1:$4</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="14">'Tail Odds'!$1:$4</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="15">'Winners Study'!$1:$4</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="16">'Asymmetry Assembly'!$1:$4</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="17">'Distressed Stub Progress'!$1:$4</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="18">'Hidden Asset Realisation'!$1:$4</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="19">'UK Capital Events'!$1:$4</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="20">'Without Valuation'!$1:$4</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="21">'Recent 30d'!$1:$4</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="22">'Foreign Markets'!$1:$4</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="23">'Turnaround Signal'!$1:$4</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="24">'Single-Measure Best'!$1:$4</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="25">'Layer Correlation'!$1:$4</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="26">'Coverage &amp; Tiers'!$1:$4</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="27">'Methodology'!$1:$4</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="12">'Structured Distressed'!$1:$4</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="13">'Re-Rate Catalysts'!$1:$4</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="14">'Re-Rate Backtest'!$1:$4</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="15">'Tail Odds'!$1:$4</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="16">'Winners Study'!$1:$4</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="17">'Asymmetry Assembly'!$1:$4</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="18">'Distressed Stub Progress'!$1:$4</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="19">'Hidden Asset Realisation'!$1:$4</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="20">'UK Capital Events'!$1:$4</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="21">'Without Valuation'!$1:$4</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="22">'Recent 30d'!$1:$4</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="23">'Foreign Markets'!$1:$4</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="24">'Turnaround Signal'!$1:$4</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="25">'Single-Measure Best'!$1:$4</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="26">'Layer Correlation'!$1:$4</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="27">'Coverage &amp; Tiers'!$1:$4</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="28">'Methodology'!$1:$4</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -604,7 +606,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:C33"/>
+  <dimension ref="A1:C34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -817,12 +819,12 @@
       </c>
       <c r="B16" s="9" t="inlineStr">
         <is>
-          <t>Re-Rate Catalysts</t>
+          <t>Structured Distressed</t>
         </is>
       </c>
       <c r="C16" s="10" t="inlineStr">
         <is>
-          <t>Spin-offs / separations / asset sales / sale-of-company / strategic reviews x geometry room.</t>
+          <t>Cundill/Sibir: asset-backed washouts raising via senior/convertible instruments (own the instrument).</t>
         </is>
       </c>
     </row>
@@ -832,12 +834,12 @@
       </c>
       <c r="B17" s="6" t="inlineStr">
         <is>
-          <t>Re-Rate Backtest</t>
+          <t>Re-Rate Catalysts</t>
         </is>
       </c>
       <c r="C17" s="7" t="inlineStr">
         <is>
-          <t>What those catalysts actually returned historically — the evidence behind the weights.</t>
+          <t>Spin-offs / separations / asset sales / sale-of-company / strategic reviews x geometry room.</t>
         </is>
       </c>
     </row>
@@ -847,12 +849,12 @@
       </c>
       <c r="B18" s="9" t="inlineStr">
         <is>
-          <t>Tail Odds</t>
+          <t>Re-Rate Backtest</t>
         </is>
       </c>
       <c r="C18" s="10" t="inlineStr">
         <is>
-          <t>Candidates ranked by measured probability of a right-tail outcome; the features that raise the odds.</t>
+          <t>What those catalysts actually returned historically — the evidence behind the weights.</t>
         </is>
       </c>
     </row>
@@ -862,12 +864,12 @@
       </c>
       <c r="B19" s="6" t="inlineStr">
         <is>
-          <t>Winners Study</t>
+          <t>Tail Odds</t>
         </is>
       </c>
       <c r="C19" s="7" t="inlineStr">
         <is>
-          <t>What realized 1-year re-raters had in common — feature/sector lifts, with the pre-move-data caveat.</t>
+          <t>Candidates ranked by measured probability of a right-tail outcome; the features that raise the odds.</t>
         </is>
       </c>
     </row>
@@ -877,12 +879,12 @@
       </c>
       <c r="B20" s="9" t="inlineStr">
         <is>
-          <t>Asymmetry Assembly</t>
+          <t>Winners Study</t>
         </is>
       </c>
       <c r="C20" s="10" t="inlineStr">
         <is>
-          <t>PSIX-recipe conjunction: cheap + inflection + leverage + insider co-occurring.</t>
+          <t>What realized 1-year re-raters had in common — feature/sector lifts, with the pre-move-data caveat.</t>
         </is>
       </c>
     </row>
@@ -892,12 +894,12 @@
       </c>
       <c r="B21" s="6" t="inlineStr">
         <is>
-          <t>Distressed Stub Progress</t>
+          <t>Asymmetry Assembly</t>
         </is>
       </c>
       <c r="C21" s="7" t="inlineStr">
         <is>
-          <t>Finality-gated capital-structure value-unlock events, waterfall-scored.</t>
+          <t>PSIX-recipe conjunction: cheap + inflection + leverage + insider co-occurring.</t>
         </is>
       </c>
     </row>
@@ -907,12 +909,12 @@
       </c>
       <c r="B22" s="9" t="inlineStr">
         <is>
-          <t>Hidden Asset Realisation</t>
+          <t>Distressed Stub Progress</t>
         </is>
       </c>
       <c r="C22" s="10" t="inlineStr">
         <is>
-          <t>Spectrum/rights/RE inside levered stubs with mandatory-prepay debt sweeps (SSP-type).</t>
+          <t>Finality-gated capital-structure value-unlock events, waterfall-scored.</t>
         </is>
       </c>
     </row>
@@ -922,12 +924,12 @@
       </c>
       <c r="B23" s="6" t="inlineStr">
         <is>
-          <t>UK Capital Events</t>
+          <t>Hidden Asset Realisation</t>
         </is>
       </c>
       <c r="C23" s="7" t="inlineStr">
         <is>
-          <t>UK RNS revealed-preference &amp; distressed monitor (separate universe; funds filtered).</t>
+          <t>Spectrum/rights/RE inside levered stubs with mandatory-prepay debt sweeps (SSP-type).</t>
         </is>
       </c>
     </row>
@@ -937,12 +939,12 @@
       </c>
       <c r="B24" s="9" t="inlineStr">
         <is>
-          <t>Without Valuation</t>
+          <t>UK Capital Events</t>
         </is>
       </c>
       <c r="C24" s="10" t="inlineStr">
         <is>
-          <t>Parallel ranking excluding the valuation leg.</t>
+          <t>UK RNS revealed-preference &amp; distressed monitor (separate universe; funds filtered).</t>
         </is>
       </c>
     </row>
@@ -952,12 +954,12 @@
       </c>
       <c r="B25" s="6" t="inlineStr">
         <is>
-          <t>Recent 30d</t>
+          <t>Without Valuation</t>
         </is>
       </c>
       <c r="C25" s="7" t="inlineStr">
         <is>
-          <t>Material incentive events disclosed in the last 30 days.</t>
+          <t>Parallel ranking excluding the valuation leg.</t>
         </is>
       </c>
     </row>
@@ -967,12 +969,12 @@
       </c>
       <c r="B26" s="9" t="inlineStr">
         <is>
-          <t>Foreign Markets</t>
+          <t>Recent 30d</t>
         </is>
       </c>
       <c r="C26" s="10" t="inlineStr">
         <is>
-          <t>Japan TSE PBR&lt;1, Korea Value-Up, UK schemes.</t>
+          <t>Material incentive events disclosed in the last 30 days.</t>
         </is>
       </c>
     </row>
@@ -982,12 +984,12 @@
       </c>
       <c r="B27" s="6" t="inlineStr">
         <is>
-          <t>Turnaround Signal</t>
+          <t>Foreign Markets</t>
         </is>
       </c>
       <c r="C27" s="7" t="inlineStr">
         <is>
-          <t>Bollenbach pattern: turnaround talent into distress.</t>
+          <t>Japan TSE PBR&lt;1, Korea Value-Up, UK schemes.</t>
         </is>
       </c>
     </row>
@@ -997,12 +999,12 @@
       </c>
       <c r="B28" s="9" t="inlineStr">
         <is>
-          <t>Single-Measure Best</t>
+          <t>Turnaround Signal</t>
         </is>
       </c>
       <c r="C28" s="10" t="inlineStr">
         <is>
-          <t>Best in class on each individual signal.</t>
+          <t>Bollenbach pattern: turnaround talent into distress.</t>
         </is>
       </c>
     </row>
@@ -1012,12 +1014,12 @@
       </c>
       <c r="B29" s="6" t="inlineStr">
         <is>
-          <t>Layer Correlation</t>
+          <t>Single-Measure Best</t>
         </is>
       </c>
       <c r="C29" s="7" t="inlineStr">
         <is>
-          <t>Pairwise layer correlation and effective independence.</t>
+          <t>Best in class on each individual signal.</t>
         </is>
       </c>
     </row>
@@ -1027,12 +1029,12 @@
       </c>
       <c r="B30" s="9" t="inlineStr">
         <is>
-          <t>Coverage &amp; Tiers</t>
+          <t>Layer Correlation</t>
         </is>
       </c>
       <c r="C30" s="10" t="inlineStr">
         <is>
-          <t>Live per-layer coverage, data age, firing distribution.</t>
+          <t>Pairwise layer correlation and effective independence.</t>
         </is>
       </c>
     </row>
@@ -1042,17 +1044,32 @@
       </c>
       <c r="B31" s="6" t="inlineStr">
         <is>
+          <t>Coverage &amp; Tiers</t>
+        </is>
+      </c>
+      <c r="C31" s="7" t="inlineStr">
+        <is>
+          <t>Live per-layer coverage, data age, firing distribution.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="16" customHeight="1">
+      <c r="A32" s="8" t="n">
+        <v>28</v>
+      </c>
+      <c r="B32" s="9" t="inlineStr">
+        <is>
           <t>Methodology</t>
         </is>
       </c>
-      <c r="C31" s="7" t="inlineStr">
+      <c r="C32" s="10" t="inlineStr">
         <is>
           <t>How the composite is built, step by step.</t>
         </is>
       </c>
     </row>
-    <row r="33" ht="28" customHeight="1">
-      <c r="A33" s="11" t="inlineStr">
+    <row r="34" ht="28" customHeight="1">
+      <c r="A34" s="11" t="inlineStr">
         <is>
           <t>Generated by build_most_asymmetric_xlsx.py from the live consensus on disk. Every figure in this workbook is computed at build time; nothing is hardcoded. Single typeface (Times New Roman, 10pt); hierarchy by weight and rule only.</t>
         </is>
@@ -1061,8 +1078,8 @@
   </sheetData>
   <mergeCells count="3">
     <mergeCell ref="A1:C1"/>
-    <mergeCell ref="A33:C33"/>
     <mergeCell ref="A2:C2"/>
+    <mergeCell ref="A34:C34"/>
   </mergeCells>
   <printOptions horizontalCentered="0"/>
   <pageMargins left="0.5" right="0.5" top="0.6" bottom="0.6" header="0.5" footer="0.5"/>
@@ -5131,38 +5148,38 @@
     <row r="10" ht="22" customHeight="1">
       <c r="A10" s="9" t="inlineStr">
         <is>
-          <t>LUCY</t>
+          <t>DFH</t>
         </is>
       </c>
       <c r="B10" s="10" t="inlineStr">
         <is>
-          <t>Innovative Eyewear, In</t>
+          <t>Dream Finders Homes, I</t>
         </is>
       </c>
       <c r="C10" s="17" t="n">
-        <v>40</v>
+        <v>40.2</v>
       </c>
       <c r="D10" s="17" t="n">
         <v>2</v>
       </c>
       <c r="E10" s="17" t="n">
-        <v>45.6</v>
+        <v>2.5</v>
       </c>
       <c r="F10" s="10" t="inlineStr">
         <is>
-          <t>sub cash buyback, tender target latent</t>
+          <t>hidden asset realization, structured distresse</t>
         </is>
       </c>
     </row>
     <row r="11" ht="22" customHeight="1">
       <c r="A11" s="6" t="inlineStr">
         <is>
-          <t>PMCB</t>
+          <t>LUCY</t>
         </is>
       </c>
       <c r="B11" s="7" t="inlineStr">
         <is>
-          <t>PharmaCyte  Biotech, I</t>
+          <t>Innovative Eyewear, In</t>
         </is>
       </c>
       <c r="C11" s="16" t="n">
@@ -5172,7 +5189,7 @@
         <v>2</v>
       </c>
       <c r="E11" s="16" t="n">
-        <v>30</v>
+        <v>45.6</v>
       </c>
       <c r="F11" s="7" t="inlineStr">
         <is>
@@ -5183,12 +5200,12 @@
     <row r="12" ht="22" customHeight="1">
       <c r="A12" s="9" t="inlineStr">
         <is>
-          <t>ACH</t>
+          <t>PMCB</t>
         </is>
       </c>
       <c r="B12" s="10" t="inlineStr">
         <is>
-          <t>Accendra Health, Inc.</t>
+          <t>PharmaCyte  Biotech, I</t>
         </is>
       </c>
       <c r="C12" s="17" t="n">
@@ -5198,7 +5215,7 @@
         <v>2</v>
       </c>
       <c r="E12" s="17" t="n">
-        <v>60</v>
+        <v>30</v>
       </c>
       <c r="F12" s="10" t="inlineStr">
         <is>
@@ -5209,100 +5226,100 @@
     <row r="13" ht="22" customHeight="1">
       <c r="A13" s="6" t="inlineStr">
         <is>
-          <t>SHEN</t>
+          <t>ACH</t>
         </is>
       </c>
       <c r="B13" s="7" t="inlineStr">
         <is>
-          <t>Shenandoah Telecommuni</t>
+          <t>Accendra Health, Inc.</t>
         </is>
       </c>
       <c r="C13" s="16" t="n">
-        <v>38.3</v>
+        <v>40</v>
       </c>
       <c r="D13" s="16" t="n">
         <v>2</v>
       </c>
       <c r="E13" s="16" t="n">
-        <v>19.5</v>
+        <v>60</v>
       </c>
       <c r="F13" s="7" t="inlineStr">
         <is>
-          <t>hidden asset realization, asset sale latent</t>
+          <t>sub cash buyback, tender target latent</t>
         </is>
       </c>
     </row>
     <row r="14" ht="22" customHeight="1">
       <c r="A14" s="9" t="inlineStr">
         <is>
-          <t>PRTA</t>
+          <t>SHEN</t>
         </is>
       </c>
       <c r="B14" s="10" t="inlineStr">
         <is>
-          <t>Prothena Corporation p</t>
+          <t>Shenandoah Telecommuni</t>
         </is>
       </c>
       <c r="C14" s="17" t="n">
-        <v>37.8</v>
+        <v>38.3</v>
       </c>
       <c r="D14" s="17" t="n">
         <v>2</v>
       </c>
       <c r="E14" s="17" t="n">
-        <v>3.3</v>
+        <v>19.5</v>
       </c>
       <c r="F14" s="10" t="inlineStr">
         <is>
-          <t>sub cash buyback, tender target latent</t>
+          <t>hidden asset realization, asset sale latent</t>
         </is>
       </c>
     </row>
     <row r="15" ht="22" customHeight="1">
       <c r="A15" s="6" t="inlineStr">
         <is>
-          <t>GTE</t>
+          <t>PRTA</t>
         </is>
       </c>
       <c r="B15" s="7" t="inlineStr">
         <is>
-          <t>Gran Tierra Energy Inc</t>
+          <t>Prothena Corporation p</t>
         </is>
       </c>
       <c r="C15" s="16" t="n">
-        <v>35.8</v>
+        <v>37.8</v>
       </c>
       <c r="D15" s="16" t="n">
         <v>2</v>
       </c>
       <c r="E15" s="16" t="n">
-        <v>3.8</v>
+        <v>3.3</v>
       </c>
       <c r="F15" s="7" t="inlineStr">
         <is>
-          <t>asset sale monetization, tender offer squeeze</t>
+          <t>sub cash buyback, tender target latent</t>
         </is>
       </c>
     </row>
     <row r="16" ht="22" customHeight="1">
       <c r="A16" s="9" t="inlineStr">
         <is>
-          <t>CYH</t>
+          <t>GTE</t>
         </is>
       </c>
       <c r="B16" s="10" t="inlineStr">
         <is>
-          <t>Community Health Syste</t>
+          <t>Gran Tierra Energy Inc</t>
         </is>
       </c>
       <c r="C16" s="17" t="n">
-        <v>35.2</v>
+        <v>35.8</v>
       </c>
       <c r="D16" s="17" t="n">
         <v>2</v>
       </c>
       <c r="E16" s="17" t="n">
-        <v>3</v>
+        <v>3.8</v>
       </c>
       <c r="F16" s="10" t="inlineStr">
         <is>
@@ -5313,38 +5330,38 @@
     <row r="17" ht="22" customHeight="1">
       <c r="A17" s="6" t="inlineStr">
         <is>
-          <t>FWRD</t>
+          <t>CYH</t>
         </is>
       </c>
       <c r="B17" s="7" t="inlineStr">
         <is>
-          <t>Forward Air Corporatio</t>
+          <t>Community Health Syste</t>
         </is>
       </c>
       <c r="C17" s="16" t="n">
-        <v>33.5</v>
+        <v>35.2</v>
       </c>
       <c r="D17" s="16" t="n">
         <v>2</v>
       </c>
       <c r="E17" s="16" t="n">
-        <v>3.3</v>
+        <v>3</v>
       </c>
       <c r="F17" s="7" t="inlineStr">
         <is>
-          <t>coiled spring delever, asset sale latent</t>
+          <t>asset sale monetization, tender offer squeeze</t>
         </is>
       </c>
     </row>
     <row r="18" ht="22" customHeight="1">
       <c r="A18" s="9" t="inlineStr">
         <is>
-          <t>BVS</t>
+          <t>FWRD</t>
         </is>
       </c>
       <c r="B18" s="10" t="inlineStr">
         <is>
-          <t>Bioventus Inc.</t>
+          <t>Forward Air Corporatio</t>
         </is>
       </c>
       <c r="C18" s="17" t="n">
@@ -5365,38 +5382,38 @@
     <row r="19" ht="22" customHeight="1">
       <c r="A19" s="6" t="inlineStr">
         <is>
-          <t>DXC</t>
+          <t>BVS</t>
         </is>
       </c>
       <c r="B19" s="7" t="inlineStr">
         <is>
-          <t>DXC Technology Company</t>
+          <t>Bioventus Inc.</t>
         </is>
       </c>
       <c r="C19" s="16" t="n">
-        <v>22</v>
+        <v>33.5</v>
       </c>
       <c r="D19" s="16" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E19" s="16" t="n">
-        <v>30</v>
+        <v>3.3</v>
       </c>
       <c r="F19" s="7" t="inlineStr">
         <is>
-          <t>sub cash buyback</t>
+          <t>coiled spring delever, asset sale latent</t>
         </is>
       </c>
     </row>
     <row r="20" ht="22" customHeight="1">
       <c r="A20" s="9" t="inlineStr">
         <is>
-          <t>VISN</t>
+          <t>DXC</t>
         </is>
       </c>
       <c r="B20" s="10" t="inlineStr">
         <is>
-          <t>Vistance Networks, Inc</t>
+          <t>DXC Technology Company</t>
         </is>
       </c>
       <c r="C20" s="17" t="n">
@@ -5406,7 +5423,7 @@
         <v>1</v>
       </c>
       <c r="E20" s="17" t="n">
-        <v>24.8</v>
+        <v>30</v>
       </c>
       <c r="F20" s="10" t="inlineStr">
         <is>
@@ -5417,22 +5434,22 @@
     <row r="21" ht="22" customHeight="1">
       <c r="A21" s="6" t="inlineStr">
         <is>
-          <t>ADNT</t>
+          <t>VISN</t>
         </is>
       </c>
       <c r="B21" s="7" t="inlineStr">
         <is>
-          <t>Adient plc</t>
+          <t>Vistance Networks, Inc</t>
         </is>
       </c>
       <c r="C21" s="16" t="n">
-        <v>20.7</v>
+        <v>22</v>
       </c>
       <c r="D21" s="16" t="n">
         <v>1</v>
       </c>
       <c r="E21" s="16" t="n">
-        <v>6.3</v>
+        <v>24.8</v>
       </c>
       <c r="F21" s="7" t="inlineStr">
         <is>
@@ -5443,38 +5460,38 @@
     <row r="22" ht="22" customHeight="1">
       <c r="A22" s="9" t="inlineStr">
         <is>
-          <t>GETY</t>
+          <t>ADNT</t>
         </is>
       </c>
       <c r="B22" s="10" t="inlineStr">
         <is>
-          <t>Getty Images Holdings,</t>
+          <t>Adient plc</t>
         </is>
       </c>
       <c r="C22" s="17" t="n">
-        <v>20</v>
+        <v>20.7</v>
       </c>
       <c r="D22" s="17" t="n">
         <v>1</v>
       </c>
       <c r="E22" s="17" t="n">
-        <v>60</v>
+        <v>6.3</v>
       </c>
       <c r="F22" s="10" t="inlineStr">
         <is>
-          <t>coiled spring delever</t>
+          <t>sub cash buyback</t>
         </is>
       </c>
     </row>
     <row r="23" ht="22" customHeight="1">
       <c r="A23" s="6" t="inlineStr">
         <is>
-          <t>CLVT</t>
+          <t>GETY</t>
         </is>
       </c>
       <c r="B23" s="7" t="inlineStr">
         <is>
-          <t>Clarivate Plc</t>
+          <t>Getty Images Holdings,</t>
         </is>
       </c>
       <c r="C23" s="16" t="n">
@@ -5488,19 +5505,19 @@
       </c>
       <c r="F23" s="7" t="inlineStr">
         <is>
-          <t>asset sale monetization</t>
+          <t>coiled spring delever</t>
         </is>
       </c>
     </row>
     <row r="24" ht="22" customHeight="1">
       <c r="A24" s="9" t="inlineStr">
         <is>
-          <t>NUS</t>
+          <t>CLVT</t>
         </is>
       </c>
       <c r="B24" s="10" t="inlineStr">
         <is>
-          <t>Nu Skin Enterprises, I</t>
+          <t>Clarivate Plc</t>
         </is>
       </c>
       <c r="C24" s="17" t="n">
@@ -5521,12 +5538,12 @@
     <row r="25" ht="22" customHeight="1">
       <c r="A25" s="6" t="inlineStr">
         <is>
-          <t>UTZ</t>
+          <t>NUS</t>
         </is>
       </c>
       <c r="B25" s="7" t="inlineStr">
         <is>
-          <t>Utz Brands Inc</t>
+          <t>Nu Skin Enterprises, I</t>
         </is>
       </c>
       <c r="C25" s="16" t="n">
@@ -5536,23 +5553,23 @@
         <v>1</v>
       </c>
       <c r="E25" s="16" t="n">
-        <v>23.9</v>
+        <v>60</v>
       </c>
       <c r="F25" s="7" t="inlineStr">
         <is>
-          <t>coiled spring delever</t>
+          <t>asset sale monetization</t>
         </is>
       </c>
     </row>
     <row r="26" ht="22" customHeight="1">
       <c r="A26" s="9" t="inlineStr">
         <is>
-          <t>LAB</t>
+          <t>UTZ</t>
         </is>
       </c>
       <c r="B26" s="10" t="inlineStr">
         <is>
-          <t>Standard BioTools Inc.</t>
+          <t>Utz Brands Inc</t>
         </is>
       </c>
       <c r="C26" s="17" t="n">
@@ -5562,23 +5579,23 @@
         <v>1</v>
       </c>
       <c r="E26" s="17" t="n">
-        <v>42.3</v>
+        <v>23.9</v>
       </c>
       <c r="F26" s="10" t="inlineStr">
         <is>
-          <t>asset sale monetization</t>
+          <t>coiled spring delever</t>
         </is>
       </c>
     </row>
     <row r="27" ht="22" customHeight="1">
       <c r="A27" s="6" t="inlineStr">
         <is>
-          <t>UEIC</t>
+          <t>LAB</t>
         </is>
       </c>
       <c r="B27" s="7" t="inlineStr">
         <is>
-          <t>Universal Electronics</t>
+          <t>Standard BioTools Inc.</t>
         </is>
       </c>
       <c r="C27" s="16" t="n">
@@ -5588,7 +5605,7 @@
         <v>1</v>
       </c>
       <c r="E27" s="16" t="n">
-        <v>60</v>
+        <v>42.3</v>
       </c>
       <c r="F27" s="7" t="inlineStr">
         <is>
@@ -5599,12 +5616,12 @@
     <row r="28" ht="22" customHeight="1">
       <c r="A28" s="9" t="inlineStr">
         <is>
-          <t>MAGN</t>
+          <t>UEIC</t>
         </is>
       </c>
       <c r="B28" s="10" t="inlineStr">
         <is>
-          <t>Magnera Corporation</t>
+          <t>Universal Electronics</t>
         </is>
       </c>
       <c r="C28" s="17" t="n">
@@ -5618,19 +5635,19 @@
       </c>
       <c r="F28" s="10" t="inlineStr">
         <is>
-          <t>coiled spring delever</t>
+          <t>asset sale monetization</t>
         </is>
       </c>
     </row>
     <row r="29" ht="22" customHeight="1">
       <c r="A29" s="6" t="inlineStr">
         <is>
-          <t>BOC</t>
+          <t>MAGN</t>
         </is>
       </c>
       <c r="B29" s="7" t="inlineStr">
         <is>
-          <t>Boston Omaha Corporati</t>
+          <t>Magnera Corporation</t>
         </is>
       </c>
       <c r="C29" s="16" t="n">
@@ -5644,19 +5661,19 @@
       </c>
       <c r="F29" s="7" t="inlineStr">
         <is>
-          <t>asset sale monetization</t>
+          <t>coiled spring delever</t>
         </is>
       </c>
     </row>
     <row r="30" ht="22" customHeight="1">
       <c r="A30" s="9" t="inlineStr">
         <is>
-          <t>BALY</t>
+          <t>BOC</t>
         </is>
       </c>
       <c r="B30" s="10" t="inlineStr">
         <is>
-          <t>Bally's Corporation</t>
+          <t>Boston Omaha Corporati</t>
         </is>
       </c>
       <c r="C30" s="17" t="n">
@@ -5666,59 +5683,59 @@
         <v>1</v>
       </c>
       <c r="E30" s="17" t="n">
-        <v>38.5</v>
+        <v>60</v>
       </c>
       <c r="F30" s="10" t="inlineStr">
         <is>
-          <t>coiled spring delever</t>
+          <t>asset sale monetization</t>
         </is>
       </c>
     </row>
     <row r="31" ht="22" customHeight="1">
       <c r="A31" s="6" t="inlineStr">
         <is>
-          <t>HAIN</t>
+          <t>BALY</t>
         </is>
       </c>
       <c r="B31" s="7" t="inlineStr">
         <is>
-          <t>The Hain Celestial Gro</t>
+          <t>Bally's Corporation</t>
         </is>
       </c>
       <c r="C31" s="16" t="n">
-        <v>19.9</v>
+        <v>20</v>
       </c>
       <c r="D31" s="16" t="n">
         <v>1</v>
       </c>
       <c r="E31" s="16" t="n">
-        <v>60</v>
+        <v>38.5</v>
       </c>
       <c r="F31" s="7" t="inlineStr">
         <is>
-          <t>asset sale monetization</t>
+          <t>coiled spring delever</t>
         </is>
       </c>
     </row>
     <row r="32" ht="22" customHeight="1">
       <c r="A32" s="9" t="inlineStr">
         <is>
-          <t>PRGO</t>
+          <t>HAIN</t>
         </is>
       </c>
       <c r="B32" s="10" t="inlineStr">
         <is>
-          <t>Perrigo Company plc</t>
+          <t>The Hain Celestial Gro</t>
         </is>
       </c>
       <c r="C32" s="17" t="n">
-        <v>19</v>
+        <v>19.9</v>
       </c>
       <c r="D32" s="17" t="n">
         <v>1</v>
       </c>
       <c r="E32" s="17" t="n">
-        <v>25.6</v>
+        <v>60</v>
       </c>
       <c r="F32" s="10" t="inlineStr">
         <is>
@@ -5729,22 +5746,22 @@
     <row r="33" ht="22" customHeight="1">
       <c r="A33" s="6" t="inlineStr">
         <is>
-          <t>ZSTK</t>
+          <t>PRGO</t>
         </is>
       </c>
       <c r="B33" s="7" t="inlineStr">
         <is>
-          <t>ZeroStack Corp.</t>
+          <t>Perrigo Company plc</t>
         </is>
       </c>
       <c r="C33" s="16" t="n">
-        <v>18.6</v>
+        <v>19</v>
       </c>
       <c r="D33" s="16" t="n">
         <v>1</v>
       </c>
       <c r="E33" s="16" t="n">
-        <v>60</v>
+        <v>25.6</v>
       </c>
       <c r="F33" s="7" t="inlineStr">
         <is>
@@ -5755,22 +5772,22 @@
     <row r="34" ht="22" customHeight="1">
       <c r="A34" s="9" t="inlineStr">
         <is>
-          <t>CMCO</t>
+          <t>ZSTK</t>
         </is>
       </c>
       <c r="B34" s="10" t="inlineStr">
         <is>
-          <t>Columbus McKinnon Corp</t>
+          <t>ZeroStack Corp.</t>
         </is>
       </c>
       <c r="C34" s="17" t="n">
-        <v>18.4</v>
+        <v>18.6</v>
       </c>
       <c r="D34" s="17" t="n">
         <v>1</v>
       </c>
       <c r="E34" s="17" t="n">
-        <v>7.1</v>
+        <v>60</v>
       </c>
       <c r="F34" s="10" t="inlineStr">
         <is>
@@ -5781,22 +5798,22 @@
     <row r="35" ht="22" customHeight="1">
       <c r="A35" s="6" t="inlineStr">
         <is>
-          <t>CERT</t>
+          <t>CMCO</t>
         </is>
       </c>
       <c r="B35" s="7" t="inlineStr">
         <is>
-          <t>Certara, Inc.</t>
+          <t>Columbus McKinnon Corp</t>
         </is>
       </c>
       <c r="C35" s="16" t="n">
-        <v>18.3</v>
+        <v>18.4</v>
       </c>
       <c r="D35" s="16" t="n">
         <v>1</v>
       </c>
       <c r="E35" s="16" t="n">
-        <v>10.7</v>
+        <v>7.1</v>
       </c>
       <c r="F35" s="7" t="inlineStr">
         <is>
@@ -5807,48 +5824,48 @@
     <row r="36" ht="22" customHeight="1">
       <c r="A36" s="9" t="inlineStr">
         <is>
-          <t>ONEW</t>
+          <t>WHR</t>
         </is>
       </c>
       <c r="B36" s="10" t="inlineStr">
         <is>
-          <t>OneWater Marine Inc.</t>
+          <t>Whirlpool Corporation</t>
         </is>
       </c>
       <c r="C36" s="17" t="n">
-        <v>18.3</v>
+        <v>18.4</v>
       </c>
       <c r="D36" s="17" t="n">
         <v>1</v>
       </c>
       <c r="E36" s="17" t="n">
-        <v>10.5</v>
+        <v>6</v>
       </c>
       <c r="F36" s="10" t="inlineStr">
         <is>
-          <t>asset sale monetization</t>
+          <t>structured distressed injection</t>
         </is>
       </c>
     </row>
     <row r="37" ht="22" customHeight="1">
       <c r="A37" s="6" t="inlineStr">
         <is>
-          <t>HLLY</t>
+          <t>CERT</t>
         </is>
       </c>
       <c r="B37" s="7" t="inlineStr">
         <is>
-          <t>Holley Inc.</t>
+          <t>Certara, Inc.</t>
         </is>
       </c>
       <c r="C37" s="16" t="n">
-        <v>18.2</v>
+        <v>18.3</v>
       </c>
       <c r="D37" s="16" t="n">
         <v>1</v>
       </c>
       <c r="E37" s="16" t="n">
-        <v>6.3</v>
+        <v>10.7</v>
       </c>
       <c r="F37" s="7" t="inlineStr">
         <is>
@@ -5859,152 +5876,152 @@
     <row r="38" ht="22" customHeight="1">
       <c r="A38" s="9" t="inlineStr">
         <is>
-          <t>WKHS</t>
+          <t>ONEW</t>
         </is>
       </c>
       <c r="B38" s="10" t="inlineStr">
         <is>
-          <t>Workhorse Group, Inc.</t>
+          <t>OneWater Marine Inc.</t>
         </is>
       </c>
       <c r="C38" s="17" t="n">
-        <v>18</v>
+        <v>18.3</v>
       </c>
       <c r="D38" s="17" t="n">
         <v>1</v>
       </c>
       <c r="E38" s="17" t="n">
-        <v>7.4</v>
+        <v>10.5</v>
       </c>
       <c r="F38" s="10" t="inlineStr">
         <is>
-          <t>hidden asset realization</t>
+          <t>asset sale monetization</t>
         </is>
       </c>
     </row>
     <row r="39" ht="22" customHeight="1">
       <c r="A39" s="6" t="inlineStr">
         <is>
-          <t>MLCI</t>
+          <t>HLLY</t>
         </is>
       </c>
       <c r="B39" s="7" t="inlineStr">
         <is>
-          <t>Mount Logan Capital In</t>
+          <t>Holley Inc.</t>
         </is>
       </c>
       <c r="C39" s="16" t="n">
-        <v>17.8</v>
+        <v>18.2</v>
       </c>
       <c r="D39" s="16" t="n">
         <v>1</v>
       </c>
       <c r="E39" s="16" t="n">
-        <v>26.1</v>
+        <v>6.3</v>
       </c>
       <c r="F39" s="7" t="inlineStr">
         <is>
-          <t>tender offer squeeze</t>
+          <t>asset sale monetization</t>
         </is>
       </c>
     </row>
     <row r="40" ht="22" customHeight="1">
       <c r="A40" s="9" t="inlineStr">
         <is>
-          <t>CMTL</t>
+          <t>WKHS</t>
         </is>
       </c>
       <c r="B40" s="10" t="inlineStr">
         <is>
-          <t>Comtech Telecommunicat</t>
+          <t>Workhorse Group, Inc.</t>
         </is>
       </c>
       <c r="C40" s="17" t="n">
-        <v>17.7</v>
+        <v>18</v>
       </c>
       <c r="D40" s="17" t="n">
         <v>1</v>
       </c>
       <c r="E40" s="17" t="n">
-        <v>11.5</v>
+        <v>7.4</v>
       </c>
       <c r="F40" s="10" t="inlineStr">
         <is>
-          <t>asset sale monetization</t>
+          <t>hidden asset realization</t>
         </is>
       </c>
     </row>
     <row r="41" ht="22" customHeight="1">
       <c r="A41" s="6" t="inlineStr">
         <is>
-          <t>AHCO</t>
+          <t>MLCI</t>
         </is>
       </c>
       <c r="B41" s="7" t="inlineStr">
         <is>
-          <t>AdaptHealth Corp.</t>
+          <t>Mount Logan Capital In</t>
         </is>
       </c>
       <c r="C41" s="16" t="n">
-        <v>17.6</v>
+        <v>17.8</v>
       </c>
       <c r="D41" s="16" t="n">
         <v>1</v>
       </c>
       <c r="E41" s="16" t="n">
-        <v>7.1</v>
+        <v>26.1</v>
       </c>
       <c r="F41" s="7" t="inlineStr">
         <is>
-          <t>asset sale monetization</t>
+          <t>tender offer squeeze</t>
         </is>
       </c>
     </row>
     <row r="42" ht="22" customHeight="1">
       <c r="A42" s="9" t="inlineStr">
         <is>
-          <t>MATV</t>
+          <t>CMTL</t>
         </is>
       </c>
       <c r="B42" s="10" t="inlineStr">
         <is>
-          <t>Mativ Holdings, Inc.</t>
+          <t>Comtech Telecommunicat</t>
         </is>
       </c>
       <c r="C42" s="17" t="n">
-        <v>17.6</v>
+        <v>17.7</v>
       </c>
       <c r="D42" s="17" t="n">
         <v>1</v>
       </c>
       <c r="E42" s="17" t="n">
-        <v>7.1</v>
+        <v>11.5</v>
       </c>
       <c r="F42" s="10" t="inlineStr">
         <is>
-          <t>coiled spring delever</t>
+          <t>asset sale monetization</t>
         </is>
       </c>
     </row>
     <row r="43" ht="22" customHeight="1">
       <c r="A43" s="6" t="inlineStr">
         <is>
-          <t>BDN</t>
+          <t>AHCO</t>
         </is>
       </c>
       <c r="B43" s="7" t="inlineStr">
         <is>
-          <t>Brandywine Realty Trus</t>
+          <t>AdaptHealth Corp.</t>
         </is>
       </c>
       <c r="C43" s="16" t="n">
-        <v>17.5</v>
+        <v>17.6</v>
       </c>
       <c r="D43" s="16" t="n">
         <v>1</v>
       </c>
       <c r="E43" s="16" t="n">
-        <v>6.5</v>
+        <v>7.1</v>
       </c>
       <c r="F43" s="7" t="inlineStr">
         <is>
@@ -6015,48 +6032,48 @@
     <row r="44" ht="22" customHeight="1">
       <c r="A44" s="9" t="inlineStr">
         <is>
-          <t>DFH</t>
+          <t>MATV</t>
         </is>
       </c>
       <c r="B44" s="10" t="inlineStr">
         <is>
-          <t>Dream Finders Homes, I</t>
+          <t>Mativ Holdings, Inc.</t>
         </is>
       </c>
       <c r="C44" s="17" t="n">
-        <v>17.2</v>
+        <v>17.6</v>
       </c>
       <c r="D44" s="17" t="n">
         <v>1</v>
       </c>
       <c r="E44" s="17" t="n">
-        <v>2.5</v>
+        <v>7.1</v>
       </c>
       <c r="F44" s="10" t="inlineStr">
         <is>
-          <t>hidden asset realization</t>
+          <t>coiled spring delever</t>
         </is>
       </c>
     </row>
     <row r="45" ht="22" customHeight="1">
       <c r="A45" s="6" t="inlineStr">
         <is>
-          <t>BGS</t>
+          <t>BDN</t>
         </is>
       </c>
       <c r="B45" s="7" t="inlineStr">
         <is>
-          <t>B&amp;G Foods, Inc.</t>
+          <t>Brandywine Realty Trus</t>
         </is>
       </c>
       <c r="C45" s="16" t="n">
-        <v>17.1</v>
+        <v>17.5</v>
       </c>
       <c r="D45" s="16" t="n">
         <v>1</v>
       </c>
       <c r="E45" s="16" t="n">
-        <v>7.8</v>
+        <v>6.5</v>
       </c>
       <c r="F45" s="7" t="inlineStr">
         <is>
@@ -6067,100 +6084,100 @@
     <row r="46" ht="22" customHeight="1">
       <c r="A46" s="9" t="inlineStr">
         <is>
-          <t>CNC</t>
+          <t>STEX</t>
         </is>
       </c>
       <c r="B46" s="10" t="inlineStr">
         <is>
-          <t>Centene Corporation</t>
+          <t>Streamex Corp.</t>
         </is>
       </c>
       <c r="C46" s="17" t="n">
-        <v>17</v>
+        <v>17.3</v>
       </c>
       <c r="D46" s="17" t="n">
         <v>1</v>
       </c>
       <c r="E46" s="17" t="n">
-        <v>4.7</v>
+        <v>12.2</v>
       </c>
       <c r="F46" s="10" t="inlineStr">
         <is>
-          <t>asset sale monetization</t>
+          <t>structured distressed injection</t>
         </is>
       </c>
     </row>
     <row r="47" ht="22" customHeight="1">
       <c r="A47" s="6" t="inlineStr">
         <is>
-          <t>ABM</t>
+          <t>BGS</t>
         </is>
       </c>
       <c r="B47" s="7" t="inlineStr">
         <is>
-          <t>ABM Industries Incorpo</t>
+          <t>B&amp;G Foods, Inc.</t>
         </is>
       </c>
       <c r="C47" s="16" t="n">
-        <v>17</v>
+        <v>17.1</v>
       </c>
       <c r="D47" s="16" t="n">
         <v>1</v>
       </c>
       <c r="E47" s="16" t="n">
-        <v>4.5</v>
+        <v>7.8</v>
       </c>
       <c r="F47" s="7" t="inlineStr">
         <is>
-          <t>coiled spring delever</t>
+          <t>asset sale monetization</t>
         </is>
       </c>
     </row>
     <row r="48" ht="22" customHeight="1">
       <c r="A48" s="9" t="inlineStr">
         <is>
-          <t>KROS</t>
+          <t>CNC</t>
         </is>
       </c>
       <c r="B48" s="10" t="inlineStr">
         <is>
-          <t>Keros Therapeutics, In</t>
+          <t>Centene Corporation</t>
         </is>
       </c>
       <c r="C48" s="17" t="n">
-        <v>16.9</v>
+        <v>17</v>
       </c>
       <c r="D48" s="17" t="n">
         <v>1</v>
       </c>
       <c r="E48" s="17" t="n">
-        <v>11.1</v>
+        <v>4.7</v>
       </c>
       <c r="F48" s="10" t="inlineStr">
         <is>
-          <t>tender offer squeeze</t>
+          <t>asset sale monetization</t>
         </is>
       </c>
     </row>
     <row r="49" ht="22" customHeight="1">
       <c r="A49" s="6" t="inlineStr">
         <is>
-          <t>NWL</t>
+          <t>ABM</t>
         </is>
       </c>
       <c r="B49" s="7" t="inlineStr">
         <is>
-          <t>Newell Brands Inc.</t>
+          <t>ABM Industries Incorpo</t>
         </is>
       </c>
       <c r="C49" s="16" t="n">
-        <v>16.7</v>
+        <v>17</v>
       </c>
       <c r="D49" s="16" t="n">
         <v>1</v>
       </c>
       <c r="E49" s="16" t="n">
-        <v>3.8</v>
+        <v>4.5</v>
       </c>
       <c r="F49" s="7" t="inlineStr">
         <is>
@@ -6171,7 +6188,7 @@
     <row r="51" ht="28" customHeight="1">
       <c r="A51" s="11" t="inlineStr">
         <is>
-          <t>102 names pass at least one mechanism gate; 14 light up two or more (the highest-conviction convergence). Unlike the additive consensus, these are HARD gates — every condition of a machine must hold: coiled-spring delever (D/E ≥ 1 + rising operating income + cheap equity), sub-cash buyback (net-cash floor ≥ 50% of price + active repurchase + not burning), forced-seller exhaustion (N-PORT forced selling into a floor, business not burning), hidden-asset realisation (small levered stub + credit-agreement asset sweep), stated-unlock triangulated (MD&amp;A value-unlock language + cheap geometry + insider buying), asset-sale monetization (asset-sale catalyst + cheap + levered/small — the backtest's best-median catalyst, +10%/58% hit), and tender-offer squeeze (tender/Dutch-auction catalyst + cheap small-cap — best hit rate, 61%). TWO ANTICIPATORY archetypes catch the setup BEFORE the catalyst: asset-sale latent (cheap + levered + de-lever pressure or MD&amp;A divestiture intent, NO sale announced) and tender-target latent (near net cash / NCAV, small controllable cap, plausible buyer — high insider ownership or self-tender-capable cash — and NO bid yet); these are speculative (weighted below the confirmed machines) but flag names likely to realise value that haven't yet. Combines the payoff-geometry shape with the catalyst layers so shape and 'why now' are both required. Source: mechanism_gates.py.</t>
+          <t>106 names pass at least one mechanism gate; 15 light up two or more (the highest-conviction convergence). Unlike the additive consensus, these are HARD gates — every condition of a machine must hold: coiled-spring delever (D/E ≥ 1 + rising operating income + cheap equity), sub-cash buyback (net-cash floor ≥ 50% of price + active repurchase + not burning), forced-seller exhaustion (N-PORT forced selling into a floor, business not burning), hidden-asset realisation (small levered stub + credit-agreement asset sweep), stated-unlock triangulated (MD&amp;A value-unlock language + cheap geometry + insider buying), asset-sale monetization (asset-sale catalyst + cheap + levered/small — the backtest's best-median catalyst, +10%/58% hit), and tender-offer squeeze (tender/Dutch-auction catalyst + cheap small-cap — best hit rate, 61%). TWO ANTICIPATORY archetypes catch the setup BEFORE the catalyst: asset-sale latent (cheap + levered + de-lever pressure or MD&amp;A divestiture intent, NO sale announced) and tender-target latent (near net cash / NCAV, small controllable cap, plausible buyer — high insider ownership or self-tender-capable cash — and NO bid yet); these are speculative (weighted below the confirmed machines) but flag names likely to realise value that haven't yet. Plus structured distressed injection (the Cundill/Sibir play — an asset-backed washout raising via a senior/convertible instrument; see the Structured Distressed tab). Combines the payoff-geometry shape with the catalyst layers so shape and 'why now' are both required. Source: mechanism_gates.py.</t>
         </is>
       </c>
     </row>
@@ -6188,6 +6205,330 @@
 </file>
 
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:H12"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="9" customWidth="1" min="1" max="1"/>
+    <col width="24" customWidth="1" min="2" max="2"/>
+    <col width="8" customWidth="1" min="3" max="3"/>
+    <col width="22" customWidth="1" min="4" max="4"/>
+    <col width="8" customWidth="1" min="5" max="5"/>
+    <col width="8" customWidth="1" min="6" max="6"/>
+    <col width="8" customWidth="1" min="7" max="7"/>
+    <col width="20" customWidth="1" min="8" max="8"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="26" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Structured Distressed Injection — the Cundill / Sibir play</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="18" customHeight="1">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Hard-asset-backed companies whose equity collapsed in a washout and that are raising capital via a SENIOR / CONVERTIBLE instrument (convertible debenture, senior/secured convertible note, convertible preferred). The margin of safety is structural — seniority + coupon + asset value floor the downside, the convert keeps the upside — so the move is to own the INSTRUMENT, not the common.</t>
+        </is>
+      </c>
+      <c r="B2" s="3" t="n"/>
+      <c r="C2" s="3" t="n"/>
+      <c r="D2" s="3" t="n"/>
+      <c r="E2" s="3" t="n"/>
+      <c r="F2" s="3" t="n"/>
+      <c r="G2" s="3" t="n"/>
+      <c r="H2" s="3" t="n"/>
+    </row>
+    <row r="3" ht="8" customHeight="1"/>
+    <row r="4" ht="18" customHeight="1">
+      <c r="A4" s="15" t="inlineStr">
+        <is>
+          <t>Ticker</t>
+        </is>
+      </c>
+      <c r="B4" s="15" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="C4" s="4" t="inlineStr">
+        <is>
+          <t>Score</t>
+        </is>
+      </c>
+      <c r="D4" s="4" t="inlineStr">
+        <is>
+          <t>Instrument</t>
+        </is>
+      </c>
+      <c r="E4" s="4" t="inlineStr">
+        <is>
+          <t>Drawdown</t>
+        </is>
+      </c>
+      <c r="F4" s="4" t="inlineStr">
+        <is>
+          <t>Coupon</t>
+        </is>
+      </c>
+      <c r="G4" s="4" t="inlineStr">
+        <is>
+          <t>Senior</t>
+        </is>
+      </c>
+      <c r="H4" s="4" t="inlineStr">
+        <is>
+          <t>Signals</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="22" customHeight="1">
+      <c r="A5" s="6" t="inlineStr">
+        <is>
+          <t>TAOX</t>
+        </is>
+      </c>
+      <c r="B5" s="7" t="inlineStr">
+        <is>
+          <t>Tao Synergies Inc.</t>
+        </is>
+      </c>
+      <c r="C5" s="16" t="n">
+        <v>27</v>
+      </c>
+      <c r="D5" s="7" t="inlineStr">
+        <is>
+          <t>convertible pipe</t>
+        </is>
+      </c>
+      <c r="E5" s="16" t="n">
+        <v>-69</v>
+      </c>
+      <c r="F5" s="16" t="n">
+        <v>7</v>
+      </c>
+      <c r="G5" s="7" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="H5" s="7" t="inlineStr">
+        <is>
+          <t>asset floor, washout</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="22" customHeight="1">
+      <c r="A6" s="9" t="inlineStr">
+        <is>
+          <t>STEX</t>
+        </is>
+      </c>
+      <c r="B6" s="10" t="inlineStr">
+        <is>
+          <t>Streamex Corp.</t>
+        </is>
+      </c>
+      <c r="C6" s="17" t="n">
+        <v>26</v>
+      </c>
+      <c r="D6" s="10" t="inlineStr">
+        <is>
+          <t>convertible debenture</t>
+        </is>
+      </c>
+      <c r="E6" s="17" t="n">
+        <v>-94</v>
+      </c>
+      <c r="F6" s="10" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="G6" s="10" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="H6" s="10" t="inlineStr">
+        <is>
+          <t>asset floor, washout</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="22" customHeight="1">
+      <c r="A7" s="6" t="inlineStr">
+        <is>
+          <t>FRMI</t>
+        </is>
+      </c>
+      <c r="B7" s="7" t="inlineStr">
+        <is>
+          <t>Fermi Inc.</t>
+        </is>
+      </c>
+      <c r="C7" s="16" t="n">
+        <v>25</v>
+      </c>
+      <c r="D7" s="7" t="inlineStr">
+        <is>
+          <t>senior convertible</t>
+        </is>
+      </c>
+      <c r="E7" s="16" t="n">
+        <v>-81</v>
+      </c>
+      <c r="F7" s="16" t="n">
+        <v>5</v>
+      </c>
+      <c r="G7" s="7" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="H7" s="7" t="inlineStr">
+        <is>
+          <t>asset floor, washout</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="22" customHeight="1">
+      <c r="A8" s="9" t="inlineStr">
+        <is>
+          <t>DFH</t>
+        </is>
+      </c>
+      <c r="B8" s="10" t="inlineStr">
+        <is>
+          <t>Dream Finders Homes, Inc</t>
+        </is>
+      </c>
+      <c r="C8" s="17" t="n">
+        <v>25</v>
+      </c>
+      <c r="D8" s="10" t="inlineStr">
+        <is>
+          <t>convertible preferred</t>
+        </is>
+      </c>
+      <c r="E8" s="17" t="n">
+        <v>-50</v>
+      </c>
+      <c r="F8" s="10" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="G8" s="10" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="H8" s="10" t="inlineStr">
+        <is>
+          <t>asset floor, washout</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="22" customHeight="1">
+      <c r="A9" s="6" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="B9" s="7" t="inlineStr">
+        <is>
+          <t>Infinity Natural Resourc</t>
+        </is>
+      </c>
+      <c r="C9" s="16" t="n">
+        <v>22</v>
+      </c>
+      <c r="D9" s="7" t="inlineStr">
+        <is>
+          <t>convertible preferred</t>
+        </is>
+      </c>
+      <c r="E9" s="16" t="n">
+        <v>-35</v>
+      </c>
+      <c r="F9" s="16" t="n">
+        <v>51</v>
+      </c>
+      <c r="G9" s="7" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="H9" s="7" t="inlineStr">
+        <is>
+          <t>asset floor, small-c</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="22" customHeight="1">
+      <c r="A10" s="9" t="inlineStr">
+        <is>
+          <t>WHR</t>
+        </is>
+      </c>
+      <c r="B10" s="10" t="inlineStr">
+        <is>
+          <t>Whirlpool Corporation</t>
+        </is>
+      </c>
+      <c r="C10" s="17" t="n">
+        <v>22</v>
+      </c>
+      <c r="D10" s="10" t="inlineStr">
+        <is>
+          <t>convertible preferred</t>
+        </is>
+      </c>
+      <c r="E10" s="17" t="n">
+        <v>-65</v>
+      </c>
+      <c r="F10" s="10" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="G10" s="10" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="H10" s="10" t="inlineStr">
+        <is>
+          <t>asset floor, washout</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="28" customHeight="1">
+      <c r="A12" s="11" t="inlineStr">
+        <is>
+          <t>6 names pass the hard conjunction: a structured raise (convertible/senior/preferred) IN an asset-backed, washed-out or small-cap name. Most convertible raises are routine dilutive growth financings and are filtered OUT — this isolates the distressed asset-play version where the instrument carries a built-in margin of safety (the engine's equity layers actually PENALISE convertibles as dilution, which is correct for the common and backwards for this play). Coupon/seniority parsed from the filing for the top names. Source: structured_distressed_injection.py.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="3">
+    <mergeCell ref="A12:H12"/>
+    <mergeCell ref="A2:H2"/>
+    <mergeCell ref="A1:H1"/>
+  </mergeCells>
+  <printOptions horizontalCentered="0"/>
+  <pageMargins left="0.5" right="0.5" top="0.6" bottom="0.6" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -7820,7 +8161,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -8613,7 +8954,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -11177,7 +11518,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -11706,7 +12047,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -12662,7 +13003,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -14235,1501 +14576,6 @@
     <mergeCell ref="A2:G2"/>
     <mergeCell ref="A1:G1"/>
     <mergeCell ref="A51:G51"/>
-  </mergeCells>
-  <printOptions horizontalCentered="0"/>
-  <pageMargins left="0.5" right="0.5" top="0.6" bottom="0.6" header="0.5" footer="0.5"/>
-  <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="1"/>
-  </sheetPr>
-  <dimension ref="A1:G46"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="9" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="8" customWidth="1" min="3" max="3"/>
-    <col width="9" customWidth="1" min="4" max="4"/>
-    <col width="15" customWidth="1" min="5" max="5"/>
-    <col width="26" customWidth="1" min="6" max="6"/>
-    <col width="30" customWidth="1" min="7" max="7"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="26" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Hidden-Asset / Incentivised Value Realisation</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="18" customHeight="1">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>Under-recognised assets across ALL industries (spectrum, water/mineral/royalty rights, real estate, NOLs, equity stakes, pension surplus, royalty streams) inside a small levered equity base, where a credit agreement sweeps disposition proceeds to debt paydown — so realising the asset is mechanically stub-accretive</t>
-        </is>
-      </c>
-      <c r="B2" s="3" t="n"/>
-      <c r="C2" s="3" t="n"/>
-      <c r="D2" s="3" t="n"/>
-      <c r="E2" s="3" t="n"/>
-      <c r="F2" s="3" t="n"/>
-      <c r="G2" s="3" t="n"/>
-    </row>
-    <row r="3" ht="8" customHeight="1"/>
-    <row r="4" ht="18" customHeight="1">
-      <c r="A4" s="15" t="inlineStr">
-        <is>
-          <t>Ticker</t>
-        </is>
-      </c>
-      <c r="B4" s="15" t="inlineStr">
-        <is>
-          <t>Name</t>
-        </is>
-      </c>
-      <c r="C4" s="4" t="inlineStr">
-        <is>
-          <t>Score</t>
-        </is>
-      </c>
-      <c r="D4" s="4" t="inlineStr">
-        <is>
-          <t>Mand. prepay</t>
-        </is>
-      </c>
-      <c r="E4" s="15" t="inlineStr">
-        <is>
-          <t>Industry</t>
-        </is>
-      </c>
-      <c r="F4" s="4" t="inlineStr">
-        <is>
-          <t>Asset types</t>
-        </is>
-      </c>
-      <c r="G4" s="4" t="inlineStr">
-        <is>
-          <t>Thesis / feature</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="22" customHeight="1">
-      <c r="A5" s="6" t="inlineStr">
-        <is>
-          <t>SSP</t>
-        </is>
-      </c>
-      <c r="B5" s="7" t="inlineStr">
-        <is>
-          <t>SSP</t>
-        </is>
-      </c>
-      <c r="C5" s="16" t="n">
-        <v>36</v>
-      </c>
-      <c r="D5" s="7" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="E5" s="7" t="inlineStr">
-        <is>
-          <t>media, telecom</t>
-        </is>
-      </c>
-      <c r="F5" s="7" t="inlineStr">
-        <is>
-          <t>spectrum, broadcast_licenc</t>
-        </is>
-      </c>
-      <c r="G5" s="7" t="inlineStr">
-        <is>
-          <t>April 2026 credit agreement an</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="22" customHeight="1">
-      <c r="A6" s="9" t="inlineStr">
-        <is>
-          <t>EVC</t>
-        </is>
-      </c>
-      <c r="B6" s="10" t="inlineStr">
-        <is>
-          <t>Entravision Commun</t>
-        </is>
-      </c>
-      <c r="C6" s="17" t="n">
-        <v>30</v>
-      </c>
-      <c r="D6" s="10" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="E6" s="10" t="inlineStr">
-        <is>
-          <t>media, telecom</t>
-        </is>
-      </c>
-      <c r="F6" s="10" t="inlineStr">
-        <is>
-          <t>spectrum, broadcast_licenc</t>
-        </is>
-      </c>
-      <c r="G6" s="10" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="22" customHeight="1">
-      <c r="A7" s="6" t="inlineStr">
-        <is>
-          <t>LMNR</t>
-        </is>
-      </c>
-      <c r="B7" s="7" t="inlineStr">
-        <is>
-          <t>Limoneira Co</t>
-        </is>
-      </c>
-      <c r="C7" s="16" t="n">
-        <v>28</v>
-      </c>
-      <c r="D7" s="7" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="E7" s="7" t="inlineStr">
-        <is>
-          <t>real_estate, re</t>
-        </is>
-      </c>
-      <c r="F7" s="7" t="inlineStr">
-        <is>
-          <t>water_rights, air_rights</t>
-        </is>
-      </c>
-      <c r="G7" s="7" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="22" customHeight="1">
-      <c r="A8" s="9" t="inlineStr">
-        <is>
-          <t>MDIA</t>
-        </is>
-      </c>
-      <c r="B8" s="10" t="inlineStr">
-        <is>
-          <t>Mediaco Holding In</t>
-        </is>
-      </c>
-      <c r="C8" s="17" t="n">
-        <v>26</v>
-      </c>
-      <c r="D8" s="10" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="E8" s="10" t="inlineStr">
-        <is>
-          <t>media, telecom</t>
-        </is>
-      </c>
-      <c r="F8" s="10" t="inlineStr">
-        <is>
-          <t>broadcast_licences, fcc_li</t>
-        </is>
-      </c>
-      <c r="G8" s="10" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="22" customHeight="1">
-      <c r="A9" s="6" t="inlineStr">
-        <is>
-          <t>SBGI</t>
-        </is>
-      </c>
-      <c r="B9" s="7" t="inlineStr">
-        <is>
-          <t>Sinclair, Inc.</t>
-        </is>
-      </c>
-      <c r="C9" s="16" t="n">
-        <v>26</v>
-      </c>
-      <c r="D9" s="7" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="E9" s="7" t="inlineStr">
-        <is>
-          <t>media, telecom</t>
-        </is>
-      </c>
-      <c r="F9" s="7" t="inlineStr">
-        <is>
-          <t>broadcast_licences, fcc_li</t>
-        </is>
-      </c>
-      <c r="G9" s="7" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="22" customHeight="1">
-      <c r="A10" s="9" t="inlineStr">
-        <is>
-          <t>SNDA</t>
-        </is>
-      </c>
-      <c r="B10" s="10" t="inlineStr">
-        <is>
-          <t>Sonida Senior Livi</t>
-        </is>
-      </c>
-      <c r="C10" s="17" t="n">
-        <v>22</v>
-      </c>
-      <c r="D10" s="10" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="E10" s="10" t="inlineStr">
-        <is>
-          <t>holdco, real_es</t>
-        </is>
-      </c>
-      <c r="F10" s="10" t="inlineStr">
-        <is>
-          <t>air_rights, minority_stake</t>
-        </is>
-      </c>
-      <c r="G10" s="10" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="22" customHeight="1">
-      <c r="A11" s="6" t="inlineStr">
-        <is>
-          <t>SGA</t>
-        </is>
-      </c>
-      <c r="B11" s="7" t="inlineStr">
-        <is>
-          <t>SGA</t>
-        </is>
-      </c>
-      <c r="C11" s="16" t="n">
-        <v>20</v>
-      </c>
-      <c r="D11" s="7" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="E11" s="7" t="inlineStr">
-        <is>
-          <t>media, telecom</t>
-        </is>
-      </c>
-      <c r="F11" s="7" t="inlineStr">
-        <is>
-          <t>broadcast_licences, fcc_li</t>
-        </is>
-      </c>
-      <c r="G11" s="7" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="22" customHeight="1">
-      <c r="A12" s="9" t="inlineStr">
-        <is>
-          <t>BBGI</t>
-        </is>
-      </c>
-      <c r="B12" s="10" t="inlineStr">
-        <is>
-          <t>BBGI</t>
-        </is>
-      </c>
-      <c r="C12" s="17" t="n">
-        <v>20</v>
-      </c>
-      <c r="D12" s="10" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="E12" s="10" t="inlineStr">
-        <is>
-          <t>media, telecom</t>
-        </is>
-      </c>
-      <c r="F12" s="10" t="inlineStr">
-        <is>
-          <t>broadcast_licences, fcc_li</t>
-        </is>
-      </c>
-      <c r="G12" s="10" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="22" customHeight="1">
-      <c r="A13" s="6" t="inlineStr">
-        <is>
-          <t>PSKY</t>
-        </is>
-      </c>
-      <c r="B13" s="7" t="inlineStr">
-        <is>
-          <t>PSKY</t>
-        </is>
-      </c>
-      <c r="C13" s="16" t="n">
-        <v>20</v>
-      </c>
-      <c r="D13" s="7" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="E13" s="7" t="inlineStr">
-        <is>
-          <t>media, telecom</t>
-        </is>
-      </c>
-      <c r="F13" s="7" t="inlineStr">
-        <is>
-          <t>broadcast_licences, fcc_li</t>
-        </is>
-      </c>
-      <c r="G13" s="7" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="22" customHeight="1">
-      <c r="A14" s="9" t="inlineStr">
-        <is>
-          <t>TSQ</t>
-        </is>
-      </c>
-      <c r="B14" s="10" t="inlineStr">
-        <is>
-          <t>TSQ</t>
-        </is>
-      </c>
-      <c r="C14" s="17" t="n">
-        <v>20</v>
-      </c>
-      <c r="D14" s="10" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="E14" s="10" t="inlineStr">
-        <is>
-          <t>media, telecom</t>
-        </is>
-      </c>
-      <c r="F14" s="10" t="inlineStr">
-        <is>
-          <t>broadcast_licences, fcc_li</t>
-        </is>
-      </c>
-      <c r="G14" s="10" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="22" customHeight="1">
-      <c r="A15" s="6" t="inlineStr">
-        <is>
-          <t>WBD</t>
-        </is>
-      </c>
-      <c r="B15" s="7" t="inlineStr">
-        <is>
-          <t>Warner Bros. Disco</t>
-        </is>
-      </c>
-      <c r="C15" s="16" t="n">
-        <v>20</v>
-      </c>
-      <c r="D15" s="7" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="E15" s="7" t="inlineStr">
-        <is>
-          <t>media, telecom</t>
-        </is>
-      </c>
-      <c r="F15" s="7" t="inlineStr">
-        <is>
-          <t>broadcast_licences, fcc_li</t>
-        </is>
-      </c>
-      <c r="G15" s="7" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="22" customHeight="1">
-      <c r="A16" s="9" t="inlineStr">
-        <is>
-          <t>NXST</t>
-        </is>
-      </c>
-      <c r="B16" s="10" t="inlineStr">
-        <is>
-          <t>Nexstar Media Grou</t>
-        </is>
-      </c>
-      <c r="C16" s="17" t="n">
-        <v>20</v>
-      </c>
-      <c r="D16" s="10" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="E16" s="10" t="inlineStr">
-        <is>
-          <t>media, telecom</t>
-        </is>
-      </c>
-      <c r="F16" s="10" t="inlineStr">
-        <is>
-          <t>broadcast_licences, fcc_li</t>
-        </is>
-      </c>
-      <c r="G16" s="10" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="22" customHeight="1">
-      <c r="A17" s="6" t="inlineStr">
-        <is>
-          <t>BTQ</t>
-        </is>
-      </c>
-      <c r="B17" s="7" t="inlineStr">
-        <is>
-          <t>BTQ</t>
-        </is>
-      </c>
-      <c r="C17" s="16" t="n">
-        <v>18</v>
-      </c>
-      <c r="D17" s="7" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="E17" s="7" t="inlineStr">
-        <is>
-          <t>holdco, tech, t</t>
-        </is>
-      </c>
-      <c r="F17" s="7" t="inlineStr">
-        <is>
-          <t>data_center, patents, stra</t>
-        </is>
-      </c>
-      <c r="G17" s="7" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="22" customHeight="1">
-      <c r="A18" s="9" t="inlineStr">
-        <is>
-          <t>LOGC</t>
-        </is>
-      </c>
-      <c r="B18" s="10" t="inlineStr">
-        <is>
-          <t>LOGC</t>
-        </is>
-      </c>
-      <c r="C18" s="17" t="n">
-        <v>18</v>
-      </c>
-      <c r="D18" s="10" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="E18" s="10" t="inlineStr">
-        <is>
-          <t>any, resources</t>
-        </is>
-      </c>
-      <c r="F18" s="10" t="inlineStr">
-        <is>
-          <t>mineral_rights, nol</t>
-        </is>
-      </c>
-      <c r="G18" s="10" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="22" customHeight="1">
-      <c r="A19" s="6" t="inlineStr">
-        <is>
-          <t>PCYO</t>
-        </is>
-      </c>
-      <c r="B19" s="7" t="inlineStr">
-        <is>
-          <t>Pure Cycle Corpora</t>
-        </is>
-      </c>
-      <c r="C19" s="16" t="n">
-        <v>18</v>
-      </c>
-      <c r="D19" s="7" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="E19" s="7" t="inlineStr">
-        <is>
-          <t>resources</t>
-        </is>
-      </c>
-      <c r="F19" s="7" t="inlineStr">
-        <is>
-          <t>water_rights</t>
-        </is>
-      </c>
-      <c r="G19" s="7" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="22" customHeight="1">
-      <c r="A20" s="9" t="inlineStr">
-        <is>
-          <t>IPI</t>
-        </is>
-      </c>
-      <c r="B20" s="10" t="inlineStr">
-        <is>
-          <t>Intrepid Potash, I</t>
-        </is>
-      </c>
-      <c r="C20" s="17" t="n">
-        <v>18</v>
-      </c>
-      <c r="D20" s="10" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="E20" s="10" t="inlineStr">
-        <is>
-          <t>resources</t>
-        </is>
-      </c>
-      <c r="F20" s="10" t="inlineStr">
-        <is>
-          <t>water_rights</t>
-        </is>
-      </c>
-      <c r="G20" s="10" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="22" customHeight="1">
-      <c r="A21" s="6" t="inlineStr">
-        <is>
-          <t>CMP</t>
-        </is>
-      </c>
-      <c r="B21" s="7" t="inlineStr">
-        <is>
-          <t>Compass Minerals I</t>
-        </is>
-      </c>
-      <c r="C21" s="16" t="n">
-        <v>18</v>
-      </c>
-      <c r="D21" s="7" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="E21" s="7" t="inlineStr">
-        <is>
-          <t>resources</t>
-        </is>
-      </c>
-      <c r="F21" s="7" t="inlineStr">
-        <is>
-          <t>water_rights</t>
-        </is>
-      </c>
-      <c r="G21" s="7" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="22" customHeight="1">
-      <c r="A22" s="9" t="inlineStr">
-        <is>
-          <t>LODE</t>
-        </is>
-      </c>
-      <c r="B22" s="10" t="inlineStr">
-        <is>
-          <t>Comstock Inc.</t>
-        </is>
-      </c>
-      <c r="C22" s="17" t="n">
-        <v>18</v>
-      </c>
-      <c r="D22" s="10" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="E22" s="10" t="inlineStr">
-        <is>
-          <t>resources</t>
-        </is>
-      </c>
-      <c r="F22" s="10" t="inlineStr">
-        <is>
-          <t>water_rights</t>
-        </is>
-      </c>
-      <c r="G22" s="10" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="22" customHeight="1">
-      <c r="A23" s="6" t="inlineStr">
-        <is>
-          <t>VNOM</t>
-        </is>
-      </c>
-      <c r="B23" s="7" t="inlineStr">
-        <is>
-          <t>Viper Energy, Inc.</t>
-        </is>
-      </c>
-      <c r="C23" s="16" t="n">
-        <v>18</v>
-      </c>
-      <c r="D23" s="7" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="E23" s="7" t="inlineStr">
-        <is>
-          <t>energy, healthc</t>
-        </is>
-      </c>
-      <c r="F23" s="7" t="inlineStr">
-        <is>
-          <t>og_reserves, royalty_acres</t>
-        </is>
-      </c>
-      <c r="G23" s="7" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-    </row>
-    <row r="24" ht="22" customHeight="1">
-      <c r="A24" s="9" t="inlineStr">
-        <is>
-          <t>KRP</t>
-        </is>
-      </c>
-      <c r="B24" s="10" t="inlineStr">
-        <is>
-          <t>Kimbell Royalty Pa</t>
-        </is>
-      </c>
-      <c r="C24" s="17" t="n">
-        <v>18</v>
-      </c>
-      <c r="D24" s="10" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="E24" s="10" t="inlineStr">
-        <is>
-          <t>energy</t>
-        </is>
-      </c>
-      <c r="F24" s="10" t="inlineStr">
-        <is>
-          <t>royalty_acres</t>
-        </is>
-      </c>
-      <c r="G24" s="10" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-    </row>
-    <row r="25" ht="22" customHeight="1">
-      <c r="A25" s="6" t="inlineStr">
-        <is>
-          <t>SATS</t>
-        </is>
-      </c>
-      <c r="B25" s="7" t="inlineStr">
-        <is>
-          <t>EchoStar Corporati</t>
-        </is>
-      </c>
-      <c r="C25" s="16" t="n">
-        <v>17</v>
-      </c>
-      <c r="D25" s="7" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="E25" s="7" t="inlineStr">
-        <is>
-          <t>telecom</t>
-        </is>
-      </c>
-      <c r="F25" s="7" t="inlineStr">
-        <is>
-          <t>spectrum, fcc_licences</t>
-        </is>
-      </c>
-      <c r="G25" s="7" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-    </row>
-    <row r="26" ht="22" customHeight="1">
-      <c r="A26" s="9" t="inlineStr">
-        <is>
-          <t>TILE</t>
-        </is>
-      </c>
-      <c r="B26" s="10" t="inlineStr">
-        <is>
-          <t>Interface, Inc.</t>
-        </is>
-      </c>
-      <c r="C26" s="17" t="n">
-        <v>17</v>
-      </c>
-      <c r="D26" s="10" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="E26" s="10" t="inlineStr">
-        <is>
-          <t>any</t>
-        </is>
-      </c>
-      <c r="F26" s="10" t="inlineStr">
-        <is>
-          <t>pension_surplus, insurance</t>
-        </is>
-      </c>
-      <c r="G26" s="10" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-    </row>
-    <row r="27" ht="22" customHeight="1">
-      <c r="A27" s="6" t="inlineStr">
-        <is>
-          <t>CCI</t>
-        </is>
-      </c>
-      <c r="B27" s="7" t="inlineStr">
-        <is>
-          <t>Crown Castle Inc.</t>
-        </is>
-      </c>
-      <c r="C27" s="16" t="n">
-        <v>16</v>
-      </c>
-      <c r="D27" s="7" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="E27" s="7" t="inlineStr">
-        <is>
-          <t>telecom</t>
-        </is>
-      </c>
-      <c r="F27" s="7" t="inlineStr">
-        <is>
-          <t>spectrum, towers</t>
-        </is>
-      </c>
-      <c r="G27" s="7" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-    </row>
-    <row r="28" ht="22" customHeight="1">
-      <c r="A28" s="9" t="inlineStr">
-        <is>
-          <t>CTGO</t>
-        </is>
-      </c>
-      <c r="B28" s="10" t="inlineStr">
-        <is>
-          <t>CTGO</t>
-        </is>
-      </c>
-      <c r="C28" s="17" t="n">
-        <v>16</v>
-      </c>
-      <c r="D28" s="10" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="E28" s="10" t="inlineStr">
-        <is>
-          <t>healthcare, res</t>
-        </is>
-      </c>
-      <c r="F28" s="10" t="inlineStr">
-        <is>
-          <t>mineral_rights, milestones</t>
-        </is>
-      </c>
-      <c r="G28" s="10" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-    </row>
-    <row r="29" ht="22" customHeight="1">
-      <c r="A29" s="6" t="inlineStr">
-        <is>
-          <t>WULF</t>
-        </is>
-      </c>
-      <c r="B29" s="7" t="inlineStr">
-        <is>
-          <t>TeraWulf Inc.</t>
-        </is>
-      </c>
-      <c r="C29" s="16" t="n">
-        <v>15</v>
-      </c>
-      <c r="D29" s="7" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="E29" s="7" t="inlineStr">
-        <is>
-          <t>real_estate, te</t>
-        </is>
-      </c>
-      <c r="F29" s="7" t="inlineStr">
-        <is>
-          <t>data_center, ground_lease</t>
-        </is>
-      </c>
-      <c r="G29" s="7" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-    </row>
-    <row r="30" ht="22" customHeight="1">
-      <c r="A30" s="9" t="inlineStr">
-        <is>
-          <t>NI</t>
-        </is>
-      </c>
-      <c r="B30" s="10" t="inlineStr">
-        <is>
-          <t>NiSource Inc</t>
-        </is>
-      </c>
-      <c r="C30" s="17" t="n">
-        <v>15</v>
-      </c>
-      <c r="D30" s="10" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="E30" s="10" t="inlineStr">
-        <is>
-          <t>any, telecom</t>
-        </is>
-      </c>
-      <c r="F30" s="10" t="inlineStr">
-        <is>
-          <t>data_center, pension_surpl</t>
-        </is>
-      </c>
-      <c r="G30" s="10" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-    </row>
-    <row r="31" ht="22" customHeight="1">
-      <c r="A31" s="6" t="inlineStr">
-        <is>
-          <t>NOG</t>
-        </is>
-      </c>
-      <c r="B31" s="7" t="inlineStr">
-        <is>
-          <t>Northern Oil and G</t>
-        </is>
-      </c>
-      <c r="C31" s="16" t="n">
-        <v>15</v>
-      </c>
-      <c r="D31" s="7" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="E31" s="7" t="inlineStr">
-        <is>
-          <t>energy</t>
-        </is>
-      </c>
-      <c r="F31" s="7" t="inlineStr">
-        <is>
-          <t>royalty_acres</t>
-        </is>
-      </c>
-      <c r="G31" s="7" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-    </row>
-    <row r="32" ht="22" customHeight="1">
-      <c r="A32" s="9" t="inlineStr">
-        <is>
-          <t>SAFE</t>
-        </is>
-      </c>
-      <c r="B32" s="10" t="inlineStr">
-        <is>
-          <t>Safehold Inc. New</t>
-        </is>
-      </c>
-      <c r="C32" s="17" t="n">
-        <v>15</v>
-      </c>
-      <c r="D32" s="10" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="E32" s="10" t="inlineStr">
-        <is>
-          <t>real_estate</t>
-        </is>
-      </c>
-      <c r="F32" s="10" t="inlineStr">
-        <is>
-          <t>ground_lease</t>
-        </is>
-      </c>
-      <c r="G32" s="10" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-    </row>
-    <row r="33" ht="22" customHeight="1">
-      <c r="A33" s="6" t="inlineStr">
-        <is>
-          <t>LW</t>
-        </is>
-      </c>
-      <c r="B33" s="7" t="inlineStr">
-        <is>
-          <t>Lamb Weston Holdin</t>
-        </is>
-      </c>
-      <c r="C33" s="16" t="n">
-        <v>15</v>
-      </c>
-      <c r="D33" s="7" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="E33" s="7" t="inlineStr">
-        <is>
-          <t>any, real_estat</t>
-        </is>
-      </c>
-      <c r="F33" s="7" t="inlineStr">
-        <is>
-          <t>land_bank, equity_stake</t>
-        </is>
-      </c>
-      <c r="G33" s="7" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-    </row>
-    <row r="34" ht="22" customHeight="1">
-      <c r="A34" s="9" t="inlineStr">
-        <is>
-          <t>JELD</t>
-        </is>
-      </c>
-      <c r="B34" s="10" t="inlineStr">
-        <is>
-          <t>JELD-WEN Holding,</t>
-        </is>
-      </c>
-      <c r="C34" s="17" t="n">
-        <v>15</v>
-      </c>
-      <c r="D34" s="10" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="E34" s="10" t="inlineStr">
-        <is>
-          <t>any</t>
-        </is>
-      </c>
-      <c r="F34" s="10" t="inlineStr">
-        <is>
-          <t>pension_surplus</t>
-        </is>
-      </c>
-      <c r="G34" s="10" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-    </row>
-    <row r="35" ht="22" customHeight="1">
-      <c r="A35" s="6" t="inlineStr">
-        <is>
-          <t>BRID</t>
-        </is>
-      </c>
-      <c r="B35" s="7" t="inlineStr">
-        <is>
-          <t>Bridgford Foods Co</t>
-        </is>
-      </c>
-      <c r="C35" s="16" t="n">
-        <v>15</v>
-      </c>
-      <c r="D35" s="7" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="E35" s="7" t="inlineStr">
-        <is>
-          <t>any</t>
-        </is>
-      </c>
-      <c r="F35" s="7" t="inlineStr">
-        <is>
-          <t>pension_surplus</t>
-        </is>
-      </c>
-      <c r="G35" s="7" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-    </row>
-    <row r="36" ht="22" customHeight="1">
-      <c r="A36" s="9" t="inlineStr">
-        <is>
-          <t>HBB</t>
-        </is>
-      </c>
-      <c r="B36" s="10" t="inlineStr">
-        <is>
-          <t>Hamilton Beach Bra</t>
-        </is>
-      </c>
-      <c r="C36" s="17" t="n">
-        <v>15</v>
-      </c>
-      <c r="D36" s="10" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="E36" s="10" t="inlineStr">
-        <is>
-          <t>any</t>
-        </is>
-      </c>
-      <c r="F36" s="10" t="inlineStr">
-        <is>
-          <t>pension_surplus</t>
-        </is>
-      </c>
-      <c r="G36" s="10" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-    </row>
-    <row r="37" ht="22" customHeight="1">
-      <c r="A37" s="6" t="inlineStr">
-        <is>
-          <t>LXFR</t>
-        </is>
-      </c>
-      <c r="B37" s="7" t="inlineStr">
-        <is>
-          <t>Luxfer Holdings PL</t>
-        </is>
-      </c>
-      <c r="C37" s="16" t="n">
-        <v>15</v>
-      </c>
-      <c r="D37" s="7" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="E37" s="7" t="inlineStr">
-        <is>
-          <t>any</t>
-        </is>
-      </c>
-      <c r="F37" s="7" t="inlineStr">
-        <is>
-          <t>pension_surplus</t>
-        </is>
-      </c>
-      <c r="G37" s="7" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-    </row>
-    <row r="38" ht="22" customHeight="1">
-      <c r="A38" s="9" t="inlineStr">
-        <is>
-          <t>ATAI</t>
-        </is>
-      </c>
-      <c r="B38" s="10" t="inlineStr">
-        <is>
-          <t>AtaiBeckley Inc.</t>
-        </is>
-      </c>
-      <c r="C38" s="17" t="n">
-        <v>15</v>
-      </c>
-      <c r="D38" s="10" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="E38" s="10" t="inlineStr">
-        <is>
-          <t>any</t>
-        </is>
-      </c>
-      <c r="F38" s="10" t="inlineStr">
-        <is>
-          <t>cvr</t>
-        </is>
-      </c>
-      <c r="G38" s="10" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-    </row>
-    <row r="39" ht="22" customHeight="1">
-      <c r="A39" s="6" t="inlineStr">
-        <is>
-          <t>LSTA</t>
-        </is>
-      </c>
-      <c r="B39" s="7" t="inlineStr">
-        <is>
-          <t>Lisata Therapeutic</t>
-        </is>
-      </c>
-      <c r="C39" s="16" t="n">
-        <v>15</v>
-      </c>
-      <c r="D39" s="7" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="E39" s="7" t="inlineStr">
-        <is>
-          <t>any</t>
-        </is>
-      </c>
-      <c r="F39" s="7" t="inlineStr">
-        <is>
-          <t>cvr</t>
-        </is>
-      </c>
-      <c r="G39" s="7" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-    </row>
-    <row r="40" ht="22" customHeight="1">
-      <c r="A40" s="9" t="inlineStr">
-        <is>
-          <t>TBPH</t>
-        </is>
-      </c>
-      <c r="B40" s="10" t="inlineStr">
-        <is>
-          <t>Theravance Biophar</t>
-        </is>
-      </c>
-      <c r="C40" s="17" t="n">
-        <v>15</v>
-      </c>
-      <c r="D40" s="10" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="E40" s="10" t="inlineStr">
-        <is>
-          <t>any</t>
-        </is>
-      </c>
-      <c r="F40" s="10" t="inlineStr">
-        <is>
-          <t>cvr</t>
-        </is>
-      </c>
-      <c r="G40" s="10" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-    </row>
-    <row r="41" ht="22" customHeight="1">
-      <c r="A41" s="6" t="inlineStr">
-        <is>
-          <t>ASRT</t>
-        </is>
-      </c>
-      <c r="B41" s="7" t="inlineStr">
-        <is>
-          <t>Assertio Holdings,</t>
-        </is>
-      </c>
-      <c r="C41" s="16" t="n">
-        <v>15</v>
-      </c>
-      <c r="D41" s="7" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="E41" s="7" t="inlineStr">
-        <is>
-          <t>any</t>
-        </is>
-      </c>
-      <c r="F41" s="7" t="inlineStr">
-        <is>
-          <t>cvr</t>
-        </is>
-      </c>
-      <c r="G41" s="7" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-    </row>
-    <row r="42" ht="22" customHeight="1">
-      <c r="A42" s="9" t="inlineStr">
-        <is>
-          <t>RNAC</t>
-        </is>
-      </c>
-      <c r="B42" s="10" t="inlineStr">
-        <is>
-          <t>Cartesian Therapeu</t>
-        </is>
-      </c>
-      <c r="C42" s="17" t="n">
-        <v>15</v>
-      </c>
-      <c r="D42" s="10" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="E42" s="10" t="inlineStr">
-        <is>
-          <t>any</t>
-        </is>
-      </c>
-      <c r="F42" s="10" t="inlineStr">
-        <is>
-          <t>cvr</t>
-        </is>
-      </c>
-      <c r="G42" s="10" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-    </row>
-    <row r="43" ht="22" customHeight="1">
-      <c r="A43" s="6" t="inlineStr">
-        <is>
-          <t>ASTS</t>
-        </is>
-      </c>
-      <c r="B43" s="7" t="inlineStr">
-        <is>
-          <t>AST SpaceMobile, I</t>
-        </is>
-      </c>
-      <c r="C43" s="16" t="n">
-        <v>14</v>
-      </c>
-      <c r="D43" s="7" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="E43" s="7" t="inlineStr">
-        <is>
-          <t>telecom</t>
-        </is>
-      </c>
-      <c r="F43" s="7" t="inlineStr">
-        <is>
-          <t>spectrum</t>
-        </is>
-      </c>
-      <c r="G43" s="7" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-    </row>
-    <row r="44" ht="22" customHeight="1">
-      <c r="A44" s="9" t="inlineStr">
-        <is>
-          <t>IRDM</t>
-        </is>
-      </c>
-      <c r="B44" s="10" t="inlineStr">
-        <is>
-          <t>IRDM</t>
-        </is>
-      </c>
-      <c r="C44" s="17" t="n">
-        <v>14</v>
-      </c>
-      <c r="D44" s="10" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="E44" s="10" t="inlineStr">
-        <is>
-          <t>telecom</t>
-        </is>
-      </c>
-      <c r="F44" s="10" t="inlineStr">
-        <is>
-          <t>spectrum</t>
-        </is>
-      </c>
-      <c r="G44" s="10" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-    </row>
-    <row r="46" ht="28" customHeight="1">
-      <c r="A46" s="11" t="inlineStr">
-        <is>
-          <t>370 hidden-asset / incentivised-realisation setups across all industries (top 40). The thesis (E.W. Scripps / SSP archetype): a credit agreement that MANDATES asset-disposition proceeds be applied to debt paydown creates a structural, incentivised path to value realisation — on a small equity base, selling a hidden asset retires senior debt and lifts the residual stub roughly one-for-one. The high-value setup is the CONJUNCTION: a rare valuable asset + the mandatory-prepayment sweep + a small levered equity base. The asset taxonomy spans every sector — telecom (spectrum, fiber, towers), resources/energy (water/mineral rights, reserves, royalty acres, timberland, carbon), real estate (land bank, ground leases, air rights), financials (MSRs, securities), IP/healthcare (royalty streams, patents, milestones, CVRs), holdco sum-of-parts (equity stakes), and cross-industry off-balance-sheet value (NOLs, deferred tax assets, pension surplus, litigation/insurance recoveries). 'watch' names are hand-curated with catalyst triggers and counter-risks (hidden_asset_watch.json); the rest are mined from EDGAR. Source: credit_agreement_mine.py.</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="3">
-    <mergeCell ref="A2:G2"/>
-    <mergeCell ref="A1:G1"/>
-    <mergeCell ref="A46:G46"/>
   </mergeCells>
   <printOptions horizontalCentered="0"/>
   <pageMargins left="0.5" right="0.5" top="0.6" bottom="0.6" header="0.5" footer="0.5"/>
@@ -16464,6 +15310,1501 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
+  <dimension ref="A1:G46"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="9" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="8" customWidth="1" min="3" max="3"/>
+    <col width="9" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
+    <col width="26" customWidth="1" min="6" max="6"/>
+    <col width="30" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="26" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Hidden-Asset / Incentivised Value Realisation</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="18" customHeight="1">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Under-recognised assets across ALL industries (spectrum, water/mineral/royalty rights, real estate, NOLs, equity stakes, pension surplus, royalty streams) inside a small levered equity base, where a credit agreement sweeps disposition proceeds to debt paydown — so realising the asset is mechanically stub-accretive</t>
+        </is>
+      </c>
+      <c r="B2" s="3" t="n"/>
+      <c r="C2" s="3" t="n"/>
+      <c r="D2" s="3" t="n"/>
+      <c r="E2" s="3" t="n"/>
+      <c r="F2" s="3" t="n"/>
+      <c r="G2" s="3" t="n"/>
+    </row>
+    <row r="3" ht="8" customHeight="1"/>
+    <row r="4" ht="18" customHeight="1">
+      <c r="A4" s="15" t="inlineStr">
+        <is>
+          <t>Ticker</t>
+        </is>
+      </c>
+      <c r="B4" s="15" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="C4" s="4" t="inlineStr">
+        <is>
+          <t>Score</t>
+        </is>
+      </c>
+      <c r="D4" s="4" t="inlineStr">
+        <is>
+          <t>Mand. prepay</t>
+        </is>
+      </c>
+      <c r="E4" s="15" t="inlineStr">
+        <is>
+          <t>Industry</t>
+        </is>
+      </c>
+      <c r="F4" s="4" t="inlineStr">
+        <is>
+          <t>Asset types</t>
+        </is>
+      </c>
+      <c r="G4" s="4" t="inlineStr">
+        <is>
+          <t>Thesis / feature</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="22" customHeight="1">
+      <c r="A5" s="6" t="inlineStr">
+        <is>
+          <t>SSP</t>
+        </is>
+      </c>
+      <c r="B5" s="7" t="inlineStr">
+        <is>
+          <t>SSP</t>
+        </is>
+      </c>
+      <c r="C5" s="16" t="n">
+        <v>36</v>
+      </c>
+      <c r="D5" s="7" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="E5" s="7" t="inlineStr">
+        <is>
+          <t>media, telecom</t>
+        </is>
+      </c>
+      <c r="F5" s="7" t="inlineStr">
+        <is>
+          <t>spectrum, broadcast_licenc</t>
+        </is>
+      </c>
+      <c r="G5" s="7" t="inlineStr">
+        <is>
+          <t>April 2026 credit agreement an</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="22" customHeight="1">
+      <c r="A6" s="9" t="inlineStr">
+        <is>
+          <t>EVC</t>
+        </is>
+      </c>
+      <c r="B6" s="10" t="inlineStr">
+        <is>
+          <t>Entravision Commun</t>
+        </is>
+      </c>
+      <c r="C6" s="17" t="n">
+        <v>30</v>
+      </c>
+      <c r="D6" s="10" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="E6" s="10" t="inlineStr">
+        <is>
+          <t>media, telecom</t>
+        </is>
+      </c>
+      <c r="F6" s="10" t="inlineStr">
+        <is>
+          <t>spectrum, broadcast_licenc</t>
+        </is>
+      </c>
+      <c r="G6" s="10" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="22" customHeight="1">
+      <c r="A7" s="6" t="inlineStr">
+        <is>
+          <t>LMNR</t>
+        </is>
+      </c>
+      <c r="B7" s="7" t="inlineStr">
+        <is>
+          <t>Limoneira Co</t>
+        </is>
+      </c>
+      <c r="C7" s="16" t="n">
+        <v>28</v>
+      </c>
+      <c r="D7" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="E7" s="7" t="inlineStr">
+        <is>
+          <t>real_estate, re</t>
+        </is>
+      </c>
+      <c r="F7" s="7" t="inlineStr">
+        <is>
+          <t>water_rights, air_rights</t>
+        </is>
+      </c>
+      <c r="G7" s="7" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="22" customHeight="1">
+      <c r="A8" s="9" t="inlineStr">
+        <is>
+          <t>MDIA</t>
+        </is>
+      </c>
+      <c r="B8" s="10" t="inlineStr">
+        <is>
+          <t>Mediaco Holding In</t>
+        </is>
+      </c>
+      <c r="C8" s="17" t="n">
+        <v>26</v>
+      </c>
+      <c r="D8" s="10" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="E8" s="10" t="inlineStr">
+        <is>
+          <t>media, telecom</t>
+        </is>
+      </c>
+      <c r="F8" s="10" t="inlineStr">
+        <is>
+          <t>broadcast_licences, fcc_li</t>
+        </is>
+      </c>
+      <c r="G8" s="10" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="22" customHeight="1">
+      <c r="A9" s="6" t="inlineStr">
+        <is>
+          <t>SBGI</t>
+        </is>
+      </c>
+      <c r="B9" s="7" t="inlineStr">
+        <is>
+          <t>Sinclair, Inc.</t>
+        </is>
+      </c>
+      <c r="C9" s="16" t="n">
+        <v>26</v>
+      </c>
+      <c r="D9" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="E9" s="7" t="inlineStr">
+        <is>
+          <t>media, telecom</t>
+        </is>
+      </c>
+      <c r="F9" s="7" t="inlineStr">
+        <is>
+          <t>broadcast_licences, fcc_li</t>
+        </is>
+      </c>
+      <c r="G9" s="7" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="22" customHeight="1">
+      <c r="A10" s="9" t="inlineStr">
+        <is>
+          <t>SNDA</t>
+        </is>
+      </c>
+      <c r="B10" s="10" t="inlineStr">
+        <is>
+          <t>Sonida Senior Livi</t>
+        </is>
+      </c>
+      <c r="C10" s="17" t="n">
+        <v>22</v>
+      </c>
+      <c r="D10" s="10" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="E10" s="10" t="inlineStr">
+        <is>
+          <t>holdco, real_es</t>
+        </is>
+      </c>
+      <c r="F10" s="10" t="inlineStr">
+        <is>
+          <t>air_rights, minority_stake</t>
+        </is>
+      </c>
+      <c r="G10" s="10" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="22" customHeight="1">
+      <c r="A11" s="6" t="inlineStr">
+        <is>
+          <t>SGA</t>
+        </is>
+      </c>
+      <c r="B11" s="7" t="inlineStr">
+        <is>
+          <t>SGA</t>
+        </is>
+      </c>
+      <c r="C11" s="16" t="n">
+        <v>20</v>
+      </c>
+      <c r="D11" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="E11" s="7" t="inlineStr">
+        <is>
+          <t>media, telecom</t>
+        </is>
+      </c>
+      <c r="F11" s="7" t="inlineStr">
+        <is>
+          <t>broadcast_licences, fcc_li</t>
+        </is>
+      </c>
+      <c r="G11" s="7" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="22" customHeight="1">
+      <c r="A12" s="9" t="inlineStr">
+        <is>
+          <t>BBGI</t>
+        </is>
+      </c>
+      <c r="B12" s="10" t="inlineStr">
+        <is>
+          <t>BBGI</t>
+        </is>
+      </c>
+      <c r="C12" s="17" t="n">
+        <v>20</v>
+      </c>
+      <c r="D12" s="10" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="E12" s="10" t="inlineStr">
+        <is>
+          <t>media, telecom</t>
+        </is>
+      </c>
+      <c r="F12" s="10" t="inlineStr">
+        <is>
+          <t>broadcast_licences, fcc_li</t>
+        </is>
+      </c>
+      <c r="G12" s="10" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="22" customHeight="1">
+      <c r="A13" s="6" t="inlineStr">
+        <is>
+          <t>PSKY</t>
+        </is>
+      </c>
+      <c r="B13" s="7" t="inlineStr">
+        <is>
+          <t>PSKY</t>
+        </is>
+      </c>
+      <c r="C13" s="16" t="n">
+        <v>20</v>
+      </c>
+      <c r="D13" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="E13" s="7" t="inlineStr">
+        <is>
+          <t>media, telecom</t>
+        </is>
+      </c>
+      <c r="F13" s="7" t="inlineStr">
+        <is>
+          <t>broadcast_licences, fcc_li</t>
+        </is>
+      </c>
+      <c r="G13" s="7" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="22" customHeight="1">
+      <c r="A14" s="9" t="inlineStr">
+        <is>
+          <t>TSQ</t>
+        </is>
+      </c>
+      <c r="B14" s="10" t="inlineStr">
+        <is>
+          <t>TSQ</t>
+        </is>
+      </c>
+      <c r="C14" s="17" t="n">
+        <v>20</v>
+      </c>
+      <c r="D14" s="10" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="E14" s="10" t="inlineStr">
+        <is>
+          <t>media, telecom</t>
+        </is>
+      </c>
+      <c r="F14" s="10" t="inlineStr">
+        <is>
+          <t>broadcast_licences, fcc_li</t>
+        </is>
+      </c>
+      <c r="G14" s="10" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="22" customHeight="1">
+      <c r="A15" s="6" t="inlineStr">
+        <is>
+          <t>WBD</t>
+        </is>
+      </c>
+      <c r="B15" s="7" t="inlineStr">
+        <is>
+          <t>Warner Bros. Disco</t>
+        </is>
+      </c>
+      <c r="C15" s="16" t="n">
+        <v>20</v>
+      </c>
+      <c r="D15" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="E15" s="7" t="inlineStr">
+        <is>
+          <t>media, telecom</t>
+        </is>
+      </c>
+      <c r="F15" s="7" t="inlineStr">
+        <is>
+          <t>broadcast_licences, fcc_li</t>
+        </is>
+      </c>
+      <c r="G15" s="7" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="22" customHeight="1">
+      <c r="A16" s="9" t="inlineStr">
+        <is>
+          <t>NXST</t>
+        </is>
+      </c>
+      <c r="B16" s="10" t="inlineStr">
+        <is>
+          <t>Nexstar Media Grou</t>
+        </is>
+      </c>
+      <c r="C16" s="17" t="n">
+        <v>20</v>
+      </c>
+      <c r="D16" s="10" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="E16" s="10" t="inlineStr">
+        <is>
+          <t>media, telecom</t>
+        </is>
+      </c>
+      <c r="F16" s="10" t="inlineStr">
+        <is>
+          <t>broadcast_licences, fcc_li</t>
+        </is>
+      </c>
+      <c r="G16" s="10" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="22" customHeight="1">
+      <c r="A17" s="6" t="inlineStr">
+        <is>
+          <t>BTQ</t>
+        </is>
+      </c>
+      <c r="B17" s="7" t="inlineStr">
+        <is>
+          <t>BTQ</t>
+        </is>
+      </c>
+      <c r="C17" s="16" t="n">
+        <v>18</v>
+      </c>
+      <c r="D17" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="E17" s="7" t="inlineStr">
+        <is>
+          <t>holdco, tech, t</t>
+        </is>
+      </c>
+      <c r="F17" s="7" t="inlineStr">
+        <is>
+          <t>data_center, patents, stra</t>
+        </is>
+      </c>
+      <c r="G17" s="7" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="22" customHeight="1">
+      <c r="A18" s="9" t="inlineStr">
+        <is>
+          <t>LOGC</t>
+        </is>
+      </c>
+      <c r="B18" s="10" t="inlineStr">
+        <is>
+          <t>LOGC</t>
+        </is>
+      </c>
+      <c r="C18" s="17" t="n">
+        <v>18</v>
+      </c>
+      <c r="D18" s="10" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="E18" s="10" t="inlineStr">
+        <is>
+          <t>any, resources</t>
+        </is>
+      </c>
+      <c r="F18" s="10" t="inlineStr">
+        <is>
+          <t>mineral_rights, nol</t>
+        </is>
+      </c>
+      <c r="G18" s="10" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="22" customHeight="1">
+      <c r="A19" s="6" t="inlineStr">
+        <is>
+          <t>PCYO</t>
+        </is>
+      </c>
+      <c r="B19" s="7" t="inlineStr">
+        <is>
+          <t>Pure Cycle Corpora</t>
+        </is>
+      </c>
+      <c r="C19" s="16" t="n">
+        <v>18</v>
+      </c>
+      <c r="D19" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="E19" s="7" t="inlineStr">
+        <is>
+          <t>resources</t>
+        </is>
+      </c>
+      <c r="F19" s="7" t="inlineStr">
+        <is>
+          <t>water_rights</t>
+        </is>
+      </c>
+      <c r="G19" s="7" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="22" customHeight="1">
+      <c r="A20" s="9" t="inlineStr">
+        <is>
+          <t>IPI</t>
+        </is>
+      </c>
+      <c r="B20" s="10" t="inlineStr">
+        <is>
+          <t>Intrepid Potash, I</t>
+        </is>
+      </c>
+      <c r="C20" s="17" t="n">
+        <v>18</v>
+      </c>
+      <c r="D20" s="10" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="E20" s="10" t="inlineStr">
+        <is>
+          <t>resources</t>
+        </is>
+      </c>
+      <c r="F20" s="10" t="inlineStr">
+        <is>
+          <t>water_rights</t>
+        </is>
+      </c>
+      <c r="G20" s="10" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="22" customHeight="1">
+      <c r="A21" s="6" t="inlineStr">
+        <is>
+          <t>CMP</t>
+        </is>
+      </c>
+      <c r="B21" s="7" t="inlineStr">
+        <is>
+          <t>Compass Minerals I</t>
+        </is>
+      </c>
+      <c r="C21" s="16" t="n">
+        <v>18</v>
+      </c>
+      <c r="D21" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="E21" s="7" t="inlineStr">
+        <is>
+          <t>resources</t>
+        </is>
+      </c>
+      <c r="F21" s="7" t="inlineStr">
+        <is>
+          <t>water_rights</t>
+        </is>
+      </c>
+      <c r="G21" s="7" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="22" customHeight="1">
+      <c r="A22" s="9" t="inlineStr">
+        <is>
+          <t>LODE</t>
+        </is>
+      </c>
+      <c r="B22" s="10" t="inlineStr">
+        <is>
+          <t>Comstock Inc.</t>
+        </is>
+      </c>
+      <c r="C22" s="17" t="n">
+        <v>18</v>
+      </c>
+      <c r="D22" s="10" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="E22" s="10" t="inlineStr">
+        <is>
+          <t>resources</t>
+        </is>
+      </c>
+      <c r="F22" s="10" t="inlineStr">
+        <is>
+          <t>water_rights</t>
+        </is>
+      </c>
+      <c r="G22" s="10" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="22" customHeight="1">
+      <c r="A23" s="6" t="inlineStr">
+        <is>
+          <t>VNOM</t>
+        </is>
+      </c>
+      <c r="B23" s="7" t="inlineStr">
+        <is>
+          <t>Viper Energy, Inc.</t>
+        </is>
+      </c>
+      <c r="C23" s="16" t="n">
+        <v>18</v>
+      </c>
+      <c r="D23" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="E23" s="7" t="inlineStr">
+        <is>
+          <t>energy, healthc</t>
+        </is>
+      </c>
+      <c r="F23" s="7" t="inlineStr">
+        <is>
+          <t>og_reserves, royalty_acres</t>
+        </is>
+      </c>
+      <c r="G23" s="7" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="22" customHeight="1">
+      <c r="A24" s="9" t="inlineStr">
+        <is>
+          <t>KRP</t>
+        </is>
+      </c>
+      <c r="B24" s="10" t="inlineStr">
+        <is>
+          <t>Kimbell Royalty Pa</t>
+        </is>
+      </c>
+      <c r="C24" s="17" t="n">
+        <v>18</v>
+      </c>
+      <c r="D24" s="10" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="E24" s="10" t="inlineStr">
+        <is>
+          <t>energy</t>
+        </is>
+      </c>
+      <c r="F24" s="10" t="inlineStr">
+        <is>
+          <t>royalty_acres</t>
+        </is>
+      </c>
+      <c r="G24" s="10" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="22" customHeight="1">
+      <c r="A25" s="6" t="inlineStr">
+        <is>
+          <t>SATS</t>
+        </is>
+      </c>
+      <c r="B25" s="7" t="inlineStr">
+        <is>
+          <t>EchoStar Corporati</t>
+        </is>
+      </c>
+      <c r="C25" s="16" t="n">
+        <v>17</v>
+      </c>
+      <c r="D25" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="E25" s="7" t="inlineStr">
+        <is>
+          <t>telecom</t>
+        </is>
+      </c>
+      <c r="F25" s="7" t="inlineStr">
+        <is>
+          <t>spectrum, fcc_licences</t>
+        </is>
+      </c>
+      <c r="G25" s="7" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="22" customHeight="1">
+      <c r="A26" s="9" t="inlineStr">
+        <is>
+          <t>TILE</t>
+        </is>
+      </c>
+      <c r="B26" s="10" t="inlineStr">
+        <is>
+          <t>Interface, Inc.</t>
+        </is>
+      </c>
+      <c r="C26" s="17" t="n">
+        <v>17</v>
+      </c>
+      <c r="D26" s="10" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="E26" s="10" t="inlineStr">
+        <is>
+          <t>any</t>
+        </is>
+      </c>
+      <c r="F26" s="10" t="inlineStr">
+        <is>
+          <t>pension_surplus, insurance</t>
+        </is>
+      </c>
+      <c r="G26" s="10" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="22" customHeight="1">
+      <c r="A27" s="6" t="inlineStr">
+        <is>
+          <t>CCI</t>
+        </is>
+      </c>
+      <c r="B27" s="7" t="inlineStr">
+        <is>
+          <t>Crown Castle Inc.</t>
+        </is>
+      </c>
+      <c r="C27" s="16" t="n">
+        <v>16</v>
+      </c>
+      <c r="D27" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="E27" s="7" t="inlineStr">
+        <is>
+          <t>telecom</t>
+        </is>
+      </c>
+      <c r="F27" s="7" t="inlineStr">
+        <is>
+          <t>spectrum, towers</t>
+        </is>
+      </c>
+      <c r="G27" s="7" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="22" customHeight="1">
+      <c r="A28" s="9" t="inlineStr">
+        <is>
+          <t>CTGO</t>
+        </is>
+      </c>
+      <c r="B28" s="10" t="inlineStr">
+        <is>
+          <t>CTGO</t>
+        </is>
+      </c>
+      <c r="C28" s="17" t="n">
+        <v>16</v>
+      </c>
+      <c r="D28" s="10" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="E28" s="10" t="inlineStr">
+        <is>
+          <t>healthcare, res</t>
+        </is>
+      </c>
+      <c r="F28" s="10" t="inlineStr">
+        <is>
+          <t>mineral_rights, milestones</t>
+        </is>
+      </c>
+      <c r="G28" s="10" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="22" customHeight="1">
+      <c r="A29" s="6" t="inlineStr">
+        <is>
+          <t>WULF</t>
+        </is>
+      </c>
+      <c r="B29" s="7" t="inlineStr">
+        <is>
+          <t>TeraWulf Inc.</t>
+        </is>
+      </c>
+      <c r="C29" s="16" t="n">
+        <v>15</v>
+      </c>
+      <c r="D29" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="E29" s="7" t="inlineStr">
+        <is>
+          <t>real_estate, te</t>
+        </is>
+      </c>
+      <c r="F29" s="7" t="inlineStr">
+        <is>
+          <t>data_center, ground_lease</t>
+        </is>
+      </c>
+      <c r="G29" s="7" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="22" customHeight="1">
+      <c r="A30" s="9" t="inlineStr">
+        <is>
+          <t>NI</t>
+        </is>
+      </c>
+      <c r="B30" s="10" t="inlineStr">
+        <is>
+          <t>NiSource Inc</t>
+        </is>
+      </c>
+      <c r="C30" s="17" t="n">
+        <v>15</v>
+      </c>
+      <c r="D30" s="10" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="E30" s="10" t="inlineStr">
+        <is>
+          <t>any, telecom</t>
+        </is>
+      </c>
+      <c r="F30" s="10" t="inlineStr">
+        <is>
+          <t>data_center, pension_surpl</t>
+        </is>
+      </c>
+      <c r="G30" s="10" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="22" customHeight="1">
+      <c r="A31" s="6" t="inlineStr">
+        <is>
+          <t>NOG</t>
+        </is>
+      </c>
+      <c r="B31" s="7" t="inlineStr">
+        <is>
+          <t>Northern Oil and G</t>
+        </is>
+      </c>
+      <c r="C31" s="16" t="n">
+        <v>15</v>
+      </c>
+      <c r="D31" s="7" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="E31" s="7" t="inlineStr">
+        <is>
+          <t>energy</t>
+        </is>
+      </c>
+      <c r="F31" s="7" t="inlineStr">
+        <is>
+          <t>royalty_acres</t>
+        </is>
+      </c>
+      <c r="G31" s="7" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="22" customHeight="1">
+      <c r="A32" s="9" t="inlineStr">
+        <is>
+          <t>SAFE</t>
+        </is>
+      </c>
+      <c r="B32" s="10" t="inlineStr">
+        <is>
+          <t>Safehold Inc. New</t>
+        </is>
+      </c>
+      <c r="C32" s="17" t="n">
+        <v>15</v>
+      </c>
+      <c r="D32" s="10" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="E32" s="10" t="inlineStr">
+        <is>
+          <t>real_estate</t>
+        </is>
+      </c>
+      <c r="F32" s="10" t="inlineStr">
+        <is>
+          <t>ground_lease</t>
+        </is>
+      </c>
+      <c r="G32" s="10" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="22" customHeight="1">
+      <c r="A33" s="6" t="inlineStr">
+        <is>
+          <t>LW</t>
+        </is>
+      </c>
+      <c r="B33" s="7" t="inlineStr">
+        <is>
+          <t>Lamb Weston Holdin</t>
+        </is>
+      </c>
+      <c r="C33" s="16" t="n">
+        <v>15</v>
+      </c>
+      <c r="D33" s="7" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="E33" s="7" t="inlineStr">
+        <is>
+          <t>any, real_estat</t>
+        </is>
+      </c>
+      <c r="F33" s="7" t="inlineStr">
+        <is>
+          <t>land_bank, equity_stake</t>
+        </is>
+      </c>
+      <c r="G33" s="7" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="22" customHeight="1">
+      <c r="A34" s="9" t="inlineStr">
+        <is>
+          <t>JELD</t>
+        </is>
+      </c>
+      <c r="B34" s="10" t="inlineStr">
+        <is>
+          <t>JELD-WEN Holding,</t>
+        </is>
+      </c>
+      <c r="C34" s="17" t="n">
+        <v>15</v>
+      </c>
+      <c r="D34" s="10" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="E34" s="10" t="inlineStr">
+        <is>
+          <t>any</t>
+        </is>
+      </c>
+      <c r="F34" s="10" t="inlineStr">
+        <is>
+          <t>pension_surplus</t>
+        </is>
+      </c>
+      <c r="G34" s="10" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="22" customHeight="1">
+      <c r="A35" s="6" t="inlineStr">
+        <is>
+          <t>BRID</t>
+        </is>
+      </c>
+      <c r="B35" s="7" t="inlineStr">
+        <is>
+          <t>Bridgford Foods Co</t>
+        </is>
+      </c>
+      <c r="C35" s="16" t="n">
+        <v>15</v>
+      </c>
+      <c r="D35" s="7" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="E35" s="7" t="inlineStr">
+        <is>
+          <t>any</t>
+        </is>
+      </c>
+      <c r="F35" s="7" t="inlineStr">
+        <is>
+          <t>pension_surplus</t>
+        </is>
+      </c>
+      <c r="G35" s="7" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="22" customHeight="1">
+      <c r="A36" s="9" t="inlineStr">
+        <is>
+          <t>HBB</t>
+        </is>
+      </c>
+      <c r="B36" s="10" t="inlineStr">
+        <is>
+          <t>Hamilton Beach Bra</t>
+        </is>
+      </c>
+      <c r="C36" s="17" t="n">
+        <v>15</v>
+      </c>
+      <c r="D36" s="10" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="E36" s="10" t="inlineStr">
+        <is>
+          <t>any</t>
+        </is>
+      </c>
+      <c r="F36" s="10" t="inlineStr">
+        <is>
+          <t>pension_surplus</t>
+        </is>
+      </c>
+      <c r="G36" s="10" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="22" customHeight="1">
+      <c r="A37" s="6" t="inlineStr">
+        <is>
+          <t>LXFR</t>
+        </is>
+      </c>
+      <c r="B37" s="7" t="inlineStr">
+        <is>
+          <t>Luxfer Holdings PL</t>
+        </is>
+      </c>
+      <c r="C37" s="16" t="n">
+        <v>15</v>
+      </c>
+      <c r="D37" s="7" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="E37" s="7" t="inlineStr">
+        <is>
+          <t>any</t>
+        </is>
+      </c>
+      <c r="F37" s="7" t="inlineStr">
+        <is>
+          <t>pension_surplus</t>
+        </is>
+      </c>
+      <c r="G37" s="7" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="22" customHeight="1">
+      <c r="A38" s="9" t="inlineStr">
+        <is>
+          <t>ATAI</t>
+        </is>
+      </c>
+      <c r="B38" s="10" t="inlineStr">
+        <is>
+          <t>AtaiBeckley Inc.</t>
+        </is>
+      </c>
+      <c r="C38" s="17" t="n">
+        <v>15</v>
+      </c>
+      <c r="D38" s="10" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="E38" s="10" t="inlineStr">
+        <is>
+          <t>any</t>
+        </is>
+      </c>
+      <c r="F38" s="10" t="inlineStr">
+        <is>
+          <t>cvr</t>
+        </is>
+      </c>
+      <c r="G38" s="10" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="22" customHeight="1">
+      <c r="A39" s="6" t="inlineStr">
+        <is>
+          <t>LSTA</t>
+        </is>
+      </c>
+      <c r="B39" s="7" t="inlineStr">
+        <is>
+          <t>Lisata Therapeutic</t>
+        </is>
+      </c>
+      <c r="C39" s="16" t="n">
+        <v>15</v>
+      </c>
+      <c r="D39" s="7" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="E39" s="7" t="inlineStr">
+        <is>
+          <t>any</t>
+        </is>
+      </c>
+      <c r="F39" s="7" t="inlineStr">
+        <is>
+          <t>cvr</t>
+        </is>
+      </c>
+      <c r="G39" s="7" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="22" customHeight="1">
+      <c r="A40" s="9" t="inlineStr">
+        <is>
+          <t>TBPH</t>
+        </is>
+      </c>
+      <c r="B40" s="10" t="inlineStr">
+        <is>
+          <t>Theravance Biophar</t>
+        </is>
+      </c>
+      <c r="C40" s="17" t="n">
+        <v>15</v>
+      </c>
+      <c r="D40" s="10" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="E40" s="10" t="inlineStr">
+        <is>
+          <t>any</t>
+        </is>
+      </c>
+      <c r="F40" s="10" t="inlineStr">
+        <is>
+          <t>cvr</t>
+        </is>
+      </c>
+      <c r="G40" s="10" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="22" customHeight="1">
+      <c r="A41" s="6" t="inlineStr">
+        <is>
+          <t>ASRT</t>
+        </is>
+      </c>
+      <c r="B41" s="7" t="inlineStr">
+        <is>
+          <t>Assertio Holdings,</t>
+        </is>
+      </c>
+      <c r="C41" s="16" t="n">
+        <v>15</v>
+      </c>
+      <c r="D41" s="7" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="E41" s="7" t="inlineStr">
+        <is>
+          <t>any</t>
+        </is>
+      </c>
+      <c r="F41" s="7" t="inlineStr">
+        <is>
+          <t>cvr</t>
+        </is>
+      </c>
+      <c r="G41" s="7" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="22" customHeight="1">
+      <c r="A42" s="9" t="inlineStr">
+        <is>
+          <t>RNAC</t>
+        </is>
+      </c>
+      <c r="B42" s="10" t="inlineStr">
+        <is>
+          <t>Cartesian Therapeu</t>
+        </is>
+      </c>
+      <c r="C42" s="17" t="n">
+        <v>15</v>
+      </c>
+      <c r="D42" s="10" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="E42" s="10" t="inlineStr">
+        <is>
+          <t>any</t>
+        </is>
+      </c>
+      <c r="F42" s="10" t="inlineStr">
+        <is>
+          <t>cvr</t>
+        </is>
+      </c>
+      <c r="G42" s="10" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="22" customHeight="1">
+      <c r="A43" s="6" t="inlineStr">
+        <is>
+          <t>ASTS</t>
+        </is>
+      </c>
+      <c r="B43" s="7" t="inlineStr">
+        <is>
+          <t>AST SpaceMobile, I</t>
+        </is>
+      </c>
+      <c r="C43" s="16" t="n">
+        <v>14</v>
+      </c>
+      <c r="D43" s="7" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="E43" s="7" t="inlineStr">
+        <is>
+          <t>telecom</t>
+        </is>
+      </c>
+      <c r="F43" s="7" t="inlineStr">
+        <is>
+          <t>spectrum</t>
+        </is>
+      </c>
+      <c r="G43" s="7" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+    </row>
+    <row r="44" ht="22" customHeight="1">
+      <c r="A44" s="9" t="inlineStr">
+        <is>
+          <t>IRDM</t>
+        </is>
+      </c>
+      <c r="B44" s="10" t="inlineStr">
+        <is>
+          <t>IRDM</t>
+        </is>
+      </c>
+      <c r="C44" s="17" t="n">
+        <v>14</v>
+      </c>
+      <c r="D44" s="10" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="E44" s="10" t="inlineStr">
+        <is>
+          <t>telecom</t>
+        </is>
+      </c>
+      <c r="F44" s="10" t="inlineStr">
+        <is>
+          <t>spectrum</t>
+        </is>
+      </c>
+      <c r="G44" s="10" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+    </row>
+    <row r="46" ht="28" customHeight="1">
+      <c r="A46" s="11" t="inlineStr">
+        <is>
+          <t>370 hidden-asset / incentivised-realisation setups across all industries (top 40). The thesis (E.W. Scripps / SSP archetype): a credit agreement that MANDATES asset-disposition proceeds be applied to debt paydown creates a structural, incentivised path to value realisation — on a small equity base, selling a hidden asset retires senior debt and lifts the residual stub roughly one-for-one. The high-value setup is the CONJUNCTION: a rare valuable asset + the mandatory-prepayment sweep + a small levered equity base. The asset taxonomy spans every sector — telecom (spectrum, fiber, towers), resources/energy (water/mineral rights, reserves, royalty acres, timberland, carbon), real estate (land bank, ground leases, air rights), financials (MSRs, securities), IP/healthcare (royalty streams, patents, milestones, CVRs), holdco sum-of-parts (equity stakes), and cross-industry off-balance-sheet value (NOLs, deferred tax assets, pension surplus, litigation/insurance recoveries). 'watch' names are hand-curated with catalyst triggers and counter-risks (hidden_asset_watch.json); the rest are mined from EDGAR. Source: credit_agreement_mine.py.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="3">
+    <mergeCell ref="A2:G2"/>
+    <mergeCell ref="A1:G1"/>
+    <mergeCell ref="A46:G46"/>
+  </mergeCells>
+  <printOptions horizontalCentered="0"/>
+  <pageMargins left="0.5" right="0.5" top="0.6" bottom="0.6" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
   <dimension ref="A1:G8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -16623,7 +16964,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -17747,7 +18088,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -19463,7 +19804,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -21721,7 +22062,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -23517,7 +23858,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -26077,7 +26418,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -26679,7 +27020,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet28.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -27491,7 +27832,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet28.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet29.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>

--- a/MOST_ASYMMETRIC.xlsx
+++ b/MOST_ASYMMETRIC.xlsx
@@ -166,7 +166,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="28">
+  <cellXfs count="27">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
@@ -223,9 +223,6 @@
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
     <xf numFmtId="165" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
@@ -12294,12 +12291,12 @@
     <row r="7" ht="22" customHeight="1">
       <c r="A7" s="6" t="inlineStr">
         <is>
-          <t>GPK</t>
+          <t>HFFG</t>
         </is>
       </c>
       <c r="B7" s="7" t="inlineStr">
         <is>
-          <t>Graphic Packaging Holdin</t>
+          <t>HF Foods Group Inc.</t>
         </is>
       </c>
       <c r="C7" s="16" t="n">
@@ -12357,12 +12354,12 @@
     <row r="8" ht="22" customHeight="1">
       <c r="A8" s="9" t="inlineStr">
         <is>
-          <t>HFFG</t>
+          <t>GPK</t>
         </is>
       </c>
       <c r="B8" s="10" t="inlineStr">
         <is>
-          <t>HF Foods Group Inc.</t>
+          <t>Graphic Packaging Holdin</t>
         </is>
       </c>
       <c r="C8" s="17" t="n">
@@ -12609,12 +12606,12 @@
     <row r="12" ht="22" customHeight="1">
       <c r="A12" s="9" t="inlineStr">
         <is>
-          <t>BCIC</t>
+          <t>NSP</t>
         </is>
       </c>
       <c r="B12" s="10" t="inlineStr">
         <is>
-          <t>BCP Investment Corporati</t>
+          <t>Insperity, Inc.</t>
         </is>
       </c>
       <c r="C12" s="17" t="n">
@@ -12672,12 +12669,12 @@
     <row r="13" ht="22" customHeight="1">
       <c r="A13" s="6" t="inlineStr">
         <is>
-          <t>PTLO</t>
+          <t>BCIC</t>
         </is>
       </c>
       <c r="B13" s="7" t="inlineStr">
         <is>
-          <t>Portillo's Inc.</t>
+          <t>BCP Investment Corporati</t>
         </is>
       </c>
       <c r="C13" s="16" t="n">
@@ -12735,12 +12732,12 @@
     <row r="14" ht="22" customHeight="1">
       <c r="A14" s="9" t="inlineStr">
         <is>
-          <t>NSP</t>
+          <t>PTLO</t>
         </is>
       </c>
       <c r="B14" s="10" t="inlineStr">
         <is>
-          <t>Insperity, Inc.</t>
+          <t>Portillo's Inc.</t>
         </is>
       </c>
       <c r="C14" s="17" t="n">
@@ -12798,12 +12795,12 @@
     <row r="15" ht="22" customHeight="1">
       <c r="A15" s="6" t="inlineStr">
         <is>
-          <t>PAL</t>
+          <t>VSNT</t>
         </is>
       </c>
       <c r="B15" s="7" t="inlineStr">
         <is>
-          <t>Proficient Auto Logistic</t>
+          <t>Versant Media Group, Inc</t>
         </is>
       </c>
       <c r="C15" s="16" t="n">
@@ -12861,12 +12858,12 @@
     <row r="16" ht="22" customHeight="1">
       <c r="A16" s="9" t="inlineStr">
         <is>
-          <t>VSNT</t>
+          <t>LCNB</t>
         </is>
       </c>
       <c r="B16" s="10" t="inlineStr">
         <is>
-          <t>Versant Media Group, Inc</t>
+          <t>LCNB Corporation</t>
         </is>
       </c>
       <c r="C16" s="17" t="n">
@@ -12924,12 +12921,12 @@
     <row r="17" ht="22" customHeight="1">
       <c r="A17" s="6" t="inlineStr">
         <is>
-          <t>LCNB</t>
+          <t>PAL</t>
         </is>
       </c>
       <c r="B17" s="7" t="inlineStr">
         <is>
-          <t>LCNB Corporation</t>
+          <t>Proficient Auto Logistic</t>
         </is>
       </c>
       <c r="C17" s="16" t="n">
@@ -14778,7 +14775,7 @@
       </c>
       <c r="E16" s="7" t="inlineStr">
         <is>
-          <t>13 layers firing | cons 10.676</t>
+          <t>13 layers firing | cons 10.698</t>
         </is>
       </c>
     </row>
@@ -14803,7 +14800,7 @@
       </c>
       <c r="E17" s="10" t="inlineStr">
         <is>
-          <t>11 layers firing | cons 10.208</t>
+          <t>11 layers firing | cons 10.412</t>
         </is>
       </c>
     </row>
@@ -14813,22 +14810,22 @@
       </c>
       <c r="B18" s="6" t="inlineStr">
         <is>
-          <t>CRM</t>
+          <t>GPK</t>
         </is>
       </c>
       <c r="C18" s="7" t="inlineStr">
         <is>
-          <t>Salesforce</t>
-        </is>
-      </c>
-      <c r="D18" s="7" t="inlineStr">
-        <is>
-          <t>Material 2-5%</t>
+          <t>GPK</t>
+        </is>
+      </c>
+      <c r="D18" s="6" t="inlineStr">
+        <is>
+          <t>Concentrated 5%+</t>
         </is>
       </c>
       <c r="E18" s="7" t="inlineStr">
         <is>
-          <t>PSU + buyback + recent 10b5-1 termination + F4 cluster</t>
+          <t>11 layers firing | cons 8.872</t>
         </is>
       </c>
     </row>
@@ -14838,22 +14835,22 @@
       </c>
       <c r="B19" s="9" t="inlineStr">
         <is>
-          <t>GPK</t>
+          <t>CRM</t>
         </is>
       </c>
       <c r="C19" s="10" t="inlineStr">
         <is>
-          <t>GPK</t>
-        </is>
-      </c>
-      <c r="D19" s="6" t="inlineStr">
-        <is>
-          <t>Concentrated 5%+</t>
+          <t>Salesforce</t>
+        </is>
+      </c>
+      <c r="D19" s="10" t="inlineStr">
+        <is>
+          <t>Material 2-5%</t>
         </is>
       </c>
       <c r="E19" s="10" t="inlineStr">
         <is>
-          <t>11 layers firing | cons 8.634</t>
+          <t>PSU + buyback + recent 10b5-1 termination + F4 cluster</t>
         </is>
       </c>
     </row>
@@ -14888,12 +14885,12 @@
       </c>
       <c r="B21" s="9" t="inlineStr">
         <is>
-          <t>POOL</t>
+          <t>WW</t>
         </is>
       </c>
       <c r="C21" s="10" t="inlineStr">
         <is>
-          <t>POOL</t>
+          <t>WW</t>
         </is>
       </c>
       <c r="D21" s="6" t="inlineStr">
@@ -14903,7 +14900,7 @@
       </c>
       <c r="E21" s="10" t="inlineStr">
         <is>
-          <t>11 layers firing | cons 7.424</t>
+          <t>10 layers firing | cons 8.756</t>
         </is>
       </c>
     </row>
@@ -14913,12 +14910,12 @@
       </c>
       <c r="B22" s="6" t="inlineStr">
         <is>
-          <t>WW</t>
+          <t>GO</t>
         </is>
       </c>
       <c r="C22" s="7" t="inlineStr">
         <is>
-          <t>WW</t>
+          <t>Grocery Outlet</t>
         </is>
       </c>
       <c r="D22" s="6" t="inlineStr">
@@ -14928,7 +14925,7 @@
       </c>
       <c r="E22" s="7" t="inlineStr">
         <is>
-          <t>10 layers firing | cons 8.76</t>
+          <t>Forward $ targets + Cohen-Malloy 6-buyer cluster</t>
         </is>
       </c>
     </row>
@@ -14938,12 +14935,12 @@
       </c>
       <c r="B23" s="9" t="inlineStr">
         <is>
-          <t>GO</t>
+          <t>FOUR</t>
         </is>
       </c>
       <c r="C23" s="10" t="inlineStr">
         <is>
-          <t>Grocery Outlet</t>
+          <t>FOUR</t>
         </is>
       </c>
       <c r="D23" s="6" t="inlineStr">
@@ -14953,7 +14950,7 @@
       </c>
       <c r="E23" s="10" t="inlineStr">
         <is>
-          <t>Forward $ targets + Cohen-Malloy 6-buyer cluster</t>
+          <t>10 layers firing | cons 8.106</t>
         </is>
       </c>
     </row>
@@ -14988,22 +14985,22 @@
       </c>
       <c r="B25" s="9" t="inlineStr">
         <is>
-          <t>DXC</t>
+          <t>LW</t>
         </is>
       </c>
       <c r="C25" s="10" t="inlineStr">
         <is>
-          <t>DXC Technology</t>
-        </is>
-      </c>
-      <c r="D25" s="6" t="inlineStr">
-        <is>
-          <t>Participation 1-2%</t>
+          <t>LW</t>
+        </is>
+      </c>
+      <c r="D25" s="10" t="inlineStr">
+        <is>
+          <t>Material 2-5%</t>
         </is>
       </c>
       <c r="E25" s="10" t="inlineStr">
         <is>
-          <t>PSU core 40 + buyback + recent-incentive 57% drawdown</t>
+          <t>10 layers firing | cons 7.834</t>
         </is>
       </c>
     </row>
@@ -15013,22 +15010,22 @@
       </c>
       <c r="B26" s="6" t="inlineStr">
         <is>
-          <t>LW</t>
+          <t>DXC</t>
         </is>
       </c>
       <c r="C26" s="7" t="inlineStr">
         <is>
-          <t>LW</t>
-        </is>
-      </c>
-      <c r="D26" s="7" t="inlineStr">
-        <is>
-          <t>Material 2-5%</t>
+          <t>DXC Technology</t>
+        </is>
+      </c>
+      <c r="D26" s="6" t="inlineStr">
+        <is>
+          <t>Participation 1-2%</t>
         </is>
       </c>
       <c r="E26" s="7" t="inlineStr">
         <is>
-          <t>10 layers firing | cons 7.74</t>
+          <t>PSU core 40 + buyback + recent-incentive 57% drawdown</t>
         </is>
       </c>
     </row>
@@ -15038,12 +15035,12 @@
       </c>
       <c r="B27" s="9" t="inlineStr">
         <is>
-          <t>FOUR</t>
+          <t>VRSK</t>
         </is>
       </c>
       <c r="C27" s="10" t="inlineStr">
         <is>
-          <t>FOUR</t>
+          <t>VRSK</t>
         </is>
       </c>
       <c r="D27" s="6" t="inlineStr">
@@ -15053,7 +15050,7 @@
       </c>
       <c r="E27" s="10" t="inlineStr">
         <is>
-          <t>10 layers firing | cons 7.716</t>
+          <t>10 layers firing | cons 7.466</t>
         </is>
       </c>
     </row>
@@ -15063,12 +15060,12 @@
       </c>
       <c r="B28" s="6" t="inlineStr">
         <is>
-          <t>ZTS</t>
+          <t>PAR</t>
         </is>
       </c>
       <c r="C28" s="7" t="inlineStr">
         <is>
-          <t>Zoetis</t>
+          <t>PAR</t>
         </is>
       </c>
       <c r="D28" s="7" t="inlineStr">
@@ -15078,7 +15075,7 @@
       </c>
       <c r="E28" s="7" t="inlineStr">
         <is>
-          <t>F4 cluster + valuation + recent-incentive 60% drawdown</t>
+          <t>10 layers firing | cons 7.138</t>
         </is>
       </c>
     </row>
@@ -15088,22 +15085,22 @@
       </c>
       <c r="B29" s="9" t="inlineStr">
         <is>
-          <t>PAR</t>
+          <t>HDSN</t>
         </is>
       </c>
       <c r="C29" s="10" t="inlineStr">
         <is>
-          <t>PAR</t>
-        </is>
-      </c>
-      <c r="D29" s="10" t="inlineStr">
-        <is>
-          <t>Material 2-5%</t>
+          <t>Hudson Technologies</t>
+        </is>
+      </c>
+      <c r="D29" s="6" t="inlineStr">
+        <is>
+          <t>Concentrated 5%+</t>
         </is>
       </c>
       <c r="E29" s="10" t="inlineStr">
         <is>
-          <t>10 layers firing | cons 7.29</t>
+          <t>Recent F4 cluster + buyback + special-sits + recent-incentive</t>
         </is>
       </c>
     </row>
@@ -15113,22 +15110,22 @@
       </c>
       <c r="B30" s="6" t="inlineStr">
         <is>
-          <t>HDSN</t>
+          <t>ZTS</t>
         </is>
       </c>
       <c r="C30" s="7" t="inlineStr">
         <is>
-          <t>Hudson Technologies</t>
-        </is>
-      </c>
-      <c r="D30" s="6" t="inlineStr">
-        <is>
-          <t>Concentrated 5%+</t>
+          <t>Zoetis</t>
+        </is>
+      </c>
+      <c r="D30" s="7" t="inlineStr">
+        <is>
+          <t>Material 2-5%</t>
         </is>
       </c>
       <c r="E30" s="7" t="inlineStr">
         <is>
-          <t>Recent F4 cluster + buyback + special-sits + recent-incentive</t>
+          <t>F4 cluster + valuation + recent-incentive 60% drawdown</t>
         </is>
       </c>
     </row>
@@ -15138,12 +15135,12 @@
       </c>
       <c r="B31" s="9" t="inlineStr">
         <is>
-          <t>CERT</t>
+          <t>POOL</t>
         </is>
       </c>
       <c r="C31" s="10" t="inlineStr">
         <is>
-          <t>CERT</t>
+          <t>POOL</t>
         </is>
       </c>
       <c r="D31" s="6" t="inlineStr">
@@ -15153,7 +15150,7 @@
       </c>
       <c r="E31" s="10" t="inlineStr">
         <is>
-          <t>10 layers firing | cons 6.426</t>
+          <t>10 layers firing | cons 6.558</t>
         </is>
       </c>
     </row>
@@ -15178,7 +15175,7 @@
       </c>
       <c r="E32" s="7" t="inlineStr">
         <is>
-          <t>10 layers firing | cons 6.138</t>
+          <t>10 layers firing | cons 6.252</t>
         </is>
       </c>
     </row>
@@ -15188,22 +15185,22 @@
       </c>
       <c r="B33" s="9" t="inlineStr">
         <is>
-          <t>LULU</t>
+          <t>PSN</t>
         </is>
       </c>
       <c r="C33" s="10" t="inlineStr">
         <is>
-          <t>LULU</t>
-        </is>
-      </c>
-      <c r="D33" s="6" t="inlineStr">
-        <is>
-          <t>Participation 1-2%</t>
+          <t>PSN</t>
+        </is>
+      </c>
+      <c r="D33" s="10" t="inlineStr">
+        <is>
+          <t>Material 2-5%</t>
         </is>
       </c>
       <c r="E33" s="10" t="inlineStr">
         <is>
-          <t>10 layers firing | cons 5.874</t>
+          <t>10 layers firing | cons 6.162</t>
         </is>
       </c>
     </row>
@@ -15213,12 +15210,12 @@
       </c>
       <c r="B34" s="6" t="inlineStr">
         <is>
-          <t>NUS</t>
+          <t>CERT</t>
         </is>
       </c>
       <c r="C34" s="7" t="inlineStr">
         <is>
-          <t>Nu Skin</t>
+          <t>CERT</t>
         </is>
       </c>
       <c r="D34" s="6" t="inlineStr">
@@ -15228,7 +15225,7 @@
       </c>
       <c r="E34" s="7" t="inlineStr">
         <is>
-          <t>Named asset-sale trigger + 5-metric clean per-share stack</t>
+          <t>10 layers firing | cons 6.112</t>
         </is>
       </c>
     </row>
@@ -15238,22 +15235,22 @@
       </c>
       <c r="B35" s="9" t="inlineStr">
         <is>
-          <t>SNBR</t>
+          <t>LULU</t>
         </is>
       </c>
       <c r="C35" s="10" t="inlineStr">
         <is>
-          <t>SNBR</t>
-        </is>
-      </c>
-      <c r="D35" s="10" t="inlineStr">
-        <is>
-          <t>Material 2-5%</t>
+          <t>LULU</t>
+        </is>
+      </c>
+      <c r="D35" s="6" t="inlineStr">
+        <is>
+          <t>Participation 1-2%</t>
         </is>
       </c>
       <c r="E35" s="10" t="inlineStr">
         <is>
-          <t>9 layers firing | cons 7.388</t>
+          <t>10 layers firing | cons 5.912</t>
         </is>
       </c>
     </row>
@@ -17065,10 +17062,10 @@
         <v>8</v>
       </c>
       <c r="E5" s="16" t="n">
-        <v>5.902</v>
+        <v>5.496</v>
       </c>
       <c r="F5" s="5" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="G5" s="7" t="inlineStr">
         <is>
@@ -17087,22 +17084,22 @@
       </c>
       <c r="B6" s="9" t="inlineStr">
         <is>
-          <t>CRM</t>
+          <t>EPAM</t>
         </is>
       </c>
       <c r="C6" s="10" t="inlineStr">
         <is>
-          <t>Salesforce, Inc.</t>
+          <t>EPAM Systems, Inc.</t>
         </is>
       </c>
       <c r="D6" s="8" t="n">
         <v>7</v>
       </c>
       <c r="E6" s="17" t="n">
-        <v>5.764</v>
+        <v>6.004</v>
       </c>
       <c r="F6" s="8" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G6" s="10" t="inlineStr">
         <is>
@@ -17111,7 +17108,7 @@
       </c>
       <c r="H6" s="10" t="inlineStr">
         <is>
-          <t>PSU:28 BB:8 C10:-5 F4:11 RI:61</t>
+          <t>PSU:21 C10:-29 F4:18 RI:53</t>
         </is>
       </c>
     </row>
@@ -17121,22 +17118,22 @@
       </c>
       <c r="B7" s="6" t="inlineStr">
         <is>
-          <t>EPAM</t>
+          <t>FOUR</t>
         </is>
       </c>
       <c r="C7" s="7" t="inlineStr">
         <is>
-          <t>EPAM Systems, Inc.</t>
+          <t>Shift4 Payments, Inc.</t>
         </is>
       </c>
       <c r="D7" s="5" t="n">
         <v>7</v>
       </c>
       <c r="E7" s="16" t="n">
-        <v>5.626</v>
+        <v>5.908</v>
       </c>
       <c r="F7" s="5" t="n">
-        <v>-2</v>
+        <v>5</v>
       </c>
       <c r="G7" s="7" t="inlineStr">
         <is>
@@ -17145,7 +17142,7 @@
       </c>
       <c r="H7" s="7" t="inlineStr">
         <is>
-          <t>PSU:21 C10:-29 F4:18 RI:53</t>
+          <t>PSU:28 BB:5 F4:10 RI:51</t>
         </is>
       </c>
     </row>
@@ -17155,22 +17152,22 @@
       </c>
       <c r="B8" s="9" t="inlineStr">
         <is>
-          <t>PAR</t>
+          <t>HUBS</t>
         </is>
       </c>
       <c r="C8" s="10" t="inlineStr">
         <is>
-          <t>PAR Technology Corporation</t>
+          <t>HubSpot, Inc.</t>
         </is>
       </c>
       <c r="D8" s="8" t="n">
         <v>7</v>
       </c>
       <c r="E8" s="17" t="n">
-        <v>5.546</v>
+        <v>5.714</v>
       </c>
       <c r="F8" s="8" t="n">
-        <v>10</v>
+        <v>26</v>
       </c>
       <c r="G8" s="10" t="inlineStr">
         <is>
@@ -17179,7 +17176,7 @@
       </c>
       <c r="H8" s="10" t="inlineStr">
         <is>
-          <t>PSU:17 C10:-50 RI:45 SS:35</t>
+          <t>PSU:25 BB:5 F4:17 RI:57</t>
         </is>
       </c>
     </row>
@@ -17189,22 +17186,22 @@
       </c>
       <c r="B9" s="6" t="inlineStr">
         <is>
-          <t>FOUR</t>
+          <t>CRM</t>
         </is>
       </c>
       <c r="C9" s="7" t="inlineStr">
         <is>
-          <t>Shift4 Payments, Inc.</t>
+          <t>Salesforce, Inc.</t>
         </is>
       </c>
       <c r="D9" s="5" t="n">
         <v>7</v>
       </c>
       <c r="E9" s="16" t="n">
-        <v>5.478</v>
+        <v>5.584</v>
       </c>
       <c r="F9" s="5" t="n">
-        <v>7</v>
+        <v>-1</v>
       </c>
       <c r="G9" s="7" t="inlineStr">
         <is>
@@ -17213,7 +17210,7 @@
       </c>
       <c r="H9" s="7" t="inlineStr">
         <is>
-          <t>PSU:28 BB:5 F4:10 RI:51</t>
+          <t>PSU:28 BB:8 C10:-5 F4:11 RI:61</t>
         </is>
       </c>
     </row>
@@ -17223,22 +17220,22 @@
       </c>
       <c r="B10" s="9" t="inlineStr">
         <is>
-          <t>HUBS</t>
+          <t>OLED</t>
         </is>
       </c>
       <c r="C10" s="10" t="inlineStr">
         <is>
-          <t>HubSpot, Inc.</t>
+          <t>Universal Display Corporation</t>
         </is>
       </c>
       <c r="D10" s="8" t="n">
         <v>7</v>
       </c>
       <c r="E10" s="17" t="n">
-        <v>5.452</v>
+        <v>5.358</v>
       </c>
       <c r="F10" s="8" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="G10" s="10" t="inlineStr">
         <is>
@@ -17247,7 +17244,7 @@
       </c>
       <c r="H10" s="10" t="inlineStr">
         <is>
-          <t>PSU:25 BB:5 F4:17 RI:57</t>
+          <t>PSU:40 BB:5 F4:17 RI:60</t>
         </is>
       </c>
     </row>
@@ -17257,22 +17254,22 @@
       </c>
       <c r="B11" s="6" t="inlineStr">
         <is>
-          <t>OLED</t>
+          <t>PAR</t>
         </is>
       </c>
       <c r="C11" s="7" t="inlineStr">
         <is>
-          <t>Universal Display Corporation</t>
+          <t>PAR Technology Corporation</t>
         </is>
       </c>
       <c r="D11" s="5" t="n">
         <v>7</v>
       </c>
       <c r="E11" s="16" t="n">
-        <v>5.378</v>
+        <v>4.988</v>
       </c>
       <c r="F11" s="5" t="n">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="G11" s="7" t="inlineStr">
         <is>
@@ -17281,7 +17278,7 @@
       </c>
       <c r="H11" s="7" t="inlineStr">
         <is>
-          <t>PSU:40 BB:5 F4:17 RI:60</t>
+          <t>PSU:17 C10:-50 RI:45 SS:35</t>
         </is>
       </c>
     </row>
@@ -17291,31 +17288,31 @@
       </c>
       <c r="B12" s="9" t="inlineStr">
         <is>
-          <t>BLND</t>
+          <t>OPCH</t>
         </is>
       </c>
       <c r="C12" s="10" t="inlineStr">
         <is>
-          <t>Blend Labs, Inc.</t>
+          <t>Option Care Health, Inc.</t>
         </is>
       </c>
       <c r="D12" s="8" t="n">
         <v>7</v>
       </c>
       <c r="E12" s="17" t="n">
-        <v>4.808</v>
+        <v>4.682</v>
       </c>
       <c r="F12" s="8" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="G12" s="10" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Healthcare</t>
         </is>
       </c>
       <c r="H12" s="10" t="inlineStr">
         <is>
-          <t>PSU:8 BB:5 C10:-35 F4:5 RI:52 SS:20</t>
+          <t>PSU:27 BB:5 C10:-1 F4:23 RI:52</t>
         </is>
       </c>
     </row>
@@ -17325,31 +17322,31 @@
       </c>
       <c r="B13" s="6" t="inlineStr">
         <is>
-          <t>ADT</t>
+          <t>BLND</t>
         </is>
       </c>
       <c r="C13" s="7" t="inlineStr">
         <is>
-          <t>ADT Inc.</t>
+          <t>Blend Labs, Inc.</t>
         </is>
       </c>
       <c r="D13" s="5" t="n">
         <v>7</v>
       </c>
       <c r="E13" s="16" t="n">
-        <v>4.59</v>
+        <v>4.548</v>
       </c>
       <c r="F13" s="5" t="n">
-        <v>-4</v>
+        <v>20</v>
       </c>
       <c r="G13" s="7" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="H13" s="7" t="inlineStr">
         <is>
-          <t>PSU:31 BB:5 F4:12 RI:50 SS:10</t>
+          <t>PSU:8 BB:5 C10:-35 F4:5 RI:52 SS:20</t>
         </is>
       </c>
     </row>
@@ -17359,31 +17356,31 @@
       </c>
       <c r="B14" s="9" t="inlineStr">
         <is>
-          <t>LULU</t>
+          <t>ADT</t>
         </is>
       </c>
       <c r="C14" s="10" t="inlineStr">
         <is>
-          <t>lululemon athletica inc.</t>
+          <t>ADT Inc.</t>
         </is>
       </c>
       <c r="D14" s="8" t="n">
         <v>7</v>
       </c>
       <c r="E14" s="17" t="n">
-        <v>4.514</v>
+        <v>4.404</v>
       </c>
       <c r="F14" s="8" t="n">
-        <v>8</v>
+        <v>-5</v>
       </c>
       <c r="G14" s="10" t="inlineStr">
         <is>
-          <t>Consumer Cyclical</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="H14" s="10" t="inlineStr">
         <is>
-          <t>PSU:1 BB:8 C10:-40 F4:11 RI:41 SS:10</t>
+          <t>PSU:31 BB:5 F4:12 RI:50 SS:10</t>
         </is>
       </c>
     </row>
@@ -17393,31 +17390,31 @@
       </c>
       <c r="B15" s="6" t="inlineStr">
         <is>
-          <t>CERT</t>
+          <t>LULU</t>
         </is>
       </c>
       <c r="C15" s="7" t="inlineStr">
         <is>
-          <t>Certara, Inc.</t>
+          <t>lululemon athletica inc.</t>
         </is>
       </c>
       <c r="D15" s="5" t="n">
         <v>7</v>
       </c>
       <c r="E15" s="16" t="n">
-        <v>4.416</v>
+        <v>4.194</v>
       </c>
       <c r="F15" s="5" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="G15" s="7" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>Consumer Cyclical</t>
         </is>
       </c>
       <c r="H15" s="7" t="inlineStr">
         <is>
-          <t>PSU:29 BB:5 C10:-12 RI:43</t>
+          <t>PSU:1 BB:8 C10:-40 F4:11 RI:41 SS:10</t>
         </is>
       </c>
     </row>
@@ -17427,31 +17424,31 @@
       </c>
       <c r="B16" s="9" t="inlineStr">
         <is>
-          <t>VTS</t>
+          <t>CERT</t>
         </is>
       </c>
       <c r="C16" s="10" t="inlineStr">
         <is>
-          <t>Vitesse Energy, Inc.</t>
+          <t>Certara, Inc.</t>
         </is>
       </c>
       <c r="D16" s="8" t="n">
         <v>7</v>
       </c>
       <c r="E16" s="17" t="n">
-        <v>4.12</v>
+        <v>3.978</v>
       </c>
       <c r="F16" s="8" t="n">
-        <v>25</v>
+        <v>7</v>
       </c>
       <c r="G16" s="10" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Healthcare</t>
         </is>
       </c>
       <c r="H16" s="10" t="inlineStr">
         <is>
-          <t>PSU:28 F4:5 RI:50</t>
+          <t>PSU:29 BB:5 C10:-12 RI:43</t>
         </is>
       </c>
     </row>
@@ -17473,10 +17470,10 @@
         <v>6</v>
       </c>
       <c r="E17" s="16" t="n">
-        <v>5.384</v>
+        <v>5.38</v>
       </c>
       <c r="F17" s="5" t="n">
-        <v>-5</v>
+        <v>-6</v>
       </c>
       <c r="G17" s="7" t="inlineStr">
         <is>
@@ -17495,31 +17492,33 @@
       </c>
       <c r="B18" s="9" t="inlineStr">
         <is>
-          <t>SBET</t>
+          <t>HDSN</t>
         </is>
       </c>
       <c r="C18" s="10" t="inlineStr">
         <is>
-          <t>SharpLink, Inc.</t>
+          <t>Hudson Technologies, Inc.</t>
         </is>
       </c>
       <c r="D18" s="8" t="n">
         <v>6</v>
       </c>
       <c r="E18" s="17" t="n">
-        <v>4.866</v>
-      </c>
-      <c r="F18" s="8" t="n">
-        <v>41</v>
+        <v>5.114</v>
+      </c>
+      <c r="F18" s="10" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
       <c r="G18" s="10" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>Basic Materials</t>
         </is>
       </c>
       <c r="H18" s="10" t="inlineStr">
         <is>
-          <t>PSU:19 C10:15 RI:71</t>
+          <t>BB:5 F4:18 RI:58</t>
         </is>
       </c>
     </row>
@@ -17541,10 +17540,10 @@
         <v>6</v>
       </c>
       <c r="E19" s="16" t="n">
-        <v>4.82</v>
+        <v>4.846</v>
       </c>
       <c r="F19" s="5" t="n">
-        <v>-5</v>
+        <v>-4</v>
       </c>
       <c r="G19" s="7" t="inlineStr">
         <is>
@@ -17563,31 +17562,31 @@
       </c>
       <c r="B20" s="9" t="inlineStr">
         <is>
-          <t>ALKT</t>
+          <t>SNBR</t>
         </is>
       </c>
       <c r="C20" s="10" t="inlineStr">
         <is>
-          <t>Alkami Technology, Inc.</t>
+          <t>Sleep Number Corporation</t>
         </is>
       </c>
       <c r="D20" s="8" t="n">
         <v>6</v>
       </c>
       <c r="E20" s="17" t="n">
-        <v>4.816</v>
+        <v>4.788</v>
       </c>
       <c r="F20" s="8" t="n">
-        <v>31</v>
+        <v>7</v>
       </c>
       <c r="G20" s="10" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Consumer Cyclical</t>
         </is>
       </c>
       <c r="H20" s="10" t="inlineStr">
         <is>
-          <t>PSU:11 C10:-6 F4:16 RI:54</t>
+          <t>PSU:49 RI:46 SS:20</t>
         </is>
       </c>
     </row>
@@ -17597,31 +17596,31 @@
       </c>
       <c r="B21" s="6" t="inlineStr">
         <is>
-          <t>GPGI</t>
+          <t>ALKT</t>
         </is>
       </c>
       <c r="C21" s="7" t="inlineStr">
         <is>
-          <t>GPGI, Inc.</t>
+          <t>Alkami Technology, Inc.</t>
         </is>
       </c>
       <c r="D21" s="5" t="n">
         <v>6</v>
       </c>
       <c r="E21" s="16" t="n">
-        <v>4.762</v>
+        <v>4.772</v>
       </c>
       <c r="F21" s="5" t="n">
-        <v>7</v>
+        <v>36</v>
       </c>
       <c r="G21" s="7" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="H21" s="7" t="inlineStr">
         <is>
-          <t>PSU:17 C10:-15 F4:12 RI:52 SS:23</t>
+          <t>PSU:11 C10:-6 F4:16 RI:54</t>
         </is>
       </c>
     </row>
@@ -17631,31 +17630,31 @@
       </c>
       <c r="B22" s="9" t="inlineStr">
         <is>
-          <t>SNBR</t>
+          <t>SBET</t>
         </is>
       </c>
       <c r="C22" s="10" t="inlineStr">
         <is>
-          <t>Sleep Number Corporation</t>
+          <t>SharpLink, Inc.</t>
         </is>
       </c>
       <c r="D22" s="8" t="n">
         <v>6</v>
       </c>
       <c r="E22" s="17" t="n">
-        <v>4.742</v>
+        <v>4.77</v>
       </c>
       <c r="F22" s="8" t="n">
-        <v>2</v>
+        <v>34</v>
       </c>
       <c r="G22" s="10" t="inlineStr">
         <is>
-          <t>Consumer Cyclical</t>
+          <t>Financial Services</t>
         </is>
       </c>
       <c r="H22" s="10" t="inlineStr">
         <is>
-          <t>PSU:49 RI:46 SS:20</t>
+          <t>PSU:19 C10:15 RI:71</t>
         </is>
       </c>
     </row>
@@ -17665,12 +17664,12 @@
       </c>
       <c r="B23" s="6" t="inlineStr">
         <is>
-          <t>ACM</t>
+          <t>GPGI</t>
         </is>
       </c>
       <c r="C23" s="7" t="inlineStr">
         <is>
-          <t>AECOM</t>
+          <t>GPGI, Inc.</t>
         </is>
       </c>
       <c r="D23" s="5" t="n">
@@ -17680,7 +17679,7 @@
         <v>4.68</v>
       </c>
       <c r="F23" s="5" t="n">
-        <v>35</v>
+        <v>6</v>
       </c>
       <c r="G23" s="7" t="inlineStr">
         <is>
@@ -17689,7 +17688,7 @@
       </c>
       <c r="H23" s="7" t="inlineStr">
         <is>
-          <t>BB:5 F4:6 RI:54</t>
+          <t>PSU:17 C10:-15 F4:12 RI:52 SS:23</t>
         </is>
       </c>
     </row>
@@ -17699,31 +17698,31 @@
       </c>
       <c r="B24" s="9" t="inlineStr">
         <is>
-          <t>HDSN</t>
+          <t>VRSK</t>
         </is>
       </c>
       <c r="C24" s="10" t="inlineStr">
         <is>
-          <t>Hudson Technologies, Inc.</t>
+          <t>Verisk Analytics, Inc.</t>
         </is>
       </c>
       <c r="D24" s="8" t="n">
         <v>6</v>
       </c>
       <c r="E24" s="17" t="n">
-        <v>4.66</v>
+        <v>4.588</v>
       </c>
       <c r="F24" s="8" t="n">
-        <v>-5</v>
+        <v>-8</v>
       </c>
       <c r="G24" s="10" t="inlineStr">
         <is>
-          <t>Basic Materials</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="H24" s="10" t="inlineStr">
         <is>
-          <t>BB:5 F4:18 RI:58</t>
+          <t>PSU:32 BB:8 F4:12 RI:32</t>
         </is>
       </c>
     </row>
@@ -17733,31 +17732,31 @@
       </c>
       <c r="B25" s="6" t="inlineStr">
         <is>
-          <t>NUS</t>
+          <t>MSCI</t>
         </is>
       </c>
       <c r="C25" s="7" t="inlineStr">
         <is>
-          <t>Nu Skin Enterprises, Inc.</t>
+          <t>MSCI Inc.</t>
         </is>
       </c>
       <c r="D25" s="5" t="n">
         <v>6</v>
       </c>
       <c r="E25" s="16" t="n">
-        <v>4.562</v>
+        <v>4.57</v>
       </c>
       <c r="F25" s="5" t="n">
-        <v>-2</v>
+        <v>7</v>
       </c>
       <c r="G25" s="7" t="inlineStr">
         <is>
-          <t>Consumer Defensive</t>
+          <t>Financial Services</t>
         </is>
       </c>
       <c r="H25" s="7" t="inlineStr">
         <is>
-          <t>PSU:54 BB:5 C10:-32 RI:53</t>
+          <t>PSU:36 BB:8 C10:-26 F4:16 RI:16</t>
         </is>
       </c>
     </row>
@@ -17767,33 +17766,31 @@
       </c>
       <c r="B26" s="9" t="inlineStr">
         <is>
-          <t>VRSK</t>
+          <t>NUS</t>
         </is>
       </c>
       <c r="C26" s="10" t="inlineStr">
         <is>
-          <t>Verisk Analytics, Inc.</t>
+          <t>Nu Skin Enterprises, Inc.</t>
         </is>
       </c>
       <c r="D26" s="8" t="n">
         <v>6</v>
       </c>
       <c r="E26" s="17" t="n">
-        <v>4.556</v>
-      </c>
-      <c r="F26" s="10" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+        <v>4.568</v>
+      </c>
+      <c r="F26" s="8" t="n">
+        <v>-1</v>
       </c>
       <c r="G26" s="10" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Consumer Defensive</t>
         </is>
       </c>
       <c r="H26" s="10" t="inlineStr">
         <is>
-          <t>PSU:32 BB:8 F4:12 RI:32</t>
+          <t>PSU:54 BB:5 C10:-32 RI:53</t>
         </is>
       </c>
     </row>
@@ -17803,22 +17800,22 @@
       </c>
       <c r="B27" s="6" t="inlineStr">
         <is>
-          <t>ZTS</t>
+          <t>AZTA</t>
         </is>
       </c>
       <c r="C27" s="7" t="inlineStr">
         <is>
-          <t>Zoetis Inc.</t>
+          <t>Azenta, Inc.</t>
         </is>
       </c>
       <c r="D27" s="5" t="n">
         <v>6</v>
       </c>
       <c r="E27" s="16" t="n">
-        <v>4.522</v>
+        <v>4.394</v>
       </c>
       <c r="F27" s="5" t="n">
-        <v>-10</v>
+        <v>19</v>
       </c>
       <c r="G27" s="7" t="inlineStr">
         <is>
@@ -17827,7 +17824,7 @@
       </c>
       <c r="H27" s="7" t="inlineStr">
         <is>
-          <t>PSU:7 BB:5 C10:-3 F4:12 RI:60</t>
+          <t>PSU:31</t>
         </is>
       </c>
     </row>
@@ -17837,31 +17834,31 @@
       </c>
       <c r="B28" s="9" t="inlineStr">
         <is>
-          <t>MSCI</t>
+          <t>ZTS</t>
         </is>
       </c>
       <c r="C28" s="10" t="inlineStr">
         <is>
-          <t>MSCI Inc.</t>
+          <t>Zoetis Inc.</t>
         </is>
       </c>
       <c r="D28" s="8" t="n">
         <v>6</v>
       </c>
       <c r="E28" s="17" t="n">
-        <v>4.498</v>
+        <v>4.33</v>
       </c>
       <c r="F28" s="8" t="n">
-        <v>2</v>
+        <v>-9</v>
       </c>
       <c r="G28" s="10" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>Healthcare</t>
         </is>
       </c>
       <c r="H28" s="10" t="inlineStr">
         <is>
-          <t>PSU:36 BB:8 C10:-26 F4:16 RI:16</t>
+          <t>PSU:7 BB:5 C10:-3 F4:12 RI:60</t>
         </is>
       </c>
     </row>
@@ -17871,31 +17868,31 @@
       </c>
       <c r="B29" s="6" t="inlineStr">
         <is>
-          <t>PSN</t>
+          <t>ACM</t>
         </is>
       </c>
       <c r="C29" s="7" t="inlineStr">
         <is>
-          <t>Parsons Corporation</t>
+          <t>AECOM</t>
         </is>
       </c>
       <c r="D29" s="5" t="n">
         <v>6</v>
       </c>
       <c r="E29" s="16" t="n">
-        <v>4.466</v>
+        <v>4.244</v>
       </c>
       <c r="F29" s="5" t="n">
-        <v>9</v>
+        <v>32</v>
       </c>
       <c r="G29" s="7" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="H29" s="7" t="inlineStr">
         <is>
-          <t>PSU:37 F4:23 RI:47</t>
+          <t>BB:5 F4:6 RI:54</t>
         </is>
       </c>
     </row>
@@ -17905,31 +17902,31 @@
       </c>
       <c r="B30" s="9" t="inlineStr">
         <is>
-          <t>AZTA</t>
+          <t>PSN</t>
         </is>
       </c>
       <c r="C30" s="10" t="inlineStr">
         <is>
-          <t>Azenta, Inc.</t>
+          <t>Parsons Corporation</t>
         </is>
       </c>
       <c r="D30" s="8" t="n">
         <v>6</v>
       </c>
       <c r="E30" s="17" t="n">
-        <v>4.348</v>
+        <v>4.172</v>
       </c>
       <c r="F30" s="8" t="n">
-        <v>12</v>
+        <v>-8</v>
       </c>
       <c r="G30" s="10" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="H30" s="10" t="inlineStr">
         <is>
-          <t>PSU:31</t>
+          <t>PSU:37 F4:23 RI:47</t>
         </is>
       </c>
     </row>
@@ -17939,31 +17936,31 @@
       </c>
       <c r="B31" s="6" t="inlineStr">
         <is>
-          <t>APTV</t>
+          <t>PRGO</t>
         </is>
       </c>
       <c r="C31" s="7" t="inlineStr">
         <is>
-          <t>Aptiv PLC</t>
+          <t>Perrigo Company plc</t>
         </is>
       </c>
       <c r="D31" s="5" t="n">
         <v>6</v>
       </c>
       <c r="E31" s="16" t="n">
-        <v>4.344</v>
+        <v>4.138</v>
       </c>
       <c r="F31" s="5" t="n">
-        <v>26</v>
+        <v>-1</v>
       </c>
       <c r="G31" s="7" t="inlineStr">
         <is>
-          <t>Consumer Cyclical</t>
+          <t>Healthcare</t>
         </is>
       </c>
       <c r="H31" s="7" t="inlineStr">
         <is>
-          <t>PSU:36 BB:5 RI:35</t>
+          <t>PSU:21 RI:48 SS:29</t>
         </is>
       </c>
     </row>
@@ -17973,31 +17970,31 @@
       </c>
       <c r="B32" s="9" t="inlineStr">
         <is>
-          <t>OPCH</t>
+          <t>APTV</t>
         </is>
       </c>
       <c r="C32" s="10" t="inlineStr">
         <is>
-          <t>Option Care Health, Inc.</t>
+          <t>Aptiv PLC</t>
         </is>
       </c>
       <c r="D32" s="8" t="n">
         <v>6</v>
       </c>
       <c r="E32" s="17" t="n">
-        <v>4.26</v>
+        <v>4.12</v>
       </c>
       <c r="F32" s="8" t="n">
-        <v>4</v>
+        <v>18</v>
       </c>
       <c r="G32" s="10" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>Consumer Cyclical</t>
         </is>
       </c>
       <c r="H32" s="10" t="inlineStr">
         <is>
-          <t>PSU:27 BB:5 C10:-1 F4:23 RI:52</t>
+          <t>PSU:36 BB:5 RI:35</t>
         </is>
       </c>
     </row>
@@ -18007,31 +18004,31 @@
       </c>
       <c r="B33" s="6" t="inlineStr">
         <is>
-          <t>MMS</t>
+          <t>VTS</t>
         </is>
       </c>
       <c r="C33" s="7" t="inlineStr">
         <is>
-          <t>Maximus, Inc.</t>
+          <t>Vitesse Energy, Inc.</t>
         </is>
       </c>
       <c r="D33" s="5" t="n">
         <v>6</v>
       </c>
       <c r="E33" s="16" t="n">
-        <v>4.182</v>
-      </c>
-      <c r="F33" s="22" t="n">
-        <v>106</v>
+        <v>4.03</v>
+      </c>
+      <c r="F33" s="5" t="n">
+        <v>11</v>
       </c>
       <c r="G33" s="7" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="H33" s="7" t="inlineStr">
         <is>
-          <t>PSU:42 BB:5 RI:53 SS:26</t>
+          <t>PSU:28 F4:5 RI:50</t>
         </is>
       </c>
     </row>
@@ -18041,31 +18038,31 @@
       </c>
       <c r="B34" s="9" t="inlineStr">
         <is>
-          <t>GTM</t>
+          <t>TSEOF</t>
         </is>
       </c>
       <c r="C34" s="10" t="inlineStr">
         <is>
-          <t>ZoomInfo Technologies Inc.</t>
+          <t>Trinseo PLC</t>
         </is>
       </c>
       <c r="D34" s="8" t="n">
         <v>6</v>
       </c>
       <c r="E34" s="17" t="n">
-        <v>4.056</v>
+        <v>4.026</v>
       </c>
       <c r="F34" s="8" t="n">
-        <v>-3</v>
+        <v>31</v>
       </c>
       <c r="G34" s="10" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Basic Materials</t>
         </is>
       </c>
       <c r="H34" s="10" t="inlineStr">
         <is>
-          <t>PSU:36 BB:5 C10:-4 RI:66 SS:20</t>
+          <t>PSU:17 C10:-10 RI:40 SS:55</t>
         </is>
       </c>
     </row>
@@ -18199,7 +18196,7 @@
           <t>Repay Holdings Corporation</t>
         </is>
       </c>
-      <c r="D5" s="23" t="n">
+      <c r="D5" s="22" t="n">
         <v>68</v>
       </c>
       <c r="E5" s="5" t="n">
@@ -18239,7 +18236,7 @@
           <t>Gossamer Bio, Inc.</t>
         </is>
       </c>
-      <c r="D6" s="23" t="n">
+      <c r="D6" s="22" t="n">
         <v>61</v>
       </c>
       <c r="E6" s="8" t="n">
@@ -18279,7 +18276,7 @@
           <t>ZoomInfo Technologies Inc.</t>
         </is>
       </c>
-      <c r="D7" s="23" t="n">
+      <c r="D7" s="22" t="n">
         <v>60</v>
       </c>
       <c r="E7" s="5" t="n">
@@ -18319,7 +18316,7 @@
           <t>Goosehead Insurance, Inc.</t>
         </is>
       </c>
-      <c r="D8" s="23" t="n">
+      <c r="D8" s="22" t="n">
         <v>53</v>
       </c>
       <c r="E8" s="8" t="n">
@@ -18359,7 +18356,7 @@
           <t>Guidewire Software, Inc.</t>
         </is>
       </c>
-      <c r="D9" s="23" t="n">
+      <c r="D9" s="22" t="n">
         <v>53</v>
       </c>
       <c r="E9" s="5" t="n">
@@ -18399,7 +18396,7 @@
           <t>Comtech Telecommunications Corp</t>
         </is>
       </c>
-      <c r="D10" s="23" t="n">
+      <c r="D10" s="22" t="n">
         <v>52</v>
       </c>
       <c r="E10" s="8" t="n">
@@ -18439,7 +18436,7 @@
           <t>BiomX Inc.</t>
         </is>
       </c>
-      <c r="D11" s="23" t="n">
+      <c r="D11" s="22" t="n">
         <v>52</v>
       </c>
       <c r="E11" s="5" t="n">
@@ -18479,7 +18476,7 @@
           <t>ChargePoint Holdings, Inc.</t>
         </is>
       </c>
-      <c r="D12" s="23" t="n">
+      <c r="D12" s="22" t="n">
         <v>52</v>
       </c>
       <c r="E12" s="8" t="n">
@@ -18519,7 +18516,7 @@
           <t>DXC Technology Company</t>
         </is>
       </c>
-      <c r="D13" s="23" t="n">
+      <c r="D13" s="22" t="n">
         <v>52</v>
       </c>
       <c r="E13" s="5" t="n">
@@ -18559,7 +18556,7 @@
           <t>Processa Pharmaceuticals, Inc.</t>
         </is>
       </c>
-      <c r="D14" s="23" t="n">
+      <c r="D14" s="22" t="n">
         <v>51</v>
       </c>
       <c r="E14" s="8" t="n">
@@ -18599,7 +18596,7 @@
           <t>Peabody Energy Corporation</t>
         </is>
       </c>
-      <c r="D15" s="23" t="n">
+      <c r="D15" s="22" t="n">
         <v>51</v>
       </c>
       <c r="E15" s="5" t="n">
@@ -18639,7 +18636,7 @@
           <t>Ready Capital Corporation</t>
         </is>
       </c>
-      <c r="D16" s="23" t="n">
+      <c r="D16" s="22" t="n">
         <v>49</v>
       </c>
       <c r="E16" s="8" t="n">
@@ -18679,7 +18676,7 @@
           <t>Kingsway Corporation</t>
         </is>
       </c>
-      <c r="D17" s="23" t="n">
+      <c r="D17" s="22" t="n">
         <v>49</v>
       </c>
       <c r="E17" s="5" t="n">
@@ -18719,7 +18716,7 @@
           <t>Heron Therapeutics, Inc.</t>
         </is>
       </c>
-      <c r="D18" s="23" t="n">
+      <c r="D18" s="22" t="n">
         <v>48</v>
       </c>
       <c r="E18" s="8" t="n">
@@ -18759,7 +18756,7 @@
           <t>Standard BioTools Inc.</t>
         </is>
       </c>
-      <c r="D19" s="23" t="n">
+      <c r="D19" s="22" t="n">
         <v>48</v>
       </c>
       <c r="E19" s="5" t="n">
@@ -18799,7 +18796,7 @@
           <t>InspireMD Inc.</t>
         </is>
       </c>
-      <c r="D20" s="23" t="n">
+      <c r="D20" s="22" t="n">
         <v>47</v>
       </c>
       <c r="E20" s="8" t="n">
@@ -18839,7 +18836,7 @@
           <t>Rein Therapeutics, Inc.</t>
         </is>
       </c>
-      <c r="D21" s="23" t="n">
+      <c r="D21" s="22" t="n">
         <v>46</v>
       </c>
       <c r="E21" s="5" t="n">
@@ -18879,7 +18876,7 @@
           <t>Booz Allen Hamilton Holding Cor</t>
         </is>
       </c>
-      <c r="D22" s="23" t="n">
+      <c r="D22" s="22" t="n">
         <v>46</v>
       </c>
       <c r="E22" s="8" t="n">
@@ -18919,7 +18916,7 @@
           <t>VolitionRX Limited</t>
         </is>
       </c>
-      <c r="D23" s="23" t="n">
+      <c r="D23" s="22" t="n">
         <v>45</v>
       </c>
       <c r="E23" s="5" t="n">
@@ -18959,7 +18956,7 @@
           <t>Total Return Securities Fund</t>
         </is>
       </c>
-      <c r="D24" s="23" t="n">
+      <c r="D24" s="22" t="n">
         <v>44</v>
       </c>
       <c r="E24" s="8" t="n">
@@ -18999,7 +18996,7 @@
           <t>Fox Corporation</t>
         </is>
       </c>
-      <c r="D25" s="23" t="n">
+      <c r="D25" s="22" t="n">
         <v>44</v>
       </c>
       <c r="E25" s="5" t="n">
@@ -19039,7 +19036,7 @@
           <t>Outlook Therapeutics, Inc.</t>
         </is>
       </c>
-      <c r="D26" s="23" t="n">
+      <c r="D26" s="22" t="n">
         <v>44</v>
       </c>
       <c r="E26" s="8" t="n">
@@ -19079,7 +19076,7 @@
           <t>My Size, Inc.</t>
         </is>
       </c>
-      <c r="D27" s="23" t="n">
+      <c r="D27" s="22" t="n">
         <v>43</v>
       </c>
       <c r="E27" s="5" t="n">
@@ -19119,7 +19116,7 @@
           <t>Purple Innovation, Inc.</t>
         </is>
       </c>
-      <c r="D28" s="23" t="n">
+      <c r="D28" s="22" t="n">
         <v>43</v>
       </c>
       <c r="E28" s="8" t="n">
@@ -19159,7 +19156,7 @@
           <t>Cosmos Health Inc.</t>
         </is>
       </c>
-      <c r="D29" s="23" t="n">
+      <c r="D29" s="22" t="n">
         <v>43</v>
       </c>
       <c r="E29" s="5" t="n">
@@ -19199,7 +19196,7 @@
           <t>Power Solutions International,</t>
         </is>
       </c>
-      <c r="D30" s="23" t="n">
+      <c r="D30" s="22" t="n">
         <v>43</v>
       </c>
       <c r="E30" s="8" t="n">
@@ -19239,7 +19236,7 @@
           <t>NexGel, Inc</t>
         </is>
       </c>
-      <c r="D31" s="23" t="n">
+      <c r="D31" s="22" t="n">
         <v>43</v>
       </c>
       <c r="E31" s="5" t="n">
@@ -19279,7 +19276,7 @@
           <t>Salesforce, Inc.</t>
         </is>
       </c>
-      <c r="D32" s="23" t="n">
+      <c r="D32" s="22" t="n">
         <v>42</v>
       </c>
       <c r="E32" s="8" t="n">
@@ -19319,7 +19316,7 @@
           <t>Vitesse Energy, Inc.</t>
         </is>
       </c>
-      <c r="D33" s="23" t="n">
+      <c r="D33" s="22" t="n">
         <v>42</v>
       </c>
       <c r="E33" s="5" t="n">
@@ -19359,7 +19356,7 @@
           <t>Krispy Kreme, Inc.</t>
         </is>
       </c>
-      <c r="D34" s="23" t="n">
+      <c r="D34" s="22" t="n">
         <v>42</v>
       </c>
       <c r="E34" s="8" t="n">
@@ -19399,7 +19396,7 @@
           <t>Nerdy Inc.</t>
         </is>
       </c>
-      <c r="D35" s="23" t="n">
+      <c r="D35" s="22" t="n">
         <v>41</v>
       </c>
       <c r="E35" s="5" t="n">
@@ -19439,7 +19436,7 @@
           <t>Artiva Biotherapeutics, Inc.</t>
         </is>
       </c>
-      <c r="D36" s="23" t="n">
+      <c r="D36" s="22" t="n">
         <v>41</v>
       </c>
       <c r="E36" s="8" t="n">
@@ -19479,7 +19476,7 @@
           <t>STERIS plc (Ireland)</t>
         </is>
       </c>
-      <c r="D37" s="23" t="n">
+      <c r="D37" s="22" t="n">
         <v>41</v>
       </c>
       <c r="E37" s="5" t="n">
@@ -19519,7 +19516,7 @@
           <t>Rubrik, Inc.</t>
         </is>
       </c>
-      <c r="D38" s="23" t="n">
+      <c r="D38" s="22" t="n">
         <v>41</v>
       </c>
       <c r="E38" s="8" t="n">
@@ -19559,7 +19556,7 @@
           <t>Medline Inc.</t>
         </is>
       </c>
-      <c r="D39" s="23" t="n">
+      <c r="D39" s="22" t="n">
         <v>40</v>
       </c>
       <c r="E39" s="5" t="n">
@@ -19599,7 +19596,7 @@
           <t>Toro Corp.</t>
         </is>
       </c>
-      <c r="D40" s="23" t="n">
+      <c r="D40" s="22" t="n">
         <v>40</v>
       </c>
       <c r="E40" s="8" t="n">
@@ -19639,7 +19636,7 @@
           <t>CuriosityStream Inc.</t>
         </is>
       </c>
-      <c r="D41" s="23" t="n">
+      <c r="D41" s="22" t="n">
         <v>40</v>
       </c>
       <c r="E41" s="5" t="n">
@@ -19679,7 +19676,7 @@
           <t>Health Catalyst, Inc</t>
         </is>
       </c>
-      <c r="D42" s="23" t="n">
+      <c r="D42" s="22" t="n">
         <v>40</v>
       </c>
       <c r="E42" s="8" t="n">
@@ -22173,7 +22170,7 @@
           <t>Jet.AI Inc.</t>
         </is>
       </c>
-      <c r="D5" s="23" t="n">
+      <c r="D5" s="22" t="n">
         <v>43</v>
       </c>
       <c r="E5" s="7" t="inlineStr">
@@ -22215,7 +22212,7 @@
           <t>BEYOND MEAT, INC.</t>
         </is>
       </c>
-      <c r="D6" s="23" t="n">
+      <c r="D6" s="22" t="n">
         <v>35</v>
       </c>
       <c r="E6" s="10" t="inlineStr">
@@ -22257,7 +22254,7 @@
           <t>COMTECH TELECOMMUNICATIONS CORP</t>
         </is>
       </c>
-      <c r="D7" s="23" t="n">
+      <c r="D7" s="22" t="n">
         <v>35</v>
       </c>
       <c r="E7" s="7" t="inlineStr">
@@ -22299,7 +22296,7 @@
           <t>FISERV INC</t>
         </is>
       </c>
-      <c r="D8" s="23" t="n">
+      <c r="D8" s="22" t="n">
         <v>35</v>
       </c>
       <c r="E8" s="10" t="inlineStr">
@@ -22341,7 +22338,7 @@
           <t>BTCS Inc.</t>
         </is>
       </c>
-      <c r="D9" s="23" t="n">
+      <c r="D9" s="22" t="n">
         <v>35</v>
       </c>
       <c r="E9" s="7" t="inlineStr">
@@ -22383,7 +22380,7 @@
           <t>HERON THERAPEUTICS, INC. /DE/</t>
         </is>
       </c>
-      <c r="D10" s="23" t="n">
+      <c r="D10" s="22" t="n">
         <v>35</v>
       </c>
       <c r="E10" s="10" t="inlineStr">
@@ -22425,7 +22422,7 @@
           <t>WW INTERNATIONAL, INC.</t>
         </is>
       </c>
-      <c r="D11" s="23" t="n">
+      <c r="D11" s="22" t="n">
         <v>33</v>
       </c>
       <c r="E11" s="7" t="inlineStr">
@@ -23896,14 +23893,14 @@
     </row>
     <row r="3" ht="8" customHeight="1"/>
     <row r="4" ht="22" customHeight="1">
-      <c r="A4" s="24" t="inlineStr">
+      <c r="A4" s="23" t="inlineStr">
         <is>
           <t>Highest PSU forensic core</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="25" t="inlineStr">
+      <c r="A5" s="24" t="inlineStr">
         <is>
           <t>What it measures: depth + rigor of the PSU plan</t>
         </is>
@@ -24166,14 +24163,14 @@
       </c>
     </row>
     <row r="16" ht="22" customHeight="1">
-      <c r="A16" s="24" t="inlineStr">
+      <c r="A16" s="23" t="inlineStr">
         <is>
           <t>Highest governance score</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="25" t="inlineStr">
+      <c r="A17" s="24" t="inlineStr">
         <is>
           <t>What it measures: clawback + anti-hedge + vesting + ownership multiple</t>
         </is>
@@ -24436,14 +24433,14 @@
       </c>
     </row>
     <row r="28" ht="22" customHeight="1">
-      <c r="A28" s="24" t="inlineStr">
+      <c r="A28" s="23" t="inlineStr">
         <is>
           <t>Deepest P/B floor (&lt;0.5x book)</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="25" t="inlineStr">
+      <c r="A29" s="24" t="inlineStr">
         <is>
           <t>What it measures: hard balance-sheet value floor</t>
         </is>
@@ -24706,14 +24703,14 @@
       </c>
     </row>
     <row r="40" ht="22" customHeight="1">
-      <c r="A40" s="24" t="inlineStr">
+      <c r="A40" s="23" t="inlineStr">
         <is>
           <t>Cheapest EV/EBITDA (&lt;6x)</t>
         </is>
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="25" t="inlineStr">
+      <c r="A41" s="24" t="inlineStr">
         <is>
           <t>What it measures: enterprise-value to earnings power</t>
         </is>
@@ -24976,14 +24973,14 @@
       </c>
     </row>
     <row r="52" ht="22" customHeight="1">
-      <c r="A52" s="24" t="inlineStr">
+      <c r="A52" s="23" t="inlineStr">
         <is>
           <t>Lowest trailing P/E (&lt;8x, positive)</t>
         </is>
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="25" t="inlineStr">
+      <c r="A53" s="24" t="inlineStr">
         <is>
           <t>What it measures: earnings yield</t>
         </is>
@@ -25246,14 +25243,14 @@
       </c>
     </row>
     <row r="64" ht="22" customHeight="1">
-      <c r="A64" s="24" t="inlineStr">
+      <c r="A64" s="23" t="inlineStr">
         <is>
           <t>Largest verified buyback shrinkage</t>
         </is>
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="25" t="inlineStr">
+      <c r="A65" s="24" t="inlineStr">
         <is>
           <t>What it measures: actual supply curve compression</t>
         </is>
@@ -25516,14 +25513,14 @@
       </c>
     </row>
     <row r="76" ht="22" customHeight="1">
-      <c r="A76" s="24" t="inlineStr">
+      <c r="A76" s="23" t="inlineStr">
         <is>
           <t>Highest 10b5-1 termination signed score</t>
         </is>
       </c>
     </row>
     <row r="77">
-      <c r="A77" s="25" t="inlineStr">
+      <c r="A77" s="24" t="inlineStr">
         <is>
           <t>What it measures: insider walked back scheduled selling</t>
         </is>
@@ -25786,14 +25783,14 @@
       </c>
     </row>
     <row r="88" ht="22" customHeight="1">
-      <c r="A88" s="24" t="inlineStr">
+      <c r="A88" s="23" t="inlineStr">
         <is>
           <t>Largest insider Form 4 dollar cluster</t>
         </is>
       </c>
     </row>
     <row r="89">
-      <c r="A89" s="25" t="inlineStr">
+      <c r="A89" s="24" t="inlineStr">
         <is>
           <t>What it measures: insider conviction in dollars</t>
         </is>
@@ -26056,14 +26053,14 @@
       </c>
     </row>
     <row r="100" ht="22" customHeight="1">
-      <c r="A100" s="24" t="inlineStr">
+      <c r="A100" s="23" t="inlineStr">
         <is>
           <t>Live tender / 13E-3 events</t>
         </is>
       </c>
     </row>
     <row r="101">
-      <c r="A101" s="25" t="inlineStr">
+      <c r="A101" s="24" t="inlineStr">
         <is>
           <t>What it measures: mechanical bid as floor</t>
         </is>
@@ -26424,7 +26421,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D34"/>
+  <dimension ref="A1:D38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -26454,7 +26451,7 @@
     <row r="4">
       <c r="A4" s="12" t="inlineStr">
         <is>
-          <t>Raw layers: 39    Effective-independent (rho&gt;0.6): 34</t>
+          <t>Raw layers: 44    Effective-independent (rho&gt;0.6): 37</t>
         </is>
       </c>
     </row>
@@ -26523,16 +26520,16 @@
     <row r="9" ht="16" customHeight="1">
       <c r="A9" s="7" t="inlineStr">
         <is>
-          <t>opportunistic</t>
+          <t>valuation</t>
         </is>
       </c>
       <c r="B9" s="7" t="inlineStr">
         <is>
-          <t>discretionary_conviction</t>
+          <t>payoff_geometry</t>
         </is>
       </c>
       <c r="C9" s="16" t="n">
-        <v>0.6850000000000001</v>
+        <v>0.704</v>
       </c>
       <c r="D9" s="7" t="inlineStr">
         <is>
@@ -26543,16 +26540,16 @@
     <row r="10" ht="16" customHeight="1">
       <c r="A10" s="10" t="inlineStr">
         <is>
-          <t>f4_buys</t>
+          <t>opportunistic</t>
         </is>
       </c>
       <c r="B10" s="10" t="inlineStr">
         <is>
-          <t>opportunistic</t>
+          <t>discretionary_conviction</t>
         </is>
       </c>
       <c r="C10" s="17" t="n">
-        <v>0.667</v>
+        <v>0.6850000000000001</v>
       </c>
       <c r="D10" s="10" t="inlineStr">
         <is>
@@ -26563,16 +26560,16 @@
     <row r="11" ht="16" customHeight="1">
       <c r="A11" s="7" t="inlineStr">
         <is>
-          <t>tender_mech</t>
+          <t>f4_buys</t>
         </is>
       </c>
       <c r="B11" s="7" t="inlineStr">
         <is>
-          <t>bumpitrage</t>
+          <t>opportunistic</t>
         </is>
       </c>
       <c r="C11" s="16" t="n">
-        <v>-0.623</v>
+        <v>0.667</v>
       </c>
       <c r="D11" s="7" t="inlineStr">
         <is>
@@ -26583,16 +26580,16 @@
     <row r="12" ht="16" customHeight="1">
       <c r="A12" s="10" t="inlineStr">
         <is>
-          <t>net_net_ncav</t>
+          <t>tender_mech</t>
         </is>
       </c>
       <c r="B12" s="10" t="inlineStr">
         <is>
-          <t>quarterly_10q</t>
+          <t>bumpitrage</t>
         </is>
       </c>
       <c r="C12" s="17" t="n">
-        <v>0.601</v>
+        <v>-0.623</v>
       </c>
       <c r="D12" s="10" t="inlineStr">
         <is>
@@ -26603,56 +26600,56 @@
     <row r="13" ht="16" customHeight="1">
       <c r="A13" s="7" t="inlineStr">
         <is>
-          <t>tender</t>
+          <t>opportunistic</t>
         </is>
       </c>
       <c r="B13" s="7" t="inlineStr">
         <is>
-          <t>tender_mech</t>
+          <t>form4_timing</t>
         </is>
       </c>
       <c r="C13" s="16" t="n">
-        <v>-0.598</v>
+        <v>0.62</v>
       </c>
       <c r="D13" s="7" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>very_high</t>
         </is>
       </c>
     </row>
     <row r="14" ht="16" customHeight="1">
       <c r="A14" s="10" t="inlineStr">
         <is>
-          <t>psu</t>
+          <t>net_net_ncav</t>
         </is>
       </c>
       <c r="B14" s="10" t="inlineStr">
         <is>
-          <t>recent_incentive</t>
+          <t>quarterly_10q</t>
         </is>
       </c>
       <c r="C14" s="17" t="n">
-        <v>0.574</v>
+        <v>0.601</v>
       </c>
       <c r="D14" s="10" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>very_high</t>
         </is>
       </c>
     </row>
     <row r="15" ht="16" customHeight="1">
       <c r="A15" s="7" t="inlineStr">
         <is>
-          <t>voss_cic</t>
+          <t>tender</t>
         </is>
       </c>
       <c r="B15" s="7" t="inlineStr">
         <is>
-          <t>coval_stafford</t>
+          <t>tender_mech</t>
         </is>
       </c>
       <c r="C15" s="16" t="n">
-        <v>0.513</v>
+        <v>-0.598</v>
       </c>
       <c r="D15" s="7" t="inlineStr">
         <is>
@@ -26668,11 +26665,11 @@
       </c>
       <c r="B16" s="10" t="inlineStr">
         <is>
-          <t>valuation</t>
+          <t>recent_incentive</t>
         </is>
       </c>
       <c r="C16" s="17" t="n">
-        <v>0.477</v>
+        <v>0.574</v>
       </c>
       <c r="D16" s="10" t="inlineStr">
         <is>
@@ -26683,7 +26680,7 @@
     <row r="17" ht="16" customHeight="1">
       <c r="A17" s="7" t="inlineStr">
         <is>
-          <t>valuation</t>
+          <t>voss_cic</t>
         </is>
       </c>
       <c r="B17" s="7" t="inlineStr">
@@ -26692,7 +26689,7 @@
         </is>
       </c>
       <c r="C17" s="16" t="n">
-        <v>0.477</v>
+        <v>0.513</v>
       </c>
       <c r="D17" s="7" t="inlineStr">
         <is>
@@ -26703,16 +26700,16 @@
     <row r="18" ht="16" customHeight="1">
       <c r="A18" s="10" t="inlineStr">
         <is>
-          <t>valuation</t>
+          <t>psu</t>
         </is>
       </c>
       <c r="B18" s="10" t="inlineStr">
         <is>
-          <t>recent_incentive</t>
+          <t>payoff_geometry</t>
         </is>
       </c>
       <c r="C18" s="17" t="n">
-        <v>0.46</v>
+        <v>0.484</v>
       </c>
       <c r="D18" s="10" t="inlineStr">
         <is>
@@ -26723,16 +26720,16 @@
     <row r="19" ht="16" customHeight="1">
       <c r="A19" s="7" t="inlineStr">
         <is>
-          <t>recent_incentive</t>
+          <t>psu</t>
         </is>
       </c>
       <c r="B19" s="7" t="inlineStr">
         <is>
-          <t>coval_stafford</t>
+          <t>valuation</t>
         </is>
       </c>
       <c r="C19" s="16" t="n">
-        <v>0.43</v>
+        <v>0.477</v>
       </c>
       <c r="D19" s="7" t="inlineStr">
         <is>
@@ -26743,7 +26740,7 @@
     <row r="20" ht="16" customHeight="1">
       <c r="A20" s="10" t="inlineStr">
         <is>
-          <t>psu</t>
+          <t>valuation</t>
         </is>
       </c>
       <c r="B20" s="10" t="inlineStr">
@@ -26752,7 +26749,7 @@
         </is>
       </c>
       <c r="C20" s="17" t="n">
-        <v>0.419</v>
+        <v>0.477</v>
       </c>
       <c r="D20" s="10" t="inlineStr">
         <is>
@@ -26763,20 +26760,20 @@
     <row r="21" ht="16" customHeight="1">
       <c r="A21" s="7" t="inlineStr">
         <is>
-          <t>psu</t>
+          <t>discretionary_conviction</t>
         </is>
       </c>
       <c r="B21" s="7" t="inlineStr">
         <is>
-          <t>voss_cic</t>
+          <t>form4_timing</t>
         </is>
       </c>
       <c r="C21" s="16" t="n">
-        <v>0.386</v>
+        <v>0.465</v>
       </c>
       <c r="D21" s="7" t="inlineStr">
         <is>
-          <t>moderate</t>
+          <t>high</t>
         </is>
       </c>
     </row>
@@ -26788,35 +26785,35 @@
       </c>
       <c r="B22" s="10" t="inlineStr">
         <is>
-          <t>net_net_ncav</t>
+          <t>recent_incentive</t>
         </is>
       </c>
       <c r="C22" s="17" t="n">
-        <v>0.342</v>
+        <v>0.46</v>
       </c>
       <c r="D22" s="10" t="inlineStr">
         <is>
-          <t>moderate</t>
+          <t>high</t>
         </is>
       </c>
     </row>
     <row r="23" ht="16" customHeight="1">
       <c r="A23" s="7" t="inlineStr">
         <is>
-          <t>recent_incentive</t>
+          <t>f4_buys</t>
         </is>
       </c>
       <c r="B23" s="7" t="inlineStr">
         <is>
-          <t>opportunistic</t>
+          <t>form4_timing</t>
         </is>
       </c>
       <c r="C23" s="16" t="n">
-        <v>0.34</v>
+        <v>0.438</v>
       </c>
       <c r="D23" s="7" t="inlineStr">
         <is>
-          <t>moderate</t>
+          <t>high</t>
         </is>
       </c>
     </row>
@@ -26828,71 +26825,71 @@
       </c>
       <c r="B24" s="10" t="inlineStr">
         <is>
-          <t>special_sits</t>
+          <t>coval_stafford</t>
         </is>
       </c>
       <c r="C24" s="17" t="n">
-        <v>0.301</v>
+        <v>0.43</v>
       </c>
       <c r="D24" s="10" t="inlineStr">
         <is>
-          <t>moderate</t>
+          <t>high</t>
         </is>
       </c>
     </row>
     <row r="25" ht="16" customHeight="1">
       <c r="A25" s="7" t="inlineStr">
         <is>
-          <t>recent_incentive</t>
+          <t>psu</t>
         </is>
       </c>
       <c r="B25" s="7" t="inlineStr">
         <is>
-          <t>voss_cic</t>
+          <t>coval_stafford</t>
         </is>
       </c>
       <c r="C25" s="16" t="n">
-        <v>0.3</v>
+        <v>0.419</v>
       </c>
       <c r="D25" s="7" t="inlineStr">
         <is>
-          <t>moderate</t>
+          <t>high</t>
         </is>
       </c>
     </row>
     <row r="26" ht="16" customHeight="1">
       <c r="A26" s="10" t="inlineStr">
         <is>
-          <t>valuation</t>
+          <t>recent_incentive</t>
         </is>
       </c>
       <c r="B26" s="10" t="inlineStr">
         <is>
-          <t>voss_cic</t>
+          <t>payoff_geometry</t>
         </is>
       </c>
       <c r="C26" s="17" t="n">
-        <v>0.297</v>
+        <v>0.407</v>
       </c>
       <c r="D26" s="10" t="inlineStr">
         <is>
-          <t>moderate</t>
+          <t>high</t>
         </is>
       </c>
     </row>
     <row r="27" ht="16" customHeight="1">
       <c r="A27" s="7" t="inlineStr">
         <is>
-          <t>discretionary_conviction</t>
+          <t>payoff_geometry</t>
         </is>
       </c>
       <c r="B27" s="7" t="inlineStr">
         <is>
-          <t>bb_insider_overlay</t>
+          <t>coval_stafford</t>
         </is>
       </c>
       <c r="C27" s="16" t="n">
-        <v>0.279</v>
+        <v>0.396</v>
       </c>
       <c r="D27" s="7" t="inlineStr">
         <is>
@@ -26903,16 +26900,16 @@
     <row r="28" ht="16" customHeight="1">
       <c r="A28" s="10" t="inlineStr">
         <is>
-          <t>post_ch11</t>
+          <t>psu</t>
         </is>
       </c>
       <c r="B28" s="10" t="inlineStr">
         <is>
-          <t>equity_committee</t>
+          <t>voss_cic</t>
         </is>
       </c>
       <c r="C28" s="17" t="n">
-        <v>0.277</v>
+        <v>0.386</v>
       </c>
       <c r="D28" s="10" t="inlineStr">
         <is>
@@ -26923,16 +26920,16 @@
     <row r="29" ht="16" customHeight="1">
       <c r="A29" s="7" t="inlineStr">
         <is>
-          <t>valuation</t>
+          <t>payoff_geometry</t>
         </is>
       </c>
       <c r="B29" s="7" t="inlineStr">
         <is>
-          <t>financial_primary</t>
+          <t>net_net_ncav</t>
         </is>
       </c>
       <c r="C29" s="16" t="n">
-        <v>0.275</v>
+        <v>0.357</v>
       </c>
       <c r="D29" s="7" t="inlineStr">
         <is>
@@ -26943,16 +26940,16 @@
     <row r="30" ht="16" customHeight="1">
       <c r="A30" s="10" t="inlineStr">
         <is>
-          <t>f4_buys</t>
+          <t>valuation</t>
         </is>
       </c>
       <c r="B30" s="10" t="inlineStr">
         <is>
-          <t>bb_insider_overlay</t>
+          <t>net_net_ncav</t>
         </is>
       </c>
       <c r="C30" s="17" t="n">
-        <v>0.274</v>
+        <v>0.342</v>
       </c>
       <c r="D30" s="10" t="inlineStr">
         <is>
@@ -26963,16 +26960,16 @@
     <row r="31" ht="16" customHeight="1">
       <c r="A31" s="7" t="inlineStr">
         <is>
-          <t>valuation</t>
+          <t>recent_incentive</t>
         </is>
       </c>
       <c r="B31" s="7" t="inlineStr">
         <is>
-          <t>quarterly_10q</t>
+          <t>opportunistic</t>
         </is>
       </c>
       <c r="C31" s="16" t="n">
-        <v>0.265</v>
+        <v>0.34</v>
       </c>
       <c r="D31" s="7" t="inlineStr">
         <is>
@@ -26983,16 +26980,16 @@
     <row r="32" ht="16" customHeight="1">
       <c r="A32" s="10" t="inlineStr">
         <is>
-          <t>psu</t>
+          <t>recent_incentive</t>
         </is>
       </c>
       <c r="B32" s="10" t="inlineStr">
         <is>
-          <t>buyback</t>
+          <t>special_sits</t>
         </is>
       </c>
       <c r="C32" s="17" t="n">
-        <v>0.253</v>
+        <v>0.301</v>
       </c>
       <c r="D32" s="10" t="inlineStr">
         <is>
@@ -27000,8 +26997,88 @@
         </is>
       </c>
     </row>
-    <row r="34" ht="28" customHeight="1">
-      <c r="A34" s="11" t="inlineStr">
+    <row r="33" ht="16" customHeight="1">
+      <c r="A33" s="7" t="inlineStr">
+        <is>
+          <t>recent_incentive</t>
+        </is>
+      </c>
+      <c r="B33" s="7" t="inlineStr">
+        <is>
+          <t>voss_cic</t>
+        </is>
+      </c>
+      <c r="C33" s="16" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="D33" s="7" t="inlineStr">
+        <is>
+          <t>moderate</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="16" customHeight="1">
+      <c r="A34" s="10" t="inlineStr">
+        <is>
+          <t>valuation</t>
+        </is>
+      </c>
+      <c r="B34" s="10" t="inlineStr">
+        <is>
+          <t>voss_cic</t>
+        </is>
+      </c>
+      <c r="C34" s="17" t="n">
+        <v>0.297</v>
+      </c>
+      <c r="D34" s="10" t="inlineStr">
+        <is>
+          <t>moderate</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="16" customHeight="1">
+      <c r="A35" s="7" t="inlineStr">
+        <is>
+          <t>voss_cic</t>
+        </is>
+      </c>
+      <c r="B35" s="7" t="inlineStr">
+        <is>
+          <t>payoff_geometry</t>
+        </is>
+      </c>
+      <c r="C35" s="16" t="n">
+        <v>0.283</v>
+      </c>
+      <c r="D35" s="7" t="inlineStr">
+        <is>
+          <t>moderate</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="16" customHeight="1">
+      <c r="A36" s="10" t="inlineStr">
+        <is>
+          <t>payoff_geometry</t>
+        </is>
+      </c>
+      <c r="B36" s="10" t="inlineStr">
+        <is>
+          <t>quarterly_10q</t>
+        </is>
+      </c>
+      <c r="C36" s="17" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="D36" s="10" t="inlineStr">
+        <is>
+          <t>moderate</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="28" customHeight="1">
+      <c r="A38" s="11" t="inlineStr">
         <is>
           <t>Spearman rank correlation across the full universe. Pairs above rho 0.6 are folded into a single effective layer for the independence count: PSU + Voss CIC (Voss derives from the PSU plan), the tender family (tender + mechanism + bumpitrage share one source), and Form 4 + opportunistic insiders (one refines the other). A high raw layer-firing count should be read against this: nine layers firing is closer to seven or eight genuinely independent confirmations.</t>
         </is>
@@ -27009,10 +27086,10 @@
     </row>
   </sheetData>
   <mergeCells count="4">
+    <mergeCell ref="A38:D38"/>
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="A4:D4"/>
     <mergeCell ref="A2:D2"/>
-    <mergeCell ref="A34:D34"/>
   </mergeCells>
   <printOptions horizontalCentered="0"/>
   <pageMargins left="0.5" right="0.5" top="0.6" bottom="0.6" header="0.5" footer="0.5"/>
@@ -27103,7 +27180,7 @@
       </c>
       <c r="D5" s="7" t="inlineStr">
         <is>
-          <t>0d</t>
+          <t>5d</t>
         </is>
       </c>
       <c r="E5" s="7" t="inlineStr">
@@ -27131,7 +27208,7 @@
       </c>
       <c r="D6" s="10" t="inlineStr">
         <is>
-          <t>0d</t>
+          <t>5d</t>
         </is>
       </c>
       <c r="E6" s="10" t="inlineStr">
@@ -27159,7 +27236,7 @@
       </c>
       <c r="D7" s="7" t="inlineStr">
         <is>
-          <t>14d</t>
+          <t>5d</t>
         </is>
       </c>
       <c r="E7" s="7" t="inlineStr">
@@ -27187,7 +27264,7 @@
       </c>
       <c r="D8" s="10" t="inlineStr">
         <is>
-          <t>14d</t>
+          <t>5d</t>
         </is>
       </c>
       <c r="E8" s="10" t="inlineStr">
@@ -27215,7 +27292,7 @@
       </c>
       <c r="D9" s="7" t="inlineStr">
         <is>
-          <t>14d</t>
+          <t>5d</t>
         </is>
       </c>
       <c r="E9" s="7" t="inlineStr">
@@ -27243,7 +27320,7 @@
       </c>
       <c r="D10" s="10" t="inlineStr">
         <is>
-          <t>14d</t>
+          <t>5d</t>
         </is>
       </c>
       <c r="E10" s="10" t="inlineStr">
@@ -27271,7 +27348,7 @@
       </c>
       <c r="D11" s="7" t="inlineStr">
         <is>
-          <t>14d</t>
+          <t>5d</t>
         </is>
       </c>
       <c r="E11" s="7" t="inlineStr">
@@ -27299,7 +27376,7 @@
       </c>
       <c r="D12" s="10" t="inlineStr">
         <is>
-          <t>14d</t>
+          <t>5d</t>
         </is>
       </c>
       <c r="E12" s="10" t="inlineStr">
@@ -27327,7 +27404,7 @@
       </c>
       <c r="D13" s="7" t="inlineStr">
         <is>
-          <t>13d</t>
+          <t>5d</t>
         </is>
       </c>
       <c r="E13" s="7" t="inlineStr">
@@ -27383,7 +27460,7 @@
       </c>
       <c r="D15" s="7" t="inlineStr">
         <is>
-          <t>14d</t>
+          <t>5d</t>
         </is>
       </c>
       <c r="E15" s="7" t="inlineStr">
@@ -27411,7 +27488,7 @@
       </c>
       <c r="D16" s="10" t="inlineStr">
         <is>
-          <t>14d</t>
+          <t>5d</t>
         </is>
       </c>
       <c r="E16" s="10" t="inlineStr">
@@ -27439,7 +27516,7 @@
       </c>
       <c r="D17" s="7" t="inlineStr">
         <is>
-          <t>14d</t>
+          <t>5d</t>
         </is>
       </c>
       <c r="E17" s="7" t="inlineStr">
@@ -27579,7 +27656,7 @@
       </c>
       <c r="D22" s="10" t="inlineStr">
         <is>
-          <t>14d</t>
+          <t>5d</t>
         </is>
       </c>
       <c r="E22" s="10" t="inlineStr">
@@ -27662,7 +27739,7 @@
         <v>11</v>
       </c>
       <c r="B28" s="16" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C28" s="7" t="inlineStr">
         <is>
@@ -27675,7 +27752,7 @@
         <v>10</v>
       </c>
       <c r="B29" s="17" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="C29" s="10" t="inlineStr">
         <is>
@@ -27688,7 +27765,7 @@
         <v>9</v>
       </c>
       <c r="B30" s="16" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C30" s="7" t="inlineStr">
         <is>
@@ -27701,7 +27778,7 @@
         <v>8</v>
       </c>
       <c r="B31" s="17" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C31" s="10" t="inlineStr">
         <is>
@@ -27714,7 +27791,7 @@
         <v>7</v>
       </c>
       <c r="B32" s="16" t="n">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="C32" s="7" t="inlineStr">
         <is>
@@ -27740,7 +27817,7 @@
         <v>5</v>
       </c>
       <c r="B34" s="16" t="n">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="C34" s="7" t="inlineStr">
         <is>
@@ -27753,7 +27830,7 @@
         <v>4</v>
       </c>
       <c r="B35" s="17" t="n">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="C35" s="10" t="inlineStr">
         <is>
@@ -27766,7 +27843,7 @@
         <v>3</v>
       </c>
       <c r="B36" s="16" t="n">
-        <v>444</v>
+        <v>439</v>
       </c>
       <c r="C36" s="7" t="inlineStr">
         <is>
@@ -27779,7 +27856,7 @@
         <v>2</v>
       </c>
       <c r="B37" s="17" t="n">
-        <v>691</v>
+        <v>703</v>
       </c>
       <c r="C37" s="10" t="inlineStr">
         <is>
@@ -27889,7 +27966,7 @@
           <t>Universe construction</t>
         </is>
       </c>
-      <c r="C5" s="26" t="inlineStr">
+      <c r="C5" s="25" t="inlineStr">
         <is>
           <t>6,164 US-listed common tickers from cancel_10b5_1.json — authoritative NYSE/Nasdaq/AMEX/CBOE set. Foreign names (JP/KR/UK) live in a separate tab and universe.</t>
         </is>
@@ -27904,7 +27981,7 @@
           <t>Layer ingestion</t>
         </is>
       </c>
-      <c r="C6" s="27" t="inlineStr">
+      <c r="C6" s="26" t="inlineStr">
         <is>
           <t>44 additive scoring layers ingested per ticker, spanning PSU forensics, governance, valuation, verified buybacks, tender mechanics, 10b5-1 direction, Form 4 (raw + Cohen-Malloy opportunistic), Form 144, quarterly 10-Q, NCAV, Voss CIC, post-Ch11, internalization, bumpitrage, spinoff timing, Arquitos, Coval-Stafford proxy + real N-PORT, backstopped rights, FDIC dark banks, activist letters, 13F-delta, biotech PDUFA, financial-sector primary, discretionary insider conviction, emergence cross-feed, Sohn pitches, asymmetry assembly (PSIX recipe), distressed-stub progress, premium injections, selective buybacks, hidden-asset realisation, net buyback (diluted-share reduction net of SBC), the Lynch reawakening momentum leg, the Form 4 filing-TIME signal (off-hours / Friday-evening open-market buys = quiet accumulators followed; market-hours buys = price support, faded), the MD&amp;A intent-language scan (value-unlock / transformative / capital-policy / governance / strategic-action phrasing mined from 10-K/10-Q narrative, negation-verified), and the payoff-geometry engine (asset-backed downside floor vs sector re-rate upside -&gt; asymmetry ratio; see the Payoff Geometry and Mechanism Gates tabs).</t>
         </is>
@@ -27919,7 +27996,7 @@
           <t>Additive discipline</t>
         </is>
       </c>
-      <c r="C7" s="26" t="inlineStr">
+      <c r="C7" s="25" t="inlineStr">
         <is>
           <t>Every layer ADDS to the composite; none modifies another's score. New legs append fields; existing weights never change. This is enforced and audited (verify_universe_methodology.py).</t>
         </is>
@@ -27934,7 +28011,7 @@
           <t>Coverage-normalised composite</t>
         </is>
       </c>
-      <c r="C8" s="27" t="inlineStr">
+      <c r="C8" s="26" t="inlineStr">
         <is>
           <t>Sparse-coverage names are not penalised for missing layers; the norm score rescales by sqrt(n_total/n_present) so a name strong on few layers competes with a name mediocre on many.</t>
         </is>
@@ -27949,7 +28026,7 @@
           <t>Per-pattern catalyst ranking</t>
         </is>
       </c>
-      <c r="C9" s="26" t="inlineStr">
+      <c r="C9" s="25" t="inlineStr">
         <is>
           <t>Top names in each catalyst pattern (forward $ hurdle, M&amp;A close, spin trigger, FDA/PDUFA, post-Ch11, asset sale, etc.) — surfaces single-mandate leaders (see Single-Measure tab).</t>
         </is>
@@ -27964,7 +28041,7 @@
           <t>Archetype winners</t>
         </is>
       </c>
-      <c r="C10" s="27" t="inlineStr">
+      <c r="C10" s="26" t="inlineStr">
         <is>
           <t>57 PSU/governance/thesis buckets — single best representative of each archetype across the universe (PSU_ARCHETYPES.md 38 + ASYMMETRIC_BY_ARCHETYPE.md 19).</t>
         </is>
@@ -27979,7 +28056,7 @@
           <t>Consensus meta-ranking</t>
         </is>
       </c>
-      <c r="C11" s="26" t="inlineStr">
+      <c r="C11" s="25" t="inlineStr">
         <is>
           <t>n_layers_firing = how many of the 44 independent layers produce a non-zero score for the ticker. consensus_score = sum of per-layer rank-decay contributions across the universe.</t>
         </is>
@@ -27994,7 +28071,7 @@
           <t>Layer independence</t>
         </is>
       </c>
-      <c r="C12" s="27" t="inlineStr">
+      <c r="C12" s="26" t="inlineStr">
         <is>
           <t>Pairwise Spearman correlation (layer_correlation_pairs.csv) collapses 44 raw layers to effective-independent at rho&gt;0.6. Three correlated clusters: PSU+Voss, tender family, F4+opportunistic. 'Fires 9 layers' ≈ 7-8 true confirmations.</t>
         </is>
@@ -28009,7 +28086,7 @@
           <t>Freshness weighting</t>
         </is>
       </c>
-      <c r="C13" s="26" t="inlineStr">
+      <c r="C13" s="25" t="inlineStr">
         <is>
           <t>layer_freshness.json records each layer's data age. Most layers are &lt;14 days old. An optional age-decay multiplier (opt-in) can down-weight stale layers; current build reports age without auto-decaying.</t>
         </is>
@@ -28024,7 +28101,7 @@
           <t>Caution layering</t>
         </is>
       </c>
-      <c r="C14" s="27" t="inlineStr">
+      <c r="C14" s="26" t="inlineStr">
         <is>
           <t>Eight red-flag classes from plan text: single-trigger CIC, repricing, retirement carveout, front-loaded grant, discretionary hurdle, aggregate-only metrics, plus structural. Convergence without direction; flag count modulates sizing.</t>
         </is>
@@ -28039,7 +28116,7 @@
           <t>Deployment / sizing</t>
         </is>
       </c>
-      <c r="C15" s="26" t="inlineStr">
+      <c r="C15" s="25" t="inlineStr">
         <is>
           <t>Concentrated (≥5%): clean high-layer-count names. Material (2-5%): strong but 1-2 flags. Participation (0.5-2%): single-leg or multi-flag. Basket (&lt;1% each): sub-archetype groups, Cohen-Malloy stack, R2000-boundary, NOL shells, foreign.</t>
         </is>
@@ -28054,7 +28131,7 @@
           <t>Honest limitations</t>
         </is>
       </c>
-      <c r="C16" s="27" t="inlineStr">
+      <c r="C16" s="26" t="inlineStr">
         <is>
           <t>Most layers are not yet return-validated (AUDIT.md S1.1) — the composite is a structurally-sound pattern-recognition system, not yet validated alpha. The one exception is the Form 4 filing-time layer, built FROM a measured test: off-hours buys showed a +3.7% median vs -8.0% for market-hours buys (+11.7pp differential, buy-to-now proxy). Cohen-Malloy needs deeper Form 4 history. Coval-Stafford proxy supplements but does not replace the N-PORT real signal. See AUDIT.md for the full ledger.</t>
         </is>
@@ -28206,7 +28283,7 @@
       </c>
       <c r="H5" s="7" t="inlineStr">
         <is>
-          <t>13 layers firing | cons 10.676</t>
+          <t>13 layers firing | cons 10.698</t>
         </is>
       </c>
       <c r="I5" s="7" t="inlineStr">
@@ -28250,7 +28327,7 @@
       </c>
       <c r="H6" s="10" t="inlineStr">
         <is>
-          <t>11 layers firing | cons 10.208</t>
+          <t>11 layers firing | cons 10.412</t>
         </is>
       </c>
       <c r="I6" s="10" t="inlineStr">
@@ -28267,25 +28344,25 @@
     <row r="7" ht="56" customHeight="1">
       <c r="A7" s="6" t="inlineStr">
         <is>
-          <t>CRM</t>
+          <t>GPK</t>
         </is>
       </c>
       <c r="B7" s="7" t="inlineStr">
         <is>
-          <t>Salesforce</t>
+          <t>GPK</t>
         </is>
       </c>
       <c r="C7" s="5" t="n">
-        <v>124308</v>
+        <v>3169</v>
       </c>
       <c r="D7" s="16" t="n">
-        <v>151.78</v>
+        <v>10.71</v>
       </c>
       <c r="E7" s="16" t="n">
-        <v>3.63</v>
+        <v>0.98</v>
       </c>
       <c r="F7" s="5" t="n">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="G7" s="7" t="inlineStr">
         <is>
@@ -28294,42 +28371,42 @@
       </c>
       <c r="H7" s="7" t="inlineStr">
         <is>
-          <t>PSU + buyback + recent 10b5-1 termination + F4 cluster</t>
+          <t>11 layers firing | cons 8.872</t>
         </is>
       </c>
       <c r="I7" s="7" t="inlineStr">
         <is>
-          <t>Mega-cap recurring revenue base</t>
-        </is>
-      </c>
-      <c r="J7" s="7" t="inlineStr">
-        <is>
-          <t>Material 2-5%</t>
+          <t>see proxy_scan + buyback_verify</t>
+        </is>
+      </c>
+      <c r="J7" s="6" t="inlineStr">
+        <is>
+          <t>Concentrated 5%+</t>
         </is>
       </c>
     </row>
     <row r="8" ht="56" customHeight="1">
       <c r="A8" s="9" t="inlineStr">
         <is>
-          <t>GPK</t>
+          <t>CRM</t>
         </is>
       </c>
       <c r="B8" s="10" t="inlineStr">
         <is>
-          <t>GPK</t>
+          <t>Salesforce</t>
         </is>
       </c>
       <c r="C8" s="8" t="n">
-        <v>3169</v>
+        <v>124308</v>
       </c>
       <c r="D8" s="17" t="n">
-        <v>10.71</v>
+        <v>151.78</v>
       </c>
       <c r="E8" s="17" t="n">
-        <v>0.98</v>
+        <v>3.63</v>
       </c>
       <c r="F8" s="8" t="n">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="G8" s="10" t="inlineStr">
         <is>
@@ -28338,17 +28415,17 @@
       </c>
       <c r="H8" s="10" t="inlineStr">
         <is>
-          <t>11 layers firing | cons 8.634</t>
+          <t>PSU + buyback + recent 10b5-1 termination + F4 cluster</t>
         </is>
       </c>
       <c r="I8" s="10" t="inlineStr">
         <is>
-          <t>see proxy_scan + buyback_verify</t>
-        </is>
-      </c>
-      <c r="J8" s="6" t="inlineStr">
-        <is>
-          <t>Concentrated 5%+</t>
+          <t>Mega-cap recurring revenue base</t>
+        </is>
+      </c>
+      <c r="J8" s="10" t="inlineStr">
+        <is>
+          <t>Material 2-5%</t>
         </is>
       </c>
     </row>
@@ -28399,34 +28476,34 @@
     <row r="10" ht="56" customHeight="1">
       <c r="A10" s="9" t="inlineStr">
         <is>
-          <t>POOL</t>
+          <t>WW</t>
         </is>
       </c>
       <c r="B10" s="10" t="inlineStr">
         <is>
-          <t>POOL</t>
+          <t>WW</t>
         </is>
       </c>
       <c r="C10" s="8" t="n">
-        <v>7252</v>
+        <v>192</v>
       </c>
       <c r="D10" s="17" t="n">
-        <v>198.99</v>
+        <v>19.2</v>
       </c>
       <c r="E10" s="17" t="n">
-        <v>6.4</v>
+        <v>0.6</v>
       </c>
       <c r="F10" s="8" t="n">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="G10" s="10" t="inlineStr">
         <is>
-          <t>fda_phase_milestone</t>
+          <t>chapter11_emergence</t>
         </is>
       </c>
       <c r="H10" s="10" t="inlineStr">
         <is>
-          <t>11 layers firing | cons 7.424</t>
+          <t>10 layers firing | cons 8.756</t>
         </is>
       </c>
       <c r="I10" s="10" t="inlineStr">
@@ -28443,39 +28520,39 @@
     <row r="11" ht="56" customHeight="1">
       <c r="A11" s="6" t="inlineStr">
         <is>
-          <t>WW</t>
+          <t>GO</t>
         </is>
       </c>
       <c r="B11" s="7" t="inlineStr">
         <is>
-          <t>WW</t>
+          <t>Grocery Outlet</t>
         </is>
       </c>
       <c r="C11" s="5" t="n">
-        <v>192</v>
+        <v>916</v>
       </c>
       <c r="D11" s="16" t="n">
-        <v>19.2</v>
+        <v>9.26</v>
       </c>
       <c r="E11" s="16" t="n">
-        <v>0.6</v>
+        <v>1.13</v>
       </c>
       <c r="F11" s="5" t="n">
-        <v>34</v>
+        <v>69</v>
       </c>
       <c r="G11" s="7" t="inlineStr">
         <is>
-          <t>chapter11_emergence</t>
+          <t>–</t>
         </is>
       </c>
       <c r="H11" s="7" t="inlineStr">
         <is>
-          <t>10 layers firing | cons 8.76</t>
+          <t>Forward $ targets + Cohen-Malloy 6-buyer cluster</t>
         </is>
       </c>
       <c r="I11" s="7" t="inlineStr">
         <is>
-          <t>see proxy_scan + buyback_verify</t>
+          <t>Discount-grocery defensive base</t>
         </is>
       </c>
       <c r="J11" s="6" t="inlineStr">
@@ -28487,25 +28564,25 @@
     <row r="12" ht="56" customHeight="1">
       <c r="A12" s="9" t="inlineStr">
         <is>
-          <t>GO</t>
+          <t>FOUR</t>
         </is>
       </c>
       <c r="B12" s="10" t="inlineStr">
         <is>
-          <t>Grocery Outlet</t>
+          <t>FOUR</t>
         </is>
       </c>
       <c r="C12" s="8" t="n">
-        <v>916</v>
+        <v>3906</v>
       </c>
       <c r="D12" s="17" t="n">
-        <v>9.26</v>
+        <v>39.4</v>
       </c>
       <c r="E12" s="17" t="n">
-        <v>1.13</v>
+        <v>4.82</v>
       </c>
       <c r="F12" s="8" t="n">
-        <v>69</v>
+        <v>35</v>
       </c>
       <c r="G12" s="10" t="inlineStr">
         <is>
@@ -28514,12 +28591,12 @@
       </c>
       <c r="H12" s="10" t="inlineStr">
         <is>
-          <t>Forward $ targets + Cohen-Malloy 6-buyer cluster</t>
+          <t>10 layers firing | cons 8.106</t>
         </is>
       </c>
       <c r="I12" s="10" t="inlineStr">
         <is>
-          <t>Discount-grocery defensive base</t>
+          <t>see proxy_scan + buyback_verify</t>
         </is>
       </c>
       <c r="J12" s="6" t="inlineStr">
@@ -28575,25 +28652,25 @@
     <row r="14" ht="56" customHeight="1">
       <c r="A14" s="9" t="inlineStr">
         <is>
-          <t>DXC</t>
+          <t>LW</t>
         </is>
       </c>
       <c r="B14" s="10" t="inlineStr">
         <is>
-          <t>DXC Technology</t>
+          <t>LW</t>
         </is>
       </c>
       <c r="C14" s="8" t="n">
-        <v>1394</v>
+        <v>6222</v>
       </c>
       <c r="D14" s="17" t="n">
-        <v>8.6</v>
+        <v>45.06</v>
       </c>
       <c r="E14" s="17" t="n">
-        <v>0.48</v>
+        <v>3.43</v>
       </c>
       <c r="F14" s="8" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="G14" s="10" t="inlineStr">
         <is>
@@ -28602,42 +28679,42 @@
       </c>
       <c r="H14" s="10" t="inlineStr">
         <is>
-          <t>PSU core 40 + buyback + recent-incentive 57% drawdown</t>
+          <t>10 layers firing | cons 7.834</t>
         </is>
       </c>
       <c r="I14" s="10" t="inlineStr">
         <is>
-          <t>IT services franchise; transformation signal in PSU</t>
-        </is>
-      </c>
-      <c r="J14" s="6" t="inlineStr">
-        <is>
-          <t>Participation 1-2%</t>
+          <t>see proxy_scan + buyback_verify</t>
+        </is>
+      </c>
+      <c r="J14" s="10" t="inlineStr">
+        <is>
+          <t>Material 2-5%</t>
         </is>
       </c>
     </row>
     <row r="15" ht="56" customHeight="1">
       <c r="A15" s="6" t="inlineStr">
         <is>
-          <t>LW</t>
+          <t>DXC</t>
         </is>
       </c>
       <c r="B15" s="7" t="inlineStr">
         <is>
-          <t>LW</t>
+          <t>DXC Technology</t>
         </is>
       </c>
       <c r="C15" s="5" t="n">
-        <v>6222</v>
+        <v>1394</v>
       </c>
       <c r="D15" s="16" t="n">
-        <v>45.06</v>
+        <v>8.6</v>
       </c>
       <c r="E15" s="16" t="n">
-        <v>3.43</v>
+        <v>0.48</v>
       </c>
       <c r="F15" s="5" t="n">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="G15" s="7" t="inlineStr">
         <is>
@@ -28646,42 +28723,42 @@
       </c>
       <c r="H15" s="7" t="inlineStr">
         <is>
-          <t>10 layers firing | cons 7.74</t>
+          <t>PSU core 40 + buyback + recent-incentive 57% drawdown</t>
         </is>
       </c>
       <c r="I15" s="7" t="inlineStr">
         <is>
-          <t>see proxy_scan + buyback_verify</t>
-        </is>
-      </c>
-      <c r="J15" s="7" t="inlineStr">
-        <is>
-          <t>Material 2-5%</t>
+          <t>IT services franchise; transformation signal in PSU</t>
+        </is>
+      </c>
+      <c r="J15" s="6" t="inlineStr">
+        <is>
+          <t>Participation 1-2%</t>
         </is>
       </c>
     </row>
     <row r="16" ht="56" customHeight="1">
       <c r="A16" s="9" t="inlineStr">
         <is>
-          <t>FOUR</t>
+          <t>VRSK</t>
         </is>
       </c>
       <c r="B16" s="10" t="inlineStr">
         <is>
-          <t>FOUR</t>
+          <t>VRSK</t>
         </is>
       </c>
       <c r="C16" s="8" t="n">
-        <v>3906</v>
+        <v>22772</v>
       </c>
       <c r="D16" s="17" t="n">
-        <v>39.4</v>
+        <v>173.8</v>
       </c>
       <c r="E16" s="17" t="n">
-        <v>4.82</v>
+        <v>77.83</v>
       </c>
       <c r="F16" s="8" t="n">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="G16" s="10" t="inlineStr">
         <is>
@@ -28690,7 +28767,7 @@
       </c>
       <c r="H16" s="10" t="inlineStr">
         <is>
-          <t>10 layers firing | cons 7.716</t>
+          <t>10 layers firing | cons 7.466</t>
         </is>
       </c>
       <c r="I16" s="10" t="inlineStr">
@@ -28707,25 +28784,25 @@
     <row r="17" ht="56" customHeight="1">
       <c r="A17" s="6" t="inlineStr">
         <is>
-          <t>ZTS</t>
+          <t>PAR</t>
         </is>
       </c>
       <c r="B17" s="7" t="inlineStr">
         <is>
-          <t>Zoetis</t>
+          <t>PAR</t>
         </is>
       </c>
       <c r="C17" s="5" t="n">
-        <v>32997</v>
+        <v>631</v>
       </c>
       <c r="D17" s="16" t="n">
-        <v>78.70999999999999</v>
+        <v>15.29</v>
       </c>
       <c r="E17" s="16" t="n">
-        <v>10.04</v>
+        <v>0.76</v>
       </c>
       <c r="F17" s="5" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="G17" s="7" t="inlineStr">
         <is>
@@ -28734,12 +28811,12 @@
       </c>
       <c r="H17" s="7" t="inlineStr">
         <is>
-          <t>F4 cluster + valuation + recent-incentive 60% drawdown</t>
+          <t>10 layers firing | cons 7.138</t>
         </is>
       </c>
       <c r="I17" s="7" t="inlineStr">
         <is>
-          <t>Animal health franchise</t>
+          <t>see proxy_scan + buyback_verify</t>
         </is>
       </c>
       <c r="J17" s="7" t="inlineStr">
@@ -28751,25 +28828,27 @@
     <row r="18" ht="56" customHeight="1">
       <c r="A18" s="9" t="inlineStr">
         <is>
-          <t>PAR</t>
+          <t>HDSN</t>
         </is>
       </c>
       <c r="B18" s="10" t="inlineStr">
         <is>
-          <t>PAR</t>
+          <t>Hudson Technologies</t>
         </is>
       </c>
       <c r="C18" s="8" t="n">
-        <v>631</v>
+        <v>222</v>
       </c>
       <c r="D18" s="17" t="n">
-        <v>15.29</v>
+        <v>5.27</v>
       </c>
       <c r="E18" s="17" t="n">
-        <v>0.76</v>
-      </c>
-      <c r="F18" s="8" t="n">
-        <v>16</v>
+        <v>0.93</v>
+      </c>
+      <c r="F18" s="10" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
       <c r="G18" s="10" t="inlineStr">
         <is>
@@ -28778,44 +28857,42 @@
       </c>
       <c r="H18" s="10" t="inlineStr">
         <is>
-          <t>10 layers firing | cons 7.29</t>
+          <t>Recent F4 cluster + buyback + special-sits + recent-incentive</t>
         </is>
       </c>
       <c r="I18" s="10" t="inlineStr">
         <is>
-          <t>see proxy_scan + buyback_verify</t>
-        </is>
-      </c>
-      <c r="J18" s="10" t="inlineStr">
-        <is>
-          <t>Material 2-5%</t>
+          <t>Refrigerant reclaim regulatory moat</t>
+        </is>
+      </c>
+      <c r="J18" s="6" t="inlineStr">
+        <is>
+          <t>Concentrated 5%+</t>
         </is>
       </c>
     </row>
     <row r="19" ht="56" customHeight="1">
       <c r="A19" s="6" t="inlineStr">
         <is>
-          <t>HDSN</t>
+          <t>ZTS</t>
         </is>
       </c>
       <c r="B19" s="7" t="inlineStr">
         <is>
-          <t>Hudson Technologies</t>
+          <t>Zoetis</t>
         </is>
       </c>
       <c r="C19" s="5" t="n">
-        <v>222</v>
+        <v>32997</v>
       </c>
       <c r="D19" s="16" t="n">
-        <v>5.27</v>
+        <v>78.70999999999999</v>
       </c>
       <c r="E19" s="16" t="n">
-        <v>0.93</v>
-      </c>
-      <c r="F19" s="7" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+        <v>10.04</v>
+      </c>
+      <c r="F19" s="5" t="n">
+        <v>8</v>
       </c>
       <c r="G19" s="7" t="inlineStr">
         <is>
@@ -28824,51 +28901,51 @@
       </c>
       <c r="H19" s="7" t="inlineStr">
         <is>
-          <t>Recent F4 cluster + buyback + special-sits + recent-incentive</t>
+          <t>F4 cluster + valuation + recent-incentive 60% drawdown</t>
         </is>
       </c>
       <c r="I19" s="7" t="inlineStr">
         <is>
-          <t>Refrigerant reclaim regulatory moat</t>
-        </is>
-      </c>
-      <c r="J19" s="6" t="inlineStr">
-        <is>
-          <t>Concentrated 5%+</t>
+          <t>Animal health franchise</t>
+        </is>
+      </c>
+      <c r="J19" s="7" t="inlineStr">
+        <is>
+          <t>Material 2-5%</t>
         </is>
       </c>
     </row>
     <row r="20" ht="56" customHeight="1">
       <c r="A20" s="9" t="inlineStr">
         <is>
-          <t>CERT</t>
+          <t>POOL</t>
         </is>
       </c>
       <c r="B20" s="10" t="inlineStr">
         <is>
-          <t>CERT</t>
+          <t>POOL</t>
         </is>
       </c>
       <c r="C20" s="8" t="n">
-        <v>862</v>
+        <v>7252</v>
       </c>
       <c r="D20" s="17" t="n">
-        <v>5.54</v>
+        <v>198.99</v>
       </c>
       <c r="E20" s="17" t="n">
-        <v>0.84</v>
+        <v>6.4</v>
       </c>
       <c r="F20" s="8" t="n">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="G20" s="10" t="inlineStr">
         <is>
-          <t>–</t>
+          <t>fda_phase_milestone</t>
         </is>
       </c>
       <c r="H20" s="10" t="inlineStr">
         <is>
-          <t>10 layers firing | cons 6.426</t>
+          <t>10 layers firing | cons 6.558</t>
         </is>
       </c>
       <c r="I20" s="10" t="inlineStr">
@@ -28912,7 +28989,7 @@
       </c>
       <c r="H21" s="7" t="inlineStr">
         <is>
-          <t>10 layers firing | cons 6.138</t>
+          <t>10 layers firing | cons 6.252</t>
         </is>
       </c>
       <c r="I21" s="7" t="inlineStr">
@@ -28929,36 +29006,34 @@
     <row r="22" ht="56" customHeight="1">
       <c r="A22" s="9" t="inlineStr">
         <is>
-          <t>LULU</t>
+          <t>PSN</t>
         </is>
       </c>
       <c r="B22" s="10" t="inlineStr">
         <is>
-          <t>LULU</t>
+          <t>PSN</t>
         </is>
       </c>
       <c r="C22" s="8" t="n">
-        <v>13781</v>
+        <v>5585</v>
       </c>
       <c r="D22" s="17" t="n">
-        <v>121.36</v>
+        <v>52.21</v>
       </c>
       <c r="E22" s="17" t="n">
-        <v>2.85</v>
-      </c>
-      <c r="F22" s="10" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+        <v>2.11</v>
+      </c>
+      <c r="F22" s="8" t="n">
+        <v>7</v>
       </c>
       <c r="G22" s="10" t="inlineStr">
         <is>
-          <t>–</t>
+          <t>ebitda_dollar_target, operating_margin_target</t>
         </is>
       </c>
       <c r="H22" s="10" t="inlineStr">
         <is>
-          <t>10 layers firing | cons 5.874</t>
+          <t>10 layers firing | cons 6.162</t>
         </is>
       </c>
       <c r="I22" s="10" t="inlineStr">
@@ -28966,48 +29041,48 @@
           <t>see proxy_scan + buyback_verify</t>
         </is>
       </c>
-      <c r="J22" s="6" t="inlineStr">
-        <is>
-          <t>Participation 1-2%</t>
+      <c r="J22" s="10" t="inlineStr">
+        <is>
+          <t>Material 2-5%</t>
         </is>
       </c>
     </row>
     <row r="23" ht="56" customHeight="1">
       <c r="A23" s="6" t="inlineStr">
         <is>
-          <t>NUS</t>
+          <t>CERT</t>
         </is>
       </c>
       <c r="B23" s="7" t="inlineStr">
         <is>
-          <t>Nu Skin</t>
+          <t>CERT</t>
         </is>
       </c>
       <c r="C23" s="5" t="n">
-        <v>244</v>
+        <v>862</v>
       </c>
       <c r="D23" s="16" t="n">
-        <v>5.02</v>
+        <v>5.54</v>
       </c>
       <c r="E23" s="16" t="n">
-        <v>0.31</v>
+        <v>0.84</v>
       </c>
       <c r="F23" s="5" t="n">
-        <v>52</v>
+        <v>31</v>
       </c>
       <c r="G23" s="7" t="inlineStr">
         <is>
-          <t>asset_sale_named</t>
+          <t>–</t>
         </is>
       </c>
       <c r="H23" s="7" t="inlineStr">
         <is>
-          <t>Named asset-sale trigger + 5-metric clean per-share stack</t>
+          <t>10 layers firing | cons 6.112</t>
         </is>
       </c>
       <c r="I23" s="7" t="inlineStr">
         <is>
-          <t>P/B 0.33 + buyback shrinking organically</t>
+          <t>see proxy_scan + buyback_verify</t>
         </is>
       </c>
       <c r="J23" s="6" t="inlineStr">
@@ -29019,34 +29094,36 @@
     <row r="24" ht="56" customHeight="1">
       <c r="A24" s="9" t="inlineStr">
         <is>
-          <t>SNBR</t>
+          <t>LULU</t>
         </is>
       </c>
       <c r="B24" s="10" t="inlineStr">
         <is>
-          <t>SNBR</t>
+          <t>LULU</t>
         </is>
       </c>
       <c r="C24" s="8" t="n">
-        <v>5</v>
+        <v>13781</v>
       </c>
       <c r="D24" s="17" t="n">
-        <v>0.21</v>
+        <v>121.36</v>
       </c>
       <c r="E24" s="17" t="n">
-        <v>-0.01</v>
-      </c>
-      <c r="F24" s="8" t="n">
-        <v>43</v>
+        <v>2.85</v>
+      </c>
+      <c r="F24" s="10" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
       <c r="G24" s="10" t="inlineStr">
         <is>
-          <t>ebitda_dollar_target</t>
+          <t>–</t>
         </is>
       </c>
       <c r="H24" s="10" t="inlineStr">
         <is>
-          <t>9 layers firing | cons 7.388</t>
+          <t>10 layers firing | cons 5.912</t>
         </is>
       </c>
       <c r="I24" s="10" t="inlineStr">
@@ -29054,9 +29131,9 @@
           <t>see proxy_scan + buyback_verify</t>
         </is>
       </c>
-      <c r="J24" s="10" t="inlineStr">
-        <is>
-          <t>Material 2-5%</t>
+      <c r="J24" s="6" t="inlineStr">
+        <is>
+          <t>Participation 1-2%</t>
         </is>
       </c>
     </row>
@@ -31683,7 +31760,7 @@
       </c>
       <c r="B15" s="6" t="inlineStr">
         <is>
-          <t>OSUR</t>
+          <t>SD</t>
         </is>
       </c>
       <c r="C15" s="16" t="n">
@@ -31691,12 +31768,12 @@
       </c>
       <c r="D15" s="7" t="inlineStr">
         <is>
-          <t>discretionary hurdle, repricing language, single-trigger CIC</t>
+          <t>front-loaded grant</t>
         </is>
       </c>
       <c r="E15" s="6" t="inlineStr">
         <is>
-          <t>Participation — limited size</t>
+          <t>Concentrate (1 flag tolerable)</t>
         </is>
       </c>
     </row>
@@ -31706,7 +31783,7 @@
       </c>
       <c r="B16" s="9" t="inlineStr">
         <is>
-          <t>SD</t>
+          <t>OSUR</t>
         </is>
       </c>
       <c r="C16" s="17" t="n">
@@ -31714,12 +31791,12 @@
       </c>
       <c r="D16" s="10" t="inlineStr">
         <is>
-          <t>front-loaded grant</t>
+          <t>discretionary hurdle, repricing language, single-trigger CIC</t>
         </is>
       </c>
       <c r="E16" s="6" t="inlineStr">
         <is>
-          <t>Concentrate (1 flag tolerable)</t>
+          <t>Participation — limited size</t>
         </is>
       </c>
     </row>
@@ -31913,7 +31990,7 @@
       </c>
       <c r="B25" s="6" t="inlineStr">
         <is>
-          <t>BEEP</t>
+          <t>DXLG</t>
         </is>
       </c>
       <c r="C25" s="16" t="n">
@@ -31936,7 +32013,7 @@
       </c>
       <c r="B26" s="9" t="inlineStr">
         <is>
-          <t>DXLG</t>
+          <t>BEEP</t>
         </is>
       </c>
       <c r="C26" s="17" t="n">

--- a/MOST_ASYMMETRIC.xlsx
+++ b/MOST_ASYMMETRIC.xlsx
@@ -6225,7 +6225,7 @@
     <row r="51" ht="28" customHeight="1">
       <c r="A51" s="11" t="inlineStr">
         <is>
-          <t>242 names pass at least one mechanism gate; 37 light up two or more (the highest-conviction convergence). Unlike the additive consensus, these are HARD gates — every condition of a machine must hold: coiled-spring delever (D/E ≥ 1 + rising operating income + cheap equity), sub-cash buyback (net-cash floor ≥ 50% of price + active repurchase + not burning), forced-seller exhaustion (N-PORT forced selling into a floor, business not burning), hidden-asset realisation (small levered stub + credit-agreement asset sweep), stated-unlock triangulated (MD&amp;A value-unlock language + cheap geometry + insider buying), asset-sale monetization (asset-sale catalyst + cheap + levered/small — the backtest's best-median catalyst, +10%/58% hit), and tender-offer squeeze (tender/Dutch-auction catalyst + cheap small-cap — best hit rate, 61%). TWO ANTICIPATORY archetypes catch the setup BEFORE the catalyst: asset-sale latent (cheap + levered + de-lever pressure or MD&amp;A divestiture intent, NO sale announced) and tender-target latent (near net cash / NCAV, small controllable cap, plausible buyer — high insider ownership or self-tender-capable cash — and NO bid yet); these are speculative (weighted below the confirmed machines) but flag names likely to realise value that haven't yet. Plus structured distressed injection (the Cundill/Sibir play — an asset-backed washout raising via a senior/convertible instrument; see the Structured Distressed tab). Combines the payoff-geometry shape with the catalyst layers so shape and 'why now' are both required. Source: mechanism_gates.py.</t>
+          <t>236 names pass at least one mechanism gate; 37 light up two or more (the highest-conviction convergence). Unlike the additive consensus, these are HARD gates — every condition of a machine must hold: coiled-spring delever (D/E ≥ 1 + rising operating income + cheap equity), sub-cash buyback (net-cash floor ≥ 50% of price + active repurchase + not burning), forced-seller exhaustion (N-PORT forced selling into a floor, business not burning), hidden-asset realisation (small levered stub + credit-agreement asset sweep), stated-unlock triangulated (MD&amp;A value-unlock language + cheap geometry + insider buying), asset-sale monetization (asset-sale catalyst + cheap + levered/small — the backtest's best-median catalyst, +10%/58% hit), and tender-offer squeeze (tender/Dutch-auction catalyst + cheap small-cap — best hit rate, 61%). TWO ANTICIPATORY archetypes catch the setup BEFORE the catalyst: asset-sale latent (cheap + levered + de-lever pressure or MD&amp;A divestiture intent, NO sale announced) and tender-target latent (near net cash / NCAV, small controllable cap, plausible buyer — high insider ownership or self-tender-capable cash — and NO bid yet); these are speculative (weighted below the confirmed machines) but flag names likely to realise value that haven't yet. Plus structured distressed injection (the Cundill/Sibir play — an asset-backed washout raising via a senior/convertible instrument; see the Structured Distressed tab). Combines the payoff-geometry shape with the catalyst layers so shape and 'why now' are both required. Source: mechanism_gates.py.</t>
         </is>
       </c>
     </row>
@@ -8953,12 +8953,12 @@
     <row r="60" ht="22" customHeight="1">
       <c r="A60" s="9" t="inlineStr">
         <is>
-          <t>BHF</t>
+          <t>STRZ</t>
         </is>
       </c>
       <c r="B60" s="10" t="inlineStr">
         <is>
-          <t>Brighthouse Financial,</t>
+          <t>Starz Entertainment Co</t>
         </is>
       </c>
       <c r="C60" s="10" t="inlineStr">
@@ -8967,13 +8967,13 @@
         </is>
       </c>
       <c r="D60" s="17" t="n">
-        <v>16.3</v>
+        <v>16</v>
       </c>
       <c r="E60" s="17" t="n">
-        <v>0.46</v>
+        <v>0.6</v>
       </c>
       <c r="F60" s="8" t="n">
-        <v>3004.7</v>
+        <v>388.9</v>
       </c>
       <c r="G60" s="10" t="inlineStr">
         <is>
@@ -8982,19 +8982,19 @@
       </c>
       <c r="H60" s="10" t="inlineStr">
         <is>
-          <t>call commit (2025-08); cic prep</t>
+          <t>pill removed (2026-03); mda unlock (2026-08)</t>
         </is>
       </c>
     </row>
     <row r="61" ht="22" customHeight="1">
       <c r="A61" s="6" t="inlineStr">
         <is>
-          <t>STRZ</t>
+          <t>FG</t>
         </is>
       </c>
       <c r="B61" s="7" t="inlineStr">
         <is>
-          <t>Starz Entertainment Co</t>
+          <t>F&amp;G Annuities &amp; Life,</t>
         </is>
       </c>
       <c r="C61" s="7" t="inlineStr">
@@ -9006,10 +9006,10 @@
         <v>16</v>
       </c>
       <c r="E61" s="16" t="n">
-        <v>0.6</v>
+        <v>0.63</v>
       </c>
       <c r="F61" s="5" t="n">
-        <v>388.9</v>
+        <v>2887.5</v>
       </c>
       <c r="G61" s="7" t="inlineStr">
         <is>
@@ -9018,19 +9018,19 @@
       </c>
       <c r="H61" s="7" t="inlineStr">
         <is>
-          <t>pill removed (2026-03); mda unlock (2026-08)</t>
+          <t>call commit (2026-08); call value gap (2026-08)</t>
         </is>
       </c>
     </row>
     <row r="62" ht="22" customHeight="1">
       <c r="A62" s="9" t="inlineStr">
         <is>
-          <t>FG</t>
+          <t>ZSQR</t>
         </is>
       </c>
       <c r="B62" s="10" t="inlineStr">
         <is>
-          <t>F&amp;G Annuities &amp; Life,</t>
+          <t>Z Squared Inc.</t>
         </is>
       </c>
       <c r="C62" s="10" t="inlineStr">
@@ -9042,31 +9042,29 @@
         <v>16</v>
       </c>
       <c r="E62" s="17" t="n">
-        <v>0.63</v>
+        <v>0.14</v>
       </c>
       <c r="F62" s="8" t="n">
-        <v>2887.5</v>
-      </c>
-      <c r="G62" s="10" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+        <v>18</v>
+      </c>
+      <c r="G62" s="17" t="n">
+        <v>28</v>
       </c>
       <c r="H62" s="10" t="inlineStr">
         <is>
-          <t>call commit (2026-08); call value gap (2026-08)</t>
+          <t>turnaround exec (2026-04)</t>
         </is>
       </c>
     </row>
     <row r="63" ht="22" customHeight="1">
       <c r="A63" s="6" t="inlineStr">
         <is>
-          <t>ZSQR</t>
+          <t>SDEV</t>
         </is>
       </c>
       <c r="B63" s="7" t="inlineStr">
         <is>
-          <t>Z Squared Inc.</t>
+          <t>Stablecoin Development</t>
         </is>
       </c>
       <c r="C63" s="7" t="inlineStr">
@@ -9078,13 +9076,13 @@
         <v>16</v>
       </c>
       <c r="E63" s="16" t="n">
-        <v>0.14</v>
+        <v>0.46</v>
       </c>
       <c r="F63" s="5" t="n">
-        <v>18</v>
+        <v>58</v>
       </c>
       <c r="G63" s="16" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="H63" s="7" t="inlineStr">
         <is>
@@ -9095,12 +9093,12 @@
     <row r="64" ht="22" customHeight="1">
       <c r="A64" s="9" t="inlineStr">
         <is>
-          <t>SDEV</t>
+          <t>RGS</t>
         </is>
       </c>
       <c r="B64" s="10" t="inlineStr">
         <is>
-          <t>Stablecoin Development</t>
+          <t>Regis Corporation</t>
         </is>
       </c>
       <c r="C64" s="10" t="inlineStr">
@@ -9109,27 +9107,29 @@
         </is>
       </c>
       <c r="D64" s="17" t="n">
-        <v>16</v>
+        <v>15.8</v>
       </c>
       <c r="E64" s="17" t="n">
-        <v>0.46</v>
+        <v>0.37</v>
       </c>
       <c r="F64" s="8" t="n">
-        <v>58</v>
-      </c>
-      <c r="G64" s="17" t="n">
-        <v>32</v>
+        <v>70</v>
+      </c>
+      <c r="G64" s="10" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
       <c r="H64" s="10" t="inlineStr">
         <is>
-          <t>turnaround exec (2026-04)</t>
+          <t>ceo change (2026-03)</t>
         </is>
       </c>
     </row>
     <row r="66" ht="28" customHeight="1">
       <c r="A66" s="11" t="inlineStr">
         <is>
-          <t>93 names trade at 0.10–0.70× book (validated FMP book: market cap ÷ latest equity) with a qualifying governance catalyst; 30 are ACTION LIKELY (a hard event — activist settlement/13D, value committee or strategic review, capital-return policy or tender, CEO change, turnaround executive — within ~9 months, plus independent corroboration). Signals are weighted by age (≤6 months full weight, 6–12 months 0.8, 12–18 months 0.5). Pay tied to TSR/ROE appears in 63% of proxies, so it is treated as context, not as a change. Sources: governance_events_8k.py (dated 8-K governance changes), activist 13D/letters, re-rate events, MD&amp;A language, proxy redesigns and say-on-pay dissent. Source: governance_discount.py.</t>
+          <t>87 names trade at 0.10–0.70× book (validated FMP book: market cap ÷ latest equity) with a qualifying governance catalyst; 30 are ACTION LIKELY (a hard event — activist settlement/13D, value committee or strategic review, capital-return policy or tender, CEO change, turnaround executive — within ~9 months, plus independent corroboration). Signals are weighted by age (≤6 months full weight, 6–12 months 0.8, 12–18 months 0.5). Pay tied to TSR/ROE appears in 63% of proxies, so it is treated as context, not as a change. Sources: governance_events_8k.py (dated 8-K governance changes), activist 13D/letters, re-rate events, MD&amp;A language, proxy redesigns and say-on-pay dissent. Source: governance_discount.py.</t>
         </is>
       </c>
     </row>
@@ -19097,7 +19097,7 @@
       </c>
       <c r="E16" s="7" t="inlineStr">
         <is>
-          <t>12 layers firing | cons 10.86</t>
+          <t>12 layers firing | cons 10.794</t>
         </is>
       </c>
     </row>
@@ -19147,7 +19147,7 @@
       </c>
       <c r="E18" s="7" t="inlineStr">
         <is>
-          <t>12 layers firing | cons 8.712</t>
+          <t>12 layers firing | cons 9.946</t>
         </is>
       </c>
     </row>
@@ -19197,7 +19197,7 @@
       </c>
       <c r="E20" s="7" t="inlineStr">
         <is>
-          <t>11 layers firing | cons 8.37</t>
+          <t>11 layers firing | cons 8.674</t>
         </is>
       </c>
     </row>
@@ -19222,7 +19222,7 @@
       </c>
       <c r="E21" s="10" t="inlineStr">
         <is>
-          <t>11 layers firing | cons 7.65</t>
+          <t>11 layers firing | cons 7.672</t>
         </is>
       </c>
     </row>
@@ -19232,22 +19232,22 @@
       </c>
       <c r="B22" s="6" t="inlineStr">
         <is>
-          <t>GO</t>
+          <t>LULU</t>
         </is>
       </c>
       <c r="C22" s="7" t="inlineStr">
         <is>
-          <t>Grocery Outlet</t>
+          <t>LULU</t>
         </is>
       </c>
       <c r="D22" s="6" t="inlineStr">
         <is>
-          <t>Concentrated 5%+</t>
+          <t>Participation 1-2%</t>
         </is>
       </c>
       <c r="E22" s="7" t="inlineStr">
         <is>
-          <t>Forward $ targets + Cohen-Malloy 6-buyer cluster</t>
+          <t>11 layers firing | cons 6.504</t>
         </is>
       </c>
     </row>
@@ -19257,12 +19257,12 @@
       </c>
       <c r="B23" s="9" t="inlineStr">
         <is>
-          <t>FOUR</t>
+          <t>GO</t>
         </is>
       </c>
       <c r="C23" s="10" t="inlineStr">
         <is>
-          <t>FOUR</t>
+          <t>Grocery Outlet</t>
         </is>
       </c>
       <c r="D23" s="6" t="inlineStr">
@@ -19272,7 +19272,7 @@
       </c>
       <c r="E23" s="10" t="inlineStr">
         <is>
-          <t>10 layers firing | cons 7.978</t>
+          <t>Forward $ targets + Cohen-Malloy 6-buyer cluster</t>
         </is>
       </c>
     </row>
@@ -19282,12 +19282,12 @@
       </c>
       <c r="B24" s="6" t="inlineStr">
         <is>
-          <t>GPK</t>
+          <t>HUBS</t>
         </is>
       </c>
       <c r="C24" s="7" t="inlineStr">
         <is>
-          <t>GPK</t>
+          <t>HUBS</t>
         </is>
       </c>
       <c r="D24" s="6" t="inlineStr">
@@ -19297,7 +19297,7 @@
       </c>
       <c r="E24" s="7" t="inlineStr">
         <is>
-          <t>10 layers firing | cons 7.912</t>
+          <t>10 layers firing | cons 8.286</t>
         </is>
       </c>
     </row>
@@ -19307,22 +19307,22 @@
       </c>
       <c r="B25" s="9" t="inlineStr">
         <is>
-          <t>LW</t>
+          <t>GPK</t>
         </is>
       </c>
       <c r="C25" s="10" t="inlineStr">
         <is>
-          <t>LW</t>
-        </is>
-      </c>
-      <c r="D25" s="10" t="inlineStr">
-        <is>
-          <t>Material 2-5%</t>
+          <t>GPK</t>
+        </is>
+      </c>
+      <c r="D25" s="6" t="inlineStr">
+        <is>
+          <t>Concentrated 5%+</t>
         </is>
       </c>
       <c r="E25" s="10" t="inlineStr">
         <is>
-          <t>10 layers firing | cons 7.674</t>
+          <t>10 layers firing | cons 8.022</t>
         </is>
       </c>
     </row>
@@ -19332,12 +19332,12 @@
       </c>
       <c r="B26" s="6" t="inlineStr">
         <is>
-          <t>APTV</t>
+          <t>FOUR</t>
         </is>
       </c>
       <c r="C26" s="7" t="inlineStr">
         <is>
-          <t>APTV</t>
+          <t>FOUR</t>
         </is>
       </c>
       <c r="D26" s="6" t="inlineStr">
@@ -19347,7 +19347,7 @@
       </c>
       <c r="E26" s="7" t="inlineStr">
         <is>
-          <t>10 layers firing | cons 7.644</t>
+          <t>10 layers firing | cons 7.766</t>
         </is>
       </c>
     </row>
@@ -19357,12 +19357,12 @@
       </c>
       <c r="B27" s="9" t="inlineStr">
         <is>
-          <t>HUBS</t>
+          <t>GPGI</t>
         </is>
       </c>
       <c r="C27" s="10" t="inlineStr">
         <is>
-          <t>HUBS</t>
+          <t>GPGI</t>
         </is>
       </c>
       <c r="D27" s="6" t="inlineStr">
@@ -19372,7 +19372,7 @@
       </c>
       <c r="E27" s="10" t="inlineStr">
         <is>
-          <t>10 layers firing | cons 7.632</t>
+          <t>10 layers firing | cons 7.544</t>
         </is>
       </c>
     </row>
@@ -19382,12 +19382,12 @@
       </c>
       <c r="B28" s="6" t="inlineStr">
         <is>
-          <t>ADT</t>
+          <t>VRSK</t>
         </is>
       </c>
       <c r="C28" s="7" t="inlineStr">
         <is>
-          <t>ADT Inc</t>
+          <t>VRSK</t>
         </is>
       </c>
       <c r="D28" s="6" t="inlineStr">
@@ -19397,7 +19397,7 @@
       </c>
       <c r="E28" s="7" t="inlineStr">
         <is>
-          <t>Heaviest PSU%LTI in universe (90%) + verified -7.3% shrinkage</t>
+          <t>10 layers firing | cons 7.48</t>
         </is>
       </c>
     </row>
@@ -19407,12 +19407,12 @@
       </c>
       <c r="B29" s="9" t="inlineStr">
         <is>
-          <t>GPGI</t>
+          <t>ADT</t>
         </is>
       </c>
       <c r="C29" s="10" t="inlineStr">
         <is>
-          <t>GPGI</t>
+          <t>ADT Inc</t>
         </is>
       </c>
       <c r="D29" s="6" t="inlineStr">
@@ -19422,7 +19422,7 @@
       </c>
       <c r="E29" s="10" t="inlineStr">
         <is>
-          <t>10 layers firing | cons 7.516</t>
+          <t>Heaviest PSU%LTI in universe (90%) + verified -7.3% shrinkage</t>
         </is>
       </c>
     </row>
@@ -19432,12 +19432,12 @@
       </c>
       <c r="B30" s="6" t="inlineStr">
         <is>
-          <t>BLND</t>
+          <t>APTV</t>
         </is>
       </c>
       <c r="C30" s="7" t="inlineStr">
         <is>
-          <t>BLND</t>
+          <t>APTV</t>
         </is>
       </c>
       <c r="D30" s="6" t="inlineStr">
@@ -19447,7 +19447,7 @@
       </c>
       <c r="E30" s="7" t="inlineStr">
         <is>
-          <t>10 layers firing | cons 6.906</t>
+          <t>10 layers firing | cons 6.684</t>
         </is>
       </c>
     </row>
@@ -19472,7 +19472,7 @@
       </c>
       <c r="E31" s="10" t="inlineStr">
         <is>
-          <t>10 layers firing | cons 6.072</t>
+          <t>10 layers firing | cons 6.578</t>
         </is>
       </c>
     </row>
@@ -19482,22 +19482,22 @@
       </c>
       <c r="B32" s="6" t="inlineStr">
         <is>
-          <t>LULU</t>
+          <t>BLND</t>
         </is>
       </c>
       <c r="C32" s="7" t="inlineStr">
         <is>
-          <t>LULU</t>
+          <t>BLND</t>
         </is>
       </c>
       <c r="D32" s="6" t="inlineStr">
         <is>
-          <t>Participation 1-2%</t>
+          <t>Concentrated 5%+</t>
         </is>
       </c>
       <c r="E32" s="7" t="inlineStr">
         <is>
-          <t>10 layers firing | cons 6.03</t>
+          <t>10 layers firing | cons 6.542</t>
         </is>
       </c>
     </row>
@@ -19507,22 +19507,22 @@
       </c>
       <c r="B33" s="9" t="inlineStr">
         <is>
-          <t>CERT</t>
+          <t>TRS</t>
         </is>
       </c>
       <c r="C33" s="10" t="inlineStr">
         <is>
-          <t>CERT</t>
-        </is>
-      </c>
-      <c r="D33" s="6" t="inlineStr">
-        <is>
-          <t>Concentrated 5%+</t>
+          <t>TRS</t>
+        </is>
+      </c>
+      <c r="D33" s="10" t="inlineStr">
+        <is>
+          <t>Material 2-5%</t>
         </is>
       </c>
       <c r="E33" s="10" t="inlineStr">
         <is>
-          <t>10 layers firing | cons 6.01</t>
+          <t>10 layers firing | cons 6.214</t>
         </is>
       </c>
     </row>
@@ -19532,22 +19532,22 @@
       </c>
       <c r="B34" s="6" t="inlineStr">
         <is>
-          <t>TRS</t>
+          <t>CERT</t>
         </is>
       </c>
       <c r="C34" s="7" t="inlineStr">
         <is>
-          <t>TRS</t>
-        </is>
-      </c>
-      <c r="D34" s="7" t="inlineStr">
-        <is>
-          <t>Material 2-5%</t>
+          <t>CERT</t>
+        </is>
+      </c>
+      <c r="D34" s="6" t="inlineStr">
+        <is>
+          <t>Concentrated 5%+</t>
         </is>
       </c>
       <c r="E34" s="7" t="inlineStr">
         <is>
-          <t>10 layers firing | cons 5.858</t>
+          <t>10 layers firing | cons 6.08</t>
         </is>
       </c>
     </row>
@@ -19572,7 +19572,7 @@
       </c>
       <c r="E35" s="10" t="inlineStr">
         <is>
-          <t>10 layers firing | cons 5.784</t>
+          <t>10 layers firing | cons 5.882</t>
         </is>
       </c>
     </row>
@@ -20462,12 +20462,12 @@
     <row r="8" ht="22" customHeight="1">
       <c r="A8" s="9" t="inlineStr">
         <is>
-          <t>GPK</t>
+          <t>HFFG</t>
         </is>
       </c>
       <c r="B8" s="10" t="inlineStr">
         <is>
-          <t>Graphic Packaging Holdin</t>
+          <t>HF Foods Group Inc.</t>
         </is>
       </c>
       <c r="C8" s="17" t="n">
@@ -20525,12 +20525,12 @@
     <row r="9" ht="22" customHeight="1">
       <c r="A9" s="6" t="inlineStr">
         <is>
-          <t>HFFG</t>
+          <t>GPK</t>
         </is>
       </c>
       <c r="B9" s="7" t="inlineStr">
         <is>
-          <t>HF Foods Group Inc.</t>
+          <t>Graphic Packaging Holdin</t>
         </is>
       </c>
       <c r="C9" s="16" t="n">
@@ -20777,12 +20777,12 @@
     <row r="13" ht="22" customHeight="1">
       <c r="A13" s="6" t="inlineStr">
         <is>
-          <t>GPN</t>
+          <t>OBDC</t>
         </is>
       </c>
       <c r="B13" s="7" t="inlineStr">
         <is>
-          <t>Global Payments Inc.</t>
+          <t>Blue Owl Capital Corpora</t>
         </is>
       </c>
       <c r="C13" s="16" t="n">
@@ -20840,12 +20840,12 @@
     <row r="14" ht="22" customHeight="1">
       <c r="A14" s="9" t="inlineStr">
         <is>
-          <t>OBDC</t>
+          <t>GPN</t>
         </is>
       </c>
       <c r="B14" s="10" t="inlineStr">
         <is>
-          <t>Blue Owl Capital Corpora</t>
+          <t>Global Payments Inc.</t>
         </is>
       </c>
       <c r="C14" s="17" t="n">
@@ -20966,12 +20966,12 @@
     <row r="16" ht="22" customHeight="1">
       <c r="A16" s="9" t="inlineStr">
         <is>
-          <t>VSNT</t>
+          <t>ACCS</t>
         </is>
       </c>
       <c r="B16" s="10" t="inlineStr">
         <is>
-          <t>Versant Media Group, Inc</t>
+          <t>ACCESS Newswire Inc.</t>
         </is>
       </c>
       <c r="C16" s="17" t="n">
@@ -21155,12 +21155,12 @@
     <row r="19" ht="22" customHeight="1">
       <c r="A19" s="6" t="inlineStr">
         <is>
-          <t>ACCS</t>
+          <t>PAL</t>
         </is>
       </c>
       <c r="B19" s="7" t="inlineStr">
         <is>
-          <t>ACCESS Newswire Inc.</t>
+          <t>Proficient Auto Logistic</t>
         </is>
       </c>
       <c r="C19" s="16" t="n">
@@ -21281,12 +21281,12 @@
     <row r="21" ht="22" customHeight="1">
       <c r="A21" s="6" t="inlineStr">
         <is>
-          <t>PAL</t>
+          <t>VSNT</t>
         </is>
       </c>
       <c r="B21" s="7" t="inlineStr">
         <is>
-          <t>Proficient Auto Logistic</t>
+          <t>Versant Media Group, Inc</t>
         </is>
       </c>
       <c r="C21" s="16" t="n">
@@ -21344,12 +21344,12 @@
     <row r="22" ht="22" customHeight="1">
       <c r="A22" s="9" t="inlineStr">
         <is>
-          <t>STRZ</t>
+          <t>SLRC</t>
         </is>
       </c>
       <c r="B22" s="10" t="inlineStr">
         <is>
-          <t>Starz Entertainment Corp</t>
+          <t>SLR Investment Corp.</t>
         </is>
       </c>
       <c r="C22" s="17" t="n">
@@ -21407,12 +21407,12 @@
     <row r="23" ht="22" customHeight="1">
       <c r="A23" s="6" t="inlineStr">
         <is>
-          <t>SLRC</t>
+          <t>LCNB</t>
         </is>
       </c>
       <c r="B23" s="7" t="inlineStr">
         <is>
-          <t>SLR Investment Corp.</t>
+          <t>LCNB Corporation</t>
         </is>
       </c>
       <c r="C23" s="16" t="n">
@@ -21722,12 +21722,12 @@
     <row r="28" ht="22" customHeight="1">
       <c r="A28" s="9" t="inlineStr">
         <is>
-          <t>LCNB</t>
+          <t>STRZ</t>
         </is>
       </c>
       <c r="B28" s="10" t="inlineStr">
         <is>
-          <t>LCNB Corporation</t>
+          <t>Starz Entertainment Corp</t>
         </is>
       </c>
       <c r="C28" s="17" t="n">
@@ -25142,7 +25142,7 @@
         <v>8</v>
       </c>
       <c r="E5" s="16" t="n">
-        <v>5.532</v>
+        <v>5.702</v>
       </c>
       <c r="F5" s="5" t="n">
         <v>5</v>
@@ -25176,10 +25176,10 @@
         <v>7</v>
       </c>
       <c r="E6" s="17" t="n">
-        <v>6.094</v>
+        <v>6.09</v>
       </c>
       <c r="F6" s="8" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="G6" s="10" t="inlineStr">
         <is>
@@ -25210,7 +25210,7 @@
         <v>7</v>
       </c>
       <c r="E7" s="16" t="n">
-        <v>5.95</v>
+        <v>5.932</v>
       </c>
       <c r="F7" s="7" t="inlineStr">
         <is>
@@ -25234,22 +25234,22 @@
       </c>
       <c r="B8" s="9" t="inlineStr">
         <is>
-          <t>OLED</t>
+          <t>CRM</t>
         </is>
       </c>
       <c r="C8" s="10" t="inlineStr">
         <is>
-          <t>Universal Display Corporation</t>
+          <t>Salesforce, Inc.</t>
         </is>
       </c>
       <c r="D8" s="8" t="n">
         <v>7</v>
       </c>
       <c r="E8" s="17" t="n">
-        <v>5.848</v>
+        <v>5.766</v>
       </c>
       <c r="F8" s="8" t="n">
-        <v>21</v>
+        <v>-2</v>
       </c>
       <c r="G8" s="10" t="inlineStr">
         <is>
@@ -25258,7 +25258,7 @@
       </c>
       <c r="H8" s="10" t="inlineStr">
         <is>
-          <t>PSU:40 BB:5 F4:17 RI:60</t>
+          <t>PSU:28 BB:8 C10:-5 F4:11 RI:61</t>
         </is>
       </c>
     </row>
@@ -25268,22 +25268,22 @@
       </c>
       <c r="B9" s="6" t="inlineStr">
         <is>
-          <t>HUBS</t>
+          <t>OLED</t>
         </is>
       </c>
       <c r="C9" s="7" t="inlineStr">
         <is>
-          <t>HubSpot, Inc.</t>
+          <t>Universal Display Corporation</t>
         </is>
       </c>
       <c r="D9" s="5" t="n">
         <v>7</v>
       </c>
       <c r="E9" s="16" t="n">
-        <v>5.694</v>
+        <v>5.726</v>
       </c>
       <c r="F9" s="5" t="n">
-        <v>7</v>
+        <v>18</v>
       </c>
       <c r="G9" s="7" t="inlineStr">
         <is>
@@ -25292,7 +25292,7 @@
       </c>
       <c r="H9" s="7" t="inlineStr">
         <is>
-          <t>PSU:25 BB:5 F4:17 RI:57</t>
+          <t>PSU:40 BB:5 F4:17 RI:60</t>
         </is>
       </c>
     </row>
@@ -25302,22 +25302,22 @@
       </c>
       <c r="B10" s="9" t="inlineStr">
         <is>
-          <t>CRM</t>
+          <t>HUBS</t>
         </is>
       </c>
       <c r="C10" s="10" t="inlineStr">
         <is>
-          <t>Salesforce, Inc.</t>
+          <t>HubSpot, Inc.</t>
         </is>
       </c>
       <c r="D10" s="8" t="n">
         <v>7</v>
       </c>
       <c r="E10" s="17" t="n">
-        <v>5.678</v>
+        <v>5.206</v>
       </c>
       <c r="F10" s="8" t="n">
-        <v>-4</v>
+        <v>3</v>
       </c>
       <c r="G10" s="10" t="inlineStr">
         <is>
@@ -25326,7 +25326,7 @@
       </c>
       <c r="H10" s="10" t="inlineStr">
         <is>
-          <t>PSU:28 BB:8 C10:-5 F4:11 RI:61</t>
+          <t>PSU:25 BB:5 F4:17 RI:57</t>
         </is>
       </c>
     </row>
@@ -25348,10 +25348,10 @@
         <v>7</v>
       </c>
       <c r="E11" s="16" t="n">
-        <v>4.95</v>
+        <v>5.01</v>
       </c>
       <c r="F11" s="5" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="G11" s="7" t="inlineStr">
         <is>
@@ -25370,31 +25370,31 @@
       </c>
       <c r="B12" s="9" t="inlineStr">
         <is>
-          <t>ADT</t>
+          <t>BLND</t>
         </is>
       </c>
       <c r="C12" s="10" t="inlineStr">
         <is>
-          <t>ADT Inc.</t>
+          <t>Blend Labs, Inc.</t>
         </is>
       </c>
       <c r="D12" s="8" t="n">
         <v>7</v>
       </c>
       <c r="E12" s="17" t="n">
-        <v>4.688</v>
+        <v>4.936</v>
       </c>
       <c r="F12" s="8" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="G12" s="10" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="H12" s="10" t="inlineStr">
         <is>
-          <t>PSU:31 BB:5 F4:12 RI:50 SS:10</t>
+          <t>PSU:8 BB:5 C10:-35 F4:5 RI:52 SS:20</t>
         </is>
       </c>
     </row>
@@ -25404,31 +25404,31 @@
       </c>
       <c r="B13" s="6" t="inlineStr">
         <is>
-          <t>BLND</t>
+          <t>ADT</t>
         </is>
       </c>
       <c r="C13" s="7" t="inlineStr">
         <is>
-          <t>Blend Labs, Inc.</t>
+          <t>ADT Inc.</t>
         </is>
       </c>
       <c r="D13" s="5" t="n">
         <v>7</v>
       </c>
       <c r="E13" s="16" t="n">
-        <v>4.648</v>
+        <v>4.114</v>
       </c>
       <c r="F13" s="5" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G13" s="7" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="H13" s="7" t="inlineStr">
         <is>
-          <t>PSU:8 BB:5 C10:-35 F4:5 RI:52 SS:20</t>
+          <t>PSU:31 BB:5 F4:12 RI:50 SS:10</t>
         </is>
       </c>
     </row>
@@ -25438,31 +25438,31 @@
       </c>
       <c r="B14" s="9" t="inlineStr">
         <is>
-          <t>LULU</t>
+          <t>CERT</t>
         </is>
       </c>
       <c r="C14" s="10" t="inlineStr">
         <is>
-          <t>lululemon athletica inc.</t>
+          <t>Certara, Inc.</t>
         </is>
       </c>
       <c r="D14" s="8" t="n">
         <v>7</v>
       </c>
       <c r="E14" s="17" t="n">
-        <v>4.436</v>
+        <v>3.996</v>
       </c>
       <c r="F14" s="8" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="G14" s="10" t="inlineStr">
         <is>
-          <t>Consumer Cyclical</t>
+          <t>Healthcare</t>
         </is>
       </c>
       <c r="H14" s="10" t="inlineStr">
         <is>
-          <t>PSU:1 BB:8 C10:-40 F4:11 RI:41 SS:10</t>
+          <t>PSU:29 BB:5 C10:-12 RI:43</t>
         </is>
       </c>
     </row>
@@ -25472,31 +25472,31 @@
       </c>
       <c r="B15" s="6" t="inlineStr">
         <is>
-          <t>CERT</t>
+          <t>LULU</t>
         </is>
       </c>
       <c r="C15" s="7" t="inlineStr">
         <is>
-          <t>Certara, Inc.</t>
+          <t>lululemon athletica inc.</t>
         </is>
       </c>
       <c r="D15" s="5" t="n">
         <v>7</v>
       </c>
       <c r="E15" s="16" t="n">
-        <v>3.714</v>
+        <v>3.868</v>
       </c>
       <c r="F15" s="5" t="n">
-        <v>7</v>
+        <v>-4</v>
       </c>
       <c r="G15" s="7" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>Consumer Cyclical</t>
         </is>
       </c>
       <c r="H15" s="7" t="inlineStr">
         <is>
-          <t>PSU:29 BB:5 C10:-12 RI:43</t>
+          <t>PSU:1 BB:8 C10:-40 F4:11 RI:41 SS:10</t>
         </is>
       </c>
     </row>
@@ -25518,10 +25518,10 @@
         <v>6</v>
       </c>
       <c r="E16" s="17" t="n">
-        <v>5.41</v>
+        <v>5.29</v>
       </c>
       <c r="F16" s="8" t="n">
-        <v>-5</v>
+        <v>-4</v>
       </c>
       <c r="G16" s="10" t="inlineStr">
         <is>
@@ -25540,31 +25540,31 @@
       </c>
       <c r="B17" s="6" t="inlineStr">
         <is>
-          <t>SNBR</t>
+          <t>HDSN</t>
         </is>
       </c>
       <c r="C17" s="7" t="inlineStr">
         <is>
-          <t>Sleep Number Corporation</t>
+          <t>Hudson Technologies, Inc.</t>
         </is>
       </c>
       <c r="D17" s="5" t="n">
         <v>6</v>
       </c>
       <c r="E17" s="16" t="n">
-        <v>4.848</v>
+        <v>4.962</v>
       </c>
       <c r="F17" s="5" t="n">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="G17" s="7" t="inlineStr">
         <is>
-          <t>Consumer Cyclical</t>
+          <t>Basic Materials</t>
         </is>
       </c>
       <c r="H17" s="7" t="inlineStr">
         <is>
-          <t>PSU:49 RI:46 SS:20</t>
+          <t>BB:5 F4:18 RI:58</t>
         </is>
       </c>
     </row>
@@ -25574,31 +25574,31 @@
       </c>
       <c r="B18" s="9" t="inlineStr">
         <is>
-          <t>HDSN</t>
+          <t>SBET</t>
         </is>
       </c>
       <c r="C18" s="10" t="inlineStr">
         <is>
-          <t>Hudson Technologies, Inc.</t>
+          <t>SharpLink, Inc.</t>
         </is>
       </c>
       <c r="D18" s="8" t="n">
         <v>6</v>
       </c>
       <c r="E18" s="17" t="n">
-        <v>4.83</v>
-      </c>
-      <c r="F18" s="8" t="n">
-        <v>13</v>
+        <v>4.89</v>
+      </c>
+      <c r="F18" s="22" t="n">
+        <v>80</v>
       </c>
       <c r="G18" s="10" t="inlineStr">
         <is>
-          <t>Basic Materials</t>
+          <t>Financial Services</t>
         </is>
       </c>
       <c r="H18" s="10" t="inlineStr">
         <is>
-          <t>BB:5 F4:18 RI:58</t>
+          <t>PSU:19 C10:15 RI:71</t>
         </is>
       </c>
     </row>
@@ -25608,31 +25608,31 @@
       </c>
       <c r="B19" s="6" t="inlineStr">
         <is>
-          <t>ALKT</t>
+          <t>SNBR</t>
         </is>
       </c>
       <c r="C19" s="7" t="inlineStr">
         <is>
-          <t>Alkami Technology, Inc.</t>
+          <t>Sleep Number Corporation</t>
         </is>
       </c>
       <c r="D19" s="5" t="n">
         <v>6</v>
       </c>
       <c r="E19" s="16" t="n">
-        <v>4.748</v>
+        <v>4.88</v>
       </c>
       <c r="F19" s="5" t="n">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="G19" s="7" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Consumer Cyclical</t>
         </is>
       </c>
       <c r="H19" s="7" t="inlineStr">
         <is>
-          <t>PSU:11 C10:-6 F4:16 RI:54</t>
+          <t>PSU:49 RI:46 SS:20</t>
         </is>
       </c>
     </row>
@@ -25642,31 +25642,31 @@
       </c>
       <c r="B20" s="9" t="inlineStr">
         <is>
-          <t>ACM</t>
+          <t>ALKT</t>
         </is>
       </c>
       <c r="C20" s="10" t="inlineStr">
         <is>
-          <t>AECOM</t>
+          <t>Alkami Technology, Inc.</t>
         </is>
       </c>
       <c r="D20" s="8" t="n">
         <v>6</v>
       </c>
       <c r="E20" s="17" t="n">
-        <v>4.744</v>
+        <v>4.856</v>
       </c>
       <c r="F20" s="8" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="G20" s="10" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="H20" s="10" t="inlineStr">
         <is>
-          <t>BB:5 F4:6 RI:54</t>
+          <t>PSU:11 C10:-6 F4:16 RI:54</t>
         </is>
       </c>
     </row>
@@ -25676,31 +25676,31 @@
       </c>
       <c r="B21" s="6" t="inlineStr">
         <is>
-          <t>SBET</t>
+          <t>ACM</t>
         </is>
       </c>
       <c r="C21" s="7" t="inlineStr">
         <is>
-          <t>SharpLink, Inc.</t>
+          <t>AECOM</t>
         </is>
       </c>
       <c r="D21" s="5" t="n">
         <v>6</v>
       </c>
       <c r="E21" s="16" t="n">
-        <v>4.71</v>
-      </c>
-      <c r="F21" s="22" t="n">
-        <v>83</v>
+        <v>4.84</v>
+      </c>
+      <c r="F21" s="5" t="n">
+        <v>42</v>
       </c>
       <c r="G21" s="7" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="H21" s="7" t="inlineStr">
         <is>
-          <t>PSU:19 C10:15 RI:71</t>
+          <t>BB:5 F4:6 RI:54</t>
         </is>
       </c>
     </row>
@@ -25722,10 +25722,10 @@
         <v>6</v>
       </c>
       <c r="E22" s="17" t="n">
-        <v>4.586</v>
+        <v>4.766</v>
       </c>
       <c r="F22" s="8" t="n">
-        <v>-4</v>
+        <v>-6</v>
       </c>
       <c r="G22" s="10" t="inlineStr">
         <is>
@@ -25744,31 +25744,31 @@
       </c>
       <c r="B23" s="6" t="inlineStr">
         <is>
-          <t>PRGO</t>
+          <t>NUS</t>
         </is>
       </c>
       <c r="C23" s="7" t="inlineStr">
         <is>
-          <t>Perrigo Company plc</t>
+          <t>Nu Skin Enterprises, Inc.</t>
         </is>
       </c>
       <c r="D23" s="5" t="n">
         <v>6</v>
       </c>
       <c r="E23" s="16" t="n">
-        <v>4.534</v>
-      </c>
-      <c r="F23" s="22" t="n">
-        <v>82</v>
+        <v>4.758</v>
+      </c>
+      <c r="F23" s="5" t="n">
+        <v>9</v>
       </c>
       <c r="G23" s="7" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>Consumer Defensive</t>
         </is>
       </c>
       <c r="H23" s="7" t="inlineStr">
         <is>
-          <t>PSU:21 RI:48 SS:29</t>
+          <t>PSU:54 BB:5 C10:-32 RI:53</t>
         </is>
       </c>
     </row>
@@ -25790,10 +25790,10 @@
         <v>6</v>
       </c>
       <c r="E24" s="17" t="n">
-        <v>4.486</v>
+        <v>4.48</v>
       </c>
       <c r="F24" s="8" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="G24" s="10" t="inlineStr">
         <is>
@@ -25812,31 +25812,31 @@
       </c>
       <c r="B25" s="6" t="inlineStr">
         <is>
-          <t>APTV</t>
+          <t>DXC</t>
         </is>
       </c>
       <c r="C25" s="7" t="inlineStr">
         <is>
-          <t>Aptiv PLC</t>
+          <t>DXC Technology Company</t>
         </is>
       </c>
       <c r="D25" s="5" t="n">
         <v>6</v>
       </c>
       <c r="E25" s="16" t="n">
-        <v>4.452</v>
+        <v>4.414</v>
       </c>
       <c r="F25" s="5" t="n">
-        <v>-10</v>
+        <v>-17</v>
       </c>
       <c r="G25" s="7" t="inlineStr">
         <is>
-          <t>Consumer Cyclical</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="H25" s="7" t="inlineStr">
         <is>
-          <t>PSU:36 BB:5 RI:35</t>
+          <t>PSU:43 BB:5 RI:57</t>
         </is>
       </c>
     </row>
@@ -25846,22 +25846,22 @@
       </c>
       <c r="B26" s="9" t="inlineStr">
         <is>
-          <t>VRSK</t>
+          <t>PSN</t>
         </is>
       </c>
       <c r="C26" s="10" t="inlineStr">
         <is>
-          <t>Verisk Analytics, Inc.</t>
+          <t>Parsons Corporation</t>
         </is>
       </c>
       <c r="D26" s="8" t="n">
         <v>6</v>
       </c>
       <c r="E26" s="17" t="n">
-        <v>4.37</v>
+        <v>4.398</v>
       </c>
       <c r="F26" s="8" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="G26" s="10" t="inlineStr">
         <is>
@@ -25870,7 +25870,7 @@
       </c>
       <c r="H26" s="10" t="inlineStr">
         <is>
-          <t>PSU:32 BB:8 F4:12 RI:32</t>
+          <t>PSU:37 F4:23 RI:47</t>
         </is>
       </c>
     </row>
@@ -25880,12 +25880,12 @@
       </c>
       <c r="B27" s="6" t="inlineStr">
         <is>
-          <t>AZTA</t>
+          <t>VRSK</t>
         </is>
       </c>
       <c r="C27" s="7" t="inlineStr">
         <is>
-          <t>Azenta, Inc.</t>
+          <t>Verisk Analytics, Inc.</t>
         </is>
       </c>
       <c r="D27" s="5" t="n">
@@ -25895,16 +25895,16 @@
         <v>4.366</v>
       </c>
       <c r="F27" s="5" t="n">
-        <v>12</v>
+        <v>-10</v>
       </c>
       <c r="G27" s="7" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="H27" s="7" t="inlineStr">
         <is>
-          <t>PSU:31</t>
+          <t>PSU:32 BB:8 F4:12 RI:32</t>
         </is>
       </c>
     </row>
@@ -25914,31 +25914,31 @@
       </c>
       <c r="B28" s="9" t="inlineStr">
         <is>
-          <t>NUS</t>
+          <t>AAT</t>
         </is>
       </c>
       <c r="C28" s="10" t="inlineStr">
         <is>
-          <t>Nu Skin Enterprises, Inc.</t>
+          <t>American Assets Trust, Inc.</t>
         </is>
       </c>
       <c r="D28" s="8" t="n">
         <v>6</v>
       </c>
       <c r="E28" s="17" t="n">
-        <v>4.268</v>
+        <v>4.342</v>
       </c>
       <c r="F28" s="8" t="n">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="G28" s="10" t="inlineStr">
         <is>
-          <t>Consumer Defensive</t>
+          <t>Real Estate</t>
         </is>
       </c>
       <c r="H28" s="10" t="inlineStr">
         <is>
-          <t>PSU:54 BB:5 C10:-32 RI:53</t>
+          <t>PSU:2 BB:5 C10:-12 F4:5 RI:37 SS:10</t>
         </is>
       </c>
     </row>
@@ -25948,31 +25948,31 @@
       </c>
       <c r="B29" s="6" t="inlineStr">
         <is>
-          <t>DXC</t>
+          <t>ZTS</t>
         </is>
       </c>
       <c r="C29" s="7" t="inlineStr">
         <is>
-          <t>DXC Technology Company</t>
+          <t>Zoetis Inc.</t>
         </is>
       </c>
       <c r="D29" s="5" t="n">
         <v>6</v>
       </c>
       <c r="E29" s="16" t="n">
-        <v>4.266</v>
+        <v>4.336</v>
       </c>
       <c r="F29" s="5" t="n">
-        <v>-21</v>
+        <v>2</v>
       </c>
       <c r="G29" s="7" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Healthcare</t>
         </is>
       </c>
       <c r="H29" s="7" t="inlineStr">
         <is>
-          <t>PSU:43 BB:5 RI:57</t>
+          <t>PSU:7 BB:5 C10:-3 F4:12 RI:60</t>
         </is>
       </c>
     </row>
@@ -25982,22 +25982,22 @@
       </c>
       <c r="B30" s="9" t="inlineStr">
         <is>
-          <t>ZTS</t>
+          <t>AZTA</t>
         </is>
       </c>
       <c r="C30" s="10" t="inlineStr">
         <is>
-          <t>Zoetis Inc.</t>
+          <t>Azenta, Inc.</t>
         </is>
       </c>
       <c r="D30" s="8" t="n">
         <v>6</v>
       </c>
       <c r="E30" s="17" t="n">
-        <v>4.21</v>
+        <v>4.316</v>
       </c>
       <c r="F30" s="8" t="n">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="G30" s="10" t="inlineStr">
         <is>
@@ -26006,7 +26006,7 @@
       </c>
       <c r="H30" s="10" t="inlineStr">
         <is>
-          <t>PSU:7 BB:5 C10:-3 F4:12 RI:60</t>
+          <t>PSU:31</t>
         </is>
       </c>
     </row>
@@ -26028,10 +26028,10 @@
         <v>6</v>
       </c>
       <c r="E31" s="16" t="n">
-        <v>4.154</v>
+        <v>4.262</v>
       </c>
       <c r="F31" s="5" t="n">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="G31" s="7" t="inlineStr">
         <is>
@@ -26050,31 +26050,31 @@
       </c>
       <c r="B32" s="9" t="inlineStr">
         <is>
-          <t>GTM</t>
+          <t>MA</t>
         </is>
       </c>
       <c r="C32" s="10" t="inlineStr">
         <is>
-          <t>ZoomInfo Technologies Inc.</t>
+          <t>Mastercard Incorporated</t>
         </is>
       </c>
       <c r="D32" s="8" t="n">
         <v>6</v>
       </c>
       <c r="E32" s="17" t="n">
-        <v>4.118</v>
+        <v>4.248</v>
       </c>
       <c r="F32" s="8" t="n">
         <v>39</v>
       </c>
       <c r="G32" s="10" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Financial Services</t>
         </is>
       </c>
       <c r="H32" s="10" t="inlineStr">
         <is>
-          <t>PSU:36 BB:5 C10:-4 RI:66 SS:20</t>
+          <t>PSU:31 BB:5 C10:78 RI:50</t>
         </is>
       </c>
     </row>
@@ -26084,31 +26084,31 @@
       </c>
       <c r="B33" s="6" t="inlineStr">
         <is>
-          <t>PSN</t>
+          <t>TKO</t>
         </is>
       </c>
       <c r="C33" s="7" t="inlineStr">
         <is>
-          <t>Parsons Corporation</t>
+          <t>TKO Group Holdings, Inc.</t>
         </is>
       </c>
       <c r="D33" s="5" t="n">
         <v>6</v>
       </c>
       <c r="E33" s="16" t="n">
-        <v>4.094</v>
+        <v>4.112</v>
       </c>
       <c r="F33" s="5" t="n">
-        <v>27</v>
+        <v>39</v>
       </c>
       <c r="G33" s="7" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Communication Services</t>
         </is>
       </c>
       <c r="H33" s="7" t="inlineStr">
         <is>
-          <t>PSU:37 F4:23 RI:47</t>
+          <t>PSU:3 BB:5 C10:2 F4:17 RI:42</t>
         </is>
       </c>
     </row>
@@ -26118,31 +26118,31 @@
       </c>
       <c r="B34" s="9" t="inlineStr">
         <is>
-          <t>MA</t>
+          <t>MMS</t>
         </is>
       </c>
       <c r="C34" s="10" t="inlineStr">
         <is>
-          <t>Mastercard Incorporated</t>
+          <t>Maximus, Inc.</t>
         </is>
       </c>
       <c r="D34" s="8" t="n">
         <v>6</v>
       </c>
       <c r="E34" s="17" t="n">
-        <v>4.074</v>
+        <v>4.098</v>
       </c>
       <c r="F34" s="22" t="n">
-        <v>99</v>
+        <v>252</v>
       </c>
       <c r="G34" s="10" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="H34" s="10" t="inlineStr">
         <is>
-          <t>PSU:31 BB:5 C10:78 RI:50</t>
+          <t>PSU:42 BB:5 RI:53 SS:26</t>
         </is>
       </c>
     </row>
@@ -34622,7 +34622,7 @@
       </c>
       <c r="H5" s="7" t="inlineStr">
         <is>
-          <t>12 layers firing | cons 10.86</t>
+          <t>12 layers firing | cons 10.794</t>
         </is>
       </c>
       <c r="I5" s="7" t="inlineStr">
@@ -34710,7 +34710,7 @@
       </c>
       <c r="H7" s="7" t="inlineStr">
         <is>
-          <t>12 layers firing | cons 8.712</t>
+          <t>12 layers firing | cons 9.946</t>
         </is>
       </c>
       <c r="I7" s="7" t="inlineStr">
@@ -34800,7 +34800,7 @@
       </c>
       <c r="H9" s="7" t="inlineStr">
         <is>
-          <t>11 layers firing | cons 8.37</t>
+          <t>11 layers firing | cons 8.674</t>
         </is>
       </c>
       <c r="I9" s="7" t="inlineStr">
@@ -34844,7 +34844,7 @@
       </c>
       <c r="H10" s="10" t="inlineStr">
         <is>
-          <t>11 layers firing | cons 7.65</t>
+          <t>11 layers firing | cons 7.672</t>
         </is>
       </c>
       <c r="I10" s="10" t="inlineStr">
@@ -34861,25 +34861,27 @@
     <row r="11" ht="56" customHeight="1">
       <c r="A11" s="6" t="inlineStr">
         <is>
-          <t>GO</t>
+          <t>LULU</t>
         </is>
       </c>
       <c r="B11" s="7" t="inlineStr">
         <is>
-          <t>Grocery Outlet</t>
+          <t>LULU</t>
         </is>
       </c>
       <c r="C11" s="5" t="n">
-        <v>1120</v>
+        <v>11657</v>
       </c>
       <c r="D11" s="16" t="n">
-        <v>11.33</v>
+        <v>102.66</v>
       </c>
       <c r="E11" s="16" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="F11" s="5" t="n">
-        <v>69</v>
+        <v>2.43</v>
+      </c>
+      <c r="F11" s="7" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
       <c r="G11" s="7" t="inlineStr">
         <is>
@@ -34888,42 +34890,42 @@
       </c>
       <c r="H11" s="7" t="inlineStr">
         <is>
-          <t>Forward $ targets + Cohen-Malloy 6-buyer cluster</t>
+          <t>11 layers firing | cons 6.504</t>
         </is>
       </c>
       <c r="I11" s="7" t="inlineStr">
         <is>
-          <t>Discount-grocery defensive base</t>
+          <t>see proxy_scan + buyback_verify</t>
         </is>
       </c>
       <c r="J11" s="6" t="inlineStr">
         <is>
-          <t>Concentrated 5%+</t>
+          <t>Participation 1-2%</t>
         </is>
       </c>
     </row>
     <row r="12" ht="56" customHeight="1">
       <c r="A12" s="9" t="inlineStr">
         <is>
-          <t>FOUR</t>
+          <t>GO</t>
         </is>
       </c>
       <c r="B12" s="10" t="inlineStr">
         <is>
-          <t>FOUR</t>
+          <t>Grocery Outlet</t>
         </is>
       </c>
       <c r="C12" s="8" t="n">
-        <v>3516</v>
+        <v>1120</v>
       </c>
       <c r="D12" s="17" t="n">
-        <v>38.61</v>
+        <v>11.33</v>
       </c>
       <c r="E12" s="17" t="n">
-        <v>2.17</v>
+        <v>1.37</v>
       </c>
       <c r="F12" s="8" t="n">
-        <v>35</v>
+        <v>69</v>
       </c>
       <c r="G12" s="10" t="inlineStr">
         <is>
@@ -34932,12 +34934,12 @@
       </c>
       <c r="H12" s="10" t="inlineStr">
         <is>
-          <t>10 layers firing | cons 7.978</t>
+          <t>Forward $ targets + Cohen-Malloy 6-buyer cluster</t>
         </is>
       </c>
       <c r="I12" s="10" t="inlineStr">
         <is>
-          <t>see proxy_scan + buyback_verify</t>
+          <t>Discount-grocery defensive base</t>
         </is>
       </c>
       <c r="J12" s="6" t="inlineStr">
@@ -34949,25 +34951,25 @@
     <row r="13" ht="56" customHeight="1">
       <c r="A13" s="6" t="inlineStr">
         <is>
-          <t>GPK</t>
+          <t>HUBS</t>
         </is>
       </c>
       <c r="B13" s="7" t="inlineStr">
         <is>
-          <t>GPK</t>
+          <t>HUBS</t>
         </is>
       </c>
       <c r="C13" s="5" t="n">
-        <v>2913</v>
+        <v>11602</v>
       </c>
       <c r="D13" s="16" t="n">
-        <v>9.85</v>
+        <v>226.52</v>
       </c>
       <c r="E13" s="16" t="n">
-        <v>0.9</v>
+        <v>7</v>
       </c>
       <c r="F13" s="5" t="n">
-        <v>22</v>
+        <v>34</v>
       </c>
       <c r="G13" s="7" t="inlineStr">
         <is>
@@ -34976,7 +34978,7 @@
       </c>
       <c r="H13" s="7" t="inlineStr">
         <is>
-          <t>10 layers firing | cons 7.912</t>
+          <t>10 layers firing | cons 8.286</t>
         </is>
       </c>
       <c r="I13" s="7" t="inlineStr">
@@ -34993,25 +34995,25 @@
     <row r="14" ht="56" customHeight="1">
       <c r="A14" s="9" t="inlineStr">
         <is>
-          <t>LW</t>
+          <t>GPK</t>
         </is>
       </c>
       <c r="B14" s="10" t="inlineStr">
         <is>
-          <t>LW</t>
+          <t>GPK</t>
         </is>
       </c>
       <c r="C14" s="8" t="n">
-        <v>6225</v>
+        <v>2913</v>
       </c>
       <c r="D14" s="17" t="n">
-        <v>45.28</v>
+        <v>9.85</v>
       </c>
       <c r="E14" s="17" t="n">
-        <v>3.41</v>
+        <v>0.9</v>
       </c>
       <c r="F14" s="8" t="n">
-        <v>51</v>
+        <v>22</v>
       </c>
       <c r="G14" s="10" t="inlineStr">
         <is>
@@ -35020,7 +35022,7 @@
       </c>
       <c r="H14" s="10" t="inlineStr">
         <is>
-          <t>10 layers firing | cons 7.674</t>
+          <t>10 layers firing | cons 8.022</t>
         </is>
       </c>
       <c r="I14" s="10" t="inlineStr">
@@ -35028,34 +35030,34 @@
           <t>see proxy_scan + buyback_verify</t>
         </is>
       </c>
-      <c r="J14" s="10" t="inlineStr">
-        <is>
-          <t>Material 2-5%</t>
+      <c r="J14" s="6" t="inlineStr">
+        <is>
+          <t>Concentrated 5%+</t>
         </is>
       </c>
     </row>
     <row r="15" ht="56" customHeight="1">
       <c r="A15" s="6" t="inlineStr">
         <is>
-          <t>APTV</t>
+          <t>FOUR</t>
         </is>
       </c>
       <c r="B15" s="7" t="inlineStr">
         <is>
-          <t>APTV</t>
+          <t>FOUR</t>
         </is>
       </c>
       <c r="C15" s="5" t="n">
-        <v>9527</v>
+        <v>3516</v>
       </c>
       <c r="D15" s="16" t="n">
-        <v>45.02</v>
+        <v>38.61</v>
       </c>
       <c r="E15" s="16" t="n">
-        <v>1.09</v>
+        <v>2.17</v>
       </c>
       <c r="F15" s="5" t="n">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="G15" s="7" t="inlineStr">
         <is>
@@ -35064,7 +35066,7 @@
       </c>
       <c r="H15" s="7" t="inlineStr">
         <is>
-          <t>10 layers firing | cons 7.644</t>
+          <t>10 layers firing | cons 7.766</t>
         </is>
       </c>
       <c r="I15" s="7" t="inlineStr">
@@ -35081,34 +35083,34 @@
     <row r="16" ht="56" customHeight="1">
       <c r="A16" s="9" t="inlineStr">
         <is>
-          <t>HUBS</t>
+          <t>GPGI</t>
         </is>
       </c>
       <c r="B16" s="10" t="inlineStr">
         <is>
-          <t>HUBS</t>
+          <t>GPGI</t>
         </is>
       </c>
       <c r="C16" s="8" t="n">
-        <v>11602</v>
+        <v>3522</v>
       </c>
       <c r="D16" s="17" t="n">
-        <v>226.52</v>
+        <v>12.15</v>
       </c>
       <c r="E16" s="17" t="n">
-        <v>7</v>
+        <v>1.11</v>
       </c>
       <c r="F16" s="8" t="n">
-        <v>34</v>
+        <v>4</v>
       </c>
       <c r="G16" s="10" t="inlineStr">
         <is>
-          <t>–</t>
+          <t>spin_separation</t>
         </is>
       </c>
       <c r="H16" s="10" t="inlineStr">
         <is>
-          <t>10 layers firing | cons 7.632</t>
+          <t>10 layers firing | cons 7.544</t>
         </is>
       </c>
       <c r="I16" s="10" t="inlineStr">
@@ -35125,25 +35127,27 @@
     <row r="17" ht="56" customHeight="1">
       <c r="A17" s="6" t="inlineStr">
         <is>
-          <t>ADT</t>
+          <t>VRSK</t>
         </is>
       </c>
       <c r="B17" s="7" t="inlineStr">
         <is>
-          <t>ADT Inc</t>
+          <t>VRSK</t>
         </is>
       </c>
       <c r="C17" s="5" t="n">
-        <v>5108</v>
+        <v>22408</v>
       </c>
       <c r="D17" s="16" t="n">
-        <v>6.38</v>
-      </c>
-      <c r="E17" s="16" t="n">
-        <v>1.47</v>
+        <v>172.16</v>
+      </c>
+      <c r="E17" s="7" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
       <c r="F17" s="5" t="n">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="G17" s="7" t="inlineStr">
         <is>
@@ -35152,12 +35156,12 @@
       </c>
       <c r="H17" s="7" t="inlineStr">
         <is>
-          <t>Heaviest PSU%LTI in universe (90%) + verified -7.3% shrinkage</t>
+          <t>10 layers firing | cons 7.48</t>
         </is>
       </c>
       <c r="I17" s="7" t="inlineStr">
         <is>
-          <t>Recurring monitoring revenue + verified supply-curve compression</t>
+          <t>see proxy_scan + buyback_verify</t>
         </is>
       </c>
       <c r="J17" s="6" t="inlineStr">
@@ -35169,39 +35173,39 @@
     <row r="18" ht="56" customHeight="1">
       <c r="A18" s="9" t="inlineStr">
         <is>
-          <t>GPGI</t>
+          <t>ADT</t>
         </is>
       </c>
       <c r="B18" s="10" t="inlineStr">
         <is>
-          <t>GPGI</t>
+          <t>ADT Inc</t>
         </is>
       </c>
       <c r="C18" s="8" t="n">
-        <v>3522</v>
+        <v>5108</v>
       </c>
       <c r="D18" s="17" t="n">
-        <v>12.15</v>
+        <v>6.38</v>
       </c>
       <c r="E18" s="17" t="n">
-        <v>1.11</v>
+        <v>1.47</v>
       </c>
       <c r="F18" s="8" t="n">
-        <v>4</v>
+        <v>27</v>
       </c>
       <c r="G18" s="10" t="inlineStr">
         <is>
-          <t>spin_separation</t>
+          <t>–</t>
         </is>
       </c>
       <c r="H18" s="10" t="inlineStr">
         <is>
-          <t>10 layers firing | cons 7.516</t>
+          <t>Heaviest PSU%LTI in universe (90%) + verified -7.3% shrinkage</t>
         </is>
       </c>
       <c r="I18" s="10" t="inlineStr">
         <is>
-          <t>see proxy_scan + buyback_verify</t>
+          <t>Recurring monitoring revenue + verified supply-curve compression</t>
         </is>
       </c>
       <c r="J18" s="6" t="inlineStr">
@@ -35213,25 +35217,25 @@
     <row r="19" ht="56" customHeight="1">
       <c r="A19" s="6" t="inlineStr">
         <is>
-          <t>BLND</t>
+          <t>APTV</t>
         </is>
       </c>
       <c r="B19" s="7" t="inlineStr">
         <is>
-          <t>BLND</t>
+          <t>APTV</t>
         </is>
       </c>
       <c r="C19" s="5" t="n">
-        <v>271</v>
+        <v>9527</v>
       </c>
       <c r="D19" s="16" t="n">
-        <v>1.12</v>
+        <v>45.02</v>
       </c>
       <c r="E19" s="16" t="n">
-        <v>2.86</v>
+        <v>1.09</v>
       </c>
       <c r="F19" s="5" t="n">
-        <v>15</v>
+        <v>38</v>
       </c>
       <c r="G19" s="7" t="inlineStr">
         <is>
@@ -35240,7 +35244,7 @@
       </c>
       <c r="H19" s="7" t="inlineStr">
         <is>
-          <t>10 layers firing | cons 6.906</t>
+          <t>10 layers firing | cons 6.684</t>
         </is>
       </c>
       <c r="I19" s="7" t="inlineStr">
@@ -35284,7 +35288,7 @@
       </c>
       <c r="H20" s="10" t="inlineStr">
         <is>
-          <t>10 layers firing | cons 6.072</t>
+          <t>10 layers firing | cons 6.578</t>
         </is>
       </c>
       <c r="I20" s="10" t="inlineStr">
@@ -35301,27 +35305,25 @@
     <row r="21" ht="56" customHeight="1">
       <c r="A21" s="6" t="inlineStr">
         <is>
-          <t>LULU</t>
+          <t>BLND</t>
         </is>
       </c>
       <c r="B21" s="7" t="inlineStr">
         <is>
-          <t>LULU</t>
+          <t>BLND</t>
         </is>
       </c>
       <c r="C21" s="5" t="n">
-        <v>11657</v>
+        <v>271</v>
       </c>
       <c r="D21" s="16" t="n">
-        <v>102.66</v>
+        <v>1.12</v>
       </c>
       <c r="E21" s="16" t="n">
-        <v>2.43</v>
-      </c>
-      <c r="F21" s="7" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+        <v>2.86</v>
+      </c>
+      <c r="F21" s="5" t="n">
+        <v>15</v>
       </c>
       <c r="G21" s="7" t="inlineStr">
         <is>
@@ -35330,7 +35332,7 @@
       </c>
       <c r="H21" s="7" t="inlineStr">
         <is>
-          <t>10 layers firing | cons 6.03</t>
+          <t>10 layers firing | cons 6.542</t>
         </is>
       </c>
       <c r="I21" s="7" t="inlineStr">
@@ -35340,32 +35342,32 @@
       </c>
       <c r="J21" s="6" t="inlineStr">
         <is>
-          <t>Participation 1-2%</t>
+          <t>Concentrated 5%+</t>
         </is>
       </c>
     </row>
     <row r="22" ht="56" customHeight="1">
       <c r="A22" s="9" t="inlineStr">
         <is>
-          <t>CERT</t>
+          <t>TRS</t>
         </is>
       </c>
       <c r="B22" s="10" t="inlineStr">
         <is>
-          <t>CERT</t>
+          <t>TRS</t>
         </is>
       </c>
       <c r="C22" s="8" t="n">
-        <v>1368</v>
+        <v>1409</v>
       </c>
       <c r="D22" s="17" t="n">
-        <v>8.789999999999999</v>
+        <v>39.32</v>
       </c>
       <c r="E22" s="17" t="n">
-        <v>1.42</v>
+        <v>0.98</v>
       </c>
       <c r="F22" s="8" t="n">
-        <v>31</v>
+        <v>38</v>
       </c>
       <c r="G22" s="10" t="inlineStr">
         <is>
@@ -35374,7 +35376,7 @@
       </c>
       <c r="H22" s="10" t="inlineStr">
         <is>
-          <t>10 layers firing | cons 6.01</t>
+          <t>10 layers firing | cons 6.214</t>
         </is>
       </c>
       <c r="I22" s="10" t="inlineStr">
@@ -35382,34 +35384,34 @@
           <t>see proxy_scan + buyback_verify</t>
         </is>
       </c>
-      <c r="J22" s="6" t="inlineStr">
-        <is>
-          <t>Concentrated 5%+</t>
+      <c r="J22" s="10" t="inlineStr">
+        <is>
+          <t>Material 2-5%</t>
         </is>
       </c>
     </row>
     <row r="23" ht="56" customHeight="1">
       <c r="A23" s="6" t="inlineStr">
         <is>
-          <t>TRS</t>
+          <t>CERT</t>
         </is>
       </c>
       <c r="B23" s="7" t="inlineStr">
         <is>
-          <t>TRS</t>
+          <t>CERT</t>
         </is>
       </c>
       <c r="C23" s="5" t="n">
-        <v>1409</v>
+        <v>1368</v>
       </c>
       <c r="D23" s="16" t="n">
-        <v>39.32</v>
+        <v>8.789999999999999</v>
       </c>
       <c r="E23" s="16" t="n">
-        <v>0.98</v>
+        <v>1.42</v>
       </c>
       <c r="F23" s="5" t="n">
-        <v>38</v>
+        <v>31</v>
       </c>
       <c r="G23" s="7" t="inlineStr">
         <is>
@@ -35418,7 +35420,7 @@
       </c>
       <c r="H23" s="7" t="inlineStr">
         <is>
-          <t>10 layers firing | cons 5.858</t>
+          <t>10 layers firing | cons 6.08</t>
         </is>
       </c>
       <c r="I23" s="7" t="inlineStr">
@@ -35426,9 +35428,9 @@
           <t>see proxy_scan + buyback_verify</t>
         </is>
       </c>
-      <c r="J23" s="7" t="inlineStr">
-        <is>
-          <t>Material 2-5%</t>
+      <c r="J23" s="6" t="inlineStr">
+        <is>
+          <t>Concentrated 5%+</t>
         </is>
       </c>
     </row>
@@ -35462,7 +35464,7 @@
       </c>
       <c r="H24" s="10" t="inlineStr">
         <is>
-          <t>10 layers firing | cons 5.784</t>
+          <t>10 layers firing | cons 5.882</t>
         </is>
       </c>
       <c r="I24" s="10" t="inlineStr">
@@ -36686,7 +36688,7 @@
         <v>12</v>
       </c>
       <c r="B27" s="17" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C27" s="10" t="inlineStr">
         <is>
@@ -36712,7 +36714,7 @@
         <v>10</v>
       </c>
       <c r="B29" s="17" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C29" s="10" t="inlineStr">
         <is>
@@ -36725,7 +36727,7 @@
         <v>9</v>
       </c>
       <c r="B30" s="16" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C30" s="7" t="inlineStr">
         <is>
@@ -36764,7 +36766,7 @@
         <v>6</v>
       </c>
       <c r="B33" s="17" t="n">
-        <v>91</v>
+        <v>95</v>
       </c>
       <c r="C33" s="10" t="inlineStr">
         <is>
@@ -36777,7 +36779,7 @@
         <v>5</v>
       </c>
       <c r="B34" s="16" t="n">
-        <v>153</v>
+        <v>140</v>
       </c>
       <c r="C34" s="7" t="inlineStr">
         <is>
@@ -36790,7 +36792,7 @@
         <v>4</v>
       </c>
       <c r="B35" s="17" t="n">
-        <v>256</v>
+        <v>261</v>
       </c>
       <c r="C35" s="10" t="inlineStr">
         <is>
@@ -36803,7 +36805,7 @@
         <v>3</v>
       </c>
       <c r="B36" s="16" t="n">
-        <v>477</v>
+        <v>479</v>
       </c>
       <c r="C36" s="7" t="inlineStr">
         <is>
@@ -36816,7 +36818,7 @@
         <v>2</v>
       </c>
       <c r="B37" s="17" t="n">
-        <v>956</v>
+        <v>958</v>
       </c>
       <c r="C37" s="10" t="inlineStr">
         <is>
@@ -36829,7 +36831,7 @@
         <v>1</v>
       </c>
       <c r="B38" s="16" t="n">
-        <v>1500</v>
+        <v>1506</v>
       </c>
       <c r="C38" s="7" t="inlineStr">
         <is>
@@ -39697,7 +39699,7 @@
       </c>
       <c r="B14" s="9" t="inlineStr">
         <is>
-          <t>FIS</t>
+          <t>CMCO</t>
         </is>
       </c>
       <c r="C14" s="17" t="n">
@@ -39705,12 +39707,12 @@
       </c>
       <c r="D14" s="10" t="inlineStr">
         <is>
-          <t>repricing language</t>
+          <t>discretionary hurdle, repricing language, retirement carveout</t>
         </is>
       </c>
       <c r="E14" s="6" t="inlineStr">
         <is>
-          <t>Concentrate (1 flag tolerable)</t>
+          <t>Participation — limited size</t>
         </is>
       </c>
     </row>
@@ -39720,7 +39722,7 @@
       </c>
       <c r="B15" s="6" t="inlineStr">
         <is>
-          <t>CMCO</t>
+          <t>FIS</t>
         </is>
       </c>
       <c r="C15" s="16" t="n">
@@ -39728,12 +39730,12 @@
       </c>
       <c r="D15" s="7" t="inlineStr">
         <is>
-          <t>discretionary hurdle, repricing language, retirement carveout</t>
+          <t>repricing language</t>
         </is>
       </c>
       <c r="E15" s="6" t="inlineStr">
         <is>
-          <t>Participation — limited size</t>
+          <t>Concentrate (1 flag tolerable)</t>
         </is>
       </c>
     </row>
@@ -40410,7 +40412,7 @@
       </c>
       <c r="B45" s="6" t="inlineStr">
         <is>
-          <t>METC</t>
+          <t>RXST</t>
         </is>
       </c>
       <c r="C45" s="16" t="n">
@@ -40418,12 +40420,12 @@
       </c>
       <c r="D45" s="7" t="inlineStr">
         <is>
-          <t>repricing language</t>
-        </is>
-      </c>
-      <c r="E45" s="6" t="inlineStr">
-        <is>
-          <t>Concentrate (1 flag tolerable)</t>
+          <t>retirement carveout, single-trigger CIC</t>
+        </is>
+      </c>
+      <c r="E45" s="7" t="inlineStr">
+        <is>
+          <t>Material — basket diversify</t>
         </is>
       </c>
     </row>
@@ -40433,7 +40435,7 @@
       </c>
       <c r="B46" s="9" t="inlineStr">
         <is>
-          <t>NXST</t>
+          <t>METC</t>
         </is>
       </c>
       <c r="C46" s="17" t="n">
@@ -40441,7 +40443,7 @@
       </c>
       <c r="D46" s="10" t="inlineStr">
         <is>
-          <t>discretionary hurdle</t>
+          <t>repricing language</t>
         </is>
       </c>
       <c r="E46" s="6" t="inlineStr">
@@ -40456,7 +40458,7 @@
       </c>
       <c r="B47" s="6" t="inlineStr">
         <is>
-          <t>RXST</t>
+          <t>NXST</t>
         </is>
       </c>
       <c r="C47" s="16" t="n">
@@ -40464,12 +40466,12 @@
       </c>
       <c r="D47" s="7" t="inlineStr">
         <is>
-          <t>retirement carveout, single-trigger CIC</t>
-        </is>
-      </c>
-      <c r="E47" s="7" t="inlineStr">
-        <is>
-          <t>Material — basket diversify</t>
+          <t>discretionary hurdle</t>
+        </is>
+      </c>
+      <c r="E47" s="6" t="inlineStr">
+        <is>
+          <t>Concentrate (1 flag tolerable)</t>
         </is>
       </c>
     </row>
@@ -40548,7 +40550,7 @@
       </c>
       <c r="B51" s="6" t="inlineStr">
         <is>
-          <t>SIG</t>
+          <t>MNST</t>
         </is>
       </c>
       <c r="C51" s="16" t="n">
@@ -40556,12 +40558,12 @@
       </c>
       <c r="D51" s="7" t="inlineStr">
         <is>
-          <t>retirement carveout</t>
-        </is>
-      </c>
-      <c r="E51" s="6" t="inlineStr">
-        <is>
-          <t>Concentrate (1 flag tolerable)</t>
+          <t>discretionary hurdle, retirement carveout</t>
+        </is>
+      </c>
+      <c r="E51" s="7" t="inlineStr">
+        <is>
+          <t>Material — basket diversify</t>
         </is>
       </c>
     </row>
@@ -40571,7 +40573,7 @@
       </c>
       <c r="B52" s="9" t="inlineStr">
         <is>
-          <t>MNST</t>
+          <t>SIG</t>
         </is>
       </c>
       <c r="C52" s="17" t="n">
@@ -40579,12 +40581,12 @@
       </c>
       <c r="D52" s="10" t="inlineStr">
         <is>
-          <t>discretionary hurdle, retirement carveout</t>
-        </is>
-      </c>
-      <c r="E52" s="10" t="inlineStr">
-        <is>
-          <t>Material — basket diversify</t>
+          <t>retirement carveout</t>
+        </is>
+      </c>
+      <c r="E52" s="6" t="inlineStr">
+        <is>
+          <t>Concentrate (1 flag tolerable)</t>
         </is>
       </c>
     </row>

--- a/MOST_ASYMMETRIC.xlsx
+++ b/MOST_ASYMMETRIC.xlsx
@@ -6225,7 +6225,7 @@
     <row r="51" ht="28" customHeight="1">
       <c r="A51" s="11" t="inlineStr">
         <is>
-          <t>236 names pass at least one mechanism gate; 37 light up two or more (the highest-conviction convergence). Unlike the additive consensus, these are HARD gates — every condition of a machine must hold: coiled-spring delever (D/E ≥ 1 + rising operating income + cheap equity), sub-cash buyback (net-cash floor ≥ 50% of price + active repurchase + not burning), forced-seller exhaustion (N-PORT forced selling into a floor, business not burning), hidden-asset realisation (small levered stub + credit-agreement asset sweep), stated-unlock triangulated (MD&amp;A value-unlock language + cheap geometry + insider buying), asset-sale monetization (asset-sale catalyst + cheap + levered/small — the backtest's best-median catalyst, +10%/58% hit), and tender-offer squeeze (tender/Dutch-auction catalyst + cheap small-cap — best hit rate, 61%). TWO ANTICIPATORY archetypes catch the setup BEFORE the catalyst: asset-sale latent (cheap + levered + de-lever pressure or MD&amp;A divestiture intent, NO sale announced) and tender-target latent (near net cash / NCAV, small controllable cap, plausible buyer — high insider ownership or self-tender-capable cash — and NO bid yet); these are speculative (weighted below the confirmed machines) but flag names likely to realise value that haven't yet. Plus structured distressed injection (the Cundill/Sibir play — an asset-backed washout raising via a senior/convertible instrument; see the Structured Distressed tab). Combines the payoff-geometry shape with the catalyst layers so shape and 'why now' are both required. Source: mechanism_gates.py.</t>
+          <t>235 names pass at least one mechanism gate; 37 light up two or more (the highest-conviction convergence). Unlike the additive consensus, these are HARD gates — every condition of a machine must hold: coiled-spring delever (D/E ≥ 1 + rising operating income + cheap equity), sub-cash buyback (net-cash floor ≥ 50% of price + active repurchase + not burning), forced-seller exhaustion (N-PORT forced selling into a floor, business not burning), hidden-asset realisation (small levered stub + credit-agreement asset sweep), stated-unlock triangulated (MD&amp;A value-unlock language + cheap geometry + insider buying), asset-sale monetization (asset-sale catalyst + cheap + levered/small — the backtest's best-median catalyst, +10%/58% hit), and tender-offer squeeze (tender/Dutch-auction catalyst + cheap small-cap — best hit rate, 61%). TWO ANTICIPATORY archetypes catch the setup BEFORE the catalyst: asset-sale latent (cheap + levered + de-lever pressure or MD&amp;A divestiture intent, NO sale announced) and tender-target latent (near net cash / NCAV, small controllable cap, plausible buyer — high insider ownership or self-tender-capable cash — and NO bid yet); these are speculative (weighted below the confirmed machines) but flag names likely to realise value that haven't yet. Plus structured distressed injection (the Cundill/Sibir play — an asset-backed washout raising via a senior/convertible instrument; see the Structured Distressed tab). Combines the payoff-geometry shape with the catalyst layers so shape and 'why now' are both required. Source: mechanism_gates.py.</t>
         </is>
       </c>
     </row>
@@ -7061,12 +7061,12 @@
     <row r="6" ht="22" customHeight="1">
       <c r="A6" s="9" t="inlineStr">
         <is>
-          <t>CMTL</t>
+          <t>ONL</t>
         </is>
       </c>
       <c r="B6" s="10" t="inlineStr">
         <is>
-          <t>Comtech Telecommunicat</t>
+          <t>Orion Properties Inc.</t>
         </is>
       </c>
       <c r="C6" s="10" t="inlineStr">
@@ -7078,10 +7078,10 @@
         <v>38.8</v>
       </c>
       <c r="E6" s="17" t="n">
-        <v>0.16</v>
+        <v>0.23</v>
       </c>
       <c r="F6" s="8" t="n">
-        <v>43.3</v>
+        <v>144.3</v>
       </c>
       <c r="G6" s="10" t="inlineStr">
         <is>
@@ -7090,19 +7090,19 @@
       </c>
       <c r="H6" s="10" t="inlineStr">
         <is>
-          <t>value committee (2025-12); turnaround exec (2026-0</t>
+          <t>activist settlement (2026-01); value committee (20</t>
         </is>
       </c>
     </row>
     <row r="7" ht="22" customHeight="1">
       <c r="A7" s="6" t="inlineStr">
         <is>
-          <t>HAIN</t>
+          <t>CMTL</t>
         </is>
       </c>
       <c r="B7" s="7" t="inlineStr">
         <is>
-          <t>The Hain Celestial Gro</t>
+          <t>Comtech Telecommunicat</t>
         </is>
       </c>
       <c r="C7" s="7" t="inlineStr">
@@ -7114,29 +7114,31 @@
         <v>38.8</v>
       </c>
       <c r="E7" s="16" t="n">
-        <v>0.23</v>
+        <v>0.16</v>
       </c>
       <c r="F7" s="5" t="n">
-        <v>49.6</v>
-      </c>
-      <c r="G7" s="16" t="n">
-        <v>89</v>
+        <v>43.3</v>
+      </c>
+      <c r="G7" s="7" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
       <c r="H7" s="7" t="inlineStr">
         <is>
-          <t>value committee (2026-04); asset sale (2026-09); m</t>
+          <t>value committee (2025-12); turnaround exec (2026-0</t>
         </is>
       </c>
     </row>
     <row r="8" ht="22" customHeight="1">
       <c r="A8" s="9" t="inlineStr">
         <is>
-          <t>JOB</t>
+          <t>HAIN</t>
         </is>
       </c>
       <c r="B8" s="10" t="inlineStr">
         <is>
-          <t>GEE Group Inc.</t>
+          <t>The Hain Celestial Gro</t>
         </is>
       </c>
       <c r="C8" s="10" t="inlineStr">
@@ -7145,32 +7147,32 @@
         </is>
       </c>
       <c r="D8" s="17" t="n">
-        <v>38</v>
+        <v>38.8</v>
       </c>
       <c r="E8" s="17" t="n">
-        <v>0.51</v>
+        <v>0.23</v>
       </c>
       <c r="F8" s="8" t="n">
-        <v>25.8</v>
+        <v>49.6</v>
       </c>
       <c r="G8" s="17" t="n">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="H8" s="10" t="inlineStr">
         <is>
-          <t>activist settlement (2026-08); declassify (2026-08</t>
+          <t>value committee (2026-04); asset sale (2026-09); m</t>
         </is>
       </c>
     </row>
     <row r="9" ht="22" customHeight="1">
       <c r="A9" s="6" t="inlineStr">
         <is>
-          <t>MED</t>
+          <t>JOB</t>
         </is>
       </c>
       <c r="B9" s="7" t="inlineStr">
         <is>
-          <t>MEDIFAST INC</t>
+          <t>GEE Group Inc.</t>
         </is>
       </c>
       <c r="C9" s="7" t="inlineStr">
@@ -7179,32 +7181,32 @@
         </is>
       </c>
       <c r="D9" s="16" t="n">
-        <v>36.6</v>
+        <v>38</v>
       </c>
       <c r="E9" s="16" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.51</v>
       </c>
       <c r="F9" s="5" t="n">
-        <v>134.9</v>
+        <v>25.8</v>
       </c>
       <c r="G9" s="16" t="n">
-        <v>53</v>
+        <v>79</v>
       </c>
       <c r="H9" s="7" t="inlineStr">
         <is>
-          <t>activist settlement (2026-03); turnaround exec (20</t>
+          <t>activist settlement (2026-08); declassify (2026-08</t>
         </is>
       </c>
     </row>
     <row r="10" ht="22" customHeight="1">
       <c r="A10" s="9" t="inlineStr">
         <is>
-          <t>ONL</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="B10" s="10" t="inlineStr">
         <is>
-          <t>Orion Properties Inc.</t>
+          <t>MEDIFAST INC</t>
         </is>
       </c>
       <c r="C10" s="10" t="inlineStr">
@@ -7213,34 +7215,32 @@
         </is>
       </c>
       <c r="D10" s="17" t="n">
-        <v>34.8</v>
+        <v>36.6</v>
       </c>
       <c r="E10" s="17" t="n">
-        <v>0.23</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="F10" s="8" t="n">
-        <v>144.3</v>
-      </c>
-      <c r="G10" s="10" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+        <v>134.9</v>
+      </c>
+      <c r="G10" s="17" t="n">
+        <v>53</v>
       </c>
       <c r="H10" s="10" t="inlineStr">
         <is>
-          <t>activist settlement (2026-01); value committee (20</t>
+          <t>activist settlement (2026-03); turnaround exec (20</t>
         </is>
       </c>
     </row>
     <row r="11" ht="22" customHeight="1">
       <c r="A11" s="6" t="inlineStr">
         <is>
-          <t>BCIC</t>
+          <t>UEIC</t>
         </is>
       </c>
       <c r="B11" s="7" t="inlineStr">
         <is>
-          <t>BCP Investment Corpora</t>
+          <t>Universal Electronics</t>
         </is>
       </c>
       <c r="C11" s="7" t="inlineStr">
@@ -7249,34 +7249,32 @@
         </is>
       </c>
       <c r="D11" s="16" t="n">
-        <v>34</v>
+        <v>33.8</v>
       </c>
       <c r="E11" s="16" t="n">
-        <v>0.49</v>
+        <v>0.47</v>
       </c>
       <c r="F11" s="5" t="n">
-        <v>88</v>
-      </c>
-      <c r="G11" s="7" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+        <v>66.5</v>
+      </c>
+      <c r="G11" s="16" t="n">
+        <v>45</v>
       </c>
       <c r="H11" s="7" t="inlineStr">
         <is>
-          <t>capital return policy (2026-05); tender offer (202</t>
+          <t>capital return policy (2026-08); turnaround exec (</t>
         </is>
       </c>
     </row>
     <row r="12" ht="22" customHeight="1">
       <c r="A12" s="9" t="inlineStr">
         <is>
-          <t>UEIC</t>
+          <t>TOON</t>
         </is>
       </c>
       <c r="B12" s="10" t="inlineStr">
         <is>
-          <t>Universal Electronics</t>
+          <t>Kartoon Studios Inc.</t>
         </is>
       </c>
       <c r="C12" s="10" t="inlineStr">
@@ -7285,32 +7283,32 @@
         </is>
       </c>
       <c r="D12" s="17" t="n">
-        <v>33.8</v>
+        <v>33</v>
       </c>
       <c r="E12" s="17" t="n">
-        <v>0.47</v>
+        <v>0.66</v>
       </c>
       <c r="F12" s="8" t="n">
-        <v>66.5</v>
+        <v>34.4</v>
       </c>
       <c r="G12" s="17" t="n">
-        <v>45</v>
+        <v>15</v>
       </c>
       <c r="H12" s="10" t="inlineStr">
         <is>
-          <t>capital return policy (2026-08); turnaround exec (</t>
+          <t>activist settlement (2026-08); pill removed (2026-</t>
         </is>
       </c>
     </row>
     <row r="13" ht="22" customHeight="1">
       <c r="A13" s="6" t="inlineStr">
         <is>
-          <t>TOON</t>
+          <t>BCIC</t>
         </is>
       </c>
       <c r="B13" s="7" t="inlineStr">
         <is>
-          <t>Kartoon Studios Inc.</t>
+          <t>BCP Investment Corpora</t>
         </is>
       </c>
       <c r="C13" s="7" t="inlineStr">
@@ -7319,32 +7317,34 @@
         </is>
       </c>
       <c r="D13" s="16" t="n">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="E13" s="16" t="n">
-        <v>0.66</v>
+        <v>0.49</v>
       </c>
       <c r="F13" s="5" t="n">
-        <v>34.4</v>
-      </c>
-      <c r="G13" s="16" t="n">
-        <v>15</v>
+        <v>88</v>
+      </c>
+      <c r="G13" s="7" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
       <c r="H13" s="7" t="inlineStr">
         <is>
-          <t>activist settlement (2026-08); pill removed (2026-</t>
+          <t>capital return policy (2026-05); tender offer (202</t>
         </is>
       </c>
     </row>
     <row r="14" ht="22" customHeight="1">
       <c r="A14" s="9" t="inlineStr">
         <is>
-          <t>VISN</t>
+          <t>CABO</t>
         </is>
       </c>
       <c r="B14" s="10" t="inlineStr">
         <is>
-          <t>Vistance Networks, Inc</t>
+          <t>Cable One, Inc.</t>
         </is>
       </c>
       <c r="C14" s="10" t="inlineStr">
@@ -7353,32 +7353,34 @@
         </is>
       </c>
       <c r="D14" s="17" t="n">
-        <v>28.8</v>
+        <v>28.4</v>
       </c>
       <c r="E14" s="17" t="n">
-        <v>0.58</v>
+        <v>0.29</v>
       </c>
       <c r="F14" s="8" t="n">
-        <v>1463.9</v>
-      </c>
-      <c r="G14" s="17" t="n">
-        <v>172</v>
+        <v>94.90000000000001</v>
+      </c>
+      <c r="G14" s="10" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
       <c r="H14" s="10" t="inlineStr">
         <is>
-          <t>call commit (2026-08); asset sale (2026-04); sop d</t>
+          <t>ceo change (2025-12); chair ceo split (2025-12); c</t>
         </is>
       </c>
     </row>
     <row r="15" ht="22" customHeight="1">
       <c r="A15" s="6" t="inlineStr">
         <is>
-          <t>CABO</t>
+          <t>ARI</t>
         </is>
       </c>
       <c r="B15" s="7" t="inlineStr">
         <is>
-          <t>Cable One, Inc.</t>
+          <t>Apollo Commercial Real</t>
         </is>
       </c>
       <c r="C15" s="7" t="inlineStr">
@@ -7387,13 +7389,13 @@
         </is>
       </c>
       <c r="D15" s="16" t="n">
-        <v>28.4</v>
+        <v>28</v>
       </c>
       <c r="E15" s="16" t="n">
-        <v>0.29</v>
+        <v>0.66</v>
       </c>
       <c r="F15" s="5" t="n">
-        <v>94.90000000000001</v>
+        <v>829.6</v>
       </c>
       <c r="G15" s="7" t="inlineStr">
         <is>
@@ -7402,19 +7404,19 @@
       </c>
       <c r="H15" s="7" t="inlineStr">
         <is>
-          <t>ceo change (2025-12); chair ceo split (2025-12); c</t>
+          <t>strategic review (2026-06); call commit (2026-04);</t>
         </is>
       </c>
     </row>
     <row r="16" ht="22" customHeight="1">
       <c r="A16" s="9" t="inlineStr">
         <is>
-          <t>ARI</t>
+          <t>BGS</t>
         </is>
       </c>
       <c r="B16" s="10" t="inlineStr">
         <is>
-          <t>Apollo Commercial Real</t>
+          <t>B&amp;G Foods, Inc.</t>
         </is>
       </c>
       <c r="C16" s="10" t="inlineStr">
@@ -7423,13 +7425,13 @@
         </is>
       </c>
       <c r="D16" s="17" t="n">
-        <v>28</v>
+        <v>26.8</v>
       </c>
       <c r="E16" s="17" t="n">
-        <v>0.66</v>
+        <v>0.62</v>
       </c>
       <c r="F16" s="8" t="n">
-        <v>829.6</v>
+        <v>244.7</v>
       </c>
       <c r="G16" s="10" t="inlineStr">
         <is>
@@ -7438,19 +7440,19 @@
       </c>
       <c r="H16" s="10" t="inlineStr">
         <is>
-          <t>strategic review (2026-06); call commit (2026-04);</t>
+          <t>turnaround exec (2026-05); asset sale (2026-06); c</t>
         </is>
       </c>
     </row>
     <row r="17" ht="22" customHeight="1">
       <c r="A17" s="6" t="inlineStr">
         <is>
-          <t>BGS</t>
+          <t>LE</t>
         </is>
       </c>
       <c r="B17" s="7" t="inlineStr">
         <is>
-          <t>B&amp;G Foods, Inc.</t>
+          <t>Lands' End, Inc.</t>
         </is>
       </c>
       <c r="C17" s="7" t="inlineStr">
@@ -7459,34 +7461,32 @@
         </is>
       </c>
       <c r="D17" s="16" t="n">
-        <v>26.8</v>
+        <v>26.4</v>
       </c>
       <c r="E17" s="16" t="n">
-        <v>0.62</v>
+        <v>0.65</v>
       </c>
       <c r="F17" s="5" t="n">
-        <v>244.7</v>
-      </c>
-      <c r="G17" s="7" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+        <v>318.2</v>
+      </c>
+      <c r="G17" s="16" t="n">
+        <v>7</v>
       </c>
       <c r="H17" s="7" t="inlineStr">
         <is>
-          <t>turnaround exec (2026-05); asset sale (2026-06); c</t>
+          <t>tender offer (2026-03); mda unlock (2026-03); call</t>
         </is>
       </c>
     </row>
     <row r="18" ht="22" customHeight="1">
       <c r="A18" s="9" t="inlineStr">
         <is>
-          <t>LE</t>
+          <t>DXLG</t>
         </is>
       </c>
       <c r="B18" s="10" t="inlineStr">
         <is>
-          <t>Lands' End, Inc.</t>
+          <t>Destination XL Group,</t>
         </is>
       </c>
       <c r="C18" s="10" t="inlineStr">
@@ -7495,32 +7495,32 @@
         </is>
       </c>
       <c r="D18" s="17" t="n">
-        <v>26.4</v>
+        <v>26</v>
       </c>
       <c r="E18" s="17" t="n">
-        <v>0.65</v>
+        <v>0.32</v>
       </c>
       <c r="F18" s="8" t="n">
-        <v>318.2</v>
+        <v>33.2</v>
       </c>
       <c r="G18" s="17" t="n">
-        <v>7</v>
+        <v>33</v>
       </c>
       <c r="H18" s="10" t="inlineStr">
         <is>
-          <t>tender offer (2026-03); mda unlock (2026-03); call</t>
+          <t>tender offer (2026-05); mda capital (2026-09)</t>
         </is>
       </c>
     </row>
     <row r="19" ht="22" customHeight="1">
       <c r="A19" s="6" t="inlineStr">
         <is>
-          <t>DXLG</t>
+          <t>CNTN</t>
         </is>
       </c>
       <c r="B19" s="7" t="inlineStr">
         <is>
-          <t>Destination XL Group,</t>
+          <t>Canton Strategic Holdi</t>
         </is>
       </c>
       <c r="C19" s="7" t="inlineStr">
@@ -7529,32 +7529,32 @@
         </is>
       </c>
       <c r="D19" s="16" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E19" s="16" t="n">
-        <v>0.32</v>
+        <v>0.4</v>
       </c>
       <c r="F19" s="5" t="n">
-        <v>33.2</v>
+        <v>180.9</v>
       </c>
       <c r="G19" s="16" t="n">
-        <v>33</v>
+        <v>23</v>
       </c>
       <c r="H19" s="7" t="inlineStr">
         <is>
-          <t>tender offer (2026-05); mda capital (2026-09)</t>
+          <t>capital return policy (2026-06); buyback auth (202</t>
         </is>
       </c>
     </row>
     <row r="20" ht="22" customHeight="1">
       <c r="A20" s="9" t="inlineStr">
         <is>
-          <t>CNTN</t>
+          <t>CLAR</t>
         </is>
       </c>
       <c r="B20" s="10" t="inlineStr">
         <is>
-          <t>Canton Strategic Holdi</t>
+          <t>Clarus Corporation</t>
         </is>
       </c>
       <c r="C20" s="10" t="inlineStr">
@@ -7566,29 +7566,29 @@
         <v>25</v>
       </c>
       <c r="E20" s="17" t="n">
-        <v>0.4</v>
+        <v>0.68</v>
       </c>
       <c r="F20" s="8" t="n">
-        <v>180.9</v>
+        <v>134.6</v>
       </c>
       <c r="G20" s="17" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H20" s="10" t="inlineStr">
         <is>
-          <t>capital return policy (2026-06); buyback auth (202</t>
+          <t>strategic review (2026-08); mda unlock (2026-05);</t>
         </is>
       </c>
     </row>
     <row r="21" ht="22" customHeight="1">
       <c r="A21" s="6" t="inlineStr">
         <is>
-          <t>CLAR</t>
+          <t>ARE</t>
         </is>
       </c>
       <c r="B21" s="7" t="inlineStr">
         <is>
-          <t>Clarus Corporation</t>
+          <t>Alexandria Real Estate</t>
         </is>
       </c>
       <c r="C21" s="7" t="inlineStr">
@@ -7597,32 +7597,34 @@
         </is>
       </c>
       <c r="D21" s="16" t="n">
-        <v>25</v>
+        <v>24.6</v>
       </c>
       <c r="E21" s="16" t="n">
-        <v>0.68</v>
+        <v>0.6</v>
       </c>
       <c r="F21" s="5" t="n">
-        <v>134.6</v>
-      </c>
-      <c r="G21" s="16" t="n">
-        <v>22</v>
+        <v>9318.200000000001</v>
+      </c>
+      <c r="G21" s="7" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
       <c r="H21" s="7" t="inlineStr">
         <is>
-          <t>strategic review (2026-08); mda unlock (2026-05);</t>
+          <t>tender offer (2026-02); proxy responsive (2026-04)</t>
         </is>
       </c>
     </row>
     <row r="22" ht="22" customHeight="1">
       <c r="A22" s="9" t="inlineStr">
         <is>
-          <t>ARE</t>
+          <t>INVE</t>
         </is>
       </c>
       <c r="B22" s="10" t="inlineStr">
         <is>
-          <t>Alexandria Real Estate</t>
+          <t>Identiv, Inc.</t>
         </is>
       </c>
       <c r="C22" s="10" t="inlineStr">
@@ -7631,34 +7633,32 @@
         </is>
       </c>
       <c r="D22" s="17" t="n">
-        <v>24.6</v>
+        <v>24</v>
       </c>
       <c r="E22" s="17" t="n">
-        <v>0.6</v>
+        <v>0.44</v>
       </c>
       <c r="F22" s="8" t="n">
-        <v>9318.200000000001</v>
-      </c>
-      <c r="G22" s="10" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+        <v>58.5</v>
+      </c>
+      <c r="G22" s="17" t="n">
+        <v>213</v>
       </c>
       <c r="H22" s="10" t="inlineStr">
         <is>
-          <t>tender offer (2026-02); proxy responsive (2026-04)</t>
+          <t>ceo change (2026-09); asset sale (2026-08)</t>
         </is>
       </c>
     </row>
     <row r="23" ht="22" customHeight="1">
       <c r="A23" s="6" t="inlineStr">
         <is>
-          <t>INVE</t>
+          <t>LBTYK</t>
         </is>
       </c>
       <c r="B23" s="7" t="inlineStr">
         <is>
-          <t>Identiv, Inc.</t>
+          <t>Liberty Global Ltd.</t>
         </is>
       </c>
       <c r="C23" s="7" t="inlineStr">
@@ -7670,29 +7670,31 @@
         <v>24</v>
       </c>
       <c r="E23" s="16" t="n">
-        <v>0.44</v>
+        <v>0.35</v>
       </c>
       <c r="F23" s="5" t="n">
-        <v>58.5</v>
-      </c>
-      <c r="G23" s="16" t="n">
-        <v>213</v>
+        <v>3238.4</v>
+      </c>
+      <c r="G23" s="7" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
       <c r="H23" s="7" t="inlineStr">
         <is>
-          <t>ceo change (2026-09); asset sale (2026-08)</t>
+          <t>turnaround exec (2026-04); proxy responsive (2026-</t>
         </is>
       </c>
     </row>
     <row r="24" ht="22" customHeight="1">
       <c r="A24" s="9" t="inlineStr">
         <is>
-          <t>LBTYK</t>
+          <t>CCS</t>
         </is>
       </c>
       <c r="B24" s="10" t="inlineStr">
         <is>
-          <t>Liberty Global Ltd.</t>
+          <t>Century Communities, I</t>
         </is>
       </c>
       <c r="C24" s="10" t="inlineStr">
@@ -7701,34 +7703,32 @@
         </is>
       </c>
       <c r="D24" s="17" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="E24" s="17" t="n">
-        <v>0.35</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="F24" s="8" t="n">
-        <v>3238.4</v>
-      </c>
-      <c r="G24" s="10" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+        <v>1776.2</v>
+      </c>
+      <c r="G24" s="17" t="n">
+        <v>4</v>
       </c>
       <c r="H24" s="10" t="inlineStr">
         <is>
-          <t>turnaround exec (2026-04); proxy responsive (2026-</t>
+          <t>call commit (2026-07); proxy responsive (2026-03);</t>
         </is>
       </c>
     </row>
     <row r="25" ht="22" customHeight="1">
       <c r="A25" s="6" t="inlineStr">
         <is>
-          <t>RYN</t>
+          <t>OPTT</t>
         </is>
       </c>
       <c r="B25" s="7" t="inlineStr">
         <is>
-          <t>Rayonier Inc. REIT</t>
+          <t>Ocean Power Technologi</t>
         </is>
       </c>
       <c r="C25" s="7" t="inlineStr">
@@ -7737,13 +7737,13 @@
         </is>
       </c>
       <c r="D25" s="16" t="n">
-        <v>22.8</v>
+        <v>20.6</v>
       </c>
       <c r="E25" s="16" t="n">
-        <v>0.6</v>
+        <v>0.66</v>
       </c>
       <c r="F25" s="5" t="n">
-        <v>3135.8</v>
+        <v>13.3</v>
       </c>
       <c r="G25" s="7" t="inlineStr">
         <is>
@@ -7752,19 +7752,19 @@
       </c>
       <c r="H25" s="7" t="inlineStr">
         <is>
-          <t>call commit (2026-08); turnaround exec (2026-02);</t>
+          <t>strategic review (2026-08); pill removed (2026-06)</t>
         </is>
       </c>
     </row>
     <row r="26" ht="22" customHeight="1">
       <c r="A26" s="9" t="inlineStr">
         <is>
-          <t>CCS</t>
+          <t>PPLI</t>
         </is>
       </c>
       <c r="B26" s="10" t="inlineStr">
         <is>
-          <t>Century Communities, I</t>
+          <t>People Incorporated</t>
         </is>
       </c>
       <c r="C26" s="10" t="inlineStr">
@@ -7773,32 +7773,34 @@
         </is>
       </c>
       <c r="D26" s="17" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="E26" s="17" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.53</v>
       </c>
       <c r="F26" s="8" t="n">
-        <v>1776.2</v>
-      </c>
-      <c r="G26" s="17" t="n">
-        <v>4</v>
+        <v>2713.3</v>
+      </c>
+      <c r="G26" s="10" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
       <c r="H26" s="10" t="inlineStr">
         <is>
-          <t>call commit (2026-07); proxy responsive (2026-03);</t>
+          <t>capital return policy (2026-09); call value gap (2</t>
         </is>
       </c>
     </row>
     <row r="27" ht="22" customHeight="1">
       <c r="A27" s="6" t="inlineStr">
         <is>
-          <t>OPTT</t>
+          <t>VSNT</t>
         </is>
       </c>
       <c r="B27" s="7" t="inlineStr">
         <is>
-          <t>Ocean Power Technologi</t>
+          <t>Versant Media Group, I</t>
         </is>
       </c>
       <c r="C27" s="7" t="inlineStr">
@@ -7807,13 +7809,13 @@
         </is>
       </c>
       <c r="D27" s="16" t="n">
-        <v>20.6</v>
+        <v>19.8</v>
       </c>
       <c r="E27" s="16" t="n">
-        <v>0.66</v>
+        <v>0.58</v>
       </c>
       <c r="F27" s="5" t="n">
-        <v>13.3</v>
+        <v>4700.6</v>
       </c>
       <c r="G27" s="7" t="inlineStr">
         <is>
@@ -7822,19 +7824,19 @@
       </c>
       <c r="H27" s="7" t="inlineStr">
         <is>
-          <t>strategic review (2026-08); pill removed (2026-06)</t>
+          <t>call commit (2026-08); turnaround exec (2026-01)</t>
         </is>
       </c>
     </row>
     <row r="28" ht="22" customHeight="1">
       <c r="A28" s="9" t="inlineStr">
         <is>
-          <t>PPLI</t>
+          <t>RYN</t>
         </is>
       </c>
       <c r="B28" s="10" t="inlineStr">
         <is>
-          <t>People Incorporated</t>
+          <t>Rayonier Inc. REIT</t>
         </is>
       </c>
       <c r="C28" s="10" t="inlineStr">
@@ -7843,13 +7845,13 @@
         </is>
       </c>
       <c r="D28" s="17" t="n">
-        <v>20</v>
+        <v>19.8</v>
       </c>
       <c r="E28" s="17" t="n">
-        <v>0.53</v>
+        <v>0.6</v>
       </c>
       <c r="F28" s="8" t="n">
-        <v>2713.3</v>
+        <v>3135.8</v>
       </c>
       <c r="G28" s="10" t="inlineStr">
         <is>
@@ -7858,19 +7860,19 @@
       </c>
       <c r="H28" s="10" t="inlineStr">
         <is>
-          <t>capital return policy (2026-09); call value gap (2</t>
+          <t>turnaround exec (2026-02); call intent (2026-08);</t>
         </is>
       </c>
     </row>
     <row r="29" ht="22" customHeight="1">
       <c r="A29" s="6" t="inlineStr">
         <is>
-          <t>VSNT</t>
+          <t>GIII</t>
         </is>
       </c>
       <c r="B29" s="7" t="inlineStr">
         <is>
-          <t>Versant Media Group, I</t>
+          <t>G-III Apparel Group, L</t>
         </is>
       </c>
       <c r="C29" s="7" t="inlineStr">
@@ -7879,34 +7881,32 @@
         </is>
       </c>
       <c r="D29" s="16" t="n">
-        <v>19.8</v>
+        <v>18.8</v>
       </c>
       <c r="E29" s="16" t="n">
-        <v>0.58</v>
+        <v>0.65</v>
       </c>
       <c r="F29" s="5" t="n">
-        <v>4700.6</v>
-      </c>
-      <c r="G29" s="7" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+        <v>1170.8</v>
+      </c>
+      <c r="G29" s="16" t="n">
+        <v>33</v>
       </c>
       <c r="H29" s="7" t="inlineStr">
         <is>
-          <t>call commit (2026-08); turnaround exec (2026-01)</t>
+          <t>turnaround exec (2026-05); cic prep</t>
         </is>
       </c>
     </row>
     <row r="30" ht="22" customHeight="1">
       <c r="A30" s="9" t="inlineStr">
         <is>
-          <t>GIII</t>
+          <t>SSTK</t>
         </is>
       </c>
       <c r="B30" s="10" t="inlineStr">
         <is>
-          <t>G-III Apparel Group, L</t>
+          <t>Shutterstock, Inc.</t>
         </is>
       </c>
       <c r="C30" s="10" t="inlineStr">
@@ -7915,32 +7915,32 @@
         </is>
       </c>
       <c r="D30" s="17" t="n">
-        <v>18.8</v>
+        <v>18.4</v>
       </c>
       <c r="E30" s="17" t="n">
-        <v>0.65</v>
+        <v>0.45</v>
       </c>
       <c r="F30" s="8" t="n">
-        <v>1170.8</v>
+        <v>162</v>
       </c>
       <c r="G30" s="17" t="n">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="H30" s="10" t="inlineStr">
         <is>
-          <t>turnaround exec (2026-05); cic prep</t>
+          <t>ceo change (2026-07); cic prep</t>
         </is>
       </c>
     </row>
     <row r="31" ht="22" customHeight="1">
       <c r="A31" s="6" t="inlineStr">
         <is>
-          <t>SSTK</t>
+          <t>BNGO</t>
         </is>
       </c>
       <c r="B31" s="7" t="inlineStr">
         <is>
-          <t>Shutterstock, Inc.</t>
+          <t>Bionano Genomics, Inc.</t>
         </is>
       </c>
       <c r="C31" s="7" t="inlineStr">
@@ -7949,32 +7949,32 @@
         </is>
       </c>
       <c r="D31" s="16" t="n">
-        <v>18.4</v>
+        <v>18</v>
       </c>
       <c r="E31" s="16" t="n">
-        <v>0.45</v>
+        <v>0.64</v>
       </c>
       <c r="F31" s="5" t="n">
-        <v>162</v>
+        <v>20.2</v>
       </c>
       <c r="G31" s="16" t="n">
-        <v>29</v>
+        <v>17</v>
       </c>
       <c r="H31" s="7" t="inlineStr">
         <is>
-          <t>ceo change (2026-07); cic prep</t>
+          <t>ceo change (2026-05); sop dissent (2026-04)</t>
         </is>
       </c>
     </row>
     <row r="32" ht="22" customHeight="1">
       <c r="A32" s="9" t="inlineStr">
         <is>
-          <t>BNGO</t>
+          <t>WW</t>
         </is>
       </c>
       <c r="B32" s="10" t="inlineStr">
         <is>
-          <t>Bionano Genomics, Inc.</t>
+          <t>WW International, Inc.</t>
         </is>
       </c>
       <c r="C32" s="10" t="inlineStr">
@@ -7983,32 +7983,34 @@
         </is>
       </c>
       <c r="D32" s="17" t="n">
-        <v>18</v>
+        <v>17.8</v>
       </c>
       <c r="E32" s="17" t="n">
-        <v>0.64</v>
+        <v>0.55</v>
       </c>
       <c r="F32" s="8" t="n">
-        <v>20.2</v>
-      </c>
-      <c r="G32" s="17" t="n">
-        <v>17</v>
+        <v>154.1</v>
+      </c>
+      <c r="G32" s="10" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
       <c r="H32" s="10" t="inlineStr">
         <is>
-          <t>ceo change (2026-05); sop dissent (2026-04)</t>
+          <t>board refresh (2026-04); turnaround exec (2025-12)</t>
         </is>
       </c>
     </row>
     <row r="33" ht="22" customHeight="1">
       <c r="A33" s="6" t="inlineStr">
         <is>
-          <t>WW</t>
+          <t>MLCI</t>
         </is>
       </c>
       <c r="B33" s="7" t="inlineStr">
         <is>
-          <t>WW International, Inc.</t>
+          <t>Mount Logan Capital In</t>
         </is>
       </c>
       <c r="C33" s="7" t="inlineStr">
@@ -8017,13 +8019,13 @@
         </is>
       </c>
       <c r="D33" s="16" t="n">
-        <v>17.8</v>
+        <v>14.6</v>
       </c>
       <c r="E33" s="16" t="n">
-        <v>0.55</v>
+        <v>0.59</v>
       </c>
       <c r="F33" s="5" t="n">
-        <v>154.1</v>
+        <v>35.6</v>
       </c>
       <c r="G33" s="7" t="inlineStr">
         <is>
@@ -8032,55 +8034,53 @@
       </c>
       <c r="H33" s="7" t="inlineStr">
         <is>
-          <t>board refresh (2026-04); turnaround exec (2025-12)</t>
+          <t>tender offer (2025-12); call value gap (2026-08)</t>
         </is>
       </c>
     </row>
     <row r="34" ht="22" customHeight="1">
       <c r="A34" s="9" t="inlineStr">
         <is>
-          <t>MLCI</t>
+          <t>CNDT</t>
         </is>
       </c>
       <c r="B34" s="10" t="inlineStr">
         <is>
-          <t>Mount Logan Capital In</t>
+          <t>Conduent Incorporated</t>
         </is>
       </c>
       <c r="C34" s="10" t="inlineStr">
         <is>
-          <t>ACTION LIKELY</t>
+          <t>BUILDING</t>
         </is>
       </c>
       <c r="D34" s="17" t="n">
-        <v>14.6</v>
+        <v>32.8</v>
       </c>
       <c r="E34" s="17" t="n">
-        <v>0.59</v>
+        <v>0.38</v>
       </c>
       <c r="F34" s="8" t="n">
-        <v>35.6</v>
-      </c>
-      <c r="G34" s="10" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+        <v>252</v>
+      </c>
+      <c r="G34" s="17" t="n">
+        <v>90</v>
       </c>
       <c r="H34" s="10" t="inlineStr">
         <is>
-          <t>tender offer (2025-12); call value gap (2026-08)</t>
+          <t>asset sale (2026-06); chair ceo split (2026-01); c</t>
         </is>
       </c>
     </row>
     <row r="35" ht="22" customHeight="1">
       <c r="A35" s="6" t="inlineStr">
         <is>
-          <t>CNDT</t>
+          <t>ONIT</t>
         </is>
       </c>
       <c r="B35" s="7" t="inlineStr">
         <is>
-          <t>Conduent Incorporated</t>
+          <t>Onity Group Inc.</t>
         </is>
       </c>
       <c r="C35" s="7" t="inlineStr">
@@ -8089,32 +8089,34 @@
         </is>
       </c>
       <c r="D35" s="16" t="n">
-        <v>32.8</v>
+        <v>31.8</v>
       </c>
       <c r="E35" s="16" t="n">
-        <v>0.38</v>
+        <v>0.4</v>
       </c>
       <c r="F35" s="5" t="n">
-        <v>252</v>
-      </c>
-      <c r="G35" s="16" t="n">
-        <v>90</v>
+        <v>265.8</v>
+      </c>
+      <c r="G35" s="7" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
       <c r="H35" s="7" t="inlineStr">
         <is>
-          <t>asset sale (2026-06); chair ceo split (2026-01); c</t>
+          <t>buyback auth (2026-02); proxy responsive (2026-04)</t>
         </is>
       </c>
     </row>
     <row r="36" ht="22" customHeight="1">
       <c r="A36" s="9" t="inlineStr">
         <is>
-          <t>ONIT</t>
+          <t>DCGO</t>
         </is>
       </c>
       <c r="B36" s="10" t="inlineStr">
         <is>
-          <t>Onity Group Inc.</t>
+          <t>DocGo Inc.</t>
         </is>
       </c>
       <c r="C36" s="10" t="inlineStr">
@@ -8123,34 +8125,32 @@
         </is>
       </c>
       <c r="D36" s="17" t="n">
-        <v>31.8</v>
+        <v>27</v>
       </c>
       <c r="E36" s="17" t="n">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="F36" s="8" t="n">
-        <v>265.8</v>
-      </c>
-      <c r="G36" s="10" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+        <v>35.8</v>
+      </c>
+      <c r="G36" s="17" t="n">
+        <v>99</v>
       </c>
       <c r="H36" s="10" t="inlineStr">
         <is>
-          <t>buyback auth (2026-02); proxy responsive (2026-04)</t>
+          <t>chair ceo split (2026-04); proxy responsive (2026-</t>
         </is>
       </c>
     </row>
     <row r="37" ht="22" customHeight="1">
       <c r="A37" s="6" t="inlineStr">
         <is>
-          <t>DCGO</t>
+          <t>VISN</t>
         </is>
       </c>
       <c r="B37" s="7" t="inlineStr">
         <is>
-          <t>DocGo Inc.</t>
+          <t>Vistance Networks, Inc</t>
         </is>
       </c>
       <c r="C37" s="7" t="inlineStr">
@@ -8159,32 +8159,32 @@
         </is>
       </c>
       <c r="D37" s="16" t="n">
-        <v>27</v>
+        <v>25.8</v>
       </c>
       <c r="E37" s="16" t="n">
-        <v>0.3</v>
+        <v>0.58</v>
       </c>
       <c r="F37" s="5" t="n">
-        <v>35.8</v>
+        <v>1463.9</v>
       </c>
       <c r="G37" s="16" t="n">
-        <v>99</v>
+        <v>172</v>
       </c>
       <c r="H37" s="7" t="inlineStr">
         <is>
-          <t>chair ceo split (2026-04); proxy responsive (2026-</t>
+          <t>asset sale (2026-04); call intent (2026-08); sop d</t>
         </is>
       </c>
     </row>
     <row r="38" ht="22" customHeight="1">
       <c r="A38" s="9" t="inlineStr">
         <is>
-          <t>CCZ</t>
+          <t>NNDM</t>
         </is>
       </c>
       <c r="B38" s="10" t="inlineStr">
         <is>
-          <t>Comcast Holdings Corp.</t>
+          <t>Nano Dimension Ltd.</t>
         </is>
       </c>
       <c r="C38" s="10" t="inlineStr">
@@ -8196,29 +8196,29 @@
         <v>25</v>
       </c>
       <c r="E38" s="17" t="n">
-        <v>0.17</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="F38" s="8" t="n">
-        <v>15715.3</v>
+        <v>332.5</v>
       </c>
       <c r="G38" s="17" t="n">
-        <v>60</v>
+        <v>107</v>
       </c>
       <c r="H38" s="10" t="inlineStr">
         <is>
-          <t>proxy responsive (2026-04); call intent (2026-07)</t>
+          <t>asset sale (2026-05); pill removed (2026-02); call</t>
         </is>
       </c>
     </row>
     <row r="39" ht="22" customHeight="1">
       <c r="A39" s="6" t="inlineStr">
         <is>
-          <t>SITC</t>
+          <t>CCZ</t>
         </is>
       </c>
       <c r="B39" s="7" t="inlineStr">
         <is>
-          <t>SITE Centers Corp.</t>
+          <t>Comcast Holdings Corp.</t>
         </is>
       </c>
       <c r="C39" s="7" t="inlineStr">
@@ -8227,34 +8227,32 @@
         </is>
       </c>
       <c r="D39" s="16" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E39" s="16" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.17</v>
       </c>
       <c r="F39" s="5" t="n">
-        <v>157.2</v>
-      </c>
-      <c r="G39" s="7" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+        <v>15715.3</v>
+      </c>
+      <c r="G39" s="16" t="n">
+        <v>60</v>
       </c>
       <c r="H39" s="7" t="inlineStr">
         <is>
-          <t>asset sale (2026-07); mda unlock (2026-08); sop di</t>
+          <t>proxy responsive (2026-04); call intent (2026-07)</t>
         </is>
       </c>
     </row>
     <row r="40" ht="22" customHeight="1">
       <c r="A40" s="9" t="inlineStr">
         <is>
-          <t>ALIT</t>
+          <t>SITC</t>
         </is>
       </c>
       <c r="B40" s="10" t="inlineStr">
         <is>
-          <t>Alight, Inc.</t>
+          <t>SITE Centers Corp.</t>
         </is>
       </c>
       <c r="C40" s="10" t="inlineStr">
@@ -8263,13 +8261,13 @@
         </is>
       </c>
       <c r="D40" s="17" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E40" s="17" t="n">
-        <v>0.33</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="F40" s="8" t="n">
-        <v>340.7</v>
+        <v>157.2</v>
       </c>
       <c r="G40" s="10" t="inlineStr">
         <is>
@@ -8278,19 +8276,19 @@
       </c>
       <c r="H40" s="10" t="inlineStr">
         <is>
-          <t>declassify (2026-07); mda capital (2026-05)</t>
+          <t>asset sale (2026-07); mda unlock (2026-08); sop di</t>
         </is>
       </c>
     </row>
     <row r="41" ht="22" customHeight="1">
       <c r="A41" s="6" t="inlineStr">
         <is>
-          <t>THRY</t>
+          <t>ALIT</t>
         </is>
       </c>
       <c r="B41" s="7" t="inlineStr">
         <is>
-          <t>Thryv Holdings, Inc.</t>
+          <t>Alight, Inc.</t>
         </is>
       </c>
       <c r="C41" s="7" t="inlineStr">
@@ -8302,10 +8300,10 @@
         <v>23</v>
       </c>
       <c r="E41" s="16" t="n">
-        <v>0.4</v>
+        <v>0.33</v>
       </c>
       <c r="F41" s="5" t="n">
-        <v>84.3</v>
+        <v>340.7</v>
       </c>
       <c r="G41" s="7" t="inlineStr">
         <is>
@@ -8314,19 +8312,19 @@
       </c>
       <c r="H41" s="7" t="inlineStr">
         <is>
-          <t>asset sale (2026-09); proxy responsive (2026-04)</t>
+          <t>declassify (2026-07); mda capital (2026-05)</t>
         </is>
       </c>
     </row>
     <row r="42" ht="22" customHeight="1">
       <c r="A42" s="9" t="inlineStr">
         <is>
-          <t>LAB</t>
+          <t>THRY</t>
         </is>
       </c>
       <c r="B42" s="10" t="inlineStr">
         <is>
-          <t>Standard BioTools Inc.</t>
+          <t>Thryv Holdings, Inc.</t>
         </is>
       </c>
       <c r="C42" s="10" t="inlineStr">
@@ -8338,29 +8336,31 @@
         <v>23</v>
       </c>
       <c r="E42" s="17" t="n">
-        <v>0.53</v>
+        <v>0.4</v>
       </c>
       <c r="F42" s="8" t="n">
-        <v>286.3</v>
-      </c>
-      <c r="G42" s="17" t="n">
-        <v>93</v>
+        <v>84.3</v>
+      </c>
+      <c r="G42" s="10" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
       <c r="H42" s="10" t="inlineStr">
         <is>
-          <t>asset sale (2026-08); mda unlock (2026-08)</t>
+          <t>asset sale (2026-09); proxy responsive (2026-04)</t>
         </is>
       </c>
     </row>
     <row r="43" ht="22" customHeight="1">
       <c r="A43" s="6" t="inlineStr">
         <is>
-          <t>HPP</t>
+          <t>LAB</t>
         </is>
       </c>
       <c r="B43" s="7" t="inlineStr">
         <is>
-          <t>Hudson Pacific Propert</t>
+          <t>Standard BioTools Inc.</t>
         </is>
       </c>
       <c r="C43" s="7" t="inlineStr">
@@ -8369,34 +8369,32 @@
         </is>
       </c>
       <c r="D43" s="16" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E43" s="16" t="n">
-        <v>0.23</v>
+        <v>0.53</v>
       </c>
       <c r="F43" s="5" t="n">
-        <v>636.8</v>
-      </c>
-      <c r="G43" s="7" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+        <v>286.3</v>
+      </c>
+      <c r="G43" s="16" t="n">
+        <v>93</v>
       </c>
       <c r="H43" s="7" t="inlineStr">
         <is>
-          <t>proxy responsive (2026-04); sop dissent (2026-04)</t>
+          <t>asset sale (2026-08); mda unlock (2026-08)</t>
         </is>
       </c>
     </row>
     <row r="44" ht="22" customHeight="1">
       <c r="A44" s="9" t="inlineStr">
         <is>
-          <t>MX</t>
+          <t>HPP</t>
         </is>
       </c>
       <c r="B44" s="10" t="inlineStr">
         <is>
-          <t>Magnachip Semiconducto</t>
+          <t>Hudson Pacific Propert</t>
         </is>
       </c>
       <c r="C44" s="10" t="inlineStr">
@@ -8405,32 +8403,34 @@
         </is>
       </c>
       <c r="D44" s="17" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E44" s="17" t="n">
-        <v>0.52</v>
+        <v>0.23</v>
       </c>
       <c r="F44" s="8" t="n">
-        <v>118.3</v>
-      </c>
-      <c r="G44" s="17" t="n">
-        <v>66</v>
+        <v>636.8</v>
+      </c>
+      <c r="G44" s="10" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
       <c r="H44" s="10" t="inlineStr">
         <is>
-          <t>mda unlock (2026-05); ceo change (2025-08)</t>
+          <t>proxy responsive (2026-04); sop dissent (2026-04)</t>
         </is>
       </c>
     </row>
     <row r="45" ht="22" customHeight="1">
       <c r="A45" s="6" t="inlineStr">
         <is>
-          <t>GETY</t>
+          <t>MX</t>
         </is>
       </c>
       <c r="B45" s="7" t="inlineStr">
         <is>
-          <t>Getty Images Holdings,</t>
+          <t>Magnachip Semiconducto</t>
         </is>
       </c>
       <c r="C45" s="7" t="inlineStr">
@@ -8439,34 +8439,32 @@
         </is>
       </c>
       <c r="D45" s="16" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E45" s="16" t="n">
-        <v>0.21</v>
+        <v>0.52</v>
       </c>
       <c r="F45" s="5" t="n">
-        <v>92.90000000000001</v>
-      </c>
-      <c r="G45" s="7" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+        <v>118.3</v>
+      </c>
+      <c r="G45" s="16" t="n">
+        <v>66</v>
       </c>
       <c r="H45" s="7" t="inlineStr">
         <is>
-          <t>activist settlement (2026-08)</t>
+          <t>mda unlock (2026-05); ceo change (2025-08)</t>
         </is>
       </c>
     </row>
     <row r="46" ht="22" customHeight="1">
       <c r="A46" s="9" t="inlineStr">
         <is>
-          <t>ORMP</t>
+          <t>GETY</t>
         </is>
       </c>
       <c r="B46" s="10" t="inlineStr">
         <is>
-          <t>Oramed Pharmaceuticals</t>
+          <t>Getty Images Holdings,</t>
         </is>
       </c>
       <c r="C46" s="10" t="inlineStr">
@@ -8475,32 +8473,34 @@
         </is>
       </c>
       <c r="D46" s="17" t="n">
-        <v>19.8</v>
+        <v>20</v>
       </c>
       <c r="E46" s="17" t="n">
-        <v>0.6</v>
+        <v>0.21</v>
       </c>
       <c r="F46" s="8" t="n">
-        <v>190.3</v>
-      </c>
-      <c r="G46" s="17" t="n">
-        <v>7</v>
+        <v>92.90000000000001</v>
+      </c>
+      <c r="G46" s="10" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
       <c r="H46" s="10" t="inlineStr">
         <is>
-          <t>pill removed (2025-11); mda unlock (2026-03); cic</t>
+          <t>activist settlement (2026-08)</t>
         </is>
       </c>
     </row>
     <row r="47" ht="22" customHeight="1">
       <c r="A47" s="6" t="inlineStr">
         <is>
-          <t>MPT</t>
+          <t>ORMP</t>
         </is>
       </c>
       <c r="B47" s="7" t="inlineStr">
         <is>
-          <t>Medical Properties Tru</t>
+          <t>Oramed Pharmaceuticals</t>
         </is>
       </c>
       <c r="C47" s="7" t="inlineStr">
@@ -8509,34 +8509,32 @@
         </is>
       </c>
       <c r="D47" s="16" t="n">
-        <v>19</v>
+        <v>19.8</v>
       </c>
       <c r="E47" s="16" t="n">
-        <v>0.47</v>
+        <v>0.6</v>
       </c>
       <c r="F47" s="5" t="n">
-        <v>2132.2</v>
-      </c>
-      <c r="G47" s="7" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+        <v>190.3</v>
+      </c>
+      <c r="G47" s="16" t="n">
+        <v>7</v>
       </c>
       <c r="H47" s="7" t="inlineStr">
         <is>
-          <t>mda unlock (2026-05); sop dissent (2026-04)</t>
+          <t>pill removed (2025-11); mda unlock (2026-03); cic</t>
         </is>
       </c>
     </row>
     <row r="48" ht="22" customHeight="1">
       <c r="A48" s="9" t="inlineStr">
         <is>
-          <t>NEUP</t>
+          <t>MPT</t>
         </is>
       </c>
       <c r="B48" s="10" t="inlineStr">
         <is>
-          <t>Neuphoria Therapeutics</t>
+          <t>Medical Properties Tru</t>
         </is>
       </c>
       <c r="C48" s="10" t="inlineStr">
@@ -8545,32 +8543,34 @@
         </is>
       </c>
       <c r="D48" s="17" t="n">
-        <v>18.6</v>
+        <v>19</v>
       </c>
       <c r="E48" s="17" t="n">
-        <v>0.68</v>
+        <v>0.47</v>
       </c>
       <c r="F48" s="8" t="n">
-        <v>20</v>
-      </c>
-      <c r="G48" s="17" t="n">
-        <v>97</v>
+        <v>2132.2</v>
+      </c>
+      <c r="G48" s="10" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
       <c r="H48" s="10" t="inlineStr">
         <is>
-          <t>pill removed (2025-10); mda unlock (2026-05)</t>
+          <t>mda unlock (2026-05); sop dissent (2026-04)</t>
         </is>
       </c>
     </row>
     <row r="49" ht="22" customHeight="1">
       <c r="A49" s="6" t="inlineStr">
         <is>
-          <t>NNDM</t>
+          <t>CHGG</t>
         </is>
       </c>
       <c r="B49" s="7" t="inlineStr">
         <is>
-          <t>Nano Dimension Ltd.</t>
+          <t>Chegg, Inc.</t>
         </is>
       </c>
       <c r="C49" s="7" t="inlineStr">
@@ -8579,32 +8579,32 @@
         </is>
       </c>
       <c r="D49" s="16" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E49" s="16" t="n">
         <v>0.6899999999999999</v>
       </c>
       <c r="F49" s="5" t="n">
-        <v>332.5</v>
+        <v>81.5</v>
       </c>
       <c r="G49" s="16" t="n">
-        <v>107</v>
+        <v>41</v>
       </c>
       <c r="H49" s="7" t="inlineStr">
         <is>
-          <t>asset sale (2026-05); pill removed (2026-02)</t>
+          <t>call commit (2026-08); call value gap (2026-08)</t>
         </is>
       </c>
     </row>
     <row r="50" ht="22" customHeight="1">
       <c r="A50" s="9" t="inlineStr">
         <is>
-          <t>ICMB</t>
+          <t>NEUP</t>
         </is>
       </c>
       <c r="B50" s="10" t="inlineStr">
         <is>
-          <t>Investcorp Credit Mana</t>
+          <t>Neuphoria Therapeutics</t>
         </is>
       </c>
       <c r="C50" s="10" t="inlineStr">
@@ -8613,34 +8613,32 @@
         </is>
       </c>
       <c r="D50" s="17" t="n">
-        <v>18</v>
+        <v>18.6</v>
       </c>
       <c r="E50" s="17" t="n">
-        <v>0.24</v>
+        <v>0.68</v>
       </c>
       <c r="F50" s="8" t="n">
-        <v>12.6</v>
-      </c>
-      <c r="G50" s="10" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+        <v>20</v>
+      </c>
+      <c r="G50" s="17" t="n">
+        <v>97</v>
       </c>
       <c r="H50" s="10" t="inlineStr">
         <is>
-          <t>strategic review (2026-04)</t>
+          <t>pill removed (2025-10); mda unlock (2026-05)</t>
         </is>
       </c>
     </row>
     <row r="51" ht="22" customHeight="1">
       <c r="A51" s="6" t="inlineStr">
         <is>
-          <t>QTRX</t>
+          <t>ICMB</t>
         </is>
       </c>
       <c r="B51" s="7" t="inlineStr">
         <is>
-          <t>Quanterix Corporation</t>
+          <t>Investcorp Credit Mana</t>
         </is>
       </c>
       <c r="C51" s="7" t="inlineStr">
@@ -8649,32 +8647,34 @@
         </is>
       </c>
       <c r="D51" s="16" t="n">
-        <v>17.8</v>
+        <v>18</v>
       </c>
       <c r="E51" s="16" t="n">
-        <v>0.62</v>
+        <v>0.24</v>
       </c>
       <c r="F51" s="5" t="n">
-        <v>146</v>
-      </c>
-      <c r="G51" s="16" t="n">
-        <v>25</v>
+        <v>12.6</v>
+      </c>
+      <c r="G51" s="7" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
       <c r="H51" s="7" t="inlineStr">
         <is>
-          <t>activist settlement (2025-08); declassify (2025-10</t>
+          <t>strategic review (2026-04)</t>
         </is>
       </c>
     </row>
     <row r="52" ht="22" customHeight="1">
       <c r="A52" s="9" t="inlineStr">
         <is>
-          <t>AHCO</t>
+          <t>QTRX</t>
         </is>
       </c>
       <c r="B52" s="10" t="inlineStr">
         <is>
-          <t>AdaptHealth Corp.</t>
+          <t>Quanterix Corporation</t>
         </is>
       </c>
       <c r="C52" s="10" t="inlineStr">
@@ -8683,34 +8683,32 @@
         </is>
       </c>
       <c r="D52" s="17" t="n">
-        <v>17</v>
+        <v>17.8</v>
       </c>
       <c r="E52" s="17" t="n">
-        <v>0.57</v>
+        <v>0.62</v>
       </c>
       <c r="F52" s="8" t="n">
-        <v>784.4</v>
-      </c>
-      <c r="G52" s="10" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+        <v>146</v>
+      </c>
+      <c r="G52" s="17" t="n">
+        <v>25</v>
       </c>
       <c r="H52" s="10" t="inlineStr">
         <is>
-          <t>asset sale (2026-08); proxy responsive (2026-04)</t>
+          <t>activist settlement (2025-08); declassify (2025-10</t>
         </is>
       </c>
     </row>
     <row r="53" ht="22" customHeight="1">
       <c r="A53" s="6" t="inlineStr">
         <is>
-          <t>BIRD</t>
+          <t>AHCO</t>
         </is>
       </c>
       <c r="B53" s="7" t="inlineStr">
         <is>
-          <t>Allbirds, Inc.</t>
+          <t>AdaptHealth Corp.</t>
         </is>
       </c>
       <c r="C53" s="7" t="inlineStr">
@@ -8722,10 +8720,10 @@
         <v>17</v>
       </c>
       <c r="E53" s="16" t="n">
-        <v>0.66</v>
+        <v>0.57</v>
       </c>
       <c r="F53" s="5" t="n">
-        <v>14.8</v>
+        <v>784.4</v>
       </c>
       <c r="G53" s="7" t="inlineStr">
         <is>
@@ -8734,19 +8732,19 @@
       </c>
       <c r="H53" s="7" t="inlineStr">
         <is>
-          <t>asset sale (2026-06); mda unlock (2026-05)</t>
+          <t>asset sale (2026-08); proxy responsive (2026-04)</t>
         </is>
       </c>
     </row>
     <row r="54" ht="22" customHeight="1">
       <c r="A54" s="9" t="inlineStr">
         <is>
-          <t>CION</t>
+          <t>BIRD</t>
         </is>
       </c>
       <c r="B54" s="10" t="inlineStr">
         <is>
-          <t>CION Investment Corpor</t>
+          <t>Allbirds, Inc.</t>
         </is>
       </c>
       <c r="C54" s="10" t="inlineStr">
@@ -8758,10 +8756,10 @@
         <v>17</v>
       </c>
       <c r="E54" s="17" t="n">
-        <v>0.54</v>
+        <v>0.66</v>
       </c>
       <c r="F54" s="8" t="n">
-        <v>357</v>
+        <v>14.8</v>
       </c>
       <c r="G54" s="10" t="inlineStr">
         <is>
@@ -8770,19 +8768,19 @@
       </c>
       <c r="H54" s="10" t="inlineStr">
         <is>
-          <t>call commit (2026-08); call value gap (2026-08)</t>
+          <t>asset sale (2026-06); mda unlock (2026-05)</t>
         </is>
       </c>
     </row>
     <row r="55" ht="22" customHeight="1">
       <c r="A55" s="6" t="inlineStr">
         <is>
-          <t>GNW</t>
+          <t>CION</t>
         </is>
       </c>
       <c r="B55" s="7" t="inlineStr">
         <is>
-          <t>Genworth Financial, In</t>
+          <t>CION Investment Corpor</t>
         </is>
       </c>
       <c r="C55" s="7" t="inlineStr">
@@ -8794,10 +8792,10 @@
         <v>17</v>
       </c>
       <c r="E55" s="16" t="n">
-        <v>0.42</v>
+        <v>0.54</v>
       </c>
       <c r="F55" s="5" t="n">
-        <v>3686.5</v>
+        <v>357</v>
       </c>
       <c r="G55" s="7" t="inlineStr">
         <is>
@@ -8813,12 +8811,12 @@
     <row r="56" ht="22" customHeight="1">
       <c r="A56" s="9" t="inlineStr">
         <is>
-          <t>SEER</t>
+          <t>FINV</t>
         </is>
       </c>
       <c r="B56" s="10" t="inlineStr">
         <is>
-          <t>Seer, Inc.</t>
+          <t>FinVolution Group</t>
         </is>
       </c>
       <c r="C56" s="10" t="inlineStr">
@@ -8830,13 +8828,15 @@
         <v>17</v>
       </c>
       <c r="E56" s="17" t="n">
-        <v>0.44</v>
+        <v>0.3</v>
       </c>
       <c r="F56" s="8" t="n">
-        <v>100.1</v>
-      </c>
-      <c r="G56" s="17" t="n">
-        <v>47</v>
+        <v>802.3</v>
+      </c>
+      <c r="G56" s="10" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
       <c r="H56" s="10" t="inlineStr">
         <is>
@@ -8847,12 +8847,12 @@
     <row r="57" ht="22" customHeight="1">
       <c r="A57" s="6" t="inlineStr">
         <is>
-          <t>SNDL</t>
+          <t>GNW</t>
         </is>
       </c>
       <c r="B57" s="7" t="inlineStr">
         <is>
-          <t>SNDL Inc.</t>
+          <t>Genworth Financial, In</t>
         </is>
       </c>
       <c r="C57" s="7" t="inlineStr">
@@ -8864,10 +8864,10 @@
         <v>17</v>
       </c>
       <c r="E57" s="16" t="n">
-        <v>0.47</v>
+        <v>0.42</v>
       </c>
       <c r="F57" s="5" t="n">
-        <v>363.1</v>
+        <v>3686.5</v>
       </c>
       <c r="G57" s="7" t="inlineStr">
         <is>
@@ -8876,19 +8876,19 @@
       </c>
       <c r="H57" s="7" t="inlineStr">
         <is>
-          <t>call commit (2026-07); call value gap (2026-07)</t>
+          <t>call commit (2026-08); call value gap (2026-08)</t>
         </is>
       </c>
     </row>
     <row r="58" ht="22" customHeight="1">
       <c r="A58" s="9" t="inlineStr">
         <is>
-          <t>USNA</t>
+          <t>ICG</t>
         </is>
       </c>
       <c r="B58" s="10" t="inlineStr">
         <is>
-          <t>USANA Health Sciences,</t>
+          <t>Intchains Group Limite</t>
         </is>
       </c>
       <c r="C58" s="10" t="inlineStr">
@@ -8897,32 +8897,34 @@
         </is>
       </c>
       <c r="D58" s="17" t="n">
-        <v>16.8</v>
+        <v>17</v>
       </c>
       <c r="E58" s="17" t="n">
-        <v>0.5</v>
+        <v>0.24</v>
       </c>
       <c r="F58" s="8" t="n">
-        <v>261.4</v>
-      </c>
-      <c r="G58" s="17" t="n">
-        <v>62</v>
+        <v>30.2</v>
+      </c>
+      <c r="G58" s="10" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
       <c r="H58" s="10" t="inlineStr">
         <is>
-          <t>ceo change (2026-01)</t>
+          <t>call commit (2026-08)</t>
         </is>
       </c>
     </row>
     <row r="59" ht="22" customHeight="1">
       <c r="A59" s="6" t="inlineStr">
         <is>
-          <t>STRR</t>
+          <t>SEER</t>
         </is>
       </c>
       <c r="B59" s="7" t="inlineStr">
         <is>
-          <t>Star Equity Holdings,</t>
+          <t>Seer, Inc.</t>
         </is>
       </c>
       <c r="C59" s="7" t="inlineStr">
@@ -8931,34 +8933,32 @@
         </is>
       </c>
       <c r="D59" s="16" t="n">
-        <v>16.8</v>
+        <v>17</v>
       </c>
       <c r="E59" s="16" t="n">
-        <v>0.63</v>
+        <v>0.44</v>
       </c>
       <c r="F59" s="5" t="n">
-        <v>37.6</v>
-      </c>
-      <c r="G59" s="7" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+        <v>100.1</v>
+      </c>
+      <c r="G59" s="16" t="n">
+        <v>47</v>
       </c>
       <c r="H59" s="7" t="inlineStr">
         <is>
-          <t>call intent (2026-08); call value gap (2026-08); c</t>
+          <t>call commit (2026-08)</t>
         </is>
       </c>
     </row>
     <row r="60" ht="22" customHeight="1">
       <c r="A60" s="9" t="inlineStr">
         <is>
-          <t>STRZ</t>
+          <t>SNDL</t>
         </is>
       </c>
       <c r="B60" s="10" t="inlineStr">
         <is>
-          <t>Starz Entertainment Co</t>
+          <t>SNDL Inc.</t>
         </is>
       </c>
       <c r="C60" s="10" t="inlineStr">
@@ -8967,13 +8967,13 @@
         </is>
       </c>
       <c r="D60" s="17" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E60" s="17" t="n">
-        <v>0.6</v>
+        <v>0.47</v>
       </c>
       <c r="F60" s="8" t="n">
-        <v>388.9</v>
+        <v>363.1</v>
       </c>
       <c r="G60" s="10" t="inlineStr">
         <is>
@@ -8982,19 +8982,19 @@
       </c>
       <c r="H60" s="10" t="inlineStr">
         <is>
-          <t>pill removed (2026-03); mda unlock (2026-08)</t>
+          <t>call commit (2026-07); call value gap (2026-07)</t>
         </is>
       </c>
     </row>
     <row r="61" ht="22" customHeight="1">
       <c r="A61" s="6" t="inlineStr">
         <is>
-          <t>FG</t>
+          <t>USNA</t>
         </is>
       </c>
       <c r="B61" s="7" t="inlineStr">
         <is>
-          <t>F&amp;G Annuities &amp; Life,</t>
+          <t>USANA Health Sciences,</t>
         </is>
       </c>
       <c r="C61" s="7" t="inlineStr">
@@ -9003,34 +9003,32 @@
         </is>
       </c>
       <c r="D61" s="16" t="n">
-        <v>16</v>
+        <v>16.8</v>
       </c>
       <c r="E61" s="16" t="n">
-        <v>0.63</v>
+        <v>0.5</v>
       </c>
       <c r="F61" s="5" t="n">
-        <v>2887.5</v>
-      </c>
-      <c r="G61" s="7" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+        <v>261.4</v>
+      </c>
+      <c r="G61" s="16" t="n">
+        <v>62</v>
       </c>
       <c r="H61" s="7" t="inlineStr">
         <is>
-          <t>call commit (2026-08); call value gap (2026-08)</t>
+          <t>ceo change (2026-01)</t>
         </is>
       </c>
     </row>
     <row r="62" ht="22" customHeight="1">
       <c r="A62" s="9" t="inlineStr">
         <is>
-          <t>ZSQR</t>
+          <t>STRZ</t>
         </is>
       </c>
       <c r="B62" s="10" t="inlineStr">
         <is>
-          <t>Z Squared Inc.</t>
+          <t>Starz Entertainment Co</t>
         </is>
       </c>
       <c r="C62" s="10" t="inlineStr">
@@ -9042,29 +9040,31 @@
         <v>16</v>
       </c>
       <c r="E62" s="17" t="n">
-        <v>0.14</v>
+        <v>0.6</v>
       </c>
       <c r="F62" s="8" t="n">
-        <v>18</v>
-      </c>
-      <c r="G62" s="17" t="n">
-        <v>28</v>
+        <v>388.9</v>
+      </c>
+      <c r="G62" s="10" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
       <c r="H62" s="10" t="inlineStr">
         <is>
-          <t>turnaround exec (2026-04)</t>
+          <t>pill removed (2026-03); mda unlock (2026-08)</t>
         </is>
       </c>
     </row>
     <row r="63" ht="22" customHeight="1">
       <c r="A63" s="6" t="inlineStr">
         <is>
-          <t>SDEV</t>
+          <t>FG</t>
         </is>
       </c>
       <c r="B63" s="7" t="inlineStr">
         <is>
-          <t>Stablecoin Development</t>
+          <t>F&amp;G Annuities &amp; Life,</t>
         </is>
       </c>
       <c r="C63" s="7" t="inlineStr">
@@ -9076,29 +9076,31 @@
         <v>16</v>
       </c>
       <c r="E63" s="16" t="n">
-        <v>0.46</v>
+        <v>0.63</v>
       </c>
       <c r="F63" s="5" t="n">
-        <v>58</v>
-      </c>
-      <c r="G63" s="16" t="n">
-        <v>32</v>
+        <v>2887.5</v>
+      </c>
+      <c r="G63" s="7" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
       <c r="H63" s="7" t="inlineStr">
         <is>
-          <t>turnaround exec (2026-04)</t>
+          <t>call commit (2026-08); call value gap (2026-08)</t>
         </is>
       </c>
     </row>
     <row r="64" ht="22" customHeight="1">
       <c r="A64" s="9" t="inlineStr">
         <is>
-          <t>RGS</t>
+          <t>ZSQR</t>
         </is>
       </c>
       <c r="B64" s="10" t="inlineStr">
         <is>
-          <t>Regis Corporation</t>
+          <t>Z Squared Inc.</t>
         </is>
       </c>
       <c r="C64" s="10" t="inlineStr">
@@ -9107,29 +9109,27 @@
         </is>
       </c>
       <c r="D64" s="17" t="n">
-        <v>15.8</v>
+        <v>16</v>
       </c>
       <c r="E64" s="17" t="n">
-        <v>0.37</v>
+        <v>0.14</v>
       </c>
       <c r="F64" s="8" t="n">
-        <v>70</v>
-      </c>
-      <c r="G64" s="10" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+        <v>18</v>
+      </c>
+      <c r="G64" s="17" t="n">
+        <v>28</v>
       </c>
       <c r="H64" s="10" t="inlineStr">
         <is>
-          <t>ceo change (2026-03)</t>
+          <t>turnaround exec (2026-04)</t>
         </is>
       </c>
     </row>
     <row r="66" ht="28" customHeight="1">
       <c r="A66" s="11" t="inlineStr">
         <is>
-          <t>87 names trade at 0.10–0.70× book (validated FMP book: market cap ÷ latest equity) with a qualifying governance catalyst; 30 are ACTION LIKELY (a hard event — activist settlement/13D, value committee or strategic review, capital-return policy or tender, CEO change, turnaround executive — within ~9 months, plus independent corroboration). Signals are weighted by age (≤6 months full weight, 6–12 months 0.8, 12–18 months 0.5). Pay tied to TSR/ROE appears in 63% of proxies, so it is treated as context, not as a change. Sources: governance_events_8k.py (dated 8-K governance changes), activist 13D/letters, re-rate events, MD&amp;A language, proxy redesigns and say-on-pay dissent. Source: governance_discount.py.</t>
+          <t>86 names trade at 0.10–0.70× book (validated FMP book: market cap ÷ latest equity) with a qualifying governance catalyst; 29 are ACTION LIKELY (a hard event — activist settlement/13D, value committee or strategic review, capital-return policy or tender, CEO change, turnaround executive — within ~9 months, plus independent corroboration). Signals are weighted by age (≤6 months full weight, 6–12 months 0.8, 12–18 months 0.5). Pay tied to TSR/ROE appears in 63% of proxies, so it is treated as context, not as a change. Sources: governance_events_8k.py (dated 8-K governance changes), activist 13D/letters, re-rate events, MD&amp;A language, proxy redesigns and say-on-pay dissent. Source: governance_discount.py.</t>
         </is>
       </c>
     </row>
@@ -9151,7 +9151,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I86"/>
+  <dimension ref="A1:K86"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -9160,9 +9160,11 @@
     <col width="7" customWidth="1" min="4" max="4"/>
     <col width="7" customWidth="1" min="5" max="5"/>
     <col width="6" customWidth="1" min="6" max="6"/>
-    <col width="8" customWidth="1" min="7" max="7"/>
-    <col width="22" customWidth="1" min="8" max="8"/>
-    <col width="58" customWidth="1" min="9" max="9"/>
+    <col width="6" customWidth="1" min="7" max="7"/>
+    <col width="6" customWidth="1" min="8" max="8"/>
+    <col width="8" customWidth="1" min="9" max="9"/>
+    <col width="22" customWidth="1" min="10" max="10"/>
+    <col width="58" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1" ht="26" customHeight="1">
@@ -9186,6 +9188,8 @@
       <c r="G2" s="3" t="n"/>
       <c r="H2" s="3" t="n"/>
       <c r="I2" s="3" t="n"/>
+      <c r="J2" s="3" t="n"/>
+      <c r="K2" s="3" t="n"/>
     </row>
     <row r="3" ht="8" customHeight="1"/>
     <row r="4" ht="18" customHeight="1">
@@ -9221,15 +9225,25 @@
       </c>
       <c r="G4" s="4" t="inlineStr">
         <is>
+          <t>Size</t>
+        </is>
+      </c>
+      <c r="H4" s="4" t="inlineStr">
+        <is>
+          <t>CEO+CFO</t>
+        </is>
+      </c>
+      <c r="I4" s="4" t="inlineStr">
+        <is>
           <t>Call</t>
         </is>
       </c>
-      <c r="H4" s="4" t="inlineStr">
+      <c r="J4" s="4" t="inlineStr">
         <is>
           <t>New / strongest families</t>
         </is>
       </c>
-      <c r="I4" s="4" t="inlineStr">
+      <c r="K4" s="4" t="inlineStr">
         <is>
           <t>Evidence (management, verbatim)</t>
         </is>
@@ -9252,7 +9266,7 @@
         </is>
       </c>
       <c r="D5" s="16" t="n">
-        <v>0.83</v>
+        <v>0.89</v>
       </c>
       <c r="E5" s="16" t="n">
         <v>0.9399999999999999</v>
@@ -9260,17 +9274,25 @@
       <c r="F5" s="16" t="n">
         <v>0.8</v>
       </c>
-      <c r="G5" s="7" t="inlineStr">
+      <c r="G5" s="16" t="n">
+        <v>35</v>
+      </c>
+      <c r="H5" s="7" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="I5" s="7" t="inlineStr">
         <is>
           <t>2026-08-07</t>
         </is>
       </c>
-      <c r="H5" s="7" t="inlineStr">
+      <c r="J5" s="7" t="inlineStr">
         <is>
           <t>buyback, monetize, dividend_return</t>
         </is>
       </c>
-      <c r="I5" s="7" t="inlineStr">
+      <c r="K5" s="7" t="inlineStr">
         <is>
           <t>[buyback] “Since July 1, 2026, we have repurchased 700,000 additional shares in the open market.”</t>
         </is>
@@ -9293,7 +9315,7 @@
         </is>
       </c>
       <c r="D6" s="17" t="n">
-        <v>0.78</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="E6" s="17" t="n">
         <v>1.14</v>
@@ -9301,17 +9323,25 @@
       <c r="F6" s="17" t="n">
         <v>0.8</v>
       </c>
-      <c r="G6" s="10" t="inlineStr">
+      <c r="G6" s="17" t="n">
+        <v>26</v>
+      </c>
+      <c r="H6" s="10" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="I6" s="10" t="inlineStr">
         <is>
           <t>2026-08-05</t>
         </is>
       </c>
-      <c r="H6" s="10" t="inlineStr">
+      <c r="J6" s="10" t="inlineStr">
         <is>
           <t>buyback, dividend_return, anticipation</t>
         </is>
       </c>
-      <c r="I6" s="10" t="inlineStr">
+      <c r="K6" s="10" t="inlineStr">
         <is>
           <t>[buyback] “In respect to the first quarter of 2026, we returned 30% of net income attributable to stockholders, comprising $6.3 million of share buybacks and $4.3 million of cash dividend, re”</t>
         </is>
@@ -9320,12 +9350,12 @@
     <row r="7" ht="30" customHeight="1">
       <c r="A7" s="6" t="inlineStr">
         <is>
-          <t>JOYY</t>
+          <t>RNR</t>
         </is>
       </c>
       <c r="B7" s="7" t="inlineStr">
         <is>
-          <t>JOYY, Inc. Sponsored</t>
+          <t>RenaissanceRe Holdin</t>
         </is>
       </c>
       <c r="C7" s="7" t="inlineStr">
@@ -9337,36 +9367,44 @@
         <v>0.76</v>
       </c>
       <c r="E7" s="16" t="n">
-        <v>0.64</v>
+        <v>1.16</v>
       </c>
       <c r="F7" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="G7" s="7" t="inlineStr">
-        <is>
-          <t>2026-08-25</t>
-        </is>
+        <v>0.4</v>
+      </c>
+      <c r="G7" s="16" t="n">
+        <v>50</v>
       </c>
       <c r="H7" s="7" t="inlineStr">
         <is>
-          <t>buyback, value_gap, monetize</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="I7" s="7" t="inlineStr">
         <is>
-          <t>[buyback] “We have repurchased a cumulative total of $216 million, maintaining an accelerated buyback pace.”</t>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="J7" s="7" t="inlineStr">
+        <is>
+          <t>buyback, anticipation, dividend_return</t>
+        </is>
+      </c>
+      <c r="K7" s="7" t="inlineStr">
+        <is>
+          <t>[buyback] “So far in the third quarter through July 20, we repurchased an additional $83 million of our shares.”</t>
         </is>
       </c>
     </row>
     <row r="8" ht="30" customHeight="1">
       <c r="A8" s="9" t="inlineStr">
         <is>
-          <t>SCHL</t>
+          <t>MRETF</t>
         </is>
       </c>
       <c r="B8" s="10" t="inlineStr">
         <is>
-          <t>Scholastic Corporati</t>
+          <t>–</t>
         </is>
       </c>
       <c r="C8" s="10" t="inlineStr">
@@ -9375,39 +9413,49 @@
         </is>
       </c>
       <c r="D8" s="17" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="E8" s="17" t="n">
-        <v>0.75</v>
+        <v>0.76</v>
+      </c>
+      <c r="E8" s="10" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
       <c r="F8" s="17" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="G8" s="10" t="inlineStr">
-        <is>
-          <t>2026-07-23</t>
-        </is>
+        <v>4.6</v>
+      </c>
+      <c r="G8" s="17" t="n">
+        <v>10</v>
       </c>
       <c r="H8" s="10" t="inlineStr">
         <is>
-          <t>monetize, buyback, dividend_return</t>
+          <t>–</t>
         </is>
       </c>
       <c r="I8" s="10" t="inlineStr">
         <is>
-          <t>[monetize] “During the year, we returned over $285 million to shareholders, substantially accelerated by the sale-leaseback transactions and subsequent repurchase activity while establishing a”</t>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="J8" s="10" t="inlineStr">
+        <is>
+          <t>NEW monetize, buyback, dividend_return,</t>
+        </is>
+      </c>
+      <c r="K8" s="10" t="inlineStr">
+        <is>
+          <t>[monetize] “As Pat noted, we sold a majority stake in our fluids plant in China during the quarter, further reducing our presence in the region, and we are exploring other potential divestitur”</t>
         </is>
       </c>
     </row>
     <row r="9" ht="30" customHeight="1">
       <c r="A9" s="6" t="inlineStr">
         <is>
-          <t>GPN</t>
+          <t>JOYY</t>
         </is>
       </c>
       <c r="B9" s="7" t="inlineStr">
         <is>
-          <t>Global Payments Inc.</t>
+          <t>JOYY, Inc. Sponsored</t>
         </is>
       </c>
       <c r="C9" s="7" t="inlineStr">
@@ -9416,39 +9464,47 @@
         </is>
       </c>
       <c r="D9" s="16" t="n">
-        <v>0.72</v>
+        <v>0.75</v>
       </c>
       <c r="E9" s="16" t="n">
-        <v>0.92</v>
+        <v>0.64</v>
       </c>
       <c r="F9" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="G9" s="7" t="inlineStr">
-        <is>
-          <t>2026-08-05</t>
-        </is>
+      <c r="G9" s="16" t="n">
+        <v>50</v>
       </c>
       <c r="H9" s="7" t="inlineStr">
         <is>
-          <t>buyback, cost, dividend_return</t>
+          <t>–</t>
         </is>
       </c>
       <c r="I9" s="7" t="inlineStr">
         <is>
-          <t>[buyback] “In the second quarter, we repurchased approximately 8 million shares for $550 million through our previously announced accelerated share repurchases as well as open market repurcha”</t>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="J9" s="7" t="inlineStr">
+        <is>
+          <t>buyback, value_gap, monetize</t>
+        </is>
+      </c>
+      <c r="K9" s="7" t="inlineStr">
+        <is>
+          <t>[buyback] “We have repurchased a cumulative total of $216 million, maintaining an accelerated buyback pace.”</t>
         </is>
       </c>
     </row>
     <row r="10" ht="30" customHeight="1">
       <c r="A10" s="9" t="inlineStr">
         <is>
-          <t>BXC</t>
+          <t>NEXN</t>
         </is>
       </c>
       <c r="B10" s="10" t="inlineStr">
         <is>
-          <t>Bluelinx Holdings In</t>
+          <t>Nexxen International</t>
         </is>
       </c>
       <c r="C10" s="10" t="inlineStr">
@@ -9457,7 +9513,7 @@
         </is>
       </c>
       <c r="D10" s="17" t="n">
-        <v>0.71</v>
+        <v>0.74</v>
       </c>
       <c r="E10" s="17" t="n">
         <v>1.02</v>
@@ -9465,31 +9521,39 @@
       <c r="F10" s="17" t="n">
         <v>0</v>
       </c>
-      <c r="G10" s="10" t="inlineStr">
-        <is>
-          <t>2026-05-06</t>
-        </is>
+      <c r="G10" s="17" t="n">
+        <v>50</v>
       </c>
       <c r="H10" s="10" t="inlineStr">
         <is>
-          <t>buyback, dividend_return, anticipation</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="I10" s="10" t="inlineStr">
         <is>
-          <t>[buyback] “From the end of the quarter through April 21, we have repurchased additional shares, bringing the total dollar amount purchased year-to-date to $5 million.”</t>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="J10" s="10" t="inlineStr">
+        <is>
+          <t>buyback, monetize, anticipation</t>
+        </is>
+      </c>
+      <c r="K10" s="10" t="inlineStr">
+        <is>
+          <t>[buyback] “On capital allocation, we repurchased roughly 1.1 million shares in Q1, investing approximately $7.2 million.”</t>
         </is>
       </c>
     </row>
     <row r="11" ht="30" customHeight="1">
       <c r="A11" s="6" t="inlineStr">
         <is>
-          <t>VSNT</t>
+          <t>SCHL</t>
         </is>
       </c>
       <c r="B11" s="7" t="inlineStr">
         <is>
-          <t>Versant Media Group,</t>
+          <t>Scholastic Corporati</t>
         </is>
       </c>
       <c r="C11" s="7" t="inlineStr">
@@ -9498,39 +9562,47 @@
         </is>
       </c>
       <c r="D11" s="16" t="n">
-        <v>0.71</v>
+        <v>0.73</v>
       </c>
       <c r="E11" s="16" t="n">
-        <v>0.58</v>
+        <v>0.75</v>
       </c>
       <c r="F11" s="16" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="G11" s="7" t="inlineStr">
-        <is>
-          <t>2026-08-06</t>
-        </is>
+        <v>0.4</v>
+      </c>
+      <c r="G11" s="16" t="n">
+        <v>39</v>
       </c>
       <c r="H11" s="7" t="inlineStr">
         <is>
-          <t>buyback, dividend_return, cost</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="I11" s="7" t="inlineStr">
         <is>
-          <t>[buyback] “Demonstrating our commitment to returning capital to shareholders, we repurchased $100 million of stock in the second quarter under the previously announced accelerated share repur”</t>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="J11" s="7" t="inlineStr">
+        <is>
+          <t>monetize, buyback, dividend_return</t>
+        </is>
+      </c>
+      <c r="K11" s="7" t="inlineStr">
+        <is>
+          <t>[monetize] “During the year, we returned over $285 million to shareholders, substantially accelerated by the sale-leaseback transactions and subsequent repurchase activity while establishing a”</t>
         </is>
       </c>
     </row>
     <row r="12" ht="30" customHeight="1">
       <c r="A12" s="9" t="inlineStr">
         <is>
-          <t>CALY</t>
+          <t>GPN</t>
         </is>
       </c>
       <c r="B12" s="10" t="inlineStr">
         <is>
-          <t>Callaway Golf Compan</t>
+          <t>Global Payments Inc.</t>
         </is>
       </c>
       <c r="C12" s="10" t="inlineStr">
@@ -9539,39 +9611,47 @@
         </is>
       </c>
       <c r="D12" s="17" t="n">
-        <v>0.7</v>
+        <v>0.73</v>
       </c>
       <c r="E12" s="17" t="n">
-        <v>1.21</v>
+        <v>0.92</v>
       </c>
       <c r="F12" s="17" t="n">
         <v>0.2</v>
       </c>
-      <c r="G12" s="10" t="inlineStr">
-        <is>
-          <t>2026-08-04</t>
-        </is>
+      <c r="G12" s="17" t="n">
+        <v>9</v>
       </c>
       <c r="H12" s="10" t="inlineStr">
         <is>
-          <t>buyback, dividend_return, cost</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="I12" s="10" t="inlineStr">
         <is>
-          <t>[buyback] “Since the beginning of this year, we announced a new $200 million share repurchase program and then repurchased approximately $42 million worth of our stock in both Q1 and Q2.”</t>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="J12" s="10" t="inlineStr">
+        <is>
+          <t>buyback, cost, dividend_return</t>
+        </is>
+      </c>
+      <c r="K12" s="10" t="inlineStr">
+        <is>
+          <t>[buyback] “In the second quarter, we repurchased approximately 8 million shares for $550 million through our previously announced accelerated share repurchases as well as open market repurcha”</t>
         </is>
       </c>
     </row>
     <row r="13" ht="30" customHeight="1">
       <c r="A13" s="6" t="inlineStr">
         <is>
-          <t>HSDT</t>
+          <t>CNMD</t>
         </is>
       </c>
       <c r="B13" s="7" t="inlineStr">
         <is>
-          <t>Solana Company</t>
+          <t>CONMED Corporation</t>
         </is>
       </c>
       <c r="C13" s="7" t="inlineStr">
@@ -9580,39 +9660,47 @@
         </is>
       </c>
       <c r="D13" s="16" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.72</v>
       </c>
       <c r="E13" s="16" t="n">
-        <v>1.06</v>
+        <v>1.31</v>
       </c>
       <c r="F13" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="G13" s="7" t="inlineStr">
-        <is>
-          <t>2026-08-14</t>
-        </is>
+        <v>2.5</v>
+      </c>
+      <c r="G13" s="16" t="n">
+        <v>50</v>
       </c>
       <c r="H13" s="7" t="inlineStr">
         <is>
-          <t>buyback, value_gap, monetize</t>
+          <t>–</t>
         </is>
       </c>
       <c r="I13" s="7" t="inlineStr">
         <is>
-          <t>[buyback] “With our stock trading at a discount to net asset value during the quarter, we executed approximately $2.3 million of share repurchases, retiring 1.3 million shares and year-to-dat”</t>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="J13" s="7" t="inlineStr">
+        <is>
+          <t>NEW delever, buyback, monetize, governan</t>
+        </is>
+      </c>
+      <c r="K13" s="7" t="inlineStr">
+        <is>
+          <t>[delever] “CONMED has made significant progress in terms of deleveraging in recent years.”</t>
         </is>
       </c>
     </row>
     <row r="14" ht="30" customHeight="1">
       <c r="A14" s="9" t="inlineStr">
         <is>
-          <t>GNL</t>
+          <t>DEC</t>
         </is>
       </c>
       <c r="B14" s="10" t="inlineStr">
         <is>
-          <t>Global Net Lease, In</t>
+          <t>Diversified Energy C</t>
         </is>
       </c>
       <c r="C14" s="10" t="inlineStr">
@@ -9621,39 +9709,47 @@
         </is>
       </c>
       <c r="D14" s="17" t="n">
-        <v>0.68</v>
+        <v>0.71</v>
       </c>
       <c r="E14" s="17" t="n">
-        <v>1.22</v>
+        <v>1.07</v>
       </c>
       <c r="F14" s="17" t="n">
         <v>0</v>
       </c>
-      <c r="G14" s="10" t="inlineStr">
-        <is>
-          <t>2026-08-06</t>
-        </is>
+      <c r="G14" s="17" t="n">
+        <v>50</v>
       </c>
       <c r="H14" s="10" t="inlineStr">
         <is>
-          <t>buyback, delever, anticipation</t>
+          <t>–</t>
         </is>
       </c>
       <c r="I14" s="10" t="inlineStr">
         <is>
-          <t>[buyback] “Since launching our share repurchase program in 2025 and through July 31, 2026, we have repurchased 20.9 million shares for a total of $169.7 million.”</t>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="J14" s="10" t="inlineStr">
+        <is>
+          <t>buyback, delever, dividend_return</t>
+        </is>
+      </c>
+      <c r="K14" s="10" t="inlineStr">
+        <is>
+          <t>[buyback] “We returned approximately $94 million to shareholders through dividends and strategic share repurchases.”</t>
         </is>
       </c>
     </row>
     <row r="15" ht="30" customHeight="1">
       <c r="A15" s="6" t="inlineStr">
         <is>
-          <t>ACT</t>
+          <t>BBUC</t>
         </is>
       </c>
       <c r="B15" s="7" t="inlineStr">
         <is>
-          <t>Enact Holdings, Inc.</t>
+          <t>Brookfield Business</t>
         </is>
       </c>
       <c r="C15" s="7" t="inlineStr">
@@ -9662,39 +9758,47 @@
         </is>
       </c>
       <c r="D15" s="16" t="n">
-        <v>0.68</v>
+        <v>0.71</v>
       </c>
       <c r="E15" s="16" t="n">
-        <v>1.23</v>
+        <v>0.96</v>
       </c>
       <c r="F15" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="G15" s="7" t="inlineStr">
-        <is>
-          <t>2026-08-05</t>
-        </is>
+        <v>0.5</v>
+      </c>
+      <c r="G15" s="16" t="n">
+        <v>24</v>
       </c>
       <c r="H15" s="7" t="inlineStr">
         <is>
-          <t>buyback, dividend_return, governance</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="I15" s="7" t="inlineStr">
         <is>
-          <t>[buyback] “Through July 31, we have repurchased an additional 0.7 million shares for $30 million.”</t>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="J15" s="7" t="inlineStr">
+        <is>
+          <t>buyback, value_gap, anticipation</t>
+        </is>
+      </c>
+      <c r="K15" s="7" t="inlineStr">
+        <is>
+          <t>[buyback] “Since we launched our buyback program early last year, on the back of our strong capital recycling activity, we have repurchased more than $300 million of our own shares at a nearl”</t>
         </is>
       </c>
     </row>
     <row r="16" ht="30" customHeight="1">
       <c r="A16" s="9" t="inlineStr">
         <is>
-          <t>BBUC</t>
+          <t>WAL</t>
         </is>
       </c>
       <c r="B16" s="10" t="inlineStr">
         <is>
-          <t>Brookfield Business</t>
+          <t>Western Alliance Ban</t>
         </is>
       </c>
       <c r="C16" s="10" t="inlineStr">
@@ -9703,39 +9807,47 @@
         </is>
       </c>
       <c r="D16" s="17" t="n">
-        <v>0.67</v>
+        <v>0.7</v>
       </c>
       <c r="E16" s="17" t="n">
-        <v>0.96</v>
+        <v>1.08</v>
       </c>
       <c r="F16" s="17" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="G16" s="10" t="inlineStr">
-        <is>
-          <t>2026-07-31</t>
-        </is>
+        <v>3.1</v>
+      </c>
+      <c r="G16" s="17" t="n">
+        <v>50</v>
       </c>
       <c r="H16" s="10" t="inlineStr">
         <is>
-          <t>buyback, value_gap, anticipation</t>
+          <t>–</t>
         </is>
       </c>
       <c r="I16" s="10" t="inlineStr">
         <is>
-          <t>[buyback] “Since we launched our buyback program early last year, on the back of our strong capital recycling activity, we have repurchased more than $300 million of our own shares at a nearl”</t>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="J16" s="10" t="inlineStr">
+        <is>
+          <t>NEW dividend_return, NEW value_gap, buyb</t>
+        </is>
+      </c>
+      <c r="K16" s="10" t="inlineStr">
+        <is>
+          <t>[dividend_return] “As we approach the $100 billion asset milestone later this year, Western Alliance is entering its next phase from a position of strength, combining industry-leading growth, improvi”</t>
         </is>
       </c>
     </row>
     <row r="17" ht="30" customHeight="1">
       <c r="A17" s="6" t="inlineStr">
         <is>
-          <t>DEC</t>
+          <t>ACT</t>
         </is>
       </c>
       <c r="B17" s="7" t="inlineStr">
         <is>
-          <t>Diversified Energy C</t>
+          <t>Enact Holdings, Inc.</t>
         </is>
       </c>
       <c r="C17" s="7" t="inlineStr">
@@ -9744,39 +9856,47 @@
         </is>
       </c>
       <c r="D17" s="16" t="n">
-        <v>0.67</v>
+        <v>0.7</v>
       </c>
       <c r="E17" s="16" t="n">
-        <v>1.07</v>
+        <v>1.23</v>
       </c>
       <c r="F17" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="G17" s="7" t="inlineStr">
-        <is>
-          <t>2026-05-07</t>
-        </is>
+      <c r="G17" s="16" t="n">
+        <v>2</v>
       </c>
       <c r="H17" s="7" t="inlineStr">
         <is>
-          <t>buyback, delever, dividend_return</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="I17" s="7" t="inlineStr">
         <is>
-          <t>[buyback] “We returned approximately $94 million to shareholders through dividends and strategic share repurchases.”</t>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="J17" s="7" t="inlineStr">
+        <is>
+          <t>buyback, dividend_return, governance</t>
+        </is>
+      </c>
+      <c r="K17" s="7" t="inlineStr">
+        <is>
+          <t>[buyback] “Through July 31, we have repurchased an additional 0.7 million shares for $30 million.”</t>
         </is>
       </c>
     </row>
     <row r="18" ht="30" customHeight="1">
       <c r="A18" s="9" t="inlineStr">
         <is>
-          <t>COO</t>
+          <t>TBB</t>
         </is>
       </c>
       <c r="B18" s="10" t="inlineStr">
         <is>
-          <t>The Cooper Companies</t>
+          <t>AT&amp;T Inc. 5.35% GLB</t>
         </is>
       </c>
       <c r="C18" s="10" t="inlineStr">
@@ -9785,39 +9905,47 @@
         </is>
       </c>
       <c r="D18" s="17" t="n">
-        <v>0.67</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="E18" s="17" t="n">
-        <v>1.29</v>
+        <v>1.42</v>
       </c>
       <c r="F18" s="17" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="G18" s="10" t="inlineStr">
-        <is>
-          <t>2026-09-09</t>
-        </is>
+        <v>0.4</v>
+      </c>
+      <c r="G18" s="17" t="n">
+        <v>11</v>
       </c>
       <c r="H18" s="10" t="inlineStr">
         <is>
-          <t>NEW dividend_return, buyback, strategic_</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="I18" s="10" t="inlineStr">
         <is>
-          <t>[dividend_return] “We also achieved a favorable resolution of HMRC's examination of our 2021 U.K. tax planning initiative and returned significant capital to shareholders.”</t>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="J18" s="10" t="inlineStr">
+        <is>
+          <t>buyback, anticipation, dividend_return</t>
+        </is>
+      </c>
+      <c r="K18" s="10" t="inlineStr">
+        <is>
+          <t>[buyback] “We returned $4.1 billion to shareholders during the second quarter, including approximately $2.2 billion of share repurchases.”</t>
         </is>
       </c>
     </row>
     <row r="19" ht="30" customHeight="1">
       <c r="A19" s="6" t="inlineStr">
         <is>
-          <t>ONB</t>
+          <t>COO</t>
         </is>
       </c>
       <c r="B19" s="7" t="inlineStr">
         <is>
-          <t>Old National Bancorp</t>
+          <t>The Cooper Companies</t>
         </is>
       </c>
       <c r="C19" s="7" t="inlineStr">
@@ -9826,39 +9954,47 @@
         </is>
       </c>
       <c r="D19" s="16" t="n">
-        <v>0.66</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="E19" s="16" t="n">
-        <v>1.11</v>
+        <v>1.29</v>
       </c>
       <c r="F19" s="16" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="G19" s="7" t="inlineStr">
-        <is>
-          <t>2026-07-22</t>
-        </is>
+        <v>1.8</v>
+      </c>
+      <c r="G19" s="16" t="n">
+        <v>12</v>
       </c>
       <c r="H19" s="7" t="inlineStr">
         <is>
-          <t>buyback, dividend_return</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="I19" s="7" t="inlineStr">
         <is>
-          <t>[buyback] “Specifically, during the second quarter, we returned a total of $163 million to shareholders in the form of increased cash dividends and share repurchases.”</t>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="J19" s="7" t="inlineStr">
+        <is>
+          <t>NEW dividend_return, buyback, strategic_</t>
+        </is>
+      </c>
+      <c r="K19" s="7" t="inlineStr">
+        <is>
+          <t>[dividend_return] “We also achieved a favorable resolution of HMRC's examination of our 2021 U.K. tax planning initiative and returned significant capital to shareholders.”</t>
         </is>
       </c>
     </row>
     <row r="20" ht="30" customHeight="1">
       <c r="A20" s="9" t="inlineStr">
         <is>
-          <t>ONBPO</t>
+          <t>INMD</t>
         </is>
       </c>
       <c r="B20" s="10" t="inlineStr">
         <is>
-          <t>Old National Bancorp</t>
+          <t>InMode Ltd.</t>
         </is>
       </c>
       <c r="C20" s="10" t="inlineStr">
@@ -9867,39 +10003,47 @@
         </is>
       </c>
       <c r="D20" s="17" t="n">
-        <v>0.66</v>
+        <v>0.68</v>
       </c>
       <c r="E20" s="17" t="n">
-        <v>1.19</v>
+        <v>1.31</v>
       </c>
       <c r="F20" s="17" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="G20" s="10" t="inlineStr">
-        <is>
-          <t>2026-07-22</t>
-        </is>
+        <v>2.3</v>
+      </c>
+      <c r="G20" s="17" t="n">
+        <v>16</v>
       </c>
       <c r="H20" s="10" t="inlineStr">
         <is>
-          <t>buyback, dividend_return</t>
+          <t>–</t>
         </is>
       </c>
       <c r="I20" s="10" t="inlineStr">
         <is>
-          <t>[buyback] “Specifically, during the second quarter, we returned a total of $163 million to shareholders in the form of increased cash dividends and share repurchases.”</t>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="J20" s="10" t="inlineStr">
+        <is>
+          <t>NEW dividend_return, buyback, strategic_</t>
+        </is>
+      </c>
+      <c r="K20" s="10" t="inlineStr">
+        <is>
+          <t>[dividend_return] “We also returned meaningful capital to shareholders, repurchasing shares in the amount of $127.4 million during 2025 and $52.7 million year-to-date under our new 2026 repurchase pr”</t>
         </is>
       </c>
     </row>
     <row r="21" ht="30" customHeight="1">
       <c r="A21" s="6" t="inlineStr">
         <is>
-          <t>ONBPP</t>
+          <t>BXC</t>
         </is>
       </c>
       <c r="B21" s="7" t="inlineStr">
         <is>
-          <t>Old National Bancorp</t>
+          <t>Bluelinx Holdings In</t>
         </is>
       </c>
       <c r="C21" s="7" t="inlineStr">
@@ -9908,39 +10052,47 @@
         </is>
       </c>
       <c r="D21" s="16" t="n">
-        <v>0.66</v>
+        <v>0.68</v>
       </c>
       <c r="E21" s="16" t="n">
-        <v>1.2</v>
+        <v>1.02</v>
       </c>
       <c r="F21" s="16" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="G21" s="7" t="inlineStr">
-        <is>
-          <t>2026-07-22</t>
-        </is>
+        <v>0</v>
+      </c>
+      <c r="G21" s="16" t="n">
+        <v>12</v>
       </c>
       <c r="H21" s="7" t="inlineStr">
         <is>
-          <t>buyback, dividend_return</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="I21" s="7" t="inlineStr">
         <is>
-          <t>[buyback] “Specifically, during the second quarter, we returned a total of $163 million to shareholders in the form of increased cash dividends and share repurchases.”</t>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="J21" s="7" t="inlineStr">
+        <is>
+          <t>buyback, dividend_return, anticipation</t>
+        </is>
+      </c>
+      <c r="K21" s="7" t="inlineStr">
+        <is>
+          <t>[buyback] “From the end of the quarter through April 21, we have repurchased additional shares, bringing the total dollar amount purchased year-to-date to $5 million.”</t>
         </is>
       </c>
     </row>
     <row r="22" ht="30" customHeight="1">
       <c r="A22" s="9" t="inlineStr">
         <is>
-          <t>SBGI</t>
+          <t>MBUU</t>
         </is>
       </c>
       <c r="B22" s="10" t="inlineStr">
         <is>
-          <t>Sinclair, Inc.</t>
+          <t>Malibu Boats, Inc.</t>
         </is>
       </c>
       <c r="C22" s="10" t="inlineStr">
@@ -9949,39 +10101,47 @@
         </is>
       </c>
       <c r="D22" s="17" t="n">
-        <v>0.66</v>
+        <v>0.68</v>
       </c>
       <c r="E22" s="17" t="n">
-        <v>2.36</v>
+        <v>0.89</v>
       </c>
       <c r="F22" s="17" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="G22" s="10" t="inlineStr">
-        <is>
-          <t>2026-08-05</t>
-        </is>
+        <v>2.2</v>
+      </c>
+      <c r="G22" s="17" t="n">
+        <v>12</v>
       </c>
       <c r="H22" s="10" t="inlineStr">
         <is>
-          <t>NEW buyback, NEW value_gap, delever, ten</t>
+          <t>–</t>
         </is>
       </c>
       <c r="I22" s="10" t="inlineStr">
         <is>
-          <t>[buyback] “In July, after quarter end, we repurchased and retired an additional $25 million sales amount of our B7 term loan at a discount and repaid and terminated the remaining B3 term loan”</t>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="J22" s="10" t="inlineStr">
+        <is>
+          <t>buyback, anticipation, dividend_return</t>
+        </is>
+      </c>
+      <c r="K22" s="10" t="inlineStr">
+        <is>
+          <t>[buyback] “While we chose to pause our open market purchases during the lender negotiations, our Board authorized a new $70 million share repurchase program for fiscal 2027 in June, and we cl”</t>
         </is>
       </c>
     </row>
     <row r="23" ht="30" customHeight="1">
       <c r="A23" s="6" t="inlineStr">
         <is>
-          <t>ARI</t>
+          <t>CALY</t>
         </is>
       </c>
       <c r="B23" s="7" t="inlineStr">
         <is>
-          <t>Apollo Commercial Re</t>
+          <t>Callaway Golf Compan</t>
         </is>
       </c>
       <c r="C23" s="7" t="inlineStr">
@@ -9993,36 +10153,44 @@
         <v>0.66</v>
       </c>
       <c r="E23" s="16" t="n">
-        <v>0.66</v>
+        <v>1.21</v>
       </c>
       <c r="F23" s="16" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="G23" s="7" t="inlineStr">
-        <is>
-          <t>2026-04-29</t>
-        </is>
+        <v>0.2</v>
+      </c>
+      <c r="G23" s="16" t="n">
+        <v>6</v>
       </c>
       <c r="H23" s="7" t="inlineStr">
         <is>
-          <t>NEW buyback, NEW strategic_review, antic</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="I23" s="7" t="inlineStr">
         <is>
-          <t>[buyback] “Following the quarter end, we repurchased an additional 3.9 million shares at a weighted average price of $10.72, bringing total repurchases year-to-date to approximately 6.8 milli”</t>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="J23" s="7" t="inlineStr">
+        <is>
+          <t>buyback, dividend_return, cost</t>
+        </is>
+      </c>
+      <c r="K23" s="7" t="inlineStr">
+        <is>
+          <t>[buyback] “Since the beginning of this year, we announced a new $200 million share repurchase program and then repurchased approximately $42 million worth of our stock in both Q1 and Q2.”</t>
         </is>
       </c>
     </row>
     <row r="24" ht="30" customHeight="1">
       <c r="A24" s="9" t="inlineStr">
         <is>
-          <t>GLRE</t>
+          <t>ARI</t>
         </is>
       </c>
       <c r="B24" s="10" t="inlineStr">
         <is>
-          <t>Greenlight Capital R</t>
+          <t>Apollo Commercial Re</t>
         </is>
       </c>
       <c r="C24" s="10" t="inlineStr">
@@ -10034,36 +10202,44 @@
         <v>0.65</v>
       </c>
       <c r="E24" s="17" t="n">
-        <v>0.71</v>
+        <v>0.66</v>
       </c>
       <c r="F24" s="17" t="n">
-        <v>0</v>
-      </c>
-      <c r="G24" s="10" t="inlineStr">
-        <is>
-          <t>2026-08-05</t>
-        </is>
+        <v>5.2</v>
+      </c>
+      <c r="G24" s="17" t="n">
+        <v>16</v>
       </c>
       <c r="H24" s="10" t="inlineStr">
         <is>
-          <t>buyback, value_gap</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="I24" s="10" t="inlineStr">
         <is>
-          <t>[buyback] “Subsequently, we repurchased an additional $3.9 million of shares.”</t>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="J24" s="10" t="inlineStr">
+        <is>
+          <t>NEW buyback, NEW strategic_review, antic</t>
+        </is>
+      </c>
+      <c r="K24" s="10" t="inlineStr">
+        <is>
+          <t>[buyback] “Following the quarter end, we repurchased an additional 3.9 million shares at a weighted average price of $10.72, bringing total repurchases year-to-date to approximately 6.8 milli”</t>
         </is>
       </c>
     </row>
     <row r="25" ht="30" customHeight="1">
       <c r="A25" s="6" t="inlineStr">
         <is>
-          <t>RWAY</t>
+          <t>SKYW</t>
         </is>
       </c>
       <c r="B25" s="7" t="inlineStr">
         <is>
-          <t>Runway Growth Financ</t>
+          <t>SkyWest, Inc.</t>
         </is>
       </c>
       <c r="C25" s="7" t="inlineStr">
@@ -10075,36 +10251,44 @@
         <v>0.65</v>
       </c>
       <c r="E25" s="16" t="n">
-        <v>0.57</v>
+        <v>1.42</v>
       </c>
       <c r="F25" s="16" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="G25" s="7" t="inlineStr">
-        <is>
-          <t>2026-08-07</t>
-        </is>
+        <v>1.5</v>
+      </c>
+      <c r="G25" s="16" t="n">
+        <v>50</v>
       </c>
       <c r="H25" s="7" t="inlineStr">
         <is>
-          <t>NEW tender, NEW strategic_review, NEW co</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="I25" s="7" t="inlineStr">
         <is>
-          <t>[tender] “Once our trading blackout period ends on August 11, we will be able to execute a new Rule 10b5-1 plan and evaluate additional repurchase opportunities through open market purchases”</t>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="J25" s="7" t="inlineStr">
+        <is>
+          <t>buyback, delever, anticipation</t>
+        </is>
+      </c>
+      <c r="K25" s="7" t="inlineStr">
+        <is>
+          <t>[buyback] “And as announced today, the Board has authorized an additional $250 million of share repurchase on top of the $63 million.”</t>
         </is>
       </c>
     </row>
     <row r="26" ht="30" customHeight="1">
       <c r="A26" s="9" t="inlineStr">
         <is>
-          <t>INMD</t>
+          <t>REXR</t>
         </is>
       </c>
       <c r="B26" s="10" t="inlineStr">
         <is>
-          <t>InMode Ltd.</t>
+          <t>Rexford Industrial R</t>
         </is>
       </c>
       <c r="C26" s="10" t="inlineStr">
@@ -10116,36 +10300,44 @@
         <v>0.65</v>
       </c>
       <c r="E26" s="17" t="n">
-        <v>1.31</v>
+        <v>1.16</v>
       </c>
       <c r="F26" s="17" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="G26" s="10" t="inlineStr">
-        <is>
-          <t>2026-05-06</t>
-        </is>
+        <v>1.3</v>
+      </c>
+      <c r="G26" s="17" t="n">
+        <v>11</v>
       </c>
       <c r="H26" s="10" t="inlineStr">
         <is>
-          <t>NEW dividend_return, buyback, strategic_</t>
+          <t>–</t>
         </is>
       </c>
       <c r="I26" s="10" t="inlineStr">
         <is>
-          <t>[dividend_return] “We also returned meaningful capital to shareholders, repurchasing shares in the amount of $127.4 million during 2025 and $52.7 million year-to-date under our new 2026 repurchase pr”</t>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="J26" s="10" t="inlineStr">
+        <is>
+          <t>NEW delever, buyback, anticipation</t>
+        </is>
+      </c>
+      <c r="K26" s="10" t="inlineStr">
+        <is>
+          <t>[delever] “We will use $1 billion of the projected proceeds to repay debt maturing in 2027 rather than refinance into a higher rate environment which will meaningfully strengthen our balance ”</t>
         </is>
       </c>
     </row>
     <row r="27" ht="30" customHeight="1">
       <c r="A27" s="6" t="inlineStr">
         <is>
-          <t>MTH</t>
+          <t>VSNT</t>
         </is>
       </c>
       <c r="B27" s="7" t="inlineStr">
         <is>
-          <t>Meritage Homes Corpo</t>
+          <t>Versant Media Group,</t>
         </is>
       </c>
       <c r="C27" s="7" t="inlineStr">
@@ -10157,36 +10349,44 @@
         <v>0.65</v>
       </c>
       <c r="E27" s="16" t="n">
-        <v>0.86</v>
+        <v>0.58</v>
       </c>
       <c r="F27" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="G27" s="7" t="inlineStr">
-        <is>
-          <t>2026-07-30</t>
-        </is>
+        <v>1.2</v>
+      </c>
+      <c r="G27" s="16" t="n">
+        <v>6</v>
       </c>
       <c r="H27" s="7" t="inlineStr">
         <is>
-          <t>buyback, value_gap, anticipation</t>
+          <t>–</t>
         </is>
       </c>
       <c r="I27" s="7" t="inlineStr">
         <is>
-          <t>[buyback] “We also returned $131 million this quarter to shareholders through dividends and share repurchases.”</t>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="J27" s="7" t="inlineStr">
+        <is>
+          <t>buyback, dividend_return, cost</t>
+        </is>
+      </c>
+      <c r="K27" s="7" t="inlineStr">
+        <is>
+          <t>[buyback] “Demonstrating our commitment to returning capital to shareholders, we repurchased $100 million of stock in the second quarter under the previously announced accelerated share repur”</t>
         </is>
       </c>
     </row>
     <row r="28" ht="30" customHeight="1">
       <c r="A28" s="9" t="inlineStr">
         <is>
-          <t>NMM</t>
+          <t>AZTA</t>
         </is>
       </c>
       <c r="B28" s="10" t="inlineStr">
         <is>
-          <t>Navios Maritime Part</t>
+          <t>Azenta, Inc.</t>
         </is>
       </c>
       <c r="C28" s="10" t="inlineStr">
@@ -10195,39 +10395,47 @@
         </is>
       </c>
       <c r="D28" s="17" t="n">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="E28" s="17" t="n">
-        <v>0.6899999999999999</v>
+        <v>1.06</v>
       </c>
       <c r="F28" s="17" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="G28" s="10" t="inlineStr">
-        <is>
-          <t>2026-08-20</t>
-        </is>
+        <v>2.5</v>
+      </c>
+      <c r="G28" s="17" t="n">
+        <v>50</v>
       </c>
       <c r="H28" s="10" t="inlineStr">
         <is>
-          <t>NEW value_gap, buyback, monetize</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="I28" s="10" t="inlineStr">
         <is>
-          <t>[value_gap] “We view this program as an important tool for creating value for our common unitholders, particularly when our units trade at a meaningful discount to underlying NAV.”</t>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="J28" s="10" t="inlineStr">
+        <is>
+          <t>NEW monetize, buyback, cost</t>
+        </is>
+      </c>
+      <c r="K28" s="10" t="inlineStr">
+        <is>
+          <t>[monetize] “As John mentioned, we completed the divestiture of B Medical Systems on July 1 for approximately $63 million, consisting of $28 million in cash proceeds and a $35 million short-ter”</t>
         </is>
       </c>
     </row>
     <row r="29" ht="30" customHeight="1">
       <c r="A29" s="6" t="inlineStr">
         <is>
-          <t>GNW</t>
+          <t>MPAA</t>
         </is>
       </c>
       <c r="B29" s="7" t="inlineStr">
         <is>
-          <t>Genworth Financial,</t>
+          <t>Motorcar Parts of Am</t>
         </is>
       </c>
       <c r="C29" s="7" t="inlineStr">
@@ -10239,36 +10447,44 @@
         <v>0.64</v>
       </c>
       <c r="E29" s="16" t="n">
-        <v>0.42</v>
+        <v>0.78</v>
       </c>
       <c r="F29" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="G29" s="7" t="inlineStr">
-        <is>
-          <t>2026-08-06</t>
-        </is>
+        <v>0.6</v>
+      </c>
+      <c r="G29" s="16" t="n">
+        <v>42</v>
       </c>
       <c r="H29" s="7" t="inlineStr">
         <is>
-          <t>buyback, delever, dividend_return</t>
+          <t>–</t>
         </is>
       </c>
       <c r="I29" s="7" t="inlineStr">
         <is>
-          <t>[buyback] “During the quarter, we repurchased $62 million of shares at an average price of $8.74 per share and an additional $4 million in July.”</t>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="J29" s="7" t="inlineStr">
+        <is>
+          <t>buyback, cost, strategic_review</t>
+        </is>
+      </c>
+      <c r="K29" s="7" t="inlineStr">
+        <is>
+          <t>[buyback] “For the fiscal first quarter, the company repurchased 130 thousand shares for $1.9 million at an average share price of $14.98.”</t>
         </is>
       </c>
     </row>
     <row r="30" ht="30" customHeight="1">
       <c r="A30" s="9" t="inlineStr">
         <is>
-          <t>REXR</t>
+          <t>MTH</t>
         </is>
       </c>
       <c r="B30" s="10" t="inlineStr">
         <is>
-          <t>Rexford Industrial R</t>
+          <t>Meritage Homes Corpo</t>
         </is>
       </c>
       <c r="C30" s="10" t="inlineStr">
@@ -10280,36 +10496,44 @@
         <v>0.64</v>
       </c>
       <c r="E30" s="17" t="n">
-        <v>1.16</v>
+        <v>0.86</v>
       </c>
       <c r="F30" s="17" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="G30" s="10" t="inlineStr">
-        <is>
-          <t>2026-07-24</t>
-        </is>
+        <v>0</v>
+      </c>
+      <c r="G30" s="17" t="n">
+        <v>3</v>
       </c>
       <c r="H30" s="10" t="inlineStr">
         <is>
-          <t>NEW delever, buyback, anticipation</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="I30" s="10" t="inlineStr">
         <is>
-          <t>[delever] “We will use $1 billion of the projected proceeds to repay debt maturing in 2027 rather than refinance into a higher rate environment which will meaningfully strengthen our balance ”</t>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="J30" s="10" t="inlineStr">
+        <is>
+          <t>buyback, value_gap, anticipation</t>
+        </is>
+      </c>
+      <c r="K30" s="10" t="inlineStr">
+        <is>
+          <t>[buyback] “We also returned $131 million this quarter to shareholders through dividends and share repurchases.”</t>
         </is>
       </c>
     </row>
     <row r="31" ht="30" customHeight="1">
       <c r="A31" s="6" t="inlineStr">
         <is>
-          <t>IVZ</t>
+          <t>GNL</t>
         </is>
       </c>
       <c r="B31" s="7" t="inlineStr">
         <is>
-          <t>Invesco Ltd</t>
+          <t>Global Net Lease, In</t>
         </is>
       </c>
       <c r="C31" s="7" t="inlineStr">
@@ -10321,36 +10545,44 @@
         <v>0.64</v>
       </c>
       <c r="E31" s="16" t="n">
-        <v>1.09</v>
+        <v>1.22</v>
       </c>
       <c r="F31" s="16" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="G31" s="7" t="inlineStr">
-        <is>
-          <t>2026-07-28</t>
-        </is>
+        <v>0</v>
+      </c>
+      <c r="G31" s="16" t="n">
+        <v>10</v>
       </c>
       <c r="H31" s="7" t="inlineStr">
         <is>
-          <t>buyback, dividend_return, monetize</t>
+          <t>–</t>
         </is>
       </c>
       <c r="I31" s="7" t="inlineStr">
         <is>
-          <t>[buyback] “We increased the amount repurchased to $50 million, or 1.9 million shares And in April, we announced an increase in the quarterly common stock dividend to $0.215 per share.”</t>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="J31" s="7" t="inlineStr">
+        <is>
+          <t>buyback, delever, anticipation</t>
+        </is>
+      </c>
+      <c r="K31" s="7" t="inlineStr">
+        <is>
+          <t>[buyback] “Since launching our share repurchase program in 2025 and through July 31, 2026, we have repurchased 20.9 million shares for a total of $169.7 million.”</t>
         </is>
       </c>
     </row>
     <row r="32" ht="30" customHeight="1">
       <c r="A32" s="9" t="inlineStr">
         <is>
-          <t>PHIN</t>
+          <t>CERT</t>
         </is>
       </c>
       <c r="B32" s="10" t="inlineStr">
         <is>
-          <t>PHINIA Inc.</t>
+          <t>Certara, Inc.</t>
         </is>
       </c>
       <c r="C32" s="10" t="inlineStr">
@@ -10362,36 +10594,44 @@
         <v>0.64</v>
       </c>
       <c r="E32" s="17" t="n">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="F32" s="17" t="n">
-        <v>0</v>
-      </c>
-      <c r="G32" s="10" t="inlineStr">
-        <is>
-          <t>2026-07-30</t>
-        </is>
+        <v>0.8</v>
+      </c>
+      <c r="G32" s="17" t="n">
+        <v>8</v>
       </c>
       <c r="H32" s="10" t="inlineStr">
         <is>
-          <t>buyback, monetize, dividend_return</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="I32" s="10" t="inlineStr">
         <is>
-          <t>[buyback] “Since the spinoff in July 2023 through the second quarter of this year, we repurchased $534 million worth of shares, representing approximately 24% of our original share count and ”</t>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="J32" s="10" t="inlineStr">
+        <is>
+          <t>buyback, monetize, anticipation</t>
+        </is>
+      </c>
+      <c r="K32" s="10" t="inlineStr">
+        <is>
+          <t>[buyback] “In the third quarter, our Board approved a new $50 million share repurchase program, reflecting our continued confidence in the business and our disciplined approach to capital all”</t>
         </is>
       </c>
     </row>
     <row r="33" ht="30" customHeight="1">
       <c r="A33" s="6" t="inlineStr">
         <is>
-          <t>VIPS</t>
+          <t>HSDT</t>
         </is>
       </c>
       <c r="B33" s="7" t="inlineStr">
         <is>
-          <t>Vipshop Holdings Lim</t>
+          <t>Solana Company</t>
         </is>
       </c>
       <c r="C33" s="7" t="inlineStr">
@@ -10403,36 +10643,44 @@
         <v>0.64</v>
       </c>
       <c r="E33" s="16" t="n">
-        <v>0.89</v>
+        <v>1.06</v>
       </c>
       <c r="F33" s="16" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="G33" s="7" t="inlineStr">
-        <is>
-          <t>2026-08-25</t>
-        </is>
+        <v>0</v>
+      </c>
+      <c r="G33" s="16" t="n">
+        <v>6</v>
       </c>
       <c r="H33" s="7" t="inlineStr">
         <is>
-          <t>NEW monetize, buyback, delever</t>
+          <t>–</t>
         </is>
       </c>
       <c r="I33" s="7" t="inlineStr">
         <is>
-          <t>[monetize] “In addition, to unlock the value of our high-quality assets and optimize capital efficiency, we successfully launched 2 public REITs backed by 3 mature Shan Shan outlet properties,”</t>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="J33" s="7" t="inlineStr">
+        <is>
+          <t>buyback, value_gap, monetize</t>
+        </is>
+      </c>
+      <c r="K33" s="7" t="inlineStr">
+        <is>
+          <t>[buyback] “With our stock trading at a discount to net asset value during the quarter, we executed approximately $2.3 million of share repurchases, retiring 1.3 million shares and year-to-dat”</t>
         </is>
       </c>
     </row>
     <row r="34" ht="30" customHeight="1">
       <c r="A34" s="9" t="inlineStr">
         <is>
-          <t>AHRT</t>
+          <t>IVZ</t>
         </is>
       </c>
       <c r="B34" s="10" t="inlineStr">
         <is>
-          <t>AH Realty Trust, Inc</t>
+          <t>Invesco Ltd</t>
         </is>
       </c>
       <c r="C34" s="10" t="inlineStr">
@@ -10441,39 +10689,47 @@
         </is>
       </c>
       <c r="D34" s="17" t="n">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="E34" s="17" t="n">
         <v>1.09</v>
       </c>
       <c r="F34" s="17" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="G34" s="10" t="inlineStr">
-        <is>
-          <t>2026-08-03</t>
-        </is>
+        <v>0.1</v>
+      </c>
+      <c r="G34" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="H34" s="10" t="inlineStr">
         <is>
-          <t>buyback, monetize, governance</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="I34" s="10" t="inlineStr">
         <is>
-          <t>[buyback] “In May, our Board of Directors increased the total authorized repurchase capacity to $100 million, doubling the original authorization and reflecting the Board's conviction in the ”</t>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="J34" s="10" t="inlineStr">
+        <is>
+          <t>buyback, dividend_return, monetize</t>
+        </is>
+      </c>
+      <c r="K34" s="10" t="inlineStr">
+        <is>
+          <t>[buyback] “We increased the amount repurchased to $50 million, or 1.9 million shares And in April, we announced an increase in the quarterly common stock dividend to $0.215 per share.”</t>
         </is>
       </c>
     </row>
     <row r="35" ht="30" customHeight="1">
       <c r="A35" s="6" t="inlineStr">
         <is>
-          <t>CERT</t>
+          <t>SHEL</t>
         </is>
       </c>
       <c r="B35" s="7" t="inlineStr">
         <is>
-          <t>Certara, Inc.</t>
+          <t>Shell plc</t>
         </is>
       </c>
       <c r="C35" s="7" t="inlineStr">
@@ -10482,39 +10738,47 @@
         </is>
       </c>
       <c r="D35" s="16" t="n">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="E35" s="16" t="n">
-        <v>1.42</v>
+        <v>1.46</v>
       </c>
       <c r="F35" s="16" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="G35" s="7" t="inlineStr">
-        <is>
-          <t>2026-08-04</t>
-        </is>
+        <v>0.3</v>
+      </c>
+      <c r="G35" s="16" t="n">
+        <v>1</v>
       </c>
       <c r="H35" s="7" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="I35" s="7" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="J35" s="7" t="inlineStr">
+        <is>
           <t>buyback, monetize, anticipation</t>
         </is>
       </c>
-      <c r="I35" s="7" t="inlineStr">
-        <is>
-          <t>[buyback] “In the third quarter, our Board approved a new $50 million share repurchase program, reflecting our continued confidence in the business and our disciplined approach to capital all”</t>
+      <c r="K35" s="7" t="inlineStr">
+        <is>
+          <t>[buyback] “And today, we have announced $3 billion of share buybacks, which we expect to complete by our Q3 results announcement in October.”</t>
         </is>
       </c>
     </row>
     <row r="36" ht="30" customHeight="1">
       <c r="A36" s="9" t="inlineStr">
         <is>
-          <t>NEXN</t>
+          <t>ASO</t>
         </is>
       </c>
       <c r="B36" s="10" t="inlineStr">
         <is>
-          <t>Nexxen International</t>
+          <t>Academy Sports and O</t>
         </is>
       </c>
       <c r="C36" s="10" t="inlineStr">
@@ -10526,36 +10790,44 @@
         <v>0.63</v>
       </c>
       <c r="E36" s="17" t="n">
-        <v>1.02</v>
+        <v>1.38</v>
       </c>
       <c r="F36" s="17" t="n">
         <v>0</v>
       </c>
-      <c r="G36" s="10" t="inlineStr">
-        <is>
-          <t>2026-05-13</t>
-        </is>
+      <c r="G36" s="17" t="n">
+        <v>50</v>
       </c>
       <c r="H36" s="10" t="inlineStr">
         <is>
-          <t>buyback, monetize, anticipation</t>
+          <t>–</t>
         </is>
       </c>
       <c r="I36" s="10" t="inlineStr">
         <is>
-          <t>[buyback] “On capital allocation, we repurchased roughly 1.1 million shares in Q1, investing approximately $7.2 million.”</t>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="J36" s="10" t="inlineStr">
+        <is>
+          <t>buyback, delever, dividend_return</t>
+        </is>
+      </c>
+      <c r="K36" s="10" t="inlineStr">
+        <is>
+          <t>[buyback] “In the first half of the year, we repurchased approximately $181 million of our shares, representing about 5% of our outstanding shares, paid approximately $19 million in dividends”</t>
         </is>
       </c>
     </row>
     <row r="37" ht="30" customHeight="1">
       <c r="A37" s="6" t="inlineStr">
         <is>
-          <t>KSS</t>
+          <t>NTR</t>
         </is>
       </c>
       <c r="B37" s="7" t="inlineStr">
         <is>
-          <t>Kohl's Corporation</t>
+          <t>Nutrien Ltd.</t>
         </is>
       </c>
       <c r="C37" s="7" t="inlineStr">
@@ -10567,36 +10839,46 @@
         <v>0.63</v>
       </c>
       <c r="E37" s="16" t="n">
-        <v>0.49</v>
+        <v>1.4</v>
       </c>
       <c r="F37" s="16" t="n">
         <v>0</v>
       </c>
       <c r="G37" s="7" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>–</t>
         </is>
       </c>
       <c r="H37" s="7" t="inlineStr">
         <is>
-          <t>delever, buyback, anticipation</t>
+          <t>–</t>
         </is>
       </c>
       <c r="I37" s="7" t="inlineStr">
         <is>
-          <t>[delever] “In the second quarter, we retired an additional $63 million of our long-term debt at a discount of $6 million through open-market debt repurchases.”</t>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="J37" s="7" t="inlineStr">
+        <is>
+          <t>monetize, anticipation, buyback</t>
+        </is>
+      </c>
+      <c r="K37" s="7" t="inlineStr">
+        <is>
+          <t>[monetize] “Since June 2026, we completed agreements to sell non-core assets for gross proceeds of approximately $90 million.”</t>
         </is>
       </c>
     </row>
     <row r="38" ht="30" customHeight="1">
       <c r="A38" s="9" t="inlineStr">
         <is>
-          <t>YALA</t>
+          <t>LAD</t>
         </is>
       </c>
       <c r="B38" s="10" t="inlineStr">
         <is>
-          <t>Yalla Group Limited</t>
+          <t>Lithia Motors, Inc.</t>
         </is>
       </c>
       <c r="C38" s="10" t="inlineStr">
@@ -10605,39 +10887,47 @@
         </is>
       </c>
       <c r="D38" s="17" t="n">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="E38" s="17" t="n">
-        <v>0.99</v>
+        <v>1.06</v>
       </c>
       <c r="F38" s="17" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="G38" s="10" t="inlineStr">
-        <is>
-          <t>2026-08-17</t>
-        </is>
+        <v>1.6</v>
+      </c>
+      <c r="G38" s="17" t="n">
+        <v>6</v>
       </c>
       <c r="H38" s="10" t="inlineStr">
         <is>
-          <t>buyback, monetize, strategic_review</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="I38" s="10" t="inlineStr">
         <is>
-          <t>[buyback] “During the quarter, we continued to deliver on our shareholder return commitment under the company's 2 share repurchase programs launched in 2021 and 2026.”</t>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="J38" s="10" t="inlineStr">
+        <is>
+          <t>NEW monetize, buyback, value_gap</t>
+        </is>
+      </c>
+      <c r="K38" s="10" t="inlineStr">
+        <is>
+          <t>[monetize] “In the first half of the year, we made strategic acquisitions of $765 million in revenue and divested $120 million of underperforming revenue that also generated extra capital to p”</t>
         </is>
       </c>
     </row>
     <row r="39" ht="30" customHeight="1">
       <c r="A39" s="6" t="inlineStr">
         <is>
-          <t>SM</t>
+          <t>LNWO</t>
         </is>
       </c>
       <c r="B39" s="7" t="inlineStr">
         <is>
-          <t>SM Energy Company</t>
+          <t>–</t>
         </is>
       </c>
       <c r="C39" s="7" t="inlineStr">
@@ -10646,39 +10936,51 @@
         </is>
       </c>
       <c r="D39" s="16" t="n">
-        <v>0.62</v>
-      </c>
-      <c r="E39" s="16" t="n">
-        <v>1.08</v>
+        <v>0.63</v>
+      </c>
+      <c r="E39" s="7" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
       <c r="F39" s="16" t="n">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="G39" s="7" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>–</t>
         </is>
       </c>
       <c r="H39" s="7" t="inlineStr">
         <is>
-          <t>buyback, dividend_return, monetize</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="I39" s="7" t="inlineStr">
         <is>
-          <t>[buyback] “This will enable us to increase the percentage allocated to buyback sooner than originally anticipated, and we expect to begin repurchasing shares in the second quarter.”</t>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="J39" s="7" t="inlineStr">
+        <is>
+          <t>buyback, delever, monetize</t>
+        </is>
+      </c>
+      <c r="K39" s="7" t="inlineStr">
+        <is>
+          <t>[buyback] “Since the inception of our first ever share repurchase program back in 2022, we have returned $2.1 billion to shareholders.”</t>
         </is>
       </c>
     </row>
     <row r="40" ht="30" customHeight="1">
       <c r="A40" s="9" t="inlineStr">
         <is>
-          <t>OTF</t>
+          <t>NOV</t>
         </is>
       </c>
       <c r="B40" s="10" t="inlineStr">
         <is>
-          <t>Blue Owl Technology</t>
+          <t>NOV Inc.</t>
         </is>
       </c>
       <c r="C40" s="10" t="inlineStr">
@@ -10687,39 +10989,47 @@
         </is>
       </c>
       <c r="D40" s="17" t="n">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="E40" s="17" t="n">
-        <v>0.64</v>
+        <v>1.18</v>
       </c>
       <c r="F40" s="17" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="G40" s="10" t="inlineStr">
-        <is>
-          <t>2026-08-06</t>
-        </is>
+        <v>0.7</v>
+      </c>
+      <c r="G40" s="17" t="n">
+        <v>15</v>
       </c>
       <c r="H40" s="10" t="inlineStr">
         <is>
-          <t>buyback, value_gap, dividend_return</t>
+          <t>–</t>
         </is>
       </c>
       <c r="I40" s="10" t="inlineStr">
         <is>
-          <t>[buyback] “We repurchased over $55 million of stock over the quarter, bringing total repurchases over the past 3 quarters to roughly $170 million.”</t>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="J40" s="10" t="inlineStr">
+        <is>
+          <t>buyback, dividend_return, cost</t>
+        </is>
+      </c>
+      <c r="K40" s="10" t="inlineStr">
+        <is>
+          <t>[buyback] “During the quarter, we repurchased 3.2 million shares for $63 million and paid dividends of $64 million which included a supplemental dividend of $0.09 per share related to the tru”</t>
         </is>
       </c>
     </row>
     <row r="41" ht="30" customHeight="1">
       <c r="A41" s="6" t="inlineStr">
         <is>
-          <t>RNR</t>
+          <t>KBH</t>
         </is>
       </c>
       <c r="B41" s="7" t="inlineStr">
         <is>
-          <t>RenaissanceRe Holdin</t>
+          <t>KB Home</t>
         </is>
       </c>
       <c r="C41" s="7" t="inlineStr">
@@ -10731,36 +11041,44 @@
         <v>0.62</v>
       </c>
       <c r="E41" s="16" t="n">
-        <v>1.16</v>
+        <v>0.78</v>
       </c>
       <c r="F41" s="16" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="G41" s="7" t="inlineStr">
-        <is>
-          <t>2026-07-23</t>
-        </is>
+        <v>0</v>
+      </c>
+      <c r="G41" s="16" t="n">
+        <v>50</v>
       </c>
       <c r="H41" s="7" t="inlineStr">
         <is>
-          <t>buyback, anticipation, dividend_return</t>
+          <t>–</t>
         </is>
       </c>
       <c r="I41" s="7" t="inlineStr">
         <is>
-          <t>[buyback] “So far in the third quarter through July 20, we repurchased an additional $83 million of our shares.”</t>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="J41" s="7" t="inlineStr">
+        <is>
+          <t>buyback, dividend_return</t>
+        </is>
+      </c>
+      <c r="K41" s="7" t="inlineStr">
+        <is>
+          <t>[buyback] “We repurchased about 890,000 shares of our common stock, or roughly 1.5% of our shares outstanding, at an average price below our current book value per share.”</t>
         </is>
       </c>
     </row>
     <row r="42" ht="30" customHeight="1">
       <c r="A42" s="9" t="inlineStr">
         <is>
-          <t>SNDL</t>
+          <t>PLGO</t>
         </is>
       </c>
       <c r="B42" s="10" t="inlineStr">
         <is>
-          <t>SNDL Inc.</t>
+          <t>Pelagos Insurance Ca</t>
         </is>
       </c>
       <c r="C42" s="10" t="inlineStr">
@@ -10772,36 +11090,44 @@
         <v>0.62</v>
       </c>
       <c r="E42" s="17" t="n">
-        <v>0.47</v>
+        <v>0.92</v>
       </c>
       <c r="F42" s="17" t="n">
-        <v>2</v>
-      </c>
-      <c r="G42" s="10" t="inlineStr">
-        <is>
-          <t>2026-07-28</t>
-        </is>
+        <v>0.7</v>
+      </c>
+      <c r="G42" s="17" t="n">
+        <v>14</v>
       </c>
       <c r="H42" s="10" t="inlineStr">
         <is>
-          <t>NEW value_gap, buyback, cost, anticipati</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="I42" s="10" t="inlineStr">
         <is>
-          <t>[value_gap] “Okay, so we still have the view that our equity is trading well below its intrinsic value.”</t>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="J42" s="10" t="inlineStr">
+        <is>
+          <t>buyback, dividend_return, cost</t>
+        </is>
+      </c>
+      <c r="K42" s="10" t="inlineStr">
+        <is>
+          <t>[buyback] “In the second quarter, we repurchased 2.8 million common shares for $60 million at an average price of $21.60 per share.”</t>
         </is>
       </c>
     </row>
     <row r="43" ht="30" customHeight="1">
       <c r="A43" s="6" t="inlineStr">
         <is>
-          <t>CNNE</t>
+          <t>VIPS</t>
         </is>
       </c>
       <c r="B43" s="7" t="inlineStr">
         <is>
-          <t>Cannae Holdings, Inc</t>
+          <t>Vipshop Holdings Lim</t>
         </is>
       </c>
       <c r="C43" s="7" t="inlineStr">
@@ -10813,36 +11139,46 @@
         <v>0.62</v>
       </c>
       <c r="E43" s="16" t="n">
-        <v>0.72</v>
+        <v>0.89</v>
       </c>
       <c r="F43" s="16" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="G43" s="7" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>–</t>
         </is>
       </c>
       <c r="H43" s="7" t="inlineStr">
         <is>
-          <t>monetize, buyback, anticipation</t>
+          <t>–</t>
         </is>
       </c>
       <c r="I43" s="7" t="inlineStr">
         <is>
-          <t>[monetize] “On the call today, I plan to cover four topics: how we allocated capital during the quarter and our expectations going forward, the sale of non-core assets, the execution of our mu”</t>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="J43" s="7" t="inlineStr">
+        <is>
+          <t>NEW monetize, buyback, delever</t>
+        </is>
+      </c>
+      <c r="K43" s="7" t="inlineStr">
+        <is>
+          <t>[monetize] “In addition, to unlock the value of our high-quality assets and optimize capital efficiency, we successfully launched 2 public REITs backed by 3 mature Shan Shan outlet properties,”</t>
         </is>
       </c>
     </row>
     <row r="44" ht="30" customHeight="1">
       <c r="A44" s="9" t="inlineStr">
         <is>
-          <t>FG</t>
+          <t>AER</t>
         </is>
       </c>
       <c r="B44" s="10" t="inlineStr">
         <is>
-          <t>F&amp;G Annuities &amp; Life</t>
+          <t>AerCap Holdings N.V.</t>
         </is>
       </c>
       <c r="C44" s="10" t="inlineStr">
@@ -10854,24 +11190,32 @@
         <v>0.62</v>
       </c>
       <c r="E44" s="17" t="n">
-        <v>0.63</v>
+        <v>1.24</v>
       </c>
       <c r="F44" s="17" t="n">
-        <v>0</v>
-      </c>
-      <c r="G44" s="10" t="inlineStr">
-        <is>
-          <t>2026-08-06</t>
-        </is>
+        <v>0.3</v>
+      </c>
+      <c r="G44" s="17" t="n">
+        <v>50</v>
       </c>
       <c r="H44" s="10" t="inlineStr">
         <is>
-          <t>buyback, strategic_review, dividend_retu</t>
+          <t>–</t>
         </is>
       </c>
       <c r="I44" s="10" t="inlineStr">
         <is>
-          <t>[buyback] “For the first 6 months, our capital self-funded the following: $75 million of common and preferred dividends paid, $80 million of holding company interest expense and $120 million ”</t>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="J44" s="10" t="inlineStr">
+        <is>
+          <t>buyback, monetize, governance</t>
+        </is>
+      </c>
+      <c r="K44" s="10" t="inlineStr">
+        <is>
+          <t>[buyback] “And so know, despite the fact that we bought back 6% of the shares in the first half of this year and all of the, all of the commitments we have made in terms of new orders and tha”</t>
         </is>
       </c>
     </row>
@@ -10892,7 +11236,7 @@
         </is>
       </c>
       <c r="D45" s="16" t="n">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="E45" s="16" t="n">
         <v>1.1</v>
@@ -10900,17 +11244,25 @@
       <c r="F45" s="16" t="n">
         <v>1.2</v>
       </c>
-      <c r="G45" s="7" t="inlineStr">
+      <c r="G45" s="16" t="n">
+        <v>12</v>
+      </c>
+      <c r="H45" s="7" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="I45" s="7" t="inlineStr">
         <is>
           <t>2026-07-23</t>
         </is>
       </c>
-      <c r="H45" s="7" t="inlineStr">
+      <c r="J45" s="7" t="inlineStr">
         <is>
           <t>buyback, anticipation, dividend_return</t>
         </is>
       </c>
-      <c r="I45" s="7" t="inlineStr">
+      <c r="K45" s="7" t="inlineStr">
         <is>
           <t>[buyback] “During the second quarter, as Clint indicated, we repurchased 6.6 million common shares, returning approximately $200 million to our shareholders through our share repurchase progr”</t>
         </is>
@@ -10919,12 +11271,12 @@
     <row r="46" ht="30" customHeight="1">
       <c r="A46" s="9" t="inlineStr">
         <is>
-          <t>DVN</t>
+          <t>NTGR</t>
         </is>
       </c>
       <c r="B46" s="10" t="inlineStr">
         <is>
-          <t>Devon Energy Corpora</t>
+          <t>NETGEAR, Inc.</t>
         </is>
       </c>
       <c r="C46" s="10" t="inlineStr">
@@ -10933,39 +11285,47 @@
         </is>
       </c>
       <c r="D46" s="17" t="n">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="E46" s="17" t="n">
-        <v>1.28</v>
+        <v>1.32</v>
       </c>
       <c r="F46" s="17" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="G46" s="10" t="inlineStr">
-        <is>
-          <t>2026-08-05</t>
-        </is>
+        <v>0.9</v>
+      </c>
+      <c r="G46" s="17" t="n">
+        <v>24</v>
       </c>
       <c r="H46" s="10" t="inlineStr">
         <is>
-          <t>delever, buyback, dividend_return</t>
+          <t>–</t>
         </is>
       </c>
       <c r="I46" s="10" t="inlineStr">
         <is>
-          <t>[delever] “In the second quarter, really the last 7 weeks of the second quarter, we returned over $1 billion through a combination of dividends, buybacks and debt reduction.”</t>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="J46" s="10" t="inlineStr">
+        <is>
+          <t>buyback, dividend_return, cost</t>
+        </is>
+      </c>
+      <c r="K46" s="10" t="inlineStr">
+        <is>
+          <t>[buyback] “In Q2, we repurchased approximately 560 thousand shares of NETGEAR common stock at an average price of $23.04.”</t>
         </is>
       </c>
     </row>
     <row r="47" ht="30" customHeight="1">
       <c r="A47" s="6" t="inlineStr">
         <is>
-          <t>SHEL</t>
+          <t>GNW</t>
         </is>
       </c>
       <c r="B47" s="7" t="inlineStr">
         <is>
-          <t>Shell plc</t>
+          <t>Genworth Financial,</t>
         </is>
       </c>
       <c r="C47" s="7" t="inlineStr">
@@ -10974,39 +11334,47 @@
         </is>
       </c>
       <c r="D47" s="16" t="n">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="E47" s="16" t="n">
-        <v>1.46</v>
+        <v>0.42</v>
       </c>
       <c r="F47" s="16" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="G47" s="7" t="inlineStr">
-        <is>
-          <t>2026-07-30</t>
-        </is>
+        <v>0</v>
+      </c>
+      <c r="G47" s="16" t="n">
+        <v>25</v>
       </c>
       <c r="H47" s="7" t="inlineStr">
         <is>
-          <t>buyback, monetize, anticipation</t>
+          <t>–</t>
         </is>
       </c>
       <c r="I47" s="7" t="inlineStr">
         <is>
-          <t>[buyback] “And today, we have announced $3 billion of share buybacks, which we expect to complete by our Q3 results announcement in October.”</t>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="J47" s="7" t="inlineStr">
+        <is>
+          <t>buyback, delever, dividend_return</t>
+        </is>
+      </c>
+      <c r="K47" s="7" t="inlineStr">
+        <is>
+          <t>[buyback] “During the quarter, we repurchased $62 million of shares at an average price of $8.74 per share and an additional $4 million in July.”</t>
         </is>
       </c>
     </row>
     <row r="48" ht="30" customHeight="1">
       <c r="A48" s="9" t="inlineStr">
         <is>
-          <t>WHF</t>
+          <t>GRWG</t>
         </is>
       </c>
       <c r="B48" s="10" t="inlineStr">
         <is>
-          <t>WhiteHorse Finance,</t>
+          <t>GrowGeneration Corp.</t>
         </is>
       </c>
       <c r="C48" s="10" t="inlineStr">
@@ -11015,39 +11383,47 @@
         </is>
       </c>
       <c r="D48" s="17" t="n">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="E48" s="17" t="n">
-        <v>0.61</v>
+        <v>1.07</v>
       </c>
       <c r="F48" s="17" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="G48" s="10" t="inlineStr">
+        <v>1.4</v>
+      </c>
+      <c r="G48" s="17" t="n">
+        <v>11</v>
+      </c>
+      <c r="H48" s="10" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="I48" s="10" t="inlineStr">
         <is>
           <t>2026-08-11</t>
         </is>
       </c>
-      <c r="H48" s="10" t="inlineStr">
-        <is>
-          <t>buyback, cost, value_gap</t>
-        </is>
-      </c>
-      <c r="I48" s="10" t="inlineStr">
-        <is>
-          <t>[buyback] “In regards to our share repurchase program, the company repurchased approximately 345,000 shares during the second quarter at a weighted average price of approximately $7.42 per sh”</t>
+      <c r="J48" s="10" t="inlineStr">
+        <is>
+          <t>buyback, cost, governance</t>
+        </is>
+      </c>
+      <c r="K48" s="10" t="inlineStr">
+        <is>
+          <t>[buyback] “During the second quarter, the company repurchased 700 thousand shares of common stock at an average price of $1.38 per share exclusive of incremental direct costs, As of 6/30/2026”</t>
         </is>
       </c>
     </row>
     <row r="49" ht="30" customHeight="1">
       <c r="A49" s="6" t="inlineStr">
         <is>
-          <t>DNOW</t>
+          <t>ONB</t>
         </is>
       </c>
       <c r="B49" s="7" t="inlineStr">
         <is>
-          <t>DNOW Inc.</t>
+          <t>Old National Bancorp</t>
         </is>
       </c>
       <c r="C49" s="7" t="inlineStr">
@@ -11059,36 +11435,44 @@
         <v>0.61</v>
       </c>
       <c r="E49" s="16" t="n">
-        <v>1.37</v>
+        <v>1.11</v>
       </c>
       <c r="F49" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="G49" s="7" t="inlineStr">
-        <is>
-          <t>2026-08-06</t>
-        </is>
+        <v>1.9</v>
+      </c>
+      <c r="G49" s="16" t="n">
+        <v>3</v>
       </c>
       <c r="H49" s="7" t="inlineStr">
         <is>
-          <t>buyback, dividend_return, cost</t>
+          <t>–</t>
         </is>
       </c>
       <c r="I49" s="7" t="inlineStr">
         <is>
-          <t>[buyback] “And additionally, we repurchased $25 million in shares in the second quarter.”</t>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="J49" s="7" t="inlineStr">
+        <is>
+          <t>buyback, dividend_return</t>
+        </is>
+      </c>
+      <c r="K49" s="7" t="inlineStr">
+        <is>
+          <t>[buyback] “Specifically, during the second quarter, we returned a total of $163 million to shareholders in the form of increased cash dividends and share repurchases.”</t>
         </is>
       </c>
     </row>
     <row r="50" ht="30" customHeight="1">
       <c r="A50" s="9" t="inlineStr">
         <is>
-          <t>LAD</t>
+          <t>ONBPO</t>
         </is>
       </c>
       <c r="B50" s="10" t="inlineStr">
         <is>
-          <t>Lithia Motors, Inc.</t>
+          <t>Old National Bancorp</t>
         </is>
       </c>
       <c r="C50" s="10" t="inlineStr">
@@ -11100,36 +11484,44 @@
         <v>0.61</v>
       </c>
       <c r="E50" s="17" t="n">
-        <v>1.06</v>
+        <v>1.19</v>
       </c>
       <c r="F50" s="17" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="G50" s="10" t="inlineStr">
-        <is>
-          <t>2026-07-29</t>
-        </is>
+        <v>1.9</v>
+      </c>
+      <c r="G50" s="17" t="n">
+        <v>3</v>
       </c>
       <c r="H50" s="10" t="inlineStr">
         <is>
-          <t>NEW monetize, buyback, value_gap</t>
+          <t>–</t>
         </is>
       </c>
       <c r="I50" s="10" t="inlineStr">
         <is>
-          <t>[monetize] “In the first half of the year, we made strategic acquisitions of $765 million in revenue and divested $120 million of underperforming revenue that also generated extra capital to p”</t>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="J50" s="10" t="inlineStr">
+        <is>
+          <t>buyback, dividend_return</t>
+        </is>
+      </c>
+      <c r="K50" s="10" t="inlineStr">
+        <is>
+          <t>[buyback] “Specifically, during the second quarter, we returned a total of $163 million to shareholders in the form of increased cash dividends and share repurchases.”</t>
         </is>
       </c>
     </row>
     <row r="51" ht="30" customHeight="1">
       <c r="A51" s="6" t="inlineStr">
         <is>
-          <t>FISV</t>
+          <t>ONBPP</t>
         </is>
       </c>
       <c r="B51" s="7" t="inlineStr">
         <is>
-          <t>Fiserv, Inc.</t>
+          <t>Old National Bancorp</t>
         </is>
       </c>
       <c r="C51" s="7" t="inlineStr">
@@ -11141,36 +11533,44 @@
         <v>0.61</v>
       </c>
       <c r="E51" s="16" t="n">
-        <v>0.91</v>
+        <v>1.2</v>
       </c>
       <c r="F51" s="16" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="G51" s="7" t="inlineStr">
-        <is>
-          <t>2026-08-06</t>
-        </is>
+        <v>1.9</v>
+      </c>
+      <c r="G51" s="16" t="n">
+        <v>3</v>
       </c>
       <c r="H51" s="7" t="inlineStr">
         <is>
-          <t>NEW tender, NEW delever, buyback, moneti</t>
+          <t>–</t>
         </is>
       </c>
       <c r="I51" s="7" t="inlineStr">
         <is>
-          <t>[tender] “We completed a $1.4 billion tender offer and open market repurchase for $1.2 billion total consideration and issued $1 billion in eurobonds to take advantage of an opportunity to l”</t>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="J51" s="7" t="inlineStr">
+        <is>
+          <t>buyback, dividend_return</t>
+        </is>
+      </c>
+      <c r="K51" s="7" t="inlineStr">
+        <is>
+          <t>[buyback] “Specifically, during the second quarter, we returned a total of $163 million to shareholders in the form of increased cash dividends and share repurchases.”</t>
         </is>
       </c>
     </row>
     <row r="52" ht="30" customHeight="1">
       <c r="A52" s="9" t="inlineStr">
         <is>
-          <t>SHO</t>
+          <t>AHRT</t>
         </is>
       </c>
       <c r="B52" s="10" t="inlineStr">
         <is>
-          <t>Sunstone Hotel Inves</t>
+          <t>AH Realty Trust, Inc</t>
         </is>
       </c>
       <c r="C52" s="10" t="inlineStr">
@@ -11179,39 +11579,47 @@
         </is>
       </c>
       <c r="D52" s="17" t="n">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="E52" s="17" t="n">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="F52" s="17" t="n">
-        <v>0</v>
-      </c>
-      <c r="G52" s="10" t="inlineStr">
-        <is>
-          <t>2026-05-05</t>
-        </is>
+        <v>0.8</v>
+      </c>
+      <c r="G52" s="17" t="n">
+        <v>50</v>
       </c>
       <c r="H52" s="10" t="inlineStr">
         <is>
-          <t>buyback, dividend_return, anticipation</t>
+          <t>–</t>
         </is>
       </c>
       <c r="I52" s="10" t="inlineStr">
         <is>
-          <t>[buyback] “Since December, we have repurchased over $19 million in liquidation value of our traded preferred stock at a 21% discount, a positive impact on both FFO and NAV.”</t>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="J52" s="10" t="inlineStr">
+        <is>
+          <t>buyback, monetize, governance</t>
+        </is>
+      </c>
+      <c r="K52" s="10" t="inlineStr">
+        <is>
+          <t>[buyback] “In May, our Board of Directors increased the total authorized repurchase capacity to $100 million, doubling the original authorization and reflecting the Board's conviction in the ”</t>
         </is>
       </c>
     </row>
     <row r="53" ht="30" customHeight="1">
       <c r="A53" s="6" t="inlineStr">
         <is>
-          <t>KREF</t>
+          <t>API</t>
         </is>
       </c>
       <c r="B53" s="7" t="inlineStr">
         <is>
-          <t>KKR Real Estate Fina</t>
+          <t>Agora, Inc.</t>
         </is>
       </c>
       <c r="C53" s="7" t="inlineStr">
@@ -11220,39 +11628,47 @@
         </is>
       </c>
       <c r="D53" s="16" t="n">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="E53" s="16" t="n">
-        <v>0.44</v>
+        <v>0.71</v>
       </c>
       <c r="F53" s="16" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="G53" s="7" t="inlineStr">
-        <is>
-          <t>2026-07-22</t>
-        </is>
+        <v>0</v>
+      </c>
+      <c r="G53" s="16" t="n">
+        <v>37</v>
       </c>
       <c r="H53" s="7" t="inlineStr">
         <is>
-          <t>NEW strategic_review, buyback, monetize</t>
+          <t>–</t>
         </is>
       </c>
       <c r="I53" s="7" t="inlineStr">
         <is>
-          <t>[strategic_review] “This process will be led by a strategic review committee composed solely of the Board's independent directors.”</t>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="J53" s="7" t="inlineStr">
+        <is>
+          <t>buyback, cost</t>
+        </is>
+      </c>
+      <c r="K53" s="7" t="inlineStr">
+        <is>
+          <t>[buyback] “During Q2, we repurchased approximately 1 million ADS for approximately $3.7 million.”</t>
         </is>
       </c>
     </row>
     <row r="54" ht="30" customHeight="1">
       <c r="A54" s="9" t="inlineStr">
         <is>
-          <t>NTR</t>
+          <t>GLRE</t>
         </is>
       </c>
       <c r="B54" s="10" t="inlineStr">
         <is>
-          <t>Nutrien Ltd.</t>
+          <t>Greenlight Capital R</t>
         </is>
       </c>
       <c r="C54" s="10" t="inlineStr">
@@ -11264,36 +11680,44 @@
         <v>0.6</v>
       </c>
       <c r="E54" s="17" t="n">
-        <v>1.4</v>
+        <v>0.71</v>
       </c>
       <c r="F54" s="17" t="n">
         <v>0</v>
       </c>
-      <c r="G54" s="10" t="inlineStr">
-        <is>
-          <t>2026-08-06</t>
-        </is>
+      <c r="G54" s="17" t="n">
+        <v>7</v>
       </c>
       <c r="H54" s="10" t="inlineStr">
         <is>
-          <t>monetize, anticipation, buyback</t>
+          <t>–</t>
         </is>
       </c>
       <c r="I54" s="10" t="inlineStr">
         <is>
-          <t>[monetize] “Since June 2026, we completed agreements to sell non-core assets for gross proceeds of approximately $90 million.”</t>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="J54" s="10" t="inlineStr">
+        <is>
+          <t>buyback, value_gap</t>
+        </is>
+      </c>
+      <c r="K54" s="10" t="inlineStr">
+        <is>
+          <t>[buyback] “Subsequently, we repurchased an additional $3.9 million of shares.”</t>
         </is>
       </c>
     </row>
     <row r="55" ht="30" customHeight="1">
       <c r="A55" s="6" t="inlineStr">
         <is>
-          <t>TBB</t>
+          <t>TSN</t>
         </is>
       </c>
       <c r="B55" s="7" t="inlineStr">
         <is>
-          <t>AT&amp;T Inc. 5.35% GLB</t>
+          <t>Tyson Foods, Inc.</t>
         </is>
       </c>
       <c r="C55" s="7" t="inlineStr">
@@ -11305,36 +11729,44 @@
         <v>0.6</v>
       </c>
       <c r="E55" s="16" t="n">
-        <v>1.42</v>
+        <v>1</v>
       </c>
       <c r="F55" s="16" t="n">
         <v>0.4</v>
       </c>
-      <c r="G55" s="7" t="inlineStr">
-        <is>
-          <t>2026-07-22</t>
-        </is>
+      <c r="G55" s="16" t="n">
+        <v>14</v>
       </c>
       <c r="H55" s="7" t="inlineStr">
         <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="I55" s="7" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="J55" s="7" t="inlineStr">
+        <is>
           <t>buyback, anticipation, dividend_return</t>
         </is>
       </c>
-      <c r="I55" s="7" t="inlineStr">
-        <is>
-          <t>[buyback] “We returned $4.1 billion to shareholders during the second quarter, including approximately $2.2 billion of share repurchases.”</t>
+      <c r="K55" s="7" t="inlineStr">
+        <is>
+          <t>[buyback] “Since quarter end, we have repurchased an additional $49 million of our shares.”</t>
         </is>
       </c>
     </row>
     <row r="56" ht="30" customHeight="1">
       <c r="A56" s="9" t="inlineStr">
         <is>
-          <t>WD</t>
+          <t>PHIN</t>
         </is>
       </c>
       <c r="B56" s="10" t="inlineStr">
         <is>
-          <t>Walker &amp; Dunlop, Inc</t>
+          <t>PHINIA Inc.</t>
         </is>
       </c>
       <c r="C56" s="10" t="inlineStr">
@@ -11346,36 +11778,44 @@
         <v>0.6</v>
       </c>
       <c r="E56" s="17" t="n">
-        <v>0.74</v>
+        <v>1.44</v>
       </c>
       <c r="F56" s="17" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="G56" s="10" t="inlineStr">
-        <is>
-          <t>2026-05-07</t>
-        </is>
+        <v>0</v>
+      </c>
+      <c r="G56" s="17" t="n">
+        <v>25</v>
       </c>
       <c r="H56" s="10" t="inlineStr">
         <is>
-          <t>buyback, delever, anticipation</t>
+          <t>–</t>
         </is>
       </c>
       <c r="I56" s="10" t="inlineStr">
         <is>
-          <t>[buyback] “We have begun executing on our disposition plan and expect to have 2 assets under contract in the second quarter with a goal of reducing our repurchase exposure to between $100 mil”</t>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="J56" s="10" t="inlineStr">
+        <is>
+          <t>buyback, monetize, dividend_return</t>
+        </is>
+      </c>
+      <c r="K56" s="10" t="inlineStr">
+        <is>
+          <t>[buyback] “Since the spinoff in July 2023 through the second quarter of this year, we repurchased $534 million worth of shares, representing approximately 24% of our original share count and ”</t>
         </is>
       </c>
     </row>
     <row r="57" ht="30" customHeight="1">
       <c r="A57" s="6" t="inlineStr">
         <is>
-          <t>HBAN</t>
+          <t>YALA</t>
         </is>
       </c>
       <c r="B57" s="7" t="inlineStr">
         <is>
-          <t>Huntington Bancshare</t>
+          <t>Yalla Group Limited</t>
         </is>
       </c>
       <c r="C57" s="7" t="inlineStr">
@@ -11387,36 +11827,44 @@
         <v>0.6</v>
       </c>
       <c r="E57" s="16" t="n">
-        <v>0.97</v>
+        <v>0.99</v>
       </c>
       <c r="F57" s="16" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="G57" s="7" t="inlineStr">
-        <is>
-          <t>2026-07-23</t>
-        </is>
+        <v>0.8</v>
+      </c>
+      <c r="G57" s="16" t="n">
+        <v>3</v>
       </c>
       <c r="H57" s="7" t="inlineStr">
         <is>
-          <t>buyback, value_gap, dividend_return</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="I57" s="7" t="inlineStr">
         <is>
-          <t>[buyback] “Year-to-date, we have completed $310 million of our $550 million planned share repurchase program for 2026.”</t>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="J57" s="7" t="inlineStr">
+        <is>
+          <t>buyback, monetize, strategic_review</t>
+        </is>
+      </c>
+      <c r="K57" s="7" t="inlineStr">
+        <is>
+          <t>[buyback] “During the quarter, we continued to deliver on our shareholder return commitment under the company's 2 share repurchase programs launched in 2021 and 2026.”</t>
         </is>
       </c>
     </row>
     <row r="58" ht="30" customHeight="1">
       <c r="A58" s="9" t="inlineStr">
         <is>
-          <t>HBANL</t>
+          <t>METC</t>
         </is>
       </c>
       <c r="B58" s="10" t="inlineStr">
         <is>
-          <t>Huntington Bancshare</t>
+          <t>Ramaco Resources, In</t>
         </is>
       </c>
       <c r="C58" s="10" t="inlineStr">
@@ -11428,36 +11876,44 @@
         <v>0.6</v>
       </c>
       <c r="E58" s="17" t="n">
-        <v>1.06</v>
+        <v>1.34</v>
       </c>
       <c r="F58" s="17" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="G58" s="10" t="inlineStr">
-        <is>
-          <t>2026-07-23</t>
-        </is>
+        <v>1.4</v>
+      </c>
+      <c r="G58" s="17" t="n">
+        <v>20</v>
       </c>
       <c r="H58" s="10" t="inlineStr">
         <is>
-          <t>buyback, value_gap, dividend_return</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="I58" s="10" t="inlineStr">
         <is>
-          <t>[buyback] “Year-to-date, we have completed $310 million of our $550 million planned share repurchase program for 2026.”</t>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="J58" s="10" t="inlineStr">
+        <is>
+          <t>NEW monetize, buyback, anticipation</t>
+        </is>
+      </c>
+      <c r="K58" s="10" t="inlineStr">
+        <is>
+          <t>[monetize] “We announced an MOU with RE Alloys for offtake and separation of MREC and are in discussion with a number of other firms to secure similar separation and offtake agreements.”</t>
         </is>
       </c>
     </row>
     <row r="59" ht="30" customHeight="1">
       <c r="A59" s="6" t="inlineStr">
         <is>
-          <t>HBANM</t>
+          <t>WD</t>
         </is>
       </c>
       <c r="B59" s="7" t="inlineStr">
         <is>
-          <t>Huntington Bancshare</t>
+          <t>Walker &amp; Dunlop, Inc</t>
         </is>
       </c>
       <c r="C59" s="7" t="inlineStr">
@@ -11469,36 +11925,44 @@
         <v>0.6</v>
       </c>
       <c r="E59" s="16" t="n">
-        <v>1.02</v>
+        <v>0.74</v>
       </c>
       <c r="F59" s="16" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="G59" s="7" t="inlineStr">
-        <is>
-          <t>2026-07-23</t>
-        </is>
+        <v>0.4</v>
+      </c>
+      <c r="G59" s="16" t="n">
+        <v>7</v>
       </c>
       <c r="H59" s="7" t="inlineStr">
         <is>
-          <t>buyback, value_gap, dividend_return</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="I59" s="7" t="inlineStr">
         <is>
-          <t>[buyback] “Year-to-date, we have completed $310 million of our $550 million planned share repurchase program for 2026.”</t>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="J59" s="7" t="inlineStr">
+        <is>
+          <t>buyback, delever, anticipation</t>
+        </is>
+      </c>
+      <c r="K59" s="7" t="inlineStr">
+        <is>
+          <t>[buyback] “We have begun executing on our disposition plan and expect to have 2 assets under contract in the second quarter with a goal of reducing our repurchase exposure to between $100 mil”</t>
         </is>
       </c>
     </row>
     <row r="60" ht="30" customHeight="1">
       <c r="A60" s="9" t="inlineStr">
         <is>
-          <t>HBANP</t>
+          <t>FG</t>
         </is>
       </c>
       <c r="B60" s="10" t="inlineStr">
         <is>
-          <t>Huntington Bancshare</t>
+          <t>F&amp;G Annuities &amp; Life</t>
         </is>
       </c>
       <c r="C60" s="10" t="inlineStr">
@@ -11510,36 +11974,44 @@
         <v>0.6</v>
       </c>
       <c r="E60" s="17" t="n">
-        <v>1.08</v>
+        <v>0.63</v>
       </c>
       <c r="F60" s="17" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="G60" s="10" t="inlineStr">
-        <is>
-          <t>2026-07-23</t>
-        </is>
+        <v>0</v>
+      </c>
+      <c r="G60" s="17" t="n">
+        <v>3</v>
       </c>
       <c r="H60" s="10" t="inlineStr">
         <is>
-          <t>buyback, value_gap, dividend_return</t>
+          <t>–</t>
         </is>
       </c>
       <c r="I60" s="10" t="inlineStr">
         <is>
-          <t>[buyback] “Year-to-date, we have completed $310 million of our $550 million planned share repurchase program for 2026.”</t>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="J60" s="10" t="inlineStr">
+        <is>
+          <t>buyback, strategic_review, dividend_retu</t>
+        </is>
+      </c>
+      <c r="K60" s="10" t="inlineStr">
+        <is>
+          <t>[buyback] “For the first 6 months, our capital self-funded the following: $75 million of common and preferred dividends paid, $80 million of holding company interest expense and $120 million ”</t>
         </is>
       </c>
     </row>
     <row r="61" ht="30" customHeight="1">
       <c r="A61" s="6" t="inlineStr">
         <is>
-          <t>RGA</t>
+          <t>SNDL</t>
         </is>
       </c>
       <c r="B61" s="7" t="inlineStr">
         <is>
-          <t>Reinsurance Group of</t>
+          <t>SNDL Inc.</t>
         </is>
       </c>
       <c r="C61" s="7" t="inlineStr">
@@ -11551,36 +12023,44 @@
         <v>0.6</v>
       </c>
       <c r="E61" s="16" t="n">
-        <v>1.19</v>
+        <v>0.47</v>
       </c>
       <c r="F61" s="16" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="G61" s="7" t="inlineStr">
-        <is>
-          <t>2026-08-07</t>
-        </is>
+        <v>2</v>
+      </c>
+      <c r="G61" s="16" t="n">
+        <v>11</v>
       </c>
       <c r="H61" s="7" t="inlineStr">
         <is>
-          <t>buyback, dividend_return, delever</t>
+          <t>–</t>
         </is>
       </c>
       <c r="I61" s="7" t="inlineStr">
         <is>
-          <t>[buyback] “This quarter, we returned $111 million to shareholders, including $50 million in share repurchases and $61 million of dividends.”</t>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="J61" s="7" t="inlineStr">
+        <is>
+          <t>NEW value_gap, buyback, cost, anticipati</t>
+        </is>
+      </c>
+      <c r="K61" s="7" t="inlineStr">
+        <is>
+          <t>[value_gap] “Okay, so we still have the view that our equity is trading well below its intrinsic value.”</t>
         </is>
       </c>
     </row>
     <row r="62" ht="30" customHeight="1">
       <c r="A62" s="9" t="inlineStr">
         <is>
-          <t>RZC</t>
+          <t>DNOW</t>
         </is>
       </c>
       <c r="B62" s="10" t="inlineStr">
         <is>
-          <t>Reinsurance Group of</t>
+          <t>DNOW Inc.</t>
         </is>
       </c>
       <c r="C62" s="10" t="inlineStr">
@@ -11592,36 +12072,44 @@
         <v>0.6</v>
       </c>
       <c r="E62" s="17" t="n">
-        <v>1.13</v>
+        <v>1.37</v>
       </c>
       <c r="F62" s="17" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="G62" s="10" t="inlineStr">
-        <is>
-          <t>2026-08-07</t>
-        </is>
+        <v>0</v>
+      </c>
+      <c r="G62" s="17" t="n">
+        <v>7</v>
       </c>
       <c r="H62" s="10" t="inlineStr">
         <is>
-          <t>buyback, dividend_return, delever</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="I62" s="10" t="inlineStr">
         <is>
-          <t>[buyback] “This quarter, we returned $111 million to shareholders, including $50 million in share repurchases and $61 million of dividends.”</t>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="J62" s="10" t="inlineStr">
+        <is>
+          <t>buyback, dividend_return, cost</t>
+        </is>
+      </c>
+      <c r="K62" s="10" t="inlineStr">
+        <is>
+          <t>[buyback] “And additionally, we repurchased $25 million in shares in the second quarter.”</t>
         </is>
       </c>
     </row>
     <row r="63" ht="30" customHeight="1">
       <c r="A63" s="6" t="inlineStr">
         <is>
-          <t>INDB</t>
+          <t>FIBK</t>
         </is>
       </c>
       <c r="B63" s="7" t="inlineStr">
         <is>
-          <t>Independent Bank Cor</t>
+          <t>First Interstate Ban</t>
         </is>
       </c>
       <c r="C63" s="7" t="inlineStr">
@@ -11630,39 +12118,47 @@
         </is>
       </c>
       <c r="D63" s="16" t="n">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="E63" s="16" t="n">
-        <v>1.1</v>
+        <v>1.07</v>
       </c>
       <c r="F63" s="16" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="G63" s="7" t="inlineStr">
-        <is>
-          <t>2026-07-17</t>
-        </is>
+        <v>0</v>
+      </c>
+      <c r="G63" s="16" t="n">
+        <v>12</v>
       </c>
       <c r="H63" s="7" t="inlineStr">
         <is>
-          <t>NEW monetize, buyback, dividend_return</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="I63" s="7" t="inlineStr">
         <is>
-          <t>[monetize] “Investment CRE and construction loans conversely declined to $176 million during the quarter, primarily reflecting elevated payoffs due to a variety of factors, including asset sal”</t>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="J63" s="7" t="inlineStr">
+        <is>
+          <t>buyback, monetize</t>
+        </is>
+      </c>
+      <c r="K63" s="7" t="inlineStr">
+        <is>
+          <t>[buyback] “We repurchased approximately 1.9 million shares in the second quarter totaling approximately $69 million and repurchases since initiation of the program in August totaled about $27”</t>
         </is>
       </c>
     </row>
     <row r="64" ht="30" customHeight="1">
       <c r="A64" s="9" t="inlineStr">
         <is>
-          <t>LBRDA</t>
+          <t>METCB</t>
         </is>
       </c>
       <c r="B64" s="10" t="inlineStr">
         <is>
-          <t>Liberty Broadband Co</t>
+          <t>Ramaco Resources, In</t>
         </is>
       </c>
       <c r="C64" s="10" t="inlineStr">
@@ -11671,39 +12167,47 @@
         </is>
       </c>
       <c r="D64" s="17" t="n">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="E64" s="17" t="n">
-        <v>0.78</v>
+        <v>1.1</v>
       </c>
       <c r="F64" s="17" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="G64" s="10" t="inlineStr">
-        <is>
-          <t>2026-08-06</t>
-        </is>
+        <v>1.4</v>
+      </c>
+      <c r="G64" s="17" t="n">
+        <v>18</v>
       </c>
       <c r="H64" s="10" t="inlineStr">
         <is>
-          <t>NEW buyback, NEW dividend_return, antici</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="I64" s="10" t="inlineStr">
         <is>
-          <t>[buyback] “We have repurchased approximately $129 million principal amount of our senior notes in the open market since the end of the second quarter through July 31.”</t>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="J64" s="10" t="inlineStr">
+        <is>
+          <t>NEW monetize, buyback, anticipation</t>
+        </is>
+      </c>
+      <c r="K64" s="10" t="inlineStr">
+        <is>
+          <t>[monetize] “We announced an MOU with RE Alloys for offtake and separation of MREC and are in discussion with a number of other firms to secure similar separation and offtake agreements.”</t>
         </is>
       </c>
     </row>
     <row r="65" ht="30" customHeight="1">
       <c r="A65" s="6" t="inlineStr">
         <is>
-          <t>PLGO</t>
+          <t>ATHM</t>
         </is>
       </c>
       <c r="B65" s="7" t="inlineStr">
         <is>
-          <t>Pelagos Insurance Ca</t>
+          <t>Autohome Inc.</t>
         </is>
       </c>
       <c r="C65" s="7" t="inlineStr">
@@ -11715,36 +12219,46 @@
         <v>0.59</v>
       </c>
       <c r="E65" s="16" t="n">
-        <v>0.92</v>
+        <v>0.76</v>
       </c>
       <c r="F65" s="16" t="n">
-        <v>0.7</v>
+        <v>0.1</v>
       </c>
       <c r="G65" s="7" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>–</t>
         </is>
       </c>
       <c r="H65" s="7" t="inlineStr">
         <is>
-          <t>buyback, dividend_return, cost</t>
+          <t>–</t>
         </is>
       </c>
       <c r="I65" s="7" t="inlineStr">
         <is>
-          <t>[buyback] “In the second quarter, we repurchased 2.8 million common shares for $60 million at an average price of $21.60 per share.”</t>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="J65" s="7" t="inlineStr">
+        <is>
+          <t>buyback, cost</t>
+        </is>
+      </c>
+      <c r="K65" s="7" t="inlineStr">
+        <is>
+          <t>[buyback] “In addition, on July 28, 2026, our Board of Directors authorized a new share repurchase program under which we may repurchase up to USD 400 million of Autohome's ADS over the next ”</t>
         </is>
       </c>
     </row>
     <row r="66" ht="30" customHeight="1">
       <c r="A66" s="9" t="inlineStr">
         <is>
-          <t>GEF</t>
+          <t>BILL</t>
         </is>
       </c>
       <c r="B66" s="10" t="inlineStr">
         <is>
-          <t>Greif Inc.</t>
+          <t>BILL Holdings, Inc.</t>
         </is>
       </c>
       <c r="C66" s="10" t="inlineStr">
@@ -11753,39 +12267,47 @@
         </is>
       </c>
       <c r="D66" s="17" t="n">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="E66" s="17" t="n">
-        <v>1.31</v>
+        <v>1.22</v>
       </c>
       <c r="F66" s="17" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="G66" s="10" t="inlineStr">
-        <is>
-          <t>2026-07-29</t>
-        </is>
+        <v>1.1</v>
+      </c>
+      <c r="G66" s="17" t="n">
+        <v>21</v>
       </c>
       <c r="H66" s="10" t="inlineStr">
         <is>
-          <t>buyback, dividend_return, anticipation</t>
+          <t>–</t>
         </is>
       </c>
       <c r="I66" s="10" t="inlineStr">
         <is>
-          <t>[buyback] “In addition to the $150 million share repurchase plan we completed earlier this year, we also announced a 10.7% increase to our recurring dividend, bringing our dividend yield to a”</t>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="J66" s="10" t="inlineStr">
+        <is>
+          <t>buyback, anticipation, cost</t>
+        </is>
+      </c>
+      <c r="K66" s="10" t="inlineStr">
+        <is>
+          <t>[buyback] “In the fourth quarter, we repurchased approximately $300 million of stock at an average price of $35.31 per share.”</t>
         </is>
       </c>
     </row>
     <row r="67" ht="30" customHeight="1">
       <c r="A67" s="6" t="inlineStr">
         <is>
-          <t>GEF-B</t>
+          <t>LADR</t>
         </is>
       </c>
       <c r="B67" s="7" t="inlineStr">
         <is>
-          <t>Greif, Inc.</t>
+          <t>Ladder Capital Corp</t>
         </is>
       </c>
       <c r="C67" s="7" t="inlineStr">
@@ -11794,39 +12316,47 @@
         </is>
       </c>
       <c r="D67" s="16" t="n">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="E67" s="16" t="n">
-        <v>1.41</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="F67" s="16" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="G67" s="7" t="inlineStr">
-        <is>
-          <t>2026-07-29</t>
-        </is>
+        <v>2.4</v>
+      </c>
+      <c r="G67" s="16" t="n">
+        <v>2</v>
       </c>
       <c r="H67" s="7" t="inlineStr">
         <is>
-          <t>buyback, dividend_return, anticipation</t>
+          <t>–</t>
         </is>
       </c>
       <c r="I67" s="7" t="inlineStr">
         <is>
-          <t>[buyback] “In addition to the $150 million share repurchase plan we completed earlier this year, we also announced a 10.7% increase to our recurring dividend, bringing our dividend yield to a”</t>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="J67" s="7" t="inlineStr">
+        <is>
+          <t>NEW monetize, NEW value_gap, buyback</t>
+        </is>
+      </c>
+      <c r="K67" s="7" t="inlineStr">
+        <is>
+          <t>[monetize] “The Virginia portfolio has since been sold at our basis, and we anticipate selling the Florida portfolio above our current basis before year-end.”</t>
         </is>
       </c>
     </row>
     <row r="68" ht="30" customHeight="1">
       <c r="A68" s="9" t="inlineStr">
         <is>
-          <t>FMS</t>
+          <t>MKL</t>
         </is>
       </c>
       <c r="B68" s="10" t="inlineStr">
         <is>
-          <t>Fresenius Medical Ca</t>
+          <t>Markel Group Inc.</t>
         </is>
       </c>
       <c r="C68" s="10" t="inlineStr">
@@ -11835,39 +12365,47 @@
         </is>
       </c>
       <c r="D68" s="17" t="n">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="E68" s="17" t="n">
-        <v>0.85</v>
+        <v>1.15</v>
       </c>
       <c r="F68" s="17" t="n">
-        <v>0</v>
-      </c>
-      <c r="G68" s="10" t="inlineStr">
-        <is>
-          <t>2026-08-04</t>
-        </is>
+        <v>0.6</v>
+      </c>
+      <c r="G68" s="17" t="n">
+        <v>50</v>
       </c>
       <c r="H68" s="10" t="inlineStr">
         <is>
-          <t>buyback, cost, monetize</t>
+          <t>–</t>
         </is>
       </c>
       <c r="I68" s="10" t="inlineStr">
         <is>
-          <t>[buyback] “After canceling 8.5% of shares, which we bought back as part of the share buyback program completed in April of this year, we initiated a new share buyback program starting in May ”</t>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="J68" s="10" t="inlineStr">
+        <is>
+          <t>buyback, value_gap</t>
+        </is>
+      </c>
+      <c r="K68" s="10" t="inlineStr">
+        <is>
+          <t>[buyback] “During the second quarter, we repurchased $237 million of our shares or roughly 1% of all shares outstanding, up from $134 million in the first quarter.”</t>
         </is>
       </c>
     </row>
     <row r="69" ht="30" customHeight="1">
       <c r="A69" s="6" t="inlineStr">
         <is>
-          <t>FIBK</t>
+          <t>RGA</t>
         </is>
       </c>
       <c r="B69" s="7" t="inlineStr">
         <is>
-          <t>First Interstate Ban</t>
+          <t>Reinsurance Group of</t>
         </is>
       </c>
       <c r="C69" s="7" t="inlineStr">
@@ -11876,39 +12414,47 @@
         </is>
       </c>
       <c r="D69" s="16" t="n">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="E69" s="16" t="n">
-        <v>1.07</v>
+        <v>1.19</v>
       </c>
       <c r="F69" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="G69" s="7" t="inlineStr">
-        <is>
-          <t>2026-07-24</t>
-        </is>
+        <v>0.8</v>
+      </c>
+      <c r="G69" s="16" t="n">
+        <v>1</v>
       </c>
       <c r="H69" s="7" t="inlineStr">
         <is>
-          <t>buyback, monetize</t>
+          <t>–</t>
         </is>
       </c>
       <c r="I69" s="7" t="inlineStr">
         <is>
-          <t>[buyback] “We repurchased approximately 1.9 million shares in the second quarter totaling approximately $69 million and repurchases since initiation of the program in August totaled about $27”</t>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="J69" s="7" t="inlineStr">
+        <is>
+          <t>buyback, dividend_return, delever</t>
+        </is>
+      </c>
+      <c r="K69" s="7" t="inlineStr">
+        <is>
+          <t>[buyback] “This quarter, we returned $111 million to shareholders, including $50 million in share repurchases and $61 million of dividends.”</t>
         </is>
       </c>
     </row>
     <row r="70" ht="30" customHeight="1">
       <c r="A70" s="9" t="inlineStr">
         <is>
-          <t>FSK</t>
+          <t>RZC</t>
         </is>
       </c>
       <c r="B70" s="10" t="inlineStr">
         <is>
-          <t>FS KKR Capital Corp.</t>
+          <t>Reinsurance Group of</t>
         </is>
       </c>
       <c r="C70" s="10" t="inlineStr">
@@ -11917,39 +12463,47 @@
         </is>
       </c>
       <c r="D70" s="17" t="n">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="E70" s="17" t="n">
-        <v>0.59</v>
+        <v>1.13</v>
       </c>
       <c r="F70" s="17" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="G70" s="10" t="inlineStr">
-        <is>
-          <t>2026-08-06</t>
-        </is>
+        <v>0.8</v>
+      </c>
+      <c r="G70" s="17" t="n">
+        <v>1</v>
       </c>
       <c r="H70" s="10" t="inlineStr">
         <is>
-          <t>buyback, delever, tender</t>
+          <t>–</t>
         </is>
       </c>
       <c r="I70" s="10" t="inlineStr">
         <is>
-          <t>[buyback] “During the second quarter, we repurchased approximately 377,800 shares of FSK's common stock through the program or approximately $4 million worth of shares.”</t>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="J70" s="10" t="inlineStr">
+        <is>
+          <t>buyback, dividend_return, delever</t>
+        </is>
+      </c>
+      <c r="K70" s="10" t="inlineStr">
+        <is>
+          <t>[buyback] “This quarter, we returned $111 million to shareholders, including $50 million in share repurchases and $61 million of dividends.”</t>
         </is>
       </c>
     </row>
     <row r="71" ht="30" customHeight="1">
       <c r="A71" s="6" t="inlineStr">
         <is>
-          <t>LADR</t>
+          <t>EG</t>
         </is>
       </c>
       <c r="B71" s="7" t="inlineStr">
         <is>
-          <t>Ladder Capital Corp</t>
+          <t>Everest Group, Ltd.</t>
         </is>
       </c>
       <c r="C71" s="7" t="inlineStr">
@@ -11958,39 +12512,47 @@
         </is>
       </c>
       <c r="D71" s="16" t="n">
-        <v>0.57</v>
+        <v>0.59</v>
       </c>
       <c r="E71" s="16" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.96</v>
       </c>
       <c r="F71" s="16" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="G71" s="7" t="inlineStr">
-        <is>
-          <t>2026-07-23</t>
-        </is>
+        <v>0</v>
+      </c>
+      <c r="G71" s="16" t="n">
+        <v>3</v>
       </c>
       <c r="H71" s="7" t="inlineStr">
         <is>
-          <t>NEW monetize, NEW value_gap, buyback</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="I71" s="7" t="inlineStr">
         <is>
-          <t>[monetize] “The Virginia portfolio has since been sold at our basis, and we anticipate selling the Florida portfolio above our current basis before year-end.”</t>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="J71" s="7" t="inlineStr">
+        <is>
+          <t>buyback, monetize, cost</t>
+        </is>
+      </c>
+      <c r="K71" s="7" t="inlineStr">
+        <is>
+          <t>[buyback] “In the second quarter, we repurchased approximately 1.2 million shares amounting to $395 million at an average share price of $342 per share.”</t>
         </is>
       </c>
     </row>
     <row r="72" ht="30" customHeight="1">
       <c r="A72" s="9" t="inlineStr">
         <is>
-          <t>MBUU</t>
+          <t>EIG</t>
         </is>
       </c>
       <c r="B72" s="10" t="inlineStr">
         <is>
-          <t>Malibu Boats, Inc.</t>
+          <t>Employers Holdings I</t>
         </is>
       </c>
       <c r="C72" s="10" t="inlineStr">
@@ -11999,39 +12561,47 @@
         </is>
       </c>
       <c r="D72" s="17" t="n">
-        <v>0.57</v>
+        <v>0.59</v>
       </c>
       <c r="E72" s="17" t="n">
-        <v>0.89</v>
+        <v>1.16</v>
       </c>
       <c r="F72" s="17" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="G72" s="10" t="inlineStr">
-        <is>
-          <t>2026-08-27</t>
-        </is>
+        <v>0.4</v>
+      </c>
+      <c r="G72" s="17" t="n">
+        <v>3</v>
       </c>
       <c r="H72" s="10" t="inlineStr">
         <is>
-          <t>buyback, anticipation, dividend_return</t>
+          <t>–</t>
         </is>
       </c>
       <c r="I72" s="10" t="inlineStr">
         <is>
-          <t>[buyback] “While we chose to pause our open market purchases during the lender negotiations, our Board authorized a new $70 million share repurchase program for fiscal 2027 in June, and we cl”</t>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="J72" s="10" t="inlineStr">
+        <is>
+          <t>buyback, value_gap, governance</t>
+        </is>
+      </c>
+      <c r="K72" s="10" t="inlineStr">
+        <is>
+          <t>[buyback] “During the second quarter, we repurchased 652 thousand shares of our common stock at an average price of $42.43 per share for $28 million.”</t>
         </is>
       </c>
     </row>
     <row r="73" ht="30" customHeight="1">
       <c r="A73" s="6" t="inlineStr">
         <is>
-          <t>ATHM</t>
+          <t>UTGPF</t>
         </is>
       </c>
       <c r="B73" s="7" t="inlineStr">
         <is>
-          <t>Autohome Inc.</t>
+          <t>–</t>
         </is>
       </c>
       <c r="C73" s="7" t="inlineStr">
@@ -12040,39 +12610,51 @@
         </is>
       </c>
       <c r="D73" s="16" t="n">
-        <v>0.57</v>
-      </c>
-      <c r="E73" s="16" t="n">
-        <v>0.76</v>
+        <v>0.59</v>
+      </c>
+      <c r="E73" s="7" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
       <c r="F73" s="16" t="n">
-        <v>0.1</v>
+        <v>0.5</v>
       </c>
       <c r="G73" s="7" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>–</t>
         </is>
       </c>
       <c r="H73" s="7" t="inlineStr">
         <is>
-          <t>buyback, cost</t>
+          <t>–</t>
         </is>
       </c>
       <c r="I73" s="7" t="inlineStr">
         <is>
-          <t>[buyback] “In addition, on July 28, 2026, our Board of Directors authorized a new share repurchase program under which we may repurchase up to USD 400 million of Autohome's ADS over the next ”</t>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="J73" s="7" t="inlineStr">
+        <is>
+          <t>buyback, anticipation, monetize</t>
+        </is>
+      </c>
+      <c r="K73" s="7" t="inlineStr">
+        <is>
+          <t>[buyback] “We've completed GBP 165 million of share buybacks in H1, and we still see Unite shares as the best way for us to invest in high-quality student accommodation today.”</t>
         </is>
       </c>
     </row>
     <row r="74" ht="30" customHeight="1">
       <c r="A74" s="9" t="inlineStr">
         <is>
-          <t>CCS</t>
+          <t>FMCQF</t>
         </is>
       </c>
       <c r="B74" s="10" t="inlineStr">
         <is>
-          <t>Century Communities,</t>
+          <t>–</t>
         </is>
       </c>
       <c r="C74" s="10" t="inlineStr">
@@ -12081,39 +12663,49 @@
         </is>
       </c>
       <c r="D74" s="17" t="n">
-        <v>0.57</v>
-      </c>
-      <c r="E74" s="17" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.59</v>
+      </c>
+      <c r="E74" s="10" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
       <c r="F74" s="17" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="G74" s="10" t="inlineStr">
-        <is>
-          <t>2026-07-22</t>
-        </is>
+        <v>0</v>
+      </c>
+      <c r="G74" s="17" t="n">
+        <v>8</v>
       </c>
       <c r="H74" s="10" t="inlineStr">
         <is>
-          <t>buyback, value_gap</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="I74" s="10" t="inlineStr">
         <is>
-          <t>[buyback] “Through the first 6 months of the year, we have repurchased 970,000 shares of our common stock for $60 million or over 3% of our shares outstanding at the beginning of the year at ”</t>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="J74" s="10" t="inlineStr">
+        <is>
+          <t>buyback, cost, monetize</t>
+        </is>
+      </c>
+      <c r="K74" s="10" t="inlineStr">
+        <is>
+          <t>[buyback] “After canceling 8.5% of shares, which we bought back as part of the share buyback program completed in April of this year, we initiated a new share buyback program starting in May ”</t>
         </is>
       </c>
     </row>
     <row r="75" ht="30" customHeight="1">
       <c r="A75" s="6" t="inlineStr">
         <is>
-          <t>FGN</t>
+          <t>FMS</t>
         </is>
       </c>
       <c r="B75" s="7" t="inlineStr">
         <is>
-          <t>F&amp;G Annuities &amp; Life</t>
+          <t>Fresenius Medical Ca</t>
         </is>
       </c>
       <c r="C75" s="7" t="inlineStr">
@@ -12122,39 +12714,47 @@
         </is>
       </c>
       <c r="D75" s="16" t="n">
-        <v>0.57</v>
+        <v>0.59</v>
       </c>
       <c r="E75" s="16" t="n">
-        <v>0.95</v>
+        <v>0.85</v>
       </c>
       <c r="F75" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="G75" s="7" t="inlineStr">
-        <is>
-          <t>2026-08-06</t>
-        </is>
+      <c r="G75" s="16" t="n">
+        <v>8</v>
       </c>
       <c r="H75" s="7" t="inlineStr">
         <is>
-          <t>buyback, strategic_review, dividend_retu</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="I75" s="7" t="inlineStr">
         <is>
-          <t>[buyback] “For the first 6 months, our capital self-funded the following: $75 million of common and preferred dividends paid, $80 million of holding company interest expense and $120 million ”</t>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="J75" s="7" t="inlineStr">
+        <is>
+          <t>buyback, cost, monetize</t>
+        </is>
+      </c>
+      <c r="K75" s="7" t="inlineStr">
+        <is>
+          <t>[buyback] “After canceling 8.5% of shares, which we bought back as part of the share buyback program completed in April of this year, we initiated a new share buyback program starting in May ”</t>
         </is>
       </c>
     </row>
     <row r="76" ht="30" customHeight="1">
       <c r="A76" s="9" t="inlineStr">
         <is>
-          <t>VRTS</t>
+          <t>PERI</t>
         </is>
       </c>
       <c r="B76" s="10" t="inlineStr">
         <is>
-          <t>Virtus Investment Pa</t>
+          <t>Perion Network Ltd.</t>
         </is>
       </c>
       <c r="C76" s="10" t="inlineStr">
@@ -12163,39 +12763,47 @@
         </is>
       </c>
       <c r="D76" s="17" t="n">
+        <v>0.58</v>
+      </c>
+      <c r="E76" s="17" t="n">
         <v>0.57</v>
       </c>
-      <c r="E76" s="17" t="n">
-        <v>0.91</v>
-      </c>
       <c r="F76" s="17" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="G76" s="10" t="inlineStr">
-        <is>
-          <t>2026-07-30</t>
-        </is>
+        <v>0.2</v>
+      </c>
+      <c r="G76" s="17" t="n">
+        <v>44</v>
       </c>
       <c r="H76" s="10" t="inlineStr">
         <is>
-          <t>buyback, tender, dividend_return</t>
+          <t>–</t>
         </is>
       </c>
       <c r="I76" s="10" t="inlineStr">
         <is>
-          <t>[buyback] “During the quarter, we repurchased approximately 70 thousand shares for $10 million and paid our quarterly dividend.”</t>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="J76" s="10" t="inlineStr">
+        <is>
+          <t>buyback, cost, monetize</t>
+        </is>
+      </c>
+      <c r="K76" s="10" t="inlineStr">
+        <is>
+          <t>[buyback] “Since the initiation of this buyback program, 9 quarters ago, we have repurchased a cumulative total of 18.0 million shares for $166.8 million.”</t>
         </is>
       </c>
     </row>
     <row r="77" ht="30" customHeight="1">
       <c r="A77" s="6" t="inlineStr">
         <is>
-          <t>CAN</t>
+          <t>WHF</t>
         </is>
       </c>
       <c r="B77" s="7" t="inlineStr">
         <is>
-          <t>Canaan Inc.</t>
+          <t>WhiteHorse Finance,</t>
         </is>
       </c>
       <c r="C77" s="7" t="inlineStr">
@@ -12204,39 +12812,47 @@
         </is>
       </c>
       <c r="D77" s="16" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.58</v>
       </c>
       <c r="E77" s="16" t="n">
-        <v>0.62</v>
+        <v>0.61</v>
       </c>
       <c r="F77" s="16" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="G77" s="7" t="inlineStr">
-        <is>
-          <t>2026-09-08</t>
-        </is>
+        <v>0.8</v>
+      </c>
+      <c r="G77" s="16" t="n">
+        <v>8</v>
       </c>
       <c r="H77" s="7" t="inlineStr">
         <is>
-          <t>NEW monetize, NEW value_gap, buyback</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="I77" s="7" t="inlineStr">
         <is>
-          <t>[monetize] “James will provide more details on the execution of digital assets monetization and the buyback.”</t>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="J77" s="7" t="inlineStr">
+        <is>
+          <t>buyback, cost, value_gap</t>
+        </is>
+      </c>
+      <c r="K77" s="7" t="inlineStr">
+        <is>
+          <t>[buyback] “In regards to our share repurchase program, the company repurchased approximately 345,000 shares during the second quarter at a weighted average price of approximately $7.42 per sh”</t>
         </is>
       </c>
     </row>
     <row r="78" ht="30" customHeight="1">
       <c r="A78" s="9" t="inlineStr">
         <is>
-          <t>AER</t>
+          <t>SHO</t>
         </is>
       </c>
       <c r="B78" s="10" t="inlineStr">
         <is>
-          <t>AerCap Holdings N.V.</t>
+          <t>Sunstone Hotel Inves</t>
         </is>
       </c>
       <c r="C78" s="10" t="inlineStr">
@@ -12245,39 +12861,47 @@
         </is>
       </c>
       <c r="D78" s="17" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.58</v>
       </c>
       <c r="E78" s="17" t="n">
-        <v>1.24</v>
+        <v>1.1</v>
       </c>
       <c r="F78" s="17" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="G78" s="10" t="inlineStr">
-        <is>
-          <t>2026-07-29</t>
-        </is>
+        <v>0</v>
+      </c>
+      <c r="G78" s="17" t="n">
+        <v>3</v>
       </c>
       <c r="H78" s="10" t="inlineStr">
         <is>
-          <t>buyback, monetize, governance</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="I78" s="10" t="inlineStr">
         <is>
-          <t>[buyback] “And so know, despite the fact that we bought back 6% of the shares in the first half of this year and all of the, all of the commitments we have made in terms of new orders and tha”</t>
+          <t>2026-05-05</t>
+        </is>
+      </c>
+      <c r="J78" s="10" t="inlineStr">
+        <is>
+          <t>buyback, dividend_return, anticipation</t>
+        </is>
+      </c>
+      <c r="K78" s="10" t="inlineStr">
+        <is>
+          <t>[buyback] “Since December, we have repurchased over $19 million in liquidation value of our traded preferred stock at a 21% discount, a positive impact on both FFO and NAV.”</t>
         </is>
       </c>
     </row>
     <row r="79" ht="30" customHeight="1">
       <c r="A79" s="6" t="inlineStr">
         <is>
-          <t>MSIF</t>
+          <t>NMM</t>
         </is>
       </c>
       <c r="B79" s="7" t="inlineStr">
         <is>
-          <t>MSC Income Fund, Inc</t>
+          <t>Navios Maritime Part</t>
         </is>
       </c>
       <c r="C79" s="7" t="inlineStr">
@@ -12286,39 +12910,47 @@
         </is>
       </c>
       <c r="D79" s="16" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.58</v>
       </c>
       <c r="E79" s="16" t="n">
-        <v>0.75</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="F79" s="16" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="G79" s="7" t="inlineStr">
-        <is>
-          <t>2026-08-07</t>
-        </is>
+        <v>1.5</v>
+      </c>
+      <c r="G79" s="16" t="n">
+        <v>8</v>
       </c>
       <c r="H79" s="7" t="inlineStr">
         <is>
-          <t>buyback, delever, cost</t>
+          <t>–</t>
         </is>
       </c>
       <c r="I79" s="7" t="inlineStr">
         <is>
-          <t>[buyback] “Now turning to other opportunities intended to add value to the Fund shareholders, we're pleased to announce that the Fund's Board of Directors recently authorized a new open marke”</t>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="J79" s="7" t="inlineStr">
+        <is>
+          <t>NEW value_gap, buyback, monetize</t>
+        </is>
+      </c>
+      <c r="K79" s="7" t="inlineStr">
+        <is>
+          <t>[value_gap] “We view this program as an important tool for creating value for our common unitholders, particularly when our units trade at a meaningful discount to underlying NAV.”</t>
         </is>
       </c>
     </row>
     <row r="80" ht="30" customHeight="1">
       <c r="A80" s="9" t="inlineStr">
         <is>
-          <t>CLDT</t>
+          <t>TALO</t>
         </is>
       </c>
       <c r="B80" s="10" t="inlineStr">
         <is>
-          <t>Chatham Lodging Trus</t>
+          <t>Talos Energy, Inc.</t>
         </is>
       </c>
       <c r="C80" s="10" t="inlineStr">
@@ -12327,39 +12959,47 @@
         </is>
       </c>
       <c r="D80" s="17" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.58</v>
       </c>
       <c r="E80" s="17" t="n">
-        <v>0.85</v>
+        <v>1.36</v>
       </c>
       <c r="F80" s="17" t="n">
-        <v>0</v>
-      </c>
-      <c r="G80" s="10" t="inlineStr">
-        <is>
-          <t>2026-08-04</t>
-        </is>
+        <v>0.9</v>
+      </c>
+      <c r="G80" s="17" t="n">
+        <v>6</v>
       </c>
       <c r="H80" s="10" t="inlineStr">
         <is>
-          <t>buyback, value_gap, monetize</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="I80" s="10" t="inlineStr">
         <is>
-          <t>[buyback] “Now let's talk about another great investment that's paying off for our shareholders, our share repurchase plan, which, by the way, we launched in May 2025.”</t>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="J80" s="10" t="inlineStr">
+        <is>
+          <t>NEW monetize, buyback, governance</t>
+        </is>
+      </c>
+      <c r="K80" s="10" t="inlineStr">
+        <is>
+          <t>[monetize] “As a result, we increased stand-alone production guidance despite the impact of the shelf divestment, generated record free cash flow, and we entered the second half of the year wi”</t>
         </is>
       </c>
     </row>
     <row r="81" ht="30" customHeight="1">
       <c r="A81" s="6" t="inlineStr">
         <is>
-          <t>AEG</t>
+          <t>ADV</t>
         </is>
       </c>
       <c r="B81" s="7" t="inlineStr">
         <is>
-          <t>Aegon Ltd.</t>
+          <t>Advantage Solutions</t>
         </is>
       </c>
       <c r="C81" s="7" t="inlineStr">
@@ -12368,39 +13008,47 @@
         </is>
       </c>
       <c r="D81" s="16" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.58</v>
       </c>
       <c r="E81" s="16" t="n">
-        <v>1.37</v>
+        <v>1.11</v>
       </c>
       <c r="F81" s="16" t="n">
         <v>1.9</v>
       </c>
-      <c r="G81" s="7" t="inlineStr">
-        <is>
-          <t>2026-08-20</t>
-        </is>
+      <c r="G81" s="16" t="n">
+        <v>50</v>
       </c>
       <c r="H81" s="7" t="inlineStr">
         <is>
-          <t>NEW tender, buyback, anticipation</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="I81" s="7" t="inlineStr">
         <is>
-          <t>[tender] “The other items largely reflect the net cash proceeds from the senior bond issuance and the tender offer, both executed in the second quarter of 2026.”</t>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="J81" s="7" t="inlineStr">
+        <is>
+          <t>NEW buyback, monetize, cost</t>
+        </is>
+      </c>
+      <c r="K81" s="7" t="inlineStr">
+        <is>
+          <t>[buyback] “In the second quarter, we repurchased approximately $15 million of our shares.”</t>
         </is>
       </c>
     </row>
     <row r="82" ht="30" customHeight="1">
       <c r="A82" s="9" t="inlineStr">
         <is>
-          <t>VIOT</t>
+          <t>WFC</t>
         </is>
       </c>
       <c r="B82" s="10" t="inlineStr">
         <is>
-          <t>Viomi Technology Co.</t>
+          <t>Wells Fargo &amp; Compan</t>
         </is>
       </c>
       <c r="C82" s="10" t="inlineStr">
@@ -12409,27 +13057,35 @@
         </is>
       </c>
       <c r="D82" s="17" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.58</v>
       </c>
       <c r="E82" s="17" t="n">
-        <v>0.4</v>
+        <v>1.39</v>
       </c>
       <c r="F82" s="17" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="G82" s="10" t="inlineStr">
-        <is>
-          <t>2026-03-25</t>
-        </is>
+        <v>0</v>
+      </c>
+      <c r="G82" s="17" t="n">
+        <v>3</v>
       </c>
       <c r="H82" s="10" t="inlineStr">
         <is>
-          <t>NEW buyback, NEW dividend_return</t>
+          <t>–</t>
         </is>
       </c>
       <c r="I82" s="10" t="inlineStr">
         <is>
-          <t>[buyback] “In terms of shareholder returns, we declared a special dividend of USD 0.088 per ADS in July 2025, in August of the same year. or core authorized a new share repurchase program of ”</t>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="J82" s="10" t="inlineStr">
+        <is>
+          <t>buyback, cost, dividend_return</t>
+        </is>
+      </c>
+      <c r="K82" s="10" t="inlineStr">
+        <is>
+          <t>[buyback] “We returned over $9.8 billion of capital to shareholders in the first half of this year, including repurchasing $7 billion of common stock while continuing to maintain the signific”</t>
         </is>
       </c>
     </row>
@@ -12450,7 +13106,7 @@
         </is>
       </c>
       <c r="D83" s="16" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.58</v>
       </c>
       <c r="E83" s="16" t="n">
         <v>0.48</v>
@@ -12460,15 +13116,25 @@
       </c>
       <c r="G83" s="7" t="inlineStr">
         <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="H83" s="7" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="I83" s="7" t="inlineStr">
+        <is>
           <t>2026-08-26</t>
         </is>
       </c>
-      <c r="H83" s="7" t="inlineStr">
+      <c r="J83" s="7" t="inlineStr">
         <is>
           <t>buyback, monetize</t>
         </is>
       </c>
-      <c r="I83" s="7" t="inlineStr">
+      <c r="K83" s="7" t="inlineStr">
         <is>
           <t>[buyback] “As of June 30, 2026, we had RMB 4.4 billion in cash and cash equivalents, time deposits, restricted cash and short-term investments, maintaining a solid liquidity position to suppo”</t>
         </is>
@@ -12477,12 +13143,12 @@
     <row r="84" ht="30" customHeight="1">
       <c r="A84" s="9" t="inlineStr">
         <is>
-          <t>CRBG</t>
+          <t>GEF</t>
         </is>
       </c>
       <c r="B84" s="10" t="inlineStr">
         <is>
-          <t>Corebridge Financial</t>
+          <t>Greif Inc.</t>
         </is>
       </c>
       <c r="C84" s="10" t="inlineStr">
@@ -12491,42 +13157,50 @@
         </is>
       </c>
       <c r="D84" s="17" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.58</v>
       </c>
       <c r="E84" s="17" t="n">
-        <v>1.42</v>
+        <v>1.31</v>
       </c>
       <c r="F84" s="17" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="G84" s="10" t="inlineStr">
-        <is>
-          <t>2026-08-05</t>
-        </is>
+        <v>1.4</v>
+      </c>
+      <c r="G84" s="17" t="n">
+        <v>4</v>
       </c>
       <c r="H84" s="10" t="inlineStr">
         <is>
-          <t>buyback, dividend_return, monetize</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="I84" s="10" t="inlineStr">
         <is>
-          <t>[buyback] “In the second quarter, we returned $412 million of capital to shareholders, including $300 million of share repurchases for our year-to-date normalized payout ratio of 84%.”</t>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="J84" s="10" t="inlineStr">
+        <is>
+          <t>buyback, dividend_return, anticipation</t>
+        </is>
+      </c>
+      <c r="K84" s="10" t="inlineStr">
+        <is>
+          <t>[buyback] “In addition to the $150 million share repurchase plan we completed earlier this year, we also announced a 10.7% increase to our recurring dividend, bringing our dividend yield to a”</t>
         </is>
       </c>
     </row>
     <row r="86" ht="28" customHeight="1">
       <c r="A86" s="11" t="inlineStr">
         <is>
-          <t>1274 names scored on their latest call. Out-of-time validation (CALL_INTENT_VALIDATION.md): AUC for ACTED — rule 0.65, past behaviour only 0.60, past behaviour + language 0.67. ACT SIGNALLED = top decile of act probability with a committed/realised shareholder action or a family that is NEW vs the prior three calls; BUILDING = top quartile. Transcripts: FMP. Source: call_intent.py + call_intent_model.py.</t>
+          <t>1789 names scored on their latest call. Out-of-time validation (CALL_INTENT_VALIDATION.md): AUC for ACTED — rule 0.64, past behaviour only 0.60, past behaviour + language 0.66. ACT SIGNALLED = top decile of act probability with a committed/realised shareholder action or a family that is NEW vs the prior three calls; BUILDING = top quartile. Transcripts: FMP. Size = stated buyback/tender as % of market cap; CEO+CFO = both committed on the call. Language predicts ACTION (it does not by itself predict the re-rating; see the validation report's deep-discount tests). Source: call_intent.py + call_intent_model.py.</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="3">
-    <mergeCell ref="A1:I1"/>
-    <mergeCell ref="A2:I2"/>
-    <mergeCell ref="A86:I86"/>
+    <mergeCell ref="A2:K2"/>
+    <mergeCell ref="A86:K86"/>
+    <mergeCell ref="A1:K1"/>
   </mergeCells>
   <printOptions horizontalCentered="0"/>
   <pageMargins left="0.5" right="0.5" top="0.6" bottom="0.6" header="0.5" footer="0.5"/>
@@ -19097,7 +19771,7 @@
       </c>
       <c r="E16" s="7" t="inlineStr">
         <is>
-          <t>12 layers firing | cons 10.794</t>
+          <t>12 layers firing | cons 10.956</t>
         </is>
       </c>
     </row>
@@ -19147,7 +19821,7 @@
       </c>
       <c r="E18" s="7" t="inlineStr">
         <is>
-          <t>12 layers firing | cons 9.946</t>
+          <t>12 layers firing | cons 9.008</t>
         </is>
       </c>
     </row>
@@ -19157,22 +19831,22 @@
       </c>
       <c r="B19" s="9" t="inlineStr">
         <is>
-          <t>DXC</t>
+          <t>GPK</t>
         </is>
       </c>
       <c r="C19" s="10" t="inlineStr">
         <is>
-          <t>DXC Technology</t>
+          <t>GPK</t>
         </is>
       </c>
       <c r="D19" s="6" t="inlineStr">
         <is>
-          <t>Participation 1-2%</t>
+          <t>Concentrated 5%+</t>
         </is>
       </c>
       <c r="E19" s="10" t="inlineStr">
         <is>
-          <t>PSU core 40 + buyback + recent-incentive 57% drawdown</t>
+          <t>11 layers firing | cons 8.642</t>
         </is>
       </c>
     </row>
@@ -19197,7 +19871,7 @@
       </c>
       <c r="E20" s="7" t="inlineStr">
         <is>
-          <t>11 layers firing | cons 8.674</t>
+          <t>11 layers firing | cons 8.618</t>
         </is>
       </c>
     </row>
@@ -19207,22 +19881,22 @@
       </c>
       <c r="B21" s="9" t="inlineStr">
         <is>
-          <t>POOL</t>
+          <t>DXC</t>
         </is>
       </c>
       <c r="C21" s="10" t="inlineStr">
         <is>
-          <t>POOL</t>
+          <t>DXC Technology</t>
         </is>
       </c>
       <c r="D21" s="6" t="inlineStr">
         <is>
-          <t>Concentrated 5%+</t>
+          <t>Participation 1-2%</t>
         </is>
       </c>
       <c r="E21" s="10" t="inlineStr">
         <is>
-          <t>11 layers firing | cons 7.672</t>
+          <t>PSU core 40 + buyback + recent-incentive 57% drawdown</t>
         </is>
       </c>
     </row>
@@ -19232,22 +19906,22 @@
       </c>
       <c r="B22" s="6" t="inlineStr">
         <is>
-          <t>LULU</t>
+          <t>ADT</t>
         </is>
       </c>
       <c r="C22" s="7" t="inlineStr">
         <is>
-          <t>LULU</t>
+          <t>ADT Inc</t>
         </is>
       </c>
       <c r="D22" s="6" t="inlineStr">
         <is>
-          <t>Participation 1-2%</t>
+          <t>Concentrated 5%+</t>
         </is>
       </c>
       <c r="E22" s="7" t="inlineStr">
         <is>
-          <t>11 layers firing | cons 6.504</t>
+          <t>Heaviest PSU%LTI in universe (90%) + verified -7.3% shrinkage</t>
         </is>
       </c>
     </row>
@@ -19257,12 +19931,12 @@
       </c>
       <c r="B23" s="9" t="inlineStr">
         <is>
-          <t>GO</t>
+          <t>POOL</t>
         </is>
       </c>
       <c r="C23" s="10" t="inlineStr">
         <is>
-          <t>Grocery Outlet</t>
+          <t>POOL</t>
         </is>
       </c>
       <c r="D23" s="6" t="inlineStr">
@@ -19272,7 +19946,7 @@
       </c>
       <c r="E23" s="10" t="inlineStr">
         <is>
-          <t>Forward $ targets + Cohen-Malloy 6-buyer cluster</t>
+          <t>11 layers firing | cons 7.474</t>
         </is>
       </c>
     </row>
@@ -19282,22 +19956,22 @@
       </c>
       <c r="B24" s="6" t="inlineStr">
         <is>
-          <t>HUBS</t>
+          <t>LULU</t>
         </is>
       </c>
       <c r="C24" s="7" t="inlineStr">
         <is>
-          <t>HUBS</t>
+          <t>LULU</t>
         </is>
       </c>
       <c r="D24" s="6" t="inlineStr">
         <is>
-          <t>Concentrated 5%+</t>
+          <t>Participation 1-2%</t>
         </is>
       </c>
       <c r="E24" s="7" t="inlineStr">
         <is>
-          <t>10 layers firing | cons 8.286</t>
+          <t>11 layers firing | cons 6.336</t>
         </is>
       </c>
     </row>
@@ -19307,12 +19981,12 @@
       </c>
       <c r="B25" s="9" t="inlineStr">
         <is>
-          <t>GPK</t>
+          <t>ANGI</t>
         </is>
       </c>
       <c r="C25" s="10" t="inlineStr">
         <is>
-          <t>GPK</t>
+          <t>ANGI</t>
         </is>
       </c>
       <c r="D25" s="6" t="inlineStr">
@@ -19322,7 +19996,7 @@
       </c>
       <c r="E25" s="10" t="inlineStr">
         <is>
-          <t>10 layers firing | cons 8.022</t>
+          <t>11 layers firing | cons 6.182</t>
         </is>
       </c>
     </row>
@@ -19332,12 +20006,12 @@
       </c>
       <c r="B26" s="6" t="inlineStr">
         <is>
-          <t>FOUR</t>
+          <t>GO</t>
         </is>
       </c>
       <c r="C26" s="7" t="inlineStr">
         <is>
-          <t>FOUR</t>
+          <t>Grocery Outlet</t>
         </is>
       </c>
       <c r="D26" s="6" t="inlineStr">
@@ -19347,7 +20021,7 @@
       </c>
       <c r="E26" s="7" t="inlineStr">
         <is>
-          <t>10 layers firing | cons 7.766</t>
+          <t>Forward $ targets + Cohen-Malloy 6-buyer cluster</t>
         </is>
       </c>
     </row>
@@ -19357,12 +20031,12 @@
       </c>
       <c r="B27" s="9" t="inlineStr">
         <is>
-          <t>GPGI</t>
+          <t>HUBS</t>
         </is>
       </c>
       <c r="C27" s="10" t="inlineStr">
         <is>
-          <t>GPGI</t>
+          <t>HUBS</t>
         </is>
       </c>
       <c r="D27" s="6" t="inlineStr">
@@ -19372,7 +20046,7 @@
       </c>
       <c r="E27" s="10" t="inlineStr">
         <is>
-          <t>10 layers firing | cons 7.544</t>
+          <t>10 layers firing | cons 8.65</t>
         </is>
       </c>
     </row>
@@ -19382,12 +20056,12 @@
       </c>
       <c r="B28" s="6" t="inlineStr">
         <is>
-          <t>VRSK</t>
+          <t>HFFG</t>
         </is>
       </c>
       <c r="C28" s="7" t="inlineStr">
         <is>
-          <t>VRSK</t>
+          <t>HF Foods Group</t>
         </is>
       </c>
       <c r="D28" s="6" t="inlineStr">
@@ -19397,7 +20071,7 @@
       </c>
       <c r="E28" s="7" t="inlineStr">
         <is>
-          <t>10 layers firing | cons 7.48</t>
+          <t>Triple PSU $ hurdle (rev/EBITDA/FCF) + clawback strengthened + 4-buyer F4 cluster</t>
         </is>
       </c>
     </row>
@@ -19407,12 +20081,12 @@
       </c>
       <c r="B29" s="9" t="inlineStr">
         <is>
-          <t>ADT</t>
+          <t>FOUR</t>
         </is>
       </c>
       <c r="C29" s="10" t="inlineStr">
         <is>
-          <t>ADT Inc</t>
+          <t>FOUR</t>
         </is>
       </c>
       <c r="D29" s="6" t="inlineStr">
@@ -19422,7 +20096,7 @@
       </c>
       <c r="E29" s="10" t="inlineStr">
         <is>
-          <t>Heaviest PSU%LTI in universe (90%) + verified -7.3% shrinkage</t>
+          <t>10 layers firing | cons 7.74</t>
         </is>
       </c>
     </row>
@@ -19432,22 +20106,22 @@
       </c>
       <c r="B30" s="6" t="inlineStr">
         <is>
-          <t>APTV</t>
+          <t>LW</t>
         </is>
       </c>
       <c r="C30" s="7" t="inlineStr">
         <is>
-          <t>APTV</t>
-        </is>
-      </c>
-      <c r="D30" s="6" t="inlineStr">
-        <is>
-          <t>Concentrated 5%+</t>
+          <t>LW</t>
+        </is>
+      </c>
+      <c r="D30" s="7" t="inlineStr">
+        <is>
+          <t>Material 2-5%</t>
         </is>
       </c>
       <c r="E30" s="7" t="inlineStr">
         <is>
-          <t>10 layers firing | cons 6.684</t>
+          <t>10 layers firing | cons 7.52</t>
         </is>
       </c>
     </row>
@@ -19457,22 +20131,22 @@
       </c>
       <c r="B31" s="9" t="inlineStr">
         <is>
-          <t>GIII</t>
+          <t>APTV</t>
         </is>
       </c>
       <c r="C31" s="10" t="inlineStr">
         <is>
-          <t>GIII</t>
-        </is>
-      </c>
-      <c r="D31" s="10" t="inlineStr">
-        <is>
-          <t>Material 2-5%</t>
+          <t>APTV</t>
+        </is>
+      </c>
+      <c r="D31" s="6" t="inlineStr">
+        <is>
+          <t>Concentrated 5%+</t>
         </is>
       </c>
       <c r="E31" s="10" t="inlineStr">
         <is>
-          <t>10 layers firing | cons 6.578</t>
+          <t>10 layers firing | cons 7.502</t>
         </is>
       </c>
     </row>
@@ -19482,12 +20156,12 @@
       </c>
       <c r="B32" s="6" t="inlineStr">
         <is>
-          <t>BLND</t>
+          <t>GPGI</t>
         </is>
       </c>
       <c r="C32" s="7" t="inlineStr">
         <is>
-          <t>BLND</t>
+          <t>GPGI</t>
         </is>
       </c>
       <c r="D32" s="6" t="inlineStr">
@@ -19497,7 +20171,7 @@
       </c>
       <c r="E32" s="7" t="inlineStr">
         <is>
-          <t>10 layers firing | cons 6.542</t>
+          <t>10 layers firing | cons 7.182</t>
         </is>
       </c>
     </row>
@@ -19507,12 +20181,12 @@
       </c>
       <c r="B33" s="9" t="inlineStr">
         <is>
-          <t>TRS</t>
+          <t>GIII</t>
         </is>
       </c>
       <c r="C33" s="10" t="inlineStr">
         <is>
-          <t>TRS</t>
+          <t>GIII</t>
         </is>
       </c>
       <c r="D33" s="10" t="inlineStr">
@@ -19522,7 +20196,7 @@
       </c>
       <c r="E33" s="10" t="inlineStr">
         <is>
-          <t>10 layers firing | cons 6.214</t>
+          <t>10 layers firing | cons 6.434</t>
         </is>
       </c>
     </row>
@@ -19532,12 +20206,12 @@
       </c>
       <c r="B34" s="6" t="inlineStr">
         <is>
-          <t>CERT</t>
+          <t>BLND</t>
         </is>
       </c>
       <c r="C34" s="7" t="inlineStr">
         <is>
-          <t>CERT</t>
+          <t>BLND</t>
         </is>
       </c>
       <c r="D34" s="6" t="inlineStr">
@@ -19547,7 +20221,7 @@
       </c>
       <c r="E34" s="7" t="inlineStr">
         <is>
-          <t>10 layers firing | cons 6.08</t>
+          <t>10 layers firing | cons 6.43</t>
         </is>
       </c>
     </row>
@@ -19557,12 +20231,12 @@
       </c>
       <c r="B35" s="9" t="inlineStr">
         <is>
-          <t>ANGI</t>
+          <t>CERT</t>
         </is>
       </c>
       <c r="C35" s="10" t="inlineStr">
         <is>
-          <t>ANGI</t>
+          <t>CERT</t>
         </is>
       </c>
       <c r="D35" s="6" t="inlineStr">
@@ -19572,7 +20246,7 @@
       </c>
       <c r="E35" s="10" t="inlineStr">
         <is>
-          <t>10 layers firing | cons 5.882</t>
+          <t>10 layers firing | cons 6.428</t>
         </is>
       </c>
     </row>
@@ -20273,12 +20947,12 @@
     <row r="5" ht="22" customHeight="1">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>MSGM</t>
+          <t>SND</t>
         </is>
       </c>
       <c r="B5" s="7" t="inlineStr">
         <is>
-          <t>Motorsport Games Inc.</t>
+          <t>Smart Sand, Inc.</t>
         </is>
       </c>
       <c r="C5" s="16" t="n">
@@ -20336,12 +21010,12 @@
     <row r="6" ht="22" customHeight="1">
       <c r="A6" s="9" t="inlineStr">
         <is>
-          <t>SND</t>
+          <t>MSGM</t>
         </is>
       </c>
       <c r="B6" s="10" t="inlineStr">
         <is>
-          <t>Smart Sand, Inc.</t>
+          <t>Motorsport Games Inc.</t>
         </is>
       </c>
       <c r="C6" s="17" t="n">
@@ -21029,12 +21703,12 @@
     <row r="17" ht="22" customHeight="1">
       <c r="A17" s="6" t="inlineStr">
         <is>
-          <t>PTLO</t>
+          <t>VSNT</t>
         </is>
       </c>
       <c r="B17" s="7" t="inlineStr">
         <is>
-          <t>Portillo's Inc.</t>
+          <t>Versant Media Group, Inc</t>
         </is>
       </c>
       <c r="C17" s="16" t="n">
@@ -21092,12 +21766,12 @@
     <row r="18" ht="22" customHeight="1">
       <c r="A18" s="9" t="inlineStr">
         <is>
-          <t>BCIC</t>
+          <t>PAL</t>
         </is>
       </c>
       <c r="B18" s="10" t="inlineStr">
         <is>
-          <t>BCP Investment Corporati</t>
+          <t>Proficient Auto Logistic</t>
         </is>
       </c>
       <c r="C18" s="17" t="n">
@@ -21155,12 +21829,12 @@
     <row r="19" ht="22" customHeight="1">
       <c r="A19" s="6" t="inlineStr">
         <is>
-          <t>PAL</t>
+          <t>BDCO</t>
         </is>
       </c>
       <c r="B19" s="7" t="inlineStr">
         <is>
-          <t>Proficient Auto Logistic</t>
+          <t>Blue Dolphin Energy Comp</t>
         </is>
       </c>
       <c r="C19" s="16" t="n">
@@ -21218,12 +21892,12 @@
     <row r="20" ht="22" customHeight="1">
       <c r="A20" s="9" t="inlineStr">
         <is>
-          <t>BDCO</t>
+          <t>PTLO</t>
         </is>
       </c>
       <c r="B20" s="10" t="inlineStr">
         <is>
-          <t>Blue Dolphin Energy Comp</t>
+          <t>Portillo's Inc.</t>
         </is>
       </c>
       <c r="C20" s="17" t="n">
@@ -21281,12 +21955,12 @@
     <row r="21" ht="22" customHeight="1">
       <c r="A21" s="6" t="inlineStr">
         <is>
-          <t>VSNT</t>
+          <t>BCIC</t>
         </is>
       </c>
       <c r="B21" s="7" t="inlineStr">
         <is>
-          <t>Versant Media Group, Inc</t>
+          <t>BCP Investment Corporati</t>
         </is>
       </c>
       <c r="C21" s="16" t="n">
@@ -21407,12 +22081,12 @@
     <row r="23" ht="22" customHeight="1">
       <c r="A23" s="6" t="inlineStr">
         <is>
-          <t>LCNB</t>
+          <t>GMRS</t>
         </is>
       </c>
       <c r="B23" s="7" t="inlineStr">
         <is>
-          <t>LCNB Corporation</t>
+          <t>GMR Solutions Inc.</t>
         </is>
       </c>
       <c r="C23" s="16" t="n">
@@ -21470,12 +22144,12 @@
     <row r="24" ht="22" customHeight="1">
       <c r="A24" s="9" t="inlineStr">
         <is>
-          <t>BXSL</t>
+          <t>OTF</t>
         </is>
       </c>
       <c r="B24" s="10" t="inlineStr">
         <is>
-          <t>Blackstone Secured Lendi</t>
+          <t>Blue Owl Technology Fina</t>
         </is>
       </c>
       <c r="C24" s="17" t="n">
@@ -21533,12 +22207,12 @@
     <row r="25" ht="22" customHeight="1">
       <c r="A25" s="6" t="inlineStr">
         <is>
-          <t>NCDL</t>
+          <t>LCNB</t>
         </is>
       </c>
       <c r="B25" s="7" t="inlineStr">
         <is>
-          <t>Nuveen Churchill Direct</t>
+          <t>LCNB Corporation</t>
         </is>
       </c>
       <c r="C25" s="16" t="n">
@@ -21596,12 +22270,12 @@
     <row r="26" ht="22" customHeight="1">
       <c r="A26" s="9" t="inlineStr">
         <is>
-          <t>GMRS</t>
+          <t>NCDL</t>
         </is>
       </c>
       <c r="B26" s="10" t="inlineStr">
         <is>
-          <t>GMR Solutions Inc.</t>
+          <t>Nuveen Churchill Direct</t>
         </is>
       </c>
       <c r="C26" s="17" t="n">
@@ -21659,12 +22333,12 @@
     <row r="27" ht="22" customHeight="1">
       <c r="A27" s="6" t="inlineStr">
         <is>
-          <t>OTF</t>
+          <t>BXSL</t>
         </is>
       </c>
       <c r="B27" s="7" t="inlineStr">
         <is>
-          <t>Blue Owl Technology Fina</t>
+          <t>Blackstone Secured Lendi</t>
         </is>
       </c>
       <c r="C27" s="16" t="n">
@@ -25142,10 +25816,10 @@
         <v>8</v>
       </c>
       <c r="E5" s="16" t="n">
-        <v>5.702</v>
+        <v>5.966</v>
       </c>
       <c r="F5" s="5" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="G5" s="7" t="inlineStr">
         <is>
@@ -25164,22 +25838,22 @@
       </c>
       <c r="B6" s="9" t="inlineStr">
         <is>
-          <t>FOUR</t>
+          <t>EPAM</t>
         </is>
       </c>
       <c r="C6" s="10" t="inlineStr">
         <is>
-          <t>Shift4 Payments, Inc.</t>
+          <t>EPAM Systems, Inc.</t>
         </is>
       </c>
       <c r="D6" s="8" t="n">
         <v>7</v>
       </c>
       <c r="E6" s="17" t="n">
-        <v>6.09</v>
+        <v>6.18</v>
       </c>
       <c r="F6" s="8" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="G6" s="10" t="inlineStr">
         <is>
@@ -25188,7 +25862,7 @@
       </c>
       <c r="H6" s="10" t="inlineStr">
         <is>
-          <t>PSU:28 BB:5 F4:10 RI:51</t>
+          <t>PSU:21 C10:-29 F4:18 RI:53</t>
         </is>
       </c>
     </row>
@@ -25198,24 +25872,22 @@
       </c>
       <c r="B7" s="6" t="inlineStr">
         <is>
-          <t>EPAM</t>
+          <t>CRM</t>
         </is>
       </c>
       <c r="C7" s="7" t="inlineStr">
         <is>
-          <t>EPAM Systems, Inc.</t>
+          <t>Salesforce, Inc.</t>
         </is>
       </c>
       <c r="D7" s="5" t="n">
         <v>7</v>
       </c>
       <c r="E7" s="16" t="n">
-        <v>5.932</v>
-      </c>
-      <c r="F7" s="7" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+        <v>5.828</v>
+      </c>
+      <c r="F7" s="5" t="n">
+        <v>-1</v>
       </c>
       <c r="G7" s="7" t="inlineStr">
         <is>
@@ -25224,7 +25896,7 @@
       </c>
       <c r="H7" s="7" t="inlineStr">
         <is>
-          <t>PSU:21 C10:-29 F4:18 RI:53</t>
+          <t>PSU:28 BB:8 C10:-5 F4:11 RI:61</t>
         </is>
       </c>
     </row>
@@ -25234,22 +25906,22 @@
       </c>
       <c r="B8" s="9" t="inlineStr">
         <is>
-          <t>CRM</t>
+          <t>OLED</t>
         </is>
       </c>
       <c r="C8" s="10" t="inlineStr">
         <is>
-          <t>Salesforce, Inc.</t>
+          <t>Universal Display Corporation</t>
         </is>
       </c>
       <c r="D8" s="8" t="n">
         <v>7</v>
       </c>
       <c r="E8" s="17" t="n">
-        <v>5.766</v>
+        <v>5.514</v>
       </c>
       <c r="F8" s="8" t="n">
-        <v>-2</v>
+        <v>20</v>
       </c>
       <c r="G8" s="10" t="inlineStr">
         <is>
@@ -25258,7 +25930,7 @@
       </c>
       <c r="H8" s="10" t="inlineStr">
         <is>
-          <t>PSU:28 BB:8 C10:-5 F4:11 RI:61</t>
+          <t>PSU:40 BB:5 F4:17 RI:60</t>
         </is>
       </c>
     </row>
@@ -25268,22 +25940,22 @@
       </c>
       <c r="B9" s="6" t="inlineStr">
         <is>
-          <t>OLED</t>
+          <t>FOUR</t>
         </is>
       </c>
       <c r="C9" s="7" t="inlineStr">
         <is>
-          <t>Universal Display Corporation</t>
+          <t>Shift4 Payments, Inc.</t>
         </is>
       </c>
       <c r="D9" s="5" t="n">
         <v>7</v>
       </c>
       <c r="E9" s="16" t="n">
-        <v>5.726</v>
+        <v>5.482</v>
       </c>
       <c r="F9" s="5" t="n">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="G9" s="7" t="inlineStr">
         <is>
@@ -25292,7 +25964,7 @@
       </c>
       <c r="H9" s="7" t="inlineStr">
         <is>
-          <t>PSU:40 BB:5 F4:17 RI:60</t>
+          <t>PSU:28 BB:5 F4:10 RI:51</t>
         </is>
       </c>
     </row>
@@ -25314,10 +25986,10 @@
         <v>7</v>
       </c>
       <c r="E10" s="17" t="n">
-        <v>5.206</v>
+        <v>5.32</v>
       </c>
       <c r="F10" s="8" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="G10" s="10" t="inlineStr">
         <is>
@@ -25348,10 +26020,10 @@
         <v>7</v>
       </c>
       <c r="E11" s="16" t="n">
-        <v>5.01</v>
+        <v>5.286</v>
       </c>
       <c r="F11" s="5" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="G11" s="7" t="inlineStr">
         <is>
@@ -25382,10 +26054,10 @@
         <v>7</v>
       </c>
       <c r="E12" s="17" t="n">
-        <v>4.936</v>
+        <v>4.892</v>
       </c>
       <c r="F12" s="8" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="G12" s="10" t="inlineStr">
         <is>
@@ -25416,10 +26088,10 @@
         <v>7</v>
       </c>
       <c r="E13" s="16" t="n">
-        <v>4.114</v>
+        <v>4.09</v>
       </c>
       <c r="F13" s="5" t="n">
-        <v>5</v>
+        <v>-2</v>
       </c>
       <c r="G13" s="7" t="inlineStr">
         <is>
@@ -25438,31 +26110,31 @@
       </c>
       <c r="B14" s="9" t="inlineStr">
         <is>
-          <t>CERT</t>
+          <t>LULU</t>
         </is>
       </c>
       <c r="C14" s="10" t="inlineStr">
         <is>
-          <t>Certara, Inc.</t>
+          <t>lululemon athletica inc.</t>
         </is>
       </c>
       <c r="D14" s="8" t="n">
         <v>7</v>
       </c>
       <c r="E14" s="17" t="n">
-        <v>3.996</v>
+        <v>3.988</v>
       </c>
       <c r="F14" s="8" t="n">
-        <v>9</v>
+        <v>-1</v>
       </c>
       <c r="G14" s="10" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>Consumer Cyclical</t>
         </is>
       </c>
       <c r="H14" s="10" t="inlineStr">
         <is>
-          <t>PSU:29 BB:5 C10:-12 RI:43</t>
+          <t>PSU:1 BB:8 C10:-40 F4:11 RI:41 SS:10</t>
         </is>
       </c>
     </row>
@@ -25472,31 +26144,31 @@
       </c>
       <c r="B15" s="6" t="inlineStr">
         <is>
-          <t>LULU</t>
+          <t>CERT</t>
         </is>
       </c>
       <c r="C15" s="7" t="inlineStr">
         <is>
-          <t>lululemon athletica inc.</t>
+          <t>Certara, Inc.</t>
         </is>
       </c>
       <c r="D15" s="5" t="n">
         <v>7</v>
       </c>
       <c r="E15" s="16" t="n">
-        <v>3.868</v>
+        <v>3.612</v>
       </c>
       <c r="F15" s="5" t="n">
-        <v>-4</v>
+        <v>9</v>
       </c>
       <c r="G15" s="7" t="inlineStr">
         <is>
-          <t>Consumer Cyclical</t>
+          <t>Healthcare</t>
         </is>
       </c>
       <c r="H15" s="7" t="inlineStr">
         <is>
-          <t>PSU:1 BB:8 C10:-40 F4:11 RI:41 SS:10</t>
+          <t>PSU:29 BB:5 C10:-12 RI:43</t>
         </is>
       </c>
     </row>
@@ -25518,10 +26190,10 @@
         <v>6</v>
       </c>
       <c r="E16" s="17" t="n">
-        <v>5.29</v>
+        <v>5.296</v>
       </c>
       <c r="F16" s="8" t="n">
-        <v>-4</v>
+        <v>-1</v>
       </c>
       <c r="G16" s="10" t="inlineStr">
         <is>
@@ -25552,10 +26224,10 @@
         <v>6</v>
       </c>
       <c r="E17" s="16" t="n">
-        <v>4.962</v>
+        <v>4.89</v>
       </c>
       <c r="F17" s="5" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="G17" s="7" t="inlineStr">
         <is>
@@ -25574,31 +26246,31 @@
       </c>
       <c r="B18" s="9" t="inlineStr">
         <is>
-          <t>SBET</t>
+          <t>NUS</t>
         </is>
       </c>
       <c r="C18" s="10" t="inlineStr">
         <is>
-          <t>SharpLink, Inc.</t>
+          <t>Nu Skin Enterprises, Inc.</t>
         </is>
       </c>
       <c r="D18" s="8" t="n">
         <v>6</v>
       </c>
       <c r="E18" s="17" t="n">
-        <v>4.89</v>
-      </c>
-      <c r="F18" s="22" t="n">
-        <v>80</v>
+        <v>4.864</v>
+      </c>
+      <c r="F18" s="8" t="n">
+        <v>16</v>
       </c>
       <c r="G18" s="10" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>Consumer Defensive</t>
         </is>
       </c>
       <c r="H18" s="10" t="inlineStr">
         <is>
-          <t>PSU:19 C10:15 RI:71</t>
+          <t>PSU:54 BB:5 C10:-32 RI:53</t>
         </is>
       </c>
     </row>
@@ -25608,31 +26280,31 @@
       </c>
       <c r="B19" s="6" t="inlineStr">
         <is>
-          <t>SNBR</t>
+          <t>SBET</t>
         </is>
       </c>
       <c r="C19" s="7" t="inlineStr">
         <is>
-          <t>Sleep Number Corporation</t>
+          <t>SharpLink, Inc.</t>
         </is>
       </c>
       <c r="D19" s="5" t="n">
         <v>6</v>
       </c>
       <c r="E19" s="16" t="n">
-        <v>4.88</v>
-      </c>
-      <c r="F19" s="5" t="n">
-        <v>11</v>
+        <v>4.724</v>
+      </c>
+      <c r="F19" s="22" t="n">
+        <v>96</v>
       </c>
       <c r="G19" s="7" t="inlineStr">
         <is>
-          <t>Consumer Cyclical</t>
+          <t>Financial Services</t>
         </is>
       </c>
       <c r="H19" s="7" t="inlineStr">
         <is>
-          <t>PSU:49 RI:46 SS:20</t>
+          <t>PSU:19 C10:15 RI:71</t>
         </is>
       </c>
     </row>
@@ -25642,31 +26314,31 @@
       </c>
       <c r="B20" s="9" t="inlineStr">
         <is>
-          <t>ALKT</t>
+          <t>SNBR</t>
         </is>
       </c>
       <c r="C20" s="10" t="inlineStr">
         <is>
-          <t>Alkami Technology, Inc.</t>
+          <t>Sleep Number Corporation</t>
         </is>
       </c>
       <c r="D20" s="8" t="n">
         <v>6</v>
       </c>
       <c r="E20" s="17" t="n">
-        <v>4.856</v>
+        <v>4.71</v>
       </c>
       <c r="F20" s="8" t="n">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="G20" s="10" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Consumer Cyclical</t>
         </is>
       </c>
       <c r="H20" s="10" t="inlineStr">
         <is>
-          <t>PSU:11 C10:-6 F4:16 RI:54</t>
+          <t>PSU:49 RI:46 SS:20</t>
         </is>
       </c>
     </row>
@@ -25676,31 +26348,31 @@
       </c>
       <c r="B21" s="6" t="inlineStr">
         <is>
-          <t>ACM</t>
+          <t>ALKT</t>
         </is>
       </c>
       <c r="C21" s="7" t="inlineStr">
         <is>
-          <t>AECOM</t>
+          <t>Alkami Technology, Inc.</t>
         </is>
       </c>
       <c r="D21" s="5" t="n">
         <v>6</v>
       </c>
       <c r="E21" s="16" t="n">
-        <v>4.84</v>
+        <v>4.672</v>
       </c>
       <c r="F21" s="5" t="n">
-        <v>42</v>
+        <v>17</v>
       </c>
       <c r="G21" s="7" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="H21" s="7" t="inlineStr">
         <is>
-          <t>BB:5 F4:6 RI:54</t>
+          <t>PSU:11 C10:-6 F4:16 RI:54</t>
         </is>
       </c>
     </row>
@@ -25722,10 +26394,10 @@
         <v>6</v>
       </c>
       <c r="E22" s="17" t="n">
-        <v>4.766</v>
+        <v>4.63</v>
       </c>
       <c r="F22" s="8" t="n">
-        <v>-6</v>
+        <v>-1</v>
       </c>
       <c r="G22" s="10" t="inlineStr">
         <is>
@@ -25744,22 +26416,22 @@
       </c>
       <c r="B23" s="6" t="inlineStr">
         <is>
-          <t>NUS</t>
+          <t>HFFG</t>
         </is>
       </c>
       <c r="C23" s="7" t="inlineStr">
         <is>
-          <t>Nu Skin Enterprises, Inc.</t>
+          <t>HF Foods Group Inc.</t>
         </is>
       </c>
       <c r="D23" s="5" t="n">
         <v>6</v>
       </c>
       <c r="E23" s="16" t="n">
-        <v>4.758</v>
+        <v>4.594</v>
       </c>
       <c r="F23" s="5" t="n">
-        <v>9</v>
+        <v>-6</v>
       </c>
       <c r="G23" s="7" t="inlineStr">
         <is>
@@ -25768,7 +26440,7 @@
       </c>
       <c r="H23" s="7" t="inlineStr">
         <is>
-          <t>PSU:54 BB:5 C10:-32 RI:53</t>
+          <t>PSU:45 F4:18 RI:59 SS:20</t>
         </is>
       </c>
     </row>
@@ -25778,31 +26450,31 @@
       </c>
       <c r="B24" s="9" t="inlineStr">
         <is>
-          <t>MSCI</t>
+          <t>ZTS</t>
         </is>
       </c>
       <c r="C24" s="10" t="inlineStr">
         <is>
-          <t>MSCI Inc.</t>
+          <t>Zoetis Inc.</t>
         </is>
       </c>
       <c r="D24" s="8" t="n">
         <v>6</v>
       </c>
       <c r="E24" s="17" t="n">
-        <v>4.48</v>
+        <v>4.562</v>
       </c>
       <c r="F24" s="8" t="n">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="G24" s="10" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>Healthcare</t>
         </is>
       </c>
       <c r="H24" s="10" t="inlineStr">
         <is>
-          <t>PSU:36 BB:8 C10:-26 F4:16 RI:16</t>
+          <t>PSU:7 BB:5 C10:-3 F4:12 RI:60</t>
         </is>
       </c>
     </row>
@@ -25812,31 +26484,31 @@
       </c>
       <c r="B25" s="6" t="inlineStr">
         <is>
-          <t>DXC</t>
+          <t>MSCI</t>
         </is>
       </c>
       <c r="C25" s="7" t="inlineStr">
         <is>
-          <t>DXC Technology Company</t>
+          <t>MSCI Inc.</t>
         </is>
       </c>
       <c r="D25" s="5" t="n">
         <v>6</v>
       </c>
       <c r="E25" s="16" t="n">
-        <v>4.414</v>
+        <v>4.54</v>
       </c>
       <c r="F25" s="5" t="n">
-        <v>-17</v>
+        <v>12</v>
       </c>
       <c r="G25" s="7" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Financial Services</t>
         </is>
       </c>
       <c r="H25" s="7" t="inlineStr">
         <is>
-          <t>PSU:43 BB:5 RI:57</t>
+          <t>PSU:36 BB:8 C10:-26 F4:16 RI:16</t>
         </is>
       </c>
     </row>
@@ -25858,10 +26530,10 @@
         <v>6</v>
       </c>
       <c r="E26" s="17" t="n">
-        <v>4.398</v>
+        <v>4.408</v>
       </c>
       <c r="F26" s="8" t="n">
-        <v>13</v>
+        <v>35</v>
       </c>
       <c r="G26" s="10" t="inlineStr">
         <is>
@@ -25880,31 +26552,31 @@
       </c>
       <c r="B27" s="6" t="inlineStr">
         <is>
-          <t>VRSK</t>
+          <t>OPCH</t>
         </is>
       </c>
       <c r="C27" s="7" t="inlineStr">
         <is>
-          <t>Verisk Analytics, Inc.</t>
+          <t>Option Care Health, Inc.</t>
         </is>
       </c>
       <c r="D27" s="5" t="n">
         <v>6</v>
       </c>
       <c r="E27" s="16" t="n">
-        <v>4.366</v>
+        <v>4.396</v>
       </c>
       <c r="F27" s="5" t="n">
-        <v>-10</v>
+        <v>14</v>
       </c>
       <c r="G27" s="7" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Healthcare</t>
         </is>
       </c>
       <c r="H27" s="7" t="inlineStr">
         <is>
-          <t>PSU:32 BB:8 F4:12 RI:32</t>
+          <t>PSU:27 BB:5 C10:-1 F4:23 RI:52</t>
         </is>
       </c>
     </row>
@@ -25914,31 +26586,31 @@
       </c>
       <c r="B28" s="9" t="inlineStr">
         <is>
-          <t>AAT</t>
+          <t>VRSK</t>
         </is>
       </c>
       <c r="C28" s="10" t="inlineStr">
         <is>
-          <t>American Assets Trust, Inc.</t>
+          <t>Verisk Analytics, Inc.</t>
         </is>
       </c>
       <c r="D28" s="8" t="n">
         <v>6</v>
       </c>
       <c r="E28" s="17" t="n">
-        <v>4.342</v>
+        <v>4.354</v>
       </c>
       <c r="F28" s="8" t="n">
-        <v>17</v>
+        <v>4</v>
       </c>
       <c r="G28" s="10" t="inlineStr">
         <is>
-          <t>Real Estate</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="H28" s="10" t="inlineStr">
         <is>
-          <t>PSU:2 BB:5 C10:-12 F4:5 RI:37 SS:10</t>
+          <t>PSU:32 BB:8 F4:12 RI:32</t>
         </is>
       </c>
     </row>
@@ -25948,31 +26620,31 @@
       </c>
       <c r="B29" s="6" t="inlineStr">
         <is>
-          <t>ZTS</t>
+          <t>DXC</t>
         </is>
       </c>
       <c r="C29" s="7" t="inlineStr">
         <is>
-          <t>Zoetis Inc.</t>
+          <t>DXC Technology Company</t>
         </is>
       </c>
       <c r="D29" s="5" t="n">
         <v>6</v>
       </c>
       <c r="E29" s="16" t="n">
-        <v>4.336</v>
+        <v>4.258</v>
       </c>
       <c r="F29" s="5" t="n">
-        <v>2</v>
+        <v>-19</v>
       </c>
       <c r="G29" s="7" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="H29" s="7" t="inlineStr">
         <is>
-          <t>PSU:7 BB:5 C10:-3 F4:12 RI:60</t>
+          <t>PSU:43 BB:5 RI:57</t>
         </is>
       </c>
     </row>
@@ -25994,10 +26666,10 @@
         <v>6</v>
       </c>
       <c r="E30" s="17" t="n">
-        <v>4.316</v>
+        <v>4.242</v>
       </c>
       <c r="F30" s="8" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="G30" s="10" t="inlineStr">
         <is>
@@ -26016,31 +26688,31 @@
       </c>
       <c r="B31" s="6" t="inlineStr">
         <is>
-          <t>OPCH</t>
+          <t>MA</t>
         </is>
       </c>
       <c r="C31" s="7" t="inlineStr">
         <is>
-          <t>Option Care Health, Inc.</t>
+          <t>Mastercard Incorporated</t>
         </is>
       </c>
       <c r="D31" s="5" t="n">
         <v>6</v>
       </c>
       <c r="E31" s="16" t="n">
-        <v>4.262</v>
+        <v>4.19</v>
       </c>
       <c r="F31" s="5" t="n">
-        <v>4</v>
+        <v>38</v>
       </c>
       <c r="G31" s="7" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>Financial Services</t>
         </is>
       </c>
       <c r="H31" s="7" t="inlineStr">
         <is>
-          <t>PSU:27 BB:5 C10:-1 F4:23 RI:52</t>
+          <t>PSU:31 BB:5 C10:78 RI:50</t>
         </is>
       </c>
     </row>
@@ -26050,31 +26722,31 @@
       </c>
       <c r="B32" s="9" t="inlineStr">
         <is>
-          <t>MA</t>
+          <t>CNMD</t>
         </is>
       </c>
       <c r="C32" s="10" t="inlineStr">
         <is>
-          <t>Mastercard Incorporated</t>
+          <t>CONMED Corporation</t>
         </is>
       </c>
       <c r="D32" s="8" t="n">
         <v>6</v>
       </c>
       <c r="E32" s="17" t="n">
-        <v>4.248</v>
+        <v>4.174</v>
       </c>
       <c r="F32" s="8" t="n">
-        <v>39</v>
+        <v>14</v>
       </c>
       <c r="G32" s="10" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>Healthcare</t>
         </is>
       </c>
       <c r="H32" s="10" t="inlineStr">
         <is>
-          <t>PSU:31 BB:5 C10:78 RI:50</t>
+          <t>PSU:32 BB:5 C10:28 RI:23</t>
         </is>
       </c>
     </row>
@@ -26084,31 +26756,31 @@
       </c>
       <c r="B33" s="6" t="inlineStr">
         <is>
-          <t>TKO</t>
+          <t>PRGO</t>
         </is>
       </c>
       <c r="C33" s="7" t="inlineStr">
         <is>
-          <t>TKO Group Holdings, Inc.</t>
+          <t>Perrigo Company plc</t>
         </is>
       </c>
       <c r="D33" s="5" t="n">
         <v>6</v>
       </c>
       <c r="E33" s="16" t="n">
-        <v>4.112</v>
-      </c>
-      <c r="F33" s="5" t="n">
-        <v>39</v>
+        <v>4.164</v>
+      </c>
+      <c r="F33" s="22" t="n">
+        <v>65</v>
       </c>
       <c r="G33" s="7" t="inlineStr">
         <is>
-          <t>Communication Services</t>
+          <t>Healthcare</t>
         </is>
       </c>
       <c r="H33" s="7" t="inlineStr">
         <is>
-          <t>PSU:3 BB:5 C10:2 F4:17 RI:42</t>
+          <t>PSU:21 RI:48 SS:29</t>
         </is>
       </c>
     </row>
@@ -26118,22 +26790,22 @@
       </c>
       <c r="B34" s="9" t="inlineStr">
         <is>
-          <t>MMS</t>
+          <t>ACM</t>
         </is>
       </c>
       <c r="C34" s="10" t="inlineStr">
         <is>
-          <t>Maximus, Inc.</t>
+          <t>AECOM</t>
         </is>
       </c>
       <c r="D34" s="8" t="n">
         <v>6</v>
       </c>
       <c r="E34" s="17" t="n">
-        <v>4.098</v>
-      </c>
-      <c r="F34" s="22" t="n">
-        <v>252</v>
+        <v>4.162</v>
+      </c>
+      <c r="F34" s="8" t="n">
+        <v>1</v>
       </c>
       <c r="G34" s="10" t="inlineStr">
         <is>
@@ -26142,7 +26814,7 @@
       </c>
       <c r="H34" s="10" t="inlineStr">
         <is>
-          <t>PSU:42 BB:5 RI:53 SS:26</t>
+          <t>BB:5 F4:6 RI:54</t>
         </is>
       </c>
     </row>
@@ -34622,7 +35294,7 @@
       </c>
       <c r="H5" s="7" t="inlineStr">
         <is>
-          <t>12 layers firing | cons 10.794</t>
+          <t>12 layers firing | cons 10.956</t>
         </is>
       </c>
       <c r="I5" s="7" t="inlineStr">
@@ -34710,7 +35382,7 @@
       </c>
       <c r="H7" s="7" t="inlineStr">
         <is>
-          <t>12 layers firing | cons 9.946</t>
+          <t>12 layers firing | cons 9.008</t>
         </is>
       </c>
       <c r="I7" s="7" t="inlineStr">
@@ -34727,25 +35399,25 @@
     <row r="8" ht="56" customHeight="1">
       <c r="A8" s="9" t="inlineStr">
         <is>
-          <t>DXC</t>
+          <t>GPK</t>
         </is>
       </c>
       <c r="B8" s="10" t="inlineStr">
         <is>
-          <t>DXC Technology</t>
+          <t>GPK</t>
         </is>
       </c>
       <c r="C8" s="8" t="n">
-        <v>1797</v>
+        <v>2913</v>
       </c>
       <c r="D8" s="17" t="n">
-        <v>11.09</v>
+        <v>9.85</v>
       </c>
       <c r="E8" s="17" t="n">
-        <v>0.57</v>
+        <v>0.9</v>
       </c>
       <c r="F8" s="8" t="n">
-        <v>50</v>
+        <v>22</v>
       </c>
       <c r="G8" s="10" t="inlineStr">
         <is>
@@ -34754,17 +35426,17 @@
       </c>
       <c r="H8" s="10" t="inlineStr">
         <is>
-          <t>PSU core 40 + buyback + recent-incentive 57% drawdown</t>
+          <t>11 layers firing | cons 8.642</t>
         </is>
       </c>
       <c r="I8" s="10" t="inlineStr">
         <is>
-          <t>IT services franchise; transformation signal in PSU</t>
+          <t>see proxy_scan + buyback_verify</t>
         </is>
       </c>
       <c r="J8" s="6" t="inlineStr">
         <is>
-          <t>Participation 1-2%</t>
+          <t>Concentrated 5%+</t>
         </is>
       </c>
     </row>
@@ -34800,7 +35472,7 @@
       </c>
       <c r="H9" s="7" t="inlineStr">
         <is>
-          <t>11 layers firing | cons 8.674</t>
+          <t>11 layers firing | cons 8.618</t>
         </is>
       </c>
       <c r="I9" s="7" t="inlineStr">
@@ -34817,71 +35489,69 @@
     <row r="10" ht="56" customHeight="1">
       <c r="A10" s="9" t="inlineStr">
         <is>
-          <t>POOL</t>
+          <t>DXC</t>
         </is>
       </c>
       <c r="B10" s="10" t="inlineStr">
         <is>
-          <t>POOL</t>
+          <t>DXC Technology</t>
         </is>
       </c>
       <c r="C10" s="8" t="n">
-        <v>6104</v>
+        <v>1797</v>
       </c>
       <c r="D10" s="17" t="n">
-        <v>167.5</v>
+        <v>11.09</v>
       </c>
       <c r="E10" s="17" t="n">
-        <v>4.84</v>
+        <v>0.57</v>
       </c>
       <c r="F10" s="8" t="n">
-        <v>26</v>
+        <v>50</v>
       </c>
       <c r="G10" s="10" t="inlineStr">
         <is>
-          <t>fda_phase_milestone</t>
+          <t>–</t>
         </is>
       </c>
       <c r="H10" s="10" t="inlineStr">
         <is>
-          <t>11 layers firing | cons 7.672</t>
+          <t>PSU core 40 + buyback + recent-incentive 57% drawdown</t>
         </is>
       </c>
       <c r="I10" s="10" t="inlineStr">
         <is>
-          <t>see proxy_scan + buyback_verify</t>
+          <t>IT services franchise; transformation signal in PSU</t>
         </is>
       </c>
       <c r="J10" s="6" t="inlineStr">
         <is>
-          <t>Concentrated 5%+</t>
+          <t>Participation 1-2%</t>
         </is>
       </c>
     </row>
     <row r="11" ht="56" customHeight="1">
       <c r="A11" s="6" t="inlineStr">
         <is>
-          <t>LULU</t>
+          <t>ADT</t>
         </is>
       </c>
       <c r="B11" s="7" t="inlineStr">
         <is>
-          <t>LULU</t>
+          <t>ADT Inc</t>
         </is>
       </c>
       <c r="C11" s="5" t="n">
-        <v>11657</v>
+        <v>5108</v>
       </c>
       <c r="D11" s="16" t="n">
-        <v>102.66</v>
+        <v>6.38</v>
       </c>
       <c r="E11" s="16" t="n">
-        <v>2.43</v>
-      </c>
-      <c r="F11" s="7" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+        <v>1.47</v>
+      </c>
+      <c r="F11" s="5" t="n">
+        <v>27</v>
       </c>
       <c r="G11" s="7" t="inlineStr">
         <is>
@@ -34890,56 +35560,56 @@
       </c>
       <c r="H11" s="7" t="inlineStr">
         <is>
-          <t>11 layers firing | cons 6.504</t>
+          <t>Heaviest PSU%LTI in universe (90%) + verified -7.3% shrinkage</t>
         </is>
       </c>
       <c r="I11" s="7" t="inlineStr">
         <is>
-          <t>see proxy_scan + buyback_verify</t>
+          <t>Recurring monitoring revenue + verified supply-curve compression</t>
         </is>
       </c>
       <c r="J11" s="6" t="inlineStr">
         <is>
-          <t>Participation 1-2%</t>
+          <t>Concentrated 5%+</t>
         </is>
       </c>
     </row>
     <row r="12" ht="56" customHeight="1">
       <c r="A12" s="9" t="inlineStr">
         <is>
-          <t>GO</t>
+          <t>POOL</t>
         </is>
       </c>
       <c r="B12" s="10" t="inlineStr">
         <is>
-          <t>Grocery Outlet</t>
+          <t>POOL</t>
         </is>
       </c>
       <c r="C12" s="8" t="n">
-        <v>1120</v>
+        <v>6104</v>
       </c>
       <c r="D12" s="17" t="n">
-        <v>11.33</v>
+        <v>167.5</v>
       </c>
       <c r="E12" s="17" t="n">
-        <v>1.37</v>
+        <v>4.84</v>
       </c>
       <c r="F12" s="8" t="n">
-        <v>69</v>
+        <v>26</v>
       </c>
       <c r="G12" s="10" t="inlineStr">
         <is>
-          <t>–</t>
+          <t>fda_phase_milestone</t>
         </is>
       </c>
       <c r="H12" s="10" t="inlineStr">
         <is>
-          <t>Forward $ targets + Cohen-Malloy 6-buyer cluster</t>
+          <t>11 layers firing | cons 7.474</t>
         </is>
       </c>
       <c r="I12" s="10" t="inlineStr">
         <is>
-          <t>Discount-grocery defensive base</t>
+          <t>see proxy_scan + buyback_verify</t>
         </is>
       </c>
       <c r="J12" s="6" t="inlineStr">
@@ -34951,25 +35621,27 @@
     <row r="13" ht="56" customHeight="1">
       <c r="A13" s="6" t="inlineStr">
         <is>
-          <t>HUBS</t>
+          <t>LULU</t>
         </is>
       </c>
       <c r="B13" s="7" t="inlineStr">
         <is>
-          <t>HUBS</t>
+          <t>LULU</t>
         </is>
       </c>
       <c r="C13" s="5" t="n">
-        <v>11602</v>
+        <v>11657</v>
       </c>
       <c r="D13" s="16" t="n">
-        <v>226.52</v>
+        <v>102.66</v>
       </c>
       <c r="E13" s="16" t="n">
-        <v>7</v>
-      </c>
-      <c r="F13" s="5" t="n">
-        <v>34</v>
+        <v>2.43</v>
+      </c>
+      <c r="F13" s="7" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
       <c r="G13" s="7" t="inlineStr">
         <is>
@@ -34978,7 +35650,7 @@
       </c>
       <c r="H13" s="7" t="inlineStr">
         <is>
-          <t>10 layers firing | cons 8.286</t>
+          <t>11 layers firing | cons 6.336</t>
         </is>
       </c>
       <c r="I13" s="7" t="inlineStr">
@@ -34988,32 +35660,32 @@
       </c>
       <c r="J13" s="6" t="inlineStr">
         <is>
-          <t>Concentrated 5%+</t>
+          <t>Participation 1-2%</t>
         </is>
       </c>
     </row>
     <row r="14" ht="56" customHeight="1">
       <c r="A14" s="9" t="inlineStr">
         <is>
-          <t>GPK</t>
+          <t>ANGI</t>
         </is>
       </c>
       <c r="B14" s="10" t="inlineStr">
         <is>
-          <t>GPK</t>
+          <t>ANGI</t>
         </is>
       </c>
       <c r="C14" s="8" t="n">
-        <v>2913</v>
+        <v>216</v>
       </c>
       <c r="D14" s="17" t="n">
-        <v>9.85</v>
+        <v>5.35</v>
       </c>
       <c r="E14" s="17" t="n">
-        <v>0.9</v>
+        <v>0.31</v>
       </c>
       <c r="F14" s="8" t="n">
-        <v>22</v>
+        <v>36</v>
       </c>
       <c r="G14" s="10" t="inlineStr">
         <is>
@@ -35022,7 +35694,7 @@
       </c>
       <c r="H14" s="10" t="inlineStr">
         <is>
-          <t>10 layers firing | cons 8.022</t>
+          <t>11 layers firing | cons 6.182</t>
         </is>
       </c>
       <c r="I14" s="10" t="inlineStr">
@@ -35039,25 +35711,25 @@
     <row r="15" ht="56" customHeight="1">
       <c r="A15" s="6" t="inlineStr">
         <is>
-          <t>FOUR</t>
+          <t>GO</t>
         </is>
       </c>
       <c r="B15" s="7" t="inlineStr">
         <is>
-          <t>FOUR</t>
+          <t>Grocery Outlet</t>
         </is>
       </c>
       <c r="C15" s="5" t="n">
-        <v>3516</v>
+        <v>1120</v>
       </c>
       <c r="D15" s="16" t="n">
-        <v>38.61</v>
+        <v>11.33</v>
       </c>
       <c r="E15" s="16" t="n">
-        <v>2.17</v>
+        <v>1.37</v>
       </c>
       <c r="F15" s="5" t="n">
-        <v>35</v>
+        <v>69</v>
       </c>
       <c r="G15" s="7" t="inlineStr">
         <is>
@@ -35066,12 +35738,12 @@
       </c>
       <c r="H15" s="7" t="inlineStr">
         <is>
-          <t>10 layers firing | cons 7.766</t>
+          <t>Forward $ targets + Cohen-Malloy 6-buyer cluster</t>
         </is>
       </c>
       <c r="I15" s="7" t="inlineStr">
         <is>
-          <t>see proxy_scan + buyback_verify</t>
+          <t>Discount-grocery defensive base</t>
         </is>
       </c>
       <c r="J15" s="6" t="inlineStr">
@@ -35083,34 +35755,34 @@
     <row r="16" ht="56" customHeight="1">
       <c r="A16" s="9" t="inlineStr">
         <is>
-          <t>GPGI</t>
+          <t>HUBS</t>
         </is>
       </c>
       <c r="B16" s="10" t="inlineStr">
         <is>
-          <t>GPGI</t>
+          <t>HUBS</t>
         </is>
       </c>
       <c r="C16" s="8" t="n">
-        <v>3522</v>
+        <v>11602</v>
       </c>
       <c r="D16" s="17" t="n">
-        <v>12.15</v>
+        <v>226.52</v>
       </c>
       <c r="E16" s="17" t="n">
-        <v>1.11</v>
+        <v>7</v>
       </c>
       <c r="F16" s="8" t="n">
-        <v>4</v>
+        <v>34</v>
       </c>
       <c r="G16" s="10" t="inlineStr">
         <is>
-          <t>spin_separation</t>
+          <t>–</t>
         </is>
       </c>
       <c r="H16" s="10" t="inlineStr">
         <is>
-          <t>10 layers firing | cons 7.544</t>
+          <t>10 layers firing | cons 8.65</t>
         </is>
       </c>
       <c r="I16" s="10" t="inlineStr">
@@ -35127,41 +35799,39 @@
     <row r="17" ht="56" customHeight="1">
       <c r="A17" s="6" t="inlineStr">
         <is>
-          <t>VRSK</t>
+          <t>HFFG</t>
         </is>
       </c>
       <c r="B17" s="7" t="inlineStr">
         <is>
-          <t>VRSK</t>
+          <t>HF Foods Group</t>
         </is>
       </c>
       <c r="C17" s="5" t="n">
-        <v>22408</v>
+        <v>82</v>
       </c>
       <c r="D17" s="16" t="n">
-        <v>172.16</v>
-      </c>
-      <c r="E17" s="7" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+        <v>1.53</v>
+      </c>
+      <c r="E17" s="16" t="n">
+        <v>0.4</v>
       </c>
       <c r="F17" s="5" t="n">
-        <v>32</v>
+        <v>48</v>
       </c>
       <c r="G17" s="7" t="inlineStr">
         <is>
-          <t>–</t>
+          <t>revenue_dollar_target</t>
         </is>
       </c>
       <c r="H17" s="7" t="inlineStr">
         <is>
-          <t>10 layers firing | cons 7.48</t>
+          <t>Triple PSU $ hurdle (rev/EBITDA/FCF) + clawback strengthened + 4-buyer F4 cluster</t>
         </is>
       </c>
       <c r="I17" s="7" t="inlineStr">
         <is>
-          <t>see proxy_scan + buyback_verify</t>
+          <t>P/B 0.48 + microcap distributor with hard assets</t>
         </is>
       </c>
       <c r="J17" s="6" t="inlineStr">
@@ -35173,25 +35843,25 @@
     <row r="18" ht="56" customHeight="1">
       <c r="A18" s="9" t="inlineStr">
         <is>
-          <t>ADT</t>
+          <t>FOUR</t>
         </is>
       </c>
       <c r="B18" s="10" t="inlineStr">
         <is>
-          <t>ADT Inc</t>
+          <t>FOUR</t>
         </is>
       </c>
       <c r="C18" s="8" t="n">
-        <v>5108</v>
+        <v>3516</v>
       </c>
       <c r="D18" s="17" t="n">
-        <v>6.38</v>
+        <v>38.61</v>
       </c>
       <c r="E18" s="17" t="n">
-        <v>1.47</v>
+        <v>2.17</v>
       </c>
       <c r="F18" s="8" t="n">
-        <v>27</v>
+        <v>35</v>
       </c>
       <c r="G18" s="10" t="inlineStr">
         <is>
@@ -35200,12 +35870,12 @@
       </c>
       <c r="H18" s="10" t="inlineStr">
         <is>
-          <t>Heaviest PSU%LTI in universe (90%) + verified -7.3% shrinkage</t>
+          <t>10 layers firing | cons 7.74</t>
         </is>
       </c>
       <c r="I18" s="10" t="inlineStr">
         <is>
-          <t>Recurring monitoring revenue + verified supply-curve compression</t>
+          <t>see proxy_scan + buyback_verify</t>
         </is>
       </c>
       <c r="J18" s="6" t="inlineStr">
@@ -35217,25 +35887,25 @@
     <row r="19" ht="56" customHeight="1">
       <c r="A19" s="6" t="inlineStr">
         <is>
-          <t>APTV</t>
+          <t>LW</t>
         </is>
       </c>
       <c r="B19" s="7" t="inlineStr">
         <is>
-          <t>APTV</t>
+          <t>LW</t>
         </is>
       </c>
       <c r="C19" s="5" t="n">
-        <v>9527</v>
+        <v>6225</v>
       </c>
       <c r="D19" s="16" t="n">
-        <v>45.02</v>
+        <v>45.28</v>
       </c>
       <c r="E19" s="16" t="n">
-        <v>1.09</v>
+        <v>3.41</v>
       </c>
       <c r="F19" s="5" t="n">
-        <v>38</v>
+        <v>51</v>
       </c>
       <c r="G19" s="7" t="inlineStr">
         <is>
@@ -35244,7 +35914,7 @@
       </c>
       <c r="H19" s="7" t="inlineStr">
         <is>
-          <t>10 layers firing | cons 6.684</t>
+          <t>10 layers firing | cons 7.52</t>
         </is>
       </c>
       <c r="I19" s="7" t="inlineStr">
@@ -35252,34 +35922,34 @@
           <t>see proxy_scan + buyback_verify</t>
         </is>
       </c>
-      <c r="J19" s="6" t="inlineStr">
-        <is>
-          <t>Concentrated 5%+</t>
+      <c r="J19" s="7" t="inlineStr">
+        <is>
+          <t>Material 2-5%</t>
         </is>
       </c>
     </row>
     <row r="20" ht="56" customHeight="1">
       <c r="A20" s="9" t="inlineStr">
         <is>
-          <t>GIII</t>
+          <t>APTV</t>
         </is>
       </c>
       <c r="B20" s="10" t="inlineStr">
         <is>
-          <t>GIII</t>
+          <t>APTV</t>
         </is>
       </c>
       <c r="C20" s="8" t="n">
-        <v>1171</v>
+        <v>9527</v>
       </c>
       <c r="D20" s="17" t="n">
-        <v>27.75</v>
+        <v>45.02</v>
       </c>
       <c r="E20" s="17" t="n">
-        <v>0.65</v>
+        <v>1.09</v>
       </c>
       <c r="F20" s="8" t="n">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="G20" s="10" t="inlineStr">
         <is>
@@ -35288,7 +35958,7 @@
       </c>
       <c r="H20" s="10" t="inlineStr">
         <is>
-          <t>10 layers firing | cons 6.578</t>
+          <t>10 layers firing | cons 7.502</t>
         </is>
       </c>
       <c r="I20" s="10" t="inlineStr">
@@ -35296,43 +35966,43 @@
           <t>see proxy_scan + buyback_verify</t>
         </is>
       </c>
-      <c r="J20" s="10" t="inlineStr">
-        <is>
-          <t>Material 2-5%</t>
+      <c r="J20" s="6" t="inlineStr">
+        <is>
+          <t>Concentrated 5%+</t>
         </is>
       </c>
     </row>
     <row r="21" ht="56" customHeight="1">
       <c r="A21" s="6" t="inlineStr">
         <is>
-          <t>BLND</t>
+          <t>GPGI</t>
         </is>
       </c>
       <c r="B21" s="7" t="inlineStr">
         <is>
-          <t>BLND</t>
+          <t>GPGI</t>
         </is>
       </c>
       <c r="C21" s="5" t="n">
-        <v>271</v>
+        <v>3522</v>
       </c>
       <c r="D21" s="16" t="n">
-        <v>1.12</v>
+        <v>12.15</v>
       </c>
       <c r="E21" s="16" t="n">
-        <v>2.86</v>
+        <v>1.11</v>
       </c>
       <c r="F21" s="5" t="n">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="G21" s="7" t="inlineStr">
         <is>
-          <t>–</t>
+          <t>spin_separation</t>
         </is>
       </c>
       <c r="H21" s="7" t="inlineStr">
         <is>
-          <t>10 layers firing | cons 6.542</t>
+          <t>10 layers firing | cons 7.182</t>
         </is>
       </c>
       <c r="I21" s="7" t="inlineStr">
@@ -35349,25 +36019,25 @@
     <row r="22" ht="56" customHeight="1">
       <c r="A22" s="9" t="inlineStr">
         <is>
-          <t>TRS</t>
+          <t>GIII</t>
         </is>
       </c>
       <c r="B22" s="10" t="inlineStr">
         <is>
-          <t>TRS</t>
+          <t>GIII</t>
         </is>
       </c>
       <c r="C22" s="8" t="n">
-        <v>1409</v>
+        <v>1171</v>
       </c>
       <c r="D22" s="17" t="n">
-        <v>39.32</v>
+        <v>27.75</v>
       </c>
       <c r="E22" s="17" t="n">
-        <v>0.98</v>
+        <v>0.65</v>
       </c>
       <c r="F22" s="8" t="n">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="G22" s="10" t="inlineStr">
         <is>
@@ -35376,7 +36046,7 @@
       </c>
       <c r="H22" s="10" t="inlineStr">
         <is>
-          <t>10 layers firing | cons 6.214</t>
+          <t>10 layers firing | cons 6.434</t>
         </is>
       </c>
       <c r="I22" s="10" t="inlineStr">
@@ -35393,25 +36063,25 @@
     <row r="23" ht="56" customHeight="1">
       <c r="A23" s="6" t="inlineStr">
         <is>
-          <t>CERT</t>
+          <t>BLND</t>
         </is>
       </c>
       <c r="B23" s="7" t="inlineStr">
         <is>
-          <t>CERT</t>
+          <t>BLND</t>
         </is>
       </c>
       <c r="C23" s="5" t="n">
-        <v>1368</v>
+        <v>271</v>
       </c>
       <c r="D23" s="16" t="n">
-        <v>8.789999999999999</v>
+        <v>1.12</v>
       </c>
       <c r="E23" s="16" t="n">
-        <v>1.42</v>
+        <v>2.86</v>
       </c>
       <c r="F23" s="5" t="n">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="G23" s="7" t="inlineStr">
         <is>
@@ -35420,7 +36090,7 @@
       </c>
       <c r="H23" s="7" t="inlineStr">
         <is>
-          <t>10 layers firing | cons 6.08</t>
+          <t>10 layers firing | cons 6.43</t>
         </is>
       </c>
       <c r="I23" s="7" t="inlineStr">
@@ -35437,25 +36107,25 @@
     <row r="24" ht="56" customHeight="1">
       <c r="A24" s="9" t="inlineStr">
         <is>
-          <t>ANGI</t>
+          <t>CERT</t>
         </is>
       </c>
       <c r="B24" s="10" t="inlineStr">
         <is>
-          <t>ANGI</t>
+          <t>CERT</t>
         </is>
       </c>
       <c r="C24" s="8" t="n">
-        <v>216</v>
+        <v>1368</v>
       </c>
       <c r="D24" s="17" t="n">
-        <v>5.35</v>
+        <v>8.789999999999999</v>
       </c>
       <c r="E24" s="17" t="n">
-        <v>0.31</v>
+        <v>1.42</v>
       </c>
       <c r="F24" s="8" t="n">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="G24" s="10" t="inlineStr">
         <is>
@@ -35464,7 +36134,7 @@
       </c>
       <c r="H24" s="10" t="inlineStr">
         <is>
-          <t>10 layers firing | cons 5.882</t>
+          <t>10 layers firing | cons 6.428</t>
         </is>
       </c>
       <c r="I24" s="10" t="inlineStr">
@@ -36688,7 +37358,7 @@
         <v>12</v>
       </c>
       <c r="B27" s="17" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C27" s="10" t="inlineStr">
         <is>
@@ -36701,7 +37371,7 @@
         <v>11</v>
       </c>
       <c r="B28" s="16" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="C28" s="7" t="inlineStr">
         <is>
@@ -36714,7 +37384,7 @@
         <v>10</v>
       </c>
       <c r="B29" s="17" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="C29" s="10" t="inlineStr">
         <is>
@@ -36727,7 +37397,7 @@
         <v>9</v>
       </c>
       <c r="B30" s="16" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="C30" s="7" t="inlineStr">
         <is>
@@ -36766,7 +37436,7 @@
         <v>6</v>
       </c>
       <c r="B33" s="17" t="n">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="C33" s="10" t="inlineStr">
         <is>
@@ -36779,7 +37449,7 @@
         <v>5</v>
       </c>
       <c r="B34" s="16" t="n">
-        <v>140</v>
+        <v>150</v>
       </c>
       <c r="C34" s="7" t="inlineStr">
         <is>
@@ -36792,7 +37462,7 @@
         <v>4</v>
       </c>
       <c r="B35" s="17" t="n">
-        <v>261</v>
+        <v>256</v>
       </c>
       <c r="C35" s="10" t="inlineStr">
         <is>
@@ -36805,7 +37475,7 @@
         <v>3</v>
       </c>
       <c r="B36" s="16" t="n">
-        <v>479</v>
+        <v>490</v>
       </c>
       <c r="C36" s="7" t="inlineStr">
         <is>
@@ -36818,7 +37488,7 @@
         <v>2</v>
       </c>
       <c r="B37" s="17" t="n">
-        <v>958</v>
+        <v>936</v>
       </c>
       <c r="C37" s="10" t="inlineStr">
         <is>
@@ -36831,7 +37501,7 @@
         <v>1</v>
       </c>
       <c r="B38" s="16" t="n">
-        <v>1506</v>
+        <v>1526</v>
       </c>
       <c r="C38" s="7" t="inlineStr">
         <is>
@@ -39699,7 +40369,7 @@
       </c>
       <c r="B14" s="9" t="inlineStr">
         <is>
-          <t>CMCO</t>
+          <t>FIS</t>
         </is>
       </c>
       <c r="C14" s="17" t="n">
@@ -39707,12 +40377,12 @@
       </c>
       <c r="D14" s="10" t="inlineStr">
         <is>
-          <t>discretionary hurdle, repricing language, retirement carveout</t>
+          <t>repricing language</t>
         </is>
       </c>
       <c r="E14" s="6" t="inlineStr">
         <is>
-          <t>Participation — limited size</t>
+          <t>Concentrate (1 flag tolerable)</t>
         </is>
       </c>
     </row>
@@ -39722,7 +40392,7 @@
       </c>
       <c r="B15" s="6" t="inlineStr">
         <is>
-          <t>FIS</t>
+          <t>CMCO</t>
         </is>
       </c>
       <c r="C15" s="16" t="n">
@@ -39730,12 +40400,12 @@
       </c>
       <c r="D15" s="7" t="inlineStr">
         <is>
-          <t>repricing language</t>
+          <t>discretionary hurdle, repricing language, retirement carveout</t>
         </is>
       </c>
       <c r="E15" s="6" t="inlineStr">
         <is>
-          <t>Concentrate (1 flag tolerable)</t>
+          <t>Participation — limited size</t>
         </is>
       </c>
     </row>
@@ -40412,7 +41082,7 @@
       </c>
       <c r="B45" s="6" t="inlineStr">
         <is>
-          <t>RXST</t>
+          <t>METC</t>
         </is>
       </c>
       <c r="C45" s="16" t="n">
@@ -40420,12 +41090,12 @@
       </c>
       <c r="D45" s="7" t="inlineStr">
         <is>
-          <t>retirement carveout, single-trigger CIC</t>
-        </is>
-      </c>
-      <c r="E45" s="7" t="inlineStr">
-        <is>
-          <t>Material — basket diversify</t>
+          <t>repricing language</t>
+        </is>
+      </c>
+      <c r="E45" s="6" t="inlineStr">
+        <is>
+          <t>Concentrate (1 flag tolerable)</t>
         </is>
       </c>
     </row>
@@ -40435,7 +41105,7 @@
       </c>
       <c r="B46" s="9" t="inlineStr">
         <is>
-          <t>METC</t>
+          <t>NXST</t>
         </is>
       </c>
       <c r="C46" s="17" t="n">
@@ -40443,7 +41113,7 @@
       </c>
       <c r="D46" s="10" t="inlineStr">
         <is>
-          <t>repricing language</t>
+          <t>discretionary hurdle</t>
         </is>
       </c>
       <c r="E46" s="6" t="inlineStr">
@@ -40458,7 +41128,7 @@
       </c>
       <c r="B47" s="6" t="inlineStr">
         <is>
-          <t>NXST</t>
+          <t>RXST</t>
         </is>
       </c>
       <c r="C47" s="16" t="n">
@@ -40466,12 +41136,12 @@
       </c>
       <c r="D47" s="7" t="inlineStr">
         <is>
-          <t>discretionary hurdle</t>
-        </is>
-      </c>
-      <c r="E47" s="6" t="inlineStr">
-        <is>
-          <t>Concentrate (1 flag tolerable)</t>
+          <t>retirement carveout, single-trigger CIC</t>
+        </is>
+      </c>
+      <c r="E47" s="7" t="inlineStr">
+        <is>
+          <t>Material — basket diversify</t>
         </is>
       </c>
     </row>
